--- a/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
@@ -4520,8 +4520,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -4537,7 +4545,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4545,12 +4553,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4850,55 +4876,55 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4918,7 +4944,7 @@
       <c r="E2" t="s">
         <v>829</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>45698</v>
       </c>
       <c r="G2" t="s">
@@ -4928,7 +4954,7 @@
         <v>1353</v>
       </c>
       <c r="I2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="K2" t="s">
         <v>1356</v>
@@ -4956,7 +4982,7 @@
       <c r="E3" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>45714</v>
       </c>
       <c r="G3" t="s">
@@ -4966,7 +4992,7 @@
         <v>1353</v>
       </c>
       <c r="I3">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="K3" t="s">
         <v>1357</v>
@@ -4994,7 +5020,7 @@
       <c r="E4" t="s">
         <v>831</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>45714</v>
       </c>
       <c r="G4" t="s">
@@ -5004,7 +5030,7 @@
         <v>1353</v>
       </c>
       <c r="I4">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="K4" t="s">
         <v>1357</v>
@@ -5032,7 +5058,7 @@
       <c r="E5" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>45714</v>
       </c>
       <c r="G5" t="s">
@@ -5042,7 +5068,7 @@
         <v>1353</v>
       </c>
       <c r="I5">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="J5">
         <v>279</v>
@@ -5053,7 +5079,7 @@
       <c r="L5" t="s">
         <v>1367</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <v>45993</v>
       </c>
       <c r="Q5" t="b">
@@ -5076,7 +5102,7 @@
       <c r="E6" t="s">
         <v>833</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>45736</v>
       </c>
       <c r="G6" t="s">
@@ -5086,7 +5112,7 @@
         <v>1353</v>
       </c>
       <c r="I6">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J6">
         <v>153</v>
@@ -5097,7 +5123,7 @@
       <c r="L6" t="s">
         <v>1368</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="2">
         <v>45889</v>
       </c>
       <c r="Q6" t="b">
@@ -5120,7 +5146,7 @@
       <c r="E7" t="s">
         <v>834</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>45736</v>
       </c>
       <c r="G7" t="s">
@@ -5130,7 +5156,7 @@
         <v>1353</v>
       </c>
       <c r="I7">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J7">
         <v>112</v>
@@ -5141,7 +5167,7 @@
       <c r="L7" t="s">
         <v>1369</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="2">
         <v>45848</v>
       </c>
       <c r="O7" t="s">
@@ -5167,7 +5193,7 @@
       <c r="E8" t="s">
         <v>835</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>45736</v>
       </c>
       <c r="G8" t="s">
@@ -5196,7 +5222,7 @@
       <c r="E9" t="s">
         <v>836</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="2">
         <v>45736</v>
       </c>
       <c r="G9" t="s">
@@ -5206,7 +5232,7 @@
         <v>1353</v>
       </c>
       <c r="I9">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J9">
         <v>362</v>
@@ -5217,7 +5243,7 @@
       <c r="L9" t="s">
         <v>1370</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="2">
         <v>46098</v>
       </c>
       <c r="O9">
@@ -5243,7 +5269,7 @@
       <c r="E10" t="s">
         <v>837</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="2">
         <v>45736</v>
       </c>
       <c r="G10" t="s">
@@ -5253,7 +5279,7 @@
         <v>1353</v>
       </c>
       <c r="I10">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J10">
         <v>378</v>
@@ -5264,7 +5290,7 @@
       <c r="L10" t="s">
         <v>1371</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="2">
         <v>46114</v>
       </c>
       <c r="O10" t="s">
@@ -5290,7 +5316,7 @@
       <c r="E11" t="s">
         <v>838</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <v>45736</v>
       </c>
       <c r="G11" t="s">
@@ -5300,7 +5326,7 @@
         <v>1353</v>
       </c>
       <c r="I11">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J11">
         <v>112</v>
@@ -5311,7 +5337,7 @@
       <c r="L11" t="s">
         <v>1369</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="2">
         <v>45848</v>
       </c>
       <c r="O11" t="s">
@@ -5337,7 +5363,7 @@
       <c r="E12" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="2">
         <v>45736</v>
       </c>
       <c r="G12" t="s">
@@ -5347,7 +5373,7 @@
         <v>1353</v>
       </c>
       <c r="I12">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J12">
         <v>124</v>
@@ -5358,7 +5384,7 @@
       <c r="L12" t="s">
         <v>1372</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="2">
         <v>45860</v>
       </c>
       <c r="Q12" t="b">
@@ -5381,7 +5407,7 @@
       <c r="E13" t="s">
         <v>840</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <v>45736</v>
       </c>
       <c r="G13" t="s">
@@ -5410,7 +5436,7 @@
       <c r="E14" t="s">
         <v>841</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="2">
         <v>45736</v>
       </c>
       <c r="G14" t="s">
@@ -5420,7 +5446,7 @@
         <v>1353</v>
       </c>
       <c r="I14">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J14">
         <v>64</v>
@@ -5431,7 +5457,7 @@
       <c r="L14" t="s">
         <v>1373</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N14" s="2">
         <v>45800</v>
       </c>
       <c r="Q14" t="b">
@@ -5454,7 +5480,7 @@
       <c r="E15" t="s">
         <v>842</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="2">
         <v>45736</v>
       </c>
       <c r="G15" t="s">
@@ -5464,7 +5490,7 @@
         <v>1353</v>
       </c>
       <c r="I15">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="K15" t="s">
         <v>1359</v>
@@ -5492,7 +5518,7 @@
       <c r="E16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <v>45736</v>
       </c>
       <c r="G16" t="s">
@@ -5502,7 +5528,7 @@
         <v>1353</v>
       </c>
       <c r="I16">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="K16" t="s">
         <v>1356</v>
@@ -5530,7 +5556,7 @@
       <c r="E17" t="s">
         <v>844</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="2">
         <v>45736</v>
       </c>
       <c r="G17" t="s">
@@ -5540,7 +5566,7 @@
         <v>1353</v>
       </c>
       <c r="I17">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J17">
         <v>161</v>
@@ -5551,7 +5577,7 @@
       <c r="L17" t="s">
         <v>1368</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17" s="2">
         <v>45897</v>
       </c>
       <c r="Q17" t="b">
@@ -5574,7 +5600,7 @@
       <c r="E18" t="s">
         <v>845</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <v>45736</v>
       </c>
       <c r="G18" t="s">
@@ -5584,7 +5610,7 @@
         <v>1353</v>
       </c>
       <c r="I18">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J18">
         <v>66</v>
@@ -5595,7 +5621,7 @@
       <c r="L18" t="s">
         <v>1373</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="2">
         <v>45802</v>
       </c>
       <c r="Q18" t="b">
@@ -5618,7 +5644,7 @@
       <c r="E19" t="s">
         <v>846</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="2">
         <v>45736</v>
       </c>
       <c r="G19" t="s">
@@ -5647,7 +5673,7 @@
       <c r="E20" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="2">
         <v>45736</v>
       </c>
       <c r="G20" t="s">
@@ -5657,7 +5683,7 @@
         <v>1353</v>
       </c>
       <c r="I20">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J20">
         <v>399</v>
@@ -5668,7 +5694,7 @@
       <c r="L20" t="s">
         <v>1374</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20" s="2">
         <v>46135</v>
       </c>
       <c r="Q20" t="b">
@@ -5691,7 +5717,7 @@
       <c r="E21" t="s">
         <v>848</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="2">
         <v>45736</v>
       </c>
       <c r="G21" t="s">
@@ -5720,7 +5746,7 @@
       <c r="E22" t="s">
         <v>849</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="2">
         <v>45736</v>
       </c>
       <c r="G22" t="s">
@@ -5730,7 +5756,7 @@
         <v>1353</v>
       </c>
       <c r="I22">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="K22" t="s">
         <v>1360</v>
@@ -5758,7 +5784,7 @@
       <c r="E23" t="s">
         <v>850</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <v>45736</v>
       </c>
       <c r="G23" t="s">
@@ -5768,7 +5794,7 @@
         <v>1353</v>
       </c>
       <c r="I23">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J23">
         <v>229</v>
@@ -5779,7 +5805,7 @@
       <c r="L23" t="s">
         <v>1375</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23" s="2">
         <v>45965</v>
       </c>
       <c r="P23" t="s">
@@ -5805,7 +5831,7 @@
       <c r="E24" t="s">
         <v>851</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="2">
         <v>45736</v>
       </c>
       <c r="G24" t="s">
@@ -5834,7 +5860,7 @@
       <c r="E25" t="s">
         <v>852</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="2">
         <v>45736</v>
       </c>
       <c r="G25" t="s">
@@ -5863,7 +5889,7 @@
       <c r="E26" t="s">
         <v>853</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="2">
         <v>45736</v>
       </c>
       <c r="G26" t="s">
@@ -5873,7 +5899,7 @@
         <v>1353</v>
       </c>
       <c r="I26">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J26">
         <v>155</v>
@@ -5884,7 +5910,7 @@
       <c r="L26" t="s">
         <v>1376</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N26" s="2">
         <v>45891</v>
       </c>
       <c r="P26" t="s">
@@ -5910,7 +5936,7 @@
       <c r="E27" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="2">
         <v>45736</v>
       </c>
       <c r="G27" t="s">
@@ -5920,7 +5946,7 @@
         <v>1353</v>
       </c>
       <c r="I27">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="K27" t="s">
         <v>1360</v>
@@ -5948,7 +5974,7 @@
       <c r="E28" t="s">
         <v>855</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="2">
         <v>45736</v>
       </c>
       <c r="G28" t="s">
@@ -5977,7 +6003,7 @@
       <c r="E29" t="s">
         <v>856</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="2">
         <v>45736</v>
       </c>
       <c r="G29" t="s">
@@ -6006,7 +6032,7 @@
       <c r="E30" t="s">
         <v>857</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="2">
         <v>45736</v>
       </c>
       <c r="G30" t="s">
@@ -6016,7 +6042,7 @@
         <v>1353</v>
       </c>
       <c r="I30">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J30">
         <v>209</v>
@@ -6027,7 +6053,7 @@
       <c r="L30" t="s">
         <v>1377</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30" s="2">
         <v>45945</v>
       </c>
       <c r="Q30" t="b">
@@ -6050,7 +6076,7 @@
       <c r="E31" t="s">
         <v>858</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="2">
         <v>45736</v>
       </c>
       <c r="G31" t="s">
@@ -6079,7 +6105,7 @@
       <c r="E32" t="s">
         <v>859</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="2">
         <v>45736</v>
       </c>
       <c r="G32" t="s">
@@ -6089,7 +6115,7 @@
         <v>1353</v>
       </c>
       <c r="I32">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="K32" t="s">
         <v>1356</v>
@@ -6117,7 +6143,7 @@
       <c r="E33" t="s">
         <v>860</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="2">
         <v>45736</v>
       </c>
       <c r="G33" t="s">
@@ -6146,7 +6172,7 @@
       <c r="E34" t="s">
         <v>861</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="2">
         <v>45736</v>
       </c>
       <c r="G34" t="s">
@@ -6175,7 +6201,7 @@
       <c r="E35" t="s">
         <v>862</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="2">
         <v>45736</v>
       </c>
       <c r="G35" t="s">
@@ -6204,7 +6230,7 @@
       <c r="E36" t="s">
         <v>863</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="2">
         <v>45736</v>
       </c>
       <c r="G36" t="s">
@@ -6233,7 +6259,7 @@
       <c r="E37" t="s">
         <v>864</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="2">
         <v>45736</v>
       </c>
       <c r="G37" t="s">
@@ -6262,7 +6288,7 @@
       <c r="E38" t="s">
         <v>844</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="2">
         <v>45736</v>
       </c>
       <c r="G38" t="s">
@@ -6288,7 +6314,7 @@
       <c r="D39" t="s">
         <v>731</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="2">
         <v>45736</v>
       </c>
       <c r="G39" t="s">
@@ -6298,7 +6324,7 @@
         <v>1353</v>
       </c>
       <c r="I39">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="K39" t="s">
         <v>1361</v>
@@ -6323,7 +6349,7 @@
       <c r="D40" t="s">
         <v>731</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="2">
         <v>45736</v>
       </c>
       <c r="G40" t="s">
@@ -6333,7 +6359,7 @@
         <v>1353</v>
       </c>
       <c r="I40">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="K40" t="s">
         <v>1359</v>
@@ -6361,7 +6387,7 @@
       <c r="E41" t="s">
         <v>865</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="2">
         <v>45736</v>
       </c>
       <c r="G41" t="s">
@@ -6390,7 +6416,7 @@
       <c r="E42" t="s">
         <v>866</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="2">
         <v>45736</v>
       </c>
       <c r="G42" t="s">
@@ -6419,7 +6445,7 @@
       <c r="E43" t="s">
         <v>867</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="2">
         <v>45736</v>
       </c>
       <c r="G43" t="s">
@@ -6454,7 +6480,7 @@
       <c r="E44" t="s">
         <v>868</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="2">
         <v>45769</v>
       </c>
       <c r="G44" t="s">
@@ -6464,7 +6490,7 @@
         <v>1353</v>
       </c>
       <c r="I44">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="J44">
         <v>87</v>
@@ -6475,7 +6501,7 @@
       <c r="L44" t="s">
         <v>1378</v>
       </c>
-      <c r="N44" s="1">
+      <c r="N44" s="2">
         <v>45856</v>
       </c>
       <c r="P44" t="s">
@@ -6501,7 +6527,7 @@
       <c r="E45" t="s">
         <v>869</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="2">
         <v>45769</v>
       </c>
       <c r="G45" t="s">
@@ -6511,7 +6537,7 @@
         <v>1353</v>
       </c>
       <c r="I45">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="J45">
         <v>331</v>
@@ -6522,7 +6548,7 @@
       <c r="L45" t="s">
         <v>1379</v>
       </c>
-      <c r="N45" s="1">
+      <c r="N45" s="2">
         <v>46100</v>
       </c>
       <c r="O45">
@@ -6548,7 +6574,7 @@
       <c r="E46" t="s">
         <v>870</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="2">
         <v>45769</v>
       </c>
       <c r="G46" t="s">
@@ -6558,7 +6584,7 @@
         <v>1353</v>
       </c>
       <c r="I46">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K46" t="s">
         <v>1360</v>
@@ -6586,7 +6612,7 @@
       <c r="E47" t="s">
         <v>871</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="2">
         <v>45769</v>
       </c>
       <c r="G47" t="s">
@@ -6596,7 +6622,7 @@
         <v>1353</v>
       </c>
       <c r="I47">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="J47">
         <v>344</v>
@@ -6607,7 +6633,7 @@
       <c r="L47" t="s">
         <v>1380</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N47" s="2">
         <v>46113</v>
       </c>
       <c r="P47" t="s">
@@ -6633,7 +6659,7 @@
       <c r="E48" t="s">
         <v>872</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="2">
         <v>45769</v>
       </c>
       <c r="G48" t="s">
@@ -6643,7 +6669,7 @@
         <v>1353</v>
       </c>
       <c r="I48">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K48" t="s">
         <v>1360</v>
@@ -6671,7 +6697,7 @@
       <c r="E49" t="s">
         <v>873</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="2">
         <v>45769</v>
       </c>
       <c r="G49" t="s">
@@ -6700,7 +6726,7 @@
       <c r="E50" t="s">
         <v>874</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="2">
         <v>45769</v>
       </c>
       <c r="G50" t="s">
@@ -6710,7 +6736,7 @@
         <v>1353</v>
       </c>
       <c r="I50">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K50" t="s">
         <v>1360</v>
@@ -6738,7 +6764,7 @@
       <c r="E51" t="s">
         <v>875</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="2">
         <v>45769</v>
       </c>
       <c r="G51" t="s">
@@ -6767,7 +6793,7 @@
       <c r="E52" t="s">
         <v>876</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="2">
         <v>45769</v>
       </c>
       <c r="G52" t="s">
@@ -6777,7 +6803,7 @@
         <v>1353</v>
       </c>
       <c r="I52">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K52" t="s">
         <v>1356</v>
@@ -6805,7 +6831,7 @@
       <c r="E53" t="s">
         <v>877</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="2">
         <v>45769</v>
       </c>
       <c r="G53" t="s">
@@ -6815,7 +6841,7 @@
         <v>1353</v>
       </c>
       <c r="I53">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K53" t="s">
         <v>1357</v>
@@ -6843,7 +6869,7 @@
       <c r="E54" t="s">
         <v>878</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="2">
         <v>45769</v>
       </c>
       <c r="G54" t="s">
@@ -6853,7 +6879,7 @@
         <v>1353</v>
       </c>
       <c r="I54">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K54" t="s">
         <v>1357</v>
@@ -6881,7 +6907,7 @@
       <c r="E55" t="s">
         <v>879</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="2">
         <v>45769</v>
       </c>
       <c r="G55" t="s">
@@ -6910,7 +6936,7 @@
       <c r="E56" t="s">
         <v>880</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="2">
         <v>45769</v>
       </c>
       <c r="G56" t="s">
@@ -6939,7 +6965,7 @@
       <c r="E57" t="s">
         <v>881</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="2">
         <v>45769</v>
       </c>
       <c r="G57" t="s">
@@ -6949,7 +6975,7 @@
         <v>1353</v>
       </c>
       <c r="I57">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K57" t="s">
         <v>1360</v>
@@ -6977,7 +7003,7 @@
       <c r="E58" t="s">
         <v>882</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="2">
         <v>45769</v>
       </c>
       <c r="G58" t="s">
@@ -7006,7 +7032,7 @@
       <c r="E59" t="s">
         <v>883</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="2">
         <v>45769</v>
       </c>
       <c r="G59" t="s">
@@ -7035,7 +7061,7 @@
       <c r="E60" t="s">
         <v>884</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="2">
         <v>45769</v>
       </c>
       <c r="G60" t="s">
@@ -7064,7 +7090,7 @@
       <c r="E61" t="s">
         <v>885</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="2">
         <v>45769</v>
       </c>
       <c r="G61" t="s">
@@ -7093,7 +7119,7 @@
       <c r="E62" t="s">
         <v>886</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="2">
         <v>45770</v>
       </c>
       <c r="G62" t="s">
@@ -7122,7 +7148,7 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="2">
         <v>45799</v>
       </c>
       <c r="G63" t="s">
@@ -7132,7 +7158,7 @@
         <v>1353</v>
       </c>
       <c r="I63">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="J63">
         <v>293</v>
@@ -7143,7 +7169,7 @@
       <c r="L63" t="s">
         <v>1381</v>
       </c>
-      <c r="N63" s="1">
+      <c r="N63" s="2">
         <v>46092</v>
       </c>
       <c r="P63" t="s">
@@ -7169,7 +7195,7 @@
       <c r="E64" t="s">
         <v>888</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="2">
         <v>45799</v>
       </c>
       <c r="G64" t="s">
@@ -7179,7 +7205,7 @@
         <v>1353</v>
       </c>
       <c r="I64">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="J64">
         <v>320</v>
@@ -7190,7 +7216,7 @@
       <c r="L64" t="s">
         <v>1382</v>
       </c>
-      <c r="N64" s="1">
+      <c r="N64" s="2">
         <v>46119</v>
       </c>
       <c r="Q64" t="b">
@@ -7213,7 +7239,7 @@
       <c r="E65" t="s">
         <v>889</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="2">
         <v>45799</v>
       </c>
       <c r="G65" t="s">
@@ -7242,7 +7268,7 @@
       <c r="E66" t="s">
         <v>890</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="2">
         <v>45799</v>
       </c>
       <c r="G66" t="s">
@@ -7271,7 +7297,7 @@
       <c r="E67" t="s">
         <v>891</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="2">
         <v>45799</v>
       </c>
       <c r="G67" t="s">
@@ -7300,7 +7326,7 @@
       <c r="E68" t="s">
         <v>892</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="2">
         <v>45799</v>
       </c>
       <c r="G68" t="s">
@@ -7329,7 +7355,7 @@
       <c r="E69" t="s">
         <v>893</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="2">
         <v>45803</v>
       </c>
       <c r="G69" t="s">
@@ -7358,7 +7384,7 @@
       <c r="E70" t="s">
         <v>894</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="2">
         <v>45803</v>
       </c>
       <c r="G70" t="s">
@@ -7368,7 +7394,7 @@
         <v>1353</v>
       </c>
       <c r="I70">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J70">
         <v>429</v>
@@ -7379,7 +7405,7 @@
       <c r="L70" t="s">
         <v>1383</v>
       </c>
-      <c r="N70" s="1">
+      <c r="N70" s="2">
         <v>46232</v>
       </c>
       <c r="Q70" t="b">
@@ -7402,7 +7428,7 @@
       <c r="E71" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="2">
         <v>45803</v>
       </c>
       <c r="G71" t="s">
@@ -7412,7 +7438,7 @@
         <v>1353</v>
       </c>
       <c r="I71">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J71">
         <v>429</v>
@@ -7423,7 +7449,7 @@
       <c r="L71" t="s">
         <v>1383</v>
       </c>
-      <c r="N71" s="1">
+      <c r="N71" s="2">
         <v>46232</v>
       </c>
       <c r="Q71" t="b">
@@ -7446,7 +7472,7 @@
       <c r="E72" t="s">
         <v>896</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="2">
         <v>45803</v>
       </c>
       <c r="G72" t="s">
@@ -7475,7 +7501,7 @@
       <c r="E73" t="s">
         <v>897</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="2">
         <v>45803</v>
       </c>
       <c r="G73" t="s">
@@ -7485,7 +7511,7 @@
         <v>1353</v>
       </c>
       <c r="I73">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="K73" t="s">
         <v>1356</v>
@@ -7513,7 +7539,7 @@
       <c r="E74" t="s">
         <v>896</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="2">
         <v>45803</v>
       </c>
       <c r="G74" t="s">
@@ -7542,7 +7568,7 @@
       <c r="E75" t="s">
         <v>898</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="2">
         <v>45803</v>
       </c>
       <c r="G75" t="s">
@@ -7552,7 +7578,7 @@
         <v>1353</v>
       </c>
       <c r="I75">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J75">
         <v>429</v>
@@ -7563,7 +7589,7 @@
       <c r="L75" t="s">
         <v>1383</v>
       </c>
-      <c r="N75" s="1">
+      <c r="N75" s="2">
         <v>46232</v>
       </c>
       <c r="Q75" t="b">
@@ -7586,7 +7612,7 @@
       <c r="E76" t="s">
         <v>899</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="2">
         <v>45803</v>
       </c>
       <c r="G76" t="s">
@@ -7596,7 +7622,7 @@
         <v>1353</v>
       </c>
       <c r="I76">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="K76" t="s">
         <v>1363</v>
@@ -7621,7 +7647,7 @@
       <c r="E77" t="s">
         <v>900</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="2">
         <v>45803</v>
       </c>
       <c r="G77" t="s">
@@ -7650,7 +7676,7 @@
       <c r="E78" t="s">
         <v>901</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78" s="2">
         <v>45803</v>
       </c>
       <c r="G78" t="s">
@@ -7679,7 +7705,7 @@
       <c r="E79" t="s">
         <v>902</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="2">
         <v>45803</v>
       </c>
       <c r="G79" t="s">
@@ -7689,7 +7715,7 @@
         <v>1353</v>
       </c>
       <c r="I79">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="K79" t="s">
         <v>1363</v>
@@ -7714,7 +7740,7 @@
       <c r="E80" t="s">
         <v>903</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="2">
         <v>45803</v>
       </c>
       <c r="G80" t="s">
@@ -7724,7 +7750,7 @@
         <v>1353</v>
       </c>
       <c r="I80">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J80">
         <v>429</v>
@@ -7735,7 +7761,7 @@
       <c r="L80" t="s">
         <v>1383</v>
       </c>
-      <c r="N80" s="1">
+      <c r="N80" s="2">
         <v>46232</v>
       </c>
       <c r="Q80" t="b">
@@ -7758,7 +7784,7 @@
       <c r="E81" t="s">
         <v>904</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="2">
         <v>45813</v>
       </c>
       <c r="G81" t="s">
@@ -7787,7 +7813,7 @@
       <c r="E82" t="s">
         <v>905</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="2">
         <v>45813</v>
       </c>
       <c r="G82" t="s">
@@ -7797,7 +7823,7 @@
         <v>1353</v>
       </c>
       <c r="I82">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K82" t="s">
         <v>1360</v>
@@ -7825,7 +7851,7 @@
       <c r="E83" t="s">
         <v>906</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="2">
         <v>45813</v>
       </c>
       <c r="G83" t="s">
@@ -7854,7 +7880,7 @@
       <c r="E84" t="s">
         <v>907</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="2">
         <v>45813</v>
       </c>
       <c r="G84" t="s">
@@ -7864,7 +7890,7 @@
         <v>1353</v>
       </c>
       <c r="I84">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="J84">
         <v>40</v>
@@ -7875,7 +7901,7 @@
       <c r="L84" t="s">
         <v>1384</v>
       </c>
-      <c r="N84" s="1">
+      <c r="N84" s="2">
         <v>45853</v>
       </c>
       <c r="O84">
@@ -7901,7 +7927,7 @@
       <c r="E85" t="s">
         <v>908</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85" s="2">
         <v>45813</v>
       </c>
       <c r="G85" t="s">
@@ -7911,7 +7937,7 @@
         <v>1353</v>
       </c>
       <c r="I85">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K85" t="s">
         <v>1357</v>
@@ -7939,7 +7965,7 @@
       <c r="E86" t="s">
         <v>909</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="2">
         <v>45813</v>
       </c>
       <c r="G86" t="s">
@@ -7949,7 +7975,7 @@
         <v>1353</v>
       </c>
       <c r="I86">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K86" t="s">
         <v>1357</v>
@@ -7977,7 +8003,7 @@
       <c r="E87" t="s">
         <v>910</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="2">
         <v>45813</v>
       </c>
       <c r="G87" t="s">
@@ -7987,7 +8013,7 @@
         <v>1353</v>
       </c>
       <c r="I87">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="J87">
         <v>-16</v>
@@ -7998,7 +8024,7 @@
       <c r="L87" t="s">
         <v>1385</v>
       </c>
-      <c r="N87" s="1">
+      <c r="N87" s="2">
         <v>45797</v>
       </c>
       <c r="O87" t="s">
@@ -8024,7 +8050,7 @@
       <c r="E88" t="s">
         <v>911</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="2">
         <v>45813</v>
       </c>
       <c r="G88" t="s">
@@ -8039,7 +8065,7 @@
       <c r="L88" t="s">
         <v>1386</v>
       </c>
-      <c r="N88" s="1">
+      <c r="N88" s="2">
         <v>46195</v>
       </c>
       <c r="Q88" t="b">
@@ -8062,7 +8088,7 @@
       <c r="E89" t="s">
         <v>912</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89" s="2">
         <v>45813</v>
       </c>
       <c r="G89" t="s">
@@ -8077,7 +8103,7 @@
       <c r="L89" t="s">
         <v>1386</v>
       </c>
-      <c r="N89" s="1">
+      <c r="N89" s="2">
         <v>46195</v>
       </c>
       <c r="Q89" t="b">
@@ -8100,7 +8126,7 @@
       <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90" s="2">
         <v>45831</v>
       </c>
       <c r="G90" t="s">
@@ -8110,7 +8136,7 @@
         <v>1353</v>
       </c>
       <c r="I90">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="K90" t="s">
         <v>1330</v>
@@ -8141,7 +8167,7 @@
       <c r="E91" t="s">
         <v>914</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="2">
         <v>45831</v>
       </c>
       <c r="G91" t="s">
@@ -8151,7 +8177,7 @@
         <v>1353</v>
       </c>
       <c r="I91">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J91">
         <v>308</v>
@@ -8162,7 +8188,7 @@
       <c r="L91" t="s">
         <v>1388</v>
       </c>
-      <c r="N91" s="1">
+      <c r="N91" s="2">
         <v>46139</v>
       </c>
       <c r="Q91" t="b">
@@ -8182,7 +8208,7 @@
       <c r="D92" t="s">
         <v>748</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92" s="2">
         <v>45831</v>
       </c>
       <c r="G92" t="s">
@@ -8211,7 +8237,7 @@
       <c r="E93" t="s">
         <v>915</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93" s="2">
         <v>45831</v>
       </c>
       <c r="G93" t="s">
@@ -8221,7 +8247,7 @@
         <v>1353</v>
       </c>
       <c r="I93">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J93">
         <v>308</v>
@@ -8232,7 +8258,7 @@
       <c r="L93" t="s">
         <v>1388</v>
       </c>
-      <c r="N93" s="1">
+      <c r="N93" s="2">
         <v>46139</v>
       </c>
       <c r="Q93" t="b">
@@ -8255,7 +8281,7 @@
       <c r="E94" t="s">
         <v>916</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94" s="2">
         <v>45831</v>
       </c>
       <c r="G94" t="s">
@@ -8265,7 +8291,7 @@
         <v>1353</v>
       </c>
       <c r="I94">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="K94" t="s">
         <v>1360</v>
@@ -8293,7 +8319,7 @@
       <c r="E95" t="s">
         <v>917</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95" s="2">
         <v>45831</v>
       </c>
       <c r="G95" t="s">
@@ -8303,7 +8329,7 @@
         <v>1353</v>
       </c>
       <c r="I95">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J95">
         <v>308</v>
@@ -8314,7 +8340,7 @@
       <c r="L95" t="s">
         <v>1388</v>
       </c>
-      <c r="N95" s="1">
+      <c r="N95" s="2">
         <v>46139</v>
       </c>
       <c r="Q95" t="b">
@@ -8337,7 +8363,7 @@
       <c r="E96" t="s">
         <v>918</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96" s="2">
         <v>45831</v>
       </c>
       <c r="G96" t="s">
@@ -8347,7 +8373,7 @@
         <v>1353</v>
       </c>
       <c r="I96">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J96">
         <v>17</v>
@@ -8358,7 +8384,7 @@
       <c r="L96" t="s">
         <v>1369</v>
       </c>
-      <c r="N96" s="1">
+      <c r="N96" s="2">
         <v>45848</v>
       </c>
       <c r="O96" t="s">
@@ -8384,7 +8410,7 @@
       <c r="E97" t="s">
         <v>919</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="2">
         <v>45840</v>
       </c>
       <c r="G97" t="s">
@@ -8394,7 +8420,7 @@
         <v>1353</v>
       </c>
       <c r="I97">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J97">
         <v>20</v>
@@ -8405,7 +8431,7 @@
       <c r="L97" t="s">
         <v>1389</v>
       </c>
-      <c r="N97" s="1">
+      <c r="N97" s="2">
         <v>45860</v>
       </c>
       <c r="P97" t="s">
@@ -8431,7 +8457,7 @@
       <c r="E98" t="s">
         <v>920</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="2">
         <v>45840</v>
       </c>
       <c r="G98" t="s">
@@ -8441,7 +8467,7 @@
         <v>1353</v>
       </c>
       <c r="I98">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K98" t="s">
         <v>1360</v>
@@ -8469,7 +8495,7 @@
       <c r="E99" t="s">
         <v>921</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99" s="2">
         <v>45840</v>
       </c>
       <c r="G99" t="s">
@@ -8498,7 +8524,7 @@
       <c r="E100" t="s">
         <v>922</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100" s="2">
         <v>45840</v>
       </c>
       <c r="G100" t="s">
@@ -8508,7 +8534,7 @@
         <v>1353</v>
       </c>
       <c r="I100">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J100">
         <v>348</v>
@@ -8519,7 +8545,7 @@
       <c r="L100" t="s">
         <v>1388</v>
       </c>
-      <c r="N100" s="1">
+      <c r="N100" s="2">
         <v>46188</v>
       </c>
       <c r="Q100" t="b">
@@ -8542,7 +8568,7 @@
       <c r="E101" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101" s="2">
         <v>45840</v>
       </c>
       <c r="G101" t="s">
@@ -8571,7 +8597,7 @@
       <c r="E102" t="s">
         <v>924</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102" s="2">
         <v>45840</v>
       </c>
       <c r="G102" t="s">
@@ -8600,7 +8626,7 @@
       <c r="E103" t="s">
         <v>925</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103" s="2">
         <v>45840</v>
       </c>
       <c r="G103" t="s">
@@ -8629,7 +8655,7 @@
       <c r="E104" t="s">
         <v>926</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104" s="2">
         <v>45840</v>
       </c>
       <c r="G104" t="s">
@@ -8639,7 +8665,7 @@
         <v>1353</v>
       </c>
       <c r="I104">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J104">
         <v>348</v>
@@ -8650,7 +8676,7 @@
       <c r="L104" t="s">
         <v>1388</v>
       </c>
-      <c r="N104" s="1">
+      <c r="N104" s="2">
         <v>46188</v>
       </c>
       <c r="Q104" t="b">
@@ -8673,7 +8699,7 @@
       <c r="E105" t="s">
         <v>927</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105" s="2">
         <v>45840</v>
       </c>
       <c r="G105" t="s">
@@ -8683,7 +8709,7 @@
         <v>1353</v>
       </c>
       <c r="I105">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J105">
         <v>348</v>
@@ -8694,7 +8720,7 @@
       <c r="L105" t="s">
         <v>1388</v>
       </c>
-      <c r="N105" s="1">
+      <c r="N105" s="2">
         <v>46188</v>
       </c>
       <c r="Q105" t="b">
@@ -8717,7 +8743,7 @@
       <c r="E106" t="s">
         <v>928</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106" s="2">
         <v>45840</v>
       </c>
       <c r="G106" t="s">
@@ -8727,7 +8753,7 @@
         <v>1353</v>
       </c>
       <c r="I106">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J106">
         <v>49</v>
@@ -8738,7 +8764,7 @@
       <c r="L106" t="s">
         <v>1390</v>
       </c>
-      <c r="N106" s="1">
+      <c r="N106" s="2">
         <v>45889</v>
       </c>
       <c r="Q106" t="b">
@@ -8761,7 +8787,7 @@
       <c r="E107" t="s">
         <v>929</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="2">
         <v>45840</v>
       </c>
       <c r="G107" t="s">
@@ -8771,7 +8797,7 @@
         <v>1353</v>
       </c>
       <c r="I107">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J107">
         <v>36</v>
@@ -8782,7 +8808,7 @@
       <c r="L107" t="s">
         <v>1391</v>
       </c>
-      <c r="N107" s="1">
+      <c r="N107" s="2">
         <v>45876</v>
       </c>
       <c r="Q107" t="b">
@@ -8805,7 +8831,7 @@
       <c r="E108" t="s">
         <v>930</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108" s="2">
         <v>45840</v>
       </c>
       <c r="G108" t="s">
@@ -8815,7 +8841,7 @@
         <v>1353</v>
       </c>
       <c r="I108">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K108" t="s">
         <v>1357</v>
@@ -8843,7 +8869,7 @@
       <c r="E109" t="s">
         <v>931</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109" s="2">
         <v>45840</v>
       </c>
       <c r="G109" t="s">
@@ -8853,7 +8879,7 @@
         <v>1353</v>
       </c>
       <c r="I109">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K109" t="s">
         <v>1357</v>
@@ -8881,7 +8907,7 @@
       <c r="E110" t="s">
         <v>932</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="2">
         <v>45840</v>
       </c>
       <c r="G110" t="s">
@@ -8910,7 +8936,7 @@
       <c r="E111" t="s">
         <v>933</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="2">
         <v>45840</v>
       </c>
       <c r="G111" t="s">
@@ -8939,7 +8965,7 @@
       <c r="E112" t="s">
         <v>934</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112" s="2">
         <v>45840</v>
       </c>
       <c r="G112" t="s">
@@ -8968,7 +8994,7 @@
       <c r="E113" t="s">
         <v>935</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113" s="2">
         <v>45840</v>
       </c>
       <c r="G113" t="s">
@@ -8997,7 +9023,7 @@
       <c r="E114" t="s">
         <v>936</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114" s="2">
         <v>45840</v>
       </c>
       <c r="G114" t="s">
@@ -9026,7 +9052,7 @@
       <c r="E115" t="s">
         <v>937</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115" s="2">
         <v>45840</v>
       </c>
       <c r="G115" t="s">
@@ -9036,7 +9062,7 @@
         <v>1353</v>
       </c>
       <c r="I115">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K115" t="s">
         <v>1357</v>
@@ -9064,7 +9090,7 @@
       <c r="E116" t="s">
         <v>938</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116" s="2">
         <v>45840</v>
       </c>
       <c r="G116" t="s">
@@ -9074,7 +9100,7 @@
         <v>1353</v>
       </c>
       <c r="I116">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K116" t="s">
         <v>1357</v>
@@ -9102,7 +9128,7 @@
       <c r="E117" t="s">
         <v>939</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117" s="2">
         <v>45840</v>
       </c>
       <c r="G117" t="s">
@@ -9112,7 +9138,7 @@
         <v>1353</v>
       </c>
       <c r="I117">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K117" t="s">
         <v>1357</v>
@@ -9140,7 +9166,7 @@
       <c r="E118" t="s">
         <v>940</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118" s="2">
         <v>45840</v>
       </c>
       <c r="G118" t="s">
@@ -9150,7 +9176,7 @@
         <v>1353</v>
       </c>
       <c r="I118">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K118" t="s">
         <v>1357</v>
@@ -9178,7 +9204,7 @@
       <c r="E119" t="s">
         <v>941</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119" s="2">
         <v>45840</v>
       </c>
       <c r="G119" t="s">
@@ -9188,7 +9214,7 @@
         <v>1353</v>
       </c>
       <c r="I119">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K119" t="s">
         <v>1357</v>
@@ -9216,7 +9242,7 @@
       <c r="E120" t="s">
         <v>942</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120" s="2">
         <v>45840</v>
       </c>
       <c r="G120" t="s">
@@ -9226,7 +9252,7 @@
         <v>1353</v>
       </c>
       <c r="I120">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K120" t="s">
         <v>1357</v>
@@ -9254,7 +9280,7 @@
       <c r="E121" t="s">
         <v>943</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="2">
         <v>45849</v>
       </c>
       <c r="G121" t="s">
@@ -9264,7 +9290,7 @@
         <v>1353</v>
       </c>
       <c r="I121">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J121">
         <v>251</v>
@@ -9275,7 +9301,7 @@
       <c r="L121" t="s">
         <v>1379</v>
       </c>
-      <c r="N121" s="1">
+      <c r="N121" s="2">
         <v>46100</v>
       </c>
       <c r="O121">
@@ -9301,7 +9327,7 @@
       <c r="E122" t="s">
         <v>944</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F122" s="2">
         <v>45849</v>
       </c>
       <c r="G122" t="s">
@@ -9311,7 +9337,7 @@
         <v>1353</v>
       </c>
       <c r="I122">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K122" t="s">
         <v>1357</v>
@@ -9339,7 +9365,7 @@
       <c r="E123" t="s">
         <v>945</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F123" s="2">
         <v>45849</v>
       </c>
       <c r="G123" t="s">
@@ -9368,7 +9394,7 @@
       <c r="E124" t="s">
         <v>946</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124" s="2">
         <v>45853</v>
       </c>
       <c r="G124" t="s">
@@ -9378,7 +9404,7 @@
         <v>1353</v>
       </c>
       <c r="I124">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K124" t="s">
         <v>1357</v>
@@ -9406,7 +9432,7 @@
       <c r="E125" t="s">
         <v>947</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125" s="2">
         <v>45855</v>
       </c>
       <c r="G125" t="s">
@@ -9416,7 +9442,7 @@
         <v>1353</v>
       </c>
       <c r="I125">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="K125" t="s">
         <v>1363</v>
@@ -9444,7 +9470,7 @@
       <c r="E126" t="s">
         <v>948</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126" s="2">
         <v>45855</v>
       </c>
       <c r="G126" t="s">
@@ -9473,7 +9499,7 @@
       <c r="E127" t="s">
         <v>949</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127" s="2">
         <v>45856</v>
       </c>
       <c r="G127" t="s">
@@ -9502,7 +9528,7 @@
       <c r="E128" t="s">
         <v>950</v>
       </c>
-      <c r="F128" s="1">
+      <c r="F128" s="2">
         <v>45869</v>
       </c>
       <c r="G128" t="s">
@@ -9512,7 +9538,7 @@
         <v>1353</v>
       </c>
       <c r="I128">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="K128" t="s">
         <v>1357</v>
@@ -9540,7 +9566,7 @@
       <c r="E129" t="s">
         <v>951</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F129" s="2">
         <v>45869</v>
       </c>
       <c r="G129" t="s">
@@ -9550,7 +9576,7 @@
         <v>1353</v>
       </c>
       <c r="I129">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="K129" t="s">
         <v>1356</v>
@@ -9578,7 +9604,7 @@
       <c r="E130" t="s">
         <v>952</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F130" s="2">
         <v>45869</v>
       </c>
       <c r="G130" t="s">
@@ -9588,7 +9614,7 @@
         <v>1353</v>
       </c>
       <c r="I130">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="J130">
         <v>47</v>
@@ -9599,7 +9625,7 @@
       <c r="L130" t="s">
         <v>1392</v>
       </c>
-      <c r="N130" s="1">
+      <c r="N130" s="2">
         <v>45916</v>
       </c>
       <c r="O130">
@@ -9625,7 +9651,7 @@
       <c r="E131" t="s">
         <v>953</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F131" s="2">
         <v>45869</v>
       </c>
       <c r="G131" t="s">
@@ -9654,7 +9680,7 @@
       <c r="E132" t="s">
         <v>954</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F132" s="2">
         <v>45869</v>
       </c>
       <c r="G132" t="s">
@@ -9664,7 +9690,7 @@
         <v>1353</v>
       </c>
       <c r="I132">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="J132">
         <v>145</v>
@@ -9675,7 +9701,7 @@
       <c r="L132" t="s">
         <v>1393</v>
       </c>
-      <c r="N132" s="1">
+      <c r="N132" s="2">
         <v>46014</v>
       </c>
       <c r="O132">
@@ -9701,7 +9727,7 @@
       <c r="E133" t="s">
         <v>955</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F133" s="2">
         <v>45869</v>
       </c>
       <c r="G133" t="s">
@@ -9730,7 +9756,7 @@
       <c r="E134" t="s">
         <v>956</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F134" s="2">
         <v>45882</v>
       </c>
       <c r="G134" t="s">
@@ -9740,7 +9766,7 @@
         <v>1353</v>
       </c>
       <c r="I134">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K134" t="s">
         <v>1356</v>
@@ -9768,7 +9794,7 @@
       <c r="E135" t="s">
         <v>957</v>
       </c>
-      <c r="F135" s="1">
+      <c r="F135" s="2">
         <v>45882</v>
       </c>
       <c r="G135" t="s">
@@ -9797,7 +9823,7 @@
       <c r="E136" t="s">
         <v>958</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F136" s="2">
         <v>45891</v>
       </c>
       <c r="G136" t="s">
@@ -9826,7 +9852,7 @@
       <c r="E137" t="s">
         <v>959</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F137" s="2">
         <v>45891</v>
       </c>
       <c r="G137" t="s">
@@ -9855,7 +9881,7 @@
       <c r="E138" t="s">
         <v>960</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F138" s="2">
         <v>45891</v>
       </c>
       <c r="G138" t="s">
@@ -9865,7 +9891,7 @@
         <v>1353</v>
       </c>
       <c r="I138">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K138" t="s">
         <v>1357</v>
@@ -9893,7 +9919,7 @@
       <c r="E139" t="s">
         <v>961</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F139" s="2">
         <v>45891</v>
       </c>
       <c r="G139" t="s">
@@ -9922,7 +9948,7 @@
       <c r="E140" t="s">
         <v>962</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F140" s="2">
         <v>45891</v>
       </c>
       <c r="G140" t="s">
@@ -9951,7 +9977,7 @@
       <c r="E141" t="s">
         <v>963</v>
       </c>
-      <c r="F141" s="1">
+      <c r="F141" s="2">
         <v>45891</v>
       </c>
       <c r="G141" t="s">
@@ -9980,7 +10006,7 @@
       <c r="E142" t="s">
         <v>964</v>
       </c>
-      <c r="F142" s="1">
+      <c r="F142" s="2">
         <v>45891</v>
       </c>
       <c r="G142" t="s">
@@ -10009,7 +10035,7 @@
       <c r="E143" t="s">
         <v>965</v>
       </c>
-      <c r="F143" s="1">
+      <c r="F143" s="2">
         <v>45891</v>
       </c>
       <c r="G143" t="s">
@@ -10038,7 +10064,7 @@
       <c r="E144" t="s">
         <v>966</v>
       </c>
-      <c r="F144" s="1">
+      <c r="F144" s="2">
         <v>45891</v>
       </c>
       <c r="G144" t="s">
@@ -10067,7 +10093,7 @@
       <c r="E145" t="s">
         <v>967</v>
       </c>
-      <c r="F145" s="1">
+      <c r="F145" s="2">
         <v>45891</v>
       </c>
       <c r="G145" t="s">
@@ -10096,7 +10122,7 @@
       <c r="E146" t="s">
         <v>968</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F146" s="2">
         <v>45891</v>
       </c>
       <c r="G146" t="s">
@@ -10125,7 +10151,7 @@
       <c r="E147" t="s">
         <v>969</v>
       </c>
-      <c r="F147" s="1">
+      <c r="F147" s="2">
         <v>45891</v>
       </c>
       <c r="G147" t="s">
@@ -10154,7 +10180,7 @@
       <c r="E148" t="s">
         <v>970</v>
       </c>
-      <c r="F148" s="1">
+      <c r="F148" s="2">
         <v>45891</v>
       </c>
       <c r="G148" t="s">
@@ -10164,7 +10190,7 @@
         <v>1353</v>
       </c>
       <c r="I148">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J148">
         <v>341</v>
@@ -10175,7 +10201,7 @@
       <c r="L148" t="s">
         <v>1383</v>
       </c>
-      <c r="N148" s="1">
+      <c r="N148" s="2">
         <v>46232</v>
       </c>
       <c r="Q148" t="b">
@@ -10198,7 +10224,7 @@
       <c r="E149" t="s">
         <v>971</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F149" s="2">
         <v>45891</v>
       </c>
       <c r="G149" t="s">
@@ -10208,7 +10234,7 @@
         <v>1353</v>
       </c>
       <c r="I149">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J149">
         <v>374</v>
@@ -10219,7 +10245,7 @@
       <c r="L149" t="s">
         <v>1394</v>
       </c>
-      <c r="N149" s="1">
+      <c r="N149" s="2">
         <v>46265</v>
       </c>
       <c r="P149" t="s">
@@ -10245,7 +10271,7 @@
       <c r="E150" t="s">
         <v>972</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F150" s="2">
         <v>45891</v>
       </c>
       <c r="G150" t="s">
@@ -10255,7 +10281,7 @@
         <v>1353</v>
       </c>
       <c r="I150">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J150">
         <v>201</v>
@@ -10266,7 +10292,7 @@
       <c r="L150" t="s">
         <v>1381</v>
       </c>
-      <c r="N150" s="1">
+      <c r="N150" s="2">
         <v>46092</v>
       </c>
       <c r="P150" t="s">
@@ -10292,7 +10318,7 @@
       <c r="E151" t="s">
         <v>973</v>
       </c>
-      <c r="F151" s="1">
+      <c r="F151" s="2">
         <v>45891</v>
       </c>
       <c r="G151" t="s">
@@ -10321,7 +10347,7 @@
       <c r="E152" t="s">
         <v>963</v>
       </c>
-      <c r="F152" s="1">
+      <c r="F152" s="2">
         <v>45891</v>
       </c>
       <c r="G152" t="s">
@@ -10331,7 +10357,7 @@
         <v>1353</v>
       </c>
       <c r="I152">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J152">
         <v>228</v>
@@ -10342,7 +10368,7 @@
       <c r="L152" t="s">
         <v>1382</v>
       </c>
-      <c r="N152" s="1">
+      <c r="N152" s="2">
         <v>46119</v>
       </c>
       <c r="Q152" t="b">
@@ -10365,7 +10391,7 @@
       <c r="E153" t="s">
         <v>974</v>
       </c>
-      <c r="F153" s="1">
+      <c r="F153" s="2">
         <v>45891</v>
       </c>
       <c r="G153" t="s">
@@ -10383,7 +10409,7 @@
       <c r="L153" t="s">
         <v>1383</v>
       </c>
-      <c r="N153" s="1">
+      <c r="N153" s="2">
         <v>46232</v>
       </c>
       <c r="Q153" t="b">
@@ -10406,7 +10432,7 @@
       <c r="E154" t="s">
         <v>975</v>
       </c>
-      <c r="F154" s="1">
+      <c r="F154" s="2">
         <v>45891</v>
       </c>
       <c r="G154" t="s">
@@ -10435,7 +10461,7 @@
       <c r="E155" t="s">
         <v>976</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F155" s="2">
         <v>45891</v>
       </c>
       <c r="G155" t="s">
@@ -10445,7 +10471,7 @@
         <v>1353</v>
       </c>
       <c r="I155">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K155" t="s">
         <v>1363</v>
@@ -10470,7 +10496,7 @@
       <c r="E156" t="s">
         <v>977</v>
       </c>
-      <c r="F156" s="1">
+      <c r="F156" s="2">
         <v>45891</v>
       </c>
       <c r="G156" t="s">
@@ -10480,7 +10506,7 @@
         <v>1353</v>
       </c>
       <c r="I156">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K156" t="s">
         <v>1357</v>
@@ -10508,7 +10534,7 @@
       <c r="E157" t="s">
         <v>978</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="2">
         <v>45891</v>
       </c>
       <c r="G157" t="s">
@@ -10518,7 +10544,7 @@
         <v>1353</v>
       </c>
       <c r="I157">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J157">
         <v>371</v>
@@ -10529,7 +10555,7 @@
       <c r="L157" t="s">
         <v>1395</v>
       </c>
-      <c r="N157" s="1">
+      <c r="N157" s="2">
         <v>46262</v>
       </c>
       <c r="Q157" t="b">
@@ -10552,7 +10578,7 @@
       <c r="E158" t="s">
         <v>979</v>
       </c>
-      <c r="F158" s="1">
+      <c r="F158" s="2">
         <v>45894</v>
       </c>
       <c r="G158" t="s">
@@ -10562,7 +10588,7 @@
         <v>1353</v>
       </c>
       <c r="I158">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J158">
         <v>52</v>
@@ -10573,7 +10599,7 @@
       <c r="L158" t="s">
         <v>1396</v>
       </c>
-      <c r="N158" s="1">
+      <c r="N158" s="2">
         <v>45946</v>
       </c>
       <c r="Q158" t="b">
@@ -10596,7 +10622,7 @@
       <c r="E159" t="s">
         <v>980</v>
       </c>
-      <c r="F159" s="1">
+      <c r="F159" s="2">
         <v>45894</v>
       </c>
       <c r="G159" t="s">
@@ -10606,7 +10632,7 @@
         <v>1353</v>
       </c>
       <c r="I159">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K159" t="s">
         <v>1357</v>
@@ -10634,7 +10660,7 @@
       <c r="E160" t="s">
         <v>981</v>
       </c>
-      <c r="F160" s="1">
+      <c r="F160" s="2">
         <v>45898</v>
       </c>
       <c r="G160" t="s">
@@ -10644,7 +10670,7 @@
         <v>1353</v>
       </c>
       <c r="I160">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K160" t="s">
         <v>1357</v>
@@ -10672,7 +10698,7 @@
       <c r="E161" t="s">
         <v>982</v>
       </c>
-      <c r="F161" s="1">
+      <c r="F161" s="2">
         <v>45898</v>
       </c>
       <c r="G161" t="s">
@@ -10682,7 +10708,7 @@
         <v>1353</v>
       </c>
       <c r="I161">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J161">
         <v>55</v>
@@ -10693,7 +10719,7 @@
       <c r="L161" t="s">
         <v>1397</v>
       </c>
-      <c r="N161" s="1">
+      <c r="N161" s="2">
         <v>45953</v>
       </c>
       <c r="O161" t="s">
@@ -10719,7 +10745,7 @@
       <c r="E162" t="s">
         <v>983</v>
       </c>
-      <c r="F162" s="1">
+      <c r="F162" s="2">
         <v>45898</v>
       </c>
       <c r="G162" t="s">
@@ -10729,7 +10755,7 @@
         <v>1353</v>
       </c>
       <c r="I162">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J162">
         <v>42</v>
@@ -10740,7 +10766,7 @@
       <c r="L162" t="s">
         <v>1398</v>
       </c>
-      <c r="N162" s="1">
+      <c r="N162" s="2">
         <v>45940</v>
       </c>
       <c r="Q162" t="b">
@@ -10763,7 +10789,7 @@
       <c r="E163" t="s">
         <v>984</v>
       </c>
-      <c r="F163" s="1">
+      <c r="F163" s="2">
         <v>45898</v>
       </c>
       <c r="G163" t="s">
@@ -10773,7 +10799,7 @@
         <v>1353</v>
       </c>
       <c r="I163">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J163">
         <v>42</v>
@@ -10784,7 +10810,7 @@
       <c r="L163" t="s">
         <v>1398</v>
       </c>
-      <c r="N163" s="1">
+      <c r="N163" s="2">
         <v>45940</v>
       </c>
       <c r="Q163" t="b">
@@ -10807,7 +10833,7 @@
       <c r="E164" t="s">
         <v>985</v>
       </c>
-      <c r="F164" s="1">
+      <c r="F164" s="2">
         <v>45910</v>
       </c>
       <c r="G164" t="s">
@@ -10817,7 +10843,7 @@
         <v>1355</v>
       </c>
       <c r="I164">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="O164" t="s">
         <v>1469</v>
@@ -10842,7 +10868,7 @@
       <c r="E165" t="s">
         <v>986</v>
       </c>
-      <c r="F165" s="1">
+      <c r="F165" s="2">
         <v>45917</v>
       </c>
       <c r="G165" t="s">
@@ -10860,7 +10886,7 @@
       <c r="L165" t="s">
         <v>1399</v>
       </c>
-      <c r="N165" s="1">
+      <c r="N165" s="2">
         <v>46204</v>
       </c>
       <c r="P165" t="s">
@@ -10886,7 +10912,7 @@
       <c r="E166" t="s">
         <v>987</v>
       </c>
-      <c r="F166" s="1">
+      <c r="F166" s="2">
         <v>45917</v>
       </c>
       <c r="G166" t="s">
@@ -10915,7 +10941,7 @@
       <c r="E167" t="s">
         <v>988</v>
       </c>
-      <c r="F167" s="1">
+      <c r="F167" s="2">
         <v>45917</v>
       </c>
       <c r="G167" t="s">
@@ -10944,7 +10970,7 @@
       <c r="E168" t="s">
         <v>989</v>
       </c>
-      <c r="F168" s="1">
+      <c r="F168" s="2">
         <v>45917</v>
       </c>
       <c r="G168" t="s">
@@ -10954,7 +10980,7 @@
         <v>1353</v>
       </c>
       <c r="I168">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K168" t="s">
         <v>1360</v>
@@ -10985,7 +11011,7 @@
       <c r="E169" t="s">
         <v>990</v>
       </c>
-      <c r="F169" s="1">
+      <c r="F169" s="2">
         <v>45917</v>
       </c>
       <c r="G169" t="s">
@@ -10995,7 +11021,7 @@
         <v>1353</v>
       </c>
       <c r="I169">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K169" t="s">
         <v>1330</v>
@@ -11003,7 +11029,7 @@
       <c r="L169" t="s">
         <v>1401</v>
       </c>
-      <c r="N169" s="1">
+      <c r="N169" s="2">
         <v>45973</v>
       </c>
       <c r="Q169" t="b">
@@ -11026,7 +11052,7 @@
       <c r="E170" t="s">
         <v>991</v>
       </c>
-      <c r="F170" s="1">
+      <c r="F170" s="2">
         <v>45917</v>
       </c>
       <c r="G170" t="s">
@@ -11061,7 +11087,7 @@
       <c r="E171" t="s">
         <v>992</v>
       </c>
-      <c r="F171" s="1">
+      <c r="F171" s="2">
         <v>45917</v>
       </c>
       <c r="G171" t="s">
@@ -11071,7 +11097,7 @@
         <v>1353</v>
       </c>
       <c r="I171">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K171" t="s">
         <v>1357</v>
@@ -11099,7 +11125,7 @@
       <c r="E172" t="s">
         <v>993</v>
       </c>
-      <c r="F172" s="1">
+      <c r="F172" s="2">
         <v>45917</v>
       </c>
       <c r="G172" t="s">
@@ -11128,7 +11154,7 @@
       <c r="E173" t="s">
         <v>994</v>
       </c>
-      <c r="F173" s="1">
+      <c r="F173" s="2">
         <v>45917</v>
       </c>
       <c r="G173" t="s">
@@ -11157,7 +11183,7 @@
       <c r="E174" t="s">
         <v>995</v>
       </c>
-      <c r="F174" s="1">
+      <c r="F174" s="2">
         <v>45917</v>
       </c>
       <c r="G174" t="s">
@@ -11172,7 +11198,7 @@
       <c r="L174" t="s">
         <v>1386</v>
       </c>
-      <c r="N174" s="1">
+      <c r="N174" s="2">
         <v>46195</v>
       </c>
       <c r="Q174" t="b">
@@ -11195,7 +11221,7 @@
       <c r="E175" t="s">
         <v>996</v>
       </c>
-      <c r="F175" s="1">
+      <c r="F175" s="2">
         <v>45917</v>
       </c>
       <c r="G175" t="s">
@@ -11205,7 +11231,7 @@
         <v>1353</v>
       </c>
       <c r="I175">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J175">
         <v>205</v>
@@ -11216,7 +11242,7 @@
       <c r="L175" t="s">
         <v>1402</v>
       </c>
-      <c r="N175" s="1">
+      <c r="N175" s="2">
         <v>46122</v>
       </c>
       <c r="P175" t="s">
@@ -11242,7 +11268,7 @@
       <c r="E176" t="s">
         <v>900</v>
       </c>
-      <c r="F176" s="1">
+      <c r="F176" s="2">
         <v>45917</v>
       </c>
       <c r="G176" t="s">
@@ -11252,7 +11278,7 @@
         <v>1353</v>
       </c>
       <c r="I176">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K176" t="s">
         <v>1357</v>
@@ -11280,7 +11306,7 @@
       <c r="E177" t="s">
         <v>997</v>
       </c>
-      <c r="F177" s="1">
+      <c r="F177" s="2">
         <v>45917</v>
       </c>
       <c r="G177" t="s">
@@ -11290,7 +11316,7 @@
         <v>1353</v>
       </c>
       <c r="I177">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J177">
         <v>44</v>
@@ -11301,7 +11327,7 @@
       <c r="L177" t="s">
         <v>1403</v>
       </c>
-      <c r="N177" s="1">
+      <c r="N177" s="2">
         <v>45961</v>
       </c>
       <c r="P177" t="s">
@@ -11327,7 +11353,7 @@
       <c r="E178" t="s">
         <v>998</v>
       </c>
-      <c r="F178" s="1">
+      <c r="F178" s="2">
         <v>45937</v>
       </c>
       <c r="G178" t="s">
@@ -11337,7 +11363,7 @@
         <v>1353</v>
       </c>
       <c r="I178">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K178" t="s">
         <v>1356</v>
@@ -11365,7 +11391,7 @@
       <c r="E179" t="s">
         <v>999</v>
       </c>
-      <c r="F179" s="1">
+      <c r="F179" s="2">
         <v>45937</v>
       </c>
       <c r="G179" t="s">
@@ -11394,7 +11420,7 @@
       <c r="E180" t="s">
         <v>1000</v>
       </c>
-      <c r="F180" s="1">
+      <c r="F180" s="2">
         <v>45937</v>
       </c>
       <c r="G180" t="s">
@@ -11404,7 +11430,7 @@
         <v>1353</v>
       </c>
       <c r="I180">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K180" t="s">
         <v>1356</v>
@@ -11432,7 +11458,7 @@
       <c r="E181" t="s">
         <v>1001</v>
       </c>
-      <c r="F181" s="1">
+      <c r="F181" s="2">
         <v>45937</v>
       </c>
       <c r="G181" t="s">
@@ -11461,7 +11487,7 @@
       <c r="E182" t="s">
         <v>1002</v>
       </c>
-      <c r="F182" s="1">
+      <c r="F182" s="2">
         <v>45937</v>
       </c>
       <c r="G182" t="s">
@@ -11490,7 +11516,7 @@
       <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="F183" s="1">
+      <c r="F183" s="2">
         <v>45937</v>
       </c>
       <c r="G183" t="s">
@@ -11500,7 +11526,7 @@
         <v>1353</v>
       </c>
       <c r="I183">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K183" t="s">
         <v>1357</v>
@@ -11528,7 +11554,7 @@
       <c r="D184" t="s">
         <v>774</v>
       </c>
-      <c r="F184" s="1">
+      <c r="F184" s="2">
         <v>45939</v>
       </c>
       <c r="G184" t="s">
@@ -11538,7 +11564,7 @@
         <v>1353</v>
       </c>
       <c r="I184">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K184" t="s">
         <v>1363</v>
@@ -11563,7 +11589,7 @@
       <c r="E185" t="s">
         <v>1004</v>
       </c>
-      <c r="F185" s="1">
+      <c r="F185" s="2">
         <v>45939</v>
       </c>
       <c r="G185" t="s">
@@ -11573,7 +11599,7 @@
         <v>1353</v>
       </c>
       <c r="I185">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K185" t="s">
         <v>1357</v>
@@ -11601,7 +11627,7 @@
       <c r="E186" t="s">
         <v>1005</v>
       </c>
-      <c r="F186" s="1">
+      <c r="F186" s="2">
         <v>45939</v>
       </c>
       <c r="G186" t="s">
@@ -11611,7 +11637,7 @@
         <v>1353</v>
       </c>
       <c r="I186">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K186" t="s">
         <v>1357</v>
@@ -11639,7 +11665,7 @@
       <c r="E187" t="s">
         <v>1006</v>
       </c>
-      <c r="F187" s="1">
+      <c r="F187" s="2">
         <v>45939</v>
       </c>
       <c r="G187" t="s">
@@ -11649,7 +11675,7 @@
         <v>1353</v>
       </c>
       <c r="I187">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J187">
         <v>75</v>
@@ -11660,7 +11686,7 @@
       <c r="L187" t="s">
         <v>1404</v>
       </c>
-      <c r="N187" s="1">
+      <c r="N187" s="2">
         <v>46014</v>
       </c>
       <c r="O187">
@@ -11686,7 +11712,7 @@
       <c r="E188" t="s">
         <v>1007</v>
       </c>
-      <c r="F188" s="1">
+      <c r="F188" s="2">
         <v>45946</v>
       </c>
       <c r="G188" t="s">
@@ -11696,7 +11722,7 @@
         <v>1353</v>
       </c>
       <c r="I188">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J188">
         <v>40</v>
@@ -11707,7 +11733,7 @@
       <c r="L188" t="s">
         <v>1405</v>
       </c>
-      <c r="N188" s="1">
+      <c r="N188" s="2">
         <v>45986</v>
       </c>
       <c r="P188" t="s">
@@ -11733,7 +11759,7 @@
       <c r="E189" t="s">
         <v>1008</v>
       </c>
-      <c r="F189" s="1">
+      <c r="F189" s="2">
         <v>45965</v>
       </c>
       <c r="G189" t="s">
@@ -11743,7 +11769,7 @@
         <v>1353</v>
       </c>
       <c r="I189">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="J189">
         <v>155</v>
@@ -11754,7 +11780,7 @@
       <c r="L189" t="s">
         <v>1406</v>
       </c>
-      <c r="N189" s="1">
+      <c r="N189" s="2">
         <v>46120</v>
       </c>
       <c r="Q189" t="b">
@@ -11777,7 +11803,7 @@
       <c r="E190" t="s">
         <v>1009</v>
       </c>
-      <c r="F190" s="1">
+      <c r="F190" s="2">
         <v>45965</v>
       </c>
       <c r="G190" t="s">
@@ -11787,7 +11813,7 @@
         <v>1353</v>
       </c>
       <c r="I190">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="J190">
         <v>107</v>
@@ -11798,7 +11824,7 @@
       <c r="L190" t="s">
         <v>1407</v>
       </c>
-      <c r="N190" s="1">
+      <c r="N190" s="2">
         <v>46072</v>
       </c>
       <c r="Q190" t="b">
@@ -11821,7 +11847,7 @@
       <c r="E191" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="1">
+      <c r="F191" s="2">
         <v>45967</v>
       </c>
       <c r="G191" t="s">
@@ -11831,7 +11857,7 @@
         <v>1353</v>
       </c>
       <c r="I191">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J191">
         <v>5</v>
@@ -11842,7 +11868,7 @@
       <c r="L191" t="s">
         <v>1408</v>
       </c>
-      <c r="N191" s="1">
+      <c r="N191" s="2">
         <v>45972</v>
       </c>
       <c r="Q191" t="b">
@@ -11865,7 +11891,7 @@
       <c r="E192" t="s">
         <v>1011</v>
       </c>
-      <c r="F192" s="1">
+      <c r="F192" s="2">
         <v>45968</v>
       </c>
       <c r="G192" t="s">
@@ -11875,7 +11901,7 @@
         <v>1353</v>
       </c>
       <c r="I192">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K192" t="s">
         <v>1357</v>
@@ -11903,7 +11929,7 @@
       <c r="E193" t="s">
         <v>1012</v>
       </c>
-      <c r="F193" s="1">
+      <c r="F193" s="2">
         <v>45968</v>
       </c>
       <c r="G193" t="s">
@@ -11913,7 +11939,7 @@
         <v>1353</v>
       </c>
       <c r="I193">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K193" t="s">
         <v>1362</v>
@@ -11941,7 +11967,7 @@
       <c r="E194" t="s">
         <v>1013</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F194" s="2">
         <v>45968</v>
       </c>
       <c r="G194" t="s">
@@ -11970,7 +11996,7 @@
       <c r="E195" t="s">
         <v>1014</v>
       </c>
-      <c r="F195" s="1">
+      <c r="F195" s="2">
         <v>45971</v>
       </c>
       <c r="G195" t="s">
@@ -11980,7 +12006,7 @@
         <v>1353</v>
       </c>
       <c r="I195">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="J195">
         <v>186</v>
@@ -11991,7 +12017,7 @@
       <c r="L195" t="s">
         <v>1409</v>
       </c>
-      <c r="N195" s="1">
+      <c r="N195" s="2">
         <v>46157</v>
       </c>
       <c r="Q195" t="b">
@@ -12014,7 +12040,7 @@
       <c r="E196" t="s">
         <v>1015</v>
       </c>
-      <c r="F196" s="1">
+      <c r="F196" s="2">
         <v>45978</v>
       </c>
       <c r="G196" t="s">
@@ -12043,7 +12069,7 @@
       <c r="E197" t="s">
         <v>1016</v>
       </c>
-      <c r="F197" s="1">
+      <c r="F197" s="2">
         <v>45978</v>
       </c>
       <c r="G197" t="s">
@@ -12072,7 +12098,7 @@
       <c r="E198" t="s">
         <v>1017</v>
       </c>
-      <c r="F198" s="1">
+      <c r="F198" s="2">
         <v>45978</v>
       </c>
       <c r="G198" t="s">
@@ -12101,7 +12127,7 @@
       <c r="E199" t="s">
         <v>1018</v>
       </c>
-      <c r="F199" s="1">
+      <c r="F199" s="2">
         <v>45979</v>
       </c>
       <c r="G199" t="s">
@@ -12111,7 +12137,7 @@
         <v>1353</v>
       </c>
       <c r="I199">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J199">
         <v>70</v>
@@ -12122,7 +12148,7 @@
       <c r="L199" t="s">
         <v>1410</v>
       </c>
-      <c r="N199" s="1">
+      <c r="N199" s="2">
         <v>46049</v>
       </c>
       <c r="Q199" t="b">
@@ -12145,7 +12171,7 @@
       <c r="E200" t="s">
         <v>1019</v>
       </c>
-      <c r="F200" s="1">
+      <c r="F200" s="2">
         <v>45986</v>
       </c>
       <c r="G200" t="s">
@@ -12155,7 +12181,7 @@
         <v>1353</v>
       </c>
       <c r="I200">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J200">
         <v>170</v>
@@ -12166,7 +12192,7 @@
       <c r="L200" t="s">
         <v>1409</v>
       </c>
-      <c r="N200" s="1">
+      <c r="N200" s="2">
         <v>46156</v>
       </c>
       <c r="Q200" t="b">
@@ -12189,7 +12215,7 @@
       <c r="E201" t="s">
         <v>1020</v>
       </c>
-      <c r="F201" s="1">
+      <c r="F201" s="2">
         <v>45986</v>
       </c>
       <c r="G201" t="s">
@@ -12199,7 +12225,7 @@
         <v>1353</v>
       </c>
       <c r="I201">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K201" t="s">
         <v>1357</v>
@@ -12227,7 +12253,7 @@
       <c r="E202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" s="1">
+      <c r="F202" s="2">
         <v>45986</v>
       </c>
       <c r="G202" t="s">
@@ -12237,7 +12263,7 @@
         <v>1353</v>
       </c>
       <c r="I202">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K202" t="s">
         <v>1357</v>
@@ -12265,7 +12291,7 @@
       <c r="E203" t="s">
         <v>1022</v>
       </c>
-      <c r="F203" s="1">
+      <c r="F203" s="2">
         <v>45986</v>
       </c>
       <c r="G203" t="s">
@@ -12283,7 +12309,7 @@
       <c r="L203" t="s">
         <v>1411</v>
       </c>
-      <c r="N203" s="1">
+      <c r="N203" s="2">
         <v>46232</v>
       </c>
       <c r="Q203" t="b">
@@ -12306,7 +12332,7 @@
       <c r="E204" t="s">
         <v>1023</v>
       </c>
-      <c r="F204" s="1">
+      <c r="F204" s="2">
         <v>45986</v>
       </c>
       <c r="G204" t="s">
@@ -12316,7 +12342,7 @@
         <v>1353</v>
       </c>
       <c r="I204">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K204" t="s">
         <v>1356</v>
@@ -12344,7 +12370,7 @@
       <c r="E205" t="s">
         <v>1024</v>
       </c>
-      <c r="F205" s="1">
+      <c r="F205" s="2">
         <v>45986</v>
       </c>
       <c r="G205" t="s">
@@ -12354,7 +12380,7 @@
         <v>1353</v>
       </c>
       <c r="I205">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K205" t="s">
         <v>1356</v>
@@ -12382,7 +12408,7 @@
       <c r="E206" t="s">
         <v>1025</v>
       </c>
-      <c r="F206" s="1">
+      <c r="F206" s="2">
         <v>45986</v>
       </c>
       <c r="G206" t="s">
@@ -12411,7 +12437,7 @@
       <c r="E207" t="s">
         <v>1026</v>
       </c>
-      <c r="F207" s="1">
+      <c r="F207" s="2">
         <v>45986</v>
       </c>
       <c r="G207" t="s">
@@ -12421,7 +12447,7 @@
         <v>1353</v>
       </c>
       <c r="I207">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J207">
         <v>167</v>
@@ -12432,7 +12458,7 @@
       <c r="L207" t="s">
         <v>1412</v>
       </c>
-      <c r="N207" s="1">
+      <c r="N207" s="2">
         <v>46153</v>
       </c>
       <c r="Q207" t="b">
@@ -12455,7 +12481,7 @@
       <c r="E208" t="s">
         <v>1027</v>
       </c>
-      <c r="F208" s="1">
+      <c r="F208" s="2">
         <v>45986</v>
       </c>
       <c r="G208" t="s">
@@ -12465,7 +12491,7 @@
         <v>1353</v>
       </c>
       <c r="I208">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J208">
         <v>45</v>
@@ -12476,7 +12502,7 @@
       <c r="L208" t="s">
         <v>1413</v>
       </c>
-      <c r="N208" s="1">
+      <c r="N208" s="2">
         <v>46031</v>
       </c>
       <c r="Q208" t="b">
@@ -12499,7 +12525,7 @@
       <c r="E209" t="s">
         <v>1028</v>
       </c>
-      <c r="F209" s="1">
+      <c r="F209" s="2">
         <v>46000</v>
       </c>
       <c r="G209" t="s">
@@ -12509,7 +12535,7 @@
         <v>1353</v>
       </c>
       <c r="I209">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="J209">
         <v>191</v>
@@ -12520,7 +12546,7 @@
       <c r="L209" t="s">
         <v>1414</v>
       </c>
-      <c r="N209" s="1">
+      <c r="N209" s="2">
         <v>46191</v>
       </c>
       <c r="Q209" t="b">
@@ -12543,7 +12569,7 @@
       <c r="E210" t="s">
         <v>1029</v>
       </c>
-      <c r="F210" s="1">
+      <c r="F210" s="2">
         <v>46000</v>
       </c>
       <c r="G210" t="s">
@@ -12553,7 +12579,7 @@
         <v>1353</v>
       </c>
       <c r="I210">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K210" t="s">
         <v>1360</v>
@@ -12581,7 +12607,7 @@
       <c r="E211" t="s">
         <v>1030</v>
       </c>
-      <c r="F211" s="1">
+      <c r="F211" s="2">
         <v>46000</v>
       </c>
       <c r="G211" t="s">
@@ -12610,7 +12636,7 @@
       <c r="E212" t="s">
         <v>1031</v>
       </c>
-      <c r="F212" s="1">
+      <c r="F212" s="2">
         <v>46000</v>
       </c>
       <c r="G212" t="s">
@@ -12639,7 +12665,7 @@
       <c r="E213" t="s">
         <v>1032</v>
       </c>
-      <c r="F213" s="1">
+      <c r="F213" s="2">
         <v>46007</v>
       </c>
       <c r="G213" t="s">
@@ -12649,7 +12675,7 @@
         <v>1353</v>
       </c>
       <c r="I213">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="K213" t="s">
         <v>1357</v>
@@ -12677,7 +12703,7 @@
       <c r="E214" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="1">
+      <c r="F214" s="2">
         <v>46007</v>
       </c>
       <c r="G214" t="s">
@@ -12687,7 +12713,7 @@
         <v>1353</v>
       </c>
       <c r="I214">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="J214">
         <v>14</v>
@@ -12698,7 +12724,7 @@
       <c r="L214" t="s">
         <v>1415</v>
       </c>
-      <c r="N214" s="1">
+      <c r="N214" s="2">
         <v>46021</v>
       </c>
       <c r="O214">
@@ -12724,7 +12750,7 @@
       <c r="E215" t="s">
         <v>1034</v>
       </c>
-      <c r="F215" s="1">
+      <c r="F215" s="2">
         <v>46007</v>
       </c>
       <c r="G215" t="s">
@@ -12734,7 +12760,7 @@
         <v>1353</v>
       </c>
       <c r="I215">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="K215" t="s">
         <v>1357</v>
@@ -12762,7 +12788,7 @@
       <c r="E216" t="s">
         <v>1035</v>
       </c>
-      <c r="F216" s="1">
+      <c r="F216" s="2">
         <v>46010</v>
       </c>
       <c r="G216" t="s">
@@ -12791,7 +12817,7 @@
       <c r="E217" t="s">
         <v>1036</v>
       </c>
-      <c r="F217" s="1">
+      <c r="F217" s="2">
         <v>46010</v>
       </c>
       <c r="G217" t="s">
@@ -12801,7 +12827,7 @@
         <v>1353</v>
       </c>
       <c r="I217">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J217">
         <v>42</v>
@@ -12812,7 +12838,7 @@
       <c r="L217" t="s">
         <v>1416</v>
       </c>
-      <c r="N217" s="1">
+      <c r="N217" s="2">
         <v>46052</v>
       </c>
       <c r="Q217" t="b">
@@ -12835,7 +12861,7 @@
       <c r="E218" t="s">
         <v>1037</v>
       </c>
-      <c r="F218" s="1">
+      <c r="F218" s="2">
         <v>46010</v>
       </c>
       <c r="G218" t="s">
@@ -12845,7 +12871,7 @@
         <v>1353</v>
       </c>
       <c r="I218">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J218">
         <v>166</v>
@@ -12853,7 +12879,7 @@
       <c r="K218" t="s">
         <v>1359</v>
       </c>
-      <c r="N218" s="1">
+      <c r="N218" s="2">
         <v>46176</v>
       </c>
       <c r="P218" t="s">
@@ -12879,7 +12905,7 @@
       <c r="E219" t="s">
         <v>1038</v>
       </c>
-      <c r="F219" s="1">
+      <c r="F219" s="2">
         <v>46010</v>
       </c>
       <c r="G219" t="s">
@@ -12897,7 +12923,7 @@
       <c r="L219" t="s">
         <v>1417</v>
       </c>
-      <c r="N219" s="1">
+      <c r="N219" s="2">
         <v>46176</v>
       </c>
       <c r="P219" t="s">
@@ -12923,7 +12949,7 @@
       <c r="E220" t="s">
         <v>1039</v>
       </c>
-      <c r="F220" s="1">
+      <c r="F220" s="2">
         <v>46010</v>
       </c>
       <c r="G220" t="s">
@@ -12933,7 +12959,7 @@
         <v>1353</v>
       </c>
       <c r="I220">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J220">
         <v>154</v>
@@ -12944,7 +12970,7 @@
       <c r="L220" t="s">
         <v>1418</v>
       </c>
-      <c r="N220" s="1">
+      <c r="N220" s="2">
         <v>46164</v>
       </c>
       <c r="Q220" t="b">
@@ -12967,7 +12993,7 @@
       <c r="E221" t="s">
         <v>1040</v>
       </c>
-      <c r="F221" s="1">
+      <c r="F221" s="2">
         <v>46028</v>
       </c>
       <c r="G221" t="s">
@@ -12982,7 +13008,7 @@
       <c r="L221" t="s">
         <v>1419</v>
       </c>
-      <c r="N221" s="1">
+      <c r="N221" s="2">
         <v>46184</v>
       </c>
       <c r="Q221" t="b">
@@ -13005,7 +13031,7 @@
       <c r="E222" t="s">
         <v>1041</v>
       </c>
-      <c r="F222" s="1">
+      <c r="F222" s="2">
         <v>46028</v>
       </c>
       <c r="G222" t="s">
@@ -13020,7 +13046,7 @@
       <c r="L222" t="s">
         <v>1383</v>
       </c>
-      <c r="N222" s="1">
+      <c r="N222" s="2">
         <v>46232</v>
       </c>
       <c r="Q222" t="b">
@@ -13043,7 +13069,7 @@
       <c r="E223" t="s">
         <v>1042</v>
       </c>
-      <c r="F223" s="1">
+      <c r="F223" s="2">
         <v>46028</v>
       </c>
       <c r="G223" t="s">
@@ -13058,7 +13084,7 @@
       <c r="L223" t="s">
         <v>1383</v>
       </c>
-      <c r="N223" s="1">
+      <c r="N223" s="2">
         <v>46232</v>
       </c>
       <c r="Q223" t="b">
@@ -13081,7 +13107,7 @@
       <c r="E224" t="s">
         <v>1043</v>
       </c>
-      <c r="F224" s="1">
+      <c r="F224" s="2">
         <v>46028</v>
       </c>
       <c r="G224" t="s">
@@ -13091,7 +13117,7 @@
         <v>1353</v>
       </c>
       <c r="I224">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J224">
         <v>204</v>
@@ -13099,7 +13125,7 @@
       <c r="L224" t="s">
         <v>1383</v>
       </c>
-      <c r="N224" s="1">
+      <c r="N224" s="2">
         <v>46232</v>
       </c>
       <c r="Q224" t="b">
@@ -13122,7 +13148,7 @@
       <c r="E225" t="s">
         <v>1044</v>
       </c>
-      <c r="F225" s="1">
+      <c r="F225" s="2">
         <v>46028</v>
       </c>
       <c r="G225" t="s">
@@ -13137,7 +13163,7 @@
       <c r="L225" t="s">
         <v>1383</v>
       </c>
-      <c r="N225" s="1">
+      <c r="N225" s="2">
         <v>46232</v>
       </c>
       <c r="Q225" t="b">
@@ -13160,7 +13186,7 @@
       <c r="E226" t="s">
         <v>1045</v>
       </c>
-      <c r="F226" s="1">
+      <c r="F226" s="2">
         <v>46028</v>
       </c>
       <c r="G226" t="s">
@@ -13175,7 +13201,7 @@
       <c r="L226" t="s">
         <v>1383</v>
       </c>
-      <c r="N226" s="1">
+      <c r="N226" s="2">
         <v>46232</v>
       </c>
       <c r="Q226" t="b">
@@ -13198,7 +13224,7 @@
       <c r="E227" t="s">
         <v>1046</v>
       </c>
-      <c r="F227" s="1">
+      <c r="F227" s="2">
         <v>46028</v>
       </c>
       <c r="G227" t="s">
@@ -13213,7 +13239,7 @@
       <c r="L227" t="s">
         <v>1383</v>
       </c>
-      <c r="N227" s="1">
+      <c r="N227" s="2">
         <v>46232</v>
       </c>
       <c r="Q227" t="b">
@@ -13236,7 +13262,7 @@
       <c r="E228" t="s">
         <v>1047</v>
       </c>
-      <c r="F228" s="1">
+      <c r="F228" s="2">
         <v>46028</v>
       </c>
       <c r="G228" t="s">
@@ -13246,7 +13272,7 @@
         <v>1353</v>
       </c>
       <c r="I228">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J228">
         <v>204</v>
@@ -13254,7 +13280,7 @@
       <c r="L228" t="s">
         <v>1383</v>
       </c>
-      <c r="N228" s="1">
+      <c r="N228" s="2">
         <v>46232</v>
       </c>
       <c r="Q228" t="b">
@@ -13277,7 +13303,7 @@
       <c r="E229" t="s">
         <v>1048</v>
       </c>
-      <c r="F229" s="1">
+      <c r="F229" s="2">
         <v>46028</v>
       </c>
       <c r="G229" t="s">
@@ -13292,7 +13318,7 @@
       <c r="L229" t="s">
         <v>1420</v>
       </c>
-      <c r="N229" s="1">
+      <c r="N229" s="2">
         <v>46191</v>
       </c>
       <c r="Q229" t="b">
@@ -13315,7 +13341,7 @@
       <c r="E230" t="s">
         <v>1049</v>
       </c>
-      <c r="F230" s="1">
+      <c r="F230" s="2">
         <v>46028</v>
       </c>
       <c r="G230" t="s">
@@ -13325,7 +13351,7 @@
         <v>1353</v>
       </c>
       <c r="I230">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J230">
         <v>197</v>
@@ -13336,7 +13362,7 @@
       <c r="L230" t="s">
         <v>1395</v>
       </c>
-      <c r="N230" s="1">
+      <c r="N230" s="2">
         <v>46225</v>
       </c>
       <c r="Q230" t="b">
@@ -13359,7 +13385,7 @@
       <c r="E231" t="s">
         <v>1050</v>
       </c>
-      <c r="F231" s="1">
+      <c r="F231" s="2">
         <v>46028</v>
       </c>
       <c r="G231" t="s">
@@ -13369,7 +13395,7 @@
         <v>1353</v>
       </c>
       <c r="I231">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J231">
         <v>35</v>
@@ -13380,7 +13406,7 @@
       <c r="L231" t="s">
         <v>1421</v>
       </c>
-      <c r="N231" s="1">
+      <c r="N231" s="2">
         <v>46063</v>
       </c>
       <c r="Q231" t="b">
@@ -13403,7 +13429,7 @@
       <c r="E232" t="s">
         <v>1051</v>
       </c>
-      <c r="F232" s="1">
+      <c r="F232" s="2">
         <v>46028</v>
       </c>
       <c r="G232" t="s">
@@ -13432,7 +13458,7 @@
       <c r="E233" t="s">
         <v>1052</v>
       </c>
-      <c r="F233" s="1">
+      <c r="F233" s="2">
         <v>46028</v>
       </c>
       <c r="G233" t="s">
@@ -13461,7 +13487,7 @@
       <c r="E234" t="s">
         <v>1053</v>
       </c>
-      <c r="F234" s="1">
+      <c r="F234" s="2">
         <v>46028</v>
       </c>
       <c r="G234" t="s">
@@ -13471,7 +13497,7 @@
         <v>1353</v>
       </c>
       <c r="I234">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J234">
         <v>35</v>
@@ -13482,7 +13508,7 @@
       <c r="L234" t="s">
         <v>1421</v>
       </c>
-      <c r="N234" s="1">
+      <c r="N234" s="2">
         <v>46063</v>
       </c>
       <c r="P234" t="s">
@@ -13508,7 +13534,7 @@
       <c r="E235" t="s">
         <v>1054</v>
       </c>
-      <c r="F235" s="1">
+      <c r="F235" s="2">
         <v>46028</v>
       </c>
       <c r="G235" t="s">
@@ -13518,7 +13544,7 @@
         <v>1353</v>
       </c>
       <c r="I235">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J235">
         <v>35</v>
@@ -13529,7 +13555,7 @@
       <c r="L235" t="s">
         <v>1421</v>
       </c>
-      <c r="N235" s="1">
+      <c r="N235" s="2">
         <v>46063</v>
       </c>
       <c r="P235" t="s">
@@ -13555,7 +13581,7 @@
       <c r="E236" t="s">
         <v>1055</v>
       </c>
-      <c r="F236" s="1">
+      <c r="F236" s="2">
         <v>46028</v>
       </c>
       <c r="G236" t="s">
@@ -13565,7 +13591,7 @@
         <v>1353</v>
       </c>
       <c r="I236">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J236">
         <v>86</v>
@@ -13576,7 +13602,7 @@
       <c r="L236" t="s">
         <v>1422</v>
       </c>
-      <c r="N236" s="1">
+      <c r="N236" s="2">
         <v>46114</v>
       </c>
       <c r="Q236" t="b">
@@ -13599,7 +13625,7 @@
       <c r="E237" t="s">
         <v>1056</v>
       </c>
-      <c r="F237" s="1">
+      <c r="F237" s="2">
         <v>46028</v>
       </c>
       <c r="G237" t="s">
@@ -13617,7 +13643,7 @@
       <c r="L237" t="s">
         <v>1423</v>
       </c>
-      <c r="N237" s="1">
+      <c r="N237" s="2">
         <v>46210</v>
       </c>
       <c r="P237" t="s">
@@ -13643,7 +13669,7 @@
       <c r="E238" t="s">
         <v>1057</v>
       </c>
-      <c r="F238" s="1">
+      <c r="F238" s="2">
         <v>46028</v>
       </c>
       <c r="G238" t="s">
@@ -13672,7 +13698,7 @@
       <c r="E239" t="s">
         <v>1058</v>
       </c>
-      <c r="F239" s="1">
+      <c r="F239" s="2">
         <v>46036</v>
       </c>
       <c r="G239" t="s">
@@ -13682,7 +13708,7 @@
         <v>1353</v>
       </c>
       <c r="I239">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K239" t="s">
         <v>1330</v>
@@ -13690,7 +13716,7 @@
       <c r="L239" t="s">
         <v>1424</v>
       </c>
-      <c r="N239" s="1">
+      <c r="N239" s="2">
         <v>46052</v>
       </c>
       <c r="Q239" t="b">
@@ -13713,7 +13739,7 @@
       <c r="E240" t="s">
         <v>1059</v>
       </c>
-      <c r="F240" s="1">
+      <c r="F240" s="2">
         <v>46036</v>
       </c>
       <c r="G240" t="s">
@@ -13742,7 +13768,7 @@
       <c r="E241" t="s">
         <v>1060</v>
       </c>
-      <c r="F241" s="1">
+      <c r="F241" s="2">
         <v>46036</v>
       </c>
       <c r="G241" t="s">
@@ -13771,7 +13797,7 @@
       <c r="E242" t="s">
         <v>1061</v>
       </c>
-      <c r="F242" s="1">
+      <c r="F242" s="2">
         <v>46036</v>
       </c>
       <c r="G242" t="s">
@@ -13781,7 +13807,7 @@
         <v>1353</v>
       </c>
       <c r="I242">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K242" t="s">
         <v>1356</v>
@@ -13809,7 +13835,7 @@
       <c r="E243" t="s">
         <v>1062</v>
       </c>
-      <c r="F243" s="1">
+      <c r="F243" s="2">
         <v>46048</v>
       </c>
       <c r="G243" t="s">
@@ -13838,7 +13864,7 @@
       <c r="E244" t="s">
         <v>1063</v>
       </c>
-      <c r="F244" s="1">
+      <c r="F244" s="2">
         <v>46048</v>
       </c>
       <c r="G244" t="s">
@@ -13848,7 +13874,7 @@
         <v>1353</v>
       </c>
       <c r="I244">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J244">
         <v>15</v>
@@ -13856,7 +13882,7 @@
       <c r="K244" t="s">
         <v>1359</v>
       </c>
-      <c r="N244" s="1">
+      <c r="N244" s="2">
         <v>46063</v>
       </c>
       <c r="Q244" t="b">
@@ -13879,7 +13905,7 @@
       <c r="E245" t="s">
         <v>1064</v>
       </c>
-      <c r="F245" s="1">
+      <c r="F245" s="2">
         <v>46048</v>
       </c>
       <c r="G245" t="s">
@@ -13889,7 +13915,7 @@
         <v>1353</v>
       </c>
       <c r="I245">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J245">
         <v>15</v>
@@ -13900,7 +13926,7 @@
       <c r="L245" t="s">
         <v>1425</v>
       </c>
-      <c r="N245" s="1">
+      <c r="N245" s="2">
         <v>46063</v>
       </c>
       <c r="Q245" t="b">
@@ -13923,7 +13949,7 @@
       <c r="E246" t="s">
         <v>1065</v>
       </c>
-      <c r="F246" s="1">
+      <c r="F246" s="2">
         <v>46050</v>
       </c>
       <c r="G246" t="s">
@@ -13941,7 +13967,7 @@
       <c r="L246" t="s">
         <v>1426</v>
       </c>
-      <c r="N246" s="1">
+      <c r="N246" s="2">
         <v>46191</v>
       </c>
       <c r="Q246" t="b">
@@ -13964,7 +13990,7 @@
       <c r="E247" t="s">
         <v>1066</v>
       </c>
-      <c r="F247" s="1">
+      <c r="F247" s="2">
         <v>46050</v>
       </c>
       <c r="G247" t="s">
@@ -13993,7 +14019,7 @@
       <c r="E248" t="s">
         <v>1067</v>
       </c>
-      <c r="F248" s="1">
+      <c r="F248" s="2">
         <v>46050</v>
       </c>
       <c r="G248" t="s">
@@ -14022,7 +14048,7 @@
       <c r="E249" t="s">
         <v>1068</v>
       </c>
-      <c r="F249" s="1">
+      <c r="F249" s="2">
         <v>46050</v>
       </c>
       <c r="G249" t="s">
@@ -14032,7 +14058,7 @@
         <v>1353</v>
       </c>
       <c r="I249">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K249" t="s">
         <v>1357</v>
@@ -14060,7 +14086,7 @@
       <c r="E250" t="s">
         <v>1069</v>
       </c>
-      <c r="F250" s="1">
+      <c r="F250" s="2">
         <v>46063</v>
       </c>
       <c r="G250" t="s">
@@ -14098,7 +14124,7 @@
       <c r="E251" t="s">
         <v>1070</v>
       </c>
-      <c r="F251" s="1">
+      <c r="F251" s="2">
         <v>46063</v>
       </c>
       <c r="G251" t="s">
@@ -14127,7 +14153,7 @@
       <c r="E252" t="s">
         <v>1071</v>
       </c>
-      <c r="F252" s="1">
+      <c r="F252" s="2">
         <v>46063</v>
       </c>
       <c r="G252" t="s">
@@ -14156,7 +14182,7 @@
       <c r="E253" t="s">
         <v>1072</v>
       </c>
-      <c r="F253" s="1">
+      <c r="F253" s="2">
         <v>46063</v>
       </c>
       <c r="G253" t="s">
@@ -14166,7 +14192,7 @@
         <v>1353</v>
       </c>
       <c r="I253">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J253">
         <v>162</v>
@@ -14177,7 +14203,7 @@
       <c r="L253" t="s">
         <v>1395</v>
       </c>
-      <c r="N253" s="1">
+      <c r="N253" s="2">
         <v>46225</v>
       </c>
       <c r="Q253" t="b">
@@ -14200,7 +14226,7 @@
       <c r="E254" t="s">
         <v>1073</v>
       </c>
-      <c r="F254" s="1">
+      <c r="F254" s="2">
         <v>46063</v>
       </c>
       <c r="G254" t="s">
@@ -14210,7 +14236,7 @@
         <v>1353</v>
       </c>
       <c r="I254">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K254" t="s">
         <v>1360</v>
@@ -14238,7 +14264,7 @@
       <c r="E255" t="s">
         <v>1074</v>
       </c>
-      <c r="F255" s="1">
+      <c r="F255" s="2">
         <v>46063</v>
       </c>
       <c r="G255" t="s">
@@ -14248,7 +14274,7 @@
         <v>1353</v>
       </c>
       <c r="I255">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J255">
         <v>72</v>
@@ -14259,7 +14285,7 @@
       <c r="L255" t="s">
         <v>1388</v>
       </c>
-      <c r="N255" s="1">
+      <c r="N255" s="2">
         <v>46135</v>
       </c>
       <c r="Q255" t="b">
@@ -14282,7 +14308,7 @@
       <c r="E256" t="s">
         <v>1075</v>
       </c>
-      <c r="F256" s="1">
+      <c r="F256" s="2">
         <v>46063</v>
       </c>
       <c r="G256" t="s">
@@ -14292,7 +14318,7 @@
         <v>1353</v>
       </c>
       <c r="I256">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J256">
         <v>23</v>
@@ -14300,7 +14326,7 @@
       <c r="K256" t="s">
         <v>1357</v>
       </c>
-      <c r="N256" s="1">
+      <c r="N256" s="2">
         <v>46086</v>
       </c>
       <c r="O256">
@@ -14326,7 +14352,7 @@
       <c r="E257" t="s">
         <v>1076</v>
       </c>
-      <c r="F257" s="1">
+      <c r="F257" s="2">
         <v>46063</v>
       </c>
       <c r="G257" t="s">
@@ -14355,7 +14381,7 @@
       <c r="E258" t="s">
         <v>1077</v>
       </c>
-      <c r="F258" s="1">
+      <c r="F258" s="2">
         <v>46063</v>
       </c>
       <c r="G258" t="s">
@@ -14384,7 +14410,7 @@
       <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="F259" s="1">
+      <c r="F259" s="2">
         <v>46063</v>
       </c>
       <c r="G259" t="s">
@@ -14394,7 +14420,7 @@
         <v>1353</v>
       </c>
       <c r="I259">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J259">
         <v>72</v>
@@ -14405,7 +14431,7 @@
       <c r="L259" t="s">
         <v>1388</v>
       </c>
-      <c r="N259" s="1">
+      <c r="N259" s="2">
         <v>46135</v>
       </c>
       <c r="Q259" t="b">
@@ -14428,7 +14454,7 @@
       <c r="E260" t="s">
         <v>1079</v>
       </c>
-      <c r="F260" s="1">
+      <c r="F260" s="2">
         <v>46063</v>
       </c>
       <c r="G260" t="s">
@@ -14438,7 +14464,7 @@
         <v>1353</v>
       </c>
       <c r="I260">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J260">
         <v>84</v>
@@ -14449,7 +14475,7 @@
       <c r="L260" t="s">
         <v>1388</v>
       </c>
-      <c r="N260" s="1">
+      <c r="N260" s="2">
         <v>46147</v>
       </c>
       <c r="Q260" t="b">
@@ -14472,7 +14498,7 @@
       <c r="E261" t="s">
         <v>1080</v>
       </c>
-      <c r="F261" s="1">
+      <c r="F261" s="2">
         <v>46063</v>
       </c>
       <c r="G261" t="s">
@@ -14482,7 +14508,7 @@
         <v>1353</v>
       </c>
       <c r="I261">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J261">
         <v>162</v>
@@ -14493,7 +14519,7 @@
       <c r="L261" t="s">
         <v>1427</v>
       </c>
-      <c r="N261" s="1">
+      <c r="N261" s="2">
         <v>46225</v>
       </c>
       <c r="Q261" t="b">
@@ -14516,7 +14542,7 @@
       <c r="E262" t="s">
         <v>1081</v>
       </c>
-      <c r="F262" s="1">
+      <c r="F262" s="2">
         <v>46063</v>
       </c>
       <c r="G262" t="s">
@@ -14534,7 +14560,7 @@
       <c r="L262" t="s">
         <v>1428</v>
       </c>
-      <c r="N262" s="1">
+      <c r="N262" s="2">
         <v>46113</v>
       </c>
       <c r="P262" t="s">
@@ -14560,7 +14586,7 @@
       <c r="E263" t="s">
         <v>1082</v>
       </c>
-      <c r="F263" s="1">
+      <c r="F263" s="2">
         <v>46063</v>
       </c>
       <c r="G263" t="s">
@@ -14589,7 +14615,7 @@
       <c r="E264" t="s">
         <v>1083</v>
       </c>
-      <c r="F264" s="1">
+      <c r="F264" s="2">
         <v>46063</v>
       </c>
       <c r="G264" t="s">
@@ -14599,7 +14625,7 @@
         <v>1353</v>
       </c>
       <c r="I264">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J264">
         <v>162</v>
@@ -14610,7 +14636,7 @@
       <c r="L264" t="s">
         <v>1388</v>
       </c>
-      <c r="N264" s="1">
+      <c r="N264" s="2">
         <v>46225</v>
       </c>
       <c r="Q264" t="b">
@@ -14633,7 +14659,7 @@
       <c r="E265" t="s">
         <v>1084</v>
       </c>
-      <c r="F265" s="1">
+      <c r="F265" s="2">
         <v>46063</v>
       </c>
       <c r="G265" t="s">
@@ -14643,7 +14669,7 @@
         <v>1353</v>
       </c>
       <c r="I265">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J265">
         <v>162</v>
@@ -14654,7 +14680,7 @@
       <c r="L265" t="s">
         <v>1395</v>
       </c>
-      <c r="N265" s="1">
+      <c r="N265" s="2">
         <v>46225</v>
       </c>
       <c r="Q265" t="b">
@@ -14677,7 +14703,7 @@
       <c r="E266" t="s">
         <v>1085</v>
       </c>
-      <c r="F266" s="1">
+      <c r="F266" s="2">
         <v>46063</v>
       </c>
       <c r="G266" t="s">
@@ -14687,7 +14713,7 @@
         <v>1353</v>
       </c>
       <c r="I266">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J266">
         <v>84</v>
@@ -14698,7 +14724,7 @@
       <c r="L266" t="s">
         <v>1388</v>
       </c>
-      <c r="N266" s="1">
+      <c r="N266" s="2">
         <v>46147</v>
       </c>
       <c r="Q266" t="b">
@@ -14721,7 +14747,7 @@
       <c r="E267" t="s">
         <v>1086</v>
       </c>
-      <c r="F267" s="1">
+      <c r="F267" s="2">
         <v>46063</v>
       </c>
       <c r="G267" t="s">
@@ -14731,7 +14757,7 @@
         <v>1353</v>
       </c>
       <c r="I267">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K267" t="s">
         <v>1360</v>
@@ -14759,7 +14785,7 @@
       <c r="E268" t="s">
         <v>1087</v>
       </c>
-      <c r="F268" s="1">
+      <c r="F268" s="2">
         <v>46063</v>
       </c>
       <c r="G268" t="s">
@@ -14769,7 +14795,7 @@
         <v>1353</v>
       </c>
       <c r="I268">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K268" t="s">
         <v>1357</v>
@@ -14794,7 +14820,7 @@
       <c r="D269" t="s">
         <v>798</v>
       </c>
-      <c r="F269" s="1">
+      <c r="F269" s="2">
         <v>46063</v>
       </c>
       <c r="G269" t="s">
@@ -14804,7 +14830,7 @@
         <v>1353</v>
       </c>
       <c r="I269">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K269" t="s">
         <v>1357</v>
@@ -14832,7 +14858,7 @@
       <c r="E270" t="s">
         <v>1088</v>
       </c>
-      <c r="F270" s="1">
+      <c r="F270" s="2">
         <v>46063</v>
       </c>
       <c r="G270" t="s">
@@ -14842,7 +14868,7 @@
         <v>1353</v>
       </c>
       <c r="I270">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K270" t="s">
         <v>1360</v>
@@ -14870,7 +14896,7 @@
       <c r="E271" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="1">
+      <c r="F271" s="2">
         <v>46063</v>
       </c>
       <c r="G271" t="s">
@@ -14880,7 +14906,7 @@
         <v>1353</v>
       </c>
       <c r="I271">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K271" t="s">
         <v>1360</v>
@@ -14908,7 +14934,7 @@
       <c r="E272" t="s">
         <v>1090</v>
       </c>
-      <c r="F272" s="1">
+      <c r="F272" s="2">
         <v>46063</v>
       </c>
       <c r="G272" t="s">
@@ -14926,7 +14952,7 @@
       <c r="L272" t="s">
         <v>1429</v>
       </c>
-      <c r="N272" s="1">
+      <c r="N272" s="2">
         <v>46185</v>
       </c>
       <c r="O272" t="s">
@@ -14952,7 +14978,7 @@
       <c r="E273" t="s">
         <v>1091</v>
       </c>
-      <c r="F273" s="1">
+      <c r="F273" s="2">
         <v>46063</v>
       </c>
       <c r="G273" t="s">
@@ -14981,7 +15007,7 @@
       <c r="E274" t="s">
         <v>1092</v>
       </c>
-      <c r="F274" s="1">
+      <c r="F274" s="2">
         <v>46063</v>
       </c>
       <c r="G274" t="s">
@@ -14996,7 +15022,7 @@
       <c r="L274" t="s">
         <v>1383</v>
       </c>
-      <c r="N274" s="1">
+      <c r="N274" s="2">
         <v>46232</v>
       </c>
       <c r="Q274" t="b">
@@ -15019,7 +15045,7 @@
       <c r="E275" t="s">
         <v>1093</v>
       </c>
-      <c r="F275" s="1">
+      <c r="F275" s="2">
         <v>46063</v>
       </c>
       <c r="G275" t="s">
@@ -15048,7 +15074,7 @@
       <c r="E276" t="s">
         <v>1094</v>
       </c>
-      <c r="F276" s="1">
+      <c r="F276" s="2">
         <v>46063</v>
       </c>
       <c r="G276" t="s">
@@ -15058,7 +15084,7 @@
         <v>1353</v>
       </c>
       <c r="I276">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K276" t="s">
         <v>1361</v>
@@ -15086,7 +15112,7 @@
       <c r="E277" t="s">
         <v>1095</v>
       </c>
-      <c r="F277" s="1">
+      <c r="F277" s="2">
         <v>46063</v>
       </c>
       <c r="G277" t="s">
@@ -15096,7 +15122,7 @@
         <v>1353</v>
       </c>
       <c r="I277">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K277" t="s">
         <v>1357</v>
@@ -15124,7 +15150,7 @@
       <c r="E278" t="s">
         <v>1096</v>
       </c>
-      <c r="F278" s="1">
+      <c r="F278" s="2">
         <v>46077</v>
       </c>
       <c r="G278" t="s">
@@ -15134,7 +15160,7 @@
         <v>1353</v>
       </c>
       <c r="I278">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J278">
         <v>148</v>
@@ -15145,7 +15171,7 @@
       <c r="L278" t="s">
         <v>1395</v>
       </c>
-      <c r="N278" s="1">
+      <c r="N278" s="2">
         <v>46225</v>
       </c>
       <c r="Q278" t="b">
@@ -15168,7 +15194,7 @@
       <c r="E279" t="s">
         <v>1097</v>
       </c>
-      <c r="F279" s="1">
+      <c r="F279" s="2">
         <v>46077</v>
       </c>
       <c r="G279" t="s">
@@ -15178,7 +15204,7 @@
         <v>1353</v>
       </c>
       <c r="I279">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K279" t="s">
         <v>1359</v>
@@ -15209,7 +15235,7 @@
       <c r="E280" t="s">
         <v>1098</v>
       </c>
-      <c r="F280" s="1">
+      <c r="F280" s="2">
         <v>46085</v>
       </c>
       <c r="G280" t="s">
@@ -15219,7 +15245,7 @@
         <v>1353</v>
       </c>
       <c r="I280">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K280" t="s">
         <v>1357</v>
@@ -15247,7 +15273,7 @@
       <c r="E281" t="s">
         <v>1099</v>
       </c>
-      <c r="F281" s="1">
+      <c r="F281" s="2">
         <v>46085</v>
       </c>
       <c r="G281" t="s">
@@ -15257,7 +15283,7 @@
         <v>1353</v>
       </c>
       <c r="I281">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K281" t="s">
         <v>1357</v>
@@ -15288,7 +15314,7 @@
       <c r="E282" t="s">
         <v>1100</v>
       </c>
-      <c r="F282" s="1">
+      <c r="F282" s="2">
         <v>46090</v>
       </c>
       <c r="G282" t="s">
@@ -15298,7 +15324,7 @@
         <v>1353</v>
       </c>
       <c r="I282">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K282" t="s">
         <v>1357</v>
@@ -15326,7 +15352,7 @@
       <c r="E283" t="s">
         <v>1101</v>
       </c>
-      <c r="F283" s="1">
+      <c r="F283" s="2">
         <v>46100</v>
       </c>
       <c r="G283" t="s">
@@ -15355,7 +15381,7 @@
       <c r="E284" t="s">
         <v>1102</v>
       </c>
-      <c r="F284" s="1">
+      <c r="F284" s="2">
         <v>46100</v>
       </c>
       <c r="G284" t="s">
@@ -15384,7 +15410,7 @@
       <c r="E285" t="s">
         <v>1103</v>
       </c>
-      <c r="F285" s="1">
+      <c r="F285" s="2">
         <v>46100</v>
       </c>
       <c r="G285" t="s">
@@ -15413,7 +15439,7 @@
       <c r="E286" t="s">
         <v>1104</v>
       </c>
-      <c r="F286" s="1">
+      <c r="F286" s="2">
         <v>46100</v>
       </c>
       <c r="G286" t="s">
@@ -15442,7 +15468,7 @@
       <c r="E287" t="s">
         <v>1105</v>
       </c>
-      <c r="F287" s="1">
+      <c r="F287" s="2">
         <v>46107</v>
       </c>
       <c r="G287" t="s">
@@ -15471,7 +15497,7 @@
       <c r="E288" t="s">
         <v>1106</v>
       </c>
-      <c r="F288" s="1">
+      <c r="F288" s="2">
         <v>46107</v>
       </c>
       <c r="G288" t="s">
@@ -15481,7 +15507,7 @@
         <v>1353</v>
       </c>
       <c r="I288">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J288">
         <v>28</v>
@@ -15492,7 +15518,7 @@
       <c r="L288" t="s">
         <v>1388</v>
       </c>
-      <c r="N288" s="1">
+      <c r="N288" s="2">
         <v>46135</v>
       </c>
       <c r="Q288" t="b">
@@ -15515,7 +15541,7 @@
       <c r="E289" t="s">
         <v>1107</v>
       </c>
-      <c r="F289" s="1">
+      <c r="F289" s="2">
         <v>46107</v>
       </c>
       <c r="G289" t="s">
@@ -15544,7 +15570,7 @@
       <c r="E290" t="s">
         <v>1108</v>
       </c>
-      <c r="F290" s="1">
+      <c r="F290" s="2">
         <v>46107</v>
       </c>
       <c r="G290" t="s">
@@ -15554,7 +15580,7 @@
         <v>1353</v>
       </c>
       <c r="I290">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J290">
         <v>20</v>
@@ -15565,7 +15591,7 @@
       <c r="L290" t="s">
         <v>1388</v>
       </c>
-      <c r="N290" s="1">
+      <c r="N290" s="2">
         <v>46127</v>
       </c>
       <c r="Q290" t="b">
@@ -15588,7 +15614,7 @@
       <c r="E291" t="s">
         <v>1109</v>
       </c>
-      <c r="F291" s="1">
+      <c r="F291" s="2">
         <v>46107</v>
       </c>
       <c r="G291" t="s">
@@ -15598,7 +15624,7 @@
         <v>1353</v>
       </c>
       <c r="I291">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J291">
         <v>20</v>
@@ -15609,7 +15635,7 @@
       <c r="L291" t="s">
         <v>1430</v>
       </c>
-      <c r="N291" s="1">
+      <c r="N291" s="2">
         <v>46127</v>
       </c>
       <c r="Q291" t="b">
@@ -15632,7 +15658,7 @@
       <c r="E292" t="s">
         <v>1110</v>
       </c>
-      <c r="F292" s="1">
+      <c r="F292" s="2">
         <v>46112</v>
       </c>
       <c r="G292" t="s">
@@ -15642,7 +15668,7 @@
         <v>1353</v>
       </c>
       <c r="I292">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K292" t="s">
         <v>1360</v>
@@ -15670,7 +15696,7 @@
       <c r="E293" t="s">
         <v>1111</v>
       </c>
-      <c r="F293" s="1">
+      <c r="F293" s="2">
         <v>46125</v>
       </c>
       <c r="G293" t="s">
@@ -15680,7 +15706,7 @@
         <v>1353</v>
       </c>
       <c r="I293">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K293" t="s">
         <v>1361</v>
@@ -15708,7 +15734,7 @@
       <c r="E294" t="s">
         <v>1112</v>
       </c>
-      <c r="F294" s="1">
+      <c r="F294" s="2">
         <v>46125</v>
       </c>
       <c r="G294" t="s">
@@ -15718,7 +15744,7 @@
         <v>1353</v>
       </c>
       <c r="I294">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K294" t="s">
         <v>1366</v>
@@ -15743,7 +15769,7 @@
       <c r="E295" t="s">
         <v>1113</v>
       </c>
-      <c r="F295" s="1">
+      <c r="F295" s="2">
         <v>46125</v>
       </c>
       <c r="G295" t="s">
@@ -15753,7 +15779,7 @@
         <v>1353</v>
       </c>
       <c r="I295">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K295" t="s">
         <v>1366</v>
@@ -15778,7 +15804,7 @@
       <c r="E296" t="s">
         <v>1114</v>
       </c>
-      <c r="F296" s="1">
+      <c r="F296" s="2">
         <v>46125</v>
       </c>
       <c r="G296" t="s">
@@ -15788,7 +15814,7 @@
         <v>1353</v>
       </c>
       <c r="I296">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K296" t="s">
         <v>1366</v>
@@ -15813,7 +15839,7 @@
       <c r="E297" t="s">
         <v>1115</v>
       </c>
-      <c r="F297" s="1">
+      <c r="F297" s="2">
         <v>46125</v>
       </c>
       <c r="G297" t="s">
@@ -15825,7 +15851,7 @@
       <c r="K297" t="s">
         <v>1359</v>
       </c>
-      <c r="N297" s="1">
+      <c r="N297" s="2">
         <v>46183</v>
       </c>
       <c r="O297">
@@ -15851,7 +15877,7 @@
       <c r="E298" t="s">
         <v>1116</v>
       </c>
-      <c r="F298" s="1">
+      <c r="F298" s="2">
         <v>46125</v>
       </c>
       <c r="G298" t="s">
@@ -15861,7 +15887,7 @@
         <v>1353</v>
       </c>
       <c r="I298">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J298">
         <v>58</v>
@@ -15869,7 +15895,7 @@
       <c r="K298" t="s">
         <v>1359</v>
       </c>
-      <c r="N298" s="1">
+      <c r="N298" s="2">
         <v>46183</v>
       </c>
       <c r="Q298" t="b">
@@ -15892,7 +15918,7 @@
       <c r="E299" t="s">
         <v>1117</v>
       </c>
-      <c r="F299" s="1">
+      <c r="F299" s="2">
         <v>46125</v>
       </c>
       <c r="G299" t="s">
@@ -15902,7 +15928,7 @@
         <v>1353</v>
       </c>
       <c r="I299">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J299">
         <v>100</v>
@@ -15913,7 +15939,7 @@
       <c r="L299" t="s">
         <v>1388</v>
       </c>
-      <c r="N299" s="1">
+      <c r="N299" s="2">
         <v>46225</v>
       </c>
       <c r="Q299" t="b">
@@ -15936,7 +15962,7 @@
       <c r="E300" t="s">
         <v>1118</v>
       </c>
-      <c r="F300" s="1">
+      <c r="F300" s="2">
         <v>46125</v>
       </c>
       <c r="G300" t="s">
@@ -15946,7 +15972,7 @@
         <v>1353</v>
       </c>
       <c r="I300">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J300">
         <v>86</v>
@@ -15957,7 +15983,7 @@
       <c r="L300" t="s">
         <v>1388</v>
       </c>
-      <c r="N300" s="1">
+      <c r="N300" s="2">
         <v>46211</v>
       </c>
       <c r="Q300" t="b">
@@ -15980,7 +16006,7 @@
       <c r="E301" t="s">
         <v>1119</v>
       </c>
-      <c r="F301" s="1">
+      <c r="F301" s="2">
         <v>46125</v>
       </c>
       <c r="G301" t="s">
@@ -15990,7 +16016,7 @@
         <v>1353</v>
       </c>
       <c r="I301">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J301">
         <v>102</v>
@@ -16001,7 +16027,7 @@
       <c r="L301" t="s">
         <v>1388</v>
       </c>
-      <c r="N301" s="1">
+      <c r="N301" s="2">
         <v>46227</v>
       </c>
       <c r="Q301" t="b">
@@ -16024,7 +16050,7 @@
       <c r="E302" t="s">
         <v>1120</v>
       </c>
-      <c r="F302" s="1">
+      <c r="F302" s="2">
         <v>46125</v>
       </c>
       <c r="G302" t="s">
@@ -16034,7 +16060,7 @@
         <v>1353</v>
       </c>
       <c r="I302">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K302" t="s">
         <v>1360</v>
@@ -16062,7 +16088,7 @@
       <c r="E303" t="s">
         <v>1121</v>
       </c>
-      <c r="F303" s="1">
+      <c r="F303" s="2">
         <v>46125</v>
       </c>
       <c r="G303" t="s">
@@ -16072,7 +16098,7 @@
         <v>1353</v>
       </c>
       <c r="I303">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K303" t="s">
         <v>1357</v>
@@ -16100,7 +16126,7 @@
       <c r="E304" t="s">
         <v>1122</v>
       </c>
-      <c r="F304" s="1">
+      <c r="F304" s="2">
         <v>46125</v>
       </c>
       <c r="G304" t="s">
@@ -16110,7 +16136,7 @@
         <v>1353</v>
       </c>
       <c r="I304">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K304" t="s">
         <v>1360</v>
@@ -16138,7 +16164,7 @@
       <c r="E305" t="s">
         <v>1123</v>
       </c>
-      <c r="F305" s="1">
+      <c r="F305" s="2">
         <v>46125</v>
       </c>
       <c r="G305" t="s">
@@ -16148,7 +16174,7 @@
         <v>1353</v>
       </c>
       <c r="I305">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J305">
         <v>35</v>
@@ -16159,7 +16185,7 @@
       <c r="L305" t="s">
         <v>1431</v>
       </c>
-      <c r="N305" s="1">
+      <c r="N305" s="2">
         <v>46160</v>
       </c>
       <c r="Q305" t="b">
@@ -16182,7 +16208,7 @@
       <c r="E306" t="s">
         <v>1124</v>
       </c>
-      <c r="F306" s="1">
+      <c r="F306" s="2">
         <v>46125</v>
       </c>
       <c r="G306" t="s">
@@ -16192,7 +16218,7 @@
         <v>1353</v>
       </c>
       <c r="I306">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J306">
         <v>31</v>
@@ -16203,7 +16229,7 @@
       <c r="L306" t="s">
         <v>1432</v>
       </c>
-      <c r="N306" s="1">
+      <c r="N306" s="2">
         <v>46156</v>
       </c>
       <c r="Q306" t="b">
@@ -16226,7 +16252,7 @@
       <c r="E307" t="s">
         <v>1125</v>
       </c>
-      <c r="F307" s="1">
+      <c r="F307" s="2">
         <v>46125</v>
       </c>
       <c r="G307" t="s">
@@ -16244,7 +16270,7 @@
       <c r="L307" t="s">
         <v>1433</v>
       </c>
-      <c r="N307" s="1">
+      <c r="N307" s="2">
         <v>46209</v>
       </c>
       <c r="P307" t="s">
@@ -16270,7 +16296,7 @@
       <c r="E308" t="s">
         <v>1126</v>
       </c>
-      <c r="F308" s="1">
+      <c r="F308" s="2">
         <v>46125</v>
       </c>
       <c r="G308" t="s">
@@ -16280,7 +16306,7 @@
         <v>1353</v>
       </c>
       <c r="I308">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K308" t="s">
         <v>1356</v>
@@ -16308,7 +16334,7 @@
       <c r="E309" t="s">
         <v>1127</v>
       </c>
-      <c r="F309" s="1">
+      <c r="F309" s="2">
         <v>46125</v>
       </c>
       <c r="G309" t="s">
@@ -16323,7 +16349,7 @@
       <c r="L309" t="s">
         <v>1383</v>
       </c>
-      <c r="N309" s="1">
+      <c r="N309" s="2">
         <v>46232</v>
       </c>
       <c r="Q309" t="b">
@@ -16346,7 +16372,7 @@
       <c r="E310" t="s">
         <v>1128</v>
       </c>
-      <c r="F310" s="1">
+      <c r="F310" s="2">
         <v>46125</v>
       </c>
       <c r="G310" t="s">
@@ -16356,7 +16382,7 @@
         <v>1353</v>
       </c>
       <c r="I310">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J310">
         <v>107</v>
@@ -16367,7 +16393,7 @@
       <c r="L310" t="s">
         <v>1383</v>
       </c>
-      <c r="N310" s="1">
+      <c r="N310" s="2">
         <v>46232</v>
       </c>
       <c r="Q310" t="b">
@@ -16390,7 +16416,7 @@
       <c r="E311" t="s">
         <v>1129</v>
       </c>
-      <c r="F311" s="1">
+      <c r="F311" s="2">
         <v>46125</v>
       </c>
       <c r="G311" t="s">
@@ -16400,7 +16426,7 @@
         <v>1353</v>
       </c>
       <c r="I311">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K311" t="s">
         <v>1356</v>
@@ -16428,7 +16454,7 @@
       <c r="E312" t="s">
         <v>1130</v>
       </c>
-      <c r="F312" s="1">
+      <c r="F312" s="2">
         <v>46125</v>
       </c>
       <c r="G312" t="s">
@@ -16446,7 +16472,7 @@
       <c r="L312" t="s">
         <v>1383</v>
       </c>
-      <c r="N312" s="1">
+      <c r="N312" s="2">
         <v>46232</v>
       </c>
       <c r="Q312" t="b">
@@ -16469,7 +16495,7 @@
       <c r="E313" t="s">
         <v>1131</v>
       </c>
-      <c r="F313" s="1">
+      <c r="F313" s="2">
         <v>46125</v>
       </c>
       <c r="G313" t="s">
@@ -16504,7 +16530,7 @@
       <c r="E314" t="s">
         <v>1132</v>
       </c>
-      <c r="F314" s="1">
+      <c r="F314" s="2">
         <v>46125</v>
       </c>
       <c r="G314" t="s">
@@ -16519,7 +16545,7 @@
       <c r="L314" t="s">
         <v>1383</v>
       </c>
-      <c r="N314" s="1">
+      <c r="N314" s="2">
         <v>46232</v>
       </c>
       <c r="Q314" t="b">
@@ -16542,7 +16568,7 @@
       <c r="E315" t="s">
         <v>1133</v>
       </c>
-      <c r="F315" s="1">
+      <c r="F315" s="2">
         <v>46125</v>
       </c>
       <c r="G315" t="s">
@@ -16557,7 +16583,7 @@
       <c r="L315" t="s">
         <v>1383</v>
       </c>
-      <c r="N315" s="1">
+      <c r="N315" s="2">
         <v>46232</v>
       </c>
       <c r="Q315" t="b">
@@ -16580,7 +16606,7 @@
       <c r="E316" t="s">
         <v>1134</v>
       </c>
-      <c r="F316" s="1">
+      <c r="F316" s="2">
         <v>46125</v>
       </c>
       <c r="G316" t="s">
@@ -16590,7 +16616,7 @@
         <v>1353</v>
       </c>
       <c r="I316">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K316" t="s">
         <v>1357</v>
@@ -16618,7 +16644,7 @@
       <c r="E317" t="s">
         <v>1135</v>
       </c>
-      <c r="F317" s="1">
+      <c r="F317" s="2">
         <v>46125</v>
       </c>
       <c r="G317" t="s">
@@ -16653,7 +16679,7 @@
       <c r="E318" t="s">
         <v>1136</v>
       </c>
-      <c r="F318" s="1">
+      <c r="F318" s="2">
         <v>46125</v>
       </c>
       <c r="G318" t="s">
@@ -16682,7 +16708,7 @@
       <c r="E319" t="s">
         <v>1137</v>
       </c>
-      <c r="F319" s="1">
+      <c r="F319" s="2">
         <v>46125</v>
       </c>
       <c r="G319" t="s">
@@ -16697,7 +16723,7 @@
       <c r="L319" t="s">
         <v>1434</v>
       </c>
-      <c r="N319" s="1">
+      <c r="N319" s="2">
         <v>46175</v>
       </c>
       <c r="Q319" t="b">
@@ -16720,7 +16746,7 @@
       <c r="E320" t="s">
         <v>1138</v>
       </c>
-      <c r="F320" s="1">
+      <c r="F320" s="2">
         <v>46125</v>
       </c>
       <c r="G320" t="s">
@@ -16730,7 +16756,7 @@
         <v>1353</v>
       </c>
       <c r="I320">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K320" t="s">
         <v>1361</v>
@@ -16758,7 +16784,7 @@
       <c r="E321" t="s">
         <v>1139</v>
       </c>
-      <c r="F321" s="1">
+      <c r="F321" s="2">
         <v>46125</v>
       </c>
       <c r="G321" t="s">
@@ -16768,7 +16794,7 @@
         <v>1353</v>
       </c>
       <c r="I321">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K321" t="s">
         <v>1357</v>
@@ -16796,7 +16822,7 @@
       <c r="E322" t="s">
         <v>1140</v>
       </c>
-      <c r="F322" s="1">
+      <c r="F322" s="2">
         <v>46125</v>
       </c>
       <c r="G322" t="s">
@@ -16806,7 +16832,7 @@
         <v>1353</v>
       </c>
       <c r="I322">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J322">
         <v>57</v>
@@ -16817,7 +16843,7 @@
       <c r="L322" t="s">
         <v>1435</v>
       </c>
-      <c r="N322" s="1">
+      <c r="N322" s="2">
         <v>46182</v>
       </c>
       <c r="Q322" t="b">
@@ -16840,7 +16866,7 @@
       <c r="E323" t="s">
         <v>1141</v>
       </c>
-      <c r="F323" s="1">
+      <c r="F323" s="2">
         <v>46125</v>
       </c>
       <c r="G323" t="s">
@@ -16875,7 +16901,7 @@
       <c r="E324" t="s">
         <v>1142</v>
       </c>
-      <c r="F324" s="1">
+      <c r="F324" s="2">
         <v>46125</v>
       </c>
       <c r="G324" t="s">
@@ -16910,7 +16936,7 @@
       <c r="E325" t="s">
         <v>1143</v>
       </c>
-      <c r="F325" s="1">
+      <c r="F325" s="2">
         <v>46125</v>
       </c>
       <c r="G325" t="s">
@@ -16920,7 +16946,7 @@
         <v>1353</v>
       </c>
       <c r="I325">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J325">
         <v>57</v>
@@ -16931,7 +16957,7 @@
       <c r="L325" t="s">
         <v>1435</v>
       </c>
-      <c r="N325" s="1">
+      <c r="N325" s="2">
         <v>46182</v>
       </c>
       <c r="Q325" t="b">
@@ -16954,7 +16980,7 @@
       <c r="E326" t="s">
         <v>1144</v>
       </c>
-      <c r="F326" s="1">
+      <c r="F326" s="2">
         <v>46125</v>
       </c>
       <c r="G326" t="s">
@@ -16969,7 +16995,7 @@
       <c r="L326" t="s">
         <v>1383</v>
       </c>
-      <c r="N326" s="1">
+      <c r="N326" s="2">
         <v>46232</v>
       </c>
       <c r="Q326" t="b">
@@ -16992,7 +17018,7 @@
       <c r="E327" t="s">
         <v>1140</v>
       </c>
-      <c r="F327" s="1">
+      <c r="F327" s="2">
         <v>46125</v>
       </c>
       <c r="G327" t="s">
@@ -17002,7 +17028,7 @@
         <v>1353</v>
       </c>
       <c r="I327">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J327">
         <v>57</v>
@@ -17013,7 +17039,7 @@
       <c r="L327" t="s">
         <v>1435</v>
       </c>
-      <c r="N327" s="1">
+      <c r="N327" s="2">
         <v>46182</v>
       </c>
       <c r="Q327" t="b">
@@ -17036,7 +17062,7 @@
       <c r="E328" t="s">
         <v>1145</v>
       </c>
-      <c r="F328" s="1">
+      <c r="F328" s="2">
         <v>46125</v>
       </c>
       <c r="G328" t="s">
@@ -17046,7 +17072,7 @@
         <v>1353</v>
       </c>
       <c r="I328">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J328">
         <v>57</v>
@@ -17057,7 +17083,7 @@
       <c r="L328" t="s">
         <v>1435</v>
       </c>
-      <c r="N328" s="1">
+      <c r="N328" s="2">
         <v>46182</v>
       </c>
       <c r="Q328" t="b">
@@ -17080,7 +17106,7 @@
       <c r="E329" t="s">
         <v>1146</v>
       </c>
-      <c r="F329" s="1">
+      <c r="F329" s="2">
         <v>46125</v>
       </c>
       <c r="G329" t="s">
@@ -17090,7 +17116,7 @@
         <v>1353</v>
       </c>
       <c r="I329">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J329">
         <v>57</v>
@@ -17101,7 +17127,7 @@
       <c r="L329" t="s">
         <v>1435</v>
       </c>
-      <c r="N329" s="1">
+      <c r="N329" s="2">
         <v>46182</v>
       </c>
       <c r="Q329" t="b">
@@ -17124,7 +17150,7 @@
       <c r="E330" t="s">
         <v>1147</v>
       </c>
-      <c r="F330" s="1">
+      <c r="F330" s="2">
         <v>46125</v>
       </c>
       <c r="G330" t="s">
@@ -17134,7 +17160,7 @@
         <v>1353</v>
       </c>
       <c r="I330">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J330">
         <v>57</v>
@@ -17145,7 +17171,7 @@
       <c r="L330" t="s">
         <v>1435</v>
       </c>
-      <c r="N330" s="1">
+      <c r="N330" s="2">
         <v>46182</v>
       </c>
       <c r="Q330" t="b">
@@ -17168,7 +17194,7 @@
       <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="F331" s="1">
+      <c r="F331" s="2">
         <v>46125</v>
       </c>
       <c r="G331" t="s">
@@ -17178,7 +17204,7 @@
         <v>1353</v>
       </c>
       <c r="I331">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K331" t="s">
         <v>1356</v>
@@ -17206,7 +17232,7 @@
       <c r="E332" t="s">
         <v>1148</v>
       </c>
-      <c r="F332" s="1">
+      <c r="F332" s="2">
         <v>46125</v>
       </c>
       <c r="G332" t="s">
@@ -17216,7 +17242,7 @@
         <v>1353</v>
       </c>
       <c r="I332">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K332" t="s">
         <v>1357</v>
@@ -17244,7 +17270,7 @@
       <c r="E333" t="s">
         <v>910</v>
       </c>
-      <c r="F333" s="1">
+      <c r="F333" s="2">
         <v>46125</v>
       </c>
       <c r="G333" t="s">
@@ -17254,7 +17280,7 @@
         <v>1353</v>
       </c>
       <c r="I333">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J333">
         <v>100</v>
@@ -17265,7 +17291,7 @@
       <c r="L333" t="s">
         <v>1395</v>
       </c>
-      <c r="N333" s="1">
+      <c r="N333" s="2">
         <v>46225</v>
       </c>
       <c r="Q333" t="b">
@@ -17288,7 +17314,7 @@
       <c r="E334" t="s">
         <v>1149</v>
       </c>
-      <c r="F334" s="1">
+      <c r="F334" s="2">
         <v>46125</v>
       </c>
       <c r="G334" t="s">
@@ -17298,7 +17324,7 @@
         <v>1353</v>
       </c>
       <c r="I334">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K334" t="s">
         <v>1357</v>
@@ -17326,7 +17352,7 @@
       <c r="E335" t="s">
         <v>1150</v>
       </c>
-      <c r="F335" s="1">
+      <c r="F335" s="2">
         <v>46127</v>
       </c>
       <c r="G335" t="s">
@@ -17341,7 +17367,7 @@
       <c r="L335" t="s">
         <v>1434</v>
       </c>
-      <c r="N335" s="1">
+      <c r="N335" s="2">
         <v>46175</v>
       </c>
       <c r="Q335" t="b">
@@ -17364,7 +17390,7 @@
       <c r="E336" t="s">
         <v>1151</v>
       </c>
-      <c r="F336" s="1">
+      <c r="F336" s="2">
         <v>46127</v>
       </c>
       <c r="G336" t="s">
@@ -17374,7 +17400,7 @@
         <v>1353</v>
       </c>
       <c r="I336">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J336">
         <v>28</v>
@@ -17385,7 +17411,7 @@
       <c r="L336" t="s">
         <v>1388</v>
       </c>
-      <c r="N336" s="1">
+      <c r="N336" s="2">
         <v>46155</v>
       </c>
       <c r="Q336" t="b">
@@ -17408,7 +17434,7 @@
       <c r="E337" t="s">
         <v>1152</v>
       </c>
-      <c r="F337" s="1">
+      <c r="F337" s="2">
         <v>46127</v>
       </c>
       <c r="G337" t="s">
@@ -17423,7 +17449,7 @@
       <c r="L337" t="s">
         <v>1434</v>
       </c>
-      <c r="N337" s="1">
+      <c r="N337" s="2">
         <v>46175</v>
       </c>
       <c r="Q337" t="b">
@@ -17446,7 +17472,7 @@
       <c r="E338" t="s">
         <v>1153</v>
       </c>
-      <c r="F338" s="1">
+      <c r="F338" s="2">
         <v>46127</v>
       </c>
       <c r="G338" t="s">
@@ -17456,7 +17482,7 @@
         <v>1353</v>
       </c>
       <c r="I338">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J338">
         <v>12</v>
@@ -17467,7 +17493,7 @@
       <c r="L338" t="s">
         <v>1388</v>
       </c>
-      <c r="N338" s="1">
+      <c r="N338" s="2">
         <v>46139</v>
       </c>
       <c r="Q338" t="b">
@@ -17490,7 +17516,7 @@
       <c r="E339" t="s">
         <v>1154</v>
       </c>
-      <c r="F339" s="1">
+      <c r="F339" s="2">
         <v>46129</v>
       </c>
       <c r="G339" t="s">
@@ -17519,7 +17545,7 @@
       <c r="E340" t="s">
         <v>1155</v>
       </c>
-      <c r="F340" s="1">
+      <c r="F340" s="2">
         <v>46142</v>
       </c>
       <c r="G340" t="s">
@@ -17529,7 +17555,7 @@
         <v>1353</v>
       </c>
       <c r="I340">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J340">
         <v>98</v>
@@ -17537,7 +17563,7 @@
       <c r="L340" t="s">
         <v>1383</v>
       </c>
-      <c r="N340" s="1">
+      <c r="N340" s="2">
         <v>46240</v>
       </c>
       <c r="Q340" t="b">
@@ -17560,7 +17586,7 @@
       <c r="E341" t="s">
         <v>1156</v>
       </c>
-      <c r="F341" s="1">
+      <c r="F341" s="2">
         <v>46142</v>
       </c>
       <c r="G341" t="s">
@@ -17570,7 +17596,7 @@
         <v>1353</v>
       </c>
       <c r="I341">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J341">
         <v>90</v>
@@ -17578,7 +17604,7 @@
       <c r="L341" t="s">
         <v>1383</v>
       </c>
-      <c r="N341" s="1">
+      <c r="N341" s="2">
         <v>46232</v>
       </c>
       <c r="Q341" t="b">
@@ -17601,7 +17627,7 @@
       <c r="E342" t="s">
         <v>1157</v>
       </c>
-      <c r="F342" s="1">
+      <c r="F342" s="2">
         <v>46142</v>
       </c>
       <c r="G342" t="s">
@@ -17611,7 +17637,7 @@
         <v>1353</v>
       </c>
       <c r="I342">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K342" t="s">
         <v>1356</v>
@@ -17639,7 +17665,7 @@
       <c r="E343" t="s">
         <v>1158</v>
       </c>
-      <c r="F343" s="1">
+      <c r="F343" s="2">
         <v>46142</v>
       </c>
       <c r="G343" t="s">
@@ -17654,7 +17680,7 @@
       <c r="L343" t="s">
         <v>1383</v>
       </c>
-      <c r="N343" s="1">
+      <c r="N343" s="2">
         <v>46232</v>
       </c>
       <c r="Q343" t="b">
@@ -17677,7 +17703,7 @@
       <c r="E344" t="s">
         <v>1159</v>
       </c>
-      <c r="F344" s="1">
+      <c r="F344" s="2">
         <v>46142</v>
       </c>
       <c r="G344" t="s">
@@ -17692,7 +17718,7 @@
       <c r="L344" t="s">
         <v>1383</v>
       </c>
-      <c r="N344" s="1">
+      <c r="N344" s="2">
         <v>46232</v>
       </c>
       <c r="Q344" t="b">
@@ -17715,7 +17741,7 @@
       <c r="E345" t="s">
         <v>1160</v>
       </c>
-      <c r="F345" s="1">
+      <c r="F345" s="2">
         <v>46142</v>
       </c>
       <c r="G345" t="s">
@@ -17725,7 +17751,7 @@
         <v>1353</v>
       </c>
       <c r="I345">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K345" t="s">
         <v>1356</v>
@@ -17753,7 +17779,7 @@
       <c r="E346" t="s">
         <v>1161</v>
       </c>
-      <c r="F346" s="1">
+      <c r="F346" s="2">
         <v>46142</v>
       </c>
       <c r="G346" t="s">
@@ -17768,7 +17794,7 @@
       <c r="L346" t="s">
         <v>1383</v>
       </c>
-      <c r="N346" s="1">
+      <c r="N346" s="2">
         <v>46232</v>
       </c>
       <c r="Q346" t="b">
@@ -17791,7 +17817,7 @@
       <c r="E347" t="s">
         <v>1162</v>
       </c>
-      <c r="F347" s="1">
+      <c r="F347" s="2">
         <v>46142</v>
       </c>
       <c r="G347" t="s">
@@ -17801,7 +17827,7 @@
         <v>1353</v>
       </c>
       <c r="I347">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J347">
         <v>18</v>
@@ -17812,7 +17838,7 @@
       <c r="L347" t="s">
         <v>1431</v>
       </c>
-      <c r="N347" s="1">
+      <c r="N347" s="2">
         <v>46160</v>
       </c>
       <c r="Q347" t="b">
@@ -17835,7 +17861,7 @@
       <c r="E348" t="s">
         <v>1163</v>
       </c>
-      <c r="F348" s="1">
+      <c r="F348" s="2">
         <v>46142</v>
       </c>
       <c r="G348" t="s">
@@ -17845,7 +17871,7 @@
         <v>1353</v>
       </c>
       <c r="I348">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J348">
         <v>14</v>
@@ -17856,7 +17882,7 @@
       <c r="L348" t="s">
         <v>1432</v>
       </c>
-      <c r="N348" s="1">
+      <c r="N348" s="2">
         <v>46156</v>
       </c>
       <c r="Q348" t="b">
@@ -17879,7 +17905,7 @@
       <c r="E349" t="s">
         <v>1164</v>
       </c>
-      <c r="F349" s="1">
+      <c r="F349" s="2">
         <v>46142</v>
       </c>
       <c r="G349" t="s">
@@ -17889,7 +17915,7 @@
         <v>1353</v>
       </c>
       <c r="I349">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K349" t="s">
         <v>1361</v>
@@ -17917,7 +17943,7 @@
       <c r="E350" t="s">
         <v>1165</v>
       </c>
-      <c r="F350" s="1">
+      <c r="F350" s="2">
         <v>46142</v>
       </c>
       <c r="G350" t="s">
@@ -17927,12 +17953,12 @@
         <v>1353</v>
       </c>
       <c r="I350">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J350">
         <v>46</v>
       </c>
-      <c r="N350" s="1">
+      <c r="N350" s="2">
         <v>46188</v>
       </c>
       <c r="Q350" t="b">
@@ -17955,7 +17981,7 @@
       <c r="E351" t="s">
         <v>1166</v>
       </c>
-      <c r="F351" s="1">
+      <c r="F351" s="2">
         <v>46142</v>
       </c>
       <c r="G351" t="s">
@@ -17965,7 +17991,7 @@
         <v>1353</v>
       </c>
       <c r="I351">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J351">
         <v>82</v>
@@ -17976,7 +18002,7 @@
       <c r="L351" t="s">
         <v>1436</v>
       </c>
-      <c r="N351" s="1">
+      <c r="N351" s="2">
         <v>46224</v>
       </c>
       <c r="Q351" t="b">
@@ -17999,7 +18025,7 @@
       <c r="E352" t="s">
         <v>1167</v>
       </c>
-      <c r="F352" s="1">
+      <c r="F352" s="2">
         <v>46142</v>
       </c>
       <c r="G352" t="s">
@@ -18009,7 +18035,7 @@
         <v>1353</v>
       </c>
       <c r="I352">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J352">
         <v>78</v>
@@ -18020,7 +18046,7 @@
       <c r="L352" t="s">
         <v>1437</v>
       </c>
-      <c r="N352" s="1">
+      <c r="N352" s="2">
         <v>46220</v>
       </c>
       <c r="Q352" t="b">
@@ -18043,7 +18069,7 @@
       <c r="E353" t="s">
         <v>1168</v>
       </c>
-      <c r="F353" s="1">
+      <c r="F353" s="2">
         <v>46142</v>
       </c>
       <c r="G353" t="s">
@@ -18053,7 +18079,7 @@
         <v>1353</v>
       </c>
       <c r="I353">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J353">
         <v>83</v>
@@ -18064,7 +18090,7 @@
       <c r="L353" t="s">
         <v>1395</v>
       </c>
-      <c r="N353" s="1">
+      <c r="N353" s="2">
         <v>46225</v>
       </c>
       <c r="Q353" t="b">
@@ -18087,7 +18113,7 @@
       <c r="E354" t="s">
         <v>1169</v>
       </c>
-      <c r="F354" s="1">
+      <c r="F354" s="2">
         <v>46142</v>
       </c>
       <c r="G354" t="s">
@@ -18097,7 +18123,7 @@
         <v>1353</v>
       </c>
       <c r="I354">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K354" t="s">
         <v>1360</v>
@@ -18125,7 +18151,7 @@
       <c r="E355" t="s">
         <v>1170</v>
       </c>
-      <c r="F355" s="1">
+      <c r="F355" s="2">
         <v>46142</v>
       </c>
       <c r="G355" t="s">
@@ -18135,7 +18161,7 @@
         <v>1353</v>
       </c>
       <c r="I355">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J355">
         <v>8</v>
@@ -18146,7 +18172,7 @@
       <c r="L355" t="s">
         <v>1438</v>
       </c>
-      <c r="N355" s="1">
+      <c r="N355" s="2">
         <v>46150</v>
       </c>
       <c r="Q355" t="b">
@@ -18169,7 +18195,7 @@
       <c r="E356" t="s">
         <v>1171</v>
       </c>
-      <c r="F356" s="1">
+      <c r="F356" s="2">
         <v>46142</v>
       </c>
       <c r="G356" t="s">
@@ -18184,7 +18210,7 @@
       <c r="L356" t="s">
         <v>1439</v>
       </c>
-      <c r="N356" s="1">
+      <c r="N356" s="2">
         <v>46176</v>
       </c>
       <c r="Q356" t="b">
@@ -18207,7 +18233,7 @@
       <c r="E357" t="s">
         <v>1172</v>
       </c>
-      <c r="F357" s="1">
+      <c r="F357" s="2">
         <v>46142</v>
       </c>
       <c r="G357" t="s">
@@ -18217,7 +18243,7 @@
         <v>1353</v>
       </c>
       <c r="I357">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J357">
         <v>85</v>
@@ -18225,7 +18251,7 @@
       <c r="K357" t="s">
         <v>1360</v>
       </c>
-      <c r="N357" s="1">
+      <c r="N357" s="2">
         <v>46227</v>
       </c>
       <c r="Q357" t="b">
@@ -18248,7 +18274,7 @@
       <c r="E358" t="s">
         <v>1173</v>
       </c>
-      <c r="F358" s="1">
+      <c r="F358" s="2">
         <v>46142</v>
       </c>
       <c r="G358" t="s">
@@ -18266,7 +18292,7 @@
       <c r="L358" t="s">
         <v>1440</v>
       </c>
-      <c r="N358" s="1">
+      <c r="N358" s="2">
         <v>46227</v>
       </c>
       <c r="P358" t="s">
@@ -18292,7 +18318,7 @@
       <c r="E359" t="s">
         <v>1174</v>
       </c>
-      <c r="F359" s="1">
+      <c r="F359" s="2">
         <v>46142</v>
       </c>
       <c r="G359" t="s">
@@ -18304,7 +18330,7 @@
       <c r="J359">
         <v>63</v>
       </c>
-      <c r="N359" s="1">
+      <c r="N359" s="2">
         <v>46205</v>
       </c>
       <c r="P359" t="s">
@@ -18330,7 +18356,7 @@
       <c r="E360" t="s">
         <v>949</v>
       </c>
-      <c r="F360" s="1">
+      <c r="F360" s="2">
         <v>46142</v>
       </c>
       <c r="G360" t="s">
@@ -18340,7 +18366,7 @@
         <v>1353</v>
       </c>
       <c r="I360">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J360">
         <v>83</v>
@@ -18351,7 +18377,7 @@
       <c r="L360" t="s">
         <v>1395</v>
       </c>
-      <c r="N360" s="1">
+      <c r="N360" s="2">
         <v>46225</v>
       </c>
       <c r="O360" t="s">
@@ -18377,7 +18403,7 @@
       <c r="E361" t="s">
         <v>961</v>
       </c>
-      <c r="F361" s="1">
+      <c r="F361" s="2">
         <v>46142</v>
       </c>
       <c r="G361" t="s">
@@ -18387,7 +18413,7 @@
         <v>1353</v>
       </c>
       <c r="I361">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J361">
         <v>83</v>
@@ -18398,7 +18424,7 @@
       <c r="L361" t="s">
         <v>1395</v>
       </c>
-      <c r="N361" s="1">
+      <c r="N361" s="2">
         <v>46225</v>
       </c>
       <c r="Q361" t="b">
@@ -18421,7 +18447,7 @@
       <c r="E362" t="s">
         <v>1175</v>
       </c>
-      <c r="F362" s="1">
+      <c r="F362" s="2">
         <v>46142</v>
       </c>
       <c r="G362" t="s">
@@ -18431,7 +18457,7 @@
         <v>1353</v>
       </c>
       <c r="I362">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K362" t="s">
         <v>1360</v>
@@ -18459,7 +18485,7 @@
       <c r="E363" t="s">
         <v>1176</v>
       </c>
-      <c r="F363" s="1">
+      <c r="F363" s="2">
         <v>46142</v>
       </c>
       <c r="G363" t="s">
@@ -18469,7 +18495,7 @@
         <v>1353</v>
       </c>
       <c r="I363">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K363" t="s">
         <v>1360</v>
@@ -18497,7 +18523,7 @@
       <c r="E364" t="s">
         <v>958</v>
       </c>
-      <c r="F364" s="1">
+      <c r="F364" s="2">
         <v>46142</v>
       </c>
       <c r="G364" t="s">
@@ -18507,7 +18533,7 @@
         <v>1353</v>
       </c>
       <c r="I364">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J364">
         <v>83</v>
@@ -18518,7 +18544,7 @@
       <c r="L364" t="s">
         <v>1395</v>
       </c>
-      <c r="N364" s="1">
+      <c r="N364" s="2">
         <v>46225</v>
       </c>
       <c r="Q364" t="b">
@@ -18541,7 +18567,7 @@
       <c r="E365" t="s">
         <v>1177</v>
       </c>
-      <c r="F365" s="1">
+      <c r="F365" s="2">
         <v>46142</v>
       </c>
       <c r="G365" t="s">
@@ -18551,7 +18577,7 @@
         <v>1353</v>
       </c>
       <c r="I365">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J365">
         <v>15</v>
@@ -18559,7 +18585,7 @@
       <c r="K365" t="s">
         <v>1359</v>
       </c>
-      <c r="N365" s="1">
+      <c r="N365" s="2">
         <v>46157</v>
       </c>
       <c r="Q365" t="b">
@@ -18582,7 +18608,7 @@
       <c r="E366" t="s">
         <v>1178</v>
       </c>
-      <c r="F366" s="1">
+      <c r="F366" s="2">
         <v>46148</v>
       </c>
       <c r="G366" t="s">
@@ -18592,7 +18618,7 @@
         <v>1353</v>
       </c>
       <c r="I366">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J366">
         <v>77</v>
@@ -18603,7 +18629,7 @@
       <c r="L366" t="s">
         <v>1388</v>
       </c>
-      <c r="N366" s="1">
+      <c r="N366" s="2">
         <v>46225</v>
       </c>
       <c r="Q366" t="b">
@@ -18626,7 +18652,7 @@
       <c r="E367" t="s">
         <v>1179</v>
       </c>
-      <c r="F367" s="1">
+      <c r="F367" s="2">
         <v>46148</v>
       </c>
       <c r="G367" t="s">
@@ -18636,7 +18662,7 @@
         <v>1353</v>
       </c>
       <c r="I367">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J367">
         <v>77</v>
@@ -18647,7 +18673,7 @@
       <c r="L367" t="s">
         <v>1388</v>
       </c>
-      <c r="N367" s="1">
+      <c r="N367" s="2">
         <v>46225</v>
       </c>
       <c r="Q367" t="b">
@@ -18670,7 +18696,7 @@
       <c r="E368" t="s">
         <v>1180</v>
       </c>
-      <c r="F368" s="1">
+      <c r="F368" s="2">
         <v>46148</v>
       </c>
       <c r="G368" t="s">
@@ -18680,7 +18706,7 @@
         <v>1353</v>
       </c>
       <c r="I368">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J368">
         <v>77</v>
@@ -18691,7 +18717,7 @@
       <c r="L368" t="s">
         <v>1395</v>
       </c>
-      <c r="N368" s="1">
+      <c r="N368" s="2">
         <v>46225</v>
       </c>
       <c r="Q368" t="b">
@@ -18714,7 +18740,7 @@
       <c r="E369" t="s">
         <v>1181</v>
       </c>
-      <c r="F369" s="1">
+      <c r="F369" s="2">
         <v>46148</v>
       </c>
       <c r="G369" t="s">
@@ -18724,7 +18750,7 @@
         <v>1353</v>
       </c>
       <c r="I369">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K369" t="s">
         <v>1360</v>
@@ -18752,7 +18778,7 @@
       <c r="E370" t="s">
         <v>1182</v>
       </c>
-      <c r="F370" s="1">
+      <c r="F370" s="2">
         <v>46148</v>
       </c>
       <c r="G370" t="s">
@@ -18762,7 +18788,7 @@
         <v>1353</v>
       </c>
       <c r="I370">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K370" t="s">
         <v>1360</v>
@@ -18790,7 +18816,7 @@
       <c r="E371" t="s">
         <v>1183</v>
       </c>
-      <c r="F371" s="1">
+      <c r="F371" s="2">
         <v>46148</v>
       </c>
       <c r="G371" t="s">
@@ -18800,7 +18826,7 @@
         <v>1353</v>
       </c>
       <c r="I371">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J371">
         <v>16</v>
@@ -18811,7 +18837,7 @@
       <c r="L371" t="s">
         <v>1441</v>
       </c>
-      <c r="N371" s="1">
+      <c r="N371" s="2">
         <v>46164</v>
       </c>
       <c r="Q371" t="b">
@@ -18834,7 +18860,7 @@
       <c r="E372" t="s">
         <v>1184</v>
       </c>
-      <c r="F372" s="1">
+      <c r="F372" s="2">
         <v>46148</v>
       </c>
       <c r="G372" t="s">
@@ -18852,7 +18878,7 @@
       <c r="L372" t="s">
         <v>1428</v>
       </c>
-      <c r="N372" s="1">
+      <c r="N372" s="2">
         <v>46113</v>
       </c>
       <c r="P372" t="s">
@@ -18878,7 +18904,7 @@
       <c r="E373" t="s">
         <v>1185</v>
       </c>
-      <c r="F373" s="1">
+      <c r="F373" s="2">
         <v>46149</v>
       </c>
       <c r="G373" t="s">
@@ -18888,7 +18914,7 @@
         <v>1353</v>
       </c>
       <c r="I373">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K373" t="s">
         <v>1356</v>
@@ -18916,7 +18942,7 @@
       <c r="E374" t="s">
         <v>1186</v>
       </c>
-      <c r="F374" s="1">
+      <c r="F374" s="2">
         <v>46149</v>
       </c>
       <c r="G374" t="s">
@@ -18926,7 +18952,7 @@
         <v>1353</v>
       </c>
       <c r="I374">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K374" t="s">
         <v>1356</v>
@@ -18954,7 +18980,7 @@
       <c r="E375" t="s">
         <v>1187</v>
       </c>
-      <c r="F375" s="1">
+      <c r="F375" s="2">
         <v>46154</v>
       </c>
       <c r="G375" t="s">
@@ -18964,7 +18990,7 @@
         <v>1353</v>
       </c>
       <c r="I375">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J375">
         <v>94</v>
@@ -18972,7 +18998,7 @@
       <c r="K375" t="s">
         <v>1360</v>
       </c>
-      <c r="N375" s="1">
+      <c r="N375" s="2">
         <v>46248</v>
       </c>
       <c r="Q375" t="b">
@@ -18995,7 +19021,7 @@
       <c r="E376" t="s">
         <v>1188</v>
       </c>
-      <c r="F376" s="1">
+      <c r="F376" s="2">
         <v>46154</v>
       </c>
       <c r="G376" t="s">
@@ -19005,7 +19031,7 @@
         <v>1353</v>
       </c>
       <c r="I376">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K376" t="s">
         <v>1360</v>
@@ -19033,7 +19059,7 @@
       <c r="E377" t="s">
         <v>1189</v>
       </c>
-      <c r="F377" s="1">
+      <c r="F377" s="2">
         <v>46154</v>
       </c>
       <c r="G377" t="s">
@@ -19045,7 +19071,7 @@
       <c r="K377" t="s">
         <v>1360</v>
       </c>
-      <c r="N377" s="1">
+      <c r="N377" s="2">
         <v>46176</v>
       </c>
       <c r="O377" t="s">
@@ -19074,7 +19100,7 @@
       <c r="E378" t="s">
         <v>1190</v>
       </c>
-      <c r="F378" s="1">
+      <c r="F378" s="2">
         <v>46154</v>
       </c>
       <c r="G378" t="s">
@@ -19084,7 +19110,7 @@
         <v>1353</v>
       </c>
       <c r="I378">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K378" t="s">
         <v>1360</v>
@@ -19112,7 +19138,7 @@
       <c r="E379" t="s">
         <v>1191</v>
       </c>
-      <c r="F379" s="1">
+      <c r="F379" s="2">
         <v>46154</v>
       </c>
       <c r="G379" t="s">
@@ -19122,7 +19148,7 @@
         <v>1353</v>
       </c>
       <c r="I379">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J379">
         <v>20</v>
@@ -19133,7 +19159,7 @@
       <c r="L379" t="s">
         <v>1442</v>
       </c>
-      <c r="N379" s="1">
+      <c r="N379" s="2">
         <v>46174</v>
       </c>
       <c r="Q379" t="b">
@@ -19156,7 +19182,7 @@
       <c r="E380" t="s">
         <v>1192</v>
       </c>
-      <c r="F380" s="1">
+      <c r="F380" s="2">
         <v>46154</v>
       </c>
       <c r="G380" t="s">
@@ -19166,7 +19192,7 @@
         <v>1353</v>
       </c>
       <c r="I380">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J380">
         <v>94</v>
@@ -19177,7 +19203,7 @@
       <c r="L380" t="s">
         <v>1443</v>
       </c>
-      <c r="N380" s="1">
+      <c r="N380" s="2">
         <v>46248</v>
       </c>
       <c r="Q380" t="b">
@@ -19200,7 +19226,7 @@
       <c r="E381" t="s">
         <v>1193</v>
       </c>
-      <c r="F381" s="1">
+      <c r="F381" s="2">
         <v>46154</v>
       </c>
       <c r="G381" t="s">
@@ -19210,7 +19236,7 @@
         <v>1353</v>
       </c>
       <c r="I381">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K381" t="s">
         <v>1360</v>
@@ -19238,7 +19264,7 @@
       <c r="E382" t="s">
         <v>1194</v>
       </c>
-      <c r="F382" s="1">
+      <c r="F382" s="2">
         <v>46154</v>
       </c>
       <c r="G382" t="s">
@@ -19248,7 +19274,7 @@
         <v>1353</v>
       </c>
       <c r="I382">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K382" t="s">
         <v>1360</v>
@@ -19276,7 +19302,7 @@
       <c r="E383" t="s">
         <v>1195</v>
       </c>
-      <c r="F383" s="1">
+      <c r="F383" s="2">
         <v>46154</v>
       </c>
       <c r="G383" t="s">
@@ -19286,7 +19312,7 @@
         <v>1353</v>
       </c>
       <c r="I383">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J383">
         <v>71</v>
@@ -19297,7 +19323,7 @@
       <c r="L383" t="s">
         <v>1444</v>
       </c>
-      <c r="N383" s="1">
+      <c r="N383" s="2">
         <v>46225</v>
       </c>
       <c r="Q383" t="b">
@@ -19320,7 +19346,7 @@
       <c r="E384" t="s">
         <v>1196</v>
       </c>
-      <c r="F384" s="1">
+      <c r="F384" s="2">
         <v>46164</v>
       </c>
       <c r="G384" t="s">
@@ -19330,7 +19356,7 @@
         <v>1353</v>
       </c>
       <c r="I384">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K384" t="s">
         <v>1357</v>
@@ -19358,7 +19384,7 @@
       <c r="E385" t="s">
         <v>1197</v>
       </c>
-      <c r="F385" s="1">
+      <c r="F385" s="2">
         <v>46164</v>
       </c>
       <c r="G385" t="s">
@@ -19368,7 +19394,7 @@
         <v>1353</v>
       </c>
       <c r="I385">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J385">
         <v>102</v>
@@ -19379,7 +19405,7 @@
       <c r="L385" t="s">
         <v>1445</v>
       </c>
-      <c r="N385" s="1">
+      <c r="N385" s="2">
         <v>46266</v>
       </c>
       <c r="P385" t="s">
@@ -19405,7 +19431,7 @@
       <c r="E386" t="s">
         <v>1198</v>
       </c>
-      <c r="F386" s="1">
+      <c r="F386" s="2">
         <v>46171</v>
       </c>
       <c r="G386" t="s">
@@ -19415,7 +19441,7 @@
         <v>1353</v>
       </c>
       <c r="I386">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K386" t="s">
         <v>1360</v>
@@ -19443,7 +19469,7 @@
       <c r="E387" t="s">
         <v>1199</v>
       </c>
-      <c r="F387" s="1">
+      <c r="F387" s="2">
         <v>46171</v>
       </c>
       <c r="G387" t="s">
@@ -19453,7 +19479,7 @@
         <v>1353</v>
       </c>
       <c r="I387">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K387" t="s">
         <v>1360</v>
@@ -19481,7 +19507,7 @@
       <c r="E388" t="s">
         <v>851</v>
       </c>
-      <c r="F388" s="1">
+      <c r="F388" s="2">
         <v>46171</v>
       </c>
       <c r="G388" t="s">
@@ -19491,7 +19517,7 @@
         <v>1353</v>
       </c>
       <c r="I388">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J388">
         <v>-85</v>
@@ -19502,7 +19528,7 @@
       <c r="L388" t="s">
         <v>1446</v>
       </c>
-      <c r="N388" s="1">
+      <c r="N388" s="2">
         <v>46086</v>
       </c>
       <c r="Q388" t="b">
@@ -19525,7 +19551,7 @@
       <c r="E389" t="s">
         <v>1200</v>
       </c>
-      <c r="F389" s="1">
+      <c r="F389" s="2">
         <v>46171</v>
       </c>
       <c r="G389" t="s">
@@ -19535,7 +19561,7 @@
         <v>1353</v>
       </c>
       <c r="I389">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K389" t="s">
         <v>1361</v>
@@ -19563,7 +19589,7 @@
       <c r="E390" t="s">
         <v>1201</v>
       </c>
-      <c r="F390" s="1">
+      <c r="F390" s="2">
         <v>46171</v>
       </c>
       <c r="G390" t="s">
@@ -19581,7 +19607,7 @@
       <c r="L390" t="s">
         <v>1447</v>
       </c>
-      <c r="N390" s="1">
+      <c r="N390" s="2">
         <v>46191</v>
       </c>
       <c r="P390" t="s">
@@ -19607,7 +19633,7 @@
       <c r="E391" t="s">
         <v>1202</v>
       </c>
-      <c r="F391" s="1">
+      <c r="F391" s="2">
         <v>46171</v>
       </c>
       <c r="G391" t="s">
@@ -19645,7 +19671,7 @@
       <c r="E392" t="s">
         <v>1203</v>
       </c>
-      <c r="F392" s="1">
+      <c r="F392" s="2">
         <v>46171</v>
       </c>
       <c r="G392" t="s">
@@ -19660,7 +19686,7 @@
       <c r="L392" t="s">
         <v>1439</v>
       </c>
-      <c r="N392" s="1">
+      <c r="N392" s="2">
         <v>46176</v>
       </c>
       <c r="Q392" t="b">
@@ -19683,7 +19709,7 @@
       <c r="E393" t="s">
         <v>1204</v>
       </c>
-      <c r="F393" s="1">
+      <c r="F393" s="2">
         <v>46171</v>
       </c>
       <c r="G393" t="s">
@@ -19693,7 +19719,7 @@
         <v>1353</v>
       </c>
       <c r="I393">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J393">
         <v>20</v>
@@ -19704,7 +19730,7 @@
       <c r="L393" t="s">
         <v>1388</v>
       </c>
-      <c r="N393" s="1">
+      <c r="N393" s="2">
         <v>46191</v>
       </c>
       <c r="Q393" t="b">
@@ -19727,7 +19753,7 @@
       <c r="E394" t="s">
         <v>1205</v>
       </c>
-      <c r="F394" s="1">
+      <c r="F394" s="2">
         <v>46171</v>
       </c>
       <c r="G394" t="s">
@@ -19745,7 +19771,7 @@
       <c r="L394" t="s">
         <v>1448</v>
       </c>
-      <c r="N394" s="1">
+      <c r="N394" s="2">
         <v>46241</v>
       </c>
       <c r="P394" t="s">
@@ -19771,7 +19797,7 @@
       <c r="E395" t="s">
         <v>1206</v>
       </c>
-      <c r="F395" s="1">
+      <c r="F395" s="2">
         <v>46171</v>
       </c>
       <c r="G395" t="s">
@@ -19789,7 +19815,7 @@
       <c r="L395" t="s">
         <v>1449</v>
       </c>
-      <c r="N395" s="1">
+      <c r="N395" s="2">
         <v>46191</v>
       </c>
       <c r="P395" t="s">
@@ -19815,7 +19841,7 @@
       <c r="E396" t="s">
         <v>1207</v>
       </c>
-      <c r="F396" s="1">
+      <c r="F396" s="2">
         <v>46171</v>
       </c>
       <c r="G396" t="s">
@@ -19827,7 +19853,7 @@
       <c r="J396">
         <v>20</v>
       </c>
-      <c r="N396" s="1">
+      <c r="N396" s="2">
         <v>46191</v>
       </c>
       <c r="P396" t="s">
@@ -19853,7 +19879,7 @@
       <c r="E397" t="s">
         <v>1208</v>
       </c>
-      <c r="F397" s="1">
+      <c r="F397" s="2">
         <v>46171</v>
       </c>
       <c r="G397" t="s">
@@ -19871,7 +19897,7 @@
       <c r="L397" t="s">
         <v>1448</v>
       </c>
-      <c r="N397" s="1">
+      <c r="N397" s="2">
         <v>46241</v>
       </c>
       <c r="P397" t="s">
@@ -19897,7 +19923,7 @@
       <c r="E398" t="s">
         <v>1209</v>
       </c>
-      <c r="F398" s="1">
+      <c r="F398" s="2">
         <v>46171</v>
       </c>
       <c r="G398" t="s">
@@ -19915,7 +19941,7 @@
       <c r="L398" t="s">
         <v>1449</v>
       </c>
-      <c r="N398" s="1">
+      <c r="N398" s="2">
         <v>46191</v>
       </c>
       <c r="P398" t="s">
@@ -19941,7 +19967,7 @@
       <c r="E399" t="s">
         <v>987</v>
       </c>
-      <c r="F399" s="1">
+      <c r="F399" s="2">
         <v>46163</v>
       </c>
       <c r="G399" t="s">
@@ -19956,7 +19982,7 @@
       <c r="L399" t="s">
         <v>1450</v>
       </c>
-      <c r="N399" s="1">
+      <c r="N399" s="2">
         <v>46171</v>
       </c>
       <c r="Q399" t="b">
@@ -19979,7 +20005,7 @@
       <c r="E400" t="s">
         <v>1210</v>
       </c>
-      <c r="F400" s="1">
+      <c r="F400" s="2">
         <v>46171</v>
       </c>
       <c r="G400" t="s">
@@ -19989,7 +20015,7 @@
         <v>1353</v>
       </c>
       <c r="I400">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K400" t="s">
         <v>1360</v>
@@ -20017,7 +20043,7 @@
       <c r="E401" t="s">
         <v>1211</v>
       </c>
-      <c r="F401" s="1">
+      <c r="F401" s="2">
         <v>46171</v>
       </c>
       <c r="G401" t="s">
@@ -20029,7 +20055,7 @@
       <c r="J401">
         <v>40</v>
       </c>
-      <c r="N401" s="1">
+      <c r="N401" s="2">
         <v>46211</v>
       </c>
       <c r="P401" t="s">
@@ -20055,7 +20081,7 @@
       <c r="E402" t="s">
         <v>1212</v>
       </c>
-      <c r="F402" s="1">
+      <c r="F402" s="2">
         <v>46171</v>
       </c>
       <c r="G402" t="s">
@@ -20065,7 +20091,7 @@
         <v>1353</v>
       </c>
       <c r="I402">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K402" t="s">
         <v>1360</v>
@@ -20093,7 +20119,7 @@
       <c r="E403" t="s">
         <v>1213</v>
       </c>
-      <c r="F403" s="1">
+      <c r="F403" s="2">
         <v>46171</v>
       </c>
       <c r="G403" t="s">
@@ -20103,7 +20129,7 @@
         <v>1353</v>
       </c>
       <c r="I403">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J403">
         <v>83</v>
@@ -20114,7 +20140,7 @@
       <c r="L403" t="s">
         <v>1451</v>
       </c>
-      <c r="N403" s="1">
+      <c r="N403" s="2">
         <v>46254</v>
       </c>
       <c r="Q403" t="b">
@@ -20137,7 +20163,7 @@
       <c r="E404" t="s">
         <v>1214</v>
       </c>
-      <c r="F404" s="1">
+      <c r="F404" s="2">
         <v>46171</v>
       </c>
       <c r="G404" t="s">
@@ -20147,7 +20173,7 @@
         <v>1353</v>
       </c>
       <c r="I404">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K404" t="s">
         <v>1360</v>
@@ -20175,7 +20201,7 @@
       <c r="E405" t="s">
         <v>1215</v>
       </c>
-      <c r="F405" s="1">
+      <c r="F405" s="2">
         <v>46183</v>
       </c>
       <c r="G405" t="s">
@@ -20207,7 +20233,7 @@
       <c r="E406" t="s">
         <v>1216</v>
       </c>
-      <c r="F406" s="1">
+      <c r="F406" s="2">
         <v>46183</v>
       </c>
       <c r="G406" t="s">
@@ -20217,7 +20243,7 @@
         <v>1353</v>
       </c>
       <c r="I406">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q406" t="b">
         <v>1</v>
@@ -20239,7 +20265,7 @@
       <c r="E407" t="s">
         <v>1217</v>
       </c>
-      <c r="F407" s="1">
+      <c r="F407" s="2">
         <v>46183</v>
       </c>
       <c r="G407" t="s">
@@ -20249,7 +20275,7 @@
         <v>1353</v>
       </c>
       <c r="I407">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q407" t="b">
         <v>1</v>
@@ -20271,7 +20297,7 @@
       <c r="E408" t="s">
         <v>1218</v>
       </c>
-      <c r="F408" s="1">
+      <c r="F408" s="2">
         <v>46183</v>
       </c>
       <c r="G408" t="s">
@@ -20281,7 +20307,7 @@
         <v>1353</v>
       </c>
       <c r="I408">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q408" t="b">
         <v>1</v>
@@ -20303,7 +20329,7 @@
       <c r="E409" t="s">
         <v>1219</v>
       </c>
-      <c r="F409" s="1">
+      <c r="F409" s="2">
         <v>46183</v>
       </c>
       <c r="G409" t="s">
@@ -20313,7 +20339,7 @@
         <v>1353</v>
       </c>
       <c r="I409">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q409" t="b">
         <v>1</v>
@@ -20335,7 +20361,7 @@
       <c r="E410" t="s">
         <v>1220</v>
       </c>
-      <c r="F410" s="1">
+      <c r="F410" s="2">
         <v>46183</v>
       </c>
       <c r="G410" t="s">
@@ -20345,7 +20371,7 @@
         <v>1353</v>
       </c>
       <c r="I410">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q410" t="b">
         <v>1</v>
@@ -20367,7 +20393,7 @@
       <c r="E411" t="s">
         <v>1221</v>
       </c>
-      <c r="F411" s="1">
+      <c r="F411" s="2">
         <v>46188</v>
       </c>
       <c r="G411" t="s">
@@ -20377,7 +20403,7 @@
         <v>1353</v>
       </c>
       <c r="I411">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q411" t="b">
         <v>1</v>
@@ -20399,7 +20425,7 @@
       <c r="E412" t="s">
         <v>1222</v>
       </c>
-      <c r="F412" s="1">
+      <c r="F412" s="2">
         <v>46188</v>
       </c>
       <c r="G412" t="s">
@@ -20409,7 +20435,7 @@
         <v>1353</v>
       </c>
       <c r="I412">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q412" t="b">
         <v>1</v>
@@ -20431,7 +20457,7 @@
       <c r="E413" t="s">
         <v>1223</v>
       </c>
-      <c r="F413" s="1">
+      <c r="F413" s="2">
         <v>46188</v>
       </c>
       <c r="G413" t="s">
@@ -20441,7 +20467,7 @@
         <v>1353</v>
       </c>
       <c r="I413">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q413" t="b">
         <v>1</v>
@@ -20463,7 +20489,7 @@
       <c r="E414" t="s">
         <v>1224</v>
       </c>
-      <c r="F414" s="1">
+      <c r="F414" s="2">
         <v>46188</v>
       </c>
       <c r="G414" t="s">
@@ -20492,7 +20518,7 @@
       <c r="E415" t="s">
         <v>1060</v>
       </c>
-      <c r="F415" s="1">
+      <c r="F415" s="2">
         <v>46188</v>
       </c>
       <c r="G415" t="s">
@@ -20521,7 +20547,7 @@
       <c r="E416" t="s">
         <v>1225</v>
       </c>
-      <c r="F416" s="1">
+      <c r="F416" s="2">
         <v>46188</v>
       </c>
       <c r="G416" t="s">
@@ -20531,7 +20557,7 @@
         <v>1353</v>
       </c>
       <c r="I416">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q416" t="b">
         <v>1</v>
@@ -20553,7 +20579,7 @@
       <c r="E417" t="s">
         <v>1226</v>
       </c>
-      <c r="F417" s="1">
+      <c r="F417" s="2">
         <v>46188</v>
       </c>
       <c r="G417" t="s">
@@ -20582,7 +20608,7 @@
       <c r="E418" t="s">
         <v>1227</v>
       </c>
-      <c r="F418" s="1">
+      <c r="F418" s="2">
         <v>46188</v>
       </c>
       <c r="G418" t="s">
@@ -20611,7 +20637,7 @@
       <c r="E419" t="s">
         <v>1228</v>
       </c>
-      <c r="F419" s="1">
+      <c r="F419" s="2">
         <v>46188</v>
       </c>
       <c r="G419" t="s">
@@ -20621,7 +20647,7 @@
         <v>1353</v>
       </c>
       <c r="I419">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q419" t="b">
         <v>1</v>
@@ -20643,7 +20669,7 @@
       <c r="E420" t="s">
         <v>1229</v>
       </c>
-      <c r="F420" s="1">
+      <c r="F420" s="2">
         <v>46188</v>
       </c>
       <c r="G420" t="s">
@@ -20653,7 +20679,7 @@
         <v>1353</v>
       </c>
       <c r="I420">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q420" t="b">
         <v>1</v>
@@ -20675,7 +20701,7 @@
       <c r="E421" t="s">
         <v>1230</v>
       </c>
-      <c r="F421" s="1">
+      <c r="F421" s="2">
         <v>46188</v>
       </c>
       <c r="G421" t="s">
@@ -20685,7 +20711,7 @@
         <v>1353</v>
       </c>
       <c r="I421">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q421" t="b">
         <v>1</v>
@@ -20707,7 +20733,7 @@
       <c r="E422" t="s">
         <v>1231</v>
       </c>
-      <c r="F422" s="1">
+      <c r="F422" s="2">
         <v>46188</v>
       </c>
       <c r="G422" t="s">
@@ -20717,7 +20743,7 @@
         <v>1353</v>
       </c>
       <c r="I422">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q422" t="b">
         <v>1</v>
@@ -20739,7 +20765,7 @@
       <c r="E423" t="s">
         <v>1232</v>
       </c>
-      <c r="F423" s="1">
+      <c r="F423" s="2">
         <v>46188</v>
       </c>
       <c r="G423" t="s">
@@ -20749,7 +20775,7 @@
         <v>1353</v>
       </c>
       <c r="I423">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q423" t="b">
         <v>1</v>
@@ -20771,7 +20797,7 @@
       <c r="E424" t="s">
         <v>1233</v>
       </c>
-      <c r="F424" s="1">
+      <c r="F424" s="2">
         <v>46188</v>
       </c>
       <c r="G424" t="s">
@@ -20781,7 +20807,7 @@
         <v>1353</v>
       </c>
       <c r="I424">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q424" t="b">
         <v>1</v>
@@ -20803,7 +20829,7 @@
       <c r="E425" t="s">
         <v>1234</v>
       </c>
-      <c r="F425" s="1">
+      <c r="F425" s="2">
         <v>46188</v>
       </c>
       <c r="G425" t="s">
@@ -20813,7 +20839,7 @@
         <v>1353</v>
       </c>
       <c r="I425">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q425" t="b">
         <v>1</v>
@@ -20835,7 +20861,7 @@
       <c r="E426" t="s">
         <v>1235</v>
       </c>
-      <c r="F426" s="1">
+      <c r="F426" s="2">
         <v>46188</v>
       </c>
       <c r="G426" t="s">
@@ -20845,7 +20871,7 @@
         <v>1353</v>
       </c>
       <c r="I426">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q426" t="b">
         <v>1</v>
@@ -20867,7 +20893,7 @@
       <c r="E427" t="s">
         <v>1236</v>
       </c>
-      <c r="F427" s="1">
+      <c r="F427" s="2">
         <v>46188</v>
       </c>
       <c r="G427" t="s">
@@ -20877,7 +20903,7 @@
         <v>1353</v>
       </c>
       <c r="I427">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q427" t="b">
         <v>1</v>
@@ -20899,7 +20925,7 @@
       <c r="E428" t="s">
         <v>1237</v>
       </c>
-      <c r="F428" s="1">
+      <c r="F428" s="2">
         <v>46188</v>
       </c>
       <c r="G428" t="s">
@@ -20928,7 +20954,7 @@
       <c r="E429" t="s">
         <v>1238</v>
       </c>
-      <c r="F429" s="1">
+      <c r="F429" s="2">
         <v>46188</v>
       </c>
       <c r="G429" t="s">
@@ -20957,7 +20983,7 @@
       <c r="E430" t="s">
         <v>1239</v>
       </c>
-      <c r="F430" s="1">
+      <c r="F430" s="2">
         <v>46188</v>
       </c>
       <c r="G430" t="s">
@@ -20967,7 +20993,7 @@
         <v>1353</v>
       </c>
       <c r="I430">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q430" t="b">
         <v>1</v>
@@ -20989,7 +21015,7 @@
       <c r="E431" t="s">
         <v>1240</v>
       </c>
-      <c r="F431" s="1">
+      <c r="F431" s="2">
         <v>46188</v>
       </c>
       <c r="G431" t="s">
@@ -20999,7 +21025,7 @@
         <v>1353</v>
       </c>
       <c r="I431">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q431" t="b">
         <v>1</v>
@@ -21021,7 +21047,7 @@
       <c r="E432" t="s">
         <v>1241</v>
       </c>
-      <c r="F432" s="1">
+      <c r="F432" s="2">
         <v>46188</v>
       </c>
       <c r="G432" t="s">
@@ -21031,7 +21057,7 @@
         <v>1353</v>
       </c>
       <c r="I432">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q432" t="b">
         <v>1</v>
@@ -21053,7 +21079,7 @@
       <c r="E433" t="s">
         <v>1242</v>
       </c>
-      <c r="F433" s="1">
+      <c r="F433" s="2">
         <v>46188</v>
       </c>
       <c r="G433" t="s">
@@ -21063,7 +21089,7 @@
         <v>1353</v>
       </c>
       <c r="I433">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q433" t="b">
         <v>1</v>
@@ -21085,7 +21111,7 @@
       <c r="E434" t="s">
         <v>1243</v>
       </c>
-      <c r="F434" s="1">
+      <c r="F434" s="2">
         <v>46188</v>
       </c>
       <c r="G434" t="s">
@@ -21095,7 +21121,7 @@
         <v>1353</v>
       </c>
       <c r="I434">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q434" t="b">
         <v>1</v>
@@ -21117,7 +21143,7 @@
       <c r="E435" t="s">
         <v>856</v>
       </c>
-      <c r="F435" s="1">
+      <c r="F435" s="2">
         <v>46188</v>
       </c>
       <c r="G435" t="s">
@@ -21127,7 +21153,7 @@
         <v>1353</v>
       </c>
       <c r="I435">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q435" t="b">
         <v>1</v>
@@ -21149,7 +21175,7 @@
       <c r="E436" t="s">
         <v>1244</v>
       </c>
-      <c r="F436" s="1">
+      <c r="F436" s="2">
         <v>46188</v>
       </c>
       <c r="G436" t="s">
@@ -21159,7 +21185,7 @@
         <v>1353</v>
       </c>
       <c r="I436">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q436" t="b">
         <v>1</v>
@@ -21181,7 +21207,7 @@
       <c r="E437" t="s">
         <v>1245</v>
       </c>
-      <c r="F437" s="1">
+      <c r="F437" s="2">
         <v>46188</v>
       </c>
       <c r="G437" t="s">
@@ -21191,7 +21217,7 @@
         <v>1355</v>
       </c>
       <c r="I437">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q437" t="b">
         <v>1</v>
@@ -21213,7 +21239,7 @@
       <c r="E438" t="s">
         <v>1246</v>
       </c>
-      <c r="F438" s="1">
+      <c r="F438" s="2">
         <v>46188</v>
       </c>
       <c r="G438" t="s">
@@ -21223,7 +21249,7 @@
         <v>1355</v>
       </c>
       <c r="I438">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q438" t="b">
         <v>1</v>
@@ -21245,7 +21271,7 @@
       <c r="E439" t="s">
         <v>1247</v>
       </c>
-      <c r="F439" s="1">
+      <c r="F439" s="2">
         <v>46196</v>
       </c>
       <c r="G439" t="s">
@@ -21255,7 +21281,7 @@
         <v>1353</v>
       </c>
       <c r="I439">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q439" t="b">
         <v>1</v>
@@ -21277,7 +21303,7 @@
       <c r="E440" t="s">
         <v>1248</v>
       </c>
-      <c r="F440" s="1">
+      <c r="F440" s="2">
         <v>46196</v>
       </c>
       <c r="G440" t="s">
@@ -21287,7 +21313,7 @@
         <v>1353</v>
       </c>
       <c r="I440">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q440" t="b">
         <v>1</v>
@@ -21309,7 +21335,7 @@
       <c r="E441" t="s">
         <v>1249</v>
       </c>
-      <c r="F441" s="1">
+      <c r="F441" s="2">
         <v>46203</v>
       </c>
       <c r="G441" t="s">
@@ -21319,7 +21345,7 @@
         <v>1353</v>
       </c>
       <c r="I441">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Q441" t="b">
         <v>1</v>
@@ -21341,7 +21367,7 @@
       <c r="E442" t="s">
         <v>1250</v>
       </c>
-      <c r="F442" s="1">
+      <c r="F442" s="2">
         <v>46203</v>
       </c>
       <c r="G442" t="s">
@@ -21370,7 +21396,7 @@
       <c r="E443" t="s">
         <v>1251</v>
       </c>
-      <c r="F443" s="1">
+      <c r="F443" s="2">
         <v>46205</v>
       </c>
       <c r="G443" t="s">
@@ -21380,7 +21406,7 @@
         <v>1353</v>
       </c>
       <c r="I443">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q443" t="b">
         <v>1</v>
@@ -21402,7 +21428,7 @@
       <c r="E444" t="s">
         <v>1252</v>
       </c>
-      <c r="F444" s="1">
+      <c r="F444" s="2">
         <v>46205</v>
       </c>
       <c r="G444" t="s">
@@ -21431,7 +21457,7 @@
       <c r="E445" t="s">
         <v>1253</v>
       </c>
-      <c r="F445" s="1">
+      <c r="F445" s="2">
         <v>46205</v>
       </c>
       <c r="G445" t="s">
@@ -21460,7 +21486,7 @@
       <c r="E446" t="s">
         <v>1254</v>
       </c>
-      <c r="F446" s="1">
+      <c r="F446" s="2">
         <v>46211</v>
       </c>
       <c r="G446" t="s">
@@ -21470,7 +21496,7 @@
         <v>1353</v>
       </c>
       <c r="I446">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Q446" t="b">
         <v>1</v>
@@ -21492,7 +21518,7 @@
       <c r="E447" t="s">
         <v>1255</v>
       </c>
-      <c r="F447" s="1">
+      <c r="F447" s="2">
         <v>46211</v>
       </c>
       <c r="G447" t="s">
@@ -21502,7 +21528,7 @@
         <v>1353</v>
       </c>
       <c r="I447">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Q447" t="b">
         <v>1</v>
@@ -21524,7 +21550,7 @@
       <c r="E448" t="s">
         <v>1256</v>
       </c>
-      <c r="F448" s="1">
+      <c r="F448" s="2">
         <v>46226</v>
       </c>
       <c r="G448" t="s">
@@ -21534,7 +21560,7 @@
         <v>1353</v>
       </c>
       <c r="I448">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q448" t="b">
         <v>1</v>
@@ -21556,7 +21582,7 @@
       <c r="E449" t="s">
         <v>1257</v>
       </c>
-      <c r="F449" s="1">
+      <c r="F449" s="2">
         <v>46226</v>
       </c>
       <c r="G449" t="s">
@@ -21566,7 +21592,7 @@
         <v>1353</v>
       </c>
       <c r="I449">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q449" t="b">
         <v>1</v>
@@ -21588,7 +21614,7 @@
       <c r="E450" t="s">
         <v>1258</v>
       </c>
-      <c r="F450" s="1">
+      <c r="F450" s="2">
         <v>46226</v>
       </c>
       <c r="G450" t="s">
@@ -21598,7 +21624,7 @@
         <v>1353</v>
       </c>
       <c r="I450">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q450" t="b">
         <v>1</v>
@@ -21620,7 +21646,7 @@
       <c r="E451" t="s">
         <v>1035</v>
       </c>
-      <c r="F451" s="1">
+      <c r="F451" s="2">
         <v>46230</v>
       </c>
       <c r="G451" t="s">
@@ -21630,7 +21656,7 @@
         <v>1353</v>
       </c>
       <c r="I451">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q451" t="b">
         <v>1</v>
@@ -21652,7 +21678,7 @@
       <c r="E452" t="s">
         <v>1259</v>
       </c>
-      <c r="F452" s="1">
+      <c r="F452" s="2">
         <v>46230</v>
       </c>
       <c r="G452" t="s">
@@ -21662,7 +21688,7 @@
         <v>1353</v>
       </c>
       <c r="I452">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q452" t="b">
         <v>1</v>
@@ -21684,7 +21710,7 @@
       <c r="E453" t="s">
         <v>1260</v>
       </c>
-      <c r="F453" s="1">
+      <c r="F453" s="2">
         <v>46230</v>
       </c>
       <c r="G453" t="s">
@@ -21694,7 +21720,7 @@
         <v>1353</v>
       </c>
       <c r="I453">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q453" t="b">
         <v>1</v>
@@ -21716,7 +21742,7 @@
       <c r="E454" t="s">
         <v>1261</v>
       </c>
-      <c r="F454" s="1">
+      <c r="F454" s="2">
         <v>46230</v>
       </c>
       <c r="G454" t="s">
@@ -21726,7 +21752,7 @@
         <v>1353</v>
       </c>
       <c r="I454">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q454" t="b">
         <v>1</v>
@@ -21748,7 +21774,7 @@
       <c r="E455" t="s">
         <v>1262</v>
       </c>
-      <c r="F455" s="1">
+      <c r="F455" s="2">
         <v>46230</v>
       </c>
       <c r="G455" t="s">
@@ -21758,7 +21784,7 @@
         <v>1353</v>
       </c>
       <c r="I455">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q455" t="b">
         <v>1</v>
@@ -21780,7 +21806,7 @@
       <c r="E456" t="s">
         <v>1263</v>
       </c>
-      <c r="F456" s="1">
+      <c r="F456" s="2">
         <v>46230</v>
       </c>
       <c r="G456" t="s">
@@ -21790,7 +21816,7 @@
         <v>1353</v>
       </c>
       <c r="I456">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q456" t="b">
         <v>1</v>
@@ -21812,7 +21838,7 @@
       <c r="E457" t="s">
         <v>1264</v>
       </c>
-      <c r="F457" s="1">
+      <c r="F457" s="2">
         <v>46230</v>
       </c>
       <c r="G457" t="s">
@@ -21822,7 +21848,7 @@
         <v>1353</v>
       </c>
       <c r="I457">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q457" t="b">
         <v>1</v>
@@ -21844,7 +21870,7 @@
       <c r="E458" t="s">
         <v>1202</v>
       </c>
-      <c r="F458" s="1">
+      <c r="F458" s="2">
         <v>46231</v>
       </c>
       <c r="G458" t="s">
@@ -21854,7 +21880,7 @@
         <v>1353</v>
       </c>
       <c r="I458">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q458" t="b">
         <v>1</v>
@@ -21876,7 +21902,7 @@
       <c r="E459" t="s">
         <v>1265</v>
       </c>
-      <c r="F459" s="1">
+      <c r="F459" s="2">
         <v>46233</v>
       </c>
       <c r="G459" t="s">
@@ -21886,7 +21912,7 @@
         <v>1353</v>
       </c>
       <c r="I459">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q459" t="b">
         <v>1</v>
@@ -21908,7 +21934,7 @@
       <c r="E460" t="s">
         <v>1266</v>
       </c>
-      <c r="F460" s="1">
+      <c r="F460" s="2">
         <v>46233</v>
       </c>
       <c r="G460" t="s">
@@ -21918,7 +21944,7 @@
         <v>1353</v>
       </c>
       <c r="I460">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q460" t="b">
         <v>1</v>
@@ -21940,7 +21966,7 @@
       <c r="E461" t="s">
         <v>1267</v>
       </c>
-      <c r="F461" s="1">
+      <c r="F461" s="2">
         <v>46233</v>
       </c>
       <c r="G461" t="s">
@@ -21950,7 +21976,7 @@
         <v>1353</v>
       </c>
       <c r="I461">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q461" t="b">
         <v>1</v>
@@ -21972,7 +21998,7 @@
       <c r="E462" t="s">
         <v>1268</v>
       </c>
-      <c r="F462" s="1">
+      <c r="F462" s="2">
         <v>46233</v>
       </c>
       <c r="G462" t="s">
@@ -21982,7 +22008,7 @@
         <v>1353</v>
       </c>
       <c r="I462">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q462" t="b">
         <v>1</v>
@@ -22004,7 +22030,7 @@
       <c r="E463" t="s">
         <v>1269</v>
       </c>
-      <c r="F463" s="1">
+      <c r="F463" s="2">
         <v>46234</v>
       </c>
       <c r="G463" t="s">
@@ -22014,7 +22040,7 @@
         <v>1353</v>
       </c>
       <c r="I463">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q463" t="b">
         <v>1</v>
@@ -22036,7 +22062,7 @@
       <c r="E464" t="s">
         <v>1270</v>
       </c>
-      <c r="F464" s="1">
+      <c r="F464" s="2">
         <v>46230</v>
       </c>
       <c r="G464" t="s">
@@ -22046,7 +22072,7 @@
         <v>1353</v>
       </c>
       <c r="I464">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q464" t="b">
         <v>1</v>
@@ -22068,7 +22094,7 @@
       <c r="E465" t="s">
         <v>1271</v>
       </c>
-      <c r="F465" s="1">
+      <c r="F465" s="2">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
@@ -22078,7 +22104,7 @@
         <v>1353</v>
       </c>
       <c r="I465">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q465" t="b">
         <v>1</v>
@@ -22100,7 +22126,7 @@
       <c r="E466" t="s">
         <v>1272</v>
       </c>
-      <c r="F466" s="1">
+      <c r="F466" s="2">
         <v>46230</v>
       </c>
       <c r="G466" t="s">
@@ -22110,7 +22136,7 @@
         <v>1353</v>
       </c>
       <c r="I466">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q466" t="b">
         <v>1</v>
@@ -22132,7 +22158,7 @@
       <c r="E467" t="s">
         <v>1273</v>
       </c>
-      <c r="F467" s="1">
+      <c r="F467" s="2">
         <v>46230</v>
       </c>
       <c r="G467" t="s">
@@ -22142,7 +22168,7 @@
         <v>1353</v>
       </c>
       <c r="I467">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q467" t="b">
         <v>1</v>
@@ -22164,7 +22190,7 @@
       <c r="E468" t="s">
         <v>1274</v>
       </c>
-      <c r="F468" s="1">
+      <c r="F468" s="2">
         <v>46230</v>
       </c>
       <c r="G468" t="s">
@@ -22174,7 +22200,7 @@
         <v>1353</v>
       </c>
       <c r="I468">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q468" t="b">
         <v>1</v>
@@ -22196,7 +22222,7 @@
       <c r="E469" t="s">
         <v>1275</v>
       </c>
-      <c r="F469" s="1">
+      <c r="F469" s="2">
         <v>46230</v>
       </c>
       <c r="G469" t="s">
@@ -22206,7 +22232,7 @@
         <v>1353</v>
       </c>
       <c r="I469">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q469" t="b">
         <v>1</v>
@@ -22228,7 +22254,7 @@
       <c r="E470" t="s">
         <v>1276</v>
       </c>
-      <c r="F470" s="1">
+      <c r="F470" s="2">
         <v>46230</v>
       </c>
       <c r="G470" t="s">
@@ -22257,7 +22283,7 @@
       <c r="E471" t="s">
         <v>1277</v>
       </c>
-      <c r="F471" s="1">
+      <c r="F471" s="2">
         <v>46230</v>
       </c>
       <c r="G471" t="s">
@@ -22267,7 +22293,7 @@
         <v>1353</v>
       </c>
       <c r="I471">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q471" t="b">
         <v>1</v>
@@ -22289,7 +22315,7 @@
       <c r="E472" t="s">
         <v>1278</v>
       </c>
-      <c r="F472" s="1">
+      <c r="F472" s="2">
         <v>46230</v>
       </c>
       <c r="G472" t="s">
@@ -22299,7 +22325,7 @@
         <v>1353</v>
       </c>
       <c r="I472">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q472" t="b">
         <v>1</v>
@@ -22321,7 +22347,7 @@
       <c r="E473" t="s">
         <v>1279</v>
       </c>
-      <c r="F473" s="1">
+      <c r="F473" s="2">
         <v>46230</v>
       </c>
       <c r="G473" t="s">
@@ -22331,7 +22357,7 @@
         <v>1353</v>
       </c>
       <c r="I473">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q473" t="b">
         <v>1</v>
@@ -22353,7 +22379,7 @@
       <c r="E474" t="s">
         <v>1280</v>
       </c>
-      <c r="F474" s="1">
+      <c r="F474" s="2">
         <v>46231</v>
       </c>
       <c r="G474" t="s">
@@ -22363,7 +22389,7 @@
         <v>1353</v>
       </c>
       <c r="I474">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q474" t="b">
         <v>1</v>
@@ -22385,7 +22411,7 @@
       <c r="E475" t="s">
         <v>1281</v>
       </c>
-      <c r="F475" s="1">
+      <c r="F475" s="2">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
@@ -22395,7 +22421,7 @@
         <v>1353</v>
       </c>
       <c r="I475">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q475" t="b">
         <v>1</v>
@@ -22417,7 +22443,7 @@
       <c r="E476" t="s">
         <v>1282</v>
       </c>
-      <c r="F476" s="1">
+      <c r="F476" s="2">
         <v>46231</v>
       </c>
       <c r="G476" t="s">
@@ -22427,7 +22453,7 @@
         <v>1353</v>
       </c>
       <c r="I476">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q476" t="b">
         <v>1</v>
@@ -22449,7 +22475,7 @@
       <c r="E477" t="s">
         <v>1283</v>
       </c>
-      <c r="F477" s="1">
+      <c r="F477" s="2">
         <v>46231</v>
       </c>
       <c r="G477" t="s">
@@ -22459,7 +22485,7 @@
         <v>1353</v>
       </c>
       <c r="I477">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q477" t="b">
         <v>1</v>
@@ -22481,7 +22507,7 @@
       <c r="E478" t="s">
         <v>1284</v>
       </c>
-      <c r="F478" s="1">
+      <c r="F478" s="2">
         <v>46231</v>
       </c>
       <c r="G478" t="s">
@@ -22491,7 +22517,7 @@
         <v>1353</v>
       </c>
       <c r="I478">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q478" t="b">
         <v>1</v>
@@ -22513,7 +22539,7 @@
       <c r="E479" t="s">
         <v>1285</v>
       </c>
-      <c r="F479" s="1">
+      <c r="F479" s="2">
         <v>46231</v>
       </c>
       <c r="G479" t="s">
@@ -22523,7 +22549,7 @@
         <v>1353</v>
       </c>
       <c r="I479">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q479" t="b">
         <v>1</v>
@@ -22545,7 +22571,7 @@
       <c r="E480" t="s">
         <v>1286</v>
       </c>
-      <c r="F480" s="1">
+      <c r="F480" s="2">
         <v>46231</v>
       </c>
       <c r="G480" t="s">
@@ -22555,7 +22581,7 @@
         <v>1353</v>
       </c>
       <c r="I480">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q480" t="b">
         <v>1</v>
@@ -22577,7 +22603,7 @@
       <c r="E481" t="s">
         <v>1287</v>
       </c>
-      <c r="F481" s="1">
+      <c r="F481" s="2">
         <v>46231</v>
       </c>
       <c r="G481" t="s">
@@ -22587,7 +22613,7 @@
         <v>1353</v>
       </c>
       <c r="I481">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q481" t="b">
         <v>1</v>
@@ -22609,7 +22635,7 @@
       <c r="E482" t="s">
         <v>1288</v>
       </c>
-      <c r="F482" s="1">
+      <c r="F482" s="2">
         <v>46231</v>
       </c>
       <c r="G482" t="s">
@@ -22619,7 +22645,7 @@
         <v>1353</v>
       </c>
       <c r="I482">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q482" t="b">
         <v>1</v>
@@ -22641,7 +22667,7 @@
       <c r="E483" t="s">
         <v>1289</v>
       </c>
-      <c r="F483" s="1">
+      <c r="F483" s="2">
         <v>46231</v>
       </c>
       <c r="G483" t="s">
@@ -22651,7 +22677,7 @@
         <v>1353</v>
       </c>
       <c r="I483">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q483" t="b">
         <v>1</v>
@@ -22673,7 +22699,7 @@
       <c r="E484" t="s">
         <v>1290</v>
       </c>
-      <c r="F484" s="1">
+      <c r="F484" s="2">
         <v>46231</v>
       </c>
       <c r="G484" t="s">
@@ -22683,7 +22709,7 @@
         <v>1353</v>
       </c>
       <c r="I484">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q484" t="b">
         <v>1</v>
@@ -22705,7 +22731,7 @@
       <c r="E485" t="s">
         <v>1291</v>
       </c>
-      <c r="F485" s="1">
+      <c r="F485" s="2">
         <v>46231</v>
       </c>
       <c r="G485" t="s">
@@ -22715,7 +22741,7 @@
         <v>1353</v>
       </c>
       <c r="I485">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q485" t="b">
         <v>1</v>
@@ -22737,7 +22763,7 @@
       <c r="E486" t="s">
         <v>1292</v>
       </c>
-      <c r="F486" s="1">
+      <c r="F486" s="2">
         <v>46231</v>
       </c>
       <c r="G486" t="s">
@@ -22747,7 +22773,7 @@
         <v>1353</v>
       </c>
       <c r="I486">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q486" t="b">
         <v>1</v>
@@ -22769,7 +22795,7 @@
       <c r="E487" t="s">
         <v>1293</v>
       </c>
-      <c r="F487" s="1">
+      <c r="F487" s="2">
         <v>46231</v>
       </c>
       <c r="G487" t="s">
@@ -22779,7 +22805,7 @@
         <v>1353</v>
       </c>
       <c r="I487">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q487" t="b">
         <v>1</v>
@@ -22801,7 +22827,7 @@
       <c r="E488" t="s">
         <v>1294</v>
       </c>
-      <c r="F488" s="1">
+      <c r="F488" s="2">
         <v>46231</v>
       </c>
       <c r="G488" t="s">
@@ -22811,7 +22837,7 @@
         <v>1353</v>
       </c>
       <c r="I488">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q488" t="b">
         <v>1</v>
@@ -22833,7 +22859,7 @@
       <c r="E489" t="s">
         <v>1295</v>
       </c>
-      <c r="F489" s="1">
+      <c r="F489" s="2">
         <v>46231</v>
       </c>
       <c r="G489" t="s">
@@ -22843,7 +22869,7 @@
         <v>1353</v>
       </c>
       <c r="I489">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q489" t="b">
         <v>1</v>
@@ -22865,7 +22891,7 @@
       <c r="E490" t="s">
         <v>1296</v>
       </c>
-      <c r="F490" s="1">
+      <c r="F490" s="2">
         <v>46231</v>
       </c>
       <c r="G490" t="s">
@@ -22875,7 +22901,7 @@
         <v>1353</v>
       </c>
       <c r="I490">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q490" t="b">
         <v>1</v>
@@ -22897,7 +22923,7 @@
       <c r="E491" t="s">
         <v>1297</v>
       </c>
-      <c r="F491" s="1">
+      <c r="F491" s="2">
         <v>46231</v>
       </c>
       <c r="G491" t="s">
@@ -22907,7 +22933,7 @@
         <v>1353</v>
       </c>
       <c r="I491">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q491" t="b">
         <v>1</v>
@@ -22929,7 +22955,7 @@
       <c r="E492" t="s">
         <v>911</v>
       </c>
-      <c r="F492" s="1">
+      <c r="F492" s="2">
         <v>46231</v>
       </c>
       <c r="G492" t="s">
@@ -22939,7 +22965,7 @@
         <v>1355</v>
       </c>
       <c r="I492">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q492" t="b">
         <v>1</v>
@@ -22961,7 +22987,7 @@
       <c r="E493" t="s">
         <v>995</v>
       </c>
-      <c r="F493" s="1">
+      <c r="F493" s="2">
         <v>46231</v>
       </c>
       <c r="G493" t="s">
@@ -22971,7 +22997,7 @@
         <v>1355</v>
       </c>
       <c r="I493">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q493" t="b">
         <v>1</v>
@@ -22993,7 +23019,7 @@
       <c r="E494" t="s">
         <v>867</v>
       </c>
-      <c r="F494" s="1">
+      <c r="F494" s="2">
         <v>46231</v>
       </c>
       <c r="G494" t="s">
@@ -23003,7 +23029,7 @@
         <v>1355</v>
       </c>
       <c r="I494">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q494" t="b">
         <v>1</v>
@@ -23025,7 +23051,7 @@
       <c r="E495" t="s">
         <v>912</v>
       </c>
-      <c r="F495" s="1">
+      <c r="F495" s="2">
         <v>46231</v>
       </c>
       <c r="G495" t="s">
@@ -23035,7 +23061,7 @@
         <v>1355</v>
       </c>
       <c r="I495">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q495" t="b">
         <v>1</v>
@@ -23057,7 +23083,7 @@
       <c r="E496" t="s">
         <v>1048</v>
       </c>
-      <c r="F496" s="1">
+      <c r="F496" s="2">
         <v>46231</v>
       </c>
       <c r="G496" t="s">
@@ -23067,7 +23093,7 @@
         <v>1355</v>
       </c>
       <c r="I496">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q496" t="b">
         <v>1</v>
@@ -23089,7 +23115,7 @@
       <c r="E497" t="s">
         <v>1298</v>
       </c>
-      <c r="F497" s="1">
+      <c r="F497" s="2">
         <v>46231</v>
       </c>
       <c r="G497" t="s">
@@ -23099,7 +23125,7 @@
         <v>1353</v>
       </c>
       <c r="I497">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q497" t="b">
         <v>1</v>
@@ -23121,7 +23147,7 @@
       <c r="E498" t="s">
         <v>1299</v>
       </c>
-      <c r="F498" s="1">
+      <c r="F498" s="2">
         <v>46231</v>
       </c>
       <c r="G498" t="s">
@@ -23131,7 +23157,7 @@
         <v>1353</v>
       </c>
       <c r="I498">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q498" t="b">
         <v>1</v>
@@ -23153,7 +23179,7 @@
       <c r="E499" t="s">
         <v>1300</v>
       </c>
-      <c r="F499" s="1">
+      <c r="F499" s="2">
         <v>46231</v>
       </c>
       <c r="G499" t="s">
@@ -23163,7 +23189,7 @@
         <v>1355</v>
       </c>
       <c r="I499">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q499" t="b">
         <v>1</v>
@@ -23185,7 +23211,7 @@
       <c r="E500" t="s">
         <v>1301</v>
       </c>
-      <c r="F500" s="1">
+      <c r="F500" s="2">
         <v>46231</v>
       </c>
       <c r="G500" t="s">
@@ -23195,7 +23221,7 @@
         <v>1353</v>
       </c>
       <c r="I500">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q500" t="b">
         <v>1</v>
@@ -23217,7 +23243,7 @@
       <c r="E501" t="s">
         <v>1302</v>
       </c>
-      <c r="F501" s="1">
+      <c r="F501" s="2">
         <v>46231</v>
       </c>
       <c r="G501" t="s">
@@ -23227,7 +23253,7 @@
         <v>1353</v>
       </c>
       <c r="I501">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q501" t="b">
         <v>1</v>
@@ -23249,7 +23275,7 @@
       <c r="E502" t="s">
         <v>1303</v>
       </c>
-      <c r="F502" s="1">
+      <c r="F502" s="2">
         <v>46231</v>
       </c>
       <c r="G502" t="s">
@@ -23259,7 +23285,7 @@
         <v>1353</v>
       </c>
       <c r="I502">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q502" t="b">
         <v>1</v>
@@ -23281,7 +23307,7 @@
       <c r="E503" t="s">
         <v>1304</v>
       </c>
-      <c r="F503" s="1">
+      <c r="F503" s="2">
         <v>46231</v>
       </c>
       <c r="G503" t="s">
@@ -23291,7 +23317,7 @@
         <v>1353</v>
       </c>
       <c r="I503">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q503" t="b">
         <v>1</v>
@@ -23313,7 +23339,7 @@
       <c r="E504" t="s">
         <v>1305</v>
       </c>
-      <c r="F504" s="1">
+      <c r="F504" s="2">
         <v>46232</v>
       </c>
       <c r="G504" t="s">
@@ -23323,7 +23349,7 @@
         <v>1353</v>
       </c>
       <c r="I504">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q504" t="b">
         <v>1</v>
@@ -23345,7 +23371,7 @@
       <c r="E505" t="s">
         <v>1306</v>
       </c>
-      <c r="F505" s="1">
+      <c r="F505" s="2">
         <v>46232</v>
       </c>
       <c r="G505" t="s">
@@ -23355,7 +23381,7 @@
         <v>1353</v>
       </c>
       <c r="I505">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q505" t="b">
         <v>1</v>
@@ -23377,7 +23403,7 @@
       <c r="E506" t="s">
         <v>1307</v>
       </c>
-      <c r="F506" s="1">
+      <c r="F506" s="2">
         <v>46232</v>
       </c>
       <c r="G506" t="s">
@@ -23387,7 +23413,7 @@
         <v>1353</v>
       </c>
       <c r="I506">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q506" t="b">
         <v>1</v>
@@ -23409,7 +23435,7 @@
       <c r="E507" t="s">
         <v>1308</v>
       </c>
-      <c r="F507" s="1">
+      <c r="F507" s="2">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
@@ -23419,7 +23445,7 @@
         <v>1353</v>
       </c>
       <c r="I507">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q507" t="b">
         <v>1</v>
@@ -23441,7 +23467,7 @@
       <c r="E508" t="s">
         <v>1309</v>
       </c>
-      <c r="F508" s="1">
+      <c r="F508" s="2">
         <v>46237</v>
       </c>
       <c r="G508" t="s">
@@ -23470,7 +23496,7 @@
       <c r="E509" t="s">
         <v>1310</v>
       </c>
-      <c r="F509" s="1">
+      <c r="F509" s="2">
         <v>46237</v>
       </c>
       <c r="G509" t="s">
@@ -23480,7 +23506,7 @@
         <v>1353</v>
       </c>
       <c r="I509">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q509" t="b">
         <v>1</v>
@@ -23502,7 +23528,7 @@
       <c r="E510" t="s">
         <v>1311</v>
       </c>
-      <c r="F510" s="1">
+      <c r="F510" s="2">
         <v>46237</v>
       </c>
       <c r="G510" t="s">
@@ -23512,7 +23538,7 @@
         <v>1353</v>
       </c>
       <c r="I510">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q510" t="b">
         <v>1</v>
@@ -23534,7 +23560,7 @@
       <c r="E511" t="s">
         <v>1312</v>
       </c>
-      <c r="F511" s="1">
+      <c r="F511" s="2">
         <v>46240</v>
       </c>
       <c r="G511" t="s">
@@ -23544,7 +23570,7 @@
         <v>1353</v>
       </c>
       <c r="I511">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Q511" t="b">
         <v>1</v>
@@ -23566,7 +23592,7 @@
       <c r="E512" t="s">
         <v>1313</v>
       </c>
-      <c r="F512" s="1">
+      <c r="F512" s="2">
         <v>46240</v>
       </c>
       <c r="G512" t="s">
@@ -23576,7 +23602,7 @@
         <v>1353</v>
       </c>
       <c r="I512">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Q512" t="b">
         <v>1</v>
@@ -23598,7 +23624,7 @@
       <c r="E513" t="s">
         <v>1314</v>
       </c>
-      <c r="F513" s="1">
+      <c r="F513" s="2">
         <v>46244</v>
       </c>
       <c r="G513" t="s">
@@ -23608,7 +23634,7 @@
         <v>1353</v>
       </c>
       <c r="I513">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Q513" t="b">
         <v>1</v>
@@ -23630,7 +23656,7 @@
       <c r="E514" t="s">
         <v>1315</v>
       </c>
-      <c r="F514" s="1">
+      <c r="F514" s="2">
         <v>46244</v>
       </c>
       <c r="G514" t="s">
@@ -23640,7 +23666,7 @@
         <v>1353</v>
       </c>
       <c r="I514">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Q514" t="b">
         <v>1</v>
@@ -23662,7 +23688,7 @@
       <c r="E515" t="s">
         <v>1043</v>
       </c>
-      <c r="F515" s="1">
+      <c r="F515" s="2">
         <v>46244</v>
       </c>
       <c r="G515" t="s">
@@ -23672,7 +23698,7 @@
         <v>1353</v>
       </c>
       <c r="I515">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Q515" t="b">
         <v>1</v>
@@ -23694,7 +23720,7 @@
       <c r="E516" t="s">
         <v>1316</v>
       </c>
-      <c r="F516" s="1">
+      <c r="F516" s="2">
         <v>46252</v>
       </c>
       <c r="G516" t="s">
@@ -23704,7 +23730,7 @@
         <v>1353</v>
       </c>
       <c r="I516">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q516" t="b">
         <v>1</v>
@@ -23726,7 +23752,7 @@
       <c r="E517" t="s">
         <v>1317</v>
       </c>
-      <c r="F517" s="1">
+      <c r="F517" s="2">
         <v>46252</v>
       </c>
       <c r="G517" t="s">
@@ -23736,7 +23762,7 @@
         <v>1353</v>
       </c>
       <c r="I517">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q517" t="b">
         <v>1</v>
@@ -23758,7 +23784,7 @@
       <c r="E518" t="s">
         <v>1318</v>
       </c>
-      <c r="F518" s="1">
+      <c r="F518" s="2">
         <v>46252</v>
       </c>
       <c r="G518" t="s">
@@ -23768,7 +23794,7 @@
         <v>1353</v>
       </c>
       <c r="I518">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q518" t="b">
         <v>1</v>
@@ -23790,7 +23816,7 @@
       <c r="E519" t="s">
         <v>1253</v>
       </c>
-      <c r="F519" s="1">
+      <c r="F519" s="2">
         <v>46254</v>
       </c>
       <c r="G519" t="s">
@@ -23800,7 +23826,7 @@
         <v>1353</v>
       </c>
       <c r="I519">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q519" t="b">
         <v>1</v>
@@ -23822,7 +23848,7 @@
       <c r="E520" t="s">
         <v>1319</v>
       </c>
-      <c r="F520" s="1">
+      <c r="F520" s="2">
         <v>46254</v>
       </c>
       <c r="G520" t="s">
@@ -23832,7 +23858,7 @@
         <v>1353</v>
       </c>
       <c r="I520">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q520" t="b">
         <v>1</v>
@@ -23854,7 +23880,7 @@
       <c r="E521" t="s">
         <v>1320</v>
       </c>
-      <c r="F521" s="1">
+      <c r="F521" s="2">
         <v>46254</v>
       </c>
       <c r="G521" t="s">
@@ -23864,7 +23890,7 @@
         <v>1353</v>
       </c>
       <c r="I521">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q521" t="b">
         <v>1</v>
@@ -23886,7 +23912,7 @@
       <c r="E522" t="s">
         <v>1253</v>
       </c>
-      <c r="F522" s="1">
+      <c r="F522" s="2">
         <v>46254</v>
       </c>
       <c r="G522" t="s">
@@ -23896,7 +23922,7 @@
         <v>1353</v>
       </c>
       <c r="I522">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q522" t="b">
         <v>1</v>
@@ -23918,7 +23944,7 @@
       <c r="E523" t="s">
         <v>1319</v>
       </c>
-      <c r="F523" s="1">
+      <c r="F523" s="2">
         <v>46254</v>
       </c>
       <c r="G523" t="s">
@@ -23928,7 +23954,7 @@
         <v>1353</v>
       </c>
       <c r="I523">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q523" t="b">
         <v>1</v>
@@ -23950,7 +23976,7 @@
       <c r="E524" t="s">
         <v>1321</v>
       </c>
-      <c r="F524" s="1">
+      <c r="F524" s="2">
         <v>46265</v>
       </c>
       <c r="G524" t="s">
@@ -23960,7 +23986,7 @@
         <v>1353</v>
       </c>
       <c r="I524">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q524" t="b">
         <v>1</v>
@@ -23982,7 +24008,7 @@
       <c r="E525" t="s">
         <v>1322</v>
       </c>
-      <c r="F525" s="1">
+      <c r="F525" s="2">
         <v>46265</v>
       </c>
       <c r="G525" t="s">
@@ -23992,7 +24018,7 @@
         <v>1353</v>
       </c>
       <c r="I525">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q525" t="b">
         <v>1</v>
@@ -24014,7 +24040,7 @@
       <c r="E526" t="s">
         <v>1323</v>
       </c>
-      <c r="F526" s="1">
+      <c r="F526" s="2">
         <v>46265</v>
       </c>
       <c r="G526" t="s">
@@ -24024,7 +24050,7 @@
         <v>1353</v>
       </c>
       <c r="I526">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q526" t="b">
         <v>1</v>
@@ -24046,7 +24072,7 @@
       <c r="E527" t="s">
         <v>1324</v>
       </c>
-      <c r="F527" s="1">
+      <c r="F527" s="2">
         <v>46265</v>
       </c>
       <c r="G527" t="s">
@@ -24056,7 +24082,7 @@
         <v>1353</v>
       </c>
       <c r="I527">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q527" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
@@ -4520,8 +4520,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -4537,7 +4545,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4545,12 +4553,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4850,55 +4876,55 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4918,7 +4944,7 @@
       <c r="E2" t="s">
         <v>829</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>45698</v>
       </c>
       <c r="G2" t="s">
@@ -4928,7 +4954,7 @@
         <v>1353</v>
       </c>
       <c r="I2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="K2" t="s">
         <v>1356</v>
@@ -4956,7 +4982,7 @@
       <c r="E3" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>45714</v>
       </c>
       <c r="G3" t="s">
@@ -4966,7 +4992,7 @@
         <v>1353</v>
       </c>
       <c r="I3">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K3" t="s">
         <v>1357</v>
@@ -4994,7 +5020,7 @@
       <c r="E4" t="s">
         <v>831</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>45714</v>
       </c>
       <c r="G4" t="s">
@@ -5004,7 +5030,7 @@
         <v>1353</v>
       </c>
       <c r="I4">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K4" t="s">
         <v>1357</v>
@@ -5032,7 +5058,7 @@
       <c r="E5" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>45714</v>
       </c>
       <c r="G5" t="s">
@@ -5042,7 +5068,7 @@
         <v>1353</v>
       </c>
       <c r="I5">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J5">
         <v>279</v>
@@ -5053,7 +5079,7 @@
       <c r="L5" t="s">
         <v>1367</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <v>45993</v>
       </c>
       <c r="Q5" t="b">
@@ -5076,7 +5102,7 @@
       <c r="E6" t="s">
         <v>833</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>45736</v>
       </c>
       <c r="G6" t="s">
@@ -5086,7 +5112,7 @@
         <v>1353</v>
       </c>
       <c r="I6">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J6">
         <v>153</v>
@@ -5097,7 +5123,7 @@
       <c r="L6" t="s">
         <v>1368</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="2">
         <v>45889</v>
       </c>
       <c r="Q6" t="b">
@@ -5120,7 +5146,7 @@
       <c r="E7" t="s">
         <v>834</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>45736</v>
       </c>
       <c r="G7" t="s">
@@ -5130,7 +5156,7 @@
         <v>1353</v>
       </c>
       <c r="I7">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J7">
         <v>112</v>
@@ -5141,7 +5167,7 @@
       <c r="L7" t="s">
         <v>1369</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="2">
         <v>45848</v>
       </c>
       <c r="O7" t="s">
@@ -5167,7 +5193,7 @@
       <c r="E8" t="s">
         <v>835</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>45736</v>
       </c>
       <c r="G8" t="s">
@@ -5196,7 +5222,7 @@
       <c r="E9" t="s">
         <v>836</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="2">
         <v>45736</v>
       </c>
       <c r="G9" t="s">
@@ -5206,7 +5232,7 @@
         <v>1353</v>
       </c>
       <c r="I9">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J9">
         <v>362</v>
@@ -5217,7 +5243,7 @@
       <c r="L9" t="s">
         <v>1370</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="2">
         <v>46098</v>
       </c>
       <c r="O9">
@@ -5243,7 +5269,7 @@
       <c r="E10" t="s">
         <v>837</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="2">
         <v>45736</v>
       </c>
       <c r="G10" t="s">
@@ -5253,7 +5279,7 @@
         <v>1353</v>
       </c>
       <c r="I10">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J10">
         <v>378</v>
@@ -5264,7 +5290,7 @@
       <c r="L10" t="s">
         <v>1371</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="2">
         <v>46114</v>
       </c>
       <c r="O10" t="s">
@@ -5290,7 +5316,7 @@
       <c r="E11" t="s">
         <v>838</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <v>45736</v>
       </c>
       <c r="G11" t="s">
@@ -5300,7 +5326,7 @@
         <v>1353</v>
       </c>
       <c r="I11">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J11">
         <v>112</v>
@@ -5311,7 +5337,7 @@
       <c r="L11" t="s">
         <v>1369</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="2">
         <v>45848</v>
       </c>
       <c r="O11" t="s">
@@ -5337,7 +5363,7 @@
       <c r="E12" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="2">
         <v>45736</v>
       </c>
       <c r="G12" t="s">
@@ -5347,7 +5373,7 @@
         <v>1353</v>
       </c>
       <c r="I12">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J12">
         <v>124</v>
@@ -5358,7 +5384,7 @@
       <c r="L12" t="s">
         <v>1372</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="2">
         <v>45860</v>
       </c>
       <c r="Q12" t="b">
@@ -5381,7 +5407,7 @@
       <c r="E13" t="s">
         <v>840</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <v>45736</v>
       </c>
       <c r="G13" t="s">
@@ -5410,7 +5436,7 @@
       <c r="E14" t="s">
         <v>841</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="2">
         <v>45736</v>
       </c>
       <c r="G14" t="s">
@@ -5420,7 +5446,7 @@
         <v>1353</v>
       </c>
       <c r="I14">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J14">
         <v>64</v>
@@ -5431,7 +5457,7 @@
       <c r="L14" t="s">
         <v>1373</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N14" s="2">
         <v>45800</v>
       </c>
       <c r="Q14" t="b">
@@ -5454,7 +5480,7 @@
       <c r="E15" t="s">
         <v>842</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="2">
         <v>45736</v>
       </c>
       <c r="G15" t="s">
@@ -5464,7 +5490,7 @@
         <v>1353</v>
       </c>
       <c r="I15">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K15" t="s">
         <v>1359</v>
@@ -5492,7 +5518,7 @@
       <c r="E16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <v>45736</v>
       </c>
       <c r="G16" t="s">
@@ -5502,7 +5528,7 @@
         <v>1353</v>
       </c>
       <c r="I16">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K16" t="s">
         <v>1356</v>
@@ -5530,7 +5556,7 @@
       <c r="E17" t="s">
         <v>844</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="2">
         <v>45736</v>
       </c>
       <c r="G17" t="s">
@@ -5540,7 +5566,7 @@
         <v>1353</v>
       </c>
       <c r="I17">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J17">
         <v>161</v>
@@ -5551,7 +5577,7 @@
       <c r="L17" t="s">
         <v>1368</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17" s="2">
         <v>45897</v>
       </c>
       <c r="Q17" t="b">
@@ -5574,7 +5600,7 @@
       <c r="E18" t="s">
         <v>845</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <v>45736</v>
       </c>
       <c r="G18" t="s">
@@ -5584,7 +5610,7 @@
         <v>1353</v>
       </c>
       <c r="I18">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J18">
         <v>66</v>
@@ -5595,7 +5621,7 @@
       <c r="L18" t="s">
         <v>1373</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="2">
         <v>45802</v>
       </c>
       <c r="Q18" t="b">
@@ -5618,7 +5644,7 @@
       <c r="E19" t="s">
         <v>846</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="2">
         <v>45736</v>
       </c>
       <c r="G19" t="s">
@@ -5647,7 +5673,7 @@
       <c r="E20" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="2">
         <v>45736</v>
       </c>
       <c r="G20" t="s">
@@ -5657,7 +5683,7 @@
         <v>1353</v>
       </c>
       <c r="I20">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J20">
         <v>399</v>
@@ -5668,7 +5694,7 @@
       <c r="L20" t="s">
         <v>1374</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20" s="2">
         <v>46135</v>
       </c>
       <c r="Q20" t="b">
@@ -5691,7 +5717,7 @@
       <c r="E21" t="s">
         <v>848</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="2">
         <v>45736</v>
       </c>
       <c r="G21" t="s">
@@ -5720,7 +5746,7 @@
       <c r="E22" t="s">
         <v>849</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="2">
         <v>45736</v>
       </c>
       <c r="G22" t="s">
@@ -5730,7 +5756,7 @@
         <v>1353</v>
       </c>
       <c r="I22">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K22" t="s">
         <v>1360</v>
@@ -5758,7 +5784,7 @@
       <c r="E23" t="s">
         <v>850</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <v>45736</v>
       </c>
       <c r="G23" t="s">
@@ -5768,7 +5794,7 @@
         <v>1353</v>
       </c>
       <c r="I23">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J23">
         <v>229</v>
@@ -5779,7 +5805,7 @@
       <c r="L23" t="s">
         <v>1375</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23" s="2">
         <v>45965</v>
       </c>
       <c r="P23" t="s">
@@ -5805,7 +5831,7 @@
       <c r="E24" t="s">
         <v>851</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="2">
         <v>45736</v>
       </c>
       <c r="G24" t="s">
@@ -5834,7 +5860,7 @@
       <c r="E25" t="s">
         <v>852</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="2">
         <v>45736</v>
       </c>
       <c r="G25" t="s">
@@ -5863,7 +5889,7 @@
       <c r="E26" t="s">
         <v>853</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="2">
         <v>45736</v>
       </c>
       <c r="G26" t="s">
@@ -5873,7 +5899,7 @@
         <v>1353</v>
       </c>
       <c r="I26">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J26">
         <v>155</v>
@@ -5884,7 +5910,7 @@
       <c r="L26" t="s">
         <v>1376</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N26" s="2">
         <v>45891</v>
       </c>
       <c r="P26" t="s">
@@ -5910,7 +5936,7 @@
       <c r="E27" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="2">
         <v>45736</v>
       </c>
       <c r="G27" t="s">
@@ -5920,7 +5946,7 @@
         <v>1353</v>
       </c>
       <c r="I27">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K27" t="s">
         <v>1360</v>
@@ -5948,7 +5974,7 @@
       <c r="E28" t="s">
         <v>855</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="2">
         <v>45736</v>
       </c>
       <c r="G28" t="s">
@@ -5977,7 +6003,7 @@
       <c r="E29" t="s">
         <v>856</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="2">
         <v>45736</v>
       </c>
       <c r="G29" t="s">
@@ -6006,7 +6032,7 @@
       <c r="E30" t="s">
         <v>857</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="2">
         <v>45736</v>
       </c>
       <c r="G30" t="s">
@@ -6016,7 +6042,7 @@
         <v>1353</v>
       </c>
       <c r="I30">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J30">
         <v>209</v>
@@ -6027,7 +6053,7 @@
       <c r="L30" t="s">
         <v>1377</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30" s="2">
         <v>45945</v>
       </c>
       <c r="Q30" t="b">
@@ -6050,7 +6076,7 @@
       <c r="E31" t="s">
         <v>858</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="2">
         <v>45736</v>
       </c>
       <c r="G31" t="s">
@@ -6079,7 +6105,7 @@
       <c r="E32" t="s">
         <v>859</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="2">
         <v>45736</v>
       </c>
       <c r="G32" t="s">
@@ -6089,7 +6115,7 @@
         <v>1353</v>
       </c>
       <c r="I32">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K32" t="s">
         <v>1356</v>
@@ -6117,7 +6143,7 @@
       <c r="E33" t="s">
         <v>860</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="2">
         <v>45736</v>
       </c>
       <c r="G33" t="s">
@@ -6146,7 +6172,7 @@
       <c r="E34" t="s">
         <v>861</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="2">
         <v>45736</v>
       </c>
       <c r="G34" t="s">
@@ -6175,7 +6201,7 @@
       <c r="E35" t="s">
         <v>862</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="2">
         <v>45736</v>
       </c>
       <c r="G35" t="s">
@@ -6204,7 +6230,7 @@
       <c r="E36" t="s">
         <v>863</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="2">
         <v>45736</v>
       </c>
       <c r="G36" t="s">
@@ -6233,7 +6259,7 @@
       <c r="E37" t="s">
         <v>864</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="2">
         <v>45736</v>
       </c>
       <c r="G37" t="s">
@@ -6262,7 +6288,7 @@
       <c r="E38" t="s">
         <v>844</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="2">
         <v>45736</v>
       </c>
       <c r="G38" t="s">
@@ -6288,7 +6314,7 @@
       <c r="D39" t="s">
         <v>731</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="2">
         <v>45736</v>
       </c>
       <c r="G39" t="s">
@@ -6298,7 +6324,7 @@
         <v>1353</v>
       </c>
       <c r="I39">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K39" t="s">
         <v>1361</v>
@@ -6323,7 +6349,7 @@
       <c r="D40" t="s">
         <v>731</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="2">
         <v>45736</v>
       </c>
       <c r="G40" t="s">
@@ -6333,7 +6359,7 @@
         <v>1353</v>
       </c>
       <c r="I40">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K40" t="s">
         <v>1359</v>
@@ -6361,7 +6387,7 @@
       <c r="E41" t="s">
         <v>865</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="2">
         <v>45736</v>
       </c>
       <c r="G41" t="s">
@@ -6390,7 +6416,7 @@
       <c r="E42" t="s">
         <v>866</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="2">
         <v>45736</v>
       </c>
       <c r="G42" t="s">
@@ -6419,7 +6445,7 @@
       <c r="E43" t="s">
         <v>867</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="2">
         <v>45736</v>
       </c>
       <c r="G43" t="s">
@@ -6454,7 +6480,7 @@
       <c r="E44" t="s">
         <v>868</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="2">
         <v>45769</v>
       </c>
       <c r="G44" t="s">
@@ -6464,7 +6490,7 @@
         <v>1353</v>
       </c>
       <c r="I44">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J44">
         <v>87</v>
@@ -6475,7 +6501,7 @@
       <c r="L44" t="s">
         <v>1378</v>
       </c>
-      <c r="N44" s="1">
+      <c r="N44" s="2">
         <v>45856</v>
       </c>
       <c r="P44" t="s">
@@ -6501,7 +6527,7 @@
       <c r="E45" t="s">
         <v>869</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="2">
         <v>45769</v>
       </c>
       <c r="G45" t="s">
@@ -6511,7 +6537,7 @@
         <v>1353</v>
       </c>
       <c r="I45">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J45">
         <v>331</v>
@@ -6522,7 +6548,7 @@
       <c r="L45" t="s">
         <v>1379</v>
       </c>
-      <c r="N45" s="1">
+      <c r="N45" s="2">
         <v>46100</v>
       </c>
       <c r="O45">
@@ -6548,7 +6574,7 @@
       <c r="E46" t="s">
         <v>870</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="2">
         <v>45769</v>
       </c>
       <c r="G46" t="s">
@@ -6558,7 +6584,7 @@
         <v>1353</v>
       </c>
       <c r="I46">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K46" t="s">
         <v>1360</v>
@@ -6586,7 +6612,7 @@
       <c r="E47" t="s">
         <v>871</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="2">
         <v>45769</v>
       </c>
       <c r="G47" t="s">
@@ -6596,7 +6622,7 @@
         <v>1353</v>
       </c>
       <c r="I47">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J47">
         <v>344</v>
@@ -6607,7 +6633,7 @@
       <c r="L47" t="s">
         <v>1380</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N47" s="2">
         <v>46113</v>
       </c>
       <c r="P47" t="s">
@@ -6633,7 +6659,7 @@
       <c r="E48" t="s">
         <v>872</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="2">
         <v>45769</v>
       </c>
       <c r="G48" t="s">
@@ -6643,7 +6669,7 @@
         <v>1353</v>
       </c>
       <c r="I48">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K48" t="s">
         <v>1360</v>
@@ -6671,7 +6697,7 @@
       <c r="E49" t="s">
         <v>873</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="2">
         <v>45769</v>
       </c>
       <c r="G49" t="s">
@@ -6700,7 +6726,7 @@
       <c r="E50" t="s">
         <v>874</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="2">
         <v>45769</v>
       </c>
       <c r="G50" t="s">
@@ -6710,7 +6736,7 @@
         <v>1353</v>
       </c>
       <c r="I50">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K50" t="s">
         <v>1360</v>
@@ -6738,7 +6764,7 @@
       <c r="E51" t="s">
         <v>875</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="2">
         <v>45769</v>
       </c>
       <c r="G51" t="s">
@@ -6767,7 +6793,7 @@
       <c r="E52" t="s">
         <v>876</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="2">
         <v>45769</v>
       </c>
       <c r="G52" t="s">
@@ -6777,7 +6803,7 @@
         <v>1353</v>
       </c>
       <c r="I52">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K52" t="s">
         <v>1356</v>
@@ -6805,7 +6831,7 @@
       <c r="E53" t="s">
         <v>877</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="2">
         <v>45769</v>
       </c>
       <c r="G53" t="s">
@@ -6815,7 +6841,7 @@
         <v>1353</v>
       </c>
       <c r="I53">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K53" t="s">
         <v>1357</v>
@@ -6843,7 +6869,7 @@
       <c r="E54" t="s">
         <v>878</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="2">
         <v>45769</v>
       </c>
       <c r="G54" t="s">
@@ -6853,7 +6879,7 @@
         <v>1353</v>
       </c>
       <c r="I54">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K54" t="s">
         <v>1357</v>
@@ -6881,7 +6907,7 @@
       <c r="E55" t="s">
         <v>879</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="2">
         <v>45769</v>
       </c>
       <c r="G55" t="s">
@@ -6910,7 +6936,7 @@
       <c r="E56" t="s">
         <v>880</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="2">
         <v>45769</v>
       </c>
       <c r="G56" t="s">
@@ -6939,7 +6965,7 @@
       <c r="E57" t="s">
         <v>881</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="2">
         <v>45769</v>
       </c>
       <c r="G57" t="s">
@@ -6949,7 +6975,7 @@
         <v>1353</v>
       </c>
       <c r="I57">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K57" t="s">
         <v>1360</v>
@@ -6977,7 +7003,7 @@
       <c r="E58" t="s">
         <v>882</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="2">
         <v>45769</v>
       </c>
       <c r="G58" t="s">
@@ -7006,7 +7032,7 @@
       <c r="E59" t="s">
         <v>883</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="2">
         <v>45769</v>
       </c>
       <c r="G59" t="s">
@@ -7035,7 +7061,7 @@
       <c r="E60" t="s">
         <v>884</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="2">
         <v>45769</v>
       </c>
       <c r="G60" t="s">
@@ -7064,7 +7090,7 @@
       <c r="E61" t="s">
         <v>885</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="2">
         <v>45769</v>
       </c>
       <c r="G61" t="s">
@@ -7093,7 +7119,7 @@
       <c r="E62" t="s">
         <v>886</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="2">
         <v>45770</v>
       </c>
       <c r="G62" t="s">
@@ -7122,7 +7148,7 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="2">
         <v>45799</v>
       </c>
       <c r="G63" t="s">
@@ -7132,7 +7158,7 @@
         <v>1353</v>
       </c>
       <c r="I63">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J63">
         <v>293</v>
@@ -7143,7 +7169,7 @@
       <c r="L63" t="s">
         <v>1381</v>
       </c>
-      <c r="N63" s="1">
+      <c r="N63" s="2">
         <v>46092</v>
       </c>
       <c r="P63" t="s">
@@ -7169,7 +7195,7 @@
       <c r="E64" t="s">
         <v>888</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="2">
         <v>45799</v>
       </c>
       <c r="G64" t="s">
@@ -7179,7 +7205,7 @@
         <v>1353</v>
       </c>
       <c r="I64">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J64">
         <v>320</v>
@@ -7190,7 +7216,7 @@
       <c r="L64" t="s">
         <v>1382</v>
       </c>
-      <c r="N64" s="1">
+      <c r="N64" s="2">
         <v>46119</v>
       </c>
       <c r="Q64" t="b">
@@ -7213,7 +7239,7 @@
       <c r="E65" t="s">
         <v>889</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="2">
         <v>45799</v>
       </c>
       <c r="G65" t="s">
@@ -7242,7 +7268,7 @@
       <c r="E66" t="s">
         <v>890</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="2">
         <v>45799</v>
       </c>
       <c r="G66" t="s">
@@ -7271,7 +7297,7 @@
       <c r="E67" t="s">
         <v>891</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="2">
         <v>45799</v>
       </c>
       <c r="G67" t="s">
@@ -7300,7 +7326,7 @@
       <c r="E68" t="s">
         <v>892</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="2">
         <v>45799</v>
       </c>
       <c r="G68" t="s">
@@ -7329,7 +7355,7 @@
       <c r="E69" t="s">
         <v>893</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="2">
         <v>45803</v>
       </c>
       <c r="G69" t="s">
@@ -7358,7 +7384,7 @@
       <c r="E70" t="s">
         <v>894</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="2">
         <v>45803</v>
       </c>
       <c r="G70" t="s">
@@ -7368,7 +7394,7 @@
         <v>1353</v>
       </c>
       <c r="I70">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J70">
         <v>429</v>
@@ -7379,7 +7405,7 @@
       <c r="L70" t="s">
         <v>1383</v>
       </c>
-      <c r="N70" s="1">
+      <c r="N70" s="2">
         <v>46232</v>
       </c>
       <c r="Q70" t="b">
@@ -7402,7 +7428,7 @@
       <c r="E71" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="2">
         <v>45803</v>
       </c>
       <c r="G71" t="s">
@@ -7412,7 +7438,7 @@
         <v>1353</v>
       </c>
       <c r="I71">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J71">
         <v>429</v>
@@ -7423,7 +7449,7 @@
       <c r="L71" t="s">
         <v>1383</v>
       </c>
-      <c r="N71" s="1">
+      <c r="N71" s="2">
         <v>46232</v>
       </c>
       <c r="Q71" t="b">
@@ -7446,7 +7472,7 @@
       <c r="E72" t="s">
         <v>896</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="2">
         <v>45803</v>
       </c>
       <c r="G72" t="s">
@@ -7475,7 +7501,7 @@
       <c r="E73" t="s">
         <v>897</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="2">
         <v>45803</v>
       </c>
       <c r="G73" t="s">
@@ -7485,7 +7511,7 @@
         <v>1353</v>
       </c>
       <c r="I73">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K73" t="s">
         <v>1356</v>
@@ -7513,7 +7539,7 @@
       <c r="E74" t="s">
         <v>896</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="2">
         <v>45803</v>
       </c>
       <c r="G74" t="s">
@@ -7542,7 +7568,7 @@
       <c r="E75" t="s">
         <v>898</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="2">
         <v>45803</v>
       </c>
       <c r="G75" t="s">
@@ -7552,7 +7578,7 @@
         <v>1353</v>
       </c>
       <c r="I75">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J75">
         <v>429</v>
@@ -7563,7 +7589,7 @@
       <c r="L75" t="s">
         <v>1383</v>
       </c>
-      <c r="N75" s="1">
+      <c r="N75" s="2">
         <v>46232</v>
       </c>
       <c r="Q75" t="b">
@@ -7586,7 +7612,7 @@
       <c r="E76" t="s">
         <v>899</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="2">
         <v>45803</v>
       </c>
       <c r="G76" t="s">
@@ -7596,7 +7622,7 @@
         <v>1353</v>
       </c>
       <c r="I76">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K76" t="s">
         <v>1363</v>
@@ -7621,7 +7647,7 @@
       <c r="E77" t="s">
         <v>900</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="2">
         <v>45803</v>
       </c>
       <c r="G77" t="s">
@@ -7650,7 +7676,7 @@
       <c r="E78" t="s">
         <v>901</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78" s="2">
         <v>45803</v>
       </c>
       <c r="G78" t="s">
@@ -7679,7 +7705,7 @@
       <c r="E79" t="s">
         <v>902</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="2">
         <v>45803</v>
       </c>
       <c r="G79" t="s">
@@ -7689,7 +7715,7 @@
         <v>1353</v>
       </c>
       <c r="I79">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K79" t="s">
         <v>1363</v>
@@ -7714,7 +7740,7 @@
       <c r="E80" t="s">
         <v>903</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="2">
         <v>45803</v>
       </c>
       <c r="G80" t="s">
@@ -7724,7 +7750,7 @@
         <v>1353</v>
       </c>
       <c r="I80">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J80">
         <v>429</v>
@@ -7735,7 +7761,7 @@
       <c r="L80" t="s">
         <v>1383</v>
       </c>
-      <c r="N80" s="1">
+      <c r="N80" s="2">
         <v>46232</v>
       </c>
       <c r="Q80" t="b">
@@ -7758,7 +7784,7 @@
       <c r="E81" t="s">
         <v>904</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="2">
         <v>45813</v>
       </c>
       <c r="G81" t="s">
@@ -7787,7 +7813,7 @@
       <c r="E82" t="s">
         <v>905</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="2">
         <v>45813</v>
       </c>
       <c r="G82" t="s">
@@ -7797,7 +7823,7 @@
         <v>1353</v>
       </c>
       <c r="I82">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K82" t="s">
         <v>1360</v>
@@ -7825,7 +7851,7 @@
       <c r="E83" t="s">
         <v>906</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="2">
         <v>45813</v>
       </c>
       <c r="G83" t="s">
@@ -7854,7 +7880,7 @@
       <c r="E84" t="s">
         <v>907</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="2">
         <v>45813</v>
       </c>
       <c r="G84" t="s">
@@ -7864,7 +7890,7 @@
         <v>1353</v>
       </c>
       <c r="I84">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J84">
         <v>40</v>
@@ -7875,7 +7901,7 @@
       <c r="L84" t="s">
         <v>1384</v>
       </c>
-      <c r="N84" s="1">
+      <c r="N84" s="2">
         <v>45853</v>
       </c>
       <c r="O84">
@@ -7901,7 +7927,7 @@
       <c r="E85" t="s">
         <v>908</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85" s="2">
         <v>45813</v>
       </c>
       <c r="G85" t="s">
@@ -7911,7 +7937,7 @@
         <v>1353</v>
       </c>
       <c r="I85">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K85" t="s">
         <v>1357</v>
@@ -7939,7 +7965,7 @@
       <c r="E86" t="s">
         <v>909</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="2">
         <v>45813</v>
       </c>
       <c r="G86" t="s">
@@ -7949,7 +7975,7 @@
         <v>1353</v>
       </c>
       <c r="I86">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K86" t="s">
         <v>1357</v>
@@ -7977,7 +8003,7 @@
       <c r="E87" t="s">
         <v>910</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="2">
         <v>45813</v>
       </c>
       <c r="G87" t="s">
@@ -7987,7 +8013,7 @@
         <v>1353</v>
       </c>
       <c r="I87">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J87">
         <v>-16</v>
@@ -7998,7 +8024,7 @@
       <c r="L87" t="s">
         <v>1385</v>
       </c>
-      <c r="N87" s="1">
+      <c r="N87" s="2">
         <v>45797</v>
       </c>
       <c r="O87" t="s">
@@ -8024,7 +8050,7 @@
       <c r="E88" t="s">
         <v>911</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="2">
         <v>45813</v>
       </c>
       <c r="G88" t="s">
@@ -8039,7 +8065,7 @@
       <c r="L88" t="s">
         <v>1386</v>
       </c>
-      <c r="N88" s="1">
+      <c r="N88" s="2">
         <v>46195</v>
       </c>
       <c r="Q88" t="b">
@@ -8062,7 +8088,7 @@
       <c r="E89" t="s">
         <v>912</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89" s="2">
         <v>45813</v>
       </c>
       <c r="G89" t="s">
@@ -8077,7 +8103,7 @@
       <c r="L89" t="s">
         <v>1386</v>
       </c>
-      <c r="N89" s="1">
+      <c r="N89" s="2">
         <v>46195</v>
       </c>
       <c r="Q89" t="b">
@@ -8100,7 +8126,7 @@
       <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90" s="2">
         <v>45831</v>
       </c>
       <c r="G90" t="s">
@@ -8110,7 +8136,7 @@
         <v>1353</v>
       </c>
       <c r="I90">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K90" t="s">
         <v>1330</v>
@@ -8141,7 +8167,7 @@
       <c r="E91" t="s">
         <v>914</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="2">
         <v>45831</v>
       </c>
       <c r="G91" t="s">
@@ -8151,7 +8177,7 @@
         <v>1353</v>
       </c>
       <c r="I91">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J91">
         <v>308</v>
@@ -8162,7 +8188,7 @@
       <c r="L91" t="s">
         <v>1388</v>
       </c>
-      <c r="N91" s="1">
+      <c r="N91" s="2">
         <v>46139</v>
       </c>
       <c r="Q91" t="b">
@@ -8182,7 +8208,7 @@
       <c r="D92" t="s">
         <v>748</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92" s="2">
         <v>45831</v>
       </c>
       <c r="G92" t="s">
@@ -8211,7 +8237,7 @@
       <c r="E93" t="s">
         <v>915</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93" s="2">
         <v>45831</v>
       </c>
       <c r="G93" t="s">
@@ -8221,7 +8247,7 @@
         <v>1353</v>
       </c>
       <c r="I93">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J93">
         <v>308</v>
@@ -8232,7 +8258,7 @@
       <c r="L93" t="s">
         <v>1388</v>
       </c>
-      <c r="N93" s="1">
+      <c r="N93" s="2">
         <v>46139</v>
       </c>
       <c r="Q93" t="b">
@@ -8255,7 +8281,7 @@
       <c r="E94" t="s">
         <v>916</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94" s="2">
         <v>45831</v>
       </c>
       <c r="G94" t="s">
@@ -8265,7 +8291,7 @@
         <v>1353</v>
       </c>
       <c r="I94">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K94" t="s">
         <v>1360</v>
@@ -8293,7 +8319,7 @@
       <c r="E95" t="s">
         <v>917</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95" s="2">
         <v>45831</v>
       </c>
       <c r="G95" t="s">
@@ -8303,7 +8329,7 @@
         <v>1353</v>
       </c>
       <c r="I95">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J95">
         <v>308</v>
@@ -8314,7 +8340,7 @@
       <c r="L95" t="s">
         <v>1388</v>
       </c>
-      <c r="N95" s="1">
+      <c r="N95" s="2">
         <v>46139</v>
       </c>
       <c r="Q95" t="b">
@@ -8337,7 +8363,7 @@
       <c r="E96" t="s">
         <v>918</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96" s="2">
         <v>45831</v>
       </c>
       <c r="G96" t="s">
@@ -8347,7 +8373,7 @@
         <v>1353</v>
       </c>
       <c r="I96">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J96">
         <v>17</v>
@@ -8358,7 +8384,7 @@
       <c r="L96" t="s">
         <v>1369</v>
       </c>
-      <c r="N96" s="1">
+      <c r="N96" s="2">
         <v>45848</v>
       </c>
       <c r="O96" t="s">
@@ -8384,7 +8410,7 @@
       <c r="E97" t="s">
         <v>919</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="2">
         <v>45840</v>
       </c>
       <c r="G97" t="s">
@@ -8394,7 +8420,7 @@
         <v>1353</v>
       </c>
       <c r="I97">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J97">
         <v>20</v>
@@ -8405,7 +8431,7 @@
       <c r="L97" t="s">
         <v>1389</v>
       </c>
-      <c r="N97" s="1">
+      <c r="N97" s="2">
         <v>45860</v>
       </c>
       <c r="P97" t="s">
@@ -8431,7 +8457,7 @@
       <c r="E98" t="s">
         <v>920</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="2">
         <v>45840</v>
       </c>
       <c r="G98" t="s">
@@ -8441,7 +8467,7 @@
         <v>1353</v>
       </c>
       <c r="I98">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K98" t="s">
         <v>1360</v>
@@ -8469,7 +8495,7 @@
       <c r="E99" t="s">
         <v>921</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99" s="2">
         <v>45840</v>
       </c>
       <c r="G99" t="s">
@@ -8498,7 +8524,7 @@
       <c r="E100" t="s">
         <v>922</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100" s="2">
         <v>45840</v>
       </c>
       <c r="G100" t="s">
@@ -8508,7 +8534,7 @@
         <v>1353</v>
       </c>
       <c r="I100">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J100">
         <v>348</v>
@@ -8519,7 +8545,7 @@
       <c r="L100" t="s">
         <v>1388</v>
       </c>
-      <c r="N100" s="1">
+      <c r="N100" s="2">
         <v>46188</v>
       </c>
       <c r="Q100" t="b">
@@ -8542,7 +8568,7 @@
       <c r="E101" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101" s="2">
         <v>45840</v>
       </c>
       <c r="G101" t="s">
@@ -8571,7 +8597,7 @@
       <c r="E102" t="s">
         <v>924</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102" s="2">
         <v>45840</v>
       </c>
       <c r="G102" t="s">
@@ -8600,7 +8626,7 @@
       <c r="E103" t="s">
         <v>925</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103" s="2">
         <v>45840</v>
       </c>
       <c r="G103" t="s">
@@ -8629,7 +8655,7 @@
       <c r="E104" t="s">
         <v>926</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104" s="2">
         <v>45840</v>
       </c>
       <c r="G104" t="s">
@@ -8639,7 +8665,7 @@
         <v>1353</v>
       </c>
       <c r="I104">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J104">
         <v>348</v>
@@ -8650,7 +8676,7 @@
       <c r="L104" t="s">
         <v>1388</v>
       </c>
-      <c r="N104" s="1">
+      <c r="N104" s="2">
         <v>46188</v>
       </c>
       <c r="Q104" t="b">
@@ -8673,7 +8699,7 @@
       <c r="E105" t="s">
         <v>927</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105" s="2">
         <v>45840</v>
       </c>
       <c r="G105" t="s">
@@ -8683,7 +8709,7 @@
         <v>1353</v>
       </c>
       <c r="I105">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J105">
         <v>348</v>
@@ -8694,7 +8720,7 @@
       <c r="L105" t="s">
         <v>1388</v>
       </c>
-      <c r="N105" s="1">
+      <c r="N105" s="2">
         <v>46188</v>
       </c>
       <c r="Q105" t="b">
@@ -8717,7 +8743,7 @@
       <c r="E106" t="s">
         <v>928</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106" s="2">
         <v>45840</v>
       </c>
       <c r="G106" t="s">
@@ -8727,7 +8753,7 @@
         <v>1353</v>
       </c>
       <c r="I106">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J106">
         <v>49</v>
@@ -8738,7 +8764,7 @@
       <c r="L106" t="s">
         <v>1390</v>
       </c>
-      <c r="N106" s="1">
+      <c r="N106" s="2">
         <v>45889</v>
       </c>
       <c r="Q106" t="b">
@@ -8761,7 +8787,7 @@
       <c r="E107" t="s">
         <v>929</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="2">
         <v>45840</v>
       </c>
       <c r="G107" t="s">
@@ -8771,7 +8797,7 @@
         <v>1353</v>
       </c>
       <c r="I107">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J107">
         <v>36</v>
@@ -8782,7 +8808,7 @@
       <c r="L107" t="s">
         <v>1391</v>
       </c>
-      <c r="N107" s="1">
+      <c r="N107" s="2">
         <v>45876</v>
       </c>
       <c r="Q107" t="b">
@@ -8805,7 +8831,7 @@
       <c r="E108" t="s">
         <v>930</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108" s="2">
         <v>45840</v>
       </c>
       <c r="G108" t="s">
@@ -8815,7 +8841,7 @@
         <v>1353</v>
       </c>
       <c r="I108">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K108" t="s">
         <v>1357</v>
@@ -8843,7 +8869,7 @@
       <c r="E109" t="s">
         <v>931</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109" s="2">
         <v>45840</v>
       </c>
       <c r="G109" t="s">
@@ -8853,7 +8879,7 @@
         <v>1353</v>
       </c>
       <c r="I109">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K109" t="s">
         <v>1357</v>
@@ -8881,7 +8907,7 @@
       <c r="E110" t="s">
         <v>932</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="2">
         <v>45840</v>
       </c>
       <c r="G110" t="s">
@@ -8910,7 +8936,7 @@
       <c r="E111" t="s">
         <v>933</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="2">
         <v>45840</v>
       </c>
       <c r="G111" t="s">
@@ -8939,7 +8965,7 @@
       <c r="E112" t="s">
         <v>934</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112" s="2">
         <v>45840</v>
       </c>
       <c r="G112" t="s">
@@ -8968,7 +8994,7 @@
       <c r="E113" t="s">
         <v>935</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113" s="2">
         <v>45840</v>
       </c>
       <c r="G113" t="s">
@@ -8997,7 +9023,7 @@
       <c r="E114" t="s">
         <v>936</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114" s="2">
         <v>45840</v>
       </c>
       <c r="G114" t="s">
@@ -9026,7 +9052,7 @@
       <c r="E115" t="s">
         <v>937</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115" s="2">
         <v>45840</v>
       </c>
       <c r="G115" t="s">
@@ -9036,7 +9062,7 @@
         <v>1353</v>
       </c>
       <c r="I115">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K115" t="s">
         <v>1357</v>
@@ -9064,7 +9090,7 @@
       <c r="E116" t="s">
         <v>938</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116" s="2">
         <v>45840</v>
       </c>
       <c r="G116" t="s">
@@ -9074,7 +9100,7 @@
         <v>1353</v>
       </c>
       <c r="I116">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K116" t="s">
         <v>1357</v>
@@ -9102,7 +9128,7 @@
       <c r="E117" t="s">
         <v>939</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117" s="2">
         <v>45840</v>
       </c>
       <c r="G117" t="s">
@@ -9112,7 +9138,7 @@
         <v>1353</v>
       </c>
       <c r="I117">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K117" t="s">
         <v>1357</v>
@@ -9140,7 +9166,7 @@
       <c r="E118" t="s">
         <v>940</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118" s="2">
         <v>45840</v>
       </c>
       <c r="G118" t="s">
@@ -9150,7 +9176,7 @@
         <v>1353</v>
       </c>
       <c r="I118">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K118" t="s">
         <v>1357</v>
@@ -9178,7 +9204,7 @@
       <c r="E119" t="s">
         <v>941</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119" s="2">
         <v>45840</v>
       </c>
       <c r="G119" t="s">
@@ -9188,7 +9214,7 @@
         <v>1353</v>
       </c>
       <c r="I119">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K119" t="s">
         <v>1357</v>
@@ -9216,7 +9242,7 @@
       <c r="E120" t="s">
         <v>942</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120" s="2">
         <v>45840</v>
       </c>
       <c r="G120" t="s">
@@ -9226,7 +9252,7 @@
         <v>1353</v>
       </c>
       <c r="I120">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K120" t="s">
         <v>1357</v>
@@ -9254,7 +9280,7 @@
       <c r="E121" t="s">
         <v>943</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="2">
         <v>45849</v>
       </c>
       <c r="G121" t="s">
@@ -9264,7 +9290,7 @@
         <v>1353</v>
       </c>
       <c r="I121">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J121">
         <v>251</v>
@@ -9275,7 +9301,7 @@
       <c r="L121" t="s">
         <v>1379</v>
       </c>
-      <c r="N121" s="1">
+      <c r="N121" s="2">
         <v>46100</v>
       </c>
       <c r="O121">
@@ -9301,7 +9327,7 @@
       <c r="E122" t="s">
         <v>944</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F122" s="2">
         <v>45849</v>
       </c>
       <c r="G122" t="s">
@@ -9311,7 +9337,7 @@
         <v>1353</v>
       </c>
       <c r="I122">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K122" t="s">
         <v>1357</v>
@@ -9339,7 +9365,7 @@
       <c r="E123" t="s">
         <v>945</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F123" s="2">
         <v>45849</v>
       </c>
       <c r="G123" t="s">
@@ -9368,7 +9394,7 @@
       <c r="E124" t="s">
         <v>946</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124" s="2">
         <v>45853</v>
       </c>
       <c r="G124" t="s">
@@ -9378,7 +9404,7 @@
         <v>1353</v>
       </c>
       <c r="I124">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K124" t="s">
         <v>1357</v>
@@ -9406,7 +9432,7 @@
       <c r="E125" t="s">
         <v>947</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125" s="2">
         <v>45855</v>
       </c>
       <c r="G125" t="s">
@@ -9416,7 +9442,7 @@
         <v>1353</v>
       </c>
       <c r="I125">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K125" t="s">
         <v>1363</v>
@@ -9444,7 +9470,7 @@
       <c r="E126" t="s">
         <v>948</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126" s="2">
         <v>45855</v>
       </c>
       <c r="G126" t="s">
@@ -9473,7 +9499,7 @@
       <c r="E127" t="s">
         <v>949</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127" s="2">
         <v>45856</v>
       </c>
       <c r="G127" t="s">
@@ -9502,7 +9528,7 @@
       <c r="E128" t="s">
         <v>950</v>
       </c>
-      <c r="F128" s="1">
+      <c r="F128" s="2">
         <v>45869</v>
       </c>
       <c r="G128" t="s">
@@ -9512,7 +9538,7 @@
         <v>1353</v>
       </c>
       <c r="I128">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K128" t="s">
         <v>1357</v>
@@ -9540,7 +9566,7 @@
       <c r="E129" t="s">
         <v>951</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F129" s="2">
         <v>45869</v>
       </c>
       <c r="G129" t="s">
@@ -9550,7 +9576,7 @@
         <v>1353</v>
       </c>
       <c r="I129">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K129" t="s">
         <v>1356</v>
@@ -9578,7 +9604,7 @@
       <c r="E130" t="s">
         <v>952</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F130" s="2">
         <v>45869</v>
       </c>
       <c r="G130" t="s">
@@ -9588,7 +9614,7 @@
         <v>1353</v>
       </c>
       <c r="I130">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J130">
         <v>47</v>
@@ -9599,7 +9625,7 @@
       <c r="L130" t="s">
         <v>1392</v>
       </c>
-      <c r="N130" s="1">
+      <c r="N130" s="2">
         <v>45916</v>
       </c>
       <c r="O130">
@@ -9625,7 +9651,7 @@
       <c r="E131" t="s">
         <v>953</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F131" s="2">
         <v>45869</v>
       </c>
       <c r="G131" t="s">
@@ -9654,7 +9680,7 @@
       <c r="E132" t="s">
         <v>954</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F132" s="2">
         <v>45869</v>
       </c>
       <c r="G132" t="s">
@@ -9664,7 +9690,7 @@
         <v>1353</v>
       </c>
       <c r="I132">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J132">
         <v>145</v>
@@ -9675,7 +9701,7 @@
       <c r="L132" t="s">
         <v>1393</v>
       </c>
-      <c r="N132" s="1">
+      <c r="N132" s="2">
         <v>46014</v>
       </c>
       <c r="O132">
@@ -9701,7 +9727,7 @@
       <c r="E133" t="s">
         <v>955</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F133" s="2">
         <v>45869</v>
       </c>
       <c r="G133" t="s">
@@ -9730,7 +9756,7 @@
       <c r="E134" t="s">
         <v>956</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F134" s="2">
         <v>45882</v>
       </c>
       <c r="G134" t="s">
@@ -9740,7 +9766,7 @@
         <v>1353</v>
       </c>
       <c r="I134">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K134" t="s">
         <v>1356</v>
@@ -9768,7 +9794,7 @@
       <c r="E135" t="s">
         <v>957</v>
       </c>
-      <c r="F135" s="1">
+      <c r="F135" s="2">
         <v>45882</v>
       </c>
       <c r="G135" t="s">
@@ -9797,7 +9823,7 @@
       <c r="E136" t="s">
         <v>958</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F136" s="2">
         <v>45891</v>
       </c>
       <c r="G136" t="s">
@@ -9826,7 +9852,7 @@
       <c r="E137" t="s">
         <v>959</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F137" s="2">
         <v>45891</v>
       </c>
       <c r="G137" t="s">
@@ -9855,7 +9881,7 @@
       <c r="E138" t="s">
         <v>960</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F138" s="2">
         <v>45891</v>
       </c>
       <c r="G138" t="s">
@@ -9865,7 +9891,7 @@
         <v>1353</v>
       </c>
       <c r="I138">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K138" t="s">
         <v>1357</v>
@@ -9893,7 +9919,7 @@
       <c r="E139" t="s">
         <v>961</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F139" s="2">
         <v>45891</v>
       </c>
       <c r="G139" t="s">
@@ -9922,7 +9948,7 @@
       <c r="E140" t="s">
         <v>962</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F140" s="2">
         <v>45891</v>
       </c>
       <c r="G140" t="s">
@@ -9951,7 +9977,7 @@
       <c r="E141" t="s">
         <v>963</v>
       </c>
-      <c r="F141" s="1">
+      <c r="F141" s="2">
         <v>45891</v>
       </c>
       <c r="G141" t="s">
@@ -9980,7 +10006,7 @@
       <c r="E142" t="s">
         <v>964</v>
       </c>
-      <c r="F142" s="1">
+      <c r="F142" s="2">
         <v>45891</v>
       </c>
       <c r="G142" t="s">
@@ -10009,7 +10035,7 @@
       <c r="E143" t="s">
         <v>965</v>
       </c>
-      <c r="F143" s="1">
+      <c r="F143" s="2">
         <v>45891</v>
       </c>
       <c r="G143" t="s">
@@ -10038,7 +10064,7 @@
       <c r="E144" t="s">
         <v>966</v>
       </c>
-      <c r="F144" s="1">
+      <c r="F144" s="2">
         <v>45891</v>
       </c>
       <c r="G144" t="s">
@@ -10067,7 +10093,7 @@
       <c r="E145" t="s">
         <v>967</v>
       </c>
-      <c r="F145" s="1">
+      <c r="F145" s="2">
         <v>45891</v>
       </c>
       <c r="G145" t="s">
@@ -10096,7 +10122,7 @@
       <c r="E146" t="s">
         <v>968</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F146" s="2">
         <v>45891</v>
       </c>
       <c r="G146" t="s">
@@ -10125,7 +10151,7 @@
       <c r="E147" t="s">
         <v>969</v>
       </c>
-      <c r="F147" s="1">
+      <c r="F147" s="2">
         <v>45891</v>
       </c>
       <c r="G147" t="s">
@@ -10154,7 +10180,7 @@
       <c r="E148" t="s">
         <v>970</v>
       </c>
-      <c r="F148" s="1">
+      <c r="F148" s="2">
         <v>45891</v>
       </c>
       <c r="G148" t="s">
@@ -10164,7 +10190,7 @@
         <v>1353</v>
       </c>
       <c r="I148">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J148">
         <v>341</v>
@@ -10175,7 +10201,7 @@
       <c r="L148" t="s">
         <v>1383</v>
       </c>
-      <c r="N148" s="1">
+      <c r="N148" s="2">
         <v>46232</v>
       </c>
       <c r="Q148" t="b">
@@ -10198,7 +10224,7 @@
       <c r="E149" t="s">
         <v>971</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F149" s="2">
         <v>45891</v>
       </c>
       <c r="G149" t="s">
@@ -10208,7 +10234,7 @@
         <v>1353</v>
       </c>
       <c r="I149">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J149">
         <v>374</v>
@@ -10219,7 +10245,7 @@
       <c r="L149" t="s">
         <v>1394</v>
       </c>
-      <c r="N149" s="1">
+      <c r="N149" s="2">
         <v>46265</v>
       </c>
       <c r="P149" t="s">
@@ -10245,7 +10271,7 @@
       <c r="E150" t="s">
         <v>972</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F150" s="2">
         <v>45891</v>
       </c>
       <c r="G150" t="s">
@@ -10255,7 +10281,7 @@
         <v>1353</v>
       </c>
       <c r="I150">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J150">
         <v>201</v>
@@ -10266,7 +10292,7 @@
       <c r="L150" t="s">
         <v>1381</v>
       </c>
-      <c r="N150" s="1">
+      <c r="N150" s="2">
         <v>46092</v>
       </c>
       <c r="P150" t="s">
@@ -10292,7 +10318,7 @@
       <c r="E151" t="s">
         <v>973</v>
       </c>
-      <c r="F151" s="1">
+      <c r="F151" s="2">
         <v>45891</v>
       </c>
       <c r="G151" t="s">
@@ -10321,7 +10347,7 @@
       <c r="E152" t="s">
         <v>963</v>
       </c>
-      <c r="F152" s="1">
+      <c r="F152" s="2">
         <v>45891</v>
       </c>
       <c r="G152" t="s">
@@ -10331,7 +10357,7 @@
         <v>1353</v>
       </c>
       <c r="I152">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J152">
         <v>228</v>
@@ -10342,7 +10368,7 @@
       <c r="L152" t="s">
         <v>1382</v>
       </c>
-      <c r="N152" s="1">
+      <c r="N152" s="2">
         <v>46119</v>
       </c>
       <c r="Q152" t="b">
@@ -10365,7 +10391,7 @@
       <c r="E153" t="s">
         <v>974</v>
       </c>
-      <c r="F153" s="1">
+      <c r="F153" s="2">
         <v>45891</v>
       </c>
       <c r="G153" t="s">
@@ -10383,7 +10409,7 @@
       <c r="L153" t="s">
         <v>1383</v>
       </c>
-      <c r="N153" s="1">
+      <c r="N153" s="2">
         <v>46232</v>
       </c>
       <c r="Q153" t="b">
@@ -10406,7 +10432,7 @@
       <c r="E154" t="s">
         <v>975</v>
       </c>
-      <c r="F154" s="1">
+      <c r="F154" s="2">
         <v>45891</v>
       </c>
       <c r="G154" t="s">
@@ -10435,7 +10461,7 @@
       <c r="E155" t="s">
         <v>976</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F155" s="2">
         <v>45891</v>
       </c>
       <c r="G155" t="s">
@@ -10445,7 +10471,7 @@
         <v>1353</v>
       </c>
       <c r="I155">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K155" t="s">
         <v>1363</v>
@@ -10470,7 +10496,7 @@
       <c r="E156" t="s">
         <v>977</v>
       </c>
-      <c r="F156" s="1">
+      <c r="F156" s="2">
         <v>45891</v>
       </c>
       <c r="G156" t="s">
@@ -10480,7 +10506,7 @@
         <v>1353</v>
       </c>
       <c r="I156">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K156" t="s">
         <v>1357</v>
@@ -10508,7 +10534,7 @@
       <c r="E157" t="s">
         <v>978</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="2">
         <v>45891</v>
       </c>
       <c r="G157" t="s">
@@ -10518,7 +10544,7 @@
         <v>1353</v>
       </c>
       <c r="I157">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J157">
         <v>371</v>
@@ -10529,7 +10555,7 @@
       <c r="L157" t="s">
         <v>1395</v>
       </c>
-      <c r="N157" s="1">
+      <c r="N157" s="2">
         <v>46262</v>
       </c>
       <c r="Q157" t="b">
@@ -10552,7 +10578,7 @@
       <c r="E158" t="s">
         <v>979</v>
       </c>
-      <c r="F158" s="1">
+      <c r="F158" s="2">
         <v>45894</v>
       </c>
       <c r="G158" t="s">
@@ -10562,7 +10588,7 @@
         <v>1353</v>
       </c>
       <c r="I158">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J158">
         <v>52</v>
@@ -10573,7 +10599,7 @@
       <c r="L158" t="s">
         <v>1396</v>
       </c>
-      <c r="N158" s="1">
+      <c r="N158" s="2">
         <v>45946</v>
       </c>
       <c r="Q158" t="b">
@@ -10596,7 +10622,7 @@
       <c r="E159" t="s">
         <v>980</v>
       </c>
-      <c r="F159" s="1">
+      <c r="F159" s="2">
         <v>45894</v>
       </c>
       <c r="G159" t="s">
@@ -10606,7 +10632,7 @@
         <v>1353</v>
       </c>
       <c r="I159">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K159" t="s">
         <v>1357</v>
@@ -10634,7 +10660,7 @@
       <c r="E160" t="s">
         <v>981</v>
       </c>
-      <c r="F160" s="1">
+      <c r="F160" s="2">
         <v>45898</v>
       </c>
       <c r="G160" t="s">
@@ -10644,7 +10670,7 @@
         <v>1353</v>
       </c>
       <c r="I160">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K160" t="s">
         <v>1357</v>
@@ -10672,7 +10698,7 @@
       <c r="E161" t="s">
         <v>982</v>
       </c>
-      <c r="F161" s="1">
+      <c r="F161" s="2">
         <v>45898</v>
       </c>
       <c r="G161" t="s">
@@ -10682,7 +10708,7 @@
         <v>1353</v>
       </c>
       <c r="I161">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J161">
         <v>55</v>
@@ -10693,7 +10719,7 @@
       <c r="L161" t="s">
         <v>1397</v>
       </c>
-      <c r="N161" s="1">
+      <c r="N161" s="2">
         <v>45953</v>
       </c>
       <c r="O161" t="s">
@@ -10719,7 +10745,7 @@
       <c r="E162" t="s">
         <v>983</v>
       </c>
-      <c r="F162" s="1">
+      <c r="F162" s="2">
         <v>45898</v>
       </c>
       <c r="G162" t="s">
@@ -10729,7 +10755,7 @@
         <v>1353</v>
       </c>
       <c r="I162">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J162">
         <v>42</v>
@@ -10740,7 +10766,7 @@
       <c r="L162" t="s">
         <v>1398</v>
       </c>
-      <c r="N162" s="1">
+      <c r="N162" s="2">
         <v>45940</v>
       </c>
       <c r="Q162" t="b">
@@ -10763,7 +10789,7 @@
       <c r="E163" t="s">
         <v>984</v>
       </c>
-      <c r="F163" s="1">
+      <c r="F163" s="2">
         <v>45898</v>
       </c>
       <c r="G163" t="s">
@@ -10773,7 +10799,7 @@
         <v>1353</v>
       </c>
       <c r="I163">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J163">
         <v>42</v>
@@ -10784,7 +10810,7 @@
       <c r="L163" t="s">
         <v>1398</v>
       </c>
-      <c r="N163" s="1">
+      <c r="N163" s="2">
         <v>45940</v>
       </c>
       <c r="Q163" t="b">
@@ -10807,7 +10833,7 @@
       <c r="E164" t="s">
         <v>985</v>
       </c>
-      <c r="F164" s="1">
+      <c r="F164" s="2">
         <v>45910</v>
       </c>
       <c r="G164" t="s">
@@ -10817,7 +10843,7 @@
         <v>1355</v>
       </c>
       <c r="I164">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O164" t="s">
         <v>1469</v>
@@ -10842,7 +10868,7 @@
       <c r="E165" t="s">
         <v>986</v>
       </c>
-      <c r="F165" s="1">
+      <c r="F165" s="2">
         <v>45917</v>
       </c>
       <c r="G165" t="s">
@@ -10860,7 +10886,7 @@
       <c r="L165" t="s">
         <v>1399</v>
       </c>
-      <c r="N165" s="1">
+      <c r="N165" s="2">
         <v>46204</v>
       </c>
       <c r="P165" t="s">
@@ -10886,7 +10912,7 @@
       <c r="E166" t="s">
         <v>987</v>
       </c>
-      <c r="F166" s="1">
+      <c r="F166" s="2">
         <v>45917</v>
       </c>
       <c r="G166" t="s">
@@ -10915,7 +10941,7 @@
       <c r="E167" t="s">
         <v>988</v>
       </c>
-      <c r="F167" s="1">
+      <c r="F167" s="2">
         <v>45917</v>
       </c>
       <c r="G167" t="s">
@@ -10944,7 +10970,7 @@
       <c r="E168" t="s">
         <v>989</v>
       </c>
-      <c r="F168" s="1">
+      <c r="F168" s="2">
         <v>45917</v>
       </c>
       <c r="G168" t="s">
@@ -10954,7 +10980,7 @@
         <v>1353</v>
       </c>
       <c r="I168">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K168" t="s">
         <v>1360</v>
@@ -10985,7 +11011,7 @@
       <c r="E169" t="s">
         <v>990</v>
       </c>
-      <c r="F169" s="1">
+      <c r="F169" s="2">
         <v>45917</v>
       </c>
       <c r="G169" t="s">
@@ -10995,7 +11021,7 @@
         <v>1353</v>
       </c>
       <c r="I169">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K169" t="s">
         <v>1330</v>
@@ -11003,7 +11029,7 @@
       <c r="L169" t="s">
         <v>1401</v>
       </c>
-      <c r="N169" s="1">
+      <c r="N169" s="2">
         <v>45973</v>
       </c>
       <c r="Q169" t="b">
@@ -11026,7 +11052,7 @@
       <c r="E170" t="s">
         <v>991</v>
       </c>
-      <c r="F170" s="1">
+      <c r="F170" s="2">
         <v>45917</v>
       </c>
       <c r="G170" t="s">
@@ -11061,7 +11087,7 @@
       <c r="E171" t="s">
         <v>992</v>
       </c>
-      <c r="F171" s="1">
+      <c r="F171" s="2">
         <v>45917</v>
       </c>
       <c r="G171" t="s">
@@ -11071,7 +11097,7 @@
         <v>1353</v>
       </c>
       <c r="I171">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K171" t="s">
         <v>1357</v>
@@ -11099,7 +11125,7 @@
       <c r="E172" t="s">
         <v>993</v>
       </c>
-      <c r="F172" s="1">
+      <c r="F172" s="2">
         <v>45917</v>
       </c>
       <c r="G172" t="s">
@@ -11128,7 +11154,7 @@
       <c r="E173" t="s">
         <v>994</v>
       </c>
-      <c r="F173" s="1">
+      <c r="F173" s="2">
         <v>45917</v>
       </c>
       <c r="G173" t="s">
@@ -11157,7 +11183,7 @@
       <c r="E174" t="s">
         <v>995</v>
       </c>
-      <c r="F174" s="1">
+      <c r="F174" s="2">
         <v>45917</v>
       </c>
       <c r="G174" t="s">
@@ -11172,7 +11198,7 @@
       <c r="L174" t="s">
         <v>1386</v>
       </c>
-      <c r="N174" s="1">
+      <c r="N174" s="2">
         <v>46195</v>
       </c>
       <c r="Q174" t="b">
@@ -11195,7 +11221,7 @@
       <c r="E175" t="s">
         <v>996</v>
       </c>
-      <c r="F175" s="1">
+      <c r="F175" s="2">
         <v>45917</v>
       </c>
       <c r="G175" t="s">
@@ -11205,7 +11231,7 @@
         <v>1353</v>
       </c>
       <c r="I175">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J175">
         <v>205</v>
@@ -11216,7 +11242,7 @@
       <c r="L175" t="s">
         <v>1402</v>
       </c>
-      <c r="N175" s="1">
+      <c r="N175" s="2">
         <v>46122</v>
       </c>
       <c r="P175" t="s">
@@ -11242,7 +11268,7 @@
       <c r="E176" t="s">
         <v>900</v>
       </c>
-      <c r="F176" s="1">
+      <c r="F176" s="2">
         <v>45917</v>
       </c>
       <c r="G176" t="s">
@@ -11252,7 +11278,7 @@
         <v>1353</v>
       </c>
       <c r="I176">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K176" t="s">
         <v>1357</v>
@@ -11280,7 +11306,7 @@
       <c r="E177" t="s">
         <v>997</v>
       </c>
-      <c r="F177" s="1">
+      <c r="F177" s="2">
         <v>45917</v>
       </c>
       <c r="G177" t="s">
@@ -11290,7 +11316,7 @@
         <v>1353</v>
       </c>
       <c r="I177">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J177">
         <v>44</v>
@@ -11301,7 +11327,7 @@
       <c r="L177" t="s">
         <v>1403</v>
       </c>
-      <c r="N177" s="1">
+      <c r="N177" s="2">
         <v>45961</v>
       </c>
       <c r="P177" t="s">
@@ -11327,7 +11353,7 @@
       <c r="E178" t="s">
         <v>998</v>
       </c>
-      <c r="F178" s="1">
+      <c r="F178" s="2">
         <v>45937</v>
       </c>
       <c r="G178" t="s">
@@ -11337,7 +11363,7 @@
         <v>1353</v>
       </c>
       <c r="I178">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K178" t="s">
         <v>1356</v>
@@ -11365,7 +11391,7 @@
       <c r="E179" t="s">
         <v>999</v>
       </c>
-      <c r="F179" s="1">
+      <c r="F179" s="2">
         <v>45937</v>
       </c>
       <c r="G179" t="s">
@@ -11394,7 +11420,7 @@
       <c r="E180" t="s">
         <v>1000</v>
       </c>
-      <c r="F180" s="1">
+      <c r="F180" s="2">
         <v>45937</v>
       </c>
       <c r="G180" t="s">
@@ -11404,7 +11430,7 @@
         <v>1353</v>
       </c>
       <c r="I180">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K180" t="s">
         <v>1356</v>
@@ -11432,7 +11458,7 @@
       <c r="E181" t="s">
         <v>1001</v>
       </c>
-      <c r="F181" s="1">
+      <c r="F181" s="2">
         <v>45937</v>
       </c>
       <c r="G181" t="s">
@@ -11461,7 +11487,7 @@
       <c r="E182" t="s">
         <v>1002</v>
       </c>
-      <c r="F182" s="1">
+      <c r="F182" s="2">
         <v>45937</v>
       </c>
       <c r="G182" t="s">
@@ -11490,7 +11516,7 @@
       <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="F183" s="1">
+      <c r="F183" s="2">
         <v>45937</v>
       </c>
       <c r="G183" t="s">
@@ -11500,7 +11526,7 @@
         <v>1353</v>
       </c>
       <c r="I183">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K183" t="s">
         <v>1357</v>
@@ -11528,7 +11554,7 @@
       <c r="D184" t="s">
         <v>774</v>
       </c>
-      <c r="F184" s="1">
+      <c r="F184" s="2">
         <v>45939</v>
       </c>
       <c r="G184" t="s">
@@ -11538,7 +11564,7 @@
         <v>1353</v>
       </c>
       <c r="I184">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K184" t="s">
         <v>1363</v>
@@ -11563,7 +11589,7 @@
       <c r="E185" t="s">
         <v>1004</v>
       </c>
-      <c r="F185" s="1">
+      <c r="F185" s="2">
         <v>45939</v>
       </c>
       <c r="G185" t="s">
@@ -11573,7 +11599,7 @@
         <v>1353</v>
       </c>
       <c r="I185">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K185" t="s">
         <v>1357</v>
@@ -11601,7 +11627,7 @@
       <c r="E186" t="s">
         <v>1005</v>
       </c>
-      <c r="F186" s="1">
+      <c r="F186" s="2">
         <v>45939</v>
       </c>
       <c r="G186" t="s">
@@ -11611,7 +11637,7 @@
         <v>1353</v>
       </c>
       <c r="I186">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K186" t="s">
         <v>1357</v>
@@ -11639,7 +11665,7 @@
       <c r="E187" t="s">
         <v>1006</v>
       </c>
-      <c r="F187" s="1">
+      <c r="F187" s="2">
         <v>45939</v>
       </c>
       <c r="G187" t="s">
@@ -11649,7 +11675,7 @@
         <v>1353</v>
       </c>
       <c r="I187">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J187">
         <v>75</v>
@@ -11660,7 +11686,7 @@
       <c r="L187" t="s">
         <v>1404</v>
       </c>
-      <c r="N187" s="1">
+      <c r="N187" s="2">
         <v>46014</v>
       </c>
       <c r="O187">
@@ -11686,7 +11712,7 @@
       <c r="E188" t="s">
         <v>1007</v>
       </c>
-      <c r="F188" s="1">
+      <c r="F188" s="2">
         <v>45946</v>
       </c>
       <c r="G188" t="s">
@@ -11696,7 +11722,7 @@
         <v>1353</v>
       </c>
       <c r="I188">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J188">
         <v>40</v>
@@ -11707,7 +11733,7 @@
       <c r="L188" t="s">
         <v>1405</v>
       </c>
-      <c r="N188" s="1">
+      <c r="N188" s="2">
         <v>45986</v>
       </c>
       <c r="P188" t="s">
@@ -11733,7 +11759,7 @@
       <c r="E189" t="s">
         <v>1008</v>
       </c>
-      <c r="F189" s="1">
+      <c r="F189" s="2">
         <v>45965</v>
       </c>
       <c r="G189" t="s">
@@ -11743,7 +11769,7 @@
         <v>1353</v>
       </c>
       <c r="I189">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J189">
         <v>155</v>
@@ -11754,7 +11780,7 @@
       <c r="L189" t="s">
         <v>1406</v>
       </c>
-      <c r="N189" s="1">
+      <c r="N189" s="2">
         <v>46120</v>
       </c>
       <c r="Q189" t="b">
@@ -11777,7 +11803,7 @@
       <c r="E190" t="s">
         <v>1009</v>
       </c>
-      <c r="F190" s="1">
+      <c r="F190" s="2">
         <v>45965</v>
       </c>
       <c r="G190" t="s">
@@ -11787,7 +11813,7 @@
         <v>1353</v>
       </c>
       <c r="I190">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J190">
         <v>107</v>
@@ -11798,7 +11824,7 @@
       <c r="L190" t="s">
         <v>1407</v>
       </c>
-      <c r="N190" s="1">
+      <c r="N190" s="2">
         <v>46072</v>
       </c>
       <c r="Q190" t="b">
@@ -11821,7 +11847,7 @@
       <c r="E191" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="1">
+      <c r="F191" s="2">
         <v>45967</v>
       </c>
       <c r="G191" t="s">
@@ -11831,7 +11857,7 @@
         <v>1353</v>
       </c>
       <c r="I191">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J191">
         <v>5</v>
@@ -11842,7 +11868,7 @@
       <c r="L191" t="s">
         <v>1408</v>
       </c>
-      <c r="N191" s="1">
+      <c r="N191" s="2">
         <v>45972</v>
       </c>
       <c r="Q191" t="b">
@@ -11865,7 +11891,7 @@
       <c r="E192" t="s">
         <v>1011</v>
       </c>
-      <c r="F192" s="1">
+      <c r="F192" s="2">
         <v>45968</v>
       </c>
       <c r="G192" t="s">
@@ -11875,7 +11901,7 @@
         <v>1353</v>
       </c>
       <c r="I192">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K192" t="s">
         <v>1357</v>
@@ -11903,7 +11929,7 @@
       <c r="E193" t="s">
         <v>1012</v>
       </c>
-      <c r="F193" s="1">
+      <c r="F193" s="2">
         <v>45968</v>
       </c>
       <c r="G193" t="s">
@@ -11913,7 +11939,7 @@
         <v>1353</v>
       </c>
       <c r="I193">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K193" t="s">
         <v>1362</v>
@@ -11941,7 +11967,7 @@
       <c r="E194" t="s">
         <v>1013</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F194" s="2">
         <v>45968</v>
       </c>
       <c r="G194" t="s">
@@ -11970,7 +11996,7 @@
       <c r="E195" t="s">
         <v>1014</v>
       </c>
-      <c r="F195" s="1">
+      <c r="F195" s="2">
         <v>45971</v>
       </c>
       <c r="G195" t="s">
@@ -11980,7 +12006,7 @@
         <v>1353</v>
       </c>
       <c r="I195">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J195">
         <v>186</v>
@@ -11991,7 +12017,7 @@
       <c r="L195" t="s">
         <v>1409</v>
       </c>
-      <c r="N195" s="1">
+      <c r="N195" s="2">
         <v>46157</v>
       </c>
       <c r="Q195" t="b">
@@ -12014,7 +12040,7 @@
       <c r="E196" t="s">
         <v>1015</v>
       </c>
-      <c r="F196" s="1">
+      <c r="F196" s="2">
         <v>45978</v>
       </c>
       <c r="G196" t="s">
@@ -12043,7 +12069,7 @@
       <c r="E197" t="s">
         <v>1016</v>
       </c>
-      <c r="F197" s="1">
+      <c r="F197" s="2">
         <v>45978</v>
       </c>
       <c r="G197" t="s">
@@ -12072,7 +12098,7 @@
       <c r="E198" t="s">
         <v>1017</v>
       </c>
-      <c r="F198" s="1">
+      <c r="F198" s="2">
         <v>45978</v>
       </c>
       <c r="G198" t="s">
@@ -12101,7 +12127,7 @@
       <c r="E199" t="s">
         <v>1018</v>
       </c>
-      <c r="F199" s="1">
+      <c r="F199" s="2">
         <v>45979</v>
       </c>
       <c r="G199" t="s">
@@ -12111,7 +12137,7 @@
         <v>1353</v>
       </c>
       <c r="I199">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J199">
         <v>70</v>
@@ -12122,7 +12148,7 @@
       <c r="L199" t="s">
         <v>1410</v>
       </c>
-      <c r="N199" s="1">
+      <c r="N199" s="2">
         <v>46049</v>
       </c>
       <c r="Q199" t="b">
@@ -12145,7 +12171,7 @@
       <c r="E200" t="s">
         <v>1019</v>
       </c>
-      <c r="F200" s="1">
+      <c r="F200" s="2">
         <v>45986</v>
       </c>
       <c r="G200" t="s">
@@ -12155,7 +12181,7 @@
         <v>1353</v>
       </c>
       <c r="I200">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J200">
         <v>170</v>
@@ -12166,7 +12192,7 @@
       <c r="L200" t="s">
         <v>1409</v>
       </c>
-      <c r="N200" s="1">
+      <c r="N200" s="2">
         <v>46156</v>
       </c>
       <c r="Q200" t="b">
@@ -12189,7 +12215,7 @@
       <c r="E201" t="s">
         <v>1020</v>
       </c>
-      <c r="F201" s="1">
+      <c r="F201" s="2">
         <v>45986</v>
       </c>
       <c r="G201" t="s">
@@ -12199,7 +12225,7 @@
         <v>1353</v>
       </c>
       <c r="I201">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K201" t="s">
         <v>1357</v>
@@ -12227,7 +12253,7 @@
       <c r="E202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" s="1">
+      <c r="F202" s="2">
         <v>45986</v>
       </c>
       <c r="G202" t="s">
@@ -12237,7 +12263,7 @@
         <v>1353</v>
       </c>
       <c r="I202">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K202" t="s">
         <v>1357</v>
@@ -12265,7 +12291,7 @@
       <c r="E203" t="s">
         <v>1022</v>
       </c>
-      <c r="F203" s="1">
+      <c r="F203" s="2">
         <v>45986</v>
       </c>
       <c r="G203" t="s">
@@ -12283,7 +12309,7 @@
       <c r="L203" t="s">
         <v>1411</v>
       </c>
-      <c r="N203" s="1">
+      <c r="N203" s="2">
         <v>46232</v>
       </c>
       <c r="Q203" t="b">
@@ -12306,7 +12332,7 @@
       <c r="E204" t="s">
         <v>1023</v>
       </c>
-      <c r="F204" s="1">
+      <c r="F204" s="2">
         <v>45986</v>
       </c>
       <c r="G204" t="s">
@@ -12316,7 +12342,7 @@
         <v>1353</v>
       </c>
       <c r="I204">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K204" t="s">
         <v>1356</v>
@@ -12344,7 +12370,7 @@
       <c r="E205" t="s">
         <v>1024</v>
       </c>
-      <c r="F205" s="1">
+      <c r="F205" s="2">
         <v>45986</v>
       </c>
       <c r="G205" t="s">
@@ -12354,7 +12380,7 @@
         <v>1353</v>
       </c>
       <c r="I205">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K205" t="s">
         <v>1356</v>
@@ -12382,7 +12408,7 @@
       <c r="E206" t="s">
         <v>1025</v>
       </c>
-      <c r="F206" s="1">
+      <c r="F206" s="2">
         <v>45986</v>
       </c>
       <c r="G206" t="s">
@@ -12411,7 +12437,7 @@
       <c r="E207" t="s">
         <v>1026</v>
       </c>
-      <c r="F207" s="1">
+      <c r="F207" s="2">
         <v>45986</v>
       </c>
       <c r="G207" t="s">
@@ -12421,7 +12447,7 @@
         <v>1353</v>
       </c>
       <c r="I207">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J207">
         <v>167</v>
@@ -12432,7 +12458,7 @@
       <c r="L207" t="s">
         <v>1412</v>
       </c>
-      <c r="N207" s="1">
+      <c r="N207" s="2">
         <v>46153</v>
       </c>
       <c r="Q207" t="b">
@@ -12455,7 +12481,7 @@
       <c r="E208" t="s">
         <v>1027</v>
       </c>
-      <c r="F208" s="1">
+      <c r="F208" s="2">
         <v>45986</v>
       </c>
       <c r="G208" t="s">
@@ -12465,7 +12491,7 @@
         <v>1353</v>
       </c>
       <c r="I208">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J208">
         <v>45</v>
@@ -12476,7 +12502,7 @@
       <c r="L208" t="s">
         <v>1413</v>
       </c>
-      <c r="N208" s="1">
+      <c r="N208" s="2">
         <v>46031</v>
       </c>
       <c r="Q208" t="b">
@@ -12499,7 +12525,7 @@
       <c r="E209" t="s">
         <v>1028</v>
       </c>
-      <c r="F209" s="1">
+      <c r="F209" s="2">
         <v>46000</v>
       </c>
       <c r="G209" t="s">
@@ -12509,7 +12535,7 @@
         <v>1353</v>
       </c>
       <c r="I209">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J209">
         <v>191</v>
@@ -12520,7 +12546,7 @@
       <c r="L209" t="s">
         <v>1414</v>
       </c>
-      <c r="N209" s="1">
+      <c r="N209" s="2">
         <v>46191</v>
       </c>
       <c r="Q209" t="b">
@@ -12543,7 +12569,7 @@
       <c r="E210" t="s">
         <v>1029</v>
       </c>
-      <c r="F210" s="1">
+      <c r="F210" s="2">
         <v>46000</v>
       </c>
       <c r="G210" t="s">
@@ -12553,7 +12579,7 @@
         <v>1353</v>
       </c>
       <c r="I210">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K210" t="s">
         <v>1360</v>
@@ -12581,7 +12607,7 @@
       <c r="E211" t="s">
         <v>1030</v>
       </c>
-      <c r="F211" s="1">
+      <c r="F211" s="2">
         <v>46000</v>
       </c>
       <c r="G211" t="s">
@@ -12610,7 +12636,7 @@
       <c r="E212" t="s">
         <v>1031</v>
       </c>
-      <c r="F212" s="1">
+      <c r="F212" s="2">
         <v>46000</v>
       </c>
       <c r="G212" t="s">
@@ -12639,7 +12665,7 @@
       <c r="E213" t="s">
         <v>1032</v>
       </c>
-      <c r="F213" s="1">
+      <c r="F213" s="2">
         <v>46007</v>
       </c>
       <c r="G213" t="s">
@@ -12649,7 +12675,7 @@
         <v>1353</v>
       </c>
       <c r="I213">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K213" t="s">
         <v>1357</v>
@@ -12677,7 +12703,7 @@
       <c r="E214" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="1">
+      <c r="F214" s="2">
         <v>46007</v>
       </c>
       <c r="G214" t="s">
@@ -12687,7 +12713,7 @@
         <v>1353</v>
       </c>
       <c r="I214">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J214">
         <v>14</v>
@@ -12698,7 +12724,7 @@
       <c r="L214" t="s">
         <v>1415</v>
       </c>
-      <c r="N214" s="1">
+      <c r="N214" s="2">
         <v>46021</v>
       </c>
       <c r="O214">
@@ -12724,7 +12750,7 @@
       <c r="E215" t="s">
         <v>1034</v>
       </c>
-      <c r="F215" s="1">
+      <c r="F215" s="2">
         <v>46007</v>
       </c>
       <c r="G215" t="s">
@@ -12734,7 +12760,7 @@
         <v>1353</v>
       </c>
       <c r="I215">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K215" t="s">
         <v>1357</v>
@@ -12762,7 +12788,7 @@
       <c r="E216" t="s">
         <v>1035</v>
       </c>
-      <c r="F216" s="1">
+      <c r="F216" s="2">
         <v>46010</v>
       </c>
       <c r="G216" t="s">
@@ -12791,7 +12817,7 @@
       <c r="E217" t="s">
         <v>1036</v>
       </c>
-      <c r="F217" s="1">
+      <c r="F217" s="2">
         <v>46010</v>
       </c>
       <c r="G217" t="s">
@@ -12801,7 +12827,7 @@
         <v>1353</v>
       </c>
       <c r="I217">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J217">
         <v>42</v>
@@ -12812,7 +12838,7 @@
       <c r="L217" t="s">
         <v>1416</v>
       </c>
-      <c r="N217" s="1">
+      <c r="N217" s="2">
         <v>46052</v>
       </c>
       <c r="Q217" t="b">
@@ -12835,7 +12861,7 @@
       <c r="E218" t="s">
         <v>1037</v>
       </c>
-      <c r="F218" s="1">
+      <c r="F218" s="2">
         <v>46010</v>
       </c>
       <c r="G218" t="s">
@@ -12845,7 +12871,7 @@
         <v>1353</v>
       </c>
       <c r="I218">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J218">
         <v>166</v>
@@ -12853,7 +12879,7 @@
       <c r="K218" t="s">
         <v>1359</v>
       </c>
-      <c r="N218" s="1">
+      <c r="N218" s="2">
         <v>46176</v>
       </c>
       <c r="P218" t="s">
@@ -12879,7 +12905,7 @@
       <c r="E219" t="s">
         <v>1038</v>
       </c>
-      <c r="F219" s="1">
+      <c r="F219" s="2">
         <v>46010</v>
       </c>
       <c r="G219" t="s">
@@ -12897,7 +12923,7 @@
       <c r="L219" t="s">
         <v>1417</v>
       </c>
-      <c r="N219" s="1">
+      <c r="N219" s="2">
         <v>46176</v>
       </c>
       <c r="P219" t="s">
@@ -12923,7 +12949,7 @@
       <c r="E220" t="s">
         <v>1039</v>
       </c>
-      <c r="F220" s="1">
+      <c r="F220" s="2">
         <v>46010</v>
       </c>
       <c r="G220" t="s">
@@ -12933,7 +12959,7 @@
         <v>1353</v>
       </c>
       <c r="I220">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J220">
         <v>154</v>
@@ -12944,7 +12970,7 @@
       <c r="L220" t="s">
         <v>1418</v>
       </c>
-      <c r="N220" s="1">
+      <c r="N220" s="2">
         <v>46164</v>
       </c>
       <c r="Q220" t="b">
@@ -12967,7 +12993,7 @@
       <c r="E221" t="s">
         <v>1040</v>
       </c>
-      <c r="F221" s="1">
+      <c r="F221" s="2">
         <v>46028</v>
       </c>
       <c r="G221" t="s">
@@ -12982,7 +13008,7 @@
       <c r="L221" t="s">
         <v>1419</v>
       </c>
-      <c r="N221" s="1">
+      <c r="N221" s="2">
         <v>46184</v>
       </c>
       <c r="Q221" t="b">
@@ -13005,7 +13031,7 @@
       <c r="E222" t="s">
         <v>1041</v>
       </c>
-      <c r="F222" s="1">
+      <c r="F222" s="2">
         <v>46028</v>
       </c>
       <c r="G222" t="s">
@@ -13020,7 +13046,7 @@
       <c r="L222" t="s">
         <v>1383</v>
       </c>
-      <c r="N222" s="1">
+      <c r="N222" s="2">
         <v>46232</v>
       </c>
       <c r="Q222" t="b">
@@ -13043,7 +13069,7 @@
       <c r="E223" t="s">
         <v>1042</v>
       </c>
-      <c r="F223" s="1">
+      <c r="F223" s="2">
         <v>46028</v>
       </c>
       <c r="G223" t="s">
@@ -13058,7 +13084,7 @@
       <c r="L223" t="s">
         <v>1383</v>
       </c>
-      <c r="N223" s="1">
+      <c r="N223" s="2">
         <v>46232</v>
       </c>
       <c r="Q223" t="b">
@@ -13081,7 +13107,7 @@
       <c r="E224" t="s">
         <v>1043</v>
       </c>
-      <c r="F224" s="1">
+      <c r="F224" s="2">
         <v>46028</v>
       </c>
       <c r="G224" t="s">
@@ -13091,7 +13117,7 @@
         <v>1353</v>
       </c>
       <c r="I224">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J224">
         <v>204</v>
@@ -13099,7 +13125,7 @@
       <c r="L224" t="s">
         <v>1383</v>
       </c>
-      <c r="N224" s="1">
+      <c r="N224" s="2">
         <v>46232</v>
       </c>
       <c r="Q224" t="b">
@@ -13122,7 +13148,7 @@
       <c r="E225" t="s">
         <v>1044</v>
       </c>
-      <c r="F225" s="1">
+      <c r="F225" s="2">
         <v>46028</v>
       </c>
       <c r="G225" t="s">
@@ -13137,7 +13163,7 @@
       <c r="L225" t="s">
         <v>1383</v>
       </c>
-      <c r="N225" s="1">
+      <c r="N225" s="2">
         <v>46232</v>
       </c>
       <c r="Q225" t="b">
@@ -13160,7 +13186,7 @@
       <c r="E226" t="s">
         <v>1045</v>
       </c>
-      <c r="F226" s="1">
+      <c r="F226" s="2">
         <v>46028</v>
       </c>
       <c r="G226" t="s">
@@ -13175,7 +13201,7 @@
       <c r="L226" t="s">
         <v>1383</v>
       </c>
-      <c r="N226" s="1">
+      <c r="N226" s="2">
         <v>46232</v>
       </c>
       <c r="Q226" t="b">
@@ -13198,7 +13224,7 @@
       <c r="E227" t="s">
         <v>1046</v>
       </c>
-      <c r="F227" s="1">
+      <c r="F227" s="2">
         <v>46028</v>
       </c>
       <c r="G227" t="s">
@@ -13213,7 +13239,7 @@
       <c r="L227" t="s">
         <v>1383</v>
       </c>
-      <c r="N227" s="1">
+      <c r="N227" s="2">
         <v>46232</v>
       </c>
       <c r="Q227" t="b">
@@ -13236,7 +13262,7 @@
       <c r="E228" t="s">
         <v>1047</v>
       </c>
-      <c r="F228" s="1">
+      <c r="F228" s="2">
         <v>46028</v>
       </c>
       <c r="G228" t="s">
@@ -13246,7 +13272,7 @@
         <v>1353</v>
       </c>
       <c r="I228">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J228">
         <v>204</v>
@@ -13254,7 +13280,7 @@
       <c r="L228" t="s">
         <v>1383</v>
       </c>
-      <c r="N228" s="1">
+      <c r="N228" s="2">
         <v>46232</v>
       </c>
       <c r="Q228" t="b">
@@ -13277,7 +13303,7 @@
       <c r="E229" t="s">
         <v>1048</v>
       </c>
-      <c r="F229" s="1">
+      <c r="F229" s="2">
         <v>46028</v>
       </c>
       <c r="G229" t="s">
@@ -13292,7 +13318,7 @@
       <c r="L229" t="s">
         <v>1420</v>
       </c>
-      <c r="N229" s="1">
+      <c r="N229" s="2">
         <v>46191</v>
       </c>
       <c r="Q229" t="b">
@@ -13315,7 +13341,7 @@
       <c r="E230" t="s">
         <v>1049</v>
       </c>
-      <c r="F230" s="1">
+      <c r="F230" s="2">
         <v>46028</v>
       </c>
       <c r="G230" t="s">
@@ -13325,7 +13351,7 @@
         <v>1353</v>
       </c>
       <c r="I230">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J230">
         <v>197</v>
@@ -13336,7 +13362,7 @@
       <c r="L230" t="s">
         <v>1395</v>
       </c>
-      <c r="N230" s="1">
+      <c r="N230" s="2">
         <v>46225</v>
       </c>
       <c r="Q230" t="b">
@@ -13359,7 +13385,7 @@
       <c r="E231" t="s">
         <v>1050</v>
       </c>
-      <c r="F231" s="1">
+      <c r="F231" s="2">
         <v>46028</v>
       </c>
       <c r="G231" t="s">
@@ -13369,7 +13395,7 @@
         <v>1353</v>
       </c>
       <c r="I231">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J231">
         <v>35</v>
@@ -13380,7 +13406,7 @@
       <c r="L231" t="s">
         <v>1421</v>
       </c>
-      <c r="N231" s="1">
+      <c r="N231" s="2">
         <v>46063</v>
       </c>
       <c r="Q231" t="b">
@@ -13403,7 +13429,7 @@
       <c r="E232" t="s">
         <v>1051</v>
       </c>
-      <c r="F232" s="1">
+      <c r="F232" s="2">
         <v>46028</v>
       </c>
       <c r="G232" t="s">
@@ -13432,7 +13458,7 @@
       <c r="E233" t="s">
         <v>1052</v>
       </c>
-      <c r="F233" s="1">
+      <c r="F233" s="2">
         <v>46028</v>
       </c>
       <c r="G233" t="s">
@@ -13461,7 +13487,7 @@
       <c r="E234" t="s">
         <v>1053</v>
       </c>
-      <c r="F234" s="1">
+      <c r="F234" s="2">
         <v>46028</v>
       </c>
       <c r="G234" t="s">
@@ -13471,7 +13497,7 @@
         <v>1353</v>
       </c>
       <c r="I234">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J234">
         <v>35</v>
@@ -13482,7 +13508,7 @@
       <c r="L234" t="s">
         <v>1421</v>
       </c>
-      <c r="N234" s="1">
+      <c r="N234" s="2">
         <v>46063</v>
       </c>
       <c r="P234" t="s">
@@ -13508,7 +13534,7 @@
       <c r="E235" t="s">
         <v>1054</v>
       </c>
-      <c r="F235" s="1">
+      <c r="F235" s="2">
         <v>46028</v>
       </c>
       <c r="G235" t="s">
@@ -13518,7 +13544,7 @@
         <v>1353</v>
       </c>
       <c r="I235">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J235">
         <v>35</v>
@@ -13529,7 +13555,7 @@
       <c r="L235" t="s">
         <v>1421</v>
       </c>
-      <c r="N235" s="1">
+      <c r="N235" s="2">
         <v>46063</v>
       </c>
       <c r="P235" t="s">
@@ -13555,7 +13581,7 @@
       <c r="E236" t="s">
         <v>1055</v>
       </c>
-      <c r="F236" s="1">
+      <c r="F236" s="2">
         <v>46028</v>
       </c>
       <c r="G236" t="s">
@@ -13565,7 +13591,7 @@
         <v>1353</v>
       </c>
       <c r="I236">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J236">
         <v>86</v>
@@ -13576,7 +13602,7 @@
       <c r="L236" t="s">
         <v>1422</v>
       </c>
-      <c r="N236" s="1">
+      <c r="N236" s="2">
         <v>46114</v>
       </c>
       <c r="Q236" t="b">
@@ -13599,7 +13625,7 @@
       <c r="E237" t="s">
         <v>1056</v>
       </c>
-      <c r="F237" s="1">
+      <c r="F237" s="2">
         <v>46028</v>
       </c>
       <c r="G237" t="s">
@@ -13617,7 +13643,7 @@
       <c r="L237" t="s">
         <v>1423</v>
       </c>
-      <c r="N237" s="1">
+      <c r="N237" s="2">
         <v>46210</v>
       </c>
       <c r="P237" t="s">
@@ -13643,7 +13669,7 @@
       <c r="E238" t="s">
         <v>1057</v>
       </c>
-      <c r="F238" s="1">
+      <c r="F238" s="2">
         <v>46028</v>
       </c>
       <c r="G238" t="s">
@@ -13672,7 +13698,7 @@
       <c r="E239" t="s">
         <v>1058</v>
       </c>
-      <c r="F239" s="1">
+      <c r="F239" s="2">
         <v>46036</v>
       </c>
       <c r="G239" t="s">
@@ -13682,7 +13708,7 @@
         <v>1353</v>
       </c>
       <c r="I239">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K239" t="s">
         <v>1330</v>
@@ -13690,7 +13716,7 @@
       <c r="L239" t="s">
         <v>1424</v>
       </c>
-      <c r="N239" s="1">
+      <c r="N239" s="2">
         <v>46052</v>
       </c>
       <c r="Q239" t="b">
@@ -13713,7 +13739,7 @@
       <c r="E240" t="s">
         <v>1059</v>
       </c>
-      <c r="F240" s="1">
+      <c r="F240" s="2">
         <v>46036</v>
       </c>
       <c r="G240" t="s">
@@ -13742,7 +13768,7 @@
       <c r="E241" t="s">
         <v>1060</v>
       </c>
-      <c r="F241" s="1">
+      <c r="F241" s="2">
         <v>46036</v>
       </c>
       <c r="G241" t="s">
@@ -13771,7 +13797,7 @@
       <c r="E242" t="s">
         <v>1061</v>
       </c>
-      <c r="F242" s="1">
+      <c r="F242" s="2">
         <v>46036</v>
       </c>
       <c r="G242" t="s">
@@ -13781,7 +13807,7 @@
         <v>1353</v>
       </c>
       <c r="I242">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K242" t="s">
         <v>1356</v>
@@ -13809,7 +13835,7 @@
       <c r="E243" t="s">
         <v>1062</v>
       </c>
-      <c r="F243" s="1">
+      <c r="F243" s="2">
         <v>46048</v>
       </c>
       <c r="G243" t="s">
@@ -13838,7 +13864,7 @@
       <c r="E244" t="s">
         <v>1063</v>
       </c>
-      <c r="F244" s="1">
+      <c r="F244" s="2">
         <v>46048</v>
       </c>
       <c r="G244" t="s">
@@ -13848,7 +13874,7 @@
         <v>1353</v>
       </c>
       <c r="I244">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J244">
         <v>15</v>
@@ -13856,7 +13882,7 @@
       <c r="K244" t="s">
         <v>1359</v>
       </c>
-      <c r="N244" s="1">
+      <c r="N244" s="2">
         <v>46063</v>
       </c>
       <c r="Q244" t="b">
@@ -13879,7 +13905,7 @@
       <c r="E245" t="s">
         <v>1064</v>
       </c>
-      <c r="F245" s="1">
+      <c r="F245" s="2">
         <v>46048</v>
       </c>
       <c r="G245" t="s">
@@ -13889,7 +13915,7 @@
         <v>1353</v>
       </c>
       <c r="I245">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J245">
         <v>15</v>
@@ -13900,7 +13926,7 @@
       <c r="L245" t="s">
         <v>1425</v>
       </c>
-      <c r="N245" s="1">
+      <c r="N245" s="2">
         <v>46063</v>
       </c>
       <c r="Q245" t="b">
@@ -13923,7 +13949,7 @@
       <c r="E246" t="s">
         <v>1065</v>
       </c>
-      <c r="F246" s="1">
+      <c r="F246" s="2">
         <v>46050</v>
       </c>
       <c r="G246" t="s">
@@ -13941,7 +13967,7 @@
       <c r="L246" t="s">
         <v>1426</v>
       </c>
-      <c r="N246" s="1">
+      <c r="N246" s="2">
         <v>46191</v>
       </c>
       <c r="Q246" t="b">
@@ -13964,7 +13990,7 @@
       <c r="E247" t="s">
         <v>1066</v>
       </c>
-      <c r="F247" s="1">
+      <c r="F247" s="2">
         <v>46050</v>
       </c>
       <c r="G247" t="s">
@@ -13993,7 +14019,7 @@
       <c r="E248" t="s">
         <v>1067</v>
       </c>
-      <c r="F248" s="1">
+      <c r="F248" s="2">
         <v>46050</v>
       </c>
       <c r="G248" t="s">
@@ -14022,7 +14048,7 @@
       <c r="E249" t="s">
         <v>1068</v>
       </c>
-      <c r="F249" s="1">
+      <c r="F249" s="2">
         <v>46050</v>
       </c>
       <c r="G249" t="s">
@@ -14032,7 +14058,7 @@
         <v>1353</v>
       </c>
       <c r="I249">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K249" t="s">
         <v>1357</v>
@@ -14060,7 +14086,7 @@
       <c r="E250" t="s">
         <v>1069</v>
       </c>
-      <c r="F250" s="1">
+      <c r="F250" s="2">
         <v>46063</v>
       </c>
       <c r="G250" t="s">
@@ -14098,7 +14124,7 @@
       <c r="E251" t="s">
         <v>1070</v>
       </c>
-      <c r="F251" s="1">
+      <c r="F251" s="2">
         <v>46063</v>
       </c>
       <c r="G251" t="s">
@@ -14127,7 +14153,7 @@
       <c r="E252" t="s">
         <v>1071</v>
       </c>
-      <c r="F252" s="1">
+      <c r="F252" s="2">
         <v>46063</v>
       </c>
       <c r="G252" t="s">
@@ -14156,7 +14182,7 @@
       <c r="E253" t="s">
         <v>1072</v>
       </c>
-      <c r="F253" s="1">
+      <c r="F253" s="2">
         <v>46063</v>
       </c>
       <c r="G253" t="s">
@@ -14166,7 +14192,7 @@
         <v>1353</v>
       </c>
       <c r="I253">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J253">
         <v>162</v>
@@ -14177,7 +14203,7 @@
       <c r="L253" t="s">
         <v>1395</v>
       </c>
-      <c r="N253" s="1">
+      <c r="N253" s="2">
         <v>46225</v>
       </c>
       <c r="Q253" t="b">
@@ -14200,7 +14226,7 @@
       <c r="E254" t="s">
         <v>1073</v>
       </c>
-      <c r="F254" s="1">
+      <c r="F254" s="2">
         <v>46063</v>
       </c>
       <c r="G254" t="s">
@@ -14210,7 +14236,7 @@
         <v>1353</v>
       </c>
       <c r="I254">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K254" t="s">
         <v>1360</v>
@@ -14238,7 +14264,7 @@
       <c r="E255" t="s">
         <v>1074</v>
       </c>
-      <c r="F255" s="1">
+      <c r="F255" s="2">
         <v>46063</v>
       </c>
       <c r="G255" t="s">
@@ -14248,7 +14274,7 @@
         <v>1353</v>
       </c>
       <c r="I255">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J255">
         <v>72</v>
@@ -14259,7 +14285,7 @@
       <c r="L255" t="s">
         <v>1388</v>
       </c>
-      <c r="N255" s="1">
+      <c r="N255" s="2">
         <v>46135</v>
       </c>
       <c r="Q255" t="b">
@@ -14282,7 +14308,7 @@
       <c r="E256" t="s">
         <v>1075</v>
       </c>
-      <c r="F256" s="1">
+      <c r="F256" s="2">
         <v>46063</v>
       </c>
       <c r="G256" t="s">
@@ -14292,7 +14318,7 @@
         <v>1353</v>
       </c>
       <c r="I256">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J256">
         <v>23</v>
@@ -14300,7 +14326,7 @@
       <c r="K256" t="s">
         <v>1357</v>
       </c>
-      <c r="N256" s="1">
+      <c r="N256" s="2">
         <v>46086</v>
       </c>
       <c r="O256">
@@ -14326,7 +14352,7 @@
       <c r="E257" t="s">
         <v>1076</v>
       </c>
-      <c r="F257" s="1">
+      <c r="F257" s="2">
         <v>46063</v>
       </c>
       <c r="G257" t="s">
@@ -14355,7 +14381,7 @@
       <c r="E258" t="s">
         <v>1077</v>
       </c>
-      <c r="F258" s="1">
+      <c r="F258" s="2">
         <v>46063</v>
       </c>
       <c r="G258" t="s">
@@ -14384,7 +14410,7 @@
       <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="F259" s="1">
+      <c r="F259" s="2">
         <v>46063</v>
       </c>
       <c r="G259" t="s">
@@ -14394,7 +14420,7 @@
         <v>1353</v>
       </c>
       <c r="I259">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J259">
         <v>72</v>
@@ -14405,7 +14431,7 @@
       <c r="L259" t="s">
         <v>1388</v>
       </c>
-      <c r="N259" s="1">
+      <c r="N259" s="2">
         <v>46135</v>
       </c>
       <c r="Q259" t="b">
@@ -14428,7 +14454,7 @@
       <c r="E260" t="s">
         <v>1079</v>
       </c>
-      <c r="F260" s="1">
+      <c r="F260" s="2">
         <v>46063</v>
       </c>
       <c r="G260" t="s">
@@ -14438,7 +14464,7 @@
         <v>1353</v>
       </c>
       <c r="I260">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J260">
         <v>84</v>
@@ -14449,7 +14475,7 @@
       <c r="L260" t="s">
         <v>1388</v>
       </c>
-      <c r="N260" s="1">
+      <c r="N260" s="2">
         <v>46147</v>
       </c>
       <c r="Q260" t="b">
@@ -14472,7 +14498,7 @@
       <c r="E261" t="s">
         <v>1080</v>
       </c>
-      <c r="F261" s="1">
+      <c r="F261" s="2">
         <v>46063</v>
       </c>
       <c r="G261" t="s">
@@ -14482,7 +14508,7 @@
         <v>1353</v>
       </c>
       <c r="I261">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J261">
         <v>162</v>
@@ -14493,7 +14519,7 @@
       <c r="L261" t="s">
         <v>1427</v>
       </c>
-      <c r="N261" s="1">
+      <c r="N261" s="2">
         <v>46225</v>
       </c>
       <c r="Q261" t="b">
@@ -14516,7 +14542,7 @@
       <c r="E262" t="s">
         <v>1081</v>
       </c>
-      <c r="F262" s="1">
+      <c r="F262" s="2">
         <v>46063</v>
       </c>
       <c r="G262" t="s">
@@ -14534,7 +14560,7 @@
       <c r="L262" t="s">
         <v>1428</v>
       </c>
-      <c r="N262" s="1">
+      <c r="N262" s="2">
         <v>46113</v>
       </c>
       <c r="P262" t="s">
@@ -14560,7 +14586,7 @@
       <c r="E263" t="s">
         <v>1082</v>
       </c>
-      <c r="F263" s="1">
+      <c r="F263" s="2">
         <v>46063</v>
       </c>
       <c r="G263" t="s">
@@ -14589,7 +14615,7 @@
       <c r="E264" t="s">
         <v>1083</v>
       </c>
-      <c r="F264" s="1">
+      <c r="F264" s="2">
         <v>46063</v>
       </c>
       <c r="G264" t="s">
@@ -14599,7 +14625,7 @@
         <v>1353</v>
       </c>
       <c r="I264">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J264">
         <v>162</v>
@@ -14610,7 +14636,7 @@
       <c r="L264" t="s">
         <v>1388</v>
       </c>
-      <c r="N264" s="1">
+      <c r="N264" s="2">
         <v>46225</v>
       </c>
       <c r="Q264" t="b">
@@ -14633,7 +14659,7 @@
       <c r="E265" t="s">
         <v>1084</v>
       </c>
-      <c r="F265" s="1">
+      <c r="F265" s="2">
         <v>46063</v>
       </c>
       <c r="G265" t="s">
@@ -14643,7 +14669,7 @@
         <v>1353</v>
       </c>
       <c r="I265">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J265">
         <v>162</v>
@@ -14654,7 +14680,7 @@
       <c r="L265" t="s">
         <v>1395</v>
       </c>
-      <c r="N265" s="1">
+      <c r="N265" s="2">
         <v>46225</v>
       </c>
       <c r="Q265" t="b">
@@ -14677,7 +14703,7 @@
       <c r="E266" t="s">
         <v>1085</v>
       </c>
-      <c r="F266" s="1">
+      <c r="F266" s="2">
         <v>46063</v>
       </c>
       <c r="G266" t="s">
@@ -14687,7 +14713,7 @@
         <v>1353</v>
       </c>
       <c r="I266">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J266">
         <v>84</v>
@@ -14698,7 +14724,7 @@
       <c r="L266" t="s">
         <v>1388</v>
       </c>
-      <c r="N266" s="1">
+      <c r="N266" s="2">
         <v>46147</v>
       </c>
       <c r="Q266" t="b">
@@ -14721,7 +14747,7 @@
       <c r="E267" t="s">
         <v>1086</v>
       </c>
-      <c r="F267" s="1">
+      <c r="F267" s="2">
         <v>46063</v>
       </c>
       <c r="G267" t="s">
@@ -14731,7 +14757,7 @@
         <v>1353</v>
       </c>
       <c r="I267">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K267" t="s">
         <v>1360</v>
@@ -14759,7 +14785,7 @@
       <c r="E268" t="s">
         <v>1087</v>
       </c>
-      <c r="F268" s="1">
+      <c r="F268" s="2">
         <v>46063</v>
       </c>
       <c r="G268" t="s">
@@ -14769,7 +14795,7 @@
         <v>1353</v>
       </c>
       <c r="I268">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K268" t="s">
         <v>1357</v>
@@ -14794,7 +14820,7 @@
       <c r="D269" t="s">
         <v>798</v>
       </c>
-      <c r="F269" s="1">
+      <c r="F269" s="2">
         <v>46063</v>
       </c>
       <c r="G269" t="s">
@@ -14804,7 +14830,7 @@
         <v>1353</v>
       </c>
       <c r="I269">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K269" t="s">
         <v>1357</v>
@@ -14832,7 +14858,7 @@
       <c r="E270" t="s">
         <v>1088</v>
       </c>
-      <c r="F270" s="1">
+      <c r="F270" s="2">
         <v>46063</v>
       </c>
       <c r="G270" t="s">
@@ -14842,7 +14868,7 @@
         <v>1353</v>
       </c>
       <c r="I270">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K270" t="s">
         <v>1360</v>
@@ -14870,7 +14896,7 @@
       <c r="E271" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="1">
+      <c r="F271" s="2">
         <v>46063</v>
       </c>
       <c r="G271" t="s">
@@ -14880,7 +14906,7 @@
         <v>1353</v>
       </c>
       <c r="I271">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K271" t="s">
         <v>1360</v>
@@ -14908,7 +14934,7 @@
       <c r="E272" t="s">
         <v>1090</v>
       </c>
-      <c r="F272" s="1">
+      <c r="F272" s="2">
         <v>46063</v>
       </c>
       <c r="G272" t="s">
@@ -14926,7 +14952,7 @@
       <c r="L272" t="s">
         <v>1429</v>
       </c>
-      <c r="N272" s="1">
+      <c r="N272" s="2">
         <v>46185</v>
       </c>
       <c r="O272" t="s">
@@ -14952,7 +14978,7 @@
       <c r="E273" t="s">
         <v>1091</v>
       </c>
-      <c r="F273" s="1">
+      <c r="F273" s="2">
         <v>46063</v>
       </c>
       <c r="G273" t="s">
@@ -14981,7 +15007,7 @@
       <c r="E274" t="s">
         <v>1092</v>
       </c>
-      <c r="F274" s="1">
+      <c r="F274" s="2">
         <v>46063</v>
       </c>
       <c r="G274" t="s">
@@ -14996,7 +15022,7 @@
       <c r="L274" t="s">
         <v>1383</v>
       </c>
-      <c r="N274" s="1">
+      <c r="N274" s="2">
         <v>46232</v>
       </c>
       <c r="Q274" t="b">
@@ -15019,7 +15045,7 @@
       <c r="E275" t="s">
         <v>1093</v>
       </c>
-      <c r="F275" s="1">
+      <c r="F275" s="2">
         <v>46063</v>
       </c>
       <c r="G275" t="s">
@@ -15048,7 +15074,7 @@
       <c r="E276" t="s">
         <v>1094</v>
       </c>
-      <c r="F276" s="1">
+      <c r="F276" s="2">
         <v>46063</v>
       </c>
       <c r="G276" t="s">
@@ -15058,7 +15084,7 @@
         <v>1353</v>
       </c>
       <c r="I276">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K276" t="s">
         <v>1361</v>
@@ -15086,7 +15112,7 @@
       <c r="E277" t="s">
         <v>1095</v>
       </c>
-      <c r="F277" s="1">
+      <c r="F277" s="2">
         <v>46063</v>
       </c>
       <c r="G277" t="s">
@@ -15096,7 +15122,7 @@
         <v>1353</v>
       </c>
       <c r="I277">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K277" t="s">
         <v>1357</v>
@@ -15124,7 +15150,7 @@
       <c r="E278" t="s">
         <v>1096</v>
       </c>
-      <c r="F278" s="1">
+      <c r="F278" s="2">
         <v>46077</v>
       </c>
       <c r="G278" t="s">
@@ -15134,7 +15160,7 @@
         <v>1353</v>
       </c>
       <c r="I278">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J278">
         <v>148</v>
@@ -15145,7 +15171,7 @@
       <c r="L278" t="s">
         <v>1395</v>
       </c>
-      <c r="N278" s="1">
+      <c r="N278" s="2">
         <v>46225</v>
       </c>
       <c r="Q278" t="b">
@@ -15168,7 +15194,7 @@
       <c r="E279" t="s">
         <v>1097</v>
       </c>
-      <c r="F279" s="1">
+      <c r="F279" s="2">
         <v>46077</v>
       </c>
       <c r="G279" t="s">
@@ -15178,7 +15204,7 @@
         <v>1353</v>
       </c>
       <c r="I279">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K279" t="s">
         <v>1359</v>
@@ -15209,7 +15235,7 @@
       <c r="E280" t="s">
         <v>1098</v>
       </c>
-      <c r="F280" s="1">
+      <c r="F280" s="2">
         <v>46085</v>
       </c>
       <c r="G280" t="s">
@@ -15219,7 +15245,7 @@
         <v>1353</v>
       </c>
       <c r="I280">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K280" t="s">
         <v>1357</v>
@@ -15247,7 +15273,7 @@
       <c r="E281" t="s">
         <v>1099</v>
       </c>
-      <c r="F281" s="1">
+      <c r="F281" s="2">
         <v>46085</v>
       </c>
       <c r="G281" t="s">
@@ -15257,7 +15283,7 @@
         <v>1353</v>
       </c>
       <c r="I281">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K281" t="s">
         <v>1357</v>
@@ -15288,7 +15314,7 @@
       <c r="E282" t="s">
         <v>1100</v>
       </c>
-      <c r="F282" s="1">
+      <c r="F282" s="2">
         <v>46090</v>
       </c>
       <c r="G282" t="s">
@@ -15298,7 +15324,7 @@
         <v>1353</v>
       </c>
       <c r="I282">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K282" t="s">
         <v>1357</v>
@@ -15326,7 +15352,7 @@
       <c r="E283" t="s">
         <v>1101</v>
       </c>
-      <c r="F283" s="1">
+      <c r="F283" s="2">
         <v>46100</v>
       </c>
       <c r="G283" t="s">
@@ -15355,7 +15381,7 @@
       <c r="E284" t="s">
         <v>1102</v>
       </c>
-      <c r="F284" s="1">
+      <c r="F284" s="2">
         <v>46100</v>
       </c>
       <c r="G284" t="s">
@@ -15384,7 +15410,7 @@
       <c r="E285" t="s">
         <v>1103</v>
       </c>
-      <c r="F285" s="1">
+      <c r="F285" s="2">
         <v>46100</v>
       </c>
       <c r="G285" t="s">
@@ -15413,7 +15439,7 @@
       <c r="E286" t="s">
         <v>1104</v>
       </c>
-      <c r="F286" s="1">
+      <c r="F286" s="2">
         <v>46100</v>
       </c>
       <c r="G286" t="s">
@@ -15442,7 +15468,7 @@
       <c r="E287" t="s">
         <v>1105</v>
       </c>
-      <c r="F287" s="1">
+      <c r="F287" s="2">
         <v>46107</v>
       </c>
       <c r="G287" t="s">
@@ -15471,7 +15497,7 @@
       <c r="E288" t="s">
         <v>1106</v>
       </c>
-      <c r="F288" s="1">
+      <c r="F288" s="2">
         <v>46107</v>
       </c>
       <c r="G288" t="s">
@@ -15481,7 +15507,7 @@
         <v>1353</v>
       </c>
       <c r="I288">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J288">
         <v>28</v>
@@ -15492,7 +15518,7 @@
       <c r="L288" t="s">
         <v>1388</v>
       </c>
-      <c r="N288" s="1">
+      <c r="N288" s="2">
         <v>46135</v>
       </c>
       <c r="Q288" t="b">
@@ -15515,7 +15541,7 @@
       <c r="E289" t="s">
         <v>1107</v>
       </c>
-      <c r="F289" s="1">
+      <c r="F289" s="2">
         <v>46107</v>
       </c>
       <c r="G289" t="s">
@@ -15544,7 +15570,7 @@
       <c r="E290" t="s">
         <v>1108</v>
       </c>
-      <c r="F290" s="1">
+      <c r="F290" s="2">
         <v>46107</v>
       </c>
       <c r="G290" t="s">
@@ -15554,7 +15580,7 @@
         <v>1353</v>
       </c>
       <c r="I290">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J290">
         <v>20</v>
@@ -15565,7 +15591,7 @@
       <c r="L290" t="s">
         <v>1388</v>
       </c>
-      <c r="N290" s="1">
+      <c r="N290" s="2">
         <v>46127</v>
       </c>
       <c r="Q290" t="b">
@@ -15588,7 +15614,7 @@
       <c r="E291" t="s">
         <v>1109</v>
       </c>
-      <c r="F291" s="1">
+      <c r="F291" s="2">
         <v>46107</v>
       </c>
       <c r="G291" t="s">
@@ -15598,7 +15624,7 @@
         <v>1353</v>
       </c>
       <c r="I291">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J291">
         <v>20</v>
@@ -15609,7 +15635,7 @@
       <c r="L291" t="s">
         <v>1430</v>
       </c>
-      <c r="N291" s="1">
+      <c r="N291" s="2">
         <v>46127</v>
       </c>
       <c r="Q291" t="b">
@@ -15632,7 +15658,7 @@
       <c r="E292" t="s">
         <v>1110</v>
       </c>
-      <c r="F292" s="1">
+      <c r="F292" s="2">
         <v>46112</v>
       </c>
       <c r="G292" t="s">
@@ -15642,7 +15668,7 @@
         <v>1353</v>
       </c>
       <c r="I292">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K292" t="s">
         <v>1360</v>
@@ -15670,7 +15696,7 @@
       <c r="E293" t="s">
         <v>1111</v>
       </c>
-      <c r="F293" s="1">
+      <c r="F293" s="2">
         <v>46125</v>
       </c>
       <c r="G293" t="s">
@@ -15680,7 +15706,7 @@
         <v>1353</v>
       </c>
       <c r="I293">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K293" t="s">
         <v>1361</v>
@@ -15708,7 +15734,7 @@
       <c r="E294" t="s">
         <v>1112</v>
       </c>
-      <c r="F294" s="1">
+      <c r="F294" s="2">
         <v>46125</v>
       </c>
       <c r="G294" t="s">
@@ -15718,7 +15744,7 @@
         <v>1353</v>
       </c>
       <c r="I294">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K294" t="s">
         <v>1366</v>
@@ -15743,7 +15769,7 @@
       <c r="E295" t="s">
         <v>1113</v>
       </c>
-      <c r="F295" s="1">
+      <c r="F295" s="2">
         <v>46125</v>
       </c>
       <c r="G295" t="s">
@@ -15753,7 +15779,7 @@
         <v>1353</v>
       </c>
       <c r="I295">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K295" t="s">
         <v>1366</v>
@@ -15778,7 +15804,7 @@
       <c r="E296" t="s">
         <v>1114</v>
       </c>
-      <c r="F296" s="1">
+      <c r="F296" s="2">
         <v>46125</v>
       </c>
       <c r="G296" t="s">
@@ -15788,7 +15814,7 @@
         <v>1353</v>
       </c>
       <c r="I296">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K296" t="s">
         <v>1366</v>
@@ -15813,7 +15839,7 @@
       <c r="E297" t="s">
         <v>1115</v>
       </c>
-      <c r="F297" s="1">
+      <c r="F297" s="2">
         <v>46125</v>
       </c>
       <c r="G297" t="s">
@@ -15825,7 +15851,7 @@
       <c r="K297" t="s">
         <v>1359</v>
       </c>
-      <c r="N297" s="1">
+      <c r="N297" s="2">
         <v>46183</v>
       </c>
       <c r="O297">
@@ -15851,7 +15877,7 @@
       <c r="E298" t="s">
         <v>1116</v>
       </c>
-      <c r="F298" s="1">
+      <c r="F298" s="2">
         <v>46125</v>
       </c>
       <c r="G298" t="s">
@@ -15861,7 +15887,7 @@
         <v>1353</v>
       </c>
       <c r="I298">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J298">
         <v>58</v>
@@ -15869,7 +15895,7 @@
       <c r="K298" t="s">
         <v>1359</v>
       </c>
-      <c r="N298" s="1">
+      <c r="N298" s="2">
         <v>46183</v>
       </c>
       <c r="Q298" t="b">
@@ -15892,7 +15918,7 @@
       <c r="E299" t="s">
         <v>1117</v>
       </c>
-      <c r="F299" s="1">
+      <c r="F299" s="2">
         <v>46125</v>
       </c>
       <c r="G299" t="s">
@@ -15902,7 +15928,7 @@
         <v>1353</v>
       </c>
       <c r="I299">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J299">
         <v>100</v>
@@ -15913,7 +15939,7 @@
       <c r="L299" t="s">
         <v>1388</v>
       </c>
-      <c r="N299" s="1">
+      <c r="N299" s="2">
         <v>46225</v>
       </c>
       <c r="Q299" t="b">
@@ -15936,7 +15962,7 @@
       <c r="E300" t="s">
         <v>1118</v>
       </c>
-      <c r="F300" s="1">
+      <c r="F300" s="2">
         <v>46125</v>
       </c>
       <c r="G300" t="s">
@@ -15946,7 +15972,7 @@
         <v>1353</v>
       </c>
       <c r="I300">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J300">
         <v>86</v>
@@ -15957,7 +15983,7 @@
       <c r="L300" t="s">
         <v>1388</v>
       </c>
-      <c r="N300" s="1">
+      <c r="N300" s="2">
         <v>46211</v>
       </c>
       <c r="Q300" t="b">
@@ -15980,7 +16006,7 @@
       <c r="E301" t="s">
         <v>1119</v>
       </c>
-      <c r="F301" s="1">
+      <c r="F301" s="2">
         <v>46125</v>
       </c>
       <c r="G301" t="s">
@@ -15990,7 +16016,7 @@
         <v>1353</v>
       </c>
       <c r="I301">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J301">
         <v>102</v>
@@ -16001,7 +16027,7 @@
       <c r="L301" t="s">
         <v>1388</v>
       </c>
-      <c r="N301" s="1">
+      <c r="N301" s="2">
         <v>46227</v>
       </c>
       <c r="Q301" t="b">
@@ -16024,7 +16050,7 @@
       <c r="E302" t="s">
         <v>1120</v>
       </c>
-      <c r="F302" s="1">
+      <c r="F302" s="2">
         <v>46125</v>
       </c>
       <c r="G302" t="s">
@@ -16034,7 +16060,7 @@
         <v>1353</v>
       </c>
       <c r="I302">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K302" t="s">
         <v>1360</v>
@@ -16062,7 +16088,7 @@
       <c r="E303" t="s">
         <v>1121</v>
       </c>
-      <c r="F303" s="1">
+      <c r="F303" s="2">
         <v>46125</v>
       </c>
       <c r="G303" t="s">
@@ -16072,7 +16098,7 @@
         <v>1353</v>
       </c>
       <c r="I303">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K303" t="s">
         <v>1357</v>
@@ -16100,7 +16126,7 @@
       <c r="E304" t="s">
         <v>1122</v>
       </c>
-      <c r="F304" s="1">
+      <c r="F304" s="2">
         <v>46125</v>
       </c>
       <c r="G304" t="s">
@@ -16110,7 +16136,7 @@
         <v>1353</v>
       </c>
       <c r="I304">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K304" t="s">
         <v>1360</v>
@@ -16138,7 +16164,7 @@
       <c r="E305" t="s">
         <v>1123</v>
       </c>
-      <c r="F305" s="1">
+      <c r="F305" s="2">
         <v>46125</v>
       </c>
       <c r="G305" t="s">
@@ -16148,7 +16174,7 @@
         <v>1353</v>
       </c>
       <c r="I305">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J305">
         <v>35</v>
@@ -16159,7 +16185,7 @@
       <c r="L305" t="s">
         <v>1431</v>
       </c>
-      <c r="N305" s="1">
+      <c r="N305" s="2">
         <v>46160</v>
       </c>
       <c r="Q305" t="b">
@@ -16182,7 +16208,7 @@
       <c r="E306" t="s">
         <v>1124</v>
       </c>
-      <c r="F306" s="1">
+      <c r="F306" s="2">
         <v>46125</v>
       </c>
       <c r="G306" t="s">
@@ -16192,7 +16218,7 @@
         <v>1353</v>
       </c>
       <c r="I306">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J306">
         <v>31</v>
@@ -16203,7 +16229,7 @@
       <c r="L306" t="s">
         <v>1432</v>
       </c>
-      <c r="N306" s="1">
+      <c r="N306" s="2">
         <v>46156</v>
       </c>
       <c r="Q306" t="b">
@@ -16226,7 +16252,7 @@
       <c r="E307" t="s">
         <v>1125</v>
       </c>
-      <c r="F307" s="1">
+      <c r="F307" s="2">
         <v>46125</v>
       </c>
       <c r="G307" t="s">
@@ -16244,7 +16270,7 @@
       <c r="L307" t="s">
         <v>1433</v>
       </c>
-      <c r="N307" s="1">
+      <c r="N307" s="2">
         <v>46209</v>
       </c>
       <c r="P307" t="s">
@@ -16270,7 +16296,7 @@
       <c r="E308" t="s">
         <v>1126</v>
       </c>
-      <c r="F308" s="1">
+      <c r="F308" s="2">
         <v>46125</v>
       </c>
       <c r="G308" t="s">
@@ -16280,7 +16306,7 @@
         <v>1353</v>
       </c>
       <c r="I308">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K308" t="s">
         <v>1356</v>
@@ -16308,7 +16334,7 @@
       <c r="E309" t="s">
         <v>1127</v>
       </c>
-      <c r="F309" s="1">
+      <c r="F309" s="2">
         <v>46125</v>
       </c>
       <c r="G309" t="s">
@@ -16323,7 +16349,7 @@
       <c r="L309" t="s">
         <v>1383</v>
       </c>
-      <c r="N309" s="1">
+      <c r="N309" s="2">
         <v>46232</v>
       </c>
       <c r="Q309" t="b">
@@ -16346,7 +16372,7 @@
       <c r="E310" t="s">
         <v>1128</v>
       </c>
-      <c r="F310" s="1">
+      <c r="F310" s="2">
         <v>46125</v>
       </c>
       <c r="G310" t="s">
@@ -16356,7 +16382,7 @@
         <v>1353</v>
       </c>
       <c r="I310">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J310">
         <v>107</v>
@@ -16367,7 +16393,7 @@
       <c r="L310" t="s">
         <v>1383</v>
       </c>
-      <c r="N310" s="1">
+      <c r="N310" s="2">
         <v>46232</v>
       </c>
       <c r="Q310" t="b">
@@ -16390,7 +16416,7 @@
       <c r="E311" t="s">
         <v>1129</v>
       </c>
-      <c r="F311" s="1">
+      <c r="F311" s="2">
         <v>46125</v>
       </c>
       <c r="G311" t="s">
@@ -16400,7 +16426,7 @@
         <v>1353</v>
       </c>
       <c r="I311">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K311" t="s">
         <v>1356</v>
@@ -16428,7 +16454,7 @@
       <c r="E312" t="s">
         <v>1130</v>
       </c>
-      <c r="F312" s="1">
+      <c r="F312" s="2">
         <v>46125</v>
       </c>
       <c r="G312" t="s">
@@ -16446,7 +16472,7 @@
       <c r="L312" t="s">
         <v>1383</v>
       </c>
-      <c r="N312" s="1">
+      <c r="N312" s="2">
         <v>46232</v>
       </c>
       <c r="Q312" t="b">
@@ -16469,7 +16495,7 @@
       <c r="E313" t="s">
         <v>1131</v>
       </c>
-      <c r="F313" s="1">
+      <c r="F313" s="2">
         <v>46125</v>
       </c>
       <c r="G313" t="s">
@@ -16504,7 +16530,7 @@
       <c r="E314" t="s">
         <v>1132</v>
       </c>
-      <c r="F314" s="1">
+      <c r="F314" s="2">
         <v>46125</v>
       </c>
       <c r="G314" t="s">
@@ -16519,7 +16545,7 @@
       <c r="L314" t="s">
         <v>1383</v>
       </c>
-      <c r="N314" s="1">
+      <c r="N314" s="2">
         <v>46232</v>
       </c>
       <c r="Q314" t="b">
@@ -16542,7 +16568,7 @@
       <c r="E315" t="s">
         <v>1133</v>
       </c>
-      <c r="F315" s="1">
+      <c r="F315" s="2">
         <v>46125</v>
       </c>
       <c r="G315" t="s">
@@ -16557,7 +16583,7 @@
       <c r="L315" t="s">
         <v>1383</v>
       </c>
-      <c r="N315" s="1">
+      <c r="N315" s="2">
         <v>46232</v>
       </c>
       <c r="Q315" t="b">
@@ -16580,7 +16606,7 @@
       <c r="E316" t="s">
         <v>1134</v>
       </c>
-      <c r="F316" s="1">
+      <c r="F316" s="2">
         <v>46125</v>
       </c>
       <c r="G316" t="s">
@@ -16590,7 +16616,7 @@
         <v>1353</v>
       </c>
       <c r="I316">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K316" t="s">
         <v>1357</v>
@@ -16618,7 +16644,7 @@
       <c r="E317" t="s">
         <v>1135</v>
       </c>
-      <c r="F317" s="1">
+      <c r="F317" s="2">
         <v>46125</v>
       </c>
       <c r="G317" t="s">
@@ -16653,7 +16679,7 @@
       <c r="E318" t="s">
         <v>1136</v>
       </c>
-      <c r="F318" s="1">
+      <c r="F318" s="2">
         <v>46125</v>
       </c>
       <c r="G318" t="s">
@@ -16682,7 +16708,7 @@
       <c r="E319" t="s">
         <v>1137</v>
       </c>
-      <c r="F319" s="1">
+      <c r="F319" s="2">
         <v>46125</v>
       </c>
       <c r="G319" t="s">
@@ -16697,7 +16723,7 @@
       <c r="L319" t="s">
         <v>1434</v>
       </c>
-      <c r="N319" s="1">
+      <c r="N319" s="2">
         <v>46175</v>
       </c>
       <c r="Q319" t="b">
@@ -16720,7 +16746,7 @@
       <c r="E320" t="s">
         <v>1138</v>
       </c>
-      <c r="F320" s="1">
+      <c r="F320" s="2">
         <v>46125</v>
       </c>
       <c r="G320" t="s">
@@ -16730,7 +16756,7 @@
         <v>1353</v>
       </c>
       <c r="I320">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K320" t="s">
         <v>1361</v>
@@ -16758,7 +16784,7 @@
       <c r="E321" t="s">
         <v>1139</v>
       </c>
-      <c r="F321" s="1">
+      <c r="F321" s="2">
         <v>46125</v>
       </c>
       <c r="G321" t="s">
@@ -16768,7 +16794,7 @@
         <v>1353</v>
       </c>
       <c r="I321">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K321" t="s">
         <v>1357</v>
@@ -16796,7 +16822,7 @@
       <c r="E322" t="s">
         <v>1140</v>
       </c>
-      <c r="F322" s="1">
+      <c r="F322" s="2">
         <v>46125</v>
       </c>
       <c r="G322" t="s">
@@ -16806,7 +16832,7 @@
         <v>1353</v>
       </c>
       <c r="I322">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J322">
         <v>57</v>
@@ -16817,7 +16843,7 @@
       <c r="L322" t="s">
         <v>1435</v>
       </c>
-      <c r="N322" s="1">
+      <c r="N322" s="2">
         <v>46182</v>
       </c>
       <c r="Q322" t="b">
@@ -16840,7 +16866,7 @@
       <c r="E323" t="s">
         <v>1141</v>
       </c>
-      <c r="F323" s="1">
+      <c r="F323" s="2">
         <v>46125</v>
       </c>
       <c r="G323" t="s">
@@ -16875,7 +16901,7 @@
       <c r="E324" t="s">
         <v>1142</v>
       </c>
-      <c r="F324" s="1">
+      <c r="F324" s="2">
         <v>46125</v>
       </c>
       <c r="G324" t="s">
@@ -16910,7 +16936,7 @@
       <c r="E325" t="s">
         <v>1143</v>
       </c>
-      <c r="F325" s="1">
+      <c r="F325" s="2">
         <v>46125</v>
       </c>
       <c r="G325" t="s">
@@ -16920,7 +16946,7 @@
         <v>1353</v>
       </c>
       <c r="I325">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J325">
         <v>57</v>
@@ -16931,7 +16957,7 @@
       <c r="L325" t="s">
         <v>1435</v>
       </c>
-      <c r="N325" s="1">
+      <c r="N325" s="2">
         <v>46182</v>
       </c>
       <c r="Q325" t="b">
@@ -16954,7 +16980,7 @@
       <c r="E326" t="s">
         <v>1144</v>
       </c>
-      <c r="F326" s="1">
+      <c r="F326" s="2">
         <v>46125</v>
       </c>
       <c r="G326" t="s">
@@ -16969,7 +16995,7 @@
       <c r="L326" t="s">
         <v>1383</v>
       </c>
-      <c r="N326" s="1">
+      <c r="N326" s="2">
         <v>46232</v>
       </c>
       <c r="Q326" t="b">
@@ -16992,7 +17018,7 @@
       <c r="E327" t="s">
         <v>1140</v>
       </c>
-      <c r="F327" s="1">
+      <c r="F327" s="2">
         <v>46125</v>
       </c>
       <c r="G327" t="s">
@@ -17002,7 +17028,7 @@
         <v>1353</v>
       </c>
       <c r="I327">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J327">
         <v>57</v>
@@ -17013,7 +17039,7 @@
       <c r="L327" t="s">
         <v>1435</v>
       </c>
-      <c r="N327" s="1">
+      <c r="N327" s="2">
         <v>46182</v>
       </c>
       <c r="Q327" t="b">
@@ -17036,7 +17062,7 @@
       <c r="E328" t="s">
         <v>1145</v>
       </c>
-      <c r="F328" s="1">
+      <c r="F328" s="2">
         <v>46125</v>
       </c>
       <c r="G328" t="s">
@@ -17046,7 +17072,7 @@
         <v>1353</v>
       </c>
       <c r="I328">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J328">
         <v>57</v>
@@ -17057,7 +17083,7 @@
       <c r="L328" t="s">
         <v>1435</v>
       </c>
-      <c r="N328" s="1">
+      <c r="N328" s="2">
         <v>46182</v>
       </c>
       <c r="Q328" t="b">
@@ -17080,7 +17106,7 @@
       <c r="E329" t="s">
         <v>1146</v>
       </c>
-      <c r="F329" s="1">
+      <c r="F329" s="2">
         <v>46125</v>
       </c>
       <c r="G329" t="s">
@@ -17090,7 +17116,7 @@
         <v>1353</v>
       </c>
       <c r="I329">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J329">
         <v>57</v>
@@ -17101,7 +17127,7 @@
       <c r="L329" t="s">
         <v>1435</v>
       </c>
-      <c r="N329" s="1">
+      <c r="N329" s="2">
         <v>46182</v>
       </c>
       <c r="Q329" t="b">
@@ -17124,7 +17150,7 @@
       <c r="E330" t="s">
         <v>1147</v>
       </c>
-      <c r="F330" s="1">
+      <c r="F330" s="2">
         <v>46125</v>
       </c>
       <c r="G330" t="s">
@@ -17134,7 +17160,7 @@
         <v>1353</v>
       </c>
       <c r="I330">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J330">
         <v>57</v>
@@ -17145,7 +17171,7 @@
       <c r="L330" t="s">
         <v>1435</v>
       </c>
-      <c r="N330" s="1">
+      <c r="N330" s="2">
         <v>46182</v>
       </c>
       <c r="Q330" t="b">
@@ -17168,7 +17194,7 @@
       <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="F331" s="1">
+      <c r="F331" s="2">
         <v>46125</v>
       </c>
       <c r="G331" t="s">
@@ -17178,7 +17204,7 @@
         <v>1353</v>
       </c>
       <c r="I331">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K331" t="s">
         <v>1356</v>
@@ -17206,7 +17232,7 @@
       <c r="E332" t="s">
         <v>1148</v>
       </c>
-      <c r="F332" s="1">
+      <c r="F332" s="2">
         <v>46125</v>
       </c>
       <c r="G332" t="s">
@@ -17216,7 +17242,7 @@
         <v>1353</v>
       </c>
       <c r="I332">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K332" t="s">
         <v>1357</v>
@@ -17244,7 +17270,7 @@
       <c r="E333" t="s">
         <v>910</v>
       </c>
-      <c r="F333" s="1">
+      <c r="F333" s="2">
         <v>46125</v>
       </c>
       <c r="G333" t="s">
@@ -17254,7 +17280,7 @@
         <v>1353</v>
       </c>
       <c r="I333">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J333">
         <v>100</v>
@@ -17265,7 +17291,7 @@
       <c r="L333" t="s">
         <v>1395</v>
       </c>
-      <c r="N333" s="1">
+      <c r="N333" s="2">
         <v>46225</v>
       </c>
       <c r="Q333" t="b">
@@ -17288,7 +17314,7 @@
       <c r="E334" t="s">
         <v>1149</v>
       </c>
-      <c r="F334" s="1">
+      <c r="F334" s="2">
         <v>46125</v>
       </c>
       <c r="G334" t="s">
@@ -17298,7 +17324,7 @@
         <v>1353</v>
       </c>
       <c r="I334">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K334" t="s">
         <v>1357</v>
@@ -17326,7 +17352,7 @@
       <c r="E335" t="s">
         <v>1150</v>
       </c>
-      <c r="F335" s="1">
+      <c r="F335" s="2">
         <v>46127</v>
       </c>
       <c r="G335" t="s">
@@ -17341,7 +17367,7 @@
       <c r="L335" t="s">
         <v>1434</v>
       </c>
-      <c r="N335" s="1">
+      <c r="N335" s="2">
         <v>46175</v>
       </c>
       <c r="Q335" t="b">
@@ -17364,7 +17390,7 @@
       <c r="E336" t="s">
         <v>1151</v>
       </c>
-      <c r="F336" s="1">
+      <c r="F336" s="2">
         <v>46127</v>
       </c>
       <c r="G336" t="s">
@@ -17374,7 +17400,7 @@
         <v>1353</v>
       </c>
       <c r="I336">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J336">
         <v>28</v>
@@ -17385,7 +17411,7 @@
       <c r="L336" t="s">
         <v>1388</v>
       </c>
-      <c r="N336" s="1">
+      <c r="N336" s="2">
         <v>46155</v>
       </c>
       <c r="Q336" t="b">
@@ -17408,7 +17434,7 @@
       <c r="E337" t="s">
         <v>1152</v>
       </c>
-      <c r="F337" s="1">
+      <c r="F337" s="2">
         <v>46127</v>
       </c>
       <c r="G337" t="s">
@@ -17423,7 +17449,7 @@
       <c r="L337" t="s">
         <v>1434</v>
       </c>
-      <c r="N337" s="1">
+      <c r="N337" s="2">
         <v>46175</v>
       </c>
       <c r="Q337" t="b">
@@ -17446,7 +17472,7 @@
       <c r="E338" t="s">
         <v>1153</v>
       </c>
-      <c r="F338" s="1">
+      <c r="F338" s="2">
         <v>46127</v>
       </c>
       <c r="G338" t="s">
@@ -17456,7 +17482,7 @@
         <v>1353</v>
       </c>
       <c r="I338">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J338">
         <v>12</v>
@@ -17467,7 +17493,7 @@
       <c r="L338" t="s">
         <v>1388</v>
       </c>
-      <c r="N338" s="1">
+      <c r="N338" s="2">
         <v>46139</v>
       </c>
       <c r="Q338" t="b">
@@ -17490,7 +17516,7 @@
       <c r="E339" t="s">
         <v>1154</v>
       </c>
-      <c r="F339" s="1">
+      <c r="F339" s="2">
         <v>46129</v>
       </c>
       <c r="G339" t="s">
@@ -17519,7 +17545,7 @@
       <c r="E340" t="s">
         <v>1155</v>
       </c>
-      <c r="F340" s="1">
+      <c r="F340" s="2">
         <v>46142</v>
       </c>
       <c r="G340" t="s">
@@ -17529,7 +17555,7 @@
         <v>1353</v>
       </c>
       <c r="I340">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J340">
         <v>98</v>
@@ -17537,7 +17563,7 @@
       <c r="L340" t="s">
         <v>1383</v>
       </c>
-      <c r="N340" s="1">
+      <c r="N340" s="2">
         <v>46240</v>
       </c>
       <c r="Q340" t="b">
@@ -17560,7 +17586,7 @@
       <c r="E341" t="s">
         <v>1156</v>
       </c>
-      <c r="F341" s="1">
+      <c r="F341" s="2">
         <v>46142</v>
       </c>
       <c r="G341" t="s">
@@ -17570,7 +17596,7 @@
         <v>1353</v>
       </c>
       <c r="I341">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J341">
         <v>90</v>
@@ -17578,7 +17604,7 @@
       <c r="L341" t="s">
         <v>1383</v>
       </c>
-      <c r="N341" s="1">
+      <c r="N341" s="2">
         <v>46232</v>
       </c>
       <c r="Q341" t="b">
@@ -17601,7 +17627,7 @@
       <c r="E342" t="s">
         <v>1157</v>
       </c>
-      <c r="F342" s="1">
+      <c r="F342" s="2">
         <v>46142</v>
       </c>
       <c r="G342" t="s">
@@ -17611,7 +17637,7 @@
         <v>1353</v>
       </c>
       <c r="I342">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K342" t="s">
         <v>1356</v>
@@ -17639,7 +17665,7 @@
       <c r="E343" t="s">
         <v>1158</v>
       </c>
-      <c r="F343" s="1">
+      <c r="F343" s="2">
         <v>46142</v>
       </c>
       <c r="G343" t="s">
@@ -17654,7 +17680,7 @@
       <c r="L343" t="s">
         <v>1383</v>
       </c>
-      <c r="N343" s="1">
+      <c r="N343" s="2">
         <v>46232</v>
       </c>
       <c r="Q343" t="b">
@@ -17677,7 +17703,7 @@
       <c r="E344" t="s">
         <v>1159</v>
       </c>
-      <c r="F344" s="1">
+      <c r="F344" s="2">
         <v>46142</v>
       </c>
       <c r="G344" t="s">
@@ -17692,7 +17718,7 @@
       <c r="L344" t="s">
         <v>1383</v>
       </c>
-      <c r="N344" s="1">
+      <c r="N344" s="2">
         <v>46232</v>
       </c>
       <c r="Q344" t="b">
@@ -17715,7 +17741,7 @@
       <c r="E345" t="s">
         <v>1160</v>
       </c>
-      <c r="F345" s="1">
+      <c r="F345" s="2">
         <v>46142</v>
       </c>
       <c r="G345" t="s">
@@ -17725,7 +17751,7 @@
         <v>1353</v>
       </c>
       <c r="I345">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K345" t="s">
         <v>1356</v>
@@ -17753,7 +17779,7 @@
       <c r="E346" t="s">
         <v>1161</v>
       </c>
-      <c r="F346" s="1">
+      <c r="F346" s="2">
         <v>46142</v>
       </c>
       <c r="G346" t="s">
@@ -17768,7 +17794,7 @@
       <c r="L346" t="s">
         <v>1383</v>
       </c>
-      <c r="N346" s="1">
+      <c r="N346" s="2">
         <v>46232</v>
       </c>
       <c r="Q346" t="b">
@@ -17791,7 +17817,7 @@
       <c r="E347" t="s">
         <v>1162</v>
       </c>
-      <c r="F347" s="1">
+      <c r="F347" s="2">
         <v>46142</v>
       </c>
       <c r="G347" t="s">
@@ -17801,7 +17827,7 @@
         <v>1353</v>
       </c>
       <c r="I347">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J347">
         <v>18</v>
@@ -17812,7 +17838,7 @@
       <c r="L347" t="s">
         <v>1431</v>
       </c>
-      <c r="N347" s="1">
+      <c r="N347" s="2">
         <v>46160</v>
       </c>
       <c r="Q347" t="b">
@@ -17835,7 +17861,7 @@
       <c r="E348" t="s">
         <v>1163</v>
       </c>
-      <c r="F348" s="1">
+      <c r="F348" s="2">
         <v>46142</v>
       </c>
       <c r="G348" t="s">
@@ -17845,7 +17871,7 @@
         <v>1353</v>
       </c>
       <c r="I348">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J348">
         <v>14</v>
@@ -17856,7 +17882,7 @@
       <c r="L348" t="s">
         <v>1432</v>
       </c>
-      <c r="N348" s="1">
+      <c r="N348" s="2">
         <v>46156</v>
       </c>
       <c r="Q348" t="b">
@@ -17879,7 +17905,7 @@
       <c r="E349" t="s">
         <v>1164</v>
       </c>
-      <c r="F349" s="1">
+      <c r="F349" s="2">
         <v>46142</v>
       </c>
       <c r="G349" t="s">
@@ -17889,7 +17915,7 @@
         <v>1353</v>
       </c>
       <c r="I349">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K349" t="s">
         <v>1361</v>
@@ -17917,7 +17943,7 @@
       <c r="E350" t="s">
         <v>1165</v>
       </c>
-      <c r="F350" s="1">
+      <c r="F350" s="2">
         <v>46142</v>
       </c>
       <c r="G350" t="s">
@@ -17927,12 +17953,12 @@
         <v>1353</v>
       </c>
       <c r="I350">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J350">
         <v>46</v>
       </c>
-      <c r="N350" s="1">
+      <c r="N350" s="2">
         <v>46188</v>
       </c>
       <c r="Q350" t="b">
@@ -17955,7 +17981,7 @@
       <c r="E351" t="s">
         <v>1166</v>
       </c>
-      <c r="F351" s="1">
+      <c r="F351" s="2">
         <v>46142</v>
       </c>
       <c r="G351" t="s">
@@ -17965,7 +17991,7 @@
         <v>1353</v>
       </c>
       <c r="I351">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J351">
         <v>82</v>
@@ -17976,7 +18002,7 @@
       <c r="L351" t="s">
         <v>1436</v>
       </c>
-      <c r="N351" s="1">
+      <c r="N351" s="2">
         <v>46224</v>
       </c>
       <c r="Q351" t="b">
@@ -17999,7 +18025,7 @@
       <c r="E352" t="s">
         <v>1167</v>
       </c>
-      <c r="F352" s="1">
+      <c r="F352" s="2">
         <v>46142</v>
       </c>
       <c r="G352" t="s">
@@ -18009,7 +18035,7 @@
         <v>1353</v>
       </c>
       <c r="I352">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J352">
         <v>78</v>
@@ -18020,7 +18046,7 @@
       <c r="L352" t="s">
         <v>1437</v>
       </c>
-      <c r="N352" s="1">
+      <c r="N352" s="2">
         <v>46220</v>
       </c>
       <c r="Q352" t="b">
@@ -18043,7 +18069,7 @@
       <c r="E353" t="s">
         <v>1168</v>
       </c>
-      <c r="F353" s="1">
+      <c r="F353" s="2">
         <v>46142</v>
       </c>
       <c r="G353" t="s">
@@ -18053,7 +18079,7 @@
         <v>1353</v>
       </c>
       <c r="I353">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J353">
         <v>83</v>
@@ -18064,7 +18090,7 @@
       <c r="L353" t="s">
         <v>1395</v>
       </c>
-      <c r="N353" s="1">
+      <c r="N353" s="2">
         <v>46225</v>
       </c>
       <c r="Q353" t="b">
@@ -18087,7 +18113,7 @@
       <c r="E354" t="s">
         <v>1169</v>
       </c>
-      <c r="F354" s="1">
+      <c r="F354" s="2">
         <v>46142</v>
       </c>
       <c r="G354" t="s">
@@ -18097,7 +18123,7 @@
         <v>1353</v>
       </c>
       <c r="I354">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K354" t="s">
         <v>1360</v>
@@ -18125,7 +18151,7 @@
       <c r="E355" t="s">
         <v>1170</v>
       </c>
-      <c r="F355" s="1">
+      <c r="F355" s="2">
         <v>46142</v>
       </c>
       <c r="G355" t="s">
@@ -18135,7 +18161,7 @@
         <v>1353</v>
       </c>
       <c r="I355">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J355">
         <v>8</v>
@@ -18146,7 +18172,7 @@
       <c r="L355" t="s">
         <v>1438</v>
       </c>
-      <c r="N355" s="1">
+      <c r="N355" s="2">
         <v>46150</v>
       </c>
       <c r="Q355" t="b">
@@ -18169,7 +18195,7 @@
       <c r="E356" t="s">
         <v>1171</v>
       </c>
-      <c r="F356" s="1">
+      <c r="F356" s="2">
         <v>46142</v>
       </c>
       <c r="G356" t="s">
@@ -18184,7 +18210,7 @@
       <c r="L356" t="s">
         <v>1439</v>
       </c>
-      <c r="N356" s="1">
+      <c r="N356" s="2">
         <v>46176</v>
       </c>
       <c r="Q356" t="b">
@@ -18207,7 +18233,7 @@
       <c r="E357" t="s">
         <v>1172</v>
       </c>
-      <c r="F357" s="1">
+      <c r="F357" s="2">
         <v>46142</v>
       </c>
       <c r="G357" t="s">
@@ -18217,7 +18243,7 @@
         <v>1353</v>
       </c>
       <c r="I357">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J357">
         <v>85</v>
@@ -18225,7 +18251,7 @@
       <c r="K357" t="s">
         <v>1360</v>
       </c>
-      <c r="N357" s="1">
+      <c r="N357" s="2">
         <v>46227</v>
       </c>
       <c r="Q357" t="b">
@@ -18248,7 +18274,7 @@
       <c r="E358" t="s">
         <v>1173</v>
       </c>
-      <c r="F358" s="1">
+      <c r="F358" s="2">
         <v>46142</v>
       </c>
       <c r="G358" t="s">
@@ -18266,7 +18292,7 @@
       <c r="L358" t="s">
         <v>1440</v>
       </c>
-      <c r="N358" s="1">
+      <c r="N358" s="2">
         <v>46227</v>
       </c>
       <c r="P358" t="s">
@@ -18292,7 +18318,7 @@
       <c r="E359" t="s">
         <v>1174</v>
       </c>
-      <c r="F359" s="1">
+      <c r="F359" s="2">
         <v>46142</v>
       </c>
       <c r="G359" t="s">
@@ -18304,7 +18330,7 @@
       <c r="J359">
         <v>63</v>
       </c>
-      <c r="N359" s="1">
+      <c r="N359" s="2">
         <v>46205</v>
       </c>
       <c r="P359" t="s">
@@ -18330,7 +18356,7 @@
       <c r="E360" t="s">
         <v>949</v>
       </c>
-      <c r="F360" s="1">
+      <c r="F360" s="2">
         <v>46142</v>
       </c>
       <c r="G360" t="s">
@@ -18340,7 +18366,7 @@
         <v>1353</v>
       </c>
       <c r="I360">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J360">
         <v>83</v>
@@ -18351,7 +18377,7 @@
       <c r="L360" t="s">
         <v>1395</v>
       </c>
-      <c r="N360" s="1">
+      <c r="N360" s="2">
         <v>46225</v>
       </c>
       <c r="O360" t="s">
@@ -18377,7 +18403,7 @@
       <c r="E361" t="s">
         <v>961</v>
       </c>
-      <c r="F361" s="1">
+      <c r="F361" s="2">
         <v>46142</v>
       </c>
       <c r="G361" t="s">
@@ -18387,7 +18413,7 @@
         <v>1353</v>
       </c>
       <c r="I361">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J361">
         <v>83</v>
@@ -18398,7 +18424,7 @@
       <c r="L361" t="s">
         <v>1395</v>
       </c>
-      <c r="N361" s="1">
+      <c r="N361" s="2">
         <v>46225</v>
       </c>
       <c r="Q361" t="b">
@@ -18421,7 +18447,7 @@
       <c r="E362" t="s">
         <v>1175</v>
       </c>
-      <c r="F362" s="1">
+      <c r="F362" s="2">
         <v>46142</v>
       </c>
       <c r="G362" t="s">
@@ -18431,7 +18457,7 @@
         <v>1353</v>
       </c>
       <c r="I362">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K362" t="s">
         <v>1360</v>
@@ -18459,7 +18485,7 @@
       <c r="E363" t="s">
         <v>1176</v>
       </c>
-      <c r="F363" s="1">
+      <c r="F363" s="2">
         <v>46142</v>
       </c>
       <c r="G363" t="s">
@@ -18469,7 +18495,7 @@
         <v>1353</v>
       </c>
       <c r="I363">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K363" t="s">
         <v>1360</v>
@@ -18497,7 +18523,7 @@
       <c r="E364" t="s">
         <v>958</v>
       </c>
-      <c r="F364" s="1">
+      <c r="F364" s="2">
         <v>46142</v>
       </c>
       <c r="G364" t="s">
@@ -18507,7 +18533,7 @@
         <v>1353</v>
       </c>
       <c r="I364">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J364">
         <v>83</v>
@@ -18518,7 +18544,7 @@
       <c r="L364" t="s">
         <v>1395</v>
       </c>
-      <c r="N364" s="1">
+      <c r="N364" s="2">
         <v>46225</v>
       </c>
       <c r="Q364" t="b">
@@ -18541,7 +18567,7 @@
       <c r="E365" t="s">
         <v>1177</v>
       </c>
-      <c r="F365" s="1">
+      <c r="F365" s="2">
         <v>46142</v>
       </c>
       <c r="G365" t="s">
@@ -18551,7 +18577,7 @@
         <v>1353</v>
       </c>
       <c r="I365">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J365">
         <v>15</v>
@@ -18559,7 +18585,7 @@
       <c r="K365" t="s">
         <v>1359</v>
       </c>
-      <c r="N365" s="1">
+      <c r="N365" s="2">
         <v>46157</v>
       </c>
       <c r="Q365" t="b">
@@ -18582,7 +18608,7 @@
       <c r="E366" t="s">
         <v>1178</v>
       </c>
-      <c r="F366" s="1">
+      <c r="F366" s="2">
         <v>46148</v>
       </c>
       <c r="G366" t="s">
@@ -18592,7 +18618,7 @@
         <v>1353</v>
       </c>
       <c r="I366">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J366">
         <v>77</v>
@@ -18603,7 +18629,7 @@
       <c r="L366" t="s">
         <v>1388</v>
       </c>
-      <c r="N366" s="1">
+      <c r="N366" s="2">
         <v>46225</v>
       </c>
       <c r="Q366" t="b">
@@ -18626,7 +18652,7 @@
       <c r="E367" t="s">
         <v>1179</v>
       </c>
-      <c r="F367" s="1">
+      <c r="F367" s="2">
         <v>46148</v>
       </c>
       <c r="G367" t="s">
@@ -18636,7 +18662,7 @@
         <v>1353</v>
       </c>
       <c r="I367">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J367">
         <v>77</v>
@@ -18647,7 +18673,7 @@
       <c r="L367" t="s">
         <v>1388</v>
       </c>
-      <c r="N367" s="1">
+      <c r="N367" s="2">
         <v>46225</v>
       </c>
       <c r="Q367" t="b">
@@ -18670,7 +18696,7 @@
       <c r="E368" t="s">
         <v>1180</v>
       </c>
-      <c r="F368" s="1">
+      <c r="F368" s="2">
         <v>46148</v>
       </c>
       <c r="G368" t="s">
@@ -18680,7 +18706,7 @@
         <v>1353</v>
       </c>
       <c r="I368">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J368">
         <v>77</v>
@@ -18691,7 +18717,7 @@
       <c r="L368" t="s">
         <v>1395</v>
       </c>
-      <c r="N368" s="1">
+      <c r="N368" s="2">
         <v>46225</v>
       </c>
       <c r="Q368" t="b">
@@ -18714,7 +18740,7 @@
       <c r="E369" t="s">
         <v>1181</v>
       </c>
-      <c r="F369" s="1">
+      <c r="F369" s="2">
         <v>46148</v>
       </c>
       <c r="G369" t="s">
@@ -18724,7 +18750,7 @@
         <v>1353</v>
       </c>
       <c r="I369">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K369" t="s">
         <v>1360</v>
@@ -18752,7 +18778,7 @@
       <c r="E370" t="s">
         <v>1182</v>
       </c>
-      <c r="F370" s="1">
+      <c r="F370" s="2">
         <v>46148</v>
       </c>
       <c r="G370" t="s">
@@ -18762,7 +18788,7 @@
         <v>1353</v>
       </c>
       <c r="I370">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K370" t="s">
         <v>1360</v>
@@ -18790,7 +18816,7 @@
       <c r="E371" t="s">
         <v>1183</v>
       </c>
-      <c r="F371" s="1">
+      <c r="F371" s="2">
         <v>46148</v>
       </c>
       <c r="G371" t="s">
@@ -18800,7 +18826,7 @@
         <v>1353</v>
       </c>
       <c r="I371">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J371">
         <v>16</v>
@@ -18811,7 +18837,7 @@
       <c r="L371" t="s">
         <v>1441</v>
       </c>
-      <c r="N371" s="1">
+      <c r="N371" s="2">
         <v>46164</v>
       </c>
       <c r="Q371" t="b">
@@ -18834,7 +18860,7 @@
       <c r="E372" t="s">
         <v>1184</v>
       </c>
-      <c r="F372" s="1">
+      <c r="F372" s="2">
         <v>46148</v>
       </c>
       <c r="G372" t="s">
@@ -18852,7 +18878,7 @@
       <c r="L372" t="s">
         <v>1428</v>
       </c>
-      <c r="N372" s="1">
+      <c r="N372" s="2">
         <v>46113</v>
       </c>
       <c r="P372" t="s">
@@ -18878,7 +18904,7 @@
       <c r="E373" t="s">
         <v>1185</v>
       </c>
-      <c r="F373" s="1">
+      <c r="F373" s="2">
         <v>46149</v>
       </c>
       <c r="G373" t="s">
@@ -18888,7 +18914,7 @@
         <v>1353</v>
       </c>
       <c r="I373">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K373" t="s">
         <v>1356</v>
@@ -18916,7 +18942,7 @@
       <c r="E374" t="s">
         <v>1186</v>
       </c>
-      <c r="F374" s="1">
+      <c r="F374" s="2">
         <v>46149</v>
       </c>
       <c r="G374" t="s">
@@ -18926,7 +18952,7 @@
         <v>1353</v>
       </c>
       <c r="I374">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K374" t="s">
         <v>1356</v>
@@ -18954,7 +18980,7 @@
       <c r="E375" t="s">
         <v>1187</v>
       </c>
-      <c r="F375" s="1">
+      <c r="F375" s="2">
         <v>46154</v>
       </c>
       <c r="G375" t="s">
@@ -18964,7 +18990,7 @@
         <v>1353</v>
       </c>
       <c r="I375">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J375">
         <v>94</v>
@@ -18972,7 +18998,7 @@
       <c r="K375" t="s">
         <v>1360</v>
       </c>
-      <c r="N375" s="1">
+      <c r="N375" s="2">
         <v>46248</v>
       </c>
       <c r="Q375" t="b">
@@ -18995,7 +19021,7 @@
       <c r="E376" t="s">
         <v>1188</v>
       </c>
-      <c r="F376" s="1">
+      <c r="F376" s="2">
         <v>46154</v>
       </c>
       <c r="G376" t="s">
@@ -19005,7 +19031,7 @@
         <v>1353</v>
       </c>
       <c r="I376">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K376" t="s">
         <v>1360</v>
@@ -19033,7 +19059,7 @@
       <c r="E377" t="s">
         <v>1189</v>
       </c>
-      <c r="F377" s="1">
+      <c r="F377" s="2">
         <v>46154</v>
       </c>
       <c r="G377" t="s">
@@ -19045,7 +19071,7 @@
       <c r="K377" t="s">
         <v>1360</v>
       </c>
-      <c r="N377" s="1">
+      <c r="N377" s="2">
         <v>46176</v>
       </c>
       <c r="O377" t="s">
@@ -19074,7 +19100,7 @@
       <c r="E378" t="s">
         <v>1190</v>
       </c>
-      <c r="F378" s="1">
+      <c r="F378" s="2">
         <v>46154</v>
       </c>
       <c r="G378" t="s">
@@ -19084,7 +19110,7 @@
         <v>1353</v>
       </c>
       <c r="I378">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K378" t="s">
         <v>1360</v>
@@ -19112,7 +19138,7 @@
       <c r="E379" t="s">
         <v>1191</v>
       </c>
-      <c r="F379" s="1">
+      <c r="F379" s="2">
         <v>46154</v>
       </c>
       <c r="G379" t="s">
@@ -19122,7 +19148,7 @@
         <v>1353</v>
       </c>
       <c r="I379">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J379">
         <v>20</v>
@@ -19133,7 +19159,7 @@
       <c r="L379" t="s">
         <v>1442</v>
       </c>
-      <c r="N379" s="1">
+      <c r="N379" s="2">
         <v>46174</v>
       </c>
       <c r="Q379" t="b">
@@ -19156,7 +19182,7 @@
       <c r="E380" t="s">
         <v>1192</v>
       </c>
-      <c r="F380" s="1">
+      <c r="F380" s="2">
         <v>46154</v>
       </c>
       <c r="G380" t="s">
@@ -19166,7 +19192,7 @@
         <v>1353</v>
       </c>
       <c r="I380">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J380">
         <v>94</v>
@@ -19177,7 +19203,7 @@
       <c r="L380" t="s">
         <v>1443</v>
       </c>
-      <c r="N380" s="1">
+      <c r="N380" s="2">
         <v>46248</v>
       </c>
       <c r="Q380" t="b">
@@ -19200,7 +19226,7 @@
       <c r="E381" t="s">
         <v>1193</v>
       </c>
-      <c r="F381" s="1">
+      <c r="F381" s="2">
         <v>46154</v>
       </c>
       <c r="G381" t="s">
@@ -19210,7 +19236,7 @@
         <v>1353</v>
       </c>
       <c r="I381">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K381" t="s">
         <v>1360</v>
@@ -19238,7 +19264,7 @@
       <c r="E382" t="s">
         <v>1194</v>
       </c>
-      <c r="F382" s="1">
+      <c r="F382" s="2">
         <v>46154</v>
       </c>
       <c r="G382" t="s">
@@ -19248,7 +19274,7 @@
         <v>1353</v>
       </c>
       <c r="I382">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K382" t="s">
         <v>1360</v>
@@ -19276,7 +19302,7 @@
       <c r="E383" t="s">
         <v>1195</v>
       </c>
-      <c r="F383" s="1">
+      <c r="F383" s="2">
         <v>46154</v>
       </c>
       <c r="G383" t="s">
@@ -19286,7 +19312,7 @@
         <v>1353</v>
       </c>
       <c r="I383">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J383">
         <v>71</v>
@@ -19297,7 +19323,7 @@
       <c r="L383" t="s">
         <v>1444</v>
       </c>
-      <c r="N383" s="1">
+      <c r="N383" s="2">
         <v>46225</v>
       </c>
       <c r="Q383" t="b">
@@ -19320,7 +19346,7 @@
       <c r="E384" t="s">
         <v>1196</v>
       </c>
-      <c r="F384" s="1">
+      <c r="F384" s="2">
         <v>46164</v>
       </c>
       <c r="G384" t="s">
@@ -19330,7 +19356,7 @@
         <v>1353</v>
       </c>
       <c r="I384">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K384" t="s">
         <v>1357</v>
@@ -19358,7 +19384,7 @@
       <c r="E385" t="s">
         <v>1197</v>
       </c>
-      <c r="F385" s="1">
+      <c r="F385" s="2">
         <v>46164</v>
       </c>
       <c r="G385" t="s">
@@ -19368,7 +19394,7 @@
         <v>1353</v>
       </c>
       <c r="I385">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J385">
         <v>102</v>
@@ -19379,7 +19405,7 @@
       <c r="L385" t="s">
         <v>1445</v>
       </c>
-      <c r="N385" s="1">
+      <c r="N385" s="2">
         <v>46266</v>
       </c>
       <c r="P385" t="s">
@@ -19405,7 +19431,7 @@
       <c r="E386" t="s">
         <v>1198</v>
       </c>
-      <c r="F386" s="1">
+      <c r="F386" s="2">
         <v>46171</v>
       </c>
       <c r="G386" t="s">
@@ -19415,7 +19441,7 @@
         <v>1353</v>
       </c>
       <c r="I386">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K386" t="s">
         <v>1360</v>
@@ -19443,7 +19469,7 @@
       <c r="E387" t="s">
         <v>1199</v>
       </c>
-      <c r="F387" s="1">
+      <c r="F387" s="2">
         <v>46171</v>
       </c>
       <c r="G387" t="s">
@@ -19453,7 +19479,7 @@
         <v>1353</v>
       </c>
       <c r="I387">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K387" t="s">
         <v>1360</v>
@@ -19481,7 +19507,7 @@
       <c r="E388" t="s">
         <v>851</v>
       </c>
-      <c r="F388" s="1">
+      <c r="F388" s="2">
         <v>46171</v>
       </c>
       <c r="G388" t="s">
@@ -19491,7 +19517,7 @@
         <v>1353</v>
       </c>
       <c r="I388">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J388">
         <v>-85</v>
@@ -19502,7 +19528,7 @@
       <c r="L388" t="s">
         <v>1446</v>
       </c>
-      <c r="N388" s="1">
+      <c r="N388" s="2">
         <v>46086</v>
       </c>
       <c r="Q388" t="b">
@@ -19525,7 +19551,7 @@
       <c r="E389" t="s">
         <v>1200</v>
       </c>
-      <c r="F389" s="1">
+      <c r="F389" s="2">
         <v>46171</v>
       </c>
       <c r="G389" t="s">
@@ -19535,7 +19561,7 @@
         <v>1353</v>
       </c>
       <c r="I389">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K389" t="s">
         <v>1361</v>
@@ -19563,7 +19589,7 @@
       <c r="E390" t="s">
         <v>1201</v>
       </c>
-      <c r="F390" s="1">
+      <c r="F390" s="2">
         <v>46171</v>
       </c>
       <c r="G390" t="s">
@@ -19581,7 +19607,7 @@
       <c r="L390" t="s">
         <v>1447</v>
       </c>
-      <c r="N390" s="1">
+      <c r="N390" s="2">
         <v>46191</v>
       </c>
       <c r="P390" t="s">
@@ -19607,7 +19633,7 @@
       <c r="E391" t="s">
         <v>1202</v>
       </c>
-      <c r="F391" s="1">
+      <c r="F391" s="2">
         <v>46171</v>
       </c>
       <c r="G391" t="s">
@@ -19645,7 +19671,7 @@
       <c r="E392" t="s">
         <v>1203</v>
       </c>
-      <c r="F392" s="1">
+      <c r="F392" s="2">
         <v>46171</v>
       </c>
       <c r="G392" t="s">
@@ -19660,7 +19686,7 @@
       <c r="L392" t="s">
         <v>1439</v>
       </c>
-      <c r="N392" s="1">
+      <c r="N392" s="2">
         <v>46176</v>
       </c>
       <c r="Q392" t="b">
@@ -19683,7 +19709,7 @@
       <c r="E393" t="s">
         <v>1204</v>
       </c>
-      <c r="F393" s="1">
+      <c r="F393" s="2">
         <v>46171</v>
       </c>
       <c r="G393" t="s">
@@ -19693,7 +19719,7 @@
         <v>1353</v>
       </c>
       <c r="I393">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J393">
         <v>20</v>
@@ -19704,7 +19730,7 @@
       <c r="L393" t="s">
         <v>1388</v>
       </c>
-      <c r="N393" s="1">
+      <c r="N393" s="2">
         <v>46191</v>
       </c>
       <c r="Q393" t="b">
@@ -19727,7 +19753,7 @@
       <c r="E394" t="s">
         <v>1205</v>
       </c>
-      <c r="F394" s="1">
+      <c r="F394" s="2">
         <v>46171</v>
       </c>
       <c r="G394" t="s">
@@ -19745,7 +19771,7 @@
       <c r="L394" t="s">
         <v>1448</v>
       </c>
-      <c r="N394" s="1">
+      <c r="N394" s="2">
         <v>46241</v>
       </c>
       <c r="P394" t="s">
@@ -19771,7 +19797,7 @@
       <c r="E395" t="s">
         <v>1206</v>
       </c>
-      <c r="F395" s="1">
+      <c r="F395" s="2">
         <v>46171</v>
       </c>
       <c r="G395" t="s">
@@ -19789,7 +19815,7 @@
       <c r="L395" t="s">
         <v>1449</v>
       </c>
-      <c r="N395" s="1">
+      <c r="N395" s="2">
         <v>46191</v>
       </c>
       <c r="P395" t="s">
@@ -19815,7 +19841,7 @@
       <c r="E396" t="s">
         <v>1207</v>
       </c>
-      <c r="F396" s="1">
+      <c r="F396" s="2">
         <v>46171</v>
       </c>
       <c r="G396" t="s">
@@ -19827,7 +19853,7 @@
       <c r="J396">
         <v>20</v>
       </c>
-      <c r="N396" s="1">
+      <c r="N396" s="2">
         <v>46191</v>
       </c>
       <c r="P396" t="s">
@@ -19853,7 +19879,7 @@
       <c r="E397" t="s">
         <v>1208</v>
       </c>
-      <c r="F397" s="1">
+      <c r="F397" s="2">
         <v>46171</v>
       </c>
       <c r="G397" t="s">
@@ -19871,7 +19897,7 @@
       <c r="L397" t="s">
         <v>1448</v>
       </c>
-      <c r="N397" s="1">
+      <c r="N397" s="2">
         <v>46241</v>
       </c>
       <c r="P397" t="s">
@@ -19897,7 +19923,7 @@
       <c r="E398" t="s">
         <v>1209</v>
       </c>
-      <c r="F398" s="1">
+      <c r="F398" s="2">
         <v>46171</v>
       </c>
       <c r="G398" t="s">
@@ -19915,7 +19941,7 @@
       <c r="L398" t="s">
         <v>1449</v>
       </c>
-      <c r="N398" s="1">
+      <c r="N398" s="2">
         <v>46191</v>
       </c>
       <c r="P398" t="s">
@@ -19941,7 +19967,7 @@
       <c r="E399" t="s">
         <v>987</v>
       </c>
-      <c r="F399" s="1">
+      <c r="F399" s="2">
         <v>46163</v>
       </c>
       <c r="G399" t="s">
@@ -19956,7 +19982,7 @@
       <c r="L399" t="s">
         <v>1450</v>
       </c>
-      <c r="N399" s="1">
+      <c r="N399" s="2">
         <v>46171</v>
       </c>
       <c r="Q399" t="b">
@@ -19979,7 +20005,7 @@
       <c r="E400" t="s">
         <v>1210</v>
       </c>
-      <c r="F400" s="1">
+      <c r="F400" s="2">
         <v>46171</v>
       </c>
       <c r="G400" t="s">
@@ -19989,7 +20015,7 @@
         <v>1353</v>
       </c>
       <c r="I400">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K400" t="s">
         <v>1360</v>
@@ -20017,7 +20043,7 @@
       <c r="E401" t="s">
         <v>1211</v>
       </c>
-      <c r="F401" s="1">
+      <c r="F401" s="2">
         <v>46171</v>
       </c>
       <c r="G401" t="s">
@@ -20029,7 +20055,7 @@
       <c r="J401">
         <v>40</v>
       </c>
-      <c r="N401" s="1">
+      <c r="N401" s="2">
         <v>46211</v>
       </c>
       <c r="P401" t="s">
@@ -20055,7 +20081,7 @@
       <c r="E402" t="s">
         <v>1212</v>
       </c>
-      <c r="F402" s="1">
+      <c r="F402" s="2">
         <v>46171</v>
       </c>
       <c r="G402" t="s">
@@ -20065,7 +20091,7 @@
         <v>1353</v>
       </c>
       <c r="I402">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K402" t="s">
         <v>1360</v>
@@ -20093,7 +20119,7 @@
       <c r="E403" t="s">
         <v>1213</v>
       </c>
-      <c r="F403" s="1">
+      <c r="F403" s="2">
         <v>46171</v>
       </c>
       <c r="G403" t="s">
@@ -20103,7 +20129,7 @@
         <v>1353</v>
       </c>
       <c r="I403">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J403">
         <v>83</v>
@@ -20114,7 +20140,7 @@
       <c r="L403" t="s">
         <v>1451</v>
       </c>
-      <c r="N403" s="1">
+      <c r="N403" s="2">
         <v>46254</v>
       </c>
       <c r="Q403" t="b">
@@ -20137,7 +20163,7 @@
       <c r="E404" t="s">
         <v>1214</v>
       </c>
-      <c r="F404" s="1">
+      <c r="F404" s="2">
         <v>46171</v>
       </c>
       <c r="G404" t="s">
@@ -20147,7 +20173,7 @@
         <v>1353</v>
       </c>
       <c r="I404">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K404" t="s">
         <v>1360</v>
@@ -20175,7 +20201,7 @@
       <c r="E405" t="s">
         <v>1215</v>
       </c>
-      <c r="F405" s="1">
+      <c r="F405" s="2">
         <v>46183</v>
       </c>
       <c r="G405" t="s">
@@ -20207,7 +20233,7 @@
       <c r="E406" t="s">
         <v>1216</v>
       </c>
-      <c r="F406" s="1">
+      <c r="F406" s="2">
         <v>46183</v>
       </c>
       <c r="G406" t="s">
@@ -20217,7 +20243,7 @@
         <v>1353</v>
       </c>
       <c r="I406">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q406" t="b">
         <v>1</v>
@@ -20239,7 +20265,7 @@
       <c r="E407" t="s">
         <v>1217</v>
       </c>
-      <c r="F407" s="1">
+      <c r="F407" s="2">
         <v>46183</v>
       </c>
       <c r="G407" t="s">
@@ -20249,7 +20275,7 @@
         <v>1353</v>
       </c>
       <c r="I407">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q407" t="b">
         <v>1</v>
@@ -20271,7 +20297,7 @@
       <c r="E408" t="s">
         <v>1218</v>
       </c>
-      <c r="F408" s="1">
+      <c r="F408" s="2">
         <v>46183</v>
       </c>
       <c r="G408" t="s">
@@ -20281,7 +20307,7 @@
         <v>1353</v>
       </c>
       <c r="I408">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q408" t="b">
         <v>1</v>
@@ -20303,7 +20329,7 @@
       <c r="E409" t="s">
         <v>1219</v>
       </c>
-      <c r="F409" s="1">
+      <c r="F409" s="2">
         <v>46183</v>
       </c>
       <c r="G409" t="s">
@@ -20313,7 +20339,7 @@
         <v>1353</v>
       </c>
       <c r="I409">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q409" t="b">
         <v>1</v>
@@ -20335,7 +20361,7 @@
       <c r="E410" t="s">
         <v>1220</v>
       </c>
-      <c r="F410" s="1">
+      <c r="F410" s="2">
         <v>46183</v>
       </c>
       <c r="G410" t="s">
@@ -20345,7 +20371,7 @@
         <v>1353</v>
       </c>
       <c r="I410">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q410" t="b">
         <v>1</v>
@@ -20367,7 +20393,7 @@
       <c r="E411" t="s">
         <v>1221</v>
       </c>
-      <c r="F411" s="1">
+      <c r="F411" s="2">
         <v>46188</v>
       </c>
       <c r="G411" t="s">
@@ -20377,7 +20403,7 @@
         <v>1353</v>
       </c>
       <c r="I411">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q411" t="b">
         <v>1</v>
@@ -20399,7 +20425,7 @@
       <c r="E412" t="s">
         <v>1222</v>
       </c>
-      <c r="F412" s="1">
+      <c r="F412" s="2">
         <v>46188</v>
       </c>
       <c r="G412" t="s">
@@ -20409,7 +20435,7 @@
         <v>1353</v>
       </c>
       <c r="I412">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q412" t="b">
         <v>1</v>
@@ -20431,7 +20457,7 @@
       <c r="E413" t="s">
         <v>1223</v>
       </c>
-      <c r="F413" s="1">
+      <c r="F413" s="2">
         <v>46188</v>
       </c>
       <c r="G413" t="s">
@@ -20441,7 +20467,7 @@
         <v>1353</v>
       </c>
       <c r="I413">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q413" t="b">
         <v>1</v>
@@ -20463,7 +20489,7 @@
       <c r="E414" t="s">
         <v>1224</v>
       </c>
-      <c r="F414" s="1">
+      <c r="F414" s="2">
         <v>46188</v>
       </c>
       <c r="G414" t="s">
@@ -20492,7 +20518,7 @@
       <c r="E415" t="s">
         <v>1060</v>
       </c>
-      <c r="F415" s="1">
+      <c r="F415" s="2">
         <v>46188</v>
       </c>
       <c r="G415" t="s">
@@ -20521,7 +20547,7 @@
       <c r="E416" t="s">
         <v>1225</v>
       </c>
-      <c r="F416" s="1">
+      <c r="F416" s="2">
         <v>46188</v>
       </c>
       <c r="G416" t="s">
@@ -20531,7 +20557,7 @@
         <v>1353</v>
       </c>
       <c r="I416">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q416" t="b">
         <v>1</v>
@@ -20553,7 +20579,7 @@
       <c r="E417" t="s">
         <v>1226</v>
       </c>
-      <c r="F417" s="1">
+      <c r="F417" s="2">
         <v>46188</v>
       </c>
       <c r="G417" t="s">
@@ -20582,7 +20608,7 @@
       <c r="E418" t="s">
         <v>1227</v>
       </c>
-      <c r="F418" s="1">
+      <c r="F418" s="2">
         <v>46188</v>
       </c>
       <c r="G418" t="s">
@@ -20611,7 +20637,7 @@
       <c r="E419" t="s">
         <v>1228</v>
       </c>
-      <c r="F419" s="1">
+      <c r="F419" s="2">
         <v>46188</v>
       </c>
       <c r="G419" t="s">
@@ -20621,7 +20647,7 @@
         <v>1353</v>
       </c>
       <c r="I419">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q419" t="b">
         <v>1</v>
@@ -20643,7 +20669,7 @@
       <c r="E420" t="s">
         <v>1229</v>
       </c>
-      <c r="F420" s="1">
+      <c r="F420" s="2">
         <v>46188</v>
       </c>
       <c r="G420" t="s">
@@ -20653,7 +20679,7 @@
         <v>1353</v>
       </c>
       <c r="I420">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q420" t="b">
         <v>1</v>
@@ -20675,7 +20701,7 @@
       <c r="E421" t="s">
         <v>1230</v>
       </c>
-      <c r="F421" s="1">
+      <c r="F421" s="2">
         <v>46188</v>
       </c>
       <c r="G421" t="s">
@@ -20685,7 +20711,7 @@
         <v>1353</v>
       </c>
       <c r="I421">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q421" t="b">
         <v>1</v>
@@ -20707,7 +20733,7 @@
       <c r="E422" t="s">
         <v>1231</v>
       </c>
-      <c r="F422" s="1">
+      <c r="F422" s="2">
         <v>46188</v>
       </c>
       <c r="G422" t="s">
@@ -20717,7 +20743,7 @@
         <v>1353</v>
       </c>
       <c r="I422">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q422" t="b">
         <v>1</v>
@@ -20739,7 +20765,7 @@
       <c r="E423" t="s">
         <v>1232</v>
       </c>
-      <c r="F423" s="1">
+      <c r="F423" s="2">
         <v>46188</v>
       </c>
       <c r="G423" t="s">
@@ -20749,7 +20775,7 @@
         <v>1353</v>
       </c>
       <c r="I423">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q423" t="b">
         <v>1</v>
@@ -20771,7 +20797,7 @@
       <c r="E424" t="s">
         <v>1233</v>
       </c>
-      <c r="F424" s="1">
+      <c r="F424" s="2">
         <v>46188</v>
       </c>
       <c r="G424" t="s">
@@ -20781,7 +20807,7 @@
         <v>1353</v>
       </c>
       <c r="I424">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q424" t="b">
         <v>1</v>
@@ -20803,7 +20829,7 @@
       <c r="E425" t="s">
         <v>1234</v>
       </c>
-      <c r="F425" s="1">
+      <c r="F425" s="2">
         <v>46188</v>
       </c>
       <c r="G425" t="s">
@@ -20813,7 +20839,7 @@
         <v>1353</v>
       </c>
       <c r="I425">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q425" t="b">
         <v>1</v>
@@ -20835,7 +20861,7 @@
       <c r="E426" t="s">
         <v>1235</v>
       </c>
-      <c r="F426" s="1">
+      <c r="F426" s="2">
         <v>46188</v>
       </c>
       <c r="G426" t="s">
@@ -20845,7 +20871,7 @@
         <v>1353</v>
       </c>
       <c r="I426">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q426" t="b">
         <v>1</v>
@@ -20867,7 +20893,7 @@
       <c r="E427" t="s">
         <v>1236</v>
       </c>
-      <c r="F427" s="1">
+      <c r="F427" s="2">
         <v>46188</v>
       </c>
       <c r="G427" t="s">
@@ -20877,7 +20903,7 @@
         <v>1353</v>
       </c>
       <c r="I427">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q427" t="b">
         <v>1</v>
@@ -20899,7 +20925,7 @@
       <c r="E428" t="s">
         <v>1237</v>
       </c>
-      <c r="F428" s="1">
+      <c r="F428" s="2">
         <v>46188</v>
       </c>
       <c r="G428" t="s">
@@ -20928,7 +20954,7 @@
       <c r="E429" t="s">
         <v>1238</v>
       </c>
-      <c r="F429" s="1">
+      <c r="F429" s="2">
         <v>46188</v>
       </c>
       <c r="G429" t="s">
@@ -20957,7 +20983,7 @@
       <c r="E430" t="s">
         <v>1239</v>
       </c>
-      <c r="F430" s="1">
+      <c r="F430" s="2">
         <v>46188</v>
       </c>
       <c r="G430" t="s">
@@ -20967,7 +20993,7 @@
         <v>1353</v>
       </c>
       <c r="I430">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q430" t="b">
         <v>1</v>
@@ -20989,7 +21015,7 @@
       <c r="E431" t="s">
         <v>1240</v>
       </c>
-      <c r="F431" s="1">
+      <c r="F431" s="2">
         <v>46188</v>
       </c>
       <c r="G431" t="s">
@@ -20999,7 +21025,7 @@
         <v>1353</v>
       </c>
       <c r="I431">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q431" t="b">
         <v>1</v>
@@ -21021,7 +21047,7 @@
       <c r="E432" t="s">
         <v>1241</v>
       </c>
-      <c r="F432" s="1">
+      <c r="F432" s="2">
         <v>46188</v>
       </c>
       <c r="G432" t="s">
@@ -21031,7 +21057,7 @@
         <v>1353</v>
       </c>
       <c r="I432">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q432" t="b">
         <v>1</v>
@@ -21053,7 +21079,7 @@
       <c r="E433" t="s">
         <v>1242</v>
       </c>
-      <c r="F433" s="1">
+      <c r="F433" s="2">
         <v>46188</v>
       </c>
       <c r="G433" t="s">
@@ -21063,7 +21089,7 @@
         <v>1353</v>
       </c>
       <c r="I433">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q433" t="b">
         <v>1</v>
@@ -21085,7 +21111,7 @@
       <c r="E434" t="s">
         <v>1243</v>
       </c>
-      <c r="F434" s="1">
+      <c r="F434" s="2">
         <v>46188</v>
       </c>
       <c r="G434" t="s">
@@ -21095,7 +21121,7 @@
         <v>1353</v>
       </c>
       <c r="I434">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q434" t="b">
         <v>1</v>
@@ -21117,7 +21143,7 @@
       <c r="E435" t="s">
         <v>856</v>
       </c>
-      <c r="F435" s="1">
+      <c r="F435" s="2">
         <v>46188</v>
       </c>
       <c r="G435" t="s">
@@ -21127,7 +21153,7 @@
         <v>1353</v>
       </c>
       <c r="I435">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q435" t="b">
         <v>1</v>
@@ -21149,7 +21175,7 @@
       <c r="E436" t="s">
         <v>1244</v>
       </c>
-      <c r="F436" s="1">
+      <c r="F436" s="2">
         <v>46188</v>
       </c>
       <c r="G436" t="s">
@@ -21159,7 +21185,7 @@
         <v>1353</v>
       </c>
       <c r="I436">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q436" t="b">
         <v>1</v>
@@ -21181,7 +21207,7 @@
       <c r="E437" t="s">
         <v>1245</v>
       </c>
-      <c r="F437" s="1">
+      <c r="F437" s="2">
         <v>46188</v>
       </c>
       <c r="G437" t="s">
@@ -21191,7 +21217,7 @@
         <v>1355</v>
       </c>
       <c r="I437">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q437" t="b">
         <v>1</v>
@@ -21213,7 +21239,7 @@
       <c r="E438" t="s">
         <v>1246</v>
       </c>
-      <c r="F438" s="1">
+      <c r="F438" s="2">
         <v>46188</v>
       </c>
       <c r="G438" t="s">
@@ -21223,7 +21249,7 @@
         <v>1355</v>
       </c>
       <c r="I438">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q438" t="b">
         <v>1</v>
@@ -21245,7 +21271,7 @@
       <c r="E439" t="s">
         <v>1247</v>
       </c>
-      <c r="F439" s="1">
+      <c r="F439" s="2">
         <v>46196</v>
       </c>
       <c r="G439" t="s">
@@ -21255,7 +21281,7 @@
         <v>1353</v>
       </c>
       <c r="I439">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q439" t="b">
         <v>1</v>
@@ -21277,7 +21303,7 @@
       <c r="E440" t="s">
         <v>1248</v>
       </c>
-      <c r="F440" s="1">
+      <c r="F440" s="2">
         <v>46196</v>
       </c>
       <c r="G440" t="s">
@@ -21287,7 +21313,7 @@
         <v>1353</v>
       </c>
       <c r="I440">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q440" t="b">
         <v>1</v>
@@ -21309,7 +21335,7 @@
       <c r="E441" t="s">
         <v>1249</v>
       </c>
-      <c r="F441" s="1">
+      <c r="F441" s="2">
         <v>46203</v>
       </c>
       <c r="G441" t="s">
@@ -21319,7 +21345,7 @@
         <v>1353</v>
       </c>
       <c r="I441">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q441" t="b">
         <v>1</v>
@@ -21341,7 +21367,7 @@
       <c r="E442" t="s">
         <v>1250</v>
       </c>
-      <c r="F442" s="1">
+      <c r="F442" s="2">
         <v>46203</v>
       </c>
       <c r="G442" t="s">
@@ -21370,7 +21396,7 @@
       <c r="E443" t="s">
         <v>1251</v>
       </c>
-      <c r="F443" s="1">
+      <c r="F443" s="2">
         <v>46205</v>
       </c>
       <c r="G443" t="s">
@@ -21380,7 +21406,7 @@
         <v>1353</v>
       </c>
       <c r="I443">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q443" t="b">
         <v>1</v>
@@ -21402,7 +21428,7 @@
       <c r="E444" t="s">
         <v>1252</v>
       </c>
-      <c r="F444" s="1">
+      <c r="F444" s="2">
         <v>46205</v>
       </c>
       <c r="G444" t="s">
@@ -21431,7 +21457,7 @@
       <c r="E445" t="s">
         <v>1253</v>
       </c>
-      <c r="F445" s="1">
+      <c r="F445" s="2">
         <v>46205</v>
       </c>
       <c r="G445" t="s">
@@ -21460,7 +21486,7 @@
       <c r="E446" t="s">
         <v>1254</v>
       </c>
-      <c r="F446" s="1">
+      <c r="F446" s="2">
         <v>46211</v>
       </c>
       <c r="G446" t="s">
@@ -21470,7 +21496,7 @@
         <v>1353</v>
       </c>
       <c r="I446">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q446" t="b">
         <v>1</v>
@@ -21492,7 +21518,7 @@
       <c r="E447" t="s">
         <v>1255</v>
       </c>
-      <c r="F447" s="1">
+      <c r="F447" s="2">
         <v>46211</v>
       </c>
       <c r="G447" t="s">
@@ -21502,7 +21528,7 @@
         <v>1353</v>
       </c>
       <c r="I447">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q447" t="b">
         <v>1</v>
@@ -21524,7 +21550,7 @@
       <c r="E448" t="s">
         <v>1256</v>
       </c>
-      <c r="F448" s="1">
+      <c r="F448" s="2">
         <v>46226</v>
       </c>
       <c r="G448" t="s">
@@ -21534,7 +21560,7 @@
         <v>1353</v>
       </c>
       <c r="I448">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q448" t="b">
         <v>1</v>
@@ -21556,7 +21582,7 @@
       <c r="E449" t="s">
         <v>1257</v>
       </c>
-      <c r="F449" s="1">
+      <c r="F449" s="2">
         <v>46226</v>
       </c>
       <c r="G449" t="s">
@@ -21566,7 +21592,7 @@
         <v>1353</v>
       </c>
       <c r="I449">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q449" t="b">
         <v>1</v>
@@ -21588,7 +21614,7 @@
       <c r="E450" t="s">
         <v>1258</v>
       </c>
-      <c r="F450" s="1">
+      <c r="F450" s="2">
         <v>46226</v>
       </c>
       <c r="G450" t="s">
@@ -21598,7 +21624,7 @@
         <v>1353</v>
       </c>
       <c r="I450">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q450" t="b">
         <v>1</v>
@@ -21620,7 +21646,7 @@
       <c r="E451" t="s">
         <v>1035</v>
       </c>
-      <c r="F451" s="1">
+      <c r="F451" s="2">
         <v>46230</v>
       </c>
       <c r="G451" t="s">
@@ -21630,7 +21656,7 @@
         <v>1353</v>
       </c>
       <c r="I451">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q451" t="b">
         <v>1</v>
@@ -21652,7 +21678,7 @@
       <c r="E452" t="s">
         <v>1259</v>
       </c>
-      <c r="F452" s="1">
+      <c r="F452" s="2">
         <v>46230</v>
       </c>
       <c r="G452" t="s">
@@ -21662,7 +21688,7 @@
         <v>1353</v>
       </c>
       <c r="I452">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q452" t="b">
         <v>1</v>
@@ -21684,7 +21710,7 @@
       <c r="E453" t="s">
         <v>1260</v>
       </c>
-      <c r="F453" s="1">
+      <c r="F453" s="2">
         <v>46230</v>
       </c>
       <c r="G453" t="s">
@@ -21694,7 +21720,7 @@
         <v>1353</v>
       </c>
       <c r="I453">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q453" t="b">
         <v>1</v>
@@ -21716,7 +21742,7 @@
       <c r="E454" t="s">
         <v>1261</v>
       </c>
-      <c r="F454" s="1">
+      <c r="F454" s="2">
         <v>46230</v>
       </c>
       <c r="G454" t="s">
@@ -21726,7 +21752,7 @@
         <v>1353</v>
       </c>
       <c r="I454">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q454" t="b">
         <v>1</v>
@@ -21748,7 +21774,7 @@
       <c r="E455" t="s">
         <v>1262</v>
       </c>
-      <c r="F455" s="1">
+      <c r="F455" s="2">
         <v>46230</v>
       </c>
       <c r="G455" t="s">
@@ -21758,7 +21784,7 @@
         <v>1353</v>
       </c>
       <c r="I455">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q455" t="b">
         <v>1</v>
@@ -21780,7 +21806,7 @@
       <c r="E456" t="s">
         <v>1263</v>
       </c>
-      <c r="F456" s="1">
+      <c r="F456" s="2">
         <v>46230</v>
       </c>
       <c r="G456" t="s">
@@ -21790,7 +21816,7 @@
         <v>1353</v>
       </c>
       <c r="I456">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q456" t="b">
         <v>1</v>
@@ -21812,7 +21838,7 @@
       <c r="E457" t="s">
         <v>1264</v>
       </c>
-      <c r="F457" s="1">
+      <c r="F457" s="2">
         <v>46230</v>
       </c>
       <c r="G457" t="s">
@@ -21822,7 +21848,7 @@
         <v>1353</v>
       </c>
       <c r="I457">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q457" t="b">
         <v>1</v>
@@ -21844,7 +21870,7 @@
       <c r="E458" t="s">
         <v>1202</v>
       </c>
-      <c r="F458" s="1">
+      <c r="F458" s="2">
         <v>46231</v>
       </c>
       <c r="G458" t="s">
@@ -21854,7 +21880,7 @@
         <v>1353</v>
       </c>
       <c r="I458">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q458" t="b">
         <v>1</v>
@@ -21876,7 +21902,7 @@
       <c r="E459" t="s">
         <v>1265</v>
       </c>
-      <c r="F459" s="1">
+      <c r="F459" s="2">
         <v>46233</v>
       </c>
       <c r="G459" t="s">
@@ -21886,7 +21912,7 @@
         <v>1353</v>
       </c>
       <c r="I459">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q459" t="b">
         <v>1</v>
@@ -21908,7 +21934,7 @@
       <c r="E460" t="s">
         <v>1266</v>
       </c>
-      <c r="F460" s="1">
+      <c r="F460" s="2">
         <v>46233</v>
       </c>
       <c r="G460" t="s">
@@ -21918,7 +21944,7 @@
         <v>1353</v>
       </c>
       <c r="I460">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q460" t="b">
         <v>1</v>
@@ -21940,7 +21966,7 @@
       <c r="E461" t="s">
         <v>1267</v>
       </c>
-      <c r="F461" s="1">
+      <c r="F461" s="2">
         <v>46233</v>
       </c>
       <c r="G461" t="s">
@@ -21950,7 +21976,7 @@
         <v>1353</v>
       </c>
       <c r="I461">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q461" t="b">
         <v>1</v>
@@ -21972,7 +21998,7 @@
       <c r="E462" t="s">
         <v>1268</v>
       </c>
-      <c r="F462" s="1">
+      <c r="F462" s="2">
         <v>46233</v>
       </c>
       <c r="G462" t="s">
@@ -21982,7 +22008,7 @@
         <v>1353</v>
       </c>
       <c r="I462">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q462" t="b">
         <v>1</v>
@@ -22004,7 +22030,7 @@
       <c r="E463" t="s">
         <v>1269</v>
       </c>
-      <c r="F463" s="1">
+      <c r="F463" s="2">
         <v>46234</v>
       </c>
       <c r="G463" t="s">
@@ -22014,7 +22040,7 @@
         <v>1353</v>
       </c>
       <c r="I463">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q463" t="b">
         <v>1</v>
@@ -22036,7 +22062,7 @@
       <c r="E464" t="s">
         <v>1270</v>
       </c>
-      <c r="F464" s="1">
+      <c r="F464" s="2">
         <v>46230</v>
       </c>
       <c r="G464" t="s">
@@ -22046,7 +22072,7 @@
         <v>1353</v>
       </c>
       <c r="I464">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q464" t="b">
         <v>1</v>
@@ -22068,7 +22094,7 @@
       <c r="E465" t="s">
         <v>1271</v>
       </c>
-      <c r="F465" s="1">
+      <c r="F465" s="2">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
@@ -22078,7 +22104,7 @@
         <v>1353</v>
       </c>
       <c r="I465">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q465" t="b">
         <v>1</v>
@@ -22100,7 +22126,7 @@
       <c r="E466" t="s">
         <v>1272</v>
       </c>
-      <c r="F466" s="1">
+      <c r="F466" s="2">
         <v>46230</v>
       </c>
       <c r="G466" t="s">
@@ -22110,7 +22136,7 @@
         <v>1353</v>
       </c>
       <c r="I466">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q466" t="b">
         <v>1</v>
@@ -22132,7 +22158,7 @@
       <c r="E467" t="s">
         <v>1273</v>
       </c>
-      <c r="F467" s="1">
+      <c r="F467" s="2">
         <v>46230</v>
       </c>
       <c r="G467" t="s">
@@ -22142,7 +22168,7 @@
         <v>1353</v>
       </c>
       <c r="I467">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q467" t="b">
         <v>1</v>
@@ -22164,7 +22190,7 @@
       <c r="E468" t="s">
         <v>1274</v>
       </c>
-      <c r="F468" s="1">
+      <c r="F468" s="2">
         <v>46230</v>
       </c>
       <c r="G468" t="s">
@@ -22174,7 +22200,7 @@
         <v>1353</v>
       </c>
       <c r="I468">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q468" t="b">
         <v>1</v>
@@ -22196,7 +22222,7 @@
       <c r="E469" t="s">
         <v>1275</v>
       </c>
-      <c r="F469" s="1">
+      <c r="F469" s="2">
         <v>46230</v>
       </c>
       <c r="G469" t="s">
@@ -22206,7 +22232,7 @@
         <v>1353</v>
       </c>
       <c r="I469">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q469" t="b">
         <v>1</v>
@@ -22228,7 +22254,7 @@
       <c r="E470" t="s">
         <v>1276</v>
       </c>
-      <c r="F470" s="1">
+      <c r="F470" s="2">
         <v>46230</v>
       </c>
       <c r="G470" t="s">
@@ -22257,7 +22283,7 @@
       <c r="E471" t="s">
         <v>1277</v>
       </c>
-      <c r="F471" s="1">
+      <c r="F471" s="2">
         <v>46230</v>
       </c>
       <c r="G471" t="s">
@@ -22267,7 +22293,7 @@
         <v>1353</v>
       </c>
       <c r="I471">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q471" t="b">
         <v>1</v>
@@ -22289,7 +22315,7 @@
       <c r="E472" t="s">
         <v>1278</v>
       </c>
-      <c r="F472" s="1">
+      <c r="F472" s="2">
         <v>46230</v>
       </c>
       <c r="G472" t="s">
@@ -22299,7 +22325,7 @@
         <v>1353</v>
       </c>
       <c r="I472">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q472" t="b">
         <v>1</v>
@@ -22321,7 +22347,7 @@
       <c r="E473" t="s">
         <v>1279</v>
       </c>
-      <c r="F473" s="1">
+      <c r="F473" s="2">
         <v>46230</v>
       </c>
       <c r="G473" t="s">
@@ -22331,7 +22357,7 @@
         <v>1353</v>
       </c>
       <c r="I473">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q473" t="b">
         <v>1</v>
@@ -22353,7 +22379,7 @@
       <c r="E474" t="s">
         <v>1280</v>
       </c>
-      <c r="F474" s="1">
+      <c r="F474" s="2">
         <v>46231</v>
       </c>
       <c r="G474" t="s">
@@ -22363,7 +22389,7 @@
         <v>1353</v>
       </c>
       <c r="I474">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q474" t="b">
         <v>1</v>
@@ -22385,7 +22411,7 @@
       <c r="E475" t="s">
         <v>1281</v>
       </c>
-      <c r="F475" s="1">
+      <c r="F475" s="2">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
@@ -22395,7 +22421,7 @@
         <v>1353</v>
       </c>
       <c r="I475">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q475" t="b">
         <v>1</v>
@@ -22417,7 +22443,7 @@
       <c r="E476" t="s">
         <v>1282</v>
       </c>
-      <c r="F476" s="1">
+      <c r="F476" s="2">
         <v>46231</v>
       </c>
       <c r="G476" t="s">
@@ -22427,7 +22453,7 @@
         <v>1353</v>
       </c>
       <c r="I476">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q476" t="b">
         <v>1</v>
@@ -22449,7 +22475,7 @@
       <c r="E477" t="s">
         <v>1283</v>
       </c>
-      <c r="F477" s="1">
+      <c r="F477" s="2">
         <v>46231</v>
       </c>
       <c r="G477" t="s">
@@ -22459,7 +22485,7 @@
         <v>1353</v>
       </c>
       <c r="I477">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q477" t="b">
         <v>1</v>
@@ -22481,7 +22507,7 @@
       <c r="E478" t="s">
         <v>1284</v>
       </c>
-      <c r="F478" s="1">
+      <c r="F478" s="2">
         <v>46231</v>
       </c>
       <c r="G478" t="s">
@@ -22491,7 +22517,7 @@
         <v>1353</v>
       </c>
       <c r="I478">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q478" t="b">
         <v>1</v>
@@ -22513,7 +22539,7 @@
       <c r="E479" t="s">
         <v>1285</v>
       </c>
-      <c r="F479" s="1">
+      <c r="F479" s="2">
         <v>46231</v>
       </c>
       <c r="G479" t="s">
@@ -22523,7 +22549,7 @@
         <v>1353</v>
       </c>
       <c r="I479">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q479" t="b">
         <v>1</v>
@@ -22545,7 +22571,7 @@
       <c r="E480" t="s">
         <v>1286</v>
       </c>
-      <c r="F480" s="1">
+      <c r="F480" s="2">
         <v>46231</v>
       </c>
       <c r="G480" t="s">
@@ -22555,7 +22581,7 @@
         <v>1353</v>
       </c>
       <c r="I480">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q480" t="b">
         <v>1</v>
@@ -22577,7 +22603,7 @@
       <c r="E481" t="s">
         <v>1287</v>
       </c>
-      <c r="F481" s="1">
+      <c r="F481" s="2">
         <v>46231</v>
       </c>
       <c r="G481" t="s">
@@ -22587,7 +22613,7 @@
         <v>1353</v>
       </c>
       <c r="I481">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q481" t="b">
         <v>1</v>
@@ -22609,7 +22635,7 @@
       <c r="E482" t="s">
         <v>1288</v>
       </c>
-      <c r="F482" s="1">
+      <c r="F482" s="2">
         <v>46231</v>
       </c>
       <c r="G482" t="s">
@@ -22619,7 +22645,7 @@
         <v>1353</v>
       </c>
       <c r="I482">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q482" t="b">
         <v>1</v>
@@ -22641,7 +22667,7 @@
       <c r="E483" t="s">
         <v>1289</v>
       </c>
-      <c r="F483" s="1">
+      <c r="F483" s="2">
         <v>46231</v>
       </c>
       <c r="G483" t="s">
@@ -22651,7 +22677,7 @@
         <v>1353</v>
       </c>
       <c r="I483">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q483" t="b">
         <v>1</v>
@@ -22673,7 +22699,7 @@
       <c r="E484" t="s">
         <v>1290</v>
       </c>
-      <c r="F484" s="1">
+      <c r="F484" s="2">
         <v>46231</v>
       </c>
       <c r="G484" t="s">
@@ -22683,7 +22709,7 @@
         <v>1353</v>
       </c>
       <c r="I484">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q484" t="b">
         <v>1</v>
@@ -22705,7 +22731,7 @@
       <c r="E485" t="s">
         <v>1291</v>
       </c>
-      <c r="F485" s="1">
+      <c r="F485" s="2">
         <v>46231</v>
       </c>
       <c r="G485" t="s">
@@ -22715,7 +22741,7 @@
         <v>1353</v>
       </c>
       <c r="I485">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q485" t="b">
         <v>1</v>
@@ -22737,7 +22763,7 @@
       <c r="E486" t="s">
         <v>1292</v>
       </c>
-      <c r="F486" s="1">
+      <c r="F486" s="2">
         <v>46231</v>
       </c>
       <c r="G486" t="s">
@@ -22747,7 +22773,7 @@
         <v>1353</v>
       </c>
       <c r="I486">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q486" t="b">
         <v>1</v>
@@ -22769,7 +22795,7 @@
       <c r="E487" t="s">
         <v>1293</v>
       </c>
-      <c r="F487" s="1">
+      <c r="F487" s="2">
         <v>46231</v>
       </c>
       <c r="G487" t="s">
@@ -22779,7 +22805,7 @@
         <v>1353</v>
       </c>
       <c r="I487">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q487" t="b">
         <v>1</v>
@@ -22801,7 +22827,7 @@
       <c r="E488" t="s">
         <v>1294</v>
       </c>
-      <c r="F488" s="1">
+      <c r="F488" s="2">
         <v>46231</v>
       </c>
       <c r="G488" t="s">
@@ -22811,7 +22837,7 @@
         <v>1353</v>
       </c>
       <c r="I488">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q488" t="b">
         <v>1</v>
@@ -22833,7 +22859,7 @@
       <c r="E489" t="s">
         <v>1295</v>
       </c>
-      <c r="F489" s="1">
+      <c r="F489" s="2">
         <v>46231</v>
       </c>
       <c r="G489" t="s">
@@ -22843,7 +22869,7 @@
         <v>1353</v>
       </c>
       <c r="I489">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q489" t="b">
         <v>1</v>
@@ -22865,7 +22891,7 @@
       <c r="E490" t="s">
         <v>1296</v>
       </c>
-      <c r="F490" s="1">
+      <c r="F490" s="2">
         <v>46231</v>
       </c>
       <c r="G490" t="s">
@@ -22875,7 +22901,7 @@
         <v>1353</v>
       </c>
       <c r="I490">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q490" t="b">
         <v>1</v>
@@ -22897,7 +22923,7 @@
       <c r="E491" t="s">
         <v>1297</v>
       </c>
-      <c r="F491" s="1">
+      <c r="F491" s="2">
         <v>46231</v>
       </c>
       <c r="G491" t="s">
@@ -22907,7 +22933,7 @@
         <v>1353</v>
       </c>
       <c r="I491">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q491" t="b">
         <v>1</v>
@@ -22929,7 +22955,7 @@
       <c r="E492" t="s">
         <v>911</v>
       </c>
-      <c r="F492" s="1">
+      <c r="F492" s="2">
         <v>46231</v>
       </c>
       <c r="G492" t="s">
@@ -22939,7 +22965,7 @@
         <v>1355</v>
       </c>
       <c r="I492">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q492" t="b">
         <v>1</v>
@@ -22961,7 +22987,7 @@
       <c r="E493" t="s">
         <v>995</v>
       </c>
-      <c r="F493" s="1">
+      <c r="F493" s="2">
         <v>46231</v>
       </c>
       <c r="G493" t="s">
@@ -22971,7 +22997,7 @@
         <v>1355</v>
       </c>
       <c r="I493">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q493" t="b">
         <v>1</v>
@@ -22993,7 +23019,7 @@
       <c r="E494" t="s">
         <v>867</v>
       </c>
-      <c r="F494" s="1">
+      <c r="F494" s="2">
         <v>46231</v>
       </c>
       <c r="G494" t="s">
@@ -23003,7 +23029,7 @@
         <v>1355</v>
       </c>
       <c r="I494">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q494" t="b">
         <v>1</v>
@@ -23025,7 +23051,7 @@
       <c r="E495" t="s">
         <v>912</v>
       </c>
-      <c r="F495" s="1">
+      <c r="F495" s="2">
         <v>46231</v>
       </c>
       <c r="G495" t="s">
@@ -23035,7 +23061,7 @@
         <v>1355</v>
       </c>
       <c r="I495">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q495" t="b">
         <v>1</v>
@@ -23057,7 +23083,7 @@
       <c r="E496" t="s">
         <v>1048</v>
       </c>
-      <c r="F496" s="1">
+      <c r="F496" s="2">
         <v>46231</v>
       </c>
       <c r="G496" t="s">
@@ -23067,7 +23093,7 @@
         <v>1355</v>
       </c>
       <c r="I496">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q496" t="b">
         <v>1</v>
@@ -23089,7 +23115,7 @@
       <c r="E497" t="s">
         <v>1298</v>
       </c>
-      <c r="F497" s="1">
+      <c r="F497" s="2">
         <v>46231</v>
       </c>
       <c r="G497" t="s">
@@ -23099,7 +23125,7 @@
         <v>1353</v>
       </c>
       <c r="I497">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q497" t="b">
         <v>1</v>
@@ -23121,7 +23147,7 @@
       <c r="E498" t="s">
         <v>1299</v>
       </c>
-      <c r="F498" s="1">
+      <c r="F498" s="2">
         <v>46231</v>
       </c>
       <c r="G498" t="s">
@@ -23131,7 +23157,7 @@
         <v>1353</v>
       </c>
       <c r="I498">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q498" t="b">
         <v>1</v>
@@ -23153,7 +23179,7 @@
       <c r="E499" t="s">
         <v>1300</v>
       </c>
-      <c r="F499" s="1">
+      <c r="F499" s="2">
         <v>46231</v>
       </c>
       <c r="G499" t="s">
@@ -23163,7 +23189,7 @@
         <v>1355</v>
       </c>
       <c r="I499">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q499" t="b">
         <v>1</v>
@@ -23185,7 +23211,7 @@
       <c r="E500" t="s">
         <v>1301</v>
       </c>
-      <c r="F500" s="1">
+      <c r="F500" s="2">
         <v>46231</v>
       </c>
       <c r="G500" t="s">
@@ -23195,7 +23221,7 @@
         <v>1353</v>
       </c>
       <c r="I500">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q500" t="b">
         <v>1</v>
@@ -23217,7 +23243,7 @@
       <c r="E501" t="s">
         <v>1302</v>
       </c>
-      <c r="F501" s="1">
+      <c r="F501" s="2">
         <v>46231</v>
       </c>
       <c r="G501" t="s">
@@ -23227,7 +23253,7 @@
         <v>1353</v>
       </c>
       <c r="I501">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q501" t="b">
         <v>1</v>
@@ -23249,7 +23275,7 @@
       <c r="E502" t="s">
         <v>1303</v>
       </c>
-      <c r="F502" s="1">
+      <c r="F502" s="2">
         <v>46231</v>
       </c>
       <c r="G502" t="s">
@@ -23259,7 +23285,7 @@
         <v>1353</v>
       </c>
       <c r="I502">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q502" t="b">
         <v>1</v>
@@ -23281,7 +23307,7 @@
       <c r="E503" t="s">
         <v>1304</v>
       </c>
-      <c r="F503" s="1">
+      <c r="F503" s="2">
         <v>46231</v>
       </c>
       <c r="G503" t="s">
@@ -23291,7 +23317,7 @@
         <v>1353</v>
       </c>
       <c r="I503">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q503" t="b">
         <v>1</v>
@@ -23313,7 +23339,7 @@
       <c r="E504" t="s">
         <v>1305</v>
       </c>
-      <c r="F504" s="1">
+      <c r="F504" s="2">
         <v>46232</v>
       </c>
       <c r="G504" t="s">
@@ -23323,7 +23349,7 @@
         <v>1353</v>
       </c>
       <c r="I504">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q504" t="b">
         <v>1</v>
@@ -23345,7 +23371,7 @@
       <c r="E505" t="s">
         <v>1306</v>
       </c>
-      <c r="F505" s="1">
+      <c r="F505" s="2">
         <v>46232</v>
       </c>
       <c r="G505" t="s">
@@ -23355,7 +23381,7 @@
         <v>1353</v>
       </c>
       <c r="I505">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q505" t="b">
         <v>1</v>
@@ -23377,7 +23403,7 @@
       <c r="E506" t="s">
         <v>1307</v>
       </c>
-      <c r="F506" s="1">
+      <c r="F506" s="2">
         <v>46232</v>
       </c>
       <c r="G506" t="s">
@@ -23387,7 +23413,7 @@
         <v>1353</v>
       </c>
       <c r="I506">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q506" t="b">
         <v>1</v>
@@ -23409,7 +23435,7 @@
       <c r="E507" t="s">
         <v>1308</v>
       </c>
-      <c r="F507" s="1">
+      <c r="F507" s="2">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
@@ -23419,7 +23445,7 @@
         <v>1353</v>
       </c>
       <c r="I507">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q507" t="b">
         <v>1</v>
@@ -23441,7 +23467,7 @@
       <c r="E508" t="s">
         <v>1309</v>
       </c>
-      <c r="F508" s="1">
+      <c r="F508" s="2">
         <v>46237</v>
       </c>
       <c r="G508" t="s">
@@ -23470,7 +23496,7 @@
       <c r="E509" t="s">
         <v>1310</v>
       </c>
-      <c r="F509" s="1">
+      <c r="F509" s="2">
         <v>46237</v>
       </c>
       <c r="G509" t="s">
@@ -23480,7 +23506,7 @@
         <v>1353</v>
       </c>
       <c r="I509">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q509" t="b">
         <v>1</v>
@@ -23502,7 +23528,7 @@
       <c r="E510" t="s">
         <v>1311</v>
       </c>
-      <c r="F510" s="1">
+      <c r="F510" s="2">
         <v>46237</v>
       </c>
       <c r="G510" t="s">
@@ -23512,7 +23538,7 @@
         <v>1353</v>
       </c>
       <c r="I510">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q510" t="b">
         <v>1</v>
@@ -23534,7 +23560,7 @@
       <c r="E511" t="s">
         <v>1312</v>
       </c>
-      <c r="F511" s="1">
+      <c r="F511" s="2">
         <v>46240</v>
       </c>
       <c r="G511" t="s">
@@ -23544,7 +23570,7 @@
         <v>1353</v>
       </c>
       <c r="I511">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q511" t="b">
         <v>1</v>
@@ -23566,7 +23592,7 @@
       <c r="E512" t="s">
         <v>1313</v>
       </c>
-      <c r="F512" s="1">
+      <c r="F512" s="2">
         <v>46240</v>
       </c>
       <c r="G512" t="s">
@@ -23576,7 +23602,7 @@
         <v>1353</v>
       </c>
       <c r="I512">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q512" t="b">
         <v>1</v>
@@ -23598,7 +23624,7 @@
       <c r="E513" t="s">
         <v>1314</v>
       </c>
-      <c r="F513" s="1">
+      <c r="F513" s="2">
         <v>46244</v>
       </c>
       <c r="G513" t="s">
@@ -23608,7 +23634,7 @@
         <v>1353</v>
       </c>
       <c r="I513">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q513" t="b">
         <v>1</v>
@@ -23630,7 +23656,7 @@
       <c r="E514" t="s">
         <v>1315</v>
       </c>
-      <c r="F514" s="1">
+      <c r="F514" s="2">
         <v>46244</v>
       </c>
       <c r="G514" t="s">
@@ -23640,7 +23666,7 @@
         <v>1353</v>
       </c>
       <c r="I514">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q514" t="b">
         <v>1</v>
@@ -23662,7 +23688,7 @@
       <c r="E515" t="s">
         <v>1043</v>
       </c>
-      <c r="F515" s="1">
+      <c r="F515" s="2">
         <v>46244</v>
       </c>
       <c r="G515" t="s">
@@ -23672,7 +23698,7 @@
         <v>1353</v>
       </c>
       <c r="I515">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q515" t="b">
         <v>1</v>
@@ -23694,7 +23720,7 @@
       <c r="E516" t="s">
         <v>1316</v>
       </c>
-      <c r="F516" s="1">
+      <c r="F516" s="2">
         <v>46252</v>
       </c>
       <c r="G516" t="s">
@@ -23704,7 +23730,7 @@
         <v>1353</v>
       </c>
       <c r="I516">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q516" t="b">
         <v>1</v>
@@ -23726,7 +23752,7 @@
       <c r="E517" t="s">
         <v>1317</v>
       </c>
-      <c r="F517" s="1">
+      <c r="F517" s="2">
         <v>46252</v>
       </c>
       <c r="G517" t="s">
@@ -23736,7 +23762,7 @@
         <v>1353</v>
       </c>
       <c r="I517">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q517" t="b">
         <v>1</v>
@@ -23758,7 +23784,7 @@
       <c r="E518" t="s">
         <v>1318</v>
       </c>
-      <c r="F518" s="1">
+      <c r="F518" s="2">
         <v>46252</v>
       </c>
       <c r="G518" t="s">
@@ -23768,7 +23794,7 @@
         <v>1353</v>
       </c>
       <c r="I518">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q518" t="b">
         <v>1</v>
@@ -23790,7 +23816,7 @@
       <c r="E519" t="s">
         <v>1253</v>
       </c>
-      <c r="F519" s="1">
+      <c r="F519" s="2">
         <v>46254</v>
       </c>
       <c r="G519" t="s">
@@ -23800,7 +23826,7 @@
         <v>1353</v>
       </c>
       <c r="I519">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q519" t="b">
         <v>1</v>
@@ -23822,7 +23848,7 @@
       <c r="E520" t="s">
         <v>1319</v>
       </c>
-      <c r="F520" s="1">
+      <c r="F520" s="2">
         <v>46254</v>
       </c>
       <c r="G520" t="s">
@@ -23832,7 +23858,7 @@
         <v>1353</v>
       </c>
       <c r="I520">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q520" t="b">
         <v>1</v>
@@ -23854,7 +23880,7 @@
       <c r="E521" t="s">
         <v>1320</v>
       </c>
-      <c r="F521" s="1">
+      <c r="F521" s="2">
         <v>46254</v>
       </c>
       <c r="G521" t="s">
@@ -23864,7 +23890,7 @@
         <v>1353</v>
       </c>
       <c r="I521">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q521" t="b">
         <v>1</v>
@@ -23886,7 +23912,7 @@
       <c r="E522" t="s">
         <v>1253</v>
       </c>
-      <c r="F522" s="1">
+      <c r="F522" s="2">
         <v>46254</v>
       </c>
       <c r="G522" t="s">
@@ -23896,7 +23922,7 @@
         <v>1353</v>
       </c>
       <c r="I522">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q522" t="b">
         <v>1</v>
@@ -23918,7 +23944,7 @@
       <c r="E523" t="s">
         <v>1319</v>
       </c>
-      <c r="F523" s="1">
+      <c r="F523" s="2">
         <v>46254</v>
       </c>
       <c r="G523" t="s">
@@ -23928,7 +23954,7 @@
         <v>1353</v>
       </c>
       <c r="I523">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q523" t="b">
         <v>1</v>
@@ -23950,7 +23976,7 @@
       <c r="E524" t="s">
         <v>1321</v>
       </c>
-      <c r="F524" s="1">
+      <c r="F524" s="2">
         <v>46265</v>
       </c>
       <c r="G524" t="s">
@@ -23960,7 +23986,7 @@
         <v>1353</v>
       </c>
       <c r="I524">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q524" t="b">
         <v>1</v>
@@ -23982,7 +24008,7 @@
       <c r="E525" t="s">
         <v>1322</v>
       </c>
-      <c r="F525" s="1">
+      <c r="F525" s="2">
         <v>46265</v>
       </c>
       <c r="G525" t="s">
@@ -23992,7 +24018,7 @@
         <v>1353</v>
       </c>
       <c r="I525">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q525" t="b">
         <v>1</v>
@@ -24014,7 +24040,7 @@
       <c r="E526" t="s">
         <v>1323</v>
       </c>
-      <c r="F526" s="1">
+      <c r="F526" s="2">
         <v>46265</v>
       </c>
       <c r="G526" t="s">
@@ -24024,7 +24050,7 @@
         <v>1353</v>
       </c>
       <c r="I526">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q526" t="b">
         <v>1</v>
@@ -24046,7 +24072,7 @@
       <c r="E527" t="s">
         <v>1324</v>
       </c>
-      <c r="F527" s="1">
+      <c r="F527" s="2">
         <v>46265</v>
       </c>
       <c r="G527" t="s">
@@ -24056,7 +24082,7 @@
         <v>1353</v>
       </c>
       <c r="I527">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q527" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
@@ -4520,8 +4520,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -4537,7 +4545,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4545,12 +4553,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4850,55 +4876,55 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4918,7 +4944,7 @@
       <c r="E2" t="s">
         <v>829</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>45698</v>
       </c>
       <c r="G2" t="s">
@@ -4956,7 +4982,7 @@
       <c r="E3" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>45714</v>
       </c>
       <c r="G3" t="s">
@@ -4994,7 +5020,7 @@
       <c r="E4" t="s">
         <v>831</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>45714</v>
       </c>
       <c r="G4" t="s">
@@ -5032,7 +5058,7 @@
       <c r="E5" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>45714</v>
       </c>
       <c r="G5" t="s">
@@ -5053,7 +5079,7 @@
       <c r="L5" t="s">
         <v>1367</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <v>45993</v>
       </c>
       <c r="Q5" t="b">
@@ -5076,7 +5102,7 @@
       <c r="E6" t="s">
         <v>833</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>45736</v>
       </c>
       <c r="G6" t="s">
@@ -5097,7 +5123,7 @@
       <c r="L6" t="s">
         <v>1368</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="2">
         <v>45889</v>
       </c>
       <c r="Q6" t="b">
@@ -5120,7 +5146,7 @@
       <c r="E7" t="s">
         <v>834</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>45736</v>
       </c>
       <c r="G7" t="s">
@@ -5141,7 +5167,7 @@
       <c r="L7" t="s">
         <v>1369</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="2">
         <v>45848</v>
       </c>
       <c r="O7" t="s">
@@ -5167,7 +5193,7 @@
       <c r="E8" t="s">
         <v>835</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>45736</v>
       </c>
       <c r="G8" t="s">
@@ -5196,7 +5222,7 @@
       <c r="E9" t="s">
         <v>836</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="2">
         <v>45736</v>
       </c>
       <c r="G9" t="s">
@@ -5217,7 +5243,7 @@
       <c r="L9" t="s">
         <v>1370</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="2">
         <v>46098</v>
       </c>
       <c r="O9">
@@ -5243,7 +5269,7 @@
       <c r="E10" t="s">
         <v>837</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="2">
         <v>45736</v>
       </c>
       <c r="G10" t="s">
@@ -5264,7 +5290,7 @@
       <c r="L10" t="s">
         <v>1371</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="2">
         <v>46114</v>
       </c>
       <c r="O10" t="s">
@@ -5290,7 +5316,7 @@
       <c r="E11" t="s">
         <v>838</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <v>45736</v>
       </c>
       <c r="G11" t="s">
@@ -5311,7 +5337,7 @@
       <c r="L11" t="s">
         <v>1369</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="2">
         <v>45848</v>
       </c>
       <c r="O11" t="s">
@@ -5337,7 +5363,7 @@
       <c r="E12" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="2">
         <v>45736</v>
       </c>
       <c r="G12" t="s">
@@ -5358,7 +5384,7 @@
       <c r="L12" t="s">
         <v>1372</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="2">
         <v>45860</v>
       </c>
       <c r="Q12" t="b">
@@ -5381,7 +5407,7 @@
       <c r="E13" t="s">
         <v>840</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <v>45736</v>
       </c>
       <c r="G13" t="s">
@@ -5410,7 +5436,7 @@
       <c r="E14" t="s">
         <v>841</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="2">
         <v>45736</v>
       </c>
       <c r="G14" t="s">
@@ -5431,7 +5457,7 @@
       <c r="L14" t="s">
         <v>1373</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N14" s="2">
         <v>45800</v>
       </c>
       <c r="Q14" t="b">
@@ -5454,7 +5480,7 @@
       <c r="E15" t="s">
         <v>842</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="2">
         <v>45736</v>
       </c>
       <c r="G15" t="s">
@@ -5492,7 +5518,7 @@
       <c r="E16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <v>45736</v>
       </c>
       <c r="G16" t="s">
@@ -5530,7 +5556,7 @@
       <c r="E17" t="s">
         <v>844</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="2">
         <v>45736</v>
       </c>
       <c r="G17" t="s">
@@ -5551,7 +5577,7 @@
       <c r="L17" t="s">
         <v>1368</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17" s="2">
         <v>45897</v>
       </c>
       <c r="Q17" t="b">
@@ -5574,7 +5600,7 @@
       <c r="E18" t="s">
         <v>845</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <v>45736</v>
       </c>
       <c r="G18" t="s">
@@ -5595,7 +5621,7 @@
       <c r="L18" t="s">
         <v>1373</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="2">
         <v>45802</v>
       </c>
       <c r="Q18" t="b">
@@ -5618,7 +5644,7 @@
       <c r="E19" t="s">
         <v>846</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="2">
         <v>45736</v>
       </c>
       <c r="G19" t="s">
@@ -5647,7 +5673,7 @@
       <c r="E20" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="2">
         <v>45736</v>
       </c>
       <c r="G20" t="s">
@@ -5668,7 +5694,7 @@
       <c r="L20" t="s">
         <v>1374</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20" s="2">
         <v>46135</v>
       </c>
       <c r="Q20" t="b">
@@ -5691,7 +5717,7 @@
       <c r="E21" t="s">
         <v>848</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="2">
         <v>45736</v>
       </c>
       <c r="G21" t="s">
@@ -5720,7 +5746,7 @@
       <c r="E22" t="s">
         <v>849</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="2">
         <v>45736</v>
       </c>
       <c r="G22" t="s">
@@ -5758,7 +5784,7 @@
       <c r="E23" t="s">
         <v>850</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <v>45736</v>
       </c>
       <c r="G23" t="s">
@@ -5779,7 +5805,7 @@
       <c r="L23" t="s">
         <v>1375</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23" s="2">
         <v>45965</v>
       </c>
       <c r="P23" t="s">
@@ -5805,7 +5831,7 @@
       <c r="E24" t="s">
         <v>851</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="2">
         <v>45736</v>
       </c>
       <c r="G24" t="s">
@@ -5834,7 +5860,7 @@
       <c r="E25" t="s">
         <v>852</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="2">
         <v>45736</v>
       </c>
       <c r="G25" t="s">
@@ -5863,7 +5889,7 @@
       <c r="E26" t="s">
         <v>853</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="2">
         <v>45736</v>
       </c>
       <c r="G26" t="s">
@@ -5884,7 +5910,7 @@
       <c r="L26" t="s">
         <v>1376</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N26" s="2">
         <v>45891</v>
       </c>
       <c r="P26" t="s">
@@ -5910,7 +5936,7 @@
       <c r="E27" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="2">
         <v>45736</v>
       </c>
       <c r="G27" t="s">
@@ -5948,7 +5974,7 @@
       <c r="E28" t="s">
         <v>855</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="2">
         <v>45736</v>
       </c>
       <c r="G28" t="s">
@@ -5977,7 +6003,7 @@
       <c r="E29" t="s">
         <v>856</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="2">
         <v>45736</v>
       </c>
       <c r="G29" t="s">
@@ -6006,7 +6032,7 @@
       <c r="E30" t="s">
         <v>857</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="2">
         <v>45736</v>
       </c>
       <c r="G30" t="s">
@@ -6027,7 +6053,7 @@
       <c r="L30" t="s">
         <v>1377</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30" s="2">
         <v>45945</v>
       </c>
       <c r="Q30" t="b">
@@ -6050,7 +6076,7 @@
       <c r="E31" t="s">
         <v>858</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="2">
         <v>45736</v>
       </c>
       <c r="G31" t="s">
@@ -6079,7 +6105,7 @@
       <c r="E32" t="s">
         <v>859</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="2">
         <v>45736</v>
       </c>
       <c r="G32" t="s">
@@ -6117,7 +6143,7 @@
       <c r="E33" t="s">
         <v>860</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="2">
         <v>45736</v>
       </c>
       <c r="G33" t="s">
@@ -6146,7 +6172,7 @@
       <c r="E34" t="s">
         <v>861</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="2">
         <v>45736</v>
       </c>
       <c r="G34" t="s">
@@ -6175,7 +6201,7 @@
       <c r="E35" t="s">
         <v>862</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="2">
         <v>45736</v>
       </c>
       <c r="G35" t="s">
@@ -6204,7 +6230,7 @@
       <c r="E36" t="s">
         <v>863</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="2">
         <v>45736</v>
       </c>
       <c r="G36" t="s">
@@ -6233,7 +6259,7 @@
       <c r="E37" t="s">
         <v>864</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="2">
         <v>45736</v>
       </c>
       <c r="G37" t="s">
@@ -6262,7 +6288,7 @@
       <c r="E38" t="s">
         <v>844</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="2">
         <v>45736</v>
       </c>
       <c r="G38" t="s">
@@ -6288,7 +6314,7 @@
       <c r="D39" t="s">
         <v>731</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="2">
         <v>45736</v>
       </c>
       <c r="G39" t="s">
@@ -6323,7 +6349,7 @@
       <c r="D40" t="s">
         <v>731</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="2">
         <v>45736</v>
       </c>
       <c r="G40" t="s">
@@ -6361,7 +6387,7 @@
       <c r="E41" t="s">
         <v>865</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="2">
         <v>45736</v>
       </c>
       <c r="G41" t="s">
@@ -6390,7 +6416,7 @@
       <c r="E42" t="s">
         <v>866</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="2">
         <v>45736</v>
       </c>
       <c r="G42" t="s">
@@ -6419,7 +6445,7 @@
       <c r="E43" t="s">
         <v>867</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="2">
         <v>45736</v>
       </c>
       <c r="G43" t="s">
@@ -6454,7 +6480,7 @@
       <c r="E44" t="s">
         <v>868</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="2">
         <v>45769</v>
       </c>
       <c r="G44" t="s">
@@ -6475,7 +6501,7 @@
       <c r="L44" t="s">
         <v>1378</v>
       </c>
-      <c r="N44" s="1">
+      <c r="N44" s="2">
         <v>45856</v>
       </c>
       <c r="P44" t="s">
@@ -6501,7 +6527,7 @@
       <c r="E45" t="s">
         <v>869</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="2">
         <v>45769</v>
       </c>
       <c r="G45" t="s">
@@ -6522,7 +6548,7 @@
       <c r="L45" t="s">
         <v>1379</v>
       </c>
-      <c r="N45" s="1">
+      <c r="N45" s="2">
         <v>46100</v>
       </c>
       <c r="O45">
@@ -6548,7 +6574,7 @@
       <c r="E46" t="s">
         <v>870</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="2">
         <v>45769</v>
       </c>
       <c r="G46" t="s">
@@ -6586,7 +6612,7 @@
       <c r="E47" t="s">
         <v>871</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="2">
         <v>45769</v>
       </c>
       <c r="G47" t="s">
@@ -6607,7 +6633,7 @@
       <c r="L47" t="s">
         <v>1380</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N47" s="2">
         <v>46113</v>
       </c>
       <c r="P47" t="s">
@@ -6633,7 +6659,7 @@
       <c r="E48" t="s">
         <v>872</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="2">
         <v>45769</v>
       </c>
       <c r="G48" t="s">
@@ -6671,7 +6697,7 @@
       <c r="E49" t="s">
         <v>873</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="2">
         <v>45769</v>
       </c>
       <c r="G49" t="s">
@@ -6700,7 +6726,7 @@
       <c r="E50" t="s">
         <v>874</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="2">
         <v>45769</v>
       </c>
       <c r="G50" t="s">
@@ -6738,7 +6764,7 @@
       <c r="E51" t="s">
         <v>875</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="2">
         <v>45769</v>
       </c>
       <c r="G51" t="s">
@@ -6767,7 +6793,7 @@
       <c r="E52" t="s">
         <v>876</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="2">
         <v>45769</v>
       </c>
       <c r="G52" t="s">
@@ -6805,7 +6831,7 @@
       <c r="E53" t="s">
         <v>877</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="2">
         <v>45769</v>
       </c>
       <c r="G53" t="s">
@@ -6843,7 +6869,7 @@
       <c r="E54" t="s">
         <v>878</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="2">
         <v>45769</v>
       </c>
       <c r="G54" t="s">
@@ -6881,7 +6907,7 @@
       <c r="E55" t="s">
         <v>879</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="2">
         <v>45769</v>
       </c>
       <c r="G55" t="s">
@@ -6910,7 +6936,7 @@
       <c r="E56" t="s">
         <v>880</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="2">
         <v>45769</v>
       </c>
       <c r="G56" t="s">
@@ -6939,7 +6965,7 @@
       <c r="E57" t="s">
         <v>881</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="2">
         <v>45769</v>
       </c>
       <c r="G57" t="s">
@@ -6977,7 +7003,7 @@
       <c r="E58" t="s">
         <v>882</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="2">
         <v>45769</v>
       </c>
       <c r="G58" t="s">
@@ -7006,7 +7032,7 @@
       <c r="E59" t="s">
         <v>883</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="2">
         <v>45769</v>
       </c>
       <c r="G59" t="s">
@@ -7035,7 +7061,7 @@
       <c r="E60" t="s">
         <v>884</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="2">
         <v>45769</v>
       </c>
       <c r="G60" t="s">
@@ -7064,7 +7090,7 @@
       <c r="E61" t="s">
         <v>885</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="2">
         <v>45769</v>
       </c>
       <c r="G61" t="s">
@@ -7093,7 +7119,7 @@
       <c r="E62" t="s">
         <v>886</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="2">
         <v>45770</v>
       </c>
       <c r="G62" t="s">
@@ -7122,7 +7148,7 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="2">
         <v>45799</v>
       </c>
       <c r="G63" t="s">
@@ -7143,7 +7169,7 @@
       <c r="L63" t="s">
         <v>1381</v>
       </c>
-      <c r="N63" s="1">
+      <c r="N63" s="2">
         <v>46092</v>
       </c>
       <c r="P63" t="s">
@@ -7169,7 +7195,7 @@
       <c r="E64" t="s">
         <v>888</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="2">
         <v>45799</v>
       </c>
       <c r="G64" t="s">
@@ -7190,7 +7216,7 @@
       <c r="L64" t="s">
         <v>1382</v>
       </c>
-      <c r="N64" s="1">
+      <c r="N64" s="2">
         <v>46119</v>
       </c>
       <c r="Q64" t="b">
@@ -7213,7 +7239,7 @@
       <c r="E65" t="s">
         <v>889</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="2">
         <v>45799</v>
       </c>
       <c r="G65" t="s">
@@ -7242,7 +7268,7 @@
       <c r="E66" t="s">
         <v>890</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="2">
         <v>45799</v>
       </c>
       <c r="G66" t="s">
@@ -7271,7 +7297,7 @@
       <c r="E67" t="s">
         <v>891</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="2">
         <v>45799</v>
       </c>
       <c r="G67" t="s">
@@ -7300,7 +7326,7 @@
       <c r="E68" t="s">
         <v>892</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="2">
         <v>45799</v>
       </c>
       <c r="G68" t="s">
@@ -7329,7 +7355,7 @@
       <c r="E69" t="s">
         <v>893</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="2">
         <v>45803</v>
       </c>
       <c r="G69" t="s">
@@ -7358,7 +7384,7 @@
       <c r="E70" t="s">
         <v>894</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="2">
         <v>45803</v>
       </c>
       <c r="G70" t="s">
@@ -7379,7 +7405,7 @@
       <c r="L70" t="s">
         <v>1383</v>
       </c>
-      <c r="N70" s="1">
+      <c r="N70" s="2">
         <v>46232</v>
       </c>
       <c r="Q70" t="b">
@@ -7402,7 +7428,7 @@
       <c r="E71" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="2">
         <v>45803</v>
       </c>
       <c r="G71" t="s">
@@ -7423,7 +7449,7 @@
       <c r="L71" t="s">
         <v>1383</v>
       </c>
-      <c r="N71" s="1">
+      <c r="N71" s="2">
         <v>46232</v>
       </c>
       <c r="Q71" t="b">
@@ -7446,7 +7472,7 @@
       <c r="E72" t="s">
         <v>896</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="2">
         <v>45803</v>
       </c>
       <c r="G72" t="s">
@@ -7475,7 +7501,7 @@
       <c r="E73" t="s">
         <v>897</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="2">
         <v>45803</v>
       </c>
       <c r="G73" t="s">
@@ -7513,7 +7539,7 @@
       <c r="E74" t="s">
         <v>896</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="2">
         <v>45803</v>
       </c>
       <c r="G74" t="s">
@@ -7542,7 +7568,7 @@
       <c r="E75" t="s">
         <v>898</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="2">
         <v>45803</v>
       </c>
       <c r="G75" t="s">
@@ -7563,7 +7589,7 @@
       <c r="L75" t="s">
         <v>1383</v>
       </c>
-      <c r="N75" s="1">
+      <c r="N75" s="2">
         <v>46232</v>
       </c>
       <c r="Q75" t="b">
@@ -7586,7 +7612,7 @@
       <c r="E76" t="s">
         <v>899</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="2">
         <v>45803</v>
       </c>
       <c r="G76" t="s">
@@ -7621,7 +7647,7 @@
       <c r="E77" t="s">
         <v>900</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="2">
         <v>45803</v>
       </c>
       <c r="G77" t="s">
@@ -7650,7 +7676,7 @@
       <c r="E78" t="s">
         <v>901</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78" s="2">
         <v>45803</v>
       </c>
       <c r="G78" t="s">
@@ -7679,7 +7705,7 @@
       <c r="E79" t="s">
         <v>902</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="2">
         <v>45803</v>
       </c>
       <c r="G79" t="s">
@@ -7714,7 +7740,7 @@
       <c r="E80" t="s">
         <v>903</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="2">
         <v>45803</v>
       </c>
       <c r="G80" t="s">
@@ -7735,7 +7761,7 @@
       <c r="L80" t="s">
         <v>1383</v>
       </c>
-      <c r="N80" s="1">
+      <c r="N80" s="2">
         <v>46232</v>
       </c>
       <c r="Q80" t="b">
@@ -7758,7 +7784,7 @@
       <c r="E81" t="s">
         <v>904</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="2">
         <v>45813</v>
       </c>
       <c r="G81" t="s">
@@ -7787,7 +7813,7 @@
       <c r="E82" t="s">
         <v>905</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="2">
         <v>45813</v>
       </c>
       <c r="G82" t="s">
@@ -7825,7 +7851,7 @@
       <c r="E83" t="s">
         <v>906</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="2">
         <v>45813</v>
       </c>
       <c r="G83" t="s">
@@ -7854,7 +7880,7 @@
       <c r="E84" t="s">
         <v>907</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="2">
         <v>45813</v>
       </c>
       <c r="G84" t="s">
@@ -7875,7 +7901,7 @@
       <c r="L84" t="s">
         <v>1384</v>
       </c>
-      <c r="N84" s="1">
+      <c r="N84" s="2">
         <v>45853</v>
       </c>
       <c r="O84">
@@ -7901,7 +7927,7 @@
       <c r="E85" t="s">
         <v>908</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85" s="2">
         <v>45813</v>
       </c>
       <c r="G85" t="s">
@@ -7939,7 +7965,7 @@
       <c r="E86" t="s">
         <v>909</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="2">
         <v>45813</v>
       </c>
       <c r="G86" t="s">
@@ -7977,7 +8003,7 @@
       <c r="E87" t="s">
         <v>910</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="2">
         <v>45813</v>
       </c>
       <c r="G87" t="s">
@@ -7998,7 +8024,7 @@
       <c r="L87" t="s">
         <v>1385</v>
       </c>
-      <c r="N87" s="1">
+      <c r="N87" s="2">
         <v>45797</v>
       </c>
       <c r="O87" t="s">
@@ -8024,7 +8050,7 @@
       <c r="E88" t="s">
         <v>911</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="2">
         <v>45813</v>
       </c>
       <c r="G88" t="s">
@@ -8039,7 +8065,7 @@
       <c r="L88" t="s">
         <v>1386</v>
       </c>
-      <c r="N88" s="1">
+      <c r="N88" s="2">
         <v>46195</v>
       </c>
       <c r="Q88" t="b">
@@ -8062,7 +8088,7 @@
       <c r="E89" t="s">
         <v>912</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89" s="2">
         <v>45813</v>
       </c>
       <c r="G89" t="s">
@@ -8077,7 +8103,7 @@
       <c r="L89" t="s">
         <v>1386</v>
       </c>
-      <c r="N89" s="1">
+      <c r="N89" s="2">
         <v>46195</v>
       </c>
       <c r="Q89" t="b">
@@ -8100,7 +8126,7 @@
       <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90" s="2">
         <v>45831</v>
       </c>
       <c r="G90" t="s">
@@ -8141,7 +8167,7 @@
       <c r="E91" t="s">
         <v>914</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="2">
         <v>45831</v>
       </c>
       <c r="G91" t="s">
@@ -8162,7 +8188,7 @@
       <c r="L91" t="s">
         <v>1388</v>
       </c>
-      <c r="N91" s="1">
+      <c r="N91" s="2">
         <v>46139</v>
       </c>
       <c r="Q91" t="b">
@@ -8182,7 +8208,7 @@
       <c r="D92" t="s">
         <v>748</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92" s="2">
         <v>45831</v>
       </c>
       <c r="G92" t="s">
@@ -8211,7 +8237,7 @@
       <c r="E93" t="s">
         <v>915</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93" s="2">
         <v>45831</v>
       </c>
       <c r="G93" t="s">
@@ -8232,7 +8258,7 @@
       <c r="L93" t="s">
         <v>1388</v>
       </c>
-      <c r="N93" s="1">
+      <c r="N93" s="2">
         <v>46139</v>
       </c>
       <c r="Q93" t="b">
@@ -8255,7 +8281,7 @@
       <c r="E94" t="s">
         <v>916</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94" s="2">
         <v>45831</v>
       </c>
       <c r="G94" t="s">
@@ -8293,7 +8319,7 @@
       <c r="E95" t="s">
         <v>917</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95" s="2">
         <v>45831</v>
       </c>
       <c r="G95" t="s">
@@ -8314,7 +8340,7 @@
       <c r="L95" t="s">
         <v>1388</v>
       </c>
-      <c r="N95" s="1">
+      <c r="N95" s="2">
         <v>46139</v>
       </c>
       <c r="Q95" t="b">
@@ -8337,7 +8363,7 @@
       <c r="E96" t="s">
         <v>918</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96" s="2">
         <v>45831</v>
       </c>
       <c r="G96" t="s">
@@ -8358,7 +8384,7 @@
       <c r="L96" t="s">
         <v>1369</v>
       </c>
-      <c r="N96" s="1">
+      <c r="N96" s="2">
         <v>45848</v>
       </c>
       <c r="O96" t="s">
@@ -8384,7 +8410,7 @@
       <c r="E97" t="s">
         <v>919</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="2">
         <v>45840</v>
       </c>
       <c r="G97" t="s">
@@ -8405,7 +8431,7 @@
       <c r="L97" t="s">
         <v>1389</v>
       </c>
-      <c r="N97" s="1">
+      <c r="N97" s="2">
         <v>45860</v>
       </c>
       <c r="P97" t="s">
@@ -8431,7 +8457,7 @@
       <c r="E98" t="s">
         <v>920</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="2">
         <v>45840</v>
       </c>
       <c r="G98" t="s">
@@ -8469,7 +8495,7 @@
       <c r="E99" t="s">
         <v>921</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99" s="2">
         <v>45840</v>
       </c>
       <c r="G99" t="s">
@@ -8498,7 +8524,7 @@
       <c r="E100" t="s">
         <v>922</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100" s="2">
         <v>45840</v>
       </c>
       <c r="G100" t="s">
@@ -8519,7 +8545,7 @@
       <c r="L100" t="s">
         <v>1388</v>
       </c>
-      <c r="N100" s="1">
+      <c r="N100" s="2">
         <v>46188</v>
       </c>
       <c r="Q100" t="b">
@@ -8542,7 +8568,7 @@
       <c r="E101" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101" s="2">
         <v>45840</v>
       </c>
       <c r="G101" t="s">
@@ -8571,7 +8597,7 @@
       <c r="E102" t="s">
         <v>924</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102" s="2">
         <v>45840</v>
       </c>
       <c r="G102" t="s">
@@ -8600,7 +8626,7 @@
       <c r="E103" t="s">
         <v>925</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103" s="2">
         <v>45840</v>
       </c>
       <c r="G103" t="s">
@@ -8629,7 +8655,7 @@
       <c r="E104" t="s">
         <v>926</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104" s="2">
         <v>45840</v>
       </c>
       <c r="G104" t="s">
@@ -8650,7 +8676,7 @@
       <c r="L104" t="s">
         <v>1388</v>
       </c>
-      <c r="N104" s="1">
+      <c r="N104" s="2">
         <v>46188</v>
       </c>
       <c r="Q104" t="b">
@@ -8673,7 +8699,7 @@
       <c r="E105" t="s">
         <v>927</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105" s="2">
         <v>45840</v>
       </c>
       <c r="G105" t="s">
@@ -8694,7 +8720,7 @@
       <c r="L105" t="s">
         <v>1388</v>
       </c>
-      <c r="N105" s="1">
+      <c r="N105" s="2">
         <v>46188</v>
       </c>
       <c r="Q105" t="b">
@@ -8717,7 +8743,7 @@
       <c r="E106" t="s">
         <v>928</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106" s="2">
         <v>45840</v>
       </c>
       <c r="G106" t="s">
@@ -8738,7 +8764,7 @@
       <c r="L106" t="s">
         <v>1390</v>
       </c>
-      <c r="N106" s="1">
+      <c r="N106" s="2">
         <v>45889</v>
       </c>
       <c r="Q106" t="b">
@@ -8761,7 +8787,7 @@
       <c r="E107" t="s">
         <v>929</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="2">
         <v>45840</v>
       </c>
       <c r="G107" t="s">
@@ -8782,7 +8808,7 @@
       <c r="L107" t="s">
         <v>1391</v>
       </c>
-      <c r="N107" s="1">
+      <c r="N107" s="2">
         <v>45876</v>
       </c>
       <c r="Q107" t="b">
@@ -8805,7 +8831,7 @@
       <c r="E108" t="s">
         <v>930</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108" s="2">
         <v>45840</v>
       </c>
       <c r="G108" t="s">
@@ -8843,7 +8869,7 @@
       <c r="E109" t="s">
         <v>931</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109" s="2">
         <v>45840</v>
       </c>
       <c r="G109" t="s">
@@ -8881,7 +8907,7 @@
       <c r="E110" t="s">
         <v>932</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="2">
         <v>45840</v>
       </c>
       <c r="G110" t="s">
@@ -8910,7 +8936,7 @@
       <c r="E111" t="s">
         <v>933</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="2">
         <v>45840</v>
       </c>
       <c r="G111" t="s">
@@ -8939,7 +8965,7 @@
       <c r="E112" t="s">
         <v>934</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112" s="2">
         <v>45840</v>
       </c>
       <c r="G112" t="s">
@@ -8968,7 +8994,7 @@
       <c r="E113" t="s">
         <v>935</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113" s="2">
         <v>45840</v>
       </c>
       <c r="G113" t="s">
@@ -8997,7 +9023,7 @@
       <c r="E114" t="s">
         <v>936</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114" s="2">
         <v>45840</v>
       </c>
       <c r="G114" t="s">
@@ -9026,7 +9052,7 @@
       <c r="E115" t="s">
         <v>937</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115" s="2">
         <v>45840</v>
       </c>
       <c r="G115" t="s">
@@ -9064,7 +9090,7 @@
       <c r="E116" t="s">
         <v>938</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116" s="2">
         <v>45840</v>
       </c>
       <c r="G116" t="s">
@@ -9102,7 +9128,7 @@
       <c r="E117" t="s">
         <v>939</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117" s="2">
         <v>45840</v>
       </c>
       <c r="G117" t="s">
@@ -9140,7 +9166,7 @@
       <c r="E118" t="s">
         <v>940</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118" s="2">
         <v>45840</v>
       </c>
       <c r="G118" t="s">
@@ -9178,7 +9204,7 @@
       <c r="E119" t="s">
         <v>941</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119" s="2">
         <v>45840</v>
       </c>
       <c r="G119" t="s">
@@ -9216,7 +9242,7 @@
       <c r="E120" t="s">
         <v>942</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120" s="2">
         <v>45840</v>
       </c>
       <c r="G120" t="s">
@@ -9254,7 +9280,7 @@
       <c r="E121" t="s">
         <v>943</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="2">
         <v>45849</v>
       </c>
       <c r="G121" t="s">
@@ -9275,7 +9301,7 @@
       <c r="L121" t="s">
         <v>1379</v>
       </c>
-      <c r="N121" s="1">
+      <c r="N121" s="2">
         <v>46100</v>
       </c>
       <c r="O121">
@@ -9301,7 +9327,7 @@
       <c r="E122" t="s">
         <v>944</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F122" s="2">
         <v>45849</v>
       </c>
       <c r="G122" t="s">
@@ -9339,7 +9365,7 @@
       <c r="E123" t="s">
         <v>945</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F123" s="2">
         <v>45849</v>
       </c>
       <c r="G123" t="s">
@@ -9368,7 +9394,7 @@
       <c r="E124" t="s">
         <v>946</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124" s="2">
         <v>45853</v>
       </c>
       <c r="G124" t="s">
@@ -9406,7 +9432,7 @@
       <c r="E125" t="s">
         <v>947</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125" s="2">
         <v>45855</v>
       </c>
       <c r="G125" t="s">
@@ -9444,7 +9470,7 @@
       <c r="E126" t="s">
         <v>948</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126" s="2">
         <v>45855</v>
       </c>
       <c r="G126" t="s">
@@ -9473,7 +9499,7 @@
       <c r="E127" t="s">
         <v>949</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127" s="2">
         <v>45856</v>
       </c>
       <c r="G127" t="s">
@@ -9502,7 +9528,7 @@
       <c r="E128" t="s">
         <v>950</v>
       </c>
-      <c r="F128" s="1">
+      <c r="F128" s="2">
         <v>45869</v>
       </c>
       <c r="G128" t="s">
@@ -9540,7 +9566,7 @@
       <c r="E129" t="s">
         <v>951</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F129" s="2">
         <v>45869</v>
       </c>
       <c r="G129" t="s">
@@ -9578,7 +9604,7 @@
       <c r="E130" t="s">
         <v>952</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F130" s="2">
         <v>45869</v>
       </c>
       <c r="G130" t="s">
@@ -9599,7 +9625,7 @@
       <c r="L130" t="s">
         <v>1392</v>
       </c>
-      <c r="N130" s="1">
+      <c r="N130" s="2">
         <v>45916</v>
       </c>
       <c r="O130">
@@ -9625,7 +9651,7 @@
       <c r="E131" t="s">
         <v>953</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F131" s="2">
         <v>45869</v>
       </c>
       <c r="G131" t="s">
@@ -9654,7 +9680,7 @@
       <c r="E132" t="s">
         <v>954</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F132" s="2">
         <v>45869</v>
       </c>
       <c r="G132" t="s">
@@ -9675,7 +9701,7 @@
       <c r="L132" t="s">
         <v>1393</v>
       </c>
-      <c r="N132" s="1">
+      <c r="N132" s="2">
         <v>46014</v>
       </c>
       <c r="O132">
@@ -9701,7 +9727,7 @@
       <c r="E133" t="s">
         <v>955</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F133" s="2">
         <v>45869</v>
       </c>
       <c r="G133" t="s">
@@ -9730,7 +9756,7 @@
       <c r="E134" t="s">
         <v>956</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F134" s="2">
         <v>45882</v>
       </c>
       <c r="G134" t="s">
@@ -9768,7 +9794,7 @@
       <c r="E135" t="s">
         <v>957</v>
       </c>
-      <c r="F135" s="1">
+      <c r="F135" s="2">
         <v>45882</v>
       </c>
       <c r="G135" t="s">
@@ -9797,7 +9823,7 @@
       <c r="E136" t="s">
         <v>958</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F136" s="2">
         <v>45891</v>
       </c>
       <c r="G136" t="s">
@@ -9826,7 +9852,7 @@
       <c r="E137" t="s">
         <v>959</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F137" s="2">
         <v>45891</v>
       </c>
       <c r="G137" t="s">
@@ -9855,7 +9881,7 @@
       <c r="E138" t="s">
         <v>960</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F138" s="2">
         <v>45891</v>
       </c>
       <c r="G138" t="s">
@@ -9893,7 +9919,7 @@
       <c r="E139" t="s">
         <v>961</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F139" s="2">
         <v>45891</v>
       </c>
       <c r="G139" t="s">
@@ -9922,7 +9948,7 @@
       <c r="E140" t="s">
         <v>962</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F140" s="2">
         <v>45891</v>
       </c>
       <c r="G140" t="s">
@@ -9951,7 +9977,7 @@
       <c r="E141" t="s">
         <v>963</v>
       </c>
-      <c r="F141" s="1">
+      <c r="F141" s="2">
         <v>45891</v>
       </c>
       <c r="G141" t="s">
@@ -9980,7 +10006,7 @@
       <c r="E142" t="s">
         <v>964</v>
       </c>
-      <c r="F142" s="1">
+      <c r="F142" s="2">
         <v>45891</v>
       </c>
       <c r="G142" t="s">
@@ -10009,7 +10035,7 @@
       <c r="E143" t="s">
         <v>965</v>
       </c>
-      <c r="F143" s="1">
+      <c r="F143" s="2">
         <v>45891</v>
       </c>
       <c r="G143" t="s">
@@ -10038,7 +10064,7 @@
       <c r="E144" t="s">
         <v>966</v>
       </c>
-      <c r="F144" s="1">
+      <c r="F144" s="2">
         <v>45891</v>
       </c>
       <c r="G144" t="s">
@@ -10067,7 +10093,7 @@
       <c r="E145" t="s">
         <v>967</v>
       </c>
-      <c r="F145" s="1">
+      <c r="F145" s="2">
         <v>45891</v>
       </c>
       <c r="G145" t="s">
@@ -10096,7 +10122,7 @@
       <c r="E146" t="s">
         <v>968</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F146" s="2">
         <v>45891</v>
       </c>
       <c r="G146" t="s">
@@ -10125,7 +10151,7 @@
       <c r="E147" t="s">
         <v>969</v>
       </c>
-      <c r="F147" s="1">
+      <c r="F147" s="2">
         <v>45891</v>
       </c>
       <c r="G147" t="s">
@@ -10154,7 +10180,7 @@
       <c r="E148" t="s">
         <v>970</v>
       </c>
-      <c r="F148" s="1">
+      <c r="F148" s="2">
         <v>45891</v>
       </c>
       <c r="G148" t="s">
@@ -10175,7 +10201,7 @@
       <c r="L148" t="s">
         <v>1383</v>
       </c>
-      <c r="N148" s="1">
+      <c r="N148" s="2">
         <v>46232</v>
       </c>
       <c r="Q148" t="b">
@@ -10198,7 +10224,7 @@
       <c r="E149" t="s">
         <v>971</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F149" s="2">
         <v>45891</v>
       </c>
       <c r="G149" t="s">
@@ -10219,7 +10245,7 @@
       <c r="L149" t="s">
         <v>1394</v>
       </c>
-      <c r="N149" s="1">
+      <c r="N149" s="2">
         <v>46265</v>
       </c>
       <c r="P149" t="s">
@@ -10245,7 +10271,7 @@
       <c r="E150" t="s">
         <v>972</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F150" s="2">
         <v>45891</v>
       </c>
       <c r="G150" t="s">
@@ -10266,7 +10292,7 @@
       <c r="L150" t="s">
         <v>1381</v>
       </c>
-      <c r="N150" s="1">
+      <c r="N150" s="2">
         <v>46092</v>
       </c>
       <c r="P150" t="s">
@@ -10292,7 +10318,7 @@
       <c r="E151" t="s">
         <v>973</v>
       </c>
-      <c r="F151" s="1">
+      <c r="F151" s="2">
         <v>45891</v>
       </c>
       <c r="G151" t="s">
@@ -10321,7 +10347,7 @@
       <c r="E152" t="s">
         <v>963</v>
       </c>
-      <c r="F152" s="1">
+      <c r="F152" s="2">
         <v>45891</v>
       </c>
       <c r="G152" t="s">
@@ -10342,7 +10368,7 @@
       <c r="L152" t="s">
         <v>1382</v>
       </c>
-      <c r="N152" s="1">
+      <c r="N152" s="2">
         <v>46119</v>
       </c>
       <c r="Q152" t="b">
@@ -10365,7 +10391,7 @@
       <c r="E153" t="s">
         <v>974</v>
       </c>
-      <c r="F153" s="1">
+      <c r="F153" s="2">
         <v>45891</v>
       </c>
       <c r="G153" t="s">
@@ -10383,7 +10409,7 @@
       <c r="L153" t="s">
         <v>1383</v>
       </c>
-      <c r="N153" s="1">
+      <c r="N153" s="2">
         <v>46232</v>
       </c>
       <c r="Q153" t="b">
@@ -10406,7 +10432,7 @@
       <c r="E154" t="s">
         <v>975</v>
       </c>
-      <c r="F154" s="1">
+      <c r="F154" s="2">
         <v>45891</v>
       </c>
       <c r="G154" t="s">
@@ -10435,7 +10461,7 @@
       <c r="E155" t="s">
         <v>976</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F155" s="2">
         <v>45891</v>
       </c>
       <c r="G155" t="s">
@@ -10470,7 +10496,7 @@
       <c r="E156" t="s">
         <v>977</v>
       </c>
-      <c r="F156" s="1">
+      <c r="F156" s="2">
         <v>45891</v>
       </c>
       <c r="G156" t="s">
@@ -10508,7 +10534,7 @@
       <c r="E157" t="s">
         <v>978</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="2">
         <v>45891</v>
       </c>
       <c r="G157" t="s">
@@ -10529,7 +10555,7 @@
       <c r="L157" t="s">
         <v>1395</v>
       </c>
-      <c r="N157" s="1">
+      <c r="N157" s="2">
         <v>46262</v>
       </c>
       <c r="Q157" t="b">
@@ -10552,7 +10578,7 @@
       <c r="E158" t="s">
         <v>979</v>
       </c>
-      <c r="F158" s="1">
+      <c r="F158" s="2">
         <v>45894</v>
       </c>
       <c r="G158" t="s">
@@ -10573,7 +10599,7 @@
       <c r="L158" t="s">
         <v>1396</v>
       </c>
-      <c r="N158" s="1">
+      <c r="N158" s="2">
         <v>45946</v>
       </c>
       <c r="Q158" t="b">
@@ -10596,7 +10622,7 @@
       <c r="E159" t="s">
         <v>980</v>
       </c>
-      <c r="F159" s="1">
+      <c r="F159" s="2">
         <v>45894</v>
       </c>
       <c r="G159" t="s">
@@ -10634,7 +10660,7 @@
       <c r="E160" t="s">
         <v>981</v>
       </c>
-      <c r="F160" s="1">
+      <c r="F160" s="2">
         <v>45898</v>
       </c>
       <c r="G160" t="s">
@@ -10672,7 +10698,7 @@
       <c r="E161" t="s">
         <v>982</v>
       </c>
-      <c r="F161" s="1">
+      <c r="F161" s="2">
         <v>45898</v>
       </c>
       <c r="G161" t="s">
@@ -10693,7 +10719,7 @@
       <c r="L161" t="s">
         <v>1397</v>
       </c>
-      <c r="N161" s="1">
+      <c r="N161" s="2">
         <v>45953</v>
       </c>
       <c r="O161" t="s">
@@ -10719,7 +10745,7 @@
       <c r="E162" t="s">
         <v>983</v>
       </c>
-      <c r="F162" s="1">
+      <c r="F162" s="2">
         <v>45898</v>
       </c>
       <c r="G162" t="s">
@@ -10740,7 +10766,7 @@
       <c r="L162" t="s">
         <v>1398</v>
       </c>
-      <c r="N162" s="1">
+      <c r="N162" s="2">
         <v>45940</v>
       </c>
       <c r="Q162" t="b">
@@ -10763,7 +10789,7 @@
       <c r="E163" t="s">
         <v>984</v>
       </c>
-      <c r="F163" s="1">
+      <c r="F163" s="2">
         <v>45898</v>
       </c>
       <c r="G163" t="s">
@@ -10784,7 +10810,7 @@
       <c r="L163" t="s">
         <v>1398</v>
       </c>
-      <c r="N163" s="1">
+      <c r="N163" s="2">
         <v>45940</v>
       </c>
       <c r="Q163" t="b">
@@ -10807,7 +10833,7 @@
       <c r="E164" t="s">
         <v>985</v>
       </c>
-      <c r="F164" s="1">
+      <c r="F164" s="2">
         <v>45910</v>
       </c>
       <c r="G164" t="s">
@@ -10842,7 +10868,7 @@
       <c r="E165" t="s">
         <v>986</v>
       </c>
-      <c r="F165" s="1">
+      <c r="F165" s="2">
         <v>45917</v>
       </c>
       <c r="G165" t="s">
@@ -10860,7 +10886,7 @@
       <c r="L165" t="s">
         <v>1399</v>
       </c>
-      <c r="N165" s="1">
+      <c r="N165" s="2">
         <v>46204</v>
       </c>
       <c r="P165" t="s">
@@ -10886,7 +10912,7 @@
       <c r="E166" t="s">
         <v>987</v>
       </c>
-      <c r="F166" s="1">
+      <c r="F166" s="2">
         <v>45917</v>
       </c>
       <c r="G166" t="s">
@@ -10915,7 +10941,7 @@
       <c r="E167" t="s">
         <v>988</v>
       </c>
-      <c r="F167" s="1">
+      <c r="F167" s="2">
         <v>45917</v>
       </c>
       <c r="G167" t="s">
@@ -10944,7 +10970,7 @@
       <c r="E168" t="s">
         <v>989</v>
       </c>
-      <c r="F168" s="1">
+      <c r="F168" s="2">
         <v>45917</v>
       </c>
       <c r="G168" t="s">
@@ -10985,7 +11011,7 @@
       <c r="E169" t="s">
         <v>990</v>
       </c>
-      <c r="F169" s="1">
+      <c r="F169" s="2">
         <v>45917</v>
       </c>
       <c r="G169" t="s">
@@ -11003,7 +11029,7 @@
       <c r="L169" t="s">
         <v>1401</v>
       </c>
-      <c r="N169" s="1">
+      <c r="N169" s="2">
         <v>45973</v>
       </c>
       <c r="Q169" t="b">
@@ -11026,7 +11052,7 @@
       <c r="E170" t="s">
         <v>991</v>
       </c>
-      <c r="F170" s="1">
+      <c r="F170" s="2">
         <v>45917</v>
       </c>
       <c r="G170" t="s">
@@ -11061,7 +11087,7 @@
       <c r="E171" t="s">
         <v>992</v>
       </c>
-      <c r="F171" s="1">
+      <c r="F171" s="2">
         <v>45917</v>
       </c>
       <c r="G171" t="s">
@@ -11099,7 +11125,7 @@
       <c r="E172" t="s">
         <v>993</v>
       </c>
-      <c r="F172" s="1">
+      <c r="F172" s="2">
         <v>45917</v>
       </c>
       <c r="G172" t="s">
@@ -11128,7 +11154,7 @@
       <c r="E173" t="s">
         <v>994</v>
       </c>
-      <c r="F173" s="1">
+      <c r="F173" s="2">
         <v>45917</v>
       </c>
       <c r="G173" t="s">
@@ -11157,7 +11183,7 @@
       <c r="E174" t="s">
         <v>995</v>
       </c>
-      <c r="F174" s="1">
+      <c r="F174" s="2">
         <v>45917</v>
       </c>
       <c r="G174" t="s">
@@ -11172,7 +11198,7 @@
       <c r="L174" t="s">
         <v>1386</v>
       </c>
-      <c r="N174" s="1">
+      <c r="N174" s="2">
         <v>46195</v>
       </c>
       <c r="Q174" t="b">
@@ -11195,7 +11221,7 @@
       <c r="E175" t="s">
         <v>996</v>
       </c>
-      <c r="F175" s="1">
+      <c r="F175" s="2">
         <v>45917</v>
       </c>
       <c r="G175" t="s">
@@ -11216,7 +11242,7 @@
       <c r="L175" t="s">
         <v>1402</v>
       </c>
-      <c r="N175" s="1">
+      <c r="N175" s="2">
         <v>46122</v>
       </c>
       <c r="P175" t="s">
@@ -11242,7 +11268,7 @@
       <c r="E176" t="s">
         <v>900</v>
       </c>
-      <c r="F176" s="1">
+      <c r="F176" s="2">
         <v>45917</v>
       </c>
       <c r="G176" t="s">
@@ -11280,7 +11306,7 @@
       <c r="E177" t="s">
         <v>997</v>
       </c>
-      <c r="F177" s="1">
+      <c r="F177" s="2">
         <v>45917</v>
       </c>
       <c r="G177" t="s">
@@ -11301,7 +11327,7 @@
       <c r="L177" t="s">
         <v>1403</v>
       </c>
-      <c r="N177" s="1">
+      <c r="N177" s="2">
         <v>45961</v>
       </c>
       <c r="P177" t="s">
@@ -11327,7 +11353,7 @@
       <c r="E178" t="s">
         <v>998</v>
       </c>
-      <c r="F178" s="1">
+      <c r="F178" s="2">
         <v>45937</v>
       </c>
       <c r="G178" t="s">
@@ -11365,7 +11391,7 @@
       <c r="E179" t="s">
         <v>999</v>
       </c>
-      <c r="F179" s="1">
+      <c r="F179" s="2">
         <v>45937</v>
       </c>
       <c r="G179" t="s">
@@ -11394,7 +11420,7 @@
       <c r="E180" t="s">
         <v>1000</v>
       </c>
-      <c r="F180" s="1">
+      <c r="F180" s="2">
         <v>45937</v>
       </c>
       <c r="G180" t="s">
@@ -11432,7 +11458,7 @@
       <c r="E181" t="s">
         <v>1001</v>
       </c>
-      <c r="F181" s="1">
+      <c r="F181" s="2">
         <v>45937</v>
       </c>
       <c r="G181" t="s">
@@ -11461,7 +11487,7 @@
       <c r="E182" t="s">
         <v>1002</v>
       </c>
-      <c r="F182" s="1">
+      <c r="F182" s="2">
         <v>45937</v>
       </c>
       <c r="G182" t="s">
@@ -11490,7 +11516,7 @@
       <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="F183" s="1">
+      <c r="F183" s="2">
         <v>45937</v>
       </c>
       <c r="G183" t="s">
@@ -11528,7 +11554,7 @@
       <c r="D184" t="s">
         <v>774</v>
       </c>
-      <c r="F184" s="1">
+      <c r="F184" s="2">
         <v>45939</v>
       </c>
       <c r="G184" t="s">
@@ -11563,7 +11589,7 @@
       <c r="E185" t="s">
         <v>1004</v>
       </c>
-      <c r="F185" s="1">
+      <c r="F185" s="2">
         <v>45939</v>
       </c>
       <c r="G185" t="s">
@@ -11601,7 +11627,7 @@
       <c r="E186" t="s">
         <v>1005</v>
       </c>
-      <c r="F186" s="1">
+      <c r="F186" s="2">
         <v>45939</v>
       </c>
       <c r="G186" t="s">
@@ -11639,7 +11665,7 @@
       <c r="E187" t="s">
         <v>1006</v>
       </c>
-      <c r="F187" s="1">
+      <c r="F187" s="2">
         <v>45939</v>
       </c>
       <c r="G187" t="s">
@@ -11660,7 +11686,7 @@
       <c r="L187" t="s">
         <v>1404</v>
       </c>
-      <c r="N187" s="1">
+      <c r="N187" s="2">
         <v>46014</v>
       </c>
       <c r="O187">
@@ -11686,7 +11712,7 @@
       <c r="E188" t="s">
         <v>1007</v>
       </c>
-      <c r="F188" s="1">
+      <c r="F188" s="2">
         <v>45946</v>
       </c>
       <c r="G188" t="s">
@@ -11707,7 +11733,7 @@
       <c r="L188" t="s">
         <v>1405</v>
       </c>
-      <c r="N188" s="1">
+      <c r="N188" s="2">
         <v>45986</v>
       </c>
       <c r="P188" t="s">
@@ -11733,7 +11759,7 @@
       <c r="E189" t="s">
         <v>1008</v>
       </c>
-      <c r="F189" s="1">
+      <c r="F189" s="2">
         <v>45965</v>
       </c>
       <c r="G189" t="s">
@@ -11754,7 +11780,7 @@
       <c r="L189" t="s">
         <v>1406</v>
       </c>
-      <c r="N189" s="1">
+      <c r="N189" s="2">
         <v>46120</v>
       </c>
       <c r="Q189" t="b">
@@ -11777,7 +11803,7 @@
       <c r="E190" t="s">
         <v>1009</v>
       </c>
-      <c r="F190" s="1">
+      <c r="F190" s="2">
         <v>45965</v>
       </c>
       <c r="G190" t="s">
@@ -11798,7 +11824,7 @@
       <c r="L190" t="s">
         <v>1407</v>
       </c>
-      <c r="N190" s="1">
+      <c r="N190" s="2">
         <v>46072</v>
       </c>
       <c r="Q190" t="b">
@@ -11821,7 +11847,7 @@
       <c r="E191" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="1">
+      <c r="F191" s="2">
         <v>45967</v>
       </c>
       <c r="G191" t="s">
@@ -11842,7 +11868,7 @@
       <c r="L191" t="s">
         <v>1408</v>
       </c>
-      <c r="N191" s="1">
+      <c r="N191" s="2">
         <v>45972</v>
       </c>
       <c r="Q191" t="b">
@@ -11865,7 +11891,7 @@
       <c r="E192" t="s">
         <v>1011</v>
       </c>
-      <c r="F192" s="1">
+      <c r="F192" s="2">
         <v>45968</v>
       </c>
       <c r="G192" t="s">
@@ -11903,7 +11929,7 @@
       <c r="E193" t="s">
         <v>1012</v>
       </c>
-      <c r="F193" s="1">
+      <c r="F193" s="2">
         <v>45968</v>
       </c>
       <c r="G193" t="s">
@@ -11941,7 +11967,7 @@
       <c r="E194" t="s">
         <v>1013</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F194" s="2">
         <v>45968</v>
       </c>
       <c r="G194" t="s">
@@ -11970,7 +11996,7 @@
       <c r="E195" t="s">
         <v>1014</v>
       </c>
-      <c r="F195" s="1">
+      <c r="F195" s="2">
         <v>45971</v>
       </c>
       <c r="G195" t="s">
@@ -11991,7 +12017,7 @@
       <c r="L195" t="s">
         <v>1409</v>
       </c>
-      <c r="N195" s="1">
+      <c r="N195" s="2">
         <v>46157</v>
       </c>
       <c r="Q195" t="b">
@@ -12014,7 +12040,7 @@
       <c r="E196" t="s">
         <v>1015</v>
       </c>
-      <c r="F196" s="1">
+      <c r="F196" s="2">
         <v>45978</v>
       </c>
       <c r="G196" t="s">
@@ -12043,7 +12069,7 @@
       <c r="E197" t="s">
         <v>1016</v>
       </c>
-      <c r="F197" s="1">
+      <c r="F197" s="2">
         <v>45978</v>
       </c>
       <c r="G197" t="s">
@@ -12072,7 +12098,7 @@
       <c r="E198" t="s">
         <v>1017</v>
       </c>
-      <c r="F198" s="1">
+      <c r="F198" s="2">
         <v>45978</v>
       </c>
       <c r="G198" t="s">
@@ -12101,7 +12127,7 @@
       <c r="E199" t="s">
         <v>1018</v>
       </c>
-      <c r="F199" s="1">
+      <c r="F199" s="2">
         <v>45979</v>
       </c>
       <c r="G199" t="s">
@@ -12122,7 +12148,7 @@
       <c r="L199" t="s">
         <v>1410</v>
       </c>
-      <c r="N199" s="1">
+      <c r="N199" s="2">
         <v>46049</v>
       </c>
       <c r="Q199" t="b">
@@ -12145,7 +12171,7 @@
       <c r="E200" t="s">
         <v>1019</v>
       </c>
-      <c r="F200" s="1">
+      <c r="F200" s="2">
         <v>45986</v>
       </c>
       <c r="G200" t="s">
@@ -12166,7 +12192,7 @@
       <c r="L200" t="s">
         <v>1409</v>
       </c>
-      <c r="N200" s="1">
+      <c r="N200" s="2">
         <v>46156</v>
       </c>
       <c r="Q200" t="b">
@@ -12189,7 +12215,7 @@
       <c r="E201" t="s">
         <v>1020</v>
       </c>
-      <c r="F201" s="1">
+      <c r="F201" s="2">
         <v>45986</v>
       </c>
       <c r="G201" t="s">
@@ -12227,7 +12253,7 @@
       <c r="E202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" s="1">
+      <c r="F202" s="2">
         <v>45986</v>
       </c>
       <c r="G202" t="s">
@@ -12265,7 +12291,7 @@
       <c r="E203" t="s">
         <v>1022</v>
       </c>
-      <c r="F203" s="1">
+      <c r="F203" s="2">
         <v>45986</v>
       </c>
       <c r="G203" t="s">
@@ -12283,7 +12309,7 @@
       <c r="L203" t="s">
         <v>1411</v>
       </c>
-      <c r="N203" s="1">
+      <c r="N203" s="2">
         <v>46232</v>
       </c>
       <c r="Q203" t="b">
@@ -12306,7 +12332,7 @@
       <c r="E204" t="s">
         <v>1023</v>
       </c>
-      <c r="F204" s="1">
+      <c r="F204" s="2">
         <v>45986</v>
       </c>
       <c r="G204" t="s">
@@ -12344,7 +12370,7 @@
       <c r="E205" t="s">
         <v>1024</v>
       </c>
-      <c r="F205" s="1">
+      <c r="F205" s="2">
         <v>45986</v>
       </c>
       <c r="G205" t="s">
@@ -12382,7 +12408,7 @@
       <c r="E206" t="s">
         <v>1025</v>
       </c>
-      <c r="F206" s="1">
+      <c r="F206" s="2">
         <v>45986</v>
       </c>
       <c r="G206" t="s">
@@ -12411,7 +12437,7 @@
       <c r="E207" t="s">
         <v>1026</v>
       </c>
-      <c r="F207" s="1">
+      <c r="F207" s="2">
         <v>45986</v>
       </c>
       <c r="G207" t="s">
@@ -12432,7 +12458,7 @@
       <c r="L207" t="s">
         <v>1412</v>
       </c>
-      <c r="N207" s="1">
+      <c r="N207" s="2">
         <v>46153</v>
       </c>
       <c r="Q207" t="b">
@@ -12455,7 +12481,7 @@
       <c r="E208" t="s">
         <v>1027</v>
       </c>
-      <c r="F208" s="1">
+      <c r="F208" s="2">
         <v>45986</v>
       </c>
       <c r="G208" t="s">
@@ -12476,7 +12502,7 @@
       <c r="L208" t="s">
         <v>1413</v>
       </c>
-      <c r="N208" s="1">
+      <c r="N208" s="2">
         <v>46031</v>
       </c>
       <c r="Q208" t="b">
@@ -12499,7 +12525,7 @@
       <c r="E209" t="s">
         <v>1028</v>
       </c>
-      <c r="F209" s="1">
+      <c r="F209" s="2">
         <v>46000</v>
       </c>
       <c r="G209" t="s">
@@ -12520,7 +12546,7 @@
       <c r="L209" t="s">
         <v>1414</v>
       </c>
-      <c r="N209" s="1">
+      <c r="N209" s="2">
         <v>46191</v>
       </c>
       <c r="Q209" t="b">
@@ -12543,7 +12569,7 @@
       <c r="E210" t="s">
         <v>1029</v>
       </c>
-      <c r="F210" s="1">
+      <c r="F210" s="2">
         <v>46000</v>
       </c>
       <c r="G210" t="s">
@@ -12581,7 +12607,7 @@
       <c r="E211" t="s">
         <v>1030</v>
       </c>
-      <c r="F211" s="1">
+      <c r="F211" s="2">
         <v>46000</v>
       </c>
       <c r="G211" t="s">
@@ -12610,7 +12636,7 @@
       <c r="E212" t="s">
         <v>1031</v>
       </c>
-      <c r="F212" s="1">
+      <c r="F212" s="2">
         <v>46000</v>
       </c>
       <c r="G212" t="s">
@@ -12639,7 +12665,7 @@
       <c r="E213" t="s">
         <v>1032</v>
       </c>
-      <c r="F213" s="1">
+      <c r="F213" s="2">
         <v>46007</v>
       </c>
       <c r="G213" t="s">
@@ -12677,7 +12703,7 @@
       <c r="E214" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="1">
+      <c r="F214" s="2">
         <v>46007</v>
       </c>
       <c r="G214" t="s">
@@ -12698,7 +12724,7 @@
       <c r="L214" t="s">
         <v>1415</v>
       </c>
-      <c r="N214" s="1">
+      <c r="N214" s="2">
         <v>46021</v>
       </c>
       <c r="O214">
@@ -12724,7 +12750,7 @@
       <c r="E215" t="s">
         <v>1034</v>
       </c>
-      <c r="F215" s="1">
+      <c r="F215" s="2">
         <v>46007</v>
       </c>
       <c r="G215" t="s">
@@ -12762,7 +12788,7 @@
       <c r="E216" t="s">
         <v>1035</v>
       </c>
-      <c r="F216" s="1">
+      <c r="F216" s="2">
         <v>46010</v>
       </c>
       <c r="G216" t="s">
@@ -12791,7 +12817,7 @@
       <c r="E217" t="s">
         <v>1036</v>
       </c>
-      <c r="F217" s="1">
+      <c r="F217" s="2">
         <v>46010</v>
       </c>
       <c r="G217" t="s">
@@ -12812,7 +12838,7 @@
       <c r="L217" t="s">
         <v>1416</v>
       </c>
-      <c r="N217" s="1">
+      <c r="N217" s="2">
         <v>46052</v>
       </c>
       <c r="Q217" t="b">
@@ -12835,7 +12861,7 @@
       <c r="E218" t="s">
         <v>1037</v>
       </c>
-      <c r="F218" s="1">
+      <c r="F218" s="2">
         <v>46010</v>
       </c>
       <c r="G218" t="s">
@@ -12853,7 +12879,7 @@
       <c r="K218" t="s">
         <v>1359</v>
       </c>
-      <c r="N218" s="1">
+      <c r="N218" s="2">
         <v>46176</v>
       </c>
       <c r="P218" t="s">
@@ -12879,7 +12905,7 @@
       <c r="E219" t="s">
         <v>1038</v>
       </c>
-      <c r="F219" s="1">
+      <c r="F219" s="2">
         <v>46010</v>
       </c>
       <c r="G219" t="s">
@@ -12897,7 +12923,7 @@
       <c r="L219" t="s">
         <v>1417</v>
       </c>
-      <c r="N219" s="1">
+      <c r="N219" s="2">
         <v>46176</v>
       </c>
       <c r="P219" t="s">
@@ -12923,7 +12949,7 @@
       <c r="E220" t="s">
         <v>1039</v>
       </c>
-      <c r="F220" s="1">
+      <c r="F220" s="2">
         <v>46010</v>
       </c>
       <c r="G220" t="s">
@@ -12944,7 +12970,7 @@
       <c r="L220" t="s">
         <v>1418</v>
       </c>
-      <c r="N220" s="1">
+      <c r="N220" s="2">
         <v>46164</v>
       </c>
       <c r="Q220" t="b">
@@ -12967,7 +12993,7 @@
       <c r="E221" t="s">
         <v>1040</v>
       </c>
-      <c r="F221" s="1">
+      <c r="F221" s="2">
         <v>46028</v>
       </c>
       <c r="G221" t="s">
@@ -12982,7 +13008,7 @@
       <c r="L221" t="s">
         <v>1419</v>
       </c>
-      <c r="N221" s="1">
+      <c r="N221" s="2">
         <v>46184</v>
       </c>
       <c r="Q221" t="b">
@@ -13005,7 +13031,7 @@
       <c r="E222" t="s">
         <v>1041</v>
       </c>
-      <c r="F222" s="1">
+      <c r="F222" s="2">
         <v>46028</v>
       </c>
       <c r="G222" t="s">
@@ -13020,7 +13046,7 @@
       <c r="L222" t="s">
         <v>1383</v>
       </c>
-      <c r="N222" s="1">
+      <c r="N222" s="2">
         <v>46232</v>
       </c>
       <c r="Q222" t="b">
@@ -13043,7 +13069,7 @@
       <c r="E223" t="s">
         <v>1042</v>
       </c>
-      <c r="F223" s="1">
+      <c r="F223" s="2">
         <v>46028</v>
       </c>
       <c r="G223" t="s">
@@ -13058,7 +13084,7 @@
       <c r="L223" t="s">
         <v>1383</v>
       </c>
-      <c r="N223" s="1">
+      <c r="N223" s="2">
         <v>46232</v>
       </c>
       <c r="Q223" t="b">
@@ -13081,7 +13107,7 @@
       <c r="E224" t="s">
         <v>1043</v>
       </c>
-      <c r="F224" s="1">
+      <c r="F224" s="2">
         <v>46028</v>
       </c>
       <c r="G224" t="s">
@@ -13099,7 +13125,7 @@
       <c r="L224" t="s">
         <v>1383</v>
       </c>
-      <c r="N224" s="1">
+      <c r="N224" s="2">
         <v>46232</v>
       </c>
       <c r="Q224" t="b">
@@ -13122,7 +13148,7 @@
       <c r="E225" t="s">
         <v>1044</v>
       </c>
-      <c r="F225" s="1">
+      <c r="F225" s="2">
         <v>46028</v>
       </c>
       <c r="G225" t="s">
@@ -13137,7 +13163,7 @@
       <c r="L225" t="s">
         <v>1383</v>
       </c>
-      <c r="N225" s="1">
+      <c r="N225" s="2">
         <v>46232</v>
       </c>
       <c r="Q225" t="b">
@@ -13160,7 +13186,7 @@
       <c r="E226" t="s">
         <v>1045</v>
       </c>
-      <c r="F226" s="1">
+      <c r="F226" s="2">
         <v>46028</v>
       </c>
       <c r="G226" t="s">
@@ -13175,7 +13201,7 @@
       <c r="L226" t="s">
         <v>1383</v>
       </c>
-      <c r="N226" s="1">
+      <c r="N226" s="2">
         <v>46232</v>
       </c>
       <c r="Q226" t="b">
@@ -13198,7 +13224,7 @@
       <c r="E227" t="s">
         <v>1046</v>
       </c>
-      <c r="F227" s="1">
+      <c r="F227" s="2">
         <v>46028</v>
       </c>
       <c r="G227" t="s">
@@ -13213,7 +13239,7 @@
       <c r="L227" t="s">
         <v>1383</v>
       </c>
-      <c r="N227" s="1">
+      <c r="N227" s="2">
         <v>46232</v>
       </c>
       <c r="Q227" t="b">
@@ -13236,7 +13262,7 @@
       <c r="E228" t="s">
         <v>1047</v>
       </c>
-      <c r="F228" s="1">
+      <c r="F228" s="2">
         <v>46028</v>
       </c>
       <c r="G228" t="s">
@@ -13254,7 +13280,7 @@
       <c r="L228" t="s">
         <v>1383</v>
       </c>
-      <c r="N228" s="1">
+      <c r="N228" s="2">
         <v>46232</v>
       </c>
       <c r="Q228" t="b">
@@ -13277,7 +13303,7 @@
       <c r="E229" t="s">
         <v>1048</v>
       </c>
-      <c r="F229" s="1">
+      <c r="F229" s="2">
         <v>46028</v>
       </c>
       <c r="G229" t="s">
@@ -13292,7 +13318,7 @@
       <c r="L229" t="s">
         <v>1420</v>
       </c>
-      <c r="N229" s="1">
+      <c r="N229" s="2">
         <v>46191</v>
       </c>
       <c r="Q229" t="b">
@@ -13315,7 +13341,7 @@
       <c r="E230" t="s">
         <v>1049</v>
       </c>
-      <c r="F230" s="1">
+      <c r="F230" s="2">
         <v>46028</v>
       </c>
       <c r="G230" t="s">
@@ -13336,7 +13362,7 @@
       <c r="L230" t="s">
         <v>1395</v>
       </c>
-      <c r="N230" s="1">
+      <c r="N230" s="2">
         <v>46225</v>
       </c>
       <c r="Q230" t="b">
@@ -13359,7 +13385,7 @@
       <c r="E231" t="s">
         <v>1050</v>
       </c>
-      <c r="F231" s="1">
+      <c r="F231" s="2">
         <v>46028</v>
       </c>
       <c r="G231" t="s">
@@ -13380,7 +13406,7 @@
       <c r="L231" t="s">
         <v>1421</v>
       </c>
-      <c r="N231" s="1">
+      <c r="N231" s="2">
         <v>46063</v>
       </c>
       <c r="Q231" t="b">
@@ -13403,7 +13429,7 @@
       <c r="E232" t="s">
         <v>1051</v>
       </c>
-      <c r="F232" s="1">
+      <c r="F232" s="2">
         <v>46028</v>
       </c>
       <c r="G232" t="s">
@@ -13432,7 +13458,7 @@
       <c r="E233" t="s">
         <v>1052</v>
       </c>
-      <c r="F233" s="1">
+      <c r="F233" s="2">
         <v>46028</v>
       </c>
       <c r="G233" t="s">
@@ -13461,7 +13487,7 @@
       <c r="E234" t="s">
         <v>1053</v>
       </c>
-      <c r="F234" s="1">
+      <c r="F234" s="2">
         <v>46028</v>
       </c>
       <c r="G234" t="s">
@@ -13482,7 +13508,7 @@
       <c r="L234" t="s">
         <v>1421</v>
       </c>
-      <c r="N234" s="1">
+      <c r="N234" s="2">
         <v>46063</v>
       </c>
       <c r="P234" t="s">
@@ -13508,7 +13534,7 @@
       <c r="E235" t="s">
         <v>1054</v>
       </c>
-      <c r="F235" s="1">
+      <c r="F235" s="2">
         <v>46028</v>
       </c>
       <c r="G235" t="s">
@@ -13529,7 +13555,7 @@
       <c r="L235" t="s">
         <v>1421</v>
       </c>
-      <c r="N235" s="1">
+      <c r="N235" s="2">
         <v>46063</v>
       </c>
       <c r="P235" t="s">
@@ -13555,7 +13581,7 @@
       <c r="E236" t="s">
         <v>1055</v>
       </c>
-      <c r="F236" s="1">
+      <c r="F236" s="2">
         <v>46028</v>
       </c>
       <c r="G236" t="s">
@@ -13576,7 +13602,7 @@
       <c r="L236" t="s">
         <v>1422</v>
       </c>
-      <c r="N236" s="1">
+      <c r="N236" s="2">
         <v>46114</v>
       </c>
       <c r="Q236" t="b">
@@ -13599,7 +13625,7 @@
       <c r="E237" t="s">
         <v>1056</v>
       </c>
-      <c r="F237" s="1">
+      <c r="F237" s="2">
         <v>46028</v>
       </c>
       <c r="G237" t="s">
@@ -13617,7 +13643,7 @@
       <c r="L237" t="s">
         <v>1423</v>
       </c>
-      <c r="N237" s="1">
+      <c r="N237" s="2">
         <v>46210</v>
       </c>
       <c r="P237" t="s">
@@ -13643,7 +13669,7 @@
       <c r="E238" t="s">
         <v>1057</v>
       </c>
-      <c r="F238" s="1">
+      <c r="F238" s="2">
         <v>46028</v>
       </c>
       <c r="G238" t="s">
@@ -13672,7 +13698,7 @@
       <c r="E239" t="s">
         <v>1058</v>
       </c>
-      <c r="F239" s="1">
+      <c r="F239" s="2">
         <v>46036</v>
       </c>
       <c r="G239" t="s">
@@ -13690,7 +13716,7 @@
       <c r="L239" t="s">
         <v>1424</v>
       </c>
-      <c r="N239" s="1">
+      <c r="N239" s="2">
         <v>46052</v>
       </c>
       <c r="Q239" t="b">
@@ -13713,7 +13739,7 @@
       <c r="E240" t="s">
         <v>1059</v>
       </c>
-      <c r="F240" s="1">
+      <c r="F240" s="2">
         <v>46036</v>
       </c>
       <c r="G240" t="s">
@@ -13742,7 +13768,7 @@
       <c r="E241" t="s">
         <v>1060</v>
       </c>
-      <c r="F241" s="1">
+      <c r="F241" s="2">
         <v>46036</v>
       </c>
       <c r="G241" t="s">
@@ -13771,7 +13797,7 @@
       <c r="E242" t="s">
         <v>1061</v>
       </c>
-      <c r="F242" s="1">
+      <c r="F242" s="2">
         <v>46036</v>
       </c>
       <c r="G242" t="s">
@@ -13809,7 +13835,7 @@
       <c r="E243" t="s">
         <v>1062</v>
       </c>
-      <c r="F243" s="1">
+      <c r="F243" s="2">
         <v>46048</v>
       </c>
       <c r="G243" t="s">
@@ -13838,7 +13864,7 @@
       <c r="E244" t="s">
         <v>1063</v>
       </c>
-      <c r="F244" s="1">
+      <c r="F244" s="2">
         <v>46048</v>
       </c>
       <c r="G244" t="s">
@@ -13856,7 +13882,7 @@
       <c r="K244" t="s">
         <v>1359</v>
       </c>
-      <c r="N244" s="1">
+      <c r="N244" s="2">
         <v>46063</v>
       </c>
       <c r="Q244" t="b">
@@ -13879,7 +13905,7 @@
       <c r="E245" t="s">
         <v>1064</v>
       </c>
-      <c r="F245" s="1">
+      <c r="F245" s="2">
         <v>46048</v>
       </c>
       <c r="G245" t="s">
@@ -13900,7 +13926,7 @@
       <c r="L245" t="s">
         <v>1425</v>
       </c>
-      <c r="N245" s="1">
+      <c r="N245" s="2">
         <v>46063</v>
       </c>
       <c r="Q245" t="b">
@@ -13923,7 +13949,7 @@
       <c r="E246" t="s">
         <v>1065</v>
       </c>
-      <c r="F246" s="1">
+      <c r="F246" s="2">
         <v>46050</v>
       </c>
       <c r="G246" t="s">
@@ -13941,7 +13967,7 @@
       <c r="L246" t="s">
         <v>1426</v>
       </c>
-      <c r="N246" s="1">
+      <c r="N246" s="2">
         <v>46191</v>
       </c>
       <c r="Q246" t="b">
@@ -13964,7 +13990,7 @@
       <c r="E247" t="s">
         <v>1066</v>
       </c>
-      <c r="F247" s="1">
+      <c r="F247" s="2">
         <v>46050</v>
       </c>
       <c r="G247" t="s">
@@ -13993,7 +14019,7 @@
       <c r="E248" t="s">
         <v>1067</v>
       </c>
-      <c r="F248" s="1">
+      <c r="F248" s="2">
         <v>46050</v>
       </c>
       <c r="G248" t="s">
@@ -14022,7 +14048,7 @@
       <c r="E249" t="s">
         <v>1068</v>
       </c>
-      <c r="F249" s="1">
+      <c r="F249" s="2">
         <v>46050</v>
       </c>
       <c r="G249" t="s">
@@ -14060,7 +14086,7 @@
       <c r="E250" t="s">
         <v>1069</v>
       </c>
-      <c r="F250" s="1">
+      <c r="F250" s="2">
         <v>46063</v>
       </c>
       <c r="G250" t="s">
@@ -14098,7 +14124,7 @@
       <c r="E251" t="s">
         <v>1070</v>
       </c>
-      <c r="F251" s="1">
+      <c r="F251" s="2">
         <v>46063</v>
       </c>
       <c r="G251" t="s">
@@ -14127,7 +14153,7 @@
       <c r="E252" t="s">
         <v>1071</v>
       </c>
-      <c r="F252" s="1">
+      <c r="F252" s="2">
         <v>46063</v>
       </c>
       <c r="G252" t="s">
@@ -14156,7 +14182,7 @@
       <c r="E253" t="s">
         <v>1072</v>
       </c>
-      <c r="F253" s="1">
+      <c r="F253" s="2">
         <v>46063</v>
       </c>
       <c r="G253" t="s">
@@ -14177,7 +14203,7 @@
       <c r="L253" t="s">
         <v>1395</v>
       </c>
-      <c r="N253" s="1">
+      <c r="N253" s="2">
         <v>46225</v>
       </c>
       <c r="Q253" t="b">
@@ -14200,7 +14226,7 @@
       <c r="E254" t="s">
         <v>1073</v>
       </c>
-      <c r="F254" s="1">
+      <c r="F254" s="2">
         <v>46063</v>
       </c>
       <c r="G254" t="s">
@@ -14238,7 +14264,7 @@
       <c r="E255" t="s">
         <v>1074</v>
       </c>
-      <c r="F255" s="1">
+      <c r="F255" s="2">
         <v>46063</v>
       </c>
       <c r="G255" t="s">
@@ -14259,7 +14285,7 @@
       <c r="L255" t="s">
         <v>1388</v>
       </c>
-      <c r="N255" s="1">
+      <c r="N255" s="2">
         <v>46135</v>
       </c>
       <c r="Q255" t="b">
@@ -14282,7 +14308,7 @@
       <c r="E256" t="s">
         <v>1075</v>
       </c>
-      <c r="F256" s="1">
+      <c r="F256" s="2">
         <v>46063</v>
       </c>
       <c r="G256" t="s">
@@ -14300,7 +14326,7 @@
       <c r="K256" t="s">
         <v>1357</v>
       </c>
-      <c r="N256" s="1">
+      <c r="N256" s="2">
         <v>46086</v>
       </c>
       <c r="O256">
@@ -14326,7 +14352,7 @@
       <c r="E257" t="s">
         <v>1076</v>
       </c>
-      <c r="F257" s="1">
+      <c r="F257" s="2">
         <v>46063</v>
       </c>
       <c r="G257" t="s">
@@ -14355,7 +14381,7 @@
       <c r="E258" t="s">
         <v>1077</v>
       </c>
-      <c r="F258" s="1">
+      <c r="F258" s="2">
         <v>46063</v>
       </c>
       <c r="G258" t="s">
@@ -14384,7 +14410,7 @@
       <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="F259" s="1">
+      <c r="F259" s="2">
         <v>46063</v>
       </c>
       <c r="G259" t="s">
@@ -14405,7 +14431,7 @@
       <c r="L259" t="s">
         <v>1388</v>
       </c>
-      <c r="N259" s="1">
+      <c r="N259" s="2">
         <v>46135</v>
       </c>
       <c r="Q259" t="b">
@@ -14428,7 +14454,7 @@
       <c r="E260" t="s">
         <v>1079</v>
       </c>
-      <c r="F260" s="1">
+      <c r="F260" s="2">
         <v>46063</v>
       </c>
       <c r="G260" t="s">
@@ -14449,7 +14475,7 @@
       <c r="L260" t="s">
         <v>1388</v>
       </c>
-      <c r="N260" s="1">
+      <c r="N260" s="2">
         <v>46147</v>
       </c>
       <c r="Q260" t="b">
@@ -14472,7 +14498,7 @@
       <c r="E261" t="s">
         <v>1080</v>
       </c>
-      <c r="F261" s="1">
+      <c r="F261" s="2">
         <v>46063</v>
       </c>
       <c r="G261" t="s">
@@ -14493,7 +14519,7 @@
       <c r="L261" t="s">
         <v>1427</v>
       </c>
-      <c r="N261" s="1">
+      <c r="N261" s="2">
         <v>46225</v>
       </c>
       <c r="Q261" t="b">
@@ -14516,7 +14542,7 @@
       <c r="E262" t="s">
         <v>1081</v>
       </c>
-      <c r="F262" s="1">
+      <c r="F262" s="2">
         <v>46063</v>
       </c>
       <c r="G262" t="s">
@@ -14534,7 +14560,7 @@
       <c r="L262" t="s">
         <v>1428</v>
       </c>
-      <c r="N262" s="1">
+      <c r="N262" s="2">
         <v>46113</v>
       </c>
       <c r="P262" t="s">
@@ -14560,7 +14586,7 @@
       <c r="E263" t="s">
         <v>1082</v>
       </c>
-      <c r="F263" s="1">
+      <c r="F263" s="2">
         <v>46063</v>
       </c>
       <c r="G263" t="s">
@@ -14589,7 +14615,7 @@
       <c r="E264" t="s">
         <v>1083</v>
       </c>
-      <c r="F264" s="1">
+      <c r="F264" s="2">
         <v>46063</v>
       </c>
       <c r="G264" t="s">
@@ -14610,7 +14636,7 @@
       <c r="L264" t="s">
         <v>1388</v>
       </c>
-      <c r="N264" s="1">
+      <c r="N264" s="2">
         <v>46225</v>
       </c>
       <c r="Q264" t="b">
@@ -14633,7 +14659,7 @@
       <c r="E265" t="s">
         <v>1084</v>
       </c>
-      <c r="F265" s="1">
+      <c r="F265" s="2">
         <v>46063</v>
       </c>
       <c r="G265" t="s">
@@ -14654,7 +14680,7 @@
       <c r="L265" t="s">
         <v>1395</v>
       </c>
-      <c r="N265" s="1">
+      <c r="N265" s="2">
         <v>46225</v>
       </c>
       <c r="Q265" t="b">
@@ -14677,7 +14703,7 @@
       <c r="E266" t="s">
         <v>1085</v>
       </c>
-      <c r="F266" s="1">
+      <c r="F266" s="2">
         <v>46063</v>
       </c>
       <c r="G266" t="s">
@@ -14698,7 +14724,7 @@
       <c r="L266" t="s">
         <v>1388</v>
       </c>
-      <c r="N266" s="1">
+      <c r="N266" s="2">
         <v>46147</v>
       </c>
       <c r="Q266" t="b">
@@ -14721,7 +14747,7 @@
       <c r="E267" t="s">
         <v>1086</v>
       </c>
-      <c r="F267" s="1">
+      <c r="F267" s="2">
         <v>46063</v>
       </c>
       <c r="G267" t="s">
@@ -14759,7 +14785,7 @@
       <c r="E268" t="s">
         <v>1087</v>
       </c>
-      <c r="F268" s="1">
+      <c r="F268" s="2">
         <v>46063</v>
       </c>
       <c r="G268" t="s">
@@ -14794,7 +14820,7 @@
       <c r="D269" t="s">
         <v>798</v>
       </c>
-      <c r="F269" s="1">
+      <c r="F269" s="2">
         <v>46063</v>
       </c>
       <c r="G269" t="s">
@@ -14832,7 +14858,7 @@
       <c r="E270" t="s">
         <v>1088</v>
       </c>
-      <c r="F270" s="1">
+      <c r="F270" s="2">
         <v>46063</v>
       </c>
       <c r="G270" t="s">
@@ -14870,7 +14896,7 @@
       <c r="E271" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="1">
+      <c r="F271" s="2">
         <v>46063</v>
       </c>
       <c r="G271" t="s">
@@ -14908,7 +14934,7 @@
       <c r="E272" t="s">
         <v>1090</v>
       </c>
-      <c r="F272" s="1">
+      <c r="F272" s="2">
         <v>46063</v>
       </c>
       <c r="G272" t="s">
@@ -14926,7 +14952,7 @@
       <c r="L272" t="s">
         <v>1429</v>
       </c>
-      <c r="N272" s="1">
+      <c r="N272" s="2">
         <v>46185</v>
       </c>
       <c r="O272" t="s">
@@ -14952,7 +14978,7 @@
       <c r="E273" t="s">
         <v>1091</v>
       </c>
-      <c r="F273" s="1">
+      <c r="F273" s="2">
         <v>46063</v>
       </c>
       <c r="G273" t="s">
@@ -14981,7 +15007,7 @@
       <c r="E274" t="s">
         <v>1092</v>
       </c>
-      <c r="F274" s="1">
+      <c r="F274" s="2">
         <v>46063</v>
       </c>
       <c r="G274" t="s">
@@ -14996,7 +15022,7 @@
       <c r="L274" t="s">
         <v>1383</v>
       </c>
-      <c r="N274" s="1">
+      <c r="N274" s="2">
         <v>46232</v>
       </c>
       <c r="Q274" t="b">
@@ -15019,7 +15045,7 @@
       <c r="E275" t="s">
         <v>1093</v>
       </c>
-      <c r="F275" s="1">
+      <c r="F275" s="2">
         <v>46063</v>
       </c>
       <c r="G275" t="s">
@@ -15048,7 +15074,7 @@
       <c r="E276" t="s">
         <v>1094</v>
       </c>
-      <c r="F276" s="1">
+      <c r="F276" s="2">
         <v>46063</v>
       </c>
       <c r="G276" t="s">
@@ -15086,7 +15112,7 @@
       <c r="E277" t="s">
         <v>1095</v>
       </c>
-      <c r="F277" s="1">
+      <c r="F277" s="2">
         <v>46063</v>
       </c>
       <c r="G277" t="s">
@@ -15124,7 +15150,7 @@
       <c r="E278" t="s">
         <v>1096</v>
       </c>
-      <c r="F278" s="1">
+      <c r="F278" s="2">
         <v>46077</v>
       </c>
       <c r="G278" t="s">
@@ -15145,7 +15171,7 @@
       <c r="L278" t="s">
         <v>1395</v>
       </c>
-      <c r="N278" s="1">
+      <c r="N278" s="2">
         <v>46225</v>
       </c>
       <c r="Q278" t="b">
@@ -15168,7 +15194,7 @@
       <c r="E279" t="s">
         <v>1097</v>
       </c>
-      <c r="F279" s="1">
+      <c r="F279" s="2">
         <v>46077</v>
       </c>
       <c r="G279" t="s">
@@ -15209,7 +15235,7 @@
       <c r="E280" t="s">
         <v>1098</v>
       </c>
-      <c r="F280" s="1">
+      <c r="F280" s="2">
         <v>46085</v>
       </c>
       <c r="G280" t="s">
@@ -15247,7 +15273,7 @@
       <c r="E281" t="s">
         <v>1099</v>
       </c>
-      <c r="F281" s="1">
+      <c r="F281" s="2">
         <v>46085</v>
       </c>
       <c r="G281" t="s">
@@ -15288,7 +15314,7 @@
       <c r="E282" t="s">
         <v>1100</v>
       </c>
-      <c r="F282" s="1">
+      <c r="F282" s="2">
         <v>46090</v>
       </c>
       <c r="G282" t="s">
@@ -15326,7 +15352,7 @@
       <c r="E283" t="s">
         <v>1101</v>
       </c>
-      <c r="F283" s="1">
+      <c r="F283" s="2">
         <v>46100</v>
       </c>
       <c r="G283" t="s">
@@ -15355,7 +15381,7 @@
       <c r="E284" t="s">
         <v>1102</v>
       </c>
-      <c r="F284" s="1">
+      <c r="F284" s="2">
         <v>46100</v>
       </c>
       <c r="G284" t="s">
@@ -15384,7 +15410,7 @@
       <c r="E285" t="s">
         <v>1103</v>
       </c>
-      <c r="F285" s="1">
+      <c r="F285" s="2">
         <v>46100</v>
       </c>
       <c r="G285" t="s">
@@ -15413,7 +15439,7 @@
       <c r="E286" t="s">
         <v>1104</v>
       </c>
-      <c r="F286" s="1">
+      <c r="F286" s="2">
         <v>46100</v>
       </c>
       <c r="G286" t="s">
@@ -15442,7 +15468,7 @@
       <c r="E287" t="s">
         <v>1105</v>
       </c>
-      <c r="F287" s="1">
+      <c r="F287" s="2">
         <v>46107</v>
       </c>
       <c r="G287" t="s">
@@ -15471,7 +15497,7 @@
       <c r="E288" t="s">
         <v>1106</v>
       </c>
-      <c r="F288" s="1">
+      <c r="F288" s="2">
         <v>46107</v>
       </c>
       <c r="G288" t="s">
@@ -15492,7 +15518,7 @@
       <c r="L288" t="s">
         <v>1388</v>
       </c>
-      <c r="N288" s="1">
+      <c r="N288" s="2">
         <v>46135</v>
       </c>
       <c r="Q288" t="b">
@@ -15515,7 +15541,7 @@
       <c r="E289" t="s">
         <v>1107</v>
       </c>
-      <c r="F289" s="1">
+      <c r="F289" s="2">
         <v>46107</v>
       </c>
       <c r="G289" t="s">
@@ -15544,7 +15570,7 @@
       <c r="E290" t="s">
         <v>1108</v>
       </c>
-      <c r="F290" s="1">
+      <c r="F290" s="2">
         <v>46107</v>
       </c>
       <c r="G290" t="s">
@@ -15565,7 +15591,7 @@
       <c r="L290" t="s">
         <v>1388</v>
       </c>
-      <c r="N290" s="1">
+      <c r="N290" s="2">
         <v>46127</v>
       </c>
       <c r="Q290" t="b">
@@ -15588,7 +15614,7 @@
       <c r="E291" t="s">
         <v>1109</v>
       </c>
-      <c r="F291" s="1">
+      <c r="F291" s="2">
         <v>46107</v>
       </c>
       <c r="G291" t="s">
@@ -15609,7 +15635,7 @@
       <c r="L291" t="s">
         <v>1430</v>
       </c>
-      <c r="N291" s="1">
+      <c r="N291" s="2">
         <v>46127</v>
       </c>
       <c r="Q291" t="b">
@@ -15632,7 +15658,7 @@
       <c r="E292" t="s">
         <v>1110</v>
       </c>
-      <c r="F292" s="1">
+      <c r="F292" s="2">
         <v>46112</v>
       </c>
       <c r="G292" t="s">
@@ -15670,7 +15696,7 @@
       <c r="E293" t="s">
         <v>1111</v>
       </c>
-      <c r="F293" s="1">
+      <c r="F293" s="2">
         <v>46125</v>
       </c>
       <c r="G293" t="s">
@@ -15708,7 +15734,7 @@
       <c r="E294" t="s">
         <v>1112</v>
       </c>
-      <c r="F294" s="1">
+      <c r="F294" s="2">
         <v>46125</v>
       </c>
       <c r="G294" t="s">
@@ -15743,7 +15769,7 @@
       <c r="E295" t="s">
         <v>1113</v>
       </c>
-      <c r="F295" s="1">
+      <c r="F295" s="2">
         <v>46125</v>
       </c>
       <c r="G295" t="s">
@@ -15778,7 +15804,7 @@
       <c r="E296" t="s">
         <v>1114</v>
       </c>
-      <c r="F296" s="1">
+      <c r="F296" s="2">
         <v>46125</v>
       </c>
       <c r="G296" t="s">
@@ -15813,7 +15839,7 @@
       <c r="E297" t="s">
         <v>1115</v>
       </c>
-      <c r="F297" s="1">
+      <c r="F297" s="2">
         <v>46125</v>
       </c>
       <c r="G297" t="s">
@@ -15825,7 +15851,7 @@
       <c r="K297" t="s">
         <v>1359</v>
       </c>
-      <c r="N297" s="1">
+      <c r="N297" s="2">
         <v>46183</v>
       </c>
       <c r="O297">
@@ -15851,7 +15877,7 @@
       <c r="E298" t="s">
         <v>1116</v>
       </c>
-      <c r="F298" s="1">
+      <c r="F298" s="2">
         <v>46125</v>
       </c>
       <c r="G298" t="s">
@@ -15869,7 +15895,7 @@
       <c r="K298" t="s">
         <v>1359</v>
       </c>
-      <c r="N298" s="1">
+      <c r="N298" s="2">
         <v>46183</v>
       </c>
       <c r="Q298" t="b">
@@ -15892,7 +15918,7 @@
       <c r="E299" t="s">
         <v>1117</v>
       </c>
-      <c r="F299" s="1">
+      <c r="F299" s="2">
         <v>46125</v>
       </c>
       <c r="G299" t="s">
@@ -15913,7 +15939,7 @@
       <c r="L299" t="s">
         <v>1388</v>
       </c>
-      <c r="N299" s="1">
+      <c r="N299" s="2">
         <v>46225</v>
       </c>
       <c r="Q299" t="b">
@@ -15936,7 +15962,7 @@
       <c r="E300" t="s">
         <v>1118</v>
       </c>
-      <c r="F300" s="1">
+      <c r="F300" s="2">
         <v>46125</v>
       </c>
       <c r="G300" t="s">
@@ -15957,7 +15983,7 @@
       <c r="L300" t="s">
         <v>1388</v>
       </c>
-      <c r="N300" s="1">
+      <c r="N300" s="2">
         <v>46211</v>
       </c>
       <c r="Q300" t="b">
@@ -15980,7 +16006,7 @@
       <c r="E301" t="s">
         <v>1119</v>
       </c>
-      <c r="F301" s="1">
+      <c r="F301" s="2">
         <v>46125</v>
       </c>
       <c r="G301" t="s">
@@ -16001,7 +16027,7 @@
       <c r="L301" t="s">
         <v>1388</v>
       </c>
-      <c r="N301" s="1">
+      <c r="N301" s="2">
         <v>46227</v>
       </c>
       <c r="Q301" t="b">
@@ -16024,7 +16050,7 @@
       <c r="E302" t="s">
         <v>1120</v>
       </c>
-      <c r="F302" s="1">
+      <c r="F302" s="2">
         <v>46125</v>
       </c>
       <c r="G302" t="s">
@@ -16062,7 +16088,7 @@
       <c r="E303" t="s">
         <v>1121</v>
       </c>
-      <c r="F303" s="1">
+      <c r="F303" s="2">
         <v>46125</v>
       </c>
       <c r="G303" t="s">
@@ -16100,7 +16126,7 @@
       <c r="E304" t="s">
         <v>1122</v>
       </c>
-      <c r="F304" s="1">
+      <c r="F304" s="2">
         <v>46125</v>
       </c>
       <c r="G304" t="s">
@@ -16138,7 +16164,7 @@
       <c r="E305" t="s">
         <v>1123</v>
       </c>
-      <c r="F305" s="1">
+      <c r="F305" s="2">
         <v>46125</v>
       </c>
       <c r="G305" t="s">
@@ -16159,7 +16185,7 @@
       <c r="L305" t="s">
         <v>1431</v>
       </c>
-      <c r="N305" s="1">
+      <c r="N305" s="2">
         <v>46160</v>
       </c>
       <c r="Q305" t="b">
@@ -16182,7 +16208,7 @@
       <c r="E306" t="s">
         <v>1124</v>
       </c>
-      <c r="F306" s="1">
+      <c r="F306" s="2">
         <v>46125</v>
       </c>
       <c r="G306" t="s">
@@ -16203,7 +16229,7 @@
       <c r="L306" t="s">
         <v>1432</v>
       </c>
-      <c r="N306" s="1">
+      <c r="N306" s="2">
         <v>46156</v>
       </c>
       <c r="Q306" t="b">
@@ -16226,7 +16252,7 @@
       <c r="E307" t="s">
         <v>1125</v>
       </c>
-      <c r="F307" s="1">
+      <c r="F307" s="2">
         <v>46125</v>
       </c>
       <c r="G307" t="s">
@@ -16244,7 +16270,7 @@
       <c r="L307" t="s">
         <v>1433</v>
       </c>
-      <c r="N307" s="1">
+      <c r="N307" s="2">
         <v>46209</v>
       </c>
       <c r="P307" t="s">
@@ -16270,7 +16296,7 @@
       <c r="E308" t="s">
         <v>1126</v>
       </c>
-      <c r="F308" s="1">
+      <c r="F308" s="2">
         <v>46125</v>
       </c>
       <c r="G308" t="s">
@@ -16308,7 +16334,7 @@
       <c r="E309" t="s">
         <v>1127</v>
       </c>
-      <c r="F309" s="1">
+      <c r="F309" s="2">
         <v>46125</v>
       </c>
       <c r="G309" t="s">
@@ -16323,7 +16349,7 @@
       <c r="L309" t="s">
         <v>1383</v>
       </c>
-      <c r="N309" s="1">
+      <c r="N309" s="2">
         <v>46232</v>
       </c>
       <c r="Q309" t="b">
@@ -16346,7 +16372,7 @@
       <c r="E310" t="s">
         <v>1128</v>
       </c>
-      <c r="F310" s="1">
+      <c r="F310" s="2">
         <v>46125</v>
       </c>
       <c r="G310" t="s">
@@ -16367,7 +16393,7 @@
       <c r="L310" t="s">
         <v>1383</v>
       </c>
-      <c r="N310" s="1">
+      <c r="N310" s="2">
         <v>46232</v>
       </c>
       <c r="Q310" t="b">
@@ -16390,7 +16416,7 @@
       <c r="E311" t="s">
         <v>1129</v>
       </c>
-      <c r="F311" s="1">
+      <c r="F311" s="2">
         <v>46125</v>
       </c>
       <c r="G311" t="s">
@@ -16428,7 +16454,7 @@
       <c r="E312" t="s">
         <v>1130</v>
       </c>
-      <c r="F312" s="1">
+      <c r="F312" s="2">
         <v>46125</v>
       </c>
       <c r="G312" t="s">
@@ -16446,7 +16472,7 @@
       <c r="L312" t="s">
         <v>1383</v>
       </c>
-      <c r="N312" s="1">
+      <c r="N312" s="2">
         <v>46232</v>
       </c>
       <c r="Q312" t="b">
@@ -16469,7 +16495,7 @@
       <c r="E313" t="s">
         <v>1131</v>
       </c>
-      <c r="F313" s="1">
+      <c r="F313" s="2">
         <v>46125</v>
       </c>
       <c r="G313" t="s">
@@ -16504,7 +16530,7 @@
       <c r="E314" t="s">
         <v>1132</v>
       </c>
-      <c r="F314" s="1">
+      <c r="F314" s="2">
         <v>46125</v>
       </c>
       <c r="G314" t="s">
@@ -16519,7 +16545,7 @@
       <c r="L314" t="s">
         <v>1383</v>
       </c>
-      <c r="N314" s="1">
+      <c r="N314" s="2">
         <v>46232</v>
       </c>
       <c r="Q314" t="b">
@@ -16542,7 +16568,7 @@
       <c r="E315" t="s">
         <v>1133</v>
       </c>
-      <c r="F315" s="1">
+      <c r="F315" s="2">
         <v>46125</v>
       </c>
       <c r="G315" t="s">
@@ -16557,7 +16583,7 @@
       <c r="L315" t="s">
         <v>1383</v>
       </c>
-      <c r="N315" s="1">
+      <c r="N315" s="2">
         <v>46232</v>
       </c>
       <c r="Q315" t="b">
@@ -16580,7 +16606,7 @@
       <c r="E316" t="s">
         <v>1134</v>
       </c>
-      <c r="F316" s="1">
+      <c r="F316" s="2">
         <v>46125</v>
       </c>
       <c r="G316" t="s">
@@ -16618,7 +16644,7 @@
       <c r="E317" t="s">
         <v>1135</v>
       </c>
-      <c r="F317" s="1">
+      <c r="F317" s="2">
         <v>46125</v>
       </c>
       <c r="G317" t="s">
@@ -16653,7 +16679,7 @@
       <c r="E318" t="s">
         <v>1136</v>
       </c>
-      <c r="F318" s="1">
+      <c r="F318" s="2">
         <v>46125</v>
       </c>
       <c r="G318" t="s">
@@ -16682,7 +16708,7 @@
       <c r="E319" t="s">
         <v>1137</v>
       </c>
-      <c r="F319" s="1">
+      <c r="F319" s="2">
         <v>46125</v>
       </c>
       <c r="G319" t="s">
@@ -16697,7 +16723,7 @@
       <c r="L319" t="s">
         <v>1434</v>
       </c>
-      <c r="N319" s="1">
+      <c r="N319" s="2">
         <v>46175</v>
       </c>
       <c r="Q319" t="b">
@@ -16720,7 +16746,7 @@
       <c r="E320" t="s">
         <v>1138</v>
       </c>
-      <c r="F320" s="1">
+      <c r="F320" s="2">
         <v>46125</v>
       </c>
       <c r="G320" t="s">
@@ -16758,7 +16784,7 @@
       <c r="E321" t="s">
         <v>1139</v>
       </c>
-      <c r="F321" s="1">
+      <c r="F321" s="2">
         <v>46125</v>
       </c>
       <c r="G321" t="s">
@@ -16796,7 +16822,7 @@
       <c r="E322" t="s">
         <v>1140</v>
       </c>
-      <c r="F322" s="1">
+      <c r="F322" s="2">
         <v>46125</v>
       </c>
       <c r="G322" t="s">
@@ -16817,7 +16843,7 @@
       <c r="L322" t="s">
         <v>1435</v>
       </c>
-      <c r="N322" s="1">
+      <c r="N322" s="2">
         <v>46182</v>
       </c>
       <c r="Q322" t="b">
@@ -16840,7 +16866,7 @@
       <c r="E323" t="s">
         <v>1141</v>
       </c>
-      <c r="F323" s="1">
+      <c r="F323" s="2">
         <v>46125</v>
       </c>
       <c r="G323" t="s">
@@ -16875,7 +16901,7 @@
       <c r="E324" t="s">
         <v>1142</v>
       </c>
-      <c r="F324" s="1">
+      <c r="F324" s="2">
         <v>46125</v>
       </c>
       <c r="G324" t="s">
@@ -16910,7 +16936,7 @@
       <c r="E325" t="s">
         <v>1143</v>
       </c>
-      <c r="F325" s="1">
+      <c r="F325" s="2">
         <v>46125</v>
       </c>
       <c r="G325" t="s">
@@ -16931,7 +16957,7 @@
       <c r="L325" t="s">
         <v>1435</v>
       </c>
-      <c r="N325" s="1">
+      <c r="N325" s="2">
         <v>46182</v>
       </c>
       <c r="Q325" t="b">
@@ -16954,7 +16980,7 @@
       <c r="E326" t="s">
         <v>1144</v>
       </c>
-      <c r="F326" s="1">
+      <c r="F326" s="2">
         <v>46125</v>
       </c>
       <c r="G326" t="s">
@@ -16969,7 +16995,7 @@
       <c r="L326" t="s">
         <v>1383</v>
       </c>
-      <c r="N326" s="1">
+      <c r="N326" s="2">
         <v>46232</v>
       </c>
       <c r="Q326" t="b">
@@ -16992,7 +17018,7 @@
       <c r="E327" t="s">
         <v>1140</v>
       </c>
-      <c r="F327" s="1">
+      <c r="F327" s="2">
         <v>46125</v>
       </c>
       <c r="G327" t="s">
@@ -17013,7 +17039,7 @@
       <c r="L327" t="s">
         <v>1435</v>
       </c>
-      <c r="N327" s="1">
+      <c r="N327" s="2">
         <v>46182</v>
       </c>
       <c r="Q327" t="b">
@@ -17036,7 +17062,7 @@
       <c r="E328" t="s">
         <v>1145</v>
       </c>
-      <c r="F328" s="1">
+      <c r="F328" s="2">
         <v>46125</v>
       </c>
       <c r="G328" t="s">
@@ -17057,7 +17083,7 @@
       <c r="L328" t="s">
         <v>1435</v>
       </c>
-      <c r="N328" s="1">
+      <c r="N328" s="2">
         <v>46182</v>
       </c>
       <c r="Q328" t="b">
@@ -17080,7 +17106,7 @@
       <c r="E329" t="s">
         <v>1146</v>
       </c>
-      <c r="F329" s="1">
+      <c r="F329" s="2">
         <v>46125</v>
       </c>
       <c r="G329" t="s">
@@ -17101,7 +17127,7 @@
       <c r="L329" t="s">
         <v>1435</v>
       </c>
-      <c r="N329" s="1">
+      <c r="N329" s="2">
         <v>46182</v>
       </c>
       <c r="Q329" t="b">
@@ -17124,7 +17150,7 @@
       <c r="E330" t="s">
         <v>1147</v>
       </c>
-      <c r="F330" s="1">
+      <c r="F330" s="2">
         <v>46125</v>
       </c>
       <c r="G330" t="s">
@@ -17145,7 +17171,7 @@
       <c r="L330" t="s">
         <v>1435</v>
       </c>
-      <c r="N330" s="1">
+      <c r="N330" s="2">
         <v>46182</v>
       </c>
       <c r="Q330" t="b">
@@ -17168,7 +17194,7 @@
       <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="F331" s="1">
+      <c r="F331" s="2">
         <v>46125</v>
       </c>
       <c r="G331" t="s">
@@ -17206,7 +17232,7 @@
       <c r="E332" t="s">
         <v>1148</v>
       </c>
-      <c r="F332" s="1">
+      <c r="F332" s="2">
         <v>46125</v>
       </c>
       <c r="G332" t="s">
@@ -17244,7 +17270,7 @@
       <c r="E333" t="s">
         <v>910</v>
       </c>
-      <c r="F333" s="1">
+      <c r="F333" s="2">
         <v>46125</v>
       </c>
       <c r="G333" t="s">
@@ -17265,7 +17291,7 @@
       <c r="L333" t="s">
         <v>1395</v>
       </c>
-      <c r="N333" s="1">
+      <c r="N333" s="2">
         <v>46225</v>
       </c>
       <c r="Q333" t="b">
@@ -17288,7 +17314,7 @@
       <c r="E334" t="s">
         <v>1149</v>
       </c>
-      <c r="F334" s="1">
+      <c r="F334" s="2">
         <v>46125</v>
       </c>
       <c r="G334" t="s">
@@ -17326,7 +17352,7 @@
       <c r="E335" t="s">
         <v>1150</v>
       </c>
-      <c r="F335" s="1">
+      <c r="F335" s="2">
         <v>46127</v>
       </c>
       <c r="G335" t="s">
@@ -17341,7 +17367,7 @@
       <c r="L335" t="s">
         <v>1434</v>
       </c>
-      <c r="N335" s="1">
+      <c r="N335" s="2">
         <v>46175</v>
       </c>
       <c r="Q335" t="b">
@@ -17364,7 +17390,7 @@
       <c r="E336" t="s">
         <v>1151</v>
       </c>
-      <c r="F336" s="1">
+      <c r="F336" s="2">
         <v>46127</v>
       </c>
       <c r="G336" t="s">
@@ -17385,7 +17411,7 @@
       <c r="L336" t="s">
         <v>1388</v>
       </c>
-      <c r="N336" s="1">
+      <c r="N336" s="2">
         <v>46155</v>
       </c>
       <c r="Q336" t="b">
@@ -17408,7 +17434,7 @@
       <c r="E337" t="s">
         <v>1152</v>
       </c>
-      <c r="F337" s="1">
+      <c r="F337" s="2">
         <v>46127</v>
       </c>
       <c r="G337" t="s">
@@ -17423,7 +17449,7 @@
       <c r="L337" t="s">
         <v>1434</v>
       </c>
-      <c r="N337" s="1">
+      <c r="N337" s="2">
         <v>46175</v>
       </c>
       <c r="Q337" t="b">
@@ -17446,7 +17472,7 @@
       <c r="E338" t="s">
         <v>1153</v>
       </c>
-      <c r="F338" s="1">
+      <c r="F338" s="2">
         <v>46127</v>
       </c>
       <c r="G338" t="s">
@@ -17467,7 +17493,7 @@
       <c r="L338" t="s">
         <v>1388</v>
       </c>
-      <c r="N338" s="1">
+      <c r="N338" s="2">
         <v>46139</v>
       </c>
       <c r="Q338" t="b">
@@ -17490,7 +17516,7 @@
       <c r="E339" t="s">
         <v>1154</v>
       </c>
-      <c r="F339" s="1">
+      <c r="F339" s="2">
         <v>46129</v>
       </c>
       <c r="G339" t="s">
@@ -17519,7 +17545,7 @@
       <c r="E340" t="s">
         <v>1155</v>
       </c>
-      <c r="F340" s="1">
+      <c r="F340" s="2">
         <v>46142</v>
       </c>
       <c r="G340" t="s">
@@ -17537,7 +17563,7 @@
       <c r="L340" t="s">
         <v>1383</v>
       </c>
-      <c r="N340" s="1">
+      <c r="N340" s="2">
         <v>46240</v>
       </c>
       <c r="Q340" t="b">
@@ -17560,7 +17586,7 @@
       <c r="E341" t="s">
         <v>1156</v>
       </c>
-      <c r="F341" s="1">
+      <c r="F341" s="2">
         <v>46142</v>
       </c>
       <c r="G341" t="s">
@@ -17578,7 +17604,7 @@
       <c r="L341" t="s">
         <v>1383</v>
       </c>
-      <c r="N341" s="1">
+      <c r="N341" s="2">
         <v>46232</v>
       </c>
       <c r="Q341" t="b">
@@ -17601,7 +17627,7 @@
       <c r="E342" t="s">
         <v>1157</v>
       </c>
-      <c r="F342" s="1">
+      <c r="F342" s="2">
         <v>46142</v>
       </c>
       <c r="G342" t="s">
@@ -17639,7 +17665,7 @@
       <c r="E343" t="s">
         <v>1158</v>
       </c>
-      <c r="F343" s="1">
+      <c r="F343" s="2">
         <v>46142</v>
       </c>
       <c r="G343" t="s">
@@ -17654,7 +17680,7 @@
       <c r="L343" t="s">
         <v>1383</v>
       </c>
-      <c r="N343" s="1">
+      <c r="N343" s="2">
         <v>46232</v>
       </c>
       <c r="Q343" t="b">
@@ -17677,7 +17703,7 @@
       <c r="E344" t="s">
         <v>1159</v>
       </c>
-      <c r="F344" s="1">
+      <c r="F344" s="2">
         <v>46142</v>
       </c>
       <c r="G344" t="s">
@@ -17692,7 +17718,7 @@
       <c r="L344" t="s">
         <v>1383</v>
       </c>
-      <c r="N344" s="1">
+      <c r="N344" s="2">
         <v>46232</v>
       </c>
       <c r="Q344" t="b">
@@ -17715,7 +17741,7 @@
       <c r="E345" t="s">
         <v>1160</v>
       </c>
-      <c r="F345" s="1">
+      <c r="F345" s="2">
         <v>46142</v>
       </c>
       <c r="G345" t="s">
@@ -17753,7 +17779,7 @@
       <c r="E346" t="s">
         <v>1161</v>
       </c>
-      <c r="F346" s="1">
+      <c r="F346" s="2">
         <v>46142</v>
       </c>
       <c r="G346" t="s">
@@ -17768,7 +17794,7 @@
       <c r="L346" t="s">
         <v>1383</v>
       </c>
-      <c r="N346" s="1">
+      <c r="N346" s="2">
         <v>46232</v>
       </c>
       <c r="Q346" t="b">
@@ -17791,7 +17817,7 @@
       <c r="E347" t="s">
         <v>1162</v>
       </c>
-      <c r="F347" s="1">
+      <c r="F347" s="2">
         <v>46142</v>
       </c>
       <c r="G347" t="s">
@@ -17812,7 +17838,7 @@
       <c r="L347" t="s">
         <v>1431</v>
       </c>
-      <c r="N347" s="1">
+      <c r="N347" s="2">
         <v>46160</v>
       </c>
       <c r="Q347" t="b">
@@ -17835,7 +17861,7 @@
       <c r="E348" t="s">
         <v>1163</v>
       </c>
-      <c r="F348" s="1">
+      <c r="F348" s="2">
         <v>46142</v>
       </c>
       <c r="G348" t="s">
@@ -17856,7 +17882,7 @@
       <c r="L348" t="s">
         <v>1432</v>
       </c>
-      <c r="N348" s="1">
+      <c r="N348" s="2">
         <v>46156</v>
       </c>
       <c r="Q348" t="b">
@@ -17879,7 +17905,7 @@
       <c r="E349" t="s">
         <v>1164</v>
       </c>
-      <c r="F349" s="1">
+      <c r="F349" s="2">
         <v>46142</v>
       </c>
       <c r="G349" t="s">
@@ -17917,7 +17943,7 @@
       <c r="E350" t="s">
         <v>1165</v>
       </c>
-      <c r="F350" s="1">
+      <c r="F350" s="2">
         <v>46142</v>
       </c>
       <c r="G350" t="s">
@@ -17932,7 +17958,7 @@
       <c r="J350">
         <v>46</v>
       </c>
-      <c r="N350" s="1">
+      <c r="N350" s="2">
         <v>46188</v>
       </c>
       <c r="Q350" t="b">
@@ -17955,7 +17981,7 @@
       <c r="E351" t="s">
         <v>1166</v>
       </c>
-      <c r="F351" s="1">
+      <c r="F351" s="2">
         <v>46142</v>
       </c>
       <c r="G351" t="s">
@@ -17976,7 +18002,7 @@
       <c r="L351" t="s">
         <v>1436</v>
       </c>
-      <c r="N351" s="1">
+      <c r="N351" s="2">
         <v>46224</v>
       </c>
       <c r="Q351" t="b">
@@ -17999,7 +18025,7 @@
       <c r="E352" t="s">
         <v>1167</v>
       </c>
-      <c r="F352" s="1">
+      <c r="F352" s="2">
         <v>46142</v>
       </c>
       <c r="G352" t="s">
@@ -18020,7 +18046,7 @@
       <c r="L352" t="s">
         <v>1437</v>
       </c>
-      <c r="N352" s="1">
+      <c r="N352" s="2">
         <v>46220</v>
       </c>
       <c r="Q352" t="b">
@@ -18043,7 +18069,7 @@
       <c r="E353" t="s">
         <v>1168</v>
       </c>
-      <c r="F353" s="1">
+      <c r="F353" s="2">
         <v>46142</v>
       </c>
       <c r="G353" t="s">
@@ -18064,7 +18090,7 @@
       <c r="L353" t="s">
         <v>1395</v>
       </c>
-      <c r="N353" s="1">
+      <c r="N353" s="2">
         <v>46225</v>
       </c>
       <c r="Q353" t="b">
@@ -18087,7 +18113,7 @@
       <c r="E354" t="s">
         <v>1169</v>
       </c>
-      <c r="F354" s="1">
+      <c r="F354" s="2">
         <v>46142</v>
       </c>
       <c r="G354" t="s">
@@ -18125,7 +18151,7 @@
       <c r="E355" t="s">
         <v>1170</v>
       </c>
-      <c r="F355" s="1">
+      <c r="F355" s="2">
         <v>46142</v>
       </c>
       <c r="G355" t="s">
@@ -18146,7 +18172,7 @@
       <c r="L355" t="s">
         <v>1438</v>
       </c>
-      <c r="N355" s="1">
+      <c r="N355" s="2">
         <v>46150</v>
       </c>
       <c r="Q355" t="b">
@@ -18169,7 +18195,7 @@
       <c r="E356" t="s">
         <v>1171</v>
       </c>
-      <c r="F356" s="1">
+      <c r="F356" s="2">
         <v>46142</v>
       </c>
       <c r="G356" t="s">
@@ -18184,7 +18210,7 @@
       <c r="L356" t="s">
         <v>1439</v>
       </c>
-      <c r="N356" s="1">
+      <c r="N356" s="2">
         <v>46176</v>
       </c>
       <c r="Q356" t="b">
@@ -18207,7 +18233,7 @@
       <c r="E357" t="s">
         <v>1172</v>
       </c>
-      <c r="F357" s="1">
+      <c r="F357" s="2">
         <v>46142</v>
       </c>
       <c r="G357" t="s">
@@ -18225,7 +18251,7 @@
       <c r="K357" t="s">
         <v>1360</v>
       </c>
-      <c r="N357" s="1">
+      <c r="N357" s="2">
         <v>46227</v>
       </c>
       <c r="Q357" t="b">
@@ -18248,7 +18274,7 @@
       <c r="E358" t="s">
         <v>1173</v>
       </c>
-      <c r="F358" s="1">
+      <c r="F358" s="2">
         <v>46142</v>
       </c>
       <c r="G358" t="s">
@@ -18266,7 +18292,7 @@
       <c r="L358" t="s">
         <v>1440</v>
       </c>
-      <c r="N358" s="1">
+      <c r="N358" s="2">
         <v>46227</v>
       </c>
       <c r="P358" t="s">
@@ -18292,7 +18318,7 @@
       <c r="E359" t="s">
         <v>1174</v>
       </c>
-      <c r="F359" s="1">
+      <c r="F359" s="2">
         <v>46142</v>
       </c>
       <c r="G359" t="s">
@@ -18304,7 +18330,7 @@
       <c r="J359">
         <v>63</v>
       </c>
-      <c r="N359" s="1">
+      <c r="N359" s="2">
         <v>46205</v>
       </c>
       <c r="P359" t="s">
@@ -18330,7 +18356,7 @@
       <c r="E360" t="s">
         <v>949</v>
       </c>
-      <c r="F360" s="1">
+      <c r="F360" s="2">
         <v>46142</v>
       </c>
       <c r="G360" t="s">
@@ -18351,7 +18377,7 @@
       <c r="L360" t="s">
         <v>1395</v>
       </c>
-      <c r="N360" s="1">
+      <c r="N360" s="2">
         <v>46225</v>
       </c>
       <c r="O360" t="s">
@@ -18377,7 +18403,7 @@
       <c r="E361" t="s">
         <v>961</v>
       </c>
-      <c r="F361" s="1">
+      <c r="F361" s="2">
         <v>46142</v>
       </c>
       <c r="G361" t="s">
@@ -18398,7 +18424,7 @@
       <c r="L361" t="s">
         <v>1395</v>
       </c>
-      <c r="N361" s="1">
+      <c r="N361" s="2">
         <v>46225</v>
       </c>
       <c r="Q361" t="b">
@@ -18421,7 +18447,7 @@
       <c r="E362" t="s">
         <v>1175</v>
       </c>
-      <c r="F362" s="1">
+      <c r="F362" s="2">
         <v>46142</v>
       </c>
       <c r="G362" t="s">
@@ -18459,7 +18485,7 @@
       <c r="E363" t="s">
         <v>1176</v>
       </c>
-      <c r="F363" s="1">
+      <c r="F363" s="2">
         <v>46142</v>
       </c>
       <c r="G363" t="s">
@@ -18497,7 +18523,7 @@
       <c r="E364" t="s">
         <v>958</v>
       </c>
-      <c r="F364" s="1">
+      <c r="F364" s="2">
         <v>46142</v>
       </c>
       <c r="G364" t="s">
@@ -18518,7 +18544,7 @@
       <c r="L364" t="s">
         <v>1395</v>
       </c>
-      <c r="N364" s="1">
+      <c r="N364" s="2">
         <v>46225</v>
       </c>
       <c r="Q364" t="b">
@@ -18541,7 +18567,7 @@
       <c r="E365" t="s">
         <v>1177</v>
       </c>
-      <c r="F365" s="1">
+      <c r="F365" s="2">
         <v>46142</v>
       </c>
       <c r="G365" t="s">
@@ -18559,7 +18585,7 @@
       <c r="K365" t="s">
         <v>1359</v>
       </c>
-      <c r="N365" s="1">
+      <c r="N365" s="2">
         <v>46157</v>
       </c>
       <c r="Q365" t="b">
@@ -18582,7 +18608,7 @@
       <c r="E366" t="s">
         <v>1178</v>
       </c>
-      <c r="F366" s="1">
+      <c r="F366" s="2">
         <v>46148</v>
       </c>
       <c r="G366" t="s">
@@ -18603,7 +18629,7 @@
       <c r="L366" t="s">
         <v>1388</v>
       </c>
-      <c r="N366" s="1">
+      <c r="N366" s="2">
         <v>46225</v>
       </c>
       <c r="Q366" t="b">
@@ -18626,7 +18652,7 @@
       <c r="E367" t="s">
         <v>1179</v>
       </c>
-      <c r="F367" s="1">
+      <c r="F367" s="2">
         <v>46148</v>
       </c>
       <c r="G367" t="s">
@@ -18647,7 +18673,7 @@
       <c r="L367" t="s">
         <v>1388</v>
       </c>
-      <c r="N367" s="1">
+      <c r="N367" s="2">
         <v>46225</v>
       </c>
       <c r="Q367" t="b">
@@ -18670,7 +18696,7 @@
       <c r="E368" t="s">
         <v>1180</v>
       </c>
-      <c r="F368" s="1">
+      <c r="F368" s="2">
         <v>46148</v>
       </c>
       <c r="G368" t="s">
@@ -18691,7 +18717,7 @@
       <c r="L368" t="s">
         <v>1395</v>
       </c>
-      <c r="N368" s="1">
+      <c r="N368" s="2">
         <v>46225</v>
       </c>
       <c r="Q368" t="b">
@@ -18714,7 +18740,7 @@
       <c r="E369" t="s">
         <v>1181</v>
       </c>
-      <c r="F369" s="1">
+      <c r="F369" s="2">
         <v>46148</v>
       </c>
       <c r="G369" t="s">
@@ -18752,7 +18778,7 @@
       <c r="E370" t="s">
         <v>1182</v>
       </c>
-      <c r="F370" s="1">
+      <c r="F370" s="2">
         <v>46148</v>
       </c>
       <c r="G370" t="s">
@@ -18790,7 +18816,7 @@
       <c r="E371" t="s">
         <v>1183</v>
       </c>
-      <c r="F371" s="1">
+      <c r="F371" s="2">
         <v>46148</v>
       </c>
       <c r="G371" t="s">
@@ -18811,7 +18837,7 @@
       <c r="L371" t="s">
         <v>1441</v>
       </c>
-      <c r="N371" s="1">
+      <c r="N371" s="2">
         <v>46164</v>
       </c>
       <c r="Q371" t="b">
@@ -18834,7 +18860,7 @@
       <c r="E372" t="s">
         <v>1184</v>
       </c>
-      <c r="F372" s="1">
+      <c r="F372" s="2">
         <v>46148</v>
       </c>
       <c r="G372" t="s">
@@ -18852,7 +18878,7 @@
       <c r="L372" t="s">
         <v>1428</v>
       </c>
-      <c r="N372" s="1">
+      <c r="N372" s="2">
         <v>46113</v>
       </c>
       <c r="P372" t="s">
@@ -18878,7 +18904,7 @@
       <c r="E373" t="s">
         <v>1185</v>
       </c>
-      <c r="F373" s="1">
+      <c r="F373" s="2">
         <v>46149</v>
       </c>
       <c r="G373" t="s">
@@ -18916,7 +18942,7 @@
       <c r="E374" t="s">
         <v>1186</v>
       </c>
-      <c r="F374" s="1">
+      <c r="F374" s="2">
         <v>46149</v>
       </c>
       <c r="G374" t="s">
@@ -18954,7 +18980,7 @@
       <c r="E375" t="s">
         <v>1187</v>
       </c>
-      <c r="F375" s="1">
+      <c r="F375" s="2">
         <v>46154</v>
       </c>
       <c r="G375" t="s">
@@ -18972,7 +18998,7 @@
       <c r="K375" t="s">
         <v>1360</v>
       </c>
-      <c r="N375" s="1">
+      <c r="N375" s="2">
         <v>46248</v>
       </c>
       <c r="Q375" t="b">
@@ -18995,7 +19021,7 @@
       <c r="E376" t="s">
         <v>1188</v>
       </c>
-      <c r="F376" s="1">
+      <c r="F376" s="2">
         <v>46154</v>
       </c>
       <c r="G376" t="s">
@@ -19033,7 +19059,7 @@
       <c r="E377" t="s">
         <v>1189</v>
       </c>
-      <c r="F377" s="1">
+      <c r="F377" s="2">
         <v>46154</v>
       </c>
       <c r="G377" t="s">
@@ -19045,7 +19071,7 @@
       <c r="K377" t="s">
         <v>1360</v>
       </c>
-      <c r="N377" s="1">
+      <c r="N377" s="2">
         <v>46176</v>
       </c>
       <c r="O377" t="s">
@@ -19074,7 +19100,7 @@
       <c r="E378" t="s">
         <v>1190</v>
       </c>
-      <c r="F378" s="1">
+      <c r="F378" s="2">
         <v>46154</v>
       </c>
       <c r="G378" t="s">
@@ -19112,7 +19138,7 @@
       <c r="E379" t="s">
         <v>1191</v>
       </c>
-      <c r="F379" s="1">
+      <c r="F379" s="2">
         <v>46154</v>
       </c>
       <c r="G379" t="s">
@@ -19133,7 +19159,7 @@
       <c r="L379" t="s">
         <v>1442</v>
       </c>
-      <c r="N379" s="1">
+      <c r="N379" s="2">
         <v>46174</v>
       </c>
       <c r="Q379" t="b">
@@ -19156,7 +19182,7 @@
       <c r="E380" t="s">
         <v>1192</v>
       </c>
-      <c r="F380" s="1">
+      <c r="F380" s="2">
         <v>46154</v>
       </c>
       <c r="G380" t="s">
@@ -19177,7 +19203,7 @@
       <c r="L380" t="s">
         <v>1443</v>
       </c>
-      <c r="N380" s="1">
+      <c r="N380" s="2">
         <v>46248</v>
       </c>
       <c r="Q380" t="b">
@@ -19200,7 +19226,7 @@
       <c r="E381" t="s">
         <v>1193</v>
       </c>
-      <c r="F381" s="1">
+      <c r="F381" s="2">
         <v>46154</v>
       </c>
       <c r="G381" t="s">
@@ -19238,7 +19264,7 @@
       <c r="E382" t="s">
         <v>1194</v>
       </c>
-      <c r="F382" s="1">
+      <c r="F382" s="2">
         <v>46154</v>
       </c>
       <c r="G382" t="s">
@@ -19276,7 +19302,7 @@
       <c r="E383" t="s">
         <v>1195</v>
       </c>
-      <c r="F383" s="1">
+      <c r="F383" s="2">
         <v>46154</v>
       </c>
       <c r="G383" t="s">
@@ -19297,7 +19323,7 @@
       <c r="L383" t="s">
         <v>1444</v>
       </c>
-      <c r="N383" s="1">
+      <c r="N383" s="2">
         <v>46225</v>
       </c>
       <c r="Q383" t="b">
@@ -19320,7 +19346,7 @@
       <c r="E384" t="s">
         <v>1196</v>
       </c>
-      <c r="F384" s="1">
+      <c r="F384" s="2">
         <v>46164</v>
       </c>
       <c r="G384" t="s">
@@ -19358,7 +19384,7 @@
       <c r="E385" t="s">
         <v>1197</v>
       </c>
-      <c r="F385" s="1">
+      <c r="F385" s="2">
         <v>46164</v>
       </c>
       <c r="G385" t="s">
@@ -19379,7 +19405,7 @@
       <c r="L385" t="s">
         <v>1445</v>
       </c>
-      <c r="N385" s="1">
+      <c r="N385" s="2">
         <v>46266</v>
       </c>
       <c r="P385" t="s">
@@ -19405,7 +19431,7 @@
       <c r="E386" t="s">
         <v>1198</v>
       </c>
-      <c r="F386" s="1">
+      <c r="F386" s="2">
         <v>46171</v>
       </c>
       <c r="G386" t="s">
@@ -19443,7 +19469,7 @@
       <c r="E387" t="s">
         <v>1199</v>
       </c>
-      <c r="F387" s="1">
+      <c r="F387" s="2">
         <v>46171</v>
       </c>
       <c r="G387" t="s">
@@ -19481,7 +19507,7 @@
       <c r="E388" t="s">
         <v>851</v>
       </c>
-      <c r="F388" s="1">
+      <c r="F388" s="2">
         <v>46171</v>
       </c>
       <c r="G388" t="s">
@@ -19502,7 +19528,7 @@
       <c r="L388" t="s">
         <v>1446</v>
       </c>
-      <c r="N388" s="1">
+      <c r="N388" s="2">
         <v>46086</v>
       </c>
       <c r="Q388" t="b">
@@ -19525,7 +19551,7 @@
       <c r="E389" t="s">
         <v>1200</v>
       </c>
-      <c r="F389" s="1">
+      <c r="F389" s="2">
         <v>46171</v>
       </c>
       <c r="G389" t="s">
@@ -19563,7 +19589,7 @@
       <c r="E390" t="s">
         <v>1201</v>
       </c>
-      <c r="F390" s="1">
+      <c r="F390" s="2">
         <v>46171</v>
       </c>
       <c r="G390" t="s">
@@ -19581,7 +19607,7 @@
       <c r="L390" t="s">
         <v>1447</v>
       </c>
-      <c r="N390" s="1">
+      <c r="N390" s="2">
         <v>46191</v>
       </c>
       <c r="P390" t="s">
@@ -19607,7 +19633,7 @@
       <c r="E391" t="s">
         <v>1202</v>
       </c>
-      <c r="F391" s="1">
+      <c r="F391" s="2">
         <v>46171</v>
       </c>
       <c r="G391" t="s">
@@ -19645,7 +19671,7 @@
       <c r="E392" t="s">
         <v>1203</v>
       </c>
-      <c r="F392" s="1">
+      <c r="F392" s="2">
         <v>46171</v>
       </c>
       <c r="G392" t="s">
@@ -19660,7 +19686,7 @@
       <c r="L392" t="s">
         <v>1439</v>
       </c>
-      <c r="N392" s="1">
+      <c r="N392" s="2">
         <v>46176</v>
       </c>
       <c r="Q392" t="b">
@@ -19683,7 +19709,7 @@
       <c r="E393" t="s">
         <v>1204</v>
       </c>
-      <c r="F393" s="1">
+      <c r="F393" s="2">
         <v>46171</v>
       </c>
       <c r="G393" t="s">
@@ -19704,7 +19730,7 @@
       <c r="L393" t="s">
         <v>1388</v>
       </c>
-      <c r="N393" s="1">
+      <c r="N393" s="2">
         <v>46191</v>
       </c>
       <c r="Q393" t="b">
@@ -19727,7 +19753,7 @@
       <c r="E394" t="s">
         <v>1205</v>
       </c>
-      <c r="F394" s="1">
+      <c r="F394" s="2">
         <v>46171</v>
       </c>
       <c r="G394" t="s">
@@ -19745,7 +19771,7 @@
       <c r="L394" t="s">
         <v>1448</v>
       </c>
-      <c r="N394" s="1">
+      <c r="N394" s="2">
         <v>46241</v>
       </c>
       <c r="P394" t="s">
@@ -19771,7 +19797,7 @@
       <c r="E395" t="s">
         <v>1206</v>
       </c>
-      <c r="F395" s="1">
+      <c r="F395" s="2">
         <v>46171</v>
       </c>
       <c r="G395" t="s">
@@ -19789,7 +19815,7 @@
       <c r="L395" t="s">
         <v>1449</v>
       </c>
-      <c r="N395" s="1">
+      <c r="N395" s="2">
         <v>46191</v>
       </c>
       <c r="P395" t="s">
@@ -19815,7 +19841,7 @@
       <c r="E396" t="s">
         <v>1207</v>
       </c>
-      <c r="F396" s="1">
+      <c r="F396" s="2">
         <v>46171</v>
       </c>
       <c r="G396" t="s">
@@ -19827,7 +19853,7 @@
       <c r="J396">
         <v>20</v>
       </c>
-      <c r="N396" s="1">
+      <c r="N396" s="2">
         <v>46191</v>
       </c>
       <c r="P396" t="s">
@@ -19853,7 +19879,7 @@
       <c r="E397" t="s">
         <v>1208</v>
       </c>
-      <c r="F397" s="1">
+      <c r="F397" s="2">
         <v>46171</v>
       </c>
       <c r="G397" t="s">
@@ -19871,7 +19897,7 @@
       <c r="L397" t="s">
         <v>1448</v>
       </c>
-      <c r="N397" s="1">
+      <c r="N397" s="2">
         <v>46241</v>
       </c>
       <c r="P397" t="s">
@@ -19897,7 +19923,7 @@
       <c r="E398" t="s">
         <v>1209</v>
       </c>
-      <c r="F398" s="1">
+      <c r="F398" s="2">
         <v>46171</v>
       </c>
       <c r="G398" t="s">
@@ -19915,7 +19941,7 @@
       <c r="L398" t="s">
         <v>1449</v>
       </c>
-      <c r="N398" s="1">
+      <c r="N398" s="2">
         <v>46191</v>
       </c>
       <c r="P398" t="s">
@@ -19941,7 +19967,7 @@
       <c r="E399" t="s">
         <v>987</v>
       </c>
-      <c r="F399" s="1">
+      <c r="F399" s="2">
         <v>46163</v>
       </c>
       <c r="G399" t="s">
@@ -19956,7 +19982,7 @@
       <c r="L399" t="s">
         <v>1450</v>
       </c>
-      <c r="N399" s="1">
+      <c r="N399" s="2">
         <v>46171</v>
       </c>
       <c r="Q399" t="b">
@@ -19979,7 +20005,7 @@
       <c r="E400" t="s">
         <v>1210</v>
       </c>
-      <c r="F400" s="1">
+      <c r="F400" s="2">
         <v>46171</v>
       </c>
       <c r="G400" t="s">
@@ -20017,7 +20043,7 @@
       <c r="E401" t="s">
         <v>1211</v>
       </c>
-      <c r="F401" s="1">
+      <c r="F401" s="2">
         <v>46171</v>
       </c>
       <c r="G401" t="s">
@@ -20029,7 +20055,7 @@
       <c r="J401">
         <v>40</v>
       </c>
-      <c r="N401" s="1">
+      <c r="N401" s="2">
         <v>46211</v>
       </c>
       <c r="P401" t="s">
@@ -20055,7 +20081,7 @@
       <c r="E402" t="s">
         <v>1212</v>
       </c>
-      <c r="F402" s="1">
+      <c r="F402" s="2">
         <v>46171</v>
       </c>
       <c r="G402" t="s">
@@ -20093,7 +20119,7 @@
       <c r="E403" t="s">
         <v>1213</v>
       </c>
-      <c r="F403" s="1">
+      <c r="F403" s="2">
         <v>46171</v>
       </c>
       <c r="G403" t="s">
@@ -20114,7 +20140,7 @@
       <c r="L403" t="s">
         <v>1451</v>
       </c>
-      <c r="N403" s="1">
+      <c r="N403" s="2">
         <v>46254</v>
       </c>
       <c r="Q403" t="b">
@@ -20137,7 +20163,7 @@
       <c r="E404" t="s">
         <v>1214</v>
       </c>
-      <c r="F404" s="1">
+      <c r="F404" s="2">
         <v>46171</v>
       </c>
       <c r="G404" t="s">
@@ -20175,7 +20201,7 @@
       <c r="E405" t="s">
         <v>1215</v>
       </c>
-      <c r="F405" s="1">
+      <c r="F405" s="2">
         <v>46183</v>
       </c>
       <c r="G405" t="s">
@@ -20207,7 +20233,7 @@
       <c r="E406" t="s">
         <v>1216</v>
       </c>
-      <c r="F406" s="1">
+      <c r="F406" s="2">
         <v>46183</v>
       </c>
       <c r="G406" t="s">
@@ -20239,7 +20265,7 @@
       <c r="E407" t="s">
         <v>1217</v>
       </c>
-      <c r="F407" s="1">
+      <c r="F407" s="2">
         <v>46183</v>
       </c>
       <c r="G407" t="s">
@@ -20271,7 +20297,7 @@
       <c r="E408" t="s">
         <v>1218</v>
       </c>
-      <c r="F408" s="1">
+      <c r="F408" s="2">
         <v>46183</v>
       </c>
       <c r="G408" t="s">
@@ -20303,7 +20329,7 @@
       <c r="E409" t="s">
         <v>1219</v>
       </c>
-      <c r="F409" s="1">
+      <c r="F409" s="2">
         <v>46183</v>
       </c>
       <c r="G409" t="s">
@@ -20335,7 +20361,7 @@
       <c r="E410" t="s">
         <v>1220</v>
       </c>
-      <c r="F410" s="1">
+      <c r="F410" s="2">
         <v>46183</v>
       </c>
       <c r="G410" t="s">
@@ -20367,7 +20393,7 @@
       <c r="E411" t="s">
         <v>1221</v>
       </c>
-      <c r="F411" s="1">
+      <c r="F411" s="2">
         <v>46188</v>
       </c>
       <c r="G411" t="s">
@@ -20399,7 +20425,7 @@
       <c r="E412" t="s">
         <v>1222</v>
       </c>
-      <c r="F412" s="1">
+      <c r="F412" s="2">
         <v>46188</v>
       </c>
       <c r="G412" t="s">
@@ -20431,7 +20457,7 @@
       <c r="E413" t="s">
         <v>1223</v>
       </c>
-      <c r="F413" s="1">
+      <c r="F413" s="2">
         <v>46188</v>
       </c>
       <c r="G413" t="s">
@@ -20463,7 +20489,7 @@
       <c r="E414" t="s">
         <v>1224</v>
       </c>
-      <c r="F414" s="1">
+      <c r="F414" s="2">
         <v>46188</v>
       </c>
       <c r="G414" t="s">
@@ -20492,7 +20518,7 @@
       <c r="E415" t="s">
         <v>1060</v>
       </c>
-      <c r="F415" s="1">
+      <c r="F415" s="2">
         <v>46188</v>
       </c>
       <c r="G415" t="s">
@@ -20521,7 +20547,7 @@
       <c r="E416" t="s">
         <v>1225</v>
       </c>
-      <c r="F416" s="1">
+      <c r="F416" s="2">
         <v>46188</v>
       </c>
       <c r="G416" t="s">
@@ -20553,7 +20579,7 @@
       <c r="E417" t="s">
         <v>1226</v>
       </c>
-      <c r="F417" s="1">
+      <c r="F417" s="2">
         <v>46188</v>
       </c>
       <c r="G417" t="s">
@@ -20582,7 +20608,7 @@
       <c r="E418" t="s">
         <v>1227</v>
       </c>
-      <c r="F418" s="1">
+      <c r="F418" s="2">
         <v>46188</v>
       </c>
       <c r="G418" t="s">
@@ -20611,7 +20637,7 @@
       <c r="E419" t="s">
         <v>1228</v>
       </c>
-      <c r="F419" s="1">
+      <c r="F419" s="2">
         <v>46188</v>
       </c>
       <c r="G419" t="s">
@@ -20643,7 +20669,7 @@
       <c r="E420" t="s">
         <v>1229</v>
       </c>
-      <c r="F420" s="1">
+      <c r="F420" s="2">
         <v>46188</v>
       </c>
       <c r="G420" t="s">
@@ -20675,7 +20701,7 @@
       <c r="E421" t="s">
         <v>1230</v>
       </c>
-      <c r="F421" s="1">
+      <c r="F421" s="2">
         <v>46188</v>
       </c>
       <c r="G421" t="s">
@@ -20707,7 +20733,7 @@
       <c r="E422" t="s">
         <v>1231</v>
       </c>
-      <c r="F422" s="1">
+      <c r="F422" s="2">
         <v>46188</v>
       </c>
       <c r="G422" t="s">
@@ -20739,7 +20765,7 @@
       <c r="E423" t="s">
         <v>1232</v>
       </c>
-      <c r="F423" s="1">
+      <c r="F423" s="2">
         <v>46188</v>
       </c>
       <c r="G423" t="s">
@@ -20771,7 +20797,7 @@
       <c r="E424" t="s">
         <v>1233</v>
       </c>
-      <c r="F424" s="1">
+      <c r="F424" s="2">
         <v>46188</v>
       </c>
       <c r="G424" t="s">
@@ -20803,7 +20829,7 @@
       <c r="E425" t="s">
         <v>1234</v>
       </c>
-      <c r="F425" s="1">
+      <c r="F425" s="2">
         <v>46188</v>
       </c>
       <c r="G425" t="s">
@@ -20835,7 +20861,7 @@
       <c r="E426" t="s">
         <v>1235</v>
       </c>
-      <c r="F426" s="1">
+      <c r="F426" s="2">
         <v>46188</v>
       </c>
       <c r="G426" t="s">
@@ -20867,7 +20893,7 @@
       <c r="E427" t="s">
         <v>1236</v>
       </c>
-      <c r="F427" s="1">
+      <c r="F427" s="2">
         <v>46188</v>
       </c>
       <c r="G427" t="s">
@@ -20899,7 +20925,7 @@
       <c r="E428" t="s">
         <v>1237</v>
       </c>
-      <c r="F428" s="1">
+      <c r="F428" s="2">
         <v>46188</v>
       </c>
       <c r="G428" t="s">
@@ -20928,7 +20954,7 @@
       <c r="E429" t="s">
         <v>1238</v>
       </c>
-      <c r="F429" s="1">
+      <c r="F429" s="2">
         <v>46188</v>
       </c>
       <c r="G429" t="s">
@@ -20957,7 +20983,7 @@
       <c r="E430" t="s">
         <v>1239</v>
       </c>
-      <c r="F430" s="1">
+      <c r="F430" s="2">
         <v>46188</v>
       </c>
       <c r="G430" t="s">
@@ -20989,7 +21015,7 @@
       <c r="E431" t="s">
         <v>1240</v>
       </c>
-      <c r="F431" s="1">
+      <c r="F431" s="2">
         <v>46188</v>
       </c>
       <c r="G431" t="s">
@@ -21021,7 +21047,7 @@
       <c r="E432" t="s">
         <v>1241</v>
       </c>
-      <c r="F432" s="1">
+      <c r="F432" s="2">
         <v>46188</v>
       </c>
       <c r="G432" t="s">
@@ -21053,7 +21079,7 @@
       <c r="E433" t="s">
         <v>1242</v>
       </c>
-      <c r="F433" s="1">
+      <c r="F433" s="2">
         <v>46188</v>
       </c>
       <c r="G433" t="s">
@@ -21085,7 +21111,7 @@
       <c r="E434" t="s">
         <v>1243</v>
       </c>
-      <c r="F434" s="1">
+      <c r="F434" s="2">
         <v>46188</v>
       </c>
       <c r="G434" t="s">
@@ -21117,7 +21143,7 @@
       <c r="E435" t="s">
         <v>856</v>
       </c>
-      <c r="F435" s="1">
+      <c r="F435" s="2">
         <v>46188</v>
       </c>
       <c r="G435" t="s">
@@ -21149,7 +21175,7 @@
       <c r="E436" t="s">
         <v>1244</v>
       </c>
-      <c r="F436" s="1">
+      <c r="F436" s="2">
         <v>46188</v>
       </c>
       <c r="G436" t="s">
@@ -21181,7 +21207,7 @@
       <c r="E437" t="s">
         <v>1245</v>
       </c>
-      <c r="F437" s="1">
+      <c r="F437" s="2">
         <v>46188</v>
       </c>
       <c r="G437" t="s">
@@ -21213,7 +21239,7 @@
       <c r="E438" t="s">
         <v>1246</v>
       </c>
-      <c r="F438" s="1">
+      <c r="F438" s="2">
         <v>46188</v>
       </c>
       <c r="G438" t="s">
@@ -21245,7 +21271,7 @@
       <c r="E439" t="s">
         <v>1247</v>
       </c>
-      <c r="F439" s="1">
+      <c r="F439" s="2">
         <v>46196</v>
       </c>
       <c r="G439" t="s">
@@ -21277,7 +21303,7 @@
       <c r="E440" t="s">
         <v>1248</v>
       </c>
-      <c r="F440" s="1">
+      <c r="F440" s="2">
         <v>46196</v>
       </c>
       <c r="G440" t="s">
@@ -21309,7 +21335,7 @@
       <c r="E441" t="s">
         <v>1249</v>
       </c>
-      <c r="F441" s="1">
+      <c r="F441" s="2">
         <v>46203</v>
       </c>
       <c r="G441" t="s">
@@ -21341,7 +21367,7 @@
       <c r="E442" t="s">
         <v>1250</v>
       </c>
-      <c r="F442" s="1">
+      <c r="F442" s="2">
         <v>46203</v>
       </c>
       <c r="G442" t="s">
@@ -21370,7 +21396,7 @@
       <c r="E443" t="s">
         <v>1251</v>
       </c>
-      <c r="F443" s="1">
+      <c r="F443" s="2">
         <v>46205</v>
       </c>
       <c r="G443" t="s">
@@ -21402,7 +21428,7 @@
       <c r="E444" t="s">
         <v>1252</v>
       </c>
-      <c r="F444" s="1">
+      <c r="F444" s="2">
         <v>46205</v>
       </c>
       <c r="G444" t="s">
@@ -21431,7 +21457,7 @@
       <c r="E445" t="s">
         <v>1253</v>
       </c>
-      <c r="F445" s="1">
+      <c r="F445" s="2">
         <v>46205</v>
       </c>
       <c r="G445" t="s">
@@ -21460,7 +21486,7 @@
       <c r="E446" t="s">
         <v>1254</v>
       </c>
-      <c r="F446" s="1">
+      <c r="F446" s="2">
         <v>46211</v>
       </c>
       <c r="G446" t="s">
@@ -21492,7 +21518,7 @@
       <c r="E447" t="s">
         <v>1255</v>
       </c>
-      <c r="F447" s="1">
+      <c r="F447" s="2">
         <v>46211</v>
       </c>
       <c r="G447" t="s">
@@ -21524,7 +21550,7 @@
       <c r="E448" t="s">
         <v>1256</v>
       </c>
-      <c r="F448" s="1">
+      <c r="F448" s="2">
         <v>46226</v>
       </c>
       <c r="G448" t="s">
@@ -21556,7 +21582,7 @@
       <c r="E449" t="s">
         <v>1257</v>
       </c>
-      <c r="F449" s="1">
+      <c r="F449" s="2">
         <v>46226</v>
       </c>
       <c r="G449" t="s">
@@ -21588,7 +21614,7 @@
       <c r="E450" t="s">
         <v>1258</v>
       </c>
-      <c r="F450" s="1">
+      <c r="F450" s="2">
         <v>46226</v>
       </c>
       <c r="G450" t="s">
@@ -21620,7 +21646,7 @@
       <c r="E451" t="s">
         <v>1035</v>
       </c>
-      <c r="F451" s="1">
+      <c r="F451" s="2">
         <v>46230</v>
       </c>
       <c r="G451" t="s">
@@ -21652,7 +21678,7 @@
       <c r="E452" t="s">
         <v>1259</v>
       </c>
-      <c r="F452" s="1">
+      <c r="F452" s="2">
         <v>46230</v>
       </c>
       <c r="G452" t="s">
@@ -21684,7 +21710,7 @@
       <c r="E453" t="s">
         <v>1260</v>
       </c>
-      <c r="F453" s="1">
+      <c r="F453" s="2">
         <v>46230</v>
       </c>
       <c r="G453" t="s">
@@ -21716,7 +21742,7 @@
       <c r="E454" t="s">
         <v>1261</v>
       </c>
-      <c r="F454" s="1">
+      <c r="F454" s="2">
         <v>46230</v>
       </c>
       <c r="G454" t="s">
@@ -21748,7 +21774,7 @@
       <c r="E455" t="s">
         <v>1262</v>
       </c>
-      <c r="F455" s="1">
+      <c r="F455" s="2">
         <v>46230</v>
       </c>
       <c r="G455" t="s">
@@ -21780,7 +21806,7 @@
       <c r="E456" t="s">
         <v>1263</v>
       </c>
-      <c r="F456" s="1">
+      <c r="F456" s="2">
         <v>46230</v>
       </c>
       <c r="G456" t="s">
@@ -21812,7 +21838,7 @@
       <c r="E457" t="s">
         <v>1264</v>
       </c>
-      <c r="F457" s="1">
+      <c r="F457" s="2">
         <v>46230</v>
       </c>
       <c r="G457" t="s">
@@ -21844,7 +21870,7 @@
       <c r="E458" t="s">
         <v>1202</v>
       </c>
-      <c r="F458" s="1">
+      <c r="F458" s="2">
         <v>46231</v>
       </c>
       <c r="G458" t="s">
@@ -21876,7 +21902,7 @@
       <c r="E459" t="s">
         <v>1265</v>
       </c>
-      <c r="F459" s="1">
+      <c r="F459" s="2">
         <v>46233</v>
       </c>
       <c r="G459" t="s">
@@ -21908,7 +21934,7 @@
       <c r="E460" t="s">
         <v>1266</v>
       </c>
-      <c r="F460" s="1">
+      <c r="F460" s="2">
         <v>46233</v>
       </c>
       <c r="G460" t="s">
@@ -21940,7 +21966,7 @@
       <c r="E461" t="s">
         <v>1267</v>
       </c>
-      <c r="F461" s="1">
+      <c r="F461" s="2">
         <v>46233</v>
       </c>
       <c r="G461" t="s">
@@ -21972,7 +21998,7 @@
       <c r="E462" t="s">
         <v>1268</v>
       </c>
-      <c r="F462" s="1">
+      <c r="F462" s="2">
         <v>46233</v>
       </c>
       <c r="G462" t="s">
@@ -22004,7 +22030,7 @@
       <c r="E463" t="s">
         <v>1269</v>
       </c>
-      <c r="F463" s="1">
+      <c r="F463" s="2">
         <v>46234</v>
       </c>
       <c r="G463" t="s">
@@ -22036,7 +22062,7 @@
       <c r="E464" t="s">
         <v>1270</v>
       </c>
-      <c r="F464" s="1">
+      <c r="F464" s="2">
         <v>46230</v>
       </c>
       <c r="G464" t="s">
@@ -22068,7 +22094,7 @@
       <c r="E465" t="s">
         <v>1271</v>
       </c>
-      <c r="F465" s="1">
+      <c r="F465" s="2">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
@@ -22100,7 +22126,7 @@
       <c r="E466" t="s">
         <v>1272</v>
       </c>
-      <c r="F466" s="1">
+      <c r="F466" s="2">
         <v>46230</v>
       </c>
       <c r="G466" t="s">
@@ -22132,7 +22158,7 @@
       <c r="E467" t="s">
         <v>1273</v>
       </c>
-      <c r="F467" s="1">
+      <c r="F467" s="2">
         <v>46230</v>
       </c>
       <c r="G467" t="s">
@@ -22164,7 +22190,7 @@
       <c r="E468" t="s">
         <v>1274</v>
       </c>
-      <c r="F468" s="1">
+      <c r="F468" s="2">
         <v>46230</v>
       </c>
       <c r="G468" t="s">
@@ -22196,7 +22222,7 @@
       <c r="E469" t="s">
         <v>1275</v>
       </c>
-      <c r="F469" s="1">
+      <c r="F469" s="2">
         <v>46230</v>
       </c>
       <c r="G469" t="s">
@@ -22228,7 +22254,7 @@
       <c r="E470" t="s">
         <v>1276</v>
       </c>
-      <c r="F470" s="1">
+      <c r="F470" s="2">
         <v>46230</v>
       </c>
       <c r="G470" t="s">
@@ -22257,7 +22283,7 @@
       <c r="E471" t="s">
         <v>1277</v>
       </c>
-      <c r="F471" s="1">
+      <c r="F471" s="2">
         <v>46230</v>
       </c>
       <c r="G471" t="s">
@@ -22289,7 +22315,7 @@
       <c r="E472" t="s">
         <v>1278</v>
       </c>
-      <c r="F472" s="1">
+      <c r="F472" s="2">
         <v>46230</v>
       </c>
       <c r="G472" t="s">
@@ -22321,7 +22347,7 @@
       <c r="E473" t="s">
         <v>1279</v>
       </c>
-      <c r="F473" s="1">
+      <c r="F473" s="2">
         <v>46230</v>
       </c>
       <c r="G473" t="s">
@@ -22353,7 +22379,7 @@
       <c r="E474" t="s">
         <v>1280</v>
       </c>
-      <c r="F474" s="1">
+      <c r="F474" s="2">
         <v>46231</v>
       </c>
       <c r="G474" t="s">
@@ -22385,7 +22411,7 @@
       <c r="E475" t="s">
         <v>1281</v>
       </c>
-      <c r="F475" s="1">
+      <c r="F475" s="2">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
@@ -22417,7 +22443,7 @@
       <c r="E476" t="s">
         <v>1282</v>
       </c>
-      <c r="F476" s="1">
+      <c r="F476" s="2">
         <v>46231</v>
       </c>
       <c r="G476" t="s">
@@ -22449,7 +22475,7 @@
       <c r="E477" t="s">
         <v>1283</v>
       </c>
-      <c r="F477" s="1">
+      <c r="F477" s="2">
         <v>46231</v>
       </c>
       <c r="G477" t="s">
@@ -22481,7 +22507,7 @@
       <c r="E478" t="s">
         <v>1284</v>
       </c>
-      <c r="F478" s="1">
+      <c r="F478" s="2">
         <v>46231</v>
       </c>
       <c r="G478" t="s">
@@ -22513,7 +22539,7 @@
       <c r="E479" t="s">
         <v>1285</v>
       </c>
-      <c r="F479" s="1">
+      <c r="F479" s="2">
         <v>46231</v>
       </c>
       <c r="G479" t="s">
@@ -22545,7 +22571,7 @@
       <c r="E480" t="s">
         <v>1286</v>
       </c>
-      <c r="F480" s="1">
+      <c r="F480" s="2">
         <v>46231</v>
       </c>
       <c r="G480" t="s">
@@ -22577,7 +22603,7 @@
       <c r="E481" t="s">
         <v>1287</v>
       </c>
-      <c r="F481" s="1">
+      <c r="F481" s="2">
         <v>46231</v>
       </c>
       <c r="G481" t="s">
@@ -22609,7 +22635,7 @@
       <c r="E482" t="s">
         <v>1288</v>
       </c>
-      <c r="F482" s="1">
+      <c r="F482" s="2">
         <v>46231</v>
       </c>
       <c r="G482" t="s">
@@ -22641,7 +22667,7 @@
       <c r="E483" t="s">
         <v>1289</v>
       </c>
-      <c r="F483" s="1">
+      <c r="F483" s="2">
         <v>46231</v>
       </c>
       <c r="G483" t="s">
@@ -22673,7 +22699,7 @@
       <c r="E484" t="s">
         <v>1290</v>
       </c>
-      <c r="F484" s="1">
+      <c r="F484" s="2">
         <v>46231</v>
       </c>
       <c r="G484" t="s">
@@ -22705,7 +22731,7 @@
       <c r="E485" t="s">
         <v>1291</v>
       </c>
-      <c r="F485" s="1">
+      <c r="F485" s="2">
         <v>46231</v>
       </c>
       <c r="G485" t="s">
@@ -22737,7 +22763,7 @@
       <c r="E486" t="s">
         <v>1292</v>
       </c>
-      <c r="F486" s="1">
+      <c r="F486" s="2">
         <v>46231</v>
       </c>
       <c r="G486" t="s">
@@ -22769,7 +22795,7 @@
       <c r="E487" t="s">
         <v>1293</v>
       </c>
-      <c r="F487" s="1">
+      <c r="F487" s="2">
         <v>46231</v>
       </c>
       <c r="G487" t="s">
@@ -22801,7 +22827,7 @@
       <c r="E488" t="s">
         <v>1294</v>
       </c>
-      <c r="F488" s="1">
+      <c r="F488" s="2">
         <v>46231</v>
       </c>
       <c r="G488" t="s">
@@ -22833,7 +22859,7 @@
       <c r="E489" t="s">
         <v>1295</v>
       </c>
-      <c r="F489" s="1">
+      <c r="F489" s="2">
         <v>46231</v>
       </c>
       <c r="G489" t="s">
@@ -22865,7 +22891,7 @@
       <c r="E490" t="s">
         <v>1296</v>
       </c>
-      <c r="F490" s="1">
+      <c r="F490" s="2">
         <v>46231</v>
       </c>
       <c r="G490" t="s">
@@ -22897,7 +22923,7 @@
       <c r="E491" t="s">
         <v>1297</v>
       </c>
-      <c r="F491" s="1">
+      <c r="F491" s="2">
         <v>46231</v>
       </c>
       <c r="G491" t="s">
@@ -22929,7 +22955,7 @@
       <c r="E492" t="s">
         <v>911</v>
       </c>
-      <c r="F492" s="1">
+      <c r="F492" s="2">
         <v>46231</v>
       </c>
       <c r="G492" t="s">
@@ -22961,7 +22987,7 @@
       <c r="E493" t="s">
         <v>995</v>
       </c>
-      <c r="F493" s="1">
+      <c r="F493" s="2">
         <v>46231</v>
       </c>
       <c r="G493" t="s">
@@ -22993,7 +23019,7 @@
       <c r="E494" t="s">
         <v>867</v>
       </c>
-      <c r="F494" s="1">
+      <c r="F494" s="2">
         <v>46231</v>
       </c>
       <c r="G494" t="s">
@@ -23025,7 +23051,7 @@
       <c r="E495" t="s">
         <v>912</v>
       </c>
-      <c r="F495" s="1">
+      <c r="F495" s="2">
         <v>46231</v>
       </c>
       <c r="G495" t="s">
@@ -23057,7 +23083,7 @@
       <c r="E496" t="s">
         <v>1048</v>
       </c>
-      <c r="F496" s="1">
+      <c r="F496" s="2">
         <v>46231</v>
       </c>
       <c r="G496" t="s">
@@ -23089,7 +23115,7 @@
       <c r="E497" t="s">
         <v>1298</v>
       </c>
-      <c r="F497" s="1">
+      <c r="F497" s="2">
         <v>46231</v>
       </c>
       <c r="G497" t="s">
@@ -23121,7 +23147,7 @@
       <c r="E498" t="s">
         <v>1299</v>
       </c>
-      <c r="F498" s="1">
+      <c r="F498" s="2">
         <v>46231</v>
       </c>
       <c r="G498" t="s">
@@ -23153,7 +23179,7 @@
       <c r="E499" t="s">
         <v>1300</v>
       </c>
-      <c r="F499" s="1">
+      <c r="F499" s="2">
         <v>46231</v>
       </c>
       <c r="G499" t="s">
@@ -23185,7 +23211,7 @@
       <c r="E500" t="s">
         <v>1301</v>
       </c>
-      <c r="F500" s="1">
+      <c r="F500" s="2">
         <v>46231</v>
       </c>
       <c r="G500" t="s">
@@ -23217,7 +23243,7 @@
       <c r="E501" t="s">
         <v>1302</v>
       </c>
-      <c r="F501" s="1">
+      <c r="F501" s="2">
         <v>46231</v>
       </c>
       <c r="G501" t="s">
@@ -23249,7 +23275,7 @@
       <c r="E502" t="s">
         <v>1303</v>
       </c>
-      <c r="F502" s="1">
+      <c r="F502" s="2">
         <v>46231</v>
       </c>
       <c r="G502" t="s">
@@ -23281,7 +23307,7 @@
       <c r="E503" t="s">
         <v>1304</v>
       </c>
-      <c r="F503" s="1">
+      <c r="F503" s="2">
         <v>46231</v>
       </c>
       <c r="G503" t="s">
@@ -23313,7 +23339,7 @@
       <c r="E504" t="s">
         <v>1305</v>
       </c>
-      <c r="F504" s="1">
+      <c r="F504" s="2">
         <v>46232</v>
       </c>
       <c r="G504" t="s">
@@ -23345,7 +23371,7 @@
       <c r="E505" t="s">
         <v>1306</v>
       </c>
-      <c r="F505" s="1">
+      <c r="F505" s="2">
         <v>46232</v>
       </c>
       <c r="G505" t="s">
@@ -23377,7 +23403,7 @@
       <c r="E506" t="s">
         <v>1307</v>
       </c>
-      <c r="F506" s="1">
+      <c r="F506" s="2">
         <v>46232</v>
       </c>
       <c r="G506" t="s">
@@ -23409,7 +23435,7 @@
       <c r="E507" t="s">
         <v>1308</v>
       </c>
-      <c r="F507" s="1">
+      <c r="F507" s="2">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
@@ -23441,7 +23467,7 @@
       <c r="E508" t="s">
         <v>1309</v>
       </c>
-      <c r="F508" s="1">
+      <c r="F508" s="2">
         <v>46237</v>
       </c>
       <c r="G508" t="s">
@@ -23470,7 +23496,7 @@
       <c r="E509" t="s">
         <v>1310</v>
       </c>
-      <c r="F509" s="1">
+      <c r="F509" s="2">
         <v>46237</v>
       </c>
       <c r="G509" t="s">
@@ -23502,7 +23528,7 @@
       <c r="E510" t="s">
         <v>1311</v>
       </c>
-      <c r="F510" s="1">
+      <c r="F510" s="2">
         <v>46237</v>
       </c>
       <c r="G510" t="s">
@@ -23534,7 +23560,7 @@
       <c r="E511" t="s">
         <v>1312</v>
       </c>
-      <c r="F511" s="1">
+      <c r="F511" s="2">
         <v>46240</v>
       </c>
       <c r="G511" t="s">
@@ -23566,7 +23592,7 @@
       <c r="E512" t="s">
         <v>1313</v>
       </c>
-      <c r="F512" s="1">
+      <c r="F512" s="2">
         <v>46240</v>
       </c>
       <c r="G512" t="s">
@@ -23598,7 +23624,7 @@
       <c r="E513" t="s">
         <v>1314</v>
       </c>
-      <c r="F513" s="1">
+      <c r="F513" s="2">
         <v>46244</v>
       </c>
       <c r="G513" t="s">
@@ -23630,7 +23656,7 @@
       <c r="E514" t="s">
         <v>1315</v>
       </c>
-      <c r="F514" s="1">
+      <c r="F514" s="2">
         <v>46244</v>
       </c>
       <c r="G514" t="s">
@@ -23662,7 +23688,7 @@
       <c r="E515" t="s">
         <v>1043</v>
       </c>
-      <c r="F515" s="1">
+      <c r="F515" s="2">
         <v>46244</v>
       </c>
       <c r="G515" t="s">
@@ -23694,7 +23720,7 @@
       <c r="E516" t="s">
         <v>1316</v>
       </c>
-      <c r="F516" s="1">
+      <c r="F516" s="2">
         <v>46252</v>
       </c>
       <c r="G516" t="s">
@@ -23726,7 +23752,7 @@
       <c r="E517" t="s">
         <v>1317</v>
       </c>
-      <c r="F517" s="1">
+      <c r="F517" s="2">
         <v>46252</v>
       </c>
       <c r="G517" t="s">
@@ -23758,7 +23784,7 @@
       <c r="E518" t="s">
         <v>1318</v>
       </c>
-      <c r="F518" s="1">
+      <c r="F518" s="2">
         <v>46252</v>
       </c>
       <c r="G518" t="s">
@@ -23790,7 +23816,7 @@
       <c r="E519" t="s">
         <v>1253</v>
       </c>
-      <c r="F519" s="1">
+      <c r="F519" s="2">
         <v>46254</v>
       </c>
       <c r="G519" t="s">
@@ -23822,7 +23848,7 @@
       <c r="E520" t="s">
         <v>1319</v>
       </c>
-      <c r="F520" s="1">
+      <c r="F520" s="2">
         <v>46254</v>
       </c>
       <c r="G520" t="s">
@@ -23854,7 +23880,7 @@
       <c r="E521" t="s">
         <v>1320</v>
       </c>
-      <c r="F521" s="1">
+      <c r="F521" s="2">
         <v>46254</v>
       </c>
       <c r="G521" t="s">
@@ -23886,7 +23912,7 @@
       <c r="E522" t="s">
         <v>1253</v>
       </c>
-      <c r="F522" s="1">
+      <c r="F522" s="2">
         <v>46254</v>
       </c>
       <c r="G522" t="s">
@@ -23918,7 +23944,7 @@
       <c r="E523" t="s">
         <v>1319</v>
       </c>
-      <c r="F523" s="1">
+      <c r="F523" s="2">
         <v>46254</v>
       </c>
       <c r="G523" t="s">
@@ -23950,7 +23976,7 @@
       <c r="E524" t="s">
         <v>1321</v>
       </c>
-      <c r="F524" s="1">
+      <c r="F524" s="2">
         <v>46265</v>
       </c>
       <c r="G524" t="s">
@@ -23982,7 +24008,7 @@
       <c r="E525" t="s">
         <v>1322</v>
       </c>
-      <c r="F525" s="1">
+      <c r="F525" s="2">
         <v>46265</v>
       </c>
       <c r="G525" t="s">
@@ -24014,7 +24040,7 @@
       <c r="E526" t="s">
         <v>1323</v>
       </c>
-      <c r="F526" s="1">
+      <c r="F526" s="2">
         <v>46265</v>
       </c>
       <c r="G526" t="s">
@@ -24046,7 +24072,7 @@
       <c r="E527" t="s">
         <v>1324</v>
       </c>
-      <c r="F527" s="1">
+      <c r="F527" s="2">
         <v>46265</v>
       </c>
       <c r="G527" t="s">

--- a/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
@@ -4520,16 +4520,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -4545,7 +4537,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -4553,30 +4545,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4876,55 +4850,55 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4944,7 +4918,7 @@
       <c r="E2" t="s">
         <v>829</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>45698</v>
       </c>
       <c r="G2" t="s">
@@ -4954,7 +4928,7 @@
         <v>1353</v>
       </c>
       <c r="I2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K2" t="s">
         <v>1356</v>
@@ -4982,7 +4956,7 @@
       <c r="E3" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>45714</v>
       </c>
       <c r="G3" t="s">
@@ -4992,7 +4966,7 @@
         <v>1353</v>
       </c>
       <c r="I3">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K3" t="s">
         <v>1357</v>
@@ -5020,7 +4994,7 @@
       <c r="E4" t="s">
         <v>831</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>45714</v>
       </c>
       <c r="G4" t="s">
@@ -5030,7 +5004,7 @@
         <v>1353</v>
       </c>
       <c r="I4">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K4" t="s">
         <v>1357</v>
@@ -5058,7 +5032,7 @@
       <c r="E5" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>45714</v>
       </c>
       <c r="G5" t="s">
@@ -5068,7 +5042,7 @@
         <v>1353</v>
       </c>
       <c r="I5">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J5">
         <v>279</v>
@@ -5079,7 +5053,7 @@
       <c r="L5" t="s">
         <v>1367</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="1">
         <v>45993</v>
       </c>
       <c r="Q5" t="b">
@@ -5102,7 +5076,7 @@
       <c r="E6" t="s">
         <v>833</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>45736</v>
       </c>
       <c r="G6" t="s">
@@ -5112,7 +5086,7 @@
         <v>1353</v>
       </c>
       <c r="I6">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J6">
         <v>153</v>
@@ -5123,7 +5097,7 @@
       <c r="L6" t="s">
         <v>1368</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="1">
         <v>45889</v>
       </c>
       <c r="Q6" t="b">
@@ -5146,7 +5120,7 @@
       <c r="E7" t="s">
         <v>834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>45736</v>
       </c>
       <c r="G7" t="s">
@@ -5156,7 +5130,7 @@
         <v>1353</v>
       </c>
       <c r="I7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J7">
         <v>112</v>
@@ -5167,7 +5141,7 @@
       <c r="L7" t="s">
         <v>1369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="1">
         <v>45848</v>
       </c>
       <c r="O7" t="s">
@@ -5193,7 +5167,7 @@
       <c r="E8" t="s">
         <v>835</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>45736</v>
       </c>
       <c r="G8" t="s">
@@ -5222,7 +5196,7 @@
       <c r="E9" t="s">
         <v>836</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>45736</v>
       </c>
       <c r="G9" t="s">
@@ -5232,7 +5206,7 @@
         <v>1353</v>
       </c>
       <c r="I9">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J9">
         <v>362</v>
@@ -5243,7 +5217,7 @@
       <c r="L9" t="s">
         <v>1370</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="1">
         <v>46098</v>
       </c>
       <c r="O9">
@@ -5269,7 +5243,7 @@
       <c r="E10" t="s">
         <v>837</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>45736</v>
       </c>
       <c r="G10" t="s">
@@ -5279,7 +5253,7 @@
         <v>1353</v>
       </c>
       <c r="I10">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J10">
         <v>378</v>
@@ -5290,7 +5264,7 @@
       <c r="L10" t="s">
         <v>1371</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="1">
         <v>46114</v>
       </c>
       <c r="O10" t="s">
@@ -5316,7 +5290,7 @@
       <c r="E11" t="s">
         <v>838</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>45736</v>
       </c>
       <c r="G11" t="s">
@@ -5326,7 +5300,7 @@
         <v>1353</v>
       </c>
       <c r="I11">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J11">
         <v>112</v>
@@ -5337,7 +5311,7 @@
       <c r="L11" t="s">
         <v>1369</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="1">
         <v>45848</v>
       </c>
       <c r="O11" t="s">
@@ -5363,7 +5337,7 @@
       <c r="E12" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>45736</v>
       </c>
       <c r="G12" t="s">
@@ -5373,7 +5347,7 @@
         <v>1353</v>
       </c>
       <c r="I12">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J12">
         <v>124</v>
@@ -5384,7 +5358,7 @@
       <c r="L12" t="s">
         <v>1372</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="1">
         <v>45860</v>
       </c>
       <c r="Q12" t="b">
@@ -5407,7 +5381,7 @@
       <c r="E13" t="s">
         <v>840</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>45736</v>
       </c>
       <c r="G13" t="s">
@@ -5436,7 +5410,7 @@
       <c r="E14" t="s">
         <v>841</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>45736</v>
       </c>
       <c r="G14" t="s">
@@ -5446,7 +5420,7 @@
         <v>1353</v>
       </c>
       <c r="I14">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J14">
         <v>64</v>
@@ -5457,7 +5431,7 @@
       <c r="L14" t="s">
         <v>1373</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="1">
         <v>45800</v>
       </c>
       <c r="Q14" t="b">
@@ -5480,7 +5454,7 @@
       <c r="E15" t="s">
         <v>842</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>45736</v>
       </c>
       <c r="G15" t="s">
@@ -5490,7 +5464,7 @@
         <v>1353</v>
       </c>
       <c r="I15">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K15" t="s">
         <v>1359</v>
@@ -5518,7 +5492,7 @@
       <c r="E16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>45736</v>
       </c>
       <c r="G16" t="s">
@@ -5528,7 +5502,7 @@
         <v>1353</v>
       </c>
       <c r="I16">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K16" t="s">
         <v>1356</v>
@@ -5556,7 +5530,7 @@
       <c r="E17" t="s">
         <v>844</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>45736</v>
       </c>
       <c r="G17" t="s">
@@ -5566,7 +5540,7 @@
         <v>1353</v>
       </c>
       <c r="I17">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J17">
         <v>161</v>
@@ -5577,7 +5551,7 @@
       <c r="L17" t="s">
         <v>1368</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="1">
         <v>45897</v>
       </c>
       <c r="Q17" t="b">
@@ -5600,7 +5574,7 @@
       <c r="E18" t="s">
         <v>845</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="1">
         <v>45736</v>
       </c>
       <c r="G18" t="s">
@@ -5610,7 +5584,7 @@
         <v>1353</v>
       </c>
       <c r="I18">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J18">
         <v>66</v>
@@ -5621,7 +5595,7 @@
       <c r="L18" t="s">
         <v>1373</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" s="1">
         <v>45802</v>
       </c>
       <c r="Q18" t="b">
@@ -5644,7 +5618,7 @@
       <c r="E19" t="s">
         <v>846</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="1">
         <v>45736</v>
       </c>
       <c r="G19" t="s">
@@ -5673,7 +5647,7 @@
       <c r="E20" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="1">
         <v>45736</v>
       </c>
       <c r="G20" t="s">
@@ -5683,7 +5657,7 @@
         <v>1353</v>
       </c>
       <c r="I20">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J20">
         <v>399</v>
@@ -5694,7 +5668,7 @@
       <c r="L20" t="s">
         <v>1374</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20" s="1">
         <v>46135</v>
       </c>
       <c r="Q20" t="b">
@@ -5717,7 +5691,7 @@
       <c r="E21" t="s">
         <v>848</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="1">
         <v>45736</v>
       </c>
       <c r="G21" t="s">
@@ -5746,7 +5720,7 @@
       <c r="E22" t="s">
         <v>849</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="1">
         <v>45736</v>
       </c>
       <c r="G22" t="s">
@@ -5756,7 +5730,7 @@
         <v>1353</v>
       </c>
       <c r="I22">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K22" t="s">
         <v>1360</v>
@@ -5784,7 +5758,7 @@
       <c r="E23" t="s">
         <v>850</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="1">
         <v>45736</v>
       </c>
       <c r="G23" t="s">
@@ -5794,7 +5768,7 @@
         <v>1353</v>
       </c>
       <c r="I23">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J23">
         <v>229</v>
@@ -5805,7 +5779,7 @@
       <c r="L23" t="s">
         <v>1375</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="1">
         <v>45965</v>
       </c>
       <c r="P23" t="s">
@@ -5831,7 +5805,7 @@
       <c r="E24" t="s">
         <v>851</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="1">
         <v>45736</v>
       </c>
       <c r="G24" t="s">
@@ -5860,7 +5834,7 @@
       <c r="E25" t="s">
         <v>852</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="1">
         <v>45736</v>
       </c>
       <c r="G25" t="s">
@@ -5889,7 +5863,7 @@
       <c r="E26" t="s">
         <v>853</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="1">
         <v>45736</v>
       </c>
       <c r="G26" t="s">
@@ -5899,7 +5873,7 @@
         <v>1353</v>
       </c>
       <c r="I26">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J26">
         <v>155</v>
@@ -5910,7 +5884,7 @@
       <c r="L26" t="s">
         <v>1376</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" s="1">
         <v>45891</v>
       </c>
       <c r="P26" t="s">
@@ -5936,7 +5910,7 @@
       <c r="E27" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="1">
         <v>45736</v>
       </c>
       <c r="G27" t="s">
@@ -5946,7 +5920,7 @@
         <v>1353</v>
       </c>
       <c r="I27">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K27" t="s">
         <v>1360</v>
@@ -5974,7 +5948,7 @@
       <c r="E28" t="s">
         <v>855</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="1">
         <v>45736</v>
       </c>
       <c r="G28" t="s">
@@ -6003,7 +5977,7 @@
       <c r="E29" t="s">
         <v>856</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="1">
         <v>45736</v>
       </c>
       <c r="G29" t="s">
@@ -6032,7 +6006,7 @@
       <c r="E30" t="s">
         <v>857</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="1">
         <v>45736</v>
       </c>
       <c r="G30" t="s">
@@ -6042,7 +6016,7 @@
         <v>1353</v>
       </c>
       <c r="I30">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J30">
         <v>209</v>
@@ -6053,7 +6027,7 @@
       <c r="L30" t="s">
         <v>1377</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" s="1">
         <v>45945</v>
       </c>
       <c r="Q30" t="b">
@@ -6076,7 +6050,7 @@
       <c r="E31" t="s">
         <v>858</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="1">
         <v>45736</v>
       </c>
       <c r="G31" t="s">
@@ -6105,7 +6079,7 @@
       <c r="E32" t="s">
         <v>859</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="1">
         <v>45736</v>
       </c>
       <c r="G32" t="s">
@@ -6115,7 +6089,7 @@
         <v>1353</v>
       </c>
       <c r="I32">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K32" t="s">
         <v>1356</v>
@@ -6143,7 +6117,7 @@
       <c r="E33" t="s">
         <v>860</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>45736</v>
       </c>
       <c r="G33" t="s">
@@ -6172,7 +6146,7 @@
       <c r="E34" t="s">
         <v>861</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="1">
         <v>45736</v>
       </c>
       <c r="G34" t="s">
@@ -6201,7 +6175,7 @@
       <c r="E35" t="s">
         <v>862</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="1">
         <v>45736</v>
       </c>
       <c r="G35" t="s">
@@ -6230,7 +6204,7 @@
       <c r="E36" t="s">
         <v>863</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="1">
         <v>45736</v>
       </c>
       <c r="G36" t="s">
@@ -6259,7 +6233,7 @@
       <c r="E37" t="s">
         <v>864</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>45736</v>
       </c>
       <c r="G37" t="s">
@@ -6288,7 +6262,7 @@
       <c r="E38" t="s">
         <v>844</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="1">
         <v>45736</v>
       </c>
       <c r="G38" t="s">
@@ -6314,7 +6288,7 @@
       <c r="D39" t="s">
         <v>731</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="1">
         <v>45736</v>
       </c>
       <c r="G39" t="s">
@@ -6324,7 +6298,7 @@
         <v>1353</v>
       </c>
       <c r="I39">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K39" t="s">
         <v>1361</v>
@@ -6349,7 +6323,7 @@
       <c r="D40" t="s">
         <v>731</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="1">
         <v>45736</v>
       </c>
       <c r="G40" t="s">
@@ -6359,7 +6333,7 @@
         <v>1353</v>
       </c>
       <c r="I40">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K40" t="s">
         <v>1359</v>
@@ -6387,7 +6361,7 @@
       <c r="E41" t="s">
         <v>865</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="1">
         <v>45736</v>
       </c>
       <c r="G41" t="s">
@@ -6416,7 +6390,7 @@
       <c r="E42" t="s">
         <v>866</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="1">
         <v>45736</v>
       </c>
       <c r="G42" t="s">
@@ -6445,7 +6419,7 @@
       <c r="E43" t="s">
         <v>867</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="1">
         <v>45736</v>
       </c>
       <c r="G43" t="s">
@@ -6480,7 +6454,7 @@
       <c r="E44" t="s">
         <v>868</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="1">
         <v>45769</v>
       </c>
       <c r="G44" t="s">
@@ -6490,7 +6464,7 @@
         <v>1353</v>
       </c>
       <c r="I44">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J44">
         <v>87</v>
@@ -6501,7 +6475,7 @@
       <c r="L44" t="s">
         <v>1378</v>
       </c>
-      <c r="N44" s="2">
+      <c r="N44" s="1">
         <v>45856</v>
       </c>
       <c r="P44" t="s">
@@ -6527,7 +6501,7 @@
       <c r="E45" t="s">
         <v>869</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="1">
         <v>45769</v>
       </c>
       <c r="G45" t="s">
@@ -6537,7 +6511,7 @@
         <v>1353</v>
       </c>
       <c r="I45">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J45">
         <v>331</v>
@@ -6548,7 +6522,7 @@
       <c r="L45" t="s">
         <v>1379</v>
       </c>
-      <c r="N45" s="2">
+      <c r="N45" s="1">
         <v>46100</v>
       </c>
       <c r="O45">
@@ -6574,7 +6548,7 @@
       <c r="E46" t="s">
         <v>870</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="1">
         <v>45769</v>
       </c>
       <c r="G46" t="s">
@@ -6584,7 +6558,7 @@
         <v>1353</v>
       </c>
       <c r="I46">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K46" t="s">
         <v>1360</v>
@@ -6612,7 +6586,7 @@
       <c r="E47" t="s">
         <v>871</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="1">
         <v>45769</v>
       </c>
       <c r="G47" t="s">
@@ -6622,7 +6596,7 @@
         <v>1353</v>
       </c>
       <c r="I47">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J47">
         <v>344</v>
@@ -6633,7 +6607,7 @@
       <c r="L47" t="s">
         <v>1380</v>
       </c>
-      <c r="N47" s="2">
+      <c r="N47" s="1">
         <v>46113</v>
       </c>
       <c r="P47" t="s">
@@ -6659,7 +6633,7 @@
       <c r="E48" t="s">
         <v>872</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="1">
         <v>45769</v>
       </c>
       <c r="G48" t="s">
@@ -6669,7 +6643,7 @@
         <v>1353</v>
       </c>
       <c r="I48">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K48" t="s">
         <v>1360</v>
@@ -6697,7 +6671,7 @@
       <c r="E49" t="s">
         <v>873</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="1">
         <v>45769</v>
       </c>
       <c r="G49" t="s">
@@ -6726,7 +6700,7 @@
       <c r="E50" t="s">
         <v>874</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="1">
         <v>45769</v>
       </c>
       <c r="G50" t="s">
@@ -6736,7 +6710,7 @@
         <v>1353</v>
       </c>
       <c r="I50">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K50" t="s">
         <v>1360</v>
@@ -6764,7 +6738,7 @@
       <c r="E51" t="s">
         <v>875</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="1">
         <v>45769</v>
       </c>
       <c r="G51" t="s">
@@ -6793,7 +6767,7 @@
       <c r="E52" t="s">
         <v>876</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="1">
         <v>45769</v>
       </c>
       <c r="G52" t="s">
@@ -6803,7 +6777,7 @@
         <v>1353</v>
       </c>
       <c r="I52">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K52" t="s">
         <v>1356</v>
@@ -6831,7 +6805,7 @@
       <c r="E53" t="s">
         <v>877</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="1">
         <v>45769</v>
       </c>
       <c r="G53" t="s">
@@ -6841,7 +6815,7 @@
         <v>1353</v>
       </c>
       <c r="I53">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K53" t="s">
         <v>1357</v>
@@ -6869,7 +6843,7 @@
       <c r="E54" t="s">
         <v>878</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="1">
         <v>45769</v>
       </c>
       <c r="G54" t="s">
@@ -6879,7 +6853,7 @@
         <v>1353</v>
       </c>
       <c r="I54">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K54" t="s">
         <v>1357</v>
@@ -6907,7 +6881,7 @@
       <c r="E55" t="s">
         <v>879</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="1">
         <v>45769</v>
       </c>
       <c r="G55" t="s">
@@ -6936,7 +6910,7 @@
       <c r="E56" t="s">
         <v>880</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="1">
         <v>45769</v>
       </c>
       <c r="G56" t="s">
@@ -6965,7 +6939,7 @@
       <c r="E57" t="s">
         <v>881</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="1">
         <v>45769</v>
       </c>
       <c r="G57" t="s">
@@ -6975,7 +6949,7 @@
         <v>1353</v>
       </c>
       <c r="I57">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K57" t="s">
         <v>1360</v>
@@ -7003,7 +6977,7 @@
       <c r="E58" t="s">
         <v>882</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="1">
         <v>45769</v>
       </c>
       <c r="G58" t="s">
@@ -7032,7 +7006,7 @@
       <c r="E59" t="s">
         <v>883</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="1">
         <v>45769</v>
       </c>
       <c r="G59" t="s">
@@ -7061,7 +7035,7 @@
       <c r="E60" t="s">
         <v>884</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="1">
         <v>45769</v>
       </c>
       <c r="G60" t="s">
@@ -7090,7 +7064,7 @@
       <c r="E61" t="s">
         <v>885</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="1">
         <v>45769</v>
       </c>
       <c r="G61" t="s">
@@ -7119,7 +7093,7 @@
       <c r="E62" t="s">
         <v>886</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="1">
         <v>45770</v>
       </c>
       <c r="G62" t="s">
@@ -7148,7 +7122,7 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="1">
         <v>45799</v>
       </c>
       <c r="G63" t="s">
@@ -7158,7 +7132,7 @@
         <v>1353</v>
       </c>
       <c r="I63">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J63">
         <v>293</v>
@@ -7169,7 +7143,7 @@
       <c r="L63" t="s">
         <v>1381</v>
       </c>
-      <c r="N63" s="2">
+      <c r="N63" s="1">
         <v>46092</v>
       </c>
       <c r="P63" t="s">
@@ -7195,7 +7169,7 @@
       <c r="E64" t="s">
         <v>888</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="1">
         <v>45799</v>
       </c>
       <c r="G64" t="s">
@@ -7205,7 +7179,7 @@
         <v>1353</v>
       </c>
       <c r="I64">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J64">
         <v>320</v>
@@ -7216,7 +7190,7 @@
       <c r="L64" t="s">
         <v>1382</v>
       </c>
-      <c r="N64" s="2">
+      <c r="N64" s="1">
         <v>46119</v>
       </c>
       <c r="Q64" t="b">
@@ -7239,7 +7213,7 @@
       <c r="E65" t="s">
         <v>889</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="1">
         <v>45799</v>
       </c>
       <c r="G65" t="s">
@@ -7268,7 +7242,7 @@
       <c r="E66" t="s">
         <v>890</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="1">
         <v>45799</v>
       </c>
       <c r="G66" t="s">
@@ -7297,7 +7271,7 @@
       <c r="E67" t="s">
         <v>891</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="1">
         <v>45799</v>
       </c>
       <c r="G67" t="s">
@@ -7326,7 +7300,7 @@
       <c r="E68" t="s">
         <v>892</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="1">
         <v>45799</v>
       </c>
       <c r="G68" t="s">
@@ -7355,7 +7329,7 @@
       <c r="E69" t="s">
         <v>893</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="1">
         <v>45803</v>
       </c>
       <c r="G69" t="s">
@@ -7384,7 +7358,7 @@
       <c r="E70" t="s">
         <v>894</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="1">
         <v>45803</v>
       </c>
       <c r="G70" t="s">
@@ -7394,7 +7368,7 @@
         <v>1353</v>
       </c>
       <c r="I70">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J70">
         <v>429</v>
@@ -7405,7 +7379,7 @@
       <c r="L70" t="s">
         <v>1383</v>
       </c>
-      <c r="N70" s="2">
+      <c r="N70" s="1">
         <v>46232</v>
       </c>
       <c r="Q70" t="b">
@@ -7428,7 +7402,7 @@
       <c r="E71" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="1">
         <v>45803</v>
       </c>
       <c r="G71" t="s">
@@ -7438,7 +7412,7 @@
         <v>1353</v>
       </c>
       <c r="I71">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J71">
         <v>429</v>
@@ -7449,7 +7423,7 @@
       <c r="L71" t="s">
         <v>1383</v>
       </c>
-      <c r="N71" s="2">
+      <c r="N71" s="1">
         <v>46232</v>
       </c>
       <c r="Q71" t="b">
@@ -7472,7 +7446,7 @@
       <c r="E72" t="s">
         <v>896</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="1">
         <v>45803</v>
       </c>
       <c r="G72" t="s">
@@ -7501,7 +7475,7 @@
       <c r="E73" t="s">
         <v>897</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="1">
         <v>45803</v>
       </c>
       <c r="G73" t="s">
@@ -7511,7 +7485,7 @@
         <v>1353</v>
       </c>
       <c r="I73">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K73" t="s">
         <v>1356</v>
@@ -7539,7 +7513,7 @@
       <c r="E74" t="s">
         <v>896</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="1">
         <v>45803</v>
       </c>
       <c r="G74" t="s">
@@ -7568,7 +7542,7 @@
       <c r="E75" t="s">
         <v>898</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="1">
         <v>45803</v>
       </c>
       <c r="G75" t="s">
@@ -7578,7 +7552,7 @@
         <v>1353</v>
       </c>
       <c r="I75">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J75">
         <v>429</v>
@@ -7589,7 +7563,7 @@
       <c r="L75" t="s">
         <v>1383</v>
       </c>
-      <c r="N75" s="2">
+      <c r="N75" s="1">
         <v>46232</v>
       </c>
       <c r="Q75" t="b">
@@ -7612,7 +7586,7 @@
       <c r="E76" t="s">
         <v>899</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="1">
         <v>45803</v>
       </c>
       <c r="G76" t="s">
@@ -7622,7 +7596,7 @@
         <v>1353</v>
       </c>
       <c r="I76">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K76" t="s">
         <v>1363</v>
@@ -7647,7 +7621,7 @@
       <c r="E77" t="s">
         <v>900</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="1">
         <v>45803</v>
       </c>
       <c r="G77" t="s">
@@ -7676,7 +7650,7 @@
       <c r="E78" t="s">
         <v>901</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="1">
         <v>45803</v>
       </c>
       <c r="G78" t="s">
@@ -7705,7 +7679,7 @@
       <c r="E79" t="s">
         <v>902</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="1">
         <v>45803</v>
       </c>
       <c r="G79" t="s">
@@ -7715,7 +7689,7 @@
         <v>1353</v>
       </c>
       <c r="I79">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K79" t="s">
         <v>1363</v>
@@ -7740,7 +7714,7 @@
       <c r="E80" t="s">
         <v>903</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="1">
         <v>45803</v>
       </c>
       <c r="G80" t="s">
@@ -7750,7 +7724,7 @@
         <v>1353</v>
       </c>
       <c r="I80">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J80">
         <v>429</v>
@@ -7761,7 +7735,7 @@
       <c r="L80" t="s">
         <v>1383</v>
       </c>
-      <c r="N80" s="2">
+      <c r="N80" s="1">
         <v>46232</v>
       </c>
       <c r="Q80" t="b">
@@ -7784,7 +7758,7 @@
       <c r="E81" t="s">
         <v>904</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="1">
         <v>45813</v>
       </c>
       <c r="G81" t="s">
@@ -7813,7 +7787,7 @@
       <c r="E82" t="s">
         <v>905</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="1">
         <v>45813</v>
       </c>
       <c r="G82" t="s">
@@ -7823,7 +7797,7 @@
         <v>1353</v>
       </c>
       <c r="I82">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K82" t="s">
         <v>1360</v>
@@ -7851,7 +7825,7 @@
       <c r="E83" t="s">
         <v>906</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="1">
         <v>45813</v>
       </c>
       <c r="G83" t="s">
@@ -7880,7 +7854,7 @@
       <c r="E84" t="s">
         <v>907</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="1">
         <v>45813</v>
       </c>
       <c r="G84" t="s">
@@ -7890,7 +7864,7 @@
         <v>1353</v>
       </c>
       <c r="I84">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J84">
         <v>40</v>
@@ -7901,7 +7875,7 @@
       <c r="L84" t="s">
         <v>1384</v>
       </c>
-      <c r="N84" s="2">
+      <c r="N84" s="1">
         <v>45853</v>
       </c>
       <c r="O84">
@@ -7927,7 +7901,7 @@
       <c r="E85" t="s">
         <v>908</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="1">
         <v>45813</v>
       </c>
       <c r="G85" t="s">
@@ -7937,7 +7911,7 @@
         <v>1353</v>
       </c>
       <c r="I85">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K85" t="s">
         <v>1357</v>
@@ -7965,7 +7939,7 @@
       <c r="E86" t="s">
         <v>909</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="1">
         <v>45813</v>
       </c>
       <c r="G86" t="s">
@@ -7975,7 +7949,7 @@
         <v>1353</v>
       </c>
       <c r="I86">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K86" t="s">
         <v>1357</v>
@@ -8003,7 +7977,7 @@
       <c r="E87" t="s">
         <v>910</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="1">
         <v>45813</v>
       </c>
       <c r="G87" t="s">
@@ -8013,7 +7987,7 @@
         <v>1353</v>
       </c>
       <c r="I87">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J87">
         <v>-16</v>
@@ -8024,7 +7998,7 @@
       <c r="L87" t="s">
         <v>1385</v>
       </c>
-      <c r="N87" s="2">
+      <c r="N87" s="1">
         <v>45797</v>
       </c>
       <c r="O87" t="s">
@@ -8050,7 +8024,7 @@
       <c r="E88" t="s">
         <v>911</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="1">
         <v>45813</v>
       </c>
       <c r="G88" t="s">
@@ -8065,7 +8039,7 @@
       <c r="L88" t="s">
         <v>1386</v>
       </c>
-      <c r="N88" s="2">
+      <c r="N88" s="1">
         <v>46195</v>
       </c>
       <c r="Q88" t="b">
@@ -8088,7 +8062,7 @@
       <c r="E89" t="s">
         <v>912</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="1">
         <v>45813</v>
       </c>
       <c r="G89" t="s">
@@ -8103,7 +8077,7 @@
       <c r="L89" t="s">
         <v>1386</v>
       </c>
-      <c r="N89" s="2">
+      <c r="N89" s="1">
         <v>46195</v>
       </c>
       <c r="Q89" t="b">
@@ -8126,7 +8100,7 @@
       <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="1">
         <v>45831</v>
       </c>
       <c r="G90" t="s">
@@ -8136,7 +8110,7 @@
         <v>1353</v>
       </c>
       <c r="I90">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K90" t="s">
         <v>1330</v>
@@ -8167,7 +8141,7 @@
       <c r="E91" t="s">
         <v>914</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="1">
         <v>45831</v>
       </c>
       <c r="G91" t="s">
@@ -8177,7 +8151,7 @@
         <v>1353</v>
       </c>
       <c r="I91">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J91">
         <v>308</v>
@@ -8188,7 +8162,7 @@
       <c r="L91" t="s">
         <v>1388</v>
       </c>
-      <c r="N91" s="2">
+      <c r="N91" s="1">
         <v>46139</v>
       </c>
       <c r="Q91" t="b">
@@ -8208,7 +8182,7 @@
       <c r="D92" t="s">
         <v>748</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="1">
         <v>45831</v>
       </c>
       <c r="G92" t="s">
@@ -8237,7 +8211,7 @@
       <c r="E93" t="s">
         <v>915</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="1">
         <v>45831</v>
       </c>
       <c r="G93" t="s">
@@ -8247,7 +8221,7 @@
         <v>1353</v>
       </c>
       <c r="I93">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J93">
         <v>308</v>
@@ -8258,7 +8232,7 @@
       <c r="L93" t="s">
         <v>1388</v>
       </c>
-      <c r="N93" s="2">
+      <c r="N93" s="1">
         <v>46139</v>
       </c>
       <c r="Q93" t="b">
@@ -8281,7 +8255,7 @@
       <c r="E94" t="s">
         <v>916</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="1">
         <v>45831</v>
       </c>
       <c r="G94" t="s">
@@ -8291,7 +8265,7 @@
         <v>1353</v>
       </c>
       <c r="I94">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K94" t="s">
         <v>1360</v>
@@ -8319,7 +8293,7 @@
       <c r="E95" t="s">
         <v>917</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="1">
         <v>45831</v>
       </c>
       <c r="G95" t="s">
@@ -8329,7 +8303,7 @@
         <v>1353</v>
       </c>
       <c r="I95">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J95">
         <v>308</v>
@@ -8340,7 +8314,7 @@
       <c r="L95" t="s">
         <v>1388</v>
       </c>
-      <c r="N95" s="2">
+      <c r="N95" s="1">
         <v>46139</v>
       </c>
       <c r="Q95" t="b">
@@ -8363,7 +8337,7 @@
       <c r="E96" t="s">
         <v>918</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="1">
         <v>45831</v>
       </c>
       <c r="G96" t="s">
@@ -8373,7 +8347,7 @@
         <v>1353</v>
       </c>
       <c r="I96">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J96">
         <v>17</v>
@@ -8384,7 +8358,7 @@
       <c r="L96" t="s">
         <v>1369</v>
       </c>
-      <c r="N96" s="2">
+      <c r="N96" s="1">
         <v>45848</v>
       </c>
       <c r="O96" t="s">
@@ -8410,7 +8384,7 @@
       <c r="E97" t="s">
         <v>919</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="1">
         <v>45840</v>
       </c>
       <c r="G97" t="s">
@@ -8420,7 +8394,7 @@
         <v>1353</v>
       </c>
       <c r="I97">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J97">
         <v>20</v>
@@ -8431,7 +8405,7 @@
       <c r="L97" t="s">
         <v>1389</v>
       </c>
-      <c r="N97" s="2">
+      <c r="N97" s="1">
         <v>45860</v>
       </c>
       <c r="P97" t="s">
@@ -8457,7 +8431,7 @@
       <c r="E98" t="s">
         <v>920</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="1">
         <v>45840</v>
       </c>
       <c r="G98" t="s">
@@ -8467,7 +8441,7 @@
         <v>1353</v>
       </c>
       <c r="I98">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K98" t="s">
         <v>1360</v>
@@ -8495,7 +8469,7 @@
       <c r="E99" t="s">
         <v>921</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="1">
         <v>45840</v>
       </c>
       <c r="G99" t="s">
@@ -8524,7 +8498,7 @@
       <c r="E100" t="s">
         <v>922</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="1">
         <v>45840</v>
       </c>
       <c r="G100" t="s">
@@ -8534,7 +8508,7 @@
         <v>1353</v>
       </c>
       <c r="I100">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J100">
         <v>348</v>
@@ -8545,7 +8519,7 @@
       <c r="L100" t="s">
         <v>1388</v>
       </c>
-      <c r="N100" s="2">
+      <c r="N100" s="1">
         <v>46188</v>
       </c>
       <c r="Q100" t="b">
@@ -8568,7 +8542,7 @@
       <c r="E101" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="1">
         <v>45840</v>
       </c>
       <c r="G101" t="s">
@@ -8597,7 +8571,7 @@
       <c r="E102" t="s">
         <v>924</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="1">
         <v>45840</v>
       </c>
       <c r="G102" t="s">
@@ -8626,7 +8600,7 @@
       <c r="E103" t="s">
         <v>925</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="1">
         <v>45840</v>
       </c>
       <c r="G103" t="s">
@@ -8655,7 +8629,7 @@
       <c r="E104" t="s">
         <v>926</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="1">
         <v>45840</v>
       </c>
       <c r="G104" t="s">
@@ -8665,7 +8639,7 @@
         <v>1353</v>
       </c>
       <c r="I104">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J104">
         <v>348</v>
@@ -8676,7 +8650,7 @@
       <c r="L104" t="s">
         <v>1388</v>
       </c>
-      <c r="N104" s="2">
+      <c r="N104" s="1">
         <v>46188</v>
       </c>
       <c r="Q104" t="b">
@@ -8699,7 +8673,7 @@
       <c r="E105" t="s">
         <v>927</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="1">
         <v>45840</v>
       </c>
       <c r="G105" t="s">
@@ -8709,7 +8683,7 @@
         <v>1353</v>
       </c>
       <c r="I105">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J105">
         <v>348</v>
@@ -8720,7 +8694,7 @@
       <c r="L105" t="s">
         <v>1388</v>
       </c>
-      <c r="N105" s="2">
+      <c r="N105" s="1">
         <v>46188</v>
       </c>
       <c r="Q105" t="b">
@@ -8743,7 +8717,7 @@
       <c r="E106" t="s">
         <v>928</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="1">
         <v>45840</v>
       </c>
       <c r="G106" t="s">
@@ -8753,7 +8727,7 @@
         <v>1353</v>
       </c>
       <c r="I106">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J106">
         <v>49</v>
@@ -8764,7 +8738,7 @@
       <c r="L106" t="s">
         <v>1390</v>
       </c>
-      <c r="N106" s="2">
+      <c r="N106" s="1">
         <v>45889</v>
       </c>
       <c r="Q106" t="b">
@@ -8787,7 +8761,7 @@
       <c r="E107" t="s">
         <v>929</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="1">
         <v>45840</v>
       </c>
       <c r="G107" t="s">
@@ -8797,7 +8771,7 @@
         <v>1353</v>
       </c>
       <c r="I107">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J107">
         <v>36</v>
@@ -8808,7 +8782,7 @@
       <c r="L107" t="s">
         <v>1391</v>
       </c>
-      <c r="N107" s="2">
+      <c r="N107" s="1">
         <v>45876</v>
       </c>
       <c r="Q107" t="b">
@@ -8831,7 +8805,7 @@
       <c r="E108" t="s">
         <v>930</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="1">
         <v>45840</v>
       </c>
       <c r="G108" t="s">
@@ -8841,7 +8815,7 @@
         <v>1353</v>
       </c>
       <c r="I108">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K108" t="s">
         <v>1357</v>
@@ -8869,7 +8843,7 @@
       <c r="E109" t="s">
         <v>931</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="1">
         <v>45840</v>
       </c>
       <c r="G109" t="s">
@@ -8879,7 +8853,7 @@
         <v>1353</v>
       </c>
       <c r="I109">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K109" t="s">
         <v>1357</v>
@@ -8907,7 +8881,7 @@
       <c r="E110" t="s">
         <v>932</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="1">
         <v>45840</v>
       </c>
       <c r="G110" t="s">
@@ -8936,7 +8910,7 @@
       <c r="E111" t="s">
         <v>933</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="1">
         <v>45840</v>
       </c>
       <c r="G111" t="s">
@@ -8965,7 +8939,7 @@
       <c r="E112" t="s">
         <v>934</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="1">
         <v>45840</v>
       </c>
       <c r="G112" t="s">
@@ -8994,7 +8968,7 @@
       <c r="E113" t="s">
         <v>935</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="1">
         <v>45840</v>
       </c>
       <c r="G113" t="s">
@@ -9023,7 +8997,7 @@
       <c r="E114" t="s">
         <v>936</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="1">
         <v>45840</v>
       </c>
       <c r="G114" t="s">
@@ -9052,7 +9026,7 @@
       <c r="E115" t="s">
         <v>937</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="1">
         <v>45840</v>
       </c>
       <c r="G115" t="s">
@@ -9062,7 +9036,7 @@
         <v>1353</v>
       </c>
       <c r="I115">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K115" t="s">
         <v>1357</v>
@@ -9090,7 +9064,7 @@
       <c r="E116" t="s">
         <v>938</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="1">
         <v>45840</v>
       </c>
       <c r="G116" t="s">
@@ -9100,7 +9074,7 @@
         <v>1353</v>
       </c>
       <c r="I116">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K116" t="s">
         <v>1357</v>
@@ -9128,7 +9102,7 @@
       <c r="E117" t="s">
         <v>939</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="1">
         <v>45840</v>
       </c>
       <c r="G117" t="s">
@@ -9138,7 +9112,7 @@
         <v>1353</v>
       </c>
       <c r="I117">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K117" t="s">
         <v>1357</v>
@@ -9166,7 +9140,7 @@
       <c r="E118" t="s">
         <v>940</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="1">
         <v>45840</v>
       </c>
       <c r="G118" t="s">
@@ -9176,7 +9150,7 @@
         <v>1353</v>
       </c>
       <c r="I118">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K118" t="s">
         <v>1357</v>
@@ -9204,7 +9178,7 @@
       <c r="E119" t="s">
         <v>941</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="1">
         <v>45840</v>
       </c>
       <c r="G119" t="s">
@@ -9214,7 +9188,7 @@
         <v>1353</v>
       </c>
       <c r="I119">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K119" t="s">
         <v>1357</v>
@@ -9242,7 +9216,7 @@
       <c r="E120" t="s">
         <v>942</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="1">
         <v>45840</v>
       </c>
       <c r="G120" t="s">
@@ -9252,7 +9226,7 @@
         <v>1353</v>
       </c>
       <c r="I120">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K120" t="s">
         <v>1357</v>
@@ -9280,7 +9254,7 @@
       <c r="E121" t="s">
         <v>943</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="1">
         <v>45849</v>
       </c>
       <c r="G121" t="s">
@@ -9290,7 +9264,7 @@
         <v>1353</v>
       </c>
       <c r="I121">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J121">
         <v>251</v>
@@ -9301,7 +9275,7 @@
       <c r="L121" t="s">
         <v>1379</v>
       </c>
-      <c r="N121" s="2">
+      <c r="N121" s="1">
         <v>46100</v>
       </c>
       <c r="O121">
@@ -9327,7 +9301,7 @@
       <c r="E122" t="s">
         <v>944</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="1">
         <v>45849</v>
       </c>
       <c r="G122" t="s">
@@ -9337,7 +9311,7 @@
         <v>1353</v>
       </c>
       <c r="I122">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K122" t="s">
         <v>1357</v>
@@ -9365,7 +9339,7 @@
       <c r="E123" t="s">
         <v>945</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="1">
         <v>45849</v>
       </c>
       <c r="G123" t="s">
@@ -9394,7 +9368,7 @@
       <c r="E124" t="s">
         <v>946</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="1">
         <v>45853</v>
       </c>
       <c r="G124" t="s">
@@ -9404,7 +9378,7 @@
         <v>1353</v>
       </c>
       <c r="I124">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K124" t="s">
         <v>1357</v>
@@ -9432,7 +9406,7 @@
       <c r="E125" t="s">
         <v>947</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="1">
         <v>45855</v>
       </c>
       <c r="G125" t="s">
@@ -9442,7 +9416,7 @@
         <v>1353</v>
       </c>
       <c r="I125">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K125" t="s">
         <v>1363</v>
@@ -9470,7 +9444,7 @@
       <c r="E126" t="s">
         <v>948</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="1">
         <v>45855</v>
       </c>
       <c r="G126" t="s">
@@ -9499,7 +9473,7 @@
       <c r="E127" t="s">
         <v>949</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="1">
         <v>45856</v>
       </c>
       <c r="G127" t="s">
@@ -9528,7 +9502,7 @@
       <c r="E128" t="s">
         <v>950</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="1">
         <v>45869</v>
       </c>
       <c r="G128" t="s">
@@ -9538,7 +9512,7 @@
         <v>1353</v>
       </c>
       <c r="I128">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K128" t="s">
         <v>1357</v>
@@ -9566,7 +9540,7 @@
       <c r="E129" t="s">
         <v>951</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="1">
         <v>45869</v>
       </c>
       <c r="G129" t="s">
@@ -9576,7 +9550,7 @@
         <v>1353</v>
       </c>
       <c r="I129">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K129" t="s">
         <v>1356</v>
@@ -9604,7 +9578,7 @@
       <c r="E130" t="s">
         <v>952</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="1">
         <v>45869</v>
       </c>
       <c r="G130" t="s">
@@ -9614,7 +9588,7 @@
         <v>1353</v>
       </c>
       <c r="I130">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J130">
         <v>47</v>
@@ -9625,7 +9599,7 @@
       <c r="L130" t="s">
         <v>1392</v>
       </c>
-      <c r="N130" s="2">
+      <c r="N130" s="1">
         <v>45916</v>
       </c>
       <c r="O130">
@@ -9651,7 +9625,7 @@
       <c r="E131" t="s">
         <v>953</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="1">
         <v>45869</v>
       </c>
       <c r="G131" t="s">
@@ -9680,7 +9654,7 @@
       <c r="E132" t="s">
         <v>954</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="1">
         <v>45869</v>
       </c>
       <c r="G132" t="s">
@@ -9690,7 +9664,7 @@
         <v>1353</v>
       </c>
       <c r="I132">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J132">
         <v>145</v>
@@ -9701,7 +9675,7 @@
       <c r="L132" t="s">
         <v>1393</v>
       </c>
-      <c r="N132" s="2">
+      <c r="N132" s="1">
         <v>46014</v>
       </c>
       <c r="O132">
@@ -9727,7 +9701,7 @@
       <c r="E133" t="s">
         <v>955</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="1">
         <v>45869</v>
       </c>
       <c r="G133" t="s">
@@ -9756,7 +9730,7 @@
       <c r="E134" t="s">
         <v>956</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="1">
         <v>45882</v>
       </c>
       <c r="G134" t="s">
@@ -9766,7 +9740,7 @@
         <v>1353</v>
       </c>
       <c r="I134">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K134" t="s">
         <v>1356</v>
@@ -9794,7 +9768,7 @@
       <c r="E135" t="s">
         <v>957</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="1">
         <v>45882</v>
       </c>
       <c r="G135" t="s">
@@ -9823,7 +9797,7 @@
       <c r="E136" t="s">
         <v>958</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="1">
         <v>45891</v>
       </c>
       <c r="G136" t="s">
@@ -9852,7 +9826,7 @@
       <c r="E137" t="s">
         <v>959</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="1">
         <v>45891</v>
       </c>
       <c r="G137" t="s">
@@ -9881,7 +9855,7 @@
       <c r="E138" t="s">
         <v>960</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="1">
         <v>45891</v>
       </c>
       <c r="G138" t="s">
@@ -9891,7 +9865,7 @@
         <v>1353</v>
       </c>
       <c r="I138">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K138" t="s">
         <v>1357</v>
@@ -9919,7 +9893,7 @@
       <c r="E139" t="s">
         <v>961</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="1">
         <v>45891</v>
       </c>
       <c r="G139" t="s">
@@ -9948,7 +9922,7 @@
       <c r="E140" t="s">
         <v>962</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="1">
         <v>45891</v>
       </c>
       <c r="G140" t="s">
@@ -9977,7 +9951,7 @@
       <c r="E141" t="s">
         <v>963</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="1">
         <v>45891</v>
       </c>
       <c r="G141" t="s">
@@ -10006,7 +9980,7 @@
       <c r="E142" t="s">
         <v>964</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="1">
         <v>45891</v>
       </c>
       <c r="G142" t="s">
@@ -10035,7 +10009,7 @@
       <c r="E143" t="s">
         <v>965</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="1">
         <v>45891</v>
       </c>
       <c r="G143" t="s">
@@ -10064,7 +10038,7 @@
       <c r="E144" t="s">
         <v>966</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="1">
         <v>45891</v>
       </c>
       <c r="G144" t="s">
@@ -10093,7 +10067,7 @@
       <c r="E145" t="s">
         <v>967</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="1">
         <v>45891</v>
       </c>
       <c r="G145" t="s">
@@ -10122,7 +10096,7 @@
       <c r="E146" t="s">
         <v>968</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="1">
         <v>45891</v>
       </c>
       <c r="G146" t="s">
@@ -10151,7 +10125,7 @@
       <c r="E147" t="s">
         <v>969</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="1">
         <v>45891</v>
       </c>
       <c r="G147" t="s">
@@ -10180,7 +10154,7 @@
       <c r="E148" t="s">
         <v>970</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="1">
         <v>45891</v>
       </c>
       <c r="G148" t="s">
@@ -10190,7 +10164,7 @@
         <v>1353</v>
       </c>
       <c r="I148">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J148">
         <v>341</v>
@@ -10201,7 +10175,7 @@
       <c r="L148" t="s">
         <v>1383</v>
       </c>
-      <c r="N148" s="2">
+      <c r="N148" s="1">
         <v>46232</v>
       </c>
       <c r="Q148" t="b">
@@ -10224,7 +10198,7 @@
       <c r="E149" t="s">
         <v>971</v>
       </c>
-      <c r="F149" s="2">
+      <c r="F149" s="1">
         <v>45891</v>
       </c>
       <c r="G149" t="s">
@@ -10234,7 +10208,7 @@
         <v>1353</v>
       </c>
       <c r="I149">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J149">
         <v>374</v>
@@ -10245,7 +10219,7 @@
       <c r="L149" t="s">
         <v>1394</v>
       </c>
-      <c r="N149" s="2">
+      <c r="N149" s="1">
         <v>46265</v>
       </c>
       <c r="P149" t="s">
@@ -10271,7 +10245,7 @@
       <c r="E150" t="s">
         <v>972</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="1">
         <v>45891</v>
       </c>
       <c r="G150" t="s">
@@ -10281,7 +10255,7 @@
         <v>1353</v>
       </c>
       <c r="I150">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J150">
         <v>201</v>
@@ -10292,7 +10266,7 @@
       <c r="L150" t="s">
         <v>1381</v>
       </c>
-      <c r="N150" s="2">
+      <c r="N150" s="1">
         <v>46092</v>
       </c>
       <c r="P150" t="s">
@@ -10318,7 +10292,7 @@
       <c r="E151" t="s">
         <v>973</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="1">
         <v>45891</v>
       </c>
       <c r="G151" t="s">
@@ -10347,7 +10321,7 @@
       <c r="E152" t="s">
         <v>963</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="1">
         <v>45891</v>
       </c>
       <c r="G152" t="s">
@@ -10357,7 +10331,7 @@
         <v>1353</v>
       </c>
       <c r="I152">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J152">
         <v>228</v>
@@ -10368,7 +10342,7 @@
       <c r="L152" t="s">
         <v>1382</v>
       </c>
-      <c r="N152" s="2">
+      <c r="N152" s="1">
         <v>46119</v>
       </c>
       <c r="Q152" t="b">
@@ -10391,7 +10365,7 @@
       <c r="E153" t="s">
         <v>974</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="1">
         <v>45891</v>
       </c>
       <c r="G153" t="s">
@@ -10409,7 +10383,7 @@
       <c r="L153" t="s">
         <v>1383</v>
       </c>
-      <c r="N153" s="2">
+      <c r="N153" s="1">
         <v>46232</v>
       </c>
       <c r="Q153" t="b">
@@ -10432,7 +10406,7 @@
       <c r="E154" t="s">
         <v>975</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="1">
         <v>45891</v>
       </c>
       <c r="G154" t="s">
@@ -10461,7 +10435,7 @@
       <c r="E155" t="s">
         <v>976</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="1">
         <v>45891</v>
       </c>
       <c r="G155" t="s">
@@ -10471,7 +10445,7 @@
         <v>1353</v>
       </c>
       <c r="I155">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K155" t="s">
         <v>1363</v>
@@ -10496,7 +10470,7 @@
       <c r="E156" t="s">
         <v>977</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="1">
         <v>45891</v>
       </c>
       <c r="G156" t="s">
@@ -10506,7 +10480,7 @@
         <v>1353</v>
       </c>
       <c r="I156">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K156" t="s">
         <v>1357</v>
@@ -10534,7 +10508,7 @@
       <c r="E157" t="s">
         <v>978</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="1">
         <v>45891</v>
       </c>
       <c r="G157" t="s">
@@ -10544,7 +10518,7 @@
         <v>1353</v>
       </c>
       <c r="I157">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J157">
         <v>371</v>
@@ -10555,7 +10529,7 @@
       <c r="L157" t="s">
         <v>1395</v>
       </c>
-      <c r="N157" s="2">
+      <c r="N157" s="1">
         <v>46262</v>
       </c>
       <c r="Q157" t="b">
@@ -10578,7 +10552,7 @@
       <c r="E158" t="s">
         <v>979</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="1">
         <v>45894</v>
       </c>
       <c r="G158" t="s">
@@ -10588,7 +10562,7 @@
         <v>1353</v>
       </c>
       <c r="I158">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J158">
         <v>52</v>
@@ -10599,7 +10573,7 @@
       <c r="L158" t="s">
         <v>1396</v>
       </c>
-      <c r="N158" s="2">
+      <c r="N158" s="1">
         <v>45946</v>
       </c>
       <c r="Q158" t="b">
@@ -10622,7 +10596,7 @@
       <c r="E159" t="s">
         <v>980</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="1">
         <v>45894</v>
       </c>
       <c r="G159" t="s">
@@ -10632,7 +10606,7 @@
         <v>1353</v>
       </c>
       <c r="I159">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K159" t="s">
         <v>1357</v>
@@ -10660,7 +10634,7 @@
       <c r="E160" t="s">
         <v>981</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="1">
         <v>45898</v>
       </c>
       <c r="G160" t="s">
@@ -10670,7 +10644,7 @@
         <v>1353</v>
       </c>
       <c r="I160">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K160" t="s">
         <v>1357</v>
@@ -10698,7 +10672,7 @@
       <c r="E161" t="s">
         <v>982</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="1">
         <v>45898</v>
       </c>
       <c r="G161" t="s">
@@ -10708,7 +10682,7 @@
         <v>1353</v>
       </c>
       <c r="I161">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J161">
         <v>55</v>
@@ -10719,7 +10693,7 @@
       <c r="L161" t="s">
         <v>1397</v>
       </c>
-      <c r="N161" s="2">
+      <c r="N161" s="1">
         <v>45953</v>
       </c>
       <c r="O161" t="s">
@@ -10745,7 +10719,7 @@
       <c r="E162" t="s">
         <v>983</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="1">
         <v>45898</v>
       </c>
       <c r="G162" t="s">
@@ -10755,7 +10729,7 @@
         <v>1353</v>
       </c>
       <c r="I162">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J162">
         <v>42</v>
@@ -10766,7 +10740,7 @@
       <c r="L162" t="s">
         <v>1398</v>
       </c>
-      <c r="N162" s="2">
+      <c r="N162" s="1">
         <v>45940</v>
       </c>
       <c r="Q162" t="b">
@@ -10789,7 +10763,7 @@
       <c r="E163" t="s">
         <v>984</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="1">
         <v>45898</v>
       </c>
       <c r="G163" t="s">
@@ -10799,7 +10773,7 @@
         <v>1353</v>
       </c>
       <c r="I163">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J163">
         <v>42</v>
@@ -10810,7 +10784,7 @@
       <c r="L163" t="s">
         <v>1398</v>
       </c>
-      <c r="N163" s="2">
+      <c r="N163" s="1">
         <v>45940</v>
       </c>
       <c r="Q163" t="b">
@@ -10833,7 +10807,7 @@
       <c r="E164" t="s">
         <v>985</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="1">
         <v>45910</v>
       </c>
       <c r="G164" t="s">
@@ -10843,7 +10817,7 @@
         <v>1355</v>
       </c>
       <c r="I164">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O164" t="s">
         <v>1469</v>
@@ -10868,7 +10842,7 @@
       <c r="E165" t="s">
         <v>986</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="1">
         <v>45917</v>
       </c>
       <c r="G165" t="s">
@@ -10886,7 +10860,7 @@
       <c r="L165" t="s">
         <v>1399</v>
       </c>
-      <c r="N165" s="2">
+      <c r="N165" s="1">
         <v>46204</v>
       </c>
       <c r="P165" t="s">
@@ -10912,7 +10886,7 @@
       <c r="E166" t="s">
         <v>987</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="1">
         <v>45917</v>
       </c>
       <c r="G166" t="s">
@@ -10941,7 +10915,7 @@
       <c r="E167" t="s">
         <v>988</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="1">
         <v>45917</v>
       </c>
       <c r="G167" t="s">
@@ -10970,7 +10944,7 @@
       <c r="E168" t="s">
         <v>989</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="1">
         <v>45917</v>
       </c>
       <c r="G168" t="s">
@@ -10980,7 +10954,7 @@
         <v>1353</v>
       </c>
       <c r="I168">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K168" t="s">
         <v>1360</v>
@@ -11011,7 +10985,7 @@
       <c r="E169" t="s">
         <v>990</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="1">
         <v>45917</v>
       </c>
       <c r="G169" t="s">
@@ -11021,7 +10995,7 @@
         <v>1353</v>
       </c>
       <c r="I169">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K169" t="s">
         <v>1330</v>
@@ -11029,7 +11003,7 @@
       <c r="L169" t="s">
         <v>1401</v>
       </c>
-      <c r="N169" s="2">
+      <c r="N169" s="1">
         <v>45973</v>
       </c>
       <c r="Q169" t="b">
@@ -11052,7 +11026,7 @@
       <c r="E170" t="s">
         <v>991</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="1">
         <v>45917</v>
       </c>
       <c r="G170" t="s">
@@ -11087,7 +11061,7 @@
       <c r="E171" t="s">
         <v>992</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="1">
         <v>45917</v>
       </c>
       <c r="G171" t="s">
@@ -11097,7 +11071,7 @@
         <v>1353</v>
       </c>
       <c r="I171">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K171" t="s">
         <v>1357</v>
@@ -11125,7 +11099,7 @@
       <c r="E172" t="s">
         <v>993</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="1">
         <v>45917</v>
       </c>
       <c r="G172" t="s">
@@ -11154,7 +11128,7 @@
       <c r="E173" t="s">
         <v>994</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="1">
         <v>45917</v>
       </c>
       <c r="G173" t="s">
@@ -11183,7 +11157,7 @@
       <c r="E174" t="s">
         <v>995</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="1">
         <v>45917</v>
       </c>
       <c r="G174" t="s">
@@ -11198,7 +11172,7 @@
       <c r="L174" t="s">
         <v>1386</v>
       </c>
-      <c r="N174" s="2">
+      <c r="N174" s="1">
         <v>46195</v>
       </c>
       <c r="Q174" t="b">
@@ -11221,7 +11195,7 @@
       <c r="E175" t="s">
         <v>996</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="1">
         <v>45917</v>
       </c>
       <c r="G175" t="s">
@@ -11231,7 +11205,7 @@
         <v>1353</v>
       </c>
       <c r="I175">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J175">
         <v>205</v>
@@ -11242,7 +11216,7 @@
       <c r="L175" t="s">
         <v>1402</v>
       </c>
-      <c r="N175" s="2">
+      <c r="N175" s="1">
         <v>46122</v>
       </c>
       <c r="P175" t="s">
@@ -11268,7 +11242,7 @@
       <c r="E176" t="s">
         <v>900</v>
       </c>
-      <c r="F176" s="2">
+      <c r="F176" s="1">
         <v>45917</v>
       </c>
       <c r="G176" t="s">
@@ -11278,7 +11252,7 @@
         <v>1353</v>
       </c>
       <c r="I176">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K176" t="s">
         <v>1357</v>
@@ -11306,7 +11280,7 @@
       <c r="E177" t="s">
         <v>997</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="1">
         <v>45917</v>
       </c>
       <c r="G177" t="s">
@@ -11316,7 +11290,7 @@
         <v>1353</v>
       </c>
       <c r="I177">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J177">
         <v>44</v>
@@ -11327,7 +11301,7 @@
       <c r="L177" t="s">
         <v>1403</v>
       </c>
-      <c r="N177" s="2">
+      <c r="N177" s="1">
         <v>45961</v>
       </c>
       <c r="P177" t="s">
@@ -11353,7 +11327,7 @@
       <c r="E178" t="s">
         <v>998</v>
       </c>
-      <c r="F178" s="2">
+      <c r="F178" s="1">
         <v>45937</v>
       </c>
       <c r="G178" t="s">
@@ -11363,7 +11337,7 @@
         <v>1353</v>
       </c>
       <c r="I178">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K178" t="s">
         <v>1356</v>
@@ -11391,7 +11365,7 @@
       <c r="E179" t="s">
         <v>999</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="1">
         <v>45937</v>
       </c>
       <c r="G179" t="s">
@@ -11420,7 +11394,7 @@
       <c r="E180" t="s">
         <v>1000</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="1">
         <v>45937</v>
       </c>
       <c r="G180" t="s">
@@ -11430,7 +11404,7 @@
         <v>1353</v>
       </c>
       <c r="I180">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K180" t="s">
         <v>1356</v>
@@ -11458,7 +11432,7 @@
       <c r="E181" t="s">
         <v>1001</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="1">
         <v>45937</v>
       </c>
       <c r="G181" t="s">
@@ -11487,7 +11461,7 @@
       <c r="E182" t="s">
         <v>1002</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="1">
         <v>45937</v>
       </c>
       <c r="G182" t="s">
@@ -11516,7 +11490,7 @@
       <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="F183" s="2">
+      <c r="F183" s="1">
         <v>45937</v>
       </c>
       <c r="G183" t="s">
@@ -11526,7 +11500,7 @@
         <v>1353</v>
       </c>
       <c r="I183">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K183" t="s">
         <v>1357</v>
@@ -11554,7 +11528,7 @@
       <c r="D184" t="s">
         <v>774</v>
       </c>
-      <c r="F184" s="2">
+      <c r="F184" s="1">
         <v>45939</v>
       </c>
       <c r="G184" t="s">
@@ -11564,7 +11538,7 @@
         <v>1353</v>
       </c>
       <c r="I184">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K184" t="s">
         <v>1363</v>
@@ -11589,7 +11563,7 @@
       <c r="E185" t="s">
         <v>1004</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="1">
         <v>45939</v>
       </c>
       <c r="G185" t="s">
@@ -11599,7 +11573,7 @@
         <v>1353</v>
       </c>
       <c r="I185">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K185" t="s">
         <v>1357</v>
@@ -11627,7 +11601,7 @@
       <c r="E186" t="s">
         <v>1005</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="1">
         <v>45939</v>
       </c>
       <c r="G186" t="s">
@@ -11637,7 +11611,7 @@
         <v>1353</v>
       </c>
       <c r="I186">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K186" t="s">
         <v>1357</v>
@@ -11665,7 +11639,7 @@
       <c r="E187" t="s">
         <v>1006</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="1">
         <v>45939</v>
       </c>
       <c r="G187" t="s">
@@ -11675,7 +11649,7 @@
         <v>1353</v>
       </c>
       <c r="I187">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J187">
         <v>75</v>
@@ -11686,7 +11660,7 @@
       <c r="L187" t="s">
         <v>1404</v>
       </c>
-      <c r="N187" s="2">
+      <c r="N187" s="1">
         <v>46014</v>
       </c>
       <c r="O187">
@@ -11712,7 +11686,7 @@
       <c r="E188" t="s">
         <v>1007</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="1">
         <v>45946</v>
       </c>
       <c r="G188" t="s">
@@ -11722,7 +11696,7 @@
         <v>1353</v>
       </c>
       <c r="I188">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J188">
         <v>40</v>
@@ -11733,7 +11707,7 @@
       <c r="L188" t="s">
         <v>1405</v>
       </c>
-      <c r="N188" s="2">
+      <c r="N188" s="1">
         <v>45986</v>
       </c>
       <c r="P188" t="s">
@@ -11759,7 +11733,7 @@
       <c r="E189" t="s">
         <v>1008</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="1">
         <v>45965</v>
       </c>
       <c r="G189" t="s">
@@ -11769,7 +11743,7 @@
         <v>1353</v>
       </c>
       <c r="I189">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J189">
         <v>155</v>
@@ -11780,7 +11754,7 @@
       <c r="L189" t="s">
         <v>1406</v>
       </c>
-      <c r="N189" s="2">
+      <c r="N189" s="1">
         <v>46120</v>
       </c>
       <c r="Q189" t="b">
@@ -11803,7 +11777,7 @@
       <c r="E190" t="s">
         <v>1009</v>
       </c>
-      <c r="F190" s="2">
+      <c r="F190" s="1">
         <v>45965</v>
       </c>
       <c r="G190" t="s">
@@ -11813,7 +11787,7 @@
         <v>1353</v>
       </c>
       <c r="I190">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J190">
         <v>107</v>
@@ -11824,7 +11798,7 @@
       <c r="L190" t="s">
         <v>1407</v>
       </c>
-      <c r="N190" s="2">
+      <c r="N190" s="1">
         <v>46072</v>
       </c>
       <c r="Q190" t="b">
@@ -11847,7 +11821,7 @@
       <c r="E191" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="2">
+      <c r="F191" s="1">
         <v>45967</v>
       </c>
       <c r="G191" t="s">
@@ -11857,7 +11831,7 @@
         <v>1353</v>
       </c>
       <c r="I191">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J191">
         <v>5</v>
@@ -11868,7 +11842,7 @@
       <c r="L191" t="s">
         <v>1408</v>
       </c>
-      <c r="N191" s="2">
+      <c r="N191" s="1">
         <v>45972</v>
       </c>
       <c r="Q191" t="b">
@@ -11891,7 +11865,7 @@
       <c r="E192" t="s">
         <v>1011</v>
       </c>
-      <c r="F192" s="2">
+      <c r="F192" s="1">
         <v>45968</v>
       </c>
       <c r="G192" t="s">
@@ -11901,7 +11875,7 @@
         <v>1353</v>
       </c>
       <c r="I192">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K192" t="s">
         <v>1357</v>
@@ -11929,7 +11903,7 @@
       <c r="E193" t="s">
         <v>1012</v>
       </c>
-      <c r="F193" s="2">
+      <c r="F193" s="1">
         <v>45968</v>
       </c>
       <c r="G193" t="s">
@@ -11939,7 +11913,7 @@
         <v>1353</v>
       </c>
       <c r="I193">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K193" t="s">
         <v>1362</v>
@@ -11967,7 +11941,7 @@
       <c r="E194" t="s">
         <v>1013</v>
       </c>
-      <c r="F194" s="2">
+      <c r="F194" s="1">
         <v>45968</v>
       </c>
       <c r="G194" t="s">
@@ -11996,7 +11970,7 @@
       <c r="E195" t="s">
         <v>1014</v>
       </c>
-      <c r="F195" s="2">
+      <c r="F195" s="1">
         <v>45971</v>
       </c>
       <c r="G195" t="s">
@@ -12006,7 +11980,7 @@
         <v>1353</v>
       </c>
       <c r="I195">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J195">
         <v>186</v>
@@ -12017,7 +11991,7 @@
       <c r="L195" t="s">
         <v>1409</v>
       </c>
-      <c r="N195" s="2">
+      <c r="N195" s="1">
         <v>46157</v>
       </c>
       <c r="Q195" t="b">
@@ -12040,7 +12014,7 @@
       <c r="E196" t="s">
         <v>1015</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="1">
         <v>45978</v>
       </c>
       <c r="G196" t="s">
@@ -12069,7 +12043,7 @@
       <c r="E197" t="s">
         <v>1016</v>
       </c>
-      <c r="F197" s="2">
+      <c r="F197" s="1">
         <v>45978</v>
       </c>
       <c r="G197" t="s">
@@ -12098,7 +12072,7 @@
       <c r="E198" t="s">
         <v>1017</v>
       </c>
-      <c r="F198" s="2">
+      <c r="F198" s="1">
         <v>45978</v>
       </c>
       <c r="G198" t="s">
@@ -12127,7 +12101,7 @@
       <c r="E199" t="s">
         <v>1018</v>
       </c>
-      <c r="F199" s="2">
+      <c r="F199" s="1">
         <v>45979</v>
       </c>
       <c r="G199" t="s">
@@ -12137,7 +12111,7 @@
         <v>1353</v>
       </c>
       <c r="I199">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J199">
         <v>70</v>
@@ -12148,7 +12122,7 @@
       <c r="L199" t="s">
         <v>1410</v>
       </c>
-      <c r="N199" s="2">
+      <c r="N199" s="1">
         <v>46049</v>
       </c>
       <c r="Q199" t="b">
@@ -12171,7 +12145,7 @@
       <c r="E200" t="s">
         <v>1019</v>
       </c>
-      <c r="F200" s="2">
+      <c r="F200" s="1">
         <v>45986</v>
       </c>
       <c r="G200" t="s">
@@ -12181,7 +12155,7 @@
         <v>1353</v>
       </c>
       <c r="I200">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J200">
         <v>170</v>
@@ -12192,7 +12166,7 @@
       <c r="L200" t="s">
         <v>1409</v>
       </c>
-      <c r="N200" s="2">
+      <c r="N200" s="1">
         <v>46156</v>
       </c>
       <c r="Q200" t="b">
@@ -12215,7 +12189,7 @@
       <c r="E201" t="s">
         <v>1020</v>
       </c>
-      <c r="F201" s="2">
+      <c r="F201" s="1">
         <v>45986</v>
       </c>
       <c r="G201" t="s">
@@ -12225,7 +12199,7 @@
         <v>1353</v>
       </c>
       <c r="I201">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K201" t="s">
         <v>1357</v>
@@ -12253,7 +12227,7 @@
       <c r="E202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" s="2">
+      <c r="F202" s="1">
         <v>45986</v>
       </c>
       <c r="G202" t="s">
@@ -12263,7 +12237,7 @@
         <v>1353</v>
       </c>
       <c r="I202">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K202" t="s">
         <v>1357</v>
@@ -12291,7 +12265,7 @@
       <c r="E203" t="s">
         <v>1022</v>
       </c>
-      <c r="F203" s="2">
+      <c r="F203" s="1">
         <v>45986</v>
       </c>
       <c r="G203" t="s">
@@ -12309,7 +12283,7 @@
       <c r="L203" t="s">
         <v>1411</v>
       </c>
-      <c r="N203" s="2">
+      <c r="N203" s="1">
         <v>46232</v>
       </c>
       <c r="Q203" t="b">
@@ -12332,7 +12306,7 @@
       <c r="E204" t="s">
         <v>1023</v>
       </c>
-      <c r="F204" s="2">
+      <c r="F204" s="1">
         <v>45986</v>
       </c>
       <c r="G204" t="s">
@@ -12342,7 +12316,7 @@
         <v>1353</v>
       </c>
       <c r="I204">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K204" t="s">
         <v>1356</v>
@@ -12370,7 +12344,7 @@
       <c r="E205" t="s">
         <v>1024</v>
       </c>
-      <c r="F205" s="2">
+      <c r="F205" s="1">
         <v>45986</v>
       </c>
       <c r="G205" t="s">
@@ -12380,7 +12354,7 @@
         <v>1353</v>
       </c>
       <c r="I205">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K205" t="s">
         <v>1356</v>
@@ -12408,7 +12382,7 @@
       <c r="E206" t="s">
         <v>1025</v>
       </c>
-      <c r="F206" s="2">
+      <c r="F206" s="1">
         <v>45986</v>
       </c>
       <c r="G206" t="s">
@@ -12437,7 +12411,7 @@
       <c r="E207" t="s">
         <v>1026</v>
       </c>
-      <c r="F207" s="2">
+      <c r="F207" s="1">
         <v>45986</v>
       </c>
       <c r="G207" t="s">
@@ -12447,7 +12421,7 @@
         <v>1353</v>
       </c>
       <c r="I207">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J207">
         <v>167</v>
@@ -12458,7 +12432,7 @@
       <c r="L207" t="s">
         <v>1412</v>
       </c>
-      <c r="N207" s="2">
+      <c r="N207" s="1">
         <v>46153</v>
       </c>
       <c r="Q207" t="b">
@@ -12481,7 +12455,7 @@
       <c r="E208" t="s">
         <v>1027</v>
       </c>
-      <c r="F208" s="2">
+      <c r="F208" s="1">
         <v>45986</v>
       </c>
       <c r="G208" t="s">
@@ -12491,7 +12465,7 @@
         <v>1353</v>
       </c>
       <c r="I208">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J208">
         <v>45</v>
@@ -12502,7 +12476,7 @@
       <c r="L208" t="s">
         <v>1413</v>
       </c>
-      <c r="N208" s="2">
+      <c r="N208" s="1">
         <v>46031</v>
       </c>
       <c r="Q208" t="b">
@@ -12525,7 +12499,7 @@
       <c r="E209" t="s">
         <v>1028</v>
       </c>
-      <c r="F209" s="2">
+      <c r="F209" s="1">
         <v>46000</v>
       </c>
       <c r="G209" t="s">
@@ -12535,7 +12509,7 @@
         <v>1353</v>
       </c>
       <c r="I209">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J209">
         <v>191</v>
@@ -12546,7 +12520,7 @@
       <c r="L209" t="s">
         <v>1414</v>
       </c>
-      <c r="N209" s="2">
+      <c r="N209" s="1">
         <v>46191</v>
       </c>
       <c r="Q209" t="b">
@@ -12569,7 +12543,7 @@
       <c r="E210" t="s">
         <v>1029</v>
       </c>
-      <c r="F210" s="2">
+      <c r="F210" s="1">
         <v>46000</v>
       </c>
       <c r="G210" t="s">
@@ -12579,7 +12553,7 @@
         <v>1353</v>
       </c>
       <c r="I210">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K210" t="s">
         <v>1360</v>
@@ -12607,7 +12581,7 @@
       <c r="E211" t="s">
         <v>1030</v>
       </c>
-      <c r="F211" s="2">
+      <c r="F211" s="1">
         <v>46000</v>
       </c>
       <c r="G211" t="s">
@@ -12636,7 +12610,7 @@
       <c r="E212" t="s">
         <v>1031</v>
       </c>
-      <c r="F212" s="2">
+      <c r="F212" s="1">
         <v>46000</v>
       </c>
       <c r="G212" t="s">
@@ -12665,7 +12639,7 @@
       <c r="E213" t="s">
         <v>1032</v>
       </c>
-      <c r="F213" s="2">
+      <c r="F213" s="1">
         <v>46007</v>
       </c>
       <c r="G213" t="s">
@@ -12675,7 +12649,7 @@
         <v>1353</v>
       </c>
       <c r="I213">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K213" t="s">
         <v>1357</v>
@@ -12703,7 +12677,7 @@
       <c r="E214" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="2">
+      <c r="F214" s="1">
         <v>46007</v>
       </c>
       <c r="G214" t="s">
@@ -12713,7 +12687,7 @@
         <v>1353</v>
       </c>
       <c r="I214">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J214">
         <v>14</v>
@@ -12724,7 +12698,7 @@
       <c r="L214" t="s">
         <v>1415</v>
       </c>
-      <c r="N214" s="2">
+      <c r="N214" s="1">
         <v>46021</v>
       </c>
       <c r="O214">
@@ -12750,7 +12724,7 @@
       <c r="E215" t="s">
         <v>1034</v>
       </c>
-      <c r="F215" s="2">
+      <c r="F215" s="1">
         <v>46007</v>
       </c>
       <c r="G215" t="s">
@@ -12760,7 +12734,7 @@
         <v>1353</v>
       </c>
       <c r="I215">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K215" t="s">
         <v>1357</v>
@@ -12788,7 +12762,7 @@
       <c r="E216" t="s">
         <v>1035</v>
       </c>
-      <c r="F216" s="2">
+      <c r="F216" s="1">
         <v>46010</v>
       </c>
       <c r="G216" t="s">
@@ -12817,7 +12791,7 @@
       <c r="E217" t="s">
         <v>1036</v>
       </c>
-      <c r="F217" s="2">
+      <c r="F217" s="1">
         <v>46010</v>
       </c>
       <c r="G217" t="s">
@@ -12827,7 +12801,7 @@
         <v>1353</v>
       </c>
       <c r="I217">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J217">
         <v>42</v>
@@ -12838,7 +12812,7 @@
       <c r="L217" t="s">
         <v>1416</v>
       </c>
-      <c r="N217" s="2">
+      <c r="N217" s="1">
         <v>46052</v>
       </c>
       <c r="Q217" t="b">
@@ -12861,7 +12835,7 @@
       <c r="E218" t="s">
         <v>1037</v>
       </c>
-      <c r="F218" s="2">
+      <c r="F218" s="1">
         <v>46010</v>
       </c>
       <c r="G218" t="s">
@@ -12871,7 +12845,7 @@
         <v>1353</v>
       </c>
       <c r="I218">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J218">
         <v>166</v>
@@ -12879,7 +12853,7 @@
       <c r="K218" t="s">
         <v>1359</v>
       </c>
-      <c r="N218" s="2">
+      <c r="N218" s="1">
         <v>46176</v>
       </c>
       <c r="P218" t="s">
@@ -12905,7 +12879,7 @@
       <c r="E219" t="s">
         <v>1038</v>
       </c>
-      <c r="F219" s="2">
+      <c r="F219" s="1">
         <v>46010</v>
       </c>
       <c r="G219" t="s">
@@ -12923,7 +12897,7 @@
       <c r="L219" t="s">
         <v>1417</v>
       </c>
-      <c r="N219" s="2">
+      <c r="N219" s="1">
         <v>46176</v>
       </c>
       <c r="P219" t="s">
@@ -12949,7 +12923,7 @@
       <c r="E220" t="s">
         <v>1039</v>
       </c>
-      <c r="F220" s="2">
+      <c r="F220" s="1">
         <v>46010</v>
       </c>
       <c r="G220" t="s">
@@ -12959,7 +12933,7 @@
         <v>1353</v>
       </c>
       <c r="I220">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J220">
         <v>154</v>
@@ -12970,7 +12944,7 @@
       <c r="L220" t="s">
         <v>1418</v>
       </c>
-      <c r="N220" s="2">
+      <c r="N220" s="1">
         <v>46164</v>
       </c>
       <c r="Q220" t="b">
@@ -12993,7 +12967,7 @@
       <c r="E221" t="s">
         <v>1040</v>
       </c>
-      <c r="F221" s="2">
+      <c r="F221" s="1">
         <v>46028</v>
       </c>
       <c r="G221" t="s">
@@ -13008,7 +12982,7 @@
       <c r="L221" t="s">
         <v>1419</v>
       </c>
-      <c r="N221" s="2">
+      <c r="N221" s="1">
         <v>46184</v>
       </c>
       <c r="Q221" t="b">
@@ -13031,7 +13005,7 @@
       <c r="E222" t="s">
         <v>1041</v>
       </c>
-      <c r="F222" s="2">
+      <c r="F222" s="1">
         <v>46028</v>
       </c>
       <c r="G222" t="s">
@@ -13046,7 +13020,7 @@
       <c r="L222" t="s">
         <v>1383</v>
       </c>
-      <c r="N222" s="2">
+      <c r="N222" s="1">
         <v>46232</v>
       </c>
       <c r="Q222" t="b">
@@ -13069,7 +13043,7 @@
       <c r="E223" t="s">
         <v>1042</v>
       </c>
-      <c r="F223" s="2">
+      <c r="F223" s="1">
         <v>46028</v>
       </c>
       <c r="G223" t="s">
@@ -13084,7 +13058,7 @@
       <c r="L223" t="s">
         <v>1383</v>
       </c>
-      <c r="N223" s="2">
+      <c r="N223" s="1">
         <v>46232</v>
       </c>
       <c r="Q223" t="b">
@@ -13107,7 +13081,7 @@
       <c r="E224" t="s">
         <v>1043</v>
       </c>
-      <c r="F224" s="2">
+      <c r="F224" s="1">
         <v>46028</v>
       </c>
       <c r="G224" t="s">
@@ -13117,7 +13091,7 @@
         <v>1353</v>
       </c>
       <c r="I224">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J224">
         <v>204</v>
@@ -13125,7 +13099,7 @@
       <c r="L224" t="s">
         <v>1383</v>
       </c>
-      <c r="N224" s="2">
+      <c r="N224" s="1">
         <v>46232</v>
       </c>
       <c r="Q224" t="b">
@@ -13148,7 +13122,7 @@
       <c r="E225" t="s">
         <v>1044</v>
       </c>
-      <c r="F225" s="2">
+      <c r="F225" s="1">
         <v>46028</v>
       </c>
       <c r="G225" t="s">
@@ -13163,7 +13137,7 @@
       <c r="L225" t="s">
         <v>1383</v>
       </c>
-      <c r="N225" s="2">
+      <c r="N225" s="1">
         <v>46232</v>
       </c>
       <c r="Q225" t="b">
@@ -13186,7 +13160,7 @@
       <c r="E226" t="s">
         <v>1045</v>
       </c>
-      <c r="F226" s="2">
+      <c r="F226" s="1">
         <v>46028</v>
       </c>
       <c r="G226" t="s">
@@ -13201,7 +13175,7 @@
       <c r="L226" t="s">
         <v>1383</v>
       </c>
-      <c r="N226" s="2">
+      <c r="N226" s="1">
         <v>46232</v>
       </c>
       <c r="Q226" t="b">
@@ -13224,7 +13198,7 @@
       <c r="E227" t="s">
         <v>1046</v>
       </c>
-      <c r="F227" s="2">
+      <c r="F227" s="1">
         <v>46028</v>
       </c>
       <c r="G227" t="s">
@@ -13239,7 +13213,7 @@
       <c r="L227" t="s">
         <v>1383</v>
       </c>
-      <c r="N227" s="2">
+      <c r="N227" s="1">
         <v>46232</v>
       </c>
       <c r="Q227" t="b">
@@ -13262,7 +13236,7 @@
       <c r="E228" t="s">
         <v>1047</v>
       </c>
-      <c r="F228" s="2">
+      <c r="F228" s="1">
         <v>46028</v>
       </c>
       <c r="G228" t="s">
@@ -13272,7 +13246,7 @@
         <v>1353</v>
       </c>
       <c r="I228">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J228">
         <v>204</v>
@@ -13280,7 +13254,7 @@
       <c r="L228" t="s">
         <v>1383</v>
       </c>
-      <c r="N228" s="2">
+      <c r="N228" s="1">
         <v>46232</v>
       </c>
       <c r="Q228" t="b">
@@ -13303,7 +13277,7 @@
       <c r="E229" t="s">
         <v>1048</v>
       </c>
-      <c r="F229" s="2">
+      <c r="F229" s="1">
         <v>46028</v>
       </c>
       <c r="G229" t="s">
@@ -13318,7 +13292,7 @@
       <c r="L229" t="s">
         <v>1420</v>
       </c>
-      <c r="N229" s="2">
+      <c r="N229" s="1">
         <v>46191</v>
       </c>
       <c r="Q229" t="b">
@@ -13341,7 +13315,7 @@
       <c r="E230" t="s">
         <v>1049</v>
       </c>
-      <c r="F230" s="2">
+      <c r="F230" s="1">
         <v>46028</v>
       </c>
       <c r="G230" t="s">
@@ -13351,7 +13325,7 @@
         <v>1353</v>
       </c>
       <c r="I230">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J230">
         <v>197</v>
@@ -13362,7 +13336,7 @@
       <c r="L230" t="s">
         <v>1395</v>
       </c>
-      <c r="N230" s="2">
+      <c r="N230" s="1">
         <v>46225</v>
       </c>
       <c r="Q230" t="b">
@@ -13385,7 +13359,7 @@
       <c r="E231" t="s">
         <v>1050</v>
       </c>
-      <c r="F231" s="2">
+      <c r="F231" s="1">
         <v>46028</v>
       </c>
       <c r="G231" t="s">
@@ -13395,7 +13369,7 @@
         <v>1353</v>
       </c>
       <c r="I231">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J231">
         <v>35</v>
@@ -13406,7 +13380,7 @@
       <c r="L231" t="s">
         <v>1421</v>
       </c>
-      <c r="N231" s="2">
+      <c r="N231" s="1">
         <v>46063</v>
       </c>
       <c r="Q231" t="b">
@@ -13429,7 +13403,7 @@
       <c r="E232" t="s">
         <v>1051</v>
       </c>
-      <c r="F232" s="2">
+      <c r="F232" s="1">
         <v>46028</v>
       </c>
       <c r="G232" t="s">
@@ -13458,7 +13432,7 @@
       <c r="E233" t="s">
         <v>1052</v>
       </c>
-      <c r="F233" s="2">
+      <c r="F233" s="1">
         <v>46028</v>
       </c>
       <c r="G233" t="s">
@@ -13487,7 +13461,7 @@
       <c r="E234" t="s">
         <v>1053</v>
       </c>
-      <c r="F234" s="2">
+      <c r="F234" s="1">
         <v>46028</v>
       </c>
       <c r="G234" t="s">
@@ -13497,7 +13471,7 @@
         <v>1353</v>
       </c>
       <c r="I234">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J234">
         <v>35</v>
@@ -13508,7 +13482,7 @@
       <c r="L234" t="s">
         <v>1421</v>
       </c>
-      <c r="N234" s="2">
+      <c r="N234" s="1">
         <v>46063</v>
       </c>
       <c r="P234" t="s">
@@ -13534,7 +13508,7 @@
       <c r="E235" t="s">
         <v>1054</v>
       </c>
-      <c r="F235" s="2">
+      <c r="F235" s="1">
         <v>46028</v>
       </c>
       <c r="G235" t="s">
@@ -13544,7 +13518,7 @@
         <v>1353</v>
       </c>
       <c r="I235">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J235">
         <v>35</v>
@@ -13555,7 +13529,7 @@
       <c r="L235" t="s">
         <v>1421</v>
       </c>
-      <c r="N235" s="2">
+      <c r="N235" s="1">
         <v>46063</v>
       </c>
       <c r="P235" t="s">
@@ -13581,7 +13555,7 @@
       <c r="E236" t="s">
         <v>1055</v>
       </c>
-      <c r="F236" s="2">
+      <c r="F236" s="1">
         <v>46028</v>
       </c>
       <c r="G236" t="s">
@@ -13591,7 +13565,7 @@
         <v>1353</v>
       </c>
       <c r="I236">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J236">
         <v>86</v>
@@ -13602,7 +13576,7 @@
       <c r="L236" t="s">
         <v>1422</v>
       </c>
-      <c r="N236" s="2">
+      <c r="N236" s="1">
         <v>46114</v>
       </c>
       <c r="Q236" t="b">
@@ -13625,7 +13599,7 @@
       <c r="E237" t="s">
         <v>1056</v>
       </c>
-      <c r="F237" s="2">
+      <c r="F237" s="1">
         <v>46028</v>
       </c>
       <c r="G237" t="s">
@@ -13643,7 +13617,7 @@
       <c r="L237" t="s">
         <v>1423</v>
       </c>
-      <c r="N237" s="2">
+      <c r="N237" s="1">
         <v>46210</v>
       </c>
       <c r="P237" t="s">
@@ -13669,7 +13643,7 @@
       <c r="E238" t="s">
         <v>1057</v>
       </c>
-      <c r="F238" s="2">
+      <c r="F238" s="1">
         <v>46028</v>
       </c>
       <c r="G238" t="s">
@@ -13698,7 +13672,7 @@
       <c r="E239" t="s">
         <v>1058</v>
       </c>
-      <c r="F239" s="2">
+      <c r="F239" s="1">
         <v>46036</v>
       </c>
       <c r="G239" t="s">
@@ -13708,7 +13682,7 @@
         <v>1353</v>
       </c>
       <c r="I239">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K239" t="s">
         <v>1330</v>
@@ -13716,7 +13690,7 @@
       <c r="L239" t="s">
         <v>1424</v>
       </c>
-      <c r="N239" s="2">
+      <c r="N239" s="1">
         <v>46052</v>
       </c>
       <c r="Q239" t="b">
@@ -13739,7 +13713,7 @@
       <c r="E240" t="s">
         <v>1059</v>
       </c>
-      <c r="F240" s="2">
+      <c r="F240" s="1">
         <v>46036</v>
       </c>
       <c r="G240" t="s">
@@ -13768,7 +13742,7 @@
       <c r="E241" t="s">
         <v>1060</v>
       </c>
-      <c r="F241" s="2">
+      <c r="F241" s="1">
         <v>46036</v>
       </c>
       <c r="G241" t="s">
@@ -13797,7 +13771,7 @@
       <c r="E242" t="s">
         <v>1061</v>
       </c>
-      <c r="F242" s="2">
+      <c r="F242" s="1">
         <v>46036</v>
       </c>
       <c r="G242" t="s">
@@ -13807,7 +13781,7 @@
         <v>1353</v>
       </c>
       <c r="I242">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K242" t="s">
         <v>1356</v>
@@ -13835,7 +13809,7 @@
       <c r="E243" t="s">
         <v>1062</v>
       </c>
-      <c r="F243" s="2">
+      <c r="F243" s="1">
         <v>46048</v>
       </c>
       <c r="G243" t="s">
@@ -13864,7 +13838,7 @@
       <c r="E244" t="s">
         <v>1063</v>
       </c>
-      <c r="F244" s="2">
+      <c r="F244" s="1">
         <v>46048</v>
       </c>
       <c r="G244" t="s">
@@ -13874,7 +13848,7 @@
         <v>1353</v>
       </c>
       <c r="I244">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J244">
         <v>15</v>
@@ -13882,7 +13856,7 @@
       <c r="K244" t="s">
         <v>1359</v>
       </c>
-      <c r="N244" s="2">
+      <c r="N244" s="1">
         <v>46063</v>
       </c>
       <c r="Q244" t="b">
@@ -13905,7 +13879,7 @@
       <c r="E245" t="s">
         <v>1064</v>
       </c>
-      <c r="F245" s="2">
+      <c r="F245" s="1">
         <v>46048</v>
       </c>
       <c r="G245" t="s">
@@ -13915,7 +13889,7 @@
         <v>1353</v>
       </c>
       <c r="I245">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J245">
         <v>15</v>
@@ -13926,7 +13900,7 @@
       <c r="L245" t="s">
         <v>1425</v>
       </c>
-      <c r="N245" s="2">
+      <c r="N245" s="1">
         <v>46063</v>
       </c>
       <c r="Q245" t="b">
@@ -13949,7 +13923,7 @@
       <c r="E246" t="s">
         <v>1065</v>
       </c>
-      <c r="F246" s="2">
+      <c r="F246" s="1">
         <v>46050</v>
       </c>
       <c r="G246" t="s">
@@ -13967,7 +13941,7 @@
       <c r="L246" t="s">
         <v>1426</v>
       </c>
-      <c r="N246" s="2">
+      <c r="N246" s="1">
         <v>46191</v>
       </c>
       <c r="Q246" t="b">
@@ -13990,7 +13964,7 @@
       <c r="E247" t="s">
         <v>1066</v>
       </c>
-      <c r="F247" s="2">
+      <c r="F247" s="1">
         <v>46050</v>
       </c>
       <c r="G247" t="s">
@@ -14019,7 +13993,7 @@
       <c r="E248" t="s">
         <v>1067</v>
       </c>
-      <c r="F248" s="2">
+      <c r="F248" s="1">
         <v>46050</v>
       </c>
       <c r="G248" t="s">
@@ -14048,7 +14022,7 @@
       <c r="E249" t="s">
         <v>1068</v>
       </c>
-      <c r="F249" s="2">
+      <c r="F249" s="1">
         <v>46050</v>
       </c>
       <c r="G249" t="s">
@@ -14058,7 +14032,7 @@
         <v>1353</v>
       </c>
       <c r="I249">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K249" t="s">
         <v>1357</v>
@@ -14086,7 +14060,7 @@
       <c r="E250" t="s">
         <v>1069</v>
       </c>
-      <c r="F250" s="2">
+      <c r="F250" s="1">
         <v>46063</v>
       </c>
       <c r="G250" t="s">
@@ -14124,7 +14098,7 @@
       <c r="E251" t="s">
         <v>1070</v>
       </c>
-      <c r="F251" s="2">
+      <c r="F251" s="1">
         <v>46063</v>
       </c>
       <c r="G251" t="s">
@@ -14153,7 +14127,7 @@
       <c r="E252" t="s">
         <v>1071</v>
       </c>
-      <c r="F252" s="2">
+      <c r="F252" s="1">
         <v>46063</v>
       </c>
       <c r="G252" t="s">
@@ -14182,7 +14156,7 @@
       <c r="E253" t="s">
         <v>1072</v>
       </c>
-      <c r="F253" s="2">
+      <c r="F253" s="1">
         <v>46063</v>
       </c>
       <c r="G253" t="s">
@@ -14192,7 +14166,7 @@
         <v>1353</v>
       </c>
       <c r="I253">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J253">
         <v>162</v>
@@ -14203,7 +14177,7 @@
       <c r="L253" t="s">
         <v>1395</v>
       </c>
-      <c r="N253" s="2">
+      <c r="N253" s="1">
         <v>46225</v>
       </c>
       <c r="Q253" t="b">
@@ -14226,7 +14200,7 @@
       <c r="E254" t="s">
         <v>1073</v>
       </c>
-      <c r="F254" s="2">
+      <c r="F254" s="1">
         <v>46063</v>
       </c>
       <c r="G254" t="s">
@@ -14236,7 +14210,7 @@
         <v>1353</v>
       </c>
       <c r="I254">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K254" t="s">
         <v>1360</v>
@@ -14264,7 +14238,7 @@
       <c r="E255" t="s">
         <v>1074</v>
       </c>
-      <c r="F255" s="2">
+      <c r="F255" s="1">
         <v>46063</v>
       </c>
       <c r="G255" t="s">
@@ -14274,7 +14248,7 @@
         <v>1353</v>
       </c>
       <c r="I255">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J255">
         <v>72</v>
@@ -14285,7 +14259,7 @@
       <c r="L255" t="s">
         <v>1388</v>
       </c>
-      <c r="N255" s="2">
+      <c r="N255" s="1">
         <v>46135</v>
       </c>
       <c r="Q255" t="b">
@@ -14308,7 +14282,7 @@
       <c r="E256" t="s">
         <v>1075</v>
       </c>
-      <c r="F256" s="2">
+      <c r="F256" s="1">
         <v>46063</v>
       </c>
       <c r="G256" t="s">
@@ -14318,7 +14292,7 @@
         <v>1353</v>
       </c>
       <c r="I256">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J256">
         <v>23</v>
@@ -14326,7 +14300,7 @@
       <c r="K256" t="s">
         <v>1357</v>
       </c>
-      <c r="N256" s="2">
+      <c r="N256" s="1">
         <v>46086</v>
       </c>
       <c r="O256">
@@ -14352,7 +14326,7 @@
       <c r="E257" t="s">
         <v>1076</v>
       </c>
-      <c r="F257" s="2">
+      <c r="F257" s="1">
         <v>46063</v>
       </c>
       <c r="G257" t="s">
@@ -14381,7 +14355,7 @@
       <c r="E258" t="s">
         <v>1077</v>
       </c>
-      <c r="F258" s="2">
+      <c r="F258" s="1">
         <v>46063</v>
       </c>
       <c r="G258" t="s">
@@ -14410,7 +14384,7 @@
       <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="F259" s="2">
+      <c r="F259" s="1">
         <v>46063</v>
       </c>
       <c r="G259" t="s">
@@ -14420,7 +14394,7 @@
         <v>1353</v>
       </c>
       <c r="I259">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J259">
         <v>72</v>
@@ -14431,7 +14405,7 @@
       <c r="L259" t="s">
         <v>1388</v>
       </c>
-      <c r="N259" s="2">
+      <c r="N259" s="1">
         <v>46135</v>
       </c>
       <c r="Q259" t="b">
@@ -14454,7 +14428,7 @@
       <c r="E260" t="s">
         <v>1079</v>
       </c>
-      <c r="F260" s="2">
+      <c r="F260" s="1">
         <v>46063</v>
       </c>
       <c r="G260" t="s">
@@ -14464,7 +14438,7 @@
         <v>1353</v>
       </c>
       <c r="I260">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J260">
         <v>84</v>
@@ -14475,7 +14449,7 @@
       <c r="L260" t="s">
         <v>1388</v>
       </c>
-      <c r="N260" s="2">
+      <c r="N260" s="1">
         <v>46147</v>
       </c>
       <c r="Q260" t="b">
@@ -14498,7 +14472,7 @@
       <c r="E261" t="s">
         <v>1080</v>
       </c>
-      <c r="F261" s="2">
+      <c r="F261" s="1">
         <v>46063</v>
       </c>
       <c r="G261" t="s">
@@ -14508,7 +14482,7 @@
         <v>1353</v>
       </c>
       <c r="I261">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J261">
         <v>162</v>
@@ -14519,7 +14493,7 @@
       <c r="L261" t="s">
         <v>1427</v>
       </c>
-      <c r="N261" s="2">
+      <c r="N261" s="1">
         <v>46225</v>
       </c>
       <c r="Q261" t="b">
@@ -14542,7 +14516,7 @@
       <c r="E262" t="s">
         <v>1081</v>
       </c>
-      <c r="F262" s="2">
+      <c r="F262" s="1">
         <v>46063</v>
       </c>
       <c r="G262" t="s">
@@ -14560,7 +14534,7 @@
       <c r="L262" t="s">
         <v>1428</v>
       </c>
-      <c r="N262" s="2">
+      <c r="N262" s="1">
         <v>46113</v>
       </c>
       <c r="P262" t="s">
@@ -14586,7 +14560,7 @@
       <c r="E263" t="s">
         <v>1082</v>
       </c>
-      <c r="F263" s="2">
+      <c r="F263" s="1">
         <v>46063</v>
       </c>
       <c r="G263" t="s">
@@ -14615,7 +14589,7 @@
       <c r="E264" t="s">
         <v>1083</v>
       </c>
-      <c r="F264" s="2">
+      <c r="F264" s="1">
         <v>46063</v>
       </c>
       <c r="G264" t="s">
@@ -14625,7 +14599,7 @@
         <v>1353</v>
       </c>
       <c r="I264">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J264">
         <v>162</v>
@@ -14636,7 +14610,7 @@
       <c r="L264" t="s">
         <v>1388</v>
       </c>
-      <c r="N264" s="2">
+      <c r="N264" s="1">
         <v>46225</v>
       </c>
       <c r="Q264" t="b">
@@ -14659,7 +14633,7 @@
       <c r="E265" t="s">
         <v>1084</v>
       </c>
-      <c r="F265" s="2">
+      <c r="F265" s="1">
         <v>46063</v>
       </c>
       <c r="G265" t="s">
@@ -14669,7 +14643,7 @@
         <v>1353</v>
       </c>
       <c r="I265">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J265">
         <v>162</v>
@@ -14680,7 +14654,7 @@
       <c r="L265" t="s">
         <v>1395</v>
       </c>
-      <c r="N265" s="2">
+      <c r="N265" s="1">
         <v>46225</v>
       </c>
       <c r="Q265" t="b">
@@ -14703,7 +14677,7 @@
       <c r="E266" t="s">
         <v>1085</v>
       </c>
-      <c r="F266" s="2">
+      <c r="F266" s="1">
         <v>46063</v>
       </c>
       <c r="G266" t="s">
@@ -14713,7 +14687,7 @@
         <v>1353</v>
       </c>
       <c r="I266">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J266">
         <v>84</v>
@@ -14724,7 +14698,7 @@
       <c r="L266" t="s">
         <v>1388</v>
       </c>
-      <c r="N266" s="2">
+      <c r="N266" s="1">
         <v>46147</v>
       </c>
       <c r="Q266" t="b">
@@ -14747,7 +14721,7 @@
       <c r="E267" t="s">
         <v>1086</v>
       </c>
-      <c r="F267" s="2">
+      <c r="F267" s="1">
         <v>46063</v>
       </c>
       <c r="G267" t="s">
@@ -14757,7 +14731,7 @@
         <v>1353</v>
       </c>
       <c r="I267">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K267" t="s">
         <v>1360</v>
@@ -14785,7 +14759,7 @@
       <c r="E268" t="s">
         <v>1087</v>
       </c>
-      <c r="F268" s="2">
+      <c r="F268" s="1">
         <v>46063</v>
       </c>
       <c r="G268" t="s">
@@ -14795,7 +14769,7 @@
         <v>1353</v>
       </c>
       <c r="I268">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K268" t="s">
         <v>1357</v>
@@ -14820,7 +14794,7 @@
       <c r="D269" t="s">
         <v>798</v>
       </c>
-      <c r="F269" s="2">
+      <c r="F269" s="1">
         <v>46063</v>
       </c>
       <c r="G269" t="s">
@@ -14830,7 +14804,7 @@
         <v>1353</v>
       </c>
       <c r="I269">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K269" t="s">
         <v>1357</v>
@@ -14858,7 +14832,7 @@
       <c r="E270" t="s">
         <v>1088</v>
       </c>
-      <c r="F270" s="2">
+      <c r="F270" s="1">
         <v>46063</v>
       </c>
       <c r="G270" t="s">
@@ -14868,7 +14842,7 @@
         <v>1353</v>
       </c>
       <c r="I270">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K270" t="s">
         <v>1360</v>
@@ -14896,7 +14870,7 @@
       <c r="E271" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="2">
+      <c r="F271" s="1">
         <v>46063</v>
       </c>
       <c r="G271" t="s">
@@ -14906,7 +14880,7 @@
         <v>1353</v>
       </c>
       <c r="I271">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K271" t="s">
         <v>1360</v>
@@ -14934,7 +14908,7 @@
       <c r="E272" t="s">
         <v>1090</v>
       </c>
-      <c r="F272" s="2">
+      <c r="F272" s="1">
         <v>46063</v>
       </c>
       <c r="G272" t="s">
@@ -14952,7 +14926,7 @@
       <c r="L272" t="s">
         <v>1429</v>
       </c>
-      <c r="N272" s="2">
+      <c r="N272" s="1">
         <v>46185</v>
       </c>
       <c r="O272" t="s">
@@ -14978,7 +14952,7 @@
       <c r="E273" t="s">
         <v>1091</v>
       </c>
-      <c r="F273" s="2">
+      <c r="F273" s="1">
         <v>46063</v>
       </c>
       <c r="G273" t="s">
@@ -15007,7 +14981,7 @@
       <c r="E274" t="s">
         <v>1092</v>
       </c>
-      <c r="F274" s="2">
+      <c r="F274" s="1">
         <v>46063</v>
       </c>
       <c r="G274" t="s">
@@ -15022,7 +14996,7 @@
       <c r="L274" t="s">
         <v>1383</v>
       </c>
-      <c r="N274" s="2">
+      <c r="N274" s="1">
         <v>46232</v>
       </c>
       <c r="Q274" t="b">
@@ -15045,7 +15019,7 @@
       <c r="E275" t="s">
         <v>1093</v>
       </c>
-      <c r="F275" s="2">
+      <c r="F275" s="1">
         <v>46063</v>
       </c>
       <c r="G275" t="s">
@@ -15074,7 +15048,7 @@
       <c r="E276" t="s">
         <v>1094</v>
       </c>
-      <c r="F276" s="2">
+      <c r="F276" s="1">
         <v>46063</v>
       </c>
       <c r="G276" t="s">
@@ -15084,7 +15058,7 @@
         <v>1353</v>
       </c>
       <c r="I276">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K276" t="s">
         <v>1361</v>
@@ -15112,7 +15086,7 @@
       <c r="E277" t="s">
         <v>1095</v>
       </c>
-      <c r="F277" s="2">
+      <c r="F277" s="1">
         <v>46063</v>
       </c>
       <c r="G277" t="s">
@@ -15122,7 +15096,7 @@
         <v>1353</v>
       </c>
       <c r="I277">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K277" t="s">
         <v>1357</v>
@@ -15150,7 +15124,7 @@
       <c r="E278" t="s">
         <v>1096</v>
       </c>
-      <c r="F278" s="2">
+      <c r="F278" s="1">
         <v>46077</v>
       </c>
       <c r="G278" t="s">
@@ -15160,7 +15134,7 @@
         <v>1353</v>
       </c>
       <c r="I278">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J278">
         <v>148</v>
@@ -15171,7 +15145,7 @@
       <c r="L278" t="s">
         <v>1395</v>
       </c>
-      <c r="N278" s="2">
+      <c r="N278" s="1">
         <v>46225</v>
       </c>
       <c r="Q278" t="b">
@@ -15194,7 +15168,7 @@
       <c r="E279" t="s">
         <v>1097</v>
       </c>
-      <c r="F279" s="2">
+      <c r="F279" s="1">
         <v>46077</v>
       </c>
       <c r="G279" t="s">
@@ -15204,7 +15178,7 @@
         <v>1353</v>
       </c>
       <c r="I279">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K279" t="s">
         <v>1359</v>
@@ -15235,7 +15209,7 @@
       <c r="E280" t="s">
         <v>1098</v>
       </c>
-      <c r="F280" s="2">
+      <c r="F280" s="1">
         <v>46085</v>
       </c>
       <c r="G280" t="s">
@@ -15245,7 +15219,7 @@
         <v>1353</v>
       </c>
       <c r="I280">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K280" t="s">
         <v>1357</v>
@@ -15273,7 +15247,7 @@
       <c r="E281" t="s">
         <v>1099</v>
       </c>
-      <c r="F281" s="2">
+      <c r="F281" s="1">
         <v>46085</v>
       </c>
       <c r="G281" t="s">
@@ -15283,7 +15257,7 @@
         <v>1353</v>
       </c>
       <c r="I281">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K281" t="s">
         <v>1357</v>
@@ -15314,7 +15288,7 @@
       <c r="E282" t="s">
         <v>1100</v>
       </c>
-      <c r="F282" s="2">
+      <c r="F282" s="1">
         <v>46090</v>
       </c>
       <c r="G282" t="s">
@@ -15324,7 +15298,7 @@
         <v>1353</v>
       </c>
       <c r="I282">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K282" t="s">
         <v>1357</v>
@@ -15352,7 +15326,7 @@
       <c r="E283" t="s">
         <v>1101</v>
       </c>
-      <c r="F283" s="2">
+      <c r="F283" s="1">
         <v>46100</v>
       </c>
       <c r="G283" t="s">
@@ -15381,7 +15355,7 @@
       <c r="E284" t="s">
         <v>1102</v>
       </c>
-      <c r="F284" s="2">
+      <c r="F284" s="1">
         <v>46100</v>
       </c>
       <c r="G284" t="s">
@@ -15410,7 +15384,7 @@
       <c r="E285" t="s">
         <v>1103</v>
       </c>
-      <c r="F285" s="2">
+      <c r="F285" s="1">
         <v>46100</v>
       </c>
       <c r="G285" t="s">
@@ -15439,7 +15413,7 @@
       <c r="E286" t="s">
         <v>1104</v>
       </c>
-      <c r="F286" s="2">
+      <c r="F286" s="1">
         <v>46100</v>
       </c>
       <c r="G286" t="s">
@@ -15468,7 +15442,7 @@
       <c r="E287" t="s">
         <v>1105</v>
       </c>
-      <c r="F287" s="2">
+      <c r="F287" s="1">
         <v>46107</v>
       </c>
       <c r="G287" t="s">
@@ -15497,7 +15471,7 @@
       <c r="E288" t="s">
         <v>1106</v>
       </c>
-      <c r="F288" s="2">
+      <c r="F288" s="1">
         <v>46107</v>
       </c>
       <c r="G288" t="s">
@@ -15507,7 +15481,7 @@
         <v>1353</v>
       </c>
       <c r="I288">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J288">
         <v>28</v>
@@ -15518,7 +15492,7 @@
       <c r="L288" t="s">
         <v>1388</v>
       </c>
-      <c r="N288" s="2">
+      <c r="N288" s="1">
         <v>46135</v>
       </c>
       <c r="Q288" t="b">
@@ -15541,7 +15515,7 @@
       <c r="E289" t="s">
         <v>1107</v>
       </c>
-      <c r="F289" s="2">
+      <c r="F289" s="1">
         <v>46107</v>
       </c>
       <c r="G289" t="s">
@@ -15570,7 +15544,7 @@
       <c r="E290" t="s">
         <v>1108</v>
       </c>
-      <c r="F290" s="2">
+      <c r="F290" s="1">
         <v>46107</v>
       </c>
       <c r="G290" t="s">
@@ -15580,7 +15554,7 @@
         <v>1353</v>
       </c>
       <c r="I290">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J290">
         <v>20</v>
@@ -15591,7 +15565,7 @@
       <c r="L290" t="s">
         <v>1388</v>
       </c>
-      <c r="N290" s="2">
+      <c r="N290" s="1">
         <v>46127</v>
       </c>
       <c r="Q290" t="b">
@@ -15614,7 +15588,7 @@
       <c r="E291" t="s">
         <v>1109</v>
       </c>
-      <c r="F291" s="2">
+      <c r="F291" s="1">
         <v>46107</v>
       </c>
       <c r="G291" t="s">
@@ -15624,7 +15598,7 @@
         <v>1353</v>
       </c>
       <c r="I291">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J291">
         <v>20</v>
@@ -15635,7 +15609,7 @@
       <c r="L291" t="s">
         <v>1430</v>
       </c>
-      <c r="N291" s="2">
+      <c r="N291" s="1">
         <v>46127</v>
       </c>
       <c r="Q291" t="b">
@@ -15658,7 +15632,7 @@
       <c r="E292" t="s">
         <v>1110</v>
       </c>
-      <c r="F292" s="2">
+      <c r="F292" s="1">
         <v>46112</v>
       </c>
       <c r="G292" t="s">
@@ -15668,7 +15642,7 @@
         <v>1353</v>
       </c>
       <c r="I292">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K292" t="s">
         <v>1360</v>
@@ -15696,7 +15670,7 @@
       <c r="E293" t="s">
         <v>1111</v>
       </c>
-      <c r="F293" s="2">
+      <c r="F293" s="1">
         <v>46125</v>
       </c>
       <c r="G293" t="s">
@@ -15706,7 +15680,7 @@
         <v>1353</v>
       </c>
       <c r="I293">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K293" t="s">
         <v>1361</v>
@@ -15734,7 +15708,7 @@
       <c r="E294" t="s">
         <v>1112</v>
       </c>
-      <c r="F294" s="2">
+      <c r="F294" s="1">
         <v>46125</v>
       </c>
       <c r="G294" t="s">
@@ -15744,7 +15718,7 @@
         <v>1353</v>
       </c>
       <c r="I294">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K294" t="s">
         <v>1366</v>
@@ -15769,7 +15743,7 @@
       <c r="E295" t="s">
         <v>1113</v>
       </c>
-      <c r="F295" s="2">
+      <c r="F295" s="1">
         <v>46125</v>
       </c>
       <c r="G295" t="s">
@@ -15779,7 +15753,7 @@
         <v>1353</v>
       </c>
       <c r="I295">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K295" t="s">
         <v>1366</v>
@@ -15804,7 +15778,7 @@
       <c r="E296" t="s">
         <v>1114</v>
       </c>
-      <c r="F296" s="2">
+      <c r="F296" s="1">
         <v>46125</v>
       </c>
       <c r="G296" t="s">
@@ -15814,7 +15788,7 @@
         <v>1353</v>
       </c>
       <c r="I296">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K296" t="s">
         <v>1366</v>
@@ -15839,7 +15813,7 @@
       <c r="E297" t="s">
         <v>1115</v>
       </c>
-      <c r="F297" s="2">
+      <c r="F297" s="1">
         <v>46125</v>
       </c>
       <c r="G297" t="s">
@@ -15851,7 +15825,7 @@
       <c r="K297" t="s">
         <v>1359</v>
       </c>
-      <c r="N297" s="2">
+      <c r="N297" s="1">
         <v>46183</v>
       </c>
       <c r="O297">
@@ -15877,7 +15851,7 @@
       <c r="E298" t="s">
         <v>1116</v>
       </c>
-      <c r="F298" s="2">
+      <c r="F298" s="1">
         <v>46125</v>
       </c>
       <c r="G298" t="s">
@@ -15887,7 +15861,7 @@
         <v>1353</v>
       </c>
       <c r="I298">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J298">
         <v>58</v>
@@ -15895,7 +15869,7 @@
       <c r="K298" t="s">
         <v>1359</v>
       </c>
-      <c r="N298" s="2">
+      <c r="N298" s="1">
         <v>46183</v>
       </c>
       <c r="Q298" t="b">
@@ -15918,7 +15892,7 @@
       <c r="E299" t="s">
         <v>1117</v>
       </c>
-      <c r="F299" s="2">
+      <c r="F299" s="1">
         <v>46125</v>
       </c>
       <c r="G299" t="s">
@@ -15928,7 +15902,7 @@
         <v>1353</v>
       </c>
       <c r="I299">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J299">
         <v>100</v>
@@ -15939,7 +15913,7 @@
       <c r="L299" t="s">
         <v>1388</v>
       </c>
-      <c r="N299" s="2">
+      <c r="N299" s="1">
         <v>46225</v>
       </c>
       <c r="Q299" t="b">
@@ -15962,7 +15936,7 @@
       <c r="E300" t="s">
         <v>1118</v>
       </c>
-      <c r="F300" s="2">
+      <c r="F300" s="1">
         <v>46125</v>
       </c>
       <c r="G300" t="s">
@@ -15972,7 +15946,7 @@
         <v>1353</v>
       </c>
       <c r="I300">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J300">
         <v>86</v>
@@ -15983,7 +15957,7 @@
       <c r="L300" t="s">
         <v>1388</v>
       </c>
-      <c r="N300" s="2">
+      <c r="N300" s="1">
         <v>46211</v>
       </c>
       <c r="Q300" t="b">
@@ -16006,7 +15980,7 @@
       <c r="E301" t="s">
         <v>1119</v>
       </c>
-      <c r="F301" s="2">
+      <c r="F301" s="1">
         <v>46125</v>
       </c>
       <c r="G301" t="s">
@@ -16016,7 +15990,7 @@
         <v>1353</v>
       </c>
       <c r="I301">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J301">
         <v>102</v>
@@ -16027,7 +16001,7 @@
       <c r="L301" t="s">
         <v>1388</v>
       </c>
-      <c r="N301" s="2">
+      <c r="N301" s="1">
         <v>46227</v>
       </c>
       <c r="Q301" t="b">
@@ -16050,7 +16024,7 @@
       <c r="E302" t="s">
         <v>1120</v>
       </c>
-      <c r="F302" s="2">
+      <c r="F302" s="1">
         <v>46125</v>
       </c>
       <c r="G302" t="s">
@@ -16060,7 +16034,7 @@
         <v>1353</v>
       </c>
       <c r="I302">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K302" t="s">
         <v>1360</v>
@@ -16088,7 +16062,7 @@
       <c r="E303" t="s">
         <v>1121</v>
       </c>
-      <c r="F303" s="2">
+      <c r="F303" s="1">
         <v>46125</v>
       </c>
       <c r="G303" t="s">
@@ -16098,7 +16072,7 @@
         <v>1353</v>
       </c>
       <c r="I303">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K303" t="s">
         <v>1357</v>
@@ -16126,7 +16100,7 @@
       <c r="E304" t="s">
         <v>1122</v>
       </c>
-      <c r="F304" s="2">
+      <c r="F304" s="1">
         <v>46125</v>
       </c>
       <c r="G304" t="s">
@@ -16136,7 +16110,7 @@
         <v>1353</v>
       </c>
       <c r="I304">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K304" t="s">
         <v>1360</v>
@@ -16164,7 +16138,7 @@
       <c r="E305" t="s">
         <v>1123</v>
       </c>
-      <c r="F305" s="2">
+      <c r="F305" s="1">
         <v>46125</v>
       </c>
       <c r="G305" t="s">
@@ -16174,7 +16148,7 @@
         <v>1353</v>
       </c>
       <c r="I305">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J305">
         <v>35</v>
@@ -16185,7 +16159,7 @@
       <c r="L305" t="s">
         <v>1431</v>
       </c>
-      <c r="N305" s="2">
+      <c r="N305" s="1">
         <v>46160</v>
       </c>
       <c r="Q305" t="b">
@@ -16208,7 +16182,7 @@
       <c r="E306" t="s">
         <v>1124</v>
       </c>
-      <c r="F306" s="2">
+      <c r="F306" s="1">
         <v>46125</v>
       </c>
       <c r="G306" t="s">
@@ -16218,7 +16192,7 @@
         <v>1353</v>
       </c>
       <c r="I306">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J306">
         <v>31</v>
@@ -16229,7 +16203,7 @@
       <c r="L306" t="s">
         <v>1432</v>
       </c>
-      <c r="N306" s="2">
+      <c r="N306" s="1">
         <v>46156</v>
       </c>
       <c r="Q306" t="b">
@@ -16252,7 +16226,7 @@
       <c r="E307" t="s">
         <v>1125</v>
       </c>
-      <c r="F307" s="2">
+      <c r="F307" s="1">
         <v>46125</v>
       </c>
       <c r="G307" t="s">
@@ -16270,7 +16244,7 @@
       <c r="L307" t="s">
         <v>1433</v>
       </c>
-      <c r="N307" s="2">
+      <c r="N307" s="1">
         <v>46209</v>
       </c>
       <c r="P307" t="s">
@@ -16296,7 +16270,7 @@
       <c r="E308" t="s">
         <v>1126</v>
       </c>
-      <c r="F308" s="2">
+      <c r="F308" s="1">
         <v>46125</v>
       </c>
       <c r="G308" t="s">
@@ -16306,7 +16280,7 @@
         <v>1353</v>
       </c>
       <c r="I308">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K308" t="s">
         <v>1356</v>
@@ -16334,7 +16308,7 @@
       <c r="E309" t="s">
         <v>1127</v>
       </c>
-      <c r="F309" s="2">
+      <c r="F309" s="1">
         <v>46125</v>
       </c>
       <c r="G309" t="s">
@@ -16349,7 +16323,7 @@
       <c r="L309" t="s">
         <v>1383</v>
       </c>
-      <c r="N309" s="2">
+      <c r="N309" s="1">
         <v>46232</v>
       </c>
       <c r="Q309" t="b">
@@ -16372,7 +16346,7 @@
       <c r="E310" t="s">
         <v>1128</v>
       </c>
-      <c r="F310" s="2">
+      <c r="F310" s="1">
         <v>46125</v>
       </c>
       <c r="G310" t="s">
@@ -16382,7 +16356,7 @@
         <v>1353</v>
       </c>
       <c r="I310">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J310">
         <v>107</v>
@@ -16393,7 +16367,7 @@
       <c r="L310" t="s">
         <v>1383</v>
       </c>
-      <c r="N310" s="2">
+      <c r="N310" s="1">
         <v>46232</v>
       </c>
       <c r="Q310" t="b">
@@ -16416,7 +16390,7 @@
       <c r="E311" t="s">
         <v>1129</v>
       </c>
-      <c r="F311" s="2">
+      <c r="F311" s="1">
         <v>46125</v>
       </c>
       <c r="G311" t="s">
@@ -16426,7 +16400,7 @@
         <v>1353</v>
       </c>
       <c r="I311">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K311" t="s">
         <v>1356</v>
@@ -16454,7 +16428,7 @@
       <c r="E312" t="s">
         <v>1130</v>
       </c>
-      <c r="F312" s="2">
+      <c r="F312" s="1">
         <v>46125</v>
       </c>
       <c r="G312" t="s">
@@ -16472,7 +16446,7 @@
       <c r="L312" t="s">
         <v>1383</v>
       </c>
-      <c r="N312" s="2">
+      <c r="N312" s="1">
         <v>46232</v>
       </c>
       <c r="Q312" t="b">
@@ -16495,7 +16469,7 @@
       <c r="E313" t="s">
         <v>1131</v>
       </c>
-      <c r="F313" s="2">
+      <c r="F313" s="1">
         <v>46125</v>
       </c>
       <c r="G313" t="s">
@@ -16530,7 +16504,7 @@
       <c r="E314" t="s">
         <v>1132</v>
       </c>
-      <c r="F314" s="2">
+      <c r="F314" s="1">
         <v>46125</v>
       </c>
       <c r="G314" t="s">
@@ -16545,7 +16519,7 @@
       <c r="L314" t="s">
         <v>1383</v>
       </c>
-      <c r="N314" s="2">
+      <c r="N314" s="1">
         <v>46232</v>
       </c>
       <c r="Q314" t="b">
@@ -16568,7 +16542,7 @@
       <c r="E315" t="s">
         <v>1133</v>
       </c>
-      <c r="F315" s="2">
+      <c r="F315" s="1">
         <v>46125</v>
       </c>
       <c r="G315" t="s">
@@ -16583,7 +16557,7 @@
       <c r="L315" t="s">
         <v>1383</v>
       </c>
-      <c r="N315" s="2">
+      <c r="N315" s="1">
         <v>46232</v>
       </c>
       <c r="Q315" t="b">
@@ -16606,7 +16580,7 @@
       <c r="E316" t="s">
         <v>1134</v>
       </c>
-      <c r="F316" s="2">
+      <c r="F316" s="1">
         <v>46125</v>
       </c>
       <c r="G316" t="s">
@@ -16616,7 +16590,7 @@
         <v>1353</v>
       </c>
       <c r="I316">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K316" t="s">
         <v>1357</v>
@@ -16644,7 +16618,7 @@
       <c r="E317" t="s">
         <v>1135</v>
       </c>
-      <c r="F317" s="2">
+      <c r="F317" s="1">
         <v>46125</v>
       </c>
       <c r="G317" t="s">
@@ -16679,7 +16653,7 @@
       <c r="E318" t="s">
         <v>1136</v>
       </c>
-      <c r="F318" s="2">
+      <c r="F318" s="1">
         <v>46125</v>
       </c>
       <c r="G318" t="s">
@@ -16708,7 +16682,7 @@
       <c r="E319" t="s">
         <v>1137</v>
       </c>
-      <c r="F319" s="2">
+      <c r="F319" s="1">
         <v>46125</v>
       </c>
       <c r="G319" t="s">
@@ -16723,7 +16697,7 @@
       <c r="L319" t="s">
         <v>1434</v>
       </c>
-      <c r="N319" s="2">
+      <c r="N319" s="1">
         <v>46175</v>
       </c>
       <c r="Q319" t="b">
@@ -16746,7 +16720,7 @@
       <c r="E320" t="s">
         <v>1138</v>
       </c>
-      <c r="F320" s="2">
+      <c r="F320" s="1">
         <v>46125</v>
       </c>
       <c r="G320" t="s">
@@ -16756,7 +16730,7 @@
         <v>1353</v>
       </c>
       <c r="I320">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K320" t="s">
         <v>1361</v>
@@ -16784,7 +16758,7 @@
       <c r="E321" t="s">
         <v>1139</v>
       </c>
-      <c r="F321" s="2">
+      <c r="F321" s="1">
         <v>46125</v>
       </c>
       <c r="G321" t="s">
@@ -16794,7 +16768,7 @@
         <v>1353</v>
       </c>
       <c r="I321">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K321" t="s">
         <v>1357</v>
@@ -16822,7 +16796,7 @@
       <c r="E322" t="s">
         <v>1140</v>
       </c>
-      <c r="F322" s="2">
+      <c r="F322" s="1">
         <v>46125</v>
       </c>
       <c r="G322" t="s">
@@ -16832,7 +16806,7 @@
         <v>1353</v>
       </c>
       <c r="I322">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J322">
         <v>57</v>
@@ -16843,7 +16817,7 @@
       <c r="L322" t="s">
         <v>1435</v>
       </c>
-      <c r="N322" s="2">
+      <c r="N322" s="1">
         <v>46182</v>
       </c>
       <c r="Q322" t="b">
@@ -16866,7 +16840,7 @@
       <c r="E323" t="s">
         <v>1141</v>
       </c>
-      <c r="F323" s="2">
+      <c r="F323" s="1">
         <v>46125</v>
       </c>
       <c r="G323" t="s">
@@ -16901,7 +16875,7 @@
       <c r="E324" t="s">
         <v>1142</v>
       </c>
-      <c r="F324" s="2">
+      <c r="F324" s="1">
         <v>46125</v>
       </c>
       <c r="G324" t="s">
@@ -16936,7 +16910,7 @@
       <c r="E325" t="s">
         <v>1143</v>
       </c>
-      <c r="F325" s="2">
+      <c r="F325" s="1">
         <v>46125</v>
       </c>
       <c r="G325" t="s">
@@ -16946,7 +16920,7 @@
         <v>1353</v>
       </c>
       <c r="I325">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J325">
         <v>57</v>
@@ -16957,7 +16931,7 @@
       <c r="L325" t="s">
         <v>1435</v>
       </c>
-      <c r="N325" s="2">
+      <c r="N325" s="1">
         <v>46182</v>
       </c>
       <c r="Q325" t="b">
@@ -16980,7 +16954,7 @@
       <c r="E326" t="s">
         <v>1144</v>
       </c>
-      <c r="F326" s="2">
+      <c r="F326" s="1">
         <v>46125</v>
       </c>
       <c r="G326" t="s">
@@ -16995,7 +16969,7 @@
       <c r="L326" t="s">
         <v>1383</v>
       </c>
-      <c r="N326" s="2">
+      <c r="N326" s="1">
         <v>46232</v>
       </c>
       <c r="Q326" t="b">
@@ -17018,7 +16992,7 @@
       <c r="E327" t="s">
         <v>1140</v>
       </c>
-      <c r="F327" s="2">
+      <c r="F327" s="1">
         <v>46125</v>
       </c>
       <c r="G327" t="s">
@@ -17028,7 +17002,7 @@
         <v>1353</v>
       </c>
       <c r="I327">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J327">
         <v>57</v>
@@ -17039,7 +17013,7 @@
       <c r="L327" t="s">
         <v>1435</v>
       </c>
-      <c r="N327" s="2">
+      <c r="N327" s="1">
         <v>46182</v>
       </c>
       <c r="Q327" t="b">
@@ -17062,7 +17036,7 @@
       <c r="E328" t="s">
         <v>1145</v>
       </c>
-      <c r="F328" s="2">
+      <c r="F328" s="1">
         <v>46125</v>
       </c>
       <c r="G328" t="s">
@@ -17072,7 +17046,7 @@
         <v>1353</v>
       </c>
       <c r="I328">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J328">
         <v>57</v>
@@ -17083,7 +17057,7 @@
       <c r="L328" t="s">
         <v>1435</v>
       </c>
-      <c r="N328" s="2">
+      <c r="N328" s="1">
         <v>46182</v>
       </c>
       <c r="Q328" t="b">
@@ -17106,7 +17080,7 @@
       <c r="E329" t="s">
         <v>1146</v>
       </c>
-      <c r="F329" s="2">
+      <c r="F329" s="1">
         <v>46125</v>
       </c>
       <c r="G329" t="s">
@@ -17116,7 +17090,7 @@
         <v>1353</v>
       </c>
       <c r="I329">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J329">
         <v>57</v>
@@ -17127,7 +17101,7 @@
       <c r="L329" t="s">
         <v>1435</v>
       </c>
-      <c r="N329" s="2">
+      <c r="N329" s="1">
         <v>46182</v>
       </c>
       <c r="Q329" t="b">
@@ -17150,7 +17124,7 @@
       <c r="E330" t="s">
         <v>1147</v>
       </c>
-      <c r="F330" s="2">
+      <c r="F330" s="1">
         <v>46125</v>
       </c>
       <c r="G330" t="s">
@@ -17160,7 +17134,7 @@
         <v>1353</v>
       </c>
       <c r="I330">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J330">
         <v>57</v>
@@ -17171,7 +17145,7 @@
       <c r="L330" t="s">
         <v>1435</v>
       </c>
-      <c r="N330" s="2">
+      <c r="N330" s="1">
         <v>46182</v>
       </c>
       <c r="Q330" t="b">
@@ -17194,7 +17168,7 @@
       <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="F331" s="2">
+      <c r="F331" s="1">
         <v>46125</v>
       </c>
       <c r="G331" t="s">
@@ -17204,7 +17178,7 @@
         <v>1353</v>
       </c>
       <c r="I331">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K331" t="s">
         <v>1356</v>
@@ -17232,7 +17206,7 @@
       <c r="E332" t="s">
         <v>1148</v>
       </c>
-      <c r="F332" s="2">
+      <c r="F332" s="1">
         <v>46125</v>
       </c>
       <c r="G332" t="s">
@@ -17242,7 +17216,7 @@
         <v>1353</v>
       </c>
       <c r="I332">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K332" t="s">
         <v>1357</v>
@@ -17270,7 +17244,7 @@
       <c r="E333" t="s">
         <v>910</v>
       </c>
-      <c r="F333" s="2">
+      <c r="F333" s="1">
         <v>46125</v>
       </c>
       <c r="G333" t="s">
@@ -17280,7 +17254,7 @@
         <v>1353</v>
       </c>
       <c r="I333">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J333">
         <v>100</v>
@@ -17291,7 +17265,7 @@
       <c r="L333" t="s">
         <v>1395</v>
       </c>
-      <c r="N333" s="2">
+      <c r="N333" s="1">
         <v>46225</v>
       </c>
       <c r="Q333" t="b">
@@ -17314,7 +17288,7 @@
       <c r="E334" t="s">
         <v>1149</v>
       </c>
-      <c r="F334" s="2">
+      <c r="F334" s="1">
         <v>46125</v>
       </c>
       <c r="G334" t="s">
@@ -17324,7 +17298,7 @@
         <v>1353</v>
       </c>
       <c r="I334">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K334" t="s">
         <v>1357</v>
@@ -17352,7 +17326,7 @@
       <c r="E335" t="s">
         <v>1150</v>
       </c>
-      <c r="F335" s="2">
+      <c r="F335" s="1">
         <v>46127</v>
       </c>
       <c r="G335" t="s">
@@ -17367,7 +17341,7 @@
       <c r="L335" t="s">
         <v>1434</v>
       </c>
-      <c r="N335" s="2">
+      <c r="N335" s="1">
         <v>46175</v>
       </c>
       <c r="Q335" t="b">
@@ -17390,7 +17364,7 @@
       <c r="E336" t="s">
         <v>1151</v>
       </c>
-      <c r="F336" s="2">
+      <c r="F336" s="1">
         <v>46127</v>
       </c>
       <c r="G336" t="s">
@@ -17400,7 +17374,7 @@
         <v>1353</v>
       </c>
       <c r="I336">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J336">
         <v>28</v>
@@ -17411,7 +17385,7 @@
       <c r="L336" t="s">
         <v>1388</v>
       </c>
-      <c r="N336" s="2">
+      <c r="N336" s="1">
         <v>46155</v>
       </c>
       <c r="Q336" t="b">
@@ -17434,7 +17408,7 @@
       <c r="E337" t="s">
         <v>1152</v>
       </c>
-      <c r="F337" s="2">
+      <c r="F337" s="1">
         <v>46127</v>
       </c>
       <c r="G337" t="s">
@@ -17449,7 +17423,7 @@
       <c r="L337" t="s">
         <v>1434</v>
       </c>
-      <c r="N337" s="2">
+      <c r="N337" s="1">
         <v>46175</v>
       </c>
       <c r="Q337" t="b">
@@ -17472,7 +17446,7 @@
       <c r="E338" t="s">
         <v>1153</v>
       </c>
-      <c r="F338" s="2">
+      <c r="F338" s="1">
         <v>46127</v>
       </c>
       <c r="G338" t="s">
@@ -17482,7 +17456,7 @@
         <v>1353</v>
       </c>
       <c r="I338">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J338">
         <v>12</v>
@@ -17493,7 +17467,7 @@
       <c r="L338" t="s">
         <v>1388</v>
       </c>
-      <c r="N338" s="2">
+      <c r="N338" s="1">
         <v>46139</v>
       </c>
       <c r="Q338" t="b">
@@ -17516,7 +17490,7 @@
       <c r="E339" t="s">
         <v>1154</v>
       </c>
-      <c r="F339" s="2">
+      <c r="F339" s="1">
         <v>46129</v>
       </c>
       <c r="G339" t="s">
@@ -17545,7 +17519,7 @@
       <c r="E340" t="s">
         <v>1155</v>
       </c>
-      <c r="F340" s="2">
+      <c r="F340" s="1">
         <v>46142</v>
       </c>
       <c r="G340" t="s">
@@ -17555,7 +17529,7 @@
         <v>1353</v>
       </c>
       <c r="I340">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J340">
         <v>98</v>
@@ -17563,7 +17537,7 @@
       <c r="L340" t="s">
         <v>1383</v>
       </c>
-      <c r="N340" s="2">
+      <c r="N340" s="1">
         <v>46240</v>
       </c>
       <c r="Q340" t="b">
@@ -17586,7 +17560,7 @@
       <c r="E341" t="s">
         <v>1156</v>
       </c>
-      <c r="F341" s="2">
+      <c r="F341" s="1">
         <v>46142</v>
       </c>
       <c r="G341" t="s">
@@ -17596,7 +17570,7 @@
         <v>1353</v>
       </c>
       <c r="I341">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J341">
         <v>90</v>
@@ -17604,7 +17578,7 @@
       <c r="L341" t="s">
         <v>1383</v>
       </c>
-      <c r="N341" s="2">
+      <c r="N341" s="1">
         <v>46232</v>
       </c>
       <c r="Q341" t="b">
@@ -17627,7 +17601,7 @@
       <c r="E342" t="s">
         <v>1157</v>
       </c>
-      <c r="F342" s="2">
+      <c r="F342" s="1">
         <v>46142</v>
       </c>
       <c r="G342" t="s">
@@ -17637,7 +17611,7 @@
         <v>1353</v>
       </c>
       <c r="I342">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K342" t="s">
         <v>1356</v>
@@ -17665,7 +17639,7 @@
       <c r="E343" t="s">
         <v>1158</v>
       </c>
-      <c r="F343" s="2">
+      <c r="F343" s="1">
         <v>46142</v>
       </c>
       <c r="G343" t="s">
@@ -17680,7 +17654,7 @@
       <c r="L343" t="s">
         <v>1383</v>
       </c>
-      <c r="N343" s="2">
+      <c r="N343" s="1">
         <v>46232</v>
       </c>
       <c r="Q343" t="b">
@@ -17703,7 +17677,7 @@
       <c r="E344" t="s">
         <v>1159</v>
       </c>
-      <c r="F344" s="2">
+      <c r="F344" s="1">
         <v>46142</v>
       </c>
       <c r="G344" t="s">
@@ -17718,7 +17692,7 @@
       <c r="L344" t="s">
         <v>1383</v>
       </c>
-      <c r="N344" s="2">
+      <c r="N344" s="1">
         <v>46232</v>
       </c>
       <c r="Q344" t="b">
@@ -17741,7 +17715,7 @@
       <c r="E345" t="s">
         <v>1160</v>
       </c>
-      <c r="F345" s="2">
+      <c r="F345" s="1">
         <v>46142</v>
       </c>
       <c r="G345" t="s">
@@ -17751,7 +17725,7 @@
         <v>1353</v>
       </c>
       <c r="I345">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K345" t="s">
         <v>1356</v>
@@ -17779,7 +17753,7 @@
       <c r="E346" t="s">
         <v>1161</v>
       </c>
-      <c r="F346" s="2">
+      <c r="F346" s="1">
         <v>46142</v>
       </c>
       <c r="G346" t="s">
@@ -17794,7 +17768,7 @@
       <c r="L346" t="s">
         <v>1383</v>
       </c>
-      <c r="N346" s="2">
+      <c r="N346" s="1">
         <v>46232</v>
       </c>
       <c r="Q346" t="b">
@@ -17817,7 +17791,7 @@
       <c r="E347" t="s">
         <v>1162</v>
       </c>
-      <c r="F347" s="2">
+      <c r="F347" s="1">
         <v>46142</v>
       </c>
       <c r="G347" t="s">
@@ -17827,7 +17801,7 @@
         <v>1353</v>
       </c>
       <c r="I347">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J347">
         <v>18</v>
@@ -17838,7 +17812,7 @@
       <c r="L347" t="s">
         <v>1431</v>
       </c>
-      <c r="N347" s="2">
+      <c r="N347" s="1">
         <v>46160</v>
       </c>
       <c r="Q347" t="b">
@@ -17861,7 +17835,7 @@
       <c r="E348" t="s">
         <v>1163</v>
       </c>
-      <c r="F348" s="2">
+      <c r="F348" s="1">
         <v>46142</v>
       </c>
       <c r="G348" t="s">
@@ -17871,7 +17845,7 @@
         <v>1353</v>
       </c>
       <c r="I348">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J348">
         <v>14</v>
@@ -17882,7 +17856,7 @@
       <c r="L348" t="s">
         <v>1432</v>
       </c>
-      <c r="N348" s="2">
+      <c r="N348" s="1">
         <v>46156</v>
       </c>
       <c r="Q348" t="b">
@@ -17905,7 +17879,7 @@
       <c r="E349" t="s">
         <v>1164</v>
       </c>
-      <c r="F349" s="2">
+      <c r="F349" s="1">
         <v>46142</v>
       </c>
       <c r="G349" t="s">
@@ -17915,7 +17889,7 @@
         <v>1353</v>
       </c>
       <c r="I349">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K349" t="s">
         <v>1361</v>
@@ -17943,7 +17917,7 @@
       <c r="E350" t="s">
         <v>1165</v>
       </c>
-      <c r="F350" s="2">
+      <c r="F350" s="1">
         <v>46142</v>
       </c>
       <c r="G350" t="s">
@@ -17953,12 +17927,12 @@
         <v>1353</v>
       </c>
       <c r="I350">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J350">
         <v>46</v>
       </c>
-      <c r="N350" s="2">
+      <c r="N350" s="1">
         <v>46188</v>
       </c>
       <c r="Q350" t="b">
@@ -17981,7 +17955,7 @@
       <c r="E351" t="s">
         <v>1166</v>
       </c>
-      <c r="F351" s="2">
+      <c r="F351" s="1">
         <v>46142</v>
       </c>
       <c r="G351" t="s">
@@ -17991,7 +17965,7 @@
         <v>1353</v>
       </c>
       <c r="I351">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J351">
         <v>82</v>
@@ -18002,7 +17976,7 @@
       <c r="L351" t="s">
         <v>1436</v>
       </c>
-      <c r="N351" s="2">
+      <c r="N351" s="1">
         <v>46224</v>
       </c>
       <c r="Q351" t="b">
@@ -18025,7 +17999,7 @@
       <c r="E352" t="s">
         <v>1167</v>
       </c>
-      <c r="F352" s="2">
+      <c r="F352" s="1">
         <v>46142</v>
       </c>
       <c r="G352" t="s">
@@ -18035,7 +18009,7 @@
         <v>1353</v>
       </c>
       <c r="I352">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J352">
         <v>78</v>
@@ -18046,7 +18020,7 @@
       <c r="L352" t="s">
         <v>1437</v>
       </c>
-      <c r="N352" s="2">
+      <c r="N352" s="1">
         <v>46220</v>
       </c>
       <c r="Q352" t="b">
@@ -18069,7 +18043,7 @@
       <c r="E353" t="s">
         <v>1168</v>
       </c>
-      <c r="F353" s="2">
+      <c r="F353" s="1">
         <v>46142</v>
       </c>
       <c r="G353" t="s">
@@ -18079,7 +18053,7 @@
         <v>1353</v>
       </c>
       <c r="I353">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J353">
         <v>83</v>
@@ -18090,7 +18064,7 @@
       <c r="L353" t="s">
         <v>1395</v>
       </c>
-      <c r="N353" s="2">
+      <c r="N353" s="1">
         <v>46225</v>
       </c>
       <c r="Q353" t="b">
@@ -18113,7 +18087,7 @@
       <c r="E354" t="s">
         <v>1169</v>
       </c>
-      <c r="F354" s="2">
+      <c r="F354" s="1">
         <v>46142</v>
       </c>
       <c r="G354" t="s">
@@ -18123,7 +18097,7 @@
         <v>1353</v>
       </c>
       <c r="I354">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K354" t="s">
         <v>1360</v>
@@ -18151,7 +18125,7 @@
       <c r="E355" t="s">
         <v>1170</v>
       </c>
-      <c r="F355" s="2">
+      <c r="F355" s="1">
         <v>46142</v>
       </c>
       <c r="G355" t="s">
@@ -18161,7 +18135,7 @@
         <v>1353</v>
       </c>
       <c r="I355">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J355">
         <v>8</v>
@@ -18172,7 +18146,7 @@
       <c r="L355" t="s">
         <v>1438</v>
       </c>
-      <c r="N355" s="2">
+      <c r="N355" s="1">
         <v>46150</v>
       </c>
       <c r="Q355" t="b">
@@ -18195,7 +18169,7 @@
       <c r="E356" t="s">
         <v>1171</v>
       </c>
-      <c r="F356" s="2">
+      <c r="F356" s="1">
         <v>46142</v>
       </c>
       <c r="G356" t="s">
@@ -18210,7 +18184,7 @@
       <c r="L356" t="s">
         <v>1439</v>
       </c>
-      <c r="N356" s="2">
+      <c r="N356" s="1">
         <v>46176</v>
       </c>
       <c r="Q356" t="b">
@@ -18233,7 +18207,7 @@
       <c r="E357" t="s">
         <v>1172</v>
       </c>
-      <c r="F357" s="2">
+      <c r="F357" s="1">
         <v>46142</v>
       </c>
       <c r="G357" t="s">
@@ -18243,7 +18217,7 @@
         <v>1353</v>
       </c>
       <c r="I357">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J357">
         <v>85</v>
@@ -18251,7 +18225,7 @@
       <c r="K357" t="s">
         <v>1360</v>
       </c>
-      <c r="N357" s="2">
+      <c r="N357" s="1">
         <v>46227</v>
       </c>
       <c r="Q357" t="b">
@@ -18274,7 +18248,7 @@
       <c r="E358" t="s">
         <v>1173</v>
       </c>
-      <c r="F358" s="2">
+      <c r="F358" s="1">
         <v>46142</v>
       </c>
       <c r="G358" t="s">
@@ -18292,7 +18266,7 @@
       <c r="L358" t="s">
         <v>1440</v>
       </c>
-      <c r="N358" s="2">
+      <c r="N358" s="1">
         <v>46227</v>
       </c>
       <c r="P358" t="s">
@@ -18318,7 +18292,7 @@
       <c r="E359" t="s">
         <v>1174</v>
       </c>
-      <c r="F359" s="2">
+      <c r="F359" s="1">
         <v>46142</v>
       </c>
       <c r="G359" t="s">
@@ -18330,7 +18304,7 @@
       <c r="J359">
         <v>63</v>
       </c>
-      <c r="N359" s="2">
+      <c r="N359" s="1">
         <v>46205</v>
       </c>
       <c r="P359" t="s">
@@ -18356,7 +18330,7 @@
       <c r="E360" t="s">
         <v>949</v>
       </c>
-      <c r="F360" s="2">
+      <c r="F360" s="1">
         <v>46142</v>
       </c>
       <c r="G360" t="s">
@@ -18366,7 +18340,7 @@
         <v>1353</v>
       </c>
       <c r="I360">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J360">
         <v>83</v>
@@ -18377,7 +18351,7 @@
       <c r="L360" t="s">
         <v>1395</v>
       </c>
-      <c r="N360" s="2">
+      <c r="N360" s="1">
         <v>46225</v>
       </c>
       <c r="O360" t="s">
@@ -18403,7 +18377,7 @@
       <c r="E361" t="s">
         <v>961</v>
       </c>
-      <c r="F361" s="2">
+      <c r="F361" s="1">
         <v>46142</v>
       </c>
       <c r="G361" t="s">
@@ -18413,7 +18387,7 @@
         <v>1353</v>
       </c>
       <c r="I361">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J361">
         <v>83</v>
@@ -18424,7 +18398,7 @@
       <c r="L361" t="s">
         <v>1395</v>
       </c>
-      <c r="N361" s="2">
+      <c r="N361" s="1">
         <v>46225</v>
       </c>
       <c r="Q361" t="b">
@@ -18447,7 +18421,7 @@
       <c r="E362" t="s">
         <v>1175</v>
       </c>
-      <c r="F362" s="2">
+      <c r="F362" s="1">
         <v>46142</v>
       </c>
       <c r="G362" t="s">
@@ -18457,7 +18431,7 @@
         <v>1353</v>
       </c>
       <c r="I362">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K362" t="s">
         <v>1360</v>
@@ -18485,7 +18459,7 @@
       <c r="E363" t="s">
         <v>1176</v>
       </c>
-      <c r="F363" s="2">
+      <c r="F363" s="1">
         <v>46142</v>
       </c>
       <c r="G363" t="s">
@@ -18495,7 +18469,7 @@
         <v>1353</v>
       </c>
       <c r="I363">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K363" t="s">
         <v>1360</v>
@@ -18523,7 +18497,7 @@
       <c r="E364" t="s">
         <v>958</v>
       </c>
-      <c r="F364" s="2">
+      <c r="F364" s="1">
         <v>46142</v>
       </c>
       <c r="G364" t="s">
@@ -18533,7 +18507,7 @@
         <v>1353</v>
       </c>
       <c r="I364">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J364">
         <v>83</v>
@@ -18544,7 +18518,7 @@
       <c r="L364" t="s">
         <v>1395</v>
       </c>
-      <c r="N364" s="2">
+      <c r="N364" s="1">
         <v>46225</v>
       </c>
       <c r="Q364" t="b">
@@ -18567,7 +18541,7 @@
       <c r="E365" t="s">
         <v>1177</v>
       </c>
-      <c r="F365" s="2">
+      <c r="F365" s="1">
         <v>46142</v>
       </c>
       <c r="G365" t="s">
@@ -18577,7 +18551,7 @@
         <v>1353</v>
       </c>
       <c r="I365">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J365">
         <v>15</v>
@@ -18585,7 +18559,7 @@
       <c r="K365" t="s">
         <v>1359</v>
       </c>
-      <c r="N365" s="2">
+      <c r="N365" s="1">
         <v>46157</v>
       </c>
       <c r="Q365" t="b">
@@ -18608,7 +18582,7 @@
       <c r="E366" t="s">
         <v>1178</v>
       </c>
-      <c r="F366" s="2">
+      <c r="F366" s="1">
         <v>46148</v>
       </c>
       <c r="G366" t="s">
@@ -18618,7 +18592,7 @@
         <v>1353</v>
       </c>
       <c r="I366">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J366">
         <v>77</v>
@@ -18629,7 +18603,7 @@
       <c r="L366" t="s">
         <v>1388</v>
       </c>
-      <c r="N366" s="2">
+      <c r="N366" s="1">
         <v>46225</v>
       </c>
       <c r="Q366" t="b">
@@ -18652,7 +18626,7 @@
       <c r="E367" t="s">
         <v>1179</v>
       </c>
-      <c r="F367" s="2">
+      <c r="F367" s="1">
         <v>46148</v>
       </c>
       <c r="G367" t="s">
@@ -18662,7 +18636,7 @@
         <v>1353</v>
       </c>
       <c r="I367">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J367">
         <v>77</v>
@@ -18673,7 +18647,7 @@
       <c r="L367" t="s">
         <v>1388</v>
       </c>
-      <c r="N367" s="2">
+      <c r="N367" s="1">
         <v>46225</v>
       </c>
       <c r="Q367" t="b">
@@ -18696,7 +18670,7 @@
       <c r="E368" t="s">
         <v>1180</v>
       </c>
-      <c r="F368" s="2">
+      <c r="F368" s="1">
         <v>46148</v>
       </c>
       <c r="G368" t="s">
@@ -18706,7 +18680,7 @@
         <v>1353</v>
       </c>
       <c r="I368">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J368">
         <v>77</v>
@@ -18717,7 +18691,7 @@
       <c r="L368" t="s">
         <v>1395</v>
       </c>
-      <c r="N368" s="2">
+      <c r="N368" s="1">
         <v>46225</v>
       </c>
       <c r="Q368" t="b">
@@ -18740,7 +18714,7 @@
       <c r="E369" t="s">
         <v>1181</v>
       </c>
-      <c r="F369" s="2">
+      <c r="F369" s="1">
         <v>46148</v>
       </c>
       <c r="G369" t="s">
@@ -18750,7 +18724,7 @@
         <v>1353</v>
       </c>
       <c r="I369">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K369" t="s">
         <v>1360</v>
@@ -18778,7 +18752,7 @@
       <c r="E370" t="s">
         <v>1182</v>
       </c>
-      <c r="F370" s="2">
+      <c r="F370" s="1">
         <v>46148</v>
       </c>
       <c r="G370" t="s">
@@ -18788,7 +18762,7 @@
         <v>1353</v>
       </c>
       <c r="I370">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K370" t="s">
         <v>1360</v>
@@ -18816,7 +18790,7 @@
       <c r="E371" t="s">
         <v>1183</v>
       </c>
-      <c r="F371" s="2">
+      <c r="F371" s="1">
         <v>46148</v>
       </c>
       <c r="G371" t="s">
@@ -18826,7 +18800,7 @@
         <v>1353</v>
       </c>
       <c r="I371">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J371">
         <v>16</v>
@@ -18837,7 +18811,7 @@
       <c r="L371" t="s">
         <v>1441</v>
       </c>
-      <c r="N371" s="2">
+      <c r="N371" s="1">
         <v>46164</v>
       </c>
       <c r="Q371" t="b">
@@ -18860,7 +18834,7 @@
       <c r="E372" t="s">
         <v>1184</v>
       </c>
-      <c r="F372" s="2">
+      <c r="F372" s="1">
         <v>46148</v>
       </c>
       <c r="G372" t="s">
@@ -18878,7 +18852,7 @@
       <c r="L372" t="s">
         <v>1428</v>
       </c>
-      <c r="N372" s="2">
+      <c r="N372" s="1">
         <v>46113</v>
       </c>
       <c r="P372" t="s">
@@ -18904,7 +18878,7 @@
       <c r="E373" t="s">
         <v>1185</v>
       </c>
-      <c r="F373" s="2">
+      <c r="F373" s="1">
         <v>46149</v>
       </c>
       <c r="G373" t="s">
@@ -18914,7 +18888,7 @@
         <v>1353</v>
       </c>
       <c r="I373">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K373" t="s">
         <v>1356</v>
@@ -18942,7 +18916,7 @@
       <c r="E374" t="s">
         <v>1186</v>
       </c>
-      <c r="F374" s="2">
+      <c r="F374" s="1">
         <v>46149</v>
       </c>
       <c r="G374" t="s">
@@ -18952,7 +18926,7 @@
         <v>1353</v>
       </c>
       <c r="I374">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K374" t="s">
         <v>1356</v>
@@ -18980,7 +18954,7 @@
       <c r="E375" t="s">
         <v>1187</v>
       </c>
-      <c r="F375" s="2">
+      <c r="F375" s="1">
         <v>46154</v>
       </c>
       <c r="G375" t="s">
@@ -18990,7 +18964,7 @@
         <v>1353</v>
       </c>
       <c r="I375">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J375">
         <v>94</v>
@@ -18998,7 +18972,7 @@
       <c r="K375" t="s">
         <v>1360</v>
       </c>
-      <c r="N375" s="2">
+      <c r="N375" s="1">
         <v>46248</v>
       </c>
       <c r="Q375" t="b">
@@ -19021,7 +18995,7 @@
       <c r="E376" t="s">
         <v>1188</v>
       </c>
-      <c r="F376" s="2">
+      <c r="F376" s="1">
         <v>46154</v>
       </c>
       <c r="G376" t="s">
@@ -19031,7 +19005,7 @@
         <v>1353</v>
       </c>
       <c r="I376">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K376" t="s">
         <v>1360</v>
@@ -19059,7 +19033,7 @@
       <c r="E377" t="s">
         <v>1189</v>
       </c>
-      <c r="F377" s="2">
+      <c r="F377" s="1">
         <v>46154</v>
       </c>
       <c r="G377" t="s">
@@ -19071,7 +19045,7 @@
       <c r="K377" t="s">
         <v>1360</v>
       </c>
-      <c r="N377" s="2">
+      <c r="N377" s="1">
         <v>46176</v>
       </c>
       <c r="O377" t="s">
@@ -19100,7 +19074,7 @@
       <c r="E378" t="s">
         <v>1190</v>
       </c>
-      <c r="F378" s="2">
+      <c r="F378" s="1">
         <v>46154</v>
       </c>
       <c r="G378" t="s">
@@ -19110,7 +19084,7 @@
         <v>1353</v>
       </c>
       <c r="I378">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K378" t="s">
         <v>1360</v>
@@ -19138,7 +19112,7 @@
       <c r="E379" t="s">
         <v>1191</v>
       </c>
-      <c r="F379" s="2">
+      <c r="F379" s="1">
         <v>46154</v>
       </c>
       <c r="G379" t="s">
@@ -19148,7 +19122,7 @@
         <v>1353</v>
       </c>
       <c r="I379">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J379">
         <v>20</v>
@@ -19159,7 +19133,7 @@
       <c r="L379" t="s">
         <v>1442</v>
       </c>
-      <c r="N379" s="2">
+      <c r="N379" s="1">
         <v>46174</v>
       </c>
       <c r="Q379" t="b">
@@ -19182,7 +19156,7 @@
       <c r="E380" t="s">
         <v>1192</v>
       </c>
-      <c r="F380" s="2">
+      <c r="F380" s="1">
         <v>46154</v>
       </c>
       <c r="G380" t="s">
@@ -19192,7 +19166,7 @@
         <v>1353</v>
       </c>
       <c r="I380">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J380">
         <v>94</v>
@@ -19203,7 +19177,7 @@
       <c r="L380" t="s">
         <v>1443</v>
       </c>
-      <c r="N380" s="2">
+      <c r="N380" s="1">
         <v>46248</v>
       </c>
       <c r="Q380" t="b">
@@ -19226,7 +19200,7 @@
       <c r="E381" t="s">
         <v>1193</v>
       </c>
-      <c r="F381" s="2">
+      <c r="F381" s="1">
         <v>46154</v>
       </c>
       <c r="G381" t="s">
@@ -19236,7 +19210,7 @@
         <v>1353</v>
       </c>
       <c r="I381">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K381" t="s">
         <v>1360</v>
@@ -19264,7 +19238,7 @@
       <c r="E382" t="s">
         <v>1194</v>
       </c>
-      <c r="F382" s="2">
+      <c r="F382" s="1">
         <v>46154</v>
       </c>
       <c r="G382" t="s">
@@ -19274,7 +19248,7 @@
         <v>1353</v>
       </c>
       <c r="I382">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K382" t="s">
         <v>1360</v>
@@ -19302,7 +19276,7 @@
       <c r="E383" t="s">
         <v>1195</v>
       </c>
-      <c r="F383" s="2">
+      <c r="F383" s="1">
         <v>46154</v>
       </c>
       <c r="G383" t="s">
@@ -19312,7 +19286,7 @@
         <v>1353</v>
       </c>
       <c r="I383">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J383">
         <v>71</v>
@@ -19323,7 +19297,7 @@
       <c r="L383" t="s">
         <v>1444</v>
       </c>
-      <c r="N383" s="2">
+      <c r="N383" s="1">
         <v>46225</v>
       </c>
       <c r="Q383" t="b">
@@ -19346,7 +19320,7 @@
       <c r="E384" t="s">
         <v>1196</v>
       </c>
-      <c r="F384" s="2">
+      <c r="F384" s="1">
         <v>46164</v>
       </c>
       <c r="G384" t="s">
@@ -19356,7 +19330,7 @@
         <v>1353</v>
       </c>
       <c r="I384">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K384" t="s">
         <v>1357</v>
@@ -19384,7 +19358,7 @@
       <c r="E385" t="s">
         <v>1197</v>
       </c>
-      <c r="F385" s="2">
+      <c r="F385" s="1">
         <v>46164</v>
       </c>
       <c r="G385" t="s">
@@ -19394,7 +19368,7 @@
         <v>1353</v>
       </c>
       <c r="I385">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J385">
         <v>102</v>
@@ -19405,7 +19379,7 @@
       <c r="L385" t="s">
         <v>1445</v>
       </c>
-      <c r="N385" s="2">
+      <c r="N385" s="1">
         <v>46266</v>
       </c>
       <c r="P385" t="s">
@@ -19431,7 +19405,7 @@
       <c r="E386" t="s">
         <v>1198</v>
       </c>
-      <c r="F386" s="2">
+      <c r="F386" s="1">
         <v>46171</v>
       </c>
       <c r="G386" t="s">
@@ -19441,7 +19415,7 @@
         <v>1353</v>
       </c>
       <c r="I386">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K386" t="s">
         <v>1360</v>
@@ -19469,7 +19443,7 @@
       <c r="E387" t="s">
         <v>1199</v>
       </c>
-      <c r="F387" s="2">
+      <c r="F387" s="1">
         <v>46171</v>
       </c>
       <c r="G387" t="s">
@@ -19479,7 +19453,7 @@
         <v>1353</v>
       </c>
       <c r="I387">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K387" t="s">
         <v>1360</v>
@@ -19507,7 +19481,7 @@
       <c r="E388" t="s">
         <v>851</v>
       </c>
-      <c r="F388" s="2">
+      <c r="F388" s="1">
         <v>46171</v>
       </c>
       <c r="G388" t="s">
@@ -19517,7 +19491,7 @@
         <v>1353</v>
       </c>
       <c r="I388">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J388">
         <v>-85</v>
@@ -19528,7 +19502,7 @@
       <c r="L388" t="s">
         <v>1446</v>
       </c>
-      <c r="N388" s="2">
+      <c r="N388" s="1">
         <v>46086</v>
       </c>
       <c r="Q388" t="b">
@@ -19551,7 +19525,7 @@
       <c r="E389" t="s">
         <v>1200</v>
       </c>
-      <c r="F389" s="2">
+      <c r="F389" s="1">
         <v>46171</v>
       </c>
       <c r="G389" t="s">
@@ -19561,7 +19535,7 @@
         <v>1353</v>
       </c>
       <c r="I389">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K389" t="s">
         <v>1361</v>
@@ -19589,7 +19563,7 @@
       <c r="E390" t="s">
         <v>1201</v>
       </c>
-      <c r="F390" s="2">
+      <c r="F390" s="1">
         <v>46171</v>
       </c>
       <c r="G390" t="s">
@@ -19607,7 +19581,7 @@
       <c r="L390" t="s">
         <v>1447</v>
       </c>
-      <c r="N390" s="2">
+      <c r="N390" s="1">
         <v>46191</v>
       </c>
       <c r="P390" t="s">
@@ -19633,7 +19607,7 @@
       <c r="E391" t="s">
         <v>1202</v>
       </c>
-      <c r="F391" s="2">
+      <c r="F391" s="1">
         <v>46171</v>
       </c>
       <c r="G391" t="s">
@@ -19671,7 +19645,7 @@
       <c r="E392" t="s">
         <v>1203</v>
       </c>
-      <c r="F392" s="2">
+      <c r="F392" s="1">
         <v>46171</v>
       </c>
       <c r="G392" t="s">
@@ -19686,7 +19660,7 @@
       <c r="L392" t="s">
         <v>1439</v>
       </c>
-      <c r="N392" s="2">
+      <c r="N392" s="1">
         <v>46176</v>
       </c>
       <c r="Q392" t="b">
@@ -19709,7 +19683,7 @@
       <c r="E393" t="s">
         <v>1204</v>
       </c>
-      <c r="F393" s="2">
+      <c r="F393" s="1">
         <v>46171</v>
       </c>
       <c r="G393" t="s">
@@ -19719,7 +19693,7 @@
         <v>1353</v>
       </c>
       <c r="I393">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J393">
         <v>20</v>
@@ -19730,7 +19704,7 @@
       <c r="L393" t="s">
         <v>1388</v>
       </c>
-      <c r="N393" s="2">
+      <c r="N393" s="1">
         <v>46191</v>
       </c>
       <c r="Q393" t="b">
@@ -19753,7 +19727,7 @@
       <c r="E394" t="s">
         <v>1205</v>
       </c>
-      <c r="F394" s="2">
+      <c r="F394" s="1">
         <v>46171</v>
       </c>
       <c r="G394" t="s">
@@ -19771,7 +19745,7 @@
       <c r="L394" t="s">
         <v>1448</v>
       </c>
-      <c r="N394" s="2">
+      <c r="N394" s="1">
         <v>46241</v>
       </c>
       <c r="P394" t="s">
@@ -19797,7 +19771,7 @@
       <c r="E395" t="s">
         <v>1206</v>
       </c>
-      <c r="F395" s="2">
+      <c r="F395" s="1">
         <v>46171</v>
       </c>
       <c r="G395" t="s">
@@ -19815,7 +19789,7 @@
       <c r="L395" t="s">
         <v>1449</v>
       </c>
-      <c r="N395" s="2">
+      <c r="N395" s="1">
         <v>46191</v>
       </c>
       <c r="P395" t="s">
@@ -19841,7 +19815,7 @@
       <c r="E396" t="s">
         <v>1207</v>
       </c>
-      <c r="F396" s="2">
+      <c r="F396" s="1">
         <v>46171</v>
       </c>
       <c r="G396" t="s">
@@ -19853,7 +19827,7 @@
       <c r="J396">
         <v>20</v>
       </c>
-      <c r="N396" s="2">
+      <c r="N396" s="1">
         <v>46191</v>
       </c>
       <c r="P396" t="s">
@@ -19879,7 +19853,7 @@
       <c r="E397" t="s">
         <v>1208</v>
       </c>
-      <c r="F397" s="2">
+      <c r="F397" s="1">
         <v>46171</v>
       </c>
       <c r="G397" t="s">
@@ -19897,7 +19871,7 @@
       <c r="L397" t="s">
         <v>1448</v>
       </c>
-      <c r="N397" s="2">
+      <c r="N397" s="1">
         <v>46241</v>
       </c>
       <c r="P397" t="s">
@@ -19923,7 +19897,7 @@
       <c r="E398" t="s">
         <v>1209</v>
       </c>
-      <c r="F398" s="2">
+      <c r="F398" s="1">
         <v>46171</v>
       </c>
       <c r="G398" t="s">
@@ -19941,7 +19915,7 @@
       <c r="L398" t="s">
         <v>1449</v>
       </c>
-      <c r="N398" s="2">
+      <c r="N398" s="1">
         <v>46191</v>
       </c>
       <c r="P398" t="s">
@@ -19967,7 +19941,7 @@
       <c r="E399" t="s">
         <v>987</v>
       </c>
-      <c r="F399" s="2">
+      <c r="F399" s="1">
         <v>46163</v>
       </c>
       <c r="G399" t="s">
@@ -19982,7 +19956,7 @@
       <c r="L399" t="s">
         <v>1450</v>
       </c>
-      <c r="N399" s="2">
+      <c r="N399" s="1">
         <v>46171</v>
       </c>
       <c r="Q399" t="b">
@@ -20005,7 +19979,7 @@
       <c r="E400" t="s">
         <v>1210</v>
       </c>
-      <c r="F400" s="2">
+      <c r="F400" s="1">
         <v>46171</v>
       </c>
       <c r="G400" t="s">
@@ -20015,7 +19989,7 @@
         <v>1353</v>
       </c>
       <c r="I400">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K400" t="s">
         <v>1360</v>
@@ -20043,7 +20017,7 @@
       <c r="E401" t="s">
         <v>1211</v>
       </c>
-      <c r="F401" s="2">
+      <c r="F401" s="1">
         <v>46171</v>
       </c>
       <c r="G401" t="s">
@@ -20055,7 +20029,7 @@
       <c r="J401">
         <v>40</v>
       </c>
-      <c r="N401" s="2">
+      <c r="N401" s="1">
         <v>46211</v>
       </c>
       <c r="P401" t="s">
@@ -20081,7 +20055,7 @@
       <c r="E402" t="s">
         <v>1212</v>
       </c>
-      <c r="F402" s="2">
+      <c r="F402" s="1">
         <v>46171</v>
       </c>
       <c r="G402" t="s">
@@ -20091,7 +20065,7 @@
         <v>1353</v>
       </c>
       <c r="I402">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K402" t="s">
         <v>1360</v>
@@ -20119,7 +20093,7 @@
       <c r="E403" t="s">
         <v>1213</v>
       </c>
-      <c r="F403" s="2">
+      <c r="F403" s="1">
         <v>46171</v>
       </c>
       <c r="G403" t="s">
@@ -20129,7 +20103,7 @@
         <v>1353</v>
       </c>
       <c r="I403">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J403">
         <v>83</v>
@@ -20140,7 +20114,7 @@
       <c r="L403" t="s">
         <v>1451</v>
       </c>
-      <c r="N403" s="2">
+      <c r="N403" s="1">
         <v>46254</v>
       </c>
       <c r="Q403" t="b">
@@ -20163,7 +20137,7 @@
       <c r="E404" t="s">
         <v>1214</v>
       </c>
-      <c r="F404" s="2">
+      <c r="F404" s="1">
         <v>46171</v>
       </c>
       <c r="G404" t="s">
@@ -20173,7 +20147,7 @@
         <v>1353</v>
       </c>
       <c r="I404">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K404" t="s">
         <v>1360</v>
@@ -20201,7 +20175,7 @@
       <c r="E405" t="s">
         <v>1215</v>
       </c>
-      <c r="F405" s="2">
+      <c r="F405" s="1">
         <v>46183</v>
       </c>
       <c r="G405" t="s">
@@ -20233,7 +20207,7 @@
       <c r="E406" t="s">
         <v>1216</v>
       </c>
-      <c r="F406" s="2">
+      <c r="F406" s="1">
         <v>46183</v>
       </c>
       <c r="G406" t="s">
@@ -20243,7 +20217,7 @@
         <v>1353</v>
       </c>
       <c r="I406">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q406" t="b">
         <v>1</v>
@@ -20265,7 +20239,7 @@
       <c r="E407" t="s">
         <v>1217</v>
       </c>
-      <c r="F407" s="2">
+      <c r="F407" s="1">
         <v>46183</v>
       </c>
       <c r="G407" t="s">
@@ -20275,7 +20249,7 @@
         <v>1353</v>
       </c>
       <c r="I407">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q407" t="b">
         <v>1</v>
@@ -20297,7 +20271,7 @@
       <c r="E408" t="s">
         <v>1218</v>
       </c>
-      <c r="F408" s="2">
+      <c r="F408" s="1">
         <v>46183</v>
       </c>
       <c r="G408" t="s">
@@ -20307,7 +20281,7 @@
         <v>1353</v>
       </c>
       <c r="I408">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q408" t="b">
         <v>1</v>
@@ -20329,7 +20303,7 @@
       <c r="E409" t="s">
         <v>1219</v>
       </c>
-      <c r="F409" s="2">
+      <c r="F409" s="1">
         <v>46183</v>
       </c>
       <c r="G409" t="s">
@@ -20339,7 +20313,7 @@
         <v>1353</v>
       </c>
       <c r="I409">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q409" t="b">
         <v>1</v>
@@ -20361,7 +20335,7 @@
       <c r="E410" t="s">
         <v>1220</v>
       </c>
-      <c r="F410" s="2">
+      <c r="F410" s="1">
         <v>46183</v>
       </c>
       <c r="G410" t="s">
@@ -20371,7 +20345,7 @@
         <v>1353</v>
       </c>
       <c r="I410">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q410" t="b">
         <v>1</v>
@@ -20393,7 +20367,7 @@
       <c r="E411" t="s">
         <v>1221</v>
       </c>
-      <c r="F411" s="2">
+      <c r="F411" s="1">
         <v>46188</v>
       </c>
       <c r="G411" t="s">
@@ -20403,7 +20377,7 @@
         <v>1353</v>
       </c>
       <c r="I411">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q411" t="b">
         <v>1</v>
@@ -20425,7 +20399,7 @@
       <c r="E412" t="s">
         <v>1222</v>
       </c>
-      <c r="F412" s="2">
+      <c r="F412" s="1">
         <v>46188</v>
       </c>
       <c r="G412" t="s">
@@ -20435,7 +20409,7 @@
         <v>1353</v>
       </c>
       <c r="I412">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q412" t="b">
         <v>1</v>
@@ -20457,7 +20431,7 @@
       <c r="E413" t="s">
         <v>1223</v>
       </c>
-      <c r="F413" s="2">
+      <c r="F413" s="1">
         <v>46188</v>
       </c>
       <c r="G413" t="s">
@@ -20467,7 +20441,7 @@
         <v>1353</v>
       </c>
       <c r="I413">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q413" t="b">
         <v>1</v>
@@ -20489,7 +20463,7 @@
       <c r="E414" t="s">
         <v>1224</v>
       </c>
-      <c r="F414" s="2">
+      <c r="F414" s="1">
         <v>46188</v>
       </c>
       <c r="G414" t="s">
@@ -20518,7 +20492,7 @@
       <c r="E415" t="s">
         <v>1060</v>
       </c>
-      <c r="F415" s="2">
+      <c r="F415" s="1">
         <v>46188</v>
       </c>
       <c r="G415" t="s">
@@ -20547,7 +20521,7 @@
       <c r="E416" t="s">
         <v>1225</v>
       </c>
-      <c r="F416" s="2">
+      <c r="F416" s="1">
         <v>46188</v>
       </c>
       <c r="G416" t="s">
@@ -20557,7 +20531,7 @@
         <v>1353</v>
       </c>
       <c r="I416">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q416" t="b">
         <v>1</v>
@@ -20579,7 +20553,7 @@
       <c r="E417" t="s">
         <v>1226</v>
       </c>
-      <c r="F417" s="2">
+      <c r="F417" s="1">
         <v>46188</v>
       </c>
       <c r="G417" t="s">
@@ -20608,7 +20582,7 @@
       <c r="E418" t="s">
         <v>1227</v>
       </c>
-      <c r="F418" s="2">
+      <c r="F418" s="1">
         <v>46188</v>
       </c>
       <c r="G418" t="s">
@@ -20637,7 +20611,7 @@
       <c r="E419" t="s">
         <v>1228</v>
       </c>
-      <c r="F419" s="2">
+      <c r="F419" s="1">
         <v>46188</v>
       </c>
       <c r="G419" t="s">
@@ -20647,7 +20621,7 @@
         <v>1353</v>
       </c>
       <c r="I419">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q419" t="b">
         <v>1</v>
@@ -20669,7 +20643,7 @@
       <c r="E420" t="s">
         <v>1229</v>
       </c>
-      <c r="F420" s="2">
+      <c r="F420" s="1">
         <v>46188</v>
       </c>
       <c r="G420" t="s">
@@ -20679,7 +20653,7 @@
         <v>1353</v>
       </c>
       <c r="I420">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q420" t="b">
         <v>1</v>
@@ -20701,7 +20675,7 @@
       <c r="E421" t="s">
         <v>1230</v>
       </c>
-      <c r="F421" s="2">
+      <c r="F421" s="1">
         <v>46188</v>
       </c>
       <c r="G421" t="s">
@@ -20711,7 +20685,7 @@
         <v>1353</v>
       </c>
       <c r="I421">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q421" t="b">
         <v>1</v>
@@ -20733,7 +20707,7 @@
       <c r="E422" t="s">
         <v>1231</v>
       </c>
-      <c r="F422" s="2">
+      <c r="F422" s="1">
         <v>46188</v>
       </c>
       <c r="G422" t="s">
@@ -20743,7 +20717,7 @@
         <v>1353</v>
       </c>
       <c r="I422">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q422" t="b">
         <v>1</v>
@@ -20765,7 +20739,7 @@
       <c r="E423" t="s">
         <v>1232</v>
       </c>
-      <c r="F423" s="2">
+      <c r="F423" s="1">
         <v>46188</v>
       </c>
       <c r="G423" t="s">
@@ -20775,7 +20749,7 @@
         <v>1353</v>
       </c>
       <c r="I423">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q423" t="b">
         <v>1</v>
@@ -20797,7 +20771,7 @@
       <c r="E424" t="s">
         <v>1233</v>
       </c>
-      <c r="F424" s="2">
+      <c r="F424" s="1">
         <v>46188</v>
       </c>
       <c r="G424" t="s">
@@ -20807,7 +20781,7 @@
         <v>1353</v>
       </c>
       <c r="I424">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q424" t="b">
         <v>1</v>
@@ -20829,7 +20803,7 @@
       <c r="E425" t="s">
         <v>1234</v>
       </c>
-      <c r="F425" s="2">
+      <c r="F425" s="1">
         <v>46188</v>
       </c>
       <c r="G425" t="s">
@@ -20839,7 +20813,7 @@
         <v>1353</v>
       </c>
       <c r="I425">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q425" t="b">
         <v>1</v>
@@ -20861,7 +20835,7 @@
       <c r="E426" t="s">
         <v>1235</v>
       </c>
-      <c r="F426" s="2">
+      <c r="F426" s="1">
         <v>46188</v>
       </c>
       <c r="G426" t="s">
@@ -20871,7 +20845,7 @@
         <v>1353</v>
       </c>
       <c r="I426">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q426" t="b">
         <v>1</v>
@@ -20893,7 +20867,7 @@
       <c r="E427" t="s">
         <v>1236</v>
       </c>
-      <c r="F427" s="2">
+      <c r="F427" s="1">
         <v>46188</v>
       </c>
       <c r="G427" t="s">
@@ -20903,7 +20877,7 @@
         <v>1353</v>
       </c>
       <c r="I427">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q427" t="b">
         <v>1</v>
@@ -20925,7 +20899,7 @@
       <c r="E428" t="s">
         <v>1237</v>
       </c>
-      <c r="F428" s="2">
+      <c r="F428" s="1">
         <v>46188</v>
       </c>
       <c r="G428" t="s">
@@ -20954,7 +20928,7 @@
       <c r="E429" t="s">
         <v>1238</v>
       </c>
-      <c r="F429" s="2">
+      <c r="F429" s="1">
         <v>46188</v>
       </c>
       <c r="G429" t="s">
@@ -20983,7 +20957,7 @@
       <c r="E430" t="s">
         <v>1239</v>
       </c>
-      <c r="F430" s="2">
+      <c r="F430" s="1">
         <v>46188</v>
       </c>
       <c r="G430" t="s">
@@ -20993,7 +20967,7 @@
         <v>1353</v>
       </c>
       <c r="I430">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q430" t="b">
         <v>1</v>
@@ -21015,7 +20989,7 @@
       <c r="E431" t="s">
         <v>1240</v>
       </c>
-      <c r="F431" s="2">
+      <c r="F431" s="1">
         <v>46188</v>
       </c>
       <c r="G431" t="s">
@@ -21025,7 +20999,7 @@
         <v>1353</v>
       </c>
       <c r="I431">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q431" t="b">
         <v>1</v>
@@ -21047,7 +21021,7 @@
       <c r="E432" t="s">
         <v>1241</v>
       </c>
-      <c r="F432" s="2">
+      <c r="F432" s="1">
         <v>46188</v>
       </c>
       <c r="G432" t="s">
@@ -21057,7 +21031,7 @@
         <v>1353</v>
       </c>
       <c r="I432">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q432" t="b">
         <v>1</v>
@@ -21079,7 +21053,7 @@
       <c r="E433" t="s">
         <v>1242</v>
       </c>
-      <c r="F433" s="2">
+      <c r="F433" s="1">
         <v>46188</v>
       </c>
       <c r="G433" t="s">
@@ -21089,7 +21063,7 @@
         <v>1353</v>
       </c>
       <c r="I433">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q433" t="b">
         <v>1</v>
@@ -21111,7 +21085,7 @@
       <c r="E434" t="s">
         <v>1243</v>
       </c>
-      <c r="F434" s="2">
+      <c r="F434" s="1">
         <v>46188</v>
       </c>
       <c r="G434" t="s">
@@ -21121,7 +21095,7 @@
         <v>1353</v>
       </c>
       <c r="I434">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q434" t="b">
         <v>1</v>
@@ -21143,7 +21117,7 @@
       <c r="E435" t="s">
         <v>856</v>
       </c>
-      <c r="F435" s="2">
+      <c r="F435" s="1">
         <v>46188</v>
       </c>
       <c r="G435" t="s">
@@ -21153,7 +21127,7 @@
         <v>1353</v>
       </c>
       <c r="I435">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q435" t="b">
         <v>1</v>
@@ -21175,7 +21149,7 @@
       <c r="E436" t="s">
         <v>1244</v>
       </c>
-      <c r="F436" s="2">
+      <c r="F436" s="1">
         <v>46188</v>
       </c>
       <c r="G436" t="s">
@@ -21185,7 +21159,7 @@
         <v>1353</v>
       </c>
       <c r="I436">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q436" t="b">
         <v>1</v>
@@ -21207,7 +21181,7 @@
       <c r="E437" t="s">
         <v>1245</v>
       </c>
-      <c r="F437" s="2">
+      <c r="F437" s="1">
         <v>46188</v>
       </c>
       <c r="G437" t="s">
@@ -21217,7 +21191,7 @@
         <v>1355</v>
       </c>
       <c r="I437">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q437" t="b">
         <v>1</v>
@@ -21239,7 +21213,7 @@
       <c r="E438" t="s">
         <v>1246</v>
       </c>
-      <c r="F438" s="2">
+      <c r="F438" s="1">
         <v>46188</v>
       </c>
       <c r="G438" t="s">
@@ -21249,7 +21223,7 @@
         <v>1355</v>
       </c>
       <c r="I438">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q438" t="b">
         <v>1</v>
@@ -21271,7 +21245,7 @@
       <c r="E439" t="s">
         <v>1247</v>
       </c>
-      <c r="F439" s="2">
+      <c r="F439" s="1">
         <v>46196</v>
       </c>
       <c r="G439" t="s">
@@ -21281,7 +21255,7 @@
         <v>1353</v>
       </c>
       <c r="I439">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q439" t="b">
         <v>1</v>
@@ -21303,7 +21277,7 @@
       <c r="E440" t="s">
         <v>1248</v>
       </c>
-      <c r="F440" s="2">
+      <c r="F440" s="1">
         <v>46196</v>
       </c>
       <c r="G440" t="s">
@@ -21313,7 +21287,7 @@
         <v>1353</v>
       </c>
       <c r="I440">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q440" t="b">
         <v>1</v>
@@ -21335,7 +21309,7 @@
       <c r="E441" t="s">
         <v>1249</v>
       </c>
-      <c r="F441" s="2">
+      <c r="F441" s="1">
         <v>46203</v>
       </c>
       <c r="G441" t="s">
@@ -21345,7 +21319,7 @@
         <v>1353</v>
       </c>
       <c r="I441">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q441" t="b">
         <v>1</v>
@@ -21367,7 +21341,7 @@
       <c r="E442" t="s">
         <v>1250</v>
       </c>
-      <c r="F442" s="2">
+      <c r="F442" s="1">
         <v>46203</v>
       </c>
       <c r="G442" t="s">
@@ -21396,7 +21370,7 @@
       <c r="E443" t="s">
         <v>1251</v>
       </c>
-      <c r="F443" s="2">
+      <c r="F443" s="1">
         <v>46205</v>
       </c>
       <c r="G443" t="s">
@@ -21406,7 +21380,7 @@
         <v>1353</v>
       </c>
       <c r="I443">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q443" t="b">
         <v>1</v>
@@ -21428,7 +21402,7 @@
       <c r="E444" t="s">
         <v>1252</v>
       </c>
-      <c r="F444" s="2">
+      <c r="F444" s="1">
         <v>46205</v>
       </c>
       <c r="G444" t="s">
@@ -21457,7 +21431,7 @@
       <c r="E445" t="s">
         <v>1253</v>
       </c>
-      <c r="F445" s="2">
+      <c r="F445" s="1">
         <v>46205</v>
       </c>
       <c r="G445" t="s">
@@ -21486,7 +21460,7 @@
       <c r="E446" t="s">
         <v>1254</v>
       </c>
-      <c r="F446" s="2">
+      <c r="F446" s="1">
         <v>46211</v>
       </c>
       <c r="G446" t="s">
@@ -21496,7 +21470,7 @@
         <v>1353</v>
       </c>
       <c r="I446">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q446" t="b">
         <v>1</v>
@@ -21518,7 +21492,7 @@
       <c r="E447" t="s">
         <v>1255</v>
       </c>
-      <c r="F447" s="2">
+      <c r="F447" s="1">
         <v>46211</v>
       </c>
       <c r="G447" t="s">
@@ -21528,7 +21502,7 @@
         <v>1353</v>
       </c>
       <c r="I447">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q447" t="b">
         <v>1</v>
@@ -21550,7 +21524,7 @@
       <c r="E448" t="s">
         <v>1256</v>
       </c>
-      <c r="F448" s="2">
+      <c r="F448" s="1">
         <v>46226</v>
       </c>
       <c r="G448" t="s">
@@ -21560,7 +21534,7 @@
         <v>1353</v>
       </c>
       <c r="I448">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q448" t="b">
         <v>1</v>
@@ -21582,7 +21556,7 @@
       <c r="E449" t="s">
         <v>1257</v>
       </c>
-      <c r="F449" s="2">
+      <c r="F449" s="1">
         <v>46226</v>
       </c>
       <c r="G449" t="s">
@@ -21592,7 +21566,7 @@
         <v>1353</v>
       </c>
       <c r="I449">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q449" t="b">
         <v>1</v>
@@ -21614,7 +21588,7 @@
       <c r="E450" t="s">
         <v>1258</v>
       </c>
-      <c r="F450" s="2">
+      <c r="F450" s="1">
         <v>46226</v>
       </c>
       <c r="G450" t="s">
@@ -21624,7 +21598,7 @@
         <v>1353</v>
       </c>
       <c r="I450">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q450" t="b">
         <v>1</v>
@@ -21646,7 +21620,7 @@
       <c r="E451" t="s">
         <v>1035</v>
       </c>
-      <c r="F451" s="2">
+      <c r="F451" s="1">
         <v>46230</v>
       </c>
       <c r="G451" t="s">
@@ -21656,7 +21630,7 @@
         <v>1353</v>
       </c>
       <c r="I451">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q451" t="b">
         <v>1</v>
@@ -21678,7 +21652,7 @@
       <c r="E452" t="s">
         <v>1259</v>
       </c>
-      <c r="F452" s="2">
+      <c r="F452" s="1">
         <v>46230</v>
       </c>
       <c r="G452" t="s">
@@ -21688,7 +21662,7 @@
         <v>1353</v>
       </c>
       <c r="I452">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q452" t="b">
         <v>1</v>
@@ -21710,7 +21684,7 @@
       <c r="E453" t="s">
         <v>1260</v>
       </c>
-      <c r="F453" s="2">
+      <c r="F453" s="1">
         <v>46230</v>
       </c>
       <c r="G453" t="s">
@@ -21720,7 +21694,7 @@
         <v>1353</v>
       </c>
       <c r="I453">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q453" t="b">
         <v>1</v>
@@ -21742,7 +21716,7 @@
       <c r="E454" t="s">
         <v>1261</v>
       </c>
-      <c r="F454" s="2">
+      <c r="F454" s="1">
         <v>46230</v>
       </c>
       <c r="G454" t="s">
@@ -21752,7 +21726,7 @@
         <v>1353</v>
       </c>
       <c r="I454">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q454" t="b">
         <v>1</v>
@@ -21774,7 +21748,7 @@
       <c r="E455" t="s">
         <v>1262</v>
       </c>
-      <c r="F455" s="2">
+      <c r="F455" s="1">
         <v>46230</v>
       </c>
       <c r="G455" t="s">
@@ -21784,7 +21758,7 @@
         <v>1353</v>
       </c>
       <c r="I455">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q455" t="b">
         <v>1</v>
@@ -21806,7 +21780,7 @@
       <c r="E456" t="s">
         <v>1263</v>
       </c>
-      <c r="F456" s="2">
+      <c r="F456" s="1">
         <v>46230</v>
       </c>
       <c r="G456" t="s">
@@ -21816,7 +21790,7 @@
         <v>1353</v>
       </c>
       <c r="I456">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q456" t="b">
         <v>1</v>
@@ -21838,7 +21812,7 @@
       <c r="E457" t="s">
         <v>1264</v>
       </c>
-      <c r="F457" s="2">
+      <c r="F457" s="1">
         <v>46230</v>
       </c>
       <c r="G457" t="s">
@@ -21848,7 +21822,7 @@
         <v>1353</v>
       </c>
       <c r="I457">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q457" t="b">
         <v>1</v>
@@ -21870,7 +21844,7 @@
       <c r="E458" t="s">
         <v>1202</v>
       </c>
-      <c r="F458" s="2">
+      <c r="F458" s="1">
         <v>46231</v>
       </c>
       <c r="G458" t="s">
@@ -21880,7 +21854,7 @@
         <v>1353</v>
       </c>
       <c r="I458">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q458" t="b">
         <v>1</v>
@@ -21902,7 +21876,7 @@
       <c r="E459" t="s">
         <v>1265</v>
       </c>
-      <c r="F459" s="2">
+      <c r="F459" s="1">
         <v>46233</v>
       </c>
       <c r="G459" t="s">
@@ -21912,7 +21886,7 @@
         <v>1353</v>
       </c>
       <c r="I459">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q459" t="b">
         <v>1</v>
@@ -21934,7 +21908,7 @@
       <c r="E460" t="s">
         <v>1266</v>
       </c>
-      <c r="F460" s="2">
+      <c r="F460" s="1">
         <v>46233</v>
       </c>
       <c r="G460" t="s">
@@ -21944,7 +21918,7 @@
         <v>1353</v>
       </c>
       <c r="I460">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q460" t="b">
         <v>1</v>
@@ -21966,7 +21940,7 @@
       <c r="E461" t="s">
         <v>1267</v>
       </c>
-      <c r="F461" s="2">
+      <c r="F461" s="1">
         <v>46233</v>
       </c>
       <c r="G461" t="s">
@@ -21976,7 +21950,7 @@
         <v>1353</v>
       </c>
       <c r="I461">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q461" t="b">
         <v>1</v>
@@ -21998,7 +21972,7 @@
       <c r="E462" t="s">
         <v>1268</v>
       </c>
-      <c r="F462" s="2">
+      <c r="F462" s="1">
         <v>46233</v>
       </c>
       <c r="G462" t="s">
@@ -22008,7 +21982,7 @@
         <v>1353</v>
       </c>
       <c r="I462">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q462" t="b">
         <v>1</v>
@@ -22030,7 +22004,7 @@
       <c r="E463" t="s">
         <v>1269</v>
       </c>
-      <c r="F463" s="2">
+      <c r="F463" s="1">
         <v>46234</v>
       </c>
       <c r="G463" t="s">
@@ -22040,7 +22014,7 @@
         <v>1353</v>
       </c>
       <c r="I463">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q463" t="b">
         <v>1</v>
@@ -22062,7 +22036,7 @@
       <c r="E464" t="s">
         <v>1270</v>
       </c>
-      <c r="F464" s="2">
+      <c r="F464" s="1">
         <v>46230</v>
       </c>
       <c r="G464" t="s">
@@ -22072,7 +22046,7 @@
         <v>1353</v>
       </c>
       <c r="I464">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q464" t="b">
         <v>1</v>
@@ -22094,7 +22068,7 @@
       <c r="E465" t="s">
         <v>1271</v>
       </c>
-      <c r="F465" s="2">
+      <c r="F465" s="1">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
@@ -22104,7 +22078,7 @@
         <v>1353</v>
       </c>
       <c r="I465">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q465" t="b">
         <v>1</v>
@@ -22126,7 +22100,7 @@
       <c r="E466" t="s">
         <v>1272</v>
       </c>
-      <c r="F466" s="2">
+      <c r="F466" s="1">
         <v>46230</v>
       </c>
       <c r="G466" t="s">
@@ -22136,7 +22110,7 @@
         <v>1353</v>
       </c>
       <c r="I466">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q466" t="b">
         <v>1</v>
@@ -22158,7 +22132,7 @@
       <c r="E467" t="s">
         <v>1273</v>
       </c>
-      <c r="F467" s="2">
+      <c r="F467" s="1">
         <v>46230</v>
       </c>
       <c r="G467" t="s">
@@ -22168,7 +22142,7 @@
         <v>1353</v>
       </c>
       <c r="I467">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q467" t="b">
         <v>1</v>
@@ -22190,7 +22164,7 @@
       <c r="E468" t="s">
         <v>1274</v>
       </c>
-      <c r="F468" s="2">
+      <c r="F468" s="1">
         <v>46230</v>
       </c>
       <c r="G468" t="s">
@@ -22200,7 +22174,7 @@
         <v>1353</v>
       </c>
       <c r="I468">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q468" t="b">
         <v>1</v>
@@ -22222,7 +22196,7 @@
       <c r="E469" t="s">
         <v>1275</v>
       </c>
-      <c r="F469" s="2">
+      <c r="F469" s="1">
         <v>46230</v>
       </c>
       <c r="G469" t="s">
@@ -22232,7 +22206,7 @@
         <v>1353</v>
       </c>
       <c r="I469">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q469" t="b">
         <v>1</v>
@@ -22254,7 +22228,7 @@
       <c r="E470" t="s">
         <v>1276</v>
       </c>
-      <c r="F470" s="2">
+      <c r="F470" s="1">
         <v>46230</v>
       </c>
       <c r="G470" t="s">
@@ -22283,7 +22257,7 @@
       <c r="E471" t="s">
         <v>1277</v>
       </c>
-      <c r="F471" s="2">
+      <c r="F471" s="1">
         <v>46230</v>
       </c>
       <c r="G471" t="s">
@@ -22293,7 +22267,7 @@
         <v>1353</v>
       </c>
       <c r="I471">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q471" t="b">
         <v>1</v>
@@ -22315,7 +22289,7 @@
       <c r="E472" t="s">
         <v>1278</v>
       </c>
-      <c r="F472" s="2">
+      <c r="F472" s="1">
         <v>46230</v>
       </c>
       <c r="G472" t="s">
@@ -22325,7 +22299,7 @@
         <v>1353</v>
       </c>
       <c r="I472">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q472" t="b">
         <v>1</v>
@@ -22347,7 +22321,7 @@
       <c r="E473" t="s">
         <v>1279</v>
       </c>
-      <c r="F473" s="2">
+      <c r="F473" s="1">
         <v>46230</v>
       </c>
       <c r="G473" t="s">
@@ -22357,7 +22331,7 @@
         <v>1353</v>
       </c>
       <c r="I473">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q473" t="b">
         <v>1</v>
@@ -22379,7 +22353,7 @@
       <c r="E474" t="s">
         <v>1280</v>
       </c>
-      <c r="F474" s="2">
+      <c r="F474" s="1">
         <v>46231</v>
       </c>
       <c r="G474" t="s">
@@ -22389,7 +22363,7 @@
         <v>1353</v>
       </c>
       <c r="I474">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q474" t="b">
         <v>1</v>
@@ -22411,7 +22385,7 @@
       <c r="E475" t="s">
         <v>1281</v>
       </c>
-      <c r="F475" s="2">
+      <c r="F475" s="1">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
@@ -22421,7 +22395,7 @@
         <v>1353</v>
       </c>
       <c r="I475">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q475" t="b">
         <v>1</v>
@@ -22443,7 +22417,7 @@
       <c r="E476" t="s">
         <v>1282</v>
       </c>
-      <c r="F476" s="2">
+      <c r="F476" s="1">
         <v>46231</v>
       </c>
       <c r="G476" t="s">
@@ -22453,7 +22427,7 @@
         <v>1353</v>
       </c>
       <c r="I476">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q476" t="b">
         <v>1</v>
@@ -22475,7 +22449,7 @@
       <c r="E477" t="s">
         <v>1283</v>
       </c>
-      <c r="F477" s="2">
+      <c r="F477" s="1">
         <v>46231</v>
       </c>
       <c r="G477" t="s">
@@ -22485,7 +22459,7 @@
         <v>1353</v>
       </c>
       <c r="I477">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q477" t="b">
         <v>1</v>
@@ -22507,7 +22481,7 @@
       <c r="E478" t="s">
         <v>1284</v>
       </c>
-      <c r="F478" s="2">
+      <c r="F478" s="1">
         <v>46231</v>
       </c>
       <c r="G478" t="s">
@@ -22517,7 +22491,7 @@
         <v>1353</v>
       </c>
       <c r="I478">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q478" t="b">
         <v>1</v>
@@ -22539,7 +22513,7 @@
       <c r="E479" t="s">
         <v>1285</v>
       </c>
-      <c r="F479" s="2">
+      <c r="F479" s="1">
         <v>46231</v>
       </c>
       <c r="G479" t="s">
@@ -22549,7 +22523,7 @@
         <v>1353</v>
       </c>
       <c r="I479">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q479" t="b">
         <v>1</v>
@@ -22571,7 +22545,7 @@
       <c r="E480" t="s">
         <v>1286</v>
       </c>
-      <c r="F480" s="2">
+      <c r="F480" s="1">
         <v>46231</v>
       </c>
       <c r="G480" t="s">
@@ -22581,7 +22555,7 @@
         <v>1353</v>
       </c>
       <c r="I480">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q480" t="b">
         <v>1</v>
@@ -22603,7 +22577,7 @@
       <c r="E481" t="s">
         <v>1287</v>
       </c>
-      <c r="F481" s="2">
+      <c r="F481" s="1">
         <v>46231</v>
       </c>
       <c r="G481" t="s">
@@ -22613,7 +22587,7 @@
         <v>1353</v>
       </c>
       <c r="I481">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q481" t="b">
         <v>1</v>
@@ -22635,7 +22609,7 @@
       <c r="E482" t="s">
         <v>1288</v>
       </c>
-      <c r="F482" s="2">
+      <c r="F482" s="1">
         <v>46231</v>
       </c>
       <c r="G482" t="s">
@@ -22645,7 +22619,7 @@
         <v>1353</v>
       </c>
       <c r="I482">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q482" t="b">
         <v>1</v>
@@ -22667,7 +22641,7 @@
       <c r="E483" t="s">
         <v>1289</v>
       </c>
-      <c r="F483" s="2">
+      <c r="F483" s="1">
         <v>46231</v>
       </c>
       <c r="G483" t="s">
@@ -22677,7 +22651,7 @@
         <v>1353</v>
       </c>
       <c r="I483">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q483" t="b">
         <v>1</v>
@@ -22699,7 +22673,7 @@
       <c r="E484" t="s">
         <v>1290</v>
       </c>
-      <c r="F484" s="2">
+      <c r="F484" s="1">
         <v>46231</v>
       </c>
       <c r="G484" t="s">
@@ -22709,7 +22683,7 @@
         <v>1353</v>
       </c>
       <c r="I484">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q484" t="b">
         <v>1</v>
@@ -22731,7 +22705,7 @@
       <c r="E485" t="s">
         <v>1291</v>
       </c>
-      <c r="F485" s="2">
+      <c r="F485" s="1">
         <v>46231</v>
       </c>
       <c r="G485" t="s">
@@ -22741,7 +22715,7 @@
         <v>1353</v>
       </c>
       <c r="I485">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q485" t="b">
         <v>1</v>
@@ -22763,7 +22737,7 @@
       <c r="E486" t="s">
         <v>1292</v>
       </c>
-      <c r="F486" s="2">
+      <c r="F486" s="1">
         <v>46231</v>
       </c>
       <c r="G486" t="s">
@@ -22773,7 +22747,7 @@
         <v>1353</v>
       </c>
       <c r="I486">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q486" t="b">
         <v>1</v>
@@ -22795,7 +22769,7 @@
       <c r="E487" t="s">
         <v>1293</v>
       </c>
-      <c r="F487" s="2">
+      <c r="F487" s="1">
         <v>46231</v>
       </c>
       <c r="G487" t="s">
@@ -22805,7 +22779,7 @@
         <v>1353</v>
       </c>
       <c r="I487">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q487" t="b">
         <v>1</v>
@@ -22827,7 +22801,7 @@
       <c r="E488" t="s">
         <v>1294</v>
       </c>
-      <c r="F488" s="2">
+      <c r="F488" s="1">
         <v>46231</v>
       </c>
       <c r="G488" t="s">
@@ -22837,7 +22811,7 @@
         <v>1353</v>
       </c>
       <c r="I488">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q488" t="b">
         <v>1</v>
@@ -22859,7 +22833,7 @@
       <c r="E489" t="s">
         <v>1295</v>
       </c>
-      <c r="F489" s="2">
+      <c r="F489" s="1">
         <v>46231</v>
       </c>
       <c r="G489" t="s">
@@ -22869,7 +22843,7 @@
         <v>1353</v>
       </c>
       <c r="I489">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q489" t="b">
         <v>1</v>
@@ -22891,7 +22865,7 @@
       <c r="E490" t="s">
         <v>1296</v>
       </c>
-      <c r="F490" s="2">
+      <c r="F490" s="1">
         <v>46231</v>
       </c>
       <c r="G490" t="s">
@@ -22901,7 +22875,7 @@
         <v>1353</v>
       </c>
       <c r="I490">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q490" t="b">
         <v>1</v>
@@ -22923,7 +22897,7 @@
       <c r="E491" t="s">
         <v>1297</v>
       </c>
-      <c r="F491" s="2">
+      <c r="F491" s="1">
         <v>46231</v>
       </c>
       <c r="G491" t="s">
@@ -22933,7 +22907,7 @@
         <v>1353</v>
       </c>
       <c r="I491">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q491" t="b">
         <v>1</v>
@@ -22955,7 +22929,7 @@
       <c r="E492" t="s">
         <v>911</v>
       </c>
-      <c r="F492" s="2">
+      <c r="F492" s="1">
         <v>46231</v>
       </c>
       <c r="G492" t="s">
@@ -22965,7 +22939,7 @@
         <v>1355</v>
       </c>
       <c r="I492">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q492" t="b">
         <v>1</v>
@@ -22987,7 +22961,7 @@
       <c r="E493" t="s">
         <v>995</v>
       </c>
-      <c r="F493" s="2">
+      <c r="F493" s="1">
         <v>46231</v>
       </c>
       <c r="G493" t="s">
@@ -22997,7 +22971,7 @@
         <v>1355</v>
       </c>
       <c r="I493">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q493" t="b">
         <v>1</v>
@@ -23019,7 +22993,7 @@
       <c r="E494" t="s">
         <v>867</v>
       </c>
-      <c r="F494" s="2">
+      <c r="F494" s="1">
         <v>46231</v>
       </c>
       <c r="G494" t="s">
@@ -23029,7 +23003,7 @@
         <v>1355</v>
       </c>
       <c r="I494">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q494" t="b">
         <v>1</v>
@@ -23051,7 +23025,7 @@
       <c r="E495" t="s">
         <v>912</v>
       </c>
-      <c r="F495" s="2">
+      <c r="F495" s="1">
         <v>46231</v>
       </c>
       <c r="G495" t="s">
@@ -23061,7 +23035,7 @@
         <v>1355</v>
       </c>
       <c r="I495">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q495" t="b">
         <v>1</v>
@@ -23083,7 +23057,7 @@
       <c r="E496" t="s">
         <v>1048</v>
       </c>
-      <c r="F496" s="2">
+      <c r="F496" s="1">
         <v>46231</v>
       </c>
       <c r="G496" t="s">
@@ -23093,7 +23067,7 @@
         <v>1355</v>
       </c>
       <c r="I496">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q496" t="b">
         <v>1</v>
@@ -23115,7 +23089,7 @@
       <c r="E497" t="s">
         <v>1298</v>
       </c>
-      <c r="F497" s="2">
+      <c r="F497" s="1">
         <v>46231</v>
       </c>
       <c r="G497" t="s">
@@ -23125,7 +23099,7 @@
         <v>1353</v>
       </c>
       <c r="I497">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q497" t="b">
         <v>1</v>
@@ -23147,7 +23121,7 @@
       <c r="E498" t="s">
         <v>1299</v>
       </c>
-      <c r="F498" s="2">
+      <c r="F498" s="1">
         <v>46231</v>
       </c>
       <c r="G498" t="s">
@@ -23157,7 +23131,7 @@
         <v>1353</v>
       </c>
       <c r="I498">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q498" t="b">
         <v>1</v>
@@ -23179,7 +23153,7 @@
       <c r="E499" t="s">
         <v>1300</v>
       </c>
-      <c r="F499" s="2">
+      <c r="F499" s="1">
         <v>46231</v>
       </c>
       <c r="G499" t="s">
@@ -23189,7 +23163,7 @@
         <v>1355</v>
       </c>
       <c r="I499">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q499" t="b">
         <v>1</v>
@@ -23211,7 +23185,7 @@
       <c r="E500" t="s">
         <v>1301</v>
       </c>
-      <c r="F500" s="2">
+      <c r="F500" s="1">
         <v>46231</v>
       </c>
       <c r="G500" t="s">
@@ -23221,7 +23195,7 @@
         <v>1353</v>
       </c>
       <c r="I500">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q500" t="b">
         <v>1</v>
@@ -23243,7 +23217,7 @@
       <c r="E501" t="s">
         <v>1302</v>
       </c>
-      <c r="F501" s="2">
+      <c r="F501" s="1">
         <v>46231</v>
       </c>
       <c r="G501" t="s">
@@ -23253,7 +23227,7 @@
         <v>1353</v>
       </c>
       <c r="I501">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q501" t="b">
         <v>1</v>
@@ -23275,7 +23249,7 @@
       <c r="E502" t="s">
         <v>1303</v>
       </c>
-      <c r="F502" s="2">
+      <c r="F502" s="1">
         <v>46231</v>
       </c>
       <c r="G502" t="s">
@@ -23285,7 +23259,7 @@
         <v>1353</v>
       </c>
       <c r="I502">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q502" t="b">
         <v>1</v>
@@ -23307,7 +23281,7 @@
       <c r="E503" t="s">
         <v>1304</v>
       </c>
-      <c r="F503" s="2">
+      <c r="F503" s="1">
         <v>46231</v>
       </c>
       <c r="G503" t="s">
@@ -23317,7 +23291,7 @@
         <v>1353</v>
       </c>
       <c r="I503">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q503" t="b">
         <v>1</v>
@@ -23339,7 +23313,7 @@
       <c r="E504" t="s">
         <v>1305</v>
       </c>
-      <c r="F504" s="2">
+      <c r="F504" s="1">
         <v>46232</v>
       </c>
       <c r="G504" t="s">
@@ -23349,7 +23323,7 @@
         <v>1353</v>
       </c>
       <c r="I504">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q504" t="b">
         <v>1</v>
@@ -23371,7 +23345,7 @@
       <c r="E505" t="s">
         <v>1306</v>
       </c>
-      <c r="F505" s="2">
+      <c r="F505" s="1">
         <v>46232</v>
       </c>
       <c r="G505" t="s">
@@ -23381,7 +23355,7 @@
         <v>1353</v>
       </c>
       <c r="I505">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q505" t="b">
         <v>1</v>
@@ -23403,7 +23377,7 @@
       <c r="E506" t="s">
         <v>1307</v>
       </c>
-      <c r="F506" s="2">
+      <c r="F506" s="1">
         <v>46232</v>
       </c>
       <c r="G506" t="s">
@@ -23413,7 +23387,7 @@
         <v>1353</v>
       </c>
       <c r="I506">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q506" t="b">
         <v>1</v>
@@ -23435,7 +23409,7 @@
       <c r="E507" t="s">
         <v>1308</v>
       </c>
-      <c r="F507" s="2">
+      <c r="F507" s="1">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
@@ -23445,7 +23419,7 @@
         <v>1353</v>
       </c>
       <c r="I507">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q507" t="b">
         <v>1</v>
@@ -23467,7 +23441,7 @@
       <c r="E508" t="s">
         <v>1309</v>
       </c>
-      <c r="F508" s="2">
+      <c r="F508" s="1">
         <v>46237</v>
       </c>
       <c r="G508" t="s">
@@ -23496,7 +23470,7 @@
       <c r="E509" t="s">
         <v>1310</v>
       </c>
-      <c r="F509" s="2">
+      <c r="F509" s="1">
         <v>46237</v>
       </c>
       <c r="G509" t="s">
@@ -23506,7 +23480,7 @@
         <v>1353</v>
       </c>
       <c r="I509">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q509" t="b">
         <v>1</v>
@@ -23528,7 +23502,7 @@
       <c r="E510" t="s">
         <v>1311</v>
       </c>
-      <c r="F510" s="2">
+      <c r="F510" s="1">
         <v>46237</v>
       </c>
       <c r="G510" t="s">
@@ -23538,7 +23512,7 @@
         <v>1353</v>
       </c>
       <c r="I510">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q510" t="b">
         <v>1</v>
@@ -23560,7 +23534,7 @@
       <c r="E511" t="s">
         <v>1312</v>
       </c>
-      <c r="F511" s="2">
+      <c r="F511" s="1">
         <v>46240</v>
       </c>
       <c r="G511" t="s">
@@ -23570,7 +23544,7 @@
         <v>1353</v>
       </c>
       <c r="I511">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q511" t="b">
         <v>1</v>
@@ -23592,7 +23566,7 @@
       <c r="E512" t="s">
         <v>1313</v>
       </c>
-      <c r="F512" s="2">
+      <c r="F512" s="1">
         <v>46240</v>
       </c>
       <c r="G512" t="s">
@@ -23602,7 +23576,7 @@
         <v>1353</v>
       </c>
       <c r="I512">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q512" t="b">
         <v>1</v>
@@ -23624,7 +23598,7 @@
       <c r="E513" t="s">
         <v>1314</v>
       </c>
-      <c r="F513" s="2">
+      <c r="F513" s="1">
         <v>46244</v>
       </c>
       <c r="G513" t="s">
@@ -23634,7 +23608,7 @@
         <v>1353</v>
       </c>
       <c r="I513">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q513" t="b">
         <v>1</v>
@@ -23656,7 +23630,7 @@
       <c r="E514" t="s">
         <v>1315</v>
       </c>
-      <c r="F514" s="2">
+      <c r="F514" s="1">
         <v>46244</v>
       </c>
       <c r="G514" t="s">
@@ -23666,7 +23640,7 @@
         <v>1353</v>
       </c>
       <c r="I514">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q514" t="b">
         <v>1</v>
@@ -23688,7 +23662,7 @@
       <c r="E515" t="s">
         <v>1043</v>
       </c>
-      <c r="F515" s="2">
+      <c r="F515" s="1">
         <v>46244</v>
       </c>
       <c r="G515" t="s">
@@ -23698,7 +23672,7 @@
         <v>1353</v>
       </c>
       <c r="I515">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q515" t="b">
         <v>1</v>
@@ -23720,7 +23694,7 @@
       <c r="E516" t="s">
         <v>1316</v>
       </c>
-      <c r="F516" s="2">
+      <c r="F516" s="1">
         <v>46252</v>
       </c>
       <c r="G516" t="s">
@@ -23730,7 +23704,7 @@
         <v>1353</v>
       </c>
       <c r="I516">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q516" t="b">
         <v>1</v>
@@ -23752,7 +23726,7 @@
       <c r="E517" t="s">
         <v>1317</v>
       </c>
-      <c r="F517" s="2">
+      <c r="F517" s="1">
         <v>46252</v>
       </c>
       <c r="G517" t="s">
@@ -23762,7 +23736,7 @@
         <v>1353</v>
       </c>
       <c r="I517">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q517" t="b">
         <v>1</v>
@@ -23784,7 +23758,7 @@
       <c r="E518" t="s">
         <v>1318</v>
       </c>
-      <c r="F518" s="2">
+      <c r="F518" s="1">
         <v>46252</v>
       </c>
       <c r="G518" t="s">
@@ -23794,7 +23768,7 @@
         <v>1353</v>
       </c>
       <c r="I518">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q518" t="b">
         <v>1</v>
@@ -23816,7 +23790,7 @@
       <c r="E519" t="s">
         <v>1253</v>
       </c>
-      <c r="F519" s="2">
+      <c r="F519" s="1">
         <v>46254</v>
       </c>
       <c r="G519" t="s">
@@ -23826,7 +23800,7 @@
         <v>1353</v>
       </c>
       <c r="I519">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q519" t="b">
         <v>1</v>
@@ -23848,7 +23822,7 @@
       <c r="E520" t="s">
         <v>1319</v>
       </c>
-      <c r="F520" s="2">
+      <c r="F520" s="1">
         <v>46254</v>
       </c>
       <c r="G520" t="s">
@@ -23858,7 +23832,7 @@
         <v>1353</v>
       </c>
       <c r="I520">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q520" t="b">
         <v>1</v>
@@ -23880,7 +23854,7 @@
       <c r="E521" t="s">
         <v>1320</v>
       </c>
-      <c r="F521" s="2">
+      <c r="F521" s="1">
         <v>46254</v>
       </c>
       <c r="G521" t="s">
@@ -23890,7 +23864,7 @@
         <v>1353</v>
       </c>
       <c r="I521">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q521" t="b">
         <v>1</v>
@@ -23912,7 +23886,7 @@
       <c r="E522" t="s">
         <v>1253</v>
       </c>
-      <c r="F522" s="2">
+      <c r="F522" s="1">
         <v>46254</v>
       </c>
       <c r="G522" t="s">
@@ -23922,7 +23896,7 @@
         <v>1353</v>
       </c>
       <c r="I522">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q522" t="b">
         <v>1</v>
@@ -23944,7 +23918,7 @@
       <c r="E523" t="s">
         <v>1319</v>
       </c>
-      <c r="F523" s="2">
+      <c r="F523" s="1">
         <v>46254</v>
       </c>
       <c r="G523" t="s">
@@ -23954,7 +23928,7 @@
         <v>1353</v>
       </c>
       <c r="I523">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q523" t="b">
         <v>1</v>
@@ -23976,7 +23950,7 @@
       <c r="E524" t="s">
         <v>1321</v>
       </c>
-      <c r="F524" s="2">
+      <c r="F524" s="1">
         <v>46265</v>
       </c>
       <c r="G524" t="s">
@@ -23986,7 +23960,7 @@
         <v>1353</v>
       </c>
       <c r="I524">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q524" t="b">
         <v>1</v>
@@ -24008,7 +23982,7 @@
       <c r="E525" t="s">
         <v>1322</v>
       </c>
-      <c r="F525" s="2">
+      <c r="F525" s="1">
         <v>46265</v>
       </c>
       <c r="G525" t="s">
@@ -24018,7 +23992,7 @@
         <v>1353</v>
       </c>
       <c r="I525">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q525" t="b">
         <v>1</v>
@@ -24040,7 +24014,7 @@
       <c r="E526" t="s">
         <v>1323</v>
       </c>
-      <c r="F526" s="2">
+      <c r="F526" s="1">
         <v>46265</v>
       </c>
       <c r="G526" t="s">
@@ -24050,7 +24024,7 @@
         <v>1353</v>
       </c>
       <c r="I526">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q526" t="b">
         <v>1</v>
@@ -24072,7 +24046,7 @@
       <c r="E527" t="s">
         <v>1324</v>
       </c>
-      <c r="F527" s="2">
+      <c r="F527" s="1">
         <v>46265</v>
       </c>
       <c r="G527" t="s">
@@ -24082,7 +24056,7 @@
         <v>1353</v>
       </c>
       <c r="I527">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q527" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
@@ -4520,16 +4520,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -4545,7 +4537,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -4553,30 +4545,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4876,55 +4850,55 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4944,7 +4918,7 @@
       <c r="E2" t="s">
         <v>829</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>45698</v>
       </c>
       <c r="G2" t="s">
@@ -4954,7 +4928,7 @@
         <v>1353</v>
       </c>
       <c r="I2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="K2" t="s">
         <v>1356</v>
@@ -4982,7 +4956,7 @@
       <c r="E3" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>45714</v>
       </c>
       <c r="G3" t="s">
@@ -4992,7 +4966,7 @@
         <v>1353</v>
       </c>
       <c r="I3">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="K3" t="s">
         <v>1357</v>
@@ -5020,7 +4994,7 @@
       <c r="E4" t="s">
         <v>831</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>45714</v>
       </c>
       <c r="G4" t="s">
@@ -5030,7 +5004,7 @@
         <v>1353</v>
       </c>
       <c r="I4">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="K4" t="s">
         <v>1357</v>
@@ -5058,7 +5032,7 @@
       <c r="E5" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>45714</v>
       </c>
       <c r="G5" t="s">
@@ -5068,7 +5042,7 @@
         <v>1353</v>
       </c>
       <c r="I5">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J5">
         <v>279</v>
@@ -5079,7 +5053,7 @@
       <c r="L5" t="s">
         <v>1367</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="1">
         <v>45993</v>
       </c>
       <c r="Q5" t="b">
@@ -5102,7 +5076,7 @@
       <c r="E6" t="s">
         <v>833</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>45736</v>
       </c>
       <c r="G6" t="s">
@@ -5112,7 +5086,7 @@
         <v>1353</v>
       </c>
       <c r="I6">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J6">
         <v>153</v>
@@ -5123,7 +5097,7 @@
       <c r="L6" t="s">
         <v>1368</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="1">
         <v>45889</v>
       </c>
       <c r="Q6" t="b">
@@ -5146,7 +5120,7 @@
       <c r="E7" t="s">
         <v>834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>45736</v>
       </c>
       <c r="G7" t="s">
@@ -5156,7 +5130,7 @@
         <v>1353</v>
       </c>
       <c r="I7">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J7">
         <v>112</v>
@@ -5167,7 +5141,7 @@
       <c r="L7" t="s">
         <v>1369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="1">
         <v>45848</v>
       </c>
       <c r="O7" t="s">
@@ -5193,7 +5167,7 @@
       <c r="E8" t="s">
         <v>835</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>45736</v>
       </c>
       <c r="G8" t="s">
@@ -5222,7 +5196,7 @@
       <c r="E9" t="s">
         <v>836</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>45736</v>
       </c>
       <c r="G9" t="s">
@@ -5232,7 +5206,7 @@
         <v>1353</v>
       </c>
       <c r="I9">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J9">
         <v>362</v>
@@ -5243,7 +5217,7 @@
       <c r="L9" t="s">
         <v>1370</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="1">
         <v>46098</v>
       </c>
       <c r="O9">
@@ -5269,7 +5243,7 @@
       <c r="E10" t="s">
         <v>837</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>45736</v>
       </c>
       <c r="G10" t="s">
@@ -5279,7 +5253,7 @@
         <v>1353</v>
       </c>
       <c r="I10">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J10">
         <v>378</v>
@@ -5290,7 +5264,7 @@
       <c r="L10" t="s">
         <v>1371</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="1">
         <v>46114</v>
       </c>
       <c r="O10" t="s">
@@ -5316,7 +5290,7 @@
       <c r="E11" t="s">
         <v>838</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>45736</v>
       </c>
       <c r="G11" t="s">
@@ -5326,7 +5300,7 @@
         <v>1353</v>
       </c>
       <c r="I11">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J11">
         <v>112</v>
@@ -5337,7 +5311,7 @@
       <c r="L11" t="s">
         <v>1369</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="1">
         <v>45848</v>
       </c>
       <c r="O11" t="s">
@@ -5363,7 +5337,7 @@
       <c r="E12" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>45736</v>
       </c>
       <c r="G12" t="s">
@@ -5373,7 +5347,7 @@
         <v>1353</v>
       </c>
       <c r="I12">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J12">
         <v>124</v>
@@ -5384,7 +5358,7 @@
       <c r="L12" t="s">
         <v>1372</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="1">
         <v>45860</v>
       </c>
       <c r="Q12" t="b">
@@ -5407,7 +5381,7 @@
       <c r="E13" t="s">
         <v>840</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>45736</v>
       </c>
       <c r="G13" t="s">
@@ -5436,7 +5410,7 @@
       <c r="E14" t="s">
         <v>841</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>45736</v>
       </c>
       <c r="G14" t="s">
@@ -5446,7 +5420,7 @@
         <v>1353</v>
       </c>
       <c r="I14">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J14">
         <v>64</v>
@@ -5457,7 +5431,7 @@
       <c r="L14" t="s">
         <v>1373</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="1">
         <v>45800</v>
       </c>
       <c r="Q14" t="b">
@@ -5480,7 +5454,7 @@
       <c r="E15" t="s">
         <v>842</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>45736</v>
       </c>
       <c r="G15" t="s">
@@ -5490,7 +5464,7 @@
         <v>1353</v>
       </c>
       <c r="I15">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K15" t="s">
         <v>1359</v>
@@ -5518,7 +5492,7 @@
       <c r="E16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>45736</v>
       </c>
       <c r="G16" t="s">
@@ -5528,7 +5502,7 @@
         <v>1353</v>
       </c>
       <c r="I16">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K16" t="s">
         <v>1356</v>
@@ -5556,7 +5530,7 @@
       <c r="E17" t="s">
         <v>844</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>45736</v>
       </c>
       <c r="G17" t="s">
@@ -5566,7 +5540,7 @@
         <v>1353</v>
       </c>
       <c r="I17">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J17">
         <v>161</v>
@@ -5577,7 +5551,7 @@
       <c r="L17" t="s">
         <v>1368</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="1">
         <v>45897</v>
       </c>
       <c r="Q17" t="b">
@@ -5600,7 +5574,7 @@
       <c r="E18" t="s">
         <v>845</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="1">
         <v>45736</v>
       </c>
       <c r="G18" t="s">
@@ -5610,7 +5584,7 @@
         <v>1353</v>
       </c>
       <c r="I18">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J18">
         <v>66</v>
@@ -5621,7 +5595,7 @@
       <c r="L18" t="s">
         <v>1373</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" s="1">
         <v>45802</v>
       </c>
       <c r="Q18" t="b">
@@ -5644,7 +5618,7 @@
       <c r="E19" t="s">
         <v>846</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="1">
         <v>45736</v>
       </c>
       <c r="G19" t="s">
@@ -5673,7 +5647,7 @@
       <c r="E20" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="1">
         <v>45736</v>
       </c>
       <c r="G20" t="s">
@@ -5683,7 +5657,7 @@
         <v>1353</v>
       </c>
       <c r="I20">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J20">
         <v>399</v>
@@ -5694,7 +5668,7 @@
       <c r="L20" t="s">
         <v>1374</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20" s="1">
         <v>46135</v>
       </c>
       <c r="Q20" t="b">
@@ -5717,7 +5691,7 @@
       <c r="E21" t="s">
         <v>848</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="1">
         <v>45736</v>
       </c>
       <c r="G21" t="s">
@@ -5746,7 +5720,7 @@
       <c r="E22" t="s">
         <v>849</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="1">
         <v>45736</v>
       </c>
       <c r="G22" t="s">
@@ -5756,7 +5730,7 @@
         <v>1353</v>
       </c>
       <c r="I22">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K22" t="s">
         <v>1360</v>
@@ -5784,7 +5758,7 @@
       <c r="E23" t="s">
         <v>850</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="1">
         <v>45736</v>
       </c>
       <c r="G23" t="s">
@@ -5794,7 +5768,7 @@
         <v>1353</v>
       </c>
       <c r="I23">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J23">
         <v>229</v>
@@ -5805,7 +5779,7 @@
       <c r="L23" t="s">
         <v>1375</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="1">
         <v>45965</v>
       </c>
       <c r="P23" t="s">
@@ -5831,7 +5805,7 @@
       <c r="E24" t="s">
         <v>851</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="1">
         <v>45736</v>
       </c>
       <c r="G24" t="s">
@@ -5860,7 +5834,7 @@
       <c r="E25" t="s">
         <v>852</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="1">
         <v>45736</v>
       </c>
       <c r="G25" t="s">
@@ -5889,7 +5863,7 @@
       <c r="E26" t="s">
         <v>853</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="1">
         <v>45736</v>
       </c>
       <c r="G26" t="s">
@@ -5899,7 +5873,7 @@
         <v>1353</v>
       </c>
       <c r="I26">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J26">
         <v>155</v>
@@ -5910,7 +5884,7 @@
       <c r="L26" t="s">
         <v>1376</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" s="1">
         <v>45891</v>
       </c>
       <c r="P26" t="s">
@@ -5936,7 +5910,7 @@
       <c r="E27" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="1">
         <v>45736</v>
       </c>
       <c r="G27" t="s">
@@ -5946,7 +5920,7 @@
         <v>1353</v>
       </c>
       <c r="I27">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K27" t="s">
         <v>1360</v>
@@ -5974,7 +5948,7 @@
       <c r="E28" t="s">
         <v>855</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="1">
         <v>45736</v>
       </c>
       <c r="G28" t="s">
@@ -6003,7 +5977,7 @@
       <c r="E29" t="s">
         <v>856</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="1">
         <v>45736</v>
       </c>
       <c r="G29" t="s">
@@ -6032,7 +6006,7 @@
       <c r="E30" t="s">
         <v>857</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="1">
         <v>45736</v>
       </c>
       <c r="G30" t="s">
@@ -6042,7 +6016,7 @@
         <v>1353</v>
       </c>
       <c r="I30">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J30">
         <v>209</v>
@@ -6053,7 +6027,7 @@
       <c r="L30" t="s">
         <v>1377</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" s="1">
         <v>45945</v>
       </c>
       <c r="Q30" t="b">
@@ -6076,7 +6050,7 @@
       <c r="E31" t="s">
         <v>858</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="1">
         <v>45736</v>
       </c>
       <c r="G31" t="s">
@@ -6105,7 +6079,7 @@
       <c r="E32" t="s">
         <v>859</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="1">
         <v>45736</v>
       </c>
       <c r="G32" t="s">
@@ -6115,7 +6089,7 @@
         <v>1353</v>
       </c>
       <c r="I32">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K32" t="s">
         <v>1356</v>
@@ -6143,7 +6117,7 @@
       <c r="E33" t="s">
         <v>860</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>45736</v>
       </c>
       <c r="G33" t="s">
@@ -6172,7 +6146,7 @@
       <c r="E34" t="s">
         <v>861</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="1">
         <v>45736</v>
       </c>
       <c r="G34" t="s">
@@ -6201,7 +6175,7 @@
       <c r="E35" t="s">
         <v>862</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="1">
         <v>45736</v>
       </c>
       <c r="G35" t="s">
@@ -6230,7 +6204,7 @@
       <c r="E36" t="s">
         <v>863</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="1">
         <v>45736</v>
       </c>
       <c r="G36" t="s">
@@ -6259,7 +6233,7 @@
       <c r="E37" t="s">
         <v>864</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>45736</v>
       </c>
       <c r="G37" t="s">
@@ -6288,7 +6262,7 @@
       <c r="E38" t="s">
         <v>844</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="1">
         <v>45736</v>
       </c>
       <c r="G38" t="s">
@@ -6314,7 +6288,7 @@
       <c r="D39" t="s">
         <v>731</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="1">
         <v>45736</v>
       </c>
       <c r="G39" t="s">
@@ -6324,7 +6298,7 @@
         <v>1353</v>
       </c>
       <c r="I39">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K39" t="s">
         <v>1361</v>
@@ -6349,7 +6323,7 @@
       <c r="D40" t="s">
         <v>731</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="1">
         <v>45736</v>
       </c>
       <c r="G40" t="s">
@@ -6359,7 +6333,7 @@
         <v>1353</v>
       </c>
       <c r="I40">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K40" t="s">
         <v>1359</v>
@@ -6387,7 +6361,7 @@
       <c r="E41" t="s">
         <v>865</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="1">
         <v>45736</v>
       </c>
       <c r="G41" t="s">
@@ -6416,7 +6390,7 @@
       <c r="E42" t="s">
         <v>866</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="1">
         <v>45736</v>
       </c>
       <c r="G42" t="s">
@@ -6445,7 +6419,7 @@
       <c r="E43" t="s">
         <v>867</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="1">
         <v>45736</v>
       </c>
       <c r="G43" t="s">
@@ -6480,7 +6454,7 @@
       <c r="E44" t="s">
         <v>868</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="1">
         <v>45769</v>
       </c>
       <c r="G44" t="s">
@@ -6490,7 +6464,7 @@
         <v>1353</v>
       </c>
       <c r="I44">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J44">
         <v>87</v>
@@ -6501,7 +6475,7 @@
       <c r="L44" t="s">
         <v>1378</v>
       </c>
-      <c r="N44" s="2">
+      <c r="N44" s="1">
         <v>45856</v>
       </c>
       <c r="P44" t="s">
@@ -6527,7 +6501,7 @@
       <c r="E45" t="s">
         <v>869</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="1">
         <v>45769</v>
       </c>
       <c r="G45" t="s">
@@ -6537,7 +6511,7 @@
         <v>1353</v>
       </c>
       <c r="I45">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J45">
         <v>331</v>
@@ -6548,7 +6522,7 @@
       <c r="L45" t="s">
         <v>1379</v>
       </c>
-      <c r="N45" s="2">
+      <c r="N45" s="1">
         <v>46100</v>
       </c>
       <c r="O45">
@@ -6574,7 +6548,7 @@
       <c r="E46" t="s">
         <v>870</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="1">
         <v>45769</v>
       </c>
       <c r="G46" t="s">
@@ -6584,7 +6558,7 @@
         <v>1353</v>
       </c>
       <c r="I46">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K46" t="s">
         <v>1360</v>
@@ -6612,7 +6586,7 @@
       <c r="E47" t="s">
         <v>871</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="1">
         <v>45769</v>
       </c>
       <c r="G47" t="s">
@@ -6622,7 +6596,7 @@
         <v>1353</v>
       </c>
       <c r="I47">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J47">
         <v>344</v>
@@ -6633,7 +6607,7 @@
       <c r="L47" t="s">
         <v>1380</v>
       </c>
-      <c r="N47" s="2">
+      <c r="N47" s="1">
         <v>46113</v>
       </c>
       <c r="P47" t="s">
@@ -6659,7 +6633,7 @@
       <c r="E48" t="s">
         <v>872</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="1">
         <v>45769</v>
       </c>
       <c r="G48" t="s">
@@ -6669,7 +6643,7 @@
         <v>1353</v>
       </c>
       <c r="I48">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K48" t="s">
         <v>1360</v>
@@ -6697,7 +6671,7 @@
       <c r="E49" t="s">
         <v>873</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="1">
         <v>45769</v>
       </c>
       <c r="G49" t="s">
@@ -6726,7 +6700,7 @@
       <c r="E50" t="s">
         <v>874</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="1">
         <v>45769</v>
       </c>
       <c r="G50" t="s">
@@ -6736,7 +6710,7 @@
         <v>1353</v>
       </c>
       <c r="I50">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K50" t="s">
         <v>1360</v>
@@ -6764,7 +6738,7 @@
       <c r="E51" t="s">
         <v>875</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="1">
         <v>45769</v>
       </c>
       <c r="G51" t="s">
@@ -6793,7 +6767,7 @@
       <c r="E52" t="s">
         <v>876</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="1">
         <v>45769</v>
       </c>
       <c r="G52" t="s">
@@ -6803,7 +6777,7 @@
         <v>1353</v>
       </c>
       <c r="I52">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K52" t="s">
         <v>1356</v>
@@ -6831,7 +6805,7 @@
       <c r="E53" t="s">
         <v>877</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="1">
         <v>45769</v>
       </c>
       <c r="G53" t="s">
@@ -6841,7 +6815,7 @@
         <v>1353</v>
       </c>
       <c r="I53">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K53" t="s">
         <v>1357</v>
@@ -6869,7 +6843,7 @@
       <c r="E54" t="s">
         <v>878</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="1">
         <v>45769</v>
       </c>
       <c r="G54" t="s">
@@ -6879,7 +6853,7 @@
         <v>1353</v>
       </c>
       <c r="I54">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K54" t="s">
         <v>1357</v>
@@ -6907,7 +6881,7 @@
       <c r="E55" t="s">
         <v>879</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="1">
         <v>45769</v>
       </c>
       <c r="G55" t="s">
@@ -6936,7 +6910,7 @@
       <c r="E56" t="s">
         <v>880</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="1">
         <v>45769</v>
       </c>
       <c r="G56" t="s">
@@ -6965,7 +6939,7 @@
       <c r="E57" t="s">
         <v>881</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="1">
         <v>45769</v>
       </c>
       <c r="G57" t="s">
@@ -6975,7 +6949,7 @@
         <v>1353</v>
       </c>
       <c r="I57">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K57" t="s">
         <v>1360</v>
@@ -7003,7 +6977,7 @@
       <c r="E58" t="s">
         <v>882</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="1">
         <v>45769</v>
       </c>
       <c r="G58" t="s">
@@ -7032,7 +7006,7 @@
       <c r="E59" t="s">
         <v>883</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="1">
         <v>45769</v>
       </c>
       <c r="G59" t="s">
@@ -7061,7 +7035,7 @@
       <c r="E60" t="s">
         <v>884</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="1">
         <v>45769</v>
       </c>
       <c r="G60" t="s">
@@ -7090,7 +7064,7 @@
       <c r="E61" t="s">
         <v>885</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="1">
         <v>45769</v>
       </c>
       <c r="G61" t="s">
@@ -7119,7 +7093,7 @@
       <c r="E62" t="s">
         <v>886</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="1">
         <v>45770</v>
       </c>
       <c r="G62" t="s">
@@ -7148,7 +7122,7 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="1">
         <v>45799</v>
       </c>
       <c r="G63" t="s">
@@ -7158,7 +7132,7 @@
         <v>1353</v>
       </c>
       <c r="I63">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J63">
         <v>293</v>
@@ -7169,7 +7143,7 @@
       <c r="L63" t="s">
         <v>1381</v>
       </c>
-      <c r="N63" s="2">
+      <c r="N63" s="1">
         <v>46092</v>
       </c>
       <c r="P63" t="s">
@@ -7195,7 +7169,7 @@
       <c r="E64" t="s">
         <v>888</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="1">
         <v>45799</v>
       </c>
       <c r="G64" t="s">
@@ -7205,7 +7179,7 @@
         <v>1353</v>
       </c>
       <c r="I64">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J64">
         <v>320</v>
@@ -7216,7 +7190,7 @@
       <c r="L64" t="s">
         <v>1382</v>
       </c>
-      <c r="N64" s="2">
+      <c r="N64" s="1">
         <v>46119</v>
       </c>
       <c r="Q64" t="b">
@@ -7239,7 +7213,7 @@
       <c r="E65" t="s">
         <v>889</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="1">
         <v>45799</v>
       </c>
       <c r="G65" t="s">
@@ -7268,7 +7242,7 @@
       <c r="E66" t="s">
         <v>890</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="1">
         <v>45799</v>
       </c>
       <c r="G66" t="s">
@@ -7297,7 +7271,7 @@
       <c r="E67" t="s">
         <v>891</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="1">
         <v>45799</v>
       </c>
       <c r="G67" t="s">
@@ -7326,7 +7300,7 @@
       <c r="E68" t="s">
         <v>892</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="1">
         <v>45799</v>
       </c>
       <c r="G68" t="s">
@@ -7355,7 +7329,7 @@
       <c r="E69" t="s">
         <v>893</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="1">
         <v>45803</v>
       </c>
       <c r="G69" t="s">
@@ -7384,7 +7358,7 @@
       <c r="E70" t="s">
         <v>894</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="1">
         <v>45803</v>
       </c>
       <c r="G70" t="s">
@@ -7394,7 +7368,7 @@
         <v>1353</v>
       </c>
       <c r="I70">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J70">
         <v>429</v>
@@ -7405,7 +7379,7 @@
       <c r="L70" t="s">
         <v>1383</v>
       </c>
-      <c r="N70" s="2">
+      <c r="N70" s="1">
         <v>46232</v>
       </c>
       <c r="Q70" t="b">
@@ -7428,7 +7402,7 @@
       <c r="E71" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="1">
         <v>45803</v>
       </c>
       <c r="G71" t="s">
@@ -7438,7 +7412,7 @@
         <v>1353</v>
       </c>
       <c r="I71">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J71">
         <v>429</v>
@@ -7449,7 +7423,7 @@
       <c r="L71" t="s">
         <v>1383</v>
       </c>
-      <c r="N71" s="2">
+      <c r="N71" s="1">
         <v>46232</v>
       </c>
       <c r="Q71" t="b">
@@ -7472,7 +7446,7 @@
       <c r="E72" t="s">
         <v>896</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="1">
         <v>45803</v>
       </c>
       <c r="G72" t="s">
@@ -7501,7 +7475,7 @@
       <c r="E73" t="s">
         <v>897</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="1">
         <v>45803</v>
       </c>
       <c r="G73" t="s">
@@ -7511,7 +7485,7 @@
         <v>1353</v>
       </c>
       <c r="I73">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K73" t="s">
         <v>1356</v>
@@ -7539,7 +7513,7 @@
       <c r="E74" t="s">
         <v>896</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="1">
         <v>45803</v>
       </c>
       <c r="G74" t="s">
@@ -7568,7 +7542,7 @@
       <c r="E75" t="s">
         <v>898</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="1">
         <v>45803</v>
       </c>
       <c r="G75" t="s">
@@ -7578,7 +7552,7 @@
         <v>1353</v>
       </c>
       <c r="I75">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J75">
         <v>429</v>
@@ -7589,7 +7563,7 @@
       <c r="L75" t="s">
         <v>1383</v>
       </c>
-      <c r="N75" s="2">
+      <c r="N75" s="1">
         <v>46232</v>
       </c>
       <c r="Q75" t="b">
@@ -7612,7 +7586,7 @@
       <c r="E76" t="s">
         <v>899</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="1">
         <v>45803</v>
       </c>
       <c r="G76" t="s">
@@ -7622,7 +7596,7 @@
         <v>1353</v>
       </c>
       <c r="I76">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K76" t="s">
         <v>1363</v>
@@ -7647,7 +7621,7 @@
       <c r="E77" t="s">
         <v>900</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="1">
         <v>45803</v>
       </c>
       <c r="G77" t="s">
@@ -7676,7 +7650,7 @@
       <c r="E78" t="s">
         <v>901</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="1">
         <v>45803</v>
       </c>
       <c r="G78" t="s">
@@ -7705,7 +7679,7 @@
       <c r="E79" t="s">
         <v>902</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="1">
         <v>45803</v>
       </c>
       <c r="G79" t="s">
@@ -7715,7 +7689,7 @@
         <v>1353</v>
       </c>
       <c r="I79">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K79" t="s">
         <v>1363</v>
@@ -7740,7 +7714,7 @@
       <c r="E80" t="s">
         <v>903</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="1">
         <v>45803</v>
       </c>
       <c r="G80" t="s">
@@ -7750,7 +7724,7 @@
         <v>1353</v>
       </c>
       <c r="I80">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J80">
         <v>429</v>
@@ -7761,7 +7735,7 @@
       <c r="L80" t="s">
         <v>1383</v>
       </c>
-      <c r="N80" s="2">
+      <c r="N80" s="1">
         <v>46232</v>
       </c>
       <c r="Q80" t="b">
@@ -7784,7 +7758,7 @@
       <c r="E81" t="s">
         <v>904</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="1">
         <v>45813</v>
       </c>
       <c r="G81" t="s">
@@ -7813,7 +7787,7 @@
       <c r="E82" t="s">
         <v>905</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="1">
         <v>45813</v>
       </c>
       <c r="G82" t="s">
@@ -7823,7 +7797,7 @@
         <v>1353</v>
       </c>
       <c r="I82">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K82" t="s">
         <v>1360</v>
@@ -7851,7 +7825,7 @@
       <c r="E83" t="s">
         <v>906</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="1">
         <v>45813</v>
       </c>
       <c r="G83" t="s">
@@ -7880,7 +7854,7 @@
       <c r="E84" t="s">
         <v>907</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="1">
         <v>45813</v>
       </c>
       <c r="G84" t="s">
@@ -7890,7 +7864,7 @@
         <v>1353</v>
       </c>
       <c r="I84">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J84">
         <v>40</v>
@@ -7901,7 +7875,7 @@
       <c r="L84" t="s">
         <v>1384</v>
       </c>
-      <c r="N84" s="2">
+      <c r="N84" s="1">
         <v>45853</v>
       </c>
       <c r="O84">
@@ -7927,7 +7901,7 @@
       <c r="E85" t="s">
         <v>908</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="1">
         <v>45813</v>
       </c>
       <c r="G85" t="s">
@@ -7937,7 +7911,7 @@
         <v>1353</v>
       </c>
       <c r="I85">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K85" t="s">
         <v>1357</v>
@@ -7965,7 +7939,7 @@
       <c r="E86" t="s">
         <v>909</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="1">
         <v>45813</v>
       </c>
       <c r="G86" t="s">
@@ -7975,7 +7949,7 @@
         <v>1353</v>
       </c>
       <c r="I86">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K86" t="s">
         <v>1357</v>
@@ -8003,7 +7977,7 @@
       <c r="E87" t="s">
         <v>910</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="1">
         <v>45813</v>
       </c>
       <c r="G87" t="s">
@@ -8013,7 +7987,7 @@
         <v>1353</v>
       </c>
       <c r="I87">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J87">
         <v>-16</v>
@@ -8024,7 +7998,7 @@
       <c r="L87" t="s">
         <v>1385</v>
       </c>
-      <c r="N87" s="2">
+      <c r="N87" s="1">
         <v>45797</v>
       </c>
       <c r="O87" t="s">
@@ -8050,7 +8024,7 @@
       <c r="E88" t="s">
         <v>911</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="1">
         <v>45813</v>
       </c>
       <c r="G88" t="s">
@@ -8065,7 +8039,7 @@
       <c r="L88" t="s">
         <v>1386</v>
       </c>
-      <c r="N88" s="2">
+      <c r="N88" s="1">
         <v>46195</v>
       </c>
       <c r="Q88" t="b">
@@ -8088,7 +8062,7 @@
       <c r="E89" t="s">
         <v>912</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="1">
         <v>45813</v>
       </c>
       <c r="G89" t="s">
@@ -8103,7 +8077,7 @@
       <c r="L89" t="s">
         <v>1386</v>
       </c>
-      <c r="N89" s="2">
+      <c r="N89" s="1">
         <v>46195</v>
       </c>
       <c r="Q89" t="b">
@@ -8126,7 +8100,7 @@
       <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="1">
         <v>45831</v>
       </c>
       <c r="G90" t="s">
@@ -8136,7 +8110,7 @@
         <v>1353</v>
       </c>
       <c r="I90">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K90" t="s">
         <v>1330</v>
@@ -8167,7 +8141,7 @@
       <c r="E91" t="s">
         <v>914</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="1">
         <v>45831</v>
       </c>
       <c r="G91" t="s">
@@ -8177,7 +8151,7 @@
         <v>1353</v>
       </c>
       <c r="I91">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J91">
         <v>308</v>
@@ -8188,7 +8162,7 @@
       <c r="L91" t="s">
         <v>1388</v>
       </c>
-      <c r="N91" s="2">
+      <c r="N91" s="1">
         <v>46139</v>
       </c>
       <c r="Q91" t="b">
@@ -8208,7 +8182,7 @@
       <c r="D92" t="s">
         <v>748</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="1">
         <v>45831</v>
       </c>
       <c r="G92" t="s">
@@ -8237,7 +8211,7 @@
       <c r="E93" t="s">
         <v>915</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="1">
         <v>45831</v>
       </c>
       <c r="G93" t="s">
@@ -8247,7 +8221,7 @@
         <v>1353</v>
       </c>
       <c r="I93">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J93">
         <v>308</v>
@@ -8258,7 +8232,7 @@
       <c r="L93" t="s">
         <v>1388</v>
       </c>
-      <c r="N93" s="2">
+      <c r="N93" s="1">
         <v>46139</v>
       </c>
       <c r="Q93" t="b">
@@ -8281,7 +8255,7 @@
       <c r="E94" t="s">
         <v>916</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="1">
         <v>45831</v>
       </c>
       <c r="G94" t="s">
@@ -8291,7 +8265,7 @@
         <v>1353</v>
       </c>
       <c r="I94">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K94" t="s">
         <v>1360</v>
@@ -8319,7 +8293,7 @@
       <c r="E95" t="s">
         <v>917</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="1">
         <v>45831</v>
       </c>
       <c r="G95" t="s">
@@ -8329,7 +8303,7 @@
         <v>1353</v>
       </c>
       <c r="I95">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J95">
         <v>308</v>
@@ -8340,7 +8314,7 @@
       <c r="L95" t="s">
         <v>1388</v>
       </c>
-      <c r="N95" s="2">
+      <c r="N95" s="1">
         <v>46139</v>
       </c>
       <c r="Q95" t="b">
@@ -8363,7 +8337,7 @@
       <c r="E96" t="s">
         <v>918</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="1">
         <v>45831</v>
       </c>
       <c r="G96" t="s">
@@ -8373,7 +8347,7 @@
         <v>1353</v>
       </c>
       <c r="I96">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J96">
         <v>17</v>
@@ -8384,7 +8358,7 @@
       <c r="L96" t="s">
         <v>1369</v>
       </c>
-      <c r="N96" s="2">
+      <c r="N96" s="1">
         <v>45848</v>
       </c>
       <c r="O96" t="s">
@@ -8410,7 +8384,7 @@
       <c r="E97" t="s">
         <v>919</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="1">
         <v>45840</v>
       </c>
       <c r="G97" t="s">
@@ -8420,7 +8394,7 @@
         <v>1353</v>
       </c>
       <c r="I97">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J97">
         <v>20</v>
@@ -8431,7 +8405,7 @@
       <c r="L97" t="s">
         <v>1389</v>
       </c>
-      <c r="N97" s="2">
+      <c r="N97" s="1">
         <v>45860</v>
       </c>
       <c r="P97" t="s">
@@ -8457,7 +8431,7 @@
       <c r="E98" t="s">
         <v>920</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="1">
         <v>45840</v>
       </c>
       <c r="G98" t="s">
@@ -8467,7 +8441,7 @@
         <v>1353</v>
       </c>
       <c r="I98">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K98" t="s">
         <v>1360</v>
@@ -8495,7 +8469,7 @@
       <c r="E99" t="s">
         <v>921</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="1">
         <v>45840</v>
       </c>
       <c r="G99" t="s">
@@ -8524,7 +8498,7 @@
       <c r="E100" t="s">
         <v>922</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="1">
         <v>45840</v>
       </c>
       <c r="G100" t="s">
@@ -8534,7 +8508,7 @@
         <v>1353</v>
       </c>
       <c r="I100">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J100">
         <v>348</v>
@@ -8545,7 +8519,7 @@
       <c r="L100" t="s">
         <v>1388</v>
       </c>
-      <c r="N100" s="2">
+      <c r="N100" s="1">
         <v>46188</v>
       </c>
       <c r="Q100" t="b">
@@ -8568,7 +8542,7 @@
       <c r="E101" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="1">
         <v>45840</v>
       </c>
       <c r="G101" t="s">
@@ -8597,7 +8571,7 @@
       <c r="E102" t="s">
         <v>924</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="1">
         <v>45840</v>
       </c>
       <c r="G102" t="s">
@@ -8626,7 +8600,7 @@
       <c r="E103" t="s">
         <v>925</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="1">
         <v>45840</v>
       </c>
       <c r="G103" t="s">
@@ -8655,7 +8629,7 @@
       <c r="E104" t="s">
         <v>926</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="1">
         <v>45840</v>
       </c>
       <c r="G104" t="s">
@@ -8665,7 +8639,7 @@
         <v>1353</v>
       </c>
       <c r="I104">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J104">
         <v>348</v>
@@ -8676,7 +8650,7 @@
       <c r="L104" t="s">
         <v>1388</v>
       </c>
-      <c r="N104" s="2">
+      <c r="N104" s="1">
         <v>46188</v>
       </c>
       <c r="Q104" t="b">
@@ -8699,7 +8673,7 @@
       <c r="E105" t="s">
         <v>927</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="1">
         <v>45840</v>
       </c>
       <c r="G105" t="s">
@@ -8709,7 +8683,7 @@
         <v>1353</v>
       </c>
       <c r="I105">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J105">
         <v>348</v>
@@ -8720,7 +8694,7 @@
       <c r="L105" t="s">
         <v>1388</v>
       </c>
-      <c r="N105" s="2">
+      <c r="N105" s="1">
         <v>46188</v>
       </c>
       <c r="Q105" t="b">
@@ -8743,7 +8717,7 @@
       <c r="E106" t="s">
         <v>928</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="1">
         <v>45840</v>
       </c>
       <c r="G106" t="s">
@@ -8753,7 +8727,7 @@
         <v>1353</v>
       </c>
       <c r="I106">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J106">
         <v>49</v>
@@ -8764,7 +8738,7 @@
       <c r="L106" t="s">
         <v>1390</v>
       </c>
-      <c r="N106" s="2">
+      <c r="N106" s="1">
         <v>45889</v>
       </c>
       <c r="Q106" t="b">
@@ -8787,7 +8761,7 @@
       <c r="E107" t="s">
         <v>929</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="1">
         <v>45840</v>
       </c>
       <c r="G107" t="s">
@@ -8797,7 +8771,7 @@
         <v>1353</v>
       </c>
       <c r="I107">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J107">
         <v>36</v>
@@ -8808,7 +8782,7 @@
       <c r="L107" t="s">
         <v>1391</v>
       </c>
-      <c r="N107" s="2">
+      <c r="N107" s="1">
         <v>45876</v>
       </c>
       <c r="Q107" t="b">
@@ -8831,7 +8805,7 @@
       <c r="E108" t="s">
         <v>930</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="1">
         <v>45840</v>
       </c>
       <c r="G108" t="s">
@@ -8841,7 +8815,7 @@
         <v>1353</v>
       </c>
       <c r="I108">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K108" t="s">
         <v>1357</v>
@@ -8869,7 +8843,7 @@
       <c r="E109" t="s">
         <v>931</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="1">
         <v>45840</v>
       </c>
       <c r="G109" t="s">
@@ -8879,7 +8853,7 @@
         <v>1353</v>
       </c>
       <c r="I109">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K109" t="s">
         <v>1357</v>
@@ -8907,7 +8881,7 @@
       <c r="E110" t="s">
         <v>932</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="1">
         <v>45840</v>
       </c>
       <c r="G110" t="s">
@@ -8936,7 +8910,7 @@
       <c r="E111" t="s">
         <v>933</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="1">
         <v>45840</v>
       </c>
       <c r="G111" t="s">
@@ -8965,7 +8939,7 @@
       <c r="E112" t="s">
         <v>934</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="1">
         <v>45840</v>
       </c>
       <c r="G112" t="s">
@@ -8994,7 +8968,7 @@
       <c r="E113" t="s">
         <v>935</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="1">
         <v>45840</v>
       </c>
       <c r="G113" t="s">
@@ -9023,7 +8997,7 @@
       <c r="E114" t="s">
         <v>936</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="1">
         <v>45840</v>
       </c>
       <c r="G114" t="s">
@@ -9052,7 +9026,7 @@
       <c r="E115" t="s">
         <v>937</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="1">
         <v>45840</v>
       </c>
       <c r="G115" t="s">
@@ -9062,7 +9036,7 @@
         <v>1353</v>
       </c>
       <c r="I115">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K115" t="s">
         <v>1357</v>
@@ -9090,7 +9064,7 @@
       <c r="E116" t="s">
         <v>938</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="1">
         <v>45840</v>
       </c>
       <c r="G116" t="s">
@@ -9100,7 +9074,7 @@
         <v>1353</v>
       </c>
       <c r="I116">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K116" t="s">
         <v>1357</v>
@@ -9128,7 +9102,7 @@
       <c r="E117" t="s">
         <v>939</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="1">
         <v>45840</v>
       </c>
       <c r="G117" t="s">
@@ -9138,7 +9112,7 @@
         <v>1353</v>
       </c>
       <c r="I117">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K117" t="s">
         <v>1357</v>
@@ -9166,7 +9140,7 @@
       <c r="E118" t="s">
         <v>940</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="1">
         <v>45840</v>
       </c>
       <c r="G118" t="s">
@@ -9176,7 +9150,7 @@
         <v>1353</v>
       </c>
       <c r="I118">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K118" t="s">
         <v>1357</v>
@@ -9204,7 +9178,7 @@
       <c r="E119" t="s">
         <v>941</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="1">
         <v>45840</v>
       </c>
       <c r="G119" t="s">
@@ -9214,7 +9188,7 @@
         <v>1353</v>
       </c>
       <c r="I119">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K119" t="s">
         <v>1357</v>
@@ -9242,7 +9216,7 @@
       <c r="E120" t="s">
         <v>942</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="1">
         <v>45840</v>
       </c>
       <c r="G120" t="s">
@@ -9252,7 +9226,7 @@
         <v>1353</v>
       </c>
       <c r="I120">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K120" t="s">
         <v>1357</v>
@@ -9280,7 +9254,7 @@
       <c r="E121" t="s">
         <v>943</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="1">
         <v>45849</v>
       </c>
       <c r="G121" t="s">
@@ -9290,7 +9264,7 @@
         <v>1353</v>
       </c>
       <c r="I121">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J121">
         <v>251</v>
@@ -9301,7 +9275,7 @@
       <c r="L121" t="s">
         <v>1379</v>
       </c>
-      <c r="N121" s="2">
+      <c r="N121" s="1">
         <v>46100</v>
       </c>
       <c r="O121">
@@ -9327,7 +9301,7 @@
       <c r="E122" t="s">
         <v>944</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="1">
         <v>45849</v>
       </c>
       <c r="G122" t="s">
@@ -9337,7 +9311,7 @@
         <v>1353</v>
       </c>
       <c r="I122">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K122" t="s">
         <v>1357</v>
@@ -9365,7 +9339,7 @@
       <c r="E123" t="s">
         <v>945</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="1">
         <v>45849</v>
       </c>
       <c r="G123" t="s">
@@ -9394,7 +9368,7 @@
       <c r="E124" t="s">
         <v>946</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="1">
         <v>45853</v>
       </c>
       <c r="G124" t="s">
@@ -9404,7 +9378,7 @@
         <v>1353</v>
       </c>
       <c r="I124">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K124" t="s">
         <v>1357</v>
@@ -9432,7 +9406,7 @@
       <c r="E125" t="s">
         <v>947</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="1">
         <v>45855</v>
       </c>
       <c r="G125" t="s">
@@ -9442,7 +9416,7 @@
         <v>1353</v>
       </c>
       <c r="I125">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K125" t="s">
         <v>1363</v>
@@ -9470,7 +9444,7 @@
       <c r="E126" t="s">
         <v>948</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="1">
         <v>45855</v>
       </c>
       <c r="G126" t="s">
@@ -9499,7 +9473,7 @@
       <c r="E127" t="s">
         <v>949</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="1">
         <v>45856</v>
       </c>
       <c r="G127" t="s">
@@ -9528,7 +9502,7 @@
       <c r="E128" t="s">
         <v>950</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="1">
         <v>45869</v>
       </c>
       <c r="G128" t="s">
@@ -9538,7 +9512,7 @@
         <v>1353</v>
       </c>
       <c r="I128">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K128" t="s">
         <v>1357</v>
@@ -9566,7 +9540,7 @@
       <c r="E129" t="s">
         <v>951</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="1">
         <v>45869</v>
       </c>
       <c r="G129" t="s">
@@ -9576,7 +9550,7 @@
         <v>1353</v>
       </c>
       <c r="I129">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K129" t="s">
         <v>1356</v>
@@ -9604,7 +9578,7 @@
       <c r="E130" t="s">
         <v>952</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="1">
         <v>45869</v>
       </c>
       <c r="G130" t="s">
@@ -9614,7 +9588,7 @@
         <v>1353</v>
       </c>
       <c r="I130">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J130">
         <v>47</v>
@@ -9625,7 +9599,7 @@
       <c r="L130" t="s">
         <v>1392</v>
       </c>
-      <c r="N130" s="2">
+      <c r="N130" s="1">
         <v>45916</v>
       </c>
       <c r="O130">
@@ -9651,7 +9625,7 @@
       <c r="E131" t="s">
         <v>953</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="1">
         <v>45869</v>
       </c>
       <c r="G131" t="s">
@@ -9680,7 +9654,7 @@
       <c r="E132" t="s">
         <v>954</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="1">
         <v>45869</v>
       </c>
       <c r="G132" t="s">
@@ -9690,7 +9664,7 @@
         <v>1353</v>
       </c>
       <c r="I132">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J132">
         <v>145</v>
@@ -9701,7 +9675,7 @@
       <c r="L132" t="s">
         <v>1393</v>
       </c>
-      <c r="N132" s="2">
+      <c r="N132" s="1">
         <v>46014</v>
       </c>
       <c r="O132">
@@ -9727,7 +9701,7 @@
       <c r="E133" t="s">
         <v>955</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="1">
         <v>45869</v>
       </c>
       <c r="G133" t="s">
@@ -9756,7 +9730,7 @@
       <c r="E134" t="s">
         <v>956</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="1">
         <v>45882</v>
       </c>
       <c r="G134" t="s">
@@ -9766,7 +9740,7 @@
         <v>1353</v>
       </c>
       <c r="I134">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K134" t="s">
         <v>1356</v>
@@ -9794,7 +9768,7 @@
       <c r="E135" t="s">
         <v>957</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="1">
         <v>45882</v>
       </c>
       <c r="G135" t="s">
@@ -9823,7 +9797,7 @@
       <c r="E136" t="s">
         <v>958</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="1">
         <v>45891</v>
       </c>
       <c r="G136" t="s">
@@ -9852,7 +9826,7 @@
       <c r="E137" t="s">
         <v>959</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="1">
         <v>45891</v>
       </c>
       <c r="G137" t="s">
@@ -9881,7 +9855,7 @@
       <c r="E138" t="s">
         <v>960</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="1">
         <v>45891</v>
       </c>
       <c r="G138" t="s">
@@ -9891,7 +9865,7 @@
         <v>1353</v>
       </c>
       <c r="I138">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K138" t="s">
         <v>1357</v>
@@ -9919,7 +9893,7 @@
       <c r="E139" t="s">
         <v>961</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="1">
         <v>45891</v>
       </c>
       <c r="G139" t="s">
@@ -9948,7 +9922,7 @@
       <c r="E140" t="s">
         <v>962</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="1">
         <v>45891</v>
       </c>
       <c r="G140" t="s">
@@ -9977,7 +9951,7 @@
       <c r="E141" t="s">
         <v>963</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="1">
         <v>45891</v>
       </c>
       <c r="G141" t="s">
@@ -10006,7 +9980,7 @@
       <c r="E142" t="s">
         <v>964</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="1">
         <v>45891</v>
       </c>
       <c r="G142" t="s">
@@ -10035,7 +10009,7 @@
       <c r="E143" t="s">
         <v>965</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="1">
         <v>45891</v>
       </c>
       <c r="G143" t="s">
@@ -10064,7 +10038,7 @@
       <c r="E144" t="s">
         <v>966</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="1">
         <v>45891</v>
       </c>
       <c r="G144" t="s">
@@ -10093,7 +10067,7 @@
       <c r="E145" t="s">
         <v>967</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="1">
         <v>45891</v>
       </c>
       <c r="G145" t="s">
@@ -10122,7 +10096,7 @@
       <c r="E146" t="s">
         <v>968</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="1">
         <v>45891</v>
       </c>
       <c r="G146" t="s">
@@ -10151,7 +10125,7 @@
       <c r="E147" t="s">
         <v>969</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="1">
         <v>45891</v>
       </c>
       <c r="G147" t="s">
@@ -10180,7 +10154,7 @@
       <c r="E148" t="s">
         <v>970</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="1">
         <v>45891</v>
       </c>
       <c r="G148" t="s">
@@ -10190,7 +10164,7 @@
         <v>1353</v>
       </c>
       <c r="I148">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J148">
         <v>341</v>
@@ -10201,7 +10175,7 @@
       <c r="L148" t="s">
         <v>1383</v>
       </c>
-      <c r="N148" s="2">
+      <c r="N148" s="1">
         <v>46232</v>
       </c>
       <c r="Q148" t="b">
@@ -10224,7 +10198,7 @@
       <c r="E149" t="s">
         <v>971</v>
       </c>
-      <c r="F149" s="2">
+      <c r="F149" s="1">
         <v>45891</v>
       </c>
       <c r="G149" t="s">
@@ -10234,7 +10208,7 @@
         <v>1353</v>
       </c>
       <c r="I149">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J149">
         <v>374</v>
@@ -10245,7 +10219,7 @@
       <c r="L149" t="s">
         <v>1394</v>
       </c>
-      <c r="N149" s="2">
+      <c r="N149" s="1">
         <v>46265</v>
       </c>
       <c r="P149" t="s">
@@ -10271,7 +10245,7 @@
       <c r="E150" t="s">
         <v>972</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="1">
         <v>45891</v>
       </c>
       <c r="G150" t="s">
@@ -10281,7 +10255,7 @@
         <v>1353</v>
       </c>
       <c r="I150">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J150">
         <v>201</v>
@@ -10292,7 +10266,7 @@
       <c r="L150" t="s">
         <v>1381</v>
       </c>
-      <c r="N150" s="2">
+      <c r="N150" s="1">
         <v>46092</v>
       </c>
       <c r="P150" t="s">
@@ -10318,7 +10292,7 @@
       <c r="E151" t="s">
         <v>973</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="1">
         <v>45891</v>
       </c>
       <c r="G151" t="s">
@@ -10347,7 +10321,7 @@
       <c r="E152" t="s">
         <v>963</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="1">
         <v>45891</v>
       </c>
       <c r="G152" t="s">
@@ -10357,7 +10331,7 @@
         <v>1353</v>
       </c>
       <c r="I152">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J152">
         <v>228</v>
@@ -10368,7 +10342,7 @@
       <c r="L152" t="s">
         <v>1382</v>
       </c>
-      <c r="N152" s="2">
+      <c r="N152" s="1">
         <v>46119</v>
       </c>
       <c r="Q152" t="b">
@@ -10391,7 +10365,7 @@
       <c r="E153" t="s">
         <v>974</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="1">
         <v>45891</v>
       </c>
       <c r="G153" t="s">
@@ -10409,7 +10383,7 @@
       <c r="L153" t="s">
         <v>1383</v>
       </c>
-      <c r="N153" s="2">
+      <c r="N153" s="1">
         <v>46232</v>
       </c>
       <c r="Q153" t="b">
@@ -10432,7 +10406,7 @@
       <c r="E154" t="s">
         <v>975</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="1">
         <v>45891</v>
       </c>
       <c r="G154" t="s">
@@ -10461,7 +10435,7 @@
       <c r="E155" t="s">
         <v>976</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="1">
         <v>45891</v>
       </c>
       <c r="G155" t="s">
@@ -10471,7 +10445,7 @@
         <v>1353</v>
       </c>
       <c r="I155">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K155" t="s">
         <v>1363</v>
@@ -10496,7 +10470,7 @@
       <c r="E156" t="s">
         <v>977</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="1">
         <v>45891</v>
       </c>
       <c r="G156" t="s">
@@ -10506,7 +10480,7 @@
         <v>1353</v>
       </c>
       <c r="I156">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K156" t="s">
         <v>1357</v>
@@ -10534,7 +10508,7 @@
       <c r="E157" t="s">
         <v>978</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="1">
         <v>45891</v>
       </c>
       <c r="G157" t="s">
@@ -10544,7 +10518,7 @@
         <v>1353</v>
       </c>
       <c r="I157">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J157">
         <v>371</v>
@@ -10555,7 +10529,7 @@
       <c r="L157" t="s">
         <v>1395</v>
       </c>
-      <c r="N157" s="2">
+      <c r="N157" s="1">
         <v>46262</v>
       </c>
       <c r="Q157" t="b">
@@ -10578,7 +10552,7 @@
       <c r="E158" t="s">
         <v>979</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="1">
         <v>45894</v>
       </c>
       <c r="G158" t="s">
@@ -10588,7 +10562,7 @@
         <v>1353</v>
       </c>
       <c r="I158">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J158">
         <v>52</v>
@@ -10599,7 +10573,7 @@
       <c r="L158" t="s">
         <v>1396</v>
       </c>
-      <c r="N158" s="2">
+      <c r="N158" s="1">
         <v>45946</v>
       </c>
       <c r="Q158" t="b">
@@ -10622,7 +10596,7 @@
       <c r="E159" t="s">
         <v>980</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="1">
         <v>45894</v>
       </c>
       <c r="G159" t="s">
@@ -10632,7 +10606,7 @@
         <v>1353</v>
       </c>
       <c r="I159">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K159" t="s">
         <v>1357</v>
@@ -10660,7 +10634,7 @@
       <c r="E160" t="s">
         <v>981</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="1">
         <v>45898</v>
       </c>
       <c r="G160" t="s">
@@ -10670,7 +10644,7 @@
         <v>1353</v>
       </c>
       <c r="I160">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K160" t="s">
         <v>1357</v>
@@ -10698,7 +10672,7 @@
       <c r="E161" t="s">
         <v>982</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="1">
         <v>45898</v>
       </c>
       <c r="G161" t="s">
@@ -10708,7 +10682,7 @@
         <v>1353</v>
       </c>
       <c r="I161">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J161">
         <v>55</v>
@@ -10719,7 +10693,7 @@
       <c r="L161" t="s">
         <v>1397</v>
       </c>
-      <c r="N161" s="2">
+      <c r="N161" s="1">
         <v>45953</v>
       </c>
       <c r="O161" t="s">
@@ -10745,7 +10719,7 @@
       <c r="E162" t="s">
         <v>983</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="1">
         <v>45898</v>
       </c>
       <c r="G162" t="s">
@@ -10755,7 +10729,7 @@
         <v>1353</v>
       </c>
       <c r="I162">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J162">
         <v>42</v>
@@ -10766,7 +10740,7 @@
       <c r="L162" t="s">
         <v>1398</v>
       </c>
-      <c r="N162" s="2">
+      <c r="N162" s="1">
         <v>45940</v>
       </c>
       <c r="Q162" t="b">
@@ -10789,7 +10763,7 @@
       <c r="E163" t="s">
         <v>984</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="1">
         <v>45898</v>
       </c>
       <c r="G163" t="s">
@@ -10799,7 +10773,7 @@
         <v>1353</v>
       </c>
       <c r="I163">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J163">
         <v>42</v>
@@ -10810,7 +10784,7 @@
       <c r="L163" t="s">
         <v>1398</v>
       </c>
-      <c r="N163" s="2">
+      <c r="N163" s="1">
         <v>45940</v>
       </c>
       <c r="Q163" t="b">
@@ -10833,7 +10807,7 @@
       <c r="E164" t="s">
         <v>985</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="1">
         <v>45910</v>
       </c>
       <c r="G164" t="s">
@@ -10843,7 +10817,7 @@
         <v>1355</v>
       </c>
       <c r="I164">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O164" t="s">
         <v>1469</v>
@@ -10868,7 +10842,7 @@
       <c r="E165" t="s">
         <v>986</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="1">
         <v>45917</v>
       </c>
       <c r="G165" t="s">
@@ -10886,7 +10860,7 @@
       <c r="L165" t="s">
         <v>1399</v>
       </c>
-      <c r="N165" s="2">
+      <c r="N165" s="1">
         <v>46204</v>
       </c>
       <c r="P165" t="s">
@@ -10912,7 +10886,7 @@
       <c r="E166" t="s">
         <v>987</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="1">
         <v>45917</v>
       </c>
       <c r="G166" t="s">
@@ -10941,7 +10915,7 @@
       <c r="E167" t="s">
         <v>988</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="1">
         <v>45917</v>
       </c>
       <c r="G167" t="s">
@@ -10970,7 +10944,7 @@
       <c r="E168" t="s">
         <v>989</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="1">
         <v>45917</v>
       </c>
       <c r="G168" t="s">
@@ -10980,7 +10954,7 @@
         <v>1353</v>
       </c>
       <c r="I168">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K168" t="s">
         <v>1360</v>
@@ -11011,7 +10985,7 @@
       <c r="E169" t="s">
         <v>990</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="1">
         <v>45917</v>
       </c>
       <c r="G169" t="s">
@@ -11021,7 +10995,7 @@
         <v>1353</v>
       </c>
       <c r="I169">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K169" t="s">
         <v>1330</v>
@@ -11029,7 +11003,7 @@
       <c r="L169" t="s">
         <v>1401</v>
       </c>
-      <c r="N169" s="2">
+      <c r="N169" s="1">
         <v>45973</v>
       </c>
       <c r="Q169" t="b">
@@ -11052,7 +11026,7 @@
       <c r="E170" t="s">
         <v>991</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="1">
         <v>45917</v>
       </c>
       <c r="G170" t="s">
@@ -11087,7 +11061,7 @@
       <c r="E171" t="s">
         <v>992</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="1">
         <v>45917</v>
       </c>
       <c r="G171" t="s">
@@ -11097,7 +11071,7 @@
         <v>1353</v>
       </c>
       <c r="I171">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K171" t="s">
         <v>1357</v>
@@ -11125,7 +11099,7 @@
       <c r="E172" t="s">
         <v>993</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="1">
         <v>45917</v>
       </c>
       <c r="G172" t="s">
@@ -11154,7 +11128,7 @@
       <c r="E173" t="s">
         <v>994</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="1">
         <v>45917</v>
       </c>
       <c r="G173" t="s">
@@ -11183,7 +11157,7 @@
       <c r="E174" t="s">
         <v>995</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="1">
         <v>45917</v>
       </c>
       <c r="G174" t="s">
@@ -11198,7 +11172,7 @@
       <c r="L174" t="s">
         <v>1386</v>
       </c>
-      <c r="N174" s="2">
+      <c r="N174" s="1">
         <v>46195</v>
       </c>
       <c r="Q174" t="b">
@@ -11221,7 +11195,7 @@
       <c r="E175" t="s">
         <v>996</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="1">
         <v>45917</v>
       </c>
       <c r="G175" t="s">
@@ -11231,7 +11205,7 @@
         <v>1353</v>
       </c>
       <c r="I175">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J175">
         <v>205</v>
@@ -11242,7 +11216,7 @@
       <c r="L175" t="s">
         <v>1402</v>
       </c>
-      <c r="N175" s="2">
+      <c r="N175" s="1">
         <v>46122</v>
       </c>
       <c r="P175" t="s">
@@ -11268,7 +11242,7 @@
       <c r="E176" t="s">
         <v>900</v>
       </c>
-      <c r="F176" s="2">
+      <c r="F176" s="1">
         <v>45917</v>
       </c>
       <c r="G176" t="s">
@@ -11278,7 +11252,7 @@
         <v>1353</v>
       </c>
       <c r="I176">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K176" t="s">
         <v>1357</v>
@@ -11306,7 +11280,7 @@
       <c r="E177" t="s">
         <v>997</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="1">
         <v>45917</v>
       </c>
       <c r="G177" t="s">
@@ -11316,7 +11290,7 @@
         <v>1353</v>
       </c>
       <c r="I177">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J177">
         <v>44</v>
@@ -11327,7 +11301,7 @@
       <c r="L177" t="s">
         <v>1403</v>
       </c>
-      <c r="N177" s="2">
+      <c r="N177" s="1">
         <v>45961</v>
       </c>
       <c r="P177" t="s">
@@ -11353,7 +11327,7 @@
       <c r="E178" t="s">
         <v>998</v>
       </c>
-      <c r="F178" s="2">
+      <c r="F178" s="1">
         <v>45937</v>
       </c>
       <c r="G178" t="s">
@@ -11363,7 +11337,7 @@
         <v>1353</v>
       </c>
       <c r="I178">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K178" t="s">
         <v>1356</v>
@@ -11391,7 +11365,7 @@
       <c r="E179" t="s">
         <v>999</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="1">
         <v>45937</v>
       </c>
       <c r="G179" t="s">
@@ -11420,7 +11394,7 @@
       <c r="E180" t="s">
         <v>1000</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="1">
         <v>45937</v>
       </c>
       <c r="G180" t="s">
@@ -11430,7 +11404,7 @@
         <v>1353</v>
       </c>
       <c r="I180">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K180" t="s">
         <v>1356</v>
@@ -11458,7 +11432,7 @@
       <c r="E181" t="s">
         <v>1001</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="1">
         <v>45937</v>
       </c>
       <c r="G181" t="s">
@@ -11487,7 +11461,7 @@
       <c r="E182" t="s">
         <v>1002</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="1">
         <v>45937</v>
       </c>
       <c r="G182" t="s">
@@ -11516,7 +11490,7 @@
       <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="F183" s="2">
+      <c r="F183" s="1">
         <v>45937</v>
       </c>
       <c r="G183" t="s">
@@ -11526,7 +11500,7 @@
         <v>1353</v>
       </c>
       <c r="I183">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K183" t="s">
         <v>1357</v>
@@ -11554,7 +11528,7 @@
       <c r="D184" t="s">
         <v>774</v>
       </c>
-      <c r="F184" s="2">
+      <c r="F184" s="1">
         <v>45939</v>
       </c>
       <c r="G184" t="s">
@@ -11564,7 +11538,7 @@
         <v>1353</v>
       </c>
       <c r="I184">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K184" t="s">
         <v>1363</v>
@@ -11589,7 +11563,7 @@
       <c r="E185" t="s">
         <v>1004</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="1">
         <v>45939</v>
       </c>
       <c r="G185" t="s">
@@ -11599,7 +11573,7 @@
         <v>1353</v>
       </c>
       <c r="I185">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K185" t="s">
         <v>1357</v>
@@ -11627,7 +11601,7 @@
       <c r="E186" t="s">
         <v>1005</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="1">
         <v>45939</v>
       </c>
       <c r="G186" t="s">
@@ -11637,7 +11611,7 @@
         <v>1353</v>
       </c>
       <c r="I186">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K186" t="s">
         <v>1357</v>
@@ -11665,7 +11639,7 @@
       <c r="E187" t="s">
         <v>1006</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="1">
         <v>45939</v>
       </c>
       <c r="G187" t="s">
@@ -11675,7 +11649,7 @@
         <v>1353</v>
       </c>
       <c r="I187">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J187">
         <v>75</v>
@@ -11686,7 +11660,7 @@
       <c r="L187" t="s">
         <v>1404</v>
       </c>
-      <c r="N187" s="2">
+      <c r="N187" s="1">
         <v>46014</v>
       </c>
       <c r="O187">
@@ -11712,7 +11686,7 @@
       <c r="E188" t="s">
         <v>1007</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="1">
         <v>45946</v>
       </c>
       <c r="G188" t="s">
@@ -11722,7 +11696,7 @@
         <v>1353</v>
       </c>
       <c r="I188">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J188">
         <v>40</v>
@@ -11733,7 +11707,7 @@
       <c r="L188" t="s">
         <v>1405</v>
       </c>
-      <c r="N188" s="2">
+      <c r="N188" s="1">
         <v>45986</v>
       </c>
       <c r="P188" t="s">
@@ -11759,7 +11733,7 @@
       <c r="E189" t="s">
         <v>1008</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="1">
         <v>45965</v>
       </c>
       <c r="G189" t="s">
@@ -11769,7 +11743,7 @@
         <v>1353</v>
       </c>
       <c r="I189">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J189">
         <v>155</v>
@@ -11780,7 +11754,7 @@
       <c r="L189" t="s">
         <v>1406</v>
       </c>
-      <c r="N189" s="2">
+      <c r="N189" s="1">
         <v>46120</v>
       </c>
       <c r="Q189" t="b">
@@ -11803,7 +11777,7 @@
       <c r="E190" t="s">
         <v>1009</v>
       </c>
-      <c r="F190" s="2">
+      <c r="F190" s="1">
         <v>45965</v>
       </c>
       <c r="G190" t="s">
@@ -11813,7 +11787,7 @@
         <v>1353</v>
       </c>
       <c r="I190">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J190">
         <v>107</v>
@@ -11824,7 +11798,7 @@
       <c r="L190" t="s">
         <v>1407</v>
       </c>
-      <c r="N190" s="2">
+      <c r="N190" s="1">
         <v>46072</v>
       </c>
       <c r="Q190" t="b">
@@ -11847,7 +11821,7 @@
       <c r="E191" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="2">
+      <c r="F191" s="1">
         <v>45967</v>
       </c>
       <c r="G191" t="s">
@@ -11857,7 +11831,7 @@
         <v>1353</v>
       </c>
       <c r="I191">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J191">
         <v>5</v>
@@ -11868,7 +11842,7 @@
       <c r="L191" t="s">
         <v>1408</v>
       </c>
-      <c r="N191" s="2">
+      <c r="N191" s="1">
         <v>45972</v>
       </c>
       <c r="Q191" t="b">
@@ -11891,7 +11865,7 @@
       <c r="E192" t="s">
         <v>1011</v>
       </c>
-      <c r="F192" s="2">
+      <c r="F192" s="1">
         <v>45968</v>
       </c>
       <c r="G192" t="s">
@@ -11901,7 +11875,7 @@
         <v>1353</v>
       </c>
       <c r="I192">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K192" t="s">
         <v>1357</v>
@@ -11929,7 +11903,7 @@
       <c r="E193" t="s">
         <v>1012</v>
       </c>
-      <c r="F193" s="2">
+      <c r="F193" s="1">
         <v>45968</v>
       </c>
       <c r="G193" t="s">
@@ -11939,7 +11913,7 @@
         <v>1353</v>
       </c>
       <c r="I193">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K193" t="s">
         <v>1362</v>
@@ -11967,7 +11941,7 @@
       <c r="E194" t="s">
         <v>1013</v>
       </c>
-      <c r="F194" s="2">
+      <c r="F194" s="1">
         <v>45968</v>
       </c>
       <c r="G194" t="s">
@@ -11996,7 +11970,7 @@
       <c r="E195" t="s">
         <v>1014</v>
       </c>
-      <c r="F195" s="2">
+      <c r="F195" s="1">
         <v>45971</v>
       </c>
       <c r="G195" t="s">
@@ -12006,7 +11980,7 @@
         <v>1353</v>
       </c>
       <c r="I195">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J195">
         <v>186</v>
@@ -12017,7 +11991,7 @@
       <c r="L195" t="s">
         <v>1409</v>
       </c>
-      <c r="N195" s="2">
+      <c r="N195" s="1">
         <v>46157</v>
       </c>
       <c r="Q195" t="b">
@@ -12040,7 +12014,7 @@
       <c r="E196" t="s">
         <v>1015</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="1">
         <v>45978</v>
       </c>
       <c r="G196" t="s">
@@ -12069,7 +12043,7 @@
       <c r="E197" t="s">
         <v>1016</v>
       </c>
-      <c r="F197" s="2">
+      <c r="F197" s="1">
         <v>45978</v>
       </c>
       <c r="G197" t="s">
@@ -12098,7 +12072,7 @@
       <c r="E198" t="s">
         <v>1017</v>
       </c>
-      <c r="F198" s="2">
+      <c r="F198" s="1">
         <v>45978</v>
       </c>
       <c r="G198" t="s">
@@ -12127,7 +12101,7 @@
       <c r="E199" t="s">
         <v>1018</v>
       </c>
-      <c r="F199" s="2">
+      <c r="F199" s="1">
         <v>45979</v>
       </c>
       <c r="G199" t="s">
@@ -12137,7 +12111,7 @@
         <v>1353</v>
       </c>
       <c r="I199">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J199">
         <v>70</v>
@@ -12148,7 +12122,7 @@
       <c r="L199" t="s">
         <v>1410</v>
       </c>
-      <c r="N199" s="2">
+      <c r="N199" s="1">
         <v>46049</v>
       </c>
       <c r="Q199" t="b">
@@ -12171,7 +12145,7 @@
       <c r="E200" t="s">
         <v>1019</v>
       </c>
-      <c r="F200" s="2">
+      <c r="F200" s="1">
         <v>45986</v>
       </c>
       <c r="G200" t="s">
@@ -12181,7 +12155,7 @@
         <v>1353</v>
       </c>
       <c r="I200">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J200">
         <v>170</v>
@@ -12192,7 +12166,7 @@
       <c r="L200" t="s">
         <v>1409</v>
       </c>
-      <c r="N200" s="2">
+      <c r="N200" s="1">
         <v>46156</v>
       </c>
       <c r="Q200" t="b">
@@ -12215,7 +12189,7 @@
       <c r="E201" t="s">
         <v>1020</v>
       </c>
-      <c r="F201" s="2">
+      <c r="F201" s="1">
         <v>45986</v>
       </c>
       <c r="G201" t="s">
@@ -12225,7 +12199,7 @@
         <v>1353</v>
       </c>
       <c r="I201">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K201" t="s">
         <v>1357</v>
@@ -12253,7 +12227,7 @@
       <c r="E202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" s="2">
+      <c r="F202" s="1">
         <v>45986</v>
       </c>
       <c r="G202" t="s">
@@ -12263,7 +12237,7 @@
         <v>1353</v>
       </c>
       <c r="I202">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K202" t="s">
         <v>1357</v>
@@ -12291,7 +12265,7 @@
       <c r="E203" t="s">
         <v>1022</v>
       </c>
-      <c r="F203" s="2">
+      <c r="F203" s="1">
         <v>45986</v>
       </c>
       <c r="G203" t="s">
@@ -12309,7 +12283,7 @@
       <c r="L203" t="s">
         <v>1411</v>
       </c>
-      <c r="N203" s="2">
+      <c r="N203" s="1">
         <v>46232</v>
       </c>
       <c r="Q203" t="b">
@@ -12332,7 +12306,7 @@
       <c r="E204" t="s">
         <v>1023</v>
       </c>
-      <c r="F204" s="2">
+      <c r="F204" s="1">
         <v>45986</v>
       </c>
       <c r="G204" t="s">
@@ -12342,7 +12316,7 @@
         <v>1353</v>
       </c>
       <c r="I204">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K204" t="s">
         <v>1356</v>
@@ -12370,7 +12344,7 @@
       <c r="E205" t="s">
         <v>1024</v>
       </c>
-      <c r="F205" s="2">
+      <c r="F205" s="1">
         <v>45986</v>
       </c>
       <c r="G205" t="s">
@@ -12380,7 +12354,7 @@
         <v>1353</v>
       </c>
       <c r="I205">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K205" t="s">
         <v>1356</v>
@@ -12408,7 +12382,7 @@
       <c r="E206" t="s">
         <v>1025</v>
       </c>
-      <c r="F206" s="2">
+      <c r="F206" s="1">
         <v>45986</v>
       </c>
       <c r="G206" t="s">
@@ -12437,7 +12411,7 @@
       <c r="E207" t="s">
         <v>1026</v>
       </c>
-      <c r="F207" s="2">
+      <c r="F207" s="1">
         <v>45986</v>
       </c>
       <c r="G207" t="s">
@@ -12447,7 +12421,7 @@
         <v>1353</v>
       </c>
       <c r="I207">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J207">
         <v>167</v>
@@ -12458,7 +12432,7 @@
       <c r="L207" t="s">
         <v>1412</v>
       </c>
-      <c r="N207" s="2">
+      <c r="N207" s="1">
         <v>46153</v>
       </c>
       <c r="Q207" t="b">
@@ -12481,7 +12455,7 @@
       <c r="E208" t="s">
         <v>1027</v>
       </c>
-      <c r="F208" s="2">
+      <c r="F208" s="1">
         <v>45986</v>
       </c>
       <c r="G208" t="s">
@@ -12491,7 +12465,7 @@
         <v>1353</v>
       </c>
       <c r="I208">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J208">
         <v>45</v>
@@ -12502,7 +12476,7 @@
       <c r="L208" t="s">
         <v>1413</v>
       </c>
-      <c r="N208" s="2">
+      <c r="N208" s="1">
         <v>46031</v>
       </c>
       <c r="Q208" t="b">
@@ -12525,7 +12499,7 @@
       <c r="E209" t="s">
         <v>1028</v>
       </c>
-      <c r="F209" s="2">
+      <c r="F209" s="1">
         <v>46000</v>
       </c>
       <c r="G209" t="s">
@@ -12535,7 +12509,7 @@
         <v>1353</v>
       </c>
       <c r="I209">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J209">
         <v>191</v>
@@ -12546,7 +12520,7 @@
       <c r="L209" t="s">
         <v>1414</v>
       </c>
-      <c r="N209" s="2">
+      <c r="N209" s="1">
         <v>46191</v>
       </c>
       <c r="Q209" t="b">
@@ -12569,7 +12543,7 @@
       <c r="E210" t="s">
         <v>1029</v>
       </c>
-      <c r="F210" s="2">
+      <c r="F210" s="1">
         <v>46000</v>
       </c>
       <c r="G210" t="s">
@@ -12579,7 +12553,7 @@
         <v>1353</v>
       </c>
       <c r="I210">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K210" t="s">
         <v>1360</v>
@@ -12607,7 +12581,7 @@
       <c r="E211" t="s">
         <v>1030</v>
       </c>
-      <c r="F211" s="2">
+      <c r="F211" s="1">
         <v>46000</v>
       </c>
       <c r="G211" t="s">
@@ -12636,7 +12610,7 @@
       <c r="E212" t="s">
         <v>1031</v>
       </c>
-      <c r="F212" s="2">
+      <c r="F212" s="1">
         <v>46000</v>
       </c>
       <c r="G212" t="s">
@@ -12665,7 +12639,7 @@
       <c r="E213" t="s">
         <v>1032</v>
       </c>
-      <c r="F213" s="2">
+      <c r="F213" s="1">
         <v>46007</v>
       </c>
       <c r="G213" t="s">
@@ -12675,7 +12649,7 @@
         <v>1353</v>
       </c>
       <c r="I213">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K213" t="s">
         <v>1357</v>
@@ -12703,7 +12677,7 @@
       <c r="E214" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="2">
+      <c r="F214" s="1">
         <v>46007</v>
       </c>
       <c r="G214" t="s">
@@ -12713,7 +12687,7 @@
         <v>1353</v>
       </c>
       <c r="I214">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J214">
         <v>14</v>
@@ -12724,7 +12698,7 @@
       <c r="L214" t="s">
         <v>1415</v>
       </c>
-      <c r="N214" s="2">
+      <c r="N214" s="1">
         <v>46021</v>
       </c>
       <c r="O214">
@@ -12750,7 +12724,7 @@
       <c r="E215" t="s">
         <v>1034</v>
       </c>
-      <c r="F215" s="2">
+      <c r="F215" s="1">
         <v>46007</v>
       </c>
       <c r="G215" t="s">
@@ -12760,7 +12734,7 @@
         <v>1353</v>
       </c>
       <c r="I215">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K215" t="s">
         <v>1357</v>
@@ -12788,7 +12762,7 @@
       <c r="E216" t="s">
         <v>1035</v>
       </c>
-      <c r="F216" s="2">
+      <c r="F216" s="1">
         <v>46010</v>
       </c>
       <c r="G216" t="s">
@@ -12817,7 +12791,7 @@
       <c r="E217" t="s">
         <v>1036</v>
       </c>
-      <c r="F217" s="2">
+      <c r="F217" s="1">
         <v>46010</v>
       </c>
       <c r="G217" t="s">
@@ -12827,7 +12801,7 @@
         <v>1353</v>
       </c>
       <c r="I217">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J217">
         <v>42</v>
@@ -12838,7 +12812,7 @@
       <c r="L217" t="s">
         <v>1416</v>
       </c>
-      <c r="N217" s="2">
+      <c r="N217" s="1">
         <v>46052</v>
       </c>
       <c r="Q217" t="b">
@@ -12861,7 +12835,7 @@
       <c r="E218" t="s">
         <v>1037</v>
       </c>
-      <c r="F218" s="2">
+      <c r="F218" s="1">
         <v>46010</v>
       </c>
       <c r="G218" t="s">
@@ -12871,7 +12845,7 @@
         <v>1353</v>
       </c>
       <c r="I218">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J218">
         <v>166</v>
@@ -12879,7 +12853,7 @@
       <c r="K218" t="s">
         <v>1359</v>
       </c>
-      <c r="N218" s="2">
+      <c r="N218" s="1">
         <v>46176</v>
       </c>
       <c r="P218" t="s">
@@ -12905,7 +12879,7 @@
       <c r="E219" t="s">
         <v>1038</v>
       </c>
-      <c r="F219" s="2">
+      <c r="F219" s="1">
         <v>46010</v>
       </c>
       <c r="G219" t="s">
@@ -12923,7 +12897,7 @@
       <c r="L219" t="s">
         <v>1417</v>
       </c>
-      <c r="N219" s="2">
+      <c r="N219" s="1">
         <v>46176</v>
       </c>
       <c r="P219" t="s">
@@ -12949,7 +12923,7 @@
       <c r="E220" t="s">
         <v>1039</v>
       </c>
-      <c r="F220" s="2">
+      <c r="F220" s="1">
         <v>46010</v>
       </c>
       <c r="G220" t="s">
@@ -12959,7 +12933,7 @@
         <v>1353</v>
       </c>
       <c r="I220">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J220">
         <v>154</v>
@@ -12970,7 +12944,7 @@
       <c r="L220" t="s">
         <v>1418</v>
       </c>
-      <c r="N220" s="2">
+      <c r="N220" s="1">
         <v>46164</v>
       </c>
       <c r="Q220" t="b">
@@ -12993,7 +12967,7 @@
       <c r="E221" t="s">
         <v>1040</v>
       </c>
-      <c r="F221" s="2">
+      <c r="F221" s="1">
         <v>46028</v>
       </c>
       <c r="G221" t="s">
@@ -13008,7 +12982,7 @@
       <c r="L221" t="s">
         <v>1419</v>
       </c>
-      <c r="N221" s="2">
+      <c r="N221" s="1">
         <v>46184</v>
       </c>
       <c r="Q221" t="b">
@@ -13031,7 +13005,7 @@
       <c r="E222" t="s">
         <v>1041</v>
       </c>
-      <c r="F222" s="2">
+      <c r="F222" s="1">
         <v>46028</v>
       </c>
       <c r="G222" t="s">
@@ -13046,7 +13020,7 @@
       <c r="L222" t="s">
         <v>1383</v>
       </c>
-      <c r="N222" s="2">
+      <c r="N222" s="1">
         <v>46232</v>
       </c>
       <c r="Q222" t="b">
@@ -13069,7 +13043,7 @@
       <c r="E223" t="s">
         <v>1042</v>
       </c>
-      <c r="F223" s="2">
+      <c r="F223" s="1">
         <v>46028</v>
       </c>
       <c r="G223" t="s">
@@ -13084,7 +13058,7 @@
       <c r="L223" t="s">
         <v>1383</v>
       </c>
-      <c r="N223" s="2">
+      <c r="N223" s="1">
         <v>46232</v>
       </c>
       <c r="Q223" t="b">
@@ -13107,7 +13081,7 @@
       <c r="E224" t="s">
         <v>1043</v>
       </c>
-      <c r="F224" s="2">
+      <c r="F224" s="1">
         <v>46028</v>
       </c>
       <c r="G224" t="s">
@@ -13117,7 +13091,7 @@
         <v>1353</v>
       </c>
       <c r="I224">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J224">
         <v>204</v>
@@ -13125,7 +13099,7 @@
       <c r="L224" t="s">
         <v>1383</v>
       </c>
-      <c r="N224" s="2">
+      <c r="N224" s="1">
         <v>46232</v>
       </c>
       <c r="Q224" t="b">
@@ -13148,7 +13122,7 @@
       <c r="E225" t="s">
         <v>1044</v>
       </c>
-      <c r="F225" s="2">
+      <c r="F225" s="1">
         <v>46028</v>
       </c>
       <c r="G225" t="s">
@@ -13163,7 +13137,7 @@
       <c r="L225" t="s">
         <v>1383</v>
       </c>
-      <c r="N225" s="2">
+      <c r="N225" s="1">
         <v>46232</v>
       </c>
       <c r="Q225" t="b">
@@ -13186,7 +13160,7 @@
       <c r="E226" t="s">
         <v>1045</v>
       </c>
-      <c r="F226" s="2">
+      <c r="F226" s="1">
         <v>46028</v>
       </c>
       <c r="G226" t="s">
@@ -13201,7 +13175,7 @@
       <c r="L226" t="s">
         <v>1383</v>
       </c>
-      <c r="N226" s="2">
+      <c r="N226" s="1">
         <v>46232</v>
       </c>
       <c r="Q226" t="b">
@@ -13224,7 +13198,7 @@
       <c r="E227" t="s">
         <v>1046</v>
       </c>
-      <c r="F227" s="2">
+      <c r="F227" s="1">
         <v>46028</v>
       </c>
       <c r="G227" t="s">
@@ -13239,7 +13213,7 @@
       <c r="L227" t="s">
         <v>1383</v>
       </c>
-      <c r="N227" s="2">
+      <c r="N227" s="1">
         <v>46232</v>
       </c>
       <c r="Q227" t="b">
@@ -13262,7 +13236,7 @@
       <c r="E228" t="s">
         <v>1047</v>
       </c>
-      <c r="F228" s="2">
+      <c r="F228" s="1">
         <v>46028</v>
       </c>
       <c r="G228" t="s">
@@ -13272,7 +13246,7 @@
         <v>1353</v>
       </c>
       <c r="I228">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J228">
         <v>204</v>
@@ -13280,7 +13254,7 @@
       <c r="L228" t="s">
         <v>1383</v>
       </c>
-      <c r="N228" s="2">
+      <c r="N228" s="1">
         <v>46232</v>
       </c>
       <c r="Q228" t="b">
@@ -13303,7 +13277,7 @@
       <c r="E229" t="s">
         <v>1048</v>
       </c>
-      <c r="F229" s="2">
+      <c r="F229" s="1">
         <v>46028</v>
       </c>
       <c r="G229" t="s">
@@ -13318,7 +13292,7 @@
       <c r="L229" t="s">
         <v>1420</v>
       </c>
-      <c r="N229" s="2">
+      <c r="N229" s="1">
         <v>46191</v>
       </c>
       <c r="Q229" t="b">
@@ -13341,7 +13315,7 @@
       <c r="E230" t="s">
         <v>1049</v>
       </c>
-      <c r="F230" s="2">
+      <c r="F230" s="1">
         <v>46028</v>
       </c>
       <c r="G230" t="s">
@@ -13351,7 +13325,7 @@
         <v>1353</v>
       </c>
       <c r="I230">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J230">
         <v>197</v>
@@ -13362,7 +13336,7 @@
       <c r="L230" t="s">
         <v>1395</v>
       </c>
-      <c r="N230" s="2">
+      <c r="N230" s="1">
         <v>46225</v>
       </c>
       <c r="Q230" t="b">
@@ -13385,7 +13359,7 @@
       <c r="E231" t="s">
         <v>1050</v>
       </c>
-      <c r="F231" s="2">
+      <c r="F231" s="1">
         <v>46028</v>
       </c>
       <c r="G231" t="s">
@@ -13395,7 +13369,7 @@
         <v>1353</v>
       </c>
       <c r="I231">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J231">
         <v>35</v>
@@ -13406,7 +13380,7 @@
       <c r="L231" t="s">
         <v>1421</v>
       </c>
-      <c r="N231" s="2">
+      <c r="N231" s="1">
         <v>46063</v>
       </c>
       <c r="Q231" t="b">
@@ -13429,7 +13403,7 @@
       <c r="E232" t="s">
         <v>1051</v>
       </c>
-      <c r="F232" s="2">
+      <c r="F232" s="1">
         <v>46028</v>
       </c>
       <c r="G232" t="s">
@@ -13458,7 +13432,7 @@
       <c r="E233" t="s">
         <v>1052</v>
       </c>
-      <c r="F233" s="2">
+      <c r="F233" s="1">
         <v>46028</v>
       </c>
       <c r="G233" t="s">
@@ -13487,7 +13461,7 @@
       <c r="E234" t="s">
         <v>1053</v>
       </c>
-      <c r="F234" s="2">
+      <c r="F234" s="1">
         <v>46028</v>
       </c>
       <c r="G234" t="s">
@@ -13497,7 +13471,7 @@
         <v>1353</v>
       </c>
       <c r="I234">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J234">
         <v>35</v>
@@ -13508,7 +13482,7 @@
       <c r="L234" t="s">
         <v>1421</v>
       </c>
-      <c r="N234" s="2">
+      <c r="N234" s="1">
         <v>46063</v>
       </c>
       <c r="P234" t="s">
@@ -13534,7 +13508,7 @@
       <c r="E235" t="s">
         <v>1054</v>
       </c>
-      <c r="F235" s="2">
+      <c r="F235" s="1">
         <v>46028</v>
       </c>
       <c r="G235" t="s">
@@ -13544,7 +13518,7 @@
         <v>1353</v>
       </c>
       <c r="I235">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J235">
         <v>35</v>
@@ -13555,7 +13529,7 @@
       <c r="L235" t="s">
         <v>1421</v>
       </c>
-      <c r="N235" s="2">
+      <c r="N235" s="1">
         <v>46063</v>
       </c>
       <c r="P235" t="s">
@@ -13581,7 +13555,7 @@
       <c r="E236" t="s">
         <v>1055</v>
       </c>
-      <c r="F236" s="2">
+      <c r="F236" s="1">
         <v>46028</v>
       </c>
       <c r="G236" t="s">
@@ -13591,7 +13565,7 @@
         <v>1353</v>
       </c>
       <c r="I236">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J236">
         <v>86</v>
@@ -13602,7 +13576,7 @@
       <c r="L236" t="s">
         <v>1422</v>
       </c>
-      <c r="N236" s="2">
+      <c r="N236" s="1">
         <v>46114</v>
       </c>
       <c r="Q236" t="b">
@@ -13625,7 +13599,7 @@
       <c r="E237" t="s">
         <v>1056</v>
       </c>
-      <c r="F237" s="2">
+      <c r="F237" s="1">
         <v>46028</v>
       </c>
       <c r="G237" t="s">
@@ -13643,7 +13617,7 @@
       <c r="L237" t="s">
         <v>1423</v>
       </c>
-      <c r="N237" s="2">
+      <c r="N237" s="1">
         <v>46210</v>
       </c>
       <c r="P237" t="s">
@@ -13669,7 +13643,7 @@
       <c r="E238" t="s">
         <v>1057</v>
       </c>
-      <c r="F238" s="2">
+      <c r="F238" s="1">
         <v>46028</v>
       </c>
       <c r="G238" t="s">
@@ -13698,7 +13672,7 @@
       <c r="E239" t="s">
         <v>1058</v>
       </c>
-      <c r="F239" s="2">
+      <c r="F239" s="1">
         <v>46036</v>
       </c>
       <c r="G239" t="s">
@@ -13708,7 +13682,7 @@
         <v>1353</v>
       </c>
       <c r="I239">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K239" t="s">
         <v>1330</v>
@@ -13716,7 +13690,7 @@
       <c r="L239" t="s">
         <v>1424</v>
       </c>
-      <c r="N239" s="2">
+      <c r="N239" s="1">
         <v>46052</v>
       </c>
       <c r="Q239" t="b">
@@ -13739,7 +13713,7 @@
       <c r="E240" t="s">
         <v>1059</v>
       </c>
-      <c r="F240" s="2">
+      <c r="F240" s="1">
         <v>46036</v>
       </c>
       <c r="G240" t="s">
@@ -13768,7 +13742,7 @@
       <c r="E241" t="s">
         <v>1060</v>
       </c>
-      <c r="F241" s="2">
+      <c r="F241" s="1">
         <v>46036</v>
       </c>
       <c r="G241" t="s">
@@ -13797,7 +13771,7 @@
       <c r="E242" t="s">
         <v>1061</v>
       </c>
-      <c r="F242" s="2">
+      <c r="F242" s="1">
         <v>46036</v>
       </c>
       <c r="G242" t="s">
@@ -13807,7 +13781,7 @@
         <v>1353</v>
       </c>
       <c r="I242">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K242" t="s">
         <v>1356</v>
@@ -13835,7 +13809,7 @@
       <c r="E243" t="s">
         <v>1062</v>
       </c>
-      <c r="F243" s="2">
+      <c r="F243" s="1">
         <v>46048</v>
       </c>
       <c r="G243" t="s">
@@ -13864,7 +13838,7 @@
       <c r="E244" t="s">
         <v>1063</v>
       </c>
-      <c r="F244" s="2">
+      <c r="F244" s="1">
         <v>46048</v>
       </c>
       <c r="G244" t="s">
@@ -13874,7 +13848,7 @@
         <v>1353</v>
       </c>
       <c r="I244">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J244">
         <v>15</v>
@@ -13882,7 +13856,7 @@
       <c r="K244" t="s">
         <v>1359</v>
       </c>
-      <c r="N244" s="2">
+      <c r="N244" s="1">
         <v>46063</v>
       </c>
       <c r="Q244" t="b">
@@ -13905,7 +13879,7 @@
       <c r="E245" t="s">
         <v>1064</v>
       </c>
-      <c r="F245" s="2">
+      <c r="F245" s="1">
         <v>46048</v>
       </c>
       <c r="G245" t="s">
@@ -13915,7 +13889,7 @@
         <v>1353</v>
       </c>
       <c r="I245">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J245">
         <v>15</v>
@@ -13926,7 +13900,7 @@
       <c r="L245" t="s">
         <v>1425</v>
       </c>
-      <c r="N245" s="2">
+      <c r="N245" s="1">
         <v>46063</v>
       </c>
       <c r="Q245" t="b">
@@ -13949,7 +13923,7 @@
       <c r="E246" t="s">
         <v>1065</v>
       </c>
-      <c r="F246" s="2">
+      <c r="F246" s="1">
         <v>46050</v>
       </c>
       <c r="G246" t="s">
@@ -13967,7 +13941,7 @@
       <c r="L246" t="s">
         <v>1426</v>
       </c>
-      <c r="N246" s="2">
+      <c r="N246" s="1">
         <v>46191</v>
       </c>
       <c r="Q246" t="b">
@@ -13990,7 +13964,7 @@
       <c r="E247" t="s">
         <v>1066</v>
       </c>
-      <c r="F247" s="2">
+      <c r="F247" s="1">
         <v>46050</v>
       </c>
       <c r="G247" t="s">
@@ -14019,7 +13993,7 @@
       <c r="E248" t="s">
         <v>1067</v>
       </c>
-      <c r="F248" s="2">
+      <c r="F248" s="1">
         <v>46050</v>
       </c>
       <c r="G248" t="s">
@@ -14048,7 +14022,7 @@
       <c r="E249" t="s">
         <v>1068</v>
       </c>
-      <c r="F249" s="2">
+      <c r="F249" s="1">
         <v>46050</v>
       </c>
       <c r="G249" t="s">
@@ -14058,7 +14032,7 @@
         <v>1353</v>
       </c>
       <c r="I249">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K249" t="s">
         <v>1357</v>
@@ -14086,7 +14060,7 @@
       <c r="E250" t="s">
         <v>1069</v>
       </c>
-      <c r="F250" s="2">
+      <c r="F250" s="1">
         <v>46063</v>
       </c>
       <c r="G250" t="s">
@@ -14124,7 +14098,7 @@
       <c r="E251" t="s">
         <v>1070</v>
       </c>
-      <c r="F251" s="2">
+      <c r="F251" s="1">
         <v>46063</v>
       </c>
       <c r="G251" t="s">
@@ -14153,7 +14127,7 @@
       <c r="E252" t="s">
         <v>1071</v>
       </c>
-      <c r="F252" s="2">
+      <c r="F252" s="1">
         <v>46063</v>
       </c>
       <c r="G252" t="s">
@@ -14182,7 +14156,7 @@
       <c r="E253" t="s">
         <v>1072</v>
       </c>
-      <c r="F253" s="2">
+      <c r="F253" s="1">
         <v>46063</v>
       </c>
       <c r="G253" t="s">
@@ -14192,7 +14166,7 @@
         <v>1353</v>
       </c>
       <c r="I253">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J253">
         <v>162</v>
@@ -14203,7 +14177,7 @@
       <c r="L253" t="s">
         <v>1395</v>
       </c>
-      <c r="N253" s="2">
+      <c r="N253" s="1">
         <v>46225</v>
       </c>
       <c r="Q253" t="b">
@@ -14226,7 +14200,7 @@
       <c r="E254" t="s">
         <v>1073</v>
       </c>
-      <c r="F254" s="2">
+      <c r="F254" s="1">
         <v>46063</v>
       </c>
       <c r="G254" t="s">
@@ -14236,7 +14210,7 @@
         <v>1353</v>
       </c>
       <c r="I254">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K254" t="s">
         <v>1360</v>
@@ -14264,7 +14238,7 @@
       <c r="E255" t="s">
         <v>1074</v>
       </c>
-      <c r="F255" s="2">
+      <c r="F255" s="1">
         <v>46063</v>
       </c>
       <c r="G255" t="s">
@@ -14274,7 +14248,7 @@
         <v>1353</v>
       </c>
       <c r="I255">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J255">
         <v>72</v>
@@ -14285,7 +14259,7 @@
       <c r="L255" t="s">
         <v>1388</v>
       </c>
-      <c r="N255" s="2">
+      <c r="N255" s="1">
         <v>46135</v>
       </c>
       <c r="Q255" t="b">
@@ -14308,7 +14282,7 @@
       <c r="E256" t="s">
         <v>1075</v>
       </c>
-      <c r="F256" s="2">
+      <c r="F256" s="1">
         <v>46063</v>
       </c>
       <c r="G256" t="s">
@@ -14318,7 +14292,7 @@
         <v>1353</v>
       </c>
       <c r="I256">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J256">
         <v>23</v>
@@ -14326,7 +14300,7 @@
       <c r="K256" t="s">
         <v>1357</v>
       </c>
-      <c r="N256" s="2">
+      <c r="N256" s="1">
         <v>46086</v>
       </c>
       <c r="O256">
@@ -14352,7 +14326,7 @@
       <c r="E257" t="s">
         <v>1076</v>
       </c>
-      <c r="F257" s="2">
+      <c r="F257" s="1">
         <v>46063</v>
       </c>
       <c r="G257" t="s">
@@ -14381,7 +14355,7 @@
       <c r="E258" t="s">
         <v>1077</v>
       </c>
-      <c r="F258" s="2">
+      <c r="F258" s="1">
         <v>46063</v>
       </c>
       <c r="G258" t="s">
@@ -14410,7 +14384,7 @@
       <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="F259" s="2">
+      <c r="F259" s="1">
         <v>46063</v>
       </c>
       <c r="G259" t="s">
@@ -14420,7 +14394,7 @@
         <v>1353</v>
       </c>
       <c r="I259">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J259">
         <v>72</v>
@@ -14431,7 +14405,7 @@
       <c r="L259" t="s">
         <v>1388</v>
       </c>
-      <c r="N259" s="2">
+      <c r="N259" s="1">
         <v>46135</v>
       </c>
       <c r="Q259" t="b">
@@ -14454,7 +14428,7 @@
       <c r="E260" t="s">
         <v>1079</v>
       </c>
-      <c r="F260" s="2">
+      <c r="F260" s="1">
         <v>46063</v>
       </c>
       <c r="G260" t="s">
@@ -14464,7 +14438,7 @@
         <v>1353</v>
       </c>
       <c r="I260">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J260">
         <v>84</v>
@@ -14475,7 +14449,7 @@
       <c r="L260" t="s">
         <v>1388</v>
       </c>
-      <c r="N260" s="2">
+      <c r="N260" s="1">
         <v>46147</v>
       </c>
       <c r="Q260" t="b">
@@ -14498,7 +14472,7 @@
       <c r="E261" t="s">
         <v>1080</v>
       </c>
-      <c r="F261" s="2">
+      <c r="F261" s="1">
         <v>46063</v>
       </c>
       <c r="G261" t="s">
@@ -14508,7 +14482,7 @@
         <v>1353</v>
       </c>
       <c r="I261">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J261">
         <v>162</v>
@@ -14519,7 +14493,7 @@
       <c r="L261" t="s">
         <v>1427</v>
       </c>
-      <c r="N261" s="2">
+      <c r="N261" s="1">
         <v>46225</v>
       </c>
       <c r="Q261" t="b">
@@ -14542,7 +14516,7 @@
       <c r="E262" t="s">
         <v>1081</v>
       </c>
-      <c r="F262" s="2">
+      <c r="F262" s="1">
         <v>46063</v>
       </c>
       <c r="G262" t="s">
@@ -14560,7 +14534,7 @@
       <c r="L262" t="s">
         <v>1428</v>
       </c>
-      <c r="N262" s="2">
+      <c r="N262" s="1">
         <v>46113</v>
       </c>
       <c r="P262" t="s">
@@ -14586,7 +14560,7 @@
       <c r="E263" t="s">
         <v>1082</v>
       </c>
-      <c r="F263" s="2">
+      <c r="F263" s="1">
         <v>46063</v>
       </c>
       <c r="G263" t="s">
@@ -14615,7 +14589,7 @@
       <c r="E264" t="s">
         <v>1083</v>
       </c>
-      <c r="F264" s="2">
+      <c r="F264" s="1">
         <v>46063</v>
       </c>
       <c r="G264" t="s">
@@ -14625,7 +14599,7 @@
         <v>1353</v>
       </c>
       <c r="I264">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J264">
         <v>162</v>
@@ -14636,7 +14610,7 @@
       <c r="L264" t="s">
         <v>1388</v>
       </c>
-      <c r="N264" s="2">
+      <c r="N264" s="1">
         <v>46225</v>
       </c>
       <c r="Q264" t="b">
@@ -14659,7 +14633,7 @@
       <c r="E265" t="s">
         <v>1084</v>
       </c>
-      <c r="F265" s="2">
+      <c r="F265" s="1">
         <v>46063</v>
       </c>
       <c r="G265" t="s">
@@ -14669,7 +14643,7 @@
         <v>1353</v>
       </c>
       <c r="I265">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J265">
         <v>162</v>
@@ -14680,7 +14654,7 @@
       <c r="L265" t="s">
         <v>1395</v>
       </c>
-      <c r="N265" s="2">
+      <c r="N265" s="1">
         <v>46225</v>
       </c>
       <c r="Q265" t="b">
@@ -14703,7 +14677,7 @@
       <c r="E266" t="s">
         <v>1085</v>
       </c>
-      <c r="F266" s="2">
+      <c r="F266" s="1">
         <v>46063</v>
       </c>
       <c r="G266" t="s">
@@ -14713,7 +14687,7 @@
         <v>1353</v>
       </c>
       <c r="I266">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J266">
         <v>84</v>
@@ -14724,7 +14698,7 @@
       <c r="L266" t="s">
         <v>1388</v>
       </c>
-      <c r="N266" s="2">
+      <c r="N266" s="1">
         <v>46147</v>
       </c>
       <c r="Q266" t="b">
@@ -14747,7 +14721,7 @@
       <c r="E267" t="s">
         <v>1086</v>
       </c>
-      <c r="F267" s="2">
+      <c r="F267" s="1">
         <v>46063</v>
       </c>
       <c r="G267" t="s">
@@ -14757,7 +14731,7 @@
         <v>1353</v>
       </c>
       <c r="I267">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K267" t="s">
         <v>1360</v>
@@ -14785,7 +14759,7 @@
       <c r="E268" t="s">
         <v>1087</v>
       </c>
-      <c r="F268" s="2">
+      <c r="F268" s="1">
         <v>46063</v>
       </c>
       <c r="G268" t="s">
@@ -14795,7 +14769,7 @@
         <v>1353</v>
       </c>
       <c r="I268">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K268" t="s">
         <v>1357</v>
@@ -14820,7 +14794,7 @@
       <c r="D269" t="s">
         <v>798</v>
       </c>
-      <c r="F269" s="2">
+      <c r="F269" s="1">
         <v>46063</v>
       </c>
       <c r="G269" t="s">
@@ -14830,7 +14804,7 @@
         <v>1353</v>
       </c>
       <c r="I269">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K269" t="s">
         <v>1357</v>
@@ -14858,7 +14832,7 @@
       <c r="E270" t="s">
         <v>1088</v>
       </c>
-      <c r="F270" s="2">
+      <c r="F270" s="1">
         <v>46063</v>
       </c>
       <c r="G270" t="s">
@@ -14868,7 +14842,7 @@
         <v>1353</v>
       </c>
       <c r="I270">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K270" t="s">
         <v>1360</v>
@@ -14896,7 +14870,7 @@
       <c r="E271" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="2">
+      <c r="F271" s="1">
         <v>46063</v>
       </c>
       <c r="G271" t="s">
@@ -14906,7 +14880,7 @@
         <v>1353</v>
       </c>
       <c r="I271">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K271" t="s">
         <v>1360</v>
@@ -14934,7 +14908,7 @@
       <c r="E272" t="s">
         <v>1090</v>
       </c>
-      <c r="F272" s="2">
+      <c r="F272" s="1">
         <v>46063</v>
       </c>
       <c r="G272" t="s">
@@ -14952,7 +14926,7 @@
       <c r="L272" t="s">
         <v>1429</v>
       </c>
-      <c r="N272" s="2">
+      <c r="N272" s="1">
         <v>46185</v>
       </c>
       <c r="O272" t="s">
@@ -14978,7 +14952,7 @@
       <c r="E273" t="s">
         <v>1091</v>
       </c>
-      <c r="F273" s="2">
+      <c r="F273" s="1">
         <v>46063</v>
       </c>
       <c r="G273" t="s">
@@ -15007,7 +14981,7 @@
       <c r="E274" t="s">
         <v>1092</v>
       </c>
-      <c r="F274" s="2">
+      <c r="F274" s="1">
         <v>46063</v>
       </c>
       <c r="G274" t="s">
@@ -15022,7 +14996,7 @@
       <c r="L274" t="s">
         <v>1383</v>
       </c>
-      <c r="N274" s="2">
+      <c r="N274" s="1">
         <v>46232</v>
       </c>
       <c r="Q274" t="b">
@@ -15045,7 +15019,7 @@
       <c r="E275" t="s">
         <v>1093</v>
       </c>
-      <c r="F275" s="2">
+      <c r="F275" s="1">
         <v>46063</v>
       </c>
       <c r="G275" t="s">
@@ -15074,7 +15048,7 @@
       <c r="E276" t="s">
         <v>1094</v>
       </c>
-      <c r="F276" s="2">
+      <c r="F276" s="1">
         <v>46063</v>
       </c>
       <c r="G276" t="s">
@@ -15084,7 +15058,7 @@
         <v>1353</v>
       </c>
       <c r="I276">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K276" t="s">
         <v>1361</v>
@@ -15112,7 +15086,7 @@
       <c r="E277" t="s">
         <v>1095</v>
       </c>
-      <c r="F277" s="2">
+      <c r="F277" s="1">
         <v>46063</v>
       </c>
       <c r="G277" t="s">
@@ -15122,7 +15096,7 @@
         <v>1353</v>
       </c>
       <c r="I277">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K277" t="s">
         <v>1357</v>
@@ -15150,7 +15124,7 @@
       <c r="E278" t="s">
         <v>1096</v>
       </c>
-      <c r="F278" s="2">
+      <c r="F278" s="1">
         <v>46077</v>
       </c>
       <c r="G278" t="s">
@@ -15160,7 +15134,7 @@
         <v>1353</v>
       </c>
       <c r="I278">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J278">
         <v>148</v>
@@ -15171,7 +15145,7 @@
       <c r="L278" t="s">
         <v>1395</v>
       </c>
-      <c r="N278" s="2">
+      <c r="N278" s="1">
         <v>46225</v>
       </c>
       <c r="Q278" t="b">
@@ -15194,7 +15168,7 @@
       <c r="E279" t="s">
         <v>1097</v>
       </c>
-      <c r="F279" s="2">
+      <c r="F279" s="1">
         <v>46077</v>
       </c>
       <c r="G279" t="s">
@@ -15204,7 +15178,7 @@
         <v>1353</v>
       </c>
       <c r="I279">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K279" t="s">
         <v>1359</v>
@@ -15235,7 +15209,7 @@
       <c r="E280" t="s">
         <v>1098</v>
       </c>
-      <c r="F280" s="2">
+      <c r="F280" s="1">
         <v>46085</v>
       </c>
       <c r="G280" t="s">
@@ -15245,7 +15219,7 @@
         <v>1353</v>
       </c>
       <c r="I280">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K280" t="s">
         <v>1357</v>
@@ -15273,7 +15247,7 @@
       <c r="E281" t="s">
         <v>1099</v>
       </c>
-      <c r="F281" s="2">
+      <c r="F281" s="1">
         <v>46085</v>
       </c>
       <c r="G281" t="s">
@@ -15283,7 +15257,7 @@
         <v>1353</v>
       </c>
       <c r="I281">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K281" t="s">
         <v>1357</v>
@@ -15314,7 +15288,7 @@
       <c r="E282" t="s">
         <v>1100</v>
       </c>
-      <c r="F282" s="2">
+      <c r="F282" s="1">
         <v>46090</v>
       </c>
       <c r="G282" t="s">
@@ -15324,7 +15298,7 @@
         <v>1353</v>
       </c>
       <c r="I282">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K282" t="s">
         <v>1357</v>
@@ -15352,7 +15326,7 @@
       <c r="E283" t="s">
         <v>1101</v>
       </c>
-      <c r="F283" s="2">
+      <c r="F283" s="1">
         <v>46100</v>
       </c>
       <c r="G283" t="s">
@@ -15381,7 +15355,7 @@
       <c r="E284" t="s">
         <v>1102</v>
       </c>
-      <c r="F284" s="2">
+      <c r="F284" s="1">
         <v>46100</v>
       </c>
       <c r="G284" t="s">
@@ -15410,7 +15384,7 @@
       <c r="E285" t="s">
         <v>1103</v>
       </c>
-      <c r="F285" s="2">
+      <c r="F285" s="1">
         <v>46100</v>
       </c>
       <c r="G285" t="s">
@@ -15439,7 +15413,7 @@
       <c r="E286" t="s">
         <v>1104</v>
       </c>
-      <c r="F286" s="2">
+      <c r="F286" s="1">
         <v>46100</v>
       </c>
       <c r="G286" t="s">
@@ -15468,7 +15442,7 @@
       <c r="E287" t="s">
         <v>1105</v>
       </c>
-      <c r="F287" s="2">
+      <c r="F287" s="1">
         <v>46107</v>
       </c>
       <c r="G287" t="s">
@@ -15497,7 +15471,7 @@
       <c r="E288" t="s">
         <v>1106</v>
       </c>
-      <c r="F288" s="2">
+      <c r="F288" s="1">
         <v>46107</v>
       </c>
       <c r="G288" t="s">
@@ -15507,7 +15481,7 @@
         <v>1353</v>
       </c>
       <c r="I288">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J288">
         <v>28</v>
@@ -15518,7 +15492,7 @@
       <c r="L288" t="s">
         <v>1388</v>
       </c>
-      <c r="N288" s="2">
+      <c r="N288" s="1">
         <v>46135</v>
       </c>
       <c r="Q288" t="b">
@@ -15541,7 +15515,7 @@
       <c r="E289" t="s">
         <v>1107</v>
       </c>
-      <c r="F289" s="2">
+      <c r="F289" s="1">
         <v>46107</v>
       </c>
       <c r="G289" t="s">
@@ -15570,7 +15544,7 @@
       <c r="E290" t="s">
         <v>1108</v>
       </c>
-      <c r="F290" s="2">
+      <c r="F290" s="1">
         <v>46107</v>
       </c>
       <c r="G290" t="s">
@@ -15580,7 +15554,7 @@
         <v>1353</v>
       </c>
       <c r="I290">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J290">
         <v>20</v>
@@ -15591,7 +15565,7 @@
       <c r="L290" t="s">
         <v>1388</v>
       </c>
-      <c r="N290" s="2">
+      <c r="N290" s="1">
         <v>46127</v>
       </c>
       <c r="Q290" t="b">
@@ -15614,7 +15588,7 @@
       <c r="E291" t="s">
         <v>1109</v>
       </c>
-      <c r="F291" s="2">
+      <c r="F291" s="1">
         <v>46107</v>
       </c>
       <c r="G291" t="s">
@@ -15624,7 +15598,7 @@
         <v>1353</v>
       </c>
       <c r="I291">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J291">
         <v>20</v>
@@ -15635,7 +15609,7 @@
       <c r="L291" t="s">
         <v>1430</v>
       </c>
-      <c r="N291" s="2">
+      <c r="N291" s="1">
         <v>46127</v>
       </c>
       <c r="Q291" t="b">
@@ -15658,7 +15632,7 @@
       <c r="E292" t="s">
         <v>1110</v>
       </c>
-      <c r="F292" s="2">
+      <c r="F292" s="1">
         <v>46112</v>
       </c>
       <c r="G292" t="s">
@@ -15668,7 +15642,7 @@
         <v>1353</v>
       </c>
       <c r="I292">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K292" t="s">
         <v>1360</v>
@@ -15696,7 +15670,7 @@
       <c r="E293" t="s">
         <v>1111</v>
       </c>
-      <c r="F293" s="2">
+      <c r="F293" s="1">
         <v>46125</v>
       </c>
       <c r="G293" t="s">
@@ -15706,7 +15680,7 @@
         <v>1353</v>
       </c>
       <c r="I293">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K293" t="s">
         <v>1361</v>
@@ -15734,7 +15708,7 @@
       <c r="E294" t="s">
         <v>1112</v>
       </c>
-      <c r="F294" s="2">
+      <c r="F294" s="1">
         <v>46125</v>
       </c>
       <c r="G294" t="s">
@@ -15744,7 +15718,7 @@
         <v>1353</v>
       </c>
       <c r="I294">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K294" t="s">
         <v>1366</v>
@@ -15769,7 +15743,7 @@
       <c r="E295" t="s">
         <v>1113</v>
       </c>
-      <c r="F295" s="2">
+      <c r="F295" s="1">
         <v>46125</v>
       </c>
       <c r="G295" t="s">
@@ -15779,7 +15753,7 @@
         <v>1353</v>
       </c>
       <c r="I295">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K295" t="s">
         <v>1366</v>
@@ -15804,7 +15778,7 @@
       <c r="E296" t="s">
         <v>1114</v>
       </c>
-      <c r="F296" s="2">
+      <c r="F296" s="1">
         <v>46125</v>
       </c>
       <c r="G296" t="s">
@@ -15814,7 +15788,7 @@
         <v>1353</v>
       </c>
       <c r="I296">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K296" t="s">
         <v>1366</v>
@@ -15839,7 +15813,7 @@
       <c r="E297" t="s">
         <v>1115</v>
       </c>
-      <c r="F297" s="2">
+      <c r="F297" s="1">
         <v>46125</v>
       </c>
       <c r="G297" t="s">
@@ -15851,7 +15825,7 @@
       <c r="K297" t="s">
         <v>1359</v>
       </c>
-      <c r="N297" s="2">
+      <c r="N297" s="1">
         <v>46183</v>
       </c>
       <c r="O297">
@@ -15877,7 +15851,7 @@
       <c r="E298" t="s">
         <v>1116</v>
       </c>
-      <c r="F298" s="2">
+      <c r="F298" s="1">
         <v>46125</v>
       </c>
       <c r="G298" t="s">
@@ -15887,7 +15861,7 @@
         <v>1353</v>
       </c>
       <c r="I298">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J298">
         <v>58</v>
@@ -15895,7 +15869,7 @@
       <c r="K298" t="s">
         <v>1359</v>
       </c>
-      <c r="N298" s="2">
+      <c r="N298" s="1">
         <v>46183</v>
       </c>
       <c r="Q298" t="b">
@@ -15918,7 +15892,7 @@
       <c r="E299" t="s">
         <v>1117</v>
       </c>
-      <c r="F299" s="2">
+      <c r="F299" s="1">
         <v>46125</v>
       </c>
       <c r="G299" t="s">
@@ -15928,7 +15902,7 @@
         <v>1353</v>
       </c>
       <c r="I299">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J299">
         <v>100</v>
@@ -15939,7 +15913,7 @@
       <c r="L299" t="s">
         <v>1388</v>
       </c>
-      <c r="N299" s="2">
+      <c r="N299" s="1">
         <v>46225</v>
       </c>
       <c r="Q299" t="b">
@@ -15962,7 +15936,7 @@
       <c r="E300" t="s">
         <v>1118</v>
       </c>
-      <c r="F300" s="2">
+      <c r="F300" s="1">
         <v>46125</v>
       </c>
       <c r="G300" t="s">
@@ -15972,7 +15946,7 @@
         <v>1353</v>
       </c>
       <c r="I300">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J300">
         <v>86</v>
@@ -15983,7 +15957,7 @@
       <c r="L300" t="s">
         <v>1388</v>
       </c>
-      <c r="N300" s="2">
+      <c r="N300" s="1">
         <v>46211</v>
       </c>
       <c r="Q300" t="b">
@@ -16006,7 +15980,7 @@
       <c r="E301" t="s">
         <v>1119</v>
       </c>
-      <c r="F301" s="2">
+      <c r="F301" s="1">
         <v>46125</v>
       </c>
       <c r="G301" t="s">
@@ -16016,7 +15990,7 @@
         <v>1353</v>
       </c>
       <c r="I301">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J301">
         <v>102</v>
@@ -16027,7 +16001,7 @@
       <c r="L301" t="s">
         <v>1388</v>
       </c>
-      <c r="N301" s="2">
+      <c r="N301" s="1">
         <v>46227</v>
       </c>
       <c r="Q301" t="b">
@@ -16050,7 +16024,7 @@
       <c r="E302" t="s">
         <v>1120</v>
       </c>
-      <c r="F302" s="2">
+      <c r="F302" s="1">
         <v>46125</v>
       </c>
       <c r="G302" t="s">
@@ -16060,7 +16034,7 @@
         <v>1353</v>
       </c>
       <c r="I302">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K302" t="s">
         <v>1360</v>
@@ -16088,7 +16062,7 @@
       <c r="E303" t="s">
         <v>1121</v>
       </c>
-      <c r="F303" s="2">
+      <c r="F303" s="1">
         <v>46125</v>
       </c>
       <c r="G303" t="s">
@@ -16098,7 +16072,7 @@
         <v>1353</v>
       </c>
       <c r="I303">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K303" t="s">
         <v>1357</v>
@@ -16126,7 +16100,7 @@
       <c r="E304" t="s">
         <v>1122</v>
       </c>
-      <c r="F304" s="2">
+      <c r="F304" s="1">
         <v>46125</v>
       </c>
       <c r="G304" t="s">
@@ -16136,7 +16110,7 @@
         <v>1353</v>
       </c>
       <c r="I304">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K304" t="s">
         <v>1360</v>
@@ -16164,7 +16138,7 @@
       <c r="E305" t="s">
         <v>1123</v>
       </c>
-      <c r="F305" s="2">
+      <c r="F305" s="1">
         <v>46125</v>
       </c>
       <c r="G305" t="s">
@@ -16174,7 +16148,7 @@
         <v>1353</v>
       </c>
       <c r="I305">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J305">
         <v>35</v>
@@ -16185,7 +16159,7 @@
       <c r="L305" t="s">
         <v>1431</v>
       </c>
-      <c r="N305" s="2">
+      <c r="N305" s="1">
         <v>46160</v>
       </c>
       <c r="Q305" t="b">
@@ -16208,7 +16182,7 @@
       <c r="E306" t="s">
         <v>1124</v>
       </c>
-      <c r="F306" s="2">
+      <c r="F306" s="1">
         <v>46125</v>
       </c>
       <c r="G306" t="s">
@@ -16218,7 +16192,7 @@
         <v>1353</v>
       </c>
       <c r="I306">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J306">
         <v>31</v>
@@ -16229,7 +16203,7 @@
       <c r="L306" t="s">
         <v>1432</v>
       </c>
-      <c r="N306" s="2">
+      <c r="N306" s="1">
         <v>46156</v>
       </c>
       <c r="Q306" t="b">
@@ -16252,7 +16226,7 @@
       <c r="E307" t="s">
         <v>1125</v>
       </c>
-      <c r="F307" s="2">
+      <c r="F307" s="1">
         <v>46125</v>
       </c>
       <c r="G307" t="s">
@@ -16270,7 +16244,7 @@
       <c r="L307" t="s">
         <v>1433</v>
       </c>
-      <c r="N307" s="2">
+      <c r="N307" s="1">
         <v>46209</v>
       </c>
       <c r="P307" t="s">
@@ -16296,7 +16270,7 @@
       <c r="E308" t="s">
         <v>1126</v>
       </c>
-      <c r="F308" s="2">
+      <c r="F308" s="1">
         <v>46125</v>
       </c>
       <c r="G308" t="s">
@@ -16306,7 +16280,7 @@
         <v>1353</v>
       </c>
       <c r="I308">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K308" t="s">
         <v>1356</v>
@@ -16334,7 +16308,7 @@
       <c r="E309" t="s">
         <v>1127</v>
       </c>
-      <c r="F309" s="2">
+      <c r="F309" s="1">
         <v>46125</v>
       </c>
       <c r="G309" t="s">
@@ -16349,7 +16323,7 @@
       <c r="L309" t="s">
         <v>1383</v>
       </c>
-      <c r="N309" s="2">
+      <c r="N309" s="1">
         <v>46232</v>
       </c>
       <c r="Q309" t="b">
@@ -16372,7 +16346,7 @@
       <c r="E310" t="s">
         <v>1128</v>
       </c>
-      <c r="F310" s="2">
+      <c r="F310" s="1">
         <v>46125</v>
       </c>
       <c r="G310" t="s">
@@ -16382,7 +16356,7 @@
         <v>1353</v>
       </c>
       <c r="I310">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J310">
         <v>107</v>
@@ -16393,7 +16367,7 @@
       <c r="L310" t="s">
         <v>1383</v>
       </c>
-      <c r="N310" s="2">
+      <c r="N310" s="1">
         <v>46232</v>
       </c>
       <c r="Q310" t="b">
@@ -16416,7 +16390,7 @@
       <c r="E311" t="s">
         <v>1129</v>
       </c>
-      <c r="F311" s="2">
+      <c r="F311" s="1">
         <v>46125</v>
       </c>
       <c r="G311" t="s">
@@ -16426,7 +16400,7 @@
         <v>1353</v>
       </c>
       <c r="I311">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K311" t="s">
         <v>1356</v>
@@ -16454,7 +16428,7 @@
       <c r="E312" t="s">
         <v>1130</v>
       </c>
-      <c r="F312" s="2">
+      <c r="F312" s="1">
         <v>46125</v>
       </c>
       <c r="G312" t="s">
@@ -16472,7 +16446,7 @@
       <c r="L312" t="s">
         <v>1383</v>
       </c>
-      <c r="N312" s="2">
+      <c r="N312" s="1">
         <v>46232</v>
       </c>
       <c r="Q312" t="b">
@@ -16495,7 +16469,7 @@
       <c r="E313" t="s">
         <v>1131</v>
       </c>
-      <c r="F313" s="2">
+      <c r="F313" s="1">
         <v>46125</v>
       </c>
       <c r="G313" t="s">
@@ -16530,7 +16504,7 @@
       <c r="E314" t="s">
         <v>1132</v>
       </c>
-      <c r="F314" s="2">
+      <c r="F314" s="1">
         <v>46125</v>
       </c>
       <c r="G314" t="s">
@@ -16545,7 +16519,7 @@
       <c r="L314" t="s">
         <v>1383</v>
       </c>
-      <c r="N314" s="2">
+      <c r="N314" s="1">
         <v>46232</v>
       </c>
       <c r="Q314" t="b">
@@ -16568,7 +16542,7 @@
       <c r="E315" t="s">
         <v>1133</v>
       </c>
-      <c r="F315" s="2">
+      <c r="F315" s="1">
         <v>46125</v>
       </c>
       <c r="G315" t="s">
@@ -16583,7 +16557,7 @@
       <c r="L315" t="s">
         <v>1383</v>
       </c>
-      <c r="N315" s="2">
+      <c r="N315" s="1">
         <v>46232</v>
       </c>
       <c r="Q315" t="b">
@@ -16606,7 +16580,7 @@
       <c r="E316" t="s">
         <v>1134</v>
       </c>
-      <c r="F316" s="2">
+      <c r="F316" s="1">
         <v>46125</v>
       </c>
       <c r="G316" t="s">
@@ -16616,7 +16590,7 @@
         <v>1353</v>
       </c>
       <c r="I316">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K316" t="s">
         <v>1357</v>
@@ -16644,7 +16618,7 @@
       <c r="E317" t="s">
         <v>1135</v>
       </c>
-      <c r="F317" s="2">
+      <c r="F317" s="1">
         <v>46125</v>
       </c>
       <c r="G317" t="s">
@@ -16679,7 +16653,7 @@
       <c r="E318" t="s">
         <v>1136</v>
       </c>
-      <c r="F318" s="2">
+      <c r="F318" s="1">
         <v>46125</v>
       </c>
       <c r="G318" t="s">
@@ -16708,7 +16682,7 @@
       <c r="E319" t="s">
         <v>1137</v>
       </c>
-      <c r="F319" s="2">
+      <c r="F319" s="1">
         <v>46125</v>
       </c>
       <c r="G319" t="s">
@@ -16723,7 +16697,7 @@
       <c r="L319" t="s">
         <v>1434</v>
       </c>
-      <c r="N319" s="2">
+      <c r="N319" s="1">
         <v>46175</v>
       </c>
       <c r="Q319" t="b">
@@ -16746,7 +16720,7 @@
       <c r="E320" t="s">
         <v>1138</v>
       </c>
-      <c r="F320" s="2">
+      <c r="F320" s="1">
         <v>46125</v>
       </c>
       <c r="G320" t="s">
@@ -16756,7 +16730,7 @@
         <v>1353</v>
       </c>
       <c r="I320">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K320" t="s">
         <v>1361</v>
@@ -16784,7 +16758,7 @@
       <c r="E321" t="s">
         <v>1139</v>
       </c>
-      <c r="F321" s="2">
+      <c r="F321" s="1">
         <v>46125</v>
       </c>
       <c r="G321" t="s">
@@ -16794,7 +16768,7 @@
         <v>1353</v>
       </c>
       <c r="I321">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K321" t="s">
         <v>1357</v>
@@ -16822,7 +16796,7 @@
       <c r="E322" t="s">
         <v>1140</v>
       </c>
-      <c r="F322" s="2">
+      <c r="F322" s="1">
         <v>46125</v>
       </c>
       <c r="G322" t="s">
@@ -16832,7 +16806,7 @@
         <v>1353</v>
       </c>
       <c r="I322">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J322">
         <v>57</v>
@@ -16843,7 +16817,7 @@
       <c r="L322" t="s">
         <v>1435</v>
       </c>
-      <c r="N322" s="2">
+      <c r="N322" s="1">
         <v>46182</v>
       </c>
       <c r="Q322" t="b">
@@ -16866,7 +16840,7 @@
       <c r="E323" t="s">
         <v>1141</v>
       </c>
-      <c r="F323" s="2">
+      <c r="F323" s="1">
         <v>46125</v>
       </c>
       <c r="G323" t="s">
@@ -16901,7 +16875,7 @@
       <c r="E324" t="s">
         <v>1142</v>
       </c>
-      <c r="F324" s="2">
+      <c r="F324" s="1">
         <v>46125</v>
       </c>
       <c r="G324" t="s">
@@ -16936,7 +16910,7 @@
       <c r="E325" t="s">
         <v>1143</v>
       </c>
-      <c r="F325" s="2">
+      <c r="F325" s="1">
         <v>46125</v>
       </c>
       <c r="G325" t="s">
@@ -16946,7 +16920,7 @@
         <v>1353</v>
       </c>
       <c r="I325">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J325">
         <v>57</v>
@@ -16957,7 +16931,7 @@
       <c r="L325" t="s">
         <v>1435</v>
       </c>
-      <c r="N325" s="2">
+      <c r="N325" s="1">
         <v>46182</v>
       </c>
       <c r="Q325" t="b">
@@ -16980,7 +16954,7 @@
       <c r="E326" t="s">
         <v>1144</v>
       </c>
-      <c r="F326" s="2">
+      <c r="F326" s="1">
         <v>46125</v>
       </c>
       <c r="G326" t="s">
@@ -16995,7 +16969,7 @@
       <c r="L326" t="s">
         <v>1383</v>
       </c>
-      <c r="N326" s="2">
+      <c r="N326" s="1">
         <v>46232</v>
       </c>
       <c r="Q326" t="b">
@@ -17018,7 +16992,7 @@
       <c r="E327" t="s">
         <v>1140</v>
       </c>
-      <c r="F327" s="2">
+      <c r="F327" s="1">
         <v>46125</v>
       </c>
       <c r="G327" t="s">
@@ -17028,7 +17002,7 @@
         <v>1353</v>
       </c>
       <c r="I327">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J327">
         <v>57</v>
@@ -17039,7 +17013,7 @@
       <c r="L327" t="s">
         <v>1435</v>
       </c>
-      <c r="N327" s="2">
+      <c r="N327" s="1">
         <v>46182</v>
       </c>
       <c r="Q327" t="b">
@@ -17062,7 +17036,7 @@
       <c r="E328" t="s">
         <v>1145</v>
       </c>
-      <c r="F328" s="2">
+      <c r="F328" s="1">
         <v>46125</v>
       </c>
       <c r="G328" t="s">
@@ -17072,7 +17046,7 @@
         <v>1353</v>
       </c>
       <c r="I328">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J328">
         <v>57</v>
@@ -17083,7 +17057,7 @@
       <c r="L328" t="s">
         <v>1435</v>
       </c>
-      <c r="N328" s="2">
+      <c r="N328" s="1">
         <v>46182</v>
       </c>
       <c r="Q328" t="b">
@@ -17106,7 +17080,7 @@
       <c r="E329" t="s">
         <v>1146</v>
       </c>
-      <c r="F329" s="2">
+      <c r="F329" s="1">
         <v>46125</v>
       </c>
       <c r="G329" t="s">
@@ -17116,7 +17090,7 @@
         <v>1353</v>
       </c>
       <c r="I329">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J329">
         <v>57</v>
@@ -17127,7 +17101,7 @@
       <c r="L329" t="s">
         <v>1435</v>
       </c>
-      <c r="N329" s="2">
+      <c r="N329" s="1">
         <v>46182</v>
       </c>
       <c r="Q329" t="b">
@@ -17150,7 +17124,7 @@
       <c r="E330" t="s">
         <v>1147</v>
       </c>
-      <c r="F330" s="2">
+      <c r="F330" s="1">
         <v>46125</v>
       </c>
       <c r="G330" t="s">
@@ -17160,7 +17134,7 @@
         <v>1353</v>
       </c>
       <c r="I330">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J330">
         <v>57</v>
@@ -17171,7 +17145,7 @@
       <c r="L330" t="s">
         <v>1435</v>
       </c>
-      <c r="N330" s="2">
+      <c r="N330" s="1">
         <v>46182</v>
       </c>
       <c r="Q330" t="b">
@@ -17194,7 +17168,7 @@
       <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="F331" s="2">
+      <c r="F331" s="1">
         <v>46125</v>
       </c>
       <c r="G331" t="s">
@@ -17204,7 +17178,7 @@
         <v>1353</v>
       </c>
       <c r="I331">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K331" t="s">
         <v>1356</v>
@@ -17232,7 +17206,7 @@
       <c r="E332" t="s">
         <v>1148</v>
       </c>
-      <c r="F332" s="2">
+      <c r="F332" s="1">
         <v>46125</v>
       </c>
       <c r="G332" t="s">
@@ -17242,7 +17216,7 @@
         <v>1353</v>
       </c>
       <c r="I332">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K332" t="s">
         <v>1357</v>
@@ -17270,7 +17244,7 @@
       <c r="E333" t="s">
         <v>910</v>
       </c>
-      <c r="F333" s="2">
+      <c r="F333" s="1">
         <v>46125</v>
       </c>
       <c r="G333" t="s">
@@ -17280,7 +17254,7 @@
         <v>1353</v>
       </c>
       <c r="I333">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J333">
         <v>100</v>
@@ -17291,7 +17265,7 @@
       <c r="L333" t="s">
         <v>1395</v>
       </c>
-      <c r="N333" s="2">
+      <c r="N333" s="1">
         <v>46225</v>
       </c>
       <c r="Q333" t="b">
@@ -17314,7 +17288,7 @@
       <c r="E334" t="s">
         <v>1149</v>
       </c>
-      <c r="F334" s="2">
+      <c r="F334" s="1">
         <v>46125</v>
       </c>
       <c r="G334" t="s">
@@ -17324,7 +17298,7 @@
         <v>1353</v>
       </c>
       <c r="I334">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K334" t="s">
         <v>1357</v>
@@ -17352,7 +17326,7 @@
       <c r="E335" t="s">
         <v>1150</v>
       </c>
-      <c r="F335" s="2">
+      <c r="F335" s="1">
         <v>46127</v>
       </c>
       <c r="G335" t="s">
@@ -17367,7 +17341,7 @@
       <c r="L335" t="s">
         <v>1434</v>
       </c>
-      <c r="N335" s="2">
+      <c r="N335" s="1">
         <v>46175</v>
       </c>
       <c r="Q335" t="b">
@@ -17390,7 +17364,7 @@
       <c r="E336" t="s">
         <v>1151</v>
       </c>
-      <c r="F336" s="2">
+      <c r="F336" s="1">
         <v>46127</v>
       </c>
       <c r="G336" t="s">
@@ -17400,7 +17374,7 @@
         <v>1353</v>
       </c>
       <c r="I336">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J336">
         <v>28</v>
@@ -17411,7 +17385,7 @@
       <c r="L336" t="s">
         <v>1388</v>
       </c>
-      <c r="N336" s="2">
+      <c r="N336" s="1">
         <v>46155</v>
       </c>
       <c r="Q336" t="b">
@@ -17434,7 +17408,7 @@
       <c r="E337" t="s">
         <v>1152</v>
       </c>
-      <c r="F337" s="2">
+      <c r="F337" s="1">
         <v>46127</v>
       </c>
       <c r="G337" t="s">
@@ -17449,7 +17423,7 @@
       <c r="L337" t="s">
         <v>1434</v>
       </c>
-      <c r="N337" s="2">
+      <c r="N337" s="1">
         <v>46175</v>
       </c>
       <c r="Q337" t="b">
@@ -17472,7 +17446,7 @@
       <c r="E338" t="s">
         <v>1153</v>
       </c>
-      <c r="F338" s="2">
+      <c r="F338" s="1">
         <v>46127</v>
       </c>
       <c r="G338" t="s">
@@ -17482,7 +17456,7 @@
         <v>1353</v>
       </c>
       <c r="I338">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J338">
         <v>12</v>
@@ -17493,7 +17467,7 @@
       <c r="L338" t="s">
         <v>1388</v>
       </c>
-      <c r="N338" s="2">
+      <c r="N338" s="1">
         <v>46139</v>
       </c>
       <c r="Q338" t="b">
@@ -17516,7 +17490,7 @@
       <c r="E339" t="s">
         <v>1154</v>
       </c>
-      <c r="F339" s="2">
+      <c r="F339" s="1">
         <v>46129</v>
       </c>
       <c r="G339" t="s">
@@ -17545,7 +17519,7 @@
       <c r="E340" t="s">
         <v>1155</v>
       </c>
-      <c r="F340" s="2">
+      <c r="F340" s="1">
         <v>46142</v>
       </c>
       <c r="G340" t="s">
@@ -17555,7 +17529,7 @@
         <v>1353</v>
       </c>
       <c r="I340">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J340">
         <v>98</v>
@@ -17563,7 +17537,7 @@
       <c r="L340" t="s">
         <v>1383</v>
       </c>
-      <c r="N340" s="2">
+      <c r="N340" s="1">
         <v>46240</v>
       </c>
       <c r="Q340" t="b">
@@ -17586,7 +17560,7 @@
       <c r="E341" t="s">
         <v>1156</v>
       </c>
-      <c r="F341" s="2">
+      <c r="F341" s="1">
         <v>46142</v>
       </c>
       <c r="G341" t="s">
@@ -17596,7 +17570,7 @@
         <v>1353</v>
       </c>
       <c r="I341">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J341">
         <v>90</v>
@@ -17604,7 +17578,7 @@
       <c r="L341" t="s">
         <v>1383</v>
       </c>
-      <c r="N341" s="2">
+      <c r="N341" s="1">
         <v>46232</v>
       </c>
       <c r="Q341" t="b">
@@ -17627,7 +17601,7 @@
       <c r="E342" t="s">
         <v>1157</v>
       </c>
-      <c r="F342" s="2">
+      <c r="F342" s="1">
         <v>46142</v>
       </c>
       <c r="G342" t="s">
@@ -17637,7 +17611,7 @@
         <v>1353</v>
       </c>
       <c r="I342">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K342" t="s">
         <v>1356</v>
@@ -17665,7 +17639,7 @@
       <c r="E343" t="s">
         <v>1158</v>
       </c>
-      <c r="F343" s="2">
+      <c r="F343" s="1">
         <v>46142</v>
       </c>
       <c r="G343" t="s">
@@ -17680,7 +17654,7 @@
       <c r="L343" t="s">
         <v>1383</v>
       </c>
-      <c r="N343" s="2">
+      <c r="N343" s="1">
         <v>46232</v>
       </c>
       <c r="Q343" t="b">
@@ -17703,7 +17677,7 @@
       <c r="E344" t="s">
         <v>1159</v>
       </c>
-      <c r="F344" s="2">
+      <c r="F344" s="1">
         <v>46142</v>
       </c>
       <c r="G344" t="s">
@@ -17718,7 +17692,7 @@
       <c r="L344" t="s">
         <v>1383</v>
       </c>
-      <c r="N344" s="2">
+      <c r="N344" s="1">
         <v>46232</v>
       </c>
       <c r="Q344" t="b">
@@ -17741,7 +17715,7 @@
       <c r="E345" t="s">
         <v>1160</v>
       </c>
-      <c r="F345" s="2">
+      <c r="F345" s="1">
         <v>46142</v>
       </c>
       <c r="G345" t="s">
@@ -17751,7 +17725,7 @@
         <v>1353</v>
       </c>
       <c r="I345">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K345" t="s">
         <v>1356</v>
@@ -17779,7 +17753,7 @@
       <c r="E346" t="s">
         <v>1161</v>
       </c>
-      <c r="F346" s="2">
+      <c r="F346" s="1">
         <v>46142</v>
       </c>
       <c r="G346" t="s">
@@ -17794,7 +17768,7 @@
       <c r="L346" t="s">
         <v>1383</v>
       </c>
-      <c r="N346" s="2">
+      <c r="N346" s="1">
         <v>46232</v>
       </c>
       <c r="Q346" t="b">
@@ -17817,7 +17791,7 @@
       <c r="E347" t="s">
         <v>1162</v>
       </c>
-      <c r="F347" s="2">
+      <c r="F347" s="1">
         <v>46142</v>
       </c>
       <c r="G347" t="s">
@@ -17827,7 +17801,7 @@
         <v>1353</v>
       </c>
       <c r="I347">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J347">
         <v>18</v>
@@ -17838,7 +17812,7 @@
       <c r="L347" t="s">
         <v>1431</v>
       </c>
-      <c r="N347" s="2">
+      <c r="N347" s="1">
         <v>46160</v>
       </c>
       <c r="Q347" t="b">
@@ -17861,7 +17835,7 @@
       <c r="E348" t="s">
         <v>1163</v>
       </c>
-      <c r="F348" s="2">
+      <c r="F348" s="1">
         <v>46142</v>
       </c>
       <c r="G348" t="s">
@@ -17871,7 +17845,7 @@
         <v>1353</v>
       </c>
       <c r="I348">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J348">
         <v>14</v>
@@ -17882,7 +17856,7 @@
       <c r="L348" t="s">
         <v>1432</v>
       </c>
-      <c r="N348" s="2">
+      <c r="N348" s="1">
         <v>46156</v>
       </c>
       <c r="Q348" t="b">
@@ -17905,7 +17879,7 @@
       <c r="E349" t="s">
         <v>1164</v>
       </c>
-      <c r="F349" s="2">
+      <c r="F349" s="1">
         <v>46142</v>
       </c>
       <c r="G349" t="s">
@@ -17915,7 +17889,7 @@
         <v>1353</v>
       </c>
       <c r="I349">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K349" t="s">
         <v>1361</v>
@@ -17943,7 +17917,7 @@
       <c r="E350" t="s">
         <v>1165</v>
       </c>
-      <c r="F350" s="2">
+      <c r="F350" s="1">
         <v>46142</v>
       </c>
       <c r="G350" t="s">
@@ -17953,12 +17927,12 @@
         <v>1353</v>
       </c>
       <c r="I350">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J350">
         <v>46</v>
       </c>
-      <c r="N350" s="2">
+      <c r="N350" s="1">
         <v>46188</v>
       </c>
       <c r="Q350" t="b">
@@ -17981,7 +17955,7 @@
       <c r="E351" t="s">
         <v>1166</v>
       </c>
-      <c r="F351" s="2">
+      <c r="F351" s="1">
         <v>46142</v>
       </c>
       <c r="G351" t="s">
@@ -17991,7 +17965,7 @@
         <v>1353</v>
       </c>
       <c r="I351">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J351">
         <v>82</v>
@@ -18002,7 +17976,7 @@
       <c r="L351" t="s">
         <v>1436</v>
       </c>
-      <c r="N351" s="2">
+      <c r="N351" s="1">
         <v>46224</v>
       </c>
       <c r="Q351" t="b">
@@ -18025,7 +17999,7 @@
       <c r="E352" t="s">
         <v>1167</v>
       </c>
-      <c r="F352" s="2">
+      <c r="F352" s="1">
         <v>46142</v>
       </c>
       <c r="G352" t="s">
@@ -18035,7 +18009,7 @@
         <v>1353</v>
       </c>
       <c r="I352">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J352">
         <v>78</v>
@@ -18046,7 +18020,7 @@
       <c r="L352" t="s">
         <v>1437</v>
       </c>
-      <c r="N352" s="2">
+      <c r="N352" s="1">
         <v>46220</v>
       </c>
       <c r="Q352" t="b">
@@ -18069,7 +18043,7 @@
       <c r="E353" t="s">
         <v>1168</v>
       </c>
-      <c r="F353" s="2">
+      <c r="F353" s="1">
         <v>46142</v>
       </c>
       <c r="G353" t="s">
@@ -18079,7 +18053,7 @@
         <v>1353</v>
       </c>
       <c r="I353">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J353">
         <v>83</v>
@@ -18090,7 +18064,7 @@
       <c r="L353" t="s">
         <v>1395</v>
       </c>
-      <c r="N353" s="2">
+      <c r="N353" s="1">
         <v>46225</v>
       </c>
       <c r="Q353" t="b">
@@ -18113,7 +18087,7 @@
       <c r="E354" t="s">
         <v>1169</v>
       </c>
-      <c r="F354" s="2">
+      <c r="F354" s="1">
         <v>46142</v>
       </c>
       <c r="G354" t="s">
@@ -18123,7 +18097,7 @@
         <v>1353</v>
       </c>
       <c r="I354">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K354" t="s">
         <v>1360</v>
@@ -18151,7 +18125,7 @@
       <c r="E355" t="s">
         <v>1170</v>
       </c>
-      <c r="F355" s="2">
+      <c r="F355" s="1">
         <v>46142</v>
       </c>
       <c r="G355" t="s">
@@ -18161,7 +18135,7 @@
         <v>1353</v>
       </c>
       <c r="I355">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J355">
         <v>8</v>
@@ -18172,7 +18146,7 @@
       <c r="L355" t="s">
         <v>1438</v>
       </c>
-      <c r="N355" s="2">
+      <c r="N355" s="1">
         <v>46150</v>
       </c>
       <c r="Q355" t="b">
@@ -18195,7 +18169,7 @@
       <c r="E356" t="s">
         <v>1171</v>
       </c>
-      <c r="F356" s="2">
+      <c r="F356" s="1">
         <v>46142</v>
       </c>
       <c r="G356" t="s">
@@ -18210,7 +18184,7 @@
       <c r="L356" t="s">
         <v>1439</v>
       </c>
-      <c r="N356" s="2">
+      <c r="N356" s="1">
         <v>46176</v>
       </c>
       <c r="Q356" t="b">
@@ -18233,7 +18207,7 @@
       <c r="E357" t="s">
         <v>1172</v>
       </c>
-      <c r="F357" s="2">
+      <c r="F357" s="1">
         <v>46142</v>
       </c>
       <c r="G357" t="s">
@@ -18243,7 +18217,7 @@
         <v>1353</v>
       </c>
       <c r="I357">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J357">
         <v>85</v>
@@ -18251,7 +18225,7 @@
       <c r="K357" t="s">
         <v>1360</v>
       </c>
-      <c r="N357" s="2">
+      <c r="N357" s="1">
         <v>46227</v>
       </c>
       <c r="Q357" t="b">
@@ -18274,7 +18248,7 @@
       <c r="E358" t="s">
         <v>1173</v>
       </c>
-      <c r="F358" s="2">
+      <c r="F358" s="1">
         <v>46142</v>
       </c>
       <c r="G358" t="s">
@@ -18292,7 +18266,7 @@
       <c r="L358" t="s">
         <v>1440</v>
       </c>
-      <c r="N358" s="2">
+      <c r="N358" s="1">
         <v>46227</v>
       </c>
       <c r="P358" t="s">
@@ -18318,7 +18292,7 @@
       <c r="E359" t="s">
         <v>1174</v>
       </c>
-      <c r="F359" s="2">
+      <c r="F359" s="1">
         <v>46142</v>
       </c>
       <c r="G359" t="s">
@@ -18330,7 +18304,7 @@
       <c r="J359">
         <v>63</v>
       </c>
-      <c r="N359" s="2">
+      <c r="N359" s="1">
         <v>46205</v>
       </c>
       <c r="P359" t="s">
@@ -18356,7 +18330,7 @@
       <c r="E360" t="s">
         <v>949</v>
       </c>
-      <c r="F360" s="2">
+      <c r="F360" s="1">
         <v>46142</v>
       </c>
       <c r="G360" t="s">
@@ -18366,7 +18340,7 @@
         <v>1353</v>
       </c>
       <c r="I360">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J360">
         <v>83</v>
@@ -18377,7 +18351,7 @@
       <c r="L360" t="s">
         <v>1395</v>
       </c>
-      <c r="N360" s="2">
+      <c r="N360" s="1">
         <v>46225</v>
       </c>
       <c r="O360" t="s">
@@ -18403,7 +18377,7 @@
       <c r="E361" t="s">
         <v>961</v>
       </c>
-      <c r="F361" s="2">
+      <c r="F361" s="1">
         <v>46142</v>
       </c>
       <c r="G361" t="s">
@@ -18413,7 +18387,7 @@
         <v>1353</v>
       </c>
       <c r="I361">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J361">
         <v>83</v>
@@ -18424,7 +18398,7 @@
       <c r="L361" t="s">
         <v>1395</v>
       </c>
-      <c r="N361" s="2">
+      <c r="N361" s="1">
         <v>46225</v>
       </c>
       <c r="Q361" t="b">
@@ -18447,7 +18421,7 @@
       <c r="E362" t="s">
         <v>1175</v>
       </c>
-      <c r="F362" s="2">
+      <c r="F362" s="1">
         <v>46142</v>
       </c>
       <c r="G362" t="s">
@@ -18457,7 +18431,7 @@
         <v>1353</v>
       </c>
       <c r="I362">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K362" t="s">
         <v>1360</v>
@@ -18485,7 +18459,7 @@
       <c r="E363" t="s">
         <v>1176</v>
       </c>
-      <c r="F363" s="2">
+      <c r="F363" s="1">
         <v>46142</v>
       </c>
       <c r="G363" t="s">
@@ -18495,7 +18469,7 @@
         <v>1353</v>
       </c>
       <c r="I363">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K363" t="s">
         <v>1360</v>
@@ -18523,7 +18497,7 @@
       <c r="E364" t="s">
         <v>958</v>
       </c>
-      <c r="F364" s="2">
+      <c r="F364" s="1">
         <v>46142</v>
       </c>
       <c r="G364" t="s">
@@ -18533,7 +18507,7 @@
         <v>1353</v>
       </c>
       <c r="I364">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J364">
         <v>83</v>
@@ -18544,7 +18518,7 @@
       <c r="L364" t="s">
         <v>1395</v>
       </c>
-      <c r="N364" s="2">
+      <c r="N364" s="1">
         <v>46225</v>
       </c>
       <c r="Q364" t="b">
@@ -18567,7 +18541,7 @@
       <c r="E365" t="s">
         <v>1177</v>
       </c>
-      <c r="F365" s="2">
+      <c r="F365" s="1">
         <v>46142</v>
       </c>
       <c r="G365" t="s">
@@ -18577,7 +18551,7 @@
         <v>1353</v>
       </c>
       <c r="I365">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J365">
         <v>15</v>
@@ -18585,7 +18559,7 @@
       <c r="K365" t="s">
         <v>1359</v>
       </c>
-      <c r="N365" s="2">
+      <c r="N365" s="1">
         <v>46157</v>
       </c>
       <c r="Q365" t="b">
@@ -18608,7 +18582,7 @@
       <c r="E366" t="s">
         <v>1178</v>
       </c>
-      <c r="F366" s="2">
+      <c r="F366" s="1">
         <v>46148</v>
       </c>
       <c r="G366" t="s">
@@ -18618,7 +18592,7 @@
         <v>1353</v>
       </c>
       <c r="I366">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J366">
         <v>77</v>
@@ -18629,7 +18603,7 @@
       <c r="L366" t="s">
         <v>1388</v>
       </c>
-      <c r="N366" s="2">
+      <c r="N366" s="1">
         <v>46225</v>
       </c>
       <c r="Q366" t="b">
@@ -18652,7 +18626,7 @@
       <c r="E367" t="s">
         <v>1179</v>
       </c>
-      <c r="F367" s="2">
+      <c r="F367" s="1">
         <v>46148</v>
       </c>
       <c r="G367" t="s">
@@ -18662,7 +18636,7 @@
         <v>1353</v>
       </c>
       <c r="I367">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J367">
         <v>77</v>
@@ -18673,7 +18647,7 @@
       <c r="L367" t="s">
         <v>1388</v>
       </c>
-      <c r="N367" s="2">
+      <c r="N367" s="1">
         <v>46225</v>
       </c>
       <c r="Q367" t="b">
@@ -18696,7 +18670,7 @@
       <c r="E368" t="s">
         <v>1180</v>
       </c>
-      <c r="F368" s="2">
+      <c r="F368" s="1">
         <v>46148</v>
       </c>
       <c r="G368" t="s">
@@ -18706,7 +18680,7 @@
         <v>1353</v>
       </c>
       <c r="I368">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J368">
         <v>77</v>
@@ -18717,7 +18691,7 @@
       <c r="L368" t="s">
         <v>1395</v>
       </c>
-      <c r="N368" s="2">
+      <c r="N368" s="1">
         <v>46225</v>
       </c>
       <c r="Q368" t="b">
@@ -18740,7 +18714,7 @@
       <c r="E369" t="s">
         <v>1181</v>
       </c>
-      <c r="F369" s="2">
+      <c r="F369" s="1">
         <v>46148</v>
       </c>
       <c r="G369" t="s">
@@ -18750,7 +18724,7 @@
         <v>1353</v>
       </c>
       <c r="I369">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K369" t="s">
         <v>1360</v>
@@ -18778,7 +18752,7 @@
       <c r="E370" t="s">
         <v>1182</v>
       </c>
-      <c r="F370" s="2">
+      <c r="F370" s="1">
         <v>46148</v>
       </c>
       <c r="G370" t="s">
@@ -18788,7 +18762,7 @@
         <v>1353</v>
       </c>
       <c r="I370">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K370" t="s">
         <v>1360</v>
@@ -18816,7 +18790,7 @@
       <c r="E371" t="s">
         <v>1183</v>
       </c>
-      <c r="F371" s="2">
+      <c r="F371" s="1">
         <v>46148</v>
       </c>
       <c r="G371" t="s">
@@ -18826,7 +18800,7 @@
         <v>1353</v>
       </c>
       <c r="I371">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J371">
         <v>16</v>
@@ -18837,7 +18811,7 @@
       <c r="L371" t="s">
         <v>1441</v>
       </c>
-      <c r="N371" s="2">
+      <c r="N371" s="1">
         <v>46164</v>
       </c>
       <c r="Q371" t="b">
@@ -18860,7 +18834,7 @@
       <c r="E372" t="s">
         <v>1184</v>
       </c>
-      <c r="F372" s="2">
+      <c r="F372" s="1">
         <v>46148</v>
       </c>
       <c r="G372" t="s">
@@ -18878,7 +18852,7 @@
       <c r="L372" t="s">
         <v>1428</v>
       </c>
-      <c r="N372" s="2">
+      <c r="N372" s="1">
         <v>46113</v>
       </c>
       <c r="P372" t="s">
@@ -18904,7 +18878,7 @@
       <c r="E373" t="s">
         <v>1185</v>
       </c>
-      <c r="F373" s="2">
+      <c r="F373" s="1">
         <v>46149</v>
       </c>
       <c r="G373" t="s">
@@ -18914,7 +18888,7 @@
         <v>1353</v>
       </c>
       <c r="I373">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K373" t="s">
         <v>1356</v>
@@ -18942,7 +18916,7 @@
       <c r="E374" t="s">
         <v>1186</v>
       </c>
-      <c r="F374" s="2">
+      <c r="F374" s="1">
         <v>46149</v>
       </c>
       <c r="G374" t="s">
@@ -18952,7 +18926,7 @@
         <v>1353</v>
       </c>
       <c r="I374">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K374" t="s">
         <v>1356</v>
@@ -18980,7 +18954,7 @@
       <c r="E375" t="s">
         <v>1187</v>
       </c>
-      <c r="F375" s="2">
+      <c r="F375" s="1">
         <v>46154</v>
       </c>
       <c r="G375" t="s">
@@ -18990,7 +18964,7 @@
         <v>1353</v>
       </c>
       <c r="I375">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J375">
         <v>94</v>
@@ -18998,7 +18972,7 @@
       <c r="K375" t="s">
         <v>1360</v>
       </c>
-      <c r="N375" s="2">
+      <c r="N375" s="1">
         <v>46248</v>
       </c>
       <c r="Q375" t="b">
@@ -19021,7 +18995,7 @@
       <c r="E376" t="s">
         <v>1188</v>
       </c>
-      <c r="F376" s="2">
+      <c r="F376" s="1">
         <v>46154</v>
       </c>
       <c r="G376" t="s">
@@ -19031,7 +19005,7 @@
         <v>1353</v>
       </c>
       <c r="I376">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K376" t="s">
         <v>1360</v>
@@ -19059,7 +19033,7 @@
       <c r="E377" t="s">
         <v>1189</v>
       </c>
-      <c r="F377" s="2">
+      <c r="F377" s="1">
         <v>46154</v>
       </c>
       <c r="G377" t="s">
@@ -19071,7 +19045,7 @@
       <c r="K377" t="s">
         <v>1360</v>
       </c>
-      <c r="N377" s="2">
+      <c r="N377" s="1">
         <v>46176</v>
       </c>
       <c r="O377" t="s">
@@ -19100,7 +19074,7 @@
       <c r="E378" t="s">
         <v>1190</v>
       </c>
-      <c r="F378" s="2">
+      <c r="F378" s="1">
         <v>46154</v>
       </c>
       <c r="G378" t="s">
@@ -19110,7 +19084,7 @@
         <v>1353</v>
       </c>
       <c r="I378">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K378" t="s">
         <v>1360</v>
@@ -19138,7 +19112,7 @@
       <c r="E379" t="s">
         <v>1191</v>
       </c>
-      <c r="F379" s="2">
+      <c r="F379" s="1">
         <v>46154</v>
       </c>
       <c r="G379" t="s">
@@ -19148,7 +19122,7 @@
         <v>1353</v>
       </c>
       <c r="I379">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J379">
         <v>20</v>
@@ -19159,7 +19133,7 @@
       <c r="L379" t="s">
         <v>1442</v>
       </c>
-      <c r="N379" s="2">
+      <c r="N379" s="1">
         <v>46174</v>
       </c>
       <c r="Q379" t="b">
@@ -19182,7 +19156,7 @@
       <c r="E380" t="s">
         <v>1192</v>
       </c>
-      <c r="F380" s="2">
+      <c r="F380" s="1">
         <v>46154</v>
       </c>
       <c r="G380" t="s">
@@ -19192,7 +19166,7 @@
         <v>1353</v>
       </c>
       <c r="I380">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J380">
         <v>94</v>
@@ -19203,7 +19177,7 @@
       <c r="L380" t="s">
         <v>1443</v>
       </c>
-      <c r="N380" s="2">
+      <c r="N380" s="1">
         <v>46248</v>
       </c>
       <c r="Q380" t="b">
@@ -19226,7 +19200,7 @@
       <c r="E381" t="s">
         <v>1193</v>
       </c>
-      <c r="F381" s="2">
+      <c r="F381" s="1">
         <v>46154</v>
       </c>
       <c r="G381" t="s">
@@ -19236,7 +19210,7 @@
         <v>1353</v>
       </c>
       <c r="I381">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K381" t="s">
         <v>1360</v>
@@ -19264,7 +19238,7 @@
       <c r="E382" t="s">
         <v>1194</v>
       </c>
-      <c r="F382" s="2">
+      <c r="F382" s="1">
         <v>46154</v>
       </c>
       <c r="G382" t="s">
@@ -19274,7 +19248,7 @@
         <v>1353</v>
       </c>
       <c r="I382">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K382" t="s">
         <v>1360</v>
@@ -19302,7 +19276,7 @@
       <c r="E383" t="s">
         <v>1195</v>
       </c>
-      <c r="F383" s="2">
+      <c r="F383" s="1">
         <v>46154</v>
       </c>
       <c r="G383" t="s">
@@ -19312,7 +19286,7 @@
         <v>1353</v>
       </c>
       <c r="I383">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J383">
         <v>71</v>
@@ -19323,7 +19297,7 @@
       <c r="L383" t="s">
         <v>1444</v>
       </c>
-      <c r="N383" s="2">
+      <c r="N383" s="1">
         <v>46225</v>
       </c>
       <c r="Q383" t="b">
@@ -19346,7 +19320,7 @@
       <c r="E384" t="s">
         <v>1196</v>
       </c>
-      <c r="F384" s="2">
+      <c r="F384" s="1">
         <v>46164</v>
       </c>
       <c r="G384" t="s">
@@ -19356,7 +19330,7 @@
         <v>1353</v>
       </c>
       <c r="I384">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K384" t="s">
         <v>1357</v>
@@ -19384,7 +19358,7 @@
       <c r="E385" t="s">
         <v>1197</v>
       </c>
-      <c r="F385" s="2">
+      <c r="F385" s="1">
         <v>46164</v>
       </c>
       <c r="G385" t="s">
@@ -19394,7 +19368,7 @@
         <v>1353</v>
       </c>
       <c r="I385">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J385">
         <v>102</v>
@@ -19405,7 +19379,7 @@
       <c r="L385" t="s">
         <v>1445</v>
       </c>
-      <c r="N385" s="2">
+      <c r="N385" s="1">
         <v>46266</v>
       </c>
       <c r="P385" t="s">
@@ -19431,7 +19405,7 @@
       <c r="E386" t="s">
         <v>1198</v>
       </c>
-      <c r="F386" s="2">
+      <c r="F386" s="1">
         <v>46171</v>
       </c>
       <c r="G386" t="s">
@@ -19441,7 +19415,7 @@
         <v>1353</v>
       </c>
       <c r="I386">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K386" t="s">
         <v>1360</v>
@@ -19469,7 +19443,7 @@
       <c r="E387" t="s">
         <v>1199</v>
       </c>
-      <c r="F387" s="2">
+      <c r="F387" s="1">
         <v>46171</v>
       </c>
       <c r="G387" t="s">
@@ -19479,7 +19453,7 @@
         <v>1353</v>
       </c>
       <c r="I387">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K387" t="s">
         <v>1360</v>
@@ -19507,7 +19481,7 @@
       <c r="E388" t="s">
         <v>851</v>
       </c>
-      <c r="F388" s="2">
+      <c r="F388" s="1">
         <v>46171</v>
       </c>
       <c r="G388" t="s">
@@ -19517,7 +19491,7 @@
         <v>1353</v>
       </c>
       <c r="I388">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J388">
         <v>-85</v>
@@ -19528,7 +19502,7 @@
       <c r="L388" t="s">
         <v>1446</v>
       </c>
-      <c r="N388" s="2">
+      <c r="N388" s="1">
         <v>46086</v>
       </c>
       <c r="Q388" t="b">
@@ -19551,7 +19525,7 @@
       <c r="E389" t="s">
         <v>1200</v>
       </c>
-      <c r="F389" s="2">
+      <c r="F389" s="1">
         <v>46171</v>
       </c>
       <c r="G389" t="s">
@@ -19561,7 +19535,7 @@
         <v>1353</v>
       </c>
       <c r="I389">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K389" t="s">
         <v>1361</v>
@@ -19589,7 +19563,7 @@
       <c r="E390" t="s">
         <v>1201</v>
       </c>
-      <c r="F390" s="2">
+      <c r="F390" s="1">
         <v>46171</v>
       </c>
       <c r="G390" t="s">
@@ -19607,7 +19581,7 @@
       <c r="L390" t="s">
         <v>1447</v>
       </c>
-      <c r="N390" s="2">
+      <c r="N390" s="1">
         <v>46191</v>
       </c>
       <c r="P390" t="s">
@@ -19633,7 +19607,7 @@
       <c r="E391" t="s">
         <v>1202</v>
       </c>
-      <c r="F391" s="2">
+      <c r="F391" s="1">
         <v>46171</v>
       </c>
       <c r="G391" t="s">
@@ -19671,7 +19645,7 @@
       <c r="E392" t="s">
         <v>1203</v>
       </c>
-      <c r="F392" s="2">
+      <c r="F392" s="1">
         <v>46171</v>
       </c>
       <c r="G392" t="s">
@@ -19686,7 +19660,7 @@
       <c r="L392" t="s">
         <v>1439</v>
       </c>
-      <c r="N392" s="2">
+      <c r="N392" s="1">
         <v>46176</v>
       </c>
       <c r="Q392" t="b">
@@ -19709,7 +19683,7 @@
       <c r="E393" t="s">
         <v>1204</v>
       </c>
-      <c r="F393" s="2">
+      <c r="F393" s="1">
         <v>46171</v>
       </c>
       <c r="G393" t="s">
@@ -19719,7 +19693,7 @@
         <v>1353</v>
       </c>
       <c r="I393">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J393">
         <v>20</v>
@@ -19730,7 +19704,7 @@
       <c r="L393" t="s">
         <v>1388</v>
       </c>
-      <c r="N393" s="2">
+      <c r="N393" s="1">
         <v>46191</v>
       </c>
       <c r="Q393" t="b">
@@ -19753,7 +19727,7 @@
       <c r="E394" t="s">
         <v>1205</v>
       </c>
-      <c r="F394" s="2">
+      <c r="F394" s="1">
         <v>46171</v>
       </c>
       <c r="G394" t="s">
@@ -19771,7 +19745,7 @@
       <c r="L394" t="s">
         <v>1448</v>
       </c>
-      <c r="N394" s="2">
+      <c r="N394" s="1">
         <v>46241</v>
       </c>
       <c r="P394" t="s">
@@ -19797,7 +19771,7 @@
       <c r="E395" t="s">
         <v>1206</v>
       </c>
-      <c r="F395" s="2">
+      <c r="F395" s="1">
         <v>46171</v>
       </c>
       <c r="G395" t="s">
@@ -19815,7 +19789,7 @@
       <c r="L395" t="s">
         <v>1449</v>
       </c>
-      <c r="N395" s="2">
+      <c r="N395" s="1">
         <v>46191</v>
       </c>
       <c r="P395" t="s">
@@ -19841,7 +19815,7 @@
       <c r="E396" t="s">
         <v>1207</v>
       </c>
-      <c r="F396" s="2">
+      <c r="F396" s="1">
         <v>46171</v>
       </c>
       <c r="G396" t="s">
@@ -19853,7 +19827,7 @@
       <c r="J396">
         <v>20</v>
       </c>
-      <c r="N396" s="2">
+      <c r="N396" s="1">
         <v>46191</v>
       </c>
       <c r="P396" t="s">
@@ -19879,7 +19853,7 @@
       <c r="E397" t="s">
         <v>1208</v>
       </c>
-      <c r="F397" s="2">
+      <c r="F397" s="1">
         <v>46171</v>
       </c>
       <c r="G397" t="s">
@@ -19897,7 +19871,7 @@
       <c r="L397" t="s">
         <v>1448</v>
       </c>
-      <c r="N397" s="2">
+      <c r="N397" s="1">
         <v>46241</v>
       </c>
       <c r="P397" t="s">
@@ -19923,7 +19897,7 @@
       <c r="E398" t="s">
         <v>1209</v>
       </c>
-      <c r="F398" s="2">
+      <c r="F398" s="1">
         <v>46171</v>
       </c>
       <c r="G398" t="s">
@@ -19941,7 +19915,7 @@
       <c r="L398" t="s">
         <v>1449</v>
       </c>
-      <c r="N398" s="2">
+      <c r="N398" s="1">
         <v>46191</v>
       </c>
       <c r="P398" t="s">
@@ -19967,7 +19941,7 @@
       <c r="E399" t="s">
         <v>987</v>
       </c>
-      <c r="F399" s="2">
+      <c r="F399" s="1">
         <v>46163</v>
       </c>
       <c r="G399" t="s">
@@ -19982,7 +19956,7 @@
       <c r="L399" t="s">
         <v>1450</v>
       </c>
-      <c r="N399" s="2">
+      <c r="N399" s="1">
         <v>46171</v>
       </c>
       <c r="Q399" t="b">
@@ -20005,7 +19979,7 @@
       <c r="E400" t="s">
         <v>1210</v>
       </c>
-      <c r="F400" s="2">
+      <c r="F400" s="1">
         <v>46171</v>
       </c>
       <c r="G400" t="s">
@@ -20015,7 +19989,7 @@
         <v>1353</v>
       </c>
       <c r="I400">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K400" t="s">
         <v>1360</v>
@@ -20043,7 +20017,7 @@
       <c r="E401" t="s">
         <v>1211</v>
       </c>
-      <c r="F401" s="2">
+      <c r="F401" s="1">
         <v>46171</v>
       </c>
       <c r="G401" t="s">
@@ -20055,7 +20029,7 @@
       <c r="J401">
         <v>40</v>
       </c>
-      <c r="N401" s="2">
+      <c r="N401" s="1">
         <v>46211</v>
       </c>
       <c r="P401" t="s">
@@ -20081,7 +20055,7 @@
       <c r="E402" t="s">
         <v>1212</v>
       </c>
-      <c r="F402" s="2">
+      <c r="F402" s="1">
         <v>46171</v>
       </c>
       <c r="G402" t="s">
@@ -20091,7 +20065,7 @@
         <v>1353</v>
       </c>
       <c r="I402">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K402" t="s">
         <v>1360</v>
@@ -20119,7 +20093,7 @@
       <c r="E403" t="s">
         <v>1213</v>
       </c>
-      <c r="F403" s="2">
+      <c r="F403" s="1">
         <v>46171</v>
       </c>
       <c r="G403" t="s">
@@ -20129,7 +20103,7 @@
         <v>1353</v>
       </c>
       <c r="I403">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J403">
         <v>83</v>
@@ -20140,7 +20114,7 @@
       <c r="L403" t="s">
         <v>1451</v>
       </c>
-      <c r="N403" s="2">
+      <c r="N403" s="1">
         <v>46254</v>
       </c>
       <c r="Q403" t="b">
@@ -20163,7 +20137,7 @@
       <c r="E404" t="s">
         <v>1214</v>
       </c>
-      <c r="F404" s="2">
+      <c r="F404" s="1">
         <v>46171</v>
       </c>
       <c r="G404" t="s">
@@ -20173,7 +20147,7 @@
         <v>1353</v>
       </c>
       <c r="I404">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K404" t="s">
         <v>1360</v>
@@ -20201,7 +20175,7 @@
       <c r="E405" t="s">
         <v>1215</v>
       </c>
-      <c r="F405" s="2">
+      <c r="F405" s="1">
         <v>46183</v>
       </c>
       <c r="G405" t="s">
@@ -20233,7 +20207,7 @@
       <c r="E406" t="s">
         <v>1216</v>
       </c>
-      <c r="F406" s="2">
+      <c r="F406" s="1">
         <v>46183</v>
       </c>
       <c r="G406" t="s">
@@ -20243,7 +20217,7 @@
         <v>1353</v>
       </c>
       <c r="I406">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q406" t="b">
         <v>1</v>
@@ -20265,7 +20239,7 @@
       <c r="E407" t="s">
         <v>1217</v>
       </c>
-      <c r="F407" s="2">
+      <c r="F407" s="1">
         <v>46183</v>
       </c>
       <c r="G407" t="s">
@@ -20275,7 +20249,7 @@
         <v>1353</v>
       </c>
       <c r="I407">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q407" t="b">
         <v>1</v>
@@ -20297,7 +20271,7 @@
       <c r="E408" t="s">
         <v>1218</v>
       </c>
-      <c r="F408" s="2">
+      <c r="F408" s="1">
         <v>46183</v>
       </c>
       <c r="G408" t="s">
@@ -20307,7 +20281,7 @@
         <v>1353</v>
       </c>
       <c r="I408">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q408" t="b">
         <v>1</v>
@@ -20329,7 +20303,7 @@
       <c r="E409" t="s">
         <v>1219</v>
       </c>
-      <c r="F409" s="2">
+      <c r="F409" s="1">
         <v>46183</v>
       </c>
       <c r="G409" t="s">
@@ -20339,7 +20313,7 @@
         <v>1353</v>
       </c>
       <c r="I409">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q409" t="b">
         <v>1</v>
@@ -20361,7 +20335,7 @@
       <c r="E410" t="s">
         <v>1220</v>
       </c>
-      <c r="F410" s="2">
+      <c r="F410" s="1">
         <v>46183</v>
       </c>
       <c r="G410" t="s">
@@ -20371,7 +20345,7 @@
         <v>1353</v>
       </c>
       <c r="I410">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q410" t="b">
         <v>1</v>
@@ -20393,7 +20367,7 @@
       <c r="E411" t="s">
         <v>1221</v>
       </c>
-      <c r="F411" s="2">
+      <c r="F411" s="1">
         <v>46188</v>
       </c>
       <c r="G411" t="s">
@@ -20403,7 +20377,7 @@
         <v>1353</v>
       </c>
       <c r="I411">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q411" t="b">
         <v>1</v>
@@ -20425,7 +20399,7 @@
       <c r="E412" t="s">
         <v>1222</v>
       </c>
-      <c r="F412" s="2">
+      <c r="F412" s="1">
         <v>46188</v>
       </c>
       <c r="G412" t="s">
@@ -20435,7 +20409,7 @@
         <v>1353</v>
       </c>
       <c r="I412">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q412" t="b">
         <v>1</v>
@@ -20457,7 +20431,7 @@
       <c r="E413" t="s">
         <v>1223</v>
       </c>
-      <c r="F413" s="2">
+      <c r="F413" s="1">
         <v>46188</v>
       </c>
       <c r="G413" t="s">
@@ -20467,7 +20441,7 @@
         <v>1353</v>
       </c>
       <c r="I413">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q413" t="b">
         <v>1</v>
@@ -20489,7 +20463,7 @@
       <c r="E414" t="s">
         <v>1224</v>
       </c>
-      <c r="F414" s="2">
+      <c r="F414" s="1">
         <v>46188</v>
       </c>
       <c r="G414" t="s">
@@ -20518,7 +20492,7 @@
       <c r="E415" t="s">
         <v>1060</v>
       </c>
-      <c r="F415" s="2">
+      <c r="F415" s="1">
         <v>46188</v>
       </c>
       <c r="G415" t="s">
@@ -20547,7 +20521,7 @@
       <c r="E416" t="s">
         <v>1225</v>
       </c>
-      <c r="F416" s="2">
+      <c r="F416" s="1">
         <v>46188</v>
       </c>
       <c r="G416" t="s">
@@ -20557,7 +20531,7 @@
         <v>1353</v>
       </c>
       <c r="I416">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q416" t="b">
         <v>1</v>
@@ -20579,7 +20553,7 @@
       <c r="E417" t="s">
         <v>1226</v>
       </c>
-      <c r="F417" s="2">
+      <c r="F417" s="1">
         <v>46188</v>
       </c>
       <c r="G417" t="s">
@@ -20608,7 +20582,7 @@
       <c r="E418" t="s">
         <v>1227</v>
       </c>
-      <c r="F418" s="2">
+      <c r="F418" s="1">
         <v>46188</v>
       </c>
       <c r="G418" t="s">
@@ -20637,7 +20611,7 @@
       <c r="E419" t="s">
         <v>1228</v>
       </c>
-      <c r="F419" s="2">
+      <c r="F419" s="1">
         <v>46188</v>
       </c>
       <c r="G419" t="s">
@@ -20647,7 +20621,7 @@
         <v>1353</v>
       </c>
       <c r="I419">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q419" t="b">
         <v>1</v>
@@ -20669,7 +20643,7 @@
       <c r="E420" t="s">
         <v>1229</v>
       </c>
-      <c r="F420" s="2">
+      <c r="F420" s="1">
         <v>46188</v>
       </c>
       <c r="G420" t="s">
@@ -20679,7 +20653,7 @@
         <v>1353</v>
       </c>
       <c r="I420">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q420" t="b">
         <v>1</v>
@@ -20701,7 +20675,7 @@
       <c r="E421" t="s">
         <v>1230</v>
       </c>
-      <c r="F421" s="2">
+      <c r="F421" s="1">
         <v>46188</v>
       </c>
       <c r="G421" t="s">
@@ -20711,7 +20685,7 @@
         <v>1353</v>
       </c>
       <c r="I421">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q421" t="b">
         <v>1</v>
@@ -20733,7 +20707,7 @@
       <c r="E422" t="s">
         <v>1231</v>
       </c>
-      <c r="F422" s="2">
+      <c r="F422" s="1">
         <v>46188</v>
       </c>
       <c r="G422" t="s">
@@ -20743,7 +20717,7 @@
         <v>1353</v>
       </c>
       <c r="I422">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q422" t="b">
         <v>1</v>
@@ -20765,7 +20739,7 @@
       <c r="E423" t="s">
         <v>1232</v>
       </c>
-      <c r="F423" s="2">
+      <c r="F423" s="1">
         <v>46188</v>
       </c>
       <c r="G423" t="s">
@@ -20775,7 +20749,7 @@
         <v>1353</v>
       </c>
       <c r="I423">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q423" t="b">
         <v>1</v>
@@ -20797,7 +20771,7 @@
       <c r="E424" t="s">
         <v>1233</v>
       </c>
-      <c r="F424" s="2">
+      <c r="F424" s="1">
         <v>46188</v>
       </c>
       <c r="G424" t="s">
@@ -20807,7 +20781,7 @@
         <v>1353</v>
       </c>
       <c r="I424">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q424" t="b">
         <v>1</v>
@@ -20829,7 +20803,7 @@
       <c r="E425" t="s">
         <v>1234</v>
       </c>
-      <c r="F425" s="2">
+      <c r="F425" s="1">
         <v>46188</v>
       </c>
       <c r="G425" t="s">
@@ -20839,7 +20813,7 @@
         <v>1353</v>
       </c>
       <c r="I425">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q425" t="b">
         <v>1</v>
@@ -20861,7 +20835,7 @@
       <c r="E426" t="s">
         <v>1235</v>
       </c>
-      <c r="F426" s="2">
+      <c r="F426" s="1">
         <v>46188</v>
       </c>
       <c r="G426" t="s">
@@ -20871,7 +20845,7 @@
         <v>1353</v>
       </c>
       <c r="I426">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q426" t="b">
         <v>1</v>
@@ -20893,7 +20867,7 @@
       <c r="E427" t="s">
         <v>1236</v>
       </c>
-      <c r="F427" s="2">
+      <c r="F427" s="1">
         <v>46188</v>
       </c>
       <c r="G427" t="s">
@@ -20903,7 +20877,7 @@
         <v>1353</v>
       </c>
       <c r="I427">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q427" t="b">
         <v>1</v>
@@ -20925,7 +20899,7 @@
       <c r="E428" t="s">
         <v>1237</v>
       </c>
-      <c r="F428" s="2">
+      <c r="F428" s="1">
         <v>46188</v>
       </c>
       <c r="G428" t="s">
@@ -20954,7 +20928,7 @@
       <c r="E429" t="s">
         <v>1238</v>
       </c>
-      <c r="F429" s="2">
+      <c r="F429" s="1">
         <v>46188</v>
       </c>
       <c r="G429" t="s">
@@ -20983,7 +20957,7 @@
       <c r="E430" t="s">
         <v>1239</v>
       </c>
-      <c r="F430" s="2">
+      <c r="F430" s="1">
         <v>46188</v>
       </c>
       <c r="G430" t="s">
@@ -20993,7 +20967,7 @@
         <v>1353</v>
       </c>
       <c r="I430">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q430" t="b">
         <v>1</v>
@@ -21015,7 +20989,7 @@
       <c r="E431" t="s">
         <v>1240</v>
       </c>
-      <c r="F431" s="2">
+      <c r="F431" s="1">
         <v>46188</v>
       </c>
       <c r="G431" t="s">
@@ -21025,7 +20999,7 @@
         <v>1353</v>
       </c>
       <c r="I431">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q431" t="b">
         <v>1</v>
@@ -21047,7 +21021,7 @@
       <c r="E432" t="s">
         <v>1241</v>
       </c>
-      <c r="F432" s="2">
+      <c r="F432" s="1">
         <v>46188</v>
       </c>
       <c r="G432" t="s">
@@ -21057,7 +21031,7 @@
         <v>1353</v>
       </c>
       <c r="I432">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q432" t="b">
         <v>1</v>
@@ -21079,7 +21053,7 @@
       <c r="E433" t="s">
         <v>1242</v>
       </c>
-      <c r="F433" s="2">
+      <c r="F433" s="1">
         <v>46188</v>
       </c>
       <c r="G433" t="s">
@@ -21089,7 +21063,7 @@
         <v>1353</v>
       </c>
       <c r="I433">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q433" t="b">
         <v>1</v>
@@ -21111,7 +21085,7 @@
       <c r="E434" t="s">
         <v>1243</v>
       </c>
-      <c r="F434" s="2">
+      <c r="F434" s="1">
         <v>46188</v>
       </c>
       <c r="G434" t="s">
@@ -21121,7 +21095,7 @@
         <v>1353</v>
       </c>
       <c r="I434">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q434" t="b">
         <v>1</v>
@@ -21143,7 +21117,7 @@
       <c r="E435" t="s">
         <v>856</v>
       </c>
-      <c r="F435" s="2">
+      <c r="F435" s="1">
         <v>46188</v>
       </c>
       <c r="G435" t="s">
@@ -21153,7 +21127,7 @@
         <v>1353</v>
       </c>
       <c r="I435">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q435" t="b">
         <v>1</v>
@@ -21175,7 +21149,7 @@
       <c r="E436" t="s">
         <v>1244</v>
       </c>
-      <c r="F436" s="2">
+      <c r="F436" s="1">
         <v>46188</v>
       </c>
       <c r="G436" t="s">
@@ -21185,7 +21159,7 @@
         <v>1353</v>
       </c>
       <c r="I436">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q436" t="b">
         <v>1</v>
@@ -21207,7 +21181,7 @@
       <c r="E437" t="s">
         <v>1245</v>
       </c>
-      <c r="F437" s="2">
+      <c r="F437" s="1">
         <v>46188</v>
       </c>
       <c r="G437" t="s">
@@ -21217,7 +21191,7 @@
         <v>1355</v>
       </c>
       <c r="I437">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q437" t="b">
         <v>1</v>
@@ -21239,7 +21213,7 @@
       <c r="E438" t="s">
         <v>1246</v>
       </c>
-      <c r="F438" s="2">
+      <c r="F438" s="1">
         <v>46188</v>
       </c>
       <c r="G438" t="s">
@@ -21249,7 +21223,7 @@
         <v>1355</v>
       </c>
       <c r="I438">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q438" t="b">
         <v>1</v>
@@ -21271,7 +21245,7 @@
       <c r="E439" t="s">
         <v>1247</v>
       </c>
-      <c r="F439" s="2">
+      <c r="F439" s="1">
         <v>46196</v>
       </c>
       <c r="G439" t="s">
@@ -21281,7 +21255,7 @@
         <v>1353</v>
       </c>
       <c r="I439">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q439" t="b">
         <v>1</v>
@@ -21303,7 +21277,7 @@
       <c r="E440" t="s">
         <v>1248</v>
       </c>
-      <c r="F440" s="2">
+      <c r="F440" s="1">
         <v>46196</v>
       </c>
       <c r="G440" t="s">
@@ -21313,7 +21287,7 @@
         <v>1353</v>
       </c>
       <c r="I440">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q440" t="b">
         <v>1</v>
@@ -21335,7 +21309,7 @@
       <c r="E441" t="s">
         <v>1249</v>
       </c>
-      <c r="F441" s="2">
+      <c r="F441" s="1">
         <v>46203</v>
       </c>
       <c r="G441" t="s">
@@ -21345,7 +21319,7 @@
         <v>1353</v>
       </c>
       <c r="I441">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q441" t="b">
         <v>1</v>
@@ -21367,7 +21341,7 @@
       <c r="E442" t="s">
         <v>1250</v>
       </c>
-      <c r="F442" s="2">
+      <c r="F442" s="1">
         <v>46203</v>
       </c>
       <c r="G442" t="s">
@@ -21396,7 +21370,7 @@
       <c r="E443" t="s">
         <v>1251</v>
       </c>
-      <c r="F443" s="2">
+      <c r="F443" s="1">
         <v>46205</v>
       </c>
       <c r="G443" t="s">
@@ -21406,7 +21380,7 @@
         <v>1353</v>
       </c>
       <c r="I443">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q443" t="b">
         <v>1</v>
@@ -21428,7 +21402,7 @@
       <c r="E444" t="s">
         <v>1252</v>
       </c>
-      <c r="F444" s="2">
+      <c r="F444" s="1">
         <v>46205</v>
       </c>
       <c r="G444" t="s">
@@ -21457,7 +21431,7 @@
       <c r="E445" t="s">
         <v>1253</v>
       </c>
-      <c r="F445" s="2">
+      <c r="F445" s="1">
         <v>46205</v>
       </c>
       <c r="G445" t="s">
@@ -21486,7 +21460,7 @@
       <c r="E446" t="s">
         <v>1254</v>
       </c>
-      <c r="F446" s="2">
+      <c r="F446" s="1">
         <v>46211</v>
       </c>
       <c r="G446" t="s">
@@ -21496,7 +21470,7 @@
         <v>1353</v>
       </c>
       <c r="I446">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q446" t="b">
         <v>1</v>
@@ -21518,7 +21492,7 @@
       <c r="E447" t="s">
         <v>1255</v>
       </c>
-      <c r="F447" s="2">
+      <c r="F447" s="1">
         <v>46211</v>
       </c>
       <c r="G447" t="s">
@@ -21528,7 +21502,7 @@
         <v>1353</v>
       </c>
       <c r="I447">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q447" t="b">
         <v>1</v>
@@ -21550,7 +21524,7 @@
       <c r="E448" t="s">
         <v>1256</v>
       </c>
-      <c r="F448" s="2">
+      <c r="F448" s="1">
         <v>46226</v>
       </c>
       <c r="G448" t="s">
@@ -21560,7 +21534,7 @@
         <v>1353</v>
       </c>
       <c r="I448">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q448" t="b">
         <v>1</v>
@@ -21582,7 +21556,7 @@
       <c r="E449" t="s">
         <v>1257</v>
       </c>
-      <c r="F449" s="2">
+      <c r="F449" s="1">
         <v>46226</v>
       </c>
       <c r="G449" t="s">
@@ -21592,7 +21566,7 @@
         <v>1353</v>
       </c>
       <c r="I449">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q449" t="b">
         <v>1</v>
@@ -21614,7 +21588,7 @@
       <c r="E450" t="s">
         <v>1258</v>
       </c>
-      <c r="F450" s="2">
+      <c r="F450" s="1">
         <v>46226</v>
       </c>
       <c r="G450" t="s">
@@ -21624,7 +21598,7 @@
         <v>1353</v>
       </c>
       <c r="I450">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q450" t="b">
         <v>1</v>
@@ -21646,7 +21620,7 @@
       <c r="E451" t="s">
         <v>1035</v>
       </c>
-      <c r="F451" s="2">
+      <c r="F451" s="1">
         <v>46230</v>
       </c>
       <c r="G451" t="s">
@@ -21656,7 +21630,7 @@
         <v>1353</v>
       </c>
       <c r="I451">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q451" t="b">
         <v>1</v>
@@ -21678,7 +21652,7 @@
       <c r="E452" t="s">
         <v>1259</v>
       </c>
-      <c r="F452" s="2">
+      <c r="F452" s="1">
         <v>46230</v>
       </c>
       <c r="G452" t="s">
@@ -21688,7 +21662,7 @@
         <v>1353</v>
       </c>
       <c r="I452">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q452" t="b">
         <v>1</v>
@@ -21710,7 +21684,7 @@
       <c r="E453" t="s">
         <v>1260</v>
       </c>
-      <c r="F453" s="2">
+      <c r="F453" s="1">
         <v>46230</v>
       </c>
       <c r="G453" t="s">
@@ -21720,7 +21694,7 @@
         <v>1353</v>
       </c>
       <c r="I453">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q453" t="b">
         <v>1</v>
@@ -21742,7 +21716,7 @@
       <c r="E454" t="s">
         <v>1261</v>
       </c>
-      <c r="F454" s="2">
+      <c r="F454" s="1">
         <v>46230</v>
       </c>
       <c r="G454" t="s">
@@ -21752,7 +21726,7 @@
         <v>1353</v>
       </c>
       <c r="I454">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q454" t="b">
         <v>1</v>
@@ -21774,7 +21748,7 @@
       <c r="E455" t="s">
         <v>1262</v>
       </c>
-      <c r="F455" s="2">
+      <c r="F455" s="1">
         <v>46230</v>
       </c>
       <c r="G455" t="s">
@@ -21784,7 +21758,7 @@
         <v>1353</v>
       </c>
       <c r="I455">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q455" t="b">
         <v>1</v>
@@ -21806,7 +21780,7 @@
       <c r="E456" t="s">
         <v>1263</v>
       </c>
-      <c r="F456" s="2">
+      <c r="F456" s="1">
         <v>46230</v>
       </c>
       <c r="G456" t="s">
@@ -21816,7 +21790,7 @@
         <v>1353</v>
       </c>
       <c r="I456">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q456" t="b">
         <v>1</v>
@@ -21838,7 +21812,7 @@
       <c r="E457" t="s">
         <v>1264</v>
       </c>
-      <c r="F457" s="2">
+      <c r="F457" s="1">
         <v>46230</v>
       </c>
       <c r="G457" t="s">
@@ -21848,7 +21822,7 @@
         <v>1353</v>
       </c>
       <c r="I457">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q457" t="b">
         <v>1</v>
@@ -21870,7 +21844,7 @@
       <c r="E458" t="s">
         <v>1202</v>
       </c>
-      <c r="F458" s="2">
+      <c r="F458" s="1">
         <v>46231</v>
       </c>
       <c r="G458" t="s">
@@ -21880,7 +21854,7 @@
         <v>1353</v>
       </c>
       <c r="I458">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q458" t="b">
         <v>1</v>
@@ -21902,7 +21876,7 @@
       <c r="E459" t="s">
         <v>1265</v>
       </c>
-      <c r="F459" s="2">
+      <c r="F459" s="1">
         <v>46233</v>
       </c>
       <c r="G459" t="s">
@@ -21912,7 +21886,7 @@
         <v>1353</v>
       </c>
       <c r="I459">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q459" t="b">
         <v>1</v>
@@ -21934,7 +21908,7 @@
       <c r="E460" t="s">
         <v>1266</v>
       </c>
-      <c r="F460" s="2">
+      <c r="F460" s="1">
         <v>46233</v>
       </c>
       <c r="G460" t="s">
@@ -21944,7 +21918,7 @@
         <v>1353</v>
       </c>
       <c r="I460">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q460" t="b">
         <v>1</v>
@@ -21966,7 +21940,7 @@
       <c r="E461" t="s">
         <v>1267</v>
       </c>
-      <c r="F461" s="2">
+      <c r="F461" s="1">
         <v>46233</v>
       </c>
       <c r="G461" t="s">
@@ -21976,7 +21950,7 @@
         <v>1353</v>
       </c>
       <c r="I461">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q461" t="b">
         <v>1</v>
@@ -21998,7 +21972,7 @@
       <c r="E462" t="s">
         <v>1268</v>
       </c>
-      <c r="F462" s="2">
+      <c r="F462" s="1">
         <v>46233</v>
       </c>
       <c r="G462" t="s">
@@ -22008,7 +21982,7 @@
         <v>1353</v>
       </c>
       <c r="I462">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q462" t="b">
         <v>1</v>
@@ -22030,7 +22004,7 @@
       <c r="E463" t="s">
         <v>1269</v>
       </c>
-      <c r="F463" s="2">
+      <c r="F463" s="1">
         <v>46234</v>
       </c>
       <c r="G463" t="s">
@@ -22040,7 +22014,7 @@
         <v>1353</v>
       </c>
       <c r="I463">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q463" t="b">
         <v>1</v>
@@ -22062,7 +22036,7 @@
       <c r="E464" t="s">
         <v>1270</v>
       </c>
-      <c r="F464" s="2">
+      <c r="F464" s="1">
         <v>46230</v>
       </c>
       <c r="G464" t="s">
@@ -22072,7 +22046,7 @@
         <v>1353</v>
       </c>
       <c r="I464">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q464" t="b">
         <v>1</v>
@@ -22094,7 +22068,7 @@
       <c r="E465" t="s">
         <v>1271</v>
       </c>
-      <c r="F465" s="2">
+      <c r="F465" s="1">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
@@ -22104,7 +22078,7 @@
         <v>1353</v>
       </c>
       <c r="I465">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q465" t="b">
         <v>1</v>
@@ -22126,7 +22100,7 @@
       <c r="E466" t="s">
         <v>1272</v>
       </c>
-      <c r="F466" s="2">
+      <c r="F466" s="1">
         <v>46230</v>
       </c>
       <c r="G466" t="s">
@@ -22136,7 +22110,7 @@
         <v>1353</v>
       </c>
       <c r="I466">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q466" t="b">
         <v>1</v>
@@ -22158,7 +22132,7 @@
       <c r="E467" t="s">
         <v>1273</v>
       </c>
-      <c r="F467" s="2">
+      <c r="F467" s="1">
         <v>46230</v>
       </c>
       <c r="G467" t="s">
@@ -22168,7 +22142,7 @@
         <v>1353</v>
       </c>
       <c r="I467">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q467" t="b">
         <v>1</v>
@@ -22190,7 +22164,7 @@
       <c r="E468" t="s">
         <v>1274</v>
       </c>
-      <c r="F468" s="2">
+      <c r="F468" s="1">
         <v>46230</v>
       </c>
       <c r="G468" t="s">
@@ -22200,7 +22174,7 @@
         <v>1353</v>
       </c>
       <c r="I468">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q468" t="b">
         <v>1</v>
@@ -22222,7 +22196,7 @@
       <c r="E469" t="s">
         <v>1275</v>
       </c>
-      <c r="F469" s="2">
+      <c r="F469" s="1">
         <v>46230</v>
       </c>
       <c r="G469" t="s">
@@ -22232,7 +22206,7 @@
         <v>1353</v>
       </c>
       <c r="I469">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q469" t="b">
         <v>1</v>
@@ -22254,7 +22228,7 @@
       <c r="E470" t="s">
         <v>1276</v>
       </c>
-      <c r="F470" s="2">
+      <c r="F470" s="1">
         <v>46230</v>
       </c>
       <c r="G470" t="s">
@@ -22283,7 +22257,7 @@
       <c r="E471" t="s">
         <v>1277</v>
       </c>
-      <c r="F471" s="2">
+      <c r="F471" s="1">
         <v>46230</v>
       </c>
       <c r="G471" t="s">
@@ -22293,7 +22267,7 @@
         <v>1353</v>
       </c>
       <c r="I471">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q471" t="b">
         <v>1</v>
@@ -22315,7 +22289,7 @@
       <c r="E472" t="s">
         <v>1278</v>
       </c>
-      <c r="F472" s="2">
+      <c r="F472" s="1">
         <v>46230</v>
       </c>
       <c r="G472" t="s">
@@ -22325,7 +22299,7 @@
         <v>1353</v>
       </c>
       <c r="I472">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q472" t="b">
         <v>1</v>
@@ -22347,7 +22321,7 @@
       <c r="E473" t="s">
         <v>1279</v>
       </c>
-      <c r="F473" s="2">
+      <c r="F473" s="1">
         <v>46230</v>
       </c>
       <c r="G473" t="s">
@@ -22357,7 +22331,7 @@
         <v>1353</v>
       </c>
       <c r="I473">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q473" t="b">
         <v>1</v>
@@ -22379,7 +22353,7 @@
       <c r="E474" t="s">
         <v>1280</v>
       </c>
-      <c r="F474" s="2">
+      <c r="F474" s="1">
         <v>46231</v>
       </c>
       <c r="G474" t="s">
@@ -22389,7 +22363,7 @@
         <v>1353</v>
       </c>
       <c r="I474">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q474" t="b">
         <v>1</v>
@@ -22411,7 +22385,7 @@
       <c r="E475" t="s">
         <v>1281</v>
       </c>
-      <c r="F475" s="2">
+      <c r="F475" s="1">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
@@ -22421,7 +22395,7 @@
         <v>1353</v>
       </c>
       <c r="I475">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q475" t="b">
         <v>1</v>
@@ -22443,7 +22417,7 @@
       <c r="E476" t="s">
         <v>1282</v>
       </c>
-      <c r="F476" s="2">
+      <c r="F476" s="1">
         <v>46231</v>
       </c>
       <c r="G476" t="s">
@@ -22453,7 +22427,7 @@
         <v>1353</v>
       </c>
       <c r="I476">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q476" t="b">
         <v>1</v>
@@ -22475,7 +22449,7 @@
       <c r="E477" t="s">
         <v>1283</v>
       </c>
-      <c r="F477" s="2">
+      <c r="F477" s="1">
         <v>46231</v>
       </c>
       <c r="G477" t="s">
@@ -22485,7 +22459,7 @@
         <v>1353</v>
       </c>
       <c r="I477">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q477" t="b">
         <v>1</v>
@@ -22507,7 +22481,7 @@
       <c r="E478" t="s">
         <v>1284</v>
       </c>
-      <c r="F478" s="2">
+      <c r="F478" s="1">
         <v>46231</v>
       </c>
       <c r="G478" t="s">
@@ -22517,7 +22491,7 @@
         <v>1353</v>
       </c>
       <c r="I478">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q478" t="b">
         <v>1</v>
@@ -22539,7 +22513,7 @@
       <c r="E479" t="s">
         <v>1285</v>
       </c>
-      <c r="F479" s="2">
+      <c r="F479" s="1">
         <v>46231</v>
       </c>
       <c r="G479" t="s">
@@ -22549,7 +22523,7 @@
         <v>1353</v>
       </c>
       <c r="I479">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q479" t="b">
         <v>1</v>
@@ -22571,7 +22545,7 @@
       <c r="E480" t="s">
         <v>1286</v>
       </c>
-      <c r="F480" s="2">
+      <c r="F480" s="1">
         <v>46231</v>
       </c>
       <c r="G480" t="s">
@@ -22581,7 +22555,7 @@
         <v>1353</v>
       </c>
       <c r="I480">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q480" t="b">
         <v>1</v>
@@ -22603,7 +22577,7 @@
       <c r="E481" t="s">
         <v>1287</v>
       </c>
-      <c r="F481" s="2">
+      <c r="F481" s="1">
         <v>46231</v>
       </c>
       <c r="G481" t="s">
@@ -22613,7 +22587,7 @@
         <v>1353</v>
       </c>
       <c r="I481">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q481" t="b">
         <v>1</v>
@@ -22635,7 +22609,7 @@
       <c r="E482" t="s">
         <v>1288</v>
       </c>
-      <c r="F482" s="2">
+      <c r="F482" s="1">
         <v>46231</v>
       </c>
       <c r="G482" t="s">
@@ -22645,7 +22619,7 @@
         <v>1353</v>
       </c>
       <c r="I482">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q482" t="b">
         <v>1</v>
@@ -22667,7 +22641,7 @@
       <c r="E483" t="s">
         <v>1289</v>
       </c>
-      <c r="F483" s="2">
+      <c r="F483" s="1">
         <v>46231</v>
       </c>
       <c r="G483" t="s">
@@ -22677,7 +22651,7 @@
         <v>1353</v>
       </c>
       <c r="I483">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q483" t="b">
         <v>1</v>
@@ -22699,7 +22673,7 @@
       <c r="E484" t="s">
         <v>1290</v>
       </c>
-      <c r="F484" s="2">
+      <c r="F484" s="1">
         <v>46231</v>
       </c>
       <c r="G484" t="s">
@@ -22709,7 +22683,7 @@
         <v>1353</v>
       </c>
       <c r="I484">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q484" t="b">
         <v>1</v>
@@ -22731,7 +22705,7 @@
       <c r="E485" t="s">
         <v>1291</v>
       </c>
-      <c r="F485" s="2">
+      <c r="F485" s="1">
         <v>46231</v>
       </c>
       <c r="G485" t="s">
@@ -22741,7 +22715,7 @@
         <v>1353</v>
       </c>
       <c r="I485">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q485" t="b">
         <v>1</v>
@@ -22763,7 +22737,7 @@
       <c r="E486" t="s">
         <v>1292</v>
       </c>
-      <c r="F486" s="2">
+      <c r="F486" s="1">
         <v>46231</v>
       </c>
       <c r="G486" t="s">
@@ -22773,7 +22747,7 @@
         <v>1353</v>
       </c>
       <c r="I486">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q486" t="b">
         <v>1</v>
@@ -22795,7 +22769,7 @@
       <c r="E487" t="s">
         <v>1293</v>
       </c>
-      <c r="F487" s="2">
+      <c r="F487" s="1">
         <v>46231</v>
       </c>
       <c r="G487" t="s">
@@ -22805,7 +22779,7 @@
         <v>1353</v>
       </c>
       <c r="I487">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q487" t="b">
         <v>1</v>
@@ -22827,7 +22801,7 @@
       <c r="E488" t="s">
         <v>1294</v>
       </c>
-      <c r="F488" s="2">
+      <c r="F488" s="1">
         <v>46231</v>
       </c>
       <c r="G488" t="s">
@@ -22837,7 +22811,7 @@
         <v>1353</v>
       </c>
       <c r="I488">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q488" t="b">
         <v>1</v>
@@ -22859,7 +22833,7 @@
       <c r="E489" t="s">
         <v>1295</v>
       </c>
-      <c r="F489" s="2">
+      <c r="F489" s="1">
         <v>46231</v>
       </c>
       <c r="G489" t="s">
@@ -22869,7 +22843,7 @@
         <v>1353</v>
       </c>
       <c r="I489">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q489" t="b">
         <v>1</v>
@@ -22891,7 +22865,7 @@
       <c r="E490" t="s">
         <v>1296</v>
       </c>
-      <c r="F490" s="2">
+      <c r="F490" s="1">
         <v>46231</v>
       </c>
       <c r="G490" t="s">
@@ -22901,7 +22875,7 @@
         <v>1353</v>
       </c>
       <c r="I490">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q490" t="b">
         <v>1</v>
@@ -22923,7 +22897,7 @@
       <c r="E491" t="s">
         <v>1297</v>
       </c>
-      <c r="F491" s="2">
+      <c r="F491" s="1">
         <v>46231</v>
       </c>
       <c r="G491" t="s">
@@ -22933,7 +22907,7 @@
         <v>1353</v>
       </c>
       <c r="I491">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q491" t="b">
         <v>1</v>
@@ -22955,7 +22929,7 @@
       <c r="E492" t="s">
         <v>911</v>
       </c>
-      <c r="F492" s="2">
+      <c r="F492" s="1">
         <v>46231</v>
       </c>
       <c r="G492" t="s">
@@ -22965,7 +22939,7 @@
         <v>1355</v>
       </c>
       <c r="I492">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q492" t="b">
         <v>1</v>
@@ -22987,7 +22961,7 @@
       <c r="E493" t="s">
         <v>995</v>
       </c>
-      <c r="F493" s="2">
+      <c r="F493" s="1">
         <v>46231</v>
       </c>
       <c r="G493" t="s">
@@ -22997,7 +22971,7 @@
         <v>1355</v>
       </c>
       <c r="I493">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q493" t="b">
         <v>1</v>
@@ -23019,7 +22993,7 @@
       <c r="E494" t="s">
         <v>867</v>
       </c>
-      <c r="F494" s="2">
+      <c r="F494" s="1">
         <v>46231</v>
       </c>
       <c r="G494" t="s">
@@ -23029,7 +23003,7 @@
         <v>1355</v>
       </c>
       <c r="I494">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q494" t="b">
         <v>1</v>
@@ -23051,7 +23025,7 @@
       <c r="E495" t="s">
         <v>912</v>
       </c>
-      <c r="F495" s="2">
+      <c r="F495" s="1">
         <v>46231</v>
       </c>
       <c r="G495" t="s">
@@ -23061,7 +23035,7 @@
         <v>1355</v>
       </c>
       <c r="I495">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q495" t="b">
         <v>1</v>
@@ -23083,7 +23057,7 @@
       <c r="E496" t="s">
         <v>1048</v>
       </c>
-      <c r="F496" s="2">
+      <c r="F496" s="1">
         <v>46231</v>
       </c>
       <c r="G496" t="s">
@@ -23093,7 +23067,7 @@
         <v>1355</v>
       </c>
       <c r="I496">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q496" t="b">
         <v>1</v>
@@ -23115,7 +23089,7 @@
       <c r="E497" t="s">
         <v>1298</v>
       </c>
-      <c r="F497" s="2">
+      <c r="F497" s="1">
         <v>46231</v>
       </c>
       <c r="G497" t="s">
@@ -23125,7 +23099,7 @@
         <v>1353</v>
       </c>
       <c r="I497">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q497" t="b">
         <v>1</v>
@@ -23147,7 +23121,7 @@
       <c r="E498" t="s">
         <v>1299</v>
       </c>
-      <c r="F498" s="2">
+      <c r="F498" s="1">
         <v>46231</v>
       </c>
       <c r="G498" t="s">
@@ -23157,7 +23131,7 @@
         <v>1353</v>
       </c>
       <c r="I498">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q498" t="b">
         <v>1</v>
@@ -23179,7 +23153,7 @@
       <c r="E499" t="s">
         <v>1300</v>
       </c>
-      <c r="F499" s="2">
+      <c r="F499" s="1">
         <v>46231</v>
       </c>
       <c r="G499" t="s">
@@ -23189,7 +23163,7 @@
         <v>1355</v>
       </c>
       <c r="I499">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q499" t="b">
         <v>1</v>
@@ -23211,7 +23185,7 @@
       <c r="E500" t="s">
         <v>1301</v>
       </c>
-      <c r="F500" s="2">
+      <c r="F500" s="1">
         <v>46231</v>
       </c>
       <c r="G500" t="s">
@@ -23221,7 +23195,7 @@
         <v>1353</v>
       </c>
       <c r="I500">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q500" t="b">
         <v>1</v>
@@ -23243,7 +23217,7 @@
       <c r="E501" t="s">
         <v>1302</v>
       </c>
-      <c r="F501" s="2">
+      <c r="F501" s="1">
         <v>46231</v>
       </c>
       <c r="G501" t="s">
@@ -23253,7 +23227,7 @@
         <v>1353</v>
       </c>
       <c r="I501">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q501" t="b">
         <v>1</v>
@@ -23275,7 +23249,7 @@
       <c r="E502" t="s">
         <v>1303</v>
       </c>
-      <c r="F502" s="2">
+      <c r="F502" s="1">
         <v>46231</v>
       </c>
       <c r="G502" t="s">
@@ -23285,7 +23259,7 @@
         <v>1353</v>
       </c>
       <c r="I502">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q502" t="b">
         <v>1</v>
@@ -23307,7 +23281,7 @@
       <c r="E503" t="s">
         <v>1304</v>
       </c>
-      <c r="F503" s="2">
+      <c r="F503" s="1">
         <v>46231</v>
       </c>
       <c r="G503" t="s">
@@ -23317,7 +23291,7 @@
         <v>1353</v>
       </c>
       <c r="I503">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q503" t="b">
         <v>1</v>
@@ -23339,7 +23313,7 @@
       <c r="E504" t="s">
         <v>1305</v>
       </c>
-      <c r="F504" s="2">
+      <c r="F504" s="1">
         <v>46232</v>
       </c>
       <c r="G504" t="s">
@@ -23349,7 +23323,7 @@
         <v>1353</v>
       </c>
       <c r="I504">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q504" t="b">
         <v>1</v>
@@ -23371,7 +23345,7 @@
       <c r="E505" t="s">
         <v>1306</v>
       </c>
-      <c r="F505" s="2">
+      <c r="F505" s="1">
         <v>46232</v>
       </c>
       <c r="G505" t="s">
@@ -23381,7 +23355,7 @@
         <v>1353</v>
       </c>
       <c r="I505">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q505" t="b">
         <v>1</v>
@@ -23403,7 +23377,7 @@
       <c r="E506" t="s">
         <v>1307</v>
       </c>
-      <c r="F506" s="2">
+      <c r="F506" s="1">
         <v>46232</v>
       </c>
       <c r="G506" t="s">
@@ -23413,7 +23387,7 @@
         <v>1353</v>
       </c>
       <c r="I506">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q506" t="b">
         <v>1</v>
@@ -23435,7 +23409,7 @@
       <c r="E507" t="s">
         <v>1308</v>
       </c>
-      <c r="F507" s="2">
+      <c r="F507" s="1">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
@@ -23445,7 +23419,7 @@
         <v>1353</v>
       </c>
       <c r="I507">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q507" t="b">
         <v>1</v>
@@ -23467,7 +23441,7 @@
       <c r="E508" t="s">
         <v>1309</v>
       </c>
-      <c r="F508" s="2">
+      <c r="F508" s="1">
         <v>46237</v>
       </c>
       <c r="G508" t="s">
@@ -23496,7 +23470,7 @@
       <c r="E509" t="s">
         <v>1310</v>
       </c>
-      <c r="F509" s="2">
+      <c r="F509" s="1">
         <v>46237</v>
       </c>
       <c r="G509" t="s">
@@ -23506,7 +23480,7 @@
         <v>1353</v>
       </c>
       <c r="I509">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q509" t="b">
         <v>1</v>
@@ -23528,7 +23502,7 @@
       <c r="E510" t="s">
         <v>1311</v>
       </c>
-      <c r="F510" s="2">
+      <c r="F510" s="1">
         <v>46237</v>
       </c>
       <c r="G510" t="s">
@@ -23538,7 +23512,7 @@
         <v>1353</v>
       </c>
       <c r="I510">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q510" t="b">
         <v>1</v>
@@ -23560,7 +23534,7 @@
       <c r="E511" t="s">
         <v>1312</v>
       </c>
-      <c r="F511" s="2">
+      <c r="F511" s="1">
         <v>46240</v>
       </c>
       <c r="G511" t="s">
@@ -23570,7 +23544,7 @@
         <v>1353</v>
       </c>
       <c r="I511">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q511" t="b">
         <v>1</v>
@@ -23592,7 +23566,7 @@
       <c r="E512" t="s">
         <v>1313</v>
       </c>
-      <c r="F512" s="2">
+      <c r="F512" s="1">
         <v>46240</v>
       </c>
       <c r="G512" t="s">
@@ -23602,7 +23576,7 @@
         <v>1353</v>
       </c>
       <c r="I512">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q512" t="b">
         <v>1</v>
@@ -23624,7 +23598,7 @@
       <c r="E513" t="s">
         <v>1314</v>
       </c>
-      <c r="F513" s="2">
+      <c r="F513" s="1">
         <v>46244</v>
       </c>
       <c r="G513" t="s">
@@ -23634,7 +23608,7 @@
         <v>1353</v>
       </c>
       <c r="I513">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q513" t="b">
         <v>1</v>
@@ -23656,7 +23630,7 @@
       <c r="E514" t="s">
         <v>1315</v>
       </c>
-      <c r="F514" s="2">
+      <c r="F514" s="1">
         <v>46244</v>
       </c>
       <c r="G514" t="s">
@@ -23666,7 +23640,7 @@
         <v>1353</v>
       </c>
       <c r="I514">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q514" t="b">
         <v>1</v>
@@ -23688,7 +23662,7 @@
       <c r="E515" t="s">
         <v>1043</v>
       </c>
-      <c r="F515" s="2">
+      <c r="F515" s="1">
         <v>46244</v>
       </c>
       <c r="G515" t="s">
@@ -23698,7 +23672,7 @@
         <v>1353</v>
       </c>
       <c r="I515">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q515" t="b">
         <v>1</v>
@@ -23720,7 +23694,7 @@
       <c r="E516" t="s">
         <v>1316</v>
       </c>
-      <c r="F516" s="2">
+      <c r="F516" s="1">
         <v>46252</v>
       </c>
       <c r="G516" t="s">
@@ -23730,7 +23704,7 @@
         <v>1353</v>
       </c>
       <c r="I516">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q516" t="b">
         <v>1</v>
@@ -23752,7 +23726,7 @@
       <c r="E517" t="s">
         <v>1317</v>
       </c>
-      <c r="F517" s="2">
+      <c r="F517" s="1">
         <v>46252</v>
       </c>
       <c r="G517" t="s">
@@ -23762,7 +23736,7 @@
         <v>1353</v>
       </c>
       <c r="I517">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q517" t="b">
         <v>1</v>
@@ -23784,7 +23758,7 @@
       <c r="E518" t="s">
         <v>1318</v>
       </c>
-      <c r="F518" s="2">
+      <c r="F518" s="1">
         <v>46252</v>
       </c>
       <c r="G518" t="s">
@@ -23794,7 +23768,7 @@
         <v>1353</v>
       </c>
       <c r="I518">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q518" t="b">
         <v>1</v>
@@ -23816,7 +23790,7 @@
       <c r="E519" t="s">
         <v>1253</v>
       </c>
-      <c r="F519" s="2">
+      <c r="F519" s="1">
         <v>46254</v>
       </c>
       <c r="G519" t="s">
@@ -23826,7 +23800,7 @@
         <v>1353</v>
       </c>
       <c r="I519">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q519" t="b">
         <v>1</v>
@@ -23848,7 +23822,7 @@
       <c r="E520" t="s">
         <v>1319</v>
       </c>
-      <c r="F520" s="2">
+      <c r="F520" s="1">
         <v>46254</v>
       </c>
       <c r="G520" t="s">
@@ -23858,7 +23832,7 @@
         <v>1353</v>
       </c>
       <c r="I520">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q520" t="b">
         <v>1</v>
@@ -23880,7 +23854,7 @@
       <c r="E521" t="s">
         <v>1320</v>
       </c>
-      <c r="F521" s="2">
+      <c r="F521" s="1">
         <v>46254</v>
       </c>
       <c r="G521" t="s">
@@ -23890,7 +23864,7 @@
         <v>1353</v>
       </c>
       <c r="I521">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q521" t="b">
         <v>1</v>
@@ -23912,7 +23886,7 @@
       <c r="E522" t="s">
         <v>1253</v>
       </c>
-      <c r="F522" s="2">
+      <c r="F522" s="1">
         <v>46254</v>
       </c>
       <c r="G522" t="s">
@@ -23922,7 +23896,7 @@
         <v>1353</v>
       </c>
       <c r="I522">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q522" t="b">
         <v>1</v>
@@ -23944,7 +23918,7 @@
       <c r="E523" t="s">
         <v>1319</v>
       </c>
-      <c r="F523" s="2">
+      <c r="F523" s="1">
         <v>46254</v>
       </c>
       <c r="G523" t="s">
@@ -23954,7 +23928,7 @@
         <v>1353</v>
       </c>
       <c r="I523">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q523" t="b">
         <v>1</v>
@@ -23976,7 +23950,7 @@
       <c r="E524" t="s">
         <v>1321</v>
       </c>
-      <c r="F524" s="2">
+      <c r="F524" s="1">
         <v>46265</v>
       </c>
       <c r="G524" t="s">
@@ -23986,7 +23960,7 @@
         <v>1353</v>
       </c>
       <c r="I524">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q524" t="b">
         <v>1</v>
@@ -24008,7 +23982,7 @@
       <c r="E525" t="s">
         <v>1322</v>
       </c>
-      <c r="F525" s="2">
+      <c r="F525" s="1">
         <v>46265</v>
       </c>
       <c r="G525" t="s">
@@ -24018,7 +23992,7 @@
         <v>1353</v>
       </c>
       <c r="I525">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q525" t="b">
         <v>1</v>
@@ -24040,7 +24014,7 @@
       <c r="E526" t="s">
         <v>1323</v>
       </c>
-      <c r="F526" s="2">
+      <c r="F526" s="1">
         <v>46265</v>
       </c>
       <c r="G526" t="s">
@@ -24050,7 +24024,7 @@
         <v>1353</v>
       </c>
       <c r="I526">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q526" t="b">
         <v>1</v>
@@ -24072,7 +24046,7 @@
       <c r="E527" t="s">
         <v>1324</v>
       </c>
-      <c r="F527" s="2">
+      <c r="F527" s="1">
         <v>46265</v>
       </c>
       <c r="G527" t="s">
@@ -24082,7 +24056,7 @@
         <v>1353</v>
       </c>
       <c r="I527">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q527" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4196" uniqueCount="1499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4199" uniqueCount="1501">
   <si>
     <t>os</t>
   </si>
@@ -4456,6 +4456,9 @@
     <t>028/2026</t>
   </si>
   <si>
+    <t>038/2026</t>
+  </si>
+  <si>
     <t>080/2026</t>
   </si>
   <si>
@@ -4487,6 +4490,9 @@
   </si>
   <si>
     <t>026/2026</t>
+  </si>
+  <si>
+    <t>001/2026</t>
   </si>
   <si>
     <t>089/2026</t>
@@ -4520,16 +4526,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -4545,7 +4543,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -4553,30 +4551,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4876,55 +4856,55 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4944,7 +4924,7 @@
       <c r="E2" t="s">
         <v>829</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>45698</v>
       </c>
       <c r="G2" t="s">
@@ -4954,7 +4934,7 @@
         <v>1353</v>
       </c>
       <c r="I2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="K2" t="s">
         <v>1356</v>
@@ -4982,7 +4962,7 @@
       <c r="E3" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>45714</v>
       </c>
       <c r="G3" t="s">
@@ -4992,7 +4972,7 @@
         <v>1353</v>
       </c>
       <c r="I3">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K3" t="s">
         <v>1357</v>
@@ -5020,7 +5000,7 @@
       <c r="E4" t="s">
         <v>831</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>45714</v>
       </c>
       <c r="G4" t="s">
@@ -5030,7 +5010,7 @@
         <v>1353</v>
       </c>
       <c r="I4">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K4" t="s">
         <v>1357</v>
@@ -5058,7 +5038,7 @@
       <c r="E5" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>45714</v>
       </c>
       <c r="G5" t="s">
@@ -5068,7 +5048,7 @@
         <v>1353</v>
       </c>
       <c r="I5">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J5">
         <v>279</v>
@@ -5079,7 +5059,7 @@
       <c r="L5" t="s">
         <v>1367</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="1">
         <v>45993</v>
       </c>
       <c r="Q5" t="b">
@@ -5102,7 +5082,7 @@
       <c r="E6" t="s">
         <v>833</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>45736</v>
       </c>
       <c r="G6" t="s">
@@ -5112,7 +5092,7 @@
         <v>1353</v>
       </c>
       <c r="I6">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J6">
         <v>153</v>
@@ -5123,7 +5103,7 @@
       <c r="L6" t="s">
         <v>1368</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="1">
         <v>45889</v>
       </c>
       <c r="Q6" t="b">
@@ -5146,7 +5126,7 @@
       <c r="E7" t="s">
         <v>834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>45736</v>
       </c>
       <c r="G7" t="s">
@@ -5156,7 +5136,7 @@
         <v>1353</v>
       </c>
       <c r="I7">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J7">
         <v>112</v>
@@ -5167,7 +5147,7 @@
       <c r="L7" t="s">
         <v>1369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="1">
         <v>45848</v>
       </c>
       <c r="O7" t="s">
@@ -5193,7 +5173,7 @@
       <c r="E8" t="s">
         <v>835</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>45736</v>
       </c>
       <c r="G8" t="s">
@@ -5222,7 +5202,7 @@
       <c r="E9" t="s">
         <v>836</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>45736</v>
       </c>
       <c r="G9" t="s">
@@ -5232,7 +5212,7 @@
         <v>1353</v>
       </c>
       <c r="I9">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J9">
         <v>362</v>
@@ -5243,7 +5223,7 @@
       <c r="L9" t="s">
         <v>1370</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="1">
         <v>46098</v>
       </c>
       <c r="O9">
@@ -5269,7 +5249,7 @@
       <c r="E10" t="s">
         <v>837</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>45736</v>
       </c>
       <c r="G10" t="s">
@@ -5279,7 +5259,7 @@
         <v>1353</v>
       </c>
       <c r="I10">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J10">
         <v>378</v>
@@ -5290,7 +5270,7 @@
       <c r="L10" t="s">
         <v>1371</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="1">
         <v>46114</v>
       </c>
       <c r="O10" t="s">
@@ -5316,7 +5296,7 @@
       <c r="E11" t="s">
         <v>838</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>45736</v>
       </c>
       <c r="G11" t="s">
@@ -5326,7 +5306,7 @@
         <v>1353</v>
       </c>
       <c r="I11">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J11">
         <v>112</v>
@@ -5337,7 +5317,7 @@
       <c r="L11" t="s">
         <v>1369</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="1">
         <v>45848</v>
       </c>
       <c r="O11" t="s">
@@ -5363,7 +5343,7 @@
       <c r="E12" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>45736</v>
       </c>
       <c r="G12" t="s">
@@ -5373,7 +5353,7 @@
         <v>1353</v>
       </c>
       <c r="I12">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J12">
         <v>124</v>
@@ -5384,7 +5364,7 @@
       <c r="L12" t="s">
         <v>1372</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="1">
         <v>45860</v>
       </c>
       <c r="Q12" t="b">
@@ -5407,7 +5387,7 @@
       <c r="E13" t="s">
         <v>840</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>45736</v>
       </c>
       <c r="G13" t="s">
@@ -5436,7 +5416,7 @@
       <c r="E14" t="s">
         <v>841</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>45736</v>
       </c>
       <c r="G14" t="s">
@@ -5446,7 +5426,7 @@
         <v>1353</v>
       </c>
       <c r="I14">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J14">
         <v>64</v>
@@ -5457,7 +5437,7 @@
       <c r="L14" t="s">
         <v>1373</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="1">
         <v>45800</v>
       </c>
       <c r="Q14" t="b">
@@ -5480,7 +5460,7 @@
       <c r="E15" t="s">
         <v>842</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>45736</v>
       </c>
       <c r="G15" t="s">
@@ -5490,7 +5470,7 @@
         <v>1353</v>
       </c>
       <c r="I15">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K15" t="s">
         <v>1359</v>
@@ -5518,7 +5498,7 @@
       <c r="E16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>45736</v>
       </c>
       <c r="G16" t="s">
@@ -5528,7 +5508,7 @@
         <v>1353</v>
       </c>
       <c r="I16">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K16" t="s">
         <v>1356</v>
@@ -5556,7 +5536,7 @@
       <c r="E17" t="s">
         <v>844</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>45736</v>
       </c>
       <c r="G17" t="s">
@@ -5566,7 +5546,7 @@
         <v>1353</v>
       </c>
       <c r="I17">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J17">
         <v>161</v>
@@ -5577,7 +5557,7 @@
       <c r="L17" t="s">
         <v>1368</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="1">
         <v>45897</v>
       </c>
       <c r="Q17" t="b">
@@ -5600,7 +5580,7 @@
       <c r="E18" t="s">
         <v>845</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="1">
         <v>45736</v>
       </c>
       <c r="G18" t="s">
@@ -5610,7 +5590,7 @@
         <v>1353</v>
       </c>
       <c r="I18">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J18">
         <v>66</v>
@@ -5621,7 +5601,7 @@
       <c r="L18" t="s">
         <v>1373</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" s="1">
         <v>45802</v>
       </c>
       <c r="Q18" t="b">
@@ -5644,7 +5624,7 @@
       <c r="E19" t="s">
         <v>846</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="1">
         <v>45736</v>
       </c>
       <c r="G19" t="s">
@@ -5673,7 +5653,7 @@
       <c r="E20" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="1">
         <v>45736</v>
       </c>
       <c r="G20" t="s">
@@ -5683,7 +5663,7 @@
         <v>1353</v>
       </c>
       <c r="I20">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J20">
         <v>399</v>
@@ -5694,7 +5674,7 @@
       <c r="L20" t="s">
         <v>1374</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20" s="1">
         <v>46135</v>
       </c>
       <c r="Q20" t="b">
@@ -5717,7 +5697,7 @@
       <c r="E21" t="s">
         <v>848</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="1">
         <v>45736</v>
       </c>
       <c r="G21" t="s">
@@ -5746,7 +5726,7 @@
       <c r="E22" t="s">
         <v>849</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="1">
         <v>45736</v>
       </c>
       <c r="G22" t="s">
@@ -5756,7 +5736,7 @@
         <v>1353</v>
       </c>
       <c r="I22">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K22" t="s">
         <v>1360</v>
@@ -5784,7 +5764,7 @@
       <c r="E23" t="s">
         <v>850</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="1">
         <v>45736</v>
       </c>
       <c r="G23" t="s">
@@ -5794,7 +5774,7 @@
         <v>1353</v>
       </c>
       <c r="I23">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J23">
         <v>229</v>
@@ -5805,7 +5785,7 @@
       <c r="L23" t="s">
         <v>1375</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="1">
         <v>45965</v>
       </c>
       <c r="P23" t="s">
@@ -5831,7 +5811,7 @@
       <c r="E24" t="s">
         <v>851</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="1">
         <v>45736</v>
       </c>
       <c r="G24" t="s">
@@ -5860,7 +5840,7 @@
       <c r="E25" t="s">
         <v>852</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="1">
         <v>45736</v>
       </c>
       <c r="G25" t="s">
@@ -5889,7 +5869,7 @@
       <c r="E26" t="s">
         <v>853</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="1">
         <v>45736</v>
       </c>
       <c r="G26" t="s">
@@ -5899,7 +5879,7 @@
         <v>1353</v>
       </c>
       <c r="I26">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J26">
         <v>155</v>
@@ -5910,7 +5890,7 @@
       <c r="L26" t="s">
         <v>1376</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" s="1">
         <v>45891</v>
       </c>
       <c r="P26" t="s">
@@ -5936,7 +5916,7 @@
       <c r="E27" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="1">
         <v>45736</v>
       </c>
       <c r="G27" t="s">
@@ -5946,7 +5926,7 @@
         <v>1353</v>
       </c>
       <c r="I27">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K27" t="s">
         <v>1360</v>
@@ -5974,7 +5954,7 @@
       <c r="E28" t="s">
         <v>855</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="1">
         <v>45736</v>
       </c>
       <c r="G28" t="s">
@@ -6003,7 +5983,7 @@
       <c r="E29" t="s">
         <v>856</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="1">
         <v>45736</v>
       </c>
       <c r="G29" t="s">
@@ -6032,7 +6012,7 @@
       <c r="E30" t="s">
         <v>857</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="1">
         <v>45736</v>
       </c>
       <c r="G30" t="s">
@@ -6042,7 +6022,7 @@
         <v>1353</v>
       </c>
       <c r="I30">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J30">
         <v>209</v>
@@ -6053,7 +6033,7 @@
       <c r="L30" t="s">
         <v>1377</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" s="1">
         <v>45945</v>
       </c>
       <c r="Q30" t="b">
@@ -6076,7 +6056,7 @@
       <c r="E31" t="s">
         <v>858</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="1">
         <v>45736</v>
       </c>
       <c r="G31" t="s">
@@ -6105,7 +6085,7 @@
       <c r="E32" t="s">
         <v>859</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="1">
         <v>45736</v>
       </c>
       <c r="G32" t="s">
@@ -6115,7 +6095,7 @@
         <v>1353</v>
       </c>
       <c r="I32">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K32" t="s">
         <v>1356</v>
@@ -6143,7 +6123,7 @@
       <c r="E33" t="s">
         <v>860</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>45736</v>
       </c>
       <c r="G33" t="s">
@@ -6172,7 +6152,7 @@
       <c r="E34" t="s">
         <v>861</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="1">
         <v>45736</v>
       </c>
       <c r="G34" t="s">
@@ -6201,7 +6181,7 @@
       <c r="E35" t="s">
         <v>862</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="1">
         <v>45736</v>
       </c>
       <c r="G35" t="s">
@@ -6230,7 +6210,7 @@
       <c r="E36" t="s">
         <v>863</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="1">
         <v>45736</v>
       </c>
       <c r="G36" t="s">
@@ -6259,7 +6239,7 @@
       <c r="E37" t="s">
         <v>864</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>45736</v>
       </c>
       <c r="G37" t="s">
@@ -6288,7 +6268,7 @@
       <c r="E38" t="s">
         <v>844</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="1">
         <v>45736</v>
       </c>
       <c r="G38" t="s">
@@ -6314,7 +6294,7 @@
       <c r="D39" t="s">
         <v>731</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="1">
         <v>45736</v>
       </c>
       <c r="G39" t="s">
@@ -6324,7 +6304,7 @@
         <v>1353</v>
       </c>
       <c r="I39">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K39" t="s">
         <v>1361</v>
@@ -6349,7 +6329,7 @@
       <c r="D40" t="s">
         <v>731</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="1">
         <v>45736</v>
       </c>
       <c r="G40" t="s">
@@ -6359,7 +6339,7 @@
         <v>1353</v>
       </c>
       <c r="I40">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K40" t="s">
         <v>1359</v>
@@ -6387,7 +6367,7 @@
       <c r="E41" t="s">
         <v>865</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="1">
         <v>45736</v>
       </c>
       <c r="G41" t="s">
@@ -6416,7 +6396,7 @@
       <c r="E42" t="s">
         <v>866</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="1">
         <v>45736</v>
       </c>
       <c r="G42" t="s">
@@ -6445,7 +6425,7 @@
       <c r="E43" t="s">
         <v>867</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="1">
         <v>45736</v>
       </c>
       <c r="G43" t="s">
@@ -6480,7 +6460,7 @@
       <c r="E44" t="s">
         <v>868</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="1">
         <v>45769</v>
       </c>
       <c r="G44" t="s">
@@ -6490,7 +6470,7 @@
         <v>1353</v>
       </c>
       <c r="I44">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J44">
         <v>87</v>
@@ -6501,7 +6481,7 @@
       <c r="L44" t="s">
         <v>1378</v>
       </c>
-      <c r="N44" s="2">
+      <c r="N44" s="1">
         <v>45856</v>
       </c>
       <c r="P44" t="s">
@@ -6527,7 +6507,7 @@
       <c r="E45" t="s">
         <v>869</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="1">
         <v>45769</v>
       </c>
       <c r="G45" t="s">
@@ -6537,7 +6517,7 @@
         <v>1353</v>
       </c>
       <c r="I45">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J45">
         <v>331</v>
@@ -6548,7 +6528,7 @@
       <c r="L45" t="s">
         <v>1379</v>
       </c>
-      <c r="N45" s="2">
+      <c r="N45" s="1">
         <v>46100</v>
       </c>
       <c r="O45">
@@ -6574,7 +6554,7 @@
       <c r="E46" t="s">
         <v>870</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="1">
         <v>45769</v>
       </c>
       <c r="G46" t="s">
@@ -6584,7 +6564,7 @@
         <v>1353</v>
       </c>
       <c r="I46">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K46" t="s">
         <v>1360</v>
@@ -6612,7 +6592,7 @@
       <c r="E47" t="s">
         <v>871</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="1">
         <v>45769</v>
       </c>
       <c r="G47" t="s">
@@ -6622,7 +6602,7 @@
         <v>1353</v>
       </c>
       <c r="I47">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J47">
         <v>344</v>
@@ -6633,7 +6613,7 @@
       <c r="L47" t="s">
         <v>1380</v>
       </c>
-      <c r="N47" s="2">
+      <c r="N47" s="1">
         <v>46113</v>
       </c>
       <c r="P47" t="s">
@@ -6659,7 +6639,7 @@
       <c r="E48" t="s">
         <v>872</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="1">
         <v>45769</v>
       </c>
       <c r="G48" t="s">
@@ -6669,7 +6649,7 @@
         <v>1353</v>
       </c>
       <c r="I48">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K48" t="s">
         <v>1360</v>
@@ -6697,7 +6677,7 @@
       <c r="E49" t="s">
         <v>873</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="1">
         <v>45769</v>
       </c>
       <c r="G49" t="s">
@@ -6726,7 +6706,7 @@
       <c r="E50" t="s">
         <v>874</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="1">
         <v>45769</v>
       </c>
       <c r="G50" t="s">
@@ -6736,7 +6716,7 @@
         <v>1353</v>
       </c>
       <c r="I50">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K50" t="s">
         <v>1360</v>
@@ -6764,7 +6744,7 @@
       <c r="E51" t="s">
         <v>875</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="1">
         <v>45769</v>
       </c>
       <c r="G51" t="s">
@@ -6793,7 +6773,7 @@
       <c r="E52" t="s">
         <v>876</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="1">
         <v>45769</v>
       </c>
       <c r="G52" t="s">
@@ -6803,7 +6783,7 @@
         <v>1353</v>
       </c>
       <c r="I52">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K52" t="s">
         <v>1356</v>
@@ -6831,7 +6811,7 @@
       <c r="E53" t="s">
         <v>877</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="1">
         <v>45769</v>
       </c>
       <c r="G53" t="s">
@@ -6841,7 +6821,7 @@
         <v>1353</v>
       </c>
       <c r="I53">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K53" t="s">
         <v>1357</v>
@@ -6869,7 +6849,7 @@
       <c r="E54" t="s">
         <v>878</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="1">
         <v>45769</v>
       </c>
       <c r="G54" t="s">
@@ -6879,7 +6859,7 @@
         <v>1353</v>
       </c>
       <c r="I54">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K54" t="s">
         <v>1357</v>
@@ -6907,7 +6887,7 @@
       <c r="E55" t="s">
         <v>879</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="1">
         <v>45769</v>
       </c>
       <c r="G55" t="s">
@@ -6936,7 +6916,7 @@
       <c r="E56" t="s">
         <v>880</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="1">
         <v>45769</v>
       </c>
       <c r="G56" t="s">
@@ -6965,7 +6945,7 @@
       <c r="E57" t="s">
         <v>881</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="1">
         <v>45769</v>
       </c>
       <c r="G57" t="s">
@@ -6975,7 +6955,7 @@
         <v>1353</v>
       </c>
       <c r="I57">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K57" t="s">
         <v>1360</v>
@@ -7003,7 +6983,7 @@
       <c r="E58" t="s">
         <v>882</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="1">
         <v>45769</v>
       </c>
       <c r="G58" t="s">
@@ -7032,7 +7012,7 @@
       <c r="E59" t="s">
         <v>883</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="1">
         <v>45769</v>
       </c>
       <c r="G59" t="s">
@@ -7061,7 +7041,7 @@
       <c r="E60" t="s">
         <v>884</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="1">
         <v>45769</v>
       </c>
       <c r="G60" t="s">
@@ -7090,7 +7070,7 @@
       <c r="E61" t="s">
         <v>885</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="1">
         <v>45769</v>
       </c>
       <c r="G61" t="s">
@@ -7119,7 +7099,7 @@
       <c r="E62" t="s">
         <v>886</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="1">
         <v>45770</v>
       </c>
       <c r="G62" t="s">
@@ -7148,7 +7128,7 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="1">
         <v>45799</v>
       </c>
       <c r="G63" t="s">
@@ -7158,7 +7138,7 @@
         <v>1353</v>
       </c>
       <c r="I63">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J63">
         <v>293</v>
@@ -7169,7 +7149,7 @@
       <c r="L63" t="s">
         <v>1381</v>
       </c>
-      <c r="N63" s="2">
+      <c r="N63" s="1">
         <v>46092</v>
       </c>
       <c r="P63" t="s">
@@ -7195,7 +7175,7 @@
       <c r="E64" t="s">
         <v>888</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="1">
         <v>45799</v>
       </c>
       <c r="G64" t="s">
@@ -7205,7 +7185,7 @@
         <v>1353</v>
       </c>
       <c r="I64">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J64">
         <v>320</v>
@@ -7216,7 +7196,7 @@
       <c r="L64" t="s">
         <v>1382</v>
       </c>
-      <c r="N64" s="2">
+      <c r="N64" s="1">
         <v>46119</v>
       </c>
       <c r="Q64" t="b">
@@ -7239,7 +7219,7 @@
       <c r="E65" t="s">
         <v>889</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="1">
         <v>45799</v>
       </c>
       <c r="G65" t="s">
@@ -7268,7 +7248,7 @@
       <c r="E66" t="s">
         <v>890</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="1">
         <v>45799</v>
       </c>
       <c r="G66" t="s">
@@ -7297,7 +7277,7 @@
       <c r="E67" t="s">
         <v>891</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="1">
         <v>45799</v>
       </c>
       <c r="G67" t="s">
@@ -7326,7 +7306,7 @@
       <c r="E68" t="s">
         <v>892</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="1">
         <v>45799</v>
       </c>
       <c r="G68" t="s">
@@ -7355,7 +7335,7 @@
       <c r="E69" t="s">
         <v>893</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="1">
         <v>45803</v>
       </c>
       <c r="G69" t="s">
@@ -7384,7 +7364,7 @@
       <c r="E70" t="s">
         <v>894</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="1">
         <v>45803</v>
       </c>
       <c r="G70" t="s">
@@ -7394,7 +7374,7 @@
         <v>1353</v>
       </c>
       <c r="I70">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J70">
         <v>429</v>
@@ -7405,7 +7385,7 @@
       <c r="L70" t="s">
         <v>1383</v>
       </c>
-      <c r="N70" s="2">
+      <c r="N70" s="1">
         <v>46232</v>
       </c>
       <c r="Q70" t="b">
@@ -7428,7 +7408,7 @@
       <c r="E71" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="1">
         <v>45803</v>
       </c>
       <c r="G71" t="s">
@@ -7438,7 +7418,7 @@
         <v>1353</v>
       </c>
       <c r="I71">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J71">
         <v>429</v>
@@ -7449,7 +7429,7 @@
       <c r="L71" t="s">
         <v>1383</v>
       </c>
-      <c r="N71" s="2">
+      <c r="N71" s="1">
         <v>46232</v>
       </c>
       <c r="Q71" t="b">
@@ -7472,7 +7452,7 @@
       <c r="E72" t="s">
         <v>896</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="1">
         <v>45803</v>
       </c>
       <c r="G72" t="s">
@@ -7501,7 +7481,7 @@
       <c r="E73" t="s">
         <v>897</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="1">
         <v>45803</v>
       </c>
       <c r="G73" t="s">
@@ -7511,7 +7491,7 @@
         <v>1353</v>
       </c>
       <c r="I73">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K73" t="s">
         <v>1356</v>
@@ -7539,7 +7519,7 @@
       <c r="E74" t="s">
         <v>896</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="1">
         <v>45803</v>
       </c>
       <c r="G74" t="s">
@@ -7568,7 +7548,7 @@
       <c r="E75" t="s">
         <v>898</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="1">
         <v>45803</v>
       </c>
       <c r="G75" t="s">
@@ -7578,7 +7558,7 @@
         <v>1353</v>
       </c>
       <c r="I75">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J75">
         <v>429</v>
@@ -7589,7 +7569,7 @@
       <c r="L75" t="s">
         <v>1383</v>
       </c>
-      <c r="N75" s="2">
+      <c r="N75" s="1">
         <v>46232</v>
       </c>
       <c r="Q75" t="b">
@@ -7612,7 +7592,7 @@
       <c r="E76" t="s">
         <v>899</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="1">
         <v>45803</v>
       </c>
       <c r="G76" t="s">
@@ -7622,7 +7602,7 @@
         <v>1353</v>
       </c>
       <c r="I76">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K76" t="s">
         <v>1363</v>
@@ -7647,7 +7627,7 @@
       <c r="E77" t="s">
         <v>900</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="1">
         <v>45803</v>
       </c>
       <c r="G77" t="s">
@@ -7676,7 +7656,7 @@
       <c r="E78" t="s">
         <v>901</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="1">
         <v>45803</v>
       </c>
       <c r="G78" t="s">
@@ -7705,7 +7685,7 @@
       <c r="E79" t="s">
         <v>902</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="1">
         <v>45803</v>
       </c>
       <c r="G79" t="s">
@@ -7715,7 +7695,7 @@
         <v>1353</v>
       </c>
       <c r="I79">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K79" t="s">
         <v>1363</v>
@@ -7740,7 +7720,7 @@
       <c r="E80" t="s">
         <v>903</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="1">
         <v>45803</v>
       </c>
       <c r="G80" t="s">
@@ -7750,7 +7730,7 @@
         <v>1353</v>
       </c>
       <c r="I80">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J80">
         <v>429</v>
@@ -7761,7 +7741,7 @@
       <c r="L80" t="s">
         <v>1383</v>
       </c>
-      <c r="N80" s="2">
+      <c r="N80" s="1">
         <v>46232</v>
       </c>
       <c r="Q80" t="b">
@@ -7784,7 +7764,7 @@
       <c r="E81" t="s">
         <v>904</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="1">
         <v>45813</v>
       </c>
       <c r="G81" t="s">
@@ -7813,7 +7793,7 @@
       <c r="E82" t="s">
         <v>905</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="1">
         <v>45813</v>
       </c>
       <c r="G82" t="s">
@@ -7823,7 +7803,7 @@
         <v>1353</v>
       </c>
       <c r="I82">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K82" t="s">
         <v>1360</v>
@@ -7851,7 +7831,7 @@
       <c r="E83" t="s">
         <v>906</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="1">
         <v>45813</v>
       </c>
       <c r="G83" t="s">
@@ -7880,7 +7860,7 @@
       <c r="E84" t="s">
         <v>907</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="1">
         <v>45813</v>
       </c>
       <c r="G84" t="s">
@@ -7890,7 +7870,7 @@
         <v>1353</v>
       </c>
       <c r="I84">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J84">
         <v>40</v>
@@ -7901,7 +7881,7 @@
       <c r="L84" t="s">
         <v>1384</v>
       </c>
-      <c r="N84" s="2">
+      <c r="N84" s="1">
         <v>45853</v>
       </c>
       <c r="O84">
@@ -7927,7 +7907,7 @@
       <c r="E85" t="s">
         <v>908</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="1">
         <v>45813</v>
       </c>
       <c r="G85" t="s">
@@ -7937,7 +7917,7 @@
         <v>1353</v>
       </c>
       <c r="I85">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K85" t="s">
         <v>1357</v>
@@ -7965,7 +7945,7 @@
       <c r="E86" t="s">
         <v>909</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="1">
         <v>45813</v>
       </c>
       <c r="G86" t="s">
@@ -7975,7 +7955,7 @@
         <v>1353</v>
       </c>
       <c r="I86">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K86" t="s">
         <v>1357</v>
@@ -8003,7 +7983,7 @@
       <c r="E87" t="s">
         <v>910</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="1">
         <v>45813</v>
       </c>
       <c r="G87" t="s">
@@ -8013,7 +7993,7 @@
         <v>1353</v>
       </c>
       <c r="I87">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J87">
         <v>-16</v>
@@ -8024,7 +8004,7 @@
       <c r="L87" t="s">
         <v>1385</v>
       </c>
-      <c r="N87" s="2">
+      <c r="N87" s="1">
         <v>45797</v>
       </c>
       <c r="O87" t="s">
@@ -8050,7 +8030,7 @@
       <c r="E88" t="s">
         <v>911</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="1">
         <v>45813</v>
       </c>
       <c r="G88" t="s">
@@ -8065,7 +8045,7 @@
       <c r="L88" t="s">
         <v>1386</v>
       </c>
-      <c r="N88" s="2">
+      <c r="N88" s="1">
         <v>46195</v>
       </c>
       <c r="Q88" t="b">
@@ -8088,7 +8068,7 @@
       <c r="E89" t="s">
         <v>912</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="1">
         <v>45813</v>
       </c>
       <c r="G89" t="s">
@@ -8103,7 +8083,7 @@
       <c r="L89" t="s">
         <v>1386</v>
       </c>
-      <c r="N89" s="2">
+      <c r="N89" s="1">
         <v>46195</v>
       </c>
       <c r="Q89" t="b">
@@ -8126,7 +8106,7 @@
       <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="1">
         <v>45831</v>
       </c>
       <c r="G90" t="s">
@@ -8136,7 +8116,7 @@
         <v>1353</v>
       </c>
       <c r="I90">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K90" t="s">
         <v>1330</v>
@@ -8167,7 +8147,7 @@
       <c r="E91" t="s">
         <v>914</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="1">
         <v>45831</v>
       </c>
       <c r="G91" t="s">
@@ -8177,7 +8157,7 @@
         <v>1353</v>
       </c>
       <c r="I91">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J91">
         <v>308</v>
@@ -8188,7 +8168,7 @@
       <c r="L91" t="s">
         <v>1388</v>
       </c>
-      <c r="N91" s="2">
+      <c r="N91" s="1">
         <v>46139</v>
       </c>
       <c r="Q91" t="b">
@@ -8208,7 +8188,7 @@
       <c r="D92" t="s">
         <v>748</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="1">
         <v>45831</v>
       </c>
       <c r="G92" t="s">
@@ -8237,7 +8217,7 @@
       <c r="E93" t="s">
         <v>915</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="1">
         <v>45831</v>
       </c>
       <c r="G93" t="s">
@@ -8247,7 +8227,7 @@
         <v>1353</v>
       </c>
       <c r="I93">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J93">
         <v>308</v>
@@ -8258,7 +8238,7 @@
       <c r="L93" t="s">
         <v>1388</v>
       </c>
-      <c r="N93" s="2">
+      <c r="N93" s="1">
         <v>46139</v>
       </c>
       <c r="Q93" t="b">
@@ -8281,7 +8261,7 @@
       <c r="E94" t="s">
         <v>916</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="1">
         <v>45831</v>
       </c>
       <c r="G94" t="s">
@@ -8291,7 +8271,7 @@
         <v>1353</v>
       </c>
       <c r="I94">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K94" t="s">
         <v>1360</v>
@@ -8319,7 +8299,7 @@
       <c r="E95" t="s">
         <v>917</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="1">
         <v>45831</v>
       </c>
       <c r="G95" t="s">
@@ -8329,7 +8309,7 @@
         <v>1353</v>
       </c>
       <c r="I95">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J95">
         <v>308</v>
@@ -8340,7 +8320,7 @@
       <c r="L95" t="s">
         <v>1388</v>
       </c>
-      <c r="N95" s="2">
+      <c r="N95" s="1">
         <v>46139</v>
       </c>
       <c r="Q95" t="b">
@@ -8363,7 +8343,7 @@
       <c r="E96" t="s">
         <v>918</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="1">
         <v>45831</v>
       </c>
       <c r="G96" t="s">
@@ -8373,7 +8353,7 @@
         <v>1353</v>
       </c>
       <c r="I96">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J96">
         <v>17</v>
@@ -8384,7 +8364,7 @@
       <c r="L96" t="s">
         <v>1369</v>
       </c>
-      <c r="N96" s="2">
+      <c r="N96" s="1">
         <v>45848</v>
       </c>
       <c r="O96" t="s">
@@ -8410,7 +8390,7 @@
       <c r="E97" t="s">
         <v>919</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="1">
         <v>45840</v>
       </c>
       <c r="G97" t="s">
@@ -8420,7 +8400,7 @@
         <v>1353</v>
       </c>
       <c r="I97">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J97">
         <v>20</v>
@@ -8431,7 +8411,7 @@
       <c r="L97" t="s">
         <v>1389</v>
       </c>
-      <c r="N97" s="2">
+      <c r="N97" s="1">
         <v>45860</v>
       </c>
       <c r="P97" t="s">
@@ -8457,7 +8437,7 @@
       <c r="E98" t="s">
         <v>920</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="1">
         <v>45840</v>
       </c>
       <c r="G98" t="s">
@@ -8467,7 +8447,7 @@
         <v>1353</v>
       </c>
       <c r="I98">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K98" t="s">
         <v>1360</v>
@@ -8495,7 +8475,7 @@
       <c r="E99" t="s">
         <v>921</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="1">
         <v>45840</v>
       </c>
       <c r="G99" t="s">
@@ -8524,7 +8504,7 @@
       <c r="E100" t="s">
         <v>922</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="1">
         <v>45840</v>
       </c>
       <c r="G100" t="s">
@@ -8534,7 +8514,7 @@
         <v>1353</v>
       </c>
       <c r="I100">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J100">
         <v>348</v>
@@ -8545,7 +8525,7 @@
       <c r="L100" t="s">
         <v>1388</v>
       </c>
-      <c r="N100" s="2">
+      <c r="N100" s="1">
         <v>46188</v>
       </c>
       <c r="Q100" t="b">
@@ -8568,7 +8548,7 @@
       <c r="E101" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="1">
         <v>45840</v>
       </c>
       <c r="G101" t="s">
@@ -8597,7 +8577,7 @@
       <c r="E102" t="s">
         <v>924</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="1">
         <v>45840</v>
       </c>
       <c r="G102" t="s">
@@ -8626,7 +8606,7 @@
       <c r="E103" t="s">
         <v>925</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="1">
         <v>45840</v>
       </c>
       <c r="G103" t="s">
@@ -8655,7 +8635,7 @@
       <c r="E104" t="s">
         <v>926</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="1">
         <v>45840</v>
       </c>
       <c r="G104" t="s">
@@ -8665,7 +8645,7 @@
         <v>1353</v>
       </c>
       <c r="I104">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J104">
         <v>348</v>
@@ -8676,7 +8656,7 @@
       <c r="L104" t="s">
         <v>1388</v>
       </c>
-      <c r="N104" s="2">
+      <c r="N104" s="1">
         <v>46188</v>
       </c>
       <c r="Q104" t="b">
@@ -8699,7 +8679,7 @@
       <c r="E105" t="s">
         <v>927</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="1">
         <v>45840</v>
       </c>
       <c r="G105" t="s">
@@ -8709,7 +8689,7 @@
         <v>1353</v>
       </c>
       <c r="I105">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J105">
         <v>348</v>
@@ -8720,7 +8700,7 @@
       <c r="L105" t="s">
         <v>1388</v>
       </c>
-      <c r="N105" s="2">
+      <c r="N105" s="1">
         <v>46188</v>
       </c>
       <c r="Q105" t="b">
@@ -8743,7 +8723,7 @@
       <c r="E106" t="s">
         <v>928</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="1">
         <v>45840</v>
       </c>
       <c r="G106" t="s">
@@ -8753,7 +8733,7 @@
         <v>1353</v>
       </c>
       <c r="I106">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J106">
         <v>49</v>
@@ -8764,7 +8744,7 @@
       <c r="L106" t="s">
         <v>1390</v>
       </c>
-      <c r="N106" s="2">
+      <c r="N106" s="1">
         <v>45889</v>
       </c>
       <c r="Q106" t="b">
@@ -8787,7 +8767,7 @@
       <c r="E107" t="s">
         <v>929</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="1">
         <v>45840</v>
       </c>
       <c r="G107" t="s">
@@ -8797,7 +8777,7 @@
         <v>1353</v>
       </c>
       <c r="I107">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J107">
         <v>36</v>
@@ -8808,7 +8788,7 @@
       <c r="L107" t="s">
         <v>1391</v>
       </c>
-      <c r="N107" s="2">
+      <c r="N107" s="1">
         <v>45876</v>
       </c>
       <c r="Q107" t="b">
@@ -8831,7 +8811,7 @@
       <c r="E108" t="s">
         <v>930</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="1">
         <v>45840</v>
       </c>
       <c r="G108" t="s">
@@ -8841,7 +8821,7 @@
         <v>1353</v>
       </c>
       <c r="I108">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K108" t="s">
         <v>1357</v>
@@ -8869,7 +8849,7 @@
       <c r="E109" t="s">
         <v>931</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="1">
         <v>45840</v>
       </c>
       <c r="G109" t="s">
@@ -8879,7 +8859,7 @@
         <v>1353</v>
       </c>
       <c r="I109">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K109" t="s">
         <v>1357</v>
@@ -8907,7 +8887,7 @@
       <c r="E110" t="s">
         <v>932</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="1">
         <v>45840</v>
       </c>
       <c r="G110" t="s">
@@ -8936,7 +8916,7 @@
       <c r="E111" t="s">
         <v>933</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="1">
         <v>45840</v>
       </c>
       <c r="G111" t="s">
@@ -8965,7 +8945,7 @@
       <c r="E112" t="s">
         <v>934</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="1">
         <v>45840</v>
       </c>
       <c r="G112" t="s">
@@ -8994,7 +8974,7 @@
       <c r="E113" t="s">
         <v>935</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="1">
         <v>45840</v>
       </c>
       <c r="G113" t="s">
@@ -9023,7 +9003,7 @@
       <c r="E114" t="s">
         <v>936</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="1">
         <v>45840</v>
       </c>
       <c r="G114" t="s">
@@ -9052,7 +9032,7 @@
       <c r="E115" t="s">
         <v>937</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="1">
         <v>45840</v>
       </c>
       <c r="G115" t="s">
@@ -9062,7 +9042,7 @@
         <v>1353</v>
       </c>
       <c r="I115">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K115" t="s">
         <v>1357</v>
@@ -9090,7 +9070,7 @@
       <c r="E116" t="s">
         <v>938</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="1">
         <v>45840</v>
       </c>
       <c r="G116" t="s">
@@ -9100,7 +9080,7 @@
         <v>1353</v>
       </c>
       <c r="I116">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K116" t="s">
         <v>1357</v>
@@ -9128,7 +9108,7 @@
       <c r="E117" t="s">
         <v>939</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="1">
         <v>45840</v>
       </c>
       <c r="G117" t="s">
@@ -9138,7 +9118,7 @@
         <v>1353</v>
       </c>
       <c r="I117">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K117" t="s">
         <v>1357</v>
@@ -9166,7 +9146,7 @@
       <c r="E118" t="s">
         <v>940</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="1">
         <v>45840</v>
       </c>
       <c r="G118" t="s">
@@ -9176,7 +9156,7 @@
         <v>1353</v>
       </c>
       <c r="I118">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K118" t="s">
         <v>1357</v>
@@ -9204,7 +9184,7 @@
       <c r="E119" t="s">
         <v>941</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="1">
         <v>45840</v>
       </c>
       <c r="G119" t="s">
@@ -9214,7 +9194,7 @@
         <v>1353</v>
       </c>
       <c r="I119">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K119" t="s">
         <v>1357</v>
@@ -9242,7 +9222,7 @@
       <c r="E120" t="s">
         <v>942</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="1">
         <v>45840</v>
       </c>
       <c r="G120" t="s">
@@ -9252,7 +9232,7 @@
         <v>1353</v>
       </c>
       <c r="I120">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K120" t="s">
         <v>1357</v>
@@ -9280,7 +9260,7 @@
       <c r="E121" t="s">
         <v>943</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="1">
         <v>45849</v>
       </c>
       <c r="G121" t="s">
@@ -9290,7 +9270,7 @@
         <v>1353</v>
       </c>
       <c r="I121">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J121">
         <v>251</v>
@@ -9301,7 +9281,7 @@
       <c r="L121" t="s">
         <v>1379</v>
       </c>
-      <c r="N121" s="2">
+      <c r="N121" s="1">
         <v>46100</v>
       </c>
       <c r="O121">
@@ -9327,7 +9307,7 @@
       <c r="E122" t="s">
         <v>944</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="1">
         <v>45849</v>
       </c>
       <c r="G122" t="s">
@@ -9337,7 +9317,7 @@
         <v>1353</v>
       </c>
       <c r="I122">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K122" t="s">
         <v>1357</v>
@@ -9365,7 +9345,7 @@
       <c r="E123" t="s">
         <v>945</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="1">
         <v>45849</v>
       </c>
       <c r="G123" t="s">
@@ -9394,7 +9374,7 @@
       <c r="E124" t="s">
         <v>946</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="1">
         <v>45853</v>
       </c>
       <c r="G124" t="s">
@@ -9404,7 +9384,7 @@
         <v>1353</v>
       </c>
       <c r="I124">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K124" t="s">
         <v>1357</v>
@@ -9432,7 +9412,7 @@
       <c r="E125" t="s">
         <v>947</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="1">
         <v>45855</v>
       </c>
       <c r="G125" t="s">
@@ -9442,7 +9422,7 @@
         <v>1353</v>
       </c>
       <c r="I125">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K125" t="s">
         <v>1363</v>
@@ -9470,7 +9450,7 @@
       <c r="E126" t="s">
         <v>948</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="1">
         <v>45855</v>
       </c>
       <c r="G126" t="s">
@@ -9499,7 +9479,7 @@
       <c r="E127" t="s">
         <v>949</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="1">
         <v>45856</v>
       </c>
       <c r="G127" t="s">
@@ -9528,7 +9508,7 @@
       <c r="E128" t="s">
         <v>950</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="1">
         <v>45869</v>
       </c>
       <c r="G128" t="s">
@@ -9538,7 +9518,7 @@
         <v>1353</v>
       </c>
       <c r="I128">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K128" t="s">
         <v>1357</v>
@@ -9566,7 +9546,7 @@
       <c r="E129" t="s">
         <v>951</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="1">
         <v>45869</v>
       </c>
       <c r="G129" t="s">
@@ -9576,7 +9556,7 @@
         <v>1353</v>
       </c>
       <c r="I129">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K129" t="s">
         <v>1356</v>
@@ -9604,7 +9584,7 @@
       <c r="E130" t="s">
         <v>952</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="1">
         <v>45869</v>
       </c>
       <c r="G130" t="s">
@@ -9614,7 +9594,7 @@
         <v>1353</v>
       </c>
       <c r="I130">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J130">
         <v>47</v>
@@ -9625,7 +9605,7 @@
       <c r="L130" t="s">
         <v>1392</v>
       </c>
-      <c r="N130" s="2">
+      <c r="N130" s="1">
         <v>45916</v>
       </c>
       <c r="O130">
@@ -9651,7 +9631,7 @@
       <c r="E131" t="s">
         <v>953</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="1">
         <v>45869</v>
       </c>
       <c r="G131" t="s">
@@ -9680,7 +9660,7 @@
       <c r="E132" t="s">
         <v>954</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="1">
         <v>45869</v>
       </c>
       <c r="G132" t="s">
@@ -9690,7 +9670,7 @@
         <v>1353</v>
       </c>
       <c r="I132">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J132">
         <v>145</v>
@@ -9701,7 +9681,7 @@
       <c r="L132" t="s">
         <v>1393</v>
       </c>
-      <c r="N132" s="2">
+      <c r="N132" s="1">
         <v>46014</v>
       </c>
       <c r="O132">
@@ -9727,7 +9707,7 @@
       <c r="E133" t="s">
         <v>955</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="1">
         <v>45869</v>
       </c>
       <c r="G133" t="s">
@@ -9756,7 +9736,7 @@
       <c r="E134" t="s">
         <v>956</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="1">
         <v>45882</v>
       </c>
       <c r="G134" t="s">
@@ -9766,7 +9746,7 @@
         <v>1353</v>
       </c>
       <c r="I134">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K134" t="s">
         <v>1356</v>
@@ -9794,7 +9774,7 @@
       <c r="E135" t="s">
         <v>957</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="1">
         <v>45882</v>
       </c>
       <c r="G135" t="s">
@@ -9823,7 +9803,7 @@
       <c r="E136" t="s">
         <v>958</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="1">
         <v>45891</v>
       </c>
       <c r="G136" t="s">
@@ -9852,7 +9832,7 @@
       <c r="E137" t="s">
         <v>959</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="1">
         <v>45891</v>
       </c>
       <c r="G137" t="s">
@@ -9881,7 +9861,7 @@
       <c r="E138" t="s">
         <v>960</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="1">
         <v>45891</v>
       </c>
       <c r="G138" t="s">
@@ -9891,7 +9871,7 @@
         <v>1353</v>
       </c>
       <c r="I138">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K138" t="s">
         <v>1357</v>
@@ -9919,7 +9899,7 @@
       <c r="E139" t="s">
         <v>961</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="1">
         <v>45891</v>
       </c>
       <c r="G139" t="s">
@@ -9948,7 +9928,7 @@
       <c r="E140" t="s">
         <v>962</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="1">
         <v>45891</v>
       </c>
       <c r="G140" t="s">
@@ -9977,7 +9957,7 @@
       <c r="E141" t="s">
         <v>963</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="1">
         <v>45891</v>
       </c>
       <c r="G141" t="s">
@@ -10006,7 +9986,7 @@
       <c r="E142" t="s">
         <v>964</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="1">
         <v>45891</v>
       </c>
       <c r="G142" t="s">
@@ -10035,7 +10015,7 @@
       <c r="E143" t="s">
         <v>965</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="1">
         <v>45891</v>
       </c>
       <c r="G143" t="s">
@@ -10064,7 +10044,7 @@
       <c r="E144" t="s">
         <v>966</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="1">
         <v>45891</v>
       </c>
       <c r="G144" t="s">
@@ -10093,7 +10073,7 @@
       <c r="E145" t="s">
         <v>967</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="1">
         <v>45891</v>
       </c>
       <c r="G145" t="s">
@@ -10122,7 +10102,7 @@
       <c r="E146" t="s">
         <v>968</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="1">
         <v>45891</v>
       </c>
       <c r="G146" t="s">
@@ -10151,7 +10131,7 @@
       <c r="E147" t="s">
         <v>969</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="1">
         <v>45891</v>
       </c>
       <c r="G147" t="s">
@@ -10180,7 +10160,7 @@
       <c r="E148" t="s">
         <v>970</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="1">
         <v>45891</v>
       </c>
       <c r="G148" t="s">
@@ -10190,7 +10170,7 @@
         <v>1353</v>
       </c>
       <c r="I148">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J148">
         <v>341</v>
@@ -10201,7 +10181,7 @@
       <c r="L148" t="s">
         <v>1383</v>
       </c>
-      <c r="N148" s="2">
+      <c r="N148" s="1">
         <v>46232</v>
       </c>
       <c r="Q148" t="b">
@@ -10224,7 +10204,7 @@
       <c r="E149" t="s">
         <v>971</v>
       </c>
-      <c r="F149" s="2">
+      <c r="F149" s="1">
         <v>45891</v>
       </c>
       <c r="G149" t="s">
@@ -10234,7 +10214,7 @@
         <v>1353</v>
       </c>
       <c r="I149">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J149">
         <v>374</v>
@@ -10245,7 +10225,7 @@
       <c r="L149" t="s">
         <v>1394</v>
       </c>
-      <c r="N149" s="2">
+      <c r="N149" s="1">
         <v>46265</v>
       </c>
       <c r="P149" t="s">
@@ -10271,7 +10251,7 @@
       <c r="E150" t="s">
         <v>972</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="1">
         <v>45891</v>
       </c>
       <c r="G150" t="s">
@@ -10281,7 +10261,7 @@
         <v>1353</v>
       </c>
       <c r="I150">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J150">
         <v>201</v>
@@ -10292,7 +10272,7 @@
       <c r="L150" t="s">
         <v>1381</v>
       </c>
-      <c r="N150" s="2">
+      <c r="N150" s="1">
         <v>46092</v>
       </c>
       <c r="P150" t="s">
@@ -10318,7 +10298,7 @@
       <c r="E151" t="s">
         <v>973</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="1">
         <v>45891</v>
       </c>
       <c r="G151" t="s">
@@ -10347,7 +10327,7 @@
       <c r="E152" t="s">
         <v>963</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="1">
         <v>45891</v>
       </c>
       <c r="G152" t="s">
@@ -10357,7 +10337,7 @@
         <v>1353</v>
       </c>
       <c r="I152">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J152">
         <v>228</v>
@@ -10368,7 +10348,7 @@
       <c r="L152" t="s">
         <v>1382</v>
       </c>
-      <c r="N152" s="2">
+      <c r="N152" s="1">
         <v>46119</v>
       </c>
       <c r="Q152" t="b">
@@ -10391,7 +10371,7 @@
       <c r="E153" t="s">
         <v>974</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="1">
         <v>45891</v>
       </c>
       <c r="G153" t="s">
@@ -10409,7 +10389,7 @@
       <c r="L153" t="s">
         <v>1383</v>
       </c>
-      <c r="N153" s="2">
+      <c r="N153" s="1">
         <v>46232</v>
       </c>
       <c r="Q153" t="b">
@@ -10432,7 +10412,7 @@
       <c r="E154" t="s">
         <v>975</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="1">
         <v>45891</v>
       </c>
       <c r="G154" t="s">
@@ -10461,7 +10441,7 @@
       <c r="E155" t="s">
         <v>976</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="1">
         <v>45891</v>
       </c>
       <c r="G155" t="s">
@@ -10471,7 +10451,7 @@
         <v>1353</v>
       </c>
       <c r="I155">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K155" t="s">
         <v>1363</v>
@@ -10496,7 +10476,7 @@
       <c r="E156" t="s">
         <v>977</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="1">
         <v>45891</v>
       </c>
       <c r="G156" t="s">
@@ -10506,7 +10486,7 @@
         <v>1353</v>
       </c>
       <c r="I156">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K156" t="s">
         <v>1357</v>
@@ -10534,7 +10514,7 @@
       <c r="E157" t="s">
         <v>978</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="1">
         <v>45891</v>
       </c>
       <c r="G157" t="s">
@@ -10544,7 +10524,7 @@
         <v>1353</v>
       </c>
       <c r="I157">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J157">
         <v>371</v>
@@ -10555,7 +10535,7 @@
       <c r="L157" t="s">
         <v>1395</v>
       </c>
-      <c r="N157" s="2">
+      <c r="N157" s="1">
         <v>46262</v>
       </c>
       <c r="Q157" t="b">
@@ -10578,7 +10558,7 @@
       <c r="E158" t="s">
         <v>979</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="1">
         <v>45894</v>
       </c>
       <c r="G158" t="s">
@@ -10588,7 +10568,7 @@
         <v>1353</v>
       </c>
       <c r="I158">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J158">
         <v>52</v>
@@ -10599,7 +10579,7 @@
       <c r="L158" t="s">
         <v>1396</v>
       </c>
-      <c r="N158" s="2">
+      <c r="N158" s="1">
         <v>45946</v>
       </c>
       <c r="Q158" t="b">
@@ -10622,7 +10602,7 @@
       <c r="E159" t="s">
         <v>980</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="1">
         <v>45894</v>
       </c>
       <c r="G159" t="s">
@@ -10632,7 +10612,7 @@
         <v>1353</v>
       </c>
       <c r="I159">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K159" t="s">
         <v>1357</v>
@@ -10660,7 +10640,7 @@
       <c r="E160" t="s">
         <v>981</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="1">
         <v>45898</v>
       </c>
       <c r="G160" t="s">
@@ -10670,7 +10650,7 @@
         <v>1353</v>
       </c>
       <c r="I160">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K160" t="s">
         <v>1357</v>
@@ -10698,7 +10678,7 @@
       <c r="E161" t="s">
         <v>982</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="1">
         <v>45898</v>
       </c>
       <c r="G161" t="s">
@@ -10708,7 +10688,7 @@
         <v>1353</v>
       </c>
       <c r="I161">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J161">
         <v>55</v>
@@ -10719,7 +10699,7 @@
       <c r="L161" t="s">
         <v>1397</v>
       </c>
-      <c r="N161" s="2">
+      <c r="N161" s="1">
         <v>45953</v>
       </c>
       <c r="O161" t="s">
@@ -10745,7 +10725,7 @@
       <c r="E162" t="s">
         <v>983</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="1">
         <v>45898</v>
       </c>
       <c r="G162" t="s">
@@ -10755,7 +10735,7 @@
         <v>1353</v>
       </c>
       <c r="I162">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J162">
         <v>42</v>
@@ -10766,8 +10746,11 @@
       <c r="L162" t="s">
         <v>1398</v>
       </c>
-      <c r="N162" s="2">
+      <c r="N162" s="1">
         <v>45940</v>
+      </c>
+      <c r="P162" t="s">
+        <v>1480</v>
       </c>
       <c r="Q162" t="b">
         <v>1</v>
@@ -10789,7 +10772,7 @@
       <c r="E163" t="s">
         <v>984</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="1">
         <v>45898</v>
       </c>
       <c r="G163" t="s">
@@ -10799,7 +10782,7 @@
         <v>1353</v>
       </c>
       <c r="I163">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J163">
         <v>42</v>
@@ -10810,8 +10793,11 @@
       <c r="L163" t="s">
         <v>1398</v>
       </c>
-      <c r="N163" s="2">
+      <c r="N163" s="1">
         <v>45940</v>
+      </c>
+      <c r="P163" t="s">
+        <v>1480</v>
       </c>
       <c r="Q163" t="b">
         <v>1</v>
@@ -10833,7 +10819,7 @@
       <c r="E164" t="s">
         <v>985</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="1">
         <v>45910</v>
       </c>
       <c r="G164" t="s">
@@ -10843,7 +10829,7 @@
         <v>1355</v>
       </c>
       <c r="I164">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O164" t="s">
         <v>1469</v>
@@ -10868,7 +10854,7 @@
       <c r="E165" t="s">
         <v>986</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="1">
         <v>45917</v>
       </c>
       <c r="G165" t="s">
@@ -10886,11 +10872,11 @@
       <c r="L165" t="s">
         <v>1399</v>
       </c>
-      <c r="N165" s="2">
+      <c r="N165" s="1">
         <v>46204</v>
       </c>
       <c r="P165" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="Q165" t="b">
         <v>0</v>
@@ -10912,7 +10898,7 @@
       <c r="E166" t="s">
         <v>987</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="1">
         <v>45917</v>
       </c>
       <c r="G166" t="s">
@@ -10941,7 +10927,7 @@
       <c r="E167" t="s">
         <v>988</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="1">
         <v>45917</v>
       </c>
       <c r="G167" t="s">
@@ -10970,7 +10956,7 @@
       <c r="E168" t="s">
         <v>989</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="1">
         <v>45917</v>
       </c>
       <c r="G168" t="s">
@@ -10980,7 +10966,7 @@
         <v>1353</v>
       </c>
       <c r="I168">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K168" t="s">
         <v>1360</v>
@@ -11011,7 +10997,7 @@
       <c r="E169" t="s">
         <v>990</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="1">
         <v>45917</v>
       </c>
       <c r="G169" t="s">
@@ -11021,7 +11007,7 @@
         <v>1353</v>
       </c>
       <c r="I169">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K169" t="s">
         <v>1330</v>
@@ -11029,7 +11015,7 @@
       <c r="L169" t="s">
         <v>1401</v>
       </c>
-      <c r="N169" s="2">
+      <c r="N169" s="1">
         <v>45973</v>
       </c>
       <c r="Q169" t="b">
@@ -11052,7 +11038,7 @@
       <c r="E170" t="s">
         <v>991</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="1">
         <v>45917</v>
       </c>
       <c r="G170" t="s">
@@ -11087,7 +11073,7 @@
       <c r="E171" t="s">
         <v>992</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="1">
         <v>45917</v>
       </c>
       <c r="G171" t="s">
@@ -11097,7 +11083,7 @@
         <v>1353</v>
       </c>
       <c r="I171">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K171" t="s">
         <v>1357</v>
@@ -11125,7 +11111,7 @@
       <c r="E172" t="s">
         <v>993</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="1">
         <v>45917</v>
       </c>
       <c r="G172" t="s">
@@ -11154,7 +11140,7 @@
       <c r="E173" t="s">
         <v>994</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="1">
         <v>45917</v>
       </c>
       <c r="G173" t="s">
@@ -11183,7 +11169,7 @@
       <c r="E174" t="s">
         <v>995</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="1">
         <v>45917</v>
       </c>
       <c r="G174" t="s">
@@ -11198,7 +11184,7 @@
       <c r="L174" t="s">
         <v>1386</v>
       </c>
-      <c r="N174" s="2">
+      <c r="N174" s="1">
         <v>46195</v>
       </c>
       <c r="Q174" t="b">
@@ -11221,7 +11207,7 @@
       <c r="E175" t="s">
         <v>996</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="1">
         <v>45917</v>
       </c>
       <c r="G175" t="s">
@@ -11231,7 +11217,7 @@
         <v>1353</v>
       </c>
       <c r="I175">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J175">
         <v>205</v>
@@ -11242,11 +11228,11 @@
       <c r="L175" t="s">
         <v>1402</v>
       </c>
-      <c r="N175" s="2">
+      <c r="N175" s="1">
         <v>46122</v>
       </c>
       <c r="P175" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Q175" t="b">
         <v>1</v>
@@ -11268,7 +11254,7 @@
       <c r="E176" t="s">
         <v>900</v>
       </c>
-      <c r="F176" s="2">
+      <c r="F176" s="1">
         <v>45917</v>
       </c>
       <c r="G176" t="s">
@@ -11278,7 +11264,7 @@
         <v>1353</v>
       </c>
       <c r="I176">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K176" t="s">
         <v>1357</v>
@@ -11306,7 +11292,7 @@
       <c r="E177" t="s">
         <v>997</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="1">
         <v>45917</v>
       </c>
       <c r="G177" t="s">
@@ -11316,7 +11302,7 @@
         <v>1353</v>
       </c>
       <c r="I177">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J177">
         <v>44</v>
@@ -11327,11 +11313,11 @@
       <c r="L177" t="s">
         <v>1403</v>
       </c>
-      <c r="N177" s="2">
+      <c r="N177" s="1">
         <v>45961</v>
       </c>
       <c r="P177" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="Q177" t="b">
         <v>1</v>
@@ -11353,7 +11339,7 @@
       <c r="E178" t="s">
         <v>998</v>
       </c>
-      <c r="F178" s="2">
+      <c r="F178" s="1">
         <v>45937</v>
       </c>
       <c r="G178" t="s">
@@ -11363,7 +11349,7 @@
         <v>1353</v>
       </c>
       <c r="I178">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K178" t="s">
         <v>1356</v>
@@ -11391,7 +11377,7 @@
       <c r="E179" t="s">
         <v>999</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="1">
         <v>45937</v>
       </c>
       <c r="G179" t="s">
@@ -11420,7 +11406,7 @@
       <c r="E180" t="s">
         <v>1000</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="1">
         <v>45937</v>
       </c>
       <c r="G180" t="s">
@@ -11430,7 +11416,7 @@
         <v>1353</v>
       </c>
       <c r="I180">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K180" t="s">
         <v>1356</v>
@@ -11458,7 +11444,7 @@
       <c r="E181" t="s">
         <v>1001</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="1">
         <v>45937</v>
       </c>
       <c r="G181" t="s">
@@ -11487,7 +11473,7 @@
       <c r="E182" t="s">
         <v>1002</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="1">
         <v>45937</v>
       </c>
       <c r="G182" t="s">
@@ -11516,7 +11502,7 @@
       <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="F183" s="2">
+      <c r="F183" s="1">
         <v>45937</v>
       </c>
       <c r="G183" t="s">
@@ -11526,7 +11512,7 @@
         <v>1353</v>
       </c>
       <c r="I183">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K183" t="s">
         <v>1357</v>
@@ -11554,7 +11540,7 @@
       <c r="D184" t="s">
         <v>774</v>
       </c>
-      <c r="F184" s="2">
+      <c r="F184" s="1">
         <v>45939</v>
       </c>
       <c r="G184" t="s">
@@ -11564,7 +11550,7 @@
         <v>1353</v>
       </c>
       <c r="I184">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K184" t="s">
         <v>1363</v>
@@ -11589,7 +11575,7 @@
       <c r="E185" t="s">
         <v>1004</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="1">
         <v>45939</v>
       </c>
       <c r="G185" t="s">
@@ -11599,7 +11585,7 @@
         <v>1353</v>
       </c>
       <c r="I185">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K185" t="s">
         <v>1357</v>
@@ -11627,7 +11613,7 @@
       <c r="E186" t="s">
         <v>1005</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="1">
         <v>45939</v>
       </c>
       <c r="G186" t="s">
@@ -11637,7 +11623,7 @@
         <v>1353</v>
       </c>
       <c r="I186">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K186" t="s">
         <v>1357</v>
@@ -11665,7 +11651,7 @@
       <c r="E187" t="s">
         <v>1006</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="1">
         <v>45939</v>
       </c>
       <c r="G187" t="s">
@@ -11675,7 +11661,7 @@
         <v>1353</v>
       </c>
       <c r="I187">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J187">
         <v>75</v>
@@ -11686,7 +11672,7 @@
       <c r="L187" t="s">
         <v>1404</v>
       </c>
-      <c r="N187" s="2">
+      <c r="N187" s="1">
         <v>46014</v>
       </c>
       <c r="O187">
@@ -11712,7 +11698,7 @@
       <c r="E188" t="s">
         <v>1007</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="1">
         <v>45946</v>
       </c>
       <c r="G188" t="s">
@@ -11722,7 +11708,7 @@
         <v>1353</v>
       </c>
       <c r="I188">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J188">
         <v>40</v>
@@ -11733,11 +11719,11 @@
       <c r="L188" t="s">
         <v>1405</v>
       </c>
-      <c r="N188" s="2">
+      <c r="N188" s="1">
         <v>45986</v>
       </c>
       <c r="P188" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="Q188" t="b">
         <v>1</v>
@@ -11759,7 +11745,7 @@
       <c r="E189" t="s">
         <v>1008</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="1">
         <v>45965</v>
       </c>
       <c r="G189" t="s">
@@ -11769,7 +11755,7 @@
         <v>1353</v>
       </c>
       <c r="I189">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J189">
         <v>155</v>
@@ -11780,7 +11766,7 @@
       <c r="L189" t="s">
         <v>1406</v>
       </c>
-      <c r="N189" s="2">
+      <c r="N189" s="1">
         <v>46120</v>
       </c>
       <c r="Q189" t="b">
@@ -11803,7 +11789,7 @@
       <c r="E190" t="s">
         <v>1009</v>
       </c>
-      <c r="F190" s="2">
+      <c r="F190" s="1">
         <v>45965</v>
       </c>
       <c r="G190" t="s">
@@ -11813,7 +11799,7 @@
         <v>1353</v>
       </c>
       <c r="I190">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J190">
         <v>107</v>
@@ -11824,7 +11810,7 @@
       <c r="L190" t="s">
         <v>1407</v>
       </c>
-      <c r="N190" s="2">
+      <c r="N190" s="1">
         <v>46072</v>
       </c>
       <c r="Q190" t="b">
@@ -11847,7 +11833,7 @@
       <c r="E191" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="2">
+      <c r="F191" s="1">
         <v>45967</v>
       </c>
       <c r="G191" t="s">
@@ -11857,7 +11843,7 @@
         <v>1353</v>
       </c>
       <c r="I191">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J191">
         <v>5</v>
@@ -11868,7 +11854,7 @@
       <c r="L191" t="s">
         <v>1408</v>
       </c>
-      <c r="N191" s="2">
+      <c r="N191" s="1">
         <v>45972</v>
       </c>
       <c r="Q191" t="b">
@@ -11891,7 +11877,7 @@
       <c r="E192" t="s">
         <v>1011</v>
       </c>
-      <c r="F192" s="2">
+      <c r="F192" s="1">
         <v>45968</v>
       </c>
       <c r="G192" t="s">
@@ -11901,7 +11887,7 @@
         <v>1353</v>
       </c>
       <c r="I192">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K192" t="s">
         <v>1357</v>
@@ -11929,7 +11915,7 @@
       <c r="E193" t="s">
         <v>1012</v>
       </c>
-      <c r="F193" s="2">
+      <c r="F193" s="1">
         <v>45968</v>
       </c>
       <c r="G193" t="s">
@@ -11939,7 +11925,7 @@
         <v>1353</v>
       </c>
       <c r="I193">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K193" t="s">
         <v>1362</v>
@@ -11967,7 +11953,7 @@
       <c r="E194" t="s">
         <v>1013</v>
       </c>
-      <c r="F194" s="2">
+      <c r="F194" s="1">
         <v>45968</v>
       </c>
       <c r="G194" t="s">
@@ -11996,7 +11982,7 @@
       <c r="E195" t="s">
         <v>1014</v>
       </c>
-      <c r="F195" s="2">
+      <c r="F195" s="1">
         <v>45971</v>
       </c>
       <c r="G195" t="s">
@@ -12006,7 +11992,7 @@
         <v>1353</v>
       </c>
       <c r="I195">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J195">
         <v>186</v>
@@ -12017,7 +12003,7 @@
       <c r="L195" t="s">
         <v>1409</v>
       </c>
-      <c r="N195" s="2">
+      <c r="N195" s="1">
         <v>46157</v>
       </c>
       <c r="Q195" t="b">
@@ -12040,7 +12026,7 @@
       <c r="E196" t="s">
         <v>1015</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="1">
         <v>45978</v>
       </c>
       <c r="G196" t="s">
@@ -12069,7 +12055,7 @@
       <c r="E197" t="s">
         <v>1016</v>
       </c>
-      <c r="F197" s="2">
+      <c r="F197" s="1">
         <v>45978</v>
       </c>
       <c r="G197" t="s">
@@ -12098,7 +12084,7 @@
       <c r="E198" t="s">
         <v>1017</v>
       </c>
-      <c r="F198" s="2">
+      <c r="F198" s="1">
         <v>45978</v>
       </c>
       <c r="G198" t="s">
@@ -12127,7 +12113,7 @@
       <c r="E199" t="s">
         <v>1018</v>
       </c>
-      <c r="F199" s="2">
+      <c r="F199" s="1">
         <v>45979</v>
       </c>
       <c r="G199" t="s">
@@ -12137,7 +12123,7 @@
         <v>1353</v>
       </c>
       <c r="I199">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J199">
         <v>70</v>
@@ -12148,7 +12134,7 @@
       <c r="L199" t="s">
         <v>1410</v>
       </c>
-      <c r="N199" s="2">
+      <c r="N199" s="1">
         <v>46049</v>
       </c>
       <c r="Q199" t="b">
@@ -12171,7 +12157,7 @@
       <c r="E200" t="s">
         <v>1019</v>
       </c>
-      <c r="F200" s="2">
+      <c r="F200" s="1">
         <v>45986</v>
       </c>
       <c r="G200" t="s">
@@ -12181,7 +12167,7 @@
         <v>1353</v>
       </c>
       <c r="I200">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J200">
         <v>170</v>
@@ -12192,7 +12178,7 @@
       <c r="L200" t="s">
         <v>1409</v>
       </c>
-      <c r="N200" s="2">
+      <c r="N200" s="1">
         <v>46156</v>
       </c>
       <c r="Q200" t="b">
@@ -12215,7 +12201,7 @@
       <c r="E201" t="s">
         <v>1020</v>
       </c>
-      <c r="F201" s="2">
+      <c r="F201" s="1">
         <v>45986</v>
       </c>
       <c r="G201" t="s">
@@ -12225,7 +12211,7 @@
         <v>1353</v>
       </c>
       <c r="I201">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K201" t="s">
         <v>1357</v>
@@ -12253,7 +12239,7 @@
       <c r="E202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" s="2">
+      <c r="F202" s="1">
         <v>45986</v>
       </c>
       <c r="G202" t="s">
@@ -12263,7 +12249,7 @@
         <v>1353</v>
       </c>
       <c r="I202">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K202" t="s">
         <v>1357</v>
@@ -12291,7 +12277,7 @@
       <c r="E203" t="s">
         <v>1022</v>
       </c>
-      <c r="F203" s="2">
+      <c r="F203" s="1">
         <v>45986</v>
       </c>
       <c r="G203" t="s">
@@ -12309,7 +12295,7 @@
       <c r="L203" t="s">
         <v>1411</v>
       </c>
-      <c r="N203" s="2">
+      <c r="N203" s="1">
         <v>46232</v>
       </c>
       <c r="Q203" t="b">
@@ -12332,7 +12318,7 @@
       <c r="E204" t="s">
         <v>1023</v>
       </c>
-      <c r="F204" s="2">
+      <c r="F204" s="1">
         <v>45986</v>
       </c>
       <c r="G204" t="s">
@@ -12342,7 +12328,7 @@
         <v>1353</v>
       </c>
       <c r="I204">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K204" t="s">
         <v>1356</v>
@@ -12370,7 +12356,7 @@
       <c r="E205" t="s">
         <v>1024</v>
       </c>
-      <c r="F205" s="2">
+      <c r="F205" s="1">
         <v>45986</v>
       </c>
       <c r="G205" t="s">
@@ -12380,7 +12366,7 @@
         <v>1353</v>
       </c>
       <c r="I205">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K205" t="s">
         <v>1356</v>
@@ -12408,7 +12394,7 @@
       <c r="E206" t="s">
         <v>1025</v>
       </c>
-      <c r="F206" s="2">
+      <c r="F206" s="1">
         <v>45986</v>
       </c>
       <c r="G206" t="s">
@@ -12437,7 +12423,7 @@
       <c r="E207" t="s">
         <v>1026</v>
       </c>
-      <c r="F207" s="2">
+      <c r="F207" s="1">
         <v>45986</v>
       </c>
       <c r="G207" t="s">
@@ -12447,7 +12433,7 @@
         <v>1353</v>
       </c>
       <c r="I207">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J207">
         <v>167</v>
@@ -12458,7 +12444,7 @@
       <c r="L207" t="s">
         <v>1412</v>
       </c>
-      <c r="N207" s="2">
+      <c r="N207" s="1">
         <v>46153</v>
       </c>
       <c r="Q207" t="b">
@@ -12481,7 +12467,7 @@
       <c r="E208" t="s">
         <v>1027</v>
       </c>
-      <c r="F208" s="2">
+      <c r="F208" s="1">
         <v>45986</v>
       </c>
       <c r="G208" t="s">
@@ -12491,7 +12477,7 @@
         <v>1353</v>
       </c>
       <c r="I208">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J208">
         <v>45</v>
@@ -12502,7 +12488,7 @@
       <c r="L208" t="s">
         <v>1413</v>
       </c>
-      <c r="N208" s="2">
+      <c r="N208" s="1">
         <v>46031</v>
       </c>
       <c r="Q208" t="b">
@@ -12525,7 +12511,7 @@
       <c r="E209" t="s">
         <v>1028</v>
       </c>
-      <c r="F209" s="2">
+      <c r="F209" s="1">
         <v>46000</v>
       </c>
       <c r="G209" t="s">
@@ -12535,7 +12521,7 @@
         <v>1353</v>
       </c>
       <c r="I209">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J209">
         <v>191</v>
@@ -12546,7 +12532,7 @@
       <c r="L209" t="s">
         <v>1414</v>
       </c>
-      <c r="N209" s="2">
+      <c r="N209" s="1">
         <v>46191</v>
       </c>
       <c r="Q209" t="b">
@@ -12569,7 +12555,7 @@
       <c r="E210" t="s">
         <v>1029</v>
       </c>
-      <c r="F210" s="2">
+      <c r="F210" s="1">
         <v>46000</v>
       </c>
       <c r="G210" t="s">
@@ -12579,7 +12565,7 @@
         <v>1353</v>
       </c>
       <c r="I210">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K210" t="s">
         <v>1360</v>
@@ -12607,7 +12593,7 @@
       <c r="E211" t="s">
         <v>1030</v>
       </c>
-      <c r="F211" s="2">
+      <c r="F211" s="1">
         <v>46000</v>
       </c>
       <c r="G211" t="s">
@@ -12636,7 +12622,7 @@
       <c r="E212" t="s">
         <v>1031</v>
       </c>
-      <c r="F212" s="2">
+      <c r="F212" s="1">
         <v>46000</v>
       </c>
       <c r="G212" t="s">
@@ -12665,7 +12651,7 @@
       <c r="E213" t="s">
         <v>1032</v>
       </c>
-      <c r="F213" s="2">
+      <c r="F213" s="1">
         <v>46007</v>
       </c>
       <c r="G213" t="s">
@@ -12675,7 +12661,7 @@
         <v>1353</v>
       </c>
       <c r="I213">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K213" t="s">
         <v>1357</v>
@@ -12703,7 +12689,7 @@
       <c r="E214" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="2">
+      <c r="F214" s="1">
         <v>46007</v>
       </c>
       <c r="G214" t="s">
@@ -12713,7 +12699,7 @@
         <v>1353</v>
       </c>
       <c r="I214">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J214">
         <v>14</v>
@@ -12724,7 +12710,7 @@
       <c r="L214" t="s">
         <v>1415</v>
       </c>
-      <c r="N214" s="2">
+      <c r="N214" s="1">
         <v>46021</v>
       </c>
       <c r="O214">
@@ -12750,7 +12736,7 @@
       <c r="E215" t="s">
         <v>1034</v>
       </c>
-      <c r="F215" s="2">
+      <c r="F215" s="1">
         <v>46007</v>
       </c>
       <c r="G215" t="s">
@@ -12760,7 +12746,7 @@
         <v>1353</v>
       </c>
       <c r="I215">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K215" t="s">
         <v>1357</v>
@@ -12788,7 +12774,7 @@
       <c r="E216" t="s">
         <v>1035</v>
       </c>
-      <c r="F216" s="2">
+      <c r="F216" s="1">
         <v>46010</v>
       </c>
       <c r="G216" t="s">
@@ -12817,7 +12803,7 @@
       <c r="E217" t="s">
         <v>1036</v>
       </c>
-      <c r="F217" s="2">
+      <c r="F217" s="1">
         <v>46010</v>
       </c>
       <c r="G217" t="s">
@@ -12827,7 +12813,7 @@
         <v>1353</v>
       </c>
       <c r="I217">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J217">
         <v>42</v>
@@ -12838,7 +12824,7 @@
       <c r="L217" t="s">
         <v>1416</v>
       </c>
-      <c r="N217" s="2">
+      <c r="N217" s="1">
         <v>46052</v>
       </c>
       <c r="Q217" t="b">
@@ -12861,7 +12847,7 @@
       <c r="E218" t="s">
         <v>1037</v>
       </c>
-      <c r="F218" s="2">
+      <c r="F218" s="1">
         <v>46010</v>
       </c>
       <c r="G218" t="s">
@@ -12871,7 +12857,7 @@
         <v>1353</v>
       </c>
       <c r="I218">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J218">
         <v>166</v>
@@ -12879,7 +12865,7 @@
       <c r="K218" t="s">
         <v>1359</v>
       </c>
-      <c r="N218" s="2">
+      <c r="N218" s="1">
         <v>46176</v>
       </c>
       <c r="P218" t="s">
@@ -12905,7 +12891,7 @@
       <c r="E219" t="s">
         <v>1038</v>
       </c>
-      <c r="F219" s="2">
+      <c r="F219" s="1">
         <v>46010</v>
       </c>
       <c r="G219" t="s">
@@ -12923,11 +12909,11 @@
       <c r="L219" t="s">
         <v>1417</v>
       </c>
-      <c r="N219" s="2">
+      <c r="N219" s="1">
         <v>46176</v>
       </c>
       <c r="P219" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="Q219" t="b">
         <v>0</v>
@@ -12949,7 +12935,7 @@
       <c r="E220" t="s">
         <v>1039</v>
       </c>
-      <c r="F220" s="2">
+      <c r="F220" s="1">
         <v>46010</v>
       </c>
       <c r="G220" t="s">
@@ -12959,7 +12945,7 @@
         <v>1353</v>
       </c>
       <c r="I220">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J220">
         <v>154</v>
@@ -12970,7 +12956,7 @@
       <c r="L220" t="s">
         <v>1418</v>
       </c>
-      <c r="N220" s="2">
+      <c r="N220" s="1">
         <v>46164</v>
       </c>
       <c r="Q220" t="b">
@@ -12993,7 +12979,7 @@
       <c r="E221" t="s">
         <v>1040</v>
       </c>
-      <c r="F221" s="2">
+      <c r="F221" s="1">
         <v>46028</v>
       </c>
       <c r="G221" t="s">
@@ -13008,7 +12994,7 @@
       <c r="L221" t="s">
         <v>1419</v>
       </c>
-      <c r="N221" s="2">
+      <c r="N221" s="1">
         <v>46184</v>
       </c>
       <c r="Q221" t="b">
@@ -13031,7 +13017,7 @@
       <c r="E222" t="s">
         <v>1041</v>
       </c>
-      <c r="F222" s="2">
+      <c r="F222" s="1">
         <v>46028</v>
       </c>
       <c r="G222" t="s">
@@ -13046,7 +13032,7 @@
       <c r="L222" t="s">
         <v>1383</v>
       </c>
-      <c r="N222" s="2">
+      <c r="N222" s="1">
         <v>46232</v>
       </c>
       <c r="Q222" t="b">
@@ -13069,7 +13055,7 @@
       <c r="E223" t="s">
         <v>1042</v>
       </c>
-      <c r="F223" s="2">
+      <c r="F223" s="1">
         <v>46028</v>
       </c>
       <c r="G223" t="s">
@@ -13084,7 +13070,7 @@
       <c r="L223" t="s">
         <v>1383</v>
       </c>
-      <c r="N223" s="2">
+      <c r="N223" s="1">
         <v>46232</v>
       </c>
       <c r="Q223" t="b">
@@ -13107,7 +13093,7 @@
       <c r="E224" t="s">
         <v>1043</v>
       </c>
-      <c r="F224" s="2">
+      <c r="F224" s="1">
         <v>46028</v>
       </c>
       <c r="G224" t="s">
@@ -13117,7 +13103,7 @@
         <v>1353</v>
       </c>
       <c r="I224">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J224">
         <v>204</v>
@@ -13125,7 +13111,7 @@
       <c r="L224" t="s">
         <v>1383</v>
       </c>
-      <c r="N224" s="2">
+      <c r="N224" s="1">
         <v>46232</v>
       </c>
       <c r="Q224" t="b">
@@ -13148,7 +13134,7 @@
       <c r="E225" t="s">
         <v>1044</v>
       </c>
-      <c r="F225" s="2">
+      <c r="F225" s="1">
         <v>46028</v>
       </c>
       <c r="G225" t="s">
@@ -13163,7 +13149,7 @@
       <c r="L225" t="s">
         <v>1383</v>
       </c>
-      <c r="N225" s="2">
+      <c r="N225" s="1">
         <v>46232</v>
       </c>
       <c r="Q225" t="b">
@@ -13186,7 +13172,7 @@
       <c r="E226" t="s">
         <v>1045</v>
       </c>
-      <c r="F226" s="2">
+      <c r="F226" s="1">
         <v>46028</v>
       </c>
       <c r="G226" t="s">
@@ -13201,7 +13187,7 @@
       <c r="L226" t="s">
         <v>1383</v>
       </c>
-      <c r="N226" s="2">
+      <c r="N226" s="1">
         <v>46232</v>
       </c>
       <c r="Q226" t="b">
@@ -13224,7 +13210,7 @@
       <c r="E227" t="s">
         <v>1046</v>
       </c>
-      <c r="F227" s="2">
+      <c r="F227" s="1">
         <v>46028</v>
       </c>
       <c r="G227" t="s">
@@ -13239,7 +13225,7 @@
       <c r="L227" t="s">
         <v>1383</v>
       </c>
-      <c r="N227" s="2">
+      <c r="N227" s="1">
         <v>46232</v>
       </c>
       <c r="Q227" t="b">
@@ -13262,7 +13248,7 @@
       <c r="E228" t="s">
         <v>1047</v>
       </c>
-      <c r="F228" s="2">
+      <c r="F228" s="1">
         <v>46028</v>
       </c>
       <c r="G228" t="s">
@@ -13272,7 +13258,7 @@
         <v>1353</v>
       </c>
       <c r="I228">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J228">
         <v>204</v>
@@ -13280,7 +13266,7 @@
       <c r="L228" t="s">
         <v>1383</v>
       </c>
-      <c r="N228" s="2">
+      <c r="N228" s="1">
         <v>46232</v>
       </c>
       <c r="Q228" t="b">
@@ -13303,7 +13289,7 @@
       <c r="E229" t="s">
         <v>1048</v>
       </c>
-      <c r="F229" s="2">
+      <c r="F229" s="1">
         <v>46028</v>
       </c>
       <c r="G229" t="s">
@@ -13318,7 +13304,7 @@
       <c r="L229" t="s">
         <v>1420</v>
       </c>
-      <c r="N229" s="2">
+      <c r="N229" s="1">
         <v>46191</v>
       </c>
       <c r="Q229" t="b">
@@ -13341,7 +13327,7 @@
       <c r="E230" t="s">
         <v>1049</v>
       </c>
-      <c r="F230" s="2">
+      <c r="F230" s="1">
         <v>46028</v>
       </c>
       <c r="G230" t="s">
@@ -13351,7 +13337,7 @@
         <v>1353</v>
       </c>
       <c r="I230">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J230">
         <v>197</v>
@@ -13362,7 +13348,7 @@
       <c r="L230" t="s">
         <v>1395</v>
       </c>
-      <c r="N230" s="2">
+      <c r="N230" s="1">
         <v>46225</v>
       </c>
       <c r="Q230" t="b">
@@ -13385,7 +13371,7 @@
       <c r="E231" t="s">
         <v>1050</v>
       </c>
-      <c r="F231" s="2">
+      <c r="F231" s="1">
         <v>46028</v>
       </c>
       <c r="G231" t="s">
@@ -13395,7 +13381,7 @@
         <v>1353</v>
       </c>
       <c r="I231">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J231">
         <v>35</v>
@@ -13406,7 +13392,7 @@
       <c r="L231" t="s">
         <v>1421</v>
       </c>
-      <c r="N231" s="2">
+      <c r="N231" s="1">
         <v>46063</v>
       </c>
       <c r="Q231" t="b">
@@ -13429,7 +13415,7 @@
       <c r="E232" t="s">
         <v>1051</v>
       </c>
-      <c r="F232" s="2">
+      <c r="F232" s="1">
         <v>46028</v>
       </c>
       <c r="G232" t="s">
@@ -13458,7 +13444,7 @@
       <c r="E233" t="s">
         <v>1052</v>
       </c>
-      <c r="F233" s="2">
+      <c r="F233" s="1">
         <v>46028</v>
       </c>
       <c r="G233" t="s">
@@ -13487,7 +13473,7 @@
       <c r="E234" t="s">
         <v>1053</v>
       </c>
-      <c r="F234" s="2">
+      <c r="F234" s="1">
         <v>46028</v>
       </c>
       <c r="G234" t="s">
@@ -13497,7 +13483,7 @@
         <v>1353</v>
       </c>
       <c r="I234">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J234">
         <v>35</v>
@@ -13508,11 +13494,11 @@
       <c r="L234" t="s">
         <v>1421</v>
       </c>
-      <c r="N234" s="2">
+      <c r="N234" s="1">
         <v>46063</v>
       </c>
       <c r="P234" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="Q234" t="b">
         <v>1</v>
@@ -13534,7 +13520,7 @@
       <c r="E235" t="s">
         <v>1054</v>
       </c>
-      <c r="F235" s="2">
+      <c r="F235" s="1">
         <v>46028</v>
       </c>
       <c r="G235" t="s">
@@ -13544,7 +13530,7 @@
         <v>1353</v>
       </c>
       <c r="I235">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J235">
         <v>35</v>
@@ -13555,11 +13541,11 @@
       <c r="L235" t="s">
         <v>1421</v>
       </c>
-      <c r="N235" s="2">
+      <c r="N235" s="1">
         <v>46063</v>
       </c>
       <c r="P235" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="Q235" t="b">
         <v>1</v>
@@ -13581,7 +13567,7 @@
       <c r="E236" t="s">
         <v>1055</v>
       </c>
-      <c r="F236" s="2">
+      <c r="F236" s="1">
         <v>46028</v>
       </c>
       <c r="G236" t="s">
@@ -13591,7 +13577,7 @@
         <v>1353</v>
       </c>
       <c r="I236">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J236">
         <v>86</v>
@@ -13602,7 +13588,7 @@
       <c r="L236" t="s">
         <v>1422</v>
       </c>
-      <c r="N236" s="2">
+      <c r="N236" s="1">
         <v>46114</v>
       </c>
       <c r="Q236" t="b">
@@ -13625,7 +13611,7 @@
       <c r="E237" t="s">
         <v>1056</v>
       </c>
-      <c r="F237" s="2">
+      <c r="F237" s="1">
         <v>46028</v>
       </c>
       <c r="G237" t="s">
@@ -13643,11 +13629,11 @@
       <c r="L237" t="s">
         <v>1423</v>
       </c>
-      <c r="N237" s="2">
+      <c r="N237" s="1">
         <v>46210</v>
       </c>
       <c r="P237" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="Q237" t="b">
         <v>0</v>
@@ -13669,7 +13655,7 @@
       <c r="E238" t="s">
         <v>1057</v>
       </c>
-      <c r="F238" s="2">
+      <c r="F238" s="1">
         <v>46028</v>
       </c>
       <c r="G238" t="s">
@@ -13698,7 +13684,7 @@
       <c r="E239" t="s">
         <v>1058</v>
       </c>
-      <c r="F239" s="2">
+      <c r="F239" s="1">
         <v>46036</v>
       </c>
       <c r="G239" t="s">
@@ -13708,7 +13694,7 @@
         <v>1353</v>
       </c>
       <c r="I239">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K239" t="s">
         <v>1330</v>
@@ -13716,7 +13702,7 @@
       <c r="L239" t="s">
         <v>1424</v>
       </c>
-      <c r="N239" s="2">
+      <c r="N239" s="1">
         <v>46052</v>
       </c>
       <c r="Q239" t="b">
@@ -13739,7 +13725,7 @@
       <c r="E240" t="s">
         <v>1059</v>
       </c>
-      <c r="F240" s="2">
+      <c r="F240" s="1">
         <v>46036</v>
       </c>
       <c r="G240" t="s">
@@ -13768,7 +13754,7 @@
       <c r="E241" t="s">
         <v>1060</v>
       </c>
-      <c r="F241" s="2">
+      <c r="F241" s="1">
         <v>46036</v>
       </c>
       <c r="G241" t="s">
@@ -13797,7 +13783,7 @@
       <c r="E242" t="s">
         <v>1061</v>
       </c>
-      <c r="F242" s="2">
+      <c r="F242" s="1">
         <v>46036</v>
       </c>
       <c r="G242" t="s">
@@ -13807,7 +13793,7 @@
         <v>1353</v>
       </c>
       <c r="I242">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K242" t="s">
         <v>1356</v>
@@ -13835,7 +13821,7 @@
       <c r="E243" t="s">
         <v>1062</v>
       </c>
-      <c r="F243" s="2">
+      <c r="F243" s="1">
         <v>46048</v>
       </c>
       <c r="G243" t="s">
@@ -13864,7 +13850,7 @@
       <c r="E244" t="s">
         <v>1063</v>
       </c>
-      <c r="F244" s="2">
+      <c r="F244" s="1">
         <v>46048</v>
       </c>
       <c r="G244" t="s">
@@ -13874,7 +13860,7 @@
         <v>1353</v>
       </c>
       <c r="I244">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J244">
         <v>15</v>
@@ -13882,7 +13868,7 @@
       <c r="K244" t="s">
         <v>1359</v>
       </c>
-      <c r="N244" s="2">
+      <c r="N244" s="1">
         <v>46063</v>
       </c>
       <c r="Q244" t="b">
@@ -13905,7 +13891,7 @@
       <c r="E245" t="s">
         <v>1064</v>
       </c>
-      <c r="F245" s="2">
+      <c r="F245" s="1">
         <v>46048</v>
       </c>
       <c r="G245" t="s">
@@ -13915,7 +13901,7 @@
         <v>1353</v>
       </c>
       <c r="I245">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J245">
         <v>15</v>
@@ -13926,7 +13912,7 @@
       <c r="L245" t="s">
         <v>1425</v>
       </c>
-      <c r="N245" s="2">
+      <c r="N245" s="1">
         <v>46063</v>
       </c>
       <c r="Q245" t="b">
@@ -13949,7 +13935,7 @@
       <c r="E246" t="s">
         <v>1065</v>
       </c>
-      <c r="F246" s="2">
+      <c r="F246" s="1">
         <v>46050</v>
       </c>
       <c r="G246" t="s">
@@ -13967,7 +13953,7 @@
       <c r="L246" t="s">
         <v>1426</v>
       </c>
-      <c r="N246" s="2">
+      <c r="N246" s="1">
         <v>46191</v>
       </c>
       <c r="Q246" t="b">
@@ -13990,7 +13976,7 @@
       <c r="E247" t="s">
         <v>1066</v>
       </c>
-      <c r="F247" s="2">
+      <c r="F247" s="1">
         <v>46050</v>
       </c>
       <c r="G247" t="s">
@@ -14019,7 +14005,7 @@
       <c r="E248" t="s">
         <v>1067</v>
       </c>
-      <c r="F248" s="2">
+      <c r="F248" s="1">
         <v>46050</v>
       </c>
       <c r="G248" t="s">
@@ -14048,7 +14034,7 @@
       <c r="E249" t="s">
         <v>1068</v>
       </c>
-      <c r="F249" s="2">
+      <c r="F249" s="1">
         <v>46050</v>
       </c>
       <c r="G249" t="s">
@@ -14058,7 +14044,7 @@
         <v>1353</v>
       </c>
       <c r="I249">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K249" t="s">
         <v>1357</v>
@@ -14086,7 +14072,7 @@
       <c r="E250" t="s">
         <v>1069</v>
       </c>
-      <c r="F250" s="2">
+      <c r="F250" s="1">
         <v>46063</v>
       </c>
       <c r="G250" t="s">
@@ -14102,7 +14088,7 @@
         <v>1454</v>
       </c>
       <c r="P250" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="Q250" t="b">
         <v>0</v>
@@ -14124,7 +14110,7 @@
       <c r="E251" t="s">
         <v>1070</v>
       </c>
-      <c r="F251" s="2">
+      <c r="F251" s="1">
         <v>46063</v>
       </c>
       <c r="G251" t="s">
@@ -14153,7 +14139,7 @@
       <c r="E252" t="s">
         <v>1071</v>
       </c>
-      <c r="F252" s="2">
+      <c r="F252" s="1">
         <v>46063</v>
       </c>
       <c r="G252" t="s">
@@ -14182,7 +14168,7 @@
       <c r="E253" t="s">
         <v>1072</v>
       </c>
-      <c r="F253" s="2">
+      <c r="F253" s="1">
         <v>46063</v>
       </c>
       <c r="G253" t="s">
@@ -14192,7 +14178,7 @@
         <v>1353</v>
       </c>
       <c r="I253">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J253">
         <v>162</v>
@@ -14203,7 +14189,7 @@
       <c r="L253" t="s">
         <v>1395</v>
       </c>
-      <c r="N253" s="2">
+      <c r="N253" s="1">
         <v>46225</v>
       </c>
       <c r="Q253" t="b">
@@ -14226,7 +14212,7 @@
       <c r="E254" t="s">
         <v>1073</v>
       </c>
-      <c r="F254" s="2">
+      <c r="F254" s="1">
         <v>46063</v>
       </c>
       <c r="G254" t="s">
@@ -14236,7 +14222,7 @@
         <v>1353</v>
       </c>
       <c r="I254">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K254" t="s">
         <v>1360</v>
@@ -14264,7 +14250,7 @@
       <c r="E255" t="s">
         <v>1074</v>
       </c>
-      <c r="F255" s="2">
+      <c r="F255" s="1">
         <v>46063</v>
       </c>
       <c r="G255" t="s">
@@ -14274,7 +14260,7 @@
         <v>1353</v>
       </c>
       <c r="I255">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J255">
         <v>72</v>
@@ -14285,7 +14271,7 @@
       <c r="L255" t="s">
         <v>1388</v>
       </c>
-      <c r="N255" s="2">
+      <c r="N255" s="1">
         <v>46135</v>
       </c>
       <c r="Q255" t="b">
@@ -14308,7 +14294,7 @@
       <c r="E256" t="s">
         <v>1075</v>
       </c>
-      <c r="F256" s="2">
+      <c r="F256" s="1">
         <v>46063</v>
       </c>
       <c r="G256" t="s">
@@ -14318,7 +14304,7 @@
         <v>1353</v>
       </c>
       <c r="I256">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J256">
         <v>23</v>
@@ -14326,7 +14312,7 @@
       <c r="K256" t="s">
         <v>1357</v>
       </c>
-      <c r="N256" s="2">
+      <c r="N256" s="1">
         <v>46086</v>
       </c>
       <c r="O256">
@@ -14352,7 +14338,7 @@
       <c r="E257" t="s">
         <v>1076</v>
       </c>
-      <c r="F257" s="2">
+      <c r="F257" s="1">
         <v>46063</v>
       </c>
       <c r="G257" t="s">
@@ -14381,7 +14367,7 @@
       <c r="E258" t="s">
         <v>1077</v>
       </c>
-      <c r="F258" s="2">
+      <c r="F258" s="1">
         <v>46063</v>
       </c>
       <c r="G258" t="s">
@@ -14410,7 +14396,7 @@
       <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="F259" s="2">
+      <c r="F259" s="1">
         <v>46063</v>
       </c>
       <c r="G259" t="s">
@@ -14420,7 +14406,7 @@
         <v>1353</v>
       </c>
       <c r="I259">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J259">
         <v>72</v>
@@ -14431,7 +14417,7 @@
       <c r="L259" t="s">
         <v>1388</v>
       </c>
-      <c r="N259" s="2">
+      <c r="N259" s="1">
         <v>46135</v>
       </c>
       <c r="Q259" t="b">
@@ -14454,7 +14440,7 @@
       <c r="E260" t="s">
         <v>1079</v>
       </c>
-      <c r="F260" s="2">
+      <c r="F260" s="1">
         <v>46063</v>
       </c>
       <c r="G260" t="s">
@@ -14464,7 +14450,7 @@
         <v>1353</v>
       </c>
       <c r="I260">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J260">
         <v>84</v>
@@ -14475,7 +14461,7 @@
       <c r="L260" t="s">
         <v>1388</v>
       </c>
-      <c r="N260" s="2">
+      <c r="N260" s="1">
         <v>46147</v>
       </c>
       <c r="Q260" t="b">
@@ -14498,7 +14484,7 @@
       <c r="E261" t="s">
         <v>1080</v>
       </c>
-      <c r="F261" s="2">
+      <c r="F261" s="1">
         <v>46063</v>
       </c>
       <c r="G261" t="s">
@@ -14508,7 +14494,7 @@
         <v>1353</v>
       </c>
       <c r="I261">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J261">
         <v>162</v>
@@ -14519,7 +14505,7 @@
       <c r="L261" t="s">
         <v>1427</v>
       </c>
-      <c r="N261" s="2">
+      <c r="N261" s="1">
         <v>46225</v>
       </c>
       <c r="Q261" t="b">
@@ -14542,7 +14528,7 @@
       <c r="E262" t="s">
         <v>1081</v>
       </c>
-      <c r="F262" s="2">
+      <c r="F262" s="1">
         <v>46063</v>
       </c>
       <c r="G262" t="s">
@@ -14560,11 +14546,11 @@
       <c r="L262" t="s">
         <v>1428</v>
       </c>
-      <c r="N262" s="2">
+      <c r="N262" s="1">
         <v>46113</v>
       </c>
       <c r="P262" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="Q262" t="b">
         <v>0</v>
@@ -14586,7 +14572,7 @@
       <c r="E263" t="s">
         <v>1082</v>
       </c>
-      <c r="F263" s="2">
+      <c r="F263" s="1">
         <v>46063</v>
       </c>
       <c r="G263" t="s">
@@ -14615,7 +14601,7 @@
       <c r="E264" t="s">
         <v>1083</v>
       </c>
-      <c r="F264" s="2">
+      <c r="F264" s="1">
         <v>46063</v>
       </c>
       <c r="G264" t="s">
@@ -14625,7 +14611,7 @@
         <v>1353</v>
       </c>
       <c r="I264">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J264">
         <v>162</v>
@@ -14636,7 +14622,7 @@
       <c r="L264" t="s">
         <v>1388</v>
       </c>
-      <c r="N264" s="2">
+      <c r="N264" s="1">
         <v>46225</v>
       </c>
       <c r="Q264" t="b">
@@ -14659,7 +14645,7 @@
       <c r="E265" t="s">
         <v>1084</v>
       </c>
-      <c r="F265" s="2">
+      <c r="F265" s="1">
         <v>46063</v>
       </c>
       <c r="G265" t="s">
@@ -14669,7 +14655,7 @@
         <v>1353</v>
       </c>
       <c r="I265">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J265">
         <v>162</v>
@@ -14680,7 +14666,7 @@
       <c r="L265" t="s">
         <v>1395</v>
       </c>
-      <c r="N265" s="2">
+      <c r="N265" s="1">
         <v>46225</v>
       </c>
       <c r="Q265" t="b">
@@ -14703,7 +14689,7 @@
       <c r="E266" t="s">
         <v>1085</v>
       </c>
-      <c r="F266" s="2">
+      <c r="F266" s="1">
         <v>46063</v>
       </c>
       <c r="G266" t="s">
@@ -14713,7 +14699,7 @@
         <v>1353</v>
       </c>
       <c r="I266">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J266">
         <v>84</v>
@@ -14724,7 +14710,7 @@
       <c r="L266" t="s">
         <v>1388</v>
       </c>
-      <c r="N266" s="2">
+      <c r="N266" s="1">
         <v>46147</v>
       </c>
       <c r="Q266" t="b">
@@ -14747,7 +14733,7 @@
       <c r="E267" t="s">
         <v>1086</v>
       </c>
-      <c r="F267" s="2">
+      <c r="F267" s="1">
         <v>46063</v>
       </c>
       <c r="G267" t="s">
@@ -14757,7 +14743,7 @@
         <v>1353</v>
       </c>
       <c r="I267">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K267" t="s">
         <v>1360</v>
@@ -14785,7 +14771,7 @@
       <c r="E268" t="s">
         <v>1087</v>
       </c>
-      <c r="F268" s="2">
+      <c r="F268" s="1">
         <v>46063</v>
       </c>
       <c r="G268" t="s">
@@ -14795,7 +14781,7 @@
         <v>1353</v>
       </c>
       <c r="I268">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K268" t="s">
         <v>1357</v>
@@ -14820,7 +14806,7 @@
       <c r="D269" t="s">
         <v>798</v>
       </c>
-      <c r="F269" s="2">
+      <c r="F269" s="1">
         <v>46063</v>
       </c>
       <c r="G269" t="s">
@@ -14830,7 +14816,7 @@
         <v>1353</v>
       </c>
       <c r="I269">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K269" t="s">
         <v>1357</v>
@@ -14858,7 +14844,7 @@
       <c r="E270" t="s">
         <v>1088</v>
       </c>
-      <c r="F270" s="2">
+      <c r="F270" s="1">
         <v>46063</v>
       </c>
       <c r="G270" t="s">
@@ -14868,7 +14854,7 @@
         <v>1353</v>
       </c>
       <c r="I270">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K270" t="s">
         <v>1360</v>
@@ -14896,7 +14882,7 @@
       <c r="E271" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="2">
+      <c r="F271" s="1">
         <v>46063</v>
       </c>
       <c r="G271" t="s">
@@ -14906,7 +14892,7 @@
         <v>1353</v>
       </c>
       <c r="I271">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K271" t="s">
         <v>1360</v>
@@ -14934,7 +14920,7 @@
       <c r="E272" t="s">
         <v>1090</v>
       </c>
-      <c r="F272" s="2">
+      <c r="F272" s="1">
         <v>46063</v>
       </c>
       <c r="G272" t="s">
@@ -14952,7 +14938,7 @@
       <c r="L272" t="s">
         <v>1429</v>
       </c>
-      <c r="N272" s="2">
+      <c r="N272" s="1">
         <v>46185</v>
       </c>
       <c r="O272" t="s">
@@ -14978,7 +14964,7 @@
       <c r="E273" t="s">
         <v>1091</v>
       </c>
-      <c r="F273" s="2">
+      <c r="F273" s="1">
         <v>46063</v>
       </c>
       <c r="G273" t="s">
@@ -15007,7 +14993,7 @@
       <c r="E274" t="s">
         <v>1092</v>
       </c>
-      <c r="F274" s="2">
+      <c r="F274" s="1">
         <v>46063</v>
       </c>
       <c r="G274" t="s">
@@ -15022,7 +15008,7 @@
       <c r="L274" t="s">
         <v>1383</v>
       </c>
-      <c r="N274" s="2">
+      <c r="N274" s="1">
         <v>46232</v>
       </c>
       <c r="Q274" t="b">
@@ -15045,7 +15031,7 @@
       <c r="E275" t="s">
         <v>1093</v>
       </c>
-      <c r="F275" s="2">
+      <c r="F275" s="1">
         <v>46063</v>
       </c>
       <c r="G275" t="s">
@@ -15074,7 +15060,7 @@
       <c r="E276" t="s">
         <v>1094</v>
       </c>
-      <c r="F276" s="2">
+      <c r="F276" s="1">
         <v>46063</v>
       </c>
       <c r="G276" t="s">
@@ -15084,7 +15070,7 @@
         <v>1353</v>
       </c>
       <c r="I276">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K276" t="s">
         <v>1361</v>
@@ -15112,7 +15098,7 @@
       <c r="E277" t="s">
         <v>1095</v>
       </c>
-      <c r="F277" s="2">
+      <c r="F277" s="1">
         <v>46063</v>
       </c>
       <c r="G277" t="s">
@@ -15122,7 +15108,7 @@
         <v>1353</v>
       </c>
       <c r="I277">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K277" t="s">
         <v>1357</v>
@@ -15150,7 +15136,7 @@
       <c r="E278" t="s">
         <v>1096</v>
       </c>
-      <c r="F278" s="2">
+      <c r="F278" s="1">
         <v>46077</v>
       </c>
       <c r="G278" t="s">
@@ -15160,7 +15146,7 @@
         <v>1353</v>
       </c>
       <c r="I278">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J278">
         <v>148</v>
@@ -15171,7 +15157,7 @@
       <c r="L278" t="s">
         <v>1395</v>
       </c>
-      <c r="N278" s="2">
+      <c r="N278" s="1">
         <v>46225</v>
       </c>
       <c r="Q278" t="b">
@@ -15194,7 +15180,7 @@
       <c r="E279" t="s">
         <v>1097</v>
       </c>
-      <c r="F279" s="2">
+      <c r="F279" s="1">
         <v>46077</v>
       </c>
       <c r="G279" t="s">
@@ -15204,7 +15190,7 @@
         <v>1353</v>
       </c>
       <c r="I279">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K279" t="s">
         <v>1359</v>
@@ -15213,7 +15199,7 @@
         <v>1454</v>
       </c>
       <c r="P279" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="Q279" t="b">
         <v>1</v>
@@ -15235,7 +15221,7 @@
       <c r="E280" t="s">
         <v>1098</v>
       </c>
-      <c r="F280" s="2">
+      <c r="F280" s="1">
         <v>46085</v>
       </c>
       <c r="G280" t="s">
@@ -15245,7 +15231,7 @@
         <v>1353</v>
       </c>
       <c r="I280">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K280" t="s">
         <v>1357</v>
@@ -15273,7 +15259,7 @@
       <c r="E281" t="s">
         <v>1099</v>
       </c>
-      <c r="F281" s="2">
+      <c r="F281" s="1">
         <v>46085</v>
       </c>
       <c r="G281" t="s">
@@ -15283,7 +15269,7 @@
         <v>1353</v>
       </c>
       <c r="I281">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K281" t="s">
         <v>1357</v>
@@ -15314,7 +15300,7 @@
       <c r="E282" t="s">
         <v>1100</v>
       </c>
-      <c r="F282" s="2">
+      <c r="F282" s="1">
         <v>46090</v>
       </c>
       <c r="G282" t="s">
@@ -15324,7 +15310,7 @@
         <v>1353</v>
       </c>
       <c r="I282">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K282" t="s">
         <v>1357</v>
@@ -15352,7 +15338,7 @@
       <c r="E283" t="s">
         <v>1101</v>
       </c>
-      <c r="F283" s="2">
+      <c r="F283" s="1">
         <v>46100</v>
       </c>
       <c r="G283" t="s">
@@ -15381,7 +15367,7 @@
       <c r="E284" t="s">
         <v>1102</v>
       </c>
-      <c r="F284" s="2">
+      <c r="F284" s="1">
         <v>46100</v>
       </c>
       <c r="G284" t="s">
@@ -15410,7 +15396,7 @@
       <c r="E285" t="s">
         <v>1103</v>
       </c>
-      <c r="F285" s="2">
+      <c r="F285" s="1">
         <v>46100</v>
       </c>
       <c r="G285" t="s">
@@ -15439,7 +15425,7 @@
       <c r="E286" t="s">
         <v>1104</v>
       </c>
-      <c r="F286" s="2">
+      <c r="F286" s="1">
         <v>46100</v>
       </c>
       <c r="G286" t="s">
@@ -15468,7 +15454,7 @@
       <c r="E287" t="s">
         <v>1105</v>
       </c>
-      <c r="F287" s="2">
+      <c r="F287" s="1">
         <v>46107</v>
       </c>
       <c r="G287" t="s">
@@ -15497,7 +15483,7 @@
       <c r="E288" t="s">
         <v>1106</v>
       </c>
-      <c r="F288" s="2">
+      <c r="F288" s="1">
         <v>46107</v>
       </c>
       <c r="G288" t="s">
@@ -15507,7 +15493,7 @@
         <v>1353</v>
       </c>
       <c r="I288">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J288">
         <v>28</v>
@@ -15518,7 +15504,7 @@
       <c r="L288" t="s">
         <v>1388</v>
       </c>
-      <c r="N288" s="2">
+      <c r="N288" s="1">
         <v>46135</v>
       </c>
       <c r="Q288" t="b">
@@ -15541,7 +15527,7 @@
       <c r="E289" t="s">
         <v>1107</v>
       </c>
-      <c r="F289" s="2">
+      <c r="F289" s="1">
         <v>46107</v>
       </c>
       <c r="G289" t="s">
@@ -15570,7 +15556,7 @@
       <c r="E290" t="s">
         <v>1108</v>
       </c>
-      <c r="F290" s="2">
+      <c r="F290" s="1">
         <v>46107</v>
       </c>
       <c r="G290" t="s">
@@ -15580,7 +15566,7 @@
         <v>1353</v>
       </c>
       <c r="I290">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J290">
         <v>20</v>
@@ -15591,7 +15577,7 @@
       <c r="L290" t="s">
         <v>1388</v>
       </c>
-      <c r="N290" s="2">
+      <c r="N290" s="1">
         <v>46127</v>
       </c>
       <c r="Q290" t="b">
@@ -15614,7 +15600,7 @@
       <c r="E291" t="s">
         <v>1109</v>
       </c>
-      <c r="F291" s="2">
+      <c r="F291" s="1">
         <v>46107</v>
       </c>
       <c r="G291" t="s">
@@ -15624,7 +15610,7 @@
         <v>1353</v>
       </c>
       <c r="I291">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J291">
         <v>20</v>
@@ -15635,7 +15621,7 @@
       <c r="L291" t="s">
         <v>1430</v>
       </c>
-      <c r="N291" s="2">
+      <c r="N291" s="1">
         <v>46127</v>
       </c>
       <c r="Q291" t="b">
@@ -15658,7 +15644,7 @@
       <c r="E292" t="s">
         <v>1110</v>
       </c>
-      <c r="F292" s="2">
+      <c r="F292" s="1">
         <v>46112</v>
       </c>
       <c r="G292" t="s">
@@ -15668,7 +15654,7 @@
         <v>1353</v>
       </c>
       <c r="I292">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K292" t="s">
         <v>1360</v>
@@ -15696,7 +15682,7 @@
       <c r="E293" t="s">
         <v>1111</v>
       </c>
-      <c r="F293" s="2">
+      <c r="F293" s="1">
         <v>46125</v>
       </c>
       <c r="G293" t="s">
@@ -15706,7 +15692,7 @@
         <v>1353</v>
       </c>
       <c r="I293">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K293" t="s">
         <v>1361</v>
@@ -15734,7 +15720,7 @@
       <c r="E294" t="s">
         <v>1112</v>
       </c>
-      <c r="F294" s="2">
+      <c r="F294" s="1">
         <v>46125</v>
       </c>
       <c r="G294" t="s">
@@ -15744,7 +15730,7 @@
         <v>1353</v>
       </c>
       <c r="I294">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K294" t="s">
         <v>1366</v>
@@ -15769,7 +15755,7 @@
       <c r="E295" t="s">
         <v>1113</v>
       </c>
-      <c r="F295" s="2">
+      <c r="F295" s="1">
         <v>46125</v>
       </c>
       <c r="G295" t="s">
@@ -15779,7 +15765,7 @@
         <v>1353</v>
       </c>
       <c r="I295">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K295" t="s">
         <v>1366</v>
@@ -15804,7 +15790,7 @@
       <c r="E296" t="s">
         <v>1114</v>
       </c>
-      <c r="F296" s="2">
+      <c r="F296" s="1">
         <v>46125</v>
       </c>
       <c r="G296" t="s">
@@ -15814,7 +15800,7 @@
         <v>1353</v>
       </c>
       <c r="I296">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K296" t="s">
         <v>1366</v>
@@ -15839,7 +15825,7 @@
       <c r="E297" t="s">
         <v>1115</v>
       </c>
-      <c r="F297" s="2">
+      <c r="F297" s="1">
         <v>46125</v>
       </c>
       <c r="G297" t="s">
@@ -15851,7 +15837,7 @@
       <c r="K297" t="s">
         <v>1359</v>
       </c>
-      <c r="N297" s="2">
+      <c r="N297" s="1">
         <v>46183</v>
       </c>
       <c r="O297">
@@ -15877,7 +15863,7 @@
       <c r="E298" t="s">
         <v>1116</v>
       </c>
-      <c r="F298" s="2">
+      <c r="F298" s="1">
         <v>46125</v>
       </c>
       <c r="G298" t="s">
@@ -15887,7 +15873,7 @@
         <v>1353</v>
       </c>
       <c r="I298">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J298">
         <v>58</v>
@@ -15895,7 +15881,7 @@
       <c r="K298" t="s">
         <v>1359</v>
       </c>
-      <c r="N298" s="2">
+      <c r="N298" s="1">
         <v>46183</v>
       </c>
       <c r="Q298" t="b">
@@ -15918,7 +15904,7 @@
       <c r="E299" t="s">
         <v>1117</v>
       </c>
-      <c r="F299" s="2">
+      <c r="F299" s="1">
         <v>46125</v>
       </c>
       <c r="G299" t="s">
@@ -15928,7 +15914,7 @@
         <v>1353</v>
       </c>
       <c r="I299">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J299">
         <v>100</v>
@@ -15939,7 +15925,7 @@
       <c r="L299" t="s">
         <v>1388</v>
       </c>
-      <c r="N299" s="2">
+      <c r="N299" s="1">
         <v>46225</v>
       </c>
       <c r="Q299" t="b">
@@ -15962,7 +15948,7 @@
       <c r="E300" t="s">
         <v>1118</v>
       </c>
-      <c r="F300" s="2">
+      <c r="F300" s="1">
         <v>46125</v>
       </c>
       <c r="G300" t="s">
@@ -15972,7 +15958,7 @@
         <v>1353</v>
       </c>
       <c r="I300">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J300">
         <v>86</v>
@@ -15983,7 +15969,7 @@
       <c r="L300" t="s">
         <v>1388</v>
       </c>
-      <c r="N300" s="2">
+      <c r="N300" s="1">
         <v>46211</v>
       </c>
       <c r="Q300" t="b">
@@ -16006,7 +15992,7 @@
       <c r="E301" t="s">
         <v>1119</v>
       </c>
-      <c r="F301" s="2">
+      <c r="F301" s="1">
         <v>46125</v>
       </c>
       <c r="G301" t="s">
@@ -16016,7 +16002,7 @@
         <v>1353</v>
       </c>
       <c r="I301">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J301">
         <v>102</v>
@@ -16027,7 +16013,7 @@
       <c r="L301" t="s">
         <v>1388</v>
       </c>
-      <c r="N301" s="2">
+      <c r="N301" s="1">
         <v>46227</v>
       </c>
       <c r="Q301" t="b">
@@ -16050,7 +16036,7 @@
       <c r="E302" t="s">
         <v>1120</v>
       </c>
-      <c r="F302" s="2">
+      <c r="F302" s="1">
         <v>46125</v>
       </c>
       <c r="G302" t="s">
@@ -16060,7 +16046,7 @@
         <v>1353</v>
       </c>
       <c r="I302">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K302" t="s">
         <v>1360</v>
@@ -16088,7 +16074,7 @@
       <c r="E303" t="s">
         <v>1121</v>
       </c>
-      <c r="F303" s="2">
+      <c r="F303" s="1">
         <v>46125</v>
       </c>
       <c r="G303" t="s">
@@ -16098,7 +16084,7 @@
         <v>1353</v>
       </c>
       <c r="I303">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K303" t="s">
         <v>1357</v>
@@ -16126,7 +16112,7 @@
       <c r="E304" t="s">
         <v>1122</v>
       </c>
-      <c r="F304" s="2">
+      <c r="F304" s="1">
         <v>46125</v>
       </c>
       <c r="G304" t="s">
@@ -16136,7 +16122,7 @@
         <v>1353</v>
       </c>
       <c r="I304">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K304" t="s">
         <v>1360</v>
@@ -16164,7 +16150,7 @@
       <c r="E305" t="s">
         <v>1123</v>
       </c>
-      <c r="F305" s="2">
+      <c r="F305" s="1">
         <v>46125</v>
       </c>
       <c r="G305" t="s">
@@ -16174,7 +16160,7 @@
         <v>1353</v>
       </c>
       <c r="I305">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J305">
         <v>35</v>
@@ -16185,7 +16171,7 @@
       <c r="L305" t="s">
         <v>1431</v>
       </c>
-      <c r="N305" s="2">
+      <c r="N305" s="1">
         <v>46160</v>
       </c>
       <c r="Q305" t="b">
@@ -16208,7 +16194,7 @@
       <c r="E306" t="s">
         <v>1124</v>
       </c>
-      <c r="F306" s="2">
+      <c r="F306" s="1">
         <v>46125</v>
       </c>
       <c r="G306" t="s">
@@ -16218,7 +16204,7 @@
         <v>1353</v>
       </c>
       <c r="I306">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J306">
         <v>31</v>
@@ -16229,7 +16215,7 @@
       <c r="L306" t="s">
         <v>1432</v>
       </c>
-      <c r="N306" s="2">
+      <c r="N306" s="1">
         <v>46156</v>
       </c>
       <c r="Q306" t="b">
@@ -16252,7 +16238,7 @@
       <c r="E307" t="s">
         <v>1125</v>
       </c>
-      <c r="F307" s="2">
+      <c r="F307" s="1">
         <v>46125</v>
       </c>
       <c r="G307" t="s">
@@ -16270,11 +16256,11 @@
       <c r="L307" t="s">
         <v>1433</v>
       </c>
-      <c r="N307" s="2">
+      <c r="N307" s="1">
         <v>46209</v>
       </c>
       <c r="P307" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="Q307" t="b">
         <v>0</v>
@@ -16296,7 +16282,7 @@
       <c r="E308" t="s">
         <v>1126</v>
       </c>
-      <c r="F308" s="2">
+      <c r="F308" s="1">
         <v>46125</v>
       </c>
       <c r="G308" t="s">
@@ -16306,7 +16292,7 @@
         <v>1353</v>
       </c>
       <c r="I308">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K308" t="s">
         <v>1356</v>
@@ -16334,7 +16320,7 @@
       <c r="E309" t="s">
         <v>1127</v>
       </c>
-      <c r="F309" s="2">
+      <c r="F309" s="1">
         <v>46125</v>
       </c>
       <c r="G309" t="s">
@@ -16349,7 +16335,7 @@
       <c r="L309" t="s">
         <v>1383</v>
       </c>
-      <c r="N309" s="2">
+      <c r="N309" s="1">
         <v>46232</v>
       </c>
       <c r="Q309" t="b">
@@ -16372,7 +16358,7 @@
       <c r="E310" t="s">
         <v>1128</v>
       </c>
-      <c r="F310" s="2">
+      <c r="F310" s="1">
         <v>46125</v>
       </c>
       <c r="G310" t="s">
@@ -16382,7 +16368,7 @@
         <v>1353</v>
       </c>
       <c r="I310">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J310">
         <v>107</v>
@@ -16393,7 +16379,7 @@
       <c r="L310" t="s">
         <v>1383</v>
       </c>
-      <c r="N310" s="2">
+      <c r="N310" s="1">
         <v>46232</v>
       </c>
       <c r="Q310" t="b">
@@ -16416,7 +16402,7 @@
       <c r="E311" t="s">
         <v>1129</v>
       </c>
-      <c r="F311" s="2">
+      <c r="F311" s="1">
         <v>46125</v>
       </c>
       <c r="G311" t="s">
@@ -16426,7 +16412,7 @@
         <v>1353</v>
       </c>
       <c r="I311">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K311" t="s">
         <v>1356</v>
@@ -16454,7 +16440,7 @@
       <c r="E312" t="s">
         <v>1130</v>
       </c>
-      <c r="F312" s="2">
+      <c r="F312" s="1">
         <v>46125</v>
       </c>
       <c r="G312" t="s">
@@ -16472,7 +16458,7 @@
       <c r="L312" t="s">
         <v>1383</v>
       </c>
-      <c r="N312" s="2">
+      <c r="N312" s="1">
         <v>46232</v>
       </c>
       <c r="Q312" t="b">
@@ -16495,7 +16481,7 @@
       <c r="E313" t="s">
         <v>1131</v>
       </c>
-      <c r="F313" s="2">
+      <c r="F313" s="1">
         <v>46125</v>
       </c>
       <c r="G313" t="s">
@@ -16530,7 +16516,7 @@
       <c r="E314" t="s">
         <v>1132</v>
       </c>
-      <c r="F314" s="2">
+      <c r="F314" s="1">
         <v>46125</v>
       </c>
       <c r="G314" t="s">
@@ -16545,7 +16531,7 @@
       <c r="L314" t="s">
         <v>1383</v>
       </c>
-      <c r="N314" s="2">
+      <c r="N314" s="1">
         <v>46232</v>
       </c>
       <c r="Q314" t="b">
@@ -16568,7 +16554,7 @@
       <c r="E315" t="s">
         <v>1133</v>
       </c>
-      <c r="F315" s="2">
+      <c r="F315" s="1">
         <v>46125</v>
       </c>
       <c r="G315" t="s">
@@ -16583,7 +16569,7 @@
       <c r="L315" t="s">
         <v>1383</v>
       </c>
-      <c r="N315" s="2">
+      <c r="N315" s="1">
         <v>46232</v>
       </c>
       <c r="Q315" t="b">
@@ -16606,7 +16592,7 @@
       <c r="E316" t="s">
         <v>1134</v>
       </c>
-      <c r="F316" s="2">
+      <c r="F316" s="1">
         <v>46125</v>
       </c>
       <c r="G316" t="s">
@@ -16616,7 +16602,7 @@
         <v>1353</v>
       </c>
       <c r="I316">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K316" t="s">
         <v>1357</v>
@@ -16644,7 +16630,7 @@
       <c r="E317" t="s">
         <v>1135</v>
       </c>
-      <c r="F317" s="2">
+      <c r="F317" s="1">
         <v>46125</v>
       </c>
       <c r="G317" t="s">
@@ -16679,7 +16665,7 @@
       <c r="E318" t="s">
         <v>1136</v>
       </c>
-      <c r="F318" s="2">
+      <c r="F318" s="1">
         <v>46125</v>
       </c>
       <c r="G318" t="s">
@@ -16708,7 +16694,7 @@
       <c r="E319" t="s">
         <v>1137</v>
       </c>
-      <c r="F319" s="2">
+      <c r="F319" s="1">
         <v>46125</v>
       </c>
       <c r="G319" t="s">
@@ -16723,7 +16709,7 @@
       <c r="L319" t="s">
         <v>1434</v>
       </c>
-      <c r="N319" s="2">
+      <c r="N319" s="1">
         <v>46175</v>
       </c>
       <c r="Q319" t="b">
@@ -16746,7 +16732,7 @@
       <c r="E320" t="s">
         <v>1138</v>
       </c>
-      <c r="F320" s="2">
+      <c r="F320" s="1">
         <v>46125</v>
       </c>
       <c r="G320" t="s">
@@ -16756,7 +16742,7 @@
         <v>1353</v>
       </c>
       <c r="I320">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K320" t="s">
         <v>1361</v>
@@ -16784,7 +16770,7 @@
       <c r="E321" t="s">
         <v>1139</v>
       </c>
-      <c r="F321" s="2">
+      <c r="F321" s="1">
         <v>46125</v>
       </c>
       <c r="G321" t="s">
@@ -16794,7 +16780,7 @@
         <v>1353</v>
       </c>
       <c r="I321">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K321" t="s">
         <v>1357</v>
@@ -16822,7 +16808,7 @@
       <c r="E322" t="s">
         <v>1140</v>
       </c>
-      <c r="F322" s="2">
+      <c r="F322" s="1">
         <v>46125</v>
       </c>
       <c r="G322" t="s">
@@ -16832,7 +16818,7 @@
         <v>1353</v>
       </c>
       <c r="I322">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J322">
         <v>57</v>
@@ -16843,7 +16829,7 @@
       <c r="L322" t="s">
         <v>1435</v>
       </c>
-      <c r="N322" s="2">
+      <c r="N322" s="1">
         <v>46182</v>
       </c>
       <c r="Q322" t="b">
@@ -16866,7 +16852,7 @@
       <c r="E323" t="s">
         <v>1141</v>
       </c>
-      <c r="F323" s="2">
+      <c r="F323" s="1">
         <v>46125</v>
       </c>
       <c r="G323" t="s">
@@ -16901,7 +16887,7 @@
       <c r="E324" t="s">
         <v>1142</v>
       </c>
-      <c r="F324" s="2">
+      <c r="F324" s="1">
         <v>46125</v>
       </c>
       <c r="G324" t="s">
@@ -16936,7 +16922,7 @@
       <c r="E325" t="s">
         <v>1143</v>
       </c>
-      <c r="F325" s="2">
+      <c r="F325" s="1">
         <v>46125</v>
       </c>
       <c r="G325" t="s">
@@ -16946,7 +16932,7 @@
         <v>1353</v>
       </c>
       <c r="I325">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J325">
         <v>57</v>
@@ -16957,7 +16943,7 @@
       <c r="L325" t="s">
         <v>1435</v>
       </c>
-      <c r="N325" s="2">
+      <c r="N325" s="1">
         <v>46182</v>
       </c>
       <c r="Q325" t="b">
@@ -16980,7 +16966,7 @@
       <c r="E326" t="s">
         <v>1144</v>
       </c>
-      <c r="F326" s="2">
+      <c r="F326" s="1">
         <v>46125</v>
       </c>
       <c r="G326" t="s">
@@ -16995,7 +16981,7 @@
       <c r="L326" t="s">
         <v>1383</v>
       </c>
-      <c r="N326" s="2">
+      <c r="N326" s="1">
         <v>46232</v>
       </c>
       <c r="Q326" t="b">
@@ -17018,7 +17004,7 @@
       <c r="E327" t="s">
         <v>1140</v>
       </c>
-      <c r="F327" s="2">
+      <c r="F327" s="1">
         <v>46125</v>
       </c>
       <c r="G327" t="s">
@@ -17028,7 +17014,7 @@
         <v>1353</v>
       </c>
       <c r="I327">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J327">
         <v>57</v>
@@ -17039,7 +17025,7 @@
       <c r="L327" t="s">
         <v>1435</v>
       </c>
-      <c r="N327" s="2">
+      <c r="N327" s="1">
         <v>46182</v>
       </c>
       <c r="Q327" t="b">
@@ -17062,7 +17048,7 @@
       <c r="E328" t="s">
         <v>1145</v>
       </c>
-      <c r="F328" s="2">
+      <c r="F328" s="1">
         <v>46125</v>
       </c>
       <c r="G328" t="s">
@@ -17072,7 +17058,7 @@
         <v>1353</v>
       </c>
       <c r="I328">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J328">
         <v>57</v>
@@ -17083,7 +17069,7 @@
       <c r="L328" t="s">
         <v>1435</v>
       </c>
-      <c r="N328" s="2">
+      <c r="N328" s="1">
         <v>46182</v>
       </c>
       <c r="Q328" t="b">
@@ -17106,7 +17092,7 @@
       <c r="E329" t="s">
         <v>1146</v>
       </c>
-      <c r="F329" s="2">
+      <c r="F329" s="1">
         <v>46125</v>
       </c>
       <c r="G329" t="s">
@@ -17116,7 +17102,7 @@
         <v>1353</v>
       </c>
       <c r="I329">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J329">
         <v>57</v>
@@ -17127,7 +17113,7 @@
       <c r="L329" t="s">
         <v>1435</v>
       </c>
-      <c r="N329" s="2">
+      <c r="N329" s="1">
         <v>46182</v>
       </c>
       <c r="Q329" t="b">
@@ -17150,7 +17136,7 @@
       <c r="E330" t="s">
         <v>1147</v>
       </c>
-      <c r="F330" s="2">
+      <c r="F330" s="1">
         <v>46125</v>
       </c>
       <c r="G330" t="s">
@@ -17160,7 +17146,7 @@
         <v>1353</v>
       </c>
       <c r="I330">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J330">
         <v>57</v>
@@ -17171,7 +17157,7 @@
       <c r="L330" t="s">
         <v>1435</v>
       </c>
-      <c r="N330" s="2">
+      <c r="N330" s="1">
         <v>46182</v>
       </c>
       <c r="Q330" t="b">
@@ -17194,7 +17180,7 @@
       <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="F331" s="2">
+      <c r="F331" s="1">
         <v>46125</v>
       </c>
       <c r="G331" t="s">
@@ -17204,7 +17190,7 @@
         <v>1353</v>
       </c>
       <c r="I331">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K331" t="s">
         <v>1356</v>
@@ -17232,7 +17218,7 @@
       <c r="E332" t="s">
         <v>1148</v>
       </c>
-      <c r="F332" s="2">
+      <c r="F332" s="1">
         <v>46125</v>
       </c>
       <c r="G332" t="s">
@@ -17242,7 +17228,7 @@
         <v>1353</v>
       </c>
       <c r="I332">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K332" t="s">
         <v>1357</v>
@@ -17270,7 +17256,7 @@
       <c r="E333" t="s">
         <v>910</v>
       </c>
-      <c r="F333" s="2">
+      <c r="F333" s="1">
         <v>46125</v>
       </c>
       <c r="G333" t="s">
@@ -17280,7 +17266,7 @@
         <v>1353</v>
       </c>
       <c r="I333">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J333">
         <v>100</v>
@@ -17291,7 +17277,7 @@
       <c r="L333" t="s">
         <v>1395</v>
       </c>
-      <c r="N333" s="2">
+      <c r="N333" s="1">
         <v>46225</v>
       </c>
       <c r="Q333" t="b">
@@ -17314,7 +17300,7 @@
       <c r="E334" t="s">
         <v>1149</v>
       </c>
-      <c r="F334" s="2">
+      <c r="F334" s="1">
         <v>46125</v>
       </c>
       <c r="G334" t="s">
@@ -17324,7 +17310,7 @@
         <v>1353</v>
       </c>
       <c r="I334">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K334" t="s">
         <v>1357</v>
@@ -17352,7 +17338,7 @@
       <c r="E335" t="s">
         <v>1150</v>
       </c>
-      <c r="F335" s="2">
+      <c r="F335" s="1">
         <v>46127</v>
       </c>
       <c r="G335" t="s">
@@ -17367,7 +17353,7 @@
       <c r="L335" t="s">
         <v>1434</v>
       </c>
-      <c r="N335" s="2">
+      <c r="N335" s="1">
         <v>46175</v>
       </c>
       <c r="Q335" t="b">
@@ -17390,7 +17376,7 @@
       <c r="E336" t="s">
         <v>1151</v>
       </c>
-      <c r="F336" s="2">
+      <c r="F336" s="1">
         <v>46127</v>
       </c>
       <c r="G336" t="s">
@@ -17400,7 +17386,7 @@
         <v>1353</v>
       </c>
       <c r="I336">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J336">
         <v>28</v>
@@ -17411,7 +17397,7 @@
       <c r="L336" t="s">
         <v>1388</v>
       </c>
-      <c r="N336" s="2">
+      <c r="N336" s="1">
         <v>46155</v>
       </c>
       <c r="Q336" t="b">
@@ -17434,7 +17420,7 @@
       <c r="E337" t="s">
         <v>1152</v>
       </c>
-      <c r="F337" s="2">
+      <c r="F337" s="1">
         <v>46127</v>
       </c>
       <c r="G337" t="s">
@@ -17449,7 +17435,7 @@
       <c r="L337" t="s">
         <v>1434</v>
       </c>
-      <c r="N337" s="2">
+      <c r="N337" s="1">
         <v>46175</v>
       </c>
       <c r="Q337" t="b">
@@ -17472,7 +17458,7 @@
       <c r="E338" t="s">
         <v>1153</v>
       </c>
-      <c r="F338" s="2">
+      <c r="F338" s="1">
         <v>46127</v>
       </c>
       <c r="G338" t="s">
@@ -17482,7 +17468,7 @@
         <v>1353</v>
       </c>
       <c r="I338">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J338">
         <v>12</v>
@@ -17493,7 +17479,7 @@
       <c r="L338" t="s">
         <v>1388</v>
       </c>
-      <c r="N338" s="2">
+      <c r="N338" s="1">
         <v>46139</v>
       </c>
       <c r="Q338" t="b">
@@ -17516,7 +17502,7 @@
       <c r="E339" t="s">
         <v>1154</v>
       </c>
-      <c r="F339" s="2">
+      <c r="F339" s="1">
         <v>46129</v>
       </c>
       <c r="G339" t="s">
@@ -17545,7 +17531,7 @@
       <c r="E340" t="s">
         <v>1155</v>
       </c>
-      <c r="F340" s="2">
+      <c r="F340" s="1">
         <v>46142</v>
       </c>
       <c r="G340" t="s">
@@ -17555,7 +17541,7 @@
         <v>1353</v>
       </c>
       <c r="I340">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J340">
         <v>98</v>
@@ -17563,7 +17549,7 @@
       <c r="L340" t="s">
         <v>1383</v>
       </c>
-      <c r="N340" s="2">
+      <c r="N340" s="1">
         <v>46240</v>
       </c>
       <c r="Q340" t="b">
@@ -17586,7 +17572,7 @@
       <c r="E341" t="s">
         <v>1156</v>
       </c>
-      <c r="F341" s="2">
+      <c r="F341" s="1">
         <v>46142</v>
       </c>
       <c r="G341" t="s">
@@ -17596,7 +17582,7 @@
         <v>1353</v>
       </c>
       <c r="I341">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J341">
         <v>90</v>
@@ -17604,7 +17590,7 @@
       <c r="L341" t="s">
         <v>1383</v>
       </c>
-      <c r="N341" s="2">
+      <c r="N341" s="1">
         <v>46232</v>
       </c>
       <c r="Q341" t="b">
@@ -17627,7 +17613,7 @@
       <c r="E342" t="s">
         <v>1157</v>
       </c>
-      <c r="F342" s="2">
+      <c r="F342" s="1">
         <v>46142</v>
       </c>
       <c r="G342" t="s">
@@ -17637,7 +17623,7 @@
         <v>1353</v>
       </c>
       <c r="I342">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K342" t="s">
         <v>1356</v>
@@ -17665,7 +17651,7 @@
       <c r="E343" t="s">
         <v>1158</v>
       </c>
-      <c r="F343" s="2">
+      <c r="F343" s="1">
         <v>46142</v>
       </c>
       <c r="G343" t="s">
@@ -17680,7 +17666,7 @@
       <c r="L343" t="s">
         <v>1383</v>
       </c>
-      <c r="N343" s="2">
+      <c r="N343" s="1">
         <v>46232</v>
       </c>
       <c r="Q343" t="b">
@@ -17703,7 +17689,7 @@
       <c r="E344" t="s">
         <v>1159</v>
       </c>
-      <c r="F344" s="2">
+      <c r="F344" s="1">
         <v>46142</v>
       </c>
       <c r="G344" t="s">
@@ -17718,7 +17704,7 @@
       <c r="L344" t="s">
         <v>1383</v>
       </c>
-      <c r="N344" s="2">
+      <c r="N344" s="1">
         <v>46232</v>
       </c>
       <c r="Q344" t="b">
@@ -17741,7 +17727,7 @@
       <c r="E345" t="s">
         <v>1160</v>
       </c>
-      <c r="F345" s="2">
+      <c r="F345" s="1">
         <v>46142</v>
       </c>
       <c r="G345" t="s">
@@ -17751,7 +17737,7 @@
         <v>1353</v>
       </c>
       <c r="I345">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K345" t="s">
         <v>1356</v>
@@ -17779,7 +17765,7 @@
       <c r="E346" t="s">
         <v>1161</v>
       </c>
-      <c r="F346" s="2">
+      <c r="F346" s="1">
         <v>46142</v>
       </c>
       <c r="G346" t="s">
@@ -17794,7 +17780,7 @@
       <c r="L346" t="s">
         <v>1383</v>
       </c>
-      <c r="N346" s="2">
+      <c r="N346" s="1">
         <v>46232</v>
       </c>
       <c r="Q346" t="b">
@@ -17817,7 +17803,7 @@
       <c r="E347" t="s">
         <v>1162</v>
       </c>
-      <c r="F347" s="2">
+      <c r="F347" s="1">
         <v>46142</v>
       </c>
       <c r="G347" t="s">
@@ -17827,7 +17813,7 @@
         <v>1353</v>
       </c>
       <c r="I347">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J347">
         <v>18</v>
@@ -17838,8 +17824,11 @@
       <c r="L347" t="s">
         <v>1431</v>
       </c>
-      <c r="N347" s="2">
+      <c r="N347" s="1">
         <v>46160</v>
+      </c>
+      <c r="P347" t="s">
+        <v>1492</v>
       </c>
       <c r="Q347" t="b">
         <v>1</v>
@@ -17861,7 +17850,7 @@
       <c r="E348" t="s">
         <v>1163</v>
       </c>
-      <c r="F348" s="2">
+      <c r="F348" s="1">
         <v>46142</v>
       </c>
       <c r="G348" t="s">
@@ -17871,7 +17860,7 @@
         <v>1353</v>
       </c>
       <c r="I348">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J348">
         <v>14</v>
@@ -17882,7 +17871,7 @@
       <c r="L348" t="s">
         <v>1432</v>
       </c>
-      <c r="N348" s="2">
+      <c r="N348" s="1">
         <v>46156</v>
       </c>
       <c r="Q348" t="b">
@@ -17905,7 +17894,7 @@
       <c r="E349" t="s">
         <v>1164</v>
       </c>
-      <c r="F349" s="2">
+      <c r="F349" s="1">
         <v>46142</v>
       </c>
       <c r="G349" t="s">
@@ -17915,7 +17904,7 @@
         <v>1353</v>
       </c>
       <c r="I349">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K349" t="s">
         <v>1361</v>
@@ -17943,7 +17932,7 @@
       <c r="E350" t="s">
         <v>1165</v>
       </c>
-      <c r="F350" s="2">
+      <c r="F350" s="1">
         <v>46142</v>
       </c>
       <c r="G350" t="s">
@@ -17953,12 +17942,12 @@
         <v>1353</v>
       </c>
       <c r="I350">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J350">
         <v>46</v>
       </c>
-      <c r="N350" s="2">
+      <c r="N350" s="1">
         <v>46188</v>
       </c>
       <c r="Q350" t="b">
@@ -17981,7 +17970,7 @@
       <c r="E351" t="s">
         <v>1166</v>
       </c>
-      <c r="F351" s="2">
+      <c r="F351" s="1">
         <v>46142</v>
       </c>
       <c r="G351" t="s">
@@ -17991,7 +17980,7 @@
         <v>1353</v>
       </c>
       <c r="I351">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J351">
         <v>82</v>
@@ -18002,7 +17991,7 @@
       <c r="L351" t="s">
         <v>1436</v>
       </c>
-      <c r="N351" s="2">
+      <c r="N351" s="1">
         <v>46224</v>
       </c>
       <c r="Q351" t="b">
@@ -18025,7 +18014,7 @@
       <c r="E352" t="s">
         <v>1167</v>
       </c>
-      <c r="F352" s="2">
+      <c r="F352" s="1">
         <v>46142</v>
       </c>
       <c r="G352" t="s">
@@ -18035,7 +18024,7 @@
         <v>1353</v>
       </c>
       <c r="I352">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J352">
         <v>78</v>
@@ -18046,7 +18035,7 @@
       <c r="L352" t="s">
         <v>1437</v>
       </c>
-      <c r="N352" s="2">
+      <c r="N352" s="1">
         <v>46220</v>
       </c>
       <c r="Q352" t="b">
@@ -18069,7 +18058,7 @@
       <c r="E353" t="s">
         <v>1168</v>
       </c>
-      <c r="F353" s="2">
+      <c r="F353" s="1">
         <v>46142</v>
       </c>
       <c r="G353" t="s">
@@ -18079,7 +18068,7 @@
         <v>1353</v>
       </c>
       <c r="I353">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J353">
         <v>83</v>
@@ -18090,7 +18079,7 @@
       <c r="L353" t="s">
         <v>1395</v>
       </c>
-      <c r="N353" s="2">
+      <c r="N353" s="1">
         <v>46225</v>
       </c>
       <c r="Q353" t="b">
@@ -18113,7 +18102,7 @@
       <c r="E354" t="s">
         <v>1169</v>
       </c>
-      <c r="F354" s="2">
+      <c r="F354" s="1">
         <v>46142</v>
       </c>
       <c r="G354" t="s">
@@ -18123,7 +18112,7 @@
         <v>1353</v>
       </c>
       <c r="I354">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K354" t="s">
         <v>1360</v>
@@ -18151,7 +18140,7 @@
       <c r="E355" t="s">
         <v>1170</v>
       </c>
-      <c r="F355" s="2">
+      <c r="F355" s="1">
         <v>46142</v>
       </c>
       <c r="G355" t="s">
@@ -18161,7 +18150,7 @@
         <v>1353</v>
       </c>
       <c r="I355">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J355">
         <v>8</v>
@@ -18172,7 +18161,7 @@
       <c r="L355" t="s">
         <v>1438</v>
       </c>
-      <c r="N355" s="2">
+      <c r="N355" s="1">
         <v>46150</v>
       </c>
       <c r="Q355" t="b">
@@ -18195,7 +18184,7 @@
       <c r="E356" t="s">
         <v>1171</v>
       </c>
-      <c r="F356" s="2">
+      <c r="F356" s="1">
         <v>46142</v>
       </c>
       <c r="G356" t="s">
@@ -18210,7 +18199,7 @@
       <c r="L356" t="s">
         <v>1439</v>
       </c>
-      <c r="N356" s="2">
+      <c r="N356" s="1">
         <v>46176</v>
       </c>
       <c r="Q356" t="b">
@@ -18233,7 +18222,7 @@
       <c r="E357" t="s">
         <v>1172</v>
       </c>
-      <c r="F357" s="2">
+      <c r="F357" s="1">
         <v>46142</v>
       </c>
       <c r="G357" t="s">
@@ -18243,7 +18232,7 @@
         <v>1353</v>
       </c>
       <c r="I357">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J357">
         <v>85</v>
@@ -18251,7 +18240,7 @@
       <c r="K357" t="s">
         <v>1360</v>
       </c>
-      <c r="N357" s="2">
+      <c r="N357" s="1">
         <v>46227</v>
       </c>
       <c r="Q357" t="b">
@@ -18274,7 +18263,7 @@
       <c r="E358" t="s">
         <v>1173</v>
       </c>
-      <c r="F358" s="2">
+      <c r="F358" s="1">
         <v>46142</v>
       </c>
       <c r="G358" t="s">
@@ -18292,11 +18281,11 @@
       <c r="L358" t="s">
         <v>1440</v>
       </c>
-      <c r="N358" s="2">
+      <c r="N358" s="1">
         <v>46227</v>
       </c>
       <c r="P358" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="Q358" t="b">
         <v>0</v>
@@ -18318,7 +18307,7 @@
       <c r="E359" t="s">
         <v>1174</v>
       </c>
-      <c r="F359" s="2">
+      <c r="F359" s="1">
         <v>46142</v>
       </c>
       <c r="G359" t="s">
@@ -18330,11 +18319,11 @@
       <c r="J359">
         <v>63</v>
       </c>
-      <c r="N359" s="2">
+      <c r="N359" s="1">
         <v>46205</v>
       </c>
       <c r="P359" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="Q359" t="b">
         <v>0</v>
@@ -18356,7 +18345,7 @@
       <c r="E360" t="s">
         <v>949</v>
       </c>
-      <c r="F360" s="2">
+      <c r="F360" s="1">
         <v>46142</v>
       </c>
       <c r="G360" t="s">
@@ -18366,7 +18355,7 @@
         <v>1353</v>
       </c>
       <c r="I360">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J360">
         <v>83</v>
@@ -18377,7 +18366,7 @@
       <c r="L360" t="s">
         <v>1395</v>
       </c>
-      <c r="N360" s="2">
+      <c r="N360" s="1">
         <v>46225</v>
       </c>
       <c r="O360" t="s">
@@ -18403,7 +18392,7 @@
       <c r="E361" t="s">
         <v>961</v>
       </c>
-      <c r="F361" s="2">
+      <c r="F361" s="1">
         <v>46142</v>
       </c>
       <c r="G361" t="s">
@@ -18413,7 +18402,7 @@
         <v>1353</v>
       </c>
       <c r="I361">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J361">
         <v>83</v>
@@ -18424,7 +18413,7 @@
       <c r="L361" t="s">
         <v>1395</v>
       </c>
-      <c r="N361" s="2">
+      <c r="N361" s="1">
         <v>46225</v>
       </c>
       <c r="Q361" t="b">
@@ -18447,7 +18436,7 @@
       <c r="E362" t="s">
         <v>1175</v>
       </c>
-      <c r="F362" s="2">
+      <c r="F362" s="1">
         <v>46142</v>
       </c>
       <c r="G362" t="s">
@@ -18457,7 +18446,7 @@
         <v>1353</v>
       </c>
       <c r="I362">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K362" t="s">
         <v>1360</v>
@@ -18485,7 +18474,7 @@
       <c r="E363" t="s">
         <v>1176</v>
       </c>
-      <c r="F363" s="2">
+      <c r="F363" s="1">
         <v>46142</v>
       </c>
       <c r="G363" t="s">
@@ -18495,7 +18484,7 @@
         <v>1353</v>
       </c>
       <c r="I363">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K363" t="s">
         <v>1360</v>
@@ -18523,7 +18512,7 @@
       <c r="E364" t="s">
         <v>958</v>
       </c>
-      <c r="F364" s="2">
+      <c r="F364" s="1">
         <v>46142</v>
       </c>
       <c r="G364" t="s">
@@ -18533,7 +18522,7 @@
         <v>1353</v>
       </c>
       <c r="I364">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J364">
         <v>83</v>
@@ -18544,7 +18533,7 @@
       <c r="L364" t="s">
         <v>1395</v>
       </c>
-      <c r="N364" s="2">
+      <c r="N364" s="1">
         <v>46225</v>
       </c>
       <c r="Q364" t="b">
@@ -18567,7 +18556,7 @@
       <c r="E365" t="s">
         <v>1177</v>
       </c>
-      <c r="F365" s="2">
+      <c r="F365" s="1">
         <v>46142</v>
       </c>
       <c r="G365" t="s">
@@ -18577,7 +18566,7 @@
         <v>1353</v>
       </c>
       <c r="I365">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J365">
         <v>15</v>
@@ -18585,7 +18574,7 @@
       <c r="K365" t="s">
         <v>1359</v>
       </c>
-      <c r="N365" s="2">
+      <c r="N365" s="1">
         <v>46157</v>
       </c>
       <c r="Q365" t="b">
@@ -18608,7 +18597,7 @@
       <c r="E366" t="s">
         <v>1178</v>
       </c>
-      <c r="F366" s="2">
+      <c r="F366" s="1">
         <v>46148</v>
       </c>
       <c r="G366" t="s">
@@ -18618,7 +18607,7 @@
         <v>1353</v>
       </c>
       <c r="I366">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J366">
         <v>77</v>
@@ -18629,7 +18618,7 @@
       <c r="L366" t="s">
         <v>1388</v>
       </c>
-      <c r="N366" s="2">
+      <c r="N366" s="1">
         <v>46225</v>
       </c>
       <c r="Q366" t="b">
@@ -18652,7 +18641,7 @@
       <c r="E367" t="s">
         <v>1179</v>
       </c>
-      <c r="F367" s="2">
+      <c r="F367" s="1">
         <v>46148</v>
       </c>
       <c r="G367" t="s">
@@ -18662,7 +18651,7 @@
         <v>1353</v>
       </c>
       <c r="I367">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J367">
         <v>77</v>
@@ -18673,7 +18662,7 @@
       <c r="L367" t="s">
         <v>1388</v>
       </c>
-      <c r="N367" s="2">
+      <c r="N367" s="1">
         <v>46225</v>
       </c>
       <c r="Q367" t="b">
@@ -18696,7 +18685,7 @@
       <c r="E368" t="s">
         <v>1180</v>
       </c>
-      <c r="F368" s="2">
+      <c r="F368" s="1">
         <v>46148</v>
       </c>
       <c r="G368" t="s">
@@ -18706,7 +18695,7 @@
         <v>1353</v>
       </c>
       <c r="I368">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J368">
         <v>77</v>
@@ -18717,7 +18706,7 @@
       <c r="L368" t="s">
         <v>1395</v>
       </c>
-      <c r="N368" s="2">
+      <c r="N368" s="1">
         <v>46225</v>
       </c>
       <c r="Q368" t="b">
@@ -18740,7 +18729,7 @@
       <c r="E369" t="s">
         <v>1181</v>
       </c>
-      <c r="F369" s="2">
+      <c r="F369" s="1">
         <v>46148</v>
       </c>
       <c r="G369" t="s">
@@ -18750,7 +18739,7 @@
         <v>1353</v>
       </c>
       <c r="I369">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K369" t="s">
         <v>1360</v>
@@ -18778,7 +18767,7 @@
       <c r="E370" t="s">
         <v>1182</v>
       </c>
-      <c r="F370" s="2">
+      <c r="F370" s="1">
         <v>46148</v>
       </c>
       <c r="G370" t="s">
@@ -18788,7 +18777,7 @@
         <v>1353</v>
       </c>
       <c r="I370">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K370" t="s">
         <v>1360</v>
@@ -18816,7 +18805,7 @@
       <c r="E371" t="s">
         <v>1183</v>
       </c>
-      <c r="F371" s="2">
+      <c r="F371" s="1">
         <v>46148</v>
       </c>
       <c r="G371" t="s">
@@ -18826,7 +18815,7 @@
         <v>1353</v>
       </c>
       <c r="I371">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J371">
         <v>16</v>
@@ -18837,7 +18826,7 @@
       <c r="L371" t="s">
         <v>1441</v>
       </c>
-      <c r="N371" s="2">
+      <c r="N371" s="1">
         <v>46164</v>
       </c>
       <c r="Q371" t="b">
@@ -18860,7 +18849,7 @@
       <c r="E372" t="s">
         <v>1184</v>
       </c>
-      <c r="F372" s="2">
+      <c r="F372" s="1">
         <v>46148</v>
       </c>
       <c r="G372" t="s">
@@ -18878,11 +18867,11 @@
       <c r="L372" t="s">
         <v>1428</v>
       </c>
-      <c r="N372" s="2">
+      <c r="N372" s="1">
         <v>46113</v>
       </c>
       <c r="P372" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="Q372" t="b">
         <v>0</v>
@@ -18904,7 +18893,7 @@
       <c r="E373" t="s">
         <v>1185</v>
       </c>
-      <c r="F373" s="2">
+      <c r="F373" s="1">
         <v>46149</v>
       </c>
       <c r="G373" t="s">
@@ -18914,7 +18903,7 @@
         <v>1353</v>
       </c>
       <c r="I373">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K373" t="s">
         <v>1356</v>
@@ -18942,7 +18931,7 @@
       <c r="E374" t="s">
         <v>1186</v>
       </c>
-      <c r="F374" s="2">
+      <c r="F374" s="1">
         <v>46149</v>
       </c>
       <c r="G374" t="s">
@@ -18952,7 +18941,7 @@
         <v>1353</v>
       </c>
       <c r="I374">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K374" t="s">
         <v>1356</v>
@@ -18980,7 +18969,7 @@
       <c r="E375" t="s">
         <v>1187</v>
       </c>
-      <c r="F375" s="2">
+      <c r="F375" s="1">
         <v>46154</v>
       </c>
       <c r="G375" t="s">
@@ -18990,7 +18979,7 @@
         <v>1353</v>
       </c>
       <c r="I375">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J375">
         <v>94</v>
@@ -18998,7 +18987,7 @@
       <c r="K375" t="s">
         <v>1360</v>
       </c>
-      <c r="N375" s="2">
+      <c r="N375" s="1">
         <v>46248</v>
       </c>
       <c r="Q375" t="b">
@@ -19021,7 +19010,7 @@
       <c r="E376" t="s">
         <v>1188</v>
       </c>
-      <c r="F376" s="2">
+      <c r="F376" s="1">
         <v>46154</v>
       </c>
       <c r="G376" t="s">
@@ -19031,7 +19020,7 @@
         <v>1353</v>
       </c>
       <c r="I376">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K376" t="s">
         <v>1360</v>
@@ -19059,7 +19048,7 @@
       <c r="E377" t="s">
         <v>1189</v>
       </c>
-      <c r="F377" s="2">
+      <c r="F377" s="1">
         <v>46154</v>
       </c>
       <c r="G377" t="s">
@@ -19071,14 +19060,14 @@
       <c r="K377" t="s">
         <v>1360</v>
       </c>
-      <c r="N377" s="2">
+      <c r="N377" s="1">
         <v>46176</v>
       </c>
       <c r="O377" t="s">
         <v>1472</v>
       </c>
       <c r="P377" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="Q377" t="b">
         <v>0</v>
@@ -19100,7 +19089,7 @@
       <c r="E378" t="s">
         <v>1190</v>
       </c>
-      <c r="F378" s="2">
+      <c r="F378" s="1">
         <v>46154</v>
       </c>
       <c r="G378" t="s">
@@ -19110,7 +19099,7 @@
         <v>1353</v>
       </c>
       <c r="I378">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K378" t="s">
         <v>1360</v>
@@ -19138,7 +19127,7 @@
       <c r="E379" t="s">
         <v>1191</v>
       </c>
-      <c r="F379" s="2">
+      <c r="F379" s="1">
         <v>46154</v>
       </c>
       <c r="G379" t="s">
@@ -19148,7 +19137,7 @@
         <v>1353</v>
       </c>
       <c r="I379">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J379">
         <v>20</v>
@@ -19159,7 +19148,7 @@
       <c r="L379" t="s">
         <v>1442</v>
       </c>
-      <c r="N379" s="2">
+      <c r="N379" s="1">
         <v>46174</v>
       </c>
       <c r="Q379" t="b">
@@ -19182,7 +19171,7 @@
       <c r="E380" t="s">
         <v>1192</v>
       </c>
-      <c r="F380" s="2">
+      <c r="F380" s="1">
         <v>46154</v>
       </c>
       <c r="G380" t="s">
@@ -19192,7 +19181,7 @@
         <v>1353</v>
       </c>
       <c r="I380">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J380">
         <v>94</v>
@@ -19203,7 +19192,7 @@
       <c r="L380" t="s">
         <v>1443</v>
       </c>
-      <c r="N380" s="2">
+      <c r="N380" s="1">
         <v>46248</v>
       </c>
       <c r="Q380" t="b">
@@ -19226,7 +19215,7 @@
       <c r="E381" t="s">
         <v>1193</v>
       </c>
-      <c r="F381" s="2">
+      <c r="F381" s="1">
         <v>46154</v>
       </c>
       <c r="G381" t="s">
@@ -19236,7 +19225,7 @@
         <v>1353</v>
       </c>
       <c r="I381">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K381" t="s">
         <v>1360</v>
@@ -19264,7 +19253,7 @@
       <c r="E382" t="s">
         <v>1194</v>
       </c>
-      <c r="F382" s="2">
+      <c r="F382" s="1">
         <v>46154</v>
       </c>
       <c r="G382" t="s">
@@ -19274,7 +19263,7 @@
         <v>1353</v>
       </c>
       <c r="I382">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K382" t="s">
         <v>1360</v>
@@ -19302,7 +19291,7 @@
       <c r="E383" t="s">
         <v>1195</v>
       </c>
-      <c r="F383" s="2">
+      <c r="F383" s="1">
         <v>46154</v>
       </c>
       <c r="G383" t="s">
@@ -19312,7 +19301,7 @@
         <v>1353</v>
       </c>
       <c r="I383">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J383">
         <v>71</v>
@@ -19323,7 +19312,7 @@
       <c r="L383" t="s">
         <v>1444</v>
       </c>
-      <c r="N383" s="2">
+      <c r="N383" s="1">
         <v>46225</v>
       </c>
       <c r="Q383" t="b">
@@ -19346,7 +19335,7 @@
       <c r="E384" t="s">
         <v>1196</v>
       </c>
-      <c r="F384" s="2">
+      <c r="F384" s="1">
         <v>46164</v>
       </c>
       <c r="G384" t="s">
@@ -19356,7 +19345,7 @@
         <v>1353</v>
       </c>
       <c r="I384">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K384" t="s">
         <v>1357</v>
@@ -19384,7 +19373,7 @@
       <c r="E385" t="s">
         <v>1197</v>
       </c>
-      <c r="F385" s="2">
+      <c r="F385" s="1">
         <v>46164</v>
       </c>
       <c r="G385" t="s">
@@ -19394,7 +19383,7 @@
         <v>1353</v>
       </c>
       <c r="I385">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J385">
         <v>102</v>
@@ -19405,7 +19394,7 @@
       <c r="L385" t="s">
         <v>1445</v>
       </c>
-      <c r="N385" s="2">
+      <c r="N385" s="1">
         <v>46266</v>
       </c>
       <c r="P385" t="s">
@@ -19431,7 +19420,7 @@
       <c r="E386" t="s">
         <v>1198</v>
       </c>
-      <c r="F386" s="2">
+      <c r="F386" s="1">
         <v>46171</v>
       </c>
       <c r="G386" t="s">
@@ -19441,7 +19430,7 @@
         <v>1353</v>
       </c>
       <c r="I386">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K386" t="s">
         <v>1360</v>
@@ -19469,7 +19458,7 @@
       <c r="E387" t="s">
         <v>1199</v>
       </c>
-      <c r="F387" s="2">
+      <c r="F387" s="1">
         <v>46171</v>
       </c>
       <c r="G387" t="s">
@@ -19479,7 +19468,7 @@
         <v>1353</v>
       </c>
       <c r="I387">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K387" t="s">
         <v>1360</v>
@@ -19507,7 +19496,7 @@
       <c r="E388" t="s">
         <v>851</v>
       </c>
-      <c r="F388" s="2">
+      <c r="F388" s="1">
         <v>46171</v>
       </c>
       <c r="G388" t="s">
@@ -19517,7 +19506,7 @@
         <v>1353</v>
       </c>
       <c r="I388">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J388">
         <v>-85</v>
@@ -19528,7 +19517,7 @@
       <c r="L388" t="s">
         <v>1446</v>
       </c>
-      <c r="N388" s="2">
+      <c r="N388" s="1">
         <v>46086</v>
       </c>
       <c r="Q388" t="b">
@@ -19551,7 +19540,7 @@
       <c r="E389" t="s">
         <v>1200</v>
       </c>
-      <c r="F389" s="2">
+      <c r="F389" s="1">
         <v>46171</v>
       </c>
       <c r="G389" t="s">
@@ -19561,7 +19550,7 @@
         <v>1353</v>
       </c>
       <c r="I389">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K389" t="s">
         <v>1361</v>
@@ -19589,7 +19578,7 @@
       <c r="E390" t="s">
         <v>1201</v>
       </c>
-      <c r="F390" s="2">
+      <c r="F390" s="1">
         <v>46171</v>
       </c>
       <c r="G390" t="s">
@@ -19607,11 +19596,11 @@
       <c r="L390" t="s">
         <v>1447</v>
       </c>
-      <c r="N390" s="2">
+      <c r="N390" s="1">
         <v>46191</v>
       </c>
       <c r="P390" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="Q390" t="b">
         <v>0</v>
@@ -19633,7 +19622,7 @@
       <c r="E391" t="s">
         <v>1202</v>
       </c>
-      <c r="F391" s="2">
+      <c r="F391" s="1">
         <v>46171</v>
       </c>
       <c r="G391" t="s">
@@ -19649,7 +19638,7 @@
         <v>1452</v>
       </c>
       <c r="P391" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="Q391" t="b">
         <v>0</v>
@@ -19671,7 +19660,7 @@
       <c r="E392" t="s">
         <v>1203</v>
       </c>
-      <c r="F392" s="2">
+      <c r="F392" s="1">
         <v>46171</v>
       </c>
       <c r="G392" t="s">
@@ -19686,7 +19675,7 @@
       <c r="L392" t="s">
         <v>1439</v>
       </c>
-      <c r="N392" s="2">
+      <c r="N392" s="1">
         <v>46176</v>
       </c>
       <c r="Q392" t="b">
@@ -19709,7 +19698,7 @@
       <c r="E393" t="s">
         <v>1204</v>
       </c>
-      <c r="F393" s="2">
+      <c r="F393" s="1">
         <v>46171</v>
       </c>
       <c r="G393" t="s">
@@ -19719,7 +19708,7 @@
         <v>1353</v>
       </c>
       <c r="I393">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J393">
         <v>20</v>
@@ -19730,7 +19719,7 @@
       <c r="L393" t="s">
         <v>1388</v>
       </c>
-      <c r="N393" s="2">
+      <c r="N393" s="1">
         <v>46191</v>
       </c>
       <c r="Q393" t="b">
@@ -19753,7 +19742,7 @@
       <c r="E394" t="s">
         <v>1205</v>
       </c>
-      <c r="F394" s="2">
+      <c r="F394" s="1">
         <v>46171</v>
       </c>
       <c r="G394" t="s">
@@ -19771,11 +19760,11 @@
       <c r="L394" t="s">
         <v>1448</v>
       </c>
-      <c r="N394" s="2">
+      <c r="N394" s="1">
         <v>46241</v>
       </c>
       <c r="P394" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="Q394" t="b">
         <v>0</v>
@@ -19797,7 +19786,7 @@
       <c r="E395" t="s">
         <v>1206</v>
       </c>
-      <c r="F395" s="2">
+      <c r="F395" s="1">
         <v>46171</v>
       </c>
       <c r="G395" t="s">
@@ -19815,11 +19804,11 @@
       <c r="L395" t="s">
         <v>1449</v>
       </c>
-      <c r="N395" s="2">
+      <c r="N395" s="1">
         <v>46191</v>
       </c>
       <c r="P395" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="Q395" t="b">
         <v>0</v>
@@ -19841,7 +19830,7 @@
       <c r="E396" t="s">
         <v>1207</v>
       </c>
-      <c r="F396" s="2">
+      <c r="F396" s="1">
         <v>46171</v>
       </c>
       <c r="G396" t="s">
@@ -19853,11 +19842,11 @@
       <c r="J396">
         <v>20</v>
       </c>
-      <c r="N396" s="2">
+      <c r="N396" s="1">
         <v>46191</v>
       </c>
       <c r="P396" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="Q396" t="b">
         <v>0</v>
@@ -19879,7 +19868,7 @@
       <c r="E397" t="s">
         <v>1208</v>
       </c>
-      <c r="F397" s="2">
+      <c r="F397" s="1">
         <v>46171</v>
       </c>
       <c r="G397" t="s">
@@ -19897,11 +19886,11 @@
       <c r="L397" t="s">
         <v>1448</v>
       </c>
-      <c r="N397" s="2">
+      <c r="N397" s="1">
         <v>46241</v>
       </c>
       <c r="P397" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="Q397" t="b">
         <v>0</v>
@@ -19923,7 +19912,7 @@
       <c r="E398" t="s">
         <v>1209</v>
       </c>
-      <c r="F398" s="2">
+      <c r="F398" s="1">
         <v>46171</v>
       </c>
       <c r="G398" t="s">
@@ -19941,11 +19930,11 @@
       <c r="L398" t="s">
         <v>1449</v>
       </c>
-      <c r="N398" s="2">
+      <c r="N398" s="1">
         <v>46191</v>
       </c>
       <c r="P398" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="Q398" t="b">
         <v>0</v>
@@ -19967,7 +19956,7 @@
       <c r="E399" t="s">
         <v>987</v>
       </c>
-      <c r="F399" s="2">
+      <c r="F399" s="1">
         <v>46163</v>
       </c>
       <c r="G399" t="s">
@@ -19982,7 +19971,7 @@
       <c r="L399" t="s">
         <v>1450</v>
       </c>
-      <c r="N399" s="2">
+      <c r="N399" s="1">
         <v>46171</v>
       </c>
       <c r="Q399" t="b">
@@ -20005,7 +19994,7 @@
       <c r="E400" t="s">
         <v>1210</v>
       </c>
-      <c r="F400" s="2">
+      <c r="F400" s="1">
         <v>46171</v>
       </c>
       <c r="G400" t="s">
@@ -20015,7 +20004,7 @@
         <v>1353</v>
       </c>
       <c r="I400">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K400" t="s">
         <v>1360</v>
@@ -20043,7 +20032,7 @@
       <c r="E401" t="s">
         <v>1211</v>
       </c>
-      <c r="F401" s="2">
+      <c r="F401" s="1">
         <v>46171</v>
       </c>
       <c r="G401" t="s">
@@ -20055,11 +20044,11 @@
       <c r="J401">
         <v>40</v>
       </c>
-      <c r="N401" s="2">
+      <c r="N401" s="1">
         <v>46211</v>
       </c>
       <c r="P401" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="Q401" t="b">
         <v>0</v>
@@ -20081,7 +20070,7 @@
       <c r="E402" t="s">
         <v>1212</v>
       </c>
-      <c r="F402" s="2">
+      <c r="F402" s="1">
         <v>46171</v>
       </c>
       <c r="G402" t="s">
@@ -20091,7 +20080,7 @@
         <v>1353</v>
       </c>
       <c r="I402">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K402" t="s">
         <v>1360</v>
@@ -20119,7 +20108,7 @@
       <c r="E403" t="s">
         <v>1213</v>
       </c>
-      <c r="F403" s="2">
+      <c r="F403" s="1">
         <v>46171</v>
       </c>
       <c r="G403" t="s">
@@ -20129,7 +20118,7 @@
         <v>1353</v>
       </c>
       <c r="I403">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J403">
         <v>83</v>
@@ -20140,7 +20129,7 @@
       <c r="L403" t="s">
         <v>1451</v>
       </c>
-      <c r="N403" s="2">
+      <c r="N403" s="1">
         <v>46254</v>
       </c>
       <c r="Q403" t="b">
@@ -20163,7 +20152,7 @@
       <c r="E404" t="s">
         <v>1214</v>
       </c>
-      <c r="F404" s="2">
+      <c r="F404" s="1">
         <v>46171</v>
       </c>
       <c r="G404" t="s">
@@ -20173,7 +20162,7 @@
         <v>1353</v>
       </c>
       <c r="I404">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K404" t="s">
         <v>1360</v>
@@ -20201,7 +20190,7 @@
       <c r="E405" t="s">
         <v>1215</v>
       </c>
-      <c r="F405" s="2">
+      <c r="F405" s="1">
         <v>46183</v>
       </c>
       <c r="G405" t="s">
@@ -20211,7 +20200,7 @@
         <v>1354</v>
       </c>
       <c r="P405" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="Q405" t="b">
         <v>0</v>
@@ -20233,7 +20222,7 @@
       <c r="E406" t="s">
         <v>1216</v>
       </c>
-      <c r="F406" s="2">
+      <c r="F406" s="1">
         <v>46183</v>
       </c>
       <c r="G406" t="s">
@@ -20243,7 +20232,7 @@
         <v>1353</v>
       </c>
       <c r="I406">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q406" t="b">
         <v>1</v>
@@ -20265,7 +20254,7 @@
       <c r="E407" t="s">
         <v>1217</v>
       </c>
-      <c r="F407" s="2">
+      <c r="F407" s="1">
         <v>46183</v>
       </c>
       <c r="G407" t="s">
@@ -20275,7 +20264,7 @@
         <v>1353</v>
       </c>
       <c r="I407">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q407" t="b">
         <v>1</v>
@@ -20297,7 +20286,7 @@
       <c r="E408" t="s">
         <v>1218</v>
       </c>
-      <c r="F408" s="2">
+      <c r="F408" s="1">
         <v>46183</v>
       </c>
       <c r="G408" t="s">
@@ -20307,7 +20296,7 @@
         <v>1353</v>
       </c>
       <c r="I408">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q408" t="b">
         <v>1</v>
@@ -20329,7 +20318,7 @@
       <c r="E409" t="s">
         <v>1219</v>
       </c>
-      <c r="F409" s="2">
+      <c r="F409" s="1">
         <v>46183</v>
       </c>
       <c r="G409" t="s">
@@ -20339,7 +20328,7 @@
         <v>1353</v>
       </c>
       <c r="I409">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q409" t="b">
         <v>1</v>
@@ -20361,7 +20350,7 @@
       <c r="E410" t="s">
         <v>1220</v>
       </c>
-      <c r="F410" s="2">
+      <c r="F410" s="1">
         <v>46183</v>
       </c>
       <c r="G410" t="s">
@@ -20371,7 +20360,7 @@
         <v>1353</v>
       </c>
       <c r="I410">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q410" t="b">
         <v>1</v>
@@ -20393,7 +20382,7 @@
       <c r="E411" t="s">
         <v>1221</v>
       </c>
-      <c r="F411" s="2">
+      <c r="F411" s="1">
         <v>46188</v>
       </c>
       <c r="G411" t="s">
@@ -20403,7 +20392,7 @@
         <v>1353</v>
       </c>
       <c r="I411">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q411" t="b">
         <v>1</v>
@@ -20425,7 +20414,7 @@
       <c r="E412" t="s">
         <v>1222</v>
       </c>
-      <c r="F412" s="2">
+      <c r="F412" s="1">
         <v>46188</v>
       </c>
       <c r="G412" t="s">
@@ -20435,7 +20424,7 @@
         <v>1353</v>
       </c>
       <c r="I412">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q412" t="b">
         <v>1</v>
@@ -20457,7 +20446,7 @@
       <c r="E413" t="s">
         <v>1223</v>
       </c>
-      <c r="F413" s="2">
+      <c r="F413" s="1">
         <v>46188</v>
       </c>
       <c r="G413" t="s">
@@ -20467,7 +20456,7 @@
         <v>1353</v>
       </c>
       <c r="I413">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q413" t="b">
         <v>1</v>
@@ -20489,7 +20478,7 @@
       <c r="E414" t="s">
         <v>1224</v>
       </c>
-      <c r="F414" s="2">
+      <c r="F414" s="1">
         <v>46188</v>
       </c>
       <c r="G414" t="s">
@@ -20518,7 +20507,7 @@
       <c r="E415" t="s">
         <v>1060</v>
       </c>
-      <c r="F415" s="2">
+      <c r="F415" s="1">
         <v>46188</v>
       </c>
       <c r="G415" t="s">
@@ -20547,7 +20536,7 @@
       <c r="E416" t="s">
         <v>1225</v>
       </c>
-      <c r="F416" s="2">
+      <c r="F416" s="1">
         <v>46188</v>
       </c>
       <c r="G416" t="s">
@@ -20557,7 +20546,7 @@
         <v>1353</v>
       </c>
       <c r="I416">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q416" t="b">
         <v>1</v>
@@ -20579,7 +20568,7 @@
       <c r="E417" t="s">
         <v>1226</v>
       </c>
-      <c r="F417" s="2">
+      <c r="F417" s="1">
         <v>46188</v>
       </c>
       <c r="G417" t="s">
@@ -20608,7 +20597,7 @@
       <c r="E418" t="s">
         <v>1227</v>
       </c>
-      <c r="F418" s="2">
+      <c r="F418" s="1">
         <v>46188</v>
       </c>
       <c r="G418" t="s">
@@ -20637,7 +20626,7 @@
       <c r="E419" t="s">
         <v>1228</v>
       </c>
-      <c r="F419" s="2">
+      <c r="F419" s="1">
         <v>46188</v>
       </c>
       <c r="G419" t="s">
@@ -20647,7 +20636,7 @@
         <v>1353</v>
       </c>
       <c r="I419">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q419" t="b">
         <v>1</v>
@@ -20669,7 +20658,7 @@
       <c r="E420" t="s">
         <v>1229</v>
       </c>
-      <c r="F420" s="2">
+      <c r="F420" s="1">
         <v>46188</v>
       </c>
       <c r="G420" t="s">
@@ -20679,7 +20668,7 @@
         <v>1353</v>
       </c>
       <c r="I420">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q420" t="b">
         <v>1</v>
@@ -20701,7 +20690,7 @@
       <c r="E421" t="s">
         <v>1230</v>
       </c>
-      <c r="F421" s="2">
+      <c r="F421" s="1">
         <v>46188</v>
       </c>
       <c r="G421" t="s">
@@ -20711,7 +20700,7 @@
         <v>1353</v>
       </c>
       <c r="I421">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q421" t="b">
         <v>1</v>
@@ -20733,7 +20722,7 @@
       <c r="E422" t="s">
         <v>1231</v>
       </c>
-      <c r="F422" s="2">
+      <c r="F422" s="1">
         <v>46188</v>
       </c>
       <c r="G422" t="s">
@@ -20743,7 +20732,7 @@
         <v>1353</v>
       </c>
       <c r="I422">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q422" t="b">
         <v>1</v>
@@ -20765,7 +20754,7 @@
       <c r="E423" t="s">
         <v>1232</v>
       </c>
-      <c r="F423" s="2">
+      <c r="F423" s="1">
         <v>46188</v>
       </c>
       <c r="G423" t="s">
@@ -20775,7 +20764,7 @@
         <v>1353</v>
       </c>
       <c r="I423">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q423" t="b">
         <v>1</v>
@@ -20797,7 +20786,7 @@
       <c r="E424" t="s">
         <v>1233</v>
       </c>
-      <c r="F424" s="2">
+      <c r="F424" s="1">
         <v>46188</v>
       </c>
       <c r="G424" t="s">
@@ -20807,7 +20796,7 @@
         <v>1353</v>
       </c>
       <c r="I424">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q424" t="b">
         <v>1</v>
@@ -20829,7 +20818,7 @@
       <c r="E425" t="s">
         <v>1234</v>
       </c>
-      <c r="F425" s="2">
+      <c r="F425" s="1">
         <v>46188</v>
       </c>
       <c r="G425" t="s">
@@ -20839,7 +20828,7 @@
         <v>1353</v>
       </c>
       <c r="I425">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q425" t="b">
         <v>1</v>
@@ -20861,7 +20850,7 @@
       <c r="E426" t="s">
         <v>1235</v>
       </c>
-      <c r="F426" s="2">
+      <c r="F426" s="1">
         <v>46188</v>
       </c>
       <c r="G426" t="s">
@@ -20871,7 +20860,7 @@
         <v>1353</v>
       </c>
       <c r="I426">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q426" t="b">
         <v>1</v>
@@ -20893,7 +20882,7 @@
       <c r="E427" t="s">
         <v>1236</v>
       </c>
-      <c r="F427" s="2">
+      <c r="F427" s="1">
         <v>46188</v>
       </c>
       <c r="G427" t="s">
@@ -20903,7 +20892,7 @@
         <v>1353</v>
       </c>
       <c r="I427">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q427" t="b">
         <v>1</v>
@@ -20925,7 +20914,7 @@
       <c r="E428" t="s">
         <v>1237</v>
       </c>
-      <c r="F428" s="2">
+      <c r="F428" s="1">
         <v>46188</v>
       </c>
       <c r="G428" t="s">
@@ -20954,7 +20943,7 @@
       <c r="E429" t="s">
         <v>1238</v>
       </c>
-      <c r="F429" s="2">
+      <c r="F429" s="1">
         <v>46188</v>
       </c>
       <c r="G429" t="s">
@@ -20983,7 +20972,7 @@
       <c r="E430" t="s">
         <v>1239</v>
       </c>
-      <c r="F430" s="2">
+      <c r="F430" s="1">
         <v>46188</v>
       </c>
       <c r="G430" t="s">
@@ -20993,7 +20982,7 @@
         <v>1353</v>
       </c>
       <c r="I430">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q430" t="b">
         <v>1</v>
@@ -21015,7 +21004,7 @@
       <c r="E431" t="s">
         <v>1240</v>
       </c>
-      <c r="F431" s="2">
+      <c r="F431" s="1">
         <v>46188</v>
       </c>
       <c r="G431" t="s">
@@ -21025,7 +21014,7 @@
         <v>1353</v>
       </c>
       <c r="I431">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q431" t="b">
         <v>1</v>
@@ -21047,7 +21036,7 @@
       <c r="E432" t="s">
         <v>1241</v>
       </c>
-      <c r="F432" s="2">
+      <c r="F432" s="1">
         <v>46188</v>
       </c>
       <c r="G432" t="s">
@@ -21057,7 +21046,7 @@
         <v>1353</v>
       </c>
       <c r="I432">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q432" t="b">
         <v>1</v>
@@ -21079,7 +21068,7 @@
       <c r="E433" t="s">
         <v>1242</v>
       </c>
-      <c r="F433" s="2">
+      <c r="F433" s="1">
         <v>46188</v>
       </c>
       <c r="G433" t="s">
@@ -21089,7 +21078,7 @@
         <v>1353</v>
       </c>
       <c r="I433">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q433" t="b">
         <v>1</v>
@@ -21111,7 +21100,7 @@
       <c r="E434" t="s">
         <v>1243</v>
       </c>
-      <c r="F434" s="2">
+      <c r="F434" s="1">
         <v>46188</v>
       </c>
       <c r="G434" t="s">
@@ -21121,7 +21110,7 @@
         <v>1353</v>
       </c>
       <c r="I434">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q434" t="b">
         <v>1</v>
@@ -21143,7 +21132,7 @@
       <c r="E435" t="s">
         <v>856</v>
       </c>
-      <c r="F435" s="2">
+      <c r="F435" s="1">
         <v>46188</v>
       </c>
       <c r="G435" t="s">
@@ -21153,7 +21142,7 @@
         <v>1353</v>
       </c>
       <c r="I435">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q435" t="b">
         <v>1</v>
@@ -21175,7 +21164,7 @@
       <c r="E436" t="s">
         <v>1244</v>
       </c>
-      <c r="F436" s="2">
+      <c r="F436" s="1">
         <v>46188</v>
       </c>
       <c r="G436" t="s">
@@ -21185,7 +21174,7 @@
         <v>1353</v>
       </c>
       <c r="I436">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q436" t="b">
         <v>1</v>
@@ -21207,7 +21196,7 @@
       <c r="E437" t="s">
         <v>1245</v>
       </c>
-      <c r="F437" s="2">
+      <c r="F437" s="1">
         <v>46188</v>
       </c>
       <c r="G437" t="s">
@@ -21217,7 +21206,7 @@
         <v>1355</v>
       </c>
       <c r="I437">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q437" t="b">
         <v>1</v>
@@ -21239,7 +21228,7 @@
       <c r="E438" t="s">
         <v>1246</v>
       </c>
-      <c r="F438" s="2">
+      <c r="F438" s="1">
         <v>46188</v>
       </c>
       <c r="G438" t="s">
@@ -21249,7 +21238,7 @@
         <v>1355</v>
       </c>
       <c r="I438">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q438" t="b">
         <v>1</v>
@@ -21271,7 +21260,7 @@
       <c r="E439" t="s">
         <v>1247</v>
       </c>
-      <c r="F439" s="2">
+      <c r="F439" s="1">
         <v>46196</v>
       </c>
       <c r="G439" t="s">
@@ -21281,7 +21270,7 @@
         <v>1353</v>
       </c>
       <c r="I439">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q439" t="b">
         <v>1</v>
@@ -21303,7 +21292,7 @@
       <c r="E440" t="s">
         <v>1248</v>
       </c>
-      <c r="F440" s="2">
+      <c r="F440" s="1">
         <v>46196</v>
       </c>
       <c r="G440" t="s">
@@ -21313,7 +21302,7 @@
         <v>1353</v>
       </c>
       <c r="I440">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q440" t="b">
         <v>1</v>
@@ -21335,7 +21324,7 @@
       <c r="E441" t="s">
         <v>1249</v>
       </c>
-      <c r="F441" s="2">
+      <c r="F441" s="1">
         <v>46203</v>
       </c>
       <c r="G441" t="s">
@@ -21345,7 +21334,7 @@
         <v>1353</v>
       </c>
       <c r="I441">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q441" t="b">
         <v>1</v>
@@ -21367,7 +21356,7 @@
       <c r="E442" t="s">
         <v>1250</v>
       </c>
-      <c r="F442" s="2">
+      <c r="F442" s="1">
         <v>46203</v>
       </c>
       <c r="G442" t="s">
@@ -21396,7 +21385,7 @@
       <c r="E443" t="s">
         <v>1251</v>
       </c>
-      <c r="F443" s="2">
+      <c r="F443" s="1">
         <v>46205</v>
       </c>
       <c r="G443" t="s">
@@ -21406,7 +21395,7 @@
         <v>1353</v>
       </c>
       <c r="I443">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q443" t="b">
         <v>1</v>
@@ -21428,7 +21417,7 @@
       <c r="E444" t="s">
         <v>1252</v>
       </c>
-      <c r="F444" s="2">
+      <c r="F444" s="1">
         <v>46205</v>
       </c>
       <c r="G444" t="s">
@@ -21457,7 +21446,7 @@
       <c r="E445" t="s">
         <v>1253</v>
       </c>
-      <c r="F445" s="2">
+      <c r="F445" s="1">
         <v>46205</v>
       </c>
       <c r="G445" t="s">
@@ -21486,7 +21475,7 @@
       <c r="E446" t="s">
         <v>1254</v>
       </c>
-      <c r="F446" s="2">
+      <c r="F446" s="1">
         <v>46211</v>
       </c>
       <c r="G446" t="s">
@@ -21496,7 +21485,7 @@
         <v>1353</v>
       </c>
       <c r="I446">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q446" t="b">
         <v>1</v>
@@ -21518,7 +21507,7 @@
       <c r="E447" t="s">
         <v>1255</v>
       </c>
-      <c r="F447" s="2">
+      <c r="F447" s="1">
         <v>46211</v>
       </c>
       <c r="G447" t="s">
@@ -21528,7 +21517,7 @@
         <v>1353</v>
       </c>
       <c r="I447">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q447" t="b">
         <v>1</v>
@@ -21550,7 +21539,7 @@
       <c r="E448" t="s">
         <v>1256</v>
       </c>
-      <c r="F448" s="2">
+      <c r="F448" s="1">
         <v>46226</v>
       </c>
       <c r="G448" t="s">
@@ -21560,7 +21549,7 @@
         <v>1353</v>
       </c>
       <c r="I448">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q448" t="b">
         <v>1</v>
@@ -21582,7 +21571,7 @@
       <c r="E449" t="s">
         <v>1257</v>
       </c>
-      <c r="F449" s="2">
+      <c r="F449" s="1">
         <v>46226</v>
       </c>
       <c r="G449" t="s">
@@ -21592,7 +21581,7 @@
         <v>1353</v>
       </c>
       <c r="I449">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q449" t="b">
         <v>1</v>
@@ -21614,7 +21603,7 @@
       <c r="E450" t="s">
         <v>1258</v>
       </c>
-      <c r="F450" s="2">
+      <c r="F450" s="1">
         <v>46226</v>
       </c>
       <c r="G450" t="s">
@@ -21624,7 +21613,7 @@
         <v>1353</v>
       </c>
       <c r="I450">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q450" t="b">
         <v>1</v>
@@ -21646,7 +21635,7 @@
       <c r="E451" t="s">
         <v>1035</v>
       </c>
-      <c r="F451" s="2">
+      <c r="F451" s="1">
         <v>46230</v>
       </c>
       <c r="G451" t="s">
@@ -21656,7 +21645,7 @@
         <v>1353</v>
       </c>
       <c r="I451">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q451" t="b">
         <v>1</v>
@@ -21678,7 +21667,7 @@
       <c r="E452" t="s">
         <v>1259</v>
       </c>
-      <c r="F452" s="2">
+      <c r="F452" s="1">
         <v>46230</v>
       </c>
       <c r="G452" t="s">
@@ -21688,7 +21677,7 @@
         <v>1353</v>
       </c>
       <c r="I452">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q452" t="b">
         <v>1</v>
@@ -21710,7 +21699,7 @@
       <c r="E453" t="s">
         <v>1260</v>
       </c>
-      <c r="F453" s="2">
+      <c r="F453" s="1">
         <v>46230</v>
       </c>
       <c r="G453" t="s">
@@ -21720,7 +21709,7 @@
         <v>1353</v>
       </c>
       <c r="I453">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q453" t="b">
         <v>1</v>
@@ -21742,7 +21731,7 @@
       <c r="E454" t="s">
         <v>1261</v>
       </c>
-      <c r="F454" s="2">
+      <c r="F454" s="1">
         <v>46230</v>
       </c>
       <c r="G454" t="s">
@@ -21752,7 +21741,7 @@
         <v>1353</v>
       </c>
       <c r="I454">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q454" t="b">
         <v>1</v>
@@ -21774,7 +21763,7 @@
       <c r="E455" t="s">
         <v>1262</v>
       </c>
-      <c r="F455" s="2">
+      <c r="F455" s="1">
         <v>46230</v>
       </c>
       <c r="G455" t="s">
@@ -21784,7 +21773,7 @@
         <v>1353</v>
       </c>
       <c r="I455">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q455" t="b">
         <v>1</v>
@@ -21806,7 +21795,7 @@
       <c r="E456" t="s">
         <v>1263</v>
       </c>
-      <c r="F456" s="2">
+      <c r="F456" s="1">
         <v>46230</v>
       </c>
       <c r="G456" t="s">
@@ -21816,7 +21805,7 @@
         <v>1353</v>
       </c>
       <c r="I456">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q456" t="b">
         <v>1</v>
@@ -21838,7 +21827,7 @@
       <c r="E457" t="s">
         <v>1264</v>
       </c>
-      <c r="F457" s="2">
+      <c r="F457" s="1">
         <v>46230</v>
       </c>
       <c r="G457" t="s">
@@ -21848,7 +21837,7 @@
         <v>1353</v>
       </c>
       <c r="I457">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q457" t="b">
         <v>1</v>
@@ -21870,7 +21859,7 @@
       <c r="E458" t="s">
         <v>1202</v>
       </c>
-      <c r="F458" s="2">
+      <c r="F458" s="1">
         <v>46231</v>
       </c>
       <c r="G458" t="s">
@@ -21880,7 +21869,7 @@
         <v>1353</v>
       </c>
       <c r="I458">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q458" t="b">
         <v>1</v>
@@ -21902,7 +21891,7 @@
       <c r="E459" t="s">
         <v>1265</v>
       </c>
-      <c r="F459" s="2">
+      <c r="F459" s="1">
         <v>46233</v>
       </c>
       <c r="G459" t="s">
@@ -21912,7 +21901,7 @@
         <v>1353</v>
       </c>
       <c r="I459">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q459" t="b">
         <v>1</v>
@@ -21934,7 +21923,7 @@
       <c r="E460" t="s">
         <v>1266</v>
       </c>
-      <c r="F460" s="2">
+      <c r="F460" s="1">
         <v>46233</v>
       </c>
       <c r="G460" t="s">
@@ -21944,7 +21933,7 @@
         <v>1353</v>
       </c>
       <c r="I460">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q460" t="b">
         <v>1</v>
@@ -21966,7 +21955,7 @@
       <c r="E461" t="s">
         <v>1267</v>
       </c>
-      <c r="F461" s="2">
+      <c r="F461" s="1">
         <v>46233</v>
       </c>
       <c r="G461" t="s">
@@ -21976,7 +21965,7 @@
         <v>1353</v>
       </c>
       <c r="I461">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q461" t="b">
         <v>1</v>
@@ -21998,7 +21987,7 @@
       <c r="E462" t="s">
         <v>1268</v>
       </c>
-      <c r="F462" s="2">
+      <c r="F462" s="1">
         <v>46233</v>
       </c>
       <c r="G462" t="s">
@@ -22008,7 +21997,7 @@
         <v>1353</v>
       </c>
       <c r="I462">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q462" t="b">
         <v>1</v>
@@ -22030,7 +22019,7 @@
       <c r="E463" t="s">
         <v>1269</v>
       </c>
-      <c r="F463" s="2">
+      <c r="F463" s="1">
         <v>46234</v>
       </c>
       <c r="G463" t="s">
@@ -22040,7 +22029,7 @@
         <v>1353</v>
       </c>
       <c r="I463">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q463" t="b">
         <v>1</v>
@@ -22062,7 +22051,7 @@
       <c r="E464" t="s">
         <v>1270</v>
       </c>
-      <c r="F464" s="2">
+      <c r="F464" s="1">
         <v>46230</v>
       </c>
       <c r="G464" t="s">
@@ -22072,7 +22061,7 @@
         <v>1353</v>
       </c>
       <c r="I464">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q464" t="b">
         <v>1</v>
@@ -22094,7 +22083,7 @@
       <c r="E465" t="s">
         <v>1271</v>
       </c>
-      <c r="F465" s="2">
+      <c r="F465" s="1">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
@@ -22104,7 +22093,7 @@
         <v>1353</v>
       </c>
       <c r="I465">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q465" t="b">
         <v>1</v>
@@ -22126,7 +22115,7 @@
       <c r="E466" t="s">
         <v>1272</v>
       </c>
-      <c r="F466" s="2">
+      <c r="F466" s="1">
         <v>46230</v>
       </c>
       <c r="G466" t="s">
@@ -22136,7 +22125,7 @@
         <v>1353</v>
       </c>
       <c r="I466">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q466" t="b">
         <v>1</v>
@@ -22158,7 +22147,7 @@
       <c r="E467" t="s">
         <v>1273</v>
       </c>
-      <c r="F467" s="2">
+      <c r="F467" s="1">
         <v>46230</v>
       </c>
       <c r="G467" t="s">
@@ -22168,7 +22157,7 @@
         <v>1353</v>
       </c>
       <c r="I467">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q467" t="b">
         <v>1</v>
@@ -22190,7 +22179,7 @@
       <c r="E468" t="s">
         <v>1274</v>
       </c>
-      <c r="F468" s="2">
+      <c r="F468" s="1">
         <v>46230</v>
       </c>
       <c r="G468" t="s">
@@ -22200,7 +22189,7 @@
         <v>1353</v>
       </c>
       <c r="I468">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q468" t="b">
         <v>1</v>
@@ -22222,7 +22211,7 @@
       <c r="E469" t="s">
         <v>1275</v>
       </c>
-      <c r="F469" s="2">
+      <c r="F469" s="1">
         <v>46230</v>
       </c>
       <c r="G469" t="s">
@@ -22232,7 +22221,7 @@
         <v>1353</v>
       </c>
       <c r="I469">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q469" t="b">
         <v>1</v>
@@ -22254,7 +22243,7 @@
       <c r="E470" t="s">
         <v>1276</v>
       </c>
-      <c r="F470" s="2">
+      <c r="F470" s="1">
         <v>46230</v>
       </c>
       <c r="G470" t="s">
@@ -22283,7 +22272,7 @@
       <c r="E471" t="s">
         <v>1277</v>
       </c>
-      <c r="F471" s="2">
+      <c r="F471" s="1">
         <v>46230</v>
       </c>
       <c r="G471" t="s">
@@ -22293,7 +22282,7 @@
         <v>1353</v>
       </c>
       <c r="I471">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q471" t="b">
         <v>1</v>
@@ -22315,7 +22304,7 @@
       <c r="E472" t="s">
         <v>1278</v>
       </c>
-      <c r="F472" s="2">
+      <c r="F472" s="1">
         <v>46230</v>
       </c>
       <c r="G472" t="s">
@@ -22325,7 +22314,7 @@
         <v>1353</v>
       </c>
       <c r="I472">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q472" t="b">
         <v>1</v>
@@ -22347,7 +22336,7 @@
       <c r="E473" t="s">
         <v>1279</v>
       </c>
-      <c r="F473" s="2">
+      <c r="F473" s="1">
         <v>46230</v>
       </c>
       <c r="G473" t="s">
@@ -22357,7 +22346,7 @@
         <v>1353</v>
       </c>
       <c r="I473">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q473" t="b">
         <v>1</v>
@@ -22379,7 +22368,7 @@
       <c r="E474" t="s">
         <v>1280</v>
       </c>
-      <c r="F474" s="2">
+      <c r="F474" s="1">
         <v>46231</v>
       </c>
       <c r="G474" t="s">
@@ -22389,7 +22378,7 @@
         <v>1353</v>
       </c>
       <c r="I474">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q474" t="b">
         <v>1</v>
@@ -22411,7 +22400,7 @@
       <c r="E475" t="s">
         <v>1281</v>
       </c>
-      <c r="F475" s="2">
+      <c r="F475" s="1">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
@@ -22421,7 +22410,7 @@
         <v>1353</v>
       </c>
       <c r="I475">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q475" t="b">
         <v>1</v>
@@ -22443,7 +22432,7 @@
       <c r="E476" t="s">
         <v>1282</v>
       </c>
-      <c r="F476" s="2">
+      <c r="F476" s="1">
         <v>46231</v>
       </c>
       <c r="G476" t="s">
@@ -22453,7 +22442,7 @@
         <v>1353</v>
       </c>
       <c r="I476">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q476" t="b">
         <v>1</v>
@@ -22475,7 +22464,7 @@
       <c r="E477" t="s">
         <v>1283</v>
       </c>
-      <c r="F477" s="2">
+      <c r="F477" s="1">
         <v>46231</v>
       </c>
       <c r="G477" t="s">
@@ -22485,7 +22474,7 @@
         <v>1353</v>
       </c>
       <c r="I477">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q477" t="b">
         <v>1</v>
@@ -22507,7 +22496,7 @@
       <c r="E478" t="s">
         <v>1284</v>
       </c>
-      <c r="F478" s="2">
+      <c r="F478" s="1">
         <v>46231</v>
       </c>
       <c r="G478" t="s">
@@ -22517,7 +22506,7 @@
         <v>1353</v>
       </c>
       <c r="I478">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q478" t="b">
         <v>1</v>
@@ -22539,7 +22528,7 @@
       <c r="E479" t="s">
         <v>1285</v>
       </c>
-      <c r="F479" s="2">
+      <c r="F479" s="1">
         <v>46231</v>
       </c>
       <c r="G479" t="s">
@@ -22549,7 +22538,7 @@
         <v>1353</v>
       </c>
       <c r="I479">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q479" t="b">
         <v>1</v>
@@ -22571,7 +22560,7 @@
       <c r="E480" t="s">
         <v>1286</v>
       </c>
-      <c r="F480" s="2">
+      <c r="F480" s="1">
         <v>46231</v>
       </c>
       <c r="G480" t="s">
@@ -22581,7 +22570,7 @@
         <v>1353</v>
       </c>
       <c r="I480">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q480" t="b">
         <v>1</v>
@@ -22603,7 +22592,7 @@
       <c r="E481" t="s">
         <v>1287</v>
       </c>
-      <c r="F481" s="2">
+      <c r="F481" s="1">
         <v>46231</v>
       </c>
       <c r="G481" t="s">
@@ -22613,7 +22602,7 @@
         <v>1353</v>
       </c>
       <c r="I481">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q481" t="b">
         <v>1</v>
@@ -22635,7 +22624,7 @@
       <c r="E482" t="s">
         <v>1288</v>
       </c>
-      <c r="F482" s="2">
+      <c r="F482" s="1">
         <v>46231</v>
       </c>
       <c r="G482" t="s">
@@ -22645,7 +22634,7 @@
         <v>1353</v>
       </c>
       <c r="I482">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q482" t="b">
         <v>1</v>
@@ -22667,7 +22656,7 @@
       <c r="E483" t="s">
         <v>1289</v>
       </c>
-      <c r="F483" s="2">
+      <c r="F483" s="1">
         <v>46231</v>
       </c>
       <c r="G483" t="s">
@@ -22677,7 +22666,7 @@
         <v>1353</v>
       </c>
       <c r="I483">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q483" t="b">
         <v>1</v>
@@ -22699,7 +22688,7 @@
       <c r="E484" t="s">
         <v>1290</v>
       </c>
-      <c r="F484" s="2">
+      <c r="F484" s="1">
         <v>46231</v>
       </c>
       <c r="G484" t="s">
@@ -22709,7 +22698,7 @@
         <v>1353</v>
       </c>
       <c r="I484">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q484" t="b">
         <v>1</v>
@@ -22731,7 +22720,7 @@
       <c r="E485" t="s">
         <v>1291</v>
       </c>
-      <c r="F485" s="2">
+      <c r="F485" s="1">
         <v>46231</v>
       </c>
       <c r="G485" t="s">
@@ -22741,7 +22730,7 @@
         <v>1353</v>
       </c>
       <c r="I485">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q485" t="b">
         <v>1</v>
@@ -22763,7 +22752,7 @@
       <c r="E486" t="s">
         <v>1292</v>
       </c>
-      <c r="F486" s="2">
+      <c r="F486" s="1">
         <v>46231</v>
       </c>
       <c r="G486" t="s">
@@ -22773,7 +22762,7 @@
         <v>1353</v>
       </c>
       <c r="I486">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q486" t="b">
         <v>1</v>
@@ -22795,7 +22784,7 @@
       <c r="E487" t="s">
         <v>1293</v>
       </c>
-      <c r="F487" s="2">
+      <c r="F487" s="1">
         <v>46231</v>
       </c>
       <c r="G487" t="s">
@@ -22805,7 +22794,7 @@
         <v>1353</v>
       </c>
       <c r="I487">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q487" t="b">
         <v>1</v>
@@ -22827,7 +22816,7 @@
       <c r="E488" t="s">
         <v>1294</v>
       </c>
-      <c r="F488" s="2">
+      <c r="F488" s="1">
         <v>46231</v>
       </c>
       <c r="G488" t="s">
@@ -22837,7 +22826,7 @@
         <v>1353</v>
       </c>
       <c r="I488">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q488" t="b">
         <v>1</v>
@@ -22859,7 +22848,7 @@
       <c r="E489" t="s">
         <v>1295</v>
       </c>
-      <c r="F489" s="2">
+      <c r="F489" s="1">
         <v>46231</v>
       </c>
       <c r="G489" t="s">
@@ -22869,7 +22858,7 @@
         <v>1353</v>
       </c>
       <c r="I489">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q489" t="b">
         <v>1</v>
@@ -22891,7 +22880,7 @@
       <c r="E490" t="s">
         <v>1296</v>
       </c>
-      <c r="F490" s="2">
+      <c r="F490" s="1">
         <v>46231</v>
       </c>
       <c r="G490" t="s">
@@ -22901,7 +22890,7 @@
         <v>1353</v>
       </c>
       <c r="I490">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q490" t="b">
         <v>1</v>
@@ -22923,7 +22912,7 @@
       <c r="E491" t="s">
         <v>1297</v>
       </c>
-      <c r="F491" s="2">
+      <c r="F491" s="1">
         <v>46231</v>
       </c>
       <c r="G491" t="s">
@@ -22933,7 +22922,7 @@
         <v>1353</v>
       </c>
       <c r="I491">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q491" t="b">
         <v>1</v>
@@ -22955,7 +22944,7 @@
       <c r="E492" t="s">
         <v>911</v>
       </c>
-      <c r="F492" s="2">
+      <c r="F492" s="1">
         <v>46231</v>
       </c>
       <c r="G492" t="s">
@@ -22965,7 +22954,7 @@
         <v>1355</v>
       </c>
       <c r="I492">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q492" t="b">
         <v>1</v>
@@ -22987,7 +22976,7 @@
       <c r="E493" t="s">
         <v>995</v>
       </c>
-      <c r="F493" s="2">
+      <c r="F493" s="1">
         <v>46231</v>
       </c>
       <c r="G493" t="s">
@@ -22997,7 +22986,7 @@
         <v>1355</v>
       </c>
       <c r="I493">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q493" t="b">
         <v>1</v>
@@ -23019,7 +23008,7 @@
       <c r="E494" t="s">
         <v>867</v>
       </c>
-      <c r="F494" s="2">
+      <c r="F494" s="1">
         <v>46231</v>
       </c>
       <c r="G494" t="s">
@@ -23029,7 +23018,7 @@
         <v>1355</v>
       </c>
       <c r="I494">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q494" t="b">
         <v>1</v>
@@ -23051,7 +23040,7 @@
       <c r="E495" t="s">
         <v>912</v>
       </c>
-      <c r="F495" s="2">
+      <c r="F495" s="1">
         <v>46231</v>
       </c>
       <c r="G495" t="s">
@@ -23061,7 +23050,7 @@
         <v>1355</v>
       </c>
       <c r="I495">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q495" t="b">
         <v>1</v>
@@ -23083,7 +23072,7 @@
       <c r="E496" t="s">
         <v>1048</v>
       </c>
-      <c r="F496" s="2">
+      <c r="F496" s="1">
         <v>46231</v>
       </c>
       <c r="G496" t="s">
@@ -23093,7 +23082,7 @@
         <v>1355</v>
       </c>
       <c r="I496">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q496" t="b">
         <v>1</v>
@@ -23115,7 +23104,7 @@
       <c r="E497" t="s">
         <v>1298</v>
       </c>
-      <c r="F497" s="2">
+      <c r="F497" s="1">
         <v>46231</v>
       </c>
       <c r="G497" t="s">
@@ -23125,7 +23114,7 @@
         <v>1353</v>
       </c>
       <c r="I497">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q497" t="b">
         <v>1</v>
@@ -23147,7 +23136,7 @@
       <c r="E498" t="s">
         <v>1299</v>
       </c>
-      <c r="F498" s="2">
+      <c r="F498" s="1">
         <v>46231</v>
       </c>
       <c r="G498" t="s">
@@ -23157,7 +23146,7 @@
         <v>1353</v>
       </c>
       <c r="I498">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q498" t="b">
         <v>1</v>
@@ -23179,7 +23168,7 @@
       <c r="E499" t="s">
         <v>1300</v>
       </c>
-      <c r="F499" s="2">
+      <c r="F499" s="1">
         <v>46231</v>
       </c>
       <c r="G499" t="s">
@@ -23189,7 +23178,7 @@
         <v>1355</v>
       </c>
       <c r="I499">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q499" t="b">
         <v>1</v>
@@ -23211,7 +23200,7 @@
       <c r="E500" t="s">
         <v>1301</v>
       </c>
-      <c r="F500" s="2">
+      <c r="F500" s="1">
         <v>46231</v>
       </c>
       <c r="G500" t="s">
@@ -23221,7 +23210,7 @@
         <v>1353</v>
       </c>
       <c r="I500">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q500" t="b">
         <v>1</v>
@@ -23243,7 +23232,7 @@
       <c r="E501" t="s">
         <v>1302</v>
       </c>
-      <c r="F501" s="2">
+      <c r="F501" s="1">
         <v>46231</v>
       </c>
       <c r="G501" t="s">
@@ -23253,7 +23242,7 @@
         <v>1353</v>
       </c>
       <c r="I501">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q501" t="b">
         <v>1</v>
@@ -23275,7 +23264,7 @@
       <c r="E502" t="s">
         <v>1303</v>
       </c>
-      <c r="F502" s="2">
+      <c r="F502" s="1">
         <v>46231</v>
       </c>
       <c r="G502" t="s">
@@ -23285,7 +23274,7 @@
         <v>1353</v>
       </c>
       <c r="I502">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q502" t="b">
         <v>1</v>
@@ -23307,7 +23296,7 @@
       <c r="E503" t="s">
         <v>1304</v>
       </c>
-      <c r="F503" s="2">
+      <c r="F503" s="1">
         <v>46231</v>
       </c>
       <c r="G503" t="s">
@@ -23317,7 +23306,7 @@
         <v>1353</v>
       </c>
       <c r="I503">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q503" t="b">
         <v>1</v>
@@ -23339,7 +23328,7 @@
       <c r="E504" t="s">
         <v>1305</v>
       </c>
-      <c r="F504" s="2">
+      <c r="F504" s="1">
         <v>46232</v>
       </c>
       <c r="G504" t="s">
@@ -23349,7 +23338,7 @@
         <v>1353</v>
       </c>
       <c r="I504">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q504" t="b">
         <v>1</v>
@@ -23371,7 +23360,7 @@
       <c r="E505" t="s">
         <v>1306</v>
       </c>
-      <c r="F505" s="2">
+      <c r="F505" s="1">
         <v>46232</v>
       </c>
       <c r="G505" t="s">
@@ -23381,7 +23370,7 @@
         <v>1353</v>
       </c>
       <c r="I505">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q505" t="b">
         <v>1</v>
@@ -23403,7 +23392,7 @@
       <c r="E506" t="s">
         <v>1307</v>
       </c>
-      <c r="F506" s="2">
+      <c r="F506" s="1">
         <v>46232</v>
       </c>
       <c r="G506" t="s">
@@ -23413,7 +23402,7 @@
         <v>1353</v>
       </c>
       <c r="I506">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q506" t="b">
         <v>1</v>
@@ -23435,7 +23424,7 @@
       <c r="E507" t="s">
         <v>1308</v>
       </c>
-      <c r="F507" s="2">
+      <c r="F507" s="1">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
@@ -23445,7 +23434,7 @@
         <v>1353</v>
       </c>
       <c r="I507">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q507" t="b">
         <v>1</v>
@@ -23467,7 +23456,7 @@
       <c r="E508" t="s">
         <v>1309</v>
       </c>
-      <c r="F508" s="2">
+      <c r="F508" s="1">
         <v>46237</v>
       </c>
       <c r="G508" t="s">
@@ -23496,7 +23485,7 @@
       <c r="E509" t="s">
         <v>1310</v>
       </c>
-      <c r="F509" s="2">
+      <c r="F509" s="1">
         <v>46237</v>
       </c>
       <c r="G509" t="s">
@@ -23506,7 +23495,7 @@
         <v>1353</v>
       </c>
       <c r="I509">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q509" t="b">
         <v>1</v>
@@ -23528,7 +23517,7 @@
       <c r="E510" t="s">
         <v>1311</v>
       </c>
-      <c r="F510" s="2">
+      <c r="F510" s="1">
         <v>46237</v>
       </c>
       <c r="G510" t="s">
@@ -23538,7 +23527,7 @@
         <v>1353</v>
       </c>
       <c r="I510">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q510" t="b">
         <v>1</v>
@@ -23560,7 +23549,7 @@
       <c r="E511" t="s">
         <v>1312</v>
       </c>
-      <c r="F511" s="2">
+      <c r="F511" s="1">
         <v>46240</v>
       </c>
       <c r="G511" t="s">
@@ -23570,7 +23559,7 @@
         <v>1353</v>
       </c>
       <c r="I511">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q511" t="b">
         <v>1</v>
@@ -23592,7 +23581,7 @@
       <c r="E512" t="s">
         <v>1313</v>
       </c>
-      <c r="F512" s="2">
+      <c r="F512" s="1">
         <v>46240</v>
       </c>
       <c r="G512" t="s">
@@ -23602,7 +23591,7 @@
         <v>1353</v>
       </c>
       <c r="I512">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q512" t="b">
         <v>1</v>
@@ -23624,7 +23613,7 @@
       <c r="E513" t="s">
         <v>1314</v>
       </c>
-      <c r="F513" s="2">
+      <c r="F513" s="1">
         <v>46244</v>
       </c>
       <c r="G513" t="s">
@@ -23634,7 +23623,7 @@
         <v>1353</v>
       </c>
       <c r="I513">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q513" t="b">
         <v>1</v>
@@ -23656,7 +23645,7 @@
       <c r="E514" t="s">
         <v>1315</v>
       </c>
-      <c r="F514" s="2">
+      <c r="F514" s="1">
         <v>46244</v>
       </c>
       <c r="G514" t="s">
@@ -23666,7 +23655,7 @@
         <v>1353</v>
       </c>
       <c r="I514">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q514" t="b">
         <v>1</v>
@@ -23688,7 +23677,7 @@
       <c r="E515" t="s">
         <v>1043</v>
       </c>
-      <c r="F515" s="2">
+      <c r="F515" s="1">
         <v>46244</v>
       </c>
       <c r="G515" t="s">
@@ -23698,7 +23687,7 @@
         <v>1353</v>
       </c>
       <c r="I515">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q515" t="b">
         <v>1</v>
@@ -23720,7 +23709,7 @@
       <c r="E516" t="s">
         <v>1316</v>
       </c>
-      <c r="F516" s="2">
+      <c r="F516" s="1">
         <v>46252</v>
       </c>
       <c r="G516" t="s">
@@ -23730,7 +23719,7 @@
         <v>1353</v>
       </c>
       <c r="I516">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q516" t="b">
         <v>1</v>
@@ -23752,7 +23741,7 @@
       <c r="E517" t="s">
         <v>1317</v>
       </c>
-      <c r="F517" s="2">
+      <c r="F517" s="1">
         <v>46252</v>
       </c>
       <c r="G517" t="s">
@@ -23762,7 +23751,7 @@
         <v>1353</v>
       </c>
       <c r="I517">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q517" t="b">
         <v>1</v>
@@ -23784,7 +23773,7 @@
       <c r="E518" t="s">
         <v>1318</v>
       </c>
-      <c r="F518" s="2">
+      <c r="F518" s="1">
         <v>46252</v>
       </c>
       <c r="G518" t="s">
@@ -23794,7 +23783,7 @@
         <v>1353</v>
       </c>
       <c r="I518">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q518" t="b">
         <v>1</v>
@@ -23816,7 +23805,7 @@
       <c r="E519" t="s">
         <v>1253</v>
       </c>
-      <c r="F519" s="2">
+      <c r="F519" s="1">
         <v>46254</v>
       </c>
       <c r="G519" t="s">
@@ -23826,7 +23815,7 @@
         <v>1353</v>
       </c>
       <c r="I519">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q519" t="b">
         <v>1</v>
@@ -23848,7 +23837,7 @@
       <c r="E520" t="s">
         <v>1319</v>
       </c>
-      <c r="F520" s="2">
+      <c r="F520" s="1">
         <v>46254</v>
       </c>
       <c r="G520" t="s">
@@ -23858,7 +23847,7 @@
         <v>1353</v>
       </c>
       <c r="I520">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q520" t="b">
         <v>1</v>
@@ -23880,7 +23869,7 @@
       <c r="E521" t="s">
         <v>1320</v>
       </c>
-      <c r="F521" s="2">
+      <c r="F521" s="1">
         <v>46254</v>
       </c>
       <c r="G521" t="s">
@@ -23890,7 +23879,7 @@
         <v>1353</v>
       </c>
       <c r="I521">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q521" t="b">
         <v>1</v>
@@ -23912,7 +23901,7 @@
       <c r="E522" t="s">
         <v>1253</v>
       </c>
-      <c r="F522" s="2">
+      <c r="F522" s="1">
         <v>46254</v>
       </c>
       <c r="G522" t="s">
@@ -23922,7 +23911,7 @@
         <v>1353</v>
       </c>
       <c r="I522">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q522" t="b">
         <v>1</v>
@@ -23944,7 +23933,7 @@
       <c r="E523" t="s">
         <v>1319</v>
       </c>
-      <c r="F523" s="2">
+      <c r="F523" s="1">
         <v>46254</v>
       </c>
       <c r="G523" t="s">
@@ -23954,7 +23943,7 @@
         <v>1353</v>
       </c>
       <c r="I523">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q523" t="b">
         <v>1</v>
@@ -23976,7 +23965,7 @@
       <c r="E524" t="s">
         <v>1321</v>
       </c>
-      <c r="F524" s="2">
+      <c r="F524" s="1">
         <v>46265</v>
       </c>
       <c r="G524" t="s">
@@ -23986,7 +23975,7 @@
         <v>1353</v>
       </c>
       <c r="I524">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q524" t="b">
         <v>1</v>
@@ -24008,7 +23997,7 @@
       <c r="E525" t="s">
         <v>1322</v>
       </c>
-      <c r="F525" s="2">
+      <c r="F525" s="1">
         <v>46265</v>
       </c>
       <c r="G525" t="s">
@@ -24018,7 +24007,7 @@
         <v>1353</v>
       </c>
       <c r="I525">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q525" t="b">
         <v>1</v>
@@ -24040,7 +24029,7 @@
       <c r="E526" t="s">
         <v>1323</v>
       </c>
-      <c r="F526" s="2">
+      <c r="F526" s="1">
         <v>46265</v>
       </c>
       <c r="G526" t="s">
@@ -24050,7 +24039,7 @@
         <v>1353</v>
       </c>
       <c r="I526">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q526" t="b">
         <v>1</v>
@@ -24072,7 +24061,7 @@
       <c r="E527" t="s">
         <v>1324</v>
       </c>
-      <c r="F527" s="2">
+      <c r="F527" s="1">
         <v>46265</v>
       </c>
       <c r="G527" t="s">
@@ -24082,7 +24071,7 @@
         <v>1353</v>
       </c>
       <c r="I527">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q527" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
@@ -4526,8 +4526,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -4543,7 +4551,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4551,12 +4559,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4856,55 +4882,55 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4924,7 +4950,7 @@
       <c r="E2" t="s">
         <v>829</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>45698</v>
       </c>
       <c r="G2" t="s">
@@ -4962,7 +4988,7 @@
       <c r="E3" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>45714</v>
       </c>
       <c r="G3" t="s">
@@ -5000,7 +5026,7 @@
       <c r="E4" t="s">
         <v>831</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>45714</v>
       </c>
       <c r="G4" t="s">
@@ -5038,7 +5064,7 @@
       <c r="E5" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>45714</v>
       </c>
       <c r="G5" t="s">
@@ -5059,7 +5085,7 @@
       <c r="L5" t="s">
         <v>1367</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <v>45993</v>
       </c>
       <c r="Q5" t="b">
@@ -5082,7 +5108,7 @@
       <c r="E6" t="s">
         <v>833</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>45736</v>
       </c>
       <c r="G6" t="s">
@@ -5103,7 +5129,7 @@
       <c r="L6" t="s">
         <v>1368</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="2">
         <v>45889</v>
       </c>
       <c r="Q6" t="b">
@@ -5126,7 +5152,7 @@
       <c r="E7" t="s">
         <v>834</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>45736</v>
       </c>
       <c r="G7" t="s">
@@ -5147,7 +5173,7 @@
       <c r="L7" t="s">
         <v>1369</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="2">
         <v>45848</v>
       </c>
       <c r="O7" t="s">
@@ -5173,7 +5199,7 @@
       <c r="E8" t="s">
         <v>835</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>45736</v>
       </c>
       <c r="G8" t="s">
@@ -5202,7 +5228,7 @@
       <c r="E9" t="s">
         <v>836</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="2">
         <v>45736</v>
       </c>
       <c r="G9" t="s">
@@ -5223,7 +5249,7 @@
       <c r="L9" t="s">
         <v>1370</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="2">
         <v>46098</v>
       </c>
       <c r="O9">
@@ -5249,7 +5275,7 @@
       <c r="E10" t="s">
         <v>837</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="2">
         <v>45736</v>
       </c>
       <c r="G10" t="s">
@@ -5270,7 +5296,7 @@
       <c r="L10" t="s">
         <v>1371</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="2">
         <v>46114</v>
       </c>
       <c r="O10" t="s">
@@ -5296,7 +5322,7 @@
       <c r="E11" t="s">
         <v>838</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <v>45736</v>
       </c>
       <c r="G11" t="s">
@@ -5317,7 +5343,7 @@
       <c r="L11" t="s">
         <v>1369</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="2">
         <v>45848</v>
       </c>
       <c r="O11" t="s">
@@ -5343,7 +5369,7 @@
       <c r="E12" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="2">
         <v>45736</v>
       </c>
       <c r="G12" t="s">
@@ -5364,7 +5390,7 @@
       <c r="L12" t="s">
         <v>1372</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="2">
         <v>45860</v>
       </c>
       <c r="Q12" t="b">
@@ -5387,7 +5413,7 @@
       <c r="E13" t="s">
         <v>840</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <v>45736</v>
       </c>
       <c r="G13" t="s">
@@ -5416,7 +5442,7 @@
       <c r="E14" t="s">
         <v>841</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="2">
         <v>45736</v>
       </c>
       <c r="G14" t="s">
@@ -5437,7 +5463,7 @@
       <c r="L14" t="s">
         <v>1373</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N14" s="2">
         <v>45800</v>
       </c>
       <c r="Q14" t="b">
@@ -5460,7 +5486,7 @@
       <c r="E15" t="s">
         <v>842</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="2">
         <v>45736</v>
       </c>
       <c r="G15" t="s">
@@ -5498,7 +5524,7 @@
       <c r="E16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <v>45736</v>
       </c>
       <c r="G16" t="s">
@@ -5536,7 +5562,7 @@
       <c r="E17" t="s">
         <v>844</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="2">
         <v>45736</v>
       </c>
       <c r="G17" t="s">
@@ -5557,7 +5583,7 @@
       <c r="L17" t="s">
         <v>1368</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17" s="2">
         <v>45897</v>
       </c>
       <c r="Q17" t="b">
@@ -5580,7 +5606,7 @@
       <c r="E18" t="s">
         <v>845</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <v>45736</v>
       </c>
       <c r="G18" t="s">
@@ -5601,7 +5627,7 @@
       <c r="L18" t="s">
         <v>1373</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="2">
         <v>45802</v>
       </c>
       <c r="Q18" t="b">
@@ -5624,7 +5650,7 @@
       <c r="E19" t="s">
         <v>846</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="2">
         <v>45736</v>
       </c>
       <c r="G19" t="s">
@@ -5653,7 +5679,7 @@
       <c r="E20" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="2">
         <v>45736</v>
       </c>
       <c r="G20" t="s">
@@ -5674,7 +5700,7 @@
       <c r="L20" t="s">
         <v>1374</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20" s="2">
         <v>46135</v>
       </c>
       <c r="Q20" t="b">
@@ -5697,7 +5723,7 @@
       <c r="E21" t="s">
         <v>848</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="2">
         <v>45736</v>
       </c>
       <c r="G21" t="s">
@@ -5726,7 +5752,7 @@
       <c r="E22" t="s">
         <v>849</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="2">
         <v>45736</v>
       </c>
       <c r="G22" t="s">
@@ -5764,7 +5790,7 @@
       <c r="E23" t="s">
         <v>850</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <v>45736</v>
       </c>
       <c r="G23" t="s">
@@ -5785,7 +5811,7 @@
       <c r="L23" t="s">
         <v>1375</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23" s="2">
         <v>45965</v>
       </c>
       <c r="P23" t="s">
@@ -5811,7 +5837,7 @@
       <c r="E24" t="s">
         <v>851</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="2">
         <v>45736</v>
       </c>
       <c r="G24" t="s">
@@ -5840,7 +5866,7 @@
       <c r="E25" t="s">
         <v>852</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="2">
         <v>45736</v>
       </c>
       <c r="G25" t="s">
@@ -5869,7 +5895,7 @@
       <c r="E26" t="s">
         <v>853</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="2">
         <v>45736</v>
       </c>
       <c r="G26" t="s">
@@ -5890,7 +5916,7 @@
       <c r="L26" t="s">
         <v>1376</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N26" s="2">
         <v>45891</v>
       </c>
       <c r="P26" t="s">
@@ -5916,7 +5942,7 @@
       <c r="E27" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="2">
         <v>45736</v>
       </c>
       <c r="G27" t="s">
@@ -5954,7 +5980,7 @@
       <c r="E28" t="s">
         <v>855</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="2">
         <v>45736</v>
       </c>
       <c r="G28" t="s">
@@ -5983,7 +6009,7 @@
       <c r="E29" t="s">
         <v>856</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="2">
         <v>45736</v>
       </c>
       <c r="G29" t="s">
@@ -6012,7 +6038,7 @@
       <c r="E30" t="s">
         <v>857</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="2">
         <v>45736</v>
       </c>
       <c r="G30" t="s">
@@ -6033,7 +6059,7 @@
       <c r="L30" t="s">
         <v>1377</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30" s="2">
         <v>45945</v>
       </c>
       <c r="Q30" t="b">
@@ -6056,7 +6082,7 @@
       <c r="E31" t="s">
         <v>858</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="2">
         <v>45736</v>
       </c>
       <c r="G31" t="s">
@@ -6085,7 +6111,7 @@
       <c r="E32" t="s">
         <v>859</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="2">
         <v>45736</v>
       </c>
       <c r="G32" t="s">
@@ -6123,7 +6149,7 @@
       <c r="E33" t="s">
         <v>860</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="2">
         <v>45736</v>
       </c>
       <c r="G33" t="s">
@@ -6152,7 +6178,7 @@
       <c r="E34" t="s">
         <v>861</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="2">
         <v>45736</v>
       </c>
       <c r="G34" t="s">
@@ -6181,7 +6207,7 @@
       <c r="E35" t="s">
         <v>862</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="2">
         <v>45736</v>
       </c>
       <c r="G35" t="s">
@@ -6210,7 +6236,7 @@
       <c r="E36" t="s">
         <v>863</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="2">
         <v>45736</v>
       </c>
       <c r="G36" t="s">
@@ -6239,7 +6265,7 @@
       <c r="E37" t="s">
         <v>864</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="2">
         <v>45736</v>
       </c>
       <c r="G37" t="s">
@@ -6268,7 +6294,7 @@
       <c r="E38" t="s">
         <v>844</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="2">
         <v>45736</v>
       </c>
       <c r="G38" t="s">
@@ -6294,7 +6320,7 @@
       <c r="D39" t="s">
         <v>731</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="2">
         <v>45736</v>
       </c>
       <c r="G39" t="s">
@@ -6329,7 +6355,7 @@
       <c r="D40" t="s">
         <v>731</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="2">
         <v>45736</v>
       </c>
       <c r="G40" t="s">
@@ -6367,7 +6393,7 @@
       <c r="E41" t="s">
         <v>865</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="2">
         <v>45736</v>
       </c>
       <c r="G41" t="s">
@@ -6396,7 +6422,7 @@
       <c r="E42" t="s">
         <v>866</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="2">
         <v>45736</v>
       </c>
       <c r="G42" t="s">
@@ -6425,7 +6451,7 @@
       <c r="E43" t="s">
         <v>867</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="2">
         <v>45736</v>
       </c>
       <c r="G43" t="s">
@@ -6460,7 +6486,7 @@
       <c r="E44" t="s">
         <v>868</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="2">
         <v>45769</v>
       </c>
       <c r="G44" t="s">
@@ -6481,7 +6507,7 @@
       <c r="L44" t="s">
         <v>1378</v>
       </c>
-      <c r="N44" s="1">
+      <c r="N44" s="2">
         <v>45856</v>
       </c>
       <c r="P44" t="s">
@@ -6507,7 +6533,7 @@
       <c r="E45" t="s">
         <v>869</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="2">
         <v>45769</v>
       </c>
       <c r="G45" t="s">
@@ -6528,7 +6554,7 @@
       <c r="L45" t="s">
         <v>1379</v>
       </c>
-      <c r="N45" s="1">
+      <c r="N45" s="2">
         <v>46100</v>
       </c>
       <c r="O45">
@@ -6554,7 +6580,7 @@
       <c r="E46" t="s">
         <v>870</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="2">
         <v>45769</v>
       </c>
       <c r="G46" t="s">
@@ -6592,7 +6618,7 @@
       <c r="E47" t="s">
         <v>871</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="2">
         <v>45769</v>
       </c>
       <c r="G47" t="s">
@@ -6613,7 +6639,7 @@
       <c r="L47" t="s">
         <v>1380</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N47" s="2">
         <v>46113</v>
       </c>
       <c r="P47" t="s">
@@ -6639,7 +6665,7 @@
       <c r="E48" t="s">
         <v>872</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="2">
         <v>45769</v>
       </c>
       <c r="G48" t="s">
@@ -6677,7 +6703,7 @@
       <c r="E49" t="s">
         <v>873</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="2">
         <v>45769</v>
       </c>
       <c r="G49" t="s">
@@ -6706,7 +6732,7 @@
       <c r="E50" t="s">
         <v>874</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="2">
         <v>45769</v>
       </c>
       <c r="G50" t="s">
@@ -6744,7 +6770,7 @@
       <c r="E51" t="s">
         <v>875</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="2">
         <v>45769</v>
       </c>
       <c r="G51" t="s">
@@ -6773,7 +6799,7 @@
       <c r="E52" t="s">
         <v>876</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="2">
         <v>45769</v>
       </c>
       <c r="G52" t="s">
@@ -6811,7 +6837,7 @@
       <c r="E53" t="s">
         <v>877</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="2">
         <v>45769</v>
       </c>
       <c r="G53" t="s">
@@ -6849,7 +6875,7 @@
       <c r="E54" t="s">
         <v>878</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="2">
         <v>45769</v>
       </c>
       <c r="G54" t="s">
@@ -6887,7 +6913,7 @@
       <c r="E55" t="s">
         <v>879</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="2">
         <v>45769</v>
       </c>
       <c r="G55" t="s">
@@ -6916,7 +6942,7 @@
       <c r="E56" t="s">
         <v>880</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="2">
         <v>45769</v>
       </c>
       <c r="G56" t="s">
@@ -6945,7 +6971,7 @@
       <c r="E57" t="s">
         <v>881</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="2">
         <v>45769</v>
       </c>
       <c r="G57" t="s">
@@ -6983,7 +7009,7 @@
       <c r="E58" t="s">
         <v>882</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="2">
         <v>45769</v>
       </c>
       <c r="G58" t="s">
@@ -7012,7 +7038,7 @@
       <c r="E59" t="s">
         <v>883</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="2">
         <v>45769</v>
       </c>
       <c r="G59" t="s">
@@ -7041,7 +7067,7 @@
       <c r="E60" t="s">
         <v>884</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="2">
         <v>45769</v>
       </c>
       <c r="G60" t="s">
@@ -7070,7 +7096,7 @@
       <c r="E61" t="s">
         <v>885</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="2">
         <v>45769</v>
       </c>
       <c r="G61" t="s">
@@ -7099,7 +7125,7 @@
       <c r="E62" t="s">
         <v>886</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="2">
         <v>45770</v>
       </c>
       <c r="G62" t="s">
@@ -7128,7 +7154,7 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="2">
         <v>45799</v>
       </c>
       <c r="G63" t="s">
@@ -7149,7 +7175,7 @@
       <c r="L63" t="s">
         <v>1381</v>
       </c>
-      <c r="N63" s="1">
+      <c r="N63" s="2">
         <v>46092</v>
       </c>
       <c r="P63" t="s">
@@ -7175,7 +7201,7 @@
       <c r="E64" t="s">
         <v>888</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="2">
         <v>45799</v>
       </c>
       <c r="G64" t="s">
@@ -7196,7 +7222,7 @@
       <c r="L64" t="s">
         <v>1382</v>
       </c>
-      <c r="N64" s="1">
+      <c r="N64" s="2">
         <v>46119</v>
       </c>
       <c r="Q64" t="b">
@@ -7219,7 +7245,7 @@
       <c r="E65" t="s">
         <v>889</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="2">
         <v>45799</v>
       </c>
       <c r="G65" t="s">
@@ -7248,7 +7274,7 @@
       <c r="E66" t="s">
         <v>890</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="2">
         <v>45799</v>
       </c>
       <c r="G66" t="s">
@@ -7277,7 +7303,7 @@
       <c r="E67" t="s">
         <v>891</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="2">
         <v>45799</v>
       </c>
       <c r="G67" t="s">
@@ -7306,7 +7332,7 @@
       <c r="E68" t="s">
         <v>892</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="2">
         <v>45799</v>
       </c>
       <c r="G68" t="s">
@@ -7335,7 +7361,7 @@
       <c r="E69" t="s">
         <v>893</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="2">
         <v>45803</v>
       </c>
       <c r="G69" t="s">
@@ -7364,7 +7390,7 @@
       <c r="E70" t="s">
         <v>894</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="2">
         <v>45803</v>
       </c>
       <c r="G70" t="s">
@@ -7385,7 +7411,7 @@
       <c r="L70" t="s">
         <v>1383</v>
       </c>
-      <c r="N70" s="1">
+      <c r="N70" s="2">
         <v>46232</v>
       </c>
       <c r="Q70" t="b">
@@ -7408,7 +7434,7 @@
       <c r="E71" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="2">
         <v>45803</v>
       </c>
       <c r="G71" t="s">
@@ -7429,7 +7455,7 @@
       <c r="L71" t="s">
         <v>1383</v>
       </c>
-      <c r="N71" s="1">
+      <c r="N71" s="2">
         <v>46232</v>
       </c>
       <c r="Q71" t="b">
@@ -7452,7 +7478,7 @@
       <c r="E72" t="s">
         <v>896</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="2">
         <v>45803</v>
       </c>
       <c r="G72" t="s">
@@ -7481,7 +7507,7 @@
       <c r="E73" t="s">
         <v>897</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="2">
         <v>45803</v>
       </c>
       <c r="G73" t="s">
@@ -7519,7 +7545,7 @@
       <c r="E74" t="s">
         <v>896</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="2">
         <v>45803</v>
       </c>
       <c r="G74" t="s">
@@ -7548,7 +7574,7 @@
       <c r="E75" t="s">
         <v>898</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="2">
         <v>45803</v>
       </c>
       <c r="G75" t="s">
@@ -7569,7 +7595,7 @@
       <c r="L75" t="s">
         <v>1383</v>
       </c>
-      <c r="N75" s="1">
+      <c r="N75" s="2">
         <v>46232</v>
       </c>
       <c r="Q75" t="b">
@@ -7592,7 +7618,7 @@
       <c r="E76" t="s">
         <v>899</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="2">
         <v>45803</v>
       </c>
       <c r="G76" t="s">
@@ -7627,7 +7653,7 @@
       <c r="E77" t="s">
         <v>900</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="2">
         <v>45803</v>
       </c>
       <c r="G77" t="s">
@@ -7656,7 +7682,7 @@
       <c r="E78" t="s">
         <v>901</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78" s="2">
         <v>45803</v>
       </c>
       <c r="G78" t="s">
@@ -7685,7 +7711,7 @@
       <c r="E79" t="s">
         <v>902</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="2">
         <v>45803</v>
       </c>
       <c r="G79" t="s">
@@ -7720,7 +7746,7 @@
       <c r="E80" t="s">
         <v>903</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="2">
         <v>45803</v>
       </c>
       <c r="G80" t="s">
@@ -7741,7 +7767,7 @@
       <c r="L80" t="s">
         <v>1383</v>
       </c>
-      <c r="N80" s="1">
+      <c r="N80" s="2">
         <v>46232</v>
       </c>
       <c r="Q80" t="b">
@@ -7764,7 +7790,7 @@
       <c r="E81" t="s">
         <v>904</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="2">
         <v>45813</v>
       </c>
       <c r="G81" t="s">
@@ -7793,7 +7819,7 @@
       <c r="E82" t="s">
         <v>905</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="2">
         <v>45813</v>
       </c>
       <c r="G82" t="s">
@@ -7831,7 +7857,7 @@
       <c r="E83" t="s">
         <v>906</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="2">
         <v>45813</v>
       </c>
       <c r="G83" t="s">
@@ -7860,7 +7886,7 @@
       <c r="E84" t="s">
         <v>907</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="2">
         <v>45813</v>
       </c>
       <c r="G84" t="s">
@@ -7881,7 +7907,7 @@
       <c r="L84" t="s">
         <v>1384</v>
       </c>
-      <c r="N84" s="1">
+      <c r="N84" s="2">
         <v>45853</v>
       </c>
       <c r="O84">
@@ -7907,7 +7933,7 @@
       <c r="E85" t="s">
         <v>908</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85" s="2">
         <v>45813</v>
       </c>
       <c r="G85" t="s">
@@ -7945,7 +7971,7 @@
       <c r="E86" t="s">
         <v>909</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="2">
         <v>45813</v>
       </c>
       <c r="G86" t="s">
@@ -7983,7 +8009,7 @@
       <c r="E87" t="s">
         <v>910</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="2">
         <v>45813</v>
       </c>
       <c r="G87" t="s">
@@ -8004,7 +8030,7 @@
       <c r="L87" t="s">
         <v>1385</v>
       </c>
-      <c r="N87" s="1">
+      <c r="N87" s="2">
         <v>45797</v>
       </c>
       <c r="O87" t="s">
@@ -8030,7 +8056,7 @@
       <c r="E88" t="s">
         <v>911</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="2">
         <v>45813</v>
       </c>
       <c r="G88" t="s">
@@ -8045,7 +8071,7 @@
       <c r="L88" t="s">
         <v>1386</v>
       </c>
-      <c r="N88" s="1">
+      <c r="N88" s="2">
         <v>46195</v>
       </c>
       <c r="Q88" t="b">
@@ -8068,7 +8094,7 @@
       <c r="E89" t="s">
         <v>912</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89" s="2">
         <v>45813</v>
       </c>
       <c r="G89" t="s">
@@ -8083,7 +8109,7 @@
       <c r="L89" t="s">
         <v>1386</v>
       </c>
-      <c r="N89" s="1">
+      <c r="N89" s="2">
         <v>46195</v>
       </c>
       <c r="Q89" t="b">
@@ -8106,7 +8132,7 @@
       <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90" s="2">
         <v>45831</v>
       </c>
       <c r="G90" t="s">
@@ -8147,7 +8173,7 @@
       <c r="E91" t="s">
         <v>914</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="2">
         <v>45831</v>
       </c>
       <c r="G91" t="s">
@@ -8168,7 +8194,7 @@
       <c r="L91" t="s">
         <v>1388</v>
       </c>
-      <c r="N91" s="1">
+      <c r="N91" s="2">
         <v>46139</v>
       </c>
       <c r="Q91" t="b">
@@ -8188,7 +8214,7 @@
       <c r="D92" t="s">
         <v>748</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92" s="2">
         <v>45831</v>
       </c>
       <c r="G92" t="s">
@@ -8217,7 +8243,7 @@
       <c r="E93" t="s">
         <v>915</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93" s="2">
         <v>45831</v>
       </c>
       <c r="G93" t="s">
@@ -8238,7 +8264,7 @@
       <c r="L93" t="s">
         <v>1388</v>
       </c>
-      <c r="N93" s="1">
+      <c r="N93" s="2">
         <v>46139</v>
       </c>
       <c r="Q93" t="b">
@@ -8261,7 +8287,7 @@
       <c r="E94" t="s">
         <v>916</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94" s="2">
         <v>45831</v>
       </c>
       <c r="G94" t="s">
@@ -8299,7 +8325,7 @@
       <c r="E95" t="s">
         <v>917</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95" s="2">
         <v>45831</v>
       </c>
       <c r="G95" t="s">
@@ -8320,7 +8346,7 @@
       <c r="L95" t="s">
         <v>1388</v>
       </c>
-      <c r="N95" s="1">
+      <c r="N95" s="2">
         <v>46139</v>
       </c>
       <c r="Q95" t="b">
@@ -8343,7 +8369,7 @@
       <c r="E96" t="s">
         <v>918</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96" s="2">
         <v>45831</v>
       </c>
       <c r="G96" t="s">
@@ -8364,7 +8390,7 @@
       <c r="L96" t="s">
         <v>1369</v>
       </c>
-      <c r="N96" s="1">
+      <c r="N96" s="2">
         <v>45848</v>
       </c>
       <c r="O96" t="s">
@@ -8390,7 +8416,7 @@
       <c r="E97" t="s">
         <v>919</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="2">
         <v>45840</v>
       </c>
       <c r="G97" t="s">
@@ -8411,7 +8437,7 @@
       <c r="L97" t="s">
         <v>1389</v>
       </c>
-      <c r="N97" s="1">
+      <c r="N97" s="2">
         <v>45860</v>
       </c>
       <c r="P97" t="s">
@@ -8437,7 +8463,7 @@
       <c r="E98" t="s">
         <v>920</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="2">
         <v>45840</v>
       </c>
       <c r="G98" t="s">
@@ -8475,7 +8501,7 @@
       <c r="E99" t="s">
         <v>921</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99" s="2">
         <v>45840</v>
       </c>
       <c r="G99" t="s">
@@ -8504,7 +8530,7 @@
       <c r="E100" t="s">
         <v>922</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100" s="2">
         <v>45840</v>
       </c>
       <c r="G100" t="s">
@@ -8525,7 +8551,7 @@
       <c r="L100" t="s">
         <v>1388</v>
       </c>
-      <c r="N100" s="1">
+      <c r="N100" s="2">
         <v>46188</v>
       </c>
       <c r="Q100" t="b">
@@ -8548,7 +8574,7 @@
       <c r="E101" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101" s="2">
         <v>45840</v>
       </c>
       <c r="G101" t="s">
@@ -8577,7 +8603,7 @@
       <c r="E102" t="s">
         <v>924</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102" s="2">
         <v>45840</v>
       </c>
       <c r="G102" t="s">
@@ -8606,7 +8632,7 @@
       <c r="E103" t="s">
         <v>925</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103" s="2">
         <v>45840</v>
       </c>
       <c r="G103" t="s">
@@ -8635,7 +8661,7 @@
       <c r="E104" t="s">
         <v>926</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104" s="2">
         <v>45840</v>
       </c>
       <c r="G104" t="s">
@@ -8656,7 +8682,7 @@
       <c r="L104" t="s">
         <v>1388</v>
       </c>
-      <c r="N104" s="1">
+      <c r="N104" s="2">
         <v>46188</v>
       </c>
       <c r="Q104" t="b">
@@ -8679,7 +8705,7 @@
       <c r="E105" t="s">
         <v>927</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105" s="2">
         <v>45840</v>
       </c>
       <c r="G105" t="s">
@@ -8700,7 +8726,7 @@
       <c r="L105" t="s">
         <v>1388</v>
       </c>
-      <c r="N105" s="1">
+      <c r="N105" s="2">
         <v>46188</v>
       </c>
       <c r="Q105" t="b">
@@ -8723,7 +8749,7 @@
       <c r="E106" t="s">
         <v>928</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106" s="2">
         <v>45840</v>
       </c>
       <c r="G106" t="s">
@@ -8744,7 +8770,7 @@
       <c r="L106" t="s">
         <v>1390</v>
       </c>
-      <c r="N106" s="1">
+      <c r="N106" s="2">
         <v>45889</v>
       </c>
       <c r="Q106" t="b">
@@ -8767,7 +8793,7 @@
       <c r="E107" t="s">
         <v>929</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="2">
         <v>45840</v>
       </c>
       <c r="G107" t="s">
@@ -8788,7 +8814,7 @@
       <c r="L107" t="s">
         <v>1391</v>
       </c>
-      <c r="N107" s="1">
+      <c r="N107" s="2">
         <v>45876</v>
       </c>
       <c r="Q107" t="b">
@@ -8811,7 +8837,7 @@
       <c r="E108" t="s">
         <v>930</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108" s="2">
         <v>45840</v>
       </c>
       <c r="G108" t="s">
@@ -8849,7 +8875,7 @@
       <c r="E109" t="s">
         <v>931</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109" s="2">
         <v>45840</v>
       </c>
       <c r="G109" t="s">
@@ -8887,7 +8913,7 @@
       <c r="E110" t="s">
         <v>932</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="2">
         <v>45840</v>
       </c>
       <c r="G110" t="s">
@@ -8916,7 +8942,7 @@
       <c r="E111" t="s">
         <v>933</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="2">
         <v>45840</v>
       </c>
       <c r="G111" t="s">
@@ -8945,7 +8971,7 @@
       <c r="E112" t="s">
         <v>934</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112" s="2">
         <v>45840</v>
       </c>
       <c r="G112" t="s">
@@ -8974,7 +9000,7 @@
       <c r="E113" t="s">
         <v>935</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113" s="2">
         <v>45840</v>
       </c>
       <c r="G113" t="s">
@@ -9003,7 +9029,7 @@
       <c r="E114" t="s">
         <v>936</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114" s="2">
         <v>45840</v>
       </c>
       <c r="G114" t="s">
@@ -9032,7 +9058,7 @@
       <c r="E115" t="s">
         <v>937</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115" s="2">
         <v>45840</v>
       </c>
       <c r="G115" t="s">
@@ -9070,7 +9096,7 @@
       <c r="E116" t="s">
         <v>938</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116" s="2">
         <v>45840</v>
       </c>
       <c r="G116" t="s">
@@ -9108,7 +9134,7 @@
       <c r="E117" t="s">
         <v>939</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117" s="2">
         <v>45840</v>
       </c>
       <c r="G117" t="s">
@@ -9146,7 +9172,7 @@
       <c r="E118" t="s">
         <v>940</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118" s="2">
         <v>45840</v>
       </c>
       <c r="G118" t="s">
@@ -9184,7 +9210,7 @@
       <c r="E119" t="s">
         <v>941</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119" s="2">
         <v>45840</v>
       </c>
       <c r="G119" t="s">
@@ -9222,7 +9248,7 @@
       <c r="E120" t="s">
         <v>942</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120" s="2">
         <v>45840</v>
       </c>
       <c r="G120" t="s">
@@ -9260,7 +9286,7 @@
       <c r="E121" t="s">
         <v>943</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="2">
         <v>45849</v>
       </c>
       <c r="G121" t="s">
@@ -9281,7 +9307,7 @@
       <c r="L121" t="s">
         <v>1379</v>
       </c>
-      <c r="N121" s="1">
+      <c r="N121" s="2">
         <v>46100</v>
       </c>
       <c r="O121">
@@ -9307,7 +9333,7 @@
       <c r="E122" t="s">
         <v>944</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F122" s="2">
         <v>45849</v>
       </c>
       <c r="G122" t="s">
@@ -9345,7 +9371,7 @@
       <c r="E123" t="s">
         <v>945</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F123" s="2">
         <v>45849</v>
       </c>
       <c r="G123" t="s">
@@ -9374,7 +9400,7 @@
       <c r="E124" t="s">
         <v>946</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124" s="2">
         <v>45853</v>
       </c>
       <c r="G124" t="s">
@@ -9412,7 +9438,7 @@
       <c r="E125" t="s">
         <v>947</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125" s="2">
         <v>45855</v>
       </c>
       <c r="G125" t="s">
@@ -9450,7 +9476,7 @@
       <c r="E126" t="s">
         <v>948</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126" s="2">
         <v>45855</v>
       </c>
       <c r="G126" t="s">
@@ -9479,7 +9505,7 @@
       <c r="E127" t="s">
         <v>949</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127" s="2">
         <v>45856</v>
       </c>
       <c r="G127" t="s">
@@ -9508,7 +9534,7 @@
       <c r="E128" t="s">
         <v>950</v>
       </c>
-      <c r="F128" s="1">
+      <c r="F128" s="2">
         <v>45869</v>
       </c>
       <c r="G128" t="s">
@@ -9546,7 +9572,7 @@
       <c r="E129" t="s">
         <v>951</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F129" s="2">
         <v>45869</v>
       </c>
       <c r="G129" t="s">
@@ -9584,7 +9610,7 @@
       <c r="E130" t="s">
         <v>952</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F130" s="2">
         <v>45869</v>
       </c>
       <c r="G130" t="s">
@@ -9605,7 +9631,7 @@
       <c r="L130" t="s">
         <v>1392</v>
       </c>
-      <c r="N130" s="1">
+      <c r="N130" s="2">
         <v>45916</v>
       </c>
       <c r="O130">
@@ -9631,7 +9657,7 @@
       <c r="E131" t="s">
         <v>953</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F131" s="2">
         <v>45869</v>
       </c>
       <c r="G131" t="s">
@@ -9660,7 +9686,7 @@
       <c r="E132" t="s">
         <v>954</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F132" s="2">
         <v>45869</v>
       </c>
       <c r="G132" t="s">
@@ -9681,7 +9707,7 @@
       <c r="L132" t="s">
         <v>1393</v>
       </c>
-      <c r="N132" s="1">
+      <c r="N132" s="2">
         <v>46014</v>
       </c>
       <c r="O132">
@@ -9707,7 +9733,7 @@
       <c r="E133" t="s">
         <v>955</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F133" s="2">
         <v>45869</v>
       </c>
       <c r="G133" t="s">
@@ -9736,7 +9762,7 @@
       <c r="E134" t="s">
         <v>956</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F134" s="2">
         <v>45882</v>
       </c>
       <c r="G134" t="s">
@@ -9774,7 +9800,7 @@
       <c r="E135" t="s">
         <v>957</v>
       </c>
-      <c r="F135" s="1">
+      <c r="F135" s="2">
         <v>45882</v>
       </c>
       <c r="G135" t="s">
@@ -9803,7 +9829,7 @@
       <c r="E136" t="s">
         <v>958</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F136" s="2">
         <v>45891</v>
       </c>
       <c r="G136" t="s">
@@ -9832,7 +9858,7 @@
       <c r="E137" t="s">
         <v>959</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F137" s="2">
         <v>45891</v>
       </c>
       <c r="G137" t="s">
@@ -9861,7 +9887,7 @@
       <c r="E138" t="s">
         <v>960</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F138" s="2">
         <v>45891</v>
       </c>
       <c r="G138" t="s">
@@ -9899,7 +9925,7 @@
       <c r="E139" t="s">
         <v>961</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F139" s="2">
         <v>45891</v>
       </c>
       <c r="G139" t="s">
@@ -9928,7 +9954,7 @@
       <c r="E140" t="s">
         <v>962</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F140" s="2">
         <v>45891</v>
       </c>
       <c r="G140" t="s">
@@ -9957,7 +9983,7 @@
       <c r="E141" t="s">
         <v>963</v>
       </c>
-      <c r="F141" s="1">
+      <c r="F141" s="2">
         <v>45891</v>
       </c>
       <c r="G141" t="s">
@@ -9986,7 +10012,7 @@
       <c r="E142" t="s">
         <v>964</v>
       </c>
-      <c r="F142" s="1">
+      <c r="F142" s="2">
         <v>45891</v>
       </c>
       <c r="G142" t="s">
@@ -10015,7 +10041,7 @@
       <c r="E143" t="s">
         <v>965</v>
       </c>
-      <c r="F143" s="1">
+      <c r="F143" s="2">
         <v>45891</v>
       </c>
       <c r="G143" t="s">
@@ -10044,7 +10070,7 @@
       <c r="E144" t="s">
         <v>966</v>
       </c>
-      <c r="F144" s="1">
+      <c r="F144" s="2">
         <v>45891</v>
       </c>
       <c r="G144" t="s">
@@ -10073,7 +10099,7 @@
       <c r="E145" t="s">
         <v>967</v>
       </c>
-      <c r="F145" s="1">
+      <c r="F145" s="2">
         <v>45891</v>
       </c>
       <c r="G145" t="s">
@@ -10102,7 +10128,7 @@
       <c r="E146" t="s">
         <v>968</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F146" s="2">
         <v>45891</v>
       </c>
       <c r="G146" t="s">
@@ -10131,7 +10157,7 @@
       <c r="E147" t="s">
         <v>969</v>
       </c>
-      <c r="F147" s="1">
+      <c r="F147" s="2">
         <v>45891</v>
       </c>
       <c r="G147" t="s">
@@ -10160,7 +10186,7 @@
       <c r="E148" t="s">
         <v>970</v>
       </c>
-      <c r="F148" s="1">
+      <c r="F148" s="2">
         <v>45891</v>
       </c>
       <c r="G148" t="s">
@@ -10181,7 +10207,7 @@
       <c r="L148" t="s">
         <v>1383</v>
       </c>
-      <c r="N148" s="1">
+      <c r="N148" s="2">
         <v>46232</v>
       </c>
       <c r="Q148" t="b">
@@ -10204,7 +10230,7 @@
       <c r="E149" t="s">
         <v>971</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F149" s="2">
         <v>45891</v>
       </c>
       <c r="G149" t="s">
@@ -10225,7 +10251,7 @@
       <c r="L149" t="s">
         <v>1394</v>
       </c>
-      <c r="N149" s="1">
+      <c r="N149" s="2">
         <v>46265</v>
       </c>
       <c r="P149" t="s">
@@ -10251,7 +10277,7 @@
       <c r="E150" t="s">
         <v>972</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F150" s="2">
         <v>45891</v>
       </c>
       <c r="G150" t="s">
@@ -10272,7 +10298,7 @@
       <c r="L150" t="s">
         <v>1381</v>
       </c>
-      <c r="N150" s="1">
+      <c r="N150" s="2">
         <v>46092</v>
       </c>
       <c r="P150" t="s">
@@ -10298,7 +10324,7 @@
       <c r="E151" t="s">
         <v>973</v>
       </c>
-      <c r="F151" s="1">
+      <c r="F151" s="2">
         <v>45891</v>
       </c>
       <c r="G151" t="s">
@@ -10327,7 +10353,7 @@
       <c r="E152" t="s">
         <v>963</v>
       </c>
-      <c r="F152" s="1">
+      <c r="F152" s="2">
         <v>45891</v>
       </c>
       <c r="G152" t="s">
@@ -10348,7 +10374,7 @@
       <c r="L152" t="s">
         <v>1382</v>
       </c>
-      <c r="N152" s="1">
+      <c r="N152" s="2">
         <v>46119</v>
       </c>
       <c r="Q152" t="b">
@@ -10371,7 +10397,7 @@
       <c r="E153" t="s">
         <v>974</v>
       </c>
-      <c r="F153" s="1">
+      <c r="F153" s="2">
         <v>45891</v>
       </c>
       <c r="G153" t="s">
@@ -10389,7 +10415,7 @@
       <c r="L153" t="s">
         <v>1383</v>
       </c>
-      <c r="N153" s="1">
+      <c r="N153" s="2">
         <v>46232</v>
       </c>
       <c r="Q153" t="b">
@@ -10412,7 +10438,7 @@
       <c r="E154" t="s">
         <v>975</v>
       </c>
-      <c r="F154" s="1">
+      <c r="F154" s="2">
         <v>45891</v>
       </c>
       <c r="G154" t="s">
@@ -10441,7 +10467,7 @@
       <c r="E155" t="s">
         <v>976</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F155" s="2">
         <v>45891</v>
       </c>
       <c r="G155" t="s">
@@ -10476,7 +10502,7 @@
       <c r="E156" t="s">
         <v>977</v>
       </c>
-      <c r="F156" s="1">
+      <c r="F156" s="2">
         <v>45891</v>
       </c>
       <c r="G156" t="s">
@@ -10514,7 +10540,7 @@
       <c r="E157" t="s">
         <v>978</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="2">
         <v>45891</v>
       </c>
       <c r="G157" t="s">
@@ -10535,7 +10561,7 @@
       <c r="L157" t="s">
         <v>1395</v>
       </c>
-      <c r="N157" s="1">
+      <c r="N157" s="2">
         <v>46262</v>
       </c>
       <c r="Q157" t="b">
@@ -10558,7 +10584,7 @@
       <c r="E158" t="s">
         <v>979</v>
       </c>
-      <c r="F158" s="1">
+      <c r="F158" s="2">
         <v>45894</v>
       </c>
       <c r="G158" t="s">
@@ -10579,7 +10605,7 @@
       <c r="L158" t="s">
         <v>1396</v>
       </c>
-      <c r="N158" s="1">
+      <c r="N158" s="2">
         <v>45946</v>
       </c>
       <c r="Q158" t="b">
@@ -10602,7 +10628,7 @@
       <c r="E159" t="s">
         <v>980</v>
       </c>
-      <c r="F159" s="1">
+      <c r="F159" s="2">
         <v>45894</v>
       </c>
       <c r="G159" t="s">
@@ -10640,7 +10666,7 @@
       <c r="E160" t="s">
         <v>981</v>
       </c>
-      <c r="F160" s="1">
+      <c r="F160" s="2">
         <v>45898</v>
       </c>
       <c r="G160" t="s">
@@ -10678,7 +10704,7 @@
       <c r="E161" t="s">
         <v>982</v>
       </c>
-      <c r="F161" s="1">
+      <c r="F161" s="2">
         <v>45898</v>
       </c>
       <c r="G161" t="s">
@@ -10699,7 +10725,7 @@
       <c r="L161" t="s">
         <v>1397</v>
       </c>
-      <c r="N161" s="1">
+      <c r="N161" s="2">
         <v>45953</v>
       </c>
       <c r="O161" t="s">
@@ -10725,7 +10751,7 @@
       <c r="E162" t="s">
         <v>983</v>
       </c>
-      <c r="F162" s="1">
+      <c r="F162" s="2">
         <v>45898</v>
       </c>
       <c r="G162" t="s">
@@ -10746,7 +10772,7 @@
       <c r="L162" t="s">
         <v>1398</v>
       </c>
-      <c r="N162" s="1">
+      <c r="N162" s="2">
         <v>45940</v>
       </c>
       <c r="P162" t="s">
@@ -10772,7 +10798,7 @@
       <c r="E163" t="s">
         <v>984</v>
       </c>
-      <c r="F163" s="1">
+      <c r="F163" s="2">
         <v>45898</v>
       </c>
       <c r="G163" t="s">
@@ -10793,7 +10819,7 @@
       <c r="L163" t="s">
         <v>1398</v>
       </c>
-      <c r="N163" s="1">
+      <c r="N163" s="2">
         <v>45940</v>
       </c>
       <c r="P163" t="s">
@@ -10819,7 +10845,7 @@
       <c r="E164" t="s">
         <v>985</v>
       </c>
-      <c r="F164" s="1">
+      <c r="F164" s="2">
         <v>45910</v>
       </c>
       <c r="G164" t="s">
@@ -10854,7 +10880,7 @@
       <c r="E165" t="s">
         <v>986</v>
       </c>
-      <c r="F165" s="1">
+      <c r="F165" s="2">
         <v>45917</v>
       </c>
       <c r="G165" t="s">
@@ -10872,7 +10898,7 @@
       <c r="L165" t="s">
         <v>1399</v>
       </c>
-      <c r="N165" s="1">
+      <c r="N165" s="2">
         <v>46204</v>
       </c>
       <c r="P165" t="s">
@@ -10898,7 +10924,7 @@
       <c r="E166" t="s">
         <v>987</v>
       </c>
-      <c r="F166" s="1">
+      <c r="F166" s="2">
         <v>45917</v>
       </c>
       <c r="G166" t="s">
@@ -10927,7 +10953,7 @@
       <c r="E167" t="s">
         <v>988</v>
       </c>
-      <c r="F167" s="1">
+      <c r="F167" s="2">
         <v>45917</v>
       </c>
       <c r="G167" t="s">
@@ -10956,7 +10982,7 @@
       <c r="E168" t="s">
         <v>989</v>
       </c>
-      <c r="F168" s="1">
+      <c r="F168" s="2">
         <v>45917</v>
       </c>
       <c r="G168" t="s">
@@ -10997,7 +11023,7 @@
       <c r="E169" t="s">
         <v>990</v>
       </c>
-      <c r="F169" s="1">
+      <c r="F169" s="2">
         <v>45917</v>
       </c>
       <c r="G169" t="s">
@@ -11015,7 +11041,7 @@
       <c r="L169" t="s">
         <v>1401</v>
       </c>
-      <c r="N169" s="1">
+      <c r="N169" s="2">
         <v>45973</v>
       </c>
       <c r="Q169" t="b">
@@ -11038,7 +11064,7 @@
       <c r="E170" t="s">
         <v>991</v>
       </c>
-      <c r="F170" s="1">
+      <c r="F170" s="2">
         <v>45917</v>
       </c>
       <c r="G170" t="s">
@@ -11073,7 +11099,7 @@
       <c r="E171" t="s">
         <v>992</v>
       </c>
-      <c r="F171" s="1">
+      <c r="F171" s="2">
         <v>45917</v>
       </c>
       <c r="G171" t="s">
@@ -11111,7 +11137,7 @@
       <c r="E172" t="s">
         <v>993</v>
       </c>
-      <c r="F172" s="1">
+      <c r="F172" s="2">
         <v>45917</v>
       </c>
       <c r="G172" t="s">
@@ -11140,7 +11166,7 @@
       <c r="E173" t="s">
         <v>994</v>
       </c>
-      <c r="F173" s="1">
+      <c r="F173" s="2">
         <v>45917</v>
       </c>
       <c r="G173" t="s">
@@ -11169,7 +11195,7 @@
       <c r="E174" t="s">
         <v>995</v>
       </c>
-      <c r="F174" s="1">
+      <c r="F174" s="2">
         <v>45917</v>
       </c>
       <c r="G174" t="s">
@@ -11184,7 +11210,7 @@
       <c r="L174" t="s">
         <v>1386</v>
       </c>
-      <c r="N174" s="1">
+      <c r="N174" s="2">
         <v>46195</v>
       </c>
       <c r="Q174" t="b">
@@ -11207,7 +11233,7 @@
       <c r="E175" t="s">
         <v>996</v>
       </c>
-      <c r="F175" s="1">
+      <c r="F175" s="2">
         <v>45917</v>
       </c>
       <c r="G175" t="s">
@@ -11228,7 +11254,7 @@
       <c r="L175" t="s">
         <v>1402</v>
       </c>
-      <c r="N175" s="1">
+      <c r="N175" s="2">
         <v>46122</v>
       </c>
       <c r="P175" t="s">
@@ -11254,7 +11280,7 @@
       <c r="E176" t="s">
         <v>900</v>
       </c>
-      <c r="F176" s="1">
+      <c r="F176" s="2">
         <v>45917</v>
       </c>
       <c r="G176" t="s">
@@ -11292,7 +11318,7 @@
       <c r="E177" t="s">
         <v>997</v>
       </c>
-      <c r="F177" s="1">
+      <c r="F177" s="2">
         <v>45917</v>
       </c>
       <c r="G177" t="s">
@@ -11313,7 +11339,7 @@
       <c r="L177" t="s">
         <v>1403</v>
       </c>
-      <c r="N177" s="1">
+      <c r="N177" s="2">
         <v>45961</v>
       </c>
       <c r="P177" t="s">
@@ -11339,7 +11365,7 @@
       <c r="E178" t="s">
         <v>998</v>
       </c>
-      <c r="F178" s="1">
+      <c r="F178" s="2">
         <v>45937</v>
       </c>
       <c r="G178" t="s">
@@ -11377,7 +11403,7 @@
       <c r="E179" t="s">
         <v>999</v>
       </c>
-      <c r="F179" s="1">
+      <c r="F179" s="2">
         <v>45937</v>
       </c>
       <c r="G179" t="s">
@@ -11406,7 +11432,7 @@
       <c r="E180" t="s">
         <v>1000</v>
       </c>
-      <c r="F180" s="1">
+      <c r="F180" s="2">
         <v>45937</v>
       </c>
       <c r="G180" t="s">
@@ -11444,7 +11470,7 @@
       <c r="E181" t="s">
         <v>1001</v>
       </c>
-      <c r="F181" s="1">
+      <c r="F181" s="2">
         <v>45937</v>
       </c>
       <c r="G181" t="s">
@@ -11473,7 +11499,7 @@
       <c r="E182" t="s">
         <v>1002</v>
       </c>
-      <c r="F182" s="1">
+      <c r="F182" s="2">
         <v>45937</v>
       </c>
       <c r="G182" t="s">
@@ -11502,7 +11528,7 @@
       <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="F183" s="1">
+      <c r="F183" s="2">
         <v>45937</v>
       </c>
       <c r="G183" t="s">
@@ -11540,7 +11566,7 @@
       <c r="D184" t="s">
         <v>774</v>
       </c>
-      <c r="F184" s="1">
+      <c r="F184" s="2">
         <v>45939</v>
       </c>
       <c r="G184" t="s">
@@ -11575,7 +11601,7 @@
       <c r="E185" t="s">
         <v>1004</v>
       </c>
-      <c r="F185" s="1">
+      <c r="F185" s="2">
         <v>45939</v>
       </c>
       <c r="G185" t="s">
@@ -11613,7 +11639,7 @@
       <c r="E186" t="s">
         <v>1005</v>
       </c>
-      <c r="F186" s="1">
+      <c r="F186" s="2">
         <v>45939</v>
       </c>
       <c r="G186" t="s">
@@ -11651,7 +11677,7 @@
       <c r="E187" t="s">
         <v>1006</v>
       </c>
-      <c r="F187" s="1">
+      <c r="F187" s="2">
         <v>45939</v>
       </c>
       <c r="G187" t="s">
@@ -11672,7 +11698,7 @@
       <c r="L187" t="s">
         <v>1404</v>
       </c>
-      <c r="N187" s="1">
+      <c r="N187" s="2">
         <v>46014</v>
       </c>
       <c r="O187">
@@ -11698,7 +11724,7 @@
       <c r="E188" t="s">
         <v>1007</v>
       </c>
-      <c r="F188" s="1">
+      <c r="F188" s="2">
         <v>45946</v>
       </c>
       <c r="G188" t="s">
@@ -11719,7 +11745,7 @@
       <c r="L188" t="s">
         <v>1405</v>
       </c>
-      <c r="N188" s="1">
+      <c r="N188" s="2">
         <v>45986</v>
       </c>
       <c r="P188" t="s">
@@ -11745,7 +11771,7 @@
       <c r="E189" t="s">
         <v>1008</v>
       </c>
-      <c r="F189" s="1">
+      <c r="F189" s="2">
         <v>45965</v>
       </c>
       <c r="G189" t="s">
@@ -11766,7 +11792,7 @@
       <c r="L189" t="s">
         <v>1406</v>
       </c>
-      <c r="N189" s="1">
+      <c r="N189" s="2">
         <v>46120</v>
       </c>
       <c r="Q189" t="b">
@@ -11789,7 +11815,7 @@
       <c r="E190" t="s">
         <v>1009</v>
       </c>
-      <c r="F190" s="1">
+      <c r="F190" s="2">
         <v>45965</v>
       </c>
       <c r="G190" t="s">
@@ -11810,7 +11836,7 @@
       <c r="L190" t="s">
         <v>1407</v>
       </c>
-      <c r="N190" s="1">
+      <c r="N190" s="2">
         <v>46072</v>
       </c>
       <c r="Q190" t="b">
@@ -11833,7 +11859,7 @@
       <c r="E191" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="1">
+      <c r="F191" s="2">
         <v>45967</v>
       </c>
       <c r="G191" t="s">
@@ -11854,7 +11880,7 @@
       <c r="L191" t="s">
         <v>1408</v>
       </c>
-      <c r="N191" s="1">
+      <c r="N191" s="2">
         <v>45972</v>
       </c>
       <c r="Q191" t="b">
@@ -11877,7 +11903,7 @@
       <c r="E192" t="s">
         <v>1011</v>
       </c>
-      <c r="F192" s="1">
+      <c r="F192" s="2">
         <v>45968</v>
       </c>
       <c r="G192" t="s">
@@ -11915,7 +11941,7 @@
       <c r="E193" t="s">
         <v>1012</v>
       </c>
-      <c r="F193" s="1">
+      <c r="F193" s="2">
         <v>45968</v>
       </c>
       <c r="G193" t="s">
@@ -11953,7 +11979,7 @@
       <c r="E194" t="s">
         <v>1013</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F194" s="2">
         <v>45968</v>
       </c>
       <c r="G194" t="s">
@@ -11982,7 +12008,7 @@
       <c r="E195" t="s">
         <v>1014</v>
       </c>
-      <c r="F195" s="1">
+      <c r="F195" s="2">
         <v>45971</v>
       </c>
       <c r="G195" t="s">
@@ -12003,7 +12029,7 @@
       <c r="L195" t="s">
         <v>1409</v>
       </c>
-      <c r="N195" s="1">
+      <c r="N195" s="2">
         <v>46157</v>
       </c>
       <c r="Q195" t="b">
@@ -12026,7 +12052,7 @@
       <c r="E196" t="s">
         <v>1015</v>
       </c>
-      <c r="F196" s="1">
+      <c r="F196" s="2">
         <v>45978</v>
       </c>
       <c r="G196" t="s">
@@ -12055,7 +12081,7 @@
       <c r="E197" t="s">
         <v>1016</v>
       </c>
-      <c r="F197" s="1">
+      <c r="F197" s="2">
         <v>45978</v>
       </c>
       <c r="G197" t="s">
@@ -12084,7 +12110,7 @@
       <c r="E198" t="s">
         <v>1017</v>
       </c>
-      <c r="F198" s="1">
+      <c r="F198" s="2">
         <v>45978</v>
       </c>
       <c r="G198" t="s">
@@ -12113,7 +12139,7 @@
       <c r="E199" t="s">
         <v>1018</v>
       </c>
-      <c r="F199" s="1">
+      <c r="F199" s="2">
         <v>45979</v>
       </c>
       <c r="G199" t="s">
@@ -12134,7 +12160,7 @@
       <c r="L199" t="s">
         <v>1410</v>
       </c>
-      <c r="N199" s="1">
+      <c r="N199" s="2">
         <v>46049</v>
       </c>
       <c r="Q199" t="b">
@@ -12157,7 +12183,7 @@
       <c r="E200" t="s">
         <v>1019</v>
       </c>
-      <c r="F200" s="1">
+      <c r="F200" s="2">
         <v>45986</v>
       </c>
       <c r="G200" t="s">
@@ -12178,7 +12204,7 @@
       <c r="L200" t="s">
         <v>1409</v>
       </c>
-      <c r="N200" s="1">
+      <c r="N200" s="2">
         <v>46156</v>
       </c>
       <c r="Q200" t="b">
@@ -12201,7 +12227,7 @@
       <c r="E201" t="s">
         <v>1020</v>
       </c>
-      <c r="F201" s="1">
+      <c r="F201" s="2">
         <v>45986</v>
       </c>
       <c r="G201" t="s">
@@ -12239,7 +12265,7 @@
       <c r="E202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" s="1">
+      <c r="F202" s="2">
         <v>45986</v>
       </c>
       <c r="G202" t="s">
@@ -12277,7 +12303,7 @@
       <c r="E203" t="s">
         <v>1022</v>
       </c>
-      <c r="F203" s="1">
+      <c r="F203" s="2">
         <v>45986</v>
       </c>
       <c r="G203" t="s">
@@ -12295,7 +12321,7 @@
       <c r="L203" t="s">
         <v>1411</v>
       </c>
-      <c r="N203" s="1">
+      <c r="N203" s="2">
         <v>46232</v>
       </c>
       <c r="Q203" t="b">
@@ -12318,7 +12344,7 @@
       <c r="E204" t="s">
         <v>1023</v>
       </c>
-      <c r="F204" s="1">
+      <c r="F204" s="2">
         <v>45986</v>
       </c>
       <c r="G204" t="s">
@@ -12356,7 +12382,7 @@
       <c r="E205" t="s">
         <v>1024</v>
       </c>
-      <c r="F205" s="1">
+      <c r="F205" s="2">
         <v>45986</v>
       </c>
       <c r="G205" t="s">
@@ -12394,7 +12420,7 @@
       <c r="E206" t="s">
         <v>1025</v>
       </c>
-      <c r="F206" s="1">
+      <c r="F206" s="2">
         <v>45986</v>
       </c>
       <c r="G206" t="s">
@@ -12423,7 +12449,7 @@
       <c r="E207" t="s">
         <v>1026</v>
       </c>
-      <c r="F207" s="1">
+      <c r="F207" s="2">
         <v>45986</v>
       </c>
       <c r="G207" t="s">
@@ -12444,7 +12470,7 @@
       <c r="L207" t="s">
         <v>1412</v>
       </c>
-      <c r="N207" s="1">
+      <c r="N207" s="2">
         <v>46153</v>
       </c>
       <c r="Q207" t="b">
@@ -12467,7 +12493,7 @@
       <c r="E208" t="s">
         <v>1027</v>
       </c>
-      <c r="F208" s="1">
+      <c r="F208" s="2">
         <v>45986</v>
       </c>
       <c r="G208" t="s">
@@ -12488,7 +12514,7 @@
       <c r="L208" t="s">
         <v>1413</v>
       </c>
-      <c r="N208" s="1">
+      <c r="N208" s="2">
         <v>46031</v>
       </c>
       <c r="Q208" t="b">
@@ -12511,7 +12537,7 @@
       <c r="E209" t="s">
         <v>1028</v>
       </c>
-      <c r="F209" s="1">
+      <c r="F209" s="2">
         <v>46000</v>
       </c>
       <c r="G209" t="s">
@@ -12532,7 +12558,7 @@
       <c r="L209" t="s">
         <v>1414</v>
       </c>
-      <c r="N209" s="1">
+      <c r="N209" s="2">
         <v>46191</v>
       </c>
       <c r="Q209" t="b">
@@ -12555,7 +12581,7 @@
       <c r="E210" t="s">
         <v>1029</v>
       </c>
-      <c r="F210" s="1">
+      <c r="F210" s="2">
         <v>46000</v>
       </c>
       <c r="G210" t="s">
@@ -12593,7 +12619,7 @@
       <c r="E211" t="s">
         <v>1030</v>
       </c>
-      <c r="F211" s="1">
+      <c r="F211" s="2">
         <v>46000</v>
       </c>
       <c r="G211" t="s">
@@ -12622,7 +12648,7 @@
       <c r="E212" t="s">
         <v>1031</v>
       </c>
-      <c r="F212" s="1">
+      <c r="F212" s="2">
         <v>46000</v>
       </c>
       <c r="G212" t="s">
@@ -12651,7 +12677,7 @@
       <c r="E213" t="s">
         <v>1032</v>
       </c>
-      <c r="F213" s="1">
+      <c r="F213" s="2">
         <v>46007</v>
       </c>
       <c r="G213" t="s">
@@ -12689,7 +12715,7 @@
       <c r="E214" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="1">
+      <c r="F214" s="2">
         <v>46007</v>
       </c>
       <c r="G214" t="s">
@@ -12710,7 +12736,7 @@
       <c r="L214" t="s">
         <v>1415</v>
       </c>
-      <c r="N214" s="1">
+      <c r="N214" s="2">
         <v>46021</v>
       </c>
       <c r="O214">
@@ -12736,7 +12762,7 @@
       <c r="E215" t="s">
         <v>1034</v>
       </c>
-      <c r="F215" s="1">
+      <c r="F215" s="2">
         <v>46007</v>
       </c>
       <c r="G215" t="s">
@@ -12774,7 +12800,7 @@
       <c r="E216" t="s">
         <v>1035</v>
       </c>
-      <c r="F216" s="1">
+      <c r="F216" s="2">
         <v>46010</v>
       </c>
       <c r="G216" t="s">
@@ -12803,7 +12829,7 @@
       <c r="E217" t="s">
         <v>1036</v>
       </c>
-      <c r="F217" s="1">
+      <c r="F217" s="2">
         <v>46010</v>
       </c>
       <c r="G217" t="s">
@@ -12824,7 +12850,7 @@
       <c r="L217" t="s">
         <v>1416</v>
       </c>
-      <c r="N217" s="1">
+      <c r="N217" s="2">
         <v>46052</v>
       </c>
       <c r="Q217" t="b">
@@ -12847,7 +12873,7 @@
       <c r="E218" t="s">
         <v>1037</v>
       </c>
-      <c r="F218" s="1">
+      <c r="F218" s="2">
         <v>46010</v>
       </c>
       <c r="G218" t="s">
@@ -12865,7 +12891,7 @@
       <c r="K218" t="s">
         <v>1359</v>
       </c>
-      <c r="N218" s="1">
+      <c r="N218" s="2">
         <v>46176</v>
       </c>
       <c r="P218" t="s">
@@ -12891,7 +12917,7 @@
       <c r="E219" t="s">
         <v>1038</v>
       </c>
-      <c r="F219" s="1">
+      <c r="F219" s="2">
         <v>46010</v>
       </c>
       <c r="G219" t="s">
@@ -12909,7 +12935,7 @@
       <c r="L219" t="s">
         <v>1417</v>
       </c>
-      <c r="N219" s="1">
+      <c r="N219" s="2">
         <v>46176</v>
       </c>
       <c r="P219" t="s">
@@ -12935,7 +12961,7 @@
       <c r="E220" t="s">
         <v>1039</v>
       </c>
-      <c r="F220" s="1">
+      <c r="F220" s="2">
         <v>46010</v>
       </c>
       <c r="G220" t="s">
@@ -12956,7 +12982,7 @@
       <c r="L220" t="s">
         <v>1418</v>
       </c>
-      <c r="N220" s="1">
+      <c r="N220" s="2">
         <v>46164</v>
       </c>
       <c r="Q220" t="b">
@@ -12979,7 +13005,7 @@
       <c r="E221" t="s">
         <v>1040</v>
       </c>
-      <c r="F221" s="1">
+      <c r="F221" s="2">
         <v>46028</v>
       </c>
       <c r="G221" t="s">
@@ -12994,7 +13020,7 @@
       <c r="L221" t="s">
         <v>1419</v>
       </c>
-      <c r="N221" s="1">
+      <c r="N221" s="2">
         <v>46184</v>
       </c>
       <c r="Q221" t="b">
@@ -13017,7 +13043,7 @@
       <c r="E222" t="s">
         <v>1041</v>
       </c>
-      <c r="F222" s="1">
+      <c r="F222" s="2">
         <v>46028</v>
       </c>
       <c r="G222" t="s">
@@ -13032,7 +13058,7 @@
       <c r="L222" t="s">
         <v>1383</v>
       </c>
-      <c r="N222" s="1">
+      <c r="N222" s="2">
         <v>46232</v>
       </c>
       <c r="Q222" t="b">
@@ -13055,7 +13081,7 @@
       <c r="E223" t="s">
         <v>1042</v>
       </c>
-      <c r="F223" s="1">
+      <c r="F223" s="2">
         <v>46028</v>
       </c>
       <c r="G223" t="s">
@@ -13070,7 +13096,7 @@
       <c r="L223" t="s">
         <v>1383</v>
       </c>
-      <c r="N223" s="1">
+      <c r="N223" s="2">
         <v>46232</v>
       </c>
       <c r="Q223" t="b">
@@ -13093,7 +13119,7 @@
       <c r="E224" t="s">
         <v>1043</v>
       </c>
-      <c r="F224" s="1">
+      <c r="F224" s="2">
         <v>46028</v>
       </c>
       <c r="G224" t="s">
@@ -13111,7 +13137,7 @@
       <c r="L224" t="s">
         <v>1383</v>
       </c>
-      <c r="N224" s="1">
+      <c r="N224" s="2">
         <v>46232</v>
       </c>
       <c r="Q224" t="b">
@@ -13134,7 +13160,7 @@
       <c r="E225" t="s">
         <v>1044</v>
       </c>
-      <c r="F225" s="1">
+      <c r="F225" s="2">
         <v>46028</v>
       </c>
       <c r="G225" t="s">
@@ -13149,7 +13175,7 @@
       <c r="L225" t="s">
         <v>1383</v>
       </c>
-      <c r="N225" s="1">
+      <c r="N225" s="2">
         <v>46232</v>
       </c>
       <c r="Q225" t="b">
@@ -13172,7 +13198,7 @@
       <c r="E226" t="s">
         <v>1045</v>
       </c>
-      <c r="F226" s="1">
+      <c r="F226" s="2">
         <v>46028</v>
       </c>
       <c r="G226" t="s">
@@ -13187,7 +13213,7 @@
       <c r="L226" t="s">
         <v>1383</v>
       </c>
-      <c r="N226" s="1">
+      <c r="N226" s="2">
         <v>46232</v>
       </c>
       <c r="Q226" t="b">
@@ -13210,7 +13236,7 @@
       <c r="E227" t="s">
         <v>1046</v>
       </c>
-      <c r="F227" s="1">
+      <c r="F227" s="2">
         <v>46028</v>
       </c>
       <c r="G227" t="s">
@@ -13225,7 +13251,7 @@
       <c r="L227" t="s">
         <v>1383</v>
       </c>
-      <c r="N227" s="1">
+      <c r="N227" s="2">
         <v>46232</v>
       </c>
       <c r="Q227" t="b">
@@ -13248,7 +13274,7 @@
       <c r="E228" t="s">
         <v>1047</v>
       </c>
-      <c r="F228" s="1">
+      <c r="F228" s="2">
         <v>46028</v>
       </c>
       <c r="G228" t="s">
@@ -13266,7 +13292,7 @@
       <c r="L228" t="s">
         <v>1383</v>
       </c>
-      <c r="N228" s="1">
+      <c r="N228" s="2">
         <v>46232</v>
       </c>
       <c r="Q228" t="b">
@@ -13289,7 +13315,7 @@
       <c r="E229" t="s">
         <v>1048</v>
       </c>
-      <c r="F229" s="1">
+      <c r="F229" s="2">
         <v>46028</v>
       </c>
       <c r="G229" t="s">
@@ -13304,7 +13330,7 @@
       <c r="L229" t="s">
         <v>1420</v>
       </c>
-      <c r="N229" s="1">
+      <c r="N229" s="2">
         <v>46191</v>
       </c>
       <c r="Q229" t="b">
@@ -13327,7 +13353,7 @@
       <c r="E230" t="s">
         <v>1049</v>
       </c>
-      <c r="F230" s="1">
+      <c r="F230" s="2">
         <v>46028</v>
       </c>
       <c r="G230" t="s">
@@ -13348,7 +13374,7 @@
       <c r="L230" t="s">
         <v>1395</v>
       </c>
-      <c r="N230" s="1">
+      <c r="N230" s="2">
         <v>46225</v>
       </c>
       <c r="Q230" t="b">
@@ -13371,7 +13397,7 @@
       <c r="E231" t="s">
         <v>1050</v>
       </c>
-      <c r="F231" s="1">
+      <c r="F231" s="2">
         <v>46028</v>
       </c>
       <c r="G231" t="s">
@@ -13392,7 +13418,7 @@
       <c r="L231" t="s">
         <v>1421</v>
       </c>
-      <c r="N231" s="1">
+      <c r="N231" s="2">
         <v>46063</v>
       </c>
       <c r="Q231" t="b">
@@ -13415,7 +13441,7 @@
       <c r="E232" t="s">
         <v>1051</v>
       </c>
-      <c r="F232" s="1">
+      <c r="F232" s="2">
         <v>46028</v>
       </c>
       <c r="G232" t="s">
@@ -13444,7 +13470,7 @@
       <c r="E233" t="s">
         <v>1052</v>
       </c>
-      <c r="F233" s="1">
+      <c r="F233" s="2">
         <v>46028</v>
       </c>
       <c r="G233" t="s">
@@ -13473,7 +13499,7 @@
       <c r="E234" t="s">
         <v>1053</v>
       </c>
-      <c r="F234" s="1">
+      <c r="F234" s="2">
         <v>46028</v>
       </c>
       <c r="G234" t="s">
@@ -13494,7 +13520,7 @@
       <c r="L234" t="s">
         <v>1421</v>
       </c>
-      <c r="N234" s="1">
+      <c r="N234" s="2">
         <v>46063</v>
       </c>
       <c r="P234" t="s">
@@ -13520,7 +13546,7 @@
       <c r="E235" t="s">
         <v>1054</v>
       </c>
-      <c r="F235" s="1">
+      <c r="F235" s="2">
         <v>46028</v>
       </c>
       <c r="G235" t="s">
@@ -13541,7 +13567,7 @@
       <c r="L235" t="s">
         <v>1421</v>
       </c>
-      <c r="N235" s="1">
+      <c r="N235" s="2">
         <v>46063</v>
       </c>
       <c r="P235" t="s">
@@ -13567,7 +13593,7 @@
       <c r="E236" t="s">
         <v>1055</v>
       </c>
-      <c r="F236" s="1">
+      <c r="F236" s="2">
         <v>46028</v>
       </c>
       <c r="G236" t="s">
@@ -13588,7 +13614,7 @@
       <c r="L236" t="s">
         <v>1422</v>
       </c>
-      <c r="N236" s="1">
+      <c r="N236" s="2">
         <v>46114</v>
       </c>
       <c r="Q236" t="b">
@@ -13611,7 +13637,7 @@
       <c r="E237" t="s">
         <v>1056</v>
       </c>
-      <c r="F237" s="1">
+      <c r="F237" s="2">
         <v>46028</v>
       </c>
       <c r="G237" t="s">
@@ -13629,7 +13655,7 @@
       <c r="L237" t="s">
         <v>1423</v>
       </c>
-      <c r="N237" s="1">
+      <c r="N237" s="2">
         <v>46210</v>
       </c>
       <c r="P237" t="s">
@@ -13655,7 +13681,7 @@
       <c r="E238" t="s">
         <v>1057</v>
       </c>
-      <c r="F238" s="1">
+      <c r="F238" s="2">
         <v>46028</v>
       </c>
       <c r="G238" t="s">
@@ -13684,7 +13710,7 @@
       <c r="E239" t="s">
         <v>1058</v>
       </c>
-      <c r="F239" s="1">
+      <c r="F239" s="2">
         <v>46036</v>
       </c>
       <c r="G239" t="s">
@@ -13702,7 +13728,7 @@
       <c r="L239" t="s">
         <v>1424</v>
       </c>
-      <c r="N239" s="1">
+      <c r="N239" s="2">
         <v>46052</v>
       </c>
       <c r="Q239" t="b">
@@ -13725,7 +13751,7 @@
       <c r="E240" t="s">
         <v>1059</v>
       </c>
-      <c r="F240" s="1">
+      <c r="F240" s="2">
         <v>46036</v>
       </c>
       <c r="G240" t="s">
@@ -13754,7 +13780,7 @@
       <c r="E241" t="s">
         <v>1060</v>
       </c>
-      <c r="F241" s="1">
+      <c r="F241" s="2">
         <v>46036</v>
       </c>
       <c r="G241" t="s">
@@ -13783,7 +13809,7 @@
       <c r="E242" t="s">
         <v>1061</v>
       </c>
-      <c r="F242" s="1">
+      <c r="F242" s="2">
         <v>46036</v>
       </c>
       <c r="G242" t="s">
@@ -13821,7 +13847,7 @@
       <c r="E243" t="s">
         <v>1062</v>
       </c>
-      <c r="F243" s="1">
+      <c r="F243" s="2">
         <v>46048</v>
       </c>
       <c r="G243" t="s">
@@ -13850,7 +13876,7 @@
       <c r="E244" t="s">
         <v>1063</v>
       </c>
-      <c r="F244" s="1">
+      <c r="F244" s="2">
         <v>46048</v>
       </c>
       <c r="G244" t="s">
@@ -13868,7 +13894,7 @@
       <c r="K244" t="s">
         <v>1359</v>
       </c>
-      <c r="N244" s="1">
+      <c r="N244" s="2">
         <v>46063</v>
       </c>
       <c r="Q244" t="b">
@@ -13891,7 +13917,7 @@
       <c r="E245" t="s">
         <v>1064</v>
       </c>
-      <c r="F245" s="1">
+      <c r="F245" s="2">
         <v>46048</v>
       </c>
       <c r="G245" t="s">
@@ -13912,7 +13938,7 @@
       <c r="L245" t="s">
         <v>1425</v>
       </c>
-      <c r="N245" s="1">
+      <c r="N245" s="2">
         <v>46063</v>
       </c>
       <c r="Q245" t="b">
@@ -13935,7 +13961,7 @@
       <c r="E246" t="s">
         <v>1065</v>
       </c>
-      <c r="F246" s="1">
+      <c r="F246" s="2">
         <v>46050</v>
       </c>
       <c r="G246" t="s">
@@ -13953,7 +13979,7 @@
       <c r="L246" t="s">
         <v>1426</v>
       </c>
-      <c r="N246" s="1">
+      <c r="N246" s="2">
         <v>46191</v>
       </c>
       <c r="Q246" t="b">
@@ -13976,7 +14002,7 @@
       <c r="E247" t="s">
         <v>1066</v>
       </c>
-      <c r="F247" s="1">
+      <c r="F247" s="2">
         <v>46050</v>
       </c>
       <c r="G247" t="s">
@@ -14005,7 +14031,7 @@
       <c r="E248" t="s">
         <v>1067</v>
       </c>
-      <c r="F248" s="1">
+      <c r="F248" s="2">
         <v>46050</v>
       </c>
       <c r="G248" t="s">
@@ -14034,7 +14060,7 @@
       <c r="E249" t="s">
         <v>1068</v>
       </c>
-      <c r="F249" s="1">
+      <c r="F249" s="2">
         <v>46050</v>
       </c>
       <c r="G249" t="s">
@@ -14072,7 +14098,7 @@
       <c r="E250" t="s">
         <v>1069</v>
       </c>
-      <c r="F250" s="1">
+      <c r="F250" s="2">
         <v>46063</v>
       </c>
       <c r="G250" t="s">
@@ -14110,7 +14136,7 @@
       <c r="E251" t="s">
         <v>1070</v>
       </c>
-      <c r="F251" s="1">
+      <c r="F251" s="2">
         <v>46063</v>
       </c>
       <c r="G251" t="s">
@@ -14139,7 +14165,7 @@
       <c r="E252" t="s">
         <v>1071</v>
       </c>
-      <c r="F252" s="1">
+      <c r="F252" s="2">
         <v>46063</v>
       </c>
       <c r="G252" t="s">
@@ -14168,7 +14194,7 @@
       <c r="E253" t="s">
         <v>1072</v>
       </c>
-      <c r="F253" s="1">
+      <c r="F253" s="2">
         <v>46063</v>
       </c>
       <c r="G253" t="s">
@@ -14189,7 +14215,7 @@
       <c r="L253" t="s">
         <v>1395</v>
       </c>
-      <c r="N253" s="1">
+      <c r="N253" s="2">
         <v>46225</v>
       </c>
       <c r="Q253" t="b">
@@ -14212,7 +14238,7 @@
       <c r="E254" t="s">
         <v>1073</v>
       </c>
-      <c r="F254" s="1">
+      <c r="F254" s="2">
         <v>46063</v>
       </c>
       <c r="G254" t="s">
@@ -14250,7 +14276,7 @@
       <c r="E255" t="s">
         <v>1074</v>
       </c>
-      <c r="F255" s="1">
+      <c r="F255" s="2">
         <v>46063</v>
       </c>
       <c r="G255" t="s">
@@ -14271,7 +14297,7 @@
       <c r="L255" t="s">
         <v>1388</v>
       </c>
-      <c r="N255" s="1">
+      <c r="N255" s="2">
         <v>46135</v>
       </c>
       <c r="Q255" t="b">
@@ -14294,7 +14320,7 @@
       <c r="E256" t="s">
         <v>1075</v>
       </c>
-      <c r="F256" s="1">
+      <c r="F256" s="2">
         <v>46063</v>
       </c>
       <c r="G256" t="s">
@@ -14312,7 +14338,7 @@
       <c r="K256" t="s">
         <v>1357</v>
       </c>
-      <c r="N256" s="1">
+      <c r="N256" s="2">
         <v>46086</v>
       </c>
       <c r="O256">
@@ -14338,7 +14364,7 @@
       <c r="E257" t="s">
         <v>1076</v>
       </c>
-      <c r="F257" s="1">
+      <c r="F257" s="2">
         <v>46063</v>
       </c>
       <c r="G257" t="s">
@@ -14367,7 +14393,7 @@
       <c r="E258" t="s">
         <v>1077</v>
       </c>
-      <c r="F258" s="1">
+      <c r="F258" s="2">
         <v>46063</v>
       </c>
       <c r="G258" t="s">
@@ -14396,7 +14422,7 @@
       <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="F259" s="1">
+      <c r="F259" s="2">
         <v>46063</v>
       </c>
       <c r="G259" t="s">
@@ -14417,7 +14443,7 @@
       <c r="L259" t="s">
         <v>1388</v>
       </c>
-      <c r="N259" s="1">
+      <c r="N259" s="2">
         <v>46135</v>
       </c>
       <c r="Q259" t="b">
@@ -14440,7 +14466,7 @@
       <c r="E260" t="s">
         <v>1079</v>
       </c>
-      <c r="F260" s="1">
+      <c r="F260" s="2">
         <v>46063</v>
       </c>
       <c r="G260" t="s">
@@ -14461,7 +14487,7 @@
       <c r="L260" t="s">
         <v>1388</v>
       </c>
-      <c r="N260" s="1">
+      <c r="N260" s="2">
         <v>46147</v>
       </c>
       <c r="Q260" t="b">
@@ -14484,7 +14510,7 @@
       <c r="E261" t="s">
         <v>1080</v>
       </c>
-      <c r="F261" s="1">
+      <c r="F261" s="2">
         <v>46063</v>
       </c>
       <c r="G261" t="s">
@@ -14505,7 +14531,7 @@
       <c r="L261" t="s">
         <v>1427</v>
       </c>
-      <c r="N261" s="1">
+      <c r="N261" s="2">
         <v>46225</v>
       </c>
       <c r="Q261" t="b">
@@ -14528,7 +14554,7 @@
       <c r="E262" t="s">
         <v>1081</v>
       </c>
-      <c r="F262" s="1">
+      <c r="F262" s="2">
         <v>46063</v>
       </c>
       <c r="G262" t="s">
@@ -14546,7 +14572,7 @@
       <c r="L262" t="s">
         <v>1428</v>
       </c>
-      <c r="N262" s="1">
+      <c r="N262" s="2">
         <v>46113</v>
       </c>
       <c r="P262" t="s">
@@ -14572,7 +14598,7 @@
       <c r="E263" t="s">
         <v>1082</v>
       </c>
-      <c r="F263" s="1">
+      <c r="F263" s="2">
         <v>46063</v>
       </c>
       <c r="G263" t="s">
@@ -14601,7 +14627,7 @@
       <c r="E264" t="s">
         <v>1083</v>
       </c>
-      <c r="F264" s="1">
+      <c r="F264" s="2">
         <v>46063</v>
       </c>
       <c r="G264" t="s">
@@ -14622,7 +14648,7 @@
       <c r="L264" t="s">
         <v>1388</v>
       </c>
-      <c r="N264" s="1">
+      <c r="N264" s="2">
         <v>46225</v>
       </c>
       <c r="Q264" t="b">
@@ -14645,7 +14671,7 @@
       <c r="E265" t="s">
         <v>1084</v>
       </c>
-      <c r="F265" s="1">
+      <c r="F265" s="2">
         <v>46063</v>
       </c>
       <c r="G265" t="s">
@@ -14666,7 +14692,7 @@
       <c r="L265" t="s">
         <v>1395</v>
       </c>
-      <c r="N265" s="1">
+      <c r="N265" s="2">
         <v>46225</v>
       </c>
       <c r="Q265" t="b">
@@ -14689,7 +14715,7 @@
       <c r="E266" t="s">
         <v>1085</v>
       </c>
-      <c r="F266" s="1">
+      <c r="F266" s="2">
         <v>46063</v>
       </c>
       <c r="G266" t="s">
@@ -14710,7 +14736,7 @@
       <c r="L266" t="s">
         <v>1388</v>
       </c>
-      <c r="N266" s="1">
+      <c r="N266" s="2">
         <v>46147</v>
       </c>
       <c r="Q266" t="b">
@@ -14733,7 +14759,7 @@
       <c r="E267" t="s">
         <v>1086</v>
       </c>
-      <c r="F267" s="1">
+      <c r="F267" s="2">
         <v>46063</v>
       </c>
       <c r="G267" t="s">
@@ -14771,7 +14797,7 @@
       <c r="E268" t="s">
         <v>1087</v>
       </c>
-      <c r="F268" s="1">
+      <c r="F268" s="2">
         <v>46063</v>
       </c>
       <c r="G268" t="s">
@@ -14806,7 +14832,7 @@
       <c r="D269" t="s">
         <v>798</v>
       </c>
-      <c r="F269" s="1">
+      <c r="F269" s="2">
         <v>46063</v>
       </c>
       <c r="G269" t="s">
@@ -14844,7 +14870,7 @@
       <c r="E270" t="s">
         <v>1088</v>
       </c>
-      <c r="F270" s="1">
+      <c r="F270" s="2">
         <v>46063</v>
       </c>
       <c r="G270" t="s">
@@ -14882,7 +14908,7 @@
       <c r="E271" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="1">
+      <c r="F271" s="2">
         <v>46063</v>
       </c>
       <c r="G271" t="s">
@@ -14920,7 +14946,7 @@
       <c r="E272" t="s">
         <v>1090</v>
       </c>
-      <c r="F272" s="1">
+      <c r="F272" s="2">
         <v>46063</v>
       </c>
       <c r="G272" t="s">
@@ -14938,7 +14964,7 @@
       <c r="L272" t="s">
         <v>1429</v>
       </c>
-      <c r="N272" s="1">
+      <c r="N272" s="2">
         <v>46185</v>
       </c>
       <c r="O272" t="s">
@@ -14964,7 +14990,7 @@
       <c r="E273" t="s">
         <v>1091</v>
       </c>
-      <c r="F273" s="1">
+      <c r="F273" s="2">
         <v>46063</v>
       </c>
       <c r="G273" t="s">
@@ -14993,7 +15019,7 @@
       <c r="E274" t="s">
         <v>1092</v>
       </c>
-      <c r="F274" s="1">
+      <c r="F274" s="2">
         <v>46063</v>
       </c>
       <c r="G274" t="s">
@@ -15008,7 +15034,7 @@
       <c r="L274" t="s">
         <v>1383</v>
       </c>
-      <c r="N274" s="1">
+      <c r="N274" s="2">
         <v>46232</v>
       </c>
       <c r="Q274" t="b">
@@ -15031,7 +15057,7 @@
       <c r="E275" t="s">
         <v>1093</v>
       </c>
-      <c r="F275" s="1">
+      <c r="F275" s="2">
         <v>46063</v>
       </c>
       <c r="G275" t="s">
@@ -15060,7 +15086,7 @@
       <c r="E276" t="s">
         <v>1094</v>
       </c>
-      <c r="F276" s="1">
+      <c r="F276" s="2">
         <v>46063</v>
       </c>
       <c r="G276" t="s">
@@ -15098,7 +15124,7 @@
       <c r="E277" t="s">
         <v>1095</v>
       </c>
-      <c r="F277" s="1">
+      <c r="F277" s="2">
         <v>46063</v>
       </c>
       <c r="G277" t="s">
@@ -15136,7 +15162,7 @@
       <c r="E278" t="s">
         <v>1096</v>
       </c>
-      <c r="F278" s="1">
+      <c r="F278" s="2">
         <v>46077</v>
       </c>
       <c r="G278" t="s">
@@ -15157,7 +15183,7 @@
       <c r="L278" t="s">
         <v>1395</v>
       </c>
-      <c r="N278" s="1">
+      <c r="N278" s="2">
         <v>46225</v>
       </c>
       <c r="Q278" t="b">
@@ -15180,7 +15206,7 @@
       <c r="E279" t="s">
         <v>1097</v>
       </c>
-      <c r="F279" s="1">
+      <c r="F279" s="2">
         <v>46077</v>
       </c>
       <c r="G279" t="s">
@@ -15221,7 +15247,7 @@
       <c r="E280" t="s">
         <v>1098</v>
       </c>
-      <c r="F280" s="1">
+      <c r="F280" s="2">
         <v>46085</v>
       </c>
       <c r="G280" t="s">
@@ -15259,7 +15285,7 @@
       <c r="E281" t="s">
         <v>1099</v>
       </c>
-      <c r="F281" s="1">
+      <c r="F281" s="2">
         <v>46085</v>
       </c>
       <c r="G281" t="s">
@@ -15300,7 +15326,7 @@
       <c r="E282" t="s">
         <v>1100</v>
       </c>
-      <c r="F282" s="1">
+      <c r="F282" s="2">
         <v>46090</v>
       </c>
       <c r="G282" t="s">
@@ -15338,7 +15364,7 @@
       <c r="E283" t="s">
         <v>1101</v>
       </c>
-      <c r="F283" s="1">
+      <c r="F283" s="2">
         <v>46100</v>
       </c>
       <c r="G283" t="s">
@@ -15367,7 +15393,7 @@
       <c r="E284" t="s">
         <v>1102</v>
       </c>
-      <c r="F284" s="1">
+      <c r="F284" s="2">
         <v>46100</v>
       </c>
       <c r="G284" t="s">
@@ -15396,7 +15422,7 @@
       <c r="E285" t="s">
         <v>1103</v>
       </c>
-      <c r="F285" s="1">
+      <c r="F285" s="2">
         <v>46100</v>
       </c>
       <c r="G285" t="s">
@@ -15425,7 +15451,7 @@
       <c r="E286" t="s">
         <v>1104</v>
       </c>
-      <c r="F286" s="1">
+      <c r="F286" s="2">
         <v>46100</v>
       </c>
       <c r="G286" t="s">
@@ -15454,7 +15480,7 @@
       <c r="E287" t="s">
         <v>1105</v>
       </c>
-      <c r="F287" s="1">
+      <c r="F287" s="2">
         <v>46107</v>
       </c>
       <c r="G287" t="s">
@@ -15483,7 +15509,7 @@
       <c r="E288" t="s">
         <v>1106</v>
       </c>
-      <c r="F288" s="1">
+      <c r="F288" s="2">
         <v>46107</v>
       </c>
       <c r="G288" t="s">
@@ -15504,7 +15530,7 @@
       <c r="L288" t="s">
         <v>1388</v>
       </c>
-      <c r="N288" s="1">
+      <c r="N288" s="2">
         <v>46135</v>
       </c>
       <c r="Q288" t="b">
@@ -15527,7 +15553,7 @@
       <c r="E289" t="s">
         <v>1107</v>
       </c>
-      <c r="F289" s="1">
+      <c r="F289" s="2">
         <v>46107</v>
       </c>
       <c r="G289" t="s">
@@ -15556,7 +15582,7 @@
       <c r="E290" t="s">
         <v>1108</v>
       </c>
-      <c r="F290" s="1">
+      <c r="F290" s="2">
         <v>46107</v>
       </c>
       <c r="G290" t="s">
@@ -15577,7 +15603,7 @@
       <c r="L290" t="s">
         <v>1388</v>
       </c>
-      <c r="N290" s="1">
+      <c r="N290" s="2">
         <v>46127</v>
       </c>
       <c r="Q290" t="b">
@@ -15600,7 +15626,7 @@
       <c r="E291" t="s">
         <v>1109</v>
       </c>
-      <c r="F291" s="1">
+      <c r="F291" s="2">
         <v>46107</v>
       </c>
       <c r="G291" t="s">
@@ -15621,7 +15647,7 @@
       <c r="L291" t="s">
         <v>1430</v>
       </c>
-      <c r="N291" s="1">
+      <c r="N291" s="2">
         <v>46127</v>
       </c>
       <c r="Q291" t="b">
@@ -15644,7 +15670,7 @@
       <c r="E292" t="s">
         <v>1110</v>
       </c>
-      <c r="F292" s="1">
+      <c r="F292" s="2">
         <v>46112</v>
       </c>
       <c r="G292" t="s">
@@ -15682,7 +15708,7 @@
       <c r="E293" t="s">
         <v>1111</v>
       </c>
-      <c r="F293" s="1">
+      <c r="F293" s="2">
         <v>46125</v>
       </c>
       <c r="G293" t="s">
@@ -15720,7 +15746,7 @@
       <c r="E294" t="s">
         <v>1112</v>
       </c>
-      <c r="F294" s="1">
+      <c r="F294" s="2">
         <v>46125</v>
       </c>
       <c r="G294" t="s">
@@ -15755,7 +15781,7 @@
       <c r="E295" t="s">
         <v>1113</v>
       </c>
-      <c r="F295" s="1">
+      <c r="F295" s="2">
         <v>46125</v>
       </c>
       <c r="G295" t="s">
@@ -15790,7 +15816,7 @@
       <c r="E296" t="s">
         <v>1114</v>
       </c>
-      <c r="F296" s="1">
+      <c r="F296" s="2">
         <v>46125</v>
       </c>
       <c r="G296" t="s">
@@ -15825,7 +15851,7 @@
       <c r="E297" t="s">
         <v>1115</v>
       </c>
-      <c r="F297" s="1">
+      <c r="F297" s="2">
         <v>46125</v>
       </c>
       <c r="G297" t="s">
@@ -15837,7 +15863,7 @@
       <c r="K297" t="s">
         <v>1359</v>
       </c>
-      <c r="N297" s="1">
+      <c r="N297" s="2">
         <v>46183</v>
       </c>
       <c r="O297">
@@ -15863,7 +15889,7 @@
       <c r="E298" t="s">
         <v>1116</v>
       </c>
-      <c r="F298" s="1">
+      <c r="F298" s="2">
         <v>46125</v>
       </c>
       <c r="G298" t="s">
@@ -15881,7 +15907,7 @@
       <c r="K298" t="s">
         <v>1359</v>
       </c>
-      <c r="N298" s="1">
+      <c r="N298" s="2">
         <v>46183</v>
       </c>
       <c r="Q298" t="b">
@@ -15904,7 +15930,7 @@
       <c r="E299" t="s">
         <v>1117</v>
       </c>
-      <c r="F299" s="1">
+      <c r="F299" s="2">
         <v>46125</v>
       </c>
       <c r="G299" t="s">
@@ -15925,7 +15951,7 @@
       <c r="L299" t="s">
         <v>1388</v>
       </c>
-      <c r="N299" s="1">
+      <c r="N299" s="2">
         <v>46225</v>
       </c>
       <c r="Q299" t="b">
@@ -15948,7 +15974,7 @@
       <c r="E300" t="s">
         <v>1118</v>
       </c>
-      <c r="F300" s="1">
+      <c r="F300" s="2">
         <v>46125</v>
       </c>
       <c r="G300" t="s">
@@ -15969,7 +15995,7 @@
       <c r="L300" t="s">
         <v>1388</v>
       </c>
-      <c r="N300" s="1">
+      <c r="N300" s="2">
         <v>46211</v>
       </c>
       <c r="Q300" t="b">
@@ -15992,7 +16018,7 @@
       <c r="E301" t="s">
         <v>1119</v>
       </c>
-      <c r="F301" s="1">
+      <c r="F301" s="2">
         <v>46125</v>
       </c>
       <c r="G301" t="s">
@@ -16013,7 +16039,7 @@
       <c r="L301" t="s">
         <v>1388</v>
       </c>
-      <c r="N301" s="1">
+      <c r="N301" s="2">
         <v>46227</v>
       </c>
       <c r="Q301" t="b">
@@ -16036,7 +16062,7 @@
       <c r="E302" t="s">
         <v>1120</v>
       </c>
-      <c r="F302" s="1">
+      <c r="F302" s="2">
         <v>46125</v>
       </c>
       <c r="G302" t="s">
@@ -16074,7 +16100,7 @@
       <c r="E303" t="s">
         <v>1121</v>
       </c>
-      <c r="F303" s="1">
+      <c r="F303" s="2">
         <v>46125</v>
       </c>
       <c r="G303" t="s">
@@ -16112,7 +16138,7 @@
       <c r="E304" t="s">
         <v>1122</v>
       </c>
-      <c r="F304" s="1">
+      <c r="F304" s="2">
         <v>46125</v>
       </c>
       <c r="G304" t="s">
@@ -16150,7 +16176,7 @@
       <c r="E305" t="s">
         <v>1123</v>
       </c>
-      <c r="F305" s="1">
+      <c r="F305" s="2">
         <v>46125</v>
       </c>
       <c r="G305" t="s">
@@ -16171,7 +16197,7 @@
       <c r="L305" t="s">
         <v>1431</v>
       </c>
-      <c r="N305" s="1">
+      <c r="N305" s="2">
         <v>46160</v>
       </c>
       <c r="Q305" t="b">
@@ -16194,7 +16220,7 @@
       <c r="E306" t="s">
         <v>1124</v>
       </c>
-      <c r="F306" s="1">
+      <c r="F306" s="2">
         <v>46125</v>
       </c>
       <c r="G306" t="s">
@@ -16215,7 +16241,7 @@
       <c r="L306" t="s">
         <v>1432</v>
       </c>
-      <c r="N306" s="1">
+      <c r="N306" s="2">
         <v>46156</v>
       </c>
       <c r="Q306" t="b">
@@ -16238,7 +16264,7 @@
       <c r="E307" t="s">
         <v>1125</v>
       </c>
-      <c r="F307" s="1">
+      <c r="F307" s="2">
         <v>46125</v>
       </c>
       <c r="G307" t="s">
@@ -16256,7 +16282,7 @@
       <c r="L307" t="s">
         <v>1433</v>
       </c>
-      <c r="N307" s="1">
+      <c r="N307" s="2">
         <v>46209</v>
       </c>
       <c r="P307" t="s">
@@ -16282,7 +16308,7 @@
       <c r="E308" t="s">
         <v>1126</v>
       </c>
-      <c r="F308" s="1">
+      <c r="F308" s="2">
         <v>46125</v>
       </c>
       <c r="G308" t="s">
@@ -16320,7 +16346,7 @@
       <c r="E309" t="s">
         <v>1127</v>
       </c>
-      <c r="F309" s="1">
+      <c r="F309" s="2">
         <v>46125</v>
       </c>
       <c r="G309" t="s">
@@ -16335,7 +16361,7 @@
       <c r="L309" t="s">
         <v>1383</v>
       </c>
-      <c r="N309" s="1">
+      <c r="N309" s="2">
         <v>46232</v>
       </c>
       <c r="Q309" t="b">
@@ -16358,7 +16384,7 @@
       <c r="E310" t="s">
         <v>1128</v>
       </c>
-      <c r="F310" s="1">
+      <c r="F310" s="2">
         <v>46125</v>
       </c>
       <c r="G310" t="s">
@@ -16379,7 +16405,7 @@
       <c r="L310" t="s">
         <v>1383</v>
       </c>
-      <c r="N310" s="1">
+      <c r="N310" s="2">
         <v>46232</v>
       </c>
       <c r="Q310" t="b">
@@ -16402,7 +16428,7 @@
       <c r="E311" t="s">
         <v>1129</v>
       </c>
-      <c r="F311" s="1">
+      <c r="F311" s="2">
         <v>46125</v>
       </c>
       <c r="G311" t="s">
@@ -16440,7 +16466,7 @@
       <c r="E312" t="s">
         <v>1130</v>
       </c>
-      <c r="F312" s="1">
+      <c r="F312" s="2">
         <v>46125</v>
       </c>
       <c r="G312" t="s">
@@ -16458,7 +16484,7 @@
       <c r="L312" t="s">
         <v>1383</v>
       </c>
-      <c r="N312" s="1">
+      <c r="N312" s="2">
         <v>46232</v>
       </c>
       <c r="Q312" t="b">
@@ -16481,7 +16507,7 @@
       <c r="E313" t="s">
         <v>1131</v>
       </c>
-      <c r="F313" s="1">
+      <c r="F313" s="2">
         <v>46125</v>
       </c>
       <c r="G313" t="s">
@@ -16516,7 +16542,7 @@
       <c r="E314" t="s">
         <v>1132</v>
       </c>
-      <c r="F314" s="1">
+      <c r="F314" s="2">
         <v>46125</v>
       </c>
       <c r="G314" t="s">
@@ -16531,7 +16557,7 @@
       <c r="L314" t="s">
         <v>1383</v>
       </c>
-      <c r="N314" s="1">
+      <c r="N314" s="2">
         <v>46232</v>
       </c>
       <c r="Q314" t="b">
@@ -16554,7 +16580,7 @@
       <c r="E315" t="s">
         <v>1133</v>
       </c>
-      <c r="F315" s="1">
+      <c r="F315" s="2">
         <v>46125</v>
       </c>
       <c r="G315" t="s">
@@ -16569,7 +16595,7 @@
       <c r="L315" t="s">
         <v>1383</v>
       </c>
-      <c r="N315" s="1">
+      <c r="N315" s="2">
         <v>46232</v>
       </c>
       <c r="Q315" t="b">
@@ -16592,7 +16618,7 @@
       <c r="E316" t="s">
         <v>1134</v>
       </c>
-      <c r="F316" s="1">
+      <c r="F316" s="2">
         <v>46125</v>
       </c>
       <c r="G316" t="s">
@@ -16630,7 +16656,7 @@
       <c r="E317" t="s">
         <v>1135</v>
       </c>
-      <c r="F317" s="1">
+      <c r="F317" s="2">
         <v>46125</v>
       </c>
       <c r="G317" t="s">
@@ -16665,7 +16691,7 @@
       <c r="E318" t="s">
         <v>1136</v>
       </c>
-      <c r="F318" s="1">
+      <c r="F318" s="2">
         <v>46125</v>
       </c>
       <c r="G318" t="s">
@@ -16694,7 +16720,7 @@
       <c r="E319" t="s">
         <v>1137</v>
       </c>
-      <c r="F319" s="1">
+      <c r="F319" s="2">
         <v>46125</v>
       </c>
       <c r="G319" t="s">
@@ -16709,7 +16735,7 @@
       <c r="L319" t="s">
         <v>1434</v>
       </c>
-      <c r="N319" s="1">
+      <c r="N319" s="2">
         <v>46175</v>
       </c>
       <c r="Q319" t="b">
@@ -16732,7 +16758,7 @@
       <c r="E320" t="s">
         <v>1138</v>
       </c>
-      <c r="F320" s="1">
+      <c r="F320" s="2">
         <v>46125</v>
       </c>
       <c r="G320" t="s">
@@ -16770,7 +16796,7 @@
       <c r="E321" t="s">
         <v>1139</v>
       </c>
-      <c r="F321" s="1">
+      <c r="F321" s="2">
         <v>46125</v>
       </c>
       <c r="G321" t="s">
@@ -16808,7 +16834,7 @@
       <c r="E322" t="s">
         <v>1140</v>
       </c>
-      <c r="F322" s="1">
+      <c r="F322" s="2">
         <v>46125</v>
       </c>
       <c r="G322" t="s">
@@ -16829,7 +16855,7 @@
       <c r="L322" t="s">
         <v>1435</v>
       </c>
-      <c r="N322" s="1">
+      <c r="N322" s="2">
         <v>46182</v>
       </c>
       <c r="Q322" t="b">
@@ -16852,7 +16878,7 @@
       <c r="E323" t="s">
         <v>1141</v>
       </c>
-      <c r="F323" s="1">
+      <c r="F323" s="2">
         <v>46125</v>
       </c>
       <c r="G323" t="s">
@@ -16887,7 +16913,7 @@
       <c r="E324" t="s">
         <v>1142</v>
       </c>
-      <c r="F324" s="1">
+      <c r="F324" s="2">
         <v>46125</v>
       </c>
       <c r="G324" t="s">
@@ -16922,7 +16948,7 @@
       <c r="E325" t="s">
         <v>1143</v>
       </c>
-      <c r="F325" s="1">
+      <c r="F325" s="2">
         <v>46125</v>
       </c>
       <c r="G325" t="s">
@@ -16943,7 +16969,7 @@
       <c r="L325" t="s">
         <v>1435</v>
       </c>
-      <c r="N325" s="1">
+      <c r="N325" s="2">
         <v>46182</v>
       </c>
       <c r="Q325" t="b">
@@ -16966,7 +16992,7 @@
       <c r="E326" t="s">
         <v>1144</v>
       </c>
-      <c r="F326" s="1">
+      <c r="F326" s="2">
         <v>46125</v>
       </c>
       <c r="G326" t="s">
@@ -16981,7 +17007,7 @@
       <c r="L326" t="s">
         <v>1383</v>
       </c>
-      <c r="N326" s="1">
+      <c r="N326" s="2">
         <v>46232</v>
       </c>
       <c r="Q326" t="b">
@@ -17004,7 +17030,7 @@
       <c r="E327" t="s">
         <v>1140</v>
       </c>
-      <c r="F327" s="1">
+      <c r="F327" s="2">
         <v>46125</v>
       </c>
       <c r="G327" t="s">
@@ -17025,7 +17051,7 @@
       <c r="L327" t="s">
         <v>1435</v>
       </c>
-      <c r="N327" s="1">
+      <c r="N327" s="2">
         <v>46182</v>
       </c>
       <c r="Q327" t="b">
@@ -17048,7 +17074,7 @@
       <c r="E328" t="s">
         <v>1145</v>
       </c>
-      <c r="F328" s="1">
+      <c r="F328" s="2">
         <v>46125</v>
       </c>
       <c r="G328" t="s">
@@ -17069,7 +17095,7 @@
       <c r="L328" t="s">
         <v>1435</v>
       </c>
-      <c r="N328" s="1">
+      <c r="N328" s="2">
         <v>46182</v>
       </c>
       <c r="Q328" t="b">
@@ -17092,7 +17118,7 @@
       <c r="E329" t="s">
         <v>1146</v>
       </c>
-      <c r="F329" s="1">
+      <c r="F329" s="2">
         <v>46125</v>
       </c>
       <c r="G329" t="s">
@@ -17113,7 +17139,7 @@
       <c r="L329" t="s">
         <v>1435</v>
       </c>
-      <c r="N329" s="1">
+      <c r="N329" s="2">
         <v>46182</v>
       </c>
       <c r="Q329" t="b">
@@ -17136,7 +17162,7 @@
       <c r="E330" t="s">
         <v>1147</v>
       </c>
-      <c r="F330" s="1">
+      <c r="F330" s="2">
         <v>46125</v>
       </c>
       <c r="G330" t="s">
@@ -17157,7 +17183,7 @@
       <c r="L330" t="s">
         <v>1435</v>
       </c>
-      <c r="N330" s="1">
+      <c r="N330" s="2">
         <v>46182</v>
       </c>
       <c r="Q330" t="b">
@@ -17180,7 +17206,7 @@
       <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="F331" s="1">
+      <c r="F331" s="2">
         <v>46125</v>
       </c>
       <c r="G331" t="s">
@@ -17218,7 +17244,7 @@
       <c r="E332" t="s">
         <v>1148</v>
       </c>
-      <c r="F332" s="1">
+      <c r="F332" s="2">
         <v>46125</v>
       </c>
       <c r="G332" t="s">
@@ -17256,7 +17282,7 @@
       <c r="E333" t="s">
         <v>910</v>
       </c>
-      <c r="F333" s="1">
+      <c r="F333" s="2">
         <v>46125</v>
       </c>
       <c r="G333" t="s">
@@ -17277,7 +17303,7 @@
       <c r="L333" t="s">
         <v>1395</v>
       </c>
-      <c r="N333" s="1">
+      <c r="N333" s="2">
         <v>46225</v>
       </c>
       <c r="Q333" t="b">
@@ -17300,7 +17326,7 @@
       <c r="E334" t="s">
         <v>1149</v>
       </c>
-      <c r="F334" s="1">
+      <c r="F334" s="2">
         <v>46125</v>
       </c>
       <c r="G334" t="s">
@@ -17338,7 +17364,7 @@
       <c r="E335" t="s">
         <v>1150</v>
       </c>
-      <c r="F335" s="1">
+      <c r="F335" s="2">
         <v>46127</v>
       </c>
       <c r="G335" t="s">
@@ -17353,7 +17379,7 @@
       <c r="L335" t="s">
         <v>1434</v>
       </c>
-      <c r="N335" s="1">
+      <c r="N335" s="2">
         <v>46175</v>
       </c>
       <c r="Q335" t="b">
@@ -17376,7 +17402,7 @@
       <c r="E336" t="s">
         <v>1151</v>
       </c>
-      <c r="F336" s="1">
+      <c r="F336" s="2">
         <v>46127</v>
       </c>
       <c r="G336" t="s">
@@ -17397,7 +17423,7 @@
       <c r="L336" t="s">
         <v>1388</v>
       </c>
-      <c r="N336" s="1">
+      <c r="N336" s="2">
         <v>46155</v>
       </c>
       <c r="Q336" t="b">
@@ -17420,7 +17446,7 @@
       <c r="E337" t="s">
         <v>1152</v>
       </c>
-      <c r="F337" s="1">
+      <c r="F337" s="2">
         <v>46127</v>
       </c>
       <c r="G337" t="s">
@@ -17435,7 +17461,7 @@
       <c r="L337" t="s">
         <v>1434</v>
       </c>
-      <c r="N337" s="1">
+      <c r="N337" s="2">
         <v>46175</v>
       </c>
       <c r="Q337" t="b">
@@ -17458,7 +17484,7 @@
       <c r="E338" t="s">
         <v>1153</v>
       </c>
-      <c r="F338" s="1">
+      <c r="F338" s="2">
         <v>46127</v>
       </c>
       <c r="G338" t="s">
@@ -17479,7 +17505,7 @@
       <c r="L338" t="s">
         <v>1388</v>
       </c>
-      <c r="N338" s="1">
+      <c r="N338" s="2">
         <v>46139</v>
       </c>
       <c r="Q338" t="b">
@@ -17502,7 +17528,7 @@
       <c r="E339" t="s">
         <v>1154</v>
       </c>
-      <c r="F339" s="1">
+      <c r="F339" s="2">
         <v>46129</v>
       </c>
       <c r="G339" t="s">
@@ -17531,7 +17557,7 @@
       <c r="E340" t="s">
         <v>1155</v>
       </c>
-      <c r="F340" s="1">
+      <c r="F340" s="2">
         <v>46142</v>
       </c>
       <c r="G340" t="s">
@@ -17549,7 +17575,7 @@
       <c r="L340" t="s">
         <v>1383</v>
       </c>
-      <c r="N340" s="1">
+      <c r="N340" s="2">
         <v>46240</v>
       </c>
       <c r="Q340" t="b">
@@ -17572,7 +17598,7 @@
       <c r="E341" t="s">
         <v>1156</v>
       </c>
-      <c r="F341" s="1">
+      <c r="F341" s="2">
         <v>46142</v>
       </c>
       <c r="G341" t="s">
@@ -17590,7 +17616,7 @@
       <c r="L341" t="s">
         <v>1383</v>
       </c>
-      <c r="N341" s="1">
+      <c r="N341" s="2">
         <v>46232</v>
       </c>
       <c r="Q341" t="b">
@@ -17613,7 +17639,7 @@
       <c r="E342" t="s">
         <v>1157</v>
       </c>
-      <c r="F342" s="1">
+      <c r="F342" s="2">
         <v>46142</v>
       </c>
       <c r="G342" t="s">
@@ -17651,7 +17677,7 @@
       <c r="E343" t="s">
         <v>1158</v>
       </c>
-      <c r="F343" s="1">
+      <c r="F343" s="2">
         <v>46142</v>
       </c>
       <c r="G343" t="s">
@@ -17666,7 +17692,7 @@
       <c r="L343" t="s">
         <v>1383</v>
       </c>
-      <c r="N343" s="1">
+      <c r="N343" s="2">
         <v>46232</v>
       </c>
       <c r="Q343" t="b">
@@ -17689,7 +17715,7 @@
       <c r="E344" t="s">
         <v>1159</v>
       </c>
-      <c r="F344" s="1">
+      <c r="F344" s="2">
         <v>46142</v>
       </c>
       <c r="G344" t="s">
@@ -17704,7 +17730,7 @@
       <c r="L344" t="s">
         <v>1383</v>
       </c>
-      <c r="N344" s="1">
+      <c r="N344" s="2">
         <v>46232</v>
       </c>
       <c r="Q344" t="b">
@@ -17727,7 +17753,7 @@
       <c r="E345" t="s">
         <v>1160</v>
       </c>
-      <c r="F345" s="1">
+      <c r="F345" s="2">
         <v>46142</v>
       </c>
       <c r="G345" t="s">
@@ -17765,7 +17791,7 @@
       <c r="E346" t="s">
         <v>1161</v>
       </c>
-      <c r="F346" s="1">
+      <c r="F346" s="2">
         <v>46142</v>
       </c>
       <c r="G346" t="s">
@@ -17780,7 +17806,7 @@
       <c r="L346" t="s">
         <v>1383</v>
       </c>
-      <c r="N346" s="1">
+      <c r="N346" s="2">
         <v>46232</v>
       </c>
       <c r="Q346" t="b">
@@ -17803,7 +17829,7 @@
       <c r="E347" t="s">
         <v>1162</v>
       </c>
-      <c r="F347" s="1">
+      <c r="F347" s="2">
         <v>46142</v>
       </c>
       <c r="G347" t="s">
@@ -17824,7 +17850,7 @@
       <c r="L347" t="s">
         <v>1431</v>
       </c>
-      <c r="N347" s="1">
+      <c r="N347" s="2">
         <v>46160</v>
       </c>
       <c r="P347" t="s">
@@ -17850,7 +17876,7 @@
       <c r="E348" t="s">
         <v>1163</v>
       </c>
-      <c r="F348" s="1">
+      <c r="F348" s="2">
         <v>46142</v>
       </c>
       <c r="G348" t="s">
@@ -17871,7 +17897,7 @@
       <c r="L348" t="s">
         <v>1432</v>
       </c>
-      <c r="N348" s="1">
+      <c r="N348" s="2">
         <v>46156</v>
       </c>
       <c r="Q348" t="b">
@@ -17894,7 +17920,7 @@
       <c r="E349" t="s">
         <v>1164</v>
       </c>
-      <c r="F349" s="1">
+      <c r="F349" s="2">
         <v>46142</v>
       </c>
       <c r="G349" t="s">
@@ -17932,7 +17958,7 @@
       <c r="E350" t="s">
         <v>1165</v>
       </c>
-      <c r="F350" s="1">
+      <c r="F350" s="2">
         <v>46142</v>
       </c>
       <c r="G350" t="s">
@@ -17947,7 +17973,7 @@
       <c r="J350">
         <v>46</v>
       </c>
-      <c r="N350" s="1">
+      <c r="N350" s="2">
         <v>46188</v>
       </c>
       <c r="Q350" t="b">
@@ -17970,7 +17996,7 @@
       <c r="E351" t="s">
         <v>1166</v>
       </c>
-      <c r="F351" s="1">
+      <c r="F351" s="2">
         <v>46142</v>
       </c>
       <c r="G351" t="s">
@@ -17991,7 +18017,7 @@
       <c r="L351" t="s">
         <v>1436</v>
       </c>
-      <c r="N351" s="1">
+      <c r="N351" s="2">
         <v>46224</v>
       </c>
       <c r="Q351" t="b">
@@ -18014,7 +18040,7 @@
       <c r="E352" t="s">
         <v>1167</v>
       </c>
-      <c r="F352" s="1">
+      <c r="F352" s="2">
         <v>46142</v>
       </c>
       <c r="G352" t="s">
@@ -18035,7 +18061,7 @@
       <c r="L352" t="s">
         <v>1437</v>
       </c>
-      <c r="N352" s="1">
+      <c r="N352" s="2">
         <v>46220</v>
       </c>
       <c r="Q352" t="b">
@@ -18058,7 +18084,7 @@
       <c r="E353" t="s">
         <v>1168</v>
       </c>
-      <c r="F353" s="1">
+      <c r="F353" s="2">
         <v>46142</v>
       </c>
       <c r="G353" t="s">
@@ -18079,7 +18105,7 @@
       <c r="L353" t="s">
         <v>1395</v>
       </c>
-      <c r="N353" s="1">
+      <c r="N353" s="2">
         <v>46225</v>
       </c>
       <c r="Q353" t="b">
@@ -18102,7 +18128,7 @@
       <c r="E354" t="s">
         <v>1169</v>
       </c>
-      <c r="F354" s="1">
+      <c r="F354" s="2">
         <v>46142</v>
       </c>
       <c r="G354" t="s">
@@ -18140,7 +18166,7 @@
       <c r="E355" t="s">
         <v>1170</v>
       </c>
-      <c r="F355" s="1">
+      <c r="F355" s="2">
         <v>46142</v>
       </c>
       <c r="G355" t="s">
@@ -18161,7 +18187,7 @@
       <c r="L355" t="s">
         <v>1438</v>
       </c>
-      <c r="N355" s="1">
+      <c r="N355" s="2">
         <v>46150</v>
       </c>
       <c r="Q355" t="b">
@@ -18184,7 +18210,7 @@
       <c r="E356" t="s">
         <v>1171</v>
       </c>
-      <c r="F356" s="1">
+      <c r="F356" s="2">
         <v>46142</v>
       </c>
       <c r="G356" t="s">
@@ -18199,7 +18225,7 @@
       <c r="L356" t="s">
         <v>1439</v>
       </c>
-      <c r="N356" s="1">
+      <c r="N356" s="2">
         <v>46176</v>
       </c>
       <c r="Q356" t="b">
@@ -18222,7 +18248,7 @@
       <c r="E357" t="s">
         <v>1172</v>
       </c>
-      <c r="F357" s="1">
+      <c r="F357" s="2">
         <v>46142</v>
       </c>
       <c r="G357" t="s">
@@ -18240,7 +18266,7 @@
       <c r="K357" t="s">
         <v>1360</v>
       </c>
-      <c r="N357" s="1">
+      <c r="N357" s="2">
         <v>46227</v>
       </c>
       <c r="Q357" t="b">
@@ -18263,7 +18289,7 @@
       <c r="E358" t="s">
         <v>1173</v>
       </c>
-      <c r="F358" s="1">
+      <c r="F358" s="2">
         <v>46142</v>
       </c>
       <c r="G358" t="s">
@@ -18281,7 +18307,7 @@
       <c r="L358" t="s">
         <v>1440</v>
       </c>
-      <c r="N358" s="1">
+      <c r="N358" s="2">
         <v>46227</v>
       </c>
       <c r="P358" t="s">
@@ -18307,7 +18333,7 @@
       <c r="E359" t="s">
         <v>1174</v>
       </c>
-      <c r="F359" s="1">
+      <c r="F359" s="2">
         <v>46142</v>
       </c>
       <c r="G359" t="s">
@@ -18319,7 +18345,7 @@
       <c r="J359">
         <v>63</v>
       </c>
-      <c r="N359" s="1">
+      <c r="N359" s="2">
         <v>46205</v>
       </c>
       <c r="P359" t="s">
@@ -18345,7 +18371,7 @@
       <c r="E360" t="s">
         <v>949</v>
       </c>
-      <c r="F360" s="1">
+      <c r="F360" s="2">
         <v>46142</v>
       </c>
       <c r="G360" t="s">
@@ -18366,7 +18392,7 @@
       <c r="L360" t="s">
         <v>1395</v>
       </c>
-      <c r="N360" s="1">
+      <c r="N360" s="2">
         <v>46225</v>
       </c>
       <c r="O360" t="s">
@@ -18392,7 +18418,7 @@
       <c r="E361" t="s">
         <v>961</v>
       </c>
-      <c r="F361" s="1">
+      <c r="F361" s="2">
         <v>46142</v>
       </c>
       <c r="G361" t="s">
@@ -18413,7 +18439,7 @@
       <c r="L361" t="s">
         <v>1395</v>
       </c>
-      <c r="N361" s="1">
+      <c r="N361" s="2">
         <v>46225</v>
       </c>
       <c r="Q361" t="b">
@@ -18436,7 +18462,7 @@
       <c r="E362" t="s">
         <v>1175</v>
       </c>
-      <c r="F362" s="1">
+      <c r="F362" s="2">
         <v>46142</v>
       </c>
       <c r="G362" t="s">
@@ -18474,7 +18500,7 @@
       <c r="E363" t="s">
         <v>1176</v>
       </c>
-      <c r="F363" s="1">
+      <c r="F363" s="2">
         <v>46142</v>
       </c>
       <c r="G363" t="s">
@@ -18512,7 +18538,7 @@
       <c r="E364" t="s">
         <v>958</v>
       </c>
-      <c r="F364" s="1">
+      <c r="F364" s="2">
         <v>46142</v>
       </c>
       <c r="G364" t="s">
@@ -18533,7 +18559,7 @@
       <c r="L364" t="s">
         <v>1395</v>
       </c>
-      <c r="N364" s="1">
+      <c r="N364" s="2">
         <v>46225</v>
       </c>
       <c r="Q364" t="b">
@@ -18556,7 +18582,7 @@
       <c r="E365" t="s">
         <v>1177</v>
       </c>
-      <c r="F365" s="1">
+      <c r="F365" s="2">
         <v>46142</v>
       </c>
       <c r="G365" t="s">
@@ -18574,7 +18600,7 @@
       <c r="K365" t="s">
         <v>1359</v>
       </c>
-      <c r="N365" s="1">
+      <c r="N365" s="2">
         <v>46157</v>
       </c>
       <c r="Q365" t="b">
@@ -18597,7 +18623,7 @@
       <c r="E366" t="s">
         <v>1178</v>
       </c>
-      <c r="F366" s="1">
+      <c r="F366" s="2">
         <v>46148</v>
       </c>
       <c r="G366" t="s">
@@ -18618,7 +18644,7 @@
       <c r="L366" t="s">
         <v>1388</v>
       </c>
-      <c r="N366" s="1">
+      <c r="N366" s="2">
         <v>46225</v>
       </c>
       <c r="Q366" t="b">
@@ -18641,7 +18667,7 @@
       <c r="E367" t="s">
         <v>1179</v>
       </c>
-      <c r="F367" s="1">
+      <c r="F367" s="2">
         <v>46148</v>
       </c>
       <c r="G367" t="s">
@@ -18662,7 +18688,7 @@
       <c r="L367" t="s">
         <v>1388</v>
       </c>
-      <c r="N367" s="1">
+      <c r="N367" s="2">
         <v>46225</v>
       </c>
       <c r="Q367" t="b">
@@ -18685,7 +18711,7 @@
       <c r="E368" t="s">
         <v>1180</v>
       </c>
-      <c r="F368" s="1">
+      <c r="F368" s="2">
         <v>46148</v>
       </c>
       <c r="G368" t="s">
@@ -18706,7 +18732,7 @@
       <c r="L368" t="s">
         <v>1395</v>
       </c>
-      <c r="N368" s="1">
+      <c r="N368" s="2">
         <v>46225</v>
       </c>
       <c r="Q368" t="b">
@@ -18729,7 +18755,7 @@
       <c r="E369" t="s">
         <v>1181</v>
       </c>
-      <c r="F369" s="1">
+      <c r="F369" s="2">
         <v>46148</v>
       </c>
       <c r="G369" t="s">
@@ -18767,7 +18793,7 @@
       <c r="E370" t="s">
         <v>1182</v>
       </c>
-      <c r="F370" s="1">
+      <c r="F370" s="2">
         <v>46148</v>
       </c>
       <c r="G370" t="s">
@@ -18805,7 +18831,7 @@
       <c r="E371" t="s">
         <v>1183</v>
       </c>
-      <c r="F371" s="1">
+      <c r="F371" s="2">
         <v>46148</v>
       </c>
       <c r="G371" t="s">
@@ -18826,7 +18852,7 @@
       <c r="L371" t="s">
         <v>1441</v>
       </c>
-      <c r="N371" s="1">
+      <c r="N371" s="2">
         <v>46164</v>
       </c>
       <c r="Q371" t="b">
@@ -18849,7 +18875,7 @@
       <c r="E372" t="s">
         <v>1184</v>
       </c>
-      <c r="F372" s="1">
+      <c r="F372" s="2">
         <v>46148</v>
       </c>
       <c r="G372" t="s">
@@ -18867,7 +18893,7 @@
       <c r="L372" t="s">
         <v>1428</v>
       </c>
-      <c r="N372" s="1">
+      <c r="N372" s="2">
         <v>46113</v>
       </c>
       <c r="P372" t="s">
@@ -18893,7 +18919,7 @@
       <c r="E373" t="s">
         <v>1185</v>
       </c>
-      <c r="F373" s="1">
+      <c r="F373" s="2">
         <v>46149</v>
       </c>
       <c r="G373" t="s">
@@ -18931,7 +18957,7 @@
       <c r="E374" t="s">
         <v>1186</v>
       </c>
-      <c r="F374" s="1">
+      <c r="F374" s="2">
         <v>46149</v>
       </c>
       <c r="G374" t="s">
@@ -18969,7 +18995,7 @@
       <c r="E375" t="s">
         <v>1187</v>
       </c>
-      <c r="F375" s="1">
+      <c r="F375" s="2">
         <v>46154</v>
       </c>
       <c r="G375" t="s">
@@ -18987,7 +19013,7 @@
       <c r="K375" t="s">
         <v>1360</v>
       </c>
-      <c r="N375" s="1">
+      <c r="N375" s="2">
         <v>46248</v>
       </c>
       <c r="Q375" t="b">
@@ -19010,7 +19036,7 @@
       <c r="E376" t="s">
         <v>1188</v>
       </c>
-      <c r="F376" s="1">
+      <c r="F376" s="2">
         <v>46154</v>
       </c>
       <c r="G376" t="s">
@@ -19048,7 +19074,7 @@
       <c r="E377" t="s">
         <v>1189</v>
       </c>
-      <c r="F377" s="1">
+      <c r="F377" s="2">
         <v>46154</v>
       </c>
       <c r="G377" t="s">
@@ -19060,7 +19086,7 @@
       <c r="K377" t="s">
         <v>1360</v>
       </c>
-      <c r="N377" s="1">
+      <c r="N377" s="2">
         <v>46176</v>
       </c>
       <c r="O377" t="s">
@@ -19089,7 +19115,7 @@
       <c r="E378" t="s">
         <v>1190</v>
       </c>
-      <c r="F378" s="1">
+      <c r="F378" s="2">
         <v>46154</v>
       </c>
       <c r="G378" t="s">
@@ -19127,7 +19153,7 @@
       <c r="E379" t="s">
         <v>1191</v>
       </c>
-      <c r="F379" s="1">
+      <c r="F379" s="2">
         <v>46154</v>
       </c>
       <c r="G379" t="s">
@@ -19148,7 +19174,7 @@
       <c r="L379" t="s">
         <v>1442</v>
       </c>
-      <c r="N379" s="1">
+      <c r="N379" s="2">
         <v>46174</v>
       </c>
       <c r="Q379" t="b">
@@ -19171,7 +19197,7 @@
       <c r="E380" t="s">
         <v>1192</v>
       </c>
-      <c r="F380" s="1">
+      <c r="F380" s="2">
         <v>46154</v>
       </c>
       <c r="G380" t="s">
@@ -19192,7 +19218,7 @@
       <c r="L380" t="s">
         <v>1443</v>
       </c>
-      <c r="N380" s="1">
+      <c r="N380" s="2">
         <v>46248</v>
       </c>
       <c r="Q380" t="b">
@@ -19215,7 +19241,7 @@
       <c r="E381" t="s">
         <v>1193</v>
       </c>
-      <c r="F381" s="1">
+      <c r="F381" s="2">
         <v>46154</v>
       </c>
       <c r="G381" t="s">
@@ -19253,7 +19279,7 @@
       <c r="E382" t="s">
         <v>1194</v>
       </c>
-      <c r="F382" s="1">
+      <c r="F382" s="2">
         <v>46154</v>
       </c>
       <c r="G382" t="s">
@@ -19291,7 +19317,7 @@
       <c r="E383" t="s">
         <v>1195</v>
       </c>
-      <c r="F383" s="1">
+      <c r="F383" s="2">
         <v>46154</v>
       </c>
       <c r="G383" t="s">
@@ -19312,7 +19338,7 @@
       <c r="L383" t="s">
         <v>1444</v>
       </c>
-      <c r="N383" s="1">
+      <c r="N383" s="2">
         <v>46225</v>
       </c>
       <c r="Q383" t="b">
@@ -19335,7 +19361,7 @@
       <c r="E384" t="s">
         <v>1196</v>
       </c>
-      <c r="F384" s="1">
+      <c r="F384" s="2">
         <v>46164</v>
       </c>
       <c r="G384" t="s">
@@ -19373,7 +19399,7 @@
       <c r="E385" t="s">
         <v>1197</v>
       </c>
-      <c r="F385" s="1">
+      <c r="F385" s="2">
         <v>46164</v>
       </c>
       <c r="G385" t="s">
@@ -19394,7 +19420,7 @@
       <c r="L385" t="s">
         <v>1445</v>
       </c>
-      <c r="N385" s="1">
+      <c r="N385" s="2">
         <v>46266</v>
       </c>
       <c r="P385" t="s">
@@ -19420,7 +19446,7 @@
       <c r="E386" t="s">
         <v>1198</v>
       </c>
-      <c r="F386" s="1">
+      <c r="F386" s="2">
         <v>46171</v>
       </c>
       <c r="G386" t="s">
@@ -19458,7 +19484,7 @@
       <c r="E387" t="s">
         <v>1199</v>
       </c>
-      <c r="F387" s="1">
+      <c r="F387" s="2">
         <v>46171</v>
       </c>
       <c r="G387" t="s">
@@ -19496,7 +19522,7 @@
       <c r="E388" t="s">
         <v>851</v>
       </c>
-      <c r="F388" s="1">
+      <c r="F388" s="2">
         <v>46171</v>
       </c>
       <c r="G388" t="s">
@@ -19517,7 +19543,7 @@
       <c r="L388" t="s">
         <v>1446</v>
       </c>
-      <c r="N388" s="1">
+      <c r="N388" s="2">
         <v>46086</v>
       </c>
       <c r="Q388" t="b">
@@ -19540,7 +19566,7 @@
       <c r="E389" t="s">
         <v>1200</v>
       </c>
-      <c r="F389" s="1">
+      <c r="F389" s="2">
         <v>46171</v>
       </c>
       <c r="G389" t="s">
@@ -19578,7 +19604,7 @@
       <c r="E390" t="s">
         <v>1201</v>
       </c>
-      <c r="F390" s="1">
+      <c r="F390" s="2">
         <v>46171</v>
       </c>
       <c r="G390" t="s">
@@ -19596,7 +19622,7 @@
       <c r="L390" t="s">
         <v>1447</v>
       </c>
-      <c r="N390" s="1">
+      <c r="N390" s="2">
         <v>46191</v>
       </c>
       <c r="P390" t="s">
@@ -19622,7 +19648,7 @@
       <c r="E391" t="s">
         <v>1202</v>
       </c>
-      <c r="F391" s="1">
+      <c r="F391" s="2">
         <v>46171</v>
       </c>
       <c r="G391" t="s">
@@ -19660,7 +19686,7 @@
       <c r="E392" t="s">
         <v>1203</v>
       </c>
-      <c r="F392" s="1">
+      <c r="F392" s="2">
         <v>46171</v>
       </c>
       <c r="G392" t="s">
@@ -19675,7 +19701,7 @@
       <c r="L392" t="s">
         <v>1439</v>
       </c>
-      <c r="N392" s="1">
+      <c r="N392" s="2">
         <v>46176</v>
       </c>
       <c r="Q392" t="b">
@@ -19698,7 +19724,7 @@
       <c r="E393" t="s">
         <v>1204</v>
       </c>
-      <c r="F393" s="1">
+      <c r="F393" s="2">
         <v>46171</v>
       </c>
       <c r="G393" t="s">
@@ -19719,7 +19745,7 @@
       <c r="L393" t="s">
         <v>1388</v>
       </c>
-      <c r="N393" s="1">
+      <c r="N393" s="2">
         <v>46191</v>
       </c>
       <c r="Q393" t="b">
@@ -19742,7 +19768,7 @@
       <c r="E394" t="s">
         <v>1205</v>
       </c>
-      <c r="F394" s="1">
+      <c r="F394" s="2">
         <v>46171</v>
       </c>
       <c r="G394" t="s">
@@ -19760,7 +19786,7 @@
       <c r="L394" t="s">
         <v>1448</v>
       </c>
-      <c r="N394" s="1">
+      <c r="N394" s="2">
         <v>46241</v>
       </c>
       <c r="P394" t="s">
@@ -19786,7 +19812,7 @@
       <c r="E395" t="s">
         <v>1206</v>
       </c>
-      <c r="F395" s="1">
+      <c r="F395" s="2">
         <v>46171</v>
       </c>
       <c r="G395" t="s">
@@ -19804,7 +19830,7 @@
       <c r="L395" t="s">
         <v>1449</v>
       </c>
-      <c r="N395" s="1">
+      <c r="N395" s="2">
         <v>46191</v>
       </c>
       <c r="P395" t="s">
@@ -19830,7 +19856,7 @@
       <c r="E396" t="s">
         <v>1207</v>
       </c>
-      <c r="F396" s="1">
+      <c r="F396" s="2">
         <v>46171</v>
       </c>
       <c r="G396" t="s">
@@ -19842,7 +19868,7 @@
       <c r="J396">
         <v>20</v>
       </c>
-      <c r="N396" s="1">
+      <c r="N396" s="2">
         <v>46191</v>
       </c>
       <c r="P396" t="s">
@@ -19868,7 +19894,7 @@
       <c r="E397" t="s">
         <v>1208</v>
       </c>
-      <c r="F397" s="1">
+      <c r="F397" s="2">
         <v>46171</v>
       </c>
       <c r="G397" t="s">
@@ -19886,7 +19912,7 @@
       <c r="L397" t="s">
         <v>1448</v>
       </c>
-      <c r="N397" s="1">
+      <c r="N397" s="2">
         <v>46241</v>
       </c>
       <c r="P397" t="s">
@@ -19912,7 +19938,7 @@
       <c r="E398" t="s">
         <v>1209</v>
       </c>
-      <c r="F398" s="1">
+      <c r="F398" s="2">
         <v>46171</v>
       </c>
       <c r="G398" t="s">
@@ -19930,7 +19956,7 @@
       <c r="L398" t="s">
         <v>1449</v>
       </c>
-      <c r="N398" s="1">
+      <c r="N398" s="2">
         <v>46191</v>
       </c>
       <c r="P398" t="s">
@@ -19956,7 +19982,7 @@
       <c r="E399" t="s">
         <v>987</v>
       </c>
-      <c r="F399" s="1">
+      <c r="F399" s="2">
         <v>46163</v>
       </c>
       <c r="G399" t="s">
@@ -19971,7 +19997,7 @@
       <c r="L399" t="s">
         <v>1450</v>
       </c>
-      <c r="N399" s="1">
+      <c r="N399" s="2">
         <v>46171</v>
       </c>
       <c r="Q399" t="b">
@@ -19994,7 +20020,7 @@
       <c r="E400" t="s">
         <v>1210</v>
       </c>
-      <c r="F400" s="1">
+      <c r="F400" s="2">
         <v>46171</v>
       </c>
       <c r="G400" t="s">
@@ -20032,7 +20058,7 @@
       <c r="E401" t="s">
         <v>1211</v>
       </c>
-      <c r="F401" s="1">
+      <c r="F401" s="2">
         <v>46171</v>
       </c>
       <c r="G401" t="s">
@@ -20044,7 +20070,7 @@
       <c r="J401">
         <v>40</v>
       </c>
-      <c r="N401" s="1">
+      <c r="N401" s="2">
         <v>46211</v>
       </c>
       <c r="P401" t="s">
@@ -20070,7 +20096,7 @@
       <c r="E402" t="s">
         <v>1212</v>
       </c>
-      <c r="F402" s="1">
+      <c r="F402" s="2">
         <v>46171</v>
       </c>
       <c r="G402" t="s">
@@ -20108,7 +20134,7 @@
       <c r="E403" t="s">
         <v>1213</v>
       </c>
-      <c r="F403" s="1">
+      <c r="F403" s="2">
         <v>46171</v>
       </c>
       <c r="G403" t="s">
@@ -20129,7 +20155,7 @@
       <c r="L403" t="s">
         <v>1451</v>
       </c>
-      <c r="N403" s="1">
+      <c r="N403" s="2">
         <v>46254</v>
       </c>
       <c r="Q403" t="b">
@@ -20152,7 +20178,7 @@
       <c r="E404" t="s">
         <v>1214</v>
       </c>
-      <c r="F404" s="1">
+      <c r="F404" s="2">
         <v>46171</v>
       </c>
       <c r="G404" t="s">
@@ -20190,7 +20216,7 @@
       <c r="E405" t="s">
         <v>1215</v>
       </c>
-      <c r="F405" s="1">
+      <c r="F405" s="2">
         <v>46183</v>
       </c>
       <c r="G405" t="s">
@@ -20222,7 +20248,7 @@
       <c r="E406" t="s">
         <v>1216</v>
       </c>
-      <c r="F406" s="1">
+      <c r="F406" s="2">
         <v>46183</v>
       </c>
       <c r="G406" t="s">
@@ -20254,7 +20280,7 @@
       <c r="E407" t="s">
         <v>1217</v>
       </c>
-      <c r="F407" s="1">
+      <c r="F407" s="2">
         <v>46183</v>
       </c>
       <c r="G407" t="s">
@@ -20286,7 +20312,7 @@
       <c r="E408" t="s">
         <v>1218</v>
       </c>
-      <c r="F408" s="1">
+      <c r="F408" s="2">
         <v>46183</v>
       </c>
       <c r="G408" t="s">
@@ -20318,7 +20344,7 @@
       <c r="E409" t="s">
         <v>1219</v>
       </c>
-      <c r="F409" s="1">
+      <c r="F409" s="2">
         <v>46183</v>
       </c>
       <c r="G409" t="s">
@@ -20350,7 +20376,7 @@
       <c r="E410" t="s">
         <v>1220</v>
       </c>
-      <c r="F410" s="1">
+      <c r="F410" s="2">
         <v>46183</v>
       </c>
       <c r="G410" t="s">
@@ -20382,7 +20408,7 @@
       <c r="E411" t="s">
         <v>1221</v>
       </c>
-      <c r="F411" s="1">
+      <c r="F411" s="2">
         <v>46188</v>
       </c>
       <c r="G411" t="s">
@@ -20414,7 +20440,7 @@
       <c r="E412" t="s">
         <v>1222</v>
       </c>
-      <c r="F412" s="1">
+      <c r="F412" s="2">
         <v>46188</v>
       </c>
       <c r="G412" t="s">
@@ -20446,7 +20472,7 @@
       <c r="E413" t="s">
         <v>1223</v>
       </c>
-      <c r="F413" s="1">
+      <c r="F413" s="2">
         <v>46188</v>
       </c>
       <c r="G413" t="s">
@@ -20478,7 +20504,7 @@
       <c r="E414" t="s">
         <v>1224</v>
       </c>
-      <c r="F414" s="1">
+      <c r="F414" s="2">
         <v>46188</v>
       </c>
       <c r="G414" t="s">
@@ -20507,7 +20533,7 @@
       <c r="E415" t="s">
         <v>1060</v>
       </c>
-      <c r="F415" s="1">
+      <c r="F415" s="2">
         <v>46188</v>
       </c>
       <c r="G415" t="s">
@@ -20536,7 +20562,7 @@
       <c r="E416" t="s">
         <v>1225</v>
       </c>
-      <c r="F416" s="1">
+      <c r="F416" s="2">
         <v>46188</v>
       </c>
       <c r="G416" t="s">
@@ -20568,7 +20594,7 @@
       <c r="E417" t="s">
         <v>1226</v>
       </c>
-      <c r="F417" s="1">
+      <c r="F417" s="2">
         <v>46188</v>
       </c>
       <c r="G417" t="s">
@@ -20597,7 +20623,7 @@
       <c r="E418" t="s">
         <v>1227</v>
       </c>
-      <c r="F418" s="1">
+      <c r="F418" s="2">
         <v>46188</v>
       </c>
       <c r="G418" t="s">
@@ -20626,7 +20652,7 @@
       <c r="E419" t="s">
         <v>1228</v>
       </c>
-      <c r="F419" s="1">
+      <c r="F419" s="2">
         <v>46188</v>
       </c>
       <c r="G419" t="s">
@@ -20658,7 +20684,7 @@
       <c r="E420" t="s">
         <v>1229</v>
       </c>
-      <c r="F420" s="1">
+      <c r="F420" s="2">
         <v>46188</v>
       </c>
       <c r="G420" t="s">
@@ -20690,7 +20716,7 @@
       <c r="E421" t="s">
         <v>1230</v>
       </c>
-      <c r="F421" s="1">
+      <c r="F421" s="2">
         <v>46188</v>
       </c>
       <c r="G421" t="s">
@@ -20722,7 +20748,7 @@
       <c r="E422" t="s">
         <v>1231</v>
       </c>
-      <c r="F422" s="1">
+      <c r="F422" s="2">
         <v>46188</v>
       </c>
       <c r="G422" t="s">
@@ -20754,7 +20780,7 @@
       <c r="E423" t="s">
         <v>1232</v>
       </c>
-      <c r="F423" s="1">
+      <c r="F423" s="2">
         <v>46188</v>
       </c>
       <c r="G423" t="s">
@@ -20786,7 +20812,7 @@
       <c r="E424" t="s">
         <v>1233</v>
       </c>
-      <c r="F424" s="1">
+      <c r="F424" s="2">
         <v>46188</v>
       </c>
       <c r="G424" t="s">
@@ -20818,7 +20844,7 @@
       <c r="E425" t="s">
         <v>1234</v>
       </c>
-      <c r="F425" s="1">
+      <c r="F425" s="2">
         <v>46188</v>
       </c>
       <c r="G425" t="s">
@@ -20850,7 +20876,7 @@
       <c r="E426" t="s">
         <v>1235</v>
       </c>
-      <c r="F426" s="1">
+      <c r="F426" s="2">
         <v>46188</v>
       </c>
       <c r="G426" t="s">
@@ -20882,7 +20908,7 @@
       <c r="E427" t="s">
         <v>1236</v>
       </c>
-      <c r="F427" s="1">
+      <c r="F427" s="2">
         <v>46188</v>
       </c>
       <c r="G427" t="s">
@@ -20914,7 +20940,7 @@
       <c r="E428" t="s">
         <v>1237</v>
       </c>
-      <c r="F428" s="1">
+      <c r="F428" s="2">
         <v>46188</v>
       </c>
       <c r="G428" t="s">
@@ -20943,7 +20969,7 @@
       <c r="E429" t="s">
         <v>1238</v>
       </c>
-      <c r="F429" s="1">
+      <c r="F429" s="2">
         <v>46188</v>
       </c>
       <c r="G429" t="s">
@@ -20972,7 +20998,7 @@
       <c r="E430" t="s">
         <v>1239</v>
       </c>
-      <c r="F430" s="1">
+      <c r="F430" s="2">
         <v>46188</v>
       </c>
       <c r="G430" t="s">
@@ -21004,7 +21030,7 @@
       <c r="E431" t="s">
         <v>1240</v>
       </c>
-      <c r="F431" s="1">
+      <c r="F431" s="2">
         <v>46188</v>
       </c>
       <c r="G431" t="s">
@@ -21036,7 +21062,7 @@
       <c r="E432" t="s">
         <v>1241</v>
       </c>
-      <c r="F432" s="1">
+      <c r="F432" s="2">
         <v>46188</v>
       </c>
       <c r="G432" t="s">
@@ -21068,7 +21094,7 @@
       <c r="E433" t="s">
         <v>1242</v>
       </c>
-      <c r="F433" s="1">
+      <c r="F433" s="2">
         <v>46188</v>
       </c>
       <c r="G433" t="s">
@@ -21100,7 +21126,7 @@
       <c r="E434" t="s">
         <v>1243</v>
       </c>
-      <c r="F434" s="1">
+      <c r="F434" s="2">
         <v>46188</v>
       </c>
       <c r="G434" t="s">
@@ -21132,7 +21158,7 @@
       <c r="E435" t="s">
         <v>856</v>
       </c>
-      <c r="F435" s="1">
+      <c r="F435" s="2">
         <v>46188</v>
       </c>
       <c r="G435" t="s">
@@ -21164,7 +21190,7 @@
       <c r="E436" t="s">
         <v>1244</v>
       </c>
-      <c r="F436" s="1">
+      <c r="F436" s="2">
         <v>46188</v>
       </c>
       <c r="G436" t="s">
@@ -21196,7 +21222,7 @@
       <c r="E437" t="s">
         <v>1245</v>
       </c>
-      <c r="F437" s="1">
+      <c r="F437" s="2">
         <v>46188</v>
       </c>
       <c r="G437" t="s">
@@ -21228,7 +21254,7 @@
       <c r="E438" t="s">
         <v>1246</v>
       </c>
-      <c r="F438" s="1">
+      <c r="F438" s="2">
         <v>46188</v>
       </c>
       <c r="G438" t="s">
@@ -21260,7 +21286,7 @@
       <c r="E439" t="s">
         <v>1247</v>
       </c>
-      <c r="F439" s="1">
+      <c r="F439" s="2">
         <v>46196</v>
       </c>
       <c r="G439" t="s">
@@ -21292,7 +21318,7 @@
       <c r="E440" t="s">
         <v>1248</v>
       </c>
-      <c r="F440" s="1">
+      <c r="F440" s="2">
         <v>46196</v>
       </c>
       <c r="G440" t="s">
@@ -21324,7 +21350,7 @@
       <c r="E441" t="s">
         <v>1249</v>
       </c>
-      <c r="F441" s="1">
+      <c r="F441" s="2">
         <v>46203</v>
       </c>
       <c r="G441" t="s">
@@ -21356,7 +21382,7 @@
       <c r="E442" t="s">
         <v>1250</v>
       </c>
-      <c r="F442" s="1">
+      <c r="F442" s="2">
         <v>46203</v>
       </c>
       <c r="G442" t="s">
@@ -21385,7 +21411,7 @@
       <c r="E443" t="s">
         <v>1251</v>
       </c>
-      <c r="F443" s="1">
+      <c r="F443" s="2">
         <v>46205</v>
       </c>
       <c r="G443" t="s">
@@ -21417,7 +21443,7 @@
       <c r="E444" t="s">
         <v>1252</v>
       </c>
-      <c r="F444" s="1">
+      <c r="F444" s="2">
         <v>46205</v>
       </c>
       <c r="G444" t="s">
@@ -21446,7 +21472,7 @@
       <c r="E445" t="s">
         <v>1253</v>
       </c>
-      <c r="F445" s="1">
+      <c r="F445" s="2">
         <v>46205</v>
       </c>
       <c r="G445" t="s">
@@ -21475,7 +21501,7 @@
       <c r="E446" t="s">
         <v>1254</v>
       </c>
-      <c r="F446" s="1">
+      <c r="F446" s="2">
         <v>46211</v>
       </c>
       <c r="G446" t="s">
@@ -21507,7 +21533,7 @@
       <c r="E447" t="s">
         <v>1255</v>
       </c>
-      <c r="F447" s="1">
+      <c r="F447" s="2">
         <v>46211</v>
       </c>
       <c r="G447" t="s">
@@ -21539,7 +21565,7 @@
       <c r="E448" t="s">
         <v>1256</v>
       </c>
-      <c r="F448" s="1">
+      <c r="F448" s="2">
         <v>46226</v>
       </c>
       <c r="G448" t="s">
@@ -21571,7 +21597,7 @@
       <c r="E449" t="s">
         <v>1257</v>
       </c>
-      <c r="F449" s="1">
+      <c r="F449" s="2">
         <v>46226</v>
       </c>
       <c r="G449" t="s">
@@ -21603,7 +21629,7 @@
       <c r="E450" t="s">
         <v>1258</v>
       </c>
-      <c r="F450" s="1">
+      <c r="F450" s="2">
         <v>46226</v>
       </c>
       <c r="G450" t="s">
@@ -21635,7 +21661,7 @@
       <c r="E451" t="s">
         <v>1035</v>
       </c>
-      <c r="F451" s="1">
+      <c r="F451" s="2">
         <v>46230</v>
       </c>
       <c r="G451" t="s">
@@ -21667,7 +21693,7 @@
       <c r="E452" t="s">
         <v>1259</v>
       </c>
-      <c r="F452" s="1">
+      <c r="F452" s="2">
         <v>46230</v>
       </c>
       <c r="G452" t="s">
@@ -21699,7 +21725,7 @@
       <c r="E453" t="s">
         <v>1260</v>
       </c>
-      <c r="F453" s="1">
+      <c r="F453" s="2">
         <v>46230</v>
       </c>
       <c r="G453" t="s">
@@ -21731,7 +21757,7 @@
       <c r="E454" t="s">
         <v>1261</v>
       </c>
-      <c r="F454" s="1">
+      <c r="F454" s="2">
         <v>46230</v>
       </c>
       <c r="G454" t="s">
@@ -21763,7 +21789,7 @@
       <c r="E455" t="s">
         <v>1262</v>
       </c>
-      <c r="F455" s="1">
+      <c r="F455" s="2">
         <v>46230</v>
       </c>
       <c r="G455" t="s">
@@ -21795,7 +21821,7 @@
       <c r="E456" t="s">
         <v>1263</v>
       </c>
-      <c r="F456" s="1">
+      <c r="F456" s="2">
         <v>46230</v>
       </c>
       <c r="G456" t="s">
@@ -21827,7 +21853,7 @@
       <c r="E457" t="s">
         <v>1264</v>
       </c>
-      <c r="F457" s="1">
+      <c r="F457" s="2">
         <v>46230</v>
       </c>
       <c r="G457" t="s">
@@ -21859,7 +21885,7 @@
       <c r="E458" t="s">
         <v>1202</v>
       </c>
-      <c r="F458" s="1">
+      <c r="F458" s="2">
         <v>46231</v>
       </c>
       <c r="G458" t="s">
@@ -21891,7 +21917,7 @@
       <c r="E459" t="s">
         <v>1265</v>
       </c>
-      <c r="F459" s="1">
+      <c r="F459" s="2">
         <v>46233</v>
       </c>
       <c r="G459" t="s">
@@ -21923,7 +21949,7 @@
       <c r="E460" t="s">
         <v>1266</v>
       </c>
-      <c r="F460" s="1">
+      <c r="F460" s="2">
         <v>46233</v>
       </c>
       <c r="G460" t="s">
@@ -21955,7 +21981,7 @@
       <c r="E461" t="s">
         <v>1267</v>
       </c>
-      <c r="F461" s="1">
+      <c r="F461" s="2">
         <v>46233</v>
       </c>
       <c r="G461" t="s">
@@ -21987,7 +22013,7 @@
       <c r="E462" t="s">
         <v>1268</v>
       </c>
-      <c r="F462" s="1">
+      <c r="F462" s="2">
         <v>46233</v>
       </c>
       <c r="G462" t="s">
@@ -22019,7 +22045,7 @@
       <c r="E463" t="s">
         <v>1269</v>
       </c>
-      <c r="F463" s="1">
+      <c r="F463" s="2">
         <v>46234</v>
       </c>
       <c r="G463" t="s">
@@ -22051,7 +22077,7 @@
       <c r="E464" t="s">
         <v>1270</v>
       </c>
-      <c r="F464" s="1">
+      <c r="F464" s="2">
         <v>46230</v>
       </c>
       <c r="G464" t="s">
@@ -22083,7 +22109,7 @@
       <c r="E465" t="s">
         <v>1271</v>
       </c>
-      <c r="F465" s="1">
+      <c r="F465" s="2">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
@@ -22115,7 +22141,7 @@
       <c r="E466" t="s">
         <v>1272</v>
       </c>
-      <c r="F466" s="1">
+      <c r="F466" s="2">
         <v>46230</v>
       </c>
       <c r="G466" t="s">
@@ -22147,7 +22173,7 @@
       <c r="E467" t="s">
         <v>1273</v>
       </c>
-      <c r="F467" s="1">
+      <c r="F467" s="2">
         <v>46230</v>
       </c>
       <c r="G467" t="s">
@@ -22179,7 +22205,7 @@
       <c r="E468" t="s">
         <v>1274</v>
       </c>
-      <c r="F468" s="1">
+      <c r="F468" s="2">
         <v>46230</v>
       </c>
       <c r="G468" t="s">
@@ -22211,7 +22237,7 @@
       <c r="E469" t="s">
         <v>1275</v>
       </c>
-      <c r="F469" s="1">
+      <c r="F469" s="2">
         <v>46230</v>
       </c>
       <c r="G469" t="s">
@@ -22243,7 +22269,7 @@
       <c r="E470" t="s">
         <v>1276</v>
       </c>
-      <c r="F470" s="1">
+      <c r="F470" s="2">
         <v>46230</v>
       </c>
       <c r="G470" t="s">
@@ -22272,7 +22298,7 @@
       <c r="E471" t="s">
         <v>1277</v>
       </c>
-      <c r="F471" s="1">
+      <c r="F471" s="2">
         <v>46230</v>
       </c>
       <c r="G471" t="s">
@@ -22304,7 +22330,7 @@
       <c r="E472" t="s">
         <v>1278</v>
       </c>
-      <c r="F472" s="1">
+      <c r="F472" s="2">
         <v>46230</v>
       </c>
       <c r="G472" t="s">
@@ -22336,7 +22362,7 @@
       <c r="E473" t="s">
         <v>1279</v>
       </c>
-      <c r="F473" s="1">
+      <c r="F473" s="2">
         <v>46230</v>
       </c>
       <c r="G473" t="s">
@@ -22368,7 +22394,7 @@
       <c r="E474" t="s">
         <v>1280</v>
       </c>
-      <c r="F474" s="1">
+      <c r="F474" s="2">
         <v>46231</v>
       </c>
       <c r="G474" t="s">
@@ -22400,7 +22426,7 @@
       <c r="E475" t="s">
         <v>1281</v>
       </c>
-      <c r="F475" s="1">
+      <c r="F475" s="2">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
@@ -22432,7 +22458,7 @@
       <c r="E476" t="s">
         <v>1282</v>
       </c>
-      <c r="F476" s="1">
+      <c r="F476" s="2">
         <v>46231</v>
       </c>
       <c r="G476" t="s">
@@ -22464,7 +22490,7 @@
       <c r="E477" t="s">
         <v>1283</v>
       </c>
-      <c r="F477" s="1">
+      <c r="F477" s="2">
         <v>46231</v>
       </c>
       <c r="G477" t="s">
@@ -22496,7 +22522,7 @@
       <c r="E478" t="s">
         <v>1284</v>
       </c>
-      <c r="F478" s="1">
+      <c r="F478" s="2">
         <v>46231</v>
       </c>
       <c r="G478" t="s">
@@ -22528,7 +22554,7 @@
       <c r="E479" t="s">
         <v>1285</v>
       </c>
-      <c r="F479" s="1">
+      <c r="F479" s="2">
         <v>46231</v>
       </c>
       <c r="G479" t="s">
@@ -22560,7 +22586,7 @@
       <c r="E480" t="s">
         <v>1286</v>
       </c>
-      <c r="F480" s="1">
+      <c r="F480" s="2">
         <v>46231</v>
       </c>
       <c r="G480" t="s">
@@ -22592,7 +22618,7 @@
       <c r="E481" t="s">
         <v>1287</v>
       </c>
-      <c r="F481" s="1">
+      <c r="F481" s="2">
         <v>46231</v>
       </c>
       <c r="G481" t="s">
@@ -22624,7 +22650,7 @@
       <c r="E482" t="s">
         <v>1288</v>
       </c>
-      <c r="F482" s="1">
+      <c r="F482" s="2">
         <v>46231</v>
       </c>
       <c r="G482" t="s">
@@ -22656,7 +22682,7 @@
       <c r="E483" t="s">
         <v>1289</v>
       </c>
-      <c r="F483" s="1">
+      <c r="F483" s="2">
         <v>46231</v>
       </c>
       <c r="G483" t="s">
@@ -22688,7 +22714,7 @@
       <c r="E484" t="s">
         <v>1290</v>
       </c>
-      <c r="F484" s="1">
+      <c r="F484" s="2">
         <v>46231</v>
       </c>
       <c r="G484" t="s">
@@ -22720,7 +22746,7 @@
       <c r="E485" t="s">
         <v>1291</v>
       </c>
-      <c r="F485" s="1">
+      <c r="F485" s="2">
         <v>46231</v>
       </c>
       <c r="G485" t="s">
@@ -22752,7 +22778,7 @@
       <c r="E486" t="s">
         <v>1292</v>
       </c>
-      <c r="F486" s="1">
+      <c r="F486" s="2">
         <v>46231</v>
       </c>
       <c r="G486" t="s">
@@ -22784,7 +22810,7 @@
       <c r="E487" t="s">
         <v>1293</v>
       </c>
-      <c r="F487" s="1">
+      <c r="F487" s="2">
         <v>46231</v>
       </c>
       <c r="G487" t="s">
@@ -22816,7 +22842,7 @@
       <c r="E488" t="s">
         <v>1294</v>
       </c>
-      <c r="F488" s="1">
+      <c r="F488" s="2">
         <v>46231</v>
       </c>
       <c r="G488" t="s">
@@ -22848,7 +22874,7 @@
       <c r="E489" t="s">
         <v>1295</v>
       </c>
-      <c r="F489" s="1">
+      <c r="F489" s="2">
         <v>46231</v>
       </c>
       <c r="G489" t="s">
@@ -22880,7 +22906,7 @@
       <c r="E490" t="s">
         <v>1296</v>
       </c>
-      <c r="F490" s="1">
+      <c r="F490" s="2">
         <v>46231</v>
       </c>
       <c r="G490" t="s">
@@ -22912,7 +22938,7 @@
       <c r="E491" t="s">
         <v>1297</v>
       </c>
-      <c r="F491" s="1">
+      <c r="F491" s="2">
         <v>46231</v>
       </c>
       <c r="G491" t="s">
@@ -22944,7 +22970,7 @@
       <c r="E492" t="s">
         <v>911</v>
       </c>
-      <c r="F492" s="1">
+      <c r="F492" s="2">
         <v>46231</v>
       </c>
       <c r="G492" t="s">
@@ -22976,7 +23002,7 @@
       <c r="E493" t="s">
         <v>995</v>
       </c>
-      <c r="F493" s="1">
+      <c r="F493" s="2">
         <v>46231</v>
       </c>
       <c r="G493" t="s">
@@ -23008,7 +23034,7 @@
       <c r="E494" t="s">
         <v>867</v>
       </c>
-      <c r="F494" s="1">
+      <c r="F494" s="2">
         <v>46231</v>
       </c>
       <c r="G494" t="s">
@@ -23040,7 +23066,7 @@
       <c r="E495" t="s">
         <v>912</v>
       </c>
-      <c r="F495" s="1">
+      <c r="F495" s="2">
         <v>46231</v>
       </c>
       <c r="G495" t="s">
@@ -23072,7 +23098,7 @@
       <c r="E496" t="s">
         <v>1048</v>
       </c>
-      <c r="F496" s="1">
+      <c r="F496" s="2">
         <v>46231</v>
       </c>
       <c r="G496" t="s">
@@ -23104,7 +23130,7 @@
       <c r="E497" t="s">
         <v>1298</v>
       </c>
-      <c r="F497" s="1">
+      <c r="F497" s="2">
         <v>46231</v>
       </c>
       <c r="G497" t="s">
@@ -23136,7 +23162,7 @@
       <c r="E498" t="s">
         <v>1299</v>
       </c>
-      <c r="F498" s="1">
+      <c r="F498" s="2">
         <v>46231</v>
       </c>
       <c r="G498" t="s">
@@ -23168,7 +23194,7 @@
       <c r="E499" t="s">
         <v>1300</v>
       </c>
-      <c r="F499" s="1">
+      <c r="F499" s="2">
         <v>46231</v>
       </c>
       <c r="G499" t="s">
@@ -23200,7 +23226,7 @@
       <c r="E500" t="s">
         <v>1301</v>
       </c>
-      <c r="F500" s="1">
+      <c r="F500" s="2">
         <v>46231</v>
       </c>
       <c r="G500" t="s">
@@ -23232,7 +23258,7 @@
       <c r="E501" t="s">
         <v>1302</v>
       </c>
-      <c r="F501" s="1">
+      <c r="F501" s="2">
         <v>46231</v>
       </c>
       <c r="G501" t="s">
@@ -23264,7 +23290,7 @@
       <c r="E502" t="s">
         <v>1303</v>
       </c>
-      <c r="F502" s="1">
+      <c r="F502" s="2">
         <v>46231</v>
       </c>
       <c r="G502" t="s">
@@ -23296,7 +23322,7 @@
       <c r="E503" t="s">
         <v>1304</v>
       </c>
-      <c r="F503" s="1">
+      <c r="F503" s="2">
         <v>46231</v>
       </c>
       <c r="G503" t="s">
@@ -23328,7 +23354,7 @@
       <c r="E504" t="s">
         <v>1305</v>
       </c>
-      <c r="F504" s="1">
+      <c r="F504" s="2">
         <v>46232</v>
       </c>
       <c r="G504" t="s">
@@ -23360,7 +23386,7 @@
       <c r="E505" t="s">
         <v>1306</v>
       </c>
-      <c r="F505" s="1">
+      <c r="F505" s="2">
         <v>46232</v>
       </c>
       <c r="G505" t="s">
@@ -23392,7 +23418,7 @@
       <c r="E506" t="s">
         <v>1307</v>
       </c>
-      <c r="F506" s="1">
+      <c r="F506" s="2">
         <v>46232</v>
       </c>
       <c r="G506" t="s">
@@ -23424,7 +23450,7 @@
       <c r="E507" t="s">
         <v>1308</v>
       </c>
-      <c r="F507" s="1">
+      <c r="F507" s="2">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
@@ -23456,7 +23482,7 @@
       <c r="E508" t="s">
         <v>1309</v>
       </c>
-      <c r="F508" s="1">
+      <c r="F508" s="2">
         <v>46237</v>
       </c>
       <c r="G508" t="s">
@@ -23485,7 +23511,7 @@
       <c r="E509" t="s">
         <v>1310</v>
       </c>
-      <c r="F509" s="1">
+      <c r="F509" s="2">
         <v>46237</v>
       </c>
       <c r="G509" t="s">
@@ -23517,7 +23543,7 @@
       <c r="E510" t="s">
         <v>1311</v>
       </c>
-      <c r="F510" s="1">
+      <c r="F510" s="2">
         <v>46237</v>
       </c>
       <c r="G510" t="s">
@@ -23549,7 +23575,7 @@
       <c r="E511" t="s">
         <v>1312</v>
       </c>
-      <c r="F511" s="1">
+      <c r="F511" s="2">
         <v>46240</v>
       </c>
       <c r="G511" t="s">
@@ -23581,7 +23607,7 @@
       <c r="E512" t="s">
         <v>1313</v>
       </c>
-      <c r="F512" s="1">
+      <c r="F512" s="2">
         <v>46240</v>
       </c>
       <c r="G512" t="s">
@@ -23613,7 +23639,7 @@
       <c r="E513" t="s">
         <v>1314</v>
       </c>
-      <c r="F513" s="1">
+      <c r="F513" s="2">
         <v>46244</v>
       </c>
       <c r="G513" t="s">
@@ -23645,7 +23671,7 @@
       <c r="E514" t="s">
         <v>1315</v>
       </c>
-      <c r="F514" s="1">
+      <c r="F514" s="2">
         <v>46244</v>
       </c>
       <c r="G514" t="s">
@@ -23677,7 +23703,7 @@
       <c r="E515" t="s">
         <v>1043</v>
       </c>
-      <c r="F515" s="1">
+      <c r="F515" s="2">
         <v>46244</v>
       </c>
       <c r="G515" t="s">
@@ -23709,7 +23735,7 @@
       <c r="E516" t="s">
         <v>1316</v>
       </c>
-      <c r="F516" s="1">
+      <c r="F516" s="2">
         <v>46252</v>
       </c>
       <c r="G516" t="s">
@@ -23741,7 +23767,7 @@
       <c r="E517" t="s">
         <v>1317</v>
       </c>
-      <c r="F517" s="1">
+      <c r="F517" s="2">
         <v>46252</v>
       </c>
       <c r="G517" t="s">
@@ -23773,7 +23799,7 @@
       <c r="E518" t="s">
         <v>1318</v>
       </c>
-      <c r="F518" s="1">
+      <c r="F518" s="2">
         <v>46252</v>
       </c>
       <c r="G518" t="s">
@@ -23805,7 +23831,7 @@
       <c r="E519" t="s">
         <v>1253</v>
       </c>
-      <c r="F519" s="1">
+      <c r="F519" s="2">
         <v>46254</v>
       </c>
       <c r="G519" t="s">
@@ -23837,7 +23863,7 @@
       <c r="E520" t="s">
         <v>1319</v>
       </c>
-      <c r="F520" s="1">
+      <c r="F520" s="2">
         <v>46254</v>
       </c>
       <c r="G520" t="s">
@@ -23869,7 +23895,7 @@
       <c r="E521" t="s">
         <v>1320</v>
       </c>
-      <c r="F521" s="1">
+      <c r="F521" s="2">
         <v>46254</v>
       </c>
       <c r="G521" t="s">
@@ -23901,7 +23927,7 @@
       <c r="E522" t="s">
         <v>1253</v>
       </c>
-      <c r="F522" s="1">
+      <c r="F522" s="2">
         <v>46254</v>
       </c>
       <c r="G522" t="s">
@@ -23933,7 +23959,7 @@
       <c r="E523" t="s">
         <v>1319</v>
       </c>
-      <c r="F523" s="1">
+      <c r="F523" s="2">
         <v>46254</v>
       </c>
       <c r="G523" t="s">
@@ -23965,7 +23991,7 @@
       <c r="E524" t="s">
         <v>1321</v>
       </c>
-      <c r="F524" s="1">
+      <c r="F524" s="2">
         <v>46265</v>
       </c>
       <c r="G524" t="s">
@@ -23997,7 +24023,7 @@
       <c r="E525" t="s">
         <v>1322</v>
       </c>
-      <c r="F525" s="1">
+      <c r="F525" s="2">
         <v>46265</v>
       </c>
       <c r="G525" t="s">
@@ -24029,7 +24055,7 @@
       <c r="E526" t="s">
         <v>1323</v>
       </c>
-      <c r="F526" s="1">
+      <c r="F526" s="2">
         <v>46265</v>
       </c>
       <c r="G526" t="s">
@@ -24061,7 +24087,7 @@
       <c r="E527" t="s">
         <v>1324</v>
       </c>
-      <c r="F527" s="1">
+      <c r="F527" s="2">
         <v>46265</v>
       </c>
       <c r="G527" t="s">

--- a/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4199" uniqueCount="1501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4200" uniqueCount="1502">
   <si>
     <t>os</t>
   </si>
@@ -4490,6 +4490,9 @@
   </si>
   <si>
     <t>026/2026</t>
+  </si>
+  <si>
+    <t>023/2026</t>
   </si>
   <si>
     <t>001/2026</t>
@@ -4526,16 +4529,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -4551,7 +4546,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -4559,30 +4554,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4882,55 +4859,55 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4950,7 +4927,7 @@
       <c r="E2" t="s">
         <v>829</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>45698</v>
       </c>
       <c r="G2" t="s">
@@ -4960,7 +4937,7 @@
         <v>1353</v>
       </c>
       <c r="I2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="K2" t="s">
         <v>1356</v>
@@ -4988,7 +4965,7 @@
       <c r="E3" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>45714</v>
       </c>
       <c r="G3" t="s">
@@ -4998,7 +4975,7 @@
         <v>1353</v>
       </c>
       <c r="I3">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K3" t="s">
         <v>1357</v>
@@ -5026,7 +5003,7 @@
       <c r="E4" t="s">
         <v>831</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>45714</v>
       </c>
       <c r="G4" t="s">
@@ -5036,7 +5013,7 @@
         <v>1353</v>
       </c>
       <c r="I4">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K4" t="s">
         <v>1357</v>
@@ -5064,7 +5041,7 @@
       <c r="E5" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>45714</v>
       </c>
       <c r="G5" t="s">
@@ -5074,7 +5051,7 @@
         <v>1353</v>
       </c>
       <c r="I5">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="J5">
         <v>279</v>
@@ -5085,7 +5062,7 @@
       <c r="L5" t="s">
         <v>1367</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="1">
         <v>45993</v>
       </c>
       <c r="Q5" t="b">
@@ -5108,7 +5085,7 @@
       <c r="E6" t="s">
         <v>833</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>45736</v>
       </c>
       <c r="G6" t="s">
@@ -5118,7 +5095,7 @@
         <v>1353</v>
       </c>
       <c r="I6">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J6">
         <v>153</v>
@@ -5129,7 +5106,7 @@
       <c r="L6" t="s">
         <v>1368</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="1">
         <v>45889</v>
       </c>
       <c r="Q6" t="b">
@@ -5152,7 +5129,7 @@
       <c r="E7" t="s">
         <v>834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>45736</v>
       </c>
       <c r="G7" t="s">
@@ -5162,7 +5139,7 @@
         <v>1353</v>
       </c>
       <c r="I7">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J7">
         <v>112</v>
@@ -5173,7 +5150,7 @@
       <c r="L7" t="s">
         <v>1369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="1">
         <v>45848</v>
       </c>
       <c r="O7" t="s">
@@ -5199,7 +5176,7 @@
       <c r="E8" t="s">
         <v>835</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>45736</v>
       </c>
       <c r="G8" t="s">
@@ -5228,7 +5205,7 @@
       <c r="E9" t="s">
         <v>836</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>45736</v>
       </c>
       <c r="G9" t="s">
@@ -5238,7 +5215,7 @@
         <v>1353</v>
       </c>
       <c r="I9">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J9">
         <v>362</v>
@@ -5249,7 +5226,7 @@
       <c r="L9" t="s">
         <v>1370</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="1">
         <v>46098</v>
       </c>
       <c r="O9">
@@ -5275,7 +5252,7 @@
       <c r="E10" t="s">
         <v>837</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>45736</v>
       </c>
       <c r="G10" t="s">
@@ -5285,7 +5262,7 @@
         <v>1353</v>
       </c>
       <c r="I10">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J10">
         <v>378</v>
@@ -5296,7 +5273,7 @@
       <c r="L10" t="s">
         <v>1371</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="1">
         <v>46114</v>
       </c>
       <c r="O10" t="s">
@@ -5322,7 +5299,7 @@
       <c r="E11" t="s">
         <v>838</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>45736</v>
       </c>
       <c r="G11" t="s">
@@ -5332,7 +5309,7 @@
         <v>1353</v>
       </c>
       <c r="I11">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J11">
         <v>112</v>
@@ -5343,7 +5320,7 @@
       <c r="L11" t="s">
         <v>1369</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="1">
         <v>45848</v>
       </c>
       <c r="O11" t="s">
@@ -5369,7 +5346,7 @@
       <c r="E12" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>45736</v>
       </c>
       <c r="G12" t="s">
@@ -5379,7 +5356,7 @@
         <v>1353</v>
       </c>
       <c r="I12">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J12">
         <v>124</v>
@@ -5390,7 +5367,7 @@
       <c r="L12" t="s">
         <v>1372</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="1">
         <v>45860</v>
       </c>
       <c r="Q12" t="b">
@@ -5413,7 +5390,7 @@
       <c r="E13" t="s">
         <v>840</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>45736</v>
       </c>
       <c r="G13" t="s">
@@ -5442,7 +5419,7 @@
       <c r="E14" t="s">
         <v>841</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>45736</v>
       </c>
       <c r="G14" t="s">
@@ -5452,7 +5429,7 @@
         <v>1353</v>
       </c>
       <c r="I14">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J14">
         <v>64</v>
@@ -5463,7 +5440,7 @@
       <c r="L14" t="s">
         <v>1373</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="1">
         <v>45800</v>
       </c>
       <c r="Q14" t="b">
@@ -5486,7 +5463,7 @@
       <c r="E15" t="s">
         <v>842</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>45736</v>
       </c>
       <c r="G15" t="s">
@@ -5496,7 +5473,7 @@
         <v>1353</v>
       </c>
       <c r="I15">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K15" t="s">
         <v>1359</v>
@@ -5524,7 +5501,7 @@
       <c r="E16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>45736</v>
       </c>
       <c r="G16" t="s">
@@ -5534,7 +5511,7 @@
         <v>1353</v>
       </c>
       <c r="I16">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K16" t="s">
         <v>1356</v>
@@ -5562,7 +5539,7 @@
       <c r="E17" t="s">
         <v>844</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>45736</v>
       </c>
       <c r="G17" t="s">
@@ -5572,7 +5549,7 @@
         <v>1353</v>
       </c>
       <c r="I17">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J17">
         <v>161</v>
@@ -5583,7 +5560,7 @@
       <c r="L17" t="s">
         <v>1368</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="1">
         <v>45897</v>
       </c>
       <c r="Q17" t="b">
@@ -5606,7 +5583,7 @@
       <c r="E18" t="s">
         <v>845</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="1">
         <v>45736</v>
       </c>
       <c r="G18" t="s">
@@ -5616,7 +5593,7 @@
         <v>1353</v>
       </c>
       <c r="I18">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J18">
         <v>66</v>
@@ -5627,7 +5604,7 @@
       <c r="L18" t="s">
         <v>1373</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" s="1">
         <v>45802</v>
       </c>
       <c r="Q18" t="b">
@@ -5650,7 +5627,7 @@
       <c r="E19" t="s">
         <v>846</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="1">
         <v>45736</v>
       </c>
       <c r="G19" t="s">
@@ -5679,7 +5656,7 @@
       <c r="E20" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="1">
         <v>45736</v>
       </c>
       <c r="G20" t="s">
@@ -5689,7 +5666,7 @@
         <v>1353</v>
       </c>
       <c r="I20">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J20">
         <v>399</v>
@@ -5700,7 +5677,7 @@
       <c r="L20" t="s">
         <v>1374</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20" s="1">
         <v>46135</v>
       </c>
       <c r="Q20" t="b">
@@ -5723,7 +5700,7 @@
       <c r="E21" t="s">
         <v>848</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="1">
         <v>45736</v>
       </c>
       <c r="G21" t="s">
@@ -5752,7 +5729,7 @@
       <c r="E22" t="s">
         <v>849</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="1">
         <v>45736</v>
       </c>
       <c r="G22" t="s">
@@ -5762,7 +5739,7 @@
         <v>1353</v>
       </c>
       <c r="I22">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K22" t="s">
         <v>1360</v>
@@ -5790,7 +5767,7 @@
       <c r="E23" t="s">
         <v>850</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="1">
         <v>45736</v>
       </c>
       <c r="G23" t="s">
@@ -5800,7 +5777,7 @@
         <v>1353</v>
       </c>
       <c r="I23">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J23">
         <v>229</v>
@@ -5811,7 +5788,7 @@
       <c r="L23" t="s">
         <v>1375</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="1">
         <v>45965</v>
       </c>
       <c r="P23" t="s">
@@ -5837,7 +5814,7 @@
       <c r="E24" t="s">
         <v>851</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="1">
         <v>45736</v>
       </c>
       <c r="G24" t="s">
@@ -5866,7 +5843,7 @@
       <c r="E25" t="s">
         <v>852</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="1">
         <v>45736</v>
       </c>
       <c r="G25" t="s">
@@ -5895,7 +5872,7 @@
       <c r="E26" t="s">
         <v>853</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="1">
         <v>45736</v>
       </c>
       <c r="G26" t="s">
@@ -5905,7 +5882,7 @@
         <v>1353</v>
       </c>
       <c r="I26">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J26">
         <v>155</v>
@@ -5916,7 +5893,7 @@
       <c r="L26" t="s">
         <v>1376</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" s="1">
         <v>45891</v>
       </c>
       <c r="P26" t="s">
@@ -5942,7 +5919,7 @@
       <c r="E27" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="1">
         <v>45736</v>
       </c>
       <c r="G27" t="s">
@@ -5952,7 +5929,7 @@
         <v>1353</v>
       </c>
       <c r="I27">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K27" t="s">
         <v>1360</v>
@@ -5980,7 +5957,7 @@
       <c r="E28" t="s">
         <v>855</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="1">
         <v>45736</v>
       </c>
       <c r="G28" t="s">
@@ -6009,7 +5986,7 @@
       <c r="E29" t="s">
         <v>856</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="1">
         <v>45736</v>
       </c>
       <c r="G29" t="s">
@@ -6038,7 +6015,7 @@
       <c r="E30" t="s">
         <v>857</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="1">
         <v>45736</v>
       </c>
       <c r="G30" t="s">
@@ -6048,7 +6025,7 @@
         <v>1353</v>
       </c>
       <c r="I30">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J30">
         <v>209</v>
@@ -6059,7 +6036,7 @@
       <c r="L30" t="s">
         <v>1377</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" s="1">
         <v>45945</v>
       </c>
       <c r="Q30" t="b">
@@ -6082,7 +6059,7 @@
       <c r="E31" t="s">
         <v>858</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="1">
         <v>45736</v>
       </c>
       <c r="G31" t="s">
@@ -6111,7 +6088,7 @@
       <c r="E32" t="s">
         <v>859</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="1">
         <v>45736</v>
       </c>
       <c r="G32" t="s">
@@ -6121,7 +6098,7 @@
         <v>1353</v>
       </c>
       <c r="I32">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K32" t="s">
         <v>1356</v>
@@ -6149,7 +6126,7 @@
       <c r="E33" t="s">
         <v>860</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>45736</v>
       </c>
       <c r="G33" t="s">
@@ -6178,7 +6155,7 @@
       <c r="E34" t="s">
         <v>861</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="1">
         <v>45736</v>
       </c>
       <c r="G34" t="s">
@@ -6207,7 +6184,7 @@
       <c r="E35" t="s">
         <v>862</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="1">
         <v>45736</v>
       </c>
       <c r="G35" t="s">
@@ -6236,7 +6213,7 @@
       <c r="E36" t="s">
         <v>863</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="1">
         <v>45736</v>
       </c>
       <c r="G36" t="s">
@@ -6265,7 +6242,7 @@
       <c r="E37" t="s">
         <v>864</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>45736</v>
       </c>
       <c r="G37" t="s">
@@ -6294,7 +6271,7 @@
       <c r="E38" t="s">
         <v>844</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="1">
         <v>45736</v>
       </c>
       <c r="G38" t="s">
@@ -6320,7 +6297,7 @@
       <c r="D39" t="s">
         <v>731</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="1">
         <v>45736</v>
       </c>
       <c r="G39" t="s">
@@ -6330,7 +6307,7 @@
         <v>1353</v>
       </c>
       <c r="I39">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K39" t="s">
         <v>1361</v>
@@ -6355,7 +6332,7 @@
       <c r="D40" t="s">
         <v>731</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="1">
         <v>45736</v>
       </c>
       <c r="G40" t="s">
@@ -6365,7 +6342,7 @@
         <v>1353</v>
       </c>
       <c r="I40">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K40" t="s">
         <v>1359</v>
@@ -6393,7 +6370,7 @@
       <c r="E41" t="s">
         <v>865</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="1">
         <v>45736</v>
       </c>
       <c r="G41" t="s">
@@ -6422,7 +6399,7 @@
       <c r="E42" t="s">
         <v>866</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="1">
         <v>45736</v>
       </c>
       <c r="G42" t="s">
@@ -6451,7 +6428,7 @@
       <c r="E43" t="s">
         <v>867</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="1">
         <v>45736</v>
       </c>
       <c r="G43" t="s">
@@ -6486,7 +6463,7 @@
       <c r="E44" t="s">
         <v>868</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="1">
         <v>45769</v>
       </c>
       <c r="G44" t="s">
@@ -6496,7 +6473,7 @@
         <v>1353</v>
       </c>
       <c r="I44">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="J44">
         <v>87</v>
@@ -6507,7 +6484,7 @@
       <c r="L44" t="s">
         <v>1378</v>
       </c>
-      <c r="N44" s="2">
+      <c r="N44" s="1">
         <v>45856</v>
       </c>
       <c r="P44" t="s">
@@ -6533,7 +6510,7 @@
       <c r="E45" t="s">
         <v>869</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="1">
         <v>45769</v>
       </c>
       <c r="G45" t="s">
@@ -6543,7 +6520,7 @@
         <v>1353</v>
       </c>
       <c r="I45">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="J45">
         <v>331</v>
@@ -6554,7 +6531,7 @@
       <c r="L45" t="s">
         <v>1379</v>
       </c>
-      <c r="N45" s="2">
+      <c r="N45" s="1">
         <v>46100</v>
       </c>
       <c r="O45">
@@ -6580,7 +6557,7 @@
       <c r="E46" t="s">
         <v>870</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="1">
         <v>45769</v>
       </c>
       <c r="G46" t="s">
@@ -6590,7 +6567,7 @@
         <v>1353</v>
       </c>
       <c r="I46">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="K46" t="s">
         <v>1360</v>
@@ -6618,7 +6595,7 @@
       <c r="E47" t="s">
         <v>871</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="1">
         <v>45769</v>
       </c>
       <c r="G47" t="s">
@@ -6628,7 +6605,7 @@
         <v>1353</v>
       </c>
       <c r="I47">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="J47">
         <v>344</v>
@@ -6639,7 +6616,7 @@
       <c r="L47" t="s">
         <v>1380</v>
       </c>
-      <c r="N47" s="2">
+      <c r="N47" s="1">
         <v>46113</v>
       </c>
       <c r="P47" t="s">
@@ -6665,7 +6642,7 @@
       <c r="E48" t="s">
         <v>872</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="1">
         <v>45769</v>
       </c>
       <c r="G48" t="s">
@@ -6675,7 +6652,7 @@
         <v>1353</v>
       </c>
       <c r="I48">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="K48" t="s">
         <v>1360</v>
@@ -6703,7 +6680,7 @@
       <c r="E49" t="s">
         <v>873</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="1">
         <v>45769</v>
       </c>
       <c r="G49" t="s">
@@ -6732,7 +6709,7 @@
       <c r="E50" t="s">
         <v>874</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="1">
         <v>45769</v>
       </c>
       <c r="G50" t="s">
@@ -6742,7 +6719,7 @@
         <v>1353</v>
       </c>
       <c r="I50">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="K50" t="s">
         <v>1360</v>
@@ -6770,7 +6747,7 @@
       <c r="E51" t="s">
         <v>875</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="1">
         <v>45769</v>
       </c>
       <c r="G51" t="s">
@@ -6799,7 +6776,7 @@
       <c r="E52" t="s">
         <v>876</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="1">
         <v>45769</v>
       </c>
       <c r="G52" t="s">
@@ -6809,7 +6786,7 @@
         <v>1353</v>
       </c>
       <c r="I52">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="K52" t="s">
         <v>1356</v>
@@ -6837,7 +6814,7 @@
       <c r="E53" t="s">
         <v>877</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="1">
         <v>45769</v>
       </c>
       <c r="G53" t="s">
@@ -6847,7 +6824,7 @@
         <v>1353</v>
       </c>
       <c r="I53">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="K53" t="s">
         <v>1357</v>
@@ -6875,7 +6852,7 @@
       <c r="E54" t="s">
         <v>878</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="1">
         <v>45769</v>
       </c>
       <c r="G54" t="s">
@@ -6885,7 +6862,7 @@
         <v>1353</v>
       </c>
       <c r="I54">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="K54" t="s">
         <v>1357</v>
@@ -6913,7 +6890,7 @@
       <c r="E55" t="s">
         <v>879</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="1">
         <v>45769</v>
       </c>
       <c r="G55" t="s">
@@ -6942,7 +6919,7 @@
       <c r="E56" t="s">
         <v>880</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="1">
         <v>45769</v>
       </c>
       <c r="G56" t="s">
@@ -6971,7 +6948,7 @@
       <c r="E57" t="s">
         <v>881</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="1">
         <v>45769</v>
       </c>
       <c r="G57" t="s">
@@ -6981,7 +6958,7 @@
         <v>1353</v>
       </c>
       <c r="I57">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="K57" t="s">
         <v>1360</v>
@@ -7009,7 +6986,7 @@
       <c r="E58" t="s">
         <v>882</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="1">
         <v>45769</v>
       </c>
       <c r="G58" t="s">
@@ -7038,7 +7015,7 @@
       <c r="E59" t="s">
         <v>883</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="1">
         <v>45769</v>
       </c>
       <c r="G59" t="s">
@@ -7067,7 +7044,7 @@
       <c r="E60" t="s">
         <v>884</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="1">
         <v>45769</v>
       </c>
       <c r="G60" t="s">
@@ -7096,7 +7073,7 @@
       <c r="E61" t="s">
         <v>885</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="1">
         <v>45769</v>
       </c>
       <c r="G61" t="s">
@@ -7125,7 +7102,7 @@
       <c r="E62" t="s">
         <v>886</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="1">
         <v>45770</v>
       </c>
       <c r="G62" t="s">
@@ -7154,7 +7131,7 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="1">
         <v>45799</v>
       </c>
       <c r="G63" t="s">
@@ -7164,7 +7141,7 @@
         <v>1353</v>
       </c>
       <c r="I63">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J63">
         <v>293</v>
@@ -7175,7 +7152,7 @@
       <c r="L63" t="s">
         <v>1381</v>
       </c>
-      <c r="N63" s="2">
+      <c r="N63" s="1">
         <v>46092</v>
       </c>
       <c r="P63" t="s">
@@ -7201,7 +7178,7 @@
       <c r="E64" t="s">
         <v>888</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="1">
         <v>45799</v>
       </c>
       <c r="G64" t="s">
@@ -7211,7 +7188,7 @@
         <v>1353</v>
       </c>
       <c r="I64">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J64">
         <v>320</v>
@@ -7222,7 +7199,7 @@
       <c r="L64" t="s">
         <v>1382</v>
       </c>
-      <c r="N64" s="2">
+      <c r="N64" s="1">
         <v>46119</v>
       </c>
       <c r="Q64" t="b">
@@ -7245,7 +7222,7 @@
       <c r="E65" t="s">
         <v>889</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="1">
         <v>45799</v>
       </c>
       <c r="G65" t="s">
@@ -7274,7 +7251,7 @@
       <c r="E66" t="s">
         <v>890</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="1">
         <v>45799</v>
       </c>
       <c r="G66" t="s">
@@ -7303,7 +7280,7 @@
       <c r="E67" t="s">
         <v>891</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="1">
         <v>45799</v>
       </c>
       <c r="G67" t="s">
@@ -7332,7 +7309,7 @@
       <c r="E68" t="s">
         <v>892</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="1">
         <v>45799</v>
       </c>
       <c r="G68" t="s">
@@ -7361,7 +7338,7 @@
       <c r="E69" t="s">
         <v>893</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="1">
         <v>45803</v>
       </c>
       <c r="G69" t="s">
@@ -7390,7 +7367,7 @@
       <c r="E70" t="s">
         <v>894</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="1">
         <v>45803</v>
       </c>
       <c r="G70" t="s">
@@ -7400,7 +7377,7 @@
         <v>1353</v>
       </c>
       <c r="I70">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J70">
         <v>429</v>
@@ -7411,7 +7388,7 @@
       <c r="L70" t="s">
         <v>1383</v>
       </c>
-      <c r="N70" s="2">
+      <c r="N70" s="1">
         <v>46232</v>
       </c>
       <c r="Q70" t="b">
@@ -7434,7 +7411,7 @@
       <c r="E71" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="1">
         <v>45803</v>
       </c>
       <c r="G71" t="s">
@@ -7444,7 +7421,7 @@
         <v>1353</v>
       </c>
       <c r="I71">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J71">
         <v>429</v>
@@ -7455,7 +7432,7 @@
       <c r="L71" t="s">
         <v>1383</v>
       </c>
-      <c r="N71" s="2">
+      <c r="N71" s="1">
         <v>46232</v>
       </c>
       <c r="Q71" t="b">
@@ -7478,7 +7455,7 @@
       <c r="E72" t="s">
         <v>896</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="1">
         <v>45803</v>
       </c>
       <c r="G72" t="s">
@@ -7507,7 +7484,7 @@
       <c r="E73" t="s">
         <v>897</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="1">
         <v>45803</v>
       </c>
       <c r="G73" t="s">
@@ -7517,7 +7494,7 @@
         <v>1353</v>
       </c>
       <c r="I73">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K73" t="s">
         <v>1356</v>
@@ -7545,7 +7522,7 @@
       <c r="E74" t="s">
         <v>896</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="1">
         <v>45803</v>
       </c>
       <c r="G74" t="s">
@@ -7574,7 +7551,7 @@
       <c r="E75" t="s">
         <v>898</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="1">
         <v>45803</v>
       </c>
       <c r="G75" t="s">
@@ -7584,7 +7561,7 @@
         <v>1353</v>
       </c>
       <c r="I75">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J75">
         <v>429</v>
@@ -7595,7 +7572,7 @@
       <c r="L75" t="s">
         <v>1383</v>
       </c>
-      <c r="N75" s="2">
+      <c r="N75" s="1">
         <v>46232</v>
       </c>
       <c r="Q75" t="b">
@@ -7618,7 +7595,7 @@
       <c r="E76" t="s">
         <v>899</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="1">
         <v>45803</v>
       </c>
       <c r="G76" t="s">
@@ -7628,7 +7605,7 @@
         <v>1353</v>
       </c>
       <c r="I76">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K76" t="s">
         <v>1363</v>
@@ -7653,7 +7630,7 @@
       <c r="E77" t="s">
         <v>900</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="1">
         <v>45803</v>
       </c>
       <c r="G77" t="s">
@@ -7682,7 +7659,7 @@
       <c r="E78" t="s">
         <v>901</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="1">
         <v>45803</v>
       </c>
       <c r="G78" t="s">
@@ -7711,7 +7688,7 @@
       <c r="E79" t="s">
         <v>902</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="1">
         <v>45803</v>
       </c>
       <c r="G79" t="s">
@@ -7721,7 +7698,7 @@
         <v>1353</v>
       </c>
       <c r="I79">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K79" t="s">
         <v>1363</v>
@@ -7746,7 +7723,7 @@
       <c r="E80" t="s">
         <v>903</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="1">
         <v>45803</v>
       </c>
       <c r="G80" t="s">
@@ -7756,7 +7733,7 @@
         <v>1353</v>
       </c>
       <c r="I80">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J80">
         <v>429</v>
@@ -7767,7 +7744,7 @@
       <c r="L80" t="s">
         <v>1383</v>
       </c>
-      <c r="N80" s="2">
+      <c r="N80" s="1">
         <v>46232</v>
       </c>
       <c r="Q80" t="b">
@@ -7790,7 +7767,7 @@
       <c r="E81" t="s">
         <v>904</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="1">
         <v>45813</v>
       </c>
       <c r="G81" t="s">
@@ -7819,7 +7796,7 @@
       <c r="E82" t="s">
         <v>905</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="1">
         <v>45813</v>
       </c>
       <c r="G82" t="s">
@@ -7829,7 +7806,7 @@
         <v>1353</v>
       </c>
       <c r="I82">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K82" t="s">
         <v>1360</v>
@@ -7857,7 +7834,7 @@
       <c r="E83" t="s">
         <v>906</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="1">
         <v>45813</v>
       </c>
       <c r="G83" t="s">
@@ -7886,7 +7863,7 @@
       <c r="E84" t="s">
         <v>907</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="1">
         <v>45813</v>
       </c>
       <c r="G84" t="s">
@@ -7896,7 +7873,7 @@
         <v>1353</v>
       </c>
       <c r="I84">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="J84">
         <v>40</v>
@@ -7907,7 +7884,7 @@
       <c r="L84" t="s">
         <v>1384</v>
       </c>
-      <c r="N84" s="2">
+      <c r="N84" s="1">
         <v>45853</v>
       </c>
       <c r="O84">
@@ -7933,7 +7910,7 @@
       <c r="E85" t="s">
         <v>908</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="1">
         <v>45813</v>
       </c>
       <c r="G85" t="s">
@@ -7943,7 +7920,7 @@
         <v>1353</v>
       </c>
       <c r="I85">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K85" t="s">
         <v>1357</v>
@@ -7971,7 +7948,7 @@
       <c r="E86" t="s">
         <v>909</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="1">
         <v>45813</v>
       </c>
       <c r="G86" t="s">
@@ -7981,7 +7958,7 @@
         <v>1353</v>
       </c>
       <c r="I86">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K86" t="s">
         <v>1357</v>
@@ -8009,7 +7986,7 @@
       <c r="E87" t="s">
         <v>910</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="1">
         <v>45813</v>
       </c>
       <c r="G87" t="s">
@@ -8019,7 +7996,7 @@
         <v>1353</v>
       </c>
       <c r="I87">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="J87">
         <v>-16</v>
@@ -8030,7 +8007,7 @@
       <c r="L87" t="s">
         <v>1385</v>
       </c>
-      <c r="N87" s="2">
+      <c r="N87" s="1">
         <v>45797</v>
       </c>
       <c r="O87" t="s">
@@ -8056,7 +8033,7 @@
       <c r="E88" t="s">
         <v>911</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="1">
         <v>45813</v>
       </c>
       <c r="G88" t="s">
@@ -8071,7 +8048,7 @@
       <c r="L88" t="s">
         <v>1386</v>
       </c>
-      <c r="N88" s="2">
+      <c r="N88" s="1">
         <v>46195</v>
       </c>
       <c r="Q88" t="b">
@@ -8094,7 +8071,7 @@
       <c r="E89" t="s">
         <v>912</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="1">
         <v>45813</v>
       </c>
       <c r="G89" t="s">
@@ -8109,7 +8086,7 @@
       <c r="L89" t="s">
         <v>1386</v>
       </c>
-      <c r="N89" s="2">
+      <c r="N89" s="1">
         <v>46195</v>
       </c>
       <c r="Q89" t="b">
@@ -8132,7 +8109,7 @@
       <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="1">
         <v>45831</v>
       </c>
       <c r="G90" t="s">
@@ -8142,7 +8119,7 @@
         <v>1353</v>
       </c>
       <c r="I90">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K90" t="s">
         <v>1330</v>
@@ -8173,7 +8150,7 @@
       <c r="E91" t="s">
         <v>914</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="1">
         <v>45831</v>
       </c>
       <c r="G91" t="s">
@@ -8183,7 +8160,7 @@
         <v>1353</v>
       </c>
       <c r="I91">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J91">
         <v>308</v>
@@ -8194,7 +8171,7 @@
       <c r="L91" t="s">
         <v>1388</v>
       </c>
-      <c r="N91" s="2">
+      <c r="N91" s="1">
         <v>46139</v>
       </c>
       <c r="Q91" t="b">
@@ -8214,7 +8191,7 @@
       <c r="D92" t="s">
         <v>748</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="1">
         <v>45831</v>
       </c>
       <c r="G92" t="s">
@@ -8243,7 +8220,7 @@
       <c r="E93" t="s">
         <v>915</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="1">
         <v>45831</v>
       </c>
       <c r="G93" t="s">
@@ -8253,7 +8230,7 @@
         <v>1353</v>
       </c>
       <c r="I93">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J93">
         <v>308</v>
@@ -8264,7 +8241,7 @@
       <c r="L93" t="s">
         <v>1388</v>
       </c>
-      <c r="N93" s="2">
+      <c r="N93" s="1">
         <v>46139</v>
       </c>
       <c r="Q93" t="b">
@@ -8287,7 +8264,7 @@
       <c r="E94" t="s">
         <v>916</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="1">
         <v>45831</v>
       </c>
       <c r="G94" t="s">
@@ -8297,7 +8274,7 @@
         <v>1353</v>
       </c>
       <c r="I94">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K94" t="s">
         <v>1360</v>
@@ -8325,7 +8302,7 @@
       <c r="E95" t="s">
         <v>917</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="1">
         <v>45831</v>
       </c>
       <c r="G95" t="s">
@@ -8335,7 +8312,7 @@
         <v>1353</v>
       </c>
       <c r="I95">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J95">
         <v>308</v>
@@ -8346,7 +8323,7 @@
       <c r="L95" t="s">
         <v>1388</v>
       </c>
-      <c r="N95" s="2">
+      <c r="N95" s="1">
         <v>46139</v>
       </c>
       <c r="Q95" t="b">
@@ -8369,7 +8346,7 @@
       <c r="E96" t="s">
         <v>918</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="1">
         <v>45831</v>
       </c>
       <c r="G96" t="s">
@@ -8379,7 +8356,7 @@
         <v>1353</v>
       </c>
       <c r="I96">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J96">
         <v>17</v>
@@ -8390,7 +8367,7 @@
       <c r="L96" t="s">
         <v>1369</v>
       </c>
-      <c r="N96" s="2">
+      <c r="N96" s="1">
         <v>45848</v>
       </c>
       <c r="O96" t="s">
@@ -8416,7 +8393,7 @@
       <c r="E97" t="s">
         <v>919</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="1">
         <v>45840</v>
       </c>
       <c r="G97" t="s">
@@ -8426,7 +8403,7 @@
         <v>1353</v>
       </c>
       <c r="I97">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J97">
         <v>20</v>
@@ -8437,7 +8414,7 @@
       <c r="L97" t="s">
         <v>1389</v>
       </c>
-      <c r="N97" s="2">
+      <c r="N97" s="1">
         <v>45860</v>
       </c>
       <c r="P97" t="s">
@@ -8463,7 +8440,7 @@
       <c r="E98" t="s">
         <v>920</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="1">
         <v>45840</v>
       </c>
       <c r="G98" t="s">
@@ -8473,7 +8450,7 @@
         <v>1353</v>
       </c>
       <c r="I98">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K98" t="s">
         <v>1360</v>
@@ -8501,7 +8478,7 @@
       <c r="E99" t="s">
         <v>921</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="1">
         <v>45840</v>
       </c>
       <c r="G99" t="s">
@@ -8530,7 +8507,7 @@
       <c r="E100" t="s">
         <v>922</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="1">
         <v>45840</v>
       </c>
       <c r="G100" t="s">
@@ -8540,7 +8517,7 @@
         <v>1353</v>
       </c>
       <c r="I100">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J100">
         <v>348</v>
@@ -8551,7 +8528,7 @@
       <c r="L100" t="s">
         <v>1388</v>
       </c>
-      <c r="N100" s="2">
+      <c r="N100" s="1">
         <v>46188</v>
       </c>
       <c r="Q100" t="b">
@@ -8574,7 +8551,7 @@
       <c r="E101" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="1">
         <v>45840</v>
       </c>
       <c r="G101" t="s">
@@ -8603,7 +8580,7 @@
       <c r="E102" t="s">
         <v>924</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="1">
         <v>45840</v>
       </c>
       <c r="G102" t="s">
@@ -8632,7 +8609,7 @@
       <c r="E103" t="s">
         <v>925</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="1">
         <v>45840</v>
       </c>
       <c r="G103" t="s">
@@ -8661,7 +8638,7 @@
       <c r="E104" t="s">
         <v>926</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="1">
         <v>45840</v>
       </c>
       <c r="G104" t="s">
@@ -8671,7 +8648,7 @@
         <v>1353</v>
       </c>
       <c r="I104">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J104">
         <v>348</v>
@@ -8682,7 +8659,7 @@
       <c r="L104" t="s">
         <v>1388</v>
       </c>
-      <c r="N104" s="2">
+      <c r="N104" s="1">
         <v>46188</v>
       </c>
       <c r="Q104" t="b">
@@ -8705,7 +8682,7 @@
       <c r="E105" t="s">
         <v>927</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="1">
         <v>45840</v>
       </c>
       <c r="G105" t="s">
@@ -8715,7 +8692,7 @@
         <v>1353</v>
       </c>
       <c r="I105">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J105">
         <v>348</v>
@@ -8726,7 +8703,7 @@
       <c r="L105" t="s">
         <v>1388</v>
       </c>
-      <c r="N105" s="2">
+      <c r="N105" s="1">
         <v>46188</v>
       </c>
       <c r="Q105" t="b">
@@ -8749,7 +8726,7 @@
       <c r="E106" t="s">
         <v>928</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="1">
         <v>45840</v>
       </c>
       <c r="G106" t="s">
@@ -8759,7 +8736,7 @@
         <v>1353</v>
       </c>
       <c r="I106">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J106">
         <v>49</v>
@@ -8770,7 +8747,7 @@
       <c r="L106" t="s">
         <v>1390</v>
       </c>
-      <c r="N106" s="2">
+      <c r="N106" s="1">
         <v>45889</v>
       </c>
       <c r="Q106" t="b">
@@ -8793,7 +8770,7 @@
       <c r="E107" t="s">
         <v>929</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="1">
         <v>45840</v>
       </c>
       <c r="G107" t="s">
@@ -8803,7 +8780,7 @@
         <v>1353</v>
       </c>
       <c r="I107">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J107">
         <v>36</v>
@@ -8814,7 +8791,7 @@
       <c r="L107" t="s">
         <v>1391</v>
       </c>
-      <c r="N107" s="2">
+      <c r="N107" s="1">
         <v>45876</v>
       </c>
       <c r="Q107" t="b">
@@ -8837,7 +8814,7 @@
       <c r="E108" t="s">
         <v>930</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="1">
         <v>45840</v>
       </c>
       <c r="G108" t="s">
@@ -8847,7 +8824,7 @@
         <v>1353</v>
       </c>
       <c r="I108">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K108" t="s">
         <v>1357</v>
@@ -8875,7 +8852,7 @@
       <c r="E109" t="s">
         <v>931</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="1">
         <v>45840</v>
       </c>
       <c r="G109" t="s">
@@ -8885,7 +8862,7 @@
         <v>1353</v>
       </c>
       <c r="I109">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K109" t="s">
         <v>1357</v>
@@ -8913,7 +8890,7 @@
       <c r="E110" t="s">
         <v>932</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="1">
         <v>45840</v>
       </c>
       <c r="G110" t="s">
@@ -8942,7 +8919,7 @@
       <c r="E111" t="s">
         <v>933</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="1">
         <v>45840</v>
       </c>
       <c r="G111" t="s">
@@ -8971,7 +8948,7 @@
       <c r="E112" t="s">
         <v>934</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="1">
         <v>45840</v>
       </c>
       <c r="G112" t="s">
@@ -9000,7 +8977,7 @@
       <c r="E113" t="s">
         <v>935</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="1">
         <v>45840</v>
       </c>
       <c r="G113" t="s">
@@ -9029,7 +9006,7 @@
       <c r="E114" t="s">
         <v>936</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="1">
         <v>45840</v>
       </c>
       <c r="G114" t="s">
@@ -9058,7 +9035,7 @@
       <c r="E115" t="s">
         <v>937</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="1">
         <v>45840</v>
       </c>
       <c r="G115" t="s">
@@ -9068,7 +9045,7 @@
         <v>1353</v>
       </c>
       <c r="I115">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K115" t="s">
         <v>1357</v>
@@ -9096,7 +9073,7 @@
       <c r="E116" t="s">
         <v>938</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="1">
         <v>45840</v>
       </c>
       <c r="G116" t="s">
@@ -9106,7 +9083,7 @@
         <v>1353</v>
       </c>
       <c r="I116">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K116" t="s">
         <v>1357</v>
@@ -9134,7 +9111,7 @@
       <c r="E117" t="s">
         <v>939</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="1">
         <v>45840</v>
       </c>
       <c r="G117" t="s">
@@ -9144,7 +9121,7 @@
         <v>1353</v>
       </c>
       <c r="I117">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K117" t="s">
         <v>1357</v>
@@ -9172,7 +9149,7 @@
       <c r="E118" t="s">
         <v>940</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="1">
         <v>45840</v>
       </c>
       <c r="G118" t="s">
@@ -9182,7 +9159,7 @@
         <v>1353</v>
       </c>
       <c r="I118">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K118" t="s">
         <v>1357</v>
@@ -9210,7 +9187,7 @@
       <c r="E119" t="s">
         <v>941</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="1">
         <v>45840</v>
       </c>
       <c r="G119" t="s">
@@ -9220,7 +9197,7 @@
         <v>1353</v>
       </c>
       <c r="I119">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K119" t="s">
         <v>1357</v>
@@ -9248,7 +9225,7 @@
       <c r="E120" t="s">
         <v>942</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="1">
         <v>45840</v>
       </c>
       <c r="G120" t="s">
@@ -9258,7 +9235,7 @@
         <v>1353</v>
       </c>
       <c r="I120">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K120" t="s">
         <v>1357</v>
@@ -9286,7 +9263,7 @@
       <c r="E121" t="s">
         <v>943</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="1">
         <v>45849</v>
       </c>
       <c r="G121" t="s">
@@ -9296,7 +9273,7 @@
         <v>1353</v>
       </c>
       <c r="I121">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J121">
         <v>251</v>
@@ -9307,7 +9284,7 @@
       <c r="L121" t="s">
         <v>1379</v>
       </c>
-      <c r="N121" s="2">
+      <c r="N121" s="1">
         <v>46100</v>
       </c>
       <c r="O121">
@@ -9333,7 +9310,7 @@
       <c r="E122" t="s">
         <v>944</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="1">
         <v>45849</v>
       </c>
       <c r="G122" t="s">
@@ -9343,7 +9320,7 @@
         <v>1353</v>
       </c>
       <c r="I122">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="K122" t="s">
         <v>1357</v>
@@ -9371,7 +9348,7 @@
       <c r="E123" t="s">
         <v>945</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="1">
         <v>45849</v>
       </c>
       <c r="G123" t="s">
@@ -9400,7 +9377,7 @@
       <c r="E124" t="s">
         <v>946</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="1">
         <v>45853</v>
       </c>
       <c r="G124" t="s">
@@ -9410,7 +9387,7 @@
         <v>1353</v>
       </c>
       <c r="I124">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="K124" t="s">
         <v>1357</v>
@@ -9438,7 +9415,7 @@
       <c r="E125" t="s">
         <v>947</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="1">
         <v>45855</v>
       </c>
       <c r="G125" t="s">
@@ -9448,7 +9425,7 @@
         <v>1353</v>
       </c>
       <c r="I125">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K125" t="s">
         <v>1363</v>
@@ -9476,7 +9453,7 @@
       <c r="E126" t="s">
         <v>948</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="1">
         <v>45855</v>
       </c>
       <c r="G126" t="s">
@@ -9505,7 +9482,7 @@
       <c r="E127" t="s">
         <v>949</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="1">
         <v>45856</v>
       </c>
       <c r="G127" t="s">
@@ -9534,7 +9511,7 @@
       <c r="E128" t="s">
         <v>950</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="1">
         <v>45869</v>
       </c>
       <c r="G128" t="s">
@@ -9544,7 +9521,7 @@
         <v>1353</v>
       </c>
       <c r="I128">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K128" t="s">
         <v>1357</v>
@@ -9572,7 +9549,7 @@
       <c r="E129" t="s">
         <v>951</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="1">
         <v>45869</v>
       </c>
       <c r="G129" t="s">
@@ -9582,7 +9559,7 @@
         <v>1353</v>
       </c>
       <c r="I129">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K129" t="s">
         <v>1356</v>
@@ -9610,7 +9587,7 @@
       <c r="E130" t="s">
         <v>952</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="1">
         <v>45869</v>
       </c>
       <c r="G130" t="s">
@@ -9620,7 +9597,7 @@
         <v>1353</v>
       </c>
       <c r="I130">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J130">
         <v>47</v>
@@ -9631,7 +9608,7 @@
       <c r="L130" t="s">
         <v>1392</v>
       </c>
-      <c r="N130" s="2">
+      <c r="N130" s="1">
         <v>45916</v>
       </c>
       <c r="O130">
@@ -9657,7 +9634,7 @@
       <c r="E131" t="s">
         <v>953</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="1">
         <v>45869</v>
       </c>
       <c r="G131" t="s">
@@ -9686,7 +9663,7 @@
       <c r="E132" t="s">
         <v>954</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="1">
         <v>45869</v>
       </c>
       <c r="G132" t="s">
@@ -9696,7 +9673,7 @@
         <v>1353</v>
       </c>
       <c r="I132">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J132">
         <v>145</v>
@@ -9707,7 +9684,7 @@
       <c r="L132" t="s">
         <v>1393</v>
       </c>
-      <c r="N132" s="2">
+      <c r="N132" s="1">
         <v>46014</v>
       </c>
       <c r="O132">
@@ -9733,7 +9710,7 @@
       <c r="E133" t="s">
         <v>955</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="1">
         <v>45869</v>
       </c>
       <c r="G133" t="s">
@@ -9762,7 +9739,7 @@
       <c r="E134" t="s">
         <v>956</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="1">
         <v>45882</v>
       </c>
       <c r="G134" t="s">
@@ -9772,7 +9749,7 @@
         <v>1353</v>
       </c>
       <c r="I134">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K134" t="s">
         <v>1356</v>
@@ -9800,7 +9777,7 @@
       <c r="E135" t="s">
         <v>957</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="1">
         <v>45882</v>
       </c>
       <c r="G135" t="s">
@@ -9829,7 +9806,7 @@
       <c r="E136" t="s">
         <v>958</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="1">
         <v>45891</v>
       </c>
       <c r="G136" t="s">
@@ -9858,7 +9835,7 @@
       <c r="E137" t="s">
         <v>959</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="1">
         <v>45891</v>
       </c>
       <c r="G137" t="s">
@@ -9887,7 +9864,7 @@
       <c r="E138" t="s">
         <v>960</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="1">
         <v>45891</v>
       </c>
       <c r="G138" t="s">
@@ -9897,7 +9874,7 @@
         <v>1353</v>
       </c>
       <c r="I138">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K138" t="s">
         <v>1357</v>
@@ -9925,7 +9902,7 @@
       <c r="E139" t="s">
         <v>961</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="1">
         <v>45891</v>
       </c>
       <c r="G139" t="s">
@@ -9954,7 +9931,7 @@
       <c r="E140" t="s">
         <v>962</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="1">
         <v>45891</v>
       </c>
       <c r="G140" t="s">
@@ -9983,7 +9960,7 @@
       <c r="E141" t="s">
         <v>963</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="1">
         <v>45891</v>
       </c>
       <c r="G141" t="s">
@@ -10012,7 +9989,7 @@
       <c r="E142" t="s">
         <v>964</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="1">
         <v>45891</v>
       </c>
       <c r="G142" t="s">
@@ -10041,7 +10018,7 @@
       <c r="E143" t="s">
         <v>965</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="1">
         <v>45891</v>
       </c>
       <c r="G143" t="s">
@@ -10070,7 +10047,7 @@
       <c r="E144" t="s">
         <v>966</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="1">
         <v>45891</v>
       </c>
       <c r="G144" t="s">
@@ -10099,7 +10076,7 @@
       <c r="E145" t="s">
         <v>967</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="1">
         <v>45891</v>
       </c>
       <c r="G145" t="s">
@@ -10128,7 +10105,7 @@
       <c r="E146" t="s">
         <v>968</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="1">
         <v>45891</v>
       </c>
       <c r="G146" t="s">
@@ -10157,7 +10134,7 @@
       <c r="E147" t="s">
         <v>969</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="1">
         <v>45891</v>
       </c>
       <c r="G147" t="s">
@@ -10186,7 +10163,7 @@
       <c r="E148" t="s">
         <v>970</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="1">
         <v>45891</v>
       </c>
       <c r="G148" t="s">
@@ -10196,7 +10173,7 @@
         <v>1353</v>
       </c>
       <c r="I148">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J148">
         <v>341</v>
@@ -10207,7 +10184,7 @@
       <c r="L148" t="s">
         <v>1383</v>
       </c>
-      <c r="N148" s="2">
+      <c r="N148" s="1">
         <v>46232</v>
       </c>
       <c r="Q148" t="b">
@@ -10230,7 +10207,7 @@
       <c r="E149" t="s">
         <v>971</v>
       </c>
-      <c r="F149" s="2">
+      <c r="F149" s="1">
         <v>45891</v>
       </c>
       <c r="G149" t="s">
@@ -10240,7 +10217,7 @@
         <v>1353</v>
       </c>
       <c r="I149">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J149">
         <v>374</v>
@@ -10251,7 +10228,7 @@
       <c r="L149" t="s">
         <v>1394</v>
       </c>
-      <c r="N149" s="2">
+      <c r="N149" s="1">
         <v>46265</v>
       </c>
       <c r="P149" t="s">
@@ -10277,7 +10254,7 @@
       <c r="E150" t="s">
         <v>972</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="1">
         <v>45891</v>
       </c>
       <c r="G150" t="s">
@@ -10287,7 +10264,7 @@
         <v>1353</v>
       </c>
       <c r="I150">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J150">
         <v>201</v>
@@ -10298,7 +10275,7 @@
       <c r="L150" t="s">
         <v>1381</v>
       </c>
-      <c r="N150" s="2">
+      <c r="N150" s="1">
         <v>46092</v>
       </c>
       <c r="P150" t="s">
@@ -10324,7 +10301,7 @@
       <c r="E151" t="s">
         <v>973</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="1">
         <v>45891</v>
       </c>
       <c r="G151" t="s">
@@ -10353,7 +10330,7 @@
       <c r="E152" t="s">
         <v>963</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="1">
         <v>45891</v>
       </c>
       <c r="G152" t="s">
@@ -10363,7 +10340,7 @@
         <v>1353</v>
       </c>
       <c r="I152">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J152">
         <v>228</v>
@@ -10374,7 +10351,7 @@
       <c r="L152" t="s">
         <v>1382</v>
       </c>
-      <c r="N152" s="2">
+      <c r="N152" s="1">
         <v>46119</v>
       </c>
       <c r="Q152" t="b">
@@ -10397,7 +10374,7 @@
       <c r="E153" t="s">
         <v>974</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="1">
         <v>45891</v>
       </c>
       <c r="G153" t="s">
@@ -10415,7 +10392,7 @@
       <c r="L153" t="s">
         <v>1383</v>
       </c>
-      <c r="N153" s="2">
+      <c r="N153" s="1">
         <v>46232</v>
       </c>
       <c r="Q153" t="b">
@@ -10438,7 +10415,7 @@
       <c r="E154" t="s">
         <v>975</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="1">
         <v>45891</v>
       </c>
       <c r="G154" t="s">
@@ -10467,7 +10444,7 @@
       <c r="E155" t="s">
         <v>976</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="1">
         <v>45891</v>
       </c>
       <c r="G155" t="s">
@@ -10477,7 +10454,7 @@
         <v>1353</v>
       </c>
       <c r="I155">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K155" t="s">
         <v>1363</v>
@@ -10502,7 +10479,7 @@
       <c r="E156" t="s">
         <v>977</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="1">
         <v>45891</v>
       </c>
       <c r="G156" t="s">
@@ -10512,7 +10489,7 @@
         <v>1353</v>
       </c>
       <c r="I156">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K156" t="s">
         <v>1357</v>
@@ -10540,7 +10517,7 @@
       <c r="E157" t="s">
         <v>978</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="1">
         <v>45891</v>
       </c>
       <c r="G157" t="s">
@@ -10550,7 +10527,7 @@
         <v>1353</v>
       </c>
       <c r="I157">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J157">
         <v>371</v>
@@ -10561,7 +10538,7 @@
       <c r="L157" t="s">
         <v>1395</v>
       </c>
-      <c r="N157" s="2">
+      <c r="N157" s="1">
         <v>46262</v>
       </c>
       <c r="Q157" t="b">
@@ -10584,7 +10561,7 @@
       <c r="E158" t="s">
         <v>979</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="1">
         <v>45894</v>
       </c>
       <c r="G158" t="s">
@@ -10594,7 +10571,7 @@
         <v>1353</v>
       </c>
       <c r="I158">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J158">
         <v>52</v>
@@ -10605,7 +10582,7 @@
       <c r="L158" t="s">
         <v>1396</v>
       </c>
-      <c r="N158" s="2">
+      <c r="N158" s="1">
         <v>45946</v>
       </c>
       <c r="Q158" t="b">
@@ -10628,7 +10605,7 @@
       <c r="E159" t="s">
         <v>980</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="1">
         <v>45894</v>
       </c>
       <c r="G159" t="s">
@@ -10638,7 +10615,7 @@
         <v>1353</v>
       </c>
       <c r="I159">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K159" t="s">
         <v>1357</v>
@@ -10666,7 +10643,7 @@
       <c r="E160" t="s">
         <v>981</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="1">
         <v>45898</v>
       </c>
       <c r="G160" t="s">
@@ -10676,7 +10653,7 @@
         <v>1353</v>
       </c>
       <c r="I160">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K160" t="s">
         <v>1357</v>
@@ -10704,7 +10681,7 @@
       <c r="E161" t="s">
         <v>982</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="1">
         <v>45898</v>
       </c>
       <c r="G161" t="s">
@@ -10714,7 +10691,7 @@
         <v>1353</v>
       </c>
       <c r="I161">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J161">
         <v>55</v>
@@ -10725,7 +10702,7 @@
       <c r="L161" t="s">
         <v>1397</v>
       </c>
-      <c r="N161" s="2">
+      <c r="N161" s="1">
         <v>45953</v>
       </c>
       <c r="O161" t="s">
@@ -10751,7 +10728,7 @@
       <c r="E162" t="s">
         <v>983</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="1">
         <v>45898</v>
       </c>
       <c r="G162" t="s">
@@ -10761,7 +10738,7 @@
         <v>1353</v>
       </c>
       <c r="I162">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J162">
         <v>42</v>
@@ -10772,7 +10749,7 @@
       <c r="L162" t="s">
         <v>1398</v>
       </c>
-      <c r="N162" s="2">
+      <c r="N162" s="1">
         <v>45940</v>
       </c>
       <c r="P162" t="s">
@@ -10798,7 +10775,7 @@
       <c r="E163" t="s">
         <v>984</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="1">
         <v>45898</v>
       </c>
       <c r="G163" t="s">
@@ -10808,7 +10785,7 @@
         <v>1353</v>
       </c>
       <c r="I163">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J163">
         <v>42</v>
@@ -10819,7 +10796,7 @@
       <c r="L163" t="s">
         <v>1398</v>
       </c>
-      <c r="N163" s="2">
+      <c r="N163" s="1">
         <v>45940</v>
       </c>
       <c r="P163" t="s">
@@ -10845,7 +10822,7 @@
       <c r="E164" t="s">
         <v>985</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="1">
         <v>45910</v>
       </c>
       <c r="G164" t="s">
@@ -10855,7 +10832,7 @@
         <v>1355</v>
       </c>
       <c r="I164">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="O164" t="s">
         <v>1469</v>
@@ -10880,7 +10857,7 @@
       <c r="E165" t="s">
         <v>986</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="1">
         <v>45917</v>
       </c>
       <c r="G165" t="s">
@@ -10898,7 +10875,7 @@
       <c r="L165" t="s">
         <v>1399</v>
       </c>
-      <c r="N165" s="2">
+      <c r="N165" s="1">
         <v>46204</v>
       </c>
       <c r="P165" t="s">
@@ -10924,7 +10901,7 @@
       <c r="E166" t="s">
         <v>987</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="1">
         <v>45917</v>
       </c>
       <c r="G166" t="s">
@@ -10953,7 +10930,7 @@
       <c r="E167" t="s">
         <v>988</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="1">
         <v>45917</v>
       </c>
       <c r="G167" t="s">
@@ -10982,7 +10959,7 @@
       <c r="E168" t="s">
         <v>989</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="1">
         <v>45917</v>
       </c>
       <c r="G168" t="s">
@@ -10992,7 +10969,7 @@
         <v>1353</v>
       </c>
       <c r="I168">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="K168" t="s">
         <v>1360</v>
@@ -11023,7 +11000,7 @@
       <c r="E169" t="s">
         <v>990</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="1">
         <v>45917</v>
       </c>
       <c r="G169" t="s">
@@ -11033,7 +11010,7 @@
         <v>1353</v>
       </c>
       <c r="I169">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="K169" t="s">
         <v>1330</v>
@@ -11041,7 +11018,7 @@
       <c r="L169" t="s">
         <v>1401</v>
       </c>
-      <c r="N169" s="2">
+      <c r="N169" s="1">
         <v>45973</v>
       </c>
       <c r="Q169" t="b">
@@ -11064,7 +11041,7 @@
       <c r="E170" t="s">
         <v>991</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="1">
         <v>45917</v>
       </c>
       <c r="G170" t="s">
@@ -11099,7 +11076,7 @@
       <c r="E171" t="s">
         <v>992</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="1">
         <v>45917</v>
       </c>
       <c r="G171" t="s">
@@ -11109,7 +11086,7 @@
         <v>1353</v>
       </c>
       <c r="I171">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="K171" t="s">
         <v>1357</v>
@@ -11137,7 +11114,7 @@
       <c r="E172" t="s">
         <v>993</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="1">
         <v>45917</v>
       </c>
       <c r="G172" t="s">
@@ -11166,7 +11143,7 @@
       <c r="E173" t="s">
         <v>994</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="1">
         <v>45917</v>
       </c>
       <c r="G173" t="s">
@@ -11195,7 +11172,7 @@
       <c r="E174" t="s">
         <v>995</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="1">
         <v>45917</v>
       </c>
       <c r="G174" t="s">
@@ -11210,7 +11187,7 @@
       <c r="L174" t="s">
         <v>1386</v>
       </c>
-      <c r="N174" s="2">
+      <c r="N174" s="1">
         <v>46195</v>
       </c>
       <c r="Q174" t="b">
@@ -11233,7 +11210,7 @@
       <c r="E175" t="s">
         <v>996</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="1">
         <v>45917</v>
       </c>
       <c r="G175" t="s">
@@ -11243,7 +11220,7 @@
         <v>1353</v>
       </c>
       <c r="I175">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="J175">
         <v>205</v>
@@ -11254,7 +11231,7 @@
       <c r="L175" t="s">
         <v>1402</v>
       </c>
-      <c r="N175" s="2">
+      <c r="N175" s="1">
         <v>46122</v>
       </c>
       <c r="P175" t="s">
@@ -11280,7 +11257,7 @@
       <c r="E176" t="s">
         <v>900</v>
       </c>
-      <c r="F176" s="2">
+      <c r="F176" s="1">
         <v>45917</v>
       </c>
       <c r="G176" t="s">
@@ -11290,7 +11267,7 @@
         <v>1353</v>
       </c>
       <c r="I176">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="K176" t="s">
         <v>1357</v>
@@ -11318,7 +11295,7 @@
       <c r="E177" t="s">
         <v>997</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="1">
         <v>45917</v>
       </c>
       <c r="G177" t="s">
@@ -11328,7 +11305,7 @@
         <v>1353</v>
       </c>
       <c r="I177">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="J177">
         <v>44</v>
@@ -11339,7 +11316,7 @@
       <c r="L177" t="s">
         <v>1403</v>
       </c>
-      <c r="N177" s="2">
+      <c r="N177" s="1">
         <v>45961</v>
       </c>
       <c r="P177" t="s">
@@ -11365,7 +11342,7 @@
       <c r="E178" t="s">
         <v>998</v>
       </c>
-      <c r="F178" s="2">
+      <c r="F178" s="1">
         <v>45937</v>
       </c>
       <c r="G178" t="s">
@@ -11375,7 +11352,7 @@
         <v>1353</v>
       </c>
       <c r="I178">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K178" t="s">
         <v>1356</v>
@@ -11403,7 +11380,7 @@
       <c r="E179" t="s">
         <v>999</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="1">
         <v>45937</v>
       </c>
       <c r="G179" t="s">
@@ -11432,7 +11409,7 @@
       <c r="E180" t="s">
         <v>1000</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="1">
         <v>45937</v>
       </c>
       <c r="G180" t="s">
@@ -11442,7 +11419,7 @@
         <v>1353</v>
       </c>
       <c r="I180">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K180" t="s">
         <v>1356</v>
@@ -11470,7 +11447,7 @@
       <c r="E181" t="s">
         <v>1001</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="1">
         <v>45937</v>
       </c>
       <c r="G181" t="s">
@@ -11499,7 +11476,7 @@
       <c r="E182" t="s">
         <v>1002</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="1">
         <v>45937</v>
       </c>
       <c r="G182" t="s">
@@ -11528,7 +11505,7 @@
       <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="F183" s="2">
+      <c r="F183" s="1">
         <v>45937</v>
       </c>
       <c r="G183" t="s">
@@ -11538,7 +11515,7 @@
         <v>1353</v>
       </c>
       <c r="I183">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K183" t="s">
         <v>1357</v>
@@ -11566,7 +11543,7 @@
       <c r="D184" t="s">
         <v>774</v>
       </c>
-      <c r="F184" s="2">
+      <c r="F184" s="1">
         <v>45939</v>
       </c>
       <c r="G184" t="s">
@@ -11576,7 +11553,7 @@
         <v>1353</v>
       </c>
       <c r="I184">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K184" t="s">
         <v>1363</v>
@@ -11601,7 +11578,7 @@
       <c r="E185" t="s">
         <v>1004</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="1">
         <v>45939</v>
       </c>
       <c r="G185" t="s">
@@ -11611,7 +11588,7 @@
         <v>1353</v>
       </c>
       <c r="I185">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K185" t="s">
         <v>1357</v>
@@ -11639,7 +11616,7 @@
       <c r="E186" t="s">
         <v>1005</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="1">
         <v>45939</v>
       </c>
       <c r="G186" t="s">
@@ -11649,7 +11626,7 @@
         <v>1353</v>
       </c>
       <c r="I186">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K186" t="s">
         <v>1357</v>
@@ -11677,7 +11654,7 @@
       <c r="E187" t="s">
         <v>1006</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="1">
         <v>45939</v>
       </c>
       <c r="G187" t="s">
@@ -11687,7 +11664,7 @@
         <v>1353</v>
       </c>
       <c r="I187">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J187">
         <v>75</v>
@@ -11698,7 +11675,7 @@
       <c r="L187" t="s">
         <v>1404</v>
       </c>
-      <c r="N187" s="2">
+      <c r="N187" s="1">
         <v>46014</v>
       </c>
       <c r="O187">
@@ -11724,7 +11701,7 @@
       <c r="E188" t="s">
         <v>1007</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="1">
         <v>45946</v>
       </c>
       <c r="G188" t="s">
@@ -11734,7 +11711,7 @@
         <v>1353</v>
       </c>
       <c r="I188">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J188">
         <v>40</v>
@@ -11745,7 +11722,7 @@
       <c r="L188" t="s">
         <v>1405</v>
       </c>
-      <c r="N188" s="2">
+      <c r="N188" s="1">
         <v>45986</v>
       </c>
       <c r="P188" t="s">
@@ -11771,7 +11748,7 @@
       <c r="E189" t="s">
         <v>1008</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="1">
         <v>45965</v>
       </c>
       <c r="G189" t="s">
@@ -11781,7 +11758,7 @@
         <v>1353</v>
       </c>
       <c r="I189">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J189">
         <v>155</v>
@@ -11792,7 +11769,7 @@
       <c r="L189" t="s">
         <v>1406</v>
       </c>
-      <c r="N189" s="2">
+      <c r="N189" s="1">
         <v>46120</v>
       </c>
       <c r="Q189" t="b">
@@ -11815,7 +11792,7 @@
       <c r="E190" t="s">
         <v>1009</v>
       </c>
-      <c r="F190" s="2">
+      <c r="F190" s="1">
         <v>45965</v>
       </c>
       <c r="G190" t="s">
@@ -11825,7 +11802,7 @@
         <v>1353</v>
       </c>
       <c r="I190">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J190">
         <v>107</v>
@@ -11836,7 +11813,7 @@
       <c r="L190" t="s">
         <v>1407</v>
       </c>
-      <c r="N190" s="2">
+      <c r="N190" s="1">
         <v>46072</v>
       </c>
       <c r="Q190" t="b">
@@ -11859,7 +11836,7 @@
       <c r="E191" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="2">
+      <c r="F191" s="1">
         <v>45967</v>
       </c>
       <c r="G191" t="s">
@@ -11869,7 +11846,7 @@
         <v>1353</v>
       </c>
       <c r="I191">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="J191">
         <v>5</v>
@@ -11880,7 +11857,7 @@
       <c r="L191" t="s">
         <v>1408</v>
       </c>
-      <c r="N191" s="2">
+      <c r="N191" s="1">
         <v>45972</v>
       </c>
       <c r="Q191" t="b">
@@ -11903,7 +11880,7 @@
       <c r="E192" t="s">
         <v>1011</v>
       </c>
-      <c r="F192" s="2">
+      <c r="F192" s="1">
         <v>45968</v>
       </c>
       <c r="G192" t="s">
@@ -11913,7 +11890,7 @@
         <v>1353</v>
       </c>
       <c r="I192">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K192" t="s">
         <v>1357</v>
@@ -11941,7 +11918,7 @@
       <c r="E193" t="s">
         <v>1012</v>
       </c>
-      <c r="F193" s="2">
+      <c r="F193" s="1">
         <v>45968</v>
       </c>
       <c r="G193" t="s">
@@ -11951,7 +11928,7 @@
         <v>1353</v>
       </c>
       <c r="I193">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K193" t="s">
         <v>1362</v>
@@ -11979,7 +11956,7 @@
       <c r="E194" t="s">
         <v>1013</v>
       </c>
-      <c r="F194" s="2">
+      <c r="F194" s="1">
         <v>45968</v>
       </c>
       <c r="G194" t="s">
@@ -12008,7 +11985,7 @@
       <c r="E195" t="s">
         <v>1014</v>
       </c>
-      <c r="F195" s="2">
+      <c r="F195" s="1">
         <v>45971</v>
       </c>
       <c r="G195" t="s">
@@ -12018,7 +11995,7 @@
         <v>1353</v>
       </c>
       <c r="I195">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J195">
         <v>186</v>
@@ -12029,7 +12006,7 @@
       <c r="L195" t="s">
         <v>1409</v>
       </c>
-      <c r="N195" s="2">
+      <c r="N195" s="1">
         <v>46157</v>
       </c>
       <c r="Q195" t="b">
@@ -12052,7 +12029,7 @@
       <c r="E196" t="s">
         <v>1015</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="1">
         <v>45978</v>
       </c>
       <c r="G196" t="s">
@@ -12081,7 +12058,7 @@
       <c r="E197" t="s">
         <v>1016</v>
       </c>
-      <c r="F197" s="2">
+      <c r="F197" s="1">
         <v>45978</v>
       </c>
       <c r="G197" t="s">
@@ -12110,7 +12087,7 @@
       <c r="E198" t="s">
         <v>1017</v>
       </c>
-      <c r="F198" s="2">
+      <c r="F198" s="1">
         <v>45978</v>
       </c>
       <c r="G198" t="s">
@@ -12139,7 +12116,7 @@
       <c r="E199" t="s">
         <v>1018</v>
       </c>
-      <c r="F199" s="2">
+      <c r="F199" s="1">
         <v>45979</v>
       </c>
       <c r="G199" t="s">
@@ -12149,7 +12126,7 @@
         <v>1353</v>
       </c>
       <c r="I199">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="J199">
         <v>70</v>
@@ -12160,7 +12137,7 @@
       <c r="L199" t="s">
         <v>1410</v>
       </c>
-      <c r="N199" s="2">
+      <c r="N199" s="1">
         <v>46049</v>
       </c>
       <c r="Q199" t="b">
@@ -12183,7 +12160,7 @@
       <c r="E200" t="s">
         <v>1019</v>
       </c>
-      <c r="F200" s="2">
+      <c r="F200" s="1">
         <v>45986</v>
       </c>
       <c r="G200" t="s">
@@ -12193,7 +12170,7 @@
         <v>1353</v>
       </c>
       <c r="I200">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J200">
         <v>170</v>
@@ -12204,7 +12181,7 @@
       <c r="L200" t="s">
         <v>1409</v>
       </c>
-      <c r="N200" s="2">
+      <c r="N200" s="1">
         <v>46156</v>
       </c>
       <c r="Q200" t="b">
@@ -12227,7 +12204,7 @@
       <c r="E201" t="s">
         <v>1020</v>
       </c>
-      <c r="F201" s="2">
+      <c r="F201" s="1">
         <v>45986</v>
       </c>
       <c r="G201" t="s">
@@ -12237,7 +12214,7 @@
         <v>1353</v>
       </c>
       <c r="I201">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K201" t="s">
         <v>1357</v>
@@ -12265,7 +12242,7 @@
       <c r="E202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" s="2">
+      <c r="F202" s="1">
         <v>45986</v>
       </c>
       <c r="G202" t="s">
@@ -12275,7 +12252,7 @@
         <v>1353</v>
       </c>
       <c r="I202">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K202" t="s">
         <v>1357</v>
@@ -12303,7 +12280,7 @@
       <c r="E203" t="s">
         <v>1022</v>
       </c>
-      <c r="F203" s="2">
+      <c r="F203" s="1">
         <v>45986</v>
       </c>
       <c r="G203" t="s">
@@ -12321,7 +12298,7 @@
       <c r="L203" t="s">
         <v>1411</v>
       </c>
-      <c r="N203" s="2">
+      <c r="N203" s="1">
         <v>46232</v>
       </c>
       <c r="Q203" t="b">
@@ -12344,7 +12321,7 @@
       <c r="E204" t="s">
         <v>1023</v>
       </c>
-      <c r="F204" s="2">
+      <c r="F204" s="1">
         <v>45986</v>
       </c>
       <c r="G204" t="s">
@@ -12354,7 +12331,7 @@
         <v>1353</v>
       </c>
       <c r="I204">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K204" t="s">
         <v>1356</v>
@@ -12382,7 +12359,7 @@
       <c r="E205" t="s">
         <v>1024</v>
       </c>
-      <c r="F205" s="2">
+      <c r="F205" s="1">
         <v>45986</v>
       </c>
       <c r="G205" t="s">
@@ -12392,7 +12369,7 @@
         <v>1353</v>
       </c>
       <c r="I205">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K205" t="s">
         <v>1356</v>
@@ -12420,7 +12397,7 @@
       <c r="E206" t="s">
         <v>1025</v>
       </c>
-      <c r="F206" s="2">
+      <c r="F206" s="1">
         <v>45986</v>
       </c>
       <c r="G206" t="s">
@@ -12449,7 +12426,7 @@
       <c r="E207" t="s">
         <v>1026</v>
       </c>
-      <c r="F207" s="2">
+      <c r="F207" s="1">
         <v>45986</v>
       </c>
       <c r="G207" t="s">
@@ -12459,7 +12436,7 @@
         <v>1353</v>
       </c>
       <c r="I207">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J207">
         <v>167</v>
@@ -12470,7 +12447,7 @@
       <c r="L207" t="s">
         <v>1412</v>
       </c>
-      <c r="N207" s="2">
+      <c r="N207" s="1">
         <v>46153</v>
       </c>
       <c r="Q207" t="b">
@@ -12493,7 +12470,7 @@
       <c r="E208" t="s">
         <v>1027</v>
       </c>
-      <c r="F208" s="2">
+      <c r="F208" s="1">
         <v>45986</v>
       </c>
       <c r="G208" t="s">
@@ -12503,7 +12480,7 @@
         <v>1353</v>
       </c>
       <c r="I208">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J208">
         <v>45</v>
@@ -12514,7 +12491,7 @@
       <c r="L208" t="s">
         <v>1413</v>
       </c>
-      <c r="N208" s="2">
+      <c r="N208" s="1">
         <v>46031</v>
       </c>
       <c r="Q208" t="b">
@@ -12537,7 +12514,7 @@
       <c r="E209" t="s">
         <v>1028</v>
       </c>
-      <c r="F209" s="2">
+      <c r="F209" s="1">
         <v>46000</v>
       </c>
       <c r="G209" t="s">
@@ -12547,7 +12524,7 @@
         <v>1353</v>
       </c>
       <c r="I209">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="J209">
         <v>191</v>
@@ -12558,7 +12535,7 @@
       <c r="L209" t="s">
         <v>1414</v>
       </c>
-      <c r="N209" s="2">
+      <c r="N209" s="1">
         <v>46191</v>
       </c>
       <c r="Q209" t="b">
@@ -12581,7 +12558,7 @@
       <c r="E210" t="s">
         <v>1029</v>
       </c>
-      <c r="F210" s="2">
+      <c r="F210" s="1">
         <v>46000</v>
       </c>
       <c r="G210" t="s">
@@ -12591,7 +12568,7 @@
         <v>1353</v>
       </c>
       <c r="I210">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K210" t="s">
         <v>1360</v>
@@ -12619,7 +12596,7 @@
       <c r="E211" t="s">
         <v>1030</v>
       </c>
-      <c r="F211" s="2">
+      <c r="F211" s="1">
         <v>46000</v>
       </c>
       <c r="G211" t="s">
@@ -12648,7 +12625,7 @@
       <c r="E212" t="s">
         <v>1031</v>
       </c>
-      <c r="F212" s="2">
+      <c r="F212" s="1">
         <v>46000</v>
       </c>
       <c r="G212" t="s">
@@ -12677,7 +12654,7 @@
       <c r="E213" t="s">
         <v>1032</v>
       </c>
-      <c r="F213" s="2">
+      <c r="F213" s="1">
         <v>46007</v>
       </c>
       <c r="G213" t="s">
@@ -12687,7 +12664,7 @@
         <v>1353</v>
       </c>
       <c r="I213">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K213" t="s">
         <v>1357</v>
@@ -12715,7 +12692,7 @@
       <c r="E214" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="2">
+      <c r="F214" s="1">
         <v>46007</v>
       </c>
       <c r="G214" t="s">
@@ -12725,7 +12702,7 @@
         <v>1353</v>
       </c>
       <c r="I214">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="J214">
         <v>14</v>
@@ -12736,7 +12713,7 @@
       <c r="L214" t="s">
         <v>1415</v>
       </c>
-      <c r="N214" s="2">
+      <c r="N214" s="1">
         <v>46021</v>
       </c>
       <c r="O214">
@@ -12762,7 +12739,7 @@
       <c r="E215" t="s">
         <v>1034</v>
       </c>
-      <c r="F215" s="2">
+      <c r="F215" s="1">
         <v>46007</v>
       </c>
       <c r="G215" t="s">
@@ -12772,7 +12749,7 @@
         <v>1353</v>
       </c>
       <c r="I215">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K215" t="s">
         <v>1357</v>
@@ -12800,7 +12777,7 @@
       <c r="E216" t="s">
         <v>1035</v>
       </c>
-      <c r="F216" s="2">
+      <c r="F216" s="1">
         <v>46010</v>
       </c>
       <c r="G216" t="s">
@@ -12829,7 +12806,7 @@
       <c r="E217" t="s">
         <v>1036</v>
       </c>
-      <c r="F217" s="2">
+      <c r="F217" s="1">
         <v>46010</v>
       </c>
       <c r="G217" t="s">
@@ -12839,7 +12816,7 @@
         <v>1353</v>
       </c>
       <c r="I217">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="J217">
         <v>42</v>
@@ -12850,7 +12827,7 @@
       <c r="L217" t="s">
         <v>1416</v>
       </c>
-      <c r="N217" s="2">
+      <c r="N217" s="1">
         <v>46052</v>
       </c>
       <c r="Q217" t="b">
@@ -12873,7 +12850,7 @@
       <c r="E218" t="s">
         <v>1037</v>
       </c>
-      <c r="F218" s="2">
+      <c r="F218" s="1">
         <v>46010</v>
       </c>
       <c r="G218" t="s">
@@ -12883,7 +12860,7 @@
         <v>1353</v>
       </c>
       <c r="I218">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="J218">
         <v>166</v>
@@ -12891,7 +12868,7 @@
       <c r="K218" t="s">
         <v>1359</v>
       </c>
-      <c r="N218" s="2">
+      <c r="N218" s="1">
         <v>46176</v>
       </c>
       <c r="P218" t="s">
@@ -12917,7 +12894,7 @@
       <c r="E219" t="s">
         <v>1038</v>
       </c>
-      <c r="F219" s="2">
+      <c r="F219" s="1">
         <v>46010</v>
       </c>
       <c r="G219" t="s">
@@ -12935,7 +12912,7 @@
       <c r="L219" t="s">
         <v>1417</v>
       </c>
-      <c r="N219" s="2">
+      <c r="N219" s="1">
         <v>46176</v>
       </c>
       <c r="P219" t="s">
@@ -12961,7 +12938,7 @@
       <c r="E220" t="s">
         <v>1039</v>
       </c>
-      <c r="F220" s="2">
+      <c r="F220" s="1">
         <v>46010</v>
       </c>
       <c r="G220" t="s">
@@ -12971,7 +12948,7 @@
         <v>1353</v>
       </c>
       <c r="I220">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="J220">
         <v>154</v>
@@ -12982,7 +12959,7 @@
       <c r="L220" t="s">
         <v>1418</v>
       </c>
-      <c r="N220" s="2">
+      <c r="N220" s="1">
         <v>46164</v>
       </c>
       <c r="Q220" t="b">
@@ -13005,7 +12982,7 @@
       <c r="E221" t="s">
         <v>1040</v>
       </c>
-      <c r="F221" s="2">
+      <c r="F221" s="1">
         <v>46028</v>
       </c>
       <c r="G221" t="s">
@@ -13020,7 +12997,7 @@
       <c r="L221" t="s">
         <v>1419</v>
       </c>
-      <c r="N221" s="2">
+      <c r="N221" s="1">
         <v>46184</v>
       </c>
       <c r="Q221" t="b">
@@ -13043,7 +13020,7 @@
       <c r="E222" t="s">
         <v>1041</v>
       </c>
-      <c r="F222" s="2">
+      <c r="F222" s="1">
         <v>46028</v>
       </c>
       <c r="G222" t="s">
@@ -13058,7 +13035,7 @@
       <c r="L222" t="s">
         <v>1383</v>
       </c>
-      <c r="N222" s="2">
+      <c r="N222" s="1">
         <v>46232</v>
       </c>
       <c r="Q222" t="b">
@@ -13081,7 +13058,7 @@
       <c r="E223" t="s">
         <v>1042</v>
       </c>
-      <c r="F223" s="2">
+      <c r="F223" s="1">
         <v>46028</v>
       </c>
       <c r="G223" t="s">
@@ -13096,7 +13073,7 @@
       <c r="L223" t="s">
         <v>1383</v>
       </c>
-      <c r="N223" s="2">
+      <c r="N223" s="1">
         <v>46232</v>
       </c>
       <c r="Q223" t="b">
@@ -13119,7 +13096,7 @@
       <c r="E224" t="s">
         <v>1043</v>
       </c>
-      <c r="F224" s="2">
+      <c r="F224" s="1">
         <v>46028</v>
       </c>
       <c r="G224" t="s">
@@ -13129,7 +13106,7 @@
         <v>1353</v>
       </c>
       <c r="I224">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J224">
         <v>204</v>
@@ -13137,7 +13114,7 @@
       <c r="L224" t="s">
         <v>1383</v>
       </c>
-      <c r="N224" s="2">
+      <c r="N224" s="1">
         <v>46232</v>
       </c>
       <c r="Q224" t="b">
@@ -13160,7 +13137,7 @@
       <c r="E225" t="s">
         <v>1044</v>
       </c>
-      <c r="F225" s="2">
+      <c r="F225" s="1">
         <v>46028</v>
       </c>
       <c r="G225" t="s">
@@ -13175,7 +13152,7 @@
       <c r="L225" t="s">
         <v>1383</v>
       </c>
-      <c r="N225" s="2">
+      <c r="N225" s="1">
         <v>46232</v>
       </c>
       <c r="Q225" t="b">
@@ -13198,7 +13175,7 @@
       <c r="E226" t="s">
         <v>1045</v>
       </c>
-      <c r="F226" s="2">
+      <c r="F226" s="1">
         <v>46028</v>
       </c>
       <c r="G226" t="s">
@@ -13213,7 +13190,7 @@
       <c r="L226" t="s">
         <v>1383</v>
       </c>
-      <c r="N226" s="2">
+      <c r="N226" s="1">
         <v>46232</v>
       </c>
       <c r="Q226" t="b">
@@ -13236,7 +13213,7 @@
       <c r="E227" t="s">
         <v>1046</v>
       </c>
-      <c r="F227" s="2">
+      <c r="F227" s="1">
         <v>46028</v>
       </c>
       <c r="G227" t="s">
@@ -13251,7 +13228,7 @@
       <c r="L227" t="s">
         <v>1383</v>
       </c>
-      <c r="N227" s="2">
+      <c r="N227" s="1">
         <v>46232</v>
       </c>
       <c r="Q227" t="b">
@@ -13274,7 +13251,7 @@
       <c r="E228" t="s">
         <v>1047</v>
       </c>
-      <c r="F228" s="2">
+      <c r="F228" s="1">
         <v>46028</v>
       </c>
       <c r="G228" t="s">
@@ -13284,7 +13261,7 @@
         <v>1353</v>
       </c>
       <c r="I228">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J228">
         <v>204</v>
@@ -13292,7 +13269,7 @@
       <c r="L228" t="s">
         <v>1383</v>
       </c>
-      <c r="N228" s="2">
+      <c r="N228" s="1">
         <v>46232</v>
       </c>
       <c r="Q228" t="b">
@@ -13315,7 +13292,7 @@
       <c r="E229" t="s">
         <v>1048</v>
       </c>
-      <c r="F229" s="2">
+      <c r="F229" s="1">
         <v>46028</v>
       </c>
       <c r="G229" t="s">
@@ -13330,7 +13307,7 @@
       <c r="L229" t="s">
         <v>1420</v>
       </c>
-      <c r="N229" s="2">
+      <c r="N229" s="1">
         <v>46191</v>
       </c>
       <c r="Q229" t="b">
@@ -13353,7 +13330,7 @@
       <c r="E230" t="s">
         <v>1049</v>
       </c>
-      <c r="F230" s="2">
+      <c r="F230" s="1">
         <v>46028</v>
       </c>
       <c r="G230" t="s">
@@ -13363,7 +13340,7 @@
         <v>1353</v>
       </c>
       <c r="I230">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J230">
         <v>197</v>
@@ -13374,7 +13351,7 @@
       <c r="L230" t="s">
         <v>1395</v>
       </c>
-      <c r="N230" s="2">
+      <c r="N230" s="1">
         <v>46225</v>
       </c>
       <c r="Q230" t="b">
@@ -13397,7 +13374,7 @@
       <c r="E231" t="s">
         <v>1050</v>
       </c>
-      <c r="F231" s="2">
+      <c r="F231" s="1">
         <v>46028</v>
       </c>
       <c r="G231" t="s">
@@ -13407,7 +13384,7 @@
         <v>1353</v>
       </c>
       <c r="I231">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J231">
         <v>35</v>
@@ -13418,7 +13395,7 @@
       <c r="L231" t="s">
         <v>1421</v>
       </c>
-      <c r="N231" s="2">
+      <c r="N231" s="1">
         <v>46063</v>
       </c>
       <c r="Q231" t="b">
@@ -13441,7 +13418,7 @@
       <c r="E232" t="s">
         <v>1051</v>
       </c>
-      <c r="F232" s="2">
+      <c r="F232" s="1">
         <v>46028</v>
       </c>
       <c r="G232" t="s">
@@ -13470,7 +13447,7 @@
       <c r="E233" t="s">
         <v>1052</v>
       </c>
-      <c r="F233" s="2">
+      <c r="F233" s="1">
         <v>46028</v>
       </c>
       <c r="G233" t="s">
@@ -13499,7 +13476,7 @@
       <c r="E234" t="s">
         <v>1053</v>
       </c>
-      <c r="F234" s="2">
+      <c r="F234" s="1">
         <v>46028</v>
       </c>
       <c r="G234" t="s">
@@ -13509,7 +13486,7 @@
         <v>1353</v>
       </c>
       <c r="I234">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J234">
         <v>35</v>
@@ -13520,7 +13497,7 @@
       <c r="L234" t="s">
         <v>1421</v>
       </c>
-      <c r="N234" s="2">
+      <c r="N234" s="1">
         <v>46063</v>
       </c>
       <c r="P234" t="s">
@@ -13546,7 +13523,7 @@
       <c r="E235" t="s">
         <v>1054</v>
       </c>
-      <c r="F235" s="2">
+      <c r="F235" s="1">
         <v>46028</v>
       </c>
       <c r="G235" t="s">
@@ -13556,7 +13533,7 @@
         <v>1353</v>
       </c>
       <c r="I235">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J235">
         <v>35</v>
@@ -13567,7 +13544,7 @@
       <c r="L235" t="s">
         <v>1421</v>
       </c>
-      <c r="N235" s="2">
+      <c r="N235" s="1">
         <v>46063</v>
       </c>
       <c r="P235" t="s">
@@ -13593,7 +13570,7 @@
       <c r="E236" t="s">
         <v>1055</v>
       </c>
-      <c r="F236" s="2">
+      <c r="F236" s="1">
         <v>46028</v>
       </c>
       <c r="G236" t="s">
@@ -13603,7 +13580,7 @@
         <v>1353</v>
       </c>
       <c r="I236">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J236">
         <v>86</v>
@@ -13614,7 +13591,7 @@
       <c r="L236" t="s">
         <v>1422</v>
       </c>
-      <c r="N236" s="2">
+      <c r="N236" s="1">
         <v>46114</v>
       </c>
       <c r="Q236" t="b">
@@ -13637,7 +13614,7 @@
       <c r="E237" t="s">
         <v>1056</v>
       </c>
-      <c r="F237" s="2">
+      <c r="F237" s="1">
         <v>46028</v>
       </c>
       <c r="G237" t="s">
@@ -13655,7 +13632,7 @@
       <c r="L237" t="s">
         <v>1423</v>
       </c>
-      <c r="N237" s="2">
+      <c r="N237" s="1">
         <v>46210</v>
       </c>
       <c r="P237" t="s">
@@ -13681,7 +13658,7 @@
       <c r="E238" t="s">
         <v>1057</v>
       </c>
-      <c r="F238" s="2">
+      <c r="F238" s="1">
         <v>46028</v>
       </c>
       <c r="G238" t="s">
@@ -13710,7 +13687,7 @@
       <c r="E239" t="s">
         <v>1058</v>
       </c>
-      <c r="F239" s="2">
+      <c r="F239" s="1">
         <v>46036</v>
       </c>
       <c r="G239" t="s">
@@ -13720,7 +13697,7 @@
         <v>1353</v>
       </c>
       <c r="I239">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K239" t="s">
         <v>1330</v>
@@ -13728,7 +13705,7 @@
       <c r="L239" t="s">
         <v>1424</v>
       </c>
-      <c r="N239" s="2">
+      <c r="N239" s="1">
         <v>46052</v>
       </c>
       <c r="Q239" t="b">
@@ -13751,7 +13728,7 @@
       <c r="E240" t="s">
         <v>1059</v>
       </c>
-      <c r="F240" s="2">
+      <c r="F240" s="1">
         <v>46036</v>
       </c>
       <c r="G240" t="s">
@@ -13780,7 +13757,7 @@
       <c r="E241" t="s">
         <v>1060</v>
       </c>
-      <c r="F241" s="2">
+      <c r="F241" s="1">
         <v>46036</v>
       </c>
       <c r="G241" t="s">
@@ -13809,7 +13786,7 @@
       <c r="E242" t="s">
         <v>1061</v>
       </c>
-      <c r="F242" s="2">
+      <c r="F242" s="1">
         <v>46036</v>
       </c>
       <c r="G242" t="s">
@@ -13819,7 +13796,7 @@
         <v>1353</v>
       </c>
       <c r="I242">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K242" t="s">
         <v>1356</v>
@@ -13847,7 +13824,7 @@
       <c r="E243" t="s">
         <v>1062</v>
       </c>
-      <c r="F243" s="2">
+      <c r="F243" s="1">
         <v>46048</v>
       </c>
       <c r="G243" t="s">
@@ -13876,7 +13853,7 @@
       <c r="E244" t="s">
         <v>1063</v>
       </c>
-      <c r="F244" s="2">
+      <c r="F244" s="1">
         <v>46048</v>
       </c>
       <c r="G244" t="s">
@@ -13886,7 +13863,7 @@
         <v>1353</v>
       </c>
       <c r="I244">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="J244">
         <v>15</v>
@@ -13894,7 +13871,7 @@
       <c r="K244" t="s">
         <v>1359</v>
       </c>
-      <c r="N244" s="2">
+      <c r="N244" s="1">
         <v>46063</v>
       </c>
       <c r="Q244" t="b">
@@ -13917,7 +13894,7 @@
       <c r="E245" t="s">
         <v>1064</v>
       </c>
-      <c r="F245" s="2">
+      <c r="F245" s="1">
         <v>46048</v>
       </c>
       <c r="G245" t="s">
@@ -13927,7 +13904,7 @@
         <v>1353</v>
       </c>
       <c r="I245">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="J245">
         <v>15</v>
@@ -13938,7 +13915,7 @@
       <c r="L245" t="s">
         <v>1425</v>
       </c>
-      <c r="N245" s="2">
+      <c r="N245" s="1">
         <v>46063</v>
       </c>
       <c r="Q245" t="b">
@@ -13961,7 +13938,7 @@
       <c r="E246" t="s">
         <v>1065</v>
       </c>
-      <c r="F246" s="2">
+      <c r="F246" s="1">
         <v>46050</v>
       </c>
       <c r="G246" t="s">
@@ -13979,7 +13956,7 @@
       <c r="L246" t="s">
         <v>1426</v>
       </c>
-      <c r="N246" s="2">
+      <c r="N246" s="1">
         <v>46191</v>
       </c>
       <c r="Q246" t="b">
@@ -14002,7 +13979,7 @@
       <c r="E247" t="s">
         <v>1066</v>
       </c>
-      <c r="F247" s="2">
+      <c r="F247" s="1">
         <v>46050</v>
       </c>
       <c r="G247" t="s">
@@ -14031,7 +14008,7 @@
       <c r="E248" t="s">
         <v>1067</v>
       </c>
-      <c r="F248" s="2">
+      <c r="F248" s="1">
         <v>46050</v>
       </c>
       <c r="G248" t="s">
@@ -14060,7 +14037,7 @@
       <c r="E249" t="s">
         <v>1068</v>
       </c>
-      <c r="F249" s="2">
+      <c r="F249" s="1">
         <v>46050</v>
       </c>
       <c r="G249" t="s">
@@ -14070,7 +14047,7 @@
         <v>1353</v>
       </c>
       <c r="I249">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="K249" t="s">
         <v>1357</v>
@@ -14098,7 +14075,7 @@
       <c r="E250" t="s">
         <v>1069</v>
       </c>
-      <c r="F250" s="2">
+      <c r="F250" s="1">
         <v>46063</v>
       </c>
       <c r="G250" t="s">
@@ -14136,7 +14113,7 @@
       <c r="E251" t="s">
         <v>1070</v>
       </c>
-      <c r="F251" s="2">
+      <c r="F251" s="1">
         <v>46063</v>
       </c>
       <c r="G251" t="s">
@@ -14165,7 +14142,7 @@
       <c r="E252" t="s">
         <v>1071</v>
       </c>
-      <c r="F252" s="2">
+      <c r="F252" s="1">
         <v>46063</v>
       </c>
       <c r="G252" t="s">
@@ -14194,7 +14171,7 @@
       <c r="E253" t="s">
         <v>1072</v>
       </c>
-      <c r="F253" s="2">
+      <c r="F253" s="1">
         <v>46063</v>
       </c>
       <c r="G253" t="s">
@@ -14204,7 +14181,7 @@
         <v>1353</v>
       </c>
       <c r="I253">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J253">
         <v>162</v>
@@ -14215,7 +14192,7 @@
       <c r="L253" t="s">
         <v>1395</v>
       </c>
-      <c r="N253" s="2">
+      <c r="N253" s="1">
         <v>46225</v>
       </c>
       <c r="Q253" t="b">
@@ -14238,7 +14215,7 @@
       <c r="E254" t="s">
         <v>1073</v>
       </c>
-      <c r="F254" s="2">
+      <c r="F254" s="1">
         <v>46063</v>
       </c>
       <c r="G254" t="s">
@@ -14248,7 +14225,7 @@
         <v>1353</v>
       </c>
       <c r="I254">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K254" t="s">
         <v>1360</v>
@@ -14276,7 +14253,7 @@
       <c r="E255" t="s">
         <v>1074</v>
       </c>
-      <c r="F255" s="2">
+      <c r="F255" s="1">
         <v>46063</v>
       </c>
       <c r="G255" t="s">
@@ -14286,7 +14263,7 @@
         <v>1353</v>
       </c>
       <c r="I255">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J255">
         <v>72</v>
@@ -14297,7 +14274,7 @@
       <c r="L255" t="s">
         <v>1388</v>
       </c>
-      <c r="N255" s="2">
+      <c r="N255" s="1">
         <v>46135</v>
       </c>
       <c r="Q255" t="b">
@@ -14320,7 +14297,7 @@
       <c r="E256" t="s">
         <v>1075</v>
       </c>
-      <c r="F256" s="2">
+      <c r="F256" s="1">
         <v>46063</v>
       </c>
       <c r="G256" t="s">
@@ -14330,7 +14307,7 @@
         <v>1353</v>
       </c>
       <c r="I256">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J256">
         <v>23</v>
@@ -14338,7 +14315,7 @@
       <c r="K256" t="s">
         <v>1357</v>
       </c>
-      <c r="N256" s="2">
+      <c r="N256" s="1">
         <v>46086</v>
       </c>
       <c r="O256">
@@ -14364,7 +14341,7 @@
       <c r="E257" t="s">
         <v>1076</v>
       </c>
-      <c r="F257" s="2">
+      <c r="F257" s="1">
         <v>46063</v>
       </c>
       <c r="G257" t="s">
@@ -14393,7 +14370,7 @@
       <c r="E258" t="s">
         <v>1077</v>
       </c>
-      <c r="F258" s="2">
+      <c r="F258" s="1">
         <v>46063</v>
       </c>
       <c r="G258" t="s">
@@ -14422,7 +14399,7 @@
       <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="F259" s="2">
+      <c r="F259" s="1">
         <v>46063</v>
       </c>
       <c r="G259" t="s">
@@ -14432,7 +14409,7 @@
         <v>1353</v>
       </c>
       <c r="I259">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J259">
         <v>72</v>
@@ -14443,7 +14420,7 @@
       <c r="L259" t="s">
         <v>1388</v>
       </c>
-      <c r="N259" s="2">
+      <c r="N259" s="1">
         <v>46135</v>
       </c>
       <c r="Q259" t="b">
@@ -14466,7 +14443,7 @@
       <c r="E260" t="s">
         <v>1079</v>
       </c>
-      <c r="F260" s="2">
+      <c r="F260" s="1">
         <v>46063</v>
       </c>
       <c r="G260" t="s">
@@ -14476,7 +14453,7 @@
         <v>1353</v>
       </c>
       <c r="I260">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J260">
         <v>84</v>
@@ -14487,7 +14464,7 @@
       <c r="L260" t="s">
         <v>1388</v>
       </c>
-      <c r="N260" s="2">
+      <c r="N260" s="1">
         <v>46147</v>
       </c>
       <c r="Q260" t="b">
@@ -14510,7 +14487,7 @@
       <c r="E261" t="s">
         <v>1080</v>
       </c>
-      <c r="F261" s="2">
+      <c r="F261" s="1">
         <v>46063</v>
       </c>
       <c r="G261" t="s">
@@ -14520,7 +14497,7 @@
         <v>1353</v>
       </c>
       <c r="I261">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J261">
         <v>162</v>
@@ -14531,7 +14508,7 @@
       <c r="L261" t="s">
         <v>1427</v>
       </c>
-      <c r="N261" s="2">
+      <c r="N261" s="1">
         <v>46225</v>
       </c>
       <c r="Q261" t="b">
@@ -14554,7 +14531,7 @@
       <c r="E262" t="s">
         <v>1081</v>
       </c>
-      <c r="F262" s="2">
+      <c r="F262" s="1">
         <v>46063</v>
       </c>
       <c r="G262" t="s">
@@ -14572,7 +14549,7 @@
       <c r="L262" t="s">
         <v>1428</v>
       </c>
-      <c r="N262" s="2">
+      <c r="N262" s="1">
         <v>46113</v>
       </c>
       <c r="P262" t="s">
@@ -14598,7 +14575,7 @@
       <c r="E263" t="s">
         <v>1082</v>
       </c>
-      <c r="F263" s="2">
+      <c r="F263" s="1">
         <v>46063</v>
       </c>
       <c r="G263" t="s">
@@ -14627,7 +14604,7 @@
       <c r="E264" t="s">
         <v>1083</v>
       </c>
-      <c r="F264" s="2">
+      <c r="F264" s="1">
         <v>46063</v>
       </c>
       <c r="G264" t="s">
@@ -14637,7 +14614,7 @@
         <v>1353</v>
       </c>
       <c r="I264">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J264">
         <v>162</v>
@@ -14648,7 +14625,7 @@
       <c r="L264" t="s">
         <v>1388</v>
       </c>
-      <c r="N264" s="2">
+      <c r="N264" s="1">
         <v>46225</v>
       </c>
       <c r="Q264" t="b">
@@ -14671,7 +14648,7 @@
       <c r="E265" t="s">
         <v>1084</v>
       </c>
-      <c r="F265" s="2">
+      <c r="F265" s="1">
         <v>46063</v>
       </c>
       <c r="G265" t="s">
@@ -14681,7 +14658,7 @@
         <v>1353</v>
       </c>
       <c r="I265">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J265">
         <v>162</v>
@@ -14692,7 +14669,7 @@
       <c r="L265" t="s">
         <v>1395</v>
       </c>
-      <c r="N265" s="2">
+      <c r="N265" s="1">
         <v>46225</v>
       </c>
       <c r="Q265" t="b">
@@ -14715,7 +14692,7 @@
       <c r="E266" t="s">
         <v>1085</v>
       </c>
-      <c r="F266" s="2">
+      <c r="F266" s="1">
         <v>46063</v>
       </c>
       <c r="G266" t="s">
@@ -14725,7 +14702,7 @@
         <v>1353</v>
       </c>
       <c r="I266">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J266">
         <v>84</v>
@@ -14736,7 +14713,7 @@
       <c r="L266" t="s">
         <v>1388</v>
       </c>
-      <c r="N266" s="2">
+      <c r="N266" s="1">
         <v>46147</v>
       </c>
       <c r="Q266" t="b">
@@ -14759,7 +14736,7 @@
       <c r="E267" t="s">
         <v>1086</v>
       </c>
-      <c r="F267" s="2">
+      <c r="F267" s="1">
         <v>46063</v>
       </c>
       <c r="G267" t="s">
@@ -14769,7 +14746,7 @@
         <v>1353</v>
       </c>
       <c r="I267">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K267" t="s">
         <v>1360</v>
@@ -14797,7 +14774,7 @@
       <c r="E268" t="s">
         <v>1087</v>
       </c>
-      <c r="F268" s="2">
+      <c r="F268" s="1">
         <v>46063</v>
       </c>
       <c r="G268" t="s">
@@ -14807,7 +14784,7 @@
         <v>1353</v>
       </c>
       <c r="I268">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K268" t="s">
         <v>1357</v>
@@ -14832,7 +14809,7 @@
       <c r="D269" t="s">
         <v>798</v>
       </c>
-      <c r="F269" s="2">
+      <c r="F269" s="1">
         <v>46063</v>
       </c>
       <c r="G269" t="s">
@@ -14842,7 +14819,7 @@
         <v>1353</v>
       </c>
       <c r="I269">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K269" t="s">
         <v>1357</v>
@@ -14870,7 +14847,7 @@
       <c r="E270" t="s">
         <v>1088</v>
       </c>
-      <c r="F270" s="2">
+      <c r="F270" s="1">
         <v>46063</v>
       </c>
       <c r="G270" t="s">
@@ -14880,7 +14857,7 @@
         <v>1353</v>
       </c>
       <c r="I270">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K270" t="s">
         <v>1360</v>
@@ -14908,7 +14885,7 @@
       <c r="E271" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="2">
+      <c r="F271" s="1">
         <v>46063</v>
       </c>
       <c r="G271" t="s">
@@ -14918,7 +14895,7 @@
         <v>1353</v>
       </c>
       <c r="I271">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K271" t="s">
         <v>1360</v>
@@ -14946,7 +14923,7 @@
       <c r="E272" t="s">
         <v>1090</v>
       </c>
-      <c r="F272" s="2">
+      <c r="F272" s="1">
         <v>46063</v>
       </c>
       <c r="G272" t="s">
@@ -14964,7 +14941,7 @@
       <c r="L272" t="s">
         <v>1429</v>
       </c>
-      <c r="N272" s="2">
+      <c r="N272" s="1">
         <v>46185</v>
       </c>
       <c r="O272" t="s">
@@ -14990,7 +14967,7 @@
       <c r="E273" t="s">
         <v>1091</v>
       </c>
-      <c r="F273" s="2">
+      <c r="F273" s="1">
         <v>46063</v>
       </c>
       <c r="G273" t="s">
@@ -15019,7 +14996,7 @@
       <c r="E274" t="s">
         <v>1092</v>
       </c>
-      <c r="F274" s="2">
+      <c r="F274" s="1">
         <v>46063</v>
       </c>
       <c r="G274" t="s">
@@ -15034,7 +15011,7 @@
       <c r="L274" t="s">
         <v>1383</v>
       </c>
-      <c r="N274" s="2">
+      <c r="N274" s="1">
         <v>46232</v>
       </c>
       <c r="Q274" t="b">
@@ -15057,7 +15034,7 @@
       <c r="E275" t="s">
         <v>1093</v>
       </c>
-      <c r="F275" s="2">
+      <c r="F275" s="1">
         <v>46063</v>
       </c>
       <c r="G275" t="s">
@@ -15086,7 +15063,7 @@
       <c r="E276" t="s">
         <v>1094</v>
       </c>
-      <c r="F276" s="2">
+      <c r="F276" s="1">
         <v>46063</v>
       </c>
       <c r="G276" t="s">
@@ -15096,7 +15073,7 @@
         <v>1353</v>
       </c>
       <c r="I276">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K276" t="s">
         <v>1361</v>
@@ -15124,7 +15101,7 @@
       <c r="E277" t="s">
         <v>1095</v>
       </c>
-      <c r="F277" s="2">
+      <c r="F277" s="1">
         <v>46063</v>
       </c>
       <c r="G277" t="s">
@@ -15134,7 +15111,7 @@
         <v>1353</v>
       </c>
       <c r="I277">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K277" t="s">
         <v>1357</v>
@@ -15162,7 +15139,7 @@
       <c r="E278" t="s">
         <v>1096</v>
       </c>
-      <c r="F278" s="2">
+      <c r="F278" s="1">
         <v>46077</v>
       </c>
       <c r="G278" t="s">
@@ -15172,7 +15149,7 @@
         <v>1353</v>
       </c>
       <c r="I278">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J278">
         <v>148</v>
@@ -15183,7 +15160,7 @@
       <c r="L278" t="s">
         <v>1395</v>
       </c>
-      <c r="N278" s="2">
+      <c r="N278" s="1">
         <v>46225</v>
       </c>
       <c r="Q278" t="b">
@@ -15206,7 +15183,7 @@
       <c r="E279" t="s">
         <v>1097</v>
       </c>
-      <c r="F279" s="2">
+      <c r="F279" s="1">
         <v>46077</v>
       </c>
       <c r="G279" t="s">
@@ -15216,7 +15193,7 @@
         <v>1353</v>
       </c>
       <c r="I279">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K279" t="s">
         <v>1359</v>
@@ -15247,7 +15224,7 @@
       <c r="E280" t="s">
         <v>1098</v>
       </c>
-      <c r="F280" s="2">
+      <c r="F280" s="1">
         <v>46085</v>
       </c>
       <c r="G280" t="s">
@@ -15257,7 +15234,7 @@
         <v>1353</v>
       </c>
       <c r="I280">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K280" t="s">
         <v>1357</v>
@@ -15285,7 +15262,7 @@
       <c r="E281" t="s">
         <v>1099</v>
       </c>
-      <c r="F281" s="2">
+      <c r="F281" s="1">
         <v>46085</v>
       </c>
       <c r="G281" t="s">
@@ -15295,7 +15272,7 @@
         <v>1353</v>
       </c>
       <c r="I281">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K281" t="s">
         <v>1357</v>
@@ -15326,7 +15303,7 @@
       <c r="E282" t="s">
         <v>1100</v>
       </c>
-      <c r="F282" s="2">
+      <c r="F282" s="1">
         <v>46090</v>
       </c>
       <c r="G282" t="s">
@@ -15336,7 +15313,7 @@
         <v>1353</v>
       </c>
       <c r="I282">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K282" t="s">
         <v>1357</v>
@@ -15364,7 +15341,7 @@
       <c r="E283" t="s">
         <v>1101</v>
       </c>
-      <c r="F283" s="2">
+      <c r="F283" s="1">
         <v>46100</v>
       </c>
       <c r="G283" t="s">
@@ -15393,7 +15370,7 @@
       <c r="E284" t="s">
         <v>1102</v>
       </c>
-      <c r="F284" s="2">
+      <c r="F284" s="1">
         <v>46100</v>
       </c>
       <c r="G284" t="s">
@@ -15422,7 +15399,7 @@
       <c r="E285" t="s">
         <v>1103</v>
       </c>
-      <c r="F285" s="2">
+      <c r="F285" s="1">
         <v>46100</v>
       </c>
       <c r="G285" t="s">
@@ -15451,7 +15428,7 @@
       <c r="E286" t="s">
         <v>1104</v>
       </c>
-      <c r="F286" s="2">
+      <c r="F286" s="1">
         <v>46100</v>
       </c>
       <c r="G286" t="s">
@@ -15480,7 +15457,7 @@
       <c r="E287" t="s">
         <v>1105</v>
       </c>
-      <c r="F287" s="2">
+      <c r="F287" s="1">
         <v>46107</v>
       </c>
       <c r="G287" t="s">
@@ -15509,7 +15486,7 @@
       <c r="E288" t="s">
         <v>1106</v>
       </c>
-      <c r="F288" s="2">
+      <c r="F288" s="1">
         <v>46107</v>
       </c>
       <c r="G288" t="s">
@@ -15519,7 +15496,7 @@
         <v>1353</v>
       </c>
       <c r="I288">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J288">
         <v>28</v>
@@ -15530,7 +15507,7 @@
       <c r="L288" t="s">
         <v>1388</v>
       </c>
-      <c r="N288" s="2">
+      <c r="N288" s="1">
         <v>46135</v>
       </c>
       <c r="Q288" t="b">
@@ -15553,7 +15530,7 @@
       <c r="E289" t="s">
         <v>1107</v>
       </c>
-      <c r="F289" s="2">
+      <c r="F289" s="1">
         <v>46107</v>
       </c>
       <c r="G289" t="s">
@@ -15582,7 +15559,7 @@
       <c r="E290" t="s">
         <v>1108</v>
       </c>
-      <c r="F290" s="2">
+      <c r="F290" s="1">
         <v>46107</v>
       </c>
       <c r="G290" t="s">
@@ -15592,7 +15569,7 @@
         <v>1353</v>
       </c>
       <c r="I290">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J290">
         <v>20</v>
@@ -15603,7 +15580,7 @@
       <c r="L290" t="s">
         <v>1388</v>
       </c>
-      <c r="N290" s="2">
+      <c r="N290" s="1">
         <v>46127</v>
       </c>
       <c r="Q290" t="b">
@@ -15626,7 +15603,7 @@
       <c r="E291" t="s">
         <v>1109</v>
       </c>
-      <c r="F291" s="2">
+      <c r="F291" s="1">
         <v>46107</v>
       </c>
       <c r="G291" t="s">
@@ -15636,7 +15613,7 @@
         <v>1353</v>
       </c>
       <c r="I291">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J291">
         <v>20</v>
@@ -15647,7 +15624,7 @@
       <c r="L291" t="s">
         <v>1430</v>
       </c>
-      <c r="N291" s="2">
+      <c r="N291" s="1">
         <v>46127</v>
       </c>
       <c r="Q291" t="b">
@@ -15670,7 +15647,7 @@
       <c r="E292" t="s">
         <v>1110</v>
       </c>
-      <c r="F292" s="2">
+      <c r="F292" s="1">
         <v>46112</v>
       </c>
       <c r="G292" t="s">
@@ -15680,7 +15657,7 @@
         <v>1353</v>
       </c>
       <c r="I292">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K292" t="s">
         <v>1360</v>
@@ -15708,7 +15685,7 @@
       <c r="E293" t="s">
         <v>1111</v>
       </c>
-      <c r="F293" s="2">
+      <c r="F293" s="1">
         <v>46125</v>
       </c>
       <c r="G293" t="s">
@@ -15718,7 +15695,7 @@
         <v>1353</v>
       </c>
       <c r="I293">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K293" t="s">
         <v>1361</v>
@@ -15746,7 +15723,7 @@
       <c r="E294" t="s">
         <v>1112</v>
       </c>
-      <c r="F294" s="2">
+      <c r="F294" s="1">
         <v>46125</v>
       </c>
       <c r="G294" t="s">
@@ -15756,7 +15733,7 @@
         <v>1353</v>
       </c>
       <c r="I294">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K294" t="s">
         <v>1366</v>
@@ -15781,7 +15758,7 @@
       <c r="E295" t="s">
         <v>1113</v>
       </c>
-      <c r="F295" s="2">
+      <c r="F295" s="1">
         <v>46125</v>
       </c>
       <c r="G295" t="s">
@@ -15791,7 +15768,7 @@
         <v>1353</v>
       </c>
       <c r="I295">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K295" t="s">
         <v>1366</v>
@@ -15816,7 +15793,7 @@
       <c r="E296" t="s">
         <v>1114</v>
       </c>
-      <c r="F296" s="2">
+      <c r="F296" s="1">
         <v>46125</v>
       </c>
       <c r="G296" t="s">
@@ -15826,7 +15803,7 @@
         <v>1353</v>
       </c>
       <c r="I296">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K296" t="s">
         <v>1366</v>
@@ -15851,7 +15828,7 @@
       <c r="E297" t="s">
         <v>1115</v>
       </c>
-      <c r="F297" s="2">
+      <c r="F297" s="1">
         <v>46125</v>
       </c>
       <c r="G297" t="s">
@@ -15863,7 +15840,7 @@
       <c r="K297" t="s">
         <v>1359</v>
       </c>
-      <c r="N297" s="2">
+      <c r="N297" s="1">
         <v>46183</v>
       </c>
       <c r="O297">
@@ -15889,7 +15866,7 @@
       <c r="E298" t="s">
         <v>1116</v>
       </c>
-      <c r="F298" s="2">
+      <c r="F298" s="1">
         <v>46125</v>
       </c>
       <c r="G298" t="s">
@@ -15899,7 +15876,7 @@
         <v>1353</v>
       </c>
       <c r="I298">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J298">
         <v>58</v>
@@ -15907,7 +15884,7 @@
       <c r="K298" t="s">
         <v>1359</v>
       </c>
-      <c r="N298" s="2">
+      <c r="N298" s="1">
         <v>46183</v>
       </c>
       <c r="Q298" t="b">
@@ -15930,7 +15907,7 @@
       <c r="E299" t="s">
         <v>1117</v>
       </c>
-      <c r="F299" s="2">
+      <c r="F299" s="1">
         <v>46125</v>
       </c>
       <c r="G299" t="s">
@@ -15940,7 +15917,7 @@
         <v>1353</v>
       </c>
       <c r="I299">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J299">
         <v>100</v>
@@ -15951,7 +15928,7 @@
       <c r="L299" t="s">
         <v>1388</v>
       </c>
-      <c r="N299" s="2">
+      <c r="N299" s="1">
         <v>46225</v>
       </c>
       <c r="Q299" t="b">
@@ -15974,7 +15951,7 @@
       <c r="E300" t="s">
         <v>1118</v>
       </c>
-      <c r="F300" s="2">
+      <c r="F300" s="1">
         <v>46125</v>
       </c>
       <c r="G300" t="s">
@@ -15984,7 +15961,7 @@
         <v>1353</v>
       </c>
       <c r="I300">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J300">
         <v>86</v>
@@ -15995,7 +15972,7 @@
       <c r="L300" t="s">
         <v>1388</v>
       </c>
-      <c r="N300" s="2">
+      <c r="N300" s="1">
         <v>46211</v>
       </c>
       <c r="Q300" t="b">
@@ -16018,7 +15995,7 @@
       <c r="E301" t="s">
         <v>1119</v>
       </c>
-      <c r="F301" s="2">
+      <c r="F301" s="1">
         <v>46125</v>
       </c>
       <c r="G301" t="s">
@@ -16028,7 +16005,7 @@
         <v>1353</v>
       </c>
       <c r="I301">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J301">
         <v>102</v>
@@ -16039,7 +16016,7 @@
       <c r="L301" t="s">
         <v>1388</v>
       </c>
-      <c r="N301" s="2">
+      <c r="N301" s="1">
         <v>46227</v>
       </c>
       <c r="Q301" t="b">
@@ -16062,7 +16039,7 @@
       <c r="E302" t="s">
         <v>1120</v>
       </c>
-      <c r="F302" s="2">
+      <c r="F302" s="1">
         <v>46125</v>
       </c>
       <c r="G302" t="s">
@@ -16072,7 +16049,7 @@
         <v>1353</v>
       </c>
       <c r="I302">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K302" t="s">
         <v>1360</v>
@@ -16100,7 +16077,7 @@
       <c r="E303" t="s">
         <v>1121</v>
       </c>
-      <c r="F303" s="2">
+      <c r="F303" s="1">
         <v>46125</v>
       </c>
       <c r="G303" t="s">
@@ -16110,7 +16087,7 @@
         <v>1353</v>
       </c>
       <c r="I303">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K303" t="s">
         <v>1357</v>
@@ -16138,7 +16115,7 @@
       <c r="E304" t="s">
         <v>1122</v>
       </c>
-      <c r="F304" s="2">
+      <c r="F304" s="1">
         <v>46125</v>
       </c>
       <c r="G304" t="s">
@@ -16148,7 +16125,7 @@
         <v>1353</v>
       </c>
       <c r="I304">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K304" t="s">
         <v>1360</v>
@@ -16176,7 +16153,7 @@
       <c r="E305" t="s">
         <v>1123</v>
       </c>
-      <c r="F305" s="2">
+      <c r="F305" s="1">
         <v>46125</v>
       </c>
       <c r="G305" t="s">
@@ -16186,7 +16163,7 @@
         <v>1353</v>
       </c>
       <c r="I305">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J305">
         <v>35</v>
@@ -16197,7 +16174,7 @@
       <c r="L305" t="s">
         <v>1431</v>
       </c>
-      <c r="N305" s="2">
+      <c r="N305" s="1">
         <v>46160</v>
       </c>
       <c r="Q305" t="b">
@@ -16220,7 +16197,7 @@
       <c r="E306" t="s">
         <v>1124</v>
       </c>
-      <c r="F306" s="2">
+      <c r="F306" s="1">
         <v>46125</v>
       </c>
       <c r="G306" t="s">
@@ -16230,7 +16207,7 @@
         <v>1353</v>
       </c>
       <c r="I306">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J306">
         <v>31</v>
@@ -16241,7 +16218,7 @@
       <c r="L306" t="s">
         <v>1432</v>
       </c>
-      <c r="N306" s="2">
+      <c r="N306" s="1">
         <v>46156</v>
       </c>
       <c r="Q306" t="b">
@@ -16264,7 +16241,7 @@
       <c r="E307" t="s">
         <v>1125</v>
       </c>
-      <c r="F307" s="2">
+      <c r="F307" s="1">
         <v>46125</v>
       </c>
       <c r="G307" t="s">
@@ -16282,7 +16259,7 @@
       <c r="L307" t="s">
         <v>1433</v>
       </c>
-      <c r="N307" s="2">
+      <c r="N307" s="1">
         <v>46209</v>
       </c>
       <c r="P307" t="s">
@@ -16308,7 +16285,7 @@
       <c r="E308" t="s">
         <v>1126</v>
       </c>
-      <c r="F308" s="2">
+      <c r="F308" s="1">
         <v>46125</v>
       </c>
       <c r="G308" t="s">
@@ -16318,7 +16295,7 @@
         <v>1353</v>
       </c>
       <c r="I308">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K308" t="s">
         <v>1356</v>
@@ -16346,7 +16323,7 @@
       <c r="E309" t="s">
         <v>1127</v>
       </c>
-      <c r="F309" s="2">
+      <c r="F309" s="1">
         <v>46125</v>
       </c>
       <c r="G309" t="s">
@@ -16361,7 +16338,7 @@
       <c r="L309" t="s">
         <v>1383</v>
       </c>
-      <c r="N309" s="2">
+      <c r="N309" s="1">
         <v>46232</v>
       </c>
       <c r="Q309" t="b">
@@ -16384,7 +16361,7 @@
       <c r="E310" t="s">
         <v>1128</v>
       </c>
-      <c r="F310" s="2">
+      <c r="F310" s="1">
         <v>46125</v>
       </c>
       <c r="G310" t="s">
@@ -16394,7 +16371,7 @@
         <v>1353</v>
       </c>
       <c r="I310">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J310">
         <v>107</v>
@@ -16405,7 +16382,7 @@
       <c r="L310" t="s">
         <v>1383</v>
       </c>
-      <c r="N310" s="2">
+      <c r="N310" s="1">
         <v>46232</v>
       </c>
       <c r="Q310" t="b">
@@ -16428,7 +16405,7 @@
       <c r="E311" t="s">
         <v>1129</v>
       </c>
-      <c r="F311" s="2">
+      <c r="F311" s="1">
         <v>46125</v>
       </c>
       <c r="G311" t="s">
@@ -16438,7 +16415,7 @@
         <v>1353</v>
       </c>
       <c r="I311">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K311" t="s">
         <v>1356</v>
@@ -16466,7 +16443,7 @@
       <c r="E312" t="s">
         <v>1130</v>
       </c>
-      <c r="F312" s="2">
+      <c r="F312" s="1">
         <v>46125</v>
       </c>
       <c r="G312" t="s">
@@ -16484,7 +16461,7 @@
       <c r="L312" t="s">
         <v>1383</v>
       </c>
-      <c r="N312" s="2">
+      <c r="N312" s="1">
         <v>46232</v>
       </c>
       <c r="Q312" t="b">
@@ -16507,7 +16484,7 @@
       <c r="E313" t="s">
         <v>1131</v>
       </c>
-      <c r="F313" s="2">
+      <c r="F313" s="1">
         <v>46125</v>
       </c>
       <c r="G313" t="s">
@@ -16542,7 +16519,7 @@
       <c r="E314" t="s">
         <v>1132</v>
       </c>
-      <c r="F314" s="2">
+      <c r="F314" s="1">
         <v>46125</v>
       </c>
       <c r="G314" t="s">
@@ -16557,7 +16534,7 @@
       <c r="L314" t="s">
         <v>1383</v>
       </c>
-      <c r="N314" s="2">
+      <c r="N314" s="1">
         <v>46232</v>
       </c>
       <c r="Q314" t="b">
@@ -16580,7 +16557,7 @@
       <c r="E315" t="s">
         <v>1133</v>
       </c>
-      <c r="F315" s="2">
+      <c r="F315" s="1">
         <v>46125</v>
       </c>
       <c r="G315" t="s">
@@ -16595,7 +16572,7 @@
       <c r="L315" t="s">
         <v>1383</v>
       </c>
-      <c r="N315" s="2">
+      <c r="N315" s="1">
         <v>46232</v>
       </c>
       <c r="Q315" t="b">
@@ -16618,7 +16595,7 @@
       <c r="E316" t="s">
         <v>1134</v>
       </c>
-      <c r="F316" s="2">
+      <c r="F316" s="1">
         <v>46125</v>
       </c>
       <c r="G316" t="s">
@@ -16628,13 +16605,16 @@
         <v>1353</v>
       </c>
       <c r="I316">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K316" t="s">
         <v>1357</v>
       </c>
       <c r="M316" t="s">
         <v>1454</v>
+      </c>
+      <c r="P316" t="s">
+        <v>1492</v>
       </c>
       <c r="Q316" t="b">
         <v>1</v>
@@ -16656,7 +16636,7 @@
       <c r="E317" t="s">
         <v>1135</v>
       </c>
-      <c r="F317" s="2">
+      <c r="F317" s="1">
         <v>46125</v>
       </c>
       <c r="G317" t="s">
@@ -16691,7 +16671,7 @@
       <c r="E318" t="s">
         <v>1136</v>
       </c>
-      <c r="F318" s="2">
+      <c r="F318" s="1">
         <v>46125</v>
       </c>
       <c r="G318" t="s">
@@ -16720,7 +16700,7 @@
       <c r="E319" t="s">
         <v>1137</v>
       </c>
-      <c r="F319" s="2">
+      <c r="F319" s="1">
         <v>46125</v>
       </c>
       <c r="G319" t="s">
@@ -16735,7 +16715,7 @@
       <c r="L319" t="s">
         <v>1434</v>
       </c>
-      <c r="N319" s="2">
+      <c r="N319" s="1">
         <v>46175</v>
       </c>
       <c r="Q319" t="b">
@@ -16758,7 +16738,7 @@
       <c r="E320" t="s">
         <v>1138</v>
       </c>
-      <c r="F320" s="2">
+      <c r="F320" s="1">
         <v>46125</v>
       </c>
       <c r="G320" t="s">
@@ -16768,7 +16748,7 @@
         <v>1353</v>
       </c>
       <c r="I320">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K320" t="s">
         <v>1361</v>
@@ -16796,7 +16776,7 @@
       <c r="E321" t="s">
         <v>1139</v>
       </c>
-      <c r="F321" s="2">
+      <c r="F321" s="1">
         <v>46125</v>
       </c>
       <c r="G321" t="s">
@@ -16806,7 +16786,7 @@
         <v>1353</v>
       </c>
       <c r="I321">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K321" t="s">
         <v>1357</v>
@@ -16834,7 +16814,7 @@
       <c r="E322" t="s">
         <v>1140</v>
       </c>
-      <c r="F322" s="2">
+      <c r="F322" s="1">
         <v>46125</v>
       </c>
       <c r="G322" t="s">
@@ -16844,7 +16824,7 @@
         <v>1353</v>
       </c>
       <c r="I322">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J322">
         <v>57</v>
@@ -16855,7 +16835,7 @@
       <c r="L322" t="s">
         <v>1435</v>
       </c>
-      <c r="N322" s="2">
+      <c r="N322" s="1">
         <v>46182</v>
       </c>
       <c r="Q322" t="b">
@@ -16878,7 +16858,7 @@
       <c r="E323" t="s">
         <v>1141</v>
       </c>
-      <c r="F323" s="2">
+      <c r="F323" s="1">
         <v>46125</v>
       </c>
       <c r="G323" t="s">
@@ -16913,7 +16893,7 @@
       <c r="E324" t="s">
         <v>1142</v>
       </c>
-      <c r="F324" s="2">
+      <c r="F324" s="1">
         <v>46125</v>
       </c>
       <c r="G324" t="s">
@@ -16948,7 +16928,7 @@
       <c r="E325" t="s">
         <v>1143</v>
       </c>
-      <c r="F325" s="2">
+      <c r="F325" s="1">
         <v>46125</v>
       </c>
       <c r="G325" t="s">
@@ -16958,7 +16938,7 @@
         <v>1353</v>
       </c>
       <c r="I325">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J325">
         <v>57</v>
@@ -16969,7 +16949,7 @@
       <c r="L325" t="s">
         <v>1435</v>
       </c>
-      <c r="N325" s="2">
+      <c r="N325" s="1">
         <v>46182</v>
       </c>
       <c r="Q325" t="b">
@@ -16992,7 +16972,7 @@
       <c r="E326" t="s">
         <v>1144</v>
       </c>
-      <c r="F326" s="2">
+      <c r="F326" s="1">
         <v>46125</v>
       </c>
       <c r="G326" t="s">
@@ -17007,7 +16987,7 @@
       <c r="L326" t="s">
         <v>1383</v>
       </c>
-      <c r="N326" s="2">
+      <c r="N326" s="1">
         <v>46232</v>
       </c>
       <c r="Q326" t="b">
@@ -17030,7 +17010,7 @@
       <c r="E327" t="s">
         <v>1140</v>
       </c>
-      <c r="F327" s="2">
+      <c r="F327" s="1">
         <v>46125</v>
       </c>
       <c r="G327" t="s">
@@ -17040,7 +17020,7 @@
         <v>1353</v>
       </c>
       <c r="I327">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J327">
         <v>57</v>
@@ -17051,7 +17031,7 @@
       <c r="L327" t="s">
         <v>1435</v>
       </c>
-      <c r="N327" s="2">
+      <c r="N327" s="1">
         <v>46182</v>
       </c>
       <c r="Q327" t="b">
@@ -17074,7 +17054,7 @@
       <c r="E328" t="s">
         <v>1145</v>
       </c>
-      <c r="F328" s="2">
+      <c r="F328" s="1">
         <v>46125</v>
       </c>
       <c r="G328" t="s">
@@ -17084,7 +17064,7 @@
         <v>1353</v>
       </c>
       <c r="I328">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J328">
         <v>57</v>
@@ -17095,7 +17075,7 @@
       <c r="L328" t="s">
         <v>1435</v>
       </c>
-      <c r="N328" s="2">
+      <c r="N328" s="1">
         <v>46182</v>
       </c>
       <c r="Q328" t="b">
@@ -17118,7 +17098,7 @@
       <c r="E329" t="s">
         <v>1146</v>
       </c>
-      <c r="F329" s="2">
+      <c r="F329" s="1">
         <v>46125</v>
       </c>
       <c r="G329" t="s">
@@ -17128,7 +17108,7 @@
         <v>1353</v>
       </c>
       <c r="I329">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J329">
         <v>57</v>
@@ -17139,7 +17119,7 @@
       <c r="L329" t="s">
         <v>1435</v>
       </c>
-      <c r="N329" s="2">
+      <c r="N329" s="1">
         <v>46182</v>
       </c>
       <c r="Q329" t="b">
@@ -17162,7 +17142,7 @@
       <c r="E330" t="s">
         <v>1147</v>
       </c>
-      <c r="F330" s="2">
+      <c r="F330" s="1">
         <v>46125</v>
       </c>
       <c r="G330" t="s">
@@ -17172,7 +17152,7 @@
         <v>1353</v>
       </c>
       <c r="I330">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J330">
         <v>57</v>
@@ -17183,7 +17163,7 @@
       <c r="L330" t="s">
         <v>1435</v>
       </c>
-      <c r="N330" s="2">
+      <c r="N330" s="1">
         <v>46182</v>
       </c>
       <c r="Q330" t="b">
@@ -17206,7 +17186,7 @@
       <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="F331" s="2">
+      <c r="F331" s="1">
         <v>46125</v>
       </c>
       <c r="G331" t="s">
@@ -17216,7 +17196,7 @@
         <v>1353</v>
       </c>
       <c r="I331">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K331" t="s">
         <v>1356</v>
@@ -17244,7 +17224,7 @@
       <c r="E332" t="s">
         <v>1148</v>
       </c>
-      <c r="F332" s="2">
+      <c r="F332" s="1">
         <v>46125</v>
       </c>
       <c r="G332" t="s">
@@ -17254,7 +17234,7 @@
         <v>1353</v>
       </c>
       <c r="I332">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K332" t="s">
         <v>1357</v>
@@ -17282,7 +17262,7 @@
       <c r="E333" t="s">
         <v>910</v>
       </c>
-      <c r="F333" s="2">
+      <c r="F333" s="1">
         <v>46125</v>
       </c>
       <c r="G333" t="s">
@@ -17292,7 +17272,7 @@
         <v>1353</v>
       </c>
       <c r="I333">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J333">
         <v>100</v>
@@ -17303,7 +17283,7 @@
       <c r="L333" t="s">
         <v>1395</v>
       </c>
-      <c r="N333" s="2">
+      <c r="N333" s="1">
         <v>46225</v>
       </c>
       <c r="Q333" t="b">
@@ -17326,7 +17306,7 @@
       <c r="E334" t="s">
         <v>1149</v>
       </c>
-      <c r="F334" s="2">
+      <c r="F334" s="1">
         <v>46125</v>
       </c>
       <c r="G334" t="s">
@@ -17336,7 +17316,7 @@
         <v>1353</v>
       </c>
       <c r="I334">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K334" t="s">
         <v>1357</v>
@@ -17364,7 +17344,7 @@
       <c r="E335" t="s">
         <v>1150</v>
       </c>
-      <c r="F335" s="2">
+      <c r="F335" s="1">
         <v>46127</v>
       </c>
       <c r="G335" t="s">
@@ -17379,7 +17359,7 @@
       <c r="L335" t="s">
         <v>1434</v>
       </c>
-      <c r="N335" s="2">
+      <c r="N335" s="1">
         <v>46175</v>
       </c>
       <c r="Q335" t="b">
@@ -17402,7 +17382,7 @@
       <c r="E336" t="s">
         <v>1151</v>
       </c>
-      <c r="F336" s="2">
+      <c r="F336" s="1">
         <v>46127</v>
       </c>
       <c r="G336" t="s">
@@ -17412,7 +17392,7 @@
         <v>1353</v>
       </c>
       <c r="I336">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J336">
         <v>28</v>
@@ -17423,7 +17403,7 @@
       <c r="L336" t="s">
         <v>1388</v>
       </c>
-      <c r="N336" s="2">
+      <c r="N336" s="1">
         <v>46155</v>
       </c>
       <c r="Q336" t="b">
@@ -17446,7 +17426,7 @@
       <c r="E337" t="s">
         <v>1152</v>
       </c>
-      <c r="F337" s="2">
+      <c r="F337" s="1">
         <v>46127</v>
       </c>
       <c r="G337" t="s">
@@ -17461,7 +17441,7 @@
       <c r="L337" t="s">
         <v>1434</v>
       </c>
-      <c r="N337" s="2">
+      <c r="N337" s="1">
         <v>46175</v>
       </c>
       <c r="Q337" t="b">
@@ -17484,7 +17464,7 @@
       <c r="E338" t="s">
         <v>1153</v>
       </c>
-      <c r="F338" s="2">
+      <c r="F338" s="1">
         <v>46127</v>
       </c>
       <c r="G338" t="s">
@@ -17494,7 +17474,7 @@
         <v>1353</v>
       </c>
       <c r="I338">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J338">
         <v>12</v>
@@ -17505,7 +17485,7 @@
       <c r="L338" t="s">
         <v>1388</v>
       </c>
-      <c r="N338" s="2">
+      <c r="N338" s="1">
         <v>46139</v>
       </c>
       <c r="Q338" t="b">
@@ -17528,7 +17508,7 @@
       <c r="E339" t="s">
         <v>1154</v>
       </c>
-      <c r="F339" s="2">
+      <c r="F339" s="1">
         <v>46129</v>
       </c>
       <c r="G339" t="s">
@@ -17557,7 +17537,7 @@
       <c r="E340" t="s">
         <v>1155</v>
       </c>
-      <c r="F340" s="2">
+      <c r="F340" s="1">
         <v>46142</v>
       </c>
       <c r="G340" t="s">
@@ -17567,7 +17547,7 @@
         <v>1353</v>
       </c>
       <c r="I340">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J340">
         <v>98</v>
@@ -17575,7 +17555,7 @@
       <c r="L340" t="s">
         <v>1383</v>
       </c>
-      <c r="N340" s="2">
+      <c r="N340" s="1">
         <v>46240</v>
       </c>
       <c r="Q340" t="b">
@@ -17598,7 +17578,7 @@
       <c r="E341" t="s">
         <v>1156</v>
       </c>
-      <c r="F341" s="2">
+      <c r="F341" s="1">
         <v>46142</v>
       </c>
       <c r="G341" t="s">
@@ -17608,7 +17588,7 @@
         <v>1353</v>
       </c>
       <c r="I341">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J341">
         <v>90</v>
@@ -17616,7 +17596,7 @@
       <c r="L341" t="s">
         <v>1383</v>
       </c>
-      <c r="N341" s="2">
+      <c r="N341" s="1">
         <v>46232</v>
       </c>
       <c r="Q341" t="b">
@@ -17639,7 +17619,7 @@
       <c r="E342" t="s">
         <v>1157</v>
       </c>
-      <c r="F342" s="2">
+      <c r="F342" s="1">
         <v>46142</v>
       </c>
       <c r="G342" t="s">
@@ -17649,7 +17629,7 @@
         <v>1353</v>
       </c>
       <c r="I342">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K342" t="s">
         <v>1356</v>
@@ -17677,7 +17657,7 @@
       <c r="E343" t="s">
         <v>1158</v>
       </c>
-      <c r="F343" s="2">
+      <c r="F343" s="1">
         <v>46142</v>
       </c>
       <c r="G343" t="s">
@@ -17692,7 +17672,7 @@
       <c r="L343" t="s">
         <v>1383</v>
       </c>
-      <c r="N343" s="2">
+      <c r="N343" s="1">
         <v>46232</v>
       </c>
       <c r="Q343" t="b">
@@ -17715,7 +17695,7 @@
       <c r="E344" t="s">
         <v>1159</v>
       </c>
-      <c r="F344" s="2">
+      <c r="F344" s="1">
         <v>46142</v>
       </c>
       <c r="G344" t="s">
@@ -17730,7 +17710,7 @@
       <c r="L344" t="s">
         <v>1383</v>
       </c>
-      <c r="N344" s="2">
+      <c r="N344" s="1">
         <v>46232</v>
       </c>
       <c r="Q344" t="b">
@@ -17753,7 +17733,7 @@
       <c r="E345" t="s">
         <v>1160</v>
       </c>
-      <c r="F345" s="2">
+      <c r="F345" s="1">
         <v>46142</v>
       </c>
       <c r="G345" t="s">
@@ -17763,7 +17743,7 @@
         <v>1353</v>
       </c>
       <c r="I345">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K345" t="s">
         <v>1356</v>
@@ -17791,7 +17771,7 @@
       <c r="E346" t="s">
         <v>1161</v>
       </c>
-      <c r="F346" s="2">
+      <c r="F346" s="1">
         <v>46142</v>
       </c>
       <c r="G346" t="s">
@@ -17806,7 +17786,7 @@
       <c r="L346" t="s">
         <v>1383</v>
       </c>
-      <c r="N346" s="2">
+      <c r="N346" s="1">
         <v>46232</v>
       </c>
       <c r="Q346" t="b">
@@ -17829,7 +17809,7 @@
       <c r="E347" t="s">
         <v>1162</v>
       </c>
-      <c r="F347" s="2">
+      <c r="F347" s="1">
         <v>46142</v>
       </c>
       <c r="G347" t="s">
@@ -17839,7 +17819,7 @@
         <v>1353</v>
       </c>
       <c r="I347">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J347">
         <v>18</v>
@@ -17850,11 +17830,11 @@
       <c r="L347" t="s">
         <v>1431</v>
       </c>
-      <c r="N347" s="2">
+      <c r="N347" s="1">
         <v>46160</v>
       </c>
       <c r="P347" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="Q347" t="b">
         <v>1</v>
@@ -17876,7 +17856,7 @@
       <c r="E348" t="s">
         <v>1163</v>
       </c>
-      <c r="F348" s="2">
+      <c r="F348" s="1">
         <v>46142</v>
       </c>
       <c r="G348" t="s">
@@ -17886,7 +17866,7 @@
         <v>1353</v>
       </c>
       <c r="I348">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J348">
         <v>14</v>
@@ -17897,7 +17877,7 @@
       <c r="L348" t="s">
         <v>1432</v>
       </c>
-      <c r="N348" s="2">
+      <c r="N348" s="1">
         <v>46156</v>
       </c>
       <c r="Q348" t="b">
@@ -17920,7 +17900,7 @@
       <c r="E349" t="s">
         <v>1164</v>
       </c>
-      <c r="F349" s="2">
+      <c r="F349" s="1">
         <v>46142</v>
       </c>
       <c r="G349" t="s">
@@ -17930,7 +17910,7 @@
         <v>1353</v>
       </c>
       <c r="I349">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K349" t="s">
         <v>1361</v>
@@ -17958,7 +17938,7 @@
       <c r="E350" t="s">
         <v>1165</v>
       </c>
-      <c r="F350" s="2">
+      <c r="F350" s="1">
         <v>46142</v>
       </c>
       <c r="G350" t="s">
@@ -17968,12 +17948,12 @@
         <v>1353</v>
       </c>
       <c r="I350">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J350">
         <v>46</v>
       </c>
-      <c r="N350" s="2">
+      <c r="N350" s="1">
         <v>46188</v>
       </c>
       <c r="Q350" t="b">
@@ -17996,7 +17976,7 @@
       <c r="E351" t="s">
         <v>1166</v>
       </c>
-      <c r="F351" s="2">
+      <c r="F351" s="1">
         <v>46142</v>
       </c>
       <c r="G351" t="s">
@@ -18006,7 +17986,7 @@
         <v>1353</v>
       </c>
       <c r="I351">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J351">
         <v>82</v>
@@ -18017,7 +17997,7 @@
       <c r="L351" t="s">
         <v>1436</v>
       </c>
-      <c r="N351" s="2">
+      <c r="N351" s="1">
         <v>46224</v>
       </c>
       <c r="Q351" t="b">
@@ -18040,7 +18020,7 @@
       <c r="E352" t="s">
         <v>1167</v>
       </c>
-      <c r="F352" s="2">
+      <c r="F352" s="1">
         <v>46142</v>
       </c>
       <c r="G352" t="s">
@@ -18050,7 +18030,7 @@
         <v>1353</v>
       </c>
       <c r="I352">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J352">
         <v>78</v>
@@ -18061,7 +18041,7 @@
       <c r="L352" t="s">
         <v>1437</v>
       </c>
-      <c r="N352" s="2">
+      <c r="N352" s="1">
         <v>46220</v>
       </c>
       <c r="Q352" t="b">
@@ -18084,7 +18064,7 @@
       <c r="E353" t="s">
         <v>1168</v>
       </c>
-      <c r="F353" s="2">
+      <c r="F353" s="1">
         <v>46142</v>
       </c>
       <c r="G353" t="s">
@@ -18094,7 +18074,7 @@
         <v>1353</v>
       </c>
       <c r="I353">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J353">
         <v>83</v>
@@ -18105,7 +18085,7 @@
       <c r="L353" t="s">
         <v>1395</v>
       </c>
-      <c r="N353" s="2">
+      <c r="N353" s="1">
         <v>46225</v>
       </c>
       <c r="Q353" t="b">
@@ -18128,7 +18108,7 @@
       <c r="E354" t="s">
         <v>1169</v>
       </c>
-      <c r="F354" s="2">
+      <c r="F354" s="1">
         <v>46142</v>
       </c>
       <c r="G354" t="s">
@@ -18138,7 +18118,7 @@
         <v>1353</v>
       </c>
       <c r="I354">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K354" t="s">
         <v>1360</v>
@@ -18166,7 +18146,7 @@
       <c r="E355" t="s">
         <v>1170</v>
       </c>
-      <c r="F355" s="2">
+      <c r="F355" s="1">
         <v>46142</v>
       </c>
       <c r="G355" t="s">
@@ -18176,7 +18156,7 @@
         <v>1353</v>
       </c>
       <c r="I355">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J355">
         <v>8</v>
@@ -18187,7 +18167,7 @@
       <c r="L355" t="s">
         <v>1438</v>
       </c>
-      <c r="N355" s="2">
+      <c r="N355" s="1">
         <v>46150</v>
       </c>
       <c r="Q355" t="b">
@@ -18210,7 +18190,7 @@
       <c r="E356" t="s">
         <v>1171</v>
       </c>
-      <c r="F356" s="2">
+      <c r="F356" s="1">
         <v>46142</v>
       </c>
       <c r="G356" t="s">
@@ -18225,7 +18205,7 @@
       <c r="L356" t="s">
         <v>1439</v>
       </c>
-      <c r="N356" s="2">
+      <c r="N356" s="1">
         <v>46176</v>
       </c>
       <c r="Q356" t="b">
@@ -18248,7 +18228,7 @@
       <c r="E357" t="s">
         <v>1172</v>
       </c>
-      <c r="F357" s="2">
+      <c r="F357" s="1">
         <v>46142</v>
       </c>
       <c r="G357" t="s">
@@ -18258,7 +18238,7 @@
         <v>1353</v>
       </c>
       <c r="I357">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J357">
         <v>85</v>
@@ -18266,7 +18246,7 @@
       <c r="K357" t="s">
         <v>1360</v>
       </c>
-      <c r="N357" s="2">
+      <c r="N357" s="1">
         <v>46227</v>
       </c>
       <c r="Q357" t="b">
@@ -18289,7 +18269,7 @@
       <c r="E358" t="s">
         <v>1173</v>
       </c>
-      <c r="F358" s="2">
+      <c r="F358" s="1">
         <v>46142</v>
       </c>
       <c r="G358" t="s">
@@ -18307,11 +18287,11 @@
       <c r="L358" t="s">
         <v>1440</v>
       </c>
-      <c r="N358" s="2">
+      <c r="N358" s="1">
         <v>46227</v>
       </c>
       <c r="P358" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="Q358" t="b">
         <v>0</v>
@@ -18333,7 +18313,7 @@
       <c r="E359" t="s">
         <v>1174</v>
       </c>
-      <c r="F359" s="2">
+      <c r="F359" s="1">
         <v>46142</v>
       </c>
       <c r="G359" t="s">
@@ -18345,11 +18325,11 @@
       <c r="J359">
         <v>63</v>
       </c>
-      <c r="N359" s="2">
+      <c r="N359" s="1">
         <v>46205</v>
       </c>
       <c r="P359" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="Q359" t="b">
         <v>0</v>
@@ -18371,7 +18351,7 @@
       <c r="E360" t="s">
         <v>949</v>
       </c>
-      <c r="F360" s="2">
+      <c r="F360" s="1">
         <v>46142</v>
       </c>
       <c r="G360" t="s">
@@ -18381,7 +18361,7 @@
         <v>1353</v>
       </c>
       <c r="I360">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J360">
         <v>83</v>
@@ -18392,7 +18372,7 @@
       <c r="L360" t="s">
         <v>1395</v>
       </c>
-      <c r="N360" s="2">
+      <c r="N360" s="1">
         <v>46225</v>
       </c>
       <c r="O360" t="s">
@@ -18418,7 +18398,7 @@
       <c r="E361" t="s">
         <v>961</v>
       </c>
-      <c r="F361" s="2">
+      <c r="F361" s="1">
         <v>46142</v>
       </c>
       <c r="G361" t="s">
@@ -18428,7 +18408,7 @@
         <v>1353</v>
       </c>
       <c r="I361">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J361">
         <v>83</v>
@@ -18439,7 +18419,7 @@
       <c r="L361" t="s">
         <v>1395</v>
       </c>
-      <c r="N361" s="2">
+      <c r="N361" s="1">
         <v>46225</v>
       </c>
       <c r="Q361" t="b">
@@ -18462,7 +18442,7 @@
       <c r="E362" t="s">
         <v>1175</v>
       </c>
-      <c r="F362" s="2">
+      <c r="F362" s="1">
         <v>46142</v>
       </c>
       <c r="G362" t="s">
@@ -18472,7 +18452,7 @@
         <v>1353</v>
       </c>
       <c r="I362">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K362" t="s">
         <v>1360</v>
@@ -18500,7 +18480,7 @@
       <c r="E363" t="s">
         <v>1176</v>
       </c>
-      <c r="F363" s="2">
+      <c r="F363" s="1">
         <v>46142</v>
       </c>
       <c r="G363" t="s">
@@ -18510,7 +18490,7 @@
         <v>1353</v>
       </c>
       <c r="I363">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K363" t="s">
         <v>1360</v>
@@ -18538,7 +18518,7 @@
       <c r="E364" t="s">
         <v>958</v>
       </c>
-      <c r="F364" s="2">
+      <c r="F364" s="1">
         <v>46142</v>
       </c>
       <c r="G364" t="s">
@@ -18548,7 +18528,7 @@
         <v>1353</v>
       </c>
       <c r="I364">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J364">
         <v>83</v>
@@ -18559,7 +18539,7 @@
       <c r="L364" t="s">
         <v>1395</v>
       </c>
-      <c r="N364" s="2">
+      <c r="N364" s="1">
         <v>46225</v>
       </c>
       <c r="Q364" t="b">
@@ -18582,7 +18562,7 @@
       <c r="E365" t="s">
         <v>1177</v>
       </c>
-      <c r="F365" s="2">
+      <c r="F365" s="1">
         <v>46142</v>
       </c>
       <c r="G365" t="s">
@@ -18592,7 +18572,7 @@
         <v>1353</v>
       </c>
       <c r="I365">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J365">
         <v>15</v>
@@ -18600,7 +18580,7 @@
       <c r="K365" t="s">
         <v>1359</v>
       </c>
-      <c r="N365" s="2">
+      <c r="N365" s="1">
         <v>46157</v>
       </c>
       <c r="Q365" t="b">
@@ -18623,7 +18603,7 @@
       <c r="E366" t="s">
         <v>1178</v>
       </c>
-      <c r="F366" s="2">
+      <c r="F366" s="1">
         <v>46148</v>
       </c>
       <c r="G366" t="s">
@@ -18633,7 +18613,7 @@
         <v>1353</v>
       </c>
       <c r="I366">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J366">
         <v>77</v>
@@ -18644,7 +18624,7 @@
       <c r="L366" t="s">
         <v>1388</v>
       </c>
-      <c r="N366" s="2">
+      <c r="N366" s="1">
         <v>46225</v>
       </c>
       <c r="Q366" t="b">
@@ -18667,7 +18647,7 @@
       <c r="E367" t="s">
         <v>1179</v>
       </c>
-      <c r="F367" s="2">
+      <c r="F367" s="1">
         <v>46148</v>
       </c>
       <c r="G367" t="s">
@@ -18677,7 +18657,7 @@
         <v>1353</v>
       </c>
       <c r="I367">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J367">
         <v>77</v>
@@ -18688,7 +18668,7 @@
       <c r="L367" t="s">
         <v>1388</v>
       </c>
-      <c r="N367" s="2">
+      <c r="N367" s="1">
         <v>46225</v>
       </c>
       <c r="Q367" t="b">
@@ -18711,7 +18691,7 @@
       <c r="E368" t="s">
         <v>1180</v>
       </c>
-      <c r="F368" s="2">
+      <c r="F368" s="1">
         <v>46148</v>
       </c>
       <c r="G368" t="s">
@@ -18721,7 +18701,7 @@
         <v>1353</v>
       </c>
       <c r="I368">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J368">
         <v>77</v>
@@ -18732,7 +18712,7 @@
       <c r="L368" t="s">
         <v>1395</v>
       </c>
-      <c r="N368" s="2">
+      <c r="N368" s="1">
         <v>46225</v>
       </c>
       <c r="Q368" t="b">
@@ -18755,7 +18735,7 @@
       <c r="E369" t="s">
         <v>1181</v>
       </c>
-      <c r="F369" s="2">
+      <c r="F369" s="1">
         <v>46148</v>
       </c>
       <c r="G369" t="s">
@@ -18765,7 +18745,7 @@
         <v>1353</v>
       </c>
       <c r="I369">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K369" t="s">
         <v>1360</v>
@@ -18793,7 +18773,7 @@
       <c r="E370" t="s">
         <v>1182</v>
       </c>
-      <c r="F370" s="2">
+      <c r="F370" s="1">
         <v>46148</v>
       </c>
       <c r="G370" t="s">
@@ -18803,7 +18783,7 @@
         <v>1353</v>
       </c>
       <c r="I370">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K370" t="s">
         <v>1360</v>
@@ -18831,7 +18811,7 @@
       <c r="E371" t="s">
         <v>1183</v>
       </c>
-      <c r="F371" s="2">
+      <c r="F371" s="1">
         <v>46148</v>
       </c>
       <c r="G371" t="s">
@@ -18841,7 +18821,7 @@
         <v>1353</v>
       </c>
       <c r="I371">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J371">
         <v>16</v>
@@ -18852,7 +18832,7 @@
       <c r="L371" t="s">
         <v>1441</v>
       </c>
-      <c r="N371" s="2">
+      <c r="N371" s="1">
         <v>46164</v>
       </c>
       <c r="Q371" t="b">
@@ -18875,7 +18855,7 @@
       <c r="E372" t="s">
         <v>1184</v>
       </c>
-      <c r="F372" s="2">
+      <c r="F372" s="1">
         <v>46148</v>
       </c>
       <c r="G372" t="s">
@@ -18893,7 +18873,7 @@
       <c r="L372" t="s">
         <v>1428</v>
       </c>
-      <c r="N372" s="2">
+      <c r="N372" s="1">
         <v>46113</v>
       </c>
       <c r="P372" t="s">
@@ -18919,7 +18899,7 @@
       <c r="E373" t="s">
         <v>1185</v>
       </c>
-      <c r="F373" s="2">
+      <c r="F373" s="1">
         <v>46149</v>
       </c>
       <c r="G373" t="s">
@@ -18929,7 +18909,7 @@
         <v>1353</v>
       </c>
       <c r="I373">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K373" t="s">
         <v>1356</v>
@@ -18957,7 +18937,7 @@
       <c r="E374" t="s">
         <v>1186</v>
       </c>
-      <c r="F374" s="2">
+      <c r="F374" s="1">
         <v>46149</v>
       </c>
       <c r="G374" t="s">
@@ -18967,7 +18947,7 @@
         <v>1353</v>
       </c>
       <c r="I374">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K374" t="s">
         <v>1356</v>
@@ -18995,7 +18975,7 @@
       <c r="E375" t="s">
         <v>1187</v>
       </c>
-      <c r="F375" s="2">
+      <c r="F375" s="1">
         <v>46154</v>
       </c>
       <c r="G375" t="s">
@@ -19005,7 +18985,7 @@
         <v>1353</v>
       </c>
       <c r="I375">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J375">
         <v>94</v>
@@ -19013,7 +18993,7 @@
       <c r="K375" t="s">
         <v>1360</v>
       </c>
-      <c r="N375" s="2">
+      <c r="N375" s="1">
         <v>46248</v>
       </c>
       <c r="Q375" t="b">
@@ -19036,7 +19016,7 @@
       <c r="E376" t="s">
         <v>1188</v>
       </c>
-      <c r="F376" s="2">
+      <c r="F376" s="1">
         <v>46154</v>
       </c>
       <c r="G376" t="s">
@@ -19046,7 +19026,7 @@
         <v>1353</v>
       </c>
       <c r="I376">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K376" t="s">
         <v>1360</v>
@@ -19074,7 +19054,7 @@
       <c r="E377" t="s">
         <v>1189</v>
       </c>
-      <c r="F377" s="2">
+      <c r="F377" s="1">
         <v>46154</v>
       </c>
       <c r="G377" t="s">
@@ -19086,14 +19066,14 @@
       <c r="K377" t="s">
         <v>1360</v>
       </c>
-      <c r="N377" s="2">
+      <c r="N377" s="1">
         <v>46176</v>
       </c>
       <c r="O377" t="s">
         <v>1472</v>
       </c>
       <c r="P377" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="Q377" t="b">
         <v>0</v>
@@ -19115,7 +19095,7 @@
       <c r="E378" t="s">
         <v>1190</v>
       </c>
-      <c r="F378" s="2">
+      <c r="F378" s="1">
         <v>46154</v>
       </c>
       <c r="G378" t="s">
@@ -19125,7 +19105,7 @@
         <v>1353</v>
       </c>
       <c r="I378">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K378" t="s">
         <v>1360</v>
@@ -19153,7 +19133,7 @@
       <c r="E379" t="s">
         <v>1191</v>
       </c>
-      <c r="F379" s="2">
+      <c r="F379" s="1">
         <v>46154</v>
       </c>
       <c r="G379" t="s">
@@ -19163,7 +19143,7 @@
         <v>1353</v>
       </c>
       <c r="I379">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J379">
         <v>20</v>
@@ -19174,7 +19154,7 @@
       <c r="L379" t="s">
         <v>1442</v>
       </c>
-      <c r="N379" s="2">
+      <c r="N379" s="1">
         <v>46174</v>
       </c>
       <c r="Q379" t="b">
@@ -19197,7 +19177,7 @@
       <c r="E380" t="s">
         <v>1192</v>
       </c>
-      <c r="F380" s="2">
+      <c r="F380" s="1">
         <v>46154</v>
       </c>
       <c r="G380" t="s">
@@ -19207,7 +19187,7 @@
         <v>1353</v>
       </c>
       <c r="I380">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J380">
         <v>94</v>
@@ -19218,7 +19198,7 @@
       <c r="L380" t="s">
         <v>1443</v>
       </c>
-      <c r="N380" s="2">
+      <c r="N380" s="1">
         <v>46248</v>
       </c>
       <c r="Q380" t="b">
@@ -19241,7 +19221,7 @@
       <c r="E381" t="s">
         <v>1193</v>
       </c>
-      <c r="F381" s="2">
+      <c r="F381" s="1">
         <v>46154</v>
       </c>
       <c r="G381" t="s">
@@ -19251,7 +19231,7 @@
         <v>1353</v>
       </c>
       <c r="I381">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K381" t="s">
         <v>1360</v>
@@ -19279,7 +19259,7 @@
       <c r="E382" t="s">
         <v>1194</v>
       </c>
-      <c r="F382" s="2">
+      <c r="F382" s="1">
         <v>46154</v>
       </c>
       <c r="G382" t="s">
@@ -19289,7 +19269,7 @@
         <v>1353</v>
       </c>
       <c r="I382">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K382" t="s">
         <v>1360</v>
@@ -19317,7 +19297,7 @@
       <c r="E383" t="s">
         <v>1195</v>
       </c>
-      <c r="F383" s="2">
+      <c r="F383" s="1">
         <v>46154</v>
       </c>
       <c r="G383" t="s">
@@ -19327,7 +19307,7 @@
         <v>1353</v>
       </c>
       <c r="I383">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J383">
         <v>71</v>
@@ -19338,7 +19318,7 @@
       <c r="L383" t="s">
         <v>1444</v>
       </c>
-      <c r="N383" s="2">
+      <c r="N383" s="1">
         <v>46225</v>
       </c>
       <c r="Q383" t="b">
@@ -19361,7 +19341,7 @@
       <c r="E384" t="s">
         <v>1196</v>
       </c>
-      <c r="F384" s="2">
+      <c r="F384" s="1">
         <v>46164</v>
       </c>
       <c r="G384" t="s">
@@ -19371,7 +19351,7 @@
         <v>1353</v>
       </c>
       <c r="I384">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K384" t="s">
         <v>1357</v>
@@ -19399,7 +19379,7 @@
       <c r="E385" t="s">
         <v>1197</v>
       </c>
-      <c r="F385" s="2">
+      <c r="F385" s="1">
         <v>46164</v>
       </c>
       <c r="G385" t="s">
@@ -19409,7 +19389,7 @@
         <v>1353</v>
       </c>
       <c r="I385">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J385">
         <v>102</v>
@@ -19420,7 +19400,7 @@
       <c r="L385" t="s">
         <v>1445</v>
       </c>
-      <c r="N385" s="2">
+      <c r="N385" s="1">
         <v>46266</v>
       </c>
       <c r="P385" t="s">
@@ -19446,7 +19426,7 @@
       <c r="E386" t="s">
         <v>1198</v>
       </c>
-      <c r="F386" s="2">
+      <c r="F386" s="1">
         <v>46171</v>
       </c>
       <c r="G386" t="s">
@@ -19456,7 +19436,7 @@
         <v>1353</v>
       </c>
       <c r="I386">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K386" t="s">
         <v>1360</v>
@@ -19484,7 +19464,7 @@
       <c r="E387" t="s">
         <v>1199</v>
       </c>
-      <c r="F387" s="2">
+      <c r="F387" s="1">
         <v>46171</v>
       </c>
       <c r="G387" t="s">
@@ -19494,7 +19474,7 @@
         <v>1353</v>
       </c>
       <c r="I387">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K387" t="s">
         <v>1360</v>
@@ -19522,7 +19502,7 @@
       <c r="E388" t="s">
         <v>851</v>
       </c>
-      <c r="F388" s="2">
+      <c r="F388" s="1">
         <v>46171</v>
       </c>
       <c r="G388" t="s">
@@ -19532,7 +19512,7 @@
         <v>1353</v>
       </c>
       <c r="I388">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J388">
         <v>-85</v>
@@ -19543,7 +19523,7 @@
       <c r="L388" t="s">
         <v>1446</v>
       </c>
-      <c r="N388" s="2">
+      <c r="N388" s="1">
         <v>46086</v>
       </c>
       <c r="Q388" t="b">
@@ -19566,7 +19546,7 @@
       <c r="E389" t="s">
         <v>1200</v>
       </c>
-      <c r="F389" s="2">
+      <c r="F389" s="1">
         <v>46171</v>
       </c>
       <c r="G389" t="s">
@@ -19576,7 +19556,7 @@
         <v>1353</v>
       </c>
       <c r="I389">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K389" t="s">
         <v>1361</v>
@@ -19604,7 +19584,7 @@
       <c r="E390" t="s">
         <v>1201</v>
       </c>
-      <c r="F390" s="2">
+      <c r="F390" s="1">
         <v>46171</v>
       </c>
       <c r="G390" t="s">
@@ -19622,11 +19602,11 @@
       <c r="L390" t="s">
         <v>1447</v>
       </c>
-      <c r="N390" s="2">
+      <c r="N390" s="1">
         <v>46191</v>
       </c>
       <c r="P390" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="Q390" t="b">
         <v>0</v>
@@ -19648,7 +19628,7 @@
       <c r="E391" t="s">
         <v>1202</v>
       </c>
-      <c r="F391" s="2">
+      <c r="F391" s="1">
         <v>46171</v>
       </c>
       <c r="G391" t="s">
@@ -19686,7 +19666,7 @@
       <c r="E392" t="s">
         <v>1203</v>
       </c>
-      <c r="F392" s="2">
+      <c r="F392" s="1">
         <v>46171</v>
       </c>
       <c r="G392" t="s">
@@ -19701,7 +19681,7 @@
       <c r="L392" t="s">
         <v>1439</v>
       </c>
-      <c r="N392" s="2">
+      <c r="N392" s="1">
         <v>46176</v>
       </c>
       <c r="Q392" t="b">
@@ -19724,7 +19704,7 @@
       <c r="E393" t="s">
         <v>1204</v>
       </c>
-      <c r="F393" s="2">
+      <c r="F393" s="1">
         <v>46171</v>
       </c>
       <c r="G393" t="s">
@@ -19734,7 +19714,7 @@
         <v>1353</v>
       </c>
       <c r="I393">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J393">
         <v>20</v>
@@ -19745,7 +19725,7 @@
       <c r="L393" t="s">
         <v>1388</v>
       </c>
-      <c r="N393" s="2">
+      <c r="N393" s="1">
         <v>46191</v>
       </c>
       <c r="Q393" t="b">
@@ -19768,7 +19748,7 @@
       <c r="E394" t="s">
         <v>1205</v>
       </c>
-      <c r="F394" s="2">
+      <c r="F394" s="1">
         <v>46171</v>
       </c>
       <c r="G394" t="s">
@@ -19786,11 +19766,11 @@
       <c r="L394" t="s">
         <v>1448</v>
       </c>
-      <c r="N394" s="2">
+      <c r="N394" s="1">
         <v>46241</v>
       </c>
       <c r="P394" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="Q394" t="b">
         <v>0</v>
@@ -19812,7 +19792,7 @@
       <c r="E395" t="s">
         <v>1206</v>
       </c>
-      <c r="F395" s="2">
+      <c r="F395" s="1">
         <v>46171</v>
       </c>
       <c r="G395" t="s">
@@ -19830,11 +19810,11 @@
       <c r="L395" t="s">
         <v>1449</v>
       </c>
-      <c r="N395" s="2">
+      <c r="N395" s="1">
         <v>46191</v>
       </c>
       <c r="P395" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="Q395" t="b">
         <v>0</v>
@@ -19856,7 +19836,7 @@
       <c r="E396" t="s">
         <v>1207</v>
       </c>
-      <c r="F396" s="2">
+      <c r="F396" s="1">
         <v>46171</v>
       </c>
       <c r="G396" t="s">
@@ -19868,11 +19848,11 @@
       <c r="J396">
         <v>20</v>
       </c>
-      <c r="N396" s="2">
+      <c r="N396" s="1">
         <v>46191</v>
       </c>
       <c r="P396" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="Q396" t="b">
         <v>0</v>
@@ -19894,7 +19874,7 @@
       <c r="E397" t="s">
         <v>1208</v>
       </c>
-      <c r="F397" s="2">
+      <c r="F397" s="1">
         <v>46171</v>
       </c>
       <c r="G397" t="s">
@@ -19912,11 +19892,11 @@
       <c r="L397" t="s">
         <v>1448</v>
       </c>
-      <c r="N397" s="2">
+      <c r="N397" s="1">
         <v>46241</v>
       </c>
       <c r="P397" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="Q397" t="b">
         <v>0</v>
@@ -19938,7 +19918,7 @@
       <c r="E398" t="s">
         <v>1209</v>
       </c>
-      <c r="F398" s="2">
+      <c r="F398" s="1">
         <v>46171</v>
       </c>
       <c r="G398" t="s">
@@ -19956,11 +19936,11 @@
       <c r="L398" t="s">
         <v>1449</v>
       </c>
-      <c r="N398" s="2">
+      <c r="N398" s="1">
         <v>46191</v>
       </c>
       <c r="P398" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="Q398" t="b">
         <v>0</v>
@@ -19982,7 +19962,7 @@
       <c r="E399" t="s">
         <v>987</v>
       </c>
-      <c r="F399" s="2">
+      <c r="F399" s="1">
         <v>46163</v>
       </c>
       <c r="G399" t="s">
@@ -19997,7 +19977,7 @@
       <c r="L399" t="s">
         <v>1450</v>
       </c>
-      <c r="N399" s="2">
+      <c r="N399" s="1">
         <v>46171</v>
       </c>
       <c r="Q399" t="b">
@@ -20020,7 +20000,7 @@
       <c r="E400" t="s">
         <v>1210</v>
       </c>
-      <c r="F400" s="2">
+      <c r="F400" s="1">
         <v>46171</v>
       </c>
       <c r="G400" t="s">
@@ -20030,7 +20010,7 @@
         <v>1353</v>
       </c>
       <c r="I400">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K400" t="s">
         <v>1360</v>
@@ -20058,7 +20038,7 @@
       <c r="E401" t="s">
         <v>1211</v>
       </c>
-      <c r="F401" s="2">
+      <c r="F401" s="1">
         <v>46171</v>
       </c>
       <c r="G401" t="s">
@@ -20070,11 +20050,11 @@
       <c r="J401">
         <v>40</v>
       </c>
-      <c r="N401" s="2">
+      <c r="N401" s="1">
         <v>46211</v>
       </c>
       <c r="P401" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="Q401" t="b">
         <v>0</v>
@@ -20096,7 +20076,7 @@
       <c r="E402" t="s">
         <v>1212</v>
       </c>
-      <c r="F402" s="2">
+      <c r="F402" s="1">
         <v>46171</v>
       </c>
       <c r="G402" t="s">
@@ -20106,7 +20086,7 @@
         <v>1353</v>
       </c>
       <c r="I402">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K402" t="s">
         <v>1360</v>
@@ -20134,7 +20114,7 @@
       <c r="E403" t="s">
         <v>1213</v>
       </c>
-      <c r="F403" s="2">
+      <c r="F403" s="1">
         <v>46171</v>
       </c>
       <c r="G403" t="s">
@@ -20144,7 +20124,7 @@
         <v>1353</v>
       </c>
       <c r="I403">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J403">
         <v>83</v>
@@ -20155,7 +20135,7 @@
       <c r="L403" t="s">
         <v>1451</v>
       </c>
-      <c r="N403" s="2">
+      <c r="N403" s="1">
         <v>46254</v>
       </c>
       <c r="Q403" t="b">
@@ -20178,7 +20158,7 @@
       <c r="E404" t="s">
         <v>1214</v>
       </c>
-      <c r="F404" s="2">
+      <c r="F404" s="1">
         <v>46171</v>
       </c>
       <c r="G404" t="s">
@@ -20188,7 +20168,7 @@
         <v>1353</v>
       </c>
       <c r="I404">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K404" t="s">
         <v>1360</v>
@@ -20216,7 +20196,7 @@
       <c r="E405" t="s">
         <v>1215</v>
       </c>
-      <c r="F405" s="2">
+      <c r="F405" s="1">
         <v>46183</v>
       </c>
       <c r="G405" t="s">
@@ -20226,7 +20206,7 @@
         <v>1354</v>
       </c>
       <c r="P405" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="Q405" t="b">
         <v>0</v>
@@ -20248,7 +20228,7 @@
       <c r="E406" t="s">
         <v>1216</v>
       </c>
-      <c r="F406" s="2">
+      <c r="F406" s="1">
         <v>46183</v>
       </c>
       <c r="G406" t="s">
@@ -20258,7 +20238,7 @@
         <v>1353</v>
       </c>
       <c r="I406">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q406" t="b">
         <v>1</v>
@@ -20280,7 +20260,7 @@
       <c r="E407" t="s">
         <v>1217</v>
       </c>
-      <c r="F407" s="2">
+      <c r="F407" s="1">
         <v>46183</v>
       </c>
       <c r="G407" t="s">
@@ -20290,7 +20270,7 @@
         <v>1353</v>
       </c>
       <c r="I407">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q407" t="b">
         <v>1</v>
@@ -20312,7 +20292,7 @@
       <c r="E408" t="s">
         <v>1218</v>
       </c>
-      <c r="F408" s="2">
+      <c r="F408" s="1">
         <v>46183</v>
       </c>
       <c r="G408" t="s">
@@ -20322,7 +20302,7 @@
         <v>1353</v>
       </c>
       <c r="I408">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q408" t="b">
         <v>1</v>
@@ -20344,7 +20324,7 @@
       <c r="E409" t="s">
         <v>1219</v>
       </c>
-      <c r="F409" s="2">
+      <c r="F409" s="1">
         <v>46183</v>
       </c>
       <c r="G409" t="s">
@@ -20354,7 +20334,7 @@
         <v>1353</v>
       </c>
       <c r="I409">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q409" t="b">
         <v>1</v>
@@ -20376,7 +20356,7 @@
       <c r="E410" t="s">
         <v>1220</v>
       </c>
-      <c r="F410" s="2">
+      <c r="F410" s="1">
         <v>46183</v>
       </c>
       <c r="G410" t="s">
@@ -20386,7 +20366,7 @@
         <v>1353</v>
       </c>
       <c r="I410">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q410" t="b">
         <v>1</v>
@@ -20408,7 +20388,7 @@
       <c r="E411" t="s">
         <v>1221</v>
       </c>
-      <c r="F411" s="2">
+      <c r="F411" s="1">
         <v>46188</v>
       </c>
       <c r="G411" t="s">
@@ -20418,7 +20398,7 @@
         <v>1353</v>
       </c>
       <c r="I411">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q411" t="b">
         <v>1</v>
@@ -20440,7 +20420,7 @@
       <c r="E412" t="s">
         <v>1222</v>
       </c>
-      <c r="F412" s="2">
+      <c r="F412" s="1">
         <v>46188</v>
       </c>
       <c r="G412" t="s">
@@ -20450,7 +20430,7 @@
         <v>1353</v>
       </c>
       <c r="I412">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q412" t="b">
         <v>1</v>
@@ -20472,7 +20452,7 @@
       <c r="E413" t="s">
         <v>1223</v>
       </c>
-      <c r="F413" s="2">
+      <c r="F413" s="1">
         <v>46188</v>
       </c>
       <c r="G413" t="s">
@@ -20482,7 +20462,7 @@
         <v>1353</v>
       </c>
       <c r="I413">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q413" t="b">
         <v>1</v>
@@ -20504,7 +20484,7 @@
       <c r="E414" t="s">
         <v>1224</v>
       </c>
-      <c r="F414" s="2">
+      <c r="F414" s="1">
         <v>46188</v>
       </c>
       <c r="G414" t="s">
@@ -20533,7 +20513,7 @@
       <c r="E415" t="s">
         <v>1060</v>
       </c>
-      <c r="F415" s="2">
+      <c r="F415" s="1">
         <v>46188</v>
       </c>
       <c r="G415" t="s">
@@ -20562,7 +20542,7 @@
       <c r="E416" t="s">
         <v>1225</v>
       </c>
-      <c r="F416" s="2">
+      <c r="F416" s="1">
         <v>46188</v>
       </c>
       <c r="G416" t="s">
@@ -20572,7 +20552,7 @@
         <v>1353</v>
       </c>
       <c r="I416">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q416" t="b">
         <v>1</v>
@@ -20594,7 +20574,7 @@
       <c r="E417" t="s">
         <v>1226</v>
       </c>
-      <c r="F417" s="2">
+      <c r="F417" s="1">
         <v>46188</v>
       </c>
       <c r="G417" t="s">
@@ -20623,7 +20603,7 @@
       <c r="E418" t="s">
         <v>1227</v>
       </c>
-      <c r="F418" s="2">
+      <c r="F418" s="1">
         <v>46188</v>
       </c>
       <c r="G418" t="s">
@@ -20652,7 +20632,7 @@
       <c r="E419" t="s">
         <v>1228</v>
       </c>
-      <c r="F419" s="2">
+      <c r="F419" s="1">
         <v>46188</v>
       </c>
       <c r="G419" t="s">
@@ -20662,7 +20642,7 @@
         <v>1353</v>
       </c>
       <c r="I419">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q419" t="b">
         <v>1</v>
@@ -20684,7 +20664,7 @@
       <c r="E420" t="s">
         <v>1229</v>
       </c>
-      <c r="F420" s="2">
+      <c r="F420" s="1">
         <v>46188</v>
       </c>
       <c r="G420" t="s">
@@ -20694,7 +20674,7 @@
         <v>1353</v>
       </c>
       <c r="I420">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q420" t="b">
         <v>1</v>
@@ -20716,7 +20696,7 @@
       <c r="E421" t="s">
         <v>1230</v>
       </c>
-      <c r="F421" s="2">
+      <c r="F421" s="1">
         <v>46188</v>
       </c>
       <c r="G421" t="s">
@@ -20726,7 +20706,7 @@
         <v>1353</v>
       </c>
       <c r="I421">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q421" t="b">
         <v>1</v>
@@ -20748,7 +20728,7 @@
       <c r="E422" t="s">
         <v>1231</v>
       </c>
-      <c r="F422" s="2">
+      <c r="F422" s="1">
         <v>46188</v>
       </c>
       <c r="G422" t="s">
@@ -20758,7 +20738,7 @@
         <v>1353</v>
       </c>
       <c r="I422">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q422" t="b">
         <v>1</v>
@@ -20780,7 +20760,7 @@
       <c r="E423" t="s">
         <v>1232</v>
       </c>
-      <c r="F423" s="2">
+      <c r="F423" s="1">
         <v>46188</v>
       </c>
       <c r="G423" t="s">
@@ -20790,7 +20770,7 @@
         <v>1353</v>
       </c>
       <c r="I423">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q423" t="b">
         <v>1</v>
@@ -20812,7 +20792,7 @@
       <c r="E424" t="s">
         <v>1233</v>
       </c>
-      <c r="F424" s="2">
+      <c r="F424" s="1">
         <v>46188</v>
       </c>
       <c r="G424" t="s">
@@ -20822,7 +20802,7 @@
         <v>1353</v>
       </c>
       <c r="I424">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q424" t="b">
         <v>1</v>
@@ -20844,7 +20824,7 @@
       <c r="E425" t="s">
         <v>1234</v>
       </c>
-      <c r="F425" s="2">
+      <c r="F425" s="1">
         <v>46188</v>
       </c>
       <c r="G425" t="s">
@@ -20854,7 +20834,7 @@
         <v>1353</v>
       </c>
       <c r="I425">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q425" t="b">
         <v>1</v>
@@ -20876,7 +20856,7 @@
       <c r="E426" t="s">
         <v>1235</v>
       </c>
-      <c r="F426" s="2">
+      <c r="F426" s="1">
         <v>46188</v>
       </c>
       <c r="G426" t="s">
@@ -20886,7 +20866,7 @@
         <v>1353</v>
       </c>
       <c r="I426">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q426" t="b">
         <v>1</v>
@@ -20908,7 +20888,7 @@
       <c r="E427" t="s">
         <v>1236</v>
       </c>
-      <c r="F427" s="2">
+      <c r="F427" s="1">
         <v>46188</v>
       </c>
       <c r="G427" t="s">
@@ -20918,7 +20898,7 @@
         <v>1353</v>
       </c>
       <c r="I427">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q427" t="b">
         <v>1</v>
@@ -20940,7 +20920,7 @@
       <c r="E428" t="s">
         <v>1237</v>
       </c>
-      <c r="F428" s="2">
+      <c r="F428" s="1">
         <v>46188</v>
       </c>
       <c r="G428" t="s">
@@ -20969,7 +20949,7 @@
       <c r="E429" t="s">
         <v>1238</v>
       </c>
-      <c r="F429" s="2">
+      <c r="F429" s="1">
         <v>46188</v>
       </c>
       <c r="G429" t="s">
@@ -20998,7 +20978,7 @@
       <c r="E430" t="s">
         <v>1239</v>
       </c>
-      <c r="F430" s="2">
+      <c r="F430" s="1">
         <v>46188</v>
       </c>
       <c r="G430" t="s">
@@ -21008,7 +20988,7 @@
         <v>1353</v>
       </c>
       <c r="I430">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q430" t="b">
         <v>1</v>
@@ -21030,7 +21010,7 @@
       <c r="E431" t="s">
         <v>1240</v>
       </c>
-      <c r="F431" s="2">
+      <c r="F431" s="1">
         <v>46188</v>
       </c>
       <c r="G431" t="s">
@@ -21040,7 +21020,7 @@
         <v>1353</v>
       </c>
       <c r="I431">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q431" t="b">
         <v>1</v>
@@ -21062,7 +21042,7 @@
       <c r="E432" t="s">
         <v>1241</v>
       </c>
-      <c r="F432" s="2">
+      <c r="F432" s="1">
         <v>46188</v>
       </c>
       <c r="G432" t="s">
@@ -21072,7 +21052,7 @@
         <v>1353</v>
       </c>
       <c r="I432">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q432" t="b">
         <v>1</v>
@@ -21094,7 +21074,7 @@
       <c r="E433" t="s">
         <v>1242</v>
       </c>
-      <c r="F433" s="2">
+      <c r="F433" s="1">
         <v>46188</v>
       </c>
       <c r="G433" t="s">
@@ -21104,7 +21084,7 @@
         <v>1353</v>
       </c>
       <c r="I433">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q433" t="b">
         <v>1</v>
@@ -21126,7 +21106,7 @@
       <c r="E434" t="s">
         <v>1243</v>
       </c>
-      <c r="F434" s="2">
+      <c r="F434" s="1">
         <v>46188</v>
       </c>
       <c r="G434" t="s">
@@ -21136,7 +21116,7 @@
         <v>1353</v>
       </c>
       <c r="I434">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q434" t="b">
         <v>1</v>
@@ -21158,7 +21138,7 @@
       <c r="E435" t="s">
         <v>856</v>
       </c>
-      <c r="F435" s="2">
+      <c r="F435" s="1">
         <v>46188</v>
       </c>
       <c r="G435" t="s">
@@ -21168,7 +21148,7 @@
         <v>1353</v>
       </c>
       <c r="I435">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q435" t="b">
         <v>1</v>
@@ -21190,7 +21170,7 @@
       <c r="E436" t="s">
         <v>1244</v>
       </c>
-      <c r="F436" s="2">
+      <c r="F436" s="1">
         <v>46188</v>
       </c>
       <c r="G436" t="s">
@@ -21200,7 +21180,7 @@
         <v>1353</v>
       </c>
       <c r="I436">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q436" t="b">
         <v>1</v>
@@ -21222,7 +21202,7 @@
       <c r="E437" t="s">
         <v>1245</v>
       </c>
-      <c r="F437" s="2">
+      <c r="F437" s="1">
         <v>46188</v>
       </c>
       <c r="G437" t="s">
@@ -21232,7 +21212,7 @@
         <v>1355</v>
       </c>
       <c r="I437">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q437" t="b">
         <v>1</v>
@@ -21254,7 +21234,7 @@
       <c r="E438" t="s">
         <v>1246</v>
       </c>
-      <c r="F438" s="2">
+      <c r="F438" s="1">
         <v>46188</v>
       </c>
       <c r="G438" t="s">
@@ -21264,7 +21244,7 @@
         <v>1355</v>
       </c>
       <c r="I438">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q438" t="b">
         <v>1</v>
@@ -21286,7 +21266,7 @@
       <c r="E439" t="s">
         <v>1247</v>
       </c>
-      <c r="F439" s="2">
+      <c r="F439" s="1">
         <v>46196</v>
       </c>
       <c r="G439" t="s">
@@ -21296,7 +21276,7 @@
         <v>1353</v>
       </c>
       <c r="I439">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Q439" t="b">
         <v>1</v>
@@ -21318,7 +21298,7 @@
       <c r="E440" t="s">
         <v>1248</v>
       </c>
-      <c r="F440" s="2">
+      <c r="F440" s="1">
         <v>46196</v>
       </c>
       <c r="G440" t="s">
@@ -21328,7 +21308,7 @@
         <v>1353</v>
       </c>
       <c r="I440">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Q440" t="b">
         <v>1</v>
@@ -21350,7 +21330,7 @@
       <c r="E441" t="s">
         <v>1249</v>
       </c>
-      <c r="F441" s="2">
+      <c r="F441" s="1">
         <v>46203</v>
       </c>
       <c r="G441" t="s">
@@ -21360,7 +21340,7 @@
         <v>1353</v>
       </c>
       <c r="I441">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q441" t="b">
         <v>1</v>
@@ -21382,7 +21362,7 @@
       <c r="E442" t="s">
         <v>1250</v>
       </c>
-      <c r="F442" s="2">
+      <c r="F442" s="1">
         <v>46203</v>
       </c>
       <c r="G442" t="s">
@@ -21411,7 +21391,7 @@
       <c r="E443" t="s">
         <v>1251</v>
       </c>
-      <c r="F443" s="2">
+      <c r="F443" s="1">
         <v>46205</v>
       </c>
       <c r="G443" t="s">
@@ -21421,7 +21401,7 @@
         <v>1353</v>
       </c>
       <c r="I443">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q443" t="b">
         <v>1</v>
@@ -21443,7 +21423,7 @@
       <c r="E444" t="s">
         <v>1252</v>
       </c>
-      <c r="F444" s="2">
+      <c r="F444" s="1">
         <v>46205</v>
       </c>
       <c r="G444" t="s">
@@ -21472,7 +21452,7 @@
       <c r="E445" t="s">
         <v>1253</v>
       </c>
-      <c r="F445" s="2">
+      <c r="F445" s="1">
         <v>46205</v>
       </c>
       <c r="G445" t="s">
@@ -21501,7 +21481,7 @@
       <c r="E446" t="s">
         <v>1254</v>
       </c>
-      <c r="F446" s="2">
+      <c r="F446" s="1">
         <v>46211</v>
       </c>
       <c r="G446" t="s">
@@ -21511,7 +21491,7 @@
         <v>1353</v>
       </c>
       <c r="I446">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q446" t="b">
         <v>1</v>
@@ -21533,7 +21513,7 @@
       <c r="E447" t="s">
         <v>1255</v>
       </c>
-      <c r="F447" s="2">
+      <c r="F447" s="1">
         <v>46211</v>
       </c>
       <c r="G447" t="s">
@@ -21543,7 +21523,7 @@
         <v>1353</v>
       </c>
       <c r="I447">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q447" t="b">
         <v>1</v>
@@ -21565,7 +21545,7 @@
       <c r="E448" t="s">
         <v>1256</v>
       </c>
-      <c r="F448" s="2">
+      <c r="F448" s="1">
         <v>46226</v>
       </c>
       <c r="G448" t="s">
@@ -21575,7 +21555,7 @@
         <v>1353</v>
       </c>
       <c r="I448">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q448" t="b">
         <v>1</v>
@@ -21597,7 +21577,7 @@
       <c r="E449" t="s">
         <v>1257</v>
       </c>
-      <c r="F449" s="2">
+      <c r="F449" s="1">
         <v>46226</v>
       </c>
       <c r="G449" t="s">
@@ -21607,7 +21587,7 @@
         <v>1353</v>
       </c>
       <c r="I449">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q449" t="b">
         <v>1</v>
@@ -21629,7 +21609,7 @@
       <c r="E450" t="s">
         <v>1258</v>
       </c>
-      <c r="F450" s="2">
+      <c r="F450" s="1">
         <v>46226</v>
       </c>
       <c r="G450" t="s">
@@ -21639,7 +21619,7 @@
         <v>1353</v>
       </c>
       <c r="I450">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q450" t="b">
         <v>1</v>
@@ -21661,7 +21641,7 @@
       <c r="E451" t="s">
         <v>1035</v>
       </c>
-      <c r="F451" s="2">
+      <c r="F451" s="1">
         <v>46230</v>
       </c>
       <c r="G451" t="s">
@@ -21671,7 +21651,7 @@
         <v>1353</v>
       </c>
       <c r="I451">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q451" t="b">
         <v>1</v>
@@ -21693,7 +21673,7 @@
       <c r="E452" t="s">
         <v>1259</v>
       </c>
-      <c r="F452" s="2">
+      <c r="F452" s="1">
         <v>46230</v>
       </c>
       <c r="G452" t="s">
@@ -21703,7 +21683,7 @@
         <v>1353</v>
       </c>
       <c r="I452">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q452" t="b">
         <v>1</v>
@@ -21725,7 +21705,7 @@
       <c r="E453" t="s">
         <v>1260</v>
       </c>
-      <c r="F453" s="2">
+      <c r="F453" s="1">
         <v>46230</v>
       </c>
       <c r="G453" t="s">
@@ -21735,7 +21715,7 @@
         <v>1353</v>
       </c>
       <c r="I453">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q453" t="b">
         <v>1</v>
@@ -21757,7 +21737,7 @@
       <c r="E454" t="s">
         <v>1261</v>
       </c>
-      <c r="F454" s="2">
+      <c r="F454" s="1">
         <v>46230</v>
       </c>
       <c r="G454" t="s">
@@ -21767,7 +21747,7 @@
         <v>1353</v>
       </c>
       <c r="I454">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q454" t="b">
         <v>1</v>
@@ -21789,7 +21769,7 @@
       <c r="E455" t="s">
         <v>1262</v>
       </c>
-      <c r="F455" s="2">
+      <c r="F455" s="1">
         <v>46230</v>
       </c>
       <c r="G455" t="s">
@@ -21799,7 +21779,7 @@
         <v>1353</v>
       </c>
       <c r="I455">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q455" t="b">
         <v>1</v>
@@ -21821,7 +21801,7 @@
       <c r="E456" t="s">
         <v>1263</v>
       </c>
-      <c r="F456" s="2">
+      <c r="F456" s="1">
         <v>46230</v>
       </c>
       <c r="G456" t="s">
@@ -21831,7 +21811,7 @@
         <v>1353</v>
       </c>
       <c r="I456">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q456" t="b">
         <v>1</v>
@@ -21853,7 +21833,7 @@
       <c r="E457" t="s">
         <v>1264</v>
       </c>
-      <c r="F457" s="2">
+      <c r="F457" s="1">
         <v>46230</v>
       </c>
       <c r="G457" t="s">
@@ -21863,7 +21843,7 @@
         <v>1353</v>
       </c>
       <c r="I457">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q457" t="b">
         <v>1</v>
@@ -21885,7 +21865,7 @@
       <c r="E458" t="s">
         <v>1202</v>
       </c>
-      <c r="F458" s="2">
+      <c r="F458" s="1">
         <v>46231</v>
       </c>
       <c r="G458" t="s">
@@ -21895,7 +21875,7 @@
         <v>1353</v>
       </c>
       <c r="I458">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q458" t="b">
         <v>1</v>
@@ -21917,7 +21897,7 @@
       <c r="E459" t="s">
         <v>1265</v>
       </c>
-      <c r="F459" s="2">
+      <c r="F459" s="1">
         <v>46233</v>
       </c>
       <c r="G459" t="s">
@@ -21927,7 +21907,7 @@
         <v>1353</v>
       </c>
       <c r="I459">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q459" t="b">
         <v>1</v>
@@ -21949,7 +21929,7 @@
       <c r="E460" t="s">
         <v>1266</v>
       </c>
-      <c r="F460" s="2">
+      <c r="F460" s="1">
         <v>46233</v>
       </c>
       <c r="G460" t="s">
@@ -21959,7 +21939,7 @@
         <v>1353</v>
       </c>
       <c r="I460">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q460" t="b">
         <v>1</v>
@@ -21981,7 +21961,7 @@
       <c r="E461" t="s">
         <v>1267</v>
       </c>
-      <c r="F461" s="2">
+      <c r="F461" s="1">
         <v>46233</v>
       </c>
       <c r="G461" t="s">
@@ -21991,7 +21971,7 @@
         <v>1353</v>
       </c>
       <c r="I461">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q461" t="b">
         <v>1</v>
@@ -22013,7 +21993,7 @@
       <c r="E462" t="s">
         <v>1268</v>
       </c>
-      <c r="F462" s="2">
+      <c r="F462" s="1">
         <v>46233</v>
       </c>
       <c r="G462" t="s">
@@ -22023,7 +22003,7 @@
         <v>1353</v>
       </c>
       <c r="I462">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q462" t="b">
         <v>1</v>
@@ -22045,7 +22025,7 @@
       <c r="E463" t="s">
         <v>1269</v>
       </c>
-      <c r="F463" s="2">
+      <c r="F463" s="1">
         <v>46234</v>
       </c>
       <c r="G463" t="s">
@@ -22055,7 +22035,7 @@
         <v>1353</v>
       </c>
       <c r="I463">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Q463" t="b">
         <v>1</v>
@@ -22077,7 +22057,7 @@
       <c r="E464" t="s">
         <v>1270</v>
       </c>
-      <c r="F464" s="2">
+      <c r="F464" s="1">
         <v>46230</v>
       </c>
       <c r="G464" t="s">
@@ -22087,7 +22067,7 @@
         <v>1353</v>
       </c>
       <c r="I464">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q464" t="b">
         <v>1</v>
@@ -22109,7 +22089,7 @@
       <c r="E465" t="s">
         <v>1271</v>
       </c>
-      <c r="F465" s="2">
+      <c r="F465" s="1">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
@@ -22119,7 +22099,7 @@
         <v>1353</v>
       </c>
       <c r="I465">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q465" t="b">
         <v>1</v>
@@ -22141,7 +22121,7 @@
       <c r="E466" t="s">
         <v>1272</v>
       </c>
-      <c r="F466" s="2">
+      <c r="F466" s="1">
         <v>46230</v>
       </c>
       <c r="G466" t="s">
@@ -22151,7 +22131,7 @@
         <v>1353</v>
       </c>
       <c r="I466">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q466" t="b">
         <v>1</v>
@@ -22173,7 +22153,7 @@
       <c r="E467" t="s">
         <v>1273</v>
       </c>
-      <c r="F467" s="2">
+      <c r="F467" s="1">
         <v>46230</v>
       </c>
       <c r="G467" t="s">
@@ -22183,7 +22163,7 @@
         <v>1353</v>
       </c>
       <c r="I467">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q467" t="b">
         <v>1</v>
@@ -22205,7 +22185,7 @@
       <c r="E468" t="s">
         <v>1274</v>
       </c>
-      <c r="F468" s="2">
+      <c r="F468" s="1">
         <v>46230</v>
       </c>
       <c r="G468" t="s">
@@ -22215,7 +22195,7 @@
         <v>1353</v>
       </c>
       <c r="I468">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q468" t="b">
         <v>1</v>
@@ -22237,7 +22217,7 @@
       <c r="E469" t="s">
         <v>1275</v>
       </c>
-      <c r="F469" s="2">
+      <c r="F469" s="1">
         <v>46230</v>
       </c>
       <c r="G469" t="s">
@@ -22247,7 +22227,7 @@
         <v>1353</v>
       </c>
       <c r="I469">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q469" t="b">
         <v>1</v>
@@ -22269,7 +22249,7 @@
       <c r="E470" t="s">
         <v>1276</v>
       </c>
-      <c r="F470" s="2">
+      <c r="F470" s="1">
         <v>46230</v>
       </c>
       <c r="G470" t="s">
@@ -22298,7 +22278,7 @@
       <c r="E471" t="s">
         <v>1277</v>
       </c>
-      <c r="F471" s="2">
+      <c r="F471" s="1">
         <v>46230</v>
       </c>
       <c r="G471" t="s">
@@ -22308,7 +22288,7 @@
         <v>1353</v>
       </c>
       <c r="I471">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q471" t="b">
         <v>1</v>
@@ -22330,7 +22310,7 @@
       <c r="E472" t="s">
         <v>1278</v>
       </c>
-      <c r="F472" s="2">
+      <c r="F472" s="1">
         <v>46230</v>
       </c>
       <c r="G472" t="s">
@@ -22340,7 +22320,7 @@
         <v>1353</v>
       </c>
       <c r="I472">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q472" t="b">
         <v>1</v>
@@ -22362,7 +22342,7 @@
       <c r="E473" t="s">
         <v>1279</v>
       </c>
-      <c r="F473" s="2">
+      <c r="F473" s="1">
         <v>46230</v>
       </c>
       <c r="G473" t="s">
@@ -22372,7 +22352,7 @@
         <v>1353</v>
       </c>
       <c r="I473">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q473" t="b">
         <v>1</v>
@@ -22394,7 +22374,7 @@
       <c r="E474" t="s">
         <v>1280</v>
       </c>
-      <c r="F474" s="2">
+      <c r="F474" s="1">
         <v>46231</v>
       </c>
       <c r="G474" t="s">
@@ -22404,7 +22384,7 @@
         <v>1353</v>
       </c>
       <c r="I474">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q474" t="b">
         <v>1</v>
@@ -22426,7 +22406,7 @@
       <c r="E475" t="s">
         <v>1281</v>
       </c>
-      <c r="F475" s="2">
+      <c r="F475" s="1">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
@@ -22436,7 +22416,7 @@
         <v>1353</v>
       </c>
       <c r="I475">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q475" t="b">
         <v>1</v>
@@ -22458,7 +22438,7 @@
       <c r="E476" t="s">
         <v>1282</v>
       </c>
-      <c r="F476" s="2">
+      <c r="F476" s="1">
         <v>46231</v>
       </c>
       <c r="G476" t="s">
@@ -22468,7 +22448,7 @@
         <v>1353</v>
       </c>
       <c r="I476">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q476" t="b">
         <v>1</v>
@@ -22490,7 +22470,7 @@
       <c r="E477" t="s">
         <v>1283</v>
       </c>
-      <c r="F477" s="2">
+      <c r="F477" s="1">
         <v>46231</v>
       </c>
       <c r="G477" t="s">
@@ -22500,7 +22480,7 @@
         <v>1353</v>
       </c>
       <c r="I477">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q477" t="b">
         <v>1</v>
@@ -22522,7 +22502,7 @@
       <c r="E478" t="s">
         <v>1284</v>
       </c>
-      <c r="F478" s="2">
+      <c r="F478" s="1">
         <v>46231</v>
       </c>
       <c r="G478" t="s">
@@ -22532,7 +22512,7 @@
         <v>1353</v>
       </c>
       <c r="I478">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q478" t="b">
         <v>1</v>
@@ -22554,7 +22534,7 @@
       <c r="E479" t="s">
         <v>1285</v>
       </c>
-      <c r="F479" s="2">
+      <c r="F479" s="1">
         <v>46231</v>
       </c>
       <c r="G479" t="s">
@@ -22564,7 +22544,7 @@
         <v>1353</v>
       </c>
       <c r="I479">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q479" t="b">
         <v>1</v>
@@ -22586,7 +22566,7 @@
       <c r="E480" t="s">
         <v>1286</v>
       </c>
-      <c r="F480" s="2">
+      <c r="F480" s="1">
         <v>46231</v>
       </c>
       <c r="G480" t="s">
@@ -22596,7 +22576,7 @@
         <v>1353</v>
       </c>
       <c r="I480">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q480" t="b">
         <v>1</v>
@@ -22618,7 +22598,7 @@
       <c r="E481" t="s">
         <v>1287</v>
       </c>
-      <c r="F481" s="2">
+      <c r="F481" s="1">
         <v>46231</v>
       </c>
       <c r="G481" t="s">
@@ -22628,7 +22608,7 @@
         <v>1353</v>
       </c>
       <c r="I481">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q481" t="b">
         <v>1</v>
@@ -22650,7 +22630,7 @@
       <c r="E482" t="s">
         <v>1288</v>
       </c>
-      <c r="F482" s="2">
+      <c r="F482" s="1">
         <v>46231</v>
       </c>
       <c r="G482" t="s">
@@ -22660,7 +22640,7 @@
         <v>1353</v>
       </c>
       <c r="I482">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q482" t="b">
         <v>1</v>
@@ -22682,7 +22662,7 @@
       <c r="E483" t="s">
         <v>1289</v>
       </c>
-      <c r="F483" s="2">
+      <c r="F483" s="1">
         <v>46231</v>
       </c>
       <c r="G483" t="s">
@@ -22692,7 +22672,7 @@
         <v>1353</v>
       </c>
       <c r="I483">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q483" t="b">
         <v>1</v>
@@ -22714,7 +22694,7 @@
       <c r="E484" t="s">
         <v>1290</v>
       </c>
-      <c r="F484" s="2">
+      <c r="F484" s="1">
         <v>46231</v>
       </c>
       <c r="G484" t="s">
@@ -22724,7 +22704,7 @@
         <v>1353</v>
       </c>
       <c r="I484">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q484" t="b">
         <v>1</v>
@@ -22746,7 +22726,7 @@
       <c r="E485" t="s">
         <v>1291</v>
       </c>
-      <c r="F485" s="2">
+      <c r="F485" s="1">
         <v>46231</v>
       </c>
       <c r="G485" t="s">
@@ -22756,7 +22736,7 @@
         <v>1353</v>
       </c>
       <c r="I485">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q485" t="b">
         <v>1</v>
@@ -22778,7 +22758,7 @@
       <c r="E486" t="s">
         <v>1292</v>
       </c>
-      <c r="F486" s="2">
+      <c r="F486" s="1">
         <v>46231</v>
       </c>
       <c r="G486" t="s">
@@ -22788,7 +22768,7 @@
         <v>1353</v>
       </c>
       <c r="I486">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q486" t="b">
         <v>1</v>
@@ -22810,7 +22790,7 @@
       <c r="E487" t="s">
         <v>1293</v>
       </c>
-      <c r="F487" s="2">
+      <c r="F487" s="1">
         <v>46231</v>
       </c>
       <c r="G487" t="s">
@@ -22820,7 +22800,7 @@
         <v>1353</v>
       </c>
       <c r="I487">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q487" t="b">
         <v>1</v>
@@ -22842,7 +22822,7 @@
       <c r="E488" t="s">
         <v>1294</v>
       </c>
-      <c r="F488" s="2">
+      <c r="F488" s="1">
         <v>46231</v>
       </c>
       <c r="G488" t="s">
@@ -22852,7 +22832,7 @@
         <v>1353</v>
       </c>
       <c r="I488">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q488" t="b">
         <v>1</v>
@@ -22874,7 +22854,7 @@
       <c r="E489" t="s">
         <v>1295</v>
       </c>
-      <c r="F489" s="2">
+      <c r="F489" s="1">
         <v>46231</v>
       </c>
       <c r="G489" t="s">
@@ -22884,7 +22864,7 @@
         <v>1353</v>
       </c>
       <c r="I489">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q489" t="b">
         <v>1</v>
@@ -22906,7 +22886,7 @@
       <c r="E490" t="s">
         <v>1296</v>
       </c>
-      <c r="F490" s="2">
+      <c r="F490" s="1">
         <v>46231</v>
       </c>
       <c r="G490" t="s">
@@ -22916,7 +22896,7 @@
         <v>1353</v>
       </c>
       <c r="I490">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q490" t="b">
         <v>1</v>
@@ -22938,7 +22918,7 @@
       <c r="E491" t="s">
         <v>1297</v>
       </c>
-      <c r="F491" s="2">
+      <c r="F491" s="1">
         <v>46231</v>
       </c>
       <c r="G491" t="s">
@@ -22948,7 +22928,7 @@
         <v>1353</v>
       </c>
       <c r="I491">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q491" t="b">
         <v>1</v>
@@ -22970,7 +22950,7 @@
       <c r="E492" t="s">
         <v>911</v>
       </c>
-      <c r="F492" s="2">
+      <c r="F492" s="1">
         <v>46231</v>
       </c>
       <c r="G492" t="s">
@@ -22980,7 +22960,7 @@
         <v>1355</v>
       </c>
       <c r="I492">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q492" t="b">
         <v>1</v>
@@ -23002,7 +22982,7 @@
       <c r="E493" t="s">
         <v>995</v>
       </c>
-      <c r="F493" s="2">
+      <c r="F493" s="1">
         <v>46231</v>
       </c>
       <c r="G493" t="s">
@@ -23012,7 +22992,7 @@
         <v>1355</v>
       </c>
       <c r="I493">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q493" t="b">
         <v>1</v>
@@ -23034,7 +23014,7 @@
       <c r="E494" t="s">
         <v>867</v>
       </c>
-      <c r="F494" s="2">
+      <c r="F494" s="1">
         <v>46231</v>
       </c>
       <c r="G494" t="s">
@@ -23044,7 +23024,7 @@
         <v>1355</v>
       </c>
       <c r="I494">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q494" t="b">
         <v>1</v>
@@ -23066,7 +23046,7 @@
       <c r="E495" t="s">
         <v>912</v>
       </c>
-      <c r="F495" s="2">
+      <c r="F495" s="1">
         <v>46231</v>
       </c>
       <c r="G495" t="s">
@@ -23076,7 +23056,7 @@
         <v>1355</v>
       </c>
       <c r="I495">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q495" t="b">
         <v>1</v>
@@ -23098,7 +23078,7 @@
       <c r="E496" t="s">
         <v>1048</v>
       </c>
-      <c r="F496" s="2">
+      <c r="F496" s="1">
         <v>46231</v>
       </c>
       <c r="G496" t="s">
@@ -23108,7 +23088,7 @@
         <v>1355</v>
       </c>
       <c r="I496">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q496" t="b">
         <v>1</v>
@@ -23130,7 +23110,7 @@
       <c r="E497" t="s">
         <v>1298</v>
       </c>
-      <c r="F497" s="2">
+      <c r="F497" s="1">
         <v>46231</v>
       </c>
       <c r="G497" t="s">
@@ -23140,7 +23120,7 @@
         <v>1353</v>
       </c>
       <c r="I497">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q497" t="b">
         <v>1</v>
@@ -23162,7 +23142,7 @@
       <c r="E498" t="s">
         <v>1299</v>
       </c>
-      <c r="F498" s="2">
+      <c r="F498" s="1">
         <v>46231</v>
       </c>
       <c r="G498" t="s">
@@ -23172,7 +23152,7 @@
         <v>1353</v>
       </c>
       <c r="I498">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q498" t="b">
         <v>1</v>
@@ -23194,7 +23174,7 @@
       <c r="E499" t="s">
         <v>1300</v>
       </c>
-      <c r="F499" s="2">
+      <c r="F499" s="1">
         <v>46231</v>
       </c>
       <c r="G499" t="s">
@@ -23204,7 +23184,7 @@
         <v>1355</v>
       </c>
       <c r="I499">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q499" t="b">
         <v>1</v>
@@ -23226,7 +23206,7 @@
       <c r="E500" t="s">
         <v>1301</v>
       </c>
-      <c r="F500" s="2">
+      <c r="F500" s="1">
         <v>46231</v>
       </c>
       <c r="G500" t="s">
@@ -23236,7 +23216,7 @@
         <v>1353</v>
       </c>
       <c r="I500">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q500" t="b">
         <v>1</v>
@@ -23258,7 +23238,7 @@
       <c r="E501" t="s">
         <v>1302</v>
       </c>
-      <c r="F501" s="2">
+      <c r="F501" s="1">
         <v>46231</v>
       </c>
       <c r="G501" t="s">
@@ -23268,7 +23248,7 @@
         <v>1353</v>
       </c>
       <c r="I501">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q501" t="b">
         <v>1</v>
@@ -23290,7 +23270,7 @@
       <c r="E502" t="s">
         <v>1303</v>
       </c>
-      <c r="F502" s="2">
+      <c r="F502" s="1">
         <v>46231</v>
       </c>
       <c r="G502" t="s">
@@ -23300,7 +23280,7 @@
         <v>1353</v>
       </c>
       <c r="I502">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q502" t="b">
         <v>1</v>
@@ -23322,7 +23302,7 @@
       <c r="E503" t="s">
         <v>1304</v>
       </c>
-      <c r="F503" s="2">
+      <c r="F503" s="1">
         <v>46231</v>
       </c>
       <c r="G503" t="s">
@@ -23332,7 +23312,7 @@
         <v>1353</v>
       </c>
       <c r="I503">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q503" t="b">
         <v>1</v>
@@ -23354,7 +23334,7 @@
       <c r="E504" t="s">
         <v>1305</v>
       </c>
-      <c r="F504" s="2">
+      <c r="F504" s="1">
         <v>46232</v>
       </c>
       <c r="G504" t="s">
@@ -23364,7 +23344,7 @@
         <v>1353</v>
       </c>
       <c r="I504">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q504" t="b">
         <v>1</v>
@@ -23386,7 +23366,7 @@
       <c r="E505" t="s">
         <v>1306</v>
       </c>
-      <c r="F505" s="2">
+      <c r="F505" s="1">
         <v>46232</v>
       </c>
       <c r="G505" t="s">
@@ -23396,7 +23376,7 @@
         <v>1353</v>
       </c>
       <c r="I505">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q505" t="b">
         <v>1</v>
@@ -23418,7 +23398,7 @@
       <c r="E506" t="s">
         <v>1307</v>
       </c>
-      <c r="F506" s="2">
+      <c r="F506" s="1">
         <v>46232</v>
       </c>
       <c r="G506" t="s">
@@ -23428,7 +23408,7 @@
         <v>1353</v>
       </c>
       <c r="I506">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q506" t="b">
         <v>1</v>
@@ -23450,7 +23430,7 @@
       <c r="E507" t="s">
         <v>1308</v>
       </c>
-      <c r="F507" s="2">
+      <c r="F507" s="1">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
@@ -23460,7 +23440,7 @@
         <v>1353</v>
       </c>
       <c r="I507">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q507" t="b">
         <v>1</v>
@@ -23482,7 +23462,7 @@
       <c r="E508" t="s">
         <v>1309</v>
       </c>
-      <c r="F508" s="2">
+      <c r="F508" s="1">
         <v>46237</v>
       </c>
       <c r="G508" t="s">
@@ -23511,7 +23491,7 @@
       <c r="E509" t="s">
         <v>1310</v>
       </c>
-      <c r="F509" s="2">
+      <c r="F509" s="1">
         <v>46237</v>
       </c>
       <c r="G509" t="s">
@@ -23521,7 +23501,7 @@
         <v>1353</v>
       </c>
       <c r="I509">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q509" t="b">
         <v>1</v>
@@ -23543,7 +23523,7 @@
       <c r="E510" t="s">
         <v>1311</v>
       </c>
-      <c r="F510" s="2">
+      <c r="F510" s="1">
         <v>46237</v>
       </c>
       <c r="G510" t="s">
@@ -23553,7 +23533,7 @@
         <v>1353</v>
       </c>
       <c r="I510">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q510" t="b">
         <v>1</v>
@@ -23575,7 +23555,7 @@
       <c r="E511" t="s">
         <v>1312</v>
       </c>
-      <c r="F511" s="2">
+      <c r="F511" s="1">
         <v>46240</v>
       </c>
       <c r="G511" t="s">
@@ -23585,7 +23565,7 @@
         <v>1353</v>
       </c>
       <c r="I511">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q511" t="b">
         <v>1</v>
@@ -23607,7 +23587,7 @@
       <c r="E512" t="s">
         <v>1313</v>
       </c>
-      <c r="F512" s="2">
+      <c r="F512" s="1">
         <v>46240</v>
       </c>
       <c r="G512" t="s">
@@ -23617,7 +23597,7 @@
         <v>1353</v>
       </c>
       <c r="I512">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q512" t="b">
         <v>1</v>
@@ -23639,7 +23619,7 @@
       <c r="E513" t="s">
         <v>1314</v>
       </c>
-      <c r="F513" s="2">
+      <c r="F513" s="1">
         <v>46244</v>
       </c>
       <c r="G513" t="s">
@@ -23649,7 +23629,7 @@
         <v>1353</v>
       </c>
       <c r="I513">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q513" t="b">
         <v>1</v>
@@ -23671,7 +23651,7 @@
       <c r="E514" t="s">
         <v>1315</v>
       </c>
-      <c r="F514" s="2">
+      <c r="F514" s="1">
         <v>46244</v>
       </c>
       <c r="G514" t="s">
@@ -23681,7 +23661,7 @@
         <v>1353</v>
       </c>
       <c r="I514">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q514" t="b">
         <v>1</v>
@@ -23703,7 +23683,7 @@
       <c r="E515" t="s">
         <v>1043</v>
       </c>
-      <c r="F515" s="2">
+      <c r="F515" s="1">
         <v>46244</v>
       </c>
       <c r="G515" t="s">
@@ -23713,7 +23693,7 @@
         <v>1353</v>
       </c>
       <c r="I515">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q515" t="b">
         <v>1</v>
@@ -23735,7 +23715,7 @@
       <c r="E516" t="s">
         <v>1316</v>
       </c>
-      <c r="F516" s="2">
+      <c r="F516" s="1">
         <v>46252</v>
       </c>
       <c r="G516" t="s">
@@ -23745,7 +23725,7 @@
         <v>1353</v>
       </c>
       <c r="I516">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q516" t="b">
         <v>1</v>
@@ -23767,7 +23747,7 @@
       <c r="E517" t="s">
         <v>1317</v>
       </c>
-      <c r="F517" s="2">
+      <c r="F517" s="1">
         <v>46252</v>
       </c>
       <c r="G517" t="s">
@@ -23777,7 +23757,7 @@
         <v>1353</v>
       </c>
       <c r="I517">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q517" t="b">
         <v>1</v>
@@ -23799,7 +23779,7 @@
       <c r="E518" t="s">
         <v>1318</v>
       </c>
-      <c r="F518" s="2">
+      <c r="F518" s="1">
         <v>46252</v>
       </c>
       <c r="G518" t="s">
@@ -23809,7 +23789,7 @@
         <v>1353</v>
       </c>
       <c r="I518">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q518" t="b">
         <v>1</v>
@@ -23831,7 +23811,7 @@
       <c r="E519" t="s">
         <v>1253</v>
       </c>
-      <c r="F519" s="2">
+      <c r="F519" s="1">
         <v>46254</v>
       </c>
       <c r="G519" t="s">
@@ -23841,7 +23821,7 @@
         <v>1353</v>
       </c>
       <c r="I519">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Q519" t="b">
         <v>1</v>
@@ -23863,7 +23843,7 @@
       <c r="E520" t="s">
         <v>1319</v>
       </c>
-      <c r="F520" s="2">
+      <c r="F520" s="1">
         <v>46254</v>
       </c>
       <c r="G520" t="s">
@@ -23873,7 +23853,7 @@
         <v>1353</v>
       </c>
       <c r="I520">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Q520" t="b">
         <v>1</v>
@@ -23895,7 +23875,7 @@
       <c r="E521" t="s">
         <v>1320</v>
       </c>
-      <c r="F521" s="2">
+      <c r="F521" s="1">
         <v>46254</v>
       </c>
       <c r="G521" t="s">
@@ -23905,7 +23885,7 @@
         <v>1353</v>
       </c>
       <c r="I521">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Q521" t="b">
         <v>1</v>
@@ -23927,7 +23907,7 @@
       <c r="E522" t="s">
         <v>1253</v>
       </c>
-      <c r="F522" s="2">
+      <c r="F522" s="1">
         <v>46254</v>
       </c>
       <c r="G522" t="s">
@@ -23937,7 +23917,7 @@
         <v>1353</v>
       </c>
       <c r="I522">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Q522" t="b">
         <v>1</v>
@@ -23959,7 +23939,7 @@
       <c r="E523" t="s">
         <v>1319</v>
       </c>
-      <c r="F523" s="2">
+      <c r="F523" s="1">
         <v>46254</v>
       </c>
       <c r="G523" t="s">
@@ -23969,7 +23949,7 @@
         <v>1353</v>
       </c>
       <c r="I523">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Q523" t="b">
         <v>1</v>
@@ -23991,7 +23971,7 @@
       <c r="E524" t="s">
         <v>1321</v>
       </c>
-      <c r="F524" s="2">
+      <c r="F524" s="1">
         <v>46265</v>
       </c>
       <c r="G524" t="s">
@@ -24001,7 +23981,7 @@
         <v>1353</v>
       </c>
       <c r="I524">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q524" t="b">
         <v>1</v>
@@ -24023,7 +24003,7 @@
       <c r="E525" t="s">
         <v>1322</v>
       </c>
-      <c r="F525" s="2">
+      <c r="F525" s="1">
         <v>46265</v>
       </c>
       <c r="G525" t="s">
@@ -24033,7 +24013,7 @@
         <v>1353</v>
       </c>
       <c r="I525">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q525" t="b">
         <v>1</v>
@@ -24055,7 +24035,7 @@
       <c r="E526" t="s">
         <v>1323</v>
       </c>
-      <c r="F526" s="2">
+      <c r="F526" s="1">
         <v>46265</v>
       </c>
       <c r="G526" t="s">
@@ -24065,7 +24045,7 @@
         <v>1353</v>
       </c>
       <c r="I526">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q526" t="b">
         <v>1</v>
@@ -24087,7 +24067,7 @@
       <c r="E527" t="s">
         <v>1324</v>
       </c>
-      <c r="F527" s="2">
+      <c r="F527" s="1">
         <v>46265</v>
       </c>
       <c r="G527" t="s">
@@ -24097,7 +24077,7 @@
         <v>1353</v>
       </c>
       <c r="I527">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q527" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
@@ -4529,8 +4529,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -4546,7 +4554,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4554,12 +4562,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4859,55 +4885,55 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4927,7 +4953,7 @@
       <c r="E2" t="s">
         <v>829</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>45698</v>
       </c>
       <c r="G2" t="s">
@@ -4965,7 +4991,7 @@
       <c r="E3" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>45714</v>
       </c>
       <c r="G3" t="s">
@@ -5003,7 +5029,7 @@
       <c r="E4" t="s">
         <v>831</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>45714</v>
       </c>
       <c r="G4" t="s">
@@ -5041,7 +5067,7 @@
       <c r="E5" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>45714</v>
       </c>
       <c r="G5" t="s">
@@ -5062,7 +5088,7 @@
       <c r="L5" t="s">
         <v>1367</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <v>45993</v>
       </c>
       <c r="Q5" t="b">
@@ -5085,7 +5111,7 @@
       <c r="E6" t="s">
         <v>833</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>45736</v>
       </c>
       <c r="G6" t="s">
@@ -5106,7 +5132,7 @@
       <c r="L6" t="s">
         <v>1368</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="2">
         <v>45889</v>
       </c>
       <c r="Q6" t="b">
@@ -5129,7 +5155,7 @@
       <c r="E7" t="s">
         <v>834</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>45736</v>
       </c>
       <c r="G7" t="s">
@@ -5150,7 +5176,7 @@
       <c r="L7" t="s">
         <v>1369</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="2">
         <v>45848</v>
       </c>
       <c r="O7" t="s">
@@ -5176,7 +5202,7 @@
       <c r="E8" t="s">
         <v>835</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>45736</v>
       </c>
       <c r="G8" t="s">
@@ -5205,7 +5231,7 @@
       <c r="E9" t="s">
         <v>836</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="2">
         <v>45736</v>
       </c>
       <c r="G9" t="s">
@@ -5226,7 +5252,7 @@
       <c r="L9" t="s">
         <v>1370</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="2">
         <v>46098</v>
       </c>
       <c r="O9">
@@ -5252,7 +5278,7 @@
       <c r="E10" t="s">
         <v>837</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="2">
         <v>45736</v>
       </c>
       <c r="G10" t="s">
@@ -5273,7 +5299,7 @@
       <c r="L10" t="s">
         <v>1371</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="2">
         <v>46114</v>
       </c>
       <c r="O10" t="s">
@@ -5299,7 +5325,7 @@
       <c r="E11" t="s">
         <v>838</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <v>45736</v>
       </c>
       <c r="G11" t="s">
@@ -5320,7 +5346,7 @@
       <c r="L11" t="s">
         <v>1369</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="2">
         <v>45848</v>
       </c>
       <c r="O11" t="s">
@@ -5346,7 +5372,7 @@
       <c r="E12" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="2">
         <v>45736</v>
       </c>
       <c r="G12" t="s">
@@ -5367,7 +5393,7 @@
       <c r="L12" t="s">
         <v>1372</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="2">
         <v>45860</v>
       </c>
       <c r="Q12" t="b">
@@ -5390,7 +5416,7 @@
       <c r="E13" t="s">
         <v>840</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <v>45736</v>
       </c>
       <c r="G13" t="s">
@@ -5419,7 +5445,7 @@
       <c r="E14" t="s">
         <v>841</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="2">
         <v>45736</v>
       </c>
       <c r="G14" t="s">
@@ -5440,7 +5466,7 @@
       <c r="L14" t="s">
         <v>1373</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N14" s="2">
         <v>45800</v>
       </c>
       <c r="Q14" t="b">
@@ -5463,7 +5489,7 @@
       <c r="E15" t="s">
         <v>842</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="2">
         <v>45736</v>
       </c>
       <c r="G15" t="s">
@@ -5501,7 +5527,7 @@
       <c r="E16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <v>45736</v>
       </c>
       <c r="G16" t="s">
@@ -5539,7 +5565,7 @@
       <c r="E17" t="s">
         <v>844</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="2">
         <v>45736</v>
       </c>
       <c r="G17" t="s">
@@ -5560,7 +5586,7 @@
       <c r="L17" t="s">
         <v>1368</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17" s="2">
         <v>45897</v>
       </c>
       <c r="Q17" t="b">
@@ -5583,7 +5609,7 @@
       <c r="E18" t="s">
         <v>845</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <v>45736</v>
       </c>
       <c r="G18" t="s">
@@ -5604,7 +5630,7 @@
       <c r="L18" t="s">
         <v>1373</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="2">
         <v>45802</v>
       </c>
       <c r="Q18" t="b">
@@ -5627,7 +5653,7 @@
       <c r="E19" t="s">
         <v>846</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="2">
         <v>45736</v>
       </c>
       <c r="G19" t="s">
@@ -5656,7 +5682,7 @@
       <c r="E20" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="2">
         <v>45736</v>
       </c>
       <c r="G20" t="s">
@@ -5677,7 +5703,7 @@
       <c r="L20" t="s">
         <v>1374</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20" s="2">
         <v>46135</v>
       </c>
       <c r="Q20" t="b">
@@ -5700,7 +5726,7 @@
       <c r="E21" t="s">
         <v>848</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="2">
         <v>45736</v>
       </c>
       <c r="G21" t="s">
@@ -5729,7 +5755,7 @@
       <c r="E22" t="s">
         <v>849</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="2">
         <v>45736</v>
       </c>
       <c r="G22" t="s">
@@ -5767,7 +5793,7 @@
       <c r="E23" t="s">
         <v>850</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <v>45736</v>
       </c>
       <c r="G23" t="s">
@@ -5788,7 +5814,7 @@
       <c r="L23" t="s">
         <v>1375</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23" s="2">
         <v>45965</v>
       </c>
       <c r="P23" t="s">
@@ -5814,7 +5840,7 @@
       <c r="E24" t="s">
         <v>851</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="2">
         <v>45736</v>
       </c>
       <c r="G24" t="s">
@@ -5843,7 +5869,7 @@
       <c r="E25" t="s">
         <v>852</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="2">
         <v>45736</v>
       </c>
       <c r="G25" t="s">
@@ -5872,7 +5898,7 @@
       <c r="E26" t="s">
         <v>853</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="2">
         <v>45736</v>
       </c>
       <c r="G26" t="s">
@@ -5893,7 +5919,7 @@
       <c r="L26" t="s">
         <v>1376</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N26" s="2">
         <v>45891</v>
       </c>
       <c r="P26" t="s">
@@ -5919,7 +5945,7 @@
       <c r="E27" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="2">
         <v>45736</v>
       </c>
       <c r="G27" t="s">
@@ -5957,7 +5983,7 @@
       <c r="E28" t="s">
         <v>855</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="2">
         <v>45736</v>
       </c>
       <c r="G28" t="s">
@@ -5986,7 +6012,7 @@
       <c r="E29" t="s">
         <v>856</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="2">
         <v>45736</v>
       </c>
       <c r="G29" t="s">
@@ -6015,7 +6041,7 @@
       <c r="E30" t="s">
         <v>857</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="2">
         <v>45736</v>
       </c>
       <c r="G30" t="s">
@@ -6036,7 +6062,7 @@
       <c r="L30" t="s">
         <v>1377</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30" s="2">
         <v>45945</v>
       </c>
       <c r="Q30" t="b">
@@ -6059,7 +6085,7 @@
       <c r="E31" t="s">
         <v>858</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="2">
         <v>45736</v>
       </c>
       <c r="G31" t="s">
@@ -6088,7 +6114,7 @@
       <c r="E32" t="s">
         <v>859</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="2">
         <v>45736</v>
       </c>
       <c r="G32" t="s">
@@ -6126,7 +6152,7 @@
       <c r="E33" t="s">
         <v>860</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="2">
         <v>45736</v>
       </c>
       <c r="G33" t="s">
@@ -6155,7 +6181,7 @@
       <c r="E34" t="s">
         <v>861</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="2">
         <v>45736</v>
       </c>
       <c r="G34" t="s">
@@ -6184,7 +6210,7 @@
       <c r="E35" t="s">
         <v>862</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="2">
         <v>45736</v>
       </c>
       <c r="G35" t="s">
@@ -6213,7 +6239,7 @@
       <c r="E36" t="s">
         <v>863</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="2">
         <v>45736</v>
       </c>
       <c r="G36" t="s">
@@ -6242,7 +6268,7 @@
       <c r="E37" t="s">
         <v>864</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="2">
         <v>45736</v>
       </c>
       <c r="G37" t="s">
@@ -6271,7 +6297,7 @@
       <c r="E38" t="s">
         <v>844</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="2">
         <v>45736</v>
       </c>
       <c r="G38" t="s">
@@ -6297,7 +6323,7 @@
       <c r="D39" t="s">
         <v>731</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="2">
         <v>45736</v>
       </c>
       <c r="G39" t="s">
@@ -6332,7 +6358,7 @@
       <c r="D40" t="s">
         <v>731</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="2">
         <v>45736</v>
       </c>
       <c r="G40" t="s">
@@ -6370,7 +6396,7 @@
       <c r="E41" t="s">
         <v>865</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="2">
         <v>45736</v>
       </c>
       <c r="G41" t="s">
@@ -6399,7 +6425,7 @@
       <c r="E42" t="s">
         <v>866</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="2">
         <v>45736</v>
       </c>
       <c r="G42" t="s">
@@ -6428,7 +6454,7 @@
       <c r="E43" t="s">
         <v>867</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="2">
         <v>45736</v>
       </c>
       <c r="G43" t="s">
@@ -6463,7 +6489,7 @@
       <c r="E44" t="s">
         <v>868</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="2">
         <v>45769</v>
       </c>
       <c r="G44" t="s">
@@ -6484,7 +6510,7 @@
       <c r="L44" t="s">
         <v>1378</v>
       </c>
-      <c r="N44" s="1">
+      <c r="N44" s="2">
         <v>45856</v>
       </c>
       <c r="P44" t="s">
@@ -6510,7 +6536,7 @@
       <c r="E45" t="s">
         <v>869</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="2">
         <v>45769</v>
       </c>
       <c r="G45" t="s">
@@ -6531,7 +6557,7 @@
       <c r="L45" t="s">
         <v>1379</v>
       </c>
-      <c r="N45" s="1">
+      <c r="N45" s="2">
         <v>46100</v>
       </c>
       <c r="O45">
@@ -6557,7 +6583,7 @@
       <c r="E46" t="s">
         <v>870</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="2">
         <v>45769</v>
       </c>
       <c r="G46" t="s">
@@ -6595,7 +6621,7 @@
       <c r="E47" t="s">
         <v>871</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="2">
         <v>45769</v>
       </c>
       <c r="G47" t="s">
@@ -6616,7 +6642,7 @@
       <c r="L47" t="s">
         <v>1380</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N47" s="2">
         <v>46113</v>
       </c>
       <c r="P47" t="s">
@@ -6642,7 +6668,7 @@
       <c r="E48" t="s">
         <v>872</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="2">
         <v>45769</v>
       </c>
       <c r="G48" t="s">
@@ -6680,7 +6706,7 @@
       <c r="E49" t="s">
         <v>873</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="2">
         <v>45769</v>
       </c>
       <c r="G49" t="s">
@@ -6709,7 +6735,7 @@
       <c r="E50" t="s">
         <v>874</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="2">
         <v>45769</v>
       </c>
       <c r="G50" t="s">
@@ -6747,7 +6773,7 @@
       <c r="E51" t="s">
         <v>875</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="2">
         <v>45769</v>
       </c>
       <c r="G51" t="s">
@@ -6776,7 +6802,7 @@
       <c r="E52" t="s">
         <v>876</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="2">
         <v>45769</v>
       </c>
       <c r="G52" t="s">
@@ -6814,7 +6840,7 @@
       <c r="E53" t="s">
         <v>877</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="2">
         <v>45769</v>
       </c>
       <c r="G53" t="s">
@@ -6852,7 +6878,7 @@
       <c r="E54" t="s">
         <v>878</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="2">
         <v>45769</v>
       </c>
       <c r="G54" t="s">
@@ -6890,7 +6916,7 @@
       <c r="E55" t="s">
         <v>879</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="2">
         <v>45769</v>
       </c>
       <c r="G55" t="s">
@@ -6919,7 +6945,7 @@
       <c r="E56" t="s">
         <v>880</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="2">
         <v>45769</v>
       </c>
       <c r="G56" t="s">
@@ -6948,7 +6974,7 @@
       <c r="E57" t="s">
         <v>881</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="2">
         <v>45769</v>
       </c>
       <c r="G57" t="s">
@@ -6986,7 +7012,7 @@
       <c r="E58" t="s">
         <v>882</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="2">
         <v>45769</v>
       </c>
       <c r="G58" t="s">
@@ -7015,7 +7041,7 @@
       <c r="E59" t="s">
         <v>883</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="2">
         <v>45769</v>
       </c>
       <c r="G59" t="s">
@@ -7044,7 +7070,7 @@
       <c r="E60" t="s">
         <v>884</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="2">
         <v>45769</v>
       </c>
       <c r="G60" t="s">
@@ -7073,7 +7099,7 @@
       <c r="E61" t="s">
         <v>885</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="2">
         <v>45769</v>
       </c>
       <c r="G61" t="s">
@@ -7102,7 +7128,7 @@
       <c r="E62" t="s">
         <v>886</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="2">
         <v>45770</v>
       </c>
       <c r="G62" t="s">
@@ -7131,7 +7157,7 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="2">
         <v>45799</v>
       </c>
       <c r="G63" t="s">
@@ -7152,7 +7178,7 @@
       <c r="L63" t="s">
         <v>1381</v>
       </c>
-      <c r="N63" s="1">
+      <c r="N63" s="2">
         <v>46092</v>
       </c>
       <c r="P63" t="s">
@@ -7178,7 +7204,7 @@
       <c r="E64" t="s">
         <v>888</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="2">
         <v>45799</v>
       </c>
       <c r="G64" t="s">
@@ -7199,7 +7225,7 @@
       <c r="L64" t="s">
         <v>1382</v>
       </c>
-      <c r="N64" s="1">
+      <c r="N64" s="2">
         <v>46119</v>
       </c>
       <c r="Q64" t="b">
@@ -7222,7 +7248,7 @@
       <c r="E65" t="s">
         <v>889</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="2">
         <v>45799</v>
       </c>
       <c r="G65" t="s">
@@ -7251,7 +7277,7 @@
       <c r="E66" t="s">
         <v>890</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="2">
         <v>45799</v>
       </c>
       <c r="G66" t="s">
@@ -7280,7 +7306,7 @@
       <c r="E67" t="s">
         <v>891</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="2">
         <v>45799</v>
       </c>
       <c r="G67" t="s">
@@ -7309,7 +7335,7 @@
       <c r="E68" t="s">
         <v>892</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="2">
         <v>45799</v>
       </c>
       <c r="G68" t="s">
@@ -7338,7 +7364,7 @@
       <c r="E69" t="s">
         <v>893</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="2">
         <v>45803</v>
       </c>
       <c r="G69" t="s">
@@ -7367,7 +7393,7 @@
       <c r="E70" t="s">
         <v>894</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="2">
         <v>45803</v>
       </c>
       <c r="G70" t="s">
@@ -7388,7 +7414,7 @@
       <c r="L70" t="s">
         <v>1383</v>
       </c>
-      <c r="N70" s="1">
+      <c r="N70" s="2">
         <v>46232</v>
       </c>
       <c r="Q70" t="b">
@@ -7411,7 +7437,7 @@
       <c r="E71" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="2">
         <v>45803</v>
       </c>
       <c r="G71" t="s">
@@ -7432,7 +7458,7 @@
       <c r="L71" t="s">
         <v>1383</v>
       </c>
-      <c r="N71" s="1">
+      <c r="N71" s="2">
         <v>46232</v>
       </c>
       <c r="Q71" t="b">
@@ -7455,7 +7481,7 @@
       <c r="E72" t="s">
         <v>896</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="2">
         <v>45803</v>
       </c>
       <c r="G72" t="s">
@@ -7484,7 +7510,7 @@
       <c r="E73" t="s">
         <v>897</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="2">
         <v>45803</v>
       </c>
       <c r="G73" t="s">
@@ -7522,7 +7548,7 @@
       <c r="E74" t="s">
         <v>896</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="2">
         <v>45803</v>
       </c>
       <c r="G74" t="s">
@@ -7551,7 +7577,7 @@
       <c r="E75" t="s">
         <v>898</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="2">
         <v>45803</v>
       </c>
       <c r="G75" t="s">
@@ -7572,7 +7598,7 @@
       <c r="L75" t="s">
         <v>1383</v>
       </c>
-      <c r="N75" s="1">
+      <c r="N75" s="2">
         <v>46232</v>
       </c>
       <c r="Q75" t="b">
@@ -7595,7 +7621,7 @@
       <c r="E76" t="s">
         <v>899</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="2">
         <v>45803</v>
       </c>
       <c r="G76" t="s">
@@ -7630,7 +7656,7 @@
       <c r="E77" t="s">
         <v>900</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="2">
         <v>45803</v>
       </c>
       <c r="G77" t="s">
@@ -7659,7 +7685,7 @@
       <c r="E78" t="s">
         <v>901</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78" s="2">
         <v>45803</v>
       </c>
       <c r="G78" t="s">
@@ -7688,7 +7714,7 @@
       <c r="E79" t="s">
         <v>902</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="2">
         <v>45803</v>
       </c>
       <c r="G79" t="s">
@@ -7723,7 +7749,7 @@
       <c r="E80" t="s">
         <v>903</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="2">
         <v>45803</v>
       </c>
       <c r="G80" t="s">
@@ -7744,7 +7770,7 @@
       <c r="L80" t="s">
         <v>1383</v>
       </c>
-      <c r="N80" s="1">
+      <c r="N80" s="2">
         <v>46232</v>
       </c>
       <c r="Q80" t="b">
@@ -7767,7 +7793,7 @@
       <c r="E81" t="s">
         <v>904</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="2">
         <v>45813</v>
       </c>
       <c r="G81" t="s">
@@ -7796,7 +7822,7 @@
       <c r="E82" t="s">
         <v>905</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="2">
         <v>45813</v>
       </c>
       <c r="G82" t="s">
@@ -7834,7 +7860,7 @@
       <c r="E83" t="s">
         <v>906</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="2">
         <v>45813</v>
       </c>
       <c r="G83" t="s">
@@ -7863,7 +7889,7 @@
       <c r="E84" t="s">
         <v>907</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="2">
         <v>45813</v>
       </c>
       <c r="G84" t="s">
@@ -7884,7 +7910,7 @@
       <c r="L84" t="s">
         <v>1384</v>
       </c>
-      <c r="N84" s="1">
+      <c r="N84" s="2">
         <v>45853</v>
       </c>
       <c r="O84">
@@ -7910,7 +7936,7 @@
       <c r="E85" t="s">
         <v>908</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85" s="2">
         <v>45813</v>
       </c>
       <c r="G85" t="s">
@@ -7948,7 +7974,7 @@
       <c r="E86" t="s">
         <v>909</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="2">
         <v>45813</v>
       </c>
       <c r="G86" t="s">
@@ -7986,7 +8012,7 @@
       <c r="E87" t="s">
         <v>910</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="2">
         <v>45813</v>
       </c>
       <c r="G87" t="s">
@@ -8007,7 +8033,7 @@
       <c r="L87" t="s">
         <v>1385</v>
       </c>
-      <c r="N87" s="1">
+      <c r="N87" s="2">
         <v>45797</v>
       </c>
       <c r="O87" t="s">
@@ -8033,7 +8059,7 @@
       <c r="E88" t="s">
         <v>911</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="2">
         <v>45813</v>
       </c>
       <c r="G88" t="s">
@@ -8048,7 +8074,7 @@
       <c r="L88" t="s">
         <v>1386</v>
       </c>
-      <c r="N88" s="1">
+      <c r="N88" s="2">
         <v>46195</v>
       </c>
       <c r="Q88" t="b">
@@ -8071,7 +8097,7 @@
       <c r="E89" t="s">
         <v>912</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89" s="2">
         <v>45813</v>
       </c>
       <c r="G89" t="s">
@@ -8086,7 +8112,7 @@
       <c r="L89" t="s">
         <v>1386</v>
       </c>
-      <c r="N89" s="1">
+      <c r="N89" s="2">
         <v>46195</v>
       </c>
       <c r="Q89" t="b">
@@ -8109,7 +8135,7 @@
       <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90" s="2">
         <v>45831</v>
       </c>
       <c r="G90" t="s">
@@ -8150,7 +8176,7 @@
       <c r="E91" t="s">
         <v>914</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="2">
         <v>45831</v>
       </c>
       <c r="G91" t="s">
@@ -8171,7 +8197,7 @@
       <c r="L91" t="s">
         <v>1388</v>
       </c>
-      <c r="N91" s="1">
+      <c r="N91" s="2">
         <v>46139</v>
       </c>
       <c r="Q91" t="b">
@@ -8191,7 +8217,7 @@
       <c r="D92" t="s">
         <v>748</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92" s="2">
         <v>45831</v>
       </c>
       <c r="G92" t="s">
@@ -8220,7 +8246,7 @@
       <c r="E93" t="s">
         <v>915</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93" s="2">
         <v>45831</v>
       </c>
       <c r="G93" t="s">
@@ -8241,7 +8267,7 @@
       <c r="L93" t="s">
         <v>1388</v>
       </c>
-      <c r="N93" s="1">
+      <c r="N93" s="2">
         <v>46139</v>
       </c>
       <c r="Q93" t="b">
@@ -8264,7 +8290,7 @@
       <c r="E94" t="s">
         <v>916</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94" s="2">
         <v>45831</v>
       </c>
       <c r="G94" t="s">
@@ -8302,7 +8328,7 @@
       <c r="E95" t="s">
         <v>917</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95" s="2">
         <v>45831</v>
       </c>
       <c r="G95" t="s">
@@ -8323,7 +8349,7 @@
       <c r="L95" t="s">
         <v>1388</v>
       </c>
-      <c r="N95" s="1">
+      <c r="N95" s="2">
         <v>46139</v>
       </c>
       <c r="Q95" t="b">
@@ -8346,7 +8372,7 @@
       <c r="E96" t="s">
         <v>918</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96" s="2">
         <v>45831</v>
       </c>
       <c r="G96" t="s">
@@ -8367,7 +8393,7 @@
       <c r="L96" t="s">
         <v>1369</v>
       </c>
-      <c r="N96" s="1">
+      <c r="N96" s="2">
         <v>45848</v>
       </c>
       <c r="O96" t="s">
@@ -8393,7 +8419,7 @@
       <c r="E97" t="s">
         <v>919</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="2">
         <v>45840</v>
       </c>
       <c r="G97" t="s">
@@ -8414,7 +8440,7 @@
       <c r="L97" t="s">
         <v>1389</v>
       </c>
-      <c r="N97" s="1">
+      <c r="N97" s="2">
         <v>45860</v>
       </c>
       <c r="P97" t="s">
@@ -8440,7 +8466,7 @@
       <c r="E98" t="s">
         <v>920</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="2">
         <v>45840</v>
       </c>
       <c r="G98" t="s">
@@ -8478,7 +8504,7 @@
       <c r="E99" t="s">
         <v>921</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99" s="2">
         <v>45840</v>
       </c>
       <c r="G99" t="s">
@@ -8507,7 +8533,7 @@
       <c r="E100" t="s">
         <v>922</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100" s="2">
         <v>45840</v>
       </c>
       <c r="G100" t="s">
@@ -8528,7 +8554,7 @@
       <c r="L100" t="s">
         <v>1388</v>
       </c>
-      <c r="N100" s="1">
+      <c r="N100" s="2">
         <v>46188</v>
       </c>
       <c r="Q100" t="b">
@@ -8551,7 +8577,7 @@
       <c r="E101" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101" s="2">
         <v>45840</v>
       </c>
       <c r="G101" t="s">
@@ -8580,7 +8606,7 @@
       <c r="E102" t="s">
         <v>924</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102" s="2">
         <v>45840</v>
       </c>
       <c r="G102" t="s">
@@ -8609,7 +8635,7 @@
       <c r="E103" t="s">
         <v>925</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103" s="2">
         <v>45840</v>
       </c>
       <c r="G103" t="s">
@@ -8638,7 +8664,7 @@
       <c r="E104" t="s">
         <v>926</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104" s="2">
         <v>45840</v>
       </c>
       <c r="G104" t="s">
@@ -8659,7 +8685,7 @@
       <c r="L104" t="s">
         <v>1388</v>
       </c>
-      <c r="N104" s="1">
+      <c r="N104" s="2">
         <v>46188</v>
       </c>
       <c r="Q104" t="b">
@@ -8682,7 +8708,7 @@
       <c r="E105" t="s">
         <v>927</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105" s="2">
         <v>45840</v>
       </c>
       <c r="G105" t="s">
@@ -8703,7 +8729,7 @@
       <c r="L105" t="s">
         <v>1388</v>
       </c>
-      <c r="N105" s="1">
+      <c r="N105" s="2">
         <v>46188</v>
       </c>
       <c r="Q105" t="b">
@@ -8726,7 +8752,7 @@
       <c r="E106" t="s">
         <v>928</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106" s="2">
         <v>45840</v>
       </c>
       <c r="G106" t="s">
@@ -8747,7 +8773,7 @@
       <c r="L106" t="s">
         <v>1390</v>
       </c>
-      <c r="N106" s="1">
+      <c r="N106" s="2">
         <v>45889</v>
       </c>
       <c r="Q106" t="b">
@@ -8770,7 +8796,7 @@
       <c r="E107" t="s">
         <v>929</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="2">
         <v>45840</v>
       </c>
       <c r="G107" t="s">
@@ -8791,7 +8817,7 @@
       <c r="L107" t="s">
         <v>1391</v>
       </c>
-      <c r="N107" s="1">
+      <c r="N107" s="2">
         <v>45876</v>
       </c>
       <c r="Q107" t="b">
@@ -8814,7 +8840,7 @@
       <c r="E108" t="s">
         <v>930</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108" s="2">
         <v>45840</v>
       </c>
       <c r="G108" t="s">
@@ -8852,7 +8878,7 @@
       <c r="E109" t="s">
         <v>931</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109" s="2">
         <v>45840</v>
       </c>
       <c r="G109" t="s">
@@ -8890,7 +8916,7 @@
       <c r="E110" t="s">
         <v>932</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="2">
         <v>45840</v>
       </c>
       <c r="G110" t="s">
@@ -8919,7 +8945,7 @@
       <c r="E111" t="s">
         <v>933</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="2">
         <v>45840</v>
       </c>
       <c r="G111" t="s">
@@ -8948,7 +8974,7 @@
       <c r="E112" t="s">
         <v>934</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112" s="2">
         <v>45840</v>
       </c>
       <c r="G112" t="s">
@@ -8977,7 +9003,7 @@
       <c r="E113" t="s">
         <v>935</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113" s="2">
         <v>45840</v>
       </c>
       <c r="G113" t="s">
@@ -9006,7 +9032,7 @@
       <c r="E114" t="s">
         <v>936</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114" s="2">
         <v>45840</v>
       </c>
       <c r="G114" t="s">
@@ -9035,7 +9061,7 @@
       <c r="E115" t="s">
         <v>937</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115" s="2">
         <v>45840</v>
       </c>
       <c r="G115" t="s">
@@ -9073,7 +9099,7 @@
       <c r="E116" t="s">
         <v>938</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116" s="2">
         <v>45840</v>
       </c>
       <c r="G116" t="s">
@@ -9111,7 +9137,7 @@
       <c r="E117" t="s">
         <v>939</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117" s="2">
         <v>45840</v>
       </c>
       <c r="G117" t="s">
@@ -9149,7 +9175,7 @@
       <c r="E118" t="s">
         <v>940</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118" s="2">
         <v>45840</v>
       </c>
       <c r="G118" t="s">
@@ -9187,7 +9213,7 @@
       <c r="E119" t="s">
         <v>941</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119" s="2">
         <v>45840</v>
       </c>
       <c r="G119" t="s">
@@ -9225,7 +9251,7 @@
       <c r="E120" t="s">
         <v>942</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120" s="2">
         <v>45840</v>
       </c>
       <c r="G120" t="s">
@@ -9263,7 +9289,7 @@
       <c r="E121" t="s">
         <v>943</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="2">
         <v>45849</v>
       </c>
       <c r="G121" t="s">
@@ -9284,7 +9310,7 @@
       <c r="L121" t="s">
         <v>1379</v>
       </c>
-      <c r="N121" s="1">
+      <c r="N121" s="2">
         <v>46100</v>
       </c>
       <c r="O121">
@@ -9310,7 +9336,7 @@
       <c r="E122" t="s">
         <v>944</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F122" s="2">
         <v>45849</v>
       </c>
       <c r="G122" t="s">
@@ -9348,7 +9374,7 @@
       <c r="E123" t="s">
         <v>945</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F123" s="2">
         <v>45849</v>
       </c>
       <c r="G123" t="s">
@@ -9377,7 +9403,7 @@
       <c r="E124" t="s">
         <v>946</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124" s="2">
         <v>45853</v>
       </c>
       <c r="G124" t="s">
@@ -9415,7 +9441,7 @@
       <c r="E125" t="s">
         <v>947</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125" s="2">
         <v>45855</v>
       </c>
       <c r="G125" t="s">
@@ -9453,7 +9479,7 @@
       <c r="E126" t="s">
         <v>948</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126" s="2">
         <v>45855</v>
       </c>
       <c r="G126" t="s">
@@ -9482,7 +9508,7 @@
       <c r="E127" t="s">
         <v>949</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127" s="2">
         <v>45856</v>
       </c>
       <c r="G127" t="s">
@@ -9511,7 +9537,7 @@
       <c r="E128" t="s">
         <v>950</v>
       </c>
-      <c r="F128" s="1">
+      <c r="F128" s="2">
         <v>45869</v>
       </c>
       <c r="G128" t="s">
@@ -9549,7 +9575,7 @@
       <c r="E129" t="s">
         <v>951</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F129" s="2">
         <v>45869</v>
       </c>
       <c r="G129" t="s">
@@ -9587,7 +9613,7 @@
       <c r="E130" t="s">
         <v>952</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F130" s="2">
         <v>45869</v>
       </c>
       <c r="G130" t="s">
@@ -9608,7 +9634,7 @@
       <c r="L130" t="s">
         <v>1392</v>
       </c>
-      <c r="N130" s="1">
+      <c r="N130" s="2">
         <v>45916</v>
       </c>
       <c r="O130">
@@ -9634,7 +9660,7 @@
       <c r="E131" t="s">
         <v>953</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F131" s="2">
         <v>45869</v>
       </c>
       <c r="G131" t="s">
@@ -9663,7 +9689,7 @@
       <c r="E132" t="s">
         <v>954</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F132" s="2">
         <v>45869</v>
       </c>
       <c r="G132" t="s">
@@ -9684,7 +9710,7 @@
       <c r="L132" t="s">
         <v>1393</v>
       </c>
-      <c r="N132" s="1">
+      <c r="N132" s="2">
         <v>46014</v>
       </c>
       <c r="O132">
@@ -9710,7 +9736,7 @@
       <c r="E133" t="s">
         <v>955</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F133" s="2">
         <v>45869</v>
       </c>
       <c r="G133" t="s">
@@ -9739,7 +9765,7 @@
       <c r="E134" t="s">
         <v>956</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F134" s="2">
         <v>45882</v>
       </c>
       <c r="G134" t="s">
@@ -9777,7 +9803,7 @@
       <c r="E135" t="s">
         <v>957</v>
       </c>
-      <c r="F135" s="1">
+      <c r="F135" s="2">
         <v>45882</v>
       </c>
       <c r="G135" t="s">
@@ -9806,7 +9832,7 @@
       <c r="E136" t="s">
         <v>958</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F136" s="2">
         <v>45891</v>
       </c>
       <c r="G136" t="s">
@@ -9835,7 +9861,7 @@
       <c r="E137" t="s">
         <v>959</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F137" s="2">
         <v>45891</v>
       </c>
       <c r="G137" t="s">
@@ -9864,7 +9890,7 @@
       <c r="E138" t="s">
         <v>960</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F138" s="2">
         <v>45891</v>
       </c>
       <c r="G138" t="s">
@@ -9902,7 +9928,7 @@
       <c r="E139" t="s">
         <v>961</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F139" s="2">
         <v>45891</v>
       </c>
       <c r="G139" t="s">
@@ -9931,7 +9957,7 @@
       <c r="E140" t="s">
         <v>962</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F140" s="2">
         <v>45891</v>
       </c>
       <c r="G140" t="s">
@@ -9960,7 +9986,7 @@
       <c r="E141" t="s">
         <v>963</v>
       </c>
-      <c r="F141" s="1">
+      <c r="F141" s="2">
         <v>45891</v>
       </c>
       <c r="G141" t="s">
@@ -9989,7 +10015,7 @@
       <c r="E142" t="s">
         <v>964</v>
       </c>
-      <c r="F142" s="1">
+      <c r="F142" s="2">
         <v>45891</v>
       </c>
       <c r="G142" t="s">
@@ -10018,7 +10044,7 @@
       <c r="E143" t="s">
         <v>965</v>
       </c>
-      <c r="F143" s="1">
+      <c r="F143" s="2">
         <v>45891</v>
       </c>
       <c r="G143" t="s">
@@ -10047,7 +10073,7 @@
       <c r="E144" t="s">
         <v>966</v>
       </c>
-      <c r="F144" s="1">
+      <c r="F144" s="2">
         <v>45891</v>
       </c>
       <c r="G144" t="s">
@@ -10076,7 +10102,7 @@
       <c r="E145" t="s">
         <v>967</v>
       </c>
-      <c r="F145" s="1">
+      <c r="F145" s="2">
         <v>45891</v>
       </c>
       <c r="G145" t="s">
@@ -10105,7 +10131,7 @@
       <c r="E146" t="s">
         <v>968</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F146" s="2">
         <v>45891</v>
       </c>
       <c r="G146" t="s">
@@ -10134,7 +10160,7 @@
       <c r="E147" t="s">
         <v>969</v>
       </c>
-      <c r="F147" s="1">
+      <c r="F147" s="2">
         <v>45891</v>
       </c>
       <c r="G147" t="s">
@@ -10163,7 +10189,7 @@
       <c r="E148" t="s">
         <v>970</v>
       </c>
-      <c r="F148" s="1">
+      <c r="F148" s="2">
         <v>45891</v>
       </c>
       <c r="G148" t="s">
@@ -10184,7 +10210,7 @@
       <c r="L148" t="s">
         <v>1383</v>
       </c>
-      <c r="N148" s="1">
+      <c r="N148" s="2">
         <v>46232</v>
       </c>
       <c r="Q148" t="b">
@@ -10207,7 +10233,7 @@
       <c r="E149" t="s">
         <v>971</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F149" s="2">
         <v>45891</v>
       </c>
       <c r="G149" t="s">
@@ -10228,7 +10254,7 @@
       <c r="L149" t="s">
         <v>1394</v>
       </c>
-      <c r="N149" s="1">
+      <c r="N149" s="2">
         <v>46265</v>
       </c>
       <c r="P149" t="s">
@@ -10254,7 +10280,7 @@
       <c r="E150" t="s">
         <v>972</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F150" s="2">
         <v>45891</v>
       </c>
       <c r="G150" t="s">
@@ -10275,7 +10301,7 @@
       <c r="L150" t="s">
         <v>1381</v>
       </c>
-      <c r="N150" s="1">
+      <c r="N150" s="2">
         <v>46092</v>
       </c>
       <c r="P150" t="s">
@@ -10301,7 +10327,7 @@
       <c r="E151" t="s">
         <v>973</v>
       </c>
-      <c r="F151" s="1">
+      <c r="F151" s="2">
         <v>45891</v>
       </c>
       <c r="G151" t="s">
@@ -10330,7 +10356,7 @@
       <c r="E152" t="s">
         <v>963</v>
       </c>
-      <c r="F152" s="1">
+      <c r="F152" s="2">
         <v>45891</v>
       </c>
       <c r="G152" t="s">
@@ -10351,7 +10377,7 @@
       <c r="L152" t="s">
         <v>1382</v>
       </c>
-      <c r="N152" s="1">
+      <c r="N152" s="2">
         <v>46119</v>
       </c>
       <c r="Q152" t="b">
@@ -10374,7 +10400,7 @@
       <c r="E153" t="s">
         <v>974</v>
       </c>
-      <c r="F153" s="1">
+      <c r="F153" s="2">
         <v>45891</v>
       </c>
       <c r="G153" t="s">
@@ -10392,7 +10418,7 @@
       <c r="L153" t="s">
         <v>1383</v>
       </c>
-      <c r="N153" s="1">
+      <c r="N153" s="2">
         <v>46232</v>
       </c>
       <c r="Q153" t="b">
@@ -10415,7 +10441,7 @@
       <c r="E154" t="s">
         <v>975</v>
       </c>
-      <c r="F154" s="1">
+      <c r="F154" s="2">
         <v>45891</v>
       </c>
       <c r="G154" t="s">
@@ -10444,7 +10470,7 @@
       <c r="E155" t="s">
         <v>976</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F155" s="2">
         <v>45891</v>
       </c>
       <c r="G155" t="s">
@@ -10479,7 +10505,7 @@
       <c r="E156" t="s">
         <v>977</v>
       </c>
-      <c r="F156" s="1">
+      <c r="F156" s="2">
         <v>45891</v>
       </c>
       <c r="G156" t="s">
@@ -10517,7 +10543,7 @@
       <c r="E157" t="s">
         <v>978</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="2">
         <v>45891</v>
       </c>
       <c r="G157" t="s">
@@ -10538,7 +10564,7 @@
       <c r="L157" t="s">
         <v>1395</v>
       </c>
-      <c r="N157" s="1">
+      <c r="N157" s="2">
         <v>46262</v>
       </c>
       <c r="Q157" t="b">
@@ -10561,7 +10587,7 @@
       <c r="E158" t="s">
         <v>979</v>
       </c>
-      <c r="F158" s="1">
+      <c r="F158" s="2">
         <v>45894</v>
       </c>
       <c r="G158" t="s">
@@ -10582,7 +10608,7 @@
       <c r="L158" t="s">
         <v>1396</v>
       </c>
-      <c r="N158" s="1">
+      <c r="N158" s="2">
         <v>45946</v>
       </c>
       <c r="Q158" t="b">
@@ -10605,7 +10631,7 @@
       <c r="E159" t="s">
         <v>980</v>
       </c>
-      <c r="F159" s="1">
+      <c r="F159" s="2">
         <v>45894</v>
       </c>
       <c r="G159" t="s">
@@ -10643,7 +10669,7 @@
       <c r="E160" t="s">
         <v>981</v>
       </c>
-      <c r="F160" s="1">
+      <c r="F160" s="2">
         <v>45898</v>
       </c>
       <c r="G160" t="s">
@@ -10681,7 +10707,7 @@
       <c r="E161" t="s">
         <v>982</v>
       </c>
-      <c r="F161" s="1">
+      <c r="F161" s="2">
         <v>45898</v>
       </c>
       <c r="G161" t="s">
@@ -10702,7 +10728,7 @@
       <c r="L161" t="s">
         <v>1397</v>
       </c>
-      <c r="N161" s="1">
+      <c r="N161" s="2">
         <v>45953</v>
       </c>
       <c r="O161" t="s">
@@ -10728,7 +10754,7 @@
       <c r="E162" t="s">
         <v>983</v>
       </c>
-      <c r="F162" s="1">
+      <c r="F162" s="2">
         <v>45898</v>
       </c>
       <c r="G162" t="s">
@@ -10749,7 +10775,7 @@
       <c r="L162" t="s">
         <v>1398</v>
       </c>
-      <c r="N162" s="1">
+      <c r="N162" s="2">
         <v>45940</v>
       </c>
       <c r="P162" t="s">
@@ -10775,7 +10801,7 @@
       <c r="E163" t="s">
         <v>984</v>
       </c>
-      <c r="F163" s="1">
+      <c r="F163" s="2">
         <v>45898</v>
       </c>
       <c r="G163" t="s">
@@ -10796,7 +10822,7 @@
       <c r="L163" t="s">
         <v>1398</v>
       </c>
-      <c r="N163" s="1">
+      <c r="N163" s="2">
         <v>45940</v>
       </c>
       <c r="P163" t="s">
@@ -10822,7 +10848,7 @@
       <c r="E164" t="s">
         <v>985</v>
       </c>
-      <c r="F164" s="1">
+      <c r="F164" s="2">
         <v>45910</v>
       </c>
       <c r="G164" t="s">
@@ -10857,7 +10883,7 @@
       <c r="E165" t="s">
         <v>986</v>
       </c>
-      <c r="F165" s="1">
+      <c r="F165" s="2">
         <v>45917</v>
       </c>
       <c r="G165" t="s">
@@ -10875,7 +10901,7 @@
       <c r="L165" t="s">
         <v>1399</v>
       </c>
-      <c r="N165" s="1">
+      <c r="N165" s="2">
         <v>46204</v>
       </c>
       <c r="P165" t="s">
@@ -10901,7 +10927,7 @@
       <c r="E166" t="s">
         <v>987</v>
       </c>
-      <c r="F166" s="1">
+      <c r="F166" s="2">
         <v>45917</v>
       </c>
       <c r="G166" t="s">
@@ -10930,7 +10956,7 @@
       <c r="E167" t="s">
         <v>988</v>
       </c>
-      <c r="F167" s="1">
+      <c r="F167" s="2">
         <v>45917</v>
       </c>
       <c r="G167" t="s">
@@ -10959,7 +10985,7 @@
       <c r="E168" t="s">
         <v>989</v>
       </c>
-      <c r="F168" s="1">
+      <c r="F168" s="2">
         <v>45917</v>
       </c>
       <c r="G168" t="s">
@@ -11000,7 +11026,7 @@
       <c r="E169" t="s">
         <v>990</v>
       </c>
-      <c r="F169" s="1">
+      <c r="F169" s="2">
         <v>45917</v>
       </c>
       <c r="G169" t="s">
@@ -11018,7 +11044,7 @@
       <c r="L169" t="s">
         <v>1401</v>
       </c>
-      <c r="N169" s="1">
+      <c r="N169" s="2">
         <v>45973</v>
       </c>
       <c r="Q169" t="b">
@@ -11041,7 +11067,7 @@
       <c r="E170" t="s">
         <v>991</v>
       </c>
-      <c r="F170" s="1">
+      <c r="F170" s="2">
         <v>45917</v>
       </c>
       <c r="G170" t="s">
@@ -11076,7 +11102,7 @@
       <c r="E171" t="s">
         <v>992</v>
       </c>
-      <c r="F171" s="1">
+      <c r="F171" s="2">
         <v>45917</v>
       </c>
       <c r="G171" t="s">
@@ -11114,7 +11140,7 @@
       <c r="E172" t="s">
         <v>993</v>
       </c>
-      <c r="F172" s="1">
+      <c r="F172" s="2">
         <v>45917</v>
       </c>
       <c r="G172" t="s">
@@ -11143,7 +11169,7 @@
       <c r="E173" t="s">
         <v>994</v>
       </c>
-      <c r="F173" s="1">
+      <c r="F173" s="2">
         <v>45917</v>
       </c>
       <c r="G173" t="s">
@@ -11172,7 +11198,7 @@
       <c r="E174" t="s">
         <v>995</v>
       </c>
-      <c r="F174" s="1">
+      <c r="F174" s="2">
         <v>45917</v>
       </c>
       <c r="G174" t="s">
@@ -11187,7 +11213,7 @@
       <c r="L174" t="s">
         <v>1386</v>
       </c>
-      <c r="N174" s="1">
+      <c r="N174" s="2">
         <v>46195</v>
       </c>
       <c r="Q174" t="b">
@@ -11210,7 +11236,7 @@
       <c r="E175" t="s">
         <v>996</v>
       </c>
-      <c r="F175" s="1">
+      <c r="F175" s="2">
         <v>45917</v>
       </c>
       <c r="G175" t="s">
@@ -11231,7 +11257,7 @@
       <c r="L175" t="s">
         <v>1402</v>
       </c>
-      <c r="N175" s="1">
+      <c r="N175" s="2">
         <v>46122</v>
       </c>
       <c r="P175" t="s">
@@ -11257,7 +11283,7 @@
       <c r="E176" t="s">
         <v>900</v>
       </c>
-      <c r="F176" s="1">
+      <c r="F176" s="2">
         <v>45917</v>
       </c>
       <c r="G176" t="s">
@@ -11295,7 +11321,7 @@
       <c r="E177" t="s">
         <v>997</v>
       </c>
-      <c r="F177" s="1">
+      <c r="F177" s="2">
         <v>45917</v>
       </c>
       <c r="G177" t="s">
@@ -11316,7 +11342,7 @@
       <c r="L177" t="s">
         <v>1403</v>
       </c>
-      <c r="N177" s="1">
+      <c r="N177" s="2">
         <v>45961</v>
       </c>
       <c r="P177" t="s">
@@ -11342,7 +11368,7 @@
       <c r="E178" t="s">
         <v>998</v>
       </c>
-      <c r="F178" s="1">
+      <c r="F178" s="2">
         <v>45937</v>
       </c>
       <c r="G178" t="s">
@@ -11380,7 +11406,7 @@
       <c r="E179" t="s">
         <v>999</v>
       </c>
-      <c r="F179" s="1">
+      <c r="F179" s="2">
         <v>45937</v>
       </c>
       <c r="G179" t="s">
@@ -11409,7 +11435,7 @@
       <c r="E180" t="s">
         <v>1000</v>
       </c>
-      <c r="F180" s="1">
+      <c r="F180" s="2">
         <v>45937</v>
       </c>
       <c r="G180" t="s">
@@ -11447,7 +11473,7 @@
       <c r="E181" t="s">
         <v>1001</v>
       </c>
-      <c r="F181" s="1">
+      <c r="F181" s="2">
         <v>45937</v>
       </c>
       <c r="G181" t="s">
@@ -11476,7 +11502,7 @@
       <c r="E182" t="s">
         <v>1002</v>
       </c>
-      <c r="F182" s="1">
+      <c r="F182" s="2">
         <v>45937</v>
       </c>
       <c r="G182" t="s">
@@ -11505,7 +11531,7 @@
       <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="F183" s="1">
+      <c r="F183" s="2">
         <v>45937</v>
       </c>
       <c r="G183" t="s">
@@ -11543,7 +11569,7 @@
       <c r="D184" t="s">
         <v>774</v>
       </c>
-      <c r="F184" s="1">
+      <c r="F184" s="2">
         <v>45939</v>
       </c>
       <c r="G184" t="s">
@@ -11578,7 +11604,7 @@
       <c r="E185" t="s">
         <v>1004</v>
       </c>
-      <c r="F185" s="1">
+      <c r="F185" s="2">
         <v>45939</v>
       </c>
       <c r="G185" t="s">
@@ -11616,7 +11642,7 @@
       <c r="E186" t="s">
         <v>1005</v>
       </c>
-      <c r="F186" s="1">
+      <c r="F186" s="2">
         <v>45939</v>
       </c>
       <c r="G186" t="s">
@@ -11654,7 +11680,7 @@
       <c r="E187" t="s">
         <v>1006</v>
       </c>
-      <c r="F187" s="1">
+      <c r="F187" s="2">
         <v>45939</v>
       </c>
       <c r="G187" t="s">
@@ -11675,7 +11701,7 @@
       <c r="L187" t="s">
         <v>1404</v>
       </c>
-      <c r="N187" s="1">
+      <c r="N187" s="2">
         <v>46014</v>
       </c>
       <c r="O187">
@@ -11701,7 +11727,7 @@
       <c r="E188" t="s">
         <v>1007</v>
       </c>
-      <c r="F188" s="1">
+      <c r="F188" s="2">
         <v>45946</v>
       </c>
       <c r="G188" t="s">
@@ -11722,7 +11748,7 @@
       <c r="L188" t="s">
         <v>1405</v>
       </c>
-      <c r="N188" s="1">
+      <c r="N188" s="2">
         <v>45986</v>
       </c>
       <c r="P188" t="s">
@@ -11748,7 +11774,7 @@
       <c r="E189" t="s">
         <v>1008</v>
       </c>
-      <c r="F189" s="1">
+      <c r="F189" s="2">
         <v>45965</v>
       </c>
       <c r="G189" t="s">
@@ -11769,7 +11795,7 @@
       <c r="L189" t="s">
         <v>1406</v>
       </c>
-      <c r="N189" s="1">
+      <c r="N189" s="2">
         <v>46120</v>
       </c>
       <c r="Q189" t="b">
@@ -11792,7 +11818,7 @@
       <c r="E190" t="s">
         <v>1009</v>
       </c>
-      <c r="F190" s="1">
+      <c r="F190" s="2">
         <v>45965</v>
       </c>
       <c r="G190" t="s">
@@ -11813,7 +11839,7 @@
       <c r="L190" t="s">
         <v>1407</v>
       </c>
-      <c r="N190" s="1">
+      <c r="N190" s="2">
         <v>46072</v>
       </c>
       <c r="Q190" t="b">
@@ -11836,7 +11862,7 @@
       <c r="E191" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="1">
+      <c r="F191" s="2">
         <v>45967</v>
       </c>
       <c r="G191" t="s">
@@ -11857,7 +11883,7 @@
       <c r="L191" t="s">
         <v>1408</v>
       </c>
-      <c r="N191" s="1">
+      <c r="N191" s="2">
         <v>45972</v>
       </c>
       <c r="Q191" t="b">
@@ -11880,7 +11906,7 @@
       <c r="E192" t="s">
         <v>1011</v>
       </c>
-      <c r="F192" s="1">
+      <c r="F192" s="2">
         <v>45968</v>
       </c>
       <c r="G192" t="s">
@@ -11918,7 +11944,7 @@
       <c r="E193" t="s">
         <v>1012</v>
       </c>
-      <c r="F193" s="1">
+      <c r="F193" s="2">
         <v>45968</v>
       </c>
       <c r="G193" t="s">
@@ -11956,7 +11982,7 @@
       <c r="E194" t="s">
         <v>1013</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F194" s="2">
         <v>45968</v>
       </c>
       <c r="G194" t="s">
@@ -11985,7 +12011,7 @@
       <c r="E195" t="s">
         <v>1014</v>
       </c>
-      <c r="F195" s="1">
+      <c r="F195" s="2">
         <v>45971</v>
       </c>
       <c r="G195" t="s">
@@ -12006,7 +12032,7 @@
       <c r="L195" t="s">
         <v>1409</v>
       </c>
-      <c r="N195" s="1">
+      <c r="N195" s="2">
         <v>46157</v>
       </c>
       <c r="Q195" t="b">
@@ -12029,7 +12055,7 @@
       <c r="E196" t="s">
         <v>1015</v>
       </c>
-      <c r="F196" s="1">
+      <c r="F196" s="2">
         <v>45978</v>
       </c>
       <c r="G196" t="s">
@@ -12058,7 +12084,7 @@
       <c r="E197" t="s">
         <v>1016</v>
       </c>
-      <c r="F197" s="1">
+      <c r="F197" s="2">
         <v>45978</v>
       </c>
       <c r="G197" t="s">
@@ -12087,7 +12113,7 @@
       <c r="E198" t="s">
         <v>1017</v>
       </c>
-      <c r="F198" s="1">
+      <c r="F198" s="2">
         <v>45978</v>
       </c>
       <c r="G198" t="s">
@@ -12116,7 +12142,7 @@
       <c r="E199" t="s">
         <v>1018</v>
       </c>
-      <c r="F199" s="1">
+      <c r="F199" s="2">
         <v>45979</v>
       </c>
       <c r="G199" t="s">
@@ -12137,7 +12163,7 @@
       <c r="L199" t="s">
         <v>1410</v>
       </c>
-      <c r="N199" s="1">
+      <c r="N199" s="2">
         <v>46049</v>
       </c>
       <c r="Q199" t="b">
@@ -12160,7 +12186,7 @@
       <c r="E200" t="s">
         <v>1019</v>
       </c>
-      <c r="F200" s="1">
+      <c r="F200" s="2">
         <v>45986</v>
       </c>
       <c r="G200" t="s">
@@ -12181,7 +12207,7 @@
       <c r="L200" t="s">
         <v>1409</v>
       </c>
-      <c r="N200" s="1">
+      <c r="N200" s="2">
         <v>46156</v>
       </c>
       <c r="Q200" t="b">
@@ -12204,7 +12230,7 @@
       <c r="E201" t="s">
         <v>1020</v>
       </c>
-      <c r="F201" s="1">
+      <c r="F201" s="2">
         <v>45986</v>
       </c>
       <c r="G201" t="s">
@@ -12242,7 +12268,7 @@
       <c r="E202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" s="1">
+      <c r="F202" s="2">
         <v>45986</v>
       </c>
       <c r="G202" t="s">
@@ -12280,7 +12306,7 @@
       <c r="E203" t="s">
         <v>1022</v>
       </c>
-      <c r="F203" s="1">
+      <c r="F203" s="2">
         <v>45986</v>
       </c>
       <c r="G203" t="s">
@@ -12298,7 +12324,7 @@
       <c r="L203" t="s">
         <v>1411</v>
       </c>
-      <c r="N203" s="1">
+      <c r="N203" s="2">
         <v>46232</v>
       </c>
       <c r="Q203" t="b">
@@ -12321,7 +12347,7 @@
       <c r="E204" t="s">
         <v>1023</v>
       </c>
-      <c r="F204" s="1">
+      <c r="F204" s="2">
         <v>45986</v>
       </c>
       <c r="G204" t="s">
@@ -12359,7 +12385,7 @@
       <c r="E205" t="s">
         <v>1024</v>
       </c>
-      <c r="F205" s="1">
+      <c r="F205" s="2">
         <v>45986</v>
       </c>
       <c r="G205" t="s">
@@ -12397,7 +12423,7 @@
       <c r="E206" t="s">
         <v>1025</v>
       </c>
-      <c r="F206" s="1">
+      <c r="F206" s="2">
         <v>45986</v>
       </c>
       <c r="G206" t="s">
@@ -12426,7 +12452,7 @@
       <c r="E207" t="s">
         <v>1026</v>
       </c>
-      <c r="F207" s="1">
+      <c r="F207" s="2">
         <v>45986</v>
       </c>
       <c r="G207" t="s">
@@ -12447,7 +12473,7 @@
       <c r="L207" t="s">
         <v>1412</v>
       </c>
-      <c r="N207" s="1">
+      <c r="N207" s="2">
         <v>46153</v>
       </c>
       <c r="Q207" t="b">
@@ -12470,7 +12496,7 @@
       <c r="E208" t="s">
         <v>1027</v>
       </c>
-      <c r="F208" s="1">
+      <c r="F208" s="2">
         <v>45986</v>
       </c>
       <c r="G208" t="s">
@@ -12491,7 +12517,7 @@
       <c r="L208" t="s">
         <v>1413</v>
       </c>
-      <c r="N208" s="1">
+      <c r="N208" s="2">
         <v>46031</v>
       </c>
       <c r="Q208" t="b">
@@ -12514,7 +12540,7 @@
       <c r="E209" t="s">
         <v>1028</v>
       </c>
-      <c r="F209" s="1">
+      <c r="F209" s="2">
         <v>46000</v>
       </c>
       <c r="G209" t="s">
@@ -12535,7 +12561,7 @@
       <c r="L209" t="s">
         <v>1414</v>
       </c>
-      <c r="N209" s="1">
+      <c r="N209" s="2">
         <v>46191</v>
       </c>
       <c r="Q209" t="b">
@@ -12558,7 +12584,7 @@
       <c r="E210" t="s">
         <v>1029</v>
       </c>
-      <c r="F210" s="1">
+      <c r="F210" s="2">
         <v>46000</v>
       </c>
       <c r="G210" t="s">
@@ -12596,7 +12622,7 @@
       <c r="E211" t="s">
         <v>1030</v>
       </c>
-      <c r="F211" s="1">
+      <c r="F211" s="2">
         <v>46000</v>
       </c>
       <c r="G211" t="s">
@@ -12625,7 +12651,7 @@
       <c r="E212" t="s">
         <v>1031</v>
       </c>
-      <c r="F212" s="1">
+      <c r="F212" s="2">
         <v>46000</v>
       </c>
       <c r="G212" t="s">
@@ -12654,7 +12680,7 @@
       <c r="E213" t="s">
         <v>1032</v>
       </c>
-      <c r="F213" s="1">
+      <c r="F213" s="2">
         <v>46007</v>
       </c>
       <c r="G213" t="s">
@@ -12692,7 +12718,7 @@
       <c r="E214" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="1">
+      <c r="F214" s="2">
         <v>46007</v>
       </c>
       <c r="G214" t="s">
@@ -12713,7 +12739,7 @@
       <c r="L214" t="s">
         <v>1415</v>
       </c>
-      <c r="N214" s="1">
+      <c r="N214" s="2">
         <v>46021</v>
       </c>
       <c r="O214">
@@ -12739,7 +12765,7 @@
       <c r="E215" t="s">
         <v>1034</v>
       </c>
-      <c r="F215" s="1">
+      <c r="F215" s="2">
         <v>46007</v>
       </c>
       <c r="G215" t="s">
@@ -12777,7 +12803,7 @@
       <c r="E216" t="s">
         <v>1035</v>
       </c>
-      <c r="F216" s="1">
+      <c r="F216" s="2">
         <v>46010</v>
       </c>
       <c r="G216" t="s">
@@ -12806,7 +12832,7 @@
       <c r="E217" t="s">
         <v>1036</v>
       </c>
-      <c r="F217" s="1">
+      <c r="F217" s="2">
         <v>46010</v>
       </c>
       <c r="G217" t="s">
@@ -12827,7 +12853,7 @@
       <c r="L217" t="s">
         <v>1416</v>
       </c>
-      <c r="N217" s="1">
+      <c r="N217" s="2">
         <v>46052</v>
       </c>
       <c r="Q217" t="b">
@@ -12850,7 +12876,7 @@
       <c r="E218" t="s">
         <v>1037</v>
       </c>
-      <c r="F218" s="1">
+      <c r="F218" s="2">
         <v>46010</v>
       </c>
       <c r="G218" t="s">
@@ -12868,7 +12894,7 @@
       <c r="K218" t="s">
         <v>1359</v>
       </c>
-      <c r="N218" s="1">
+      <c r="N218" s="2">
         <v>46176</v>
       </c>
       <c r="P218" t="s">
@@ -12894,7 +12920,7 @@
       <c r="E219" t="s">
         <v>1038</v>
       </c>
-      <c r="F219" s="1">
+      <c r="F219" s="2">
         <v>46010</v>
       </c>
       <c r="G219" t="s">
@@ -12912,7 +12938,7 @@
       <c r="L219" t="s">
         <v>1417</v>
       </c>
-      <c r="N219" s="1">
+      <c r="N219" s="2">
         <v>46176</v>
       </c>
       <c r="P219" t="s">
@@ -12938,7 +12964,7 @@
       <c r="E220" t="s">
         <v>1039</v>
       </c>
-      <c r="F220" s="1">
+      <c r="F220" s="2">
         <v>46010</v>
       </c>
       <c r="G220" t="s">
@@ -12959,7 +12985,7 @@
       <c r="L220" t="s">
         <v>1418</v>
       </c>
-      <c r="N220" s="1">
+      <c r="N220" s="2">
         <v>46164</v>
       </c>
       <c r="Q220" t="b">
@@ -12982,7 +13008,7 @@
       <c r="E221" t="s">
         <v>1040</v>
       </c>
-      <c r="F221" s="1">
+      <c r="F221" s="2">
         <v>46028</v>
       </c>
       <c r="G221" t="s">
@@ -12997,7 +13023,7 @@
       <c r="L221" t="s">
         <v>1419</v>
       </c>
-      <c r="N221" s="1">
+      <c r="N221" s="2">
         <v>46184</v>
       </c>
       <c r="Q221" t="b">
@@ -13020,7 +13046,7 @@
       <c r="E222" t="s">
         <v>1041</v>
       </c>
-      <c r="F222" s="1">
+      <c r="F222" s="2">
         <v>46028</v>
       </c>
       <c r="G222" t="s">
@@ -13035,7 +13061,7 @@
       <c r="L222" t="s">
         <v>1383</v>
       </c>
-      <c r="N222" s="1">
+      <c r="N222" s="2">
         <v>46232</v>
       </c>
       <c r="Q222" t="b">
@@ -13058,7 +13084,7 @@
       <c r="E223" t="s">
         <v>1042</v>
       </c>
-      <c r="F223" s="1">
+      <c r="F223" s="2">
         <v>46028</v>
       </c>
       <c r="G223" t="s">
@@ -13073,7 +13099,7 @@
       <c r="L223" t="s">
         <v>1383</v>
       </c>
-      <c r="N223" s="1">
+      <c r="N223" s="2">
         <v>46232</v>
       </c>
       <c r="Q223" t="b">
@@ -13096,7 +13122,7 @@
       <c r="E224" t="s">
         <v>1043</v>
       </c>
-      <c r="F224" s="1">
+      <c r="F224" s="2">
         <v>46028</v>
       </c>
       <c r="G224" t="s">
@@ -13114,7 +13140,7 @@
       <c r="L224" t="s">
         <v>1383</v>
       </c>
-      <c r="N224" s="1">
+      <c r="N224" s="2">
         <v>46232</v>
       </c>
       <c r="Q224" t="b">
@@ -13137,7 +13163,7 @@
       <c r="E225" t="s">
         <v>1044</v>
       </c>
-      <c r="F225" s="1">
+      <c r="F225" s="2">
         <v>46028</v>
       </c>
       <c r="G225" t="s">
@@ -13152,7 +13178,7 @@
       <c r="L225" t="s">
         <v>1383</v>
       </c>
-      <c r="N225" s="1">
+      <c r="N225" s="2">
         <v>46232</v>
       </c>
       <c r="Q225" t="b">
@@ -13175,7 +13201,7 @@
       <c r="E226" t="s">
         <v>1045</v>
       </c>
-      <c r="F226" s="1">
+      <c r="F226" s="2">
         <v>46028</v>
       </c>
       <c r="G226" t="s">
@@ -13190,7 +13216,7 @@
       <c r="L226" t="s">
         <v>1383</v>
       </c>
-      <c r="N226" s="1">
+      <c r="N226" s="2">
         <v>46232</v>
       </c>
       <c r="Q226" t="b">
@@ -13213,7 +13239,7 @@
       <c r="E227" t="s">
         <v>1046</v>
       </c>
-      <c r="F227" s="1">
+      <c r="F227" s="2">
         <v>46028</v>
       </c>
       <c r="G227" t="s">
@@ -13228,7 +13254,7 @@
       <c r="L227" t="s">
         <v>1383</v>
       </c>
-      <c r="N227" s="1">
+      <c r="N227" s="2">
         <v>46232</v>
       </c>
       <c r="Q227" t="b">
@@ -13251,7 +13277,7 @@
       <c r="E228" t="s">
         <v>1047</v>
       </c>
-      <c r="F228" s="1">
+      <c r="F228" s="2">
         <v>46028</v>
       </c>
       <c r="G228" t="s">
@@ -13269,7 +13295,7 @@
       <c r="L228" t="s">
         <v>1383</v>
       </c>
-      <c r="N228" s="1">
+      <c r="N228" s="2">
         <v>46232</v>
       </c>
       <c r="Q228" t="b">
@@ -13292,7 +13318,7 @@
       <c r="E229" t="s">
         <v>1048</v>
       </c>
-      <c r="F229" s="1">
+      <c r="F229" s="2">
         <v>46028</v>
       </c>
       <c r="G229" t="s">
@@ -13307,7 +13333,7 @@
       <c r="L229" t="s">
         <v>1420</v>
       </c>
-      <c r="N229" s="1">
+      <c r="N229" s="2">
         <v>46191</v>
       </c>
       <c r="Q229" t="b">
@@ -13330,7 +13356,7 @@
       <c r="E230" t="s">
         <v>1049</v>
       </c>
-      <c r="F230" s="1">
+      <c r="F230" s="2">
         <v>46028</v>
       </c>
       <c r="G230" t="s">
@@ -13351,7 +13377,7 @@
       <c r="L230" t="s">
         <v>1395</v>
       </c>
-      <c r="N230" s="1">
+      <c r="N230" s="2">
         <v>46225</v>
       </c>
       <c r="Q230" t="b">
@@ -13374,7 +13400,7 @@
       <c r="E231" t="s">
         <v>1050</v>
       </c>
-      <c r="F231" s="1">
+      <c r="F231" s="2">
         <v>46028</v>
       </c>
       <c r="G231" t="s">
@@ -13395,7 +13421,7 @@
       <c r="L231" t="s">
         <v>1421</v>
       </c>
-      <c r="N231" s="1">
+      <c r="N231" s="2">
         <v>46063</v>
       </c>
       <c r="Q231" t="b">
@@ -13418,7 +13444,7 @@
       <c r="E232" t="s">
         <v>1051</v>
       </c>
-      <c r="F232" s="1">
+      <c r="F232" s="2">
         <v>46028</v>
       </c>
       <c r="G232" t="s">
@@ -13447,7 +13473,7 @@
       <c r="E233" t="s">
         <v>1052</v>
       </c>
-      <c r="F233" s="1">
+      <c r="F233" s="2">
         <v>46028</v>
       </c>
       <c r="G233" t="s">
@@ -13476,7 +13502,7 @@
       <c r="E234" t="s">
         <v>1053</v>
       </c>
-      <c r="F234" s="1">
+      <c r="F234" s="2">
         <v>46028</v>
       </c>
       <c r="G234" t="s">
@@ -13497,7 +13523,7 @@
       <c r="L234" t="s">
         <v>1421</v>
       </c>
-      <c r="N234" s="1">
+      <c r="N234" s="2">
         <v>46063</v>
       </c>
       <c r="P234" t="s">
@@ -13523,7 +13549,7 @@
       <c r="E235" t="s">
         <v>1054</v>
       </c>
-      <c r="F235" s="1">
+      <c r="F235" s="2">
         <v>46028</v>
       </c>
       <c r="G235" t="s">
@@ -13544,7 +13570,7 @@
       <c r="L235" t="s">
         <v>1421</v>
       </c>
-      <c r="N235" s="1">
+      <c r="N235" s="2">
         <v>46063</v>
       </c>
       <c r="P235" t="s">
@@ -13570,7 +13596,7 @@
       <c r="E236" t="s">
         <v>1055</v>
       </c>
-      <c r="F236" s="1">
+      <c r="F236" s="2">
         <v>46028</v>
       </c>
       <c r="G236" t="s">
@@ -13591,7 +13617,7 @@
       <c r="L236" t="s">
         <v>1422</v>
       </c>
-      <c r="N236" s="1">
+      <c r="N236" s="2">
         <v>46114</v>
       </c>
       <c r="Q236" t="b">
@@ -13614,7 +13640,7 @@
       <c r="E237" t="s">
         <v>1056</v>
       </c>
-      <c r="F237" s="1">
+      <c r="F237" s="2">
         <v>46028</v>
       </c>
       <c r="G237" t="s">
@@ -13632,7 +13658,7 @@
       <c r="L237" t="s">
         <v>1423</v>
       </c>
-      <c r="N237" s="1">
+      <c r="N237" s="2">
         <v>46210</v>
       </c>
       <c r="P237" t="s">
@@ -13658,7 +13684,7 @@
       <c r="E238" t="s">
         <v>1057</v>
       </c>
-      <c r="F238" s="1">
+      <c r="F238" s="2">
         <v>46028</v>
       </c>
       <c r="G238" t="s">
@@ -13687,7 +13713,7 @@
       <c r="E239" t="s">
         <v>1058</v>
       </c>
-      <c r="F239" s="1">
+      <c r="F239" s="2">
         <v>46036</v>
       </c>
       <c r="G239" t="s">
@@ -13705,7 +13731,7 @@
       <c r="L239" t="s">
         <v>1424</v>
       </c>
-      <c r="N239" s="1">
+      <c r="N239" s="2">
         <v>46052</v>
       </c>
       <c r="Q239" t="b">
@@ -13728,7 +13754,7 @@
       <c r="E240" t="s">
         <v>1059</v>
       </c>
-      <c r="F240" s="1">
+      <c r="F240" s="2">
         <v>46036</v>
       </c>
       <c r="G240" t="s">
@@ -13757,7 +13783,7 @@
       <c r="E241" t="s">
         <v>1060</v>
       </c>
-      <c r="F241" s="1">
+      <c r="F241" s="2">
         <v>46036</v>
       </c>
       <c r="G241" t="s">
@@ -13786,7 +13812,7 @@
       <c r="E242" t="s">
         <v>1061</v>
       </c>
-      <c r="F242" s="1">
+      <c r="F242" s="2">
         <v>46036</v>
       </c>
       <c r="G242" t="s">
@@ -13824,7 +13850,7 @@
       <c r="E243" t="s">
         <v>1062</v>
       </c>
-      <c r="F243" s="1">
+      <c r="F243" s="2">
         <v>46048</v>
       </c>
       <c r="G243" t="s">
@@ -13853,7 +13879,7 @@
       <c r="E244" t="s">
         <v>1063</v>
       </c>
-      <c r="F244" s="1">
+      <c r="F244" s="2">
         <v>46048</v>
       </c>
       <c r="G244" t="s">
@@ -13871,7 +13897,7 @@
       <c r="K244" t="s">
         <v>1359</v>
       </c>
-      <c r="N244" s="1">
+      <c r="N244" s="2">
         <v>46063</v>
       </c>
       <c r="Q244" t="b">
@@ -13894,7 +13920,7 @@
       <c r="E245" t="s">
         <v>1064</v>
       </c>
-      <c r="F245" s="1">
+      <c r="F245" s="2">
         <v>46048</v>
       </c>
       <c r="G245" t="s">
@@ -13915,7 +13941,7 @@
       <c r="L245" t="s">
         <v>1425</v>
       </c>
-      <c r="N245" s="1">
+      <c r="N245" s="2">
         <v>46063</v>
       </c>
       <c r="Q245" t="b">
@@ -13938,7 +13964,7 @@
       <c r="E246" t="s">
         <v>1065</v>
       </c>
-      <c r="F246" s="1">
+      <c r="F246" s="2">
         <v>46050</v>
       </c>
       <c r="G246" t="s">
@@ -13956,7 +13982,7 @@
       <c r="L246" t="s">
         <v>1426</v>
       </c>
-      <c r="N246" s="1">
+      <c r="N246" s="2">
         <v>46191</v>
       </c>
       <c r="Q246" t="b">
@@ -13979,7 +14005,7 @@
       <c r="E247" t="s">
         <v>1066</v>
       </c>
-      <c r="F247" s="1">
+      <c r="F247" s="2">
         <v>46050</v>
       </c>
       <c r="G247" t="s">
@@ -14008,7 +14034,7 @@
       <c r="E248" t="s">
         <v>1067</v>
       </c>
-      <c r="F248" s="1">
+      <c r="F248" s="2">
         <v>46050</v>
       </c>
       <c r="G248" t="s">
@@ -14037,7 +14063,7 @@
       <c r="E249" t="s">
         <v>1068</v>
       </c>
-      <c r="F249" s="1">
+      <c r="F249" s="2">
         <v>46050</v>
       </c>
       <c r="G249" t="s">
@@ -14075,7 +14101,7 @@
       <c r="E250" t="s">
         <v>1069</v>
       </c>
-      <c r="F250" s="1">
+      <c r="F250" s="2">
         <v>46063</v>
       </c>
       <c r="G250" t="s">
@@ -14113,7 +14139,7 @@
       <c r="E251" t="s">
         <v>1070</v>
       </c>
-      <c r="F251" s="1">
+      <c r="F251" s="2">
         <v>46063</v>
       </c>
       <c r="G251" t="s">
@@ -14142,7 +14168,7 @@
       <c r="E252" t="s">
         <v>1071</v>
       </c>
-      <c r="F252" s="1">
+      <c r="F252" s="2">
         <v>46063</v>
       </c>
       <c r="G252" t="s">
@@ -14171,7 +14197,7 @@
       <c r="E253" t="s">
         <v>1072</v>
       </c>
-      <c r="F253" s="1">
+      <c r="F253" s="2">
         <v>46063</v>
       </c>
       <c r="G253" t="s">
@@ -14192,7 +14218,7 @@
       <c r="L253" t="s">
         <v>1395</v>
       </c>
-      <c r="N253" s="1">
+      <c r="N253" s="2">
         <v>46225</v>
       </c>
       <c r="Q253" t="b">
@@ -14215,7 +14241,7 @@
       <c r="E254" t="s">
         <v>1073</v>
       </c>
-      <c r="F254" s="1">
+      <c r="F254" s="2">
         <v>46063</v>
       </c>
       <c r="G254" t="s">
@@ -14253,7 +14279,7 @@
       <c r="E255" t="s">
         <v>1074</v>
       </c>
-      <c r="F255" s="1">
+      <c r="F255" s="2">
         <v>46063</v>
       </c>
       <c r="G255" t="s">
@@ -14274,7 +14300,7 @@
       <c r="L255" t="s">
         <v>1388</v>
       </c>
-      <c r="N255" s="1">
+      <c r="N255" s="2">
         <v>46135</v>
       </c>
       <c r="Q255" t="b">
@@ -14297,7 +14323,7 @@
       <c r="E256" t="s">
         <v>1075</v>
       </c>
-      <c r="F256" s="1">
+      <c r="F256" s="2">
         <v>46063</v>
       </c>
       <c r="G256" t="s">
@@ -14315,7 +14341,7 @@
       <c r="K256" t="s">
         <v>1357</v>
       </c>
-      <c r="N256" s="1">
+      <c r="N256" s="2">
         <v>46086</v>
       </c>
       <c r="O256">
@@ -14341,7 +14367,7 @@
       <c r="E257" t="s">
         <v>1076</v>
       </c>
-      <c r="F257" s="1">
+      <c r="F257" s="2">
         <v>46063</v>
       </c>
       <c r="G257" t="s">
@@ -14370,7 +14396,7 @@
       <c r="E258" t="s">
         <v>1077</v>
       </c>
-      <c r="F258" s="1">
+      <c r="F258" s="2">
         <v>46063</v>
       </c>
       <c r="G258" t="s">
@@ -14399,7 +14425,7 @@
       <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="F259" s="1">
+      <c r="F259" s="2">
         <v>46063</v>
       </c>
       <c r="G259" t="s">
@@ -14420,7 +14446,7 @@
       <c r="L259" t="s">
         <v>1388</v>
       </c>
-      <c r="N259" s="1">
+      <c r="N259" s="2">
         <v>46135</v>
       </c>
       <c r="Q259" t="b">
@@ -14443,7 +14469,7 @@
       <c r="E260" t="s">
         <v>1079</v>
       </c>
-      <c r="F260" s="1">
+      <c r="F260" s="2">
         <v>46063</v>
       </c>
       <c r="G260" t="s">
@@ -14464,7 +14490,7 @@
       <c r="L260" t="s">
         <v>1388</v>
       </c>
-      <c r="N260" s="1">
+      <c r="N260" s="2">
         <v>46147</v>
       </c>
       <c r="Q260" t="b">
@@ -14487,7 +14513,7 @@
       <c r="E261" t="s">
         <v>1080</v>
       </c>
-      <c r="F261" s="1">
+      <c r="F261" s="2">
         <v>46063</v>
       </c>
       <c r="G261" t="s">
@@ -14508,7 +14534,7 @@
       <c r="L261" t="s">
         <v>1427</v>
       </c>
-      <c r="N261" s="1">
+      <c r="N261" s="2">
         <v>46225</v>
       </c>
       <c r="Q261" t="b">
@@ -14531,7 +14557,7 @@
       <c r="E262" t="s">
         <v>1081</v>
       </c>
-      <c r="F262" s="1">
+      <c r="F262" s="2">
         <v>46063</v>
       </c>
       <c r="G262" t="s">
@@ -14549,7 +14575,7 @@
       <c r="L262" t="s">
         <v>1428</v>
       </c>
-      <c r="N262" s="1">
+      <c r="N262" s="2">
         <v>46113</v>
       </c>
       <c r="P262" t="s">
@@ -14575,7 +14601,7 @@
       <c r="E263" t="s">
         <v>1082</v>
       </c>
-      <c r="F263" s="1">
+      <c r="F263" s="2">
         <v>46063</v>
       </c>
       <c r="G263" t="s">
@@ -14604,7 +14630,7 @@
       <c r="E264" t="s">
         <v>1083</v>
       </c>
-      <c r="F264" s="1">
+      <c r="F264" s="2">
         <v>46063</v>
       </c>
       <c r="G264" t="s">
@@ -14625,7 +14651,7 @@
       <c r="L264" t="s">
         <v>1388</v>
       </c>
-      <c r="N264" s="1">
+      <c r="N264" s="2">
         <v>46225</v>
       </c>
       <c r="Q264" t="b">
@@ -14648,7 +14674,7 @@
       <c r="E265" t="s">
         <v>1084</v>
       </c>
-      <c r="F265" s="1">
+      <c r="F265" s="2">
         <v>46063</v>
       </c>
       <c r="G265" t="s">
@@ -14669,7 +14695,7 @@
       <c r="L265" t="s">
         <v>1395</v>
       </c>
-      <c r="N265" s="1">
+      <c r="N265" s="2">
         <v>46225</v>
       </c>
       <c r="Q265" t="b">
@@ -14692,7 +14718,7 @@
       <c r="E266" t="s">
         <v>1085</v>
       </c>
-      <c r="F266" s="1">
+      <c r="F266" s="2">
         <v>46063</v>
       </c>
       <c r="G266" t="s">
@@ -14713,7 +14739,7 @@
       <c r="L266" t="s">
         <v>1388</v>
       </c>
-      <c r="N266" s="1">
+      <c r="N266" s="2">
         <v>46147</v>
       </c>
       <c r="Q266" t="b">
@@ -14736,7 +14762,7 @@
       <c r="E267" t="s">
         <v>1086</v>
       </c>
-      <c r="F267" s="1">
+      <c r="F267" s="2">
         <v>46063</v>
       </c>
       <c r="G267" t="s">
@@ -14774,7 +14800,7 @@
       <c r="E268" t="s">
         <v>1087</v>
       </c>
-      <c r="F268" s="1">
+      <c r="F268" s="2">
         <v>46063</v>
       </c>
       <c r="G268" t="s">
@@ -14809,7 +14835,7 @@
       <c r="D269" t="s">
         <v>798</v>
       </c>
-      <c r="F269" s="1">
+      <c r="F269" s="2">
         <v>46063</v>
       </c>
       <c r="G269" t="s">
@@ -14847,7 +14873,7 @@
       <c r="E270" t="s">
         <v>1088</v>
       </c>
-      <c r="F270" s="1">
+      <c r="F270" s="2">
         <v>46063</v>
       </c>
       <c r="G270" t="s">
@@ -14885,7 +14911,7 @@
       <c r="E271" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="1">
+      <c r="F271" s="2">
         <v>46063</v>
       </c>
       <c r="G271" t="s">
@@ -14923,7 +14949,7 @@
       <c r="E272" t="s">
         <v>1090</v>
       </c>
-      <c r="F272" s="1">
+      <c r="F272" s="2">
         <v>46063</v>
       </c>
       <c r="G272" t="s">
@@ -14941,7 +14967,7 @@
       <c r="L272" t="s">
         <v>1429</v>
       </c>
-      <c r="N272" s="1">
+      <c r="N272" s="2">
         <v>46185</v>
       </c>
       <c r="O272" t="s">
@@ -14967,7 +14993,7 @@
       <c r="E273" t="s">
         <v>1091</v>
       </c>
-      <c r="F273" s="1">
+      <c r="F273" s="2">
         <v>46063</v>
       </c>
       <c r="G273" t="s">
@@ -14996,7 +15022,7 @@
       <c r="E274" t="s">
         <v>1092</v>
       </c>
-      <c r="F274" s="1">
+      <c r="F274" s="2">
         <v>46063</v>
       </c>
       <c r="G274" t="s">
@@ -15011,7 +15037,7 @@
       <c r="L274" t="s">
         <v>1383</v>
       </c>
-      <c r="N274" s="1">
+      <c r="N274" s="2">
         <v>46232</v>
       </c>
       <c r="Q274" t="b">
@@ -15034,7 +15060,7 @@
       <c r="E275" t="s">
         <v>1093</v>
       </c>
-      <c r="F275" s="1">
+      <c r="F275" s="2">
         <v>46063</v>
       </c>
       <c r="G275" t="s">
@@ -15063,7 +15089,7 @@
       <c r="E276" t="s">
         <v>1094</v>
       </c>
-      <c r="F276" s="1">
+      <c r="F276" s="2">
         <v>46063</v>
       </c>
       <c r="G276" t="s">
@@ -15101,7 +15127,7 @@
       <c r="E277" t="s">
         <v>1095</v>
       </c>
-      <c r="F277" s="1">
+      <c r="F277" s="2">
         <v>46063</v>
       </c>
       <c r="G277" t="s">
@@ -15139,7 +15165,7 @@
       <c r="E278" t="s">
         <v>1096</v>
       </c>
-      <c r="F278" s="1">
+      <c r="F278" s="2">
         <v>46077</v>
       </c>
       <c r="G278" t="s">
@@ -15160,7 +15186,7 @@
       <c r="L278" t="s">
         <v>1395</v>
       </c>
-      <c r="N278" s="1">
+      <c r="N278" s="2">
         <v>46225</v>
       </c>
       <c r="Q278" t="b">
@@ -15183,7 +15209,7 @@
       <c r="E279" t="s">
         <v>1097</v>
       </c>
-      <c r="F279" s="1">
+      <c r="F279" s="2">
         <v>46077</v>
       </c>
       <c r="G279" t="s">
@@ -15224,7 +15250,7 @@
       <c r="E280" t="s">
         <v>1098</v>
       </c>
-      <c r="F280" s="1">
+      <c r="F280" s="2">
         <v>46085</v>
       </c>
       <c r="G280" t="s">
@@ -15262,7 +15288,7 @@
       <c r="E281" t="s">
         <v>1099</v>
       </c>
-      <c r="F281" s="1">
+      <c r="F281" s="2">
         <v>46085</v>
       </c>
       <c r="G281" t="s">
@@ -15303,7 +15329,7 @@
       <c r="E282" t="s">
         <v>1100</v>
       </c>
-      <c r="F282" s="1">
+      <c r="F282" s="2">
         <v>46090</v>
       </c>
       <c r="G282" t="s">
@@ -15341,7 +15367,7 @@
       <c r="E283" t="s">
         <v>1101</v>
       </c>
-      <c r="F283" s="1">
+      <c r="F283" s="2">
         <v>46100</v>
       </c>
       <c r="G283" t="s">
@@ -15370,7 +15396,7 @@
       <c r="E284" t="s">
         <v>1102</v>
       </c>
-      <c r="F284" s="1">
+      <c r="F284" s="2">
         <v>46100</v>
       </c>
       <c r="G284" t="s">
@@ -15399,7 +15425,7 @@
       <c r="E285" t="s">
         <v>1103</v>
       </c>
-      <c r="F285" s="1">
+      <c r="F285" s="2">
         <v>46100</v>
       </c>
       <c r="G285" t="s">
@@ -15428,7 +15454,7 @@
       <c r="E286" t="s">
         <v>1104</v>
       </c>
-      <c r="F286" s="1">
+      <c r="F286" s="2">
         <v>46100</v>
       </c>
       <c r="G286" t="s">
@@ -15457,7 +15483,7 @@
       <c r="E287" t="s">
         <v>1105</v>
       </c>
-      <c r="F287" s="1">
+      <c r="F287" s="2">
         <v>46107</v>
       </c>
       <c r="G287" t="s">
@@ -15486,7 +15512,7 @@
       <c r="E288" t="s">
         <v>1106</v>
       </c>
-      <c r="F288" s="1">
+      <c r="F288" s="2">
         <v>46107</v>
       </c>
       <c r="G288" t="s">
@@ -15507,7 +15533,7 @@
       <c r="L288" t="s">
         <v>1388</v>
       </c>
-      <c r="N288" s="1">
+      <c r="N288" s="2">
         <v>46135</v>
       </c>
       <c r="Q288" t="b">
@@ -15530,7 +15556,7 @@
       <c r="E289" t="s">
         <v>1107</v>
       </c>
-      <c r="F289" s="1">
+      <c r="F289" s="2">
         <v>46107</v>
       </c>
       <c r="G289" t="s">
@@ -15559,7 +15585,7 @@
       <c r="E290" t="s">
         <v>1108</v>
       </c>
-      <c r="F290" s="1">
+      <c r="F290" s="2">
         <v>46107</v>
       </c>
       <c r="G290" t="s">
@@ -15580,7 +15606,7 @@
       <c r="L290" t="s">
         <v>1388</v>
       </c>
-      <c r="N290" s="1">
+      <c r="N290" s="2">
         <v>46127</v>
       </c>
       <c r="Q290" t="b">
@@ -15603,7 +15629,7 @@
       <c r="E291" t="s">
         <v>1109</v>
       </c>
-      <c r="F291" s="1">
+      <c r="F291" s="2">
         <v>46107</v>
       </c>
       <c r="G291" t="s">
@@ -15624,7 +15650,7 @@
       <c r="L291" t="s">
         <v>1430</v>
       </c>
-      <c r="N291" s="1">
+      <c r="N291" s="2">
         <v>46127</v>
       </c>
       <c r="Q291" t="b">
@@ -15647,7 +15673,7 @@
       <c r="E292" t="s">
         <v>1110</v>
       </c>
-      <c r="F292" s="1">
+      <c r="F292" s="2">
         <v>46112</v>
       </c>
       <c r="G292" t="s">
@@ -15685,7 +15711,7 @@
       <c r="E293" t="s">
         <v>1111</v>
       </c>
-      <c r="F293" s="1">
+      <c r="F293" s="2">
         <v>46125</v>
       </c>
       <c r="G293" t="s">
@@ -15723,7 +15749,7 @@
       <c r="E294" t="s">
         <v>1112</v>
       </c>
-      <c r="F294" s="1">
+      <c r="F294" s="2">
         <v>46125</v>
       </c>
       <c r="G294" t="s">
@@ -15758,7 +15784,7 @@
       <c r="E295" t="s">
         <v>1113</v>
       </c>
-      <c r="F295" s="1">
+      <c r="F295" s="2">
         <v>46125</v>
       </c>
       <c r="G295" t="s">
@@ -15793,7 +15819,7 @@
       <c r="E296" t="s">
         <v>1114</v>
       </c>
-      <c r="F296" s="1">
+      <c r="F296" s="2">
         <v>46125</v>
       </c>
       <c r="G296" t="s">
@@ -15828,7 +15854,7 @@
       <c r="E297" t="s">
         <v>1115</v>
       </c>
-      <c r="F297" s="1">
+      <c r="F297" s="2">
         <v>46125</v>
       </c>
       <c r="G297" t="s">
@@ -15840,7 +15866,7 @@
       <c r="K297" t="s">
         <v>1359</v>
       </c>
-      <c r="N297" s="1">
+      <c r="N297" s="2">
         <v>46183</v>
       </c>
       <c r="O297">
@@ -15866,7 +15892,7 @@
       <c r="E298" t="s">
         <v>1116</v>
       </c>
-      <c r="F298" s="1">
+      <c r="F298" s="2">
         <v>46125</v>
       </c>
       <c r="G298" t="s">
@@ -15884,7 +15910,7 @@
       <c r="K298" t="s">
         <v>1359</v>
       </c>
-      <c r="N298" s="1">
+      <c r="N298" s="2">
         <v>46183</v>
       </c>
       <c r="Q298" t="b">
@@ -15907,7 +15933,7 @@
       <c r="E299" t="s">
         <v>1117</v>
       </c>
-      <c r="F299" s="1">
+      <c r="F299" s="2">
         <v>46125</v>
       </c>
       <c r="G299" t="s">
@@ -15928,7 +15954,7 @@
       <c r="L299" t="s">
         <v>1388</v>
       </c>
-      <c r="N299" s="1">
+      <c r="N299" s="2">
         <v>46225</v>
       </c>
       <c r="Q299" t="b">
@@ -15951,7 +15977,7 @@
       <c r="E300" t="s">
         <v>1118</v>
       </c>
-      <c r="F300" s="1">
+      <c r="F300" s="2">
         <v>46125</v>
       </c>
       <c r="G300" t="s">
@@ -15972,7 +15998,7 @@
       <c r="L300" t="s">
         <v>1388</v>
       </c>
-      <c r="N300" s="1">
+      <c r="N300" s="2">
         <v>46211</v>
       </c>
       <c r="Q300" t="b">
@@ -15995,7 +16021,7 @@
       <c r="E301" t="s">
         <v>1119</v>
       </c>
-      <c r="F301" s="1">
+      <c r="F301" s="2">
         <v>46125</v>
       </c>
       <c r="G301" t="s">
@@ -16016,7 +16042,7 @@
       <c r="L301" t="s">
         <v>1388</v>
       </c>
-      <c r="N301" s="1">
+      <c r="N301" s="2">
         <v>46227</v>
       </c>
       <c r="Q301" t="b">
@@ -16039,7 +16065,7 @@
       <c r="E302" t="s">
         <v>1120</v>
       </c>
-      <c r="F302" s="1">
+      <c r="F302" s="2">
         <v>46125</v>
       </c>
       <c r="G302" t="s">
@@ -16077,7 +16103,7 @@
       <c r="E303" t="s">
         <v>1121</v>
       </c>
-      <c r="F303" s="1">
+      <c r="F303" s="2">
         <v>46125</v>
       </c>
       <c r="G303" t="s">
@@ -16115,7 +16141,7 @@
       <c r="E304" t="s">
         <v>1122</v>
       </c>
-      <c r="F304" s="1">
+      <c r="F304" s="2">
         <v>46125</v>
       </c>
       <c r="G304" t="s">
@@ -16153,7 +16179,7 @@
       <c r="E305" t="s">
         <v>1123</v>
       </c>
-      <c r="F305" s="1">
+      <c r="F305" s="2">
         <v>46125</v>
       </c>
       <c r="G305" t="s">
@@ -16174,7 +16200,7 @@
       <c r="L305" t="s">
         <v>1431</v>
       </c>
-      <c r="N305" s="1">
+      <c r="N305" s="2">
         <v>46160</v>
       </c>
       <c r="Q305" t="b">
@@ -16197,7 +16223,7 @@
       <c r="E306" t="s">
         <v>1124</v>
       </c>
-      <c r="F306" s="1">
+      <c r="F306" s="2">
         <v>46125</v>
       </c>
       <c r="G306" t="s">
@@ -16218,7 +16244,7 @@
       <c r="L306" t="s">
         <v>1432</v>
       </c>
-      <c r="N306" s="1">
+      <c r="N306" s="2">
         <v>46156</v>
       </c>
       <c r="Q306" t="b">
@@ -16241,7 +16267,7 @@
       <c r="E307" t="s">
         <v>1125</v>
       </c>
-      <c r="F307" s="1">
+      <c r="F307" s="2">
         <v>46125</v>
       </c>
       <c r="G307" t="s">
@@ -16259,7 +16285,7 @@
       <c r="L307" t="s">
         <v>1433</v>
       </c>
-      <c r="N307" s="1">
+      <c r="N307" s="2">
         <v>46209</v>
       </c>
       <c r="P307" t="s">
@@ -16285,7 +16311,7 @@
       <c r="E308" t="s">
         <v>1126</v>
       </c>
-      <c r="F308" s="1">
+      <c r="F308" s="2">
         <v>46125</v>
       </c>
       <c r="G308" t="s">
@@ -16323,7 +16349,7 @@
       <c r="E309" t="s">
         <v>1127</v>
       </c>
-      <c r="F309" s="1">
+      <c r="F309" s="2">
         <v>46125</v>
       </c>
       <c r="G309" t="s">
@@ -16338,7 +16364,7 @@
       <c r="L309" t="s">
         <v>1383</v>
       </c>
-      <c r="N309" s="1">
+      <c r="N309" s="2">
         <v>46232</v>
       </c>
       <c r="Q309" t="b">
@@ -16361,7 +16387,7 @@
       <c r="E310" t="s">
         <v>1128</v>
       </c>
-      <c r="F310" s="1">
+      <c r="F310" s="2">
         <v>46125</v>
       </c>
       <c r="G310" t="s">
@@ -16382,7 +16408,7 @@
       <c r="L310" t="s">
         <v>1383</v>
       </c>
-      <c r="N310" s="1">
+      <c r="N310" s="2">
         <v>46232</v>
       </c>
       <c r="Q310" t="b">
@@ -16405,7 +16431,7 @@
       <c r="E311" t="s">
         <v>1129</v>
       </c>
-      <c r="F311" s="1">
+      <c r="F311" s="2">
         <v>46125</v>
       </c>
       <c r="G311" t="s">
@@ -16443,7 +16469,7 @@
       <c r="E312" t="s">
         <v>1130</v>
       </c>
-      <c r="F312" s="1">
+      <c r="F312" s="2">
         <v>46125</v>
       </c>
       <c r="G312" t="s">
@@ -16461,7 +16487,7 @@
       <c r="L312" t="s">
         <v>1383</v>
       </c>
-      <c r="N312" s="1">
+      <c r="N312" s="2">
         <v>46232</v>
       </c>
       <c r="Q312" t="b">
@@ -16484,7 +16510,7 @@
       <c r="E313" t="s">
         <v>1131</v>
       </c>
-      <c r="F313" s="1">
+      <c r="F313" s="2">
         <v>46125</v>
       </c>
       <c r="G313" t="s">
@@ -16519,7 +16545,7 @@
       <c r="E314" t="s">
         <v>1132</v>
       </c>
-      <c r="F314" s="1">
+      <c r="F314" s="2">
         <v>46125</v>
       </c>
       <c r="G314" t="s">
@@ -16534,7 +16560,7 @@
       <c r="L314" t="s">
         <v>1383</v>
       </c>
-      <c r="N314" s="1">
+      <c r="N314" s="2">
         <v>46232</v>
       </c>
       <c r="Q314" t="b">
@@ -16557,7 +16583,7 @@
       <c r="E315" t="s">
         <v>1133</v>
       </c>
-      <c r="F315" s="1">
+      <c r="F315" s="2">
         <v>46125</v>
       </c>
       <c r="G315" t="s">
@@ -16572,7 +16598,7 @@
       <c r="L315" t="s">
         <v>1383</v>
       </c>
-      <c r="N315" s="1">
+      <c r="N315" s="2">
         <v>46232</v>
       </c>
       <c r="Q315" t="b">
@@ -16595,7 +16621,7 @@
       <c r="E316" t="s">
         <v>1134</v>
       </c>
-      <c r="F316" s="1">
+      <c r="F316" s="2">
         <v>46125</v>
       </c>
       <c r="G316" t="s">
@@ -16636,7 +16662,7 @@
       <c r="E317" t="s">
         <v>1135</v>
       </c>
-      <c r="F317" s="1">
+      <c r="F317" s="2">
         <v>46125</v>
       </c>
       <c r="G317" t="s">
@@ -16671,7 +16697,7 @@
       <c r="E318" t="s">
         <v>1136</v>
       </c>
-      <c r="F318" s="1">
+      <c r="F318" s="2">
         <v>46125</v>
       </c>
       <c r="G318" t="s">
@@ -16700,7 +16726,7 @@
       <c r="E319" t="s">
         <v>1137</v>
       </c>
-      <c r="F319" s="1">
+      <c r="F319" s="2">
         <v>46125</v>
       </c>
       <c r="G319" t="s">
@@ -16715,7 +16741,7 @@
       <c r="L319" t="s">
         <v>1434</v>
       </c>
-      <c r="N319" s="1">
+      <c r="N319" s="2">
         <v>46175</v>
       </c>
       <c r="Q319" t="b">
@@ -16738,7 +16764,7 @@
       <c r="E320" t="s">
         <v>1138</v>
       </c>
-      <c r="F320" s="1">
+      <c r="F320" s="2">
         <v>46125</v>
       </c>
       <c r="G320" t="s">
@@ -16776,7 +16802,7 @@
       <c r="E321" t="s">
         <v>1139</v>
       </c>
-      <c r="F321" s="1">
+      <c r="F321" s="2">
         <v>46125</v>
       </c>
       <c r="G321" t="s">
@@ -16814,7 +16840,7 @@
       <c r="E322" t="s">
         <v>1140</v>
       </c>
-      <c r="F322" s="1">
+      <c r="F322" s="2">
         <v>46125</v>
       </c>
       <c r="G322" t="s">
@@ -16835,7 +16861,7 @@
       <c r="L322" t="s">
         <v>1435</v>
       </c>
-      <c r="N322" s="1">
+      <c r="N322" s="2">
         <v>46182</v>
       </c>
       <c r="Q322" t="b">
@@ -16858,7 +16884,7 @@
       <c r="E323" t="s">
         <v>1141</v>
       </c>
-      <c r="F323" s="1">
+      <c r="F323" s="2">
         <v>46125</v>
       </c>
       <c r="G323" t="s">
@@ -16893,7 +16919,7 @@
       <c r="E324" t="s">
         <v>1142</v>
       </c>
-      <c r="F324" s="1">
+      <c r="F324" s="2">
         <v>46125</v>
       </c>
       <c r="G324" t="s">
@@ -16928,7 +16954,7 @@
       <c r="E325" t="s">
         <v>1143</v>
       </c>
-      <c r="F325" s="1">
+      <c r="F325" s="2">
         <v>46125</v>
       </c>
       <c r="G325" t="s">
@@ -16949,7 +16975,7 @@
       <c r="L325" t="s">
         <v>1435</v>
       </c>
-      <c r="N325" s="1">
+      <c r="N325" s="2">
         <v>46182</v>
       </c>
       <c r="Q325" t="b">
@@ -16972,7 +16998,7 @@
       <c r="E326" t="s">
         <v>1144</v>
       </c>
-      <c r="F326" s="1">
+      <c r="F326" s="2">
         <v>46125</v>
       </c>
       <c r="G326" t="s">
@@ -16987,7 +17013,7 @@
       <c r="L326" t="s">
         <v>1383</v>
       </c>
-      <c r="N326" s="1">
+      <c r="N326" s="2">
         <v>46232</v>
       </c>
       <c r="Q326" t="b">
@@ -17010,7 +17036,7 @@
       <c r="E327" t="s">
         <v>1140</v>
       </c>
-      <c r="F327" s="1">
+      <c r="F327" s="2">
         <v>46125</v>
       </c>
       <c r="G327" t="s">
@@ -17031,7 +17057,7 @@
       <c r="L327" t="s">
         <v>1435</v>
       </c>
-      <c r="N327" s="1">
+      <c r="N327" s="2">
         <v>46182</v>
       </c>
       <c r="Q327" t="b">
@@ -17054,7 +17080,7 @@
       <c r="E328" t="s">
         <v>1145</v>
       </c>
-      <c r="F328" s="1">
+      <c r="F328" s="2">
         <v>46125</v>
       </c>
       <c r="G328" t="s">
@@ -17075,7 +17101,7 @@
       <c r="L328" t="s">
         <v>1435</v>
       </c>
-      <c r="N328" s="1">
+      <c r="N328" s="2">
         <v>46182</v>
       </c>
       <c r="Q328" t="b">
@@ -17098,7 +17124,7 @@
       <c r="E329" t="s">
         <v>1146</v>
       </c>
-      <c r="F329" s="1">
+      <c r="F329" s="2">
         <v>46125</v>
       </c>
       <c r="G329" t="s">
@@ -17119,7 +17145,7 @@
       <c r="L329" t="s">
         <v>1435</v>
       </c>
-      <c r="N329" s="1">
+      <c r="N329" s="2">
         <v>46182</v>
       </c>
       <c r="Q329" t="b">
@@ -17142,7 +17168,7 @@
       <c r="E330" t="s">
         <v>1147</v>
       </c>
-      <c r="F330" s="1">
+      <c r="F330" s="2">
         <v>46125</v>
       </c>
       <c r="G330" t="s">
@@ -17163,7 +17189,7 @@
       <c r="L330" t="s">
         <v>1435</v>
       </c>
-      <c r="N330" s="1">
+      <c r="N330" s="2">
         <v>46182</v>
       </c>
       <c r="Q330" t="b">
@@ -17186,7 +17212,7 @@
       <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="F331" s="1">
+      <c r="F331" s="2">
         <v>46125</v>
       </c>
       <c r="G331" t="s">
@@ -17224,7 +17250,7 @@
       <c r="E332" t="s">
         <v>1148</v>
       </c>
-      <c r="F332" s="1">
+      <c r="F332" s="2">
         <v>46125</v>
       </c>
       <c r="G332" t="s">
@@ -17262,7 +17288,7 @@
       <c r="E333" t="s">
         <v>910</v>
       </c>
-      <c r="F333" s="1">
+      <c r="F333" s="2">
         <v>46125</v>
       </c>
       <c r="G333" t="s">
@@ -17283,7 +17309,7 @@
       <c r="L333" t="s">
         <v>1395</v>
       </c>
-      <c r="N333" s="1">
+      <c r="N333" s="2">
         <v>46225</v>
       </c>
       <c r="Q333" t="b">
@@ -17306,7 +17332,7 @@
       <c r="E334" t="s">
         <v>1149</v>
       </c>
-      <c r="F334" s="1">
+      <c r="F334" s="2">
         <v>46125</v>
       </c>
       <c r="G334" t="s">
@@ -17344,7 +17370,7 @@
       <c r="E335" t="s">
         <v>1150</v>
       </c>
-      <c r="F335" s="1">
+      <c r="F335" s="2">
         <v>46127</v>
       </c>
       <c r="G335" t="s">
@@ -17359,7 +17385,7 @@
       <c r="L335" t="s">
         <v>1434</v>
       </c>
-      <c r="N335" s="1">
+      <c r="N335" s="2">
         <v>46175</v>
       </c>
       <c r="Q335" t="b">
@@ -17382,7 +17408,7 @@
       <c r="E336" t="s">
         <v>1151</v>
       </c>
-      <c r="F336" s="1">
+      <c r="F336" s="2">
         <v>46127</v>
       </c>
       <c r="G336" t="s">
@@ -17403,7 +17429,7 @@
       <c r="L336" t="s">
         <v>1388</v>
       </c>
-      <c r="N336" s="1">
+      <c r="N336" s="2">
         <v>46155</v>
       </c>
       <c r="Q336" t="b">
@@ -17426,7 +17452,7 @@
       <c r="E337" t="s">
         <v>1152</v>
       </c>
-      <c r="F337" s="1">
+      <c r="F337" s="2">
         <v>46127</v>
       </c>
       <c r="G337" t="s">
@@ -17441,7 +17467,7 @@
       <c r="L337" t="s">
         <v>1434</v>
       </c>
-      <c r="N337" s="1">
+      <c r="N337" s="2">
         <v>46175</v>
       </c>
       <c r="Q337" t="b">
@@ -17464,7 +17490,7 @@
       <c r="E338" t="s">
         <v>1153</v>
       </c>
-      <c r="F338" s="1">
+      <c r="F338" s="2">
         <v>46127</v>
       </c>
       <c r="G338" t="s">
@@ -17485,7 +17511,7 @@
       <c r="L338" t="s">
         <v>1388</v>
       </c>
-      <c r="N338" s="1">
+      <c r="N338" s="2">
         <v>46139</v>
       </c>
       <c r="Q338" t="b">
@@ -17508,7 +17534,7 @@
       <c r="E339" t="s">
         <v>1154</v>
       </c>
-      <c r="F339" s="1">
+      <c r="F339" s="2">
         <v>46129</v>
       </c>
       <c r="G339" t="s">
@@ -17537,7 +17563,7 @@
       <c r="E340" t="s">
         <v>1155</v>
       </c>
-      <c r="F340" s="1">
+      <c r="F340" s="2">
         <v>46142</v>
       </c>
       <c r="G340" t="s">
@@ -17555,7 +17581,7 @@
       <c r="L340" t="s">
         <v>1383</v>
       </c>
-      <c r="N340" s="1">
+      <c r="N340" s="2">
         <v>46240</v>
       </c>
       <c r="Q340" t="b">
@@ -17578,7 +17604,7 @@
       <c r="E341" t="s">
         <v>1156</v>
       </c>
-      <c r="F341" s="1">
+      <c r="F341" s="2">
         <v>46142</v>
       </c>
       <c r="G341" t="s">
@@ -17596,7 +17622,7 @@
       <c r="L341" t="s">
         <v>1383</v>
       </c>
-      <c r="N341" s="1">
+      <c r="N341" s="2">
         <v>46232</v>
       </c>
       <c r="Q341" t="b">
@@ -17619,7 +17645,7 @@
       <c r="E342" t="s">
         <v>1157</v>
       </c>
-      <c r="F342" s="1">
+      <c r="F342" s="2">
         <v>46142</v>
       </c>
       <c r="G342" t="s">
@@ -17657,7 +17683,7 @@
       <c r="E343" t="s">
         <v>1158</v>
       </c>
-      <c r="F343" s="1">
+      <c r="F343" s="2">
         <v>46142</v>
       </c>
       <c r="G343" t="s">
@@ -17672,7 +17698,7 @@
       <c r="L343" t="s">
         <v>1383</v>
       </c>
-      <c r="N343" s="1">
+      <c r="N343" s="2">
         <v>46232</v>
       </c>
       <c r="Q343" t="b">
@@ -17695,7 +17721,7 @@
       <c r="E344" t="s">
         <v>1159</v>
       </c>
-      <c r="F344" s="1">
+      <c r="F344" s="2">
         <v>46142</v>
       </c>
       <c r="G344" t="s">
@@ -17710,7 +17736,7 @@
       <c r="L344" t="s">
         <v>1383</v>
       </c>
-      <c r="N344" s="1">
+      <c r="N344" s="2">
         <v>46232</v>
       </c>
       <c r="Q344" t="b">
@@ -17733,7 +17759,7 @@
       <c r="E345" t="s">
         <v>1160</v>
       </c>
-      <c r="F345" s="1">
+      <c r="F345" s="2">
         <v>46142</v>
       </c>
       <c r="G345" t="s">
@@ -17771,7 +17797,7 @@
       <c r="E346" t="s">
         <v>1161</v>
       </c>
-      <c r="F346" s="1">
+      <c r="F346" s="2">
         <v>46142</v>
       </c>
       <c r="G346" t="s">
@@ -17786,7 +17812,7 @@
       <c r="L346" t="s">
         <v>1383</v>
       </c>
-      <c r="N346" s="1">
+      <c r="N346" s="2">
         <v>46232</v>
       </c>
       <c r="Q346" t="b">
@@ -17809,7 +17835,7 @@
       <c r="E347" t="s">
         <v>1162</v>
       </c>
-      <c r="F347" s="1">
+      <c r="F347" s="2">
         <v>46142</v>
       </c>
       <c r="G347" t="s">
@@ -17830,7 +17856,7 @@
       <c r="L347" t="s">
         <v>1431</v>
       </c>
-      <c r="N347" s="1">
+      <c r="N347" s="2">
         <v>46160</v>
       </c>
       <c r="P347" t="s">
@@ -17856,7 +17882,7 @@
       <c r="E348" t="s">
         <v>1163</v>
       </c>
-      <c r="F348" s="1">
+      <c r="F348" s="2">
         <v>46142</v>
       </c>
       <c r="G348" t="s">
@@ -17877,7 +17903,7 @@
       <c r="L348" t="s">
         <v>1432</v>
       </c>
-      <c r="N348" s="1">
+      <c r="N348" s="2">
         <v>46156</v>
       </c>
       <c r="Q348" t="b">
@@ -17900,7 +17926,7 @@
       <c r="E349" t="s">
         <v>1164</v>
       </c>
-      <c r="F349" s="1">
+      <c r="F349" s="2">
         <v>46142</v>
       </c>
       <c r="G349" t="s">
@@ -17938,7 +17964,7 @@
       <c r="E350" t="s">
         <v>1165</v>
       </c>
-      <c r="F350" s="1">
+      <c r="F350" s="2">
         <v>46142</v>
       </c>
       <c r="G350" t="s">
@@ -17953,7 +17979,7 @@
       <c r="J350">
         <v>46</v>
       </c>
-      <c r="N350" s="1">
+      <c r="N350" s="2">
         <v>46188</v>
       </c>
       <c r="Q350" t="b">
@@ -17976,7 +18002,7 @@
       <c r="E351" t="s">
         <v>1166</v>
       </c>
-      <c r="F351" s="1">
+      <c r="F351" s="2">
         <v>46142</v>
       </c>
       <c r="G351" t="s">
@@ -17997,7 +18023,7 @@
       <c r="L351" t="s">
         <v>1436</v>
       </c>
-      <c r="N351" s="1">
+      <c r="N351" s="2">
         <v>46224</v>
       </c>
       <c r="Q351" t="b">
@@ -18020,7 +18046,7 @@
       <c r="E352" t="s">
         <v>1167</v>
       </c>
-      <c r="F352" s="1">
+      <c r="F352" s="2">
         <v>46142</v>
       </c>
       <c r="G352" t="s">
@@ -18041,7 +18067,7 @@
       <c r="L352" t="s">
         <v>1437</v>
       </c>
-      <c r="N352" s="1">
+      <c r="N352" s="2">
         <v>46220</v>
       </c>
       <c r="Q352" t="b">
@@ -18064,7 +18090,7 @@
       <c r="E353" t="s">
         <v>1168</v>
       </c>
-      <c r="F353" s="1">
+      <c r="F353" s="2">
         <v>46142</v>
       </c>
       <c r="G353" t="s">
@@ -18085,7 +18111,7 @@
       <c r="L353" t="s">
         <v>1395</v>
       </c>
-      <c r="N353" s="1">
+      <c r="N353" s="2">
         <v>46225</v>
       </c>
       <c r="Q353" t="b">
@@ -18108,7 +18134,7 @@
       <c r="E354" t="s">
         <v>1169</v>
       </c>
-      <c r="F354" s="1">
+      <c r="F354" s="2">
         <v>46142</v>
       </c>
       <c r="G354" t="s">
@@ -18146,7 +18172,7 @@
       <c r="E355" t="s">
         <v>1170</v>
       </c>
-      <c r="F355" s="1">
+      <c r="F355" s="2">
         <v>46142</v>
       </c>
       <c r="G355" t="s">
@@ -18167,7 +18193,7 @@
       <c r="L355" t="s">
         <v>1438</v>
       </c>
-      <c r="N355" s="1">
+      <c r="N355" s="2">
         <v>46150</v>
       </c>
       <c r="Q355" t="b">
@@ -18190,7 +18216,7 @@
       <c r="E356" t="s">
         <v>1171</v>
       </c>
-      <c r="F356" s="1">
+      <c r="F356" s="2">
         <v>46142</v>
       </c>
       <c r="G356" t="s">
@@ -18205,7 +18231,7 @@
       <c r="L356" t="s">
         <v>1439</v>
       </c>
-      <c r="N356" s="1">
+      <c r="N356" s="2">
         <v>46176</v>
       </c>
       <c r="Q356" t="b">
@@ -18228,7 +18254,7 @@
       <c r="E357" t="s">
         <v>1172</v>
       </c>
-      <c r="F357" s="1">
+      <c r="F357" s="2">
         <v>46142</v>
       </c>
       <c r="G357" t="s">
@@ -18246,7 +18272,7 @@
       <c r="K357" t="s">
         <v>1360</v>
       </c>
-      <c r="N357" s="1">
+      <c r="N357" s="2">
         <v>46227</v>
       </c>
       <c r="Q357" t="b">
@@ -18269,7 +18295,7 @@
       <c r="E358" t="s">
         <v>1173</v>
       </c>
-      <c r="F358" s="1">
+      <c r="F358" s="2">
         <v>46142</v>
       </c>
       <c r="G358" t="s">
@@ -18287,7 +18313,7 @@
       <c r="L358" t="s">
         <v>1440</v>
       </c>
-      <c r="N358" s="1">
+      <c r="N358" s="2">
         <v>46227</v>
       </c>
       <c r="P358" t="s">
@@ -18313,7 +18339,7 @@
       <c r="E359" t="s">
         <v>1174</v>
       </c>
-      <c r="F359" s="1">
+      <c r="F359" s="2">
         <v>46142</v>
       </c>
       <c r="G359" t="s">
@@ -18325,7 +18351,7 @@
       <c r="J359">
         <v>63</v>
       </c>
-      <c r="N359" s="1">
+      <c r="N359" s="2">
         <v>46205</v>
       </c>
       <c r="P359" t="s">
@@ -18351,7 +18377,7 @@
       <c r="E360" t="s">
         <v>949</v>
       </c>
-      <c r="F360" s="1">
+      <c r="F360" s="2">
         <v>46142</v>
       </c>
       <c r="G360" t="s">
@@ -18372,7 +18398,7 @@
       <c r="L360" t="s">
         <v>1395</v>
       </c>
-      <c r="N360" s="1">
+      <c r="N360" s="2">
         <v>46225</v>
       </c>
       <c r="O360" t="s">
@@ -18398,7 +18424,7 @@
       <c r="E361" t="s">
         <v>961</v>
       </c>
-      <c r="F361" s="1">
+      <c r="F361" s="2">
         <v>46142</v>
       </c>
       <c r="G361" t="s">
@@ -18419,7 +18445,7 @@
       <c r="L361" t="s">
         <v>1395</v>
       </c>
-      <c r="N361" s="1">
+      <c r="N361" s="2">
         <v>46225</v>
       </c>
       <c r="Q361" t="b">
@@ -18442,7 +18468,7 @@
       <c r="E362" t="s">
         <v>1175</v>
       </c>
-      <c r="F362" s="1">
+      <c r="F362" s="2">
         <v>46142</v>
       </c>
       <c r="G362" t="s">
@@ -18480,7 +18506,7 @@
       <c r="E363" t="s">
         <v>1176</v>
       </c>
-      <c r="F363" s="1">
+      <c r="F363" s="2">
         <v>46142</v>
       </c>
       <c r="G363" t="s">
@@ -18518,7 +18544,7 @@
       <c r="E364" t="s">
         <v>958</v>
       </c>
-      <c r="F364" s="1">
+      <c r="F364" s="2">
         <v>46142</v>
       </c>
       <c r="G364" t="s">
@@ -18539,7 +18565,7 @@
       <c r="L364" t="s">
         <v>1395</v>
       </c>
-      <c r="N364" s="1">
+      <c r="N364" s="2">
         <v>46225</v>
       </c>
       <c r="Q364" t="b">
@@ -18562,7 +18588,7 @@
       <c r="E365" t="s">
         <v>1177</v>
       </c>
-      <c r="F365" s="1">
+      <c r="F365" s="2">
         <v>46142</v>
       </c>
       <c r="G365" t="s">
@@ -18580,7 +18606,7 @@
       <c r="K365" t="s">
         <v>1359</v>
       </c>
-      <c r="N365" s="1">
+      <c r="N365" s="2">
         <v>46157</v>
       </c>
       <c r="Q365" t="b">
@@ -18603,7 +18629,7 @@
       <c r="E366" t="s">
         <v>1178</v>
       </c>
-      <c r="F366" s="1">
+      <c r="F366" s="2">
         <v>46148</v>
       </c>
       <c r="G366" t="s">
@@ -18624,7 +18650,7 @@
       <c r="L366" t="s">
         <v>1388</v>
       </c>
-      <c r="N366" s="1">
+      <c r="N366" s="2">
         <v>46225</v>
       </c>
       <c r="Q366" t="b">
@@ -18647,7 +18673,7 @@
       <c r="E367" t="s">
         <v>1179</v>
       </c>
-      <c r="F367" s="1">
+      <c r="F367" s="2">
         <v>46148</v>
       </c>
       <c r="G367" t="s">
@@ -18668,7 +18694,7 @@
       <c r="L367" t="s">
         <v>1388</v>
       </c>
-      <c r="N367" s="1">
+      <c r="N367" s="2">
         <v>46225</v>
       </c>
       <c r="Q367" t="b">
@@ -18691,7 +18717,7 @@
       <c r="E368" t="s">
         <v>1180</v>
       </c>
-      <c r="F368" s="1">
+      <c r="F368" s="2">
         <v>46148</v>
       </c>
       <c r="G368" t="s">
@@ -18712,7 +18738,7 @@
       <c r="L368" t="s">
         <v>1395</v>
       </c>
-      <c r="N368" s="1">
+      <c r="N368" s="2">
         <v>46225</v>
       </c>
       <c r="Q368" t="b">
@@ -18735,7 +18761,7 @@
       <c r="E369" t="s">
         <v>1181</v>
       </c>
-      <c r="F369" s="1">
+      <c r="F369" s="2">
         <v>46148</v>
       </c>
       <c r="G369" t="s">
@@ -18773,7 +18799,7 @@
       <c r="E370" t="s">
         <v>1182</v>
       </c>
-      <c r="F370" s="1">
+      <c r="F370" s="2">
         <v>46148</v>
       </c>
       <c r="G370" t="s">
@@ -18811,7 +18837,7 @@
       <c r="E371" t="s">
         <v>1183</v>
       </c>
-      <c r="F371" s="1">
+      <c r="F371" s="2">
         <v>46148</v>
       </c>
       <c r="G371" t="s">
@@ -18832,7 +18858,7 @@
       <c r="L371" t="s">
         <v>1441</v>
       </c>
-      <c r="N371" s="1">
+      <c r="N371" s="2">
         <v>46164</v>
       </c>
       <c r="Q371" t="b">
@@ -18855,7 +18881,7 @@
       <c r="E372" t="s">
         <v>1184</v>
       </c>
-      <c r="F372" s="1">
+      <c r="F372" s="2">
         <v>46148</v>
       </c>
       <c r="G372" t="s">
@@ -18873,7 +18899,7 @@
       <c r="L372" t="s">
         <v>1428</v>
       </c>
-      <c r="N372" s="1">
+      <c r="N372" s="2">
         <v>46113</v>
       </c>
       <c r="P372" t="s">
@@ -18899,7 +18925,7 @@
       <c r="E373" t="s">
         <v>1185</v>
       </c>
-      <c r="F373" s="1">
+      <c r="F373" s="2">
         <v>46149</v>
       </c>
       <c r="G373" t="s">
@@ -18937,7 +18963,7 @@
       <c r="E374" t="s">
         <v>1186</v>
       </c>
-      <c r="F374" s="1">
+      <c r="F374" s="2">
         <v>46149</v>
       </c>
       <c r="G374" t="s">
@@ -18975,7 +19001,7 @@
       <c r="E375" t="s">
         <v>1187</v>
       </c>
-      <c r="F375" s="1">
+      <c r="F375" s="2">
         <v>46154</v>
       </c>
       <c r="G375" t="s">
@@ -18993,7 +19019,7 @@
       <c r="K375" t="s">
         <v>1360</v>
       </c>
-      <c r="N375" s="1">
+      <c r="N375" s="2">
         <v>46248</v>
       </c>
       <c r="Q375" t="b">
@@ -19016,7 +19042,7 @@
       <c r="E376" t="s">
         <v>1188</v>
       </c>
-      <c r="F376" s="1">
+      <c r="F376" s="2">
         <v>46154</v>
       </c>
       <c r="G376" t="s">
@@ -19054,7 +19080,7 @@
       <c r="E377" t="s">
         <v>1189</v>
       </c>
-      <c r="F377" s="1">
+      <c r="F377" s="2">
         <v>46154</v>
       </c>
       <c r="G377" t="s">
@@ -19066,7 +19092,7 @@
       <c r="K377" t="s">
         <v>1360</v>
       </c>
-      <c r="N377" s="1">
+      <c r="N377" s="2">
         <v>46176</v>
       </c>
       <c r="O377" t="s">
@@ -19095,7 +19121,7 @@
       <c r="E378" t="s">
         <v>1190</v>
       </c>
-      <c r="F378" s="1">
+      <c r="F378" s="2">
         <v>46154</v>
       </c>
       <c r="G378" t="s">
@@ -19133,7 +19159,7 @@
       <c r="E379" t="s">
         <v>1191</v>
       </c>
-      <c r="F379" s="1">
+      <c r="F379" s="2">
         <v>46154</v>
       </c>
       <c r="G379" t="s">
@@ -19154,7 +19180,7 @@
       <c r="L379" t="s">
         <v>1442</v>
       </c>
-      <c r="N379" s="1">
+      <c r="N379" s="2">
         <v>46174</v>
       </c>
       <c r="Q379" t="b">
@@ -19177,7 +19203,7 @@
       <c r="E380" t="s">
         <v>1192</v>
       </c>
-      <c r="F380" s="1">
+      <c r="F380" s="2">
         <v>46154</v>
       </c>
       <c r="G380" t="s">
@@ -19198,7 +19224,7 @@
       <c r="L380" t="s">
         <v>1443</v>
       </c>
-      <c r="N380" s="1">
+      <c r="N380" s="2">
         <v>46248</v>
       </c>
       <c r="Q380" t="b">
@@ -19221,7 +19247,7 @@
       <c r="E381" t="s">
         <v>1193</v>
       </c>
-      <c r="F381" s="1">
+      <c r="F381" s="2">
         <v>46154</v>
       </c>
       <c r="G381" t="s">
@@ -19259,7 +19285,7 @@
       <c r="E382" t="s">
         <v>1194</v>
       </c>
-      <c r="F382" s="1">
+      <c r="F382" s="2">
         <v>46154</v>
       </c>
       <c r="G382" t="s">
@@ -19297,7 +19323,7 @@
       <c r="E383" t="s">
         <v>1195</v>
       </c>
-      <c r="F383" s="1">
+      <c r="F383" s="2">
         <v>46154</v>
       </c>
       <c r="G383" t="s">
@@ -19318,7 +19344,7 @@
       <c r="L383" t="s">
         <v>1444</v>
       </c>
-      <c r="N383" s="1">
+      <c r="N383" s="2">
         <v>46225</v>
       </c>
       <c r="Q383" t="b">
@@ -19341,7 +19367,7 @@
       <c r="E384" t="s">
         <v>1196</v>
       </c>
-      <c r="F384" s="1">
+      <c r="F384" s="2">
         <v>46164</v>
       </c>
       <c r="G384" t="s">
@@ -19379,7 +19405,7 @@
       <c r="E385" t="s">
         <v>1197</v>
       </c>
-      <c r="F385" s="1">
+      <c r="F385" s="2">
         <v>46164</v>
       </c>
       <c r="G385" t="s">
@@ -19400,7 +19426,7 @@
       <c r="L385" t="s">
         <v>1445</v>
       </c>
-      <c r="N385" s="1">
+      <c r="N385" s="2">
         <v>46266</v>
       </c>
       <c r="P385" t="s">
@@ -19426,7 +19452,7 @@
       <c r="E386" t="s">
         <v>1198</v>
       </c>
-      <c r="F386" s="1">
+      <c r="F386" s="2">
         <v>46171</v>
       </c>
       <c r="G386" t="s">
@@ -19464,7 +19490,7 @@
       <c r="E387" t="s">
         <v>1199</v>
       </c>
-      <c r="F387" s="1">
+      <c r="F387" s="2">
         <v>46171</v>
       </c>
       <c r="G387" t="s">
@@ -19502,7 +19528,7 @@
       <c r="E388" t="s">
         <v>851</v>
       </c>
-      <c r="F388" s="1">
+      <c r="F388" s="2">
         <v>46171</v>
       </c>
       <c r="G388" t="s">
@@ -19523,7 +19549,7 @@
       <c r="L388" t="s">
         <v>1446</v>
       </c>
-      <c r="N388" s="1">
+      <c r="N388" s="2">
         <v>46086</v>
       </c>
       <c r="Q388" t="b">
@@ -19546,7 +19572,7 @@
       <c r="E389" t="s">
         <v>1200</v>
       </c>
-      <c r="F389" s="1">
+      <c r="F389" s="2">
         <v>46171</v>
       </c>
       <c r="G389" t="s">
@@ -19584,7 +19610,7 @@
       <c r="E390" t="s">
         <v>1201</v>
       </c>
-      <c r="F390" s="1">
+      <c r="F390" s="2">
         <v>46171</v>
       </c>
       <c r="G390" t="s">
@@ -19602,7 +19628,7 @@
       <c r="L390" t="s">
         <v>1447</v>
       </c>
-      <c r="N390" s="1">
+      <c r="N390" s="2">
         <v>46191</v>
       </c>
       <c r="P390" t="s">
@@ -19628,7 +19654,7 @@
       <c r="E391" t="s">
         <v>1202</v>
       </c>
-      <c r="F391" s="1">
+      <c r="F391" s="2">
         <v>46171</v>
       </c>
       <c r="G391" t="s">
@@ -19666,7 +19692,7 @@
       <c r="E392" t="s">
         <v>1203</v>
       </c>
-      <c r="F392" s="1">
+      <c r="F392" s="2">
         <v>46171</v>
       </c>
       <c r="G392" t="s">
@@ -19681,7 +19707,7 @@
       <c r="L392" t="s">
         <v>1439</v>
       </c>
-      <c r="N392" s="1">
+      <c r="N392" s="2">
         <v>46176</v>
       </c>
       <c r="Q392" t="b">
@@ -19704,7 +19730,7 @@
       <c r="E393" t="s">
         <v>1204</v>
       </c>
-      <c r="F393" s="1">
+      <c r="F393" s="2">
         <v>46171</v>
       </c>
       <c r="G393" t="s">
@@ -19725,7 +19751,7 @@
       <c r="L393" t="s">
         <v>1388</v>
       </c>
-      <c r="N393" s="1">
+      <c r="N393" s="2">
         <v>46191</v>
       </c>
       <c r="Q393" t="b">
@@ -19748,7 +19774,7 @@
       <c r="E394" t="s">
         <v>1205</v>
       </c>
-      <c r="F394" s="1">
+      <c r="F394" s="2">
         <v>46171</v>
       </c>
       <c r="G394" t="s">
@@ -19766,7 +19792,7 @@
       <c r="L394" t="s">
         <v>1448</v>
       </c>
-      <c r="N394" s="1">
+      <c r="N394" s="2">
         <v>46241</v>
       </c>
       <c r="P394" t="s">
@@ -19792,7 +19818,7 @@
       <c r="E395" t="s">
         <v>1206</v>
       </c>
-      <c r="F395" s="1">
+      <c r="F395" s="2">
         <v>46171</v>
       </c>
       <c r="G395" t="s">
@@ -19810,7 +19836,7 @@
       <c r="L395" t="s">
         <v>1449</v>
       </c>
-      <c r="N395" s="1">
+      <c r="N395" s="2">
         <v>46191</v>
       </c>
       <c r="P395" t="s">
@@ -19836,7 +19862,7 @@
       <c r="E396" t="s">
         <v>1207</v>
       </c>
-      <c r="F396" s="1">
+      <c r="F396" s="2">
         <v>46171</v>
       </c>
       <c r="G396" t="s">
@@ -19848,7 +19874,7 @@
       <c r="J396">
         <v>20</v>
       </c>
-      <c r="N396" s="1">
+      <c r="N396" s="2">
         <v>46191</v>
       </c>
       <c r="P396" t="s">
@@ -19874,7 +19900,7 @@
       <c r="E397" t="s">
         <v>1208</v>
       </c>
-      <c r="F397" s="1">
+      <c r="F397" s="2">
         <v>46171</v>
       </c>
       <c r="G397" t="s">
@@ -19892,7 +19918,7 @@
       <c r="L397" t="s">
         <v>1448</v>
       </c>
-      <c r="N397" s="1">
+      <c r="N397" s="2">
         <v>46241</v>
       </c>
       <c r="P397" t="s">
@@ -19918,7 +19944,7 @@
       <c r="E398" t="s">
         <v>1209</v>
       </c>
-      <c r="F398" s="1">
+      <c r="F398" s="2">
         <v>46171</v>
       </c>
       <c r="G398" t="s">
@@ -19936,7 +19962,7 @@
       <c r="L398" t="s">
         <v>1449</v>
       </c>
-      <c r="N398" s="1">
+      <c r="N398" s="2">
         <v>46191</v>
       </c>
       <c r="P398" t="s">
@@ -19962,7 +19988,7 @@
       <c r="E399" t="s">
         <v>987</v>
       </c>
-      <c r="F399" s="1">
+      <c r="F399" s="2">
         <v>46163</v>
       </c>
       <c r="G399" t="s">
@@ -19977,7 +20003,7 @@
       <c r="L399" t="s">
         <v>1450</v>
       </c>
-      <c r="N399" s="1">
+      <c r="N399" s="2">
         <v>46171</v>
       </c>
       <c r="Q399" t="b">
@@ -20000,7 +20026,7 @@
       <c r="E400" t="s">
         <v>1210</v>
       </c>
-      <c r="F400" s="1">
+      <c r="F400" s="2">
         <v>46171</v>
       </c>
       <c r="G400" t="s">
@@ -20038,7 +20064,7 @@
       <c r="E401" t="s">
         <v>1211</v>
       </c>
-      <c r="F401" s="1">
+      <c r="F401" s="2">
         <v>46171</v>
       </c>
       <c r="G401" t="s">
@@ -20050,7 +20076,7 @@
       <c r="J401">
         <v>40</v>
       </c>
-      <c r="N401" s="1">
+      <c r="N401" s="2">
         <v>46211</v>
       </c>
       <c r="P401" t="s">
@@ -20076,7 +20102,7 @@
       <c r="E402" t="s">
         <v>1212</v>
       </c>
-      <c r="F402" s="1">
+      <c r="F402" s="2">
         <v>46171</v>
       </c>
       <c r="G402" t="s">
@@ -20114,7 +20140,7 @@
       <c r="E403" t="s">
         <v>1213</v>
       </c>
-      <c r="F403" s="1">
+      <c r="F403" s="2">
         <v>46171</v>
       </c>
       <c r="G403" t="s">
@@ -20135,7 +20161,7 @@
       <c r="L403" t="s">
         <v>1451</v>
       </c>
-      <c r="N403" s="1">
+      <c r="N403" s="2">
         <v>46254</v>
       </c>
       <c r="Q403" t="b">
@@ -20158,7 +20184,7 @@
       <c r="E404" t="s">
         <v>1214</v>
       </c>
-      <c r="F404" s="1">
+      <c r="F404" s="2">
         <v>46171</v>
       </c>
       <c r="G404" t="s">
@@ -20196,7 +20222,7 @@
       <c r="E405" t="s">
         <v>1215</v>
       </c>
-      <c r="F405" s="1">
+      <c r="F405" s="2">
         <v>46183</v>
       </c>
       <c r="G405" t="s">
@@ -20228,7 +20254,7 @@
       <c r="E406" t="s">
         <v>1216</v>
       </c>
-      <c r="F406" s="1">
+      <c r="F406" s="2">
         <v>46183</v>
       </c>
       <c r="G406" t="s">
@@ -20260,7 +20286,7 @@
       <c r="E407" t="s">
         <v>1217</v>
       </c>
-      <c r="F407" s="1">
+      <c r="F407" s="2">
         <v>46183</v>
       </c>
       <c r="G407" t="s">
@@ -20292,7 +20318,7 @@
       <c r="E408" t="s">
         <v>1218</v>
       </c>
-      <c r="F408" s="1">
+      <c r="F408" s="2">
         <v>46183</v>
       </c>
       <c r="G408" t="s">
@@ -20324,7 +20350,7 @@
       <c r="E409" t="s">
         <v>1219</v>
       </c>
-      <c r="F409" s="1">
+      <c r="F409" s="2">
         <v>46183</v>
       </c>
       <c r="G409" t="s">
@@ -20356,7 +20382,7 @@
       <c r="E410" t="s">
         <v>1220</v>
       </c>
-      <c r="F410" s="1">
+      <c r="F410" s="2">
         <v>46183</v>
       </c>
       <c r="G410" t="s">
@@ -20388,7 +20414,7 @@
       <c r="E411" t="s">
         <v>1221</v>
       </c>
-      <c r="F411" s="1">
+      <c r="F411" s="2">
         <v>46188</v>
       </c>
       <c r="G411" t="s">
@@ -20420,7 +20446,7 @@
       <c r="E412" t="s">
         <v>1222</v>
       </c>
-      <c r="F412" s="1">
+      <c r="F412" s="2">
         <v>46188</v>
       </c>
       <c r="G412" t="s">
@@ -20452,7 +20478,7 @@
       <c r="E413" t="s">
         <v>1223</v>
       </c>
-      <c r="F413" s="1">
+      <c r="F413" s="2">
         <v>46188</v>
       </c>
       <c r="G413" t="s">
@@ -20484,7 +20510,7 @@
       <c r="E414" t="s">
         <v>1224</v>
       </c>
-      <c r="F414" s="1">
+      <c r="F414" s="2">
         <v>46188</v>
       </c>
       <c r="G414" t="s">
@@ -20513,7 +20539,7 @@
       <c r="E415" t="s">
         <v>1060</v>
       </c>
-      <c r="F415" s="1">
+      <c r="F415" s="2">
         <v>46188</v>
       </c>
       <c r="G415" t="s">
@@ -20542,7 +20568,7 @@
       <c r="E416" t="s">
         <v>1225</v>
       </c>
-      <c r="F416" s="1">
+      <c r="F416" s="2">
         <v>46188</v>
       </c>
       <c r="G416" t="s">
@@ -20574,7 +20600,7 @@
       <c r="E417" t="s">
         <v>1226</v>
       </c>
-      <c r="F417" s="1">
+      <c r="F417" s="2">
         <v>46188</v>
       </c>
       <c r="G417" t="s">
@@ -20603,7 +20629,7 @@
       <c r="E418" t="s">
         <v>1227</v>
       </c>
-      <c r="F418" s="1">
+      <c r="F418" s="2">
         <v>46188</v>
       </c>
       <c r="G418" t="s">
@@ -20632,7 +20658,7 @@
       <c r="E419" t="s">
         <v>1228</v>
       </c>
-      <c r="F419" s="1">
+      <c r="F419" s="2">
         <v>46188</v>
       </c>
       <c r="G419" t="s">
@@ -20664,7 +20690,7 @@
       <c r="E420" t="s">
         <v>1229</v>
       </c>
-      <c r="F420" s="1">
+      <c r="F420" s="2">
         <v>46188</v>
       </c>
       <c r="G420" t="s">
@@ -20696,7 +20722,7 @@
       <c r="E421" t="s">
         <v>1230</v>
       </c>
-      <c r="F421" s="1">
+      <c r="F421" s="2">
         <v>46188</v>
       </c>
       <c r="G421" t="s">
@@ -20728,7 +20754,7 @@
       <c r="E422" t="s">
         <v>1231</v>
       </c>
-      <c r="F422" s="1">
+      <c r="F422" s="2">
         <v>46188</v>
       </c>
       <c r="G422" t="s">
@@ -20760,7 +20786,7 @@
       <c r="E423" t="s">
         <v>1232</v>
       </c>
-      <c r="F423" s="1">
+      <c r="F423" s="2">
         <v>46188</v>
       </c>
       <c r="G423" t="s">
@@ -20792,7 +20818,7 @@
       <c r="E424" t="s">
         <v>1233</v>
       </c>
-      <c r="F424" s="1">
+      <c r="F424" s="2">
         <v>46188</v>
       </c>
       <c r="G424" t="s">
@@ -20824,7 +20850,7 @@
       <c r="E425" t="s">
         <v>1234</v>
       </c>
-      <c r="F425" s="1">
+      <c r="F425" s="2">
         <v>46188</v>
       </c>
       <c r="G425" t="s">
@@ -20856,7 +20882,7 @@
       <c r="E426" t="s">
         <v>1235</v>
       </c>
-      <c r="F426" s="1">
+      <c r="F426" s="2">
         <v>46188</v>
       </c>
       <c r="G426" t="s">
@@ -20888,7 +20914,7 @@
       <c r="E427" t="s">
         <v>1236</v>
       </c>
-      <c r="F427" s="1">
+      <c r="F427" s="2">
         <v>46188</v>
       </c>
       <c r="G427" t="s">
@@ -20920,7 +20946,7 @@
       <c r="E428" t="s">
         <v>1237</v>
       </c>
-      <c r="F428" s="1">
+      <c r="F428" s="2">
         <v>46188</v>
       </c>
       <c r="G428" t="s">
@@ -20949,7 +20975,7 @@
       <c r="E429" t="s">
         <v>1238</v>
       </c>
-      <c r="F429" s="1">
+      <c r="F429" s="2">
         <v>46188</v>
       </c>
       <c r="G429" t="s">
@@ -20978,7 +21004,7 @@
       <c r="E430" t="s">
         <v>1239</v>
       </c>
-      <c r="F430" s="1">
+      <c r="F430" s="2">
         <v>46188</v>
       </c>
       <c r="G430" t="s">
@@ -21010,7 +21036,7 @@
       <c r="E431" t="s">
         <v>1240</v>
       </c>
-      <c r="F431" s="1">
+      <c r="F431" s="2">
         <v>46188</v>
       </c>
       <c r="G431" t="s">
@@ -21042,7 +21068,7 @@
       <c r="E432" t="s">
         <v>1241</v>
       </c>
-      <c r="F432" s="1">
+      <c r="F432" s="2">
         <v>46188</v>
       </c>
       <c r="G432" t="s">
@@ -21074,7 +21100,7 @@
       <c r="E433" t="s">
         <v>1242</v>
       </c>
-      <c r="F433" s="1">
+      <c r="F433" s="2">
         <v>46188</v>
       </c>
       <c r="G433" t="s">
@@ -21106,7 +21132,7 @@
       <c r="E434" t="s">
         <v>1243</v>
       </c>
-      <c r="F434" s="1">
+      <c r="F434" s="2">
         <v>46188</v>
       </c>
       <c r="G434" t="s">
@@ -21138,7 +21164,7 @@
       <c r="E435" t="s">
         <v>856</v>
       </c>
-      <c r="F435" s="1">
+      <c r="F435" s="2">
         <v>46188</v>
       </c>
       <c r="G435" t="s">
@@ -21170,7 +21196,7 @@
       <c r="E436" t="s">
         <v>1244</v>
       </c>
-      <c r="F436" s="1">
+      <c r="F436" s="2">
         <v>46188</v>
       </c>
       <c r="G436" t="s">
@@ -21202,7 +21228,7 @@
       <c r="E437" t="s">
         <v>1245</v>
       </c>
-      <c r="F437" s="1">
+      <c r="F437" s="2">
         <v>46188</v>
       </c>
       <c r="G437" t="s">
@@ -21234,7 +21260,7 @@
       <c r="E438" t="s">
         <v>1246</v>
       </c>
-      <c r="F438" s="1">
+      <c r="F438" s="2">
         <v>46188</v>
       </c>
       <c r="G438" t="s">
@@ -21266,7 +21292,7 @@
       <c r="E439" t="s">
         <v>1247</v>
       </c>
-      <c r="F439" s="1">
+      <c r="F439" s="2">
         <v>46196</v>
       </c>
       <c r="G439" t="s">
@@ -21298,7 +21324,7 @@
       <c r="E440" t="s">
         <v>1248</v>
       </c>
-      <c r="F440" s="1">
+      <c r="F440" s="2">
         <v>46196</v>
       </c>
       <c r="G440" t="s">
@@ -21330,7 +21356,7 @@
       <c r="E441" t="s">
         <v>1249</v>
       </c>
-      <c r="F441" s="1">
+      <c r="F441" s="2">
         <v>46203</v>
       </c>
       <c r="G441" t="s">
@@ -21362,7 +21388,7 @@
       <c r="E442" t="s">
         <v>1250</v>
       </c>
-      <c r="F442" s="1">
+      <c r="F442" s="2">
         <v>46203</v>
       </c>
       <c r="G442" t="s">
@@ -21391,7 +21417,7 @@
       <c r="E443" t="s">
         <v>1251</v>
       </c>
-      <c r="F443" s="1">
+      <c r="F443" s="2">
         <v>46205</v>
       </c>
       <c r="G443" t="s">
@@ -21423,7 +21449,7 @@
       <c r="E444" t="s">
         <v>1252</v>
       </c>
-      <c r="F444" s="1">
+      <c r="F444" s="2">
         <v>46205</v>
       </c>
       <c r="G444" t="s">
@@ -21452,7 +21478,7 @@
       <c r="E445" t="s">
         <v>1253</v>
       </c>
-      <c r="F445" s="1">
+      <c r="F445" s="2">
         <v>46205</v>
       </c>
       <c r="G445" t="s">
@@ -21481,7 +21507,7 @@
       <c r="E446" t="s">
         <v>1254</v>
       </c>
-      <c r="F446" s="1">
+      <c r="F446" s="2">
         <v>46211</v>
       </c>
       <c r="G446" t="s">
@@ -21513,7 +21539,7 @@
       <c r="E447" t="s">
         <v>1255</v>
       </c>
-      <c r="F447" s="1">
+      <c r="F447" s="2">
         <v>46211</v>
       </c>
       <c r="G447" t="s">
@@ -21545,7 +21571,7 @@
       <c r="E448" t="s">
         <v>1256</v>
       </c>
-      <c r="F448" s="1">
+      <c r="F448" s="2">
         <v>46226</v>
       </c>
       <c r="G448" t="s">
@@ -21577,7 +21603,7 @@
       <c r="E449" t="s">
         <v>1257</v>
       </c>
-      <c r="F449" s="1">
+      <c r="F449" s="2">
         <v>46226</v>
       </c>
       <c r="G449" t="s">
@@ -21609,7 +21635,7 @@
       <c r="E450" t="s">
         <v>1258</v>
       </c>
-      <c r="F450" s="1">
+      <c r="F450" s="2">
         <v>46226</v>
       </c>
       <c r="G450" t="s">
@@ -21641,7 +21667,7 @@
       <c r="E451" t="s">
         <v>1035</v>
       </c>
-      <c r="F451" s="1">
+      <c r="F451" s="2">
         <v>46230</v>
       </c>
       <c r="G451" t="s">
@@ -21673,7 +21699,7 @@
       <c r="E452" t="s">
         <v>1259</v>
       </c>
-      <c r="F452" s="1">
+      <c r="F452" s="2">
         <v>46230</v>
       </c>
       <c r="G452" t="s">
@@ -21705,7 +21731,7 @@
       <c r="E453" t="s">
         <v>1260</v>
       </c>
-      <c r="F453" s="1">
+      <c r="F453" s="2">
         <v>46230</v>
       </c>
       <c r="G453" t="s">
@@ -21737,7 +21763,7 @@
       <c r="E454" t="s">
         <v>1261</v>
       </c>
-      <c r="F454" s="1">
+      <c r="F454" s="2">
         <v>46230</v>
       </c>
       <c r="G454" t="s">
@@ -21769,7 +21795,7 @@
       <c r="E455" t="s">
         <v>1262</v>
       </c>
-      <c r="F455" s="1">
+      <c r="F455" s="2">
         <v>46230</v>
       </c>
       <c r="G455" t="s">
@@ -21801,7 +21827,7 @@
       <c r="E456" t="s">
         <v>1263</v>
       </c>
-      <c r="F456" s="1">
+      <c r="F456" s="2">
         <v>46230</v>
       </c>
       <c r="G456" t="s">
@@ -21833,7 +21859,7 @@
       <c r="E457" t="s">
         <v>1264</v>
       </c>
-      <c r="F457" s="1">
+      <c r="F457" s="2">
         <v>46230</v>
       </c>
       <c r="G457" t="s">
@@ -21865,7 +21891,7 @@
       <c r="E458" t="s">
         <v>1202</v>
       </c>
-      <c r="F458" s="1">
+      <c r="F458" s="2">
         <v>46231</v>
       </c>
       <c r="G458" t="s">
@@ -21897,7 +21923,7 @@
       <c r="E459" t="s">
         <v>1265</v>
       </c>
-      <c r="F459" s="1">
+      <c r="F459" s="2">
         <v>46233</v>
       </c>
       <c r="G459" t="s">
@@ -21929,7 +21955,7 @@
       <c r="E460" t="s">
         <v>1266</v>
       </c>
-      <c r="F460" s="1">
+      <c r="F460" s="2">
         <v>46233</v>
       </c>
       <c r="G460" t="s">
@@ -21961,7 +21987,7 @@
       <c r="E461" t="s">
         <v>1267</v>
       </c>
-      <c r="F461" s="1">
+      <c r="F461" s="2">
         <v>46233</v>
       </c>
       <c r="G461" t="s">
@@ -21993,7 +22019,7 @@
       <c r="E462" t="s">
         <v>1268</v>
       </c>
-      <c r="F462" s="1">
+      <c r="F462" s="2">
         <v>46233</v>
       </c>
       <c r="G462" t="s">
@@ -22025,7 +22051,7 @@
       <c r="E463" t="s">
         <v>1269</v>
       </c>
-      <c r="F463" s="1">
+      <c r="F463" s="2">
         <v>46234</v>
       </c>
       <c r="G463" t="s">
@@ -22057,7 +22083,7 @@
       <c r="E464" t="s">
         <v>1270</v>
       </c>
-      <c r="F464" s="1">
+      <c r="F464" s="2">
         <v>46230</v>
       </c>
       <c r="G464" t="s">
@@ -22089,7 +22115,7 @@
       <c r="E465" t="s">
         <v>1271</v>
       </c>
-      <c r="F465" s="1">
+      <c r="F465" s="2">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
@@ -22121,7 +22147,7 @@
       <c r="E466" t="s">
         <v>1272</v>
       </c>
-      <c r="F466" s="1">
+      <c r="F466" s="2">
         <v>46230</v>
       </c>
       <c r="G466" t="s">
@@ -22153,7 +22179,7 @@
       <c r="E467" t="s">
         <v>1273</v>
       </c>
-      <c r="F467" s="1">
+      <c r="F467" s="2">
         <v>46230</v>
       </c>
       <c r="G467" t="s">
@@ -22185,7 +22211,7 @@
       <c r="E468" t="s">
         <v>1274</v>
       </c>
-      <c r="F468" s="1">
+      <c r="F468" s="2">
         <v>46230</v>
       </c>
       <c r="G468" t="s">
@@ -22217,7 +22243,7 @@
       <c r="E469" t="s">
         <v>1275</v>
       </c>
-      <c r="F469" s="1">
+      <c r="F469" s="2">
         <v>46230</v>
       </c>
       <c r="G469" t="s">
@@ -22249,7 +22275,7 @@
       <c r="E470" t="s">
         <v>1276</v>
       </c>
-      <c r="F470" s="1">
+      <c r="F470" s="2">
         <v>46230</v>
       </c>
       <c r="G470" t="s">
@@ -22278,7 +22304,7 @@
       <c r="E471" t="s">
         <v>1277</v>
       </c>
-      <c r="F471" s="1">
+      <c r="F471" s="2">
         <v>46230</v>
       </c>
       <c r="G471" t="s">
@@ -22310,7 +22336,7 @@
       <c r="E472" t="s">
         <v>1278</v>
       </c>
-      <c r="F472" s="1">
+      <c r="F472" s="2">
         <v>46230</v>
       </c>
       <c r="G472" t="s">
@@ -22342,7 +22368,7 @@
       <c r="E473" t="s">
         <v>1279</v>
       </c>
-      <c r="F473" s="1">
+      <c r="F473" s="2">
         <v>46230</v>
       </c>
       <c r="G473" t="s">
@@ -22374,7 +22400,7 @@
       <c r="E474" t="s">
         <v>1280</v>
       </c>
-      <c r="F474" s="1">
+      <c r="F474" s="2">
         <v>46231</v>
       </c>
       <c r="G474" t="s">
@@ -22406,7 +22432,7 @@
       <c r="E475" t="s">
         <v>1281</v>
       </c>
-      <c r="F475" s="1">
+      <c r="F475" s="2">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
@@ -22438,7 +22464,7 @@
       <c r="E476" t="s">
         <v>1282</v>
       </c>
-      <c r="F476" s="1">
+      <c r="F476" s="2">
         <v>46231</v>
       </c>
       <c r="G476" t="s">
@@ -22470,7 +22496,7 @@
       <c r="E477" t="s">
         <v>1283</v>
       </c>
-      <c r="F477" s="1">
+      <c r="F477" s="2">
         <v>46231</v>
       </c>
       <c r="G477" t="s">
@@ -22502,7 +22528,7 @@
       <c r="E478" t="s">
         <v>1284</v>
       </c>
-      <c r="F478" s="1">
+      <c r="F478" s="2">
         <v>46231</v>
       </c>
       <c r="G478" t="s">
@@ -22534,7 +22560,7 @@
       <c r="E479" t="s">
         <v>1285</v>
       </c>
-      <c r="F479" s="1">
+      <c r="F479" s="2">
         <v>46231</v>
       </c>
       <c r="G479" t="s">
@@ -22566,7 +22592,7 @@
       <c r="E480" t="s">
         <v>1286</v>
       </c>
-      <c r="F480" s="1">
+      <c r="F480" s="2">
         <v>46231</v>
       </c>
       <c r="G480" t="s">
@@ -22598,7 +22624,7 @@
       <c r="E481" t="s">
         <v>1287</v>
       </c>
-      <c r="F481" s="1">
+      <c r="F481" s="2">
         <v>46231</v>
       </c>
       <c r="G481" t="s">
@@ -22630,7 +22656,7 @@
       <c r="E482" t="s">
         <v>1288</v>
       </c>
-      <c r="F482" s="1">
+      <c r="F482" s="2">
         <v>46231</v>
       </c>
       <c r="G482" t="s">
@@ -22662,7 +22688,7 @@
       <c r="E483" t="s">
         <v>1289</v>
       </c>
-      <c r="F483" s="1">
+      <c r="F483" s="2">
         <v>46231</v>
       </c>
       <c r="G483" t="s">
@@ -22694,7 +22720,7 @@
       <c r="E484" t="s">
         <v>1290</v>
       </c>
-      <c r="F484" s="1">
+      <c r="F484" s="2">
         <v>46231</v>
       </c>
       <c r="G484" t="s">
@@ -22726,7 +22752,7 @@
       <c r="E485" t="s">
         <v>1291</v>
       </c>
-      <c r="F485" s="1">
+      <c r="F485" s="2">
         <v>46231</v>
       </c>
       <c r="G485" t="s">
@@ -22758,7 +22784,7 @@
       <c r="E486" t="s">
         <v>1292</v>
       </c>
-      <c r="F486" s="1">
+      <c r="F486" s="2">
         <v>46231</v>
       </c>
       <c r="G486" t="s">
@@ -22790,7 +22816,7 @@
       <c r="E487" t="s">
         <v>1293</v>
       </c>
-      <c r="F487" s="1">
+      <c r="F487" s="2">
         <v>46231</v>
       </c>
       <c r="G487" t="s">
@@ -22822,7 +22848,7 @@
       <c r="E488" t="s">
         <v>1294</v>
       </c>
-      <c r="F488" s="1">
+      <c r="F488" s="2">
         <v>46231</v>
       </c>
       <c r="G488" t="s">
@@ -22854,7 +22880,7 @@
       <c r="E489" t="s">
         <v>1295</v>
       </c>
-      <c r="F489" s="1">
+      <c r="F489" s="2">
         <v>46231</v>
       </c>
       <c r="G489" t="s">
@@ -22886,7 +22912,7 @@
       <c r="E490" t="s">
         <v>1296</v>
       </c>
-      <c r="F490" s="1">
+      <c r="F490" s="2">
         <v>46231</v>
       </c>
       <c r="G490" t="s">
@@ -22918,7 +22944,7 @@
       <c r="E491" t="s">
         <v>1297</v>
       </c>
-      <c r="F491" s="1">
+      <c r="F491" s="2">
         <v>46231</v>
       </c>
       <c r="G491" t="s">
@@ -22950,7 +22976,7 @@
       <c r="E492" t="s">
         <v>911</v>
       </c>
-      <c r="F492" s="1">
+      <c r="F492" s="2">
         <v>46231</v>
       </c>
       <c r="G492" t="s">
@@ -22982,7 +23008,7 @@
       <c r="E493" t="s">
         <v>995</v>
       </c>
-      <c r="F493" s="1">
+      <c r="F493" s="2">
         <v>46231</v>
       </c>
       <c r="G493" t="s">
@@ -23014,7 +23040,7 @@
       <c r="E494" t="s">
         <v>867</v>
       </c>
-      <c r="F494" s="1">
+      <c r="F494" s="2">
         <v>46231</v>
       </c>
       <c r="G494" t="s">
@@ -23046,7 +23072,7 @@
       <c r="E495" t="s">
         <v>912</v>
       </c>
-      <c r="F495" s="1">
+      <c r="F495" s="2">
         <v>46231</v>
       </c>
       <c r="G495" t="s">
@@ -23078,7 +23104,7 @@
       <c r="E496" t="s">
         <v>1048</v>
       </c>
-      <c r="F496" s="1">
+      <c r="F496" s="2">
         <v>46231</v>
       </c>
       <c r="G496" t="s">
@@ -23110,7 +23136,7 @@
       <c r="E497" t="s">
         <v>1298</v>
       </c>
-      <c r="F497" s="1">
+      <c r="F497" s="2">
         <v>46231</v>
       </c>
       <c r="G497" t="s">
@@ -23142,7 +23168,7 @@
       <c r="E498" t="s">
         <v>1299</v>
       </c>
-      <c r="F498" s="1">
+      <c r="F498" s="2">
         <v>46231</v>
       </c>
       <c r="G498" t="s">
@@ -23174,7 +23200,7 @@
       <c r="E499" t="s">
         <v>1300</v>
       </c>
-      <c r="F499" s="1">
+      <c r="F499" s="2">
         <v>46231</v>
       </c>
       <c r="G499" t="s">
@@ -23206,7 +23232,7 @@
       <c r="E500" t="s">
         <v>1301</v>
       </c>
-      <c r="F500" s="1">
+      <c r="F500" s="2">
         <v>46231</v>
       </c>
       <c r="G500" t="s">
@@ -23238,7 +23264,7 @@
       <c r="E501" t="s">
         <v>1302</v>
       </c>
-      <c r="F501" s="1">
+      <c r="F501" s="2">
         <v>46231</v>
       </c>
       <c r="G501" t="s">
@@ -23270,7 +23296,7 @@
       <c r="E502" t="s">
         <v>1303</v>
       </c>
-      <c r="F502" s="1">
+      <c r="F502" s="2">
         <v>46231</v>
       </c>
       <c r="G502" t="s">
@@ -23302,7 +23328,7 @@
       <c r="E503" t="s">
         <v>1304</v>
       </c>
-      <c r="F503" s="1">
+      <c r="F503" s="2">
         <v>46231</v>
       </c>
       <c r="G503" t="s">
@@ -23334,7 +23360,7 @@
       <c r="E504" t="s">
         <v>1305</v>
       </c>
-      <c r="F504" s="1">
+      <c r="F504" s="2">
         <v>46232</v>
       </c>
       <c r="G504" t="s">
@@ -23366,7 +23392,7 @@
       <c r="E505" t="s">
         <v>1306</v>
       </c>
-      <c r="F505" s="1">
+      <c r="F505" s="2">
         <v>46232</v>
       </c>
       <c r="G505" t="s">
@@ -23398,7 +23424,7 @@
       <c r="E506" t="s">
         <v>1307</v>
       </c>
-      <c r="F506" s="1">
+      <c r="F506" s="2">
         <v>46232</v>
       </c>
       <c r="G506" t="s">
@@ -23430,7 +23456,7 @@
       <c r="E507" t="s">
         <v>1308</v>
       </c>
-      <c r="F507" s="1">
+      <c r="F507" s="2">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
@@ -23462,7 +23488,7 @@
       <c r="E508" t="s">
         <v>1309</v>
       </c>
-      <c r="F508" s="1">
+      <c r="F508" s="2">
         <v>46237</v>
       </c>
       <c r="G508" t="s">
@@ -23491,7 +23517,7 @@
       <c r="E509" t="s">
         <v>1310</v>
       </c>
-      <c r="F509" s="1">
+      <c r="F509" s="2">
         <v>46237</v>
       </c>
       <c r="G509" t="s">
@@ -23523,7 +23549,7 @@
       <c r="E510" t="s">
         <v>1311</v>
       </c>
-      <c r="F510" s="1">
+      <c r="F510" s="2">
         <v>46237</v>
       </c>
       <c r="G510" t="s">
@@ -23555,7 +23581,7 @@
       <c r="E511" t="s">
         <v>1312</v>
       </c>
-      <c r="F511" s="1">
+      <c r="F511" s="2">
         <v>46240</v>
       </c>
       <c r="G511" t="s">
@@ -23587,7 +23613,7 @@
       <c r="E512" t="s">
         <v>1313</v>
       </c>
-      <c r="F512" s="1">
+      <c r="F512" s="2">
         <v>46240</v>
       </c>
       <c r="G512" t="s">
@@ -23619,7 +23645,7 @@
       <c r="E513" t="s">
         <v>1314</v>
       </c>
-      <c r="F513" s="1">
+      <c r="F513" s="2">
         <v>46244</v>
       </c>
       <c r="G513" t="s">
@@ -23651,7 +23677,7 @@
       <c r="E514" t="s">
         <v>1315</v>
       </c>
-      <c r="F514" s="1">
+      <c r="F514" s="2">
         <v>46244</v>
       </c>
       <c r="G514" t="s">
@@ -23683,7 +23709,7 @@
       <c r="E515" t="s">
         <v>1043</v>
       </c>
-      <c r="F515" s="1">
+      <c r="F515" s="2">
         <v>46244</v>
       </c>
       <c r="G515" t="s">
@@ -23715,7 +23741,7 @@
       <c r="E516" t="s">
         <v>1316</v>
       </c>
-      <c r="F516" s="1">
+      <c r="F516" s="2">
         <v>46252</v>
       </c>
       <c r="G516" t="s">
@@ -23747,7 +23773,7 @@
       <c r="E517" t="s">
         <v>1317</v>
       </c>
-      <c r="F517" s="1">
+      <c r="F517" s="2">
         <v>46252</v>
       </c>
       <c r="G517" t="s">
@@ -23779,7 +23805,7 @@
       <c r="E518" t="s">
         <v>1318</v>
       </c>
-      <c r="F518" s="1">
+      <c r="F518" s="2">
         <v>46252</v>
       </c>
       <c r="G518" t="s">
@@ -23811,7 +23837,7 @@
       <c r="E519" t="s">
         <v>1253</v>
       </c>
-      <c r="F519" s="1">
+      <c r="F519" s="2">
         <v>46254</v>
       </c>
       <c r="G519" t="s">
@@ -23843,7 +23869,7 @@
       <c r="E520" t="s">
         <v>1319</v>
       </c>
-      <c r="F520" s="1">
+      <c r="F520" s="2">
         <v>46254</v>
       </c>
       <c r="G520" t="s">
@@ -23875,7 +23901,7 @@
       <c r="E521" t="s">
         <v>1320</v>
       </c>
-      <c r="F521" s="1">
+      <c r="F521" s="2">
         <v>46254</v>
       </c>
       <c r="G521" t="s">
@@ -23907,7 +23933,7 @@
       <c r="E522" t="s">
         <v>1253</v>
       </c>
-      <c r="F522" s="1">
+      <c r="F522" s="2">
         <v>46254</v>
       </c>
       <c r="G522" t="s">
@@ -23939,7 +23965,7 @@
       <c r="E523" t="s">
         <v>1319</v>
       </c>
-      <c r="F523" s="1">
+      <c r="F523" s="2">
         <v>46254</v>
       </c>
       <c r="G523" t="s">
@@ -23971,7 +23997,7 @@
       <c r="E524" t="s">
         <v>1321</v>
       </c>
-      <c r="F524" s="1">
+      <c r="F524" s="2">
         <v>46265</v>
       </c>
       <c r="G524" t="s">
@@ -24003,7 +24029,7 @@
       <c r="E525" t="s">
         <v>1322</v>
       </c>
-      <c r="F525" s="1">
+      <c r="F525" s="2">
         <v>46265</v>
       </c>
       <c r="G525" t="s">
@@ -24035,7 +24061,7 @@
       <c r="E526" t="s">
         <v>1323</v>
       </c>
-      <c r="F526" s="1">
+      <c r="F526" s="2">
         <v>46265</v>
       </c>
       <c r="G526" t="s">
@@ -24067,7 +24093,7 @@
       <c r="E527" t="s">
         <v>1324</v>
       </c>
-      <c r="F527" s="1">
+      <c r="F527" s="2">
         <v>46265</v>
       </c>
       <c r="G527" t="s">

--- a/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4200" uniqueCount="1502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4201" uniqueCount="1503">
   <si>
     <t>os</t>
   </si>
@@ -4460,6 +4460,9 @@
   </si>
   <si>
     <t>080/2026</t>
+  </si>
+  <si>
+    <t>032/2026</t>
   </si>
   <si>
     <t>062/2026</t>
@@ -4529,16 +4532,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -4554,7 +4549,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -4562,30 +4557,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4885,55 +4862,55 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4953,7 +4930,7 @@
       <c r="E2" t="s">
         <v>829</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>45698</v>
       </c>
       <c r="G2" t="s">
@@ -4963,7 +4940,7 @@
         <v>1353</v>
       </c>
       <c r="I2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="K2" t="s">
         <v>1356</v>
@@ -4991,7 +4968,7 @@
       <c r="E3" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>45714</v>
       </c>
       <c r="G3" t="s">
@@ -5001,7 +4978,7 @@
         <v>1353</v>
       </c>
       <c r="I3">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K3" t="s">
         <v>1357</v>
@@ -5029,7 +5006,7 @@
       <c r="E4" t="s">
         <v>831</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>45714</v>
       </c>
       <c r="G4" t="s">
@@ -5039,7 +5016,7 @@
         <v>1353</v>
       </c>
       <c r="I4">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K4" t="s">
         <v>1357</v>
@@ -5067,7 +5044,7 @@
       <c r="E5" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>45714</v>
       </c>
       <c r="G5" t="s">
@@ -5077,7 +5054,7 @@
         <v>1353</v>
       </c>
       <c r="I5">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="J5">
         <v>279</v>
@@ -5088,7 +5065,7 @@
       <c r="L5" t="s">
         <v>1367</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="1">
         <v>45993</v>
       </c>
       <c r="Q5" t="b">
@@ -5111,7 +5088,7 @@
       <c r="E6" t="s">
         <v>833</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>45736</v>
       </c>
       <c r="G6" t="s">
@@ -5121,7 +5098,7 @@
         <v>1353</v>
       </c>
       <c r="I6">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J6">
         <v>153</v>
@@ -5132,7 +5109,7 @@
       <c r="L6" t="s">
         <v>1368</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="1">
         <v>45889</v>
       </c>
       <c r="Q6" t="b">
@@ -5155,7 +5132,7 @@
       <c r="E7" t="s">
         <v>834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>45736</v>
       </c>
       <c r="G7" t="s">
@@ -5165,7 +5142,7 @@
         <v>1353</v>
       </c>
       <c r="I7">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J7">
         <v>112</v>
@@ -5176,7 +5153,7 @@
       <c r="L7" t="s">
         <v>1369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="1">
         <v>45848</v>
       </c>
       <c r="O7" t="s">
@@ -5202,7 +5179,7 @@
       <c r="E8" t="s">
         <v>835</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>45736</v>
       </c>
       <c r="G8" t="s">
@@ -5231,7 +5208,7 @@
       <c r="E9" t="s">
         <v>836</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>45736</v>
       </c>
       <c r="G9" t="s">
@@ -5241,7 +5218,7 @@
         <v>1353</v>
       </c>
       <c r="I9">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J9">
         <v>362</v>
@@ -5252,7 +5229,7 @@
       <c r="L9" t="s">
         <v>1370</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="1">
         <v>46098</v>
       </c>
       <c r="O9">
@@ -5278,7 +5255,7 @@
       <c r="E10" t="s">
         <v>837</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>45736</v>
       </c>
       <c r="G10" t="s">
@@ -5288,7 +5265,7 @@
         <v>1353</v>
       </c>
       <c r="I10">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J10">
         <v>378</v>
@@ -5299,7 +5276,7 @@
       <c r="L10" t="s">
         <v>1371</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="1">
         <v>46114</v>
       </c>
       <c r="O10" t="s">
@@ -5325,7 +5302,7 @@
       <c r="E11" t="s">
         <v>838</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>45736</v>
       </c>
       <c r="G11" t="s">
@@ -5335,7 +5312,7 @@
         <v>1353</v>
       </c>
       <c r="I11">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J11">
         <v>112</v>
@@ -5346,7 +5323,7 @@
       <c r="L11" t="s">
         <v>1369</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="1">
         <v>45848</v>
       </c>
       <c r="O11" t="s">
@@ -5372,7 +5349,7 @@
       <c r="E12" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>45736</v>
       </c>
       <c r="G12" t="s">
@@ -5382,7 +5359,7 @@
         <v>1353</v>
       </c>
       <c r="I12">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J12">
         <v>124</v>
@@ -5393,7 +5370,7 @@
       <c r="L12" t="s">
         <v>1372</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="1">
         <v>45860</v>
       </c>
       <c r="Q12" t="b">
@@ -5416,7 +5393,7 @@
       <c r="E13" t="s">
         <v>840</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>45736</v>
       </c>
       <c r="G13" t="s">
@@ -5445,7 +5422,7 @@
       <c r="E14" t="s">
         <v>841</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>45736</v>
       </c>
       <c r="G14" t="s">
@@ -5455,7 +5432,7 @@
         <v>1353</v>
       </c>
       <c r="I14">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J14">
         <v>64</v>
@@ -5466,7 +5443,7 @@
       <c r="L14" t="s">
         <v>1373</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="1">
         <v>45800</v>
       </c>
       <c r="Q14" t="b">
@@ -5489,7 +5466,7 @@
       <c r="E15" t="s">
         <v>842</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>45736</v>
       </c>
       <c r="G15" t="s">
@@ -5499,7 +5476,7 @@
         <v>1353</v>
       </c>
       <c r="I15">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K15" t="s">
         <v>1359</v>
@@ -5527,7 +5504,7 @@
       <c r="E16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>45736</v>
       </c>
       <c r="G16" t="s">
@@ -5537,7 +5514,7 @@
         <v>1353</v>
       </c>
       <c r="I16">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K16" t="s">
         <v>1356</v>
@@ -5565,7 +5542,7 @@
       <c r="E17" t="s">
         <v>844</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>45736</v>
       </c>
       <c r="G17" t="s">
@@ -5575,7 +5552,7 @@
         <v>1353</v>
       </c>
       <c r="I17">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J17">
         <v>161</v>
@@ -5586,7 +5563,7 @@
       <c r="L17" t="s">
         <v>1368</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="1">
         <v>45897</v>
       </c>
       <c r="Q17" t="b">
@@ -5609,7 +5586,7 @@
       <c r="E18" t="s">
         <v>845</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="1">
         <v>45736</v>
       </c>
       <c r="G18" t="s">
@@ -5619,7 +5596,7 @@
         <v>1353</v>
       </c>
       <c r="I18">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J18">
         <v>66</v>
@@ -5630,7 +5607,7 @@
       <c r="L18" t="s">
         <v>1373</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" s="1">
         <v>45802</v>
       </c>
       <c r="Q18" t="b">
@@ -5653,7 +5630,7 @@
       <c r="E19" t="s">
         <v>846</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="1">
         <v>45736</v>
       </c>
       <c r="G19" t="s">
@@ -5682,7 +5659,7 @@
       <c r="E20" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="1">
         <v>45736</v>
       </c>
       <c r="G20" t="s">
@@ -5692,7 +5669,7 @@
         <v>1353</v>
       </c>
       <c r="I20">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J20">
         <v>399</v>
@@ -5703,7 +5680,7 @@
       <c r="L20" t="s">
         <v>1374</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20" s="1">
         <v>46135</v>
       </c>
       <c r="Q20" t="b">
@@ -5726,7 +5703,7 @@
       <c r="E21" t="s">
         <v>848</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="1">
         <v>45736</v>
       </c>
       <c r="G21" t="s">
@@ -5755,7 +5732,7 @@
       <c r="E22" t="s">
         <v>849</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="1">
         <v>45736</v>
       </c>
       <c r="G22" t="s">
@@ -5765,7 +5742,7 @@
         <v>1353</v>
       </c>
       <c r="I22">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K22" t="s">
         <v>1360</v>
@@ -5793,7 +5770,7 @@
       <c r="E23" t="s">
         <v>850</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="1">
         <v>45736</v>
       </c>
       <c r="G23" t="s">
@@ -5803,7 +5780,7 @@
         <v>1353</v>
       </c>
       <c r="I23">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J23">
         <v>229</v>
@@ -5814,7 +5791,7 @@
       <c r="L23" t="s">
         <v>1375</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="1">
         <v>45965</v>
       </c>
       <c r="P23" t="s">
@@ -5840,7 +5817,7 @@
       <c r="E24" t="s">
         <v>851</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="1">
         <v>45736</v>
       </c>
       <c r="G24" t="s">
@@ -5869,7 +5846,7 @@
       <c r="E25" t="s">
         <v>852</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="1">
         <v>45736</v>
       </c>
       <c r="G25" t="s">
@@ -5898,7 +5875,7 @@
       <c r="E26" t="s">
         <v>853</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="1">
         <v>45736</v>
       </c>
       <c r="G26" t="s">
@@ -5908,7 +5885,7 @@
         <v>1353</v>
       </c>
       <c r="I26">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J26">
         <v>155</v>
@@ -5919,7 +5896,7 @@
       <c r="L26" t="s">
         <v>1376</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" s="1">
         <v>45891</v>
       </c>
       <c r="P26" t="s">
@@ -5945,7 +5922,7 @@
       <c r="E27" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="1">
         <v>45736</v>
       </c>
       <c r="G27" t="s">
@@ -5955,7 +5932,7 @@
         <v>1353</v>
       </c>
       <c r="I27">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K27" t="s">
         <v>1360</v>
@@ -5983,7 +5960,7 @@
       <c r="E28" t="s">
         <v>855</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="1">
         <v>45736</v>
       </c>
       <c r="G28" t="s">
@@ -6012,7 +5989,7 @@
       <c r="E29" t="s">
         <v>856</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="1">
         <v>45736</v>
       </c>
       <c r="G29" t="s">
@@ -6041,7 +6018,7 @@
       <c r="E30" t="s">
         <v>857</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="1">
         <v>45736</v>
       </c>
       <c r="G30" t="s">
@@ -6051,7 +6028,7 @@
         <v>1353</v>
       </c>
       <c r="I30">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J30">
         <v>209</v>
@@ -6062,7 +6039,7 @@
       <c r="L30" t="s">
         <v>1377</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" s="1">
         <v>45945</v>
       </c>
       <c r="Q30" t="b">
@@ -6085,7 +6062,7 @@
       <c r="E31" t="s">
         <v>858</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="1">
         <v>45736</v>
       </c>
       <c r="G31" t="s">
@@ -6114,7 +6091,7 @@
       <c r="E32" t="s">
         <v>859</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="1">
         <v>45736</v>
       </c>
       <c r="G32" t="s">
@@ -6124,7 +6101,7 @@
         <v>1353</v>
       </c>
       <c r="I32">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K32" t="s">
         <v>1356</v>
@@ -6152,7 +6129,7 @@
       <c r="E33" t="s">
         <v>860</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>45736</v>
       </c>
       <c r="G33" t="s">
@@ -6181,7 +6158,7 @@
       <c r="E34" t="s">
         <v>861</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="1">
         <v>45736</v>
       </c>
       <c r="G34" t="s">
@@ -6210,7 +6187,7 @@
       <c r="E35" t="s">
         <v>862</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="1">
         <v>45736</v>
       </c>
       <c r="G35" t="s">
@@ -6239,7 +6216,7 @@
       <c r="E36" t="s">
         <v>863</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="1">
         <v>45736</v>
       </c>
       <c r="G36" t="s">
@@ -6268,7 +6245,7 @@
       <c r="E37" t="s">
         <v>864</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>45736</v>
       </c>
       <c r="G37" t="s">
@@ -6297,7 +6274,7 @@
       <c r="E38" t="s">
         <v>844</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="1">
         <v>45736</v>
       </c>
       <c r="G38" t="s">
@@ -6323,7 +6300,7 @@
       <c r="D39" t="s">
         <v>731</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="1">
         <v>45736</v>
       </c>
       <c r="G39" t="s">
@@ -6333,7 +6310,7 @@
         <v>1353</v>
       </c>
       <c r="I39">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K39" t="s">
         <v>1361</v>
@@ -6358,7 +6335,7 @@
       <c r="D40" t="s">
         <v>731</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="1">
         <v>45736</v>
       </c>
       <c r="G40" t="s">
@@ -6368,7 +6345,7 @@
         <v>1353</v>
       </c>
       <c r="I40">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K40" t="s">
         <v>1359</v>
@@ -6396,7 +6373,7 @@
       <c r="E41" t="s">
         <v>865</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="1">
         <v>45736</v>
       </c>
       <c r="G41" t="s">
@@ -6425,7 +6402,7 @@
       <c r="E42" t="s">
         <v>866</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="1">
         <v>45736</v>
       </c>
       <c r="G42" t="s">
@@ -6454,7 +6431,7 @@
       <c r="E43" t="s">
         <v>867</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="1">
         <v>45736</v>
       </c>
       <c r="G43" t="s">
@@ -6489,7 +6466,7 @@
       <c r="E44" t="s">
         <v>868</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="1">
         <v>45769</v>
       </c>
       <c r="G44" t="s">
@@ -6499,7 +6476,7 @@
         <v>1353</v>
       </c>
       <c r="I44">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J44">
         <v>87</v>
@@ -6510,7 +6487,7 @@
       <c r="L44" t="s">
         <v>1378</v>
       </c>
-      <c r="N44" s="2">
+      <c r="N44" s="1">
         <v>45856</v>
       </c>
       <c r="P44" t="s">
@@ -6536,7 +6513,7 @@
       <c r="E45" t="s">
         <v>869</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="1">
         <v>45769</v>
       </c>
       <c r="G45" t="s">
@@ -6546,7 +6523,7 @@
         <v>1353</v>
       </c>
       <c r="I45">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J45">
         <v>331</v>
@@ -6557,7 +6534,7 @@
       <c r="L45" t="s">
         <v>1379</v>
       </c>
-      <c r="N45" s="2">
+      <c r="N45" s="1">
         <v>46100</v>
       </c>
       <c r="O45">
@@ -6583,7 +6560,7 @@
       <c r="E46" t="s">
         <v>870</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="1">
         <v>45769</v>
       </c>
       <c r="G46" t="s">
@@ -6593,7 +6570,7 @@
         <v>1353</v>
       </c>
       <c r="I46">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K46" t="s">
         <v>1360</v>
@@ -6621,7 +6598,7 @@
       <c r="E47" t="s">
         <v>871</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="1">
         <v>45769</v>
       </c>
       <c r="G47" t="s">
@@ -6631,7 +6608,7 @@
         <v>1353</v>
       </c>
       <c r="I47">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J47">
         <v>344</v>
@@ -6642,7 +6619,7 @@
       <c r="L47" t="s">
         <v>1380</v>
       </c>
-      <c r="N47" s="2">
+      <c r="N47" s="1">
         <v>46113</v>
       </c>
       <c r="P47" t="s">
@@ -6668,7 +6645,7 @@
       <c r="E48" t="s">
         <v>872</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="1">
         <v>45769</v>
       </c>
       <c r="G48" t="s">
@@ -6678,7 +6655,7 @@
         <v>1353</v>
       </c>
       <c r="I48">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K48" t="s">
         <v>1360</v>
@@ -6706,7 +6683,7 @@
       <c r="E49" t="s">
         <v>873</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="1">
         <v>45769</v>
       </c>
       <c r="G49" t="s">
@@ -6735,7 +6712,7 @@
       <c r="E50" t="s">
         <v>874</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="1">
         <v>45769</v>
       </c>
       <c r="G50" t="s">
@@ -6745,7 +6722,7 @@
         <v>1353</v>
       </c>
       <c r="I50">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K50" t="s">
         <v>1360</v>
@@ -6773,7 +6750,7 @@
       <c r="E51" t="s">
         <v>875</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="1">
         <v>45769</v>
       </c>
       <c r="G51" t="s">
@@ -6802,7 +6779,7 @@
       <c r="E52" t="s">
         <v>876</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="1">
         <v>45769</v>
       </c>
       <c r="G52" t="s">
@@ -6812,7 +6789,7 @@
         <v>1353</v>
       </c>
       <c r="I52">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K52" t="s">
         <v>1356</v>
@@ -6840,7 +6817,7 @@
       <c r="E53" t="s">
         <v>877</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="1">
         <v>45769</v>
       </c>
       <c r="G53" t="s">
@@ -6850,7 +6827,7 @@
         <v>1353</v>
       </c>
       <c r="I53">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K53" t="s">
         <v>1357</v>
@@ -6878,7 +6855,7 @@
       <c r="E54" t="s">
         <v>878</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="1">
         <v>45769</v>
       </c>
       <c r="G54" t="s">
@@ -6888,7 +6865,7 @@
         <v>1353</v>
       </c>
       <c r="I54">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K54" t="s">
         <v>1357</v>
@@ -6916,7 +6893,7 @@
       <c r="E55" t="s">
         <v>879</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="1">
         <v>45769</v>
       </c>
       <c r="G55" t="s">
@@ -6945,7 +6922,7 @@
       <c r="E56" t="s">
         <v>880</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="1">
         <v>45769</v>
       </c>
       <c r="G56" t="s">
@@ -6974,7 +6951,7 @@
       <c r="E57" t="s">
         <v>881</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="1">
         <v>45769</v>
       </c>
       <c r="G57" t="s">
@@ -6984,7 +6961,7 @@
         <v>1353</v>
       </c>
       <c r="I57">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K57" t="s">
         <v>1360</v>
@@ -7012,7 +6989,7 @@
       <c r="E58" t="s">
         <v>882</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="1">
         <v>45769</v>
       </c>
       <c r="G58" t="s">
@@ -7041,7 +7018,7 @@
       <c r="E59" t="s">
         <v>883</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="1">
         <v>45769</v>
       </c>
       <c r="G59" t="s">
@@ -7070,7 +7047,7 @@
       <c r="E60" t="s">
         <v>884</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="1">
         <v>45769</v>
       </c>
       <c r="G60" t="s">
@@ -7099,7 +7076,7 @@
       <c r="E61" t="s">
         <v>885</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="1">
         <v>45769</v>
       </c>
       <c r="G61" t="s">
@@ -7128,7 +7105,7 @@
       <c r="E62" t="s">
         <v>886</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="1">
         <v>45770</v>
       </c>
       <c r="G62" t="s">
@@ -7157,7 +7134,7 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="1">
         <v>45799</v>
       </c>
       <c r="G63" t="s">
@@ -7167,7 +7144,7 @@
         <v>1353</v>
       </c>
       <c r="I63">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J63">
         <v>293</v>
@@ -7178,7 +7155,7 @@
       <c r="L63" t="s">
         <v>1381</v>
       </c>
-      <c r="N63" s="2">
+      <c r="N63" s="1">
         <v>46092</v>
       </c>
       <c r="P63" t="s">
@@ -7204,7 +7181,7 @@
       <c r="E64" t="s">
         <v>888</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="1">
         <v>45799</v>
       </c>
       <c r="G64" t="s">
@@ -7214,7 +7191,7 @@
         <v>1353</v>
       </c>
       <c r="I64">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J64">
         <v>320</v>
@@ -7225,7 +7202,7 @@
       <c r="L64" t="s">
         <v>1382</v>
       </c>
-      <c r="N64" s="2">
+      <c r="N64" s="1">
         <v>46119</v>
       </c>
       <c r="Q64" t="b">
@@ -7248,7 +7225,7 @@
       <c r="E65" t="s">
         <v>889</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="1">
         <v>45799</v>
       </c>
       <c r="G65" t="s">
@@ -7277,7 +7254,7 @@
       <c r="E66" t="s">
         <v>890</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="1">
         <v>45799</v>
       </c>
       <c r="G66" t="s">
@@ -7306,7 +7283,7 @@
       <c r="E67" t="s">
         <v>891</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="1">
         <v>45799</v>
       </c>
       <c r="G67" t="s">
@@ -7335,7 +7312,7 @@
       <c r="E68" t="s">
         <v>892</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="1">
         <v>45799</v>
       </c>
       <c r="G68" t="s">
@@ -7364,7 +7341,7 @@
       <c r="E69" t="s">
         <v>893</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="1">
         <v>45803</v>
       </c>
       <c r="G69" t="s">
@@ -7393,7 +7370,7 @@
       <c r="E70" t="s">
         <v>894</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="1">
         <v>45803</v>
       </c>
       <c r="G70" t="s">
@@ -7403,7 +7380,7 @@
         <v>1353</v>
       </c>
       <c r="I70">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J70">
         <v>429</v>
@@ -7414,7 +7391,7 @@
       <c r="L70" t="s">
         <v>1383</v>
       </c>
-      <c r="N70" s="2">
+      <c r="N70" s="1">
         <v>46232</v>
       </c>
       <c r="Q70" t="b">
@@ -7437,7 +7414,7 @@
       <c r="E71" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="1">
         <v>45803</v>
       </c>
       <c r="G71" t="s">
@@ -7447,7 +7424,7 @@
         <v>1353</v>
       </c>
       <c r="I71">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J71">
         <v>429</v>
@@ -7458,7 +7435,7 @@
       <c r="L71" t="s">
         <v>1383</v>
       </c>
-      <c r="N71" s="2">
+      <c r="N71" s="1">
         <v>46232</v>
       </c>
       <c r="Q71" t="b">
@@ -7481,7 +7458,7 @@
       <c r="E72" t="s">
         <v>896</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="1">
         <v>45803</v>
       </c>
       <c r="G72" t="s">
@@ -7510,7 +7487,7 @@
       <c r="E73" t="s">
         <v>897</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="1">
         <v>45803</v>
       </c>
       <c r="G73" t="s">
@@ -7520,7 +7497,7 @@
         <v>1353</v>
       </c>
       <c r="I73">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K73" t="s">
         <v>1356</v>
@@ -7548,7 +7525,7 @@
       <c r="E74" t="s">
         <v>896</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="1">
         <v>45803</v>
       </c>
       <c r="G74" t="s">
@@ -7577,7 +7554,7 @@
       <c r="E75" t="s">
         <v>898</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="1">
         <v>45803</v>
       </c>
       <c r="G75" t="s">
@@ -7587,7 +7564,7 @@
         <v>1353</v>
       </c>
       <c r="I75">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J75">
         <v>429</v>
@@ -7598,7 +7575,7 @@
       <c r="L75" t="s">
         <v>1383</v>
       </c>
-      <c r="N75" s="2">
+      <c r="N75" s="1">
         <v>46232</v>
       </c>
       <c r="Q75" t="b">
@@ -7621,7 +7598,7 @@
       <c r="E76" t="s">
         <v>899</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="1">
         <v>45803</v>
       </c>
       <c r="G76" t="s">
@@ -7631,7 +7608,7 @@
         <v>1353</v>
       </c>
       <c r="I76">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K76" t="s">
         <v>1363</v>
@@ -7656,7 +7633,7 @@
       <c r="E77" t="s">
         <v>900</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="1">
         <v>45803</v>
       </c>
       <c r="G77" t="s">
@@ -7685,7 +7662,7 @@
       <c r="E78" t="s">
         <v>901</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="1">
         <v>45803</v>
       </c>
       <c r="G78" t="s">
@@ -7714,7 +7691,7 @@
       <c r="E79" t="s">
         <v>902</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="1">
         <v>45803</v>
       </c>
       <c r="G79" t="s">
@@ -7724,7 +7701,7 @@
         <v>1353</v>
       </c>
       <c r="I79">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K79" t="s">
         <v>1363</v>
@@ -7749,7 +7726,7 @@
       <c r="E80" t="s">
         <v>903</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="1">
         <v>45803</v>
       </c>
       <c r="G80" t="s">
@@ -7759,7 +7736,7 @@
         <v>1353</v>
       </c>
       <c r="I80">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J80">
         <v>429</v>
@@ -7770,7 +7747,7 @@
       <c r="L80" t="s">
         <v>1383</v>
       </c>
-      <c r="N80" s="2">
+      <c r="N80" s="1">
         <v>46232</v>
       </c>
       <c r="Q80" t="b">
@@ -7793,7 +7770,7 @@
       <c r="E81" t="s">
         <v>904</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="1">
         <v>45813</v>
       </c>
       <c r="G81" t="s">
@@ -7822,7 +7799,7 @@
       <c r="E82" t="s">
         <v>905</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="1">
         <v>45813</v>
       </c>
       <c r="G82" t="s">
@@ -7832,7 +7809,7 @@
         <v>1353</v>
       </c>
       <c r="I82">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K82" t="s">
         <v>1360</v>
@@ -7860,7 +7837,7 @@
       <c r="E83" t="s">
         <v>906</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="1">
         <v>45813</v>
       </c>
       <c r="G83" t="s">
@@ -7889,7 +7866,7 @@
       <c r="E84" t="s">
         <v>907</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="1">
         <v>45813</v>
       </c>
       <c r="G84" t="s">
@@ -7899,7 +7876,7 @@
         <v>1353</v>
       </c>
       <c r="I84">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J84">
         <v>40</v>
@@ -7910,7 +7887,7 @@
       <c r="L84" t="s">
         <v>1384</v>
       </c>
-      <c r="N84" s="2">
+      <c r="N84" s="1">
         <v>45853</v>
       </c>
       <c r="O84">
@@ -7936,7 +7913,7 @@
       <c r="E85" t="s">
         <v>908</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="1">
         <v>45813</v>
       </c>
       <c r="G85" t="s">
@@ -7946,7 +7923,7 @@
         <v>1353</v>
       </c>
       <c r="I85">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K85" t="s">
         <v>1357</v>
@@ -7974,7 +7951,7 @@
       <c r="E86" t="s">
         <v>909</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="1">
         <v>45813</v>
       </c>
       <c r="G86" t="s">
@@ -7984,7 +7961,7 @@
         <v>1353</v>
       </c>
       <c r="I86">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K86" t="s">
         <v>1357</v>
@@ -8012,7 +7989,7 @@
       <c r="E87" t="s">
         <v>910</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="1">
         <v>45813</v>
       </c>
       <c r="G87" t="s">
@@ -8022,7 +7999,7 @@
         <v>1353</v>
       </c>
       <c r="I87">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J87">
         <v>-16</v>
@@ -8033,7 +8010,7 @@
       <c r="L87" t="s">
         <v>1385</v>
       </c>
-      <c r="N87" s="2">
+      <c r="N87" s="1">
         <v>45797</v>
       </c>
       <c r="O87" t="s">
@@ -8059,7 +8036,7 @@
       <c r="E88" t="s">
         <v>911</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="1">
         <v>45813</v>
       </c>
       <c r="G88" t="s">
@@ -8074,7 +8051,7 @@
       <c r="L88" t="s">
         <v>1386</v>
       </c>
-      <c r="N88" s="2">
+      <c r="N88" s="1">
         <v>46195</v>
       </c>
       <c r="Q88" t="b">
@@ -8097,7 +8074,7 @@
       <c r="E89" t="s">
         <v>912</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="1">
         <v>45813</v>
       </c>
       <c r="G89" t="s">
@@ -8112,7 +8089,7 @@
       <c r="L89" t="s">
         <v>1386</v>
       </c>
-      <c r="N89" s="2">
+      <c r="N89" s="1">
         <v>46195</v>
       </c>
       <c r="Q89" t="b">
@@ -8135,7 +8112,7 @@
       <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="1">
         <v>45831</v>
       </c>
       <c r="G90" t="s">
@@ -8145,7 +8122,7 @@
         <v>1353</v>
       </c>
       <c r="I90">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K90" t="s">
         <v>1330</v>
@@ -8176,7 +8153,7 @@
       <c r="E91" t="s">
         <v>914</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="1">
         <v>45831</v>
       </c>
       <c r="G91" t="s">
@@ -8186,7 +8163,7 @@
         <v>1353</v>
       </c>
       <c r="I91">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J91">
         <v>308</v>
@@ -8197,7 +8174,7 @@
       <c r="L91" t="s">
         <v>1388</v>
       </c>
-      <c r="N91" s="2">
+      <c r="N91" s="1">
         <v>46139</v>
       </c>
       <c r="Q91" t="b">
@@ -8217,7 +8194,7 @@
       <c r="D92" t="s">
         <v>748</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="1">
         <v>45831</v>
       </c>
       <c r="G92" t="s">
@@ -8246,7 +8223,7 @@
       <c r="E93" t="s">
         <v>915</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="1">
         <v>45831</v>
       </c>
       <c r="G93" t="s">
@@ -8256,7 +8233,7 @@
         <v>1353</v>
       </c>
       <c r="I93">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J93">
         <v>308</v>
@@ -8267,7 +8244,7 @@
       <c r="L93" t="s">
         <v>1388</v>
       </c>
-      <c r="N93" s="2">
+      <c r="N93" s="1">
         <v>46139</v>
       </c>
       <c r="Q93" t="b">
@@ -8290,7 +8267,7 @@
       <c r="E94" t="s">
         <v>916</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="1">
         <v>45831</v>
       </c>
       <c r="G94" t="s">
@@ -8300,7 +8277,7 @@
         <v>1353</v>
       </c>
       <c r="I94">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K94" t="s">
         <v>1360</v>
@@ -8328,7 +8305,7 @@
       <c r="E95" t="s">
         <v>917</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="1">
         <v>45831</v>
       </c>
       <c r="G95" t="s">
@@ -8338,7 +8315,7 @@
         <v>1353</v>
       </c>
       <c r="I95">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J95">
         <v>308</v>
@@ -8349,7 +8326,7 @@
       <c r="L95" t="s">
         <v>1388</v>
       </c>
-      <c r="N95" s="2">
+      <c r="N95" s="1">
         <v>46139</v>
       </c>
       <c r="Q95" t="b">
@@ -8372,7 +8349,7 @@
       <c r="E96" t="s">
         <v>918</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="1">
         <v>45831</v>
       </c>
       <c r="G96" t="s">
@@ -8382,7 +8359,7 @@
         <v>1353</v>
       </c>
       <c r="I96">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J96">
         <v>17</v>
@@ -8393,7 +8370,7 @@
       <c r="L96" t="s">
         <v>1369</v>
       </c>
-      <c r="N96" s="2">
+      <c r="N96" s="1">
         <v>45848</v>
       </c>
       <c r="O96" t="s">
@@ -8419,7 +8396,7 @@
       <c r="E97" t="s">
         <v>919</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="1">
         <v>45840</v>
       </c>
       <c r="G97" t="s">
@@ -8429,7 +8406,7 @@
         <v>1353</v>
       </c>
       <c r="I97">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J97">
         <v>20</v>
@@ -8440,7 +8417,7 @@
       <c r="L97" t="s">
         <v>1389</v>
       </c>
-      <c r="N97" s="2">
+      <c r="N97" s="1">
         <v>45860</v>
       </c>
       <c r="P97" t="s">
@@ -8466,7 +8443,7 @@
       <c r="E98" t="s">
         <v>920</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="1">
         <v>45840</v>
       </c>
       <c r="G98" t="s">
@@ -8476,7 +8453,7 @@
         <v>1353</v>
       </c>
       <c r="I98">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K98" t="s">
         <v>1360</v>
@@ -8504,7 +8481,7 @@
       <c r="E99" t="s">
         <v>921</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="1">
         <v>45840</v>
       </c>
       <c r="G99" t="s">
@@ -8533,7 +8510,7 @@
       <c r="E100" t="s">
         <v>922</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="1">
         <v>45840</v>
       </c>
       <c r="G100" t="s">
@@ -8543,7 +8520,7 @@
         <v>1353</v>
       </c>
       <c r="I100">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J100">
         <v>348</v>
@@ -8554,7 +8531,7 @@
       <c r="L100" t="s">
         <v>1388</v>
       </c>
-      <c r="N100" s="2">
+      <c r="N100" s="1">
         <v>46188</v>
       </c>
       <c r="Q100" t="b">
@@ -8577,7 +8554,7 @@
       <c r="E101" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="1">
         <v>45840</v>
       </c>
       <c r="G101" t="s">
@@ -8606,7 +8583,7 @@
       <c r="E102" t="s">
         <v>924</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="1">
         <v>45840</v>
       </c>
       <c r="G102" t="s">
@@ -8635,7 +8612,7 @@
       <c r="E103" t="s">
         <v>925</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="1">
         <v>45840</v>
       </c>
       <c r="G103" t="s">
@@ -8664,7 +8641,7 @@
       <c r="E104" t="s">
         <v>926</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="1">
         <v>45840</v>
       </c>
       <c r="G104" t="s">
@@ -8674,7 +8651,7 @@
         <v>1353</v>
       </c>
       <c r="I104">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J104">
         <v>348</v>
@@ -8685,7 +8662,7 @@
       <c r="L104" t="s">
         <v>1388</v>
       </c>
-      <c r="N104" s="2">
+      <c r="N104" s="1">
         <v>46188</v>
       </c>
       <c r="Q104" t="b">
@@ -8708,7 +8685,7 @@
       <c r="E105" t="s">
         <v>927</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="1">
         <v>45840</v>
       </c>
       <c r="G105" t="s">
@@ -8718,7 +8695,7 @@
         <v>1353</v>
       </c>
       <c r="I105">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J105">
         <v>348</v>
@@ -8729,7 +8706,7 @@
       <c r="L105" t="s">
         <v>1388</v>
       </c>
-      <c r="N105" s="2">
+      <c r="N105" s="1">
         <v>46188</v>
       </c>
       <c r="Q105" t="b">
@@ -8752,7 +8729,7 @@
       <c r="E106" t="s">
         <v>928</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="1">
         <v>45840</v>
       </c>
       <c r="G106" t="s">
@@ -8762,7 +8739,7 @@
         <v>1353</v>
       </c>
       <c r="I106">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J106">
         <v>49</v>
@@ -8773,7 +8750,7 @@
       <c r="L106" t="s">
         <v>1390</v>
       </c>
-      <c r="N106" s="2">
+      <c r="N106" s="1">
         <v>45889</v>
       </c>
       <c r="Q106" t="b">
@@ -8796,7 +8773,7 @@
       <c r="E107" t="s">
         <v>929</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="1">
         <v>45840</v>
       </c>
       <c r="G107" t="s">
@@ -8806,7 +8783,7 @@
         <v>1353</v>
       </c>
       <c r="I107">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J107">
         <v>36</v>
@@ -8817,7 +8794,7 @@
       <c r="L107" t="s">
         <v>1391</v>
       </c>
-      <c r="N107" s="2">
+      <c r="N107" s="1">
         <v>45876</v>
       </c>
       <c r="Q107" t="b">
@@ -8840,7 +8817,7 @@
       <c r="E108" t="s">
         <v>930</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="1">
         <v>45840</v>
       </c>
       <c r="G108" t="s">
@@ -8850,7 +8827,7 @@
         <v>1353</v>
       </c>
       <c r="I108">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K108" t="s">
         <v>1357</v>
@@ -8878,7 +8855,7 @@
       <c r="E109" t="s">
         <v>931</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="1">
         <v>45840</v>
       </c>
       <c r="G109" t="s">
@@ -8888,7 +8865,7 @@
         <v>1353</v>
       </c>
       <c r="I109">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K109" t="s">
         <v>1357</v>
@@ -8916,7 +8893,7 @@
       <c r="E110" t="s">
         <v>932</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="1">
         <v>45840</v>
       </c>
       <c r="G110" t="s">
@@ -8945,7 +8922,7 @@
       <c r="E111" t="s">
         <v>933</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="1">
         <v>45840</v>
       </c>
       <c r="G111" t="s">
@@ -8974,7 +8951,7 @@
       <c r="E112" t="s">
         <v>934</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="1">
         <v>45840</v>
       </c>
       <c r="G112" t="s">
@@ -9003,7 +8980,7 @@
       <c r="E113" t="s">
         <v>935</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="1">
         <v>45840</v>
       </c>
       <c r="G113" t="s">
@@ -9032,7 +9009,7 @@
       <c r="E114" t="s">
         <v>936</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="1">
         <v>45840</v>
       </c>
       <c r="G114" t="s">
@@ -9061,7 +9038,7 @@
       <c r="E115" t="s">
         <v>937</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="1">
         <v>45840</v>
       </c>
       <c r="G115" t="s">
@@ -9071,7 +9048,7 @@
         <v>1353</v>
       </c>
       <c r="I115">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K115" t="s">
         <v>1357</v>
@@ -9099,7 +9076,7 @@
       <c r="E116" t="s">
         <v>938</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="1">
         <v>45840</v>
       </c>
       <c r="G116" t="s">
@@ -9109,7 +9086,7 @@
         <v>1353</v>
       </c>
       <c r="I116">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K116" t="s">
         <v>1357</v>
@@ -9137,7 +9114,7 @@
       <c r="E117" t="s">
         <v>939</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="1">
         <v>45840</v>
       </c>
       <c r="G117" t="s">
@@ -9147,7 +9124,7 @@
         <v>1353</v>
       </c>
       <c r="I117">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K117" t="s">
         <v>1357</v>
@@ -9175,7 +9152,7 @@
       <c r="E118" t="s">
         <v>940</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="1">
         <v>45840</v>
       </c>
       <c r="G118" t="s">
@@ -9185,7 +9162,7 @@
         <v>1353</v>
       </c>
       <c r="I118">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K118" t="s">
         <v>1357</v>
@@ -9213,7 +9190,7 @@
       <c r="E119" t="s">
         <v>941</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="1">
         <v>45840</v>
       </c>
       <c r="G119" t="s">
@@ -9223,7 +9200,7 @@
         <v>1353</v>
       </c>
       <c r="I119">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K119" t="s">
         <v>1357</v>
@@ -9251,7 +9228,7 @@
       <c r="E120" t="s">
         <v>942</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="1">
         <v>45840</v>
       </c>
       <c r="G120" t="s">
@@ -9261,7 +9238,7 @@
         <v>1353</v>
       </c>
       <c r="I120">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K120" t="s">
         <v>1357</v>
@@ -9289,7 +9266,7 @@
       <c r="E121" t="s">
         <v>943</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="1">
         <v>45849</v>
       </c>
       <c r="G121" t="s">
@@ -9299,7 +9276,7 @@
         <v>1353</v>
       </c>
       <c r="I121">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J121">
         <v>251</v>
@@ -9310,7 +9287,7 @@
       <c r="L121" t="s">
         <v>1379</v>
       </c>
-      <c r="N121" s="2">
+      <c r="N121" s="1">
         <v>46100</v>
       </c>
       <c r="O121">
@@ -9336,7 +9313,7 @@
       <c r="E122" t="s">
         <v>944</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="1">
         <v>45849</v>
       </c>
       <c r="G122" t="s">
@@ -9346,7 +9323,7 @@
         <v>1353</v>
       </c>
       <c r="I122">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K122" t="s">
         <v>1357</v>
@@ -9374,7 +9351,7 @@
       <c r="E123" t="s">
         <v>945</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="1">
         <v>45849</v>
       </c>
       <c r="G123" t="s">
@@ -9403,7 +9380,7 @@
       <c r="E124" t="s">
         <v>946</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="1">
         <v>45853</v>
       </c>
       <c r="G124" t="s">
@@ -9413,7 +9390,7 @@
         <v>1353</v>
       </c>
       <c r="I124">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K124" t="s">
         <v>1357</v>
@@ -9441,7 +9418,7 @@
       <c r="E125" t="s">
         <v>947</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="1">
         <v>45855</v>
       </c>
       <c r="G125" t="s">
@@ -9451,7 +9428,7 @@
         <v>1353</v>
       </c>
       <c r="I125">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K125" t="s">
         <v>1363</v>
@@ -9479,7 +9456,7 @@
       <c r="E126" t="s">
         <v>948</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="1">
         <v>45855</v>
       </c>
       <c r="G126" t="s">
@@ -9508,7 +9485,7 @@
       <c r="E127" t="s">
         <v>949</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="1">
         <v>45856</v>
       </c>
       <c r="G127" t="s">
@@ -9537,7 +9514,7 @@
       <c r="E128" t="s">
         <v>950</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="1">
         <v>45869</v>
       </c>
       <c r="G128" t="s">
@@ -9547,7 +9524,7 @@
         <v>1353</v>
       </c>
       <c r="I128">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K128" t="s">
         <v>1357</v>
@@ -9575,7 +9552,7 @@
       <c r="E129" t="s">
         <v>951</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="1">
         <v>45869</v>
       </c>
       <c r="G129" t="s">
@@ -9585,7 +9562,7 @@
         <v>1353</v>
       </c>
       <c r="I129">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K129" t="s">
         <v>1356</v>
@@ -9613,7 +9590,7 @@
       <c r="E130" t="s">
         <v>952</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="1">
         <v>45869</v>
       </c>
       <c r="G130" t="s">
@@ -9623,7 +9600,7 @@
         <v>1353</v>
       </c>
       <c r="I130">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J130">
         <v>47</v>
@@ -9634,7 +9611,7 @@
       <c r="L130" t="s">
         <v>1392</v>
       </c>
-      <c r="N130" s="2">
+      <c r="N130" s="1">
         <v>45916</v>
       </c>
       <c r="O130">
@@ -9660,7 +9637,7 @@
       <c r="E131" t="s">
         <v>953</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="1">
         <v>45869</v>
       </c>
       <c r="G131" t="s">
@@ -9689,7 +9666,7 @@
       <c r="E132" t="s">
         <v>954</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="1">
         <v>45869</v>
       </c>
       <c r="G132" t="s">
@@ -9699,7 +9676,7 @@
         <v>1353</v>
       </c>
       <c r="I132">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J132">
         <v>145</v>
@@ -9710,7 +9687,7 @@
       <c r="L132" t="s">
         <v>1393</v>
       </c>
-      <c r="N132" s="2">
+      <c r="N132" s="1">
         <v>46014</v>
       </c>
       <c r="O132">
@@ -9736,7 +9713,7 @@
       <c r="E133" t="s">
         <v>955</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="1">
         <v>45869</v>
       </c>
       <c r="G133" t="s">
@@ -9765,7 +9742,7 @@
       <c r="E134" t="s">
         <v>956</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="1">
         <v>45882</v>
       </c>
       <c r="G134" t="s">
@@ -9775,7 +9752,7 @@
         <v>1353</v>
       </c>
       <c r="I134">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K134" t="s">
         <v>1356</v>
@@ -9803,7 +9780,7 @@
       <c r="E135" t="s">
         <v>957</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="1">
         <v>45882</v>
       </c>
       <c r="G135" t="s">
@@ -9832,7 +9809,7 @@
       <c r="E136" t="s">
         <v>958</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="1">
         <v>45891</v>
       </c>
       <c r="G136" t="s">
@@ -9861,7 +9838,7 @@
       <c r="E137" t="s">
         <v>959</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="1">
         <v>45891</v>
       </c>
       <c r="G137" t="s">
@@ -9890,7 +9867,7 @@
       <c r="E138" t="s">
         <v>960</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="1">
         <v>45891</v>
       </c>
       <c r="G138" t="s">
@@ -9900,7 +9877,7 @@
         <v>1353</v>
       </c>
       <c r="I138">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K138" t="s">
         <v>1357</v>
@@ -9928,7 +9905,7 @@
       <c r="E139" t="s">
         <v>961</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="1">
         <v>45891</v>
       </c>
       <c r="G139" t="s">
@@ -9957,7 +9934,7 @@
       <c r="E140" t="s">
         <v>962</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="1">
         <v>45891</v>
       </c>
       <c r="G140" t="s">
@@ -9986,7 +9963,7 @@
       <c r="E141" t="s">
         <v>963</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="1">
         <v>45891</v>
       </c>
       <c r="G141" t="s">
@@ -10015,7 +9992,7 @@
       <c r="E142" t="s">
         <v>964</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="1">
         <v>45891</v>
       </c>
       <c r="G142" t="s">
@@ -10044,7 +10021,7 @@
       <c r="E143" t="s">
         <v>965</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="1">
         <v>45891</v>
       </c>
       <c r="G143" t="s">
@@ -10073,7 +10050,7 @@
       <c r="E144" t="s">
         <v>966</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="1">
         <v>45891</v>
       </c>
       <c r="G144" t="s">
@@ -10102,7 +10079,7 @@
       <c r="E145" t="s">
         <v>967</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="1">
         <v>45891</v>
       </c>
       <c r="G145" t="s">
@@ -10131,7 +10108,7 @@
       <c r="E146" t="s">
         <v>968</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="1">
         <v>45891</v>
       </c>
       <c r="G146" t="s">
@@ -10160,7 +10137,7 @@
       <c r="E147" t="s">
         <v>969</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="1">
         <v>45891</v>
       </c>
       <c r="G147" t="s">
@@ -10189,7 +10166,7 @@
       <c r="E148" t="s">
         <v>970</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="1">
         <v>45891</v>
       </c>
       <c r="G148" t="s">
@@ -10199,7 +10176,7 @@
         <v>1353</v>
       </c>
       <c r="I148">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J148">
         <v>341</v>
@@ -10210,7 +10187,7 @@
       <c r="L148" t="s">
         <v>1383</v>
       </c>
-      <c r="N148" s="2">
+      <c r="N148" s="1">
         <v>46232</v>
       </c>
       <c r="Q148" t="b">
@@ -10233,7 +10210,7 @@
       <c r="E149" t="s">
         <v>971</v>
       </c>
-      <c r="F149" s="2">
+      <c r="F149" s="1">
         <v>45891</v>
       </c>
       <c r="G149" t="s">
@@ -10243,7 +10220,7 @@
         <v>1353</v>
       </c>
       <c r="I149">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J149">
         <v>374</v>
@@ -10254,7 +10231,7 @@
       <c r="L149" t="s">
         <v>1394</v>
       </c>
-      <c r="N149" s="2">
+      <c r="N149" s="1">
         <v>46265</v>
       </c>
       <c r="P149" t="s">
@@ -10280,7 +10257,7 @@
       <c r="E150" t="s">
         <v>972</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="1">
         <v>45891</v>
       </c>
       <c r="G150" t="s">
@@ -10290,7 +10267,7 @@
         <v>1353</v>
       </c>
       <c r="I150">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J150">
         <v>201</v>
@@ -10301,7 +10278,7 @@
       <c r="L150" t="s">
         <v>1381</v>
       </c>
-      <c r="N150" s="2">
+      <c r="N150" s="1">
         <v>46092</v>
       </c>
       <c r="P150" t="s">
@@ -10327,7 +10304,7 @@
       <c r="E151" t="s">
         <v>973</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="1">
         <v>45891</v>
       </c>
       <c r="G151" t="s">
@@ -10356,7 +10333,7 @@
       <c r="E152" t="s">
         <v>963</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="1">
         <v>45891</v>
       </c>
       <c r="G152" t="s">
@@ -10366,7 +10343,7 @@
         <v>1353</v>
       </c>
       <c r="I152">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J152">
         <v>228</v>
@@ -10377,7 +10354,7 @@
       <c r="L152" t="s">
         <v>1382</v>
       </c>
-      <c r="N152" s="2">
+      <c r="N152" s="1">
         <v>46119</v>
       </c>
       <c r="Q152" t="b">
@@ -10400,7 +10377,7 @@
       <c r="E153" t="s">
         <v>974</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="1">
         <v>45891</v>
       </c>
       <c r="G153" t="s">
@@ -10418,7 +10395,7 @@
       <c r="L153" t="s">
         <v>1383</v>
       </c>
-      <c r="N153" s="2">
+      <c r="N153" s="1">
         <v>46232</v>
       </c>
       <c r="Q153" t="b">
@@ -10441,7 +10418,7 @@
       <c r="E154" t="s">
         <v>975</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="1">
         <v>45891</v>
       </c>
       <c r="G154" t="s">
@@ -10470,7 +10447,7 @@
       <c r="E155" t="s">
         <v>976</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="1">
         <v>45891</v>
       </c>
       <c r="G155" t="s">
@@ -10480,7 +10457,7 @@
         <v>1353</v>
       </c>
       <c r="I155">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K155" t="s">
         <v>1363</v>
@@ -10505,7 +10482,7 @@
       <c r="E156" t="s">
         <v>977</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="1">
         <v>45891</v>
       </c>
       <c r="G156" t="s">
@@ -10515,7 +10492,7 @@
         <v>1353</v>
       </c>
       <c r="I156">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K156" t="s">
         <v>1357</v>
@@ -10543,7 +10520,7 @@
       <c r="E157" t="s">
         <v>978</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="1">
         <v>45891</v>
       </c>
       <c r="G157" t="s">
@@ -10553,7 +10530,7 @@
         <v>1353</v>
       </c>
       <c r="I157">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J157">
         <v>371</v>
@@ -10564,7 +10541,7 @@
       <c r="L157" t="s">
         <v>1395</v>
       </c>
-      <c r="N157" s="2">
+      <c r="N157" s="1">
         <v>46262</v>
       </c>
       <c r="Q157" t="b">
@@ -10587,7 +10564,7 @@
       <c r="E158" t="s">
         <v>979</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="1">
         <v>45894</v>
       </c>
       <c r="G158" t="s">
@@ -10597,7 +10574,7 @@
         <v>1353</v>
       </c>
       <c r="I158">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J158">
         <v>52</v>
@@ -10608,7 +10585,7 @@
       <c r="L158" t="s">
         <v>1396</v>
       </c>
-      <c r="N158" s="2">
+      <c r="N158" s="1">
         <v>45946</v>
       </c>
       <c r="Q158" t="b">
@@ -10631,7 +10608,7 @@
       <c r="E159" t="s">
         <v>980</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="1">
         <v>45894</v>
       </c>
       <c r="G159" t="s">
@@ -10641,7 +10618,7 @@
         <v>1353</v>
       </c>
       <c r="I159">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K159" t="s">
         <v>1357</v>
@@ -10669,7 +10646,7 @@
       <c r="E160" t="s">
         <v>981</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="1">
         <v>45898</v>
       </c>
       <c r="G160" t="s">
@@ -10679,7 +10656,7 @@
         <v>1353</v>
       </c>
       <c r="I160">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K160" t="s">
         <v>1357</v>
@@ -10707,7 +10684,7 @@
       <c r="E161" t="s">
         <v>982</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="1">
         <v>45898</v>
       </c>
       <c r="G161" t="s">
@@ -10717,7 +10694,7 @@
         <v>1353</v>
       </c>
       <c r="I161">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J161">
         <v>55</v>
@@ -10728,7 +10705,7 @@
       <c r="L161" t="s">
         <v>1397</v>
       </c>
-      <c r="N161" s="2">
+      <c r="N161" s="1">
         <v>45953</v>
       </c>
       <c r="O161" t="s">
@@ -10754,7 +10731,7 @@
       <c r="E162" t="s">
         <v>983</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="1">
         <v>45898</v>
       </c>
       <c r="G162" t="s">
@@ -10764,7 +10741,7 @@
         <v>1353</v>
       </c>
       <c r="I162">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J162">
         <v>42</v>
@@ -10775,7 +10752,7 @@
       <c r="L162" t="s">
         <v>1398</v>
       </c>
-      <c r="N162" s="2">
+      <c r="N162" s="1">
         <v>45940</v>
       </c>
       <c r="P162" t="s">
@@ -10801,7 +10778,7 @@
       <c r="E163" t="s">
         <v>984</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="1">
         <v>45898</v>
       </c>
       <c r="G163" t="s">
@@ -10811,7 +10788,7 @@
         <v>1353</v>
       </c>
       <c r="I163">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J163">
         <v>42</v>
@@ -10822,7 +10799,7 @@
       <c r="L163" t="s">
         <v>1398</v>
       </c>
-      <c r="N163" s="2">
+      <c r="N163" s="1">
         <v>45940</v>
       </c>
       <c r="P163" t="s">
@@ -10848,7 +10825,7 @@
       <c r="E164" t="s">
         <v>985</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="1">
         <v>45910</v>
       </c>
       <c r="G164" t="s">
@@ -10858,7 +10835,7 @@
         <v>1355</v>
       </c>
       <c r="I164">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O164" t="s">
         <v>1469</v>
@@ -10883,7 +10860,7 @@
       <c r="E165" t="s">
         <v>986</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="1">
         <v>45917</v>
       </c>
       <c r="G165" t="s">
@@ -10901,7 +10878,7 @@
       <c r="L165" t="s">
         <v>1399</v>
       </c>
-      <c r="N165" s="2">
+      <c r="N165" s="1">
         <v>46204</v>
       </c>
       <c r="P165" t="s">
@@ -10927,7 +10904,7 @@
       <c r="E166" t="s">
         <v>987</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="1">
         <v>45917</v>
       </c>
       <c r="G166" t="s">
@@ -10956,7 +10933,7 @@
       <c r="E167" t="s">
         <v>988</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="1">
         <v>45917</v>
       </c>
       <c r="G167" t="s">
@@ -10985,7 +10962,7 @@
       <c r="E168" t="s">
         <v>989</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="1">
         <v>45917</v>
       </c>
       <c r="G168" t="s">
@@ -10995,7 +10972,7 @@
         <v>1353</v>
       </c>
       <c r="I168">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K168" t="s">
         <v>1360</v>
@@ -11026,7 +11003,7 @@
       <c r="E169" t="s">
         <v>990</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="1">
         <v>45917</v>
       </c>
       <c r="G169" t="s">
@@ -11036,7 +11013,7 @@
         <v>1353</v>
       </c>
       <c r="I169">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K169" t="s">
         <v>1330</v>
@@ -11044,7 +11021,7 @@
       <c r="L169" t="s">
         <v>1401</v>
       </c>
-      <c r="N169" s="2">
+      <c r="N169" s="1">
         <v>45973</v>
       </c>
       <c r="Q169" t="b">
@@ -11067,7 +11044,7 @@
       <c r="E170" t="s">
         <v>991</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="1">
         <v>45917</v>
       </c>
       <c r="G170" t="s">
@@ -11102,7 +11079,7 @@
       <c r="E171" t="s">
         <v>992</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="1">
         <v>45917</v>
       </c>
       <c r="G171" t="s">
@@ -11112,13 +11089,16 @@
         <v>1353</v>
       </c>
       <c r="I171">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K171" t="s">
         <v>1357</v>
       </c>
       <c r="M171" t="s">
         <v>1454</v>
+      </c>
+      <c r="P171" t="s">
+        <v>1482</v>
       </c>
       <c r="Q171" t="b">
         <v>1</v>
@@ -11140,7 +11120,7 @@
       <c r="E172" t="s">
         <v>993</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="1">
         <v>45917</v>
       </c>
       <c r="G172" t="s">
@@ -11169,7 +11149,7 @@
       <c r="E173" t="s">
         <v>994</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="1">
         <v>45917</v>
       </c>
       <c r="G173" t="s">
@@ -11198,7 +11178,7 @@
       <c r="E174" t="s">
         <v>995</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="1">
         <v>45917</v>
       </c>
       <c r="G174" t="s">
@@ -11213,7 +11193,7 @@
       <c r="L174" t="s">
         <v>1386</v>
       </c>
-      <c r="N174" s="2">
+      <c r="N174" s="1">
         <v>46195</v>
       </c>
       <c r="Q174" t="b">
@@ -11236,7 +11216,7 @@
       <c r="E175" t="s">
         <v>996</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="1">
         <v>45917</v>
       </c>
       <c r="G175" t="s">
@@ -11246,7 +11226,7 @@
         <v>1353</v>
       </c>
       <c r="I175">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J175">
         <v>205</v>
@@ -11257,11 +11237,11 @@
       <c r="L175" t="s">
         <v>1402</v>
       </c>
-      <c r="N175" s="2">
+      <c r="N175" s="1">
         <v>46122</v>
       </c>
       <c r="P175" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="Q175" t="b">
         <v>1</v>
@@ -11283,7 +11263,7 @@
       <c r="E176" t="s">
         <v>900</v>
       </c>
-      <c r="F176" s="2">
+      <c r="F176" s="1">
         <v>45917</v>
       </c>
       <c r="G176" t="s">
@@ -11293,7 +11273,7 @@
         <v>1353</v>
       </c>
       <c r="I176">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K176" t="s">
         <v>1357</v>
@@ -11321,7 +11301,7 @@
       <c r="E177" t="s">
         <v>997</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="1">
         <v>45917</v>
       </c>
       <c r="G177" t="s">
@@ -11331,7 +11311,7 @@
         <v>1353</v>
       </c>
       <c r="I177">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J177">
         <v>44</v>
@@ -11342,11 +11322,11 @@
       <c r="L177" t="s">
         <v>1403</v>
       </c>
-      <c r="N177" s="2">
+      <c r="N177" s="1">
         <v>45961</v>
       </c>
       <c r="P177" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="Q177" t="b">
         <v>1</v>
@@ -11368,7 +11348,7 @@
       <c r="E178" t="s">
         <v>998</v>
       </c>
-      <c r="F178" s="2">
+      <c r="F178" s="1">
         <v>45937</v>
       </c>
       <c r="G178" t="s">
@@ -11378,7 +11358,7 @@
         <v>1353</v>
       </c>
       <c r="I178">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K178" t="s">
         <v>1356</v>
@@ -11406,7 +11386,7 @@
       <c r="E179" t="s">
         <v>999</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="1">
         <v>45937</v>
       </c>
       <c r="G179" t="s">
@@ -11435,7 +11415,7 @@
       <c r="E180" t="s">
         <v>1000</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="1">
         <v>45937</v>
       </c>
       <c r="G180" t="s">
@@ -11445,7 +11425,7 @@
         <v>1353</v>
       </c>
       <c r="I180">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K180" t="s">
         <v>1356</v>
@@ -11473,7 +11453,7 @@
       <c r="E181" t="s">
         <v>1001</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="1">
         <v>45937</v>
       </c>
       <c r="G181" t="s">
@@ -11502,7 +11482,7 @@
       <c r="E182" t="s">
         <v>1002</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="1">
         <v>45937</v>
       </c>
       <c r="G182" t="s">
@@ -11531,7 +11511,7 @@
       <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="F183" s="2">
+      <c r="F183" s="1">
         <v>45937</v>
       </c>
       <c r="G183" t="s">
@@ -11541,7 +11521,7 @@
         <v>1353</v>
       </c>
       <c r="I183">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K183" t="s">
         <v>1357</v>
@@ -11569,7 +11549,7 @@
       <c r="D184" t="s">
         <v>774</v>
       </c>
-      <c r="F184" s="2">
+      <c r="F184" s="1">
         <v>45939</v>
       </c>
       <c r="G184" t="s">
@@ -11579,7 +11559,7 @@
         <v>1353</v>
       </c>
       <c r="I184">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K184" t="s">
         <v>1363</v>
@@ -11604,7 +11584,7 @@
       <c r="E185" t="s">
         <v>1004</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="1">
         <v>45939</v>
       </c>
       <c r="G185" t="s">
@@ -11614,7 +11594,7 @@
         <v>1353</v>
       </c>
       <c r="I185">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K185" t="s">
         <v>1357</v>
@@ -11642,7 +11622,7 @@
       <c r="E186" t="s">
         <v>1005</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="1">
         <v>45939</v>
       </c>
       <c r="G186" t="s">
@@ -11652,7 +11632,7 @@
         <v>1353</v>
       </c>
       <c r="I186">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K186" t="s">
         <v>1357</v>
@@ -11680,7 +11660,7 @@
       <c r="E187" t="s">
         <v>1006</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="1">
         <v>45939</v>
       </c>
       <c r="G187" t="s">
@@ -11690,7 +11670,7 @@
         <v>1353</v>
       </c>
       <c r="I187">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J187">
         <v>75</v>
@@ -11701,7 +11681,7 @@
       <c r="L187" t="s">
         <v>1404</v>
       </c>
-      <c r="N187" s="2">
+      <c r="N187" s="1">
         <v>46014</v>
       </c>
       <c r="O187">
@@ -11727,7 +11707,7 @@
       <c r="E188" t="s">
         <v>1007</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="1">
         <v>45946</v>
       </c>
       <c r="G188" t="s">
@@ -11737,7 +11717,7 @@
         <v>1353</v>
       </c>
       <c r="I188">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J188">
         <v>40</v>
@@ -11748,11 +11728,11 @@
       <c r="L188" t="s">
         <v>1405</v>
       </c>
-      <c r="N188" s="2">
+      <c r="N188" s="1">
         <v>45986</v>
       </c>
       <c r="P188" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="Q188" t="b">
         <v>1</v>
@@ -11774,7 +11754,7 @@
       <c r="E189" t="s">
         <v>1008</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="1">
         <v>45965</v>
       </c>
       <c r="G189" t="s">
@@ -11784,7 +11764,7 @@
         <v>1353</v>
       </c>
       <c r="I189">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J189">
         <v>155</v>
@@ -11795,7 +11775,7 @@
       <c r="L189" t="s">
         <v>1406</v>
       </c>
-      <c r="N189" s="2">
+      <c r="N189" s="1">
         <v>46120</v>
       </c>
       <c r="Q189" t="b">
@@ -11818,7 +11798,7 @@
       <c r="E190" t="s">
         <v>1009</v>
       </c>
-      <c r="F190" s="2">
+      <c r="F190" s="1">
         <v>45965</v>
       </c>
       <c r="G190" t="s">
@@ -11828,7 +11808,7 @@
         <v>1353</v>
       </c>
       <c r="I190">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J190">
         <v>107</v>
@@ -11839,7 +11819,7 @@
       <c r="L190" t="s">
         <v>1407</v>
       </c>
-      <c r="N190" s="2">
+      <c r="N190" s="1">
         <v>46072</v>
       </c>
       <c r="Q190" t="b">
@@ -11862,7 +11842,7 @@
       <c r="E191" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="2">
+      <c r="F191" s="1">
         <v>45967</v>
       </c>
       <c r="G191" t="s">
@@ -11872,7 +11852,7 @@
         <v>1353</v>
       </c>
       <c r="I191">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J191">
         <v>5</v>
@@ -11883,7 +11863,7 @@
       <c r="L191" t="s">
         <v>1408</v>
       </c>
-      <c r="N191" s="2">
+      <c r="N191" s="1">
         <v>45972</v>
       </c>
       <c r="Q191" t="b">
@@ -11906,7 +11886,7 @@
       <c r="E192" t="s">
         <v>1011</v>
       </c>
-      <c r="F192" s="2">
+      <c r="F192" s="1">
         <v>45968</v>
       </c>
       <c r="G192" t="s">
@@ -11916,7 +11896,7 @@
         <v>1353</v>
       </c>
       <c r="I192">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K192" t="s">
         <v>1357</v>
@@ -11944,7 +11924,7 @@
       <c r="E193" t="s">
         <v>1012</v>
       </c>
-      <c r="F193" s="2">
+      <c r="F193" s="1">
         <v>45968</v>
       </c>
       <c r="G193" t="s">
@@ -11954,7 +11934,7 @@
         <v>1353</v>
       </c>
       <c r="I193">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K193" t="s">
         <v>1362</v>
@@ -11982,7 +11962,7 @@
       <c r="E194" t="s">
         <v>1013</v>
       </c>
-      <c r="F194" s="2">
+      <c r="F194" s="1">
         <v>45968</v>
       </c>
       <c r="G194" t="s">
@@ -12011,7 +11991,7 @@
       <c r="E195" t="s">
         <v>1014</v>
       </c>
-      <c r="F195" s="2">
+      <c r="F195" s="1">
         <v>45971</v>
       </c>
       <c r="G195" t="s">
@@ -12021,7 +12001,7 @@
         <v>1353</v>
       </c>
       <c r="I195">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J195">
         <v>186</v>
@@ -12032,7 +12012,7 @@
       <c r="L195" t="s">
         <v>1409</v>
       </c>
-      <c r="N195" s="2">
+      <c r="N195" s="1">
         <v>46157</v>
       </c>
       <c r="Q195" t="b">
@@ -12055,7 +12035,7 @@
       <c r="E196" t="s">
         <v>1015</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="1">
         <v>45978</v>
       </c>
       <c r="G196" t="s">
@@ -12084,7 +12064,7 @@
       <c r="E197" t="s">
         <v>1016</v>
       </c>
-      <c r="F197" s="2">
+      <c r="F197" s="1">
         <v>45978</v>
       </c>
       <c r="G197" t="s">
@@ -12113,7 +12093,7 @@
       <c r="E198" t="s">
         <v>1017</v>
       </c>
-      <c r="F198" s="2">
+      <c r="F198" s="1">
         <v>45978</v>
       </c>
       <c r="G198" t="s">
@@ -12142,7 +12122,7 @@
       <c r="E199" t="s">
         <v>1018</v>
       </c>
-      <c r="F199" s="2">
+      <c r="F199" s="1">
         <v>45979</v>
       </c>
       <c r="G199" t="s">
@@ -12152,7 +12132,7 @@
         <v>1353</v>
       </c>
       <c r="I199">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J199">
         <v>70</v>
@@ -12163,7 +12143,7 @@
       <c r="L199" t="s">
         <v>1410</v>
       </c>
-      <c r="N199" s="2">
+      <c r="N199" s="1">
         <v>46049</v>
       </c>
       <c r="Q199" t="b">
@@ -12186,7 +12166,7 @@
       <c r="E200" t="s">
         <v>1019</v>
       </c>
-      <c r="F200" s="2">
+      <c r="F200" s="1">
         <v>45986</v>
       </c>
       <c r="G200" t="s">
@@ -12196,7 +12176,7 @@
         <v>1353</v>
       </c>
       <c r="I200">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J200">
         <v>170</v>
@@ -12207,7 +12187,7 @@
       <c r="L200" t="s">
         <v>1409</v>
       </c>
-      <c r="N200" s="2">
+      <c r="N200" s="1">
         <v>46156</v>
       </c>
       <c r="Q200" t="b">
@@ -12230,7 +12210,7 @@
       <c r="E201" t="s">
         <v>1020</v>
       </c>
-      <c r="F201" s="2">
+      <c r="F201" s="1">
         <v>45986</v>
       </c>
       <c r="G201" t="s">
@@ -12240,7 +12220,7 @@
         <v>1353</v>
       </c>
       <c r="I201">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K201" t="s">
         <v>1357</v>
@@ -12268,7 +12248,7 @@
       <c r="E202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" s="2">
+      <c r="F202" s="1">
         <v>45986</v>
       </c>
       <c r="G202" t="s">
@@ -12278,7 +12258,7 @@
         <v>1353</v>
       </c>
       <c r="I202">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K202" t="s">
         <v>1357</v>
@@ -12306,7 +12286,7 @@
       <c r="E203" t="s">
         <v>1022</v>
       </c>
-      <c r="F203" s="2">
+      <c r="F203" s="1">
         <v>45986</v>
       </c>
       <c r="G203" t="s">
@@ -12324,7 +12304,7 @@
       <c r="L203" t="s">
         <v>1411</v>
       </c>
-      <c r="N203" s="2">
+      <c r="N203" s="1">
         <v>46232</v>
       </c>
       <c r="Q203" t="b">
@@ -12347,7 +12327,7 @@
       <c r="E204" t="s">
         <v>1023</v>
       </c>
-      <c r="F204" s="2">
+      <c r="F204" s="1">
         <v>45986</v>
       </c>
       <c r="G204" t="s">
@@ -12357,7 +12337,7 @@
         <v>1353</v>
       </c>
       <c r="I204">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K204" t="s">
         <v>1356</v>
@@ -12385,7 +12365,7 @@
       <c r="E205" t="s">
         <v>1024</v>
       </c>
-      <c r="F205" s="2">
+      <c r="F205" s="1">
         <v>45986</v>
       </c>
       <c r="G205" t="s">
@@ -12395,7 +12375,7 @@
         <v>1353</v>
       </c>
       <c r="I205">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K205" t="s">
         <v>1356</v>
@@ -12423,7 +12403,7 @@
       <c r="E206" t="s">
         <v>1025</v>
       </c>
-      <c r="F206" s="2">
+      <c r="F206" s="1">
         <v>45986</v>
       </c>
       <c r="G206" t="s">
@@ -12452,7 +12432,7 @@
       <c r="E207" t="s">
         <v>1026</v>
       </c>
-      <c r="F207" s="2">
+      <c r="F207" s="1">
         <v>45986</v>
       </c>
       <c r="G207" t="s">
@@ -12462,7 +12442,7 @@
         <v>1353</v>
       </c>
       <c r="I207">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J207">
         <v>167</v>
@@ -12473,7 +12453,7 @@
       <c r="L207" t="s">
         <v>1412</v>
       </c>
-      <c r="N207" s="2">
+      <c r="N207" s="1">
         <v>46153</v>
       </c>
       <c r="Q207" t="b">
@@ -12496,7 +12476,7 @@
       <c r="E208" t="s">
         <v>1027</v>
       </c>
-      <c r="F208" s="2">
+      <c r="F208" s="1">
         <v>45986</v>
       </c>
       <c r="G208" t="s">
@@ -12506,7 +12486,7 @@
         <v>1353</v>
       </c>
       <c r="I208">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J208">
         <v>45</v>
@@ -12517,7 +12497,7 @@
       <c r="L208" t="s">
         <v>1413</v>
       </c>
-      <c r="N208" s="2">
+      <c r="N208" s="1">
         <v>46031</v>
       </c>
       <c r="Q208" t="b">
@@ -12540,7 +12520,7 @@
       <c r="E209" t="s">
         <v>1028</v>
       </c>
-      <c r="F209" s="2">
+      <c r="F209" s="1">
         <v>46000</v>
       </c>
       <c r="G209" t="s">
@@ -12550,7 +12530,7 @@
         <v>1353</v>
       </c>
       <c r="I209">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J209">
         <v>191</v>
@@ -12561,7 +12541,7 @@
       <c r="L209" t="s">
         <v>1414</v>
       </c>
-      <c r="N209" s="2">
+      <c r="N209" s="1">
         <v>46191</v>
       </c>
       <c r="Q209" t="b">
@@ -12584,7 +12564,7 @@
       <c r="E210" t="s">
         <v>1029</v>
       </c>
-      <c r="F210" s="2">
+      <c r="F210" s="1">
         <v>46000</v>
       </c>
       <c r="G210" t="s">
@@ -12594,7 +12574,7 @@
         <v>1353</v>
       </c>
       <c r="I210">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K210" t="s">
         <v>1360</v>
@@ -12622,7 +12602,7 @@
       <c r="E211" t="s">
         <v>1030</v>
       </c>
-      <c r="F211" s="2">
+      <c r="F211" s="1">
         <v>46000</v>
       </c>
       <c r="G211" t="s">
@@ -12651,7 +12631,7 @@
       <c r="E212" t="s">
         <v>1031</v>
       </c>
-      <c r="F212" s="2">
+      <c r="F212" s="1">
         <v>46000</v>
       </c>
       <c r="G212" t="s">
@@ -12680,7 +12660,7 @@
       <c r="E213" t="s">
         <v>1032</v>
       </c>
-      <c r="F213" s="2">
+      <c r="F213" s="1">
         <v>46007</v>
       </c>
       <c r="G213" t="s">
@@ -12690,7 +12670,7 @@
         <v>1353</v>
       </c>
       <c r="I213">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K213" t="s">
         <v>1357</v>
@@ -12718,7 +12698,7 @@
       <c r="E214" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="2">
+      <c r="F214" s="1">
         <v>46007</v>
       </c>
       <c r="G214" t="s">
@@ -12728,7 +12708,7 @@
         <v>1353</v>
       </c>
       <c r="I214">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J214">
         <v>14</v>
@@ -12739,7 +12719,7 @@
       <c r="L214" t="s">
         <v>1415</v>
       </c>
-      <c r="N214" s="2">
+      <c r="N214" s="1">
         <v>46021</v>
       </c>
       <c r="O214">
@@ -12765,7 +12745,7 @@
       <c r="E215" t="s">
         <v>1034</v>
       </c>
-      <c r="F215" s="2">
+      <c r="F215" s="1">
         <v>46007</v>
       </c>
       <c r="G215" t="s">
@@ -12775,7 +12755,7 @@
         <v>1353</v>
       </c>
       <c r="I215">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K215" t="s">
         <v>1357</v>
@@ -12803,7 +12783,7 @@
       <c r="E216" t="s">
         <v>1035</v>
       </c>
-      <c r="F216" s="2">
+      <c r="F216" s="1">
         <v>46010</v>
       </c>
       <c r="G216" t="s">
@@ -12832,7 +12812,7 @@
       <c r="E217" t="s">
         <v>1036</v>
       </c>
-      <c r="F217" s="2">
+      <c r="F217" s="1">
         <v>46010</v>
       </c>
       <c r="G217" t="s">
@@ -12842,7 +12822,7 @@
         <v>1353</v>
       </c>
       <c r="I217">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J217">
         <v>42</v>
@@ -12853,7 +12833,7 @@
       <c r="L217" t="s">
         <v>1416</v>
       </c>
-      <c r="N217" s="2">
+      <c r="N217" s="1">
         <v>46052</v>
       </c>
       <c r="Q217" t="b">
@@ -12876,7 +12856,7 @@
       <c r="E218" t="s">
         <v>1037</v>
       </c>
-      <c r="F218" s="2">
+      <c r="F218" s="1">
         <v>46010</v>
       </c>
       <c r="G218" t="s">
@@ -12886,7 +12866,7 @@
         <v>1353</v>
       </c>
       <c r="I218">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J218">
         <v>166</v>
@@ -12894,7 +12874,7 @@
       <c r="K218" t="s">
         <v>1359</v>
       </c>
-      <c r="N218" s="2">
+      <c r="N218" s="1">
         <v>46176</v>
       </c>
       <c r="P218" t="s">
@@ -12920,7 +12900,7 @@
       <c r="E219" t="s">
         <v>1038</v>
       </c>
-      <c r="F219" s="2">
+      <c r="F219" s="1">
         <v>46010</v>
       </c>
       <c r="G219" t="s">
@@ -12938,11 +12918,11 @@
       <c r="L219" t="s">
         <v>1417</v>
       </c>
-      <c r="N219" s="2">
+      <c r="N219" s="1">
         <v>46176</v>
       </c>
       <c r="P219" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="Q219" t="b">
         <v>0</v>
@@ -12964,7 +12944,7 @@
       <c r="E220" t="s">
         <v>1039</v>
       </c>
-      <c r="F220" s="2">
+      <c r="F220" s="1">
         <v>46010</v>
       </c>
       <c r="G220" t="s">
@@ -12974,7 +12954,7 @@
         <v>1353</v>
       </c>
       <c r="I220">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J220">
         <v>154</v>
@@ -12985,7 +12965,7 @@
       <c r="L220" t="s">
         <v>1418</v>
       </c>
-      <c r="N220" s="2">
+      <c r="N220" s="1">
         <v>46164</v>
       </c>
       <c r="Q220" t="b">
@@ -13008,7 +12988,7 @@
       <c r="E221" t="s">
         <v>1040</v>
       </c>
-      <c r="F221" s="2">
+      <c r="F221" s="1">
         <v>46028</v>
       </c>
       <c r="G221" t="s">
@@ -13023,7 +13003,7 @@
       <c r="L221" t="s">
         <v>1419</v>
       </c>
-      <c r="N221" s="2">
+      <c r="N221" s="1">
         <v>46184</v>
       </c>
       <c r="Q221" t="b">
@@ -13046,7 +13026,7 @@
       <c r="E222" t="s">
         <v>1041</v>
       </c>
-      <c r="F222" s="2">
+      <c r="F222" s="1">
         <v>46028</v>
       </c>
       <c r="G222" t="s">
@@ -13061,7 +13041,7 @@
       <c r="L222" t="s">
         <v>1383</v>
       </c>
-      <c r="N222" s="2">
+      <c r="N222" s="1">
         <v>46232</v>
       </c>
       <c r="Q222" t="b">
@@ -13084,7 +13064,7 @@
       <c r="E223" t="s">
         <v>1042</v>
       </c>
-      <c r="F223" s="2">
+      <c r="F223" s="1">
         <v>46028</v>
       </c>
       <c r="G223" t="s">
@@ -13099,7 +13079,7 @@
       <c r="L223" t="s">
         <v>1383</v>
       </c>
-      <c r="N223" s="2">
+      <c r="N223" s="1">
         <v>46232</v>
       </c>
       <c r="Q223" t="b">
@@ -13122,7 +13102,7 @@
       <c r="E224" t="s">
         <v>1043</v>
       </c>
-      <c r="F224" s="2">
+      <c r="F224" s="1">
         <v>46028</v>
       </c>
       <c r="G224" t="s">
@@ -13132,7 +13112,7 @@
         <v>1353</v>
       </c>
       <c r="I224">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J224">
         <v>204</v>
@@ -13140,7 +13120,7 @@
       <c r="L224" t="s">
         <v>1383</v>
       </c>
-      <c r="N224" s="2">
+      <c r="N224" s="1">
         <v>46232</v>
       </c>
       <c r="Q224" t="b">
@@ -13163,7 +13143,7 @@
       <c r="E225" t="s">
         <v>1044</v>
       </c>
-      <c r="F225" s="2">
+      <c r="F225" s="1">
         <v>46028</v>
       </c>
       <c r="G225" t="s">
@@ -13178,7 +13158,7 @@
       <c r="L225" t="s">
         <v>1383</v>
       </c>
-      <c r="N225" s="2">
+      <c r="N225" s="1">
         <v>46232</v>
       </c>
       <c r="Q225" t="b">
@@ -13201,7 +13181,7 @@
       <c r="E226" t="s">
         <v>1045</v>
       </c>
-      <c r="F226" s="2">
+      <c r="F226" s="1">
         <v>46028</v>
       </c>
       <c r="G226" t="s">
@@ -13216,7 +13196,7 @@
       <c r="L226" t="s">
         <v>1383</v>
       </c>
-      <c r="N226" s="2">
+      <c r="N226" s="1">
         <v>46232</v>
       </c>
       <c r="Q226" t="b">
@@ -13239,7 +13219,7 @@
       <c r="E227" t="s">
         <v>1046</v>
       </c>
-      <c r="F227" s="2">
+      <c r="F227" s="1">
         <v>46028</v>
       </c>
       <c r="G227" t="s">
@@ -13254,7 +13234,7 @@
       <c r="L227" t="s">
         <v>1383</v>
       </c>
-      <c r="N227" s="2">
+      <c r="N227" s="1">
         <v>46232</v>
       </c>
       <c r="Q227" t="b">
@@ -13277,7 +13257,7 @@
       <c r="E228" t="s">
         <v>1047</v>
       </c>
-      <c r="F228" s="2">
+      <c r="F228" s="1">
         <v>46028</v>
       </c>
       <c r="G228" t="s">
@@ -13287,7 +13267,7 @@
         <v>1353</v>
       </c>
       <c r="I228">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J228">
         <v>204</v>
@@ -13295,7 +13275,7 @@
       <c r="L228" t="s">
         <v>1383</v>
       </c>
-      <c r="N228" s="2">
+      <c r="N228" s="1">
         <v>46232</v>
       </c>
       <c r="Q228" t="b">
@@ -13318,7 +13298,7 @@
       <c r="E229" t="s">
         <v>1048</v>
       </c>
-      <c r="F229" s="2">
+      <c r="F229" s="1">
         <v>46028</v>
       </c>
       <c r="G229" t="s">
@@ -13333,7 +13313,7 @@
       <c r="L229" t="s">
         <v>1420</v>
       </c>
-      <c r="N229" s="2">
+      <c r="N229" s="1">
         <v>46191</v>
       </c>
       <c r="Q229" t="b">
@@ -13356,7 +13336,7 @@
       <c r="E230" t="s">
         <v>1049</v>
       </c>
-      <c r="F230" s="2">
+      <c r="F230" s="1">
         <v>46028</v>
       </c>
       <c r="G230" t="s">
@@ -13366,7 +13346,7 @@
         <v>1353</v>
       </c>
       <c r="I230">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J230">
         <v>197</v>
@@ -13377,7 +13357,7 @@
       <c r="L230" t="s">
         <v>1395</v>
       </c>
-      <c r="N230" s="2">
+      <c r="N230" s="1">
         <v>46225</v>
       </c>
       <c r="Q230" t="b">
@@ -13400,7 +13380,7 @@
       <c r="E231" t="s">
         <v>1050</v>
       </c>
-      <c r="F231" s="2">
+      <c r="F231" s="1">
         <v>46028</v>
       </c>
       <c r="G231" t="s">
@@ -13410,7 +13390,7 @@
         <v>1353</v>
       </c>
       <c r="I231">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J231">
         <v>35</v>
@@ -13421,7 +13401,7 @@
       <c r="L231" t="s">
         <v>1421</v>
       </c>
-      <c r="N231" s="2">
+      <c r="N231" s="1">
         <v>46063</v>
       </c>
       <c r="Q231" t="b">
@@ -13444,7 +13424,7 @@
       <c r="E232" t="s">
         <v>1051</v>
       </c>
-      <c r="F232" s="2">
+      <c r="F232" s="1">
         <v>46028</v>
       </c>
       <c r="G232" t="s">
@@ -13473,7 +13453,7 @@
       <c r="E233" t="s">
         <v>1052</v>
       </c>
-      <c r="F233" s="2">
+      <c r="F233" s="1">
         <v>46028</v>
       </c>
       <c r="G233" t="s">
@@ -13502,7 +13482,7 @@
       <c r="E234" t="s">
         <v>1053</v>
       </c>
-      <c r="F234" s="2">
+      <c r="F234" s="1">
         <v>46028</v>
       </c>
       <c r="G234" t="s">
@@ -13512,7 +13492,7 @@
         <v>1353</v>
       </c>
       <c r="I234">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J234">
         <v>35</v>
@@ -13523,11 +13503,11 @@
       <c r="L234" t="s">
         <v>1421</v>
       </c>
-      <c r="N234" s="2">
+      <c r="N234" s="1">
         <v>46063</v>
       </c>
       <c r="P234" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="Q234" t="b">
         <v>1</v>
@@ -13549,7 +13529,7 @@
       <c r="E235" t="s">
         <v>1054</v>
       </c>
-      <c r="F235" s="2">
+      <c r="F235" s="1">
         <v>46028</v>
       </c>
       <c r="G235" t="s">
@@ -13559,7 +13539,7 @@
         <v>1353</v>
       </c>
       <c r="I235">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J235">
         <v>35</v>
@@ -13570,11 +13550,11 @@
       <c r="L235" t="s">
         <v>1421</v>
       </c>
-      <c r="N235" s="2">
+      <c r="N235" s="1">
         <v>46063</v>
       </c>
       <c r="P235" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="Q235" t="b">
         <v>1</v>
@@ -13596,7 +13576,7 @@
       <c r="E236" t="s">
         <v>1055</v>
       </c>
-      <c r="F236" s="2">
+      <c r="F236" s="1">
         <v>46028</v>
       </c>
       <c r="G236" t="s">
@@ -13606,7 +13586,7 @@
         <v>1353</v>
       </c>
       <c r="I236">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J236">
         <v>86</v>
@@ -13617,7 +13597,7 @@
       <c r="L236" t="s">
         <v>1422</v>
       </c>
-      <c r="N236" s="2">
+      <c r="N236" s="1">
         <v>46114</v>
       </c>
       <c r="Q236" t="b">
@@ -13640,7 +13620,7 @@
       <c r="E237" t="s">
         <v>1056</v>
       </c>
-      <c r="F237" s="2">
+      <c r="F237" s="1">
         <v>46028</v>
       </c>
       <c r="G237" t="s">
@@ -13658,11 +13638,11 @@
       <c r="L237" t="s">
         <v>1423</v>
       </c>
-      <c r="N237" s="2">
+      <c r="N237" s="1">
         <v>46210</v>
       </c>
       <c r="P237" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="Q237" t="b">
         <v>0</v>
@@ -13684,7 +13664,7 @@
       <c r="E238" t="s">
         <v>1057</v>
       </c>
-      <c r="F238" s="2">
+      <c r="F238" s="1">
         <v>46028</v>
       </c>
       <c r="G238" t="s">
@@ -13713,7 +13693,7 @@
       <c r="E239" t="s">
         <v>1058</v>
       </c>
-      <c r="F239" s="2">
+      <c r="F239" s="1">
         <v>46036</v>
       </c>
       <c r="G239" t="s">
@@ -13723,7 +13703,7 @@
         <v>1353</v>
       </c>
       <c r="I239">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K239" t="s">
         <v>1330</v>
@@ -13731,7 +13711,7 @@
       <c r="L239" t="s">
         <v>1424</v>
       </c>
-      <c r="N239" s="2">
+      <c r="N239" s="1">
         <v>46052</v>
       </c>
       <c r="Q239" t="b">
@@ -13754,7 +13734,7 @@
       <c r="E240" t="s">
         <v>1059</v>
       </c>
-      <c r="F240" s="2">
+      <c r="F240" s="1">
         <v>46036</v>
       </c>
       <c r="G240" t="s">
@@ -13783,7 +13763,7 @@
       <c r="E241" t="s">
         <v>1060</v>
       </c>
-      <c r="F241" s="2">
+      <c r="F241" s="1">
         <v>46036</v>
       </c>
       <c r="G241" t="s">
@@ -13812,7 +13792,7 @@
       <c r="E242" t="s">
         <v>1061</v>
       </c>
-      <c r="F242" s="2">
+      <c r="F242" s="1">
         <v>46036</v>
       </c>
       <c r="G242" t="s">
@@ -13822,7 +13802,7 @@
         <v>1353</v>
       </c>
       <c r="I242">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K242" t="s">
         <v>1356</v>
@@ -13850,7 +13830,7 @@
       <c r="E243" t="s">
         <v>1062</v>
       </c>
-      <c r="F243" s="2">
+      <c r="F243" s="1">
         <v>46048</v>
       </c>
       <c r="G243" t="s">
@@ -13879,7 +13859,7 @@
       <c r="E244" t="s">
         <v>1063</v>
       </c>
-      <c r="F244" s="2">
+      <c r="F244" s="1">
         <v>46048</v>
       </c>
       <c r="G244" t="s">
@@ -13889,7 +13869,7 @@
         <v>1353</v>
       </c>
       <c r="I244">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J244">
         <v>15</v>
@@ -13897,7 +13877,7 @@
       <c r="K244" t="s">
         <v>1359</v>
       </c>
-      <c r="N244" s="2">
+      <c r="N244" s="1">
         <v>46063</v>
       </c>
       <c r="Q244" t="b">
@@ -13920,7 +13900,7 @@
       <c r="E245" t="s">
         <v>1064</v>
       </c>
-      <c r="F245" s="2">
+      <c r="F245" s="1">
         <v>46048</v>
       </c>
       <c r="G245" t="s">
@@ -13930,7 +13910,7 @@
         <v>1353</v>
       </c>
       <c r="I245">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J245">
         <v>15</v>
@@ -13941,7 +13921,7 @@
       <c r="L245" t="s">
         <v>1425</v>
       </c>
-      <c r="N245" s="2">
+      <c r="N245" s="1">
         <v>46063</v>
       </c>
       <c r="Q245" t="b">
@@ -13964,7 +13944,7 @@
       <c r="E246" t="s">
         <v>1065</v>
       </c>
-      <c r="F246" s="2">
+      <c r="F246" s="1">
         <v>46050</v>
       </c>
       <c r="G246" t="s">
@@ -13982,7 +13962,7 @@
       <c r="L246" t="s">
         <v>1426</v>
       </c>
-      <c r="N246" s="2">
+      <c r="N246" s="1">
         <v>46191</v>
       </c>
       <c r="Q246" t="b">
@@ -14005,7 +13985,7 @@
       <c r="E247" t="s">
         <v>1066</v>
       </c>
-      <c r="F247" s="2">
+      <c r="F247" s="1">
         <v>46050</v>
       </c>
       <c r="G247" t="s">
@@ -14034,7 +14014,7 @@
       <c r="E248" t="s">
         <v>1067</v>
       </c>
-      <c r="F248" s="2">
+      <c r="F248" s="1">
         <v>46050</v>
       </c>
       <c r="G248" t="s">
@@ -14063,7 +14043,7 @@
       <c r="E249" t="s">
         <v>1068</v>
       </c>
-      <c r="F249" s="2">
+      <c r="F249" s="1">
         <v>46050</v>
       </c>
       <c r="G249" t="s">
@@ -14073,7 +14053,7 @@
         <v>1353</v>
       </c>
       <c r="I249">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K249" t="s">
         <v>1357</v>
@@ -14101,7 +14081,7 @@
       <c r="E250" t="s">
         <v>1069</v>
       </c>
-      <c r="F250" s="2">
+      <c r="F250" s="1">
         <v>46063</v>
       </c>
       <c r="G250" t="s">
@@ -14117,7 +14097,7 @@
         <v>1454</v>
       </c>
       <c r="P250" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="Q250" t="b">
         <v>0</v>
@@ -14139,7 +14119,7 @@
       <c r="E251" t="s">
         <v>1070</v>
       </c>
-      <c r="F251" s="2">
+      <c r="F251" s="1">
         <v>46063</v>
       </c>
       <c r="G251" t="s">
@@ -14168,7 +14148,7 @@
       <c r="E252" t="s">
         <v>1071</v>
       </c>
-      <c r="F252" s="2">
+      <c r="F252" s="1">
         <v>46063</v>
       </c>
       <c r="G252" t="s">
@@ -14197,7 +14177,7 @@
       <c r="E253" t="s">
         <v>1072</v>
       </c>
-      <c r="F253" s="2">
+      <c r="F253" s="1">
         <v>46063</v>
       </c>
       <c r="G253" t="s">
@@ -14207,7 +14187,7 @@
         <v>1353</v>
       </c>
       <c r="I253">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J253">
         <v>162</v>
@@ -14218,7 +14198,7 @@
       <c r="L253" t="s">
         <v>1395</v>
       </c>
-      <c r="N253" s="2">
+      <c r="N253" s="1">
         <v>46225</v>
       </c>
       <c r="Q253" t="b">
@@ -14241,7 +14221,7 @@
       <c r="E254" t="s">
         <v>1073</v>
       </c>
-      <c r="F254" s="2">
+      <c r="F254" s="1">
         <v>46063</v>
       </c>
       <c r="G254" t="s">
@@ -14251,7 +14231,7 @@
         <v>1353</v>
       </c>
       <c r="I254">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K254" t="s">
         <v>1360</v>
@@ -14279,7 +14259,7 @@
       <c r="E255" t="s">
         <v>1074</v>
       </c>
-      <c r="F255" s="2">
+      <c r="F255" s="1">
         <v>46063</v>
       </c>
       <c r="G255" t="s">
@@ -14289,7 +14269,7 @@
         <v>1353</v>
       </c>
       <c r="I255">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J255">
         <v>72</v>
@@ -14300,7 +14280,7 @@
       <c r="L255" t="s">
         <v>1388</v>
       </c>
-      <c r="N255" s="2">
+      <c r="N255" s="1">
         <v>46135</v>
       </c>
       <c r="Q255" t="b">
@@ -14323,7 +14303,7 @@
       <c r="E256" t="s">
         <v>1075</v>
       </c>
-      <c r="F256" s="2">
+      <c r="F256" s="1">
         <v>46063</v>
       </c>
       <c r="G256" t="s">
@@ -14333,7 +14313,7 @@
         <v>1353</v>
       </c>
       <c r="I256">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J256">
         <v>23</v>
@@ -14341,7 +14321,7 @@
       <c r="K256" t="s">
         <v>1357</v>
       </c>
-      <c r="N256" s="2">
+      <c r="N256" s="1">
         <v>46086</v>
       </c>
       <c r="O256">
@@ -14367,7 +14347,7 @@
       <c r="E257" t="s">
         <v>1076</v>
       </c>
-      <c r="F257" s="2">
+      <c r="F257" s="1">
         <v>46063</v>
       </c>
       <c r="G257" t="s">
@@ -14396,7 +14376,7 @@
       <c r="E258" t="s">
         <v>1077</v>
       </c>
-      <c r="F258" s="2">
+      <c r="F258" s="1">
         <v>46063</v>
       </c>
       <c r="G258" t="s">
@@ -14425,7 +14405,7 @@
       <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="F259" s="2">
+      <c r="F259" s="1">
         <v>46063</v>
       </c>
       <c r="G259" t="s">
@@ -14435,7 +14415,7 @@
         <v>1353</v>
       </c>
       <c r="I259">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J259">
         <v>72</v>
@@ -14446,7 +14426,7 @@
       <c r="L259" t="s">
         <v>1388</v>
       </c>
-      <c r="N259" s="2">
+      <c r="N259" s="1">
         <v>46135</v>
       </c>
       <c r="Q259" t="b">
@@ -14469,7 +14449,7 @@
       <c r="E260" t="s">
         <v>1079</v>
       </c>
-      <c r="F260" s="2">
+      <c r="F260" s="1">
         <v>46063</v>
       </c>
       <c r="G260" t="s">
@@ -14479,7 +14459,7 @@
         <v>1353</v>
       </c>
       <c r="I260">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J260">
         <v>84</v>
@@ -14490,7 +14470,7 @@
       <c r="L260" t="s">
         <v>1388</v>
       </c>
-      <c r="N260" s="2">
+      <c r="N260" s="1">
         <v>46147</v>
       </c>
       <c r="Q260" t="b">
@@ -14513,7 +14493,7 @@
       <c r="E261" t="s">
         <v>1080</v>
       </c>
-      <c r="F261" s="2">
+      <c r="F261" s="1">
         <v>46063</v>
       </c>
       <c r="G261" t="s">
@@ -14523,7 +14503,7 @@
         <v>1353</v>
       </c>
       <c r="I261">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J261">
         <v>162</v>
@@ -14534,7 +14514,7 @@
       <c r="L261" t="s">
         <v>1427</v>
       </c>
-      <c r="N261" s="2">
+      <c r="N261" s="1">
         <v>46225</v>
       </c>
       <c r="Q261" t="b">
@@ -14557,7 +14537,7 @@
       <c r="E262" t="s">
         <v>1081</v>
       </c>
-      <c r="F262" s="2">
+      <c r="F262" s="1">
         <v>46063</v>
       </c>
       <c r="G262" t="s">
@@ -14575,11 +14555,11 @@
       <c r="L262" t="s">
         <v>1428</v>
       </c>
-      <c r="N262" s="2">
+      <c r="N262" s="1">
         <v>46113</v>
       </c>
       <c r="P262" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="Q262" t="b">
         <v>0</v>
@@ -14601,7 +14581,7 @@
       <c r="E263" t="s">
         <v>1082</v>
       </c>
-      <c r="F263" s="2">
+      <c r="F263" s="1">
         <v>46063</v>
       </c>
       <c r="G263" t="s">
@@ -14630,7 +14610,7 @@
       <c r="E264" t="s">
         <v>1083</v>
       </c>
-      <c r="F264" s="2">
+      <c r="F264" s="1">
         <v>46063</v>
       </c>
       <c r="G264" t="s">
@@ -14640,7 +14620,7 @@
         <v>1353</v>
       </c>
       <c r="I264">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J264">
         <v>162</v>
@@ -14651,7 +14631,7 @@
       <c r="L264" t="s">
         <v>1388</v>
       </c>
-      <c r="N264" s="2">
+      <c r="N264" s="1">
         <v>46225</v>
       </c>
       <c r="Q264" t="b">
@@ -14674,7 +14654,7 @@
       <c r="E265" t="s">
         <v>1084</v>
       </c>
-      <c r="F265" s="2">
+      <c r="F265" s="1">
         <v>46063</v>
       </c>
       <c r="G265" t="s">
@@ -14684,7 +14664,7 @@
         <v>1353</v>
       </c>
       <c r="I265">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J265">
         <v>162</v>
@@ -14695,7 +14675,7 @@
       <c r="L265" t="s">
         <v>1395</v>
       </c>
-      <c r="N265" s="2">
+      <c r="N265" s="1">
         <v>46225</v>
       </c>
       <c r="Q265" t="b">
@@ -14718,7 +14698,7 @@
       <c r="E266" t="s">
         <v>1085</v>
       </c>
-      <c r="F266" s="2">
+      <c r="F266" s="1">
         <v>46063</v>
       </c>
       <c r="G266" t="s">
@@ -14728,7 +14708,7 @@
         <v>1353</v>
       </c>
       <c r="I266">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J266">
         <v>84</v>
@@ -14739,7 +14719,7 @@
       <c r="L266" t="s">
         <v>1388</v>
       </c>
-      <c r="N266" s="2">
+      <c r="N266" s="1">
         <v>46147</v>
       </c>
       <c r="Q266" t="b">
@@ -14762,7 +14742,7 @@
       <c r="E267" t="s">
         <v>1086</v>
       </c>
-      <c r="F267" s="2">
+      <c r="F267" s="1">
         <v>46063</v>
       </c>
       <c r="G267" t="s">
@@ -14772,7 +14752,7 @@
         <v>1353</v>
       </c>
       <c r="I267">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K267" t="s">
         <v>1360</v>
@@ -14800,7 +14780,7 @@
       <c r="E268" t="s">
         <v>1087</v>
       </c>
-      <c r="F268" s="2">
+      <c r="F268" s="1">
         <v>46063</v>
       </c>
       <c r="G268" t="s">
@@ -14810,7 +14790,7 @@
         <v>1353</v>
       </c>
       <c r="I268">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K268" t="s">
         <v>1357</v>
@@ -14835,7 +14815,7 @@
       <c r="D269" t="s">
         <v>798</v>
       </c>
-      <c r="F269" s="2">
+      <c r="F269" s="1">
         <v>46063</v>
       </c>
       <c r="G269" t="s">
@@ -14845,7 +14825,7 @@
         <v>1353</v>
       </c>
       <c r="I269">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K269" t="s">
         <v>1357</v>
@@ -14873,7 +14853,7 @@
       <c r="E270" t="s">
         <v>1088</v>
       </c>
-      <c r="F270" s="2">
+      <c r="F270" s="1">
         <v>46063</v>
       </c>
       <c r="G270" t="s">
@@ -14883,7 +14863,7 @@
         <v>1353</v>
       </c>
       <c r="I270">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K270" t="s">
         <v>1360</v>
@@ -14911,7 +14891,7 @@
       <c r="E271" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="2">
+      <c r="F271" s="1">
         <v>46063</v>
       </c>
       <c r="G271" t="s">
@@ -14921,7 +14901,7 @@
         <v>1353</v>
       </c>
       <c r="I271">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K271" t="s">
         <v>1360</v>
@@ -14949,7 +14929,7 @@
       <c r="E272" t="s">
         <v>1090</v>
       </c>
-      <c r="F272" s="2">
+      <c r="F272" s="1">
         <v>46063</v>
       </c>
       <c r="G272" t="s">
@@ -14967,7 +14947,7 @@
       <c r="L272" t="s">
         <v>1429</v>
       </c>
-      <c r="N272" s="2">
+      <c r="N272" s="1">
         <v>46185</v>
       </c>
       <c r="O272" t="s">
@@ -14993,7 +14973,7 @@
       <c r="E273" t="s">
         <v>1091</v>
       </c>
-      <c r="F273" s="2">
+      <c r="F273" s="1">
         <v>46063</v>
       </c>
       <c r="G273" t="s">
@@ -15022,7 +15002,7 @@
       <c r="E274" t="s">
         <v>1092</v>
       </c>
-      <c r="F274" s="2">
+      <c r="F274" s="1">
         <v>46063</v>
       </c>
       <c r="G274" t="s">
@@ -15037,7 +15017,7 @@
       <c r="L274" t="s">
         <v>1383</v>
       </c>
-      <c r="N274" s="2">
+      <c r="N274" s="1">
         <v>46232</v>
       </c>
       <c r="Q274" t="b">
@@ -15060,7 +15040,7 @@
       <c r="E275" t="s">
         <v>1093</v>
       </c>
-      <c r="F275" s="2">
+      <c r="F275" s="1">
         <v>46063</v>
       </c>
       <c r="G275" t="s">
@@ -15089,7 +15069,7 @@
       <c r="E276" t="s">
         <v>1094</v>
       </c>
-      <c r="F276" s="2">
+      <c r="F276" s="1">
         <v>46063</v>
       </c>
       <c r="G276" t="s">
@@ -15099,7 +15079,7 @@
         <v>1353</v>
       </c>
       <c r="I276">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K276" t="s">
         <v>1361</v>
@@ -15127,7 +15107,7 @@
       <c r="E277" t="s">
         <v>1095</v>
       </c>
-      <c r="F277" s="2">
+      <c r="F277" s="1">
         <v>46063</v>
       </c>
       <c r="G277" t="s">
@@ -15137,7 +15117,7 @@
         <v>1353</v>
       </c>
       <c r="I277">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K277" t="s">
         <v>1357</v>
@@ -15165,7 +15145,7 @@
       <c r="E278" t="s">
         <v>1096</v>
       </c>
-      <c r="F278" s="2">
+      <c r="F278" s="1">
         <v>46077</v>
       </c>
       <c r="G278" t="s">
@@ -15175,7 +15155,7 @@
         <v>1353</v>
       </c>
       <c r="I278">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J278">
         <v>148</v>
@@ -15186,7 +15166,7 @@
       <c r="L278" t="s">
         <v>1395</v>
       </c>
-      <c r="N278" s="2">
+      <c r="N278" s="1">
         <v>46225</v>
       </c>
       <c r="Q278" t="b">
@@ -15209,7 +15189,7 @@
       <c r="E279" t="s">
         <v>1097</v>
       </c>
-      <c r="F279" s="2">
+      <c r="F279" s="1">
         <v>46077</v>
       </c>
       <c r="G279" t="s">
@@ -15219,7 +15199,7 @@
         <v>1353</v>
       </c>
       <c r="I279">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K279" t="s">
         <v>1359</v>
@@ -15228,7 +15208,7 @@
         <v>1454</v>
       </c>
       <c r="P279" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="Q279" t="b">
         <v>1</v>
@@ -15250,7 +15230,7 @@
       <c r="E280" t="s">
         <v>1098</v>
       </c>
-      <c r="F280" s="2">
+      <c r="F280" s="1">
         <v>46085</v>
       </c>
       <c r="G280" t="s">
@@ -15260,7 +15240,7 @@
         <v>1353</v>
       </c>
       <c r="I280">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K280" t="s">
         <v>1357</v>
@@ -15288,7 +15268,7 @@
       <c r="E281" t="s">
         <v>1099</v>
       </c>
-      <c r="F281" s="2">
+      <c r="F281" s="1">
         <v>46085</v>
       </c>
       <c r="G281" t="s">
@@ -15298,7 +15278,7 @@
         <v>1353</v>
       </c>
       <c r="I281">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K281" t="s">
         <v>1357</v>
@@ -15329,7 +15309,7 @@
       <c r="E282" t="s">
         <v>1100</v>
       </c>
-      <c r="F282" s="2">
+      <c r="F282" s="1">
         <v>46090</v>
       </c>
       <c r="G282" t="s">
@@ -15339,7 +15319,7 @@
         <v>1353</v>
       </c>
       <c r="I282">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K282" t="s">
         <v>1357</v>
@@ -15367,7 +15347,7 @@
       <c r="E283" t="s">
         <v>1101</v>
       </c>
-      <c r="F283" s="2">
+      <c r="F283" s="1">
         <v>46100</v>
       </c>
       <c r="G283" t="s">
@@ -15396,7 +15376,7 @@
       <c r="E284" t="s">
         <v>1102</v>
       </c>
-      <c r="F284" s="2">
+      <c r="F284" s="1">
         <v>46100</v>
       </c>
       <c r="G284" t="s">
@@ -15425,7 +15405,7 @@
       <c r="E285" t="s">
         <v>1103</v>
       </c>
-      <c r="F285" s="2">
+      <c r="F285" s="1">
         <v>46100</v>
       </c>
       <c r="G285" t="s">
@@ -15454,7 +15434,7 @@
       <c r="E286" t="s">
         <v>1104</v>
       </c>
-      <c r="F286" s="2">
+      <c r="F286" s="1">
         <v>46100</v>
       </c>
       <c r="G286" t="s">
@@ -15483,7 +15463,7 @@
       <c r="E287" t="s">
         <v>1105</v>
       </c>
-      <c r="F287" s="2">
+      <c r="F287" s="1">
         <v>46107</v>
       </c>
       <c r="G287" t="s">
@@ -15512,7 +15492,7 @@
       <c r="E288" t="s">
         <v>1106</v>
       </c>
-      <c r="F288" s="2">
+      <c r="F288" s="1">
         <v>46107</v>
       </c>
       <c r="G288" t="s">
@@ -15522,7 +15502,7 @@
         <v>1353</v>
       </c>
       <c r="I288">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J288">
         <v>28</v>
@@ -15533,7 +15513,7 @@
       <c r="L288" t="s">
         <v>1388</v>
       </c>
-      <c r="N288" s="2">
+      <c r="N288" s="1">
         <v>46135</v>
       </c>
       <c r="Q288" t="b">
@@ -15556,7 +15536,7 @@
       <c r="E289" t="s">
         <v>1107</v>
       </c>
-      <c r="F289" s="2">
+      <c r="F289" s="1">
         <v>46107</v>
       </c>
       <c r="G289" t="s">
@@ -15585,7 +15565,7 @@
       <c r="E290" t="s">
         <v>1108</v>
       </c>
-      <c r="F290" s="2">
+      <c r="F290" s="1">
         <v>46107</v>
       </c>
       <c r="G290" t="s">
@@ -15595,7 +15575,7 @@
         <v>1353</v>
       </c>
       <c r="I290">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J290">
         <v>20</v>
@@ -15606,7 +15586,7 @@
       <c r="L290" t="s">
         <v>1388</v>
       </c>
-      <c r="N290" s="2">
+      <c r="N290" s="1">
         <v>46127</v>
       </c>
       <c r="Q290" t="b">
@@ -15629,7 +15609,7 @@
       <c r="E291" t="s">
         <v>1109</v>
       </c>
-      <c r="F291" s="2">
+      <c r="F291" s="1">
         <v>46107</v>
       </c>
       <c r="G291" t="s">
@@ -15639,7 +15619,7 @@
         <v>1353</v>
       </c>
       <c r="I291">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J291">
         <v>20</v>
@@ -15650,7 +15630,7 @@
       <c r="L291" t="s">
         <v>1430</v>
       </c>
-      <c r="N291" s="2">
+      <c r="N291" s="1">
         <v>46127</v>
       </c>
       <c r="Q291" t="b">
@@ -15673,7 +15653,7 @@
       <c r="E292" t="s">
         <v>1110</v>
       </c>
-      <c r="F292" s="2">
+      <c r="F292" s="1">
         <v>46112</v>
       </c>
       <c r="G292" t="s">
@@ -15683,7 +15663,7 @@
         <v>1353</v>
       </c>
       <c r="I292">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K292" t="s">
         <v>1360</v>
@@ -15711,7 +15691,7 @@
       <c r="E293" t="s">
         <v>1111</v>
       </c>
-      <c r="F293" s="2">
+      <c r="F293" s="1">
         <v>46125</v>
       </c>
       <c r="G293" t="s">
@@ -15721,7 +15701,7 @@
         <v>1353</v>
       </c>
       <c r="I293">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K293" t="s">
         <v>1361</v>
@@ -15749,7 +15729,7 @@
       <c r="E294" t="s">
         <v>1112</v>
       </c>
-      <c r="F294" s="2">
+      <c r="F294" s="1">
         <v>46125</v>
       </c>
       <c r="G294" t="s">
@@ -15759,7 +15739,7 @@
         <v>1353</v>
       </c>
       <c r="I294">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K294" t="s">
         <v>1366</v>
@@ -15784,7 +15764,7 @@
       <c r="E295" t="s">
         <v>1113</v>
       </c>
-      <c r="F295" s="2">
+      <c r="F295" s="1">
         <v>46125</v>
       </c>
       <c r="G295" t="s">
@@ -15794,7 +15774,7 @@
         <v>1353</v>
       </c>
       <c r="I295">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K295" t="s">
         <v>1366</v>
@@ -15819,7 +15799,7 @@
       <c r="E296" t="s">
         <v>1114</v>
       </c>
-      <c r="F296" s="2">
+      <c r="F296" s="1">
         <v>46125</v>
       </c>
       <c r="G296" t="s">
@@ -15829,7 +15809,7 @@
         <v>1353</v>
       </c>
       <c r="I296">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K296" t="s">
         <v>1366</v>
@@ -15854,7 +15834,7 @@
       <c r="E297" t="s">
         <v>1115</v>
       </c>
-      <c r="F297" s="2">
+      <c r="F297" s="1">
         <v>46125</v>
       </c>
       <c r="G297" t="s">
@@ -15866,7 +15846,7 @@
       <c r="K297" t="s">
         <v>1359</v>
       </c>
-      <c r="N297" s="2">
+      <c r="N297" s="1">
         <v>46183</v>
       </c>
       <c r="O297">
@@ -15892,7 +15872,7 @@
       <c r="E298" t="s">
         <v>1116</v>
       </c>
-      <c r="F298" s="2">
+      <c r="F298" s="1">
         <v>46125</v>
       </c>
       <c r="G298" t="s">
@@ -15902,7 +15882,7 @@
         <v>1353</v>
       </c>
       <c r="I298">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J298">
         <v>58</v>
@@ -15910,7 +15890,7 @@
       <c r="K298" t="s">
         <v>1359</v>
       </c>
-      <c r="N298" s="2">
+      <c r="N298" s="1">
         <v>46183</v>
       </c>
       <c r="Q298" t="b">
@@ -15933,7 +15913,7 @@
       <c r="E299" t="s">
         <v>1117</v>
       </c>
-      <c r="F299" s="2">
+      <c r="F299" s="1">
         <v>46125</v>
       </c>
       <c r="G299" t="s">
@@ -15943,7 +15923,7 @@
         <v>1353</v>
       </c>
       <c r="I299">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J299">
         <v>100</v>
@@ -15954,7 +15934,7 @@
       <c r="L299" t="s">
         <v>1388</v>
       </c>
-      <c r="N299" s="2">
+      <c r="N299" s="1">
         <v>46225</v>
       </c>
       <c r="Q299" t="b">
@@ -15977,7 +15957,7 @@
       <c r="E300" t="s">
         <v>1118</v>
       </c>
-      <c r="F300" s="2">
+      <c r="F300" s="1">
         <v>46125</v>
       </c>
       <c r="G300" t="s">
@@ -15987,7 +15967,7 @@
         <v>1353</v>
       </c>
       <c r="I300">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J300">
         <v>86</v>
@@ -15998,7 +15978,7 @@
       <c r="L300" t="s">
         <v>1388</v>
       </c>
-      <c r="N300" s="2">
+      <c r="N300" s="1">
         <v>46211</v>
       </c>
       <c r="Q300" t="b">
@@ -16021,7 +16001,7 @@
       <c r="E301" t="s">
         <v>1119</v>
       </c>
-      <c r="F301" s="2">
+      <c r="F301" s="1">
         <v>46125</v>
       </c>
       <c r="G301" t="s">
@@ -16031,7 +16011,7 @@
         <v>1353</v>
       </c>
       <c r="I301">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J301">
         <v>102</v>
@@ -16042,7 +16022,7 @@
       <c r="L301" t="s">
         <v>1388</v>
       </c>
-      <c r="N301" s="2">
+      <c r="N301" s="1">
         <v>46227</v>
       </c>
       <c r="Q301" t="b">
@@ -16065,7 +16045,7 @@
       <c r="E302" t="s">
         <v>1120</v>
       </c>
-      <c r="F302" s="2">
+      <c r="F302" s="1">
         <v>46125</v>
       </c>
       <c r="G302" t="s">
@@ -16075,7 +16055,7 @@
         <v>1353</v>
       </c>
       <c r="I302">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K302" t="s">
         <v>1360</v>
@@ -16103,7 +16083,7 @@
       <c r="E303" t="s">
         <v>1121</v>
       </c>
-      <c r="F303" s="2">
+      <c r="F303" s="1">
         <v>46125</v>
       </c>
       <c r="G303" t="s">
@@ -16113,7 +16093,7 @@
         <v>1353</v>
       </c>
       <c r="I303">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K303" t="s">
         <v>1357</v>
@@ -16141,7 +16121,7 @@
       <c r="E304" t="s">
         <v>1122</v>
       </c>
-      <c r="F304" s="2">
+      <c r="F304" s="1">
         <v>46125</v>
       </c>
       <c r="G304" t="s">
@@ -16151,7 +16131,7 @@
         <v>1353</v>
       </c>
       <c r="I304">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K304" t="s">
         <v>1360</v>
@@ -16179,7 +16159,7 @@
       <c r="E305" t="s">
         <v>1123</v>
       </c>
-      <c r="F305" s="2">
+      <c r="F305" s="1">
         <v>46125</v>
       </c>
       <c r="G305" t="s">
@@ -16189,7 +16169,7 @@
         <v>1353</v>
       </c>
       <c r="I305">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J305">
         <v>35</v>
@@ -16200,7 +16180,7 @@
       <c r="L305" t="s">
         <v>1431</v>
       </c>
-      <c r="N305" s="2">
+      <c r="N305" s="1">
         <v>46160</v>
       </c>
       <c r="Q305" t="b">
@@ -16223,7 +16203,7 @@
       <c r="E306" t="s">
         <v>1124</v>
       </c>
-      <c r="F306" s="2">
+      <c r="F306" s="1">
         <v>46125</v>
       </c>
       <c r="G306" t="s">
@@ -16233,7 +16213,7 @@
         <v>1353</v>
       </c>
       <c r="I306">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J306">
         <v>31</v>
@@ -16244,7 +16224,7 @@
       <c r="L306" t="s">
         <v>1432</v>
       </c>
-      <c r="N306" s="2">
+      <c r="N306" s="1">
         <v>46156</v>
       </c>
       <c r="Q306" t="b">
@@ -16267,7 +16247,7 @@
       <c r="E307" t="s">
         <v>1125</v>
       </c>
-      <c r="F307" s="2">
+      <c r="F307" s="1">
         <v>46125</v>
       </c>
       <c r="G307" t="s">
@@ -16285,11 +16265,11 @@
       <c r="L307" t="s">
         <v>1433</v>
       </c>
-      <c r="N307" s="2">
+      <c r="N307" s="1">
         <v>46209</v>
       </c>
       <c r="P307" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="Q307" t="b">
         <v>0</v>
@@ -16311,7 +16291,7 @@
       <c r="E308" t="s">
         <v>1126</v>
       </c>
-      <c r="F308" s="2">
+      <c r="F308" s="1">
         <v>46125</v>
       </c>
       <c r="G308" t="s">
@@ -16321,7 +16301,7 @@
         <v>1353</v>
       </c>
       <c r="I308">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K308" t="s">
         <v>1356</v>
@@ -16349,7 +16329,7 @@
       <c r="E309" t="s">
         <v>1127</v>
       </c>
-      <c r="F309" s="2">
+      <c r="F309" s="1">
         <v>46125</v>
       </c>
       <c r="G309" t="s">
@@ -16364,7 +16344,7 @@
       <c r="L309" t="s">
         <v>1383</v>
       </c>
-      <c r="N309" s="2">
+      <c r="N309" s="1">
         <v>46232</v>
       </c>
       <c r="Q309" t="b">
@@ -16387,7 +16367,7 @@
       <c r="E310" t="s">
         <v>1128</v>
       </c>
-      <c r="F310" s="2">
+      <c r="F310" s="1">
         <v>46125</v>
       </c>
       <c r="G310" t="s">
@@ -16397,7 +16377,7 @@
         <v>1353</v>
       </c>
       <c r="I310">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J310">
         <v>107</v>
@@ -16408,7 +16388,7 @@
       <c r="L310" t="s">
         <v>1383</v>
       </c>
-      <c r="N310" s="2">
+      <c r="N310" s="1">
         <v>46232</v>
       </c>
       <c r="Q310" t="b">
@@ -16431,7 +16411,7 @@
       <c r="E311" t="s">
         <v>1129</v>
       </c>
-      <c r="F311" s="2">
+      <c r="F311" s="1">
         <v>46125</v>
       </c>
       <c r="G311" t="s">
@@ -16441,7 +16421,7 @@
         <v>1353</v>
       </c>
       <c r="I311">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K311" t="s">
         <v>1356</v>
@@ -16469,7 +16449,7 @@
       <c r="E312" t="s">
         <v>1130</v>
       </c>
-      <c r="F312" s="2">
+      <c r="F312" s="1">
         <v>46125</v>
       </c>
       <c r="G312" t="s">
@@ -16487,7 +16467,7 @@
       <c r="L312" t="s">
         <v>1383</v>
       </c>
-      <c r="N312" s="2">
+      <c r="N312" s="1">
         <v>46232</v>
       </c>
       <c r="Q312" t="b">
@@ -16510,7 +16490,7 @@
       <c r="E313" t="s">
         <v>1131</v>
       </c>
-      <c r="F313" s="2">
+      <c r="F313" s="1">
         <v>46125</v>
       </c>
       <c r="G313" t="s">
@@ -16545,7 +16525,7 @@
       <c r="E314" t="s">
         <v>1132</v>
       </c>
-      <c r="F314" s="2">
+      <c r="F314" s="1">
         <v>46125</v>
       </c>
       <c r="G314" t="s">
@@ -16560,7 +16540,7 @@
       <c r="L314" t="s">
         <v>1383</v>
       </c>
-      <c r="N314" s="2">
+      <c r="N314" s="1">
         <v>46232</v>
       </c>
       <c r="Q314" t="b">
@@ -16583,7 +16563,7 @@
       <c r="E315" t="s">
         <v>1133</v>
       </c>
-      <c r="F315" s="2">
+      <c r="F315" s="1">
         <v>46125</v>
       </c>
       <c r="G315" t="s">
@@ -16598,7 +16578,7 @@
       <c r="L315" t="s">
         <v>1383</v>
       </c>
-      <c r="N315" s="2">
+      <c r="N315" s="1">
         <v>46232</v>
       </c>
       <c r="Q315" t="b">
@@ -16621,7 +16601,7 @@
       <c r="E316" t="s">
         <v>1134</v>
       </c>
-      <c r="F316" s="2">
+      <c r="F316" s="1">
         <v>46125</v>
       </c>
       <c r="G316" t="s">
@@ -16631,7 +16611,7 @@
         <v>1353</v>
       </c>
       <c r="I316">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K316" t="s">
         <v>1357</v>
@@ -16640,7 +16620,7 @@
         <v>1454</v>
       </c>
       <c r="P316" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="Q316" t="b">
         <v>1</v>
@@ -16662,7 +16642,7 @@
       <c r="E317" t="s">
         <v>1135</v>
       </c>
-      <c r="F317" s="2">
+      <c r="F317" s="1">
         <v>46125</v>
       </c>
       <c r="G317" t="s">
@@ -16697,7 +16677,7 @@
       <c r="E318" t="s">
         <v>1136</v>
       </c>
-      <c r="F318" s="2">
+      <c r="F318" s="1">
         <v>46125</v>
       </c>
       <c r="G318" t="s">
@@ -16726,7 +16706,7 @@
       <c r="E319" t="s">
         <v>1137</v>
       </c>
-      <c r="F319" s="2">
+      <c r="F319" s="1">
         <v>46125</v>
       </c>
       <c r="G319" t="s">
@@ -16741,7 +16721,7 @@
       <c r="L319" t="s">
         <v>1434</v>
       </c>
-      <c r="N319" s="2">
+      <c r="N319" s="1">
         <v>46175</v>
       </c>
       <c r="Q319" t="b">
@@ -16764,7 +16744,7 @@
       <c r="E320" t="s">
         <v>1138</v>
       </c>
-      <c r="F320" s="2">
+      <c r="F320" s="1">
         <v>46125</v>
       </c>
       <c r="G320" t="s">
@@ -16774,7 +16754,7 @@
         <v>1353</v>
       </c>
       <c r="I320">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K320" t="s">
         <v>1361</v>
@@ -16802,7 +16782,7 @@
       <c r="E321" t="s">
         <v>1139</v>
       </c>
-      <c r="F321" s="2">
+      <c r="F321" s="1">
         <v>46125</v>
       </c>
       <c r="G321" t="s">
@@ -16812,7 +16792,7 @@
         <v>1353</v>
       </c>
       <c r="I321">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K321" t="s">
         <v>1357</v>
@@ -16840,7 +16820,7 @@
       <c r="E322" t="s">
         <v>1140</v>
       </c>
-      <c r="F322" s="2">
+      <c r="F322" s="1">
         <v>46125</v>
       </c>
       <c r="G322" t="s">
@@ -16850,7 +16830,7 @@
         <v>1353</v>
       </c>
       <c r="I322">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J322">
         <v>57</v>
@@ -16861,7 +16841,7 @@
       <c r="L322" t="s">
         <v>1435</v>
       </c>
-      <c r="N322" s="2">
+      <c r="N322" s="1">
         <v>46182</v>
       </c>
       <c r="Q322" t="b">
@@ -16884,7 +16864,7 @@
       <c r="E323" t="s">
         <v>1141</v>
       </c>
-      <c r="F323" s="2">
+      <c r="F323" s="1">
         <v>46125</v>
       </c>
       <c r="G323" t="s">
@@ -16919,7 +16899,7 @@
       <c r="E324" t="s">
         <v>1142</v>
       </c>
-      <c r="F324" s="2">
+      <c r="F324" s="1">
         <v>46125</v>
       </c>
       <c r="G324" t="s">
@@ -16954,7 +16934,7 @@
       <c r="E325" t="s">
         <v>1143</v>
       </c>
-      <c r="F325" s="2">
+      <c r="F325" s="1">
         <v>46125</v>
       </c>
       <c r="G325" t="s">
@@ -16964,7 +16944,7 @@
         <v>1353</v>
       </c>
       <c r="I325">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J325">
         <v>57</v>
@@ -16975,7 +16955,7 @@
       <c r="L325" t="s">
         <v>1435</v>
       </c>
-      <c r="N325" s="2">
+      <c r="N325" s="1">
         <v>46182</v>
       </c>
       <c r="Q325" t="b">
@@ -16998,7 +16978,7 @@
       <c r="E326" t="s">
         <v>1144</v>
       </c>
-      <c r="F326" s="2">
+      <c r="F326" s="1">
         <v>46125</v>
       </c>
       <c r="G326" t="s">
@@ -17013,7 +16993,7 @@
       <c r="L326" t="s">
         <v>1383</v>
       </c>
-      <c r="N326" s="2">
+      <c r="N326" s="1">
         <v>46232</v>
       </c>
       <c r="Q326" t="b">
@@ -17036,7 +17016,7 @@
       <c r="E327" t="s">
         <v>1140</v>
       </c>
-      <c r="F327" s="2">
+      <c r="F327" s="1">
         <v>46125</v>
       </c>
       <c r="G327" t="s">
@@ -17046,7 +17026,7 @@
         <v>1353</v>
       </c>
       <c r="I327">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J327">
         <v>57</v>
@@ -17057,7 +17037,7 @@
       <c r="L327" t="s">
         <v>1435</v>
       </c>
-      <c r="N327" s="2">
+      <c r="N327" s="1">
         <v>46182</v>
       </c>
       <c r="Q327" t="b">
@@ -17080,7 +17060,7 @@
       <c r="E328" t="s">
         <v>1145</v>
       </c>
-      <c r="F328" s="2">
+      <c r="F328" s="1">
         <v>46125</v>
       </c>
       <c r="G328" t="s">
@@ -17090,7 +17070,7 @@
         <v>1353</v>
       </c>
       <c r="I328">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J328">
         <v>57</v>
@@ -17101,7 +17081,7 @@
       <c r="L328" t="s">
         <v>1435</v>
       </c>
-      <c r="N328" s="2">
+      <c r="N328" s="1">
         <v>46182</v>
       </c>
       <c r="Q328" t="b">
@@ -17124,7 +17104,7 @@
       <c r="E329" t="s">
         <v>1146</v>
       </c>
-      <c r="F329" s="2">
+      <c r="F329" s="1">
         <v>46125</v>
       </c>
       <c r="G329" t="s">
@@ -17134,7 +17114,7 @@
         <v>1353</v>
       </c>
       <c r="I329">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J329">
         <v>57</v>
@@ -17145,7 +17125,7 @@
       <c r="L329" t="s">
         <v>1435</v>
       </c>
-      <c r="N329" s="2">
+      <c r="N329" s="1">
         <v>46182</v>
       </c>
       <c r="Q329" t="b">
@@ -17168,7 +17148,7 @@
       <c r="E330" t="s">
         <v>1147</v>
       </c>
-      <c r="F330" s="2">
+      <c r="F330" s="1">
         <v>46125</v>
       </c>
       <c r="G330" t="s">
@@ -17178,7 +17158,7 @@
         <v>1353</v>
       </c>
       <c r="I330">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J330">
         <v>57</v>
@@ -17189,7 +17169,7 @@
       <c r="L330" t="s">
         <v>1435</v>
       </c>
-      <c r="N330" s="2">
+      <c r="N330" s="1">
         <v>46182</v>
       </c>
       <c r="Q330" t="b">
@@ -17212,7 +17192,7 @@
       <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="F331" s="2">
+      <c r="F331" s="1">
         <v>46125</v>
       </c>
       <c r="G331" t="s">
@@ -17222,7 +17202,7 @@
         <v>1353</v>
       </c>
       <c r="I331">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K331" t="s">
         <v>1356</v>
@@ -17250,7 +17230,7 @@
       <c r="E332" t="s">
         <v>1148</v>
       </c>
-      <c r="F332" s="2">
+      <c r="F332" s="1">
         <v>46125</v>
       </c>
       <c r="G332" t="s">
@@ -17260,7 +17240,7 @@
         <v>1353</v>
       </c>
       <c r="I332">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K332" t="s">
         <v>1357</v>
@@ -17288,7 +17268,7 @@
       <c r="E333" t="s">
         <v>910</v>
       </c>
-      <c r="F333" s="2">
+      <c r="F333" s="1">
         <v>46125</v>
       </c>
       <c r="G333" t="s">
@@ -17298,7 +17278,7 @@
         <v>1353</v>
       </c>
       <c r="I333">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J333">
         <v>100</v>
@@ -17309,7 +17289,7 @@
       <c r="L333" t="s">
         <v>1395</v>
       </c>
-      <c r="N333" s="2">
+      <c r="N333" s="1">
         <v>46225</v>
       </c>
       <c r="Q333" t="b">
@@ -17332,7 +17312,7 @@
       <c r="E334" t="s">
         <v>1149</v>
       </c>
-      <c r="F334" s="2">
+      <c r="F334" s="1">
         <v>46125</v>
       </c>
       <c r="G334" t="s">
@@ -17342,7 +17322,7 @@
         <v>1353</v>
       </c>
       <c r="I334">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K334" t="s">
         <v>1357</v>
@@ -17370,7 +17350,7 @@
       <c r="E335" t="s">
         <v>1150</v>
       </c>
-      <c r="F335" s="2">
+      <c r="F335" s="1">
         <v>46127</v>
       </c>
       <c r="G335" t="s">
@@ -17385,7 +17365,7 @@
       <c r="L335" t="s">
         <v>1434</v>
       </c>
-      <c r="N335" s="2">
+      <c r="N335" s="1">
         <v>46175</v>
       </c>
       <c r="Q335" t="b">
@@ -17408,7 +17388,7 @@
       <c r="E336" t="s">
         <v>1151</v>
       </c>
-      <c r="F336" s="2">
+      <c r="F336" s="1">
         <v>46127</v>
       </c>
       <c r="G336" t="s">
@@ -17418,7 +17398,7 @@
         <v>1353</v>
       </c>
       <c r="I336">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J336">
         <v>28</v>
@@ -17429,7 +17409,7 @@
       <c r="L336" t="s">
         <v>1388</v>
       </c>
-      <c r="N336" s="2">
+      <c r="N336" s="1">
         <v>46155</v>
       </c>
       <c r="Q336" t="b">
@@ -17452,7 +17432,7 @@
       <c r="E337" t="s">
         <v>1152</v>
       </c>
-      <c r="F337" s="2">
+      <c r="F337" s="1">
         <v>46127</v>
       </c>
       <c r="G337" t="s">
@@ -17467,7 +17447,7 @@
       <c r="L337" t="s">
         <v>1434</v>
       </c>
-      <c r="N337" s="2">
+      <c r="N337" s="1">
         <v>46175</v>
       </c>
       <c r="Q337" t="b">
@@ -17490,7 +17470,7 @@
       <c r="E338" t="s">
         <v>1153</v>
       </c>
-      <c r="F338" s="2">
+      <c r="F338" s="1">
         <v>46127</v>
       </c>
       <c r="G338" t="s">
@@ -17500,7 +17480,7 @@
         <v>1353</v>
       </c>
       <c r="I338">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J338">
         <v>12</v>
@@ -17511,7 +17491,7 @@
       <c r="L338" t="s">
         <v>1388</v>
       </c>
-      <c r="N338" s="2">
+      <c r="N338" s="1">
         <v>46139</v>
       </c>
       <c r="Q338" t="b">
@@ -17534,7 +17514,7 @@
       <c r="E339" t="s">
         <v>1154</v>
       </c>
-      <c r="F339" s="2">
+      <c r="F339" s="1">
         <v>46129</v>
       </c>
       <c r="G339" t="s">
@@ -17563,7 +17543,7 @@
       <c r="E340" t="s">
         <v>1155</v>
       </c>
-      <c r="F340" s="2">
+      <c r="F340" s="1">
         <v>46142</v>
       </c>
       <c r="G340" t="s">
@@ -17573,7 +17553,7 @@
         <v>1353</v>
       </c>
       <c r="I340">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J340">
         <v>98</v>
@@ -17581,7 +17561,7 @@
       <c r="L340" t="s">
         <v>1383</v>
       </c>
-      <c r="N340" s="2">
+      <c r="N340" s="1">
         <v>46240</v>
       </c>
       <c r="Q340" t="b">
@@ -17604,7 +17584,7 @@
       <c r="E341" t="s">
         <v>1156</v>
       </c>
-      <c r="F341" s="2">
+      <c r="F341" s="1">
         <v>46142</v>
       </c>
       <c r="G341" t="s">
@@ -17614,7 +17594,7 @@
         <v>1353</v>
       </c>
       <c r="I341">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J341">
         <v>90</v>
@@ -17622,7 +17602,7 @@
       <c r="L341" t="s">
         <v>1383</v>
       </c>
-      <c r="N341" s="2">
+      <c r="N341" s="1">
         <v>46232</v>
       </c>
       <c r="Q341" t="b">
@@ -17645,7 +17625,7 @@
       <c r="E342" t="s">
         <v>1157</v>
       </c>
-      <c r="F342" s="2">
+      <c r="F342" s="1">
         <v>46142</v>
       </c>
       <c r="G342" t="s">
@@ -17655,7 +17635,7 @@
         <v>1353</v>
       </c>
       <c r="I342">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K342" t="s">
         <v>1356</v>
@@ -17683,7 +17663,7 @@
       <c r="E343" t="s">
         <v>1158</v>
       </c>
-      <c r="F343" s="2">
+      <c r="F343" s="1">
         <v>46142</v>
       </c>
       <c r="G343" t="s">
@@ -17698,7 +17678,7 @@
       <c r="L343" t="s">
         <v>1383</v>
       </c>
-      <c r="N343" s="2">
+      <c r="N343" s="1">
         <v>46232</v>
       </c>
       <c r="Q343" t="b">
@@ -17721,7 +17701,7 @@
       <c r="E344" t="s">
         <v>1159</v>
       </c>
-      <c r="F344" s="2">
+      <c r="F344" s="1">
         <v>46142</v>
       </c>
       <c r="G344" t="s">
@@ -17736,7 +17716,7 @@
       <c r="L344" t="s">
         <v>1383</v>
       </c>
-      <c r="N344" s="2">
+      <c r="N344" s="1">
         <v>46232</v>
       </c>
       <c r="Q344" t="b">
@@ -17759,7 +17739,7 @@
       <c r="E345" t="s">
         <v>1160</v>
       </c>
-      <c r="F345" s="2">
+      <c r="F345" s="1">
         <v>46142</v>
       </c>
       <c r="G345" t="s">
@@ -17769,7 +17749,7 @@
         <v>1353</v>
       </c>
       <c r="I345">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K345" t="s">
         <v>1356</v>
@@ -17797,7 +17777,7 @@
       <c r="E346" t="s">
         <v>1161</v>
       </c>
-      <c r="F346" s="2">
+      <c r="F346" s="1">
         <v>46142</v>
       </c>
       <c r="G346" t="s">
@@ -17812,7 +17792,7 @@
       <c r="L346" t="s">
         <v>1383</v>
       </c>
-      <c r="N346" s="2">
+      <c r="N346" s="1">
         <v>46232</v>
       </c>
       <c r="Q346" t="b">
@@ -17835,7 +17815,7 @@
       <c r="E347" t="s">
         <v>1162</v>
       </c>
-      <c r="F347" s="2">
+      <c r="F347" s="1">
         <v>46142</v>
       </c>
       <c r="G347" t="s">
@@ -17845,7 +17825,7 @@
         <v>1353</v>
       </c>
       <c r="I347">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J347">
         <v>18</v>
@@ -17856,11 +17836,11 @@
       <c r="L347" t="s">
         <v>1431</v>
       </c>
-      <c r="N347" s="2">
+      <c r="N347" s="1">
         <v>46160</v>
       </c>
       <c r="P347" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="Q347" t="b">
         <v>1</v>
@@ -17882,7 +17862,7 @@
       <c r="E348" t="s">
         <v>1163</v>
       </c>
-      <c r="F348" s="2">
+      <c r="F348" s="1">
         <v>46142</v>
       </c>
       <c r="G348" t="s">
@@ -17892,7 +17872,7 @@
         <v>1353</v>
       </c>
       <c r="I348">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J348">
         <v>14</v>
@@ -17903,7 +17883,7 @@
       <c r="L348" t="s">
         <v>1432</v>
       </c>
-      <c r="N348" s="2">
+      <c r="N348" s="1">
         <v>46156</v>
       </c>
       <c r="Q348" t="b">
@@ -17926,7 +17906,7 @@
       <c r="E349" t="s">
         <v>1164</v>
       </c>
-      <c r="F349" s="2">
+      <c r="F349" s="1">
         <v>46142</v>
       </c>
       <c r="G349" t="s">
@@ -17936,7 +17916,7 @@
         <v>1353</v>
       </c>
       <c r="I349">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K349" t="s">
         <v>1361</v>
@@ -17964,7 +17944,7 @@
       <c r="E350" t="s">
         <v>1165</v>
       </c>
-      <c r="F350" s="2">
+      <c r="F350" s="1">
         <v>46142</v>
       </c>
       <c r="G350" t="s">
@@ -17974,12 +17954,12 @@
         <v>1353</v>
       </c>
       <c r="I350">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J350">
         <v>46</v>
       </c>
-      <c r="N350" s="2">
+      <c r="N350" s="1">
         <v>46188</v>
       </c>
       <c r="Q350" t="b">
@@ -18002,7 +17982,7 @@
       <c r="E351" t="s">
         <v>1166</v>
       </c>
-      <c r="F351" s="2">
+      <c r="F351" s="1">
         <v>46142</v>
       </c>
       <c r="G351" t="s">
@@ -18012,7 +17992,7 @@
         <v>1353</v>
       </c>
       <c r="I351">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J351">
         <v>82</v>
@@ -18023,7 +18003,7 @@
       <c r="L351" t="s">
         <v>1436</v>
       </c>
-      <c r="N351" s="2">
+      <c r="N351" s="1">
         <v>46224</v>
       </c>
       <c r="Q351" t="b">
@@ -18046,7 +18026,7 @@
       <c r="E352" t="s">
         <v>1167</v>
       </c>
-      <c r="F352" s="2">
+      <c r="F352" s="1">
         <v>46142</v>
       </c>
       <c r="G352" t="s">
@@ -18056,7 +18036,7 @@
         <v>1353</v>
       </c>
       <c r="I352">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J352">
         <v>78</v>
@@ -18067,7 +18047,7 @@
       <c r="L352" t="s">
         <v>1437</v>
       </c>
-      <c r="N352" s="2">
+      <c r="N352" s="1">
         <v>46220</v>
       </c>
       <c r="Q352" t="b">
@@ -18090,7 +18070,7 @@
       <c r="E353" t="s">
         <v>1168</v>
       </c>
-      <c r="F353" s="2">
+      <c r="F353" s="1">
         <v>46142</v>
       </c>
       <c r="G353" t="s">
@@ -18100,7 +18080,7 @@
         <v>1353</v>
       </c>
       <c r="I353">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J353">
         <v>83</v>
@@ -18111,7 +18091,7 @@
       <c r="L353" t="s">
         <v>1395</v>
       </c>
-      <c r="N353" s="2">
+      <c r="N353" s="1">
         <v>46225</v>
       </c>
       <c r="Q353" t="b">
@@ -18134,7 +18114,7 @@
       <c r="E354" t="s">
         <v>1169</v>
       </c>
-      <c r="F354" s="2">
+      <c r="F354" s="1">
         <v>46142</v>
       </c>
       <c r="G354" t="s">
@@ -18144,7 +18124,7 @@
         <v>1353</v>
       </c>
       <c r="I354">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K354" t="s">
         <v>1360</v>
@@ -18172,7 +18152,7 @@
       <c r="E355" t="s">
         <v>1170</v>
       </c>
-      <c r="F355" s="2">
+      <c r="F355" s="1">
         <v>46142</v>
       </c>
       <c r="G355" t="s">
@@ -18182,7 +18162,7 @@
         <v>1353</v>
       </c>
       <c r="I355">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J355">
         <v>8</v>
@@ -18193,7 +18173,7 @@
       <c r="L355" t="s">
         <v>1438</v>
       </c>
-      <c r="N355" s="2">
+      <c r="N355" s="1">
         <v>46150</v>
       </c>
       <c r="Q355" t="b">
@@ -18216,7 +18196,7 @@
       <c r="E356" t="s">
         <v>1171</v>
       </c>
-      <c r="F356" s="2">
+      <c r="F356" s="1">
         <v>46142</v>
       </c>
       <c r="G356" t="s">
@@ -18231,7 +18211,7 @@
       <c r="L356" t="s">
         <v>1439</v>
       </c>
-      <c r="N356" s="2">
+      <c r="N356" s="1">
         <v>46176</v>
       </c>
       <c r="Q356" t="b">
@@ -18254,7 +18234,7 @@
       <c r="E357" t="s">
         <v>1172</v>
       </c>
-      <c r="F357" s="2">
+      <c r="F357" s="1">
         <v>46142</v>
       </c>
       <c r="G357" t="s">
@@ -18264,7 +18244,7 @@
         <v>1353</v>
       </c>
       <c r="I357">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J357">
         <v>85</v>
@@ -18272,7 +18252,7 @@
       <c r="K357" t="s">
         <v>1360</v>
       </c>
-      <c r="N357" s="2">
+      <c r="N357" s="1">
         <v>46227</v>
       </c>
       <c r="Q357" t="b">
@@ -18295,7 +18275,7 @@
       <c r="E358" t="s">
         <v>1173</v>
       </c>
-      <c r="F358" s="2">
+      <c r="F358" s="1">
         <v>46142</v>
       </c>
       <c r="G358" t="s">
@@ -18313,11 +18293,11 @@
       <c r="L358" t="s">
         <v>1440</v>
       </c>
-      <c r="N358" s="2">
+      <c r="N358" s="1">
         <v>46227</v>
       </c>
       <c r="P358" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="Q358" t="b">
         <v>0</v>
@@ -18339,7 +18319,7 @@
       <c r="E359" t="s">
         <v>1174</v>
       </c>
-      <c r="F359" s="2">
+      <c r="F359" s="1">
         <v>46142</v>
       </c>
       <c r="G359" t="s">
@@ -18351,11 +18331,11 @@
       <c r="J359">
         <v>63</v>
       </c>
-      <c r="N359" s="2">
+      <c r="N359" s="1">
         <v>46205</v>
       </c>
       <c r="P359" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="Q359" t="b">
         <v>0</v>
@@ -18377,7 +18357,7 @@
       <c r="E360" t="s">
         <v>949</v>
       </c>
-      <c r="F360" s="2">
+      <c r="F360" s="1">
         <v>46142</v>
       </c>
       <c r="G360" t="s">
@@ -18387,7 +18367,7 @@
         <v>1353</v>
       </c>
       <c r="I360">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J360">
         <v>83</v>
@@ -18398,7 +18378,7 @@
       <c r="L360" t="s">
         <v>1395</v>
       </c>
-      <c r="N360" s="2">
+      <c r="N360" s="1">
         <v>46225</v>
       </c>
       <c r="O360" t="s">
@@ -18424,7 +18404,7 @@
       <c r="E361" t="s">
         <v>961</v>
       </c>
-      <c r="F361" s="2">
+      <c r="F361" s="1">
         <v>46142</v>
       </c>
       <c r="G361" t="s">
@@ -18434,7 +18414,7 @@
         <v>1353</v>
       </c>
       <c r="I361">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J361">
         <v>83</v>
@@ -18445,7 +18425,7 @@
       <c r="L361" t="s">
         <v>1395</v>
       </c>
-      <c r="N361" s="2">
+      <c r="N361" s="1">
         <v>46225</v>
       </c>
       <c r="Q361" t="b">
@@ -18468,7 +18448,7 @@
       <c r="E362" t="s">
         <v>1175</v>
       </c>
-      <c r="F362" s="2">
+      <c r="F362" s="1">
         <v>46142</v>
       </c>
       <c r="G362" t="s">
@@ -18478,7 +18458,7 @@
         <v>1353</v>
       </c>
       <c r="I362">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K362" t="s">
         <v>1360</v>
@@ -18506,7 +18486,7 @@
       <c r="E363" t="s">
         <v>1176</v>
       </c>
-      <c r="F363" s="2">
+      <c r="F363" s="1">
         <v>46142</v>
       </c>
       <c r="G363" t="s">
@@ -18516,7 +18496,7 @@
         <v>1353</v>
       </c>
       <c r="I363">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K363" t="s">
         <v>1360</v>
@@ -18544,7 +18524,7 @@
       <c r="E364" t="s">
         <v>958</v>
       </c>
-      <c r="F364" s="2">
+      <c r="F364" s="1">
         <v>46142</v>
       </c>
       <c r="G364" t="s">
@@ -18554,7 +18534,7 @@
         <v>1353</v>
       </c>
       <c r="I364">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J364">
         <v>83</v>
@@ -18565,7 +18545,7 @@
       <c r="L364" t="s">
         <v>1395</v>
       </c>
-      <c r="N364" s="2">
+      <c r="N364" s="1">
         <v>46225</v>
       </c>
       <c r="Q364" t="b">
@@ -18588,7 +18568,7 @@
       <c r="E365" t="s">
         <v>1177</v>
       </c>
-      <c r="F365" s="2">
+      <c r="F365" s="1">
         <v>46142</v>
       </c>
       <c r="G365" t="s">
@@ -18598,7 +18578,7 @@
         <v>1353</v>
       </c>
       <c r="I365">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J365">
         <v>15</v>
@@ -18606,7 +18586,7 @@
       <c r="K365" t="s">
         <v>1359</v>
       </c>
-      <c r="N365" s="2">
+      <c r="N365" s="1">
         <v>46157</v>
       </c>
       <c r="Q365" t="b">
@@ -18629,7 +18609,7 @@
       <c r="E366" t="s">
         <v>1178</v>
       </c>
-      <c r="F366" s="2">
+      <c r="F366" s="1">
         <v>46148</v>
       </c>
       <c r="G366" t="s">
@@ -18639,7 +18619,7 @@
         <v>1353</v>
       </c>
       <c r="I366">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J366">
         <v>77</v>
@@ -18650,7 +18630,7 @@
       <c r="L366" t="s">
         <v>1388</v>
       </c>
-      <c r="N366" s="2">
+      <c r="N366" s="1">
         <v>46225</v>
       </c>
       <c r="Q366" t="b">
@@ -18673,7 +18653,7 @@
       <c r="E367" t="s">
         <v>1179</v>
       </c>
-      <c r="F367" s="2">
+      <c r="F367" s="1">
         <v>46148</v>
       </c>
       <c r="G367" t="s">
@@ -18683,7 +18663,7 @@
         <v>1353</v>
       </c>
       <c r="I367">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J367">
         <v>77</v>
@@ -18694,7 +18674,7 @@
       <c r="L367" t="s">
         <v>1388</v>
       </c>
-      <c r="N367" s="2">
+      <c r="N367" s="1">
         <v>46225</v>
       </c>
       <c r="Q367" t="b">
@@ -18717,7 +18697,7 @@
       <c r="E368" t="s">
         <v>1180</v>
       </c>
-      <c r="F368" s="2">
+      <c r="F368" s="1">
         <v>46148</v>
       </c>
       <c r="G368" t="s">
@@ -18727,7 +18707,7 @@
         <v>1353</v>
       </c>
       <c r="I368">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J368">
         <v>77</v>
@@ -18738,7 +18718,7 @@
       <c r="L368" t="s">
         <v>1395</v>
       </c>
-      <c r="N368" s="2">
+      <c r="N368" s="1">
         <v>46225</v>
       </c>
       <c r="Q368" t="b">
@@ -18761,7 +18741,7 @@
       <c r="E369" t="s">
         <v>1181</v>
       </c>
-      <c r="F369" s="2">
+      <c r="F369" s="1">
         <v>46148</v>
       </c>
       <c r="G369" t="s">
@@ -18771,7 +18751,7 @@
         <v>1353</v>
       </c>
       <c r="I369">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K369" t="s">
         <v>1360</v>
@@ -18799,7 +18779,7 @@
       <c r="E370" t="s">
         <v>1182</v>
       </c>
-      <c r="F370" s="2">
+      <c r="F370" s="1">
         <v>46148</v>
       </c>
       <c r="G370" t="s">
@@ -18809,7 +18789,7 @@
         <v>1353</v>
       </c>
       <c r="I370">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K370" t="s">
         <v>1360</v>
@@ -18837,7 +18817,7 @@
       <c r="E371" t="s">
         <v>1183</v>
       </c>
-      <c r="F371" s="2">
+      <c r="F371" s="1">
         <v>46148</v>
       </c>
       <c r="G371" t="s">
@@ -18847,7 +18827,7 @@
         <v>1353</v>
       </c>
       <c r="I371">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J371">
         <v>16</v>
@@ -18858,7 +18838,7 @@
       <c r="L371" t="s">
         <v>1441</v>
       </c>
-      <c r="N371" s="2">
+      <c r="N371" s="1">
         <v>46164</v>
       </c>
       <c r="Q371" t="b">
@@ -18881,7 +18861,7 @@
       <c r="E372" t="s">
         <v>1184</v>
       </c>
-      <c r="F372" s="2">
+      <c r="F372" s="1">
         <v>46148</v>
       </c>
       <c r="G372" t="s">
@@ -18899,11 +18879,11 @@
       <c r="L372" t="s">
         <v>1428</v>
       </c>
-      <c r="N372" s="2">
+      <c r="N372" s="1">
         <v>46113</v>
       </c>
       <c r="P372" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="Q372" t="b">
         <v>0</v>
@@ -18925,7 +18905,7 @@
       <c r="E373" t="s">
         <v>1185</v>
       </c>
-      <c r="F373" s="2">
+      <c r="F373" s="1">
         <v>46149</v>
       </c>
       <c r="G373" t="s">
@@ -18935,7 +18915,7 @@
         <v>1353</v>
       </c>
       <c r="I373">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K373" t="s">
         <v>1356</v>
@@ -18963,7 +18943,7 @@
       <c r="E374" t="s">
         <v>1186</v>
       </c>
-      <c r="F374" s="2">
+      <c r="F374" s="1">
         <v>46149</v>
       </c>
       <c r="G374" t="s">
@@ -18973,7 +18953,7 @@
         <v>1353</v>
       </c>
       <c r="I374">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K374" t="s">
         <v>1356</v>
@@ -19001,7 +18981,7 @@
       <c r="E375" t="s">
         <v>1187</v>
       </c>
-      <c r="F375" s="2">
+      <c r="F375" s="1">
         <v>46154</v>
       </c>
       <c r="G375" t="s">
@@ -19011,7 +18991,7 @@
         <v>1353</v>
       </c>
       <c r="I375">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J375">
         <v>94</v>
@@ -19019,7 +18999,7 @@
       <c r="K375" t="s">
         <v>1360</v>
       </c>
-      <c r="N375" s="2">
+      <c r="N375" s="1">
         <v>46248</v>
       </c>
       <c r="Q375" t="b">
@@ -19042,7 +19022,7 @@
       <c r="E376" t="s">
         <v>1188</v>
       </c>
-      <c r="F376" s="2">
+      <c r="F376" s="1">
         <v>46154</v>
       </c>
       <c r="G376" t="s">
@@ -19052,7 +19032,7 @@
         <v>1353</v>
       </c>
       <c r="I376">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K376" t="s">
         <v>1360</v>
@@ -19080,7 +19060,7 @@
       <c r="E377" t="s">
         <v>1189</v>
       </c>
-      <c r="F377" s="2">
+      <c r="F377" s="1">
         <v>46154</v>
       </c>
       <c r="G377" t="s">
@@ -19092,14 +19072,14 @@
       <c r="K377" t="s">
         <v>1360</v>
       </c>
-      <c r="N377" s="2">
+      <c r="N377" s="1">
         <v>46176</v>
       </c>
       <c r="O377" t="s">
         <v>1472</v>
       </c>
       <c r="P377" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="Q377" t="b">
         <v>0</v>
@@ -19121,7 +19101,7 @@
       <c r="E378" t="s">
         <v>1190</v>
       </c>
-      <c r="F378" s="2">
+      <c r="F378" s="1">
         <v>46154</v>
       </c>
       <c r="G378" t="s">
@@ -19131,7 +19111,7 @@
         <v>1353</v>
       </c>
       <c r="I378">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K378" t="s">
         <v>1360</v>
@@ -19159,7 +19139,7 @@
       <c r="E379" t="s">
         <v>1191</v>
       </c>
-      <c r="F379" s="2">
+      <c r="F379" s="1">
         <v>46154</v>
       </c>
       <c r="G379" t="s">
@@ -19169,7 +19149,7 @@
         <v>1353</v>
       </c>
       <c r="I379">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J379">
         <v>20</v>
@@ -19180,7 +19160,7 @@
       <c r="L379" t="s">
         <v>1442</v>
       </c>
-      <c r="N379" s="2">
+      <c r="N379" s="1">
         <v>46174</v>
       </c>
       <c r="Q379" t="b">
@@ -19203,7 +19183,7 @@
       <c r="E380" t="s">
         <v>1192</v>
       </c>
-      <c r="F380" s="2">
+      <c r="F380" s="1">
         <v>46154</v>
       </c>
       <c r="G380" t="s">
@@ -19213,7 +19193,7 @@
         <v>1353</v>
       </c>
       <c r="I380">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J380">
         <v>94</v>
@@ -19224,7 +19204,7 @@
       <c r="L380" t="s">
         <v>1443</v>
       </c>
-      <c r="N380" s="2">
+      <c r="N380" s="1">
         <v>46248</v>
       </c>
       <c r="Q380" t="b">
@@ -19247,7 +19227,7 @@
       <c r="E381" t="s">
         <v>1193</v>
       </c>
-      <c r="F381" s="2">
+      <c r="F381" s="1">
         <v>46154</v>
       </c>
       <c r="G381" t="s">
@@ -19257,7 +19237,7 @@
         <v>1353</v>
       </c>
       <c r="I381">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K381" t="s">
         <v>1360</v>
@@ -19285,7 +19265,7 @@
       <c r="E382" t="s">
         <v>1194</v>
       </c>
-      <c r="F382" s="2">
+      <c r="F382" s="1">
         <v>46154</v>
       </c>
       <c r="G382" t="s">
@@ -19295,7 +19275,7 @@
         <v>1353</v>
       </c>
       <c r="I382">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K382" t="s">
         <v>1360</v>
@@ -19323,7 +19303,7 @@
       <c r="E383" t="s">
         <v>1195</v>
       </c>
-      <c r="F383" s="2">
+      <c r="F383" s="1">
         <v>46154</v>
       </c>
       <c r="G383" t="s">
@@ -19333,7 +19313,7 @@
         <v>1353</v>
       </c>
       <c r="I383">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J383">
         <v>71</v>
@@ -19344,7 +19324,7 @@
       <c r="L383" t="s">
         <v>1444</v>
       </c>
-      <c r="N383" s="2">
+      <c r="N383" s="1">
         <v>46225</v>
       </c>
       <c r="Q383" t="b">
@@ -19367,7 +19347,7 @@
       <c r="E384" t="s">
         <v>1196</v>
       </c>
-      <c r="F384" s="2">
+      <c r="F384" s="1">
         <v>46164</v>
       </c>
       <c r="G384" t="s">
@@ -19377,7 +19357,7 @@
         <v>1353</v>
       </c>
       <c r="I384">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K384" t="s">
         <v>1357</v>
@@ -19405,7 +19385,7 @@
       <c r="E385" t="s">
         <v>1197</v>
       </c>
-      <c r="F385" s="2">
+      <c r="F385" s="1">
         <v>46164</v>
       </c>
       <c r="G385" t="s">
@@ -19415,7 +19395,7 @@
         <v>1353</v>
       </c>
       <c r="I385">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J385">
         <v>102</v>
@@ -19426,7 +19406,7 @@
       <c r="L385" t="s">
         <v>1445</v>
       </c>
-      <c r="N385" s="2">
+      <c r="N385" s="1">
         <v>46266</v>
       </c>
       <c r="P385" t="s">
@@ -19452,7 +19432,7 @@
       <c r="E386" t="s">
         <v>1198</v>
       </c>
-      <c r="F386" s="2">
+      <c r="F386" s="1">
         <v>46171</v>
       </c>
       <c r="G386" t="s">
@@ -19462,7 +19442,7 @@
         <v>1353</v>
       </c>
       <c r="I386">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K386" t="s">
         <v>1360</v>
@@ -19490,7 +19470,7 @@
       <c r="E387" t="s">
         <v>1199</v>
       </c>
-      <c r="F387" s="2">
+      <c r="F387" s="1">
         <v>46171</v>
       </c>
       <c r="G387" t="s">
@@ -19500,7 +19480,7 @@
         <v>1353</v>
       </c>
       <c r="I387">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K387" t="s">
         <v>1360</v>
@@ -19528,7 +19508,7 @@
       <c r="E388" t="s">
         <v>851</v>
       </c>
-      <c r="F388" s="2">
+      <c r="F388" s="1">
         <v>46171</v>
       </c>
       <c r="G388" t="s">
@@ -19538,7 +19518,7 @@
         <v>1353</v>
       </c>
       <c r="I388">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J388">
         <v>-85</v>
@@ -19549,7 +19529,7 @@
       <c r="L388" t="s">
         <v>1446</v>
       </c>
-      <c r="N388" s="2">
+      <c r="N388" s="1">
         <v>46086</v>
       </c>
       <c r="Q388" t="b">
@@ -19572,7 +19552,7 @@
       <c r="E389" t="s">
         <v>1200</v>
       </c>
-      <c r="F389" s="2">
+      <c r="F389" s="1">
         <v>46171</v>
       </c>
       <c r="G389" t="s">
@@ -19582,7 +19562,7 @@
         <v>1353</v>
       </c>
       <c r="I389">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K389" t="s">
         <v>1361</v>
@@ -19610,7 +19590,7 @@
       <c r="E390" t="s">
         <v>1201</v>
       </c>
-      <c r="F390" s="2">
+      <c r="F390" s="1">
         <v>46171</v>
       </c>
       <c r="G390" t="s">
@@ -19628,11 +19608,11 @@
       <c r="L390" t="s">
         <v>1447</v>
       </c>
-      <c r="N390" s="2">
+      <c r="N390" s="1">
         <v>46191</v>
       </c>
       <c r="P390" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="Q390" t="b">
         <v>0</v>
@@ -19654,7 +19634,7 @@
       <c r="E391" t="s">
         <v>1202</v>
       </c>
-      <c r="F391" s="2">
+      <c r="F391" s="1">
         <v>46171</v>
       </c>
       <c r="G391" t="s">
@@ -19670,7 +19650,7 @@
         <v>1452</v>
       </c>
       <c r="P391" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="Q391" t="b">
         <v>0</v>
@@ -19692,7 +19672,7 @@
       <c r="E392" t="s">
         <v>1203</v>
       </c>
-      <c r="F392" s="2">
+      <c r="F392" s="1">
         <v>46171</v>
       </c>
       <c r="G392" t="s">
@@ -19707,7 +19687,7 @@
       <c r="L392" t="s">
         <v>1439</v>
       </c>
-      <c r="N392" s="2">
+      <c r="N392" s="1">
         <v>46176</v>
       </c>
       <c r="Q392" t="b">
@@ -19730,7 +19710,7 @@
       <c r="E393" t="s">
         <v>1204</v>
       </c>
-      <c r="F393" s="2">
+      <c r="F393" s="1">
         <v>46171</v>
       </c>
       <c r="G393" t="s">
@@ -19740,7 +19720,7 @@
         <v>1353</v>
       </c>
       <c r="I393">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J393">
         <v>20</v>
@@ -19751,7 +19731,7 @@
       <c r="L393" t="s">
         <v>1388</v>
       </c>
-      <c r="N393" s="2">
+      <c r="N393" s="1">
         <v>46191</v>
       </c>
       <c r="Q393" t="b">
@@ -19774,7 +19754,7 @@
       <c r="E394" t="s">
         <v>1205</v>
       </c>
-      <c r="F394" s="2">
+      <c r="F394" s="1">
         <v>46171</v>
       </c>
       <c r="G394" t="s">
@@ -19792,11 +19772,11 @@
       <c r="L394" t="s">
         <v>1448</v>
       </c>
-      <c r="N394" s="2">
+      <c r="N394" s="1">
         <v>46241</v>
       </c>
       <c r="P394" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="Q394" t="b">
         <v>0</v>
@@ -19818,7 +19798,7 @@
       <c r="E395" t="s">
         <v>1206</v>
       </c>
-      <c r="F395" s="2">
+      <c r="F395" s="1">
         <v>46171</v>
       </c>
       <c r="G395" t="s">
@@ -19836,11 +19816,11 @@
       <c r="L395" t="s">
         <v>1449</v>
       </c>
-      <c r="N395" s="2">
+      <c r="N395" s="1">
         <v>46191</v>
       </c>
       <c r="P395" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="Q395" t="b">
         <v>0</v>
@@ -19862,7 +19842,7 @@
       <c r="E396" t="s">
         <v>1207</v>
       </c>
-      <c r="F396" s="2">
+      <c r="F396" s="1">
         <v>46171</v>
       </c>
       <c r="G396" t="s">
@@ -19874,11 +19854,11 @@
       <c r="J396">
         <v>20</v>
       </c>
-      <c r="N396" s="2">
+      <c r="N396" s="1">
         <v>46191</v>
       </c>
       <c r="P396" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="Q396" t="b">
         <v>0</v>
@@ -19900,7 +19880,7 @@
       <c r="E397" t="s">
         <v>1208</v>
       </c>
-      <c r="F397" s="2">
+      <c r="F397" s="1">
         <v>46171</v>
       </c>
       <c r="G397" t="s">
@@ -19918,11 +19898,11 @@
       <c r="L397" t="s">
         <v>1448</v>
       </c>
-      <c r="N397" s="2">
+      <c r="N397" s="1">
         <v>46241</v>
       </c>
       <c r="P397" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="Q397" t="b">
         <v>0</v>
@@ -19944,7 +19924,7 @@
       <c r="E398" t="s">
         <v>1209</v>
       </c>
-      <c r="F398" s="2">
+      <c r="F398" s="1">
         <v>46171</v>
       </c>
       <c r="G398" t="s">
@@ -19962,11 +19942,11 @@
       <c r="L398" t="s">
         <v>1449</v>
       </c>
-      <c r="N398" s="2">
+      <c r="N398" s="1">
         <v>46191</v>
       </c>
       <c r="P398" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="Q398" t="b">
         <v>0</v>
@@ -19988,7 +19968,7 @@
       <c r="E399" t="s">
         <v>987</v>
       </c>
-      <c r="F399" s="2">
+      <c r="F399" s="1">
         <v>46163</v>
       </c>
       <c r="G399" t="s">
@@ -20003,7 +19983,7 @@
       <c r="L399" t="s">
         <v>1450</v>
       </c>
-      <c r="N399" s="2">
+      <c r="N399" s="1">
         <v>46171</v>
       </c>
       <c r="Q399" t="b">
@@ -20026,7 +20006,7 @@
       <c r="E400" t="s">
         <v>1210</v>
       </c>
-      <c r="F400" s="2">
+      <c r="F400" s="1">
         <v>46171</v>
       </c>
       <c r="G400" t="s">
@@ -20036,7 +20016,7 @@
         <v>1353</v>
       </c>
       <c r="I400">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K400" t="s">
         <v>1360</v>
@@ -20064,7 +20044,7 @@
       <c r="E401" t="s">
         <v>1211</v>
       </c>
-      <c r="F401" s="2">
+      <c r="F401" s="1">
         <v>46171</v>
       </c>
       <c r="G401" t="s">
@@ -20076,11 +20056,11 @@
       <c r="J401">
         <v>40</v>
       </c>
-      <c r="N401" s="2">
+      <c r="N401" s="1">
         <v>46211</v>
       </c>
       <c r="P401" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="Q401" t="b">
         <v>0</v>
@@ -20102,7 +20082,7 @@
       <c r="E402" t="s">
         <v>1212</v>
       </c>
-      <c r="F402" s="2">
+      <c r="F402" s="1">
         <v>46171</v>
       </c>
       <c r="G402" t="s">
@@ -20112,7 +20092,7 @@
         <v>1353</v>
       </c>
       <c r="I402">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K402" t="s">
         <v>1360</v>
@@ -20140,7 +20120,7 @@
       <c r="E403" t="s">
         <v>1213</v>
       </c>
-      <c r="F403" s="2">
+      <c r="F403" s="1">
         <v>46171</v>
       </c>
       <c r="G403" t="s">
@@ -20150,7 +20130,7 @@
         <v>1353</v>
       </c>
       <c r="I403">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J403">
         <v>83</v>
@@ -20161,7 +20141,7 @@
       <c r="L403" t="s">
         <v>1451</v>
       </c>
-      <c r="N403" s="2">
+      <c r="N403" s="1">
         <v>46254</v>
       </c>
       <c r="Q403" t="b">
@@ -20184,7 +20164,7 @@
       <c r="E404" t="s">
         <v>1214</v>
       </c>
-      <c r="F404" s="2">
+      <c r="F404" s="1">
         <v>46171</v>
       </c>
       <c r="G404" t="s">
@@ -20194,7 +20174,7 @@
         <v>1353</v>
       </c>
       <c r="I404">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K404" t="s">
         <v>1360</v>
@@ -20222,7 +20202,7 @@
       <c r="E405" t="s">
         <v>1215</v>
       </c>
-      <c r="F405" s="2">
+      <c r="F405" s="1">
         <v>46183</v>
       </c>
       <c r="G405" t="s">
@@ -20232,7 +20212,7 @@
         <v>1354</v>
       </c>
       <c r="P405" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q405" t="b">
         <v>0</v>
@@ -20254,7 +20234,7 @@
       <c r="E406" t="s">
         <v>1216</v>
       </c>
-      <c r="F406" s="2">
+      <c r="F406" s="1">
         <v>46183</v>
       </c>
       <c r="G406" t="s">
@@ -20264,7 +20244,7 @@
         <v>1353</v>
       </c>
       <c r="I406">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q406" t="b">
         <v>1</v>
@@ -20286,7 +20266,7 @@
       <c r="E407" t="s">
         <v>1217</v>
       </c>
-      <c r="F407" s="2">
+      <c r="F407" s="1">
         <v>46183</v>
       </c>
       <c r="G407" t="s">
@@ -20296,7 +20276,7 @@
         <v>1353</v>
       </c>
       <c r="I407">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q407" t="b">
         <v>1</v>
@@ -20318,7 +20298,7 @@
       <c r="E408" t="s">
         <v>1218</v>
       </c>
-      <c r="F408" s="2">
+      <c r="F408" s="1">
         <v>46183</v>
       </c>
       <c r="G408" t="s">
@@ -20328,7 +20308,7 @@
         <v>1353</v>
       </c>
       <c r="I408">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q408" t="b">
         <v>1</v>
@@ -20350,7 +20330,7 @@
       <c r="E409" t="s">
         <v>1219</v>
       </c>
-      <c r="F409" s="2">
+      <c r="F409" s="1">
         <v>46183</v>
       </c>
       <c r="G409" t="s">
@@ -20360,7 +20340,7 @@
         <v>1353</v>
       </c>
       <c r="I409">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q409" t="b">
         <v>1</v>
@@ -20382,7 +20362,7 @@
       <c r="E410" t="s">
         <v>1220</v>
       </c>
-      <c r="F410" s="2">
+      <c r="F410" s="1">
         <v>46183</v>
       </c>
       <c r="G410" t="s">
@@ -20392,7 +20372,7 @@
         <v>1353</v>
       </c>
       <c r="I410">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q410" t="b">
         <v>1</v>
@@ -20414,7 +20394,7 @@
       <c r="E411" t="s">
         <v>1221</v>
       </c>
-      <c r="F411" s="2">
+      <c r="F411" s="1">
         <v>46188</v>
       </c>
       <c r="G411" t="s">
@@ -20424,7 +20404,7 @@
         <v>1353</v>
       </c>
       <c r="I411">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q411" t="b">
         <v>1</v>
@@ -20446,7 +20426,7 @@
       <c r="E412" t="s">
         <v>1222</v>
       </c>
-      <c r="F412" s="2">
+      <c r="F412" s="1">
         <v>46188</v>
       </c>
       <c r="G412" t="s">
@@ -20456,7 +20436,7 @@
         <v>1353</v>
       </c>
       <c r="I412">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q412" t="b">
         <v>1</v>
@@ -20478,7 +20458,7 @@
       <c r="E413" t="s">
         <v>1223</v>
       </c>
-      <c r="F413" s="2">
+      <c r="F413" s="1">
         <v>46188</v>
       </c>
       <c r="G413" t="s">
@@ -20488,7 +20468,7 @@
         <v>1353</v>
       </c>
       <c r="I413">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q413" t="b">
         <v>1</v>
@@ -20510,7 +20490,7 @@
       <c r="E414" t="s">
         <v>1224</v>
       </c>
-      <c r="F414" s="2">
+      <c r="F414" s="1">
         <v>46188</v>
       </c>
       <c r="G414" t="s">
@@ -20539,7 +20519,7 @@
       <c r="E415" t="s">
         <v>1060</v>
       </c>
-      <c r="F415" s="2">
+      <c r="F415" s="1">
         <v>46188</v>
       </c>
       <c r="G415" t="s">
@@ -20568,7 +20548,7 @@
       <c r="E416" t="s">
         <v>1225</v>
       </c>
-      <c r="F416" s="2">
+      <c r="F416" s="1">
         <v>46188</v>
       </c>
       <c r="G416" t="s">
@@ -20578,7 +20558,7 @@
         <v>1353</v>
       </c>
       <c r="I416">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q416" t="b">
         <v>1</v>
@@ -20600,7 +20580,7 @@
       <c r="E417" t="s">
         <v>1226</v>
       </c>
-      <c r="F417" s="2">
+      <c r="F417" s="1">
         <v>46188</v>
       </c>
       <c r="G417" t="s">
@@ -20629,7 +20609,7 @@
       <c r="E418" t="s">
         <v>1227</v>
       </c>
-      <c r="F418" s="2">
+      <c r="F418" s="1">
         <v>46188</v>
       </c>
       <c r="G418" t="s">
@@ -20658,7 +20638,7 @@
       <c r="E419" t="s">
         <v>1228</v>
       </c>
-      <c r="F419" s="2">
+      <c r="F419" s="1">
         <v>46188</v>
       </c>
       <c r="G419" t="s">
@@ -20668,7 +20648,7 @@
         <v>1353</v>
       </c>
       <c r="I419">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q419" t="b">
         <v>1</v>
@@ -20690,7 +20670,7 @@
       <c r="E420" t="s">
         <v>1229</v>
       </c>
-      <c r="F420" s="2">
+      <c r="F420" s="1">
         <v>46188</v>
       </c>
       <c r="G420" t="s">
@@ -20700,7 +20680,7 @@
         <v>1353</v>
       </c>
       <c r="I420">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q420" t="b">
         <v>1</v>
@@ -20722,7 +20702,7 @@
       <c r="E421" t="s">
         <v>1230</v>
       </c>
-      <c r="F421" s="2">
+      <c r="F421" s="1">
         <v>46188</v>
       </c>
       <c r="G421" t="s">
@@ -20732,7 +20712,7 @@
         <v>1353</v>
       </c>
       <c r="I421">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q421" t="b">
         <v>1</v>
@@ -20754,7 +20734,7 @@
       <c r="E422" t="s">
         <v>1231</v>
       </c>
-      <c r="F422" s="2">
+      <c r="F422" s="1">
         <v>46188</v>
       </c>
       <c r="G422" t="s">
@@ -20764,7 +20744,7 @@
         <v>1353</v>
       </c>
       <c r="I422">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q422" t="b">
         <v>1</v>
@@ -20786,7 +20766,7 @@
       <c r="E423" t="s">
         <v>1232</v>
       </c>
-      <c r="F423" s="2">
+      <c r="F423" s="1">
         <v>46188</v>
       </c>
       <c r="G423" t="s">
@@ -20796,7 +20776,7 @@
         <v>1353</v>
       </c>
       <c r="I423">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q423" t="b">
         <v>1</v>
@@ -20818,7 +20798,7 @@
       <c r="E424" t="s">
         <v>1233</v>
       </c>
-      <c r="F424" s="2">
+      <c r="F424" s="1">
         <v>46188</v>
       </c>
       <c r="G424" t="s">
@@ -20828,7 +20808,7 @@
         <v>1353</v>
       </c>
       <c r="I424">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q424" t="b">
         <v>1</v>
@@ -20850,7 +20830,7 @@
       <c r="E425" t="s">
         <v>1234</v>
       </c>
-      <c r="F425" s="2">
+      <c r="F425" s="1">
         <v>46188</v>
       </c>
       <c r="G425" t="s">
@@ -20860,7 +20840,7 @@
         <v>1353</v>
       </c>
       <c r="I425">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q425" t="b">
         <v>1</v>
@@ -20882,7 +20862,7 @@
       <c r="E426" t="s">
         <v>1235</v>
       </c>
-      <c r="F426" s="2">
+      <c r="F426" s="1">
         <v>46188</v>
       </c>
       <c r="G426" t="s">
@@ -20892,7 +20872,7 @@
         <v>1353</v>
       </c>
       <c r="I426">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q426" t="b">
         <v>1</v>
@@ -20914,7 +20894,7 @@
       <c r="E427" t="s">
         <v>1236</v>
       </c>
-      <c r="F427" s="2">
+      <c r="F427" s="1">
         <v>46188</v>
       </c>
       <c r="G427" t="s">
@@ -20924,7 +20904,7 @@
         <v>1353</v>
       </c>
       <c r="I427">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q427" t="b">
         <v>1</v>
@@ -20946,7 +20926,7 @@
       <c r="E428" t="s">
         <v>1237</v>
       </c>
-      <c r="F428" s="2">
+      <c r="F428" s="1">
         <v>46188</v>
       </c>
       <c r="G428" t="s">
@@ -20975,7 +20955,7 @@
       <c r="E429" t="s">
         <v>1238</v>
       </c>
-      <c r="F429" s="2">
+      <c r="F429" s="1">
         <v>46188</v>
       </c>
       <c r="G429" t="s">
@@ -21004,7 +20984,7 @@
       <c r="E430" t="s">
         <v>1239</v>
       </c>
-      <c r="F430" s="2">
+      <c r="F430" s="1">
         <v>46188</v>
       </c>
       <c r="G430" t="s">
@@ -21014,7 +20994,7 @@
         <v>1353</v>
       </c>
       <c r="I430">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q430" t="b">
         <v>1</v>
@@ -21036,7 +21016,7 @@
       <c r="E431" t="s">
         <v>1240</v>
       </c>
-      <c r="F431" s="2">
+      <c r="F431" s="1">
         <v>46188</v>
       </c>
       <c r="G431" t="s">
@@ -21046,7 +21026,7 @@
         <v>1353</v>
       </c>
       <c r="I431">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q431" t="b">
         <v>1</v>
@@ -21068,7 +21048,7 @@
       <c r="E432" t="s">
         <v>1241</v>
       </c>
-      <c r="F432" s="2">
+      <c r="F432" s="1">
         <v>46188</v>
       </c>
       <c r="G432" t="s">
@@ -21078,7 +21058,7 @@
         <v>1353</v>
       </c>
       <c r="I432">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q432" t="b">
         <v>1</v>
@@ -21100,7 +21080,7 @@
       <c r="E433" t="s">
         <v>1242</v>
       </c>
-      <c r="F433" s="2">
+      <c r="F433" s="1">
         <v>46188</v>
       </c>
       <c r="G433" t="s">
@@ -21110,7 +21090,7 @@
         <v>1353</v>
       </c>
       <c r="I433">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q433" t="b">
         <v>1</v>
@@ -21132,7 +21112,7 @@
       <c r="E434" t="s">
         <v>1243</v>
       </c>
-      <c r="F434" s="2">
+      <c r="F434" s="1">
         <v>46188</v>
       </c>
       <c r="G434" t="s">
@@ -21142,7 +21122,7 @@
         <v>1353</v>
       </c>
       <c r="I434">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q434" t="b">
         <v>1</v>
@@ -21164,7 +21144,7 @@
       <c r="E435" t="s">
         <v>856</v>
       </c>
-      <c r="F435" s="2">
+      <c r="F435" s="1">
         <v>46188</v>
       </c>
       <c r="G435" t="s">
@@ -21174,7 +21154,7 @@
         <v>1353</v>
       </c>
       <c r="I435">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q435" t="b">
         <v>1</v>
@@ -21196,7 +21176,7 @@
       <c r="E436" t="s">
         <v>1244</v>
       </c>
-      <c r="F436" s="2">
+      <c r="F436" s="1">
         <v>46188</v>
       </c>
       <c r="G436" t="s">
@@ -21206,7 +21186,7 @@
         <v>1353</v>
       </c>
       <c r="I436">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q436" t="b">
         <v>1</v>
@@ -21228,7 +21208,7 @@
       <c r="E437" t="s">
         <v>1245</v>
       </c>
-      <c r="F437" s="2">
+      <c r="F437" s="1">
         <v>46188</v>
       </c>
       <c r="G437" t="s">
@@ -21238,7 +21218,7 @@
         <v>1355</v>
       </c>
       <c r="I437">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q437" t="b">
         <v>1</v>
@@ -21260,7 +21240,7 @@
       <c r="E438" t="s">
         <v>1246</v>
       </c>
-      <c r="F438" s="2">
+      <c r="F438" s="1">
         <v>46188</v>
       </c>
       <c r="G438" t="s">
@@ -21270,7 +21250,7 @@
         <v>1355</v>
       </c>
       <c r="I438">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q438" t="b">
         <v>1</v>
@@ -21292,7 +21272,7 @@
       <c r="E439" t="s">
         <v>1247</v>
       </c>
-      <c r="F439" s="2">
+      <c r="F439" s="1">
         <v>46196</v>
       </c>
       <c r="G439" t="s">
@@ -21302,7 +21282,7 @@
         <v>1353</v>
       </c>
       <c r="I439">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q439" t="b">
         <v>1</v>
@@ -21324,7 +21304,7 @@
       <c r="E440" t="s">
         <v>1248</v>
       </c>
-      <c r="F440" s="2">
+      <c r="F440" s="1">
         <v>46196</v>
       </c>
       <c r="G440" t="s">
@@ -21334,7 +21314,7 @@
         <v>1353</v>
       </c>
       <c r="I440">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q440" t="b">
         <v>1</v>
@@ -21356,7 +21336,7 @@
       <c r="E441" t="s">
         <v>1249</v>
       </c>
-      <c r="F441" s="2">
+      <c r="F441" s="1">
         <v>46203</v>
       </c>
       <c r="G441" t="s">
@@ -21366,7 +21346,7 @@
         <v>1353</v>
       </c>
       <c r="I441">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q441" t="b">
         <v>1</v>
@@ -21388,7 +21368,7 @@
       <c r="E442" t="s">
         <v>1250</v>
       </c>
-      <c r="F442" s="2">
+      <c r="F442" s="1">
         <v>46203</v>
       </c>
       <c r="G442" t="s">
@@ -21417,7 +21397,7 @@
       <c r="E443" t="s">
         <v>1251</v>
       </c>
-      <c r="F443" s="2">
+      <c r="F443" s="1">
         <v>46205</v>
       </c>
       <c r="G443" t="s">
@@ -21427,7 +21407,7 @@
         <v>1353</v>
       </c>
       <c r="I443">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q443" t="b">
         <v>1</v>
@@ -21449,7 +21429,7 @@
       <c r="E444" t="s">
         <v>1252</v>
       </c>
-      <c r="F444" s="2">
+      <c r="F444" s="1">
         <v>46205</v>
       </c>
       <c r="G444" t="s">
@@ -21478,7 +21458,7 @@
       <c r="E445" t="s">
         <v>1253</v>
       </c>
-      <c r="F445" s="2">
+      <c r="F445" s="1">
         <v>46205</v>
       </c>
       <c r="G445" t="s">
@@ -21507,7 +21487,7 @@
       <c r="E446" t="s">
         <v>1254</v>
       </c>
-      <c r="F446" s="2">
+      <c r="F446" s="1">
         <v>46211</v>
       </c>
       <c r="G446" t="s">
@@ -21517,7 +21497,7 @@
         <v>1353</v>
       </c>
       <c r="I446">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q446" t="b">
         <v>1</v>
@@ -21539,7 +21519,7 @@
       <c r="E447" t="s">
         <v>1255</v>
       </c>
-      <c r="F447" s="2">
+      <c r="F447" s="1">
         <v>46211</v>
       </c>
       <c r="G447" t="s">
@@ -21549,7 +21529,7 @@
         <v>1353</v>
       </c>
       <c r="I447">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q447" t="b">
         <v>1</v>
@@ -21571,7 +21551,7 @@
       <c r="E448" t="s">
         <v>1256</v>
       </c>
-      <c r="F448" s="2">
+      <c r="F448" s="1">
         <v>46226</v>
       </c>
       <c r="G448" t="s">
@@ -21581,7 +21561,7 @@
         <v>1353</v>
       </c>
       <c r="I448">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q448" t="b">
         <v>1</v>
@@ -21603,7 +21583,7 @@
       <c r="E449" t="s">
         <v>1257</v>
       </c>
-      <c r="F449" s="2">
+      <c r="F449" s="1">
         <v>46226</v>
       </c>
       <c r="G449" t="s">
@@ -21613,7 +21593,7 @@
         <v>1353</v>
       </c>
       <c r="I449">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q449" t="b">
         <v>1</v>
@@ -21635,7 +21615,7 @@
       <c r="E450" t="s">
         <v>1258</v>
       </c>
-      <c r="F450" s="2">
+      <c r="F450" s="1">
         <v>46226</v>
       </c>
       <c r="G450" t="s">
@@ -21645,7 +21625,7 @@
         <v>1353</v>
       </c>
       <c r="I450">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q450" t="b">
         <v>1</v>
@@ -21667,7 +21647,7 @@
       <c r="E451" t="s">
         <v>1035</v>
       </c>
-      <c r="F451" s="2">
+      <c r="F451" s="1">
         <v>46230</v>
       </c>
       <c r="G451" t="s">
@@ -21677,7 +21657,7 @@
         <v>1353</v>
       </c>
       <c r="I451">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q451" t="b">
         <v>1</v>
@@ -21699,7 +21679,7 @@
       <c r="E452" t="s">
         <v>1259</v>
       </c>
-      <c r="F452" s="2">
+      <c r="F452" s="1">
         <v>46230</v>
       </c>
       <c r="G452" t="s">
@@ -21709,7 +21689,7 @@
         <v>1353</v>
       </c>
       <c r="I452">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q452" t="b">
         <v>1</v>
@@ -21731,7 +21711,7 @@
       <c r="E453" t="s">
         <v>1260</v>
       </c>
-      <c r="F453" s="2">
+      <c r="F453" s="1">
         <v>46230</v>
       </c>
       <c r="G453" t="s">
@@ -21741,7 +21721,7 @@
         <v>1353</v>
       </c>
       <c r="I453">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q453" t="b">
         <v>1</v>
@@ -21763,7 +21743,7 @@
       <c r="E454" t="s">
         <v>1261</v>
       </c>
-      <c r="F454" s="2">
+      <c r="F454" s="1">
         <v>46230</v>
       </c>
       <c r="G454" t="s">
@@ -21773,7 +21753,7 @@
         <v>1353</v>
       </c>
       <c r="I454">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q454" t="b">
         <v>1</v>
@@ -21795,7 +21775,7 @@
       <c r="E455" t="s">
         <v>1262</v>
       </c>
-      <c r="F455" s="2">
+      <c r="F455" s="1">
         <v>46230</v>
       </c>
       <c r="G455" t="s">
@@ -21805,7 +21785,7 @@
         <v>1353</v>
       </c>
       <c r="I455">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q455" t="b">
         <v>1</v>
@@ -21827,7 +21807,7 @@
       <c r="E456" t="s">
         <v>1263</v>
       </c>
-      <c r="F456" s="2">
+      <c r="F456" s="1">
         <v>46230</v>
       </c>
       <c r="G456" t="s">
@@ -21837,7 +21817,7 @@
         <v>1353</v>
       </c>
       <c r="I456">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q456" t="b">
         <v>1</v>
@@ -21859,7 +21839,7 @@
       <c r="E457" t="s">
         <v>1264</v>
       </c>
-      <c r="F457" s="2">
+      <c r="F457" s="1">
         <v>46230</v>
       </c>
       <c r="G457" t="s">
@@ -21869,7 +21849,7 @@
         <v>1353</v>
       </c>
       <c r="I457">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q457" t="b">
         <v>1</v>
@@ -21891,7 +21871,7 @@
       <c r="E458" t="s">
         <v>1202</v>
       </c>
-      <c r="F458" s="2">
+      <c r="F458" s="1">
         <v>46231</v>
       </c>
       <c r="G458" t="s">
@@ -21901,7 +21881,7 @@
         <v>1353</v>
       </c>
       <c r="I458">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q458" t="b">
         <v>1</v>
@@ -21923,7 +21903,7 @@
       <c r="E459" t="s">
         <v>1265</v>
       </c>
-      <c r="F459" s="2">
+      <c r="F459" s="1">
         <v>46233</v>
       </c>
       <c r="G459" t="s">
@@ -21933,7 +21913,7 @@
         <v>1353</v>
       </c>
       <c r="I459">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q459" t="b">
         <v>1</v>
@@ -21955,7 +21935,7 @@
       <c r="E460" t="s">
         <v>1266</v>
       </c>
-      <c r="F460" s="2">
+      <c r="F460" s="1">
         <v>46233</v>
       </c>
       <c r="G460" t="s">
@@ -21965,7 +21945,7 @@
         <v>1353</v>
       </c>
       <c r="I460">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q460" t="b">
         <v>1</v>
@@ -21987,7 +21967,7 @@
       <c r="E461" t="s">
         <v>1267</v>
       </c>
-      <c r="F461" s="2">
+      <c r="F461" s="1">
         <v>46233</v>
       </c>
       <c r="G461" t="s">
@@ -21997,7 +21977,7 @@
         <v>1353</v>
       </c>
       <c r="I461">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q461" t="b">
         <v>1</v>
@@ -22019,7 +21999,7 @@
       <c r="E462" t="s">
         <v>1268</v>
       </c>
-      <c r="F462" s="2">
+      <c r="F462" s="1">
         <v>46233</v>
       </c>
       <c r="G462" t="s">
@@ -22029,7 +22009,7 @@
         <v>1353</v>
       </c>
       <c r="I462">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q462" t="b">
         <v>1</v>
@@ -22051,7 +22031,7 @@
       <c r="E463" t="s">
         <v>1269</v>
       </c>
-      <c r="F463" s="2">
+      <c r="F463" s="1">
         <v>46234</v>
       </c>
       <c r="G463" t="s">
@@ -22061,7 +22041,7 @@
         <v>1353</v>
       </c>
       <c r="I463">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q463" t="b">
         <v>1</v>
@@ -22083,7 +22063,7 @@
       <c r="E464" t="s">
         <v>1270</v>
       </c>
-      <c r="F464" s="2">
+      <c r="F464" s="1">
         <v>46230</v>
       </c>
       <c r="G464" t="s">
@@ -22093,7 +22073,7 @@
         <v>1353</v>
       </c>
       <c r="I464">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q464" t="b">
         <v>1</v>
@@ -22115,7 +22095,7 @@
       <c r="E465" t="s">
         <v>1271</v>
       </c>
-      <c r="F465" s="2">
+      <c r="F465" s="1">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
@@ -22125,7 +22105,7 @@
         <v>1353</v>
       </c>
       <c r="I465">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q465" t="b">
         <v>1</v>
@@ -22147,7 +22127,7 @@
       <c r="E466" t="s">
         <v>1272</v>
       </c>
-      <c r="F466" s="2">
+      <c r="F466" s="1">
         <v>46230</v>
       </c>
       <c r="G466" t="s">
@@ -22157,7 +22137,7 @@
         <v>1353</v>
       </c>
       <c r="I466">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q466" t="b">
         <v>1</v>
@@ -22179,7 +22159,7 @@
       <c r="E467" t="s">
         <v>1273</v>
       </c>
-      <c r="F467" s="2">
+      <c r="F467" s="1">
         <v>46230</v>
       </c>
       <c r="G467" t="s">
@@ -22189,7 +22169,7 @@
         <v>1353</v>
       </c>
       <c r="I467">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q467" t="b">
         <v>1</v>
@@ -22211,7 +22191,7 @@
       <c r="E468" t="s">
         <v>1274</v>
       </c>
-      <c r="F468" s="2">
+      <c r="F468" s="1">
         <v>46230</v>
       </c>
       <c r="G468" t="s">
@@ -22221,7 +22201,7 @@
         <v>1353</v>
       </c>
       <c r="I468">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q468" t="b">
         <v>1</v>
@@ -22243,7 +22223,7 @@
       <c r="E469" t="s">
         <v>1275</v>
       </c>
-      <c r="F469" s="2">
+      <c r="F469" s="1">
         <v>46230</v>
       </c>
       <c r="G469" t="s">
@@ -22253,7 +22233,7 @@
         <v>1353</v>
       </c>
       <c r="I469">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q469" t="b">
         <v>1</v>
@@ -22275,7 +22255,7 @@
       <c r="E470" t="s">
         <v>1276</v>
       </c>
-      <c r="F470" s="2">
+      <c r="F470" s="1">
         <v>46230</v>
       </c>
       <c r="G470" t="s">
@@ -22304,7 +22284,7 @@
       <c r="E471" t="s">
         <v>1277</v>
       </c>
-      <c r="F471" s="2">
+      <c r="F471" s="1">
         <v>46230</v>
       </c>
       <c r="G471" t="s">
@@ -22314,7 +22294,7 @@
         <v>1353</v>
       </c>
       <c r="I471">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q471" t="b">
         <v>1</v>
@@ -22336,7 +22316,7 @@
       <c r="E472" t="s">
         <v>1278</v>
       </c>
-      <c r="F472" s="2">
+      <c r="F472" s="1">
         <v>46230</v>
       </c>
       <c r="G472" t="s">
@@ -22346,7 +22326,7 @@
         <v>1353</v>
       </c>
       <c r="I472">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q472" t="b">
         <v>1</v>
@@ -22368,7 +22348,7 @@
       <c r="E473" t="s">
         <v>1279</v>
       </c>
-      <c r="F473" s="2">
+      <c r="F473" s="1">
         <v>46230</v>
       </c>
       <c r="G473" t="s">
@@ -22378,7 +22358,7 @@
         <v>1353</v>
       </c>
       <c r="I473">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q473" t="b">
         <v>1</v>
@@ -22400,7 +22380,7 @@
       <c r="E474" t="s">
         <v>1280</v>
       </c>
-      <c r="F474" s="2">
+      <c r="F474" s="1">
         <v>46231</v>
       </c>
       <c r="G474" t="s">
@@ -22410,7 +22390,7 @@
         <v>1353</v>
       </c>
       <c r="I474">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q474" t="b">
         <v>1</v>
@@ -22432,7 +22412,7 @@
       <c r="E475" t="s">
         <v>1281</v>
       </c>
-      <c r="F475" s="2">
+      <c r="F475" s="1">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
@@ -22442,7 +22422,7 @@
         <v>1353</v>
       </c>
       <c r="I475">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q475" t="b">
         <v>1</v>
@@ -22464,7 +22444,7 @@
       <c r="E476" t="s">
         <v>1282</v>
       </c>
-      <c r="F476" s="2">
+      <c r="F476" s="1">
         <v>46231</v>
       </c>
       <c r="G476" t="s">
@@ -22474,7 +22454,7 @@
         <v>1353</v>
       </c>
       <c r="I476">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q476" t="b">
         <v>1</v>
@@ -22496,7 +22476,7 @@
       <c r="E477" t="s">
         <v>1283</v>
       </c>
-      <c r="F477" s="2">
+      <c r="F477" s="1">
         <v>46231</v>
       </c>
       <c r="G477" t="s">
@@ -22506,7 +22486,7 @@
         <v>1353</v>
       </c>
       <c r="I477">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q477" t="b">
         <v>1</v>
@@ -22528,7 +22508,7 @@
       <c r="E478" t="s">
         <v>1284</v>
       </c>
-      <c r="F478" s="2">
+      <c r="F478" s="1">
         <v>46231</v>
       </c>
       <c r="G478" t="s">
@@ -22538,7 +22518,7 @@
         <v>1353</v>
       </c>
       <c r="I478">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q478" t="b">
         <v>1</v>
@@ -22560,7 +22540,7 @@
       <c r="E479" t="s">
         <v>1285</v>
       </c>
-      <c r="F479" s="2">
+      <c r="F479" s="1">
         <v>46231</v>
       </c>
       <c r="G479" t="s">
@@ -22570,7 +22550,7 @@
         <v>1353</v>
       </c>
       <c r="I479">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q479" t="b">
         <v>1</v>
@@ -22592,7 +22572,7 @@
       <c r="E480" t="s">
         <v>1286</v>
       </c>
-      <c r="F480" s="2">
+      <c r="F480" s="1">
         <v>46231</v>
       </c>
       <c r="G480" t="s">
@@ -22602,7 +22582,7 @@
         <v>1353</v>
       </c>
       <c r="I480">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q480" t="b">
         <v>1</v>
@@ -22624,7 +22604,7 @@
       <c r="E481" t="s">
         <v>1287</v>
       </c>
-      <c r="F481" s="2">
+      <c r="F481" s="1">
         <v>46231</v>
       </c>
       <c r="G481" t="s">
@@ -22634,7 +22614,7 @@
         <v>1353</v>
       </c>
       <c r="I481">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q481" t="b">
         <v>1</v>
@@ -22656,7 +22636,7 @@
       <c r="E482" t="s">
         <v>1288</v>
       </c>
-      <c r="F482" s="2">
+      <c r="F482" s="1">
         <v>46231</v>
       </c>
       <c r="G482" t="s">
@@ -22666,7 +22646,7 @@
         <v>1353</v>
       </c>
       <c r="I482">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q482" t="b">
         <v>1</v>
@@ -22688,7 +22668,7 @@
       <c r="E483" t="s">
         <v>1289</v>
       </c>
-      <c r="F483" s="2">
+      <c r="F483" s="1">
         <v>46231</v>
       </c>
       <c r="G483" t="s">
@@ -22698,7 +22678,7 @@
         <v>1353</v>
       </c>
       <c r="I483">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q483" t="b">
         <v>1</v>
@@ -22720,7 +22700,7 @@
       <c r="E484" t="s">
         <v>1290</v>
       </c>
-      <c r="F484" s="2">
+      <c r="F484" s="1">
         <v>46231</v>
       </c>
       <c r="G484" t="s">
@@ -22730,7 +22710,7 @@
         <v>1353</v>
       </c>
       <c r="I484">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q484" t="b">
         <v>1</v>
@@ -22752,7 +22732,7 @@
       <c r="E485" t="s">
         <v>1291</v>
       </c>
-      <c r="F485" s="2">
+      <c r="F485" s="1">
         <v>46231</v>
       </c>
       <c r="G485" t="s">
@@ -22762,7 +22742,7 @@
         <v>1353</v>
       </c>
       <c r="I485">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q485" t="b">
         <v>1</v>
@@ -22784,7 +22764,7 @@
       <c r="E486" t="s">
         <v>1292</v>
       </c>
-      <c r="F486" s="2">
+      <c r="F486" s="1">
         <v>46231</v>
       </c>
       <c r="G486" t="s">
@@ -22794,7 +22774,7 @@
         <v>1353</v>
       </c>
       <c r="I486">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q486" t="b">
         <v>1</v>
@@ -22816,7 +22796,7 @@
       <c r="E487" t="s">
         <v>1293</v>
       </c>
-      <c r="F487" s="2">
+      <c r="F487" s="1">
         <v>46231</v>
       </c>
       <c r="G487" t="s">
@@ -22826,7 +22806,7 @@
         <v>1353</v>
       </c>
       <c r="I487">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q487" t="b">
         <v>1</v>
@@ -22848,7 +22828,7 @@
       <c r="E488" t="s">
         <v>1294</v>
       </c>
-      <c r="F488" s="2">
+      <c r="F488" s="1">
         <v>46231</v>
       </c>
       <c r="G488" t="s">
@@ -22858,7 +22838,7 @@
         <v>1353</v>
       </c>
       <c r="I488">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q488" t="b">
         <v>1</v>
@@ -22880,7 +22860,7 @@
       <c r="E489" t="s">
         <v>1295</v>
       </c>
-      <c r="F489" s="2">
+      <c r="F489" s="1">
         <v>46231</v>
       </c>
       <c r="G489" t="s">
@@ -22890,7 +22870,7 @@
         <v>1353</v>
       </c>
       <c r="I489">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q489" t="b">
         <v>1</v>
@@ -22912,7 +22892,7 @@
       <c r="E490" t="s">
         <v>1296</v>
       </c>
-      <c r="F490" s="2">
+      <c r="F490" s="1">
         <v>46231</v>
       </c>
       <c r="G490" t="s">
@@ -22922,7 +22902,7 @@
         <v>1353</v>
       </c>
       <c r="I490">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q490" t="b">
         <v>1</v>
@@ -22944,7 +22924,7 @@
       <c r="E491" t="s">
         <v>1297</v>
       </c>
-      <c r="F491" s="2">
+      <c r="F491" s="1">
         <v>46231</v>
       </c>
       <c r="G491" t="s">
@@ -22954,7 +22934,7 @@
         <v>1353</v>
       </c>
       <c r="I491">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q491" t="b">
         <v>1</v>
@@ -22976,7 +22956,7 @@
       <c r="E492" t="s">
         <v>911</v>
       </c>
-      <c r="F492" s="2">
+      <c r="F492" s="1">
         <v>46231</v>
       </c>
       <c r="G492" t="s">
@@ -22986,7 +22966,7 @@
         <v>1355</v>
       </c>
       <c r="I492">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q492" t="b">
         <v>1</v>
@@ -23008,7 +22988,7 @@
       <c r="E493" t="s">
         <v>995</v>
       </c>
-      <c r="F493" s="2">
+      <c r="F493" s="1">
         <v>46231</v>
       </c>
       <c r="G493" t="s">
@@ -23018,7 +22998,7 @@
         <v>1355</v>
       </c>
       <c r="I493">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q493" t="b">
         <v>1</v>
@@ -23040,7 +23020,7 @@
       <c r="E494" t="s">
         <v>867</v>
       </c>
-      <c r="F494" s="2">
+      <c r="F494" s="1">
         <v>46231</v>
       </c>
       <c r="G494" t="s">
@@ -23050,7 +23030,7 @@
         <v>1355</v>
       </c>
       <c r="I494">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q494" t="b">
         <v>1</v>
@@ -23072,7 +23052,7 @@
       <c r="E495" t="s">
         <v>912</v>
       </c>
-      <c r="F495" s="2">
+      <c r="F495" s="1">
         <v>46231</v>
       </c>
       <c r="G495" t="s">
@@ -23082,7 +23062,7 @@
         <v>1355</v>
       </c>
       <c r="I495">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q495" t="b">
         <v>1</v>
@@ -23104,7 +23084,7 @@
       <c r="E496" t="s">
         <v>1048</v>
       </c>
-      <c r="F496" s="2">
+      <c r="F496" s="1">
         <v>46231</v>
       </c>
       <c r="G496" t="s">
@@ -23114,7 +23094,7 @@
         <v>1355</v>
       </c>
       <c r="I496">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q496" t="b">
         <v>1</v>
@@ -23136,7 +23116,7 @@
       <c r="E497" t="s">
         <v>1298</v>
       </c>
-      <c r="F497" s="2">
+      <c r="F497" s="1">
         <v>46231</v>
       </c>
       <c r="G497" t="s">
@@ -23146,7 +23126,7 @@
         <v>1353</v>
       </c>
       <c r="I497">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q497" t="b">
         <v>1</v>
@@ -23168,7 +23148,7 @@
       <c r="E498" t="s">
         <v>1299</v>
       </c>
-      <c r="F498" s="2">
+      <c r="F498" s="1">
         <v>46231</v>
       </c>
       <c r="G498" t="s">
@@ -23178,7 +23158,7 @@
         <v>1353</v>
       </c>
       <c r="I498">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q498" t="b">
         <v>1</v>
@@ -23200,7 +23180,7 @@
       <c r="E499" t="s">
         <v>1300</v>
       </c>
-      <c r="F499" s="2">
+      <c r="F499" s="1">
         <v>46231</v>
       </c>
       <c r="G499" t="s">
@@ -23210,7 +23190,7 @@
         <v>1355</v>
       </c>
       <c r="I499">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q499" t="b">
         <v>1</v>
@@ -23232,7 +23212,7 @@
       <c r="E500" t="s">
         <v>1301</v>
       </c>
-      <c r="F500" s="2">
+      <c r="F500" s="1">
         <v>46231</v>
       </c>
       <c r="G500" t="s">
@@ -23242,7 +23222,7 @@
         <v>1353</v>
       </c>
       <c r="I500">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q500" t="b">
         <v>1</v>
@@ -23264,7 +23244,7 @@
       <c r="E501" t="s">
         <v>1302</v>
       </c>
-      <c r="F501" s="2">
+      <c r="F501" s="1">
         <v>46231</v>
       </c>
       <c r="G501" t="s">
@@ -23274,7 +23254,7 @@
         <v>1353</v>
       </c>
       <c r="I501">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q501" t="b">
         <v>1</v>
@@ -23296,7 +23276,7 @@
       <c r="E502" t="s">
         <v>1303</v>
       </c>
-      <c r="F502" s="2">
+      <c r="F502" s="1">
         <v>46231</v>
       </c>
       <c r="G502" t="s">
@@ -23306,7 +23286,7 @@
         <v>1353</v>
       </c>
       <c r="I502">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q502" t="b">
         <v>1</v>
@@ -23328,7 +23308,7 @@
       <c r="E503" t="s">
         <v>1304</v>
       </c>
-      <c r="F503" s="2">
+      <c r="F503" s="1">
         <v>46231</v>
       </c>
       <c r="G503" t="s">
@@ -23338,7 +23318,7 @@
         <v>1353</v>
       </c>
       <c r="I503">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q503" t="b">
         <v>1</v>
@@ -23360,7 +23340,7 @@
       <c r="E504" t="s">
         <v>1305</v>
       </c>
-      <c r="F504" s="2">
+      <c r="F504" s="1">
         <v>46232</v>
       </c>
       <c r="G504" t="s">
@@ -23370,7 +23350,7 @@
         <v>1353</v>
       </c>
       <c r="I504">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q504" t="b">
         <v>1</v>
@@ -23392,7 +23372,7 @@
       <c r="E505" t="s">
         <v>1306</v>
       </c>
-      <c r="F505" s="2">
+      <c r="F505" s="1">
         <v>46232</v>
       </c>
       <c r="G505" t="s">
@@ -23402,7 +23382,7 @@
         <v>1353</v>
       </c>
       <c r="I505">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q505" t="b">
         <v>1</v>
@@ -23424,7 +23404,7 @@
       <c r="E506" t="s">
         <v>1307</v>
       </c>
-      <c r="F506" s="2">
+      <c r="F506" s="1">
         <v>46232</v>
       </c>
       <c r="G506" t="s">
@@ -23434,7 +23414,7 @@
         <v>1353</v>
       </c>
       <c r="I506">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q506" t="b">
         <v>1</v>
@@ -23456,7 +23436,7 @@
       <c r="E507" t="s">
         <v>1308</v>
       </c>
-      <c r="F507" s="2">
+      <c r="F507" s="1">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
@@ -23466,7 +23446,7 @@
         <v>1353</v>
       </c>
       <c r="I507">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q507" t="b">
         <v>1</v>
@@ -23488,7 +23468,7 @@
       <c r="E508" t="s">
         <v>1309</v>
       </c>
-      <c r="F508" s="2">
+      <c r="F508" s="1">
         <v>46237</v>
       </c>
       <c r="G508" t="s">
@@ -23517,7 +23497,7 @@
       <c r="E509" t="s">
         <v>1310</v>
       </c>
-      <c r="F509" s="2">
+      <c r="F509" s="1">
         <v>46237</v>
       </c>
       <c r="G509" t="s">
@@ -23527,7 +23507,7 @@
         <v>1353</v>
       </c>
       <c r="I509">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q509" t="b">
         <v>1</v>
@@ -23549,7 +23529,7 @@
       <c r="E510" t="s">
         <v>1311</v>
       </c>
-      <c r="F510" s="2">
+      <c r="F510" s="1">
         <v>46237</v>
       </c>
       <c r="G510" t="s">
@@ -23559,7 +23539,7 @@
         <v>1353</v>
       </c>
       <c r="I510">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q510" t="b">
         <v>1</v>
@@ -23581,7 +23561,7 @@
       <c r="E511" t="s">
         <v>1312</v>
       </c>
-      <c r="F511" s="2">
+      <c r="F511" s="1">
         <v>46240</v>
       </c>
       <c r="G511" t="s">
@@ -23591,7 +23571,7 @@
         <v>1353</v>
       </c>
       <c r="I511">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q511" t="b">
         <v>1</v>
@@ -23613,7 +23593,7 @@
       <c r="E512" t="s">
         <v>1313</v>
       </c>
-      <c r="F512" s="2">
+      <c r="F512" s="1">
         <v>46240</v>
       </c>
       <c r="G512" t="s">
@@ -23623,7 +23603,7 @@
         <v>1353</v>
       </c>
       <c r="I512">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q512" t="b">
         <v>1</v>
@@ -23645,7 +23625,7 @@
       <c r="E513" t="s">
         <v>1314</v>
       </c>
-      <c r="F513" s="2">
+      <c r="F513" s="1">
         <v>46244</v>
       </c>
       <c r="G513" t="s">
@@ -23655,7 +23635,7 @@
         <v>1353</v>
       </c>
       <c r="I513">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q513" t="b">
         <v>1</v>
@@ -23677,7 +23657,7 @@
       <c r="E514" t="s">
         <v>1315</v>
       </c>
-      <c r="F514" s="2">
+      <c r="F514" s="1">
         <v>46244</v>
       </c>
       <c r="G514" t="s">
@@ -23687,7 +23667,7 @@
         <v>1353</v>
       </c>
       <c r="I514">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q514" t="b">
         <v>1</v>
@@ -23709,7 +23689,7 @@
       <c r="E515" t="s">
         <v>1043</v>
       </c>
-      <c r="F515" s="2">
+      <c r="F515" s="1">
         <v>46244</v>
       </c>
       <c r="G515" t="s">
@@ -23719,7 +23699,7 @@
         <v>1353</v>
       </c>
       <c r="I515">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q515" t="b">
         <v>1</v>
@@ -23741,7 +23721,7 @@
       <c r="E516" t="s">
         <v>1316</v>
       </c>
-      <c r="F516" s="2">
+      <c r="F516" s="1">
         <v>46252</v>
       </c>
       <c r="G516" t="s">
@@ -23751,7 +23731,7 @@
         <v>1353</v>
       </c>
       <c r="I516">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q516" t="b">
         <v>1</v>
@@ -23773,7 +23753,7 @@
       <c r="E517" t="s">
         <v>1317</v>
       </c>
-      <c r="F517" s="2">
+      <c r="F517" s="1">
         <v>46252</v>
       </c>
       <c r="G517" t="s">
@@ -23783,7 +23763,7 @@
         <v>1353</v>
       </c>
       <c r="I517">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q517" t="b">
         <v>1</v>
@@ -23805,7 +23785,7 @@
       <c r="E518" t="s">
         <v>1318</v>
       </c>
-      <c r="F518" s="2">
+      <c r="F518" s="1">
         <v>46252</v>
       </c>
       <c r="G518" t="s">
@@ -23815,7 +23795,7 @@
         <v>1353</v>
       </c>
       <c r="I518">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q518" t="b">
         <v>1</v>
@@ -23837,7 +23817,7 @@
       <c r="E519" t="s">
         <v>1253</v>
       </c>
-      <c r="F519" s="2">
+      <c r="F519" s="1">
         <v>46254</v>
       </c>
       <c r="G519" t="s">
@@ -23847,7 +23827,7 @@
         <v>1353</v>
       </c>
       <c r="I519">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q519" t="b">
         <v>1</v>
@@ -23869,7 +23849,7 @@
       <c r="E520" t="s">
         <v>1319</v>
       </c>
-      <c r="F520" s="2">
+      <c r="F520" s="1">
         <v>46254</v>
       </c>
       <c r="G520" t="s">
@@ -23879,7 +23859,7 @@
         <v>1353</v>
       </c>
       <c r="I520">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q520" t="b">
         <v>1</v>
@@ -23901,7 +23881,7 @@
       <c r="E521" t="s">
         <v>1320</v>
       </c>
-      <c r="F521" s="2">
+      <c r="F521" s="1">
         <v>46254</v>
       </c>
       <c r="G521" t="s">
@@ -23911,7 +23891,7 @@
         <v>1353</v>
       </c>
       <c r="I521">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q521" t="b">
         <v>1</v>
@@ -23933,7 +23913,7 @@
       <c r="E522" t="s">
         <v>1253</v>
       </c>
-      <c r="F522" s="2">
+      <c r="F522" s="1">
         <v>46254</v>
       </c>
       <c r="G522" t="s">
@@ -23943,7 +23923,7 @@
         <v>1353</v>
       </c>
       <c r="I522">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q522" t="b">
         <v>1</v>
@@ -23965,7 +23945,7 @@
       <c r="E523" t="s">
         <v>1319</v>
       </c>
-      <c r="F523" s="2">
+      <c r="F523" s="1">
         <v>46254</v>
       </c>
       <c r="G523" t="s">
@@ -23975,7 +23955,7 @@
         <v>1353</v>
       </c>
       <c r="I523">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q523" t="b">
         <v>1</v>
@@ -23997,7 +23977,7 @@
       <c r="E524" t="s">
         <v>1321</v>
       </c>
-      <c r="F524" s="2">
+      <c r="F524" s="1">
         <v>46265</v>
       </c>
       <c r="G524" t="s">
@@ -24007,7 +23987,7 @@
         <v>1353</v>
       </c>
       <c r="I524">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q524" t="b">
         <v>1</v>
@@ -24029,7 +24009,7 @@
       <c r="E525" t="s">
         <v>1322</v>
       </c>
-      <c r="F525" s="2">
+      <c r="F525" s="1">
         <v>46265</v>
       </c>
       <c r="G525" t="s">
@@ -24039,7 +24019,7 @@
         <v>1353</v>
       </c>
       <c r="I525">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q525" t="b">
         <v>1</v>
@@ -24061,7 +24041,7 @@
       <c r="E526" t="s">
         <v>1323</v>
       </c>
-      <c r="F526" s="2">
+      <c r="F526" s="1">
         <v>46265</v>
       </c>
       <c r="G526" t="s">
@@ -24071,7 +24051,7 @@
         <v>1353</v>
       </c>
       <c r="I526">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q526" t="b">
         <v>1</v>
@@ -24093,7 +24073,7 @@
       <c r="E527" t="s">
         <v>1324</v>
       </c>
-      <c r="F527" s="2">
+      <c r="F527" s="1">
         <v>46265</v>
       </c>
       <c r="G527" t="s">
@@ -24103,7 +24083,7 @@
         <v>1353</v>
       </c>
       <c r="I527">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q527" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/base_reparaveis_tratada.xlsx
@@ -4532,8 +4532,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -4549,7 +4557,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4557,12 +4565,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4862,55 +4888,55 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4930,7 +4956,7 @@
       <c r="E2" t="s">
         <v>829</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>45698</v>
       </c>
       <c r="G2" t="s">
@@ -4940,7 +4966,7 @@
         <v>1353</v>
       </c>
       <c r="I2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K2" t="s">
         <v>1356</v>
@@ -4968,7 +4994,7 @@
       <c r="E3" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>45714</v>
       </c>
       <c r="G3" t="s">
@@ -4978,7 +5004,7 @@
         <v>1353</v>
       </c>
       <c r="I3">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K3" t="s">
         <v>1357</v>
@@ -5006,7 +5032,7 @@
       <c r="E4" t="s">
         <v>831</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>45714</v>
       </c>
       <c r="G4" t="s">
@@ -5016,7 +5042,7 @@
         <v>1353</v>
       </c>
       <c r="I4">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K4" t="s">
         <v>1357</v>
@@ -5044,7 +5070,7 @@
       <c r="E5" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>45714</v>
       </c>
       <c r="G5" t="s">
@@ -5054,7 +5080,7 @@
         <v>1353</v>
       </c>
       <c r="I5">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J5">
         <v>279</v>
@@ -5065,7 +5091,7 @@
       <c r="L5" t="s">
         <v>1367</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <v>45993</v>
       </c>
       <c r="Q5" t="b">
@@ -5088,7 +5114,7 @@
       <c r="E6" t="s">
         <v>833</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>45736</v>
       </c>
       <c r="G6" t="s">
@@ -5098,7 +5124,7 @@
         <v>1353</v>
       </c>
       <c r="I6">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J6">
         <v>153</v>
@@ -5109,7 +5135,7 @@
       <c r="L6" t="s">
         <v>1368</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="2">
         <v>45889</v>
       </c>
       <c r="Q6" t="b">
@@ -5132,7 +5158,7 @@
       <c r="E7" t="s">
         <v>834</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>45736</v>
       </c>
       <c r="G7" t="s">
@@ -5142,7 +5168,7 @@
         <v>1353</v>
       </c>
       <c r="I7">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J7">
         <v>112</v>
@@ -5153,7 +5179,7 @@
       <c r="L7" t="s">
         <v>1369</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="2">
         <v>45848</v>
       </c>
       <c r="O7" t="s">
@@ -5179,7 +5205,7 @@
       <c r="E8" t="s">
         <v>835</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>45736</v>
       </c>
       <c r="G8" t="s">
@@ -5208,7 +5234,7 @@
       <c r="E9" t="s">
         <v>836</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="2">
         <v>45736</v>
       </c>
       <c r="G9" t="s">
@@ -5218,7 +5244,7 @@
         <v>1353</v>
       </c>
       <c r="I9">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J9">
         <v>362</v>
@@ -5229,7 +5255,7 @@
       <c r="L9" t="s">
         <v>1370</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="2">
         <v>46098</v>
       </c>
       <c r="O9">
@@ -5255,7 +5281,7 @@
       <c r="E10" t="s">
         <v>837</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="2">
         <v>45736</v>
       </c>
       <c r="G10" t="s">
@@ -5265,7 +5291,7 @@
         <v>1353</v>
       </c>
       <c r="I10">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J10">
         <v>378</v>
@@ -5276,7 +5302,7 @@
       <c r="L10" t="s">
         <v>1371</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="2">
         <v>46114</v>
       </c>
       <c r="O10" t="s">
@@ -5302,7 +5328,7 @@
       <c r="E11" t="s">
         <v>838</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <v>45736</v>
       </c>
       <c r="G11" t="s">
@@ -5312,7 +5338,7 @@
         <v>1353</v>
       </c>
       <c r="I11">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J11">
         <v>112</v>
@@ -5323,7 +5349,7 @@
       <c r="L11" t="s">
         <v>1369</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="2">
         <v>45848</v>
       </c>
       <c r="O11" t="s">
@@ -5349,7 +5375,7 @@
       <c r="E12" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="2">
         <v>45736</v>
       </c>
       <c r="G12" t="s">
@@ -5359,7 +5385,7 @@
         <v>1353</v>
       </c>
       <c r="I12">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J12">
         <v>124</v>
@@ -5370,7 +5396,7 @@
       <c r="L12" t="s">
         <v>1372</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="2">
         <v>45860</v>
       </c>
       <c r="Q12" t="b">
@@ -5393,7 +5419,7 @@
       <c r="E13" t="s">
         <v>840</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <v>45736</v>
       </c>
       <c r="G13" t="s">
@@ -5422,7 +5448,7 @@
       <c r="E14" t="s">
         <v>841</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="2">
         <v>45736</v>
       </c>
       <c r="G14" t="s">
@@ -5432,7 +5458,7 @@
         <v>1353</v>
       </c>
       <c r="I14">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J14">
         <v>64</v>
@@ -5443,7 +5469,7 @@
       <c r="L14" t="s">
         <v>1373</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N14" s="2">
         <v>45800</v>
       </c>
       <c r="Q14" t="b">
@@ -5466,7 +5492,7 @@
       <c r="E15" t="s">
         <v>842</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="2">
         <v>45736</v>
       </c>
       <c r="G15" t="s">
@@ -5476,7 +5502,7 @@
         <v>1353</v>
       </c>
       <c r="I15">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K15" t="s">
         <v>1359</v>
@@ -5504,7 +5530,7 @@
       <c r="E16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <v>45736</v>
       </c>
       <c r="G16" t="s">
@@ -5514,7 +5540,7 @@
         <v>1353</v>
       </c>
       <c r="I16">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K16" t="s">
         <v>1356</v>
@@ -5542,7 +5568,7 @@
       <c r="E17" t="s">
         <v>844</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="2">
         <v>45736</v>
       </c>
       <c r="G17" t="s">
@@ -5552,7 +5578,7 @@
         <v>1353</v>
       </c>
       <c r="I17">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J17">
         <v>161</v>
@@ -5563,7 +5589,7 @@
       <c r="L17" t="s">
         <v>1368</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17" s="2">
         <v>45897</v>
       </c>
       <c r="Q17" t="b">
@@ -5586,7 +5612,7 @@
       <c r="E18" t="s">
         <v>845</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <v>45736</v>
       </c>
       <c r="G18" t="s">
@@ -5596,7 +5622,7 @@
         <v>1353</v>
       </c>
       <c r="I18">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J18">
         <v>66</v>
@@ -5607,7 +5633,7 @@
       <c r="L18" t="s">
         <v>1373</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="2">
         <v>45802</v>
       </c>
       <c r="Q18" t="b">
@@ -5630,7 +5656,7 @@
       <c r="E19" t="s">
         <v>846</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="2">
         <v>45736</v>
       </c>
       <c r="G19" t="s">
@@ -5659,7 +5685,7 @@
       <c r="E20" t="s">
         <v>847</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="2">
         <v>45736</v>
       </c>
       <c r="G20" t="s">
@@ -5669,7 +5695,7 @@
         <v>1353</v>
       </c>
       <c r="I20">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J20">
         <v>399</v>
@@ -5680,7 +5706,7 @@
       <c r="L20" t="s">
         <v>1374</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20" s="2">
         <v>46135</v>
       </c>
       <c r="Q20" t="b">
@@ -5703,7 +5729,7 @@
       <c r="E21" t="s">
         <v>848</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="2">
         <v>45736</v>
       </c>
       <c r="G21" t="s">
@@ -5732,7 +5758,7 @@
       <c r="E22" t="s">
         <v>849</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="2">
         <v>45736</v>
       </c>
       <c r="G22" t="s">
@@ -5742,7 +5768,7 @@
         <v>1353</v>
       </c>
       <c r="I22">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K22" t="s">
         <v>1360</v>
@@ -5770,7 +5796,7 @@
       <c r="E23" t="s">
         <v>850</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <v>45736</v>
       </c>
       <c r="G23" t="s">
@@ -5780,7 +5806,7 @@
         <v>1353</v>
       </c>
       <c r="I23">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J23">
         <v>229</v>
@@ -5791,7 +5817,7 @@
       <c r="L23" t="s">
         <v>1375</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23" s="2">
         <v>45965</v>
       </c>
       <c r="P23" t="s">
@@ -5817,7 +5843,7 @@
       <c r="E24" t="s">
         <v>851</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="2">
         <v>45736</v>
       </c>
       <c r="G24" t="s">
@@ -5846,7 +5872,7 @@
       <c r="E25" t="s">
         <v>852</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="2">
         <v>45736</v>
       </c>
       <c r="G25" t="s">
@@ -5875,7 +5901,7 @@
       <c r="E26" t="s">
         <v>853</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="2">
         <v>45736</v>
       </c>
       <c r="G26" t="s">
@@ -5885,7 +5911,7 @@
         <v>1353</v>
       </c>
       <c r="I26">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J26">
         <v>155</v>
@@ -5896,7 +5922,7 @@
       <c r="L26" t="s">
         <v>1376</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N26" s="2">
         <v>45891</v>
       </c>
       <c r="P26" t="s">
@@ -5922,7 +5948,7 @@
       <c r="E27" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="2">
         <v>45736</v>
       </c>
       <c r="G27" t="s">
@@ -5932,7 +5958,7 @@
         <v>1353</v>
       </c>
       <c r="I27">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K27" t="s">
         <v>1360</v>
@@ -5960,7 +5986,7 @@
       <c r="E28" t="s">
         <v>855</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="2">
         <v>45736</v>
       </c>
       <c r="G28" t="s">
@@ -5989,7 +6015,7 @@
       <c r="E29" t="s">
         <v>856</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="2">
         <v>45736</v>
       </c>
       <c r="G29" t="s">
@@ -6018,7 +6044,7 @@
       <c r="E30" t="s">
         <v>857</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="2">
         <v>45736</v>
       </c>
       <c r="G30" t="s">
@@ -6028,7 +6054,7 @@
         <v>1353</v>
       </c>
       <c r="I30">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J30">
         <v>209</v>
@@ -6039,7 +6065,7 @@
       <c r="L30" t="s">
         <v>1377</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30" s="2">
         <v>45945</v>
       </c>
       <c r="Q30" t="b">
@@ -6062,7 +6088,7 @@
       <c r="E31" t="s">
         <v>858</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="2">
         <v>45736</v>
       </c>
       <c r="G31" t="s">
@@ -6091,7 +6117,7 @@
       <c r="E32" t="s">
         <v>859</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="2">
         <v>45736</v>
       </c>
       <c r="G32" t="s">
@@ -6101,7 +6127,7 @@
         <v>1353</v>
       </c>
       <c r="I32">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K32" t="s">
         <v>1356</v>
@@ -6129,7 +6155,7 @@
       <c r="E33" t="s">
         <v>860</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="2">
         <v>45736</v>
       </c>
       <c r="G33" t="s">
@@ -6158,7 +6184,7 @@
       <c r="E34" t="s">
         <v>861</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="2">
         <v>45736</v>
       </c>
       <c r="G34" t="s">
@@ -6187,7 +6213,7 @@
       <c r="E35" t="s">
         <v>862</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="2">
         <v>45736</v>
       </c>
       <c r="G35" t="s">
@@ -6216,7 +6242,7 @@
       <c r="E36" t="s">
         <v>863</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="2">
         <v>45736</v>
       </c>
       <c r="G36" t="s">
@@ -6245,7 +6271,7 @@
       <c r="E37" t="s">
         <v>864</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="2">
         <v>45736</v>
       </c>
       <c r="G37" t="s">
@@ -6274,7 +6300,7 @@
       <c r="E38" t="s">
         <v>844</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="2">
         <v>45736</v>
       </c>
       <c r="G38" t="s">
@@ -6300,7 +6326,7 @@
       <c r="D39" t="s">
         <v>731</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="2">
         <v>45736</v>
       </c>
       <c r="G39" t="s">
@@ -6310,7 +6336,7 @@
         <v>1353</v>
       </c>
       <c r="I39">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K39" t="s">
         <v>1361</v>
@@ -6335,7 +6361,7 @@
       <c r="D40" t="s">
         <v>731</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="2">
         <v>45736</v>
       </c>
       <c r="G40" t="s">
@@ -6345,7 +6371,7 @@
         <v>1353</v>
       </c>
       <c r="I40">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K40" t="s">
         <v>1359</v>
@@ -6373,7 +6399,7 @@
       <c r="E41" t="s">
         <v>865</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="2">
         <v>45736</v>
       </c>
       <c r="G41" t="s">
@@ -6402,7 +6428,7 @@
       <c r="E42" t="s">
         <v>866</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="2">
         <v>45736</v>
       </c>
       <c r="G42" t="s">
@@ -6431,7 +6457,7 @@
       <c r="E43" t="s">
         <v>867</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="2">
         <v>45736</v>
       </c>
       <c r="G43" t="s">
@@ -6466,7 +6492,7 @@
       <c r="E44" t="s">
         <v>868</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="2">
         <v>45769</v>
       </c>
       <c r="G44" t="s">
@@ -6476,7 +6502,7 @@
         <v>1353</v>
       </c>
       <c r="I44">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J44">
         <v>87</v>
@@ -6487,7 +6513,7 @@
       <c r="L44" t="s">
         <v>1378</v>
       </c>
-      <c r="N44" s="1">
+      <c r="N44" s="2">
         <v>45856</v>
       </c>
       <c r="P44" t="s">
@@ -6513,7 +6539,7 @@
       <c r="E45" t="s">
         <v>869</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="2">
         <v>45769</v>
       </c>
       <c r="G45" t="s">
@@ -6523,7 +6549,7 @@
         <v>1353</v>
       </c>
       <c r="I45">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J45">
         <v>331</v>
@@ -6534,7 +6560,7 @@
       <c r="L45" t="s">
         <v>1379</v>
       </c>
-      <c r="N45" s="1">
+      <c r="N45" s="2">
         <v>46100</v>
       </c>
       <c r="O45">
@@ -6560,7 +6586,7 @@
       <c r="E46" t="s">
         <v>870</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="2">
         <v>45769</v>
       </c>
       <c r="G46" t="s">
@@ -6570,7 +6596,7 @@
         <v>1353</v>
       </c>
       <c r="I46">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K46" t="s">
         <v>1360</v>
@@ -6598,7 +6624,7 @@
       <c r="E47" t="s">
         <v>871</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="2">
         <v>45769</v>
       </c>
       <c r="G47" t="s">
@@ -6608,7 +6634,7 @@
         <v>1353</v>
       </c>
       <c r="I47">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J47">
         <v>344</v>
@@ -6619,7 +6645,7 @@
       <c r="L47" t="s">
         <v>1380</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N47" s="2">
         <v>46113</v>
       </c>
       <c r="P47" t="s">
@@ -6645,7 +6671,7 @@
       <c r="E48" t="s">
         <v>872</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="2">
         <v>45769</v>
       </c>
       <c r="G48" t="s">
@@ -6655,7 +6681,7 @@
         <v>1353</v>
       </c>
       <c r="I48">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K48" t="s">
         <v>1360</v>
@@ -6683,7 +6709,7 @@
       <c r="E49" t="s">
         <v>873</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="2">
         <v>45769</v>
       </c>
       <c r="G49" t="s">
@@ -6712,7 +6738,7 @@
       <c r="E50" t="s">
         <v>874</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="2">
         <v>45769</v>
       </c>
       <c r="G50" t="s">
@@ -6722,7 +6748,7 @@
         <v>1353</v>
       </c>
       <c r="I50">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K50" t="s">
         <v>1360</v>
@@ -6750,7 +6776,7 @@
       <c r="E51" t="s">
         <v>875</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="2">
         <v>45769</v>
       </c>
       <c r="G51" t="s">
@@ -6779,7 +6805,7 @@
       <c r="E52" t="s">
         <v>876</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="2">
         <v>45769</v>
       </c>
       <c r="G52" t="s">
@@ -6789,7 +6815,7 @@
         <v>1353</v>
       </c>
       <c r="I52">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K52" t="s">
         <v>1356</v>
@@ -6817,7 +6843,7 @@
       <c r="E53" t="s">
         <v>877</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="2">
         <v>45769</v>
       </c>
       <c r="G53" t="s">
@@ -6827,7 +6853,7 @@
         <v>1353</v>
       </c>
       <c r="I53">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K53" t="s">
         <v>1357</v>
@@ -6855,7 +6881,7 @@
       <c r="E54" t="s">
         <v>878</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="2">
         <v>45769</v>
       </c>
       <c r="G54" t="s">
@@ -6865,7 +6891,7 @@
         <v>1353</v>
       </c>
       <c r="I54">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K54" t="s">
         <v>1357</v>
@@ -6893,7 +6919,7 @@
       <c r="E55" t="s">
         <v>879</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="2">
         <v>45769</v>
       </c>
       <c r="G55" t="s">
@@ -6922,7 +6948,7 @@
       <c r="E56" t="s">
         <v>880</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="2">
         <v>45769</v>
       </c>
       <c r="G56" t="s">
@@ -6951,7 +6977,7 @@
       <c r="E57" t="s">
         <v>881</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="2">
         <v>45769</v>
       </c>
       <c r="G57" t="s">
@@ -6961,7 +6987,7 @@
         <v>1353</v>
       </c>
       <c r="I57">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K57" t="s">
         <v>1360</v>
@@ -6989,7 +7015,7 @@
       <c r="E58" t="s">
         <v>882</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="2">
         <v>45769</v>
       </c>
       <c r="G58" t="s">
@@ -7018,7 +7044,7 @@
       <c r="E59" t="s">
         <v>883</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="2">
         <v>45769</v>
       </c>
       <c r="G59" t="s">
@@ -7047,7 +7073,7 @@
       <c r="E60" t="s">
         <v>884</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="2">
         <v>45769</v>
       </c>
       <c r="G60" t="s">
@@ -7076,7 +7102,7 @@
       <c r="E61" t="s">
         <v>885</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="2">
         <v>45769</v>
       </c>
       <c r="G61" t="s">
@@ -7105,7 +7131,7 @@
       <c r="E62" t="s">
         <v>886</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="2">
         <v>45770</v>
       </c>
       <c r="G62" t="s">
@@ -7134,7 +7160,7 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="2">
         <v>45799</v>
       </c>
       <c r="G63" t="s">
@@ -7144,7 +7170,7 @@
         <v>1353</v>
       </c>
       <c r="I63">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J63">
         <v>293</v>
@@ -7155,7 +7181,7 @@
       <c r="L63" t="s">
         <v>1381</v>
       </c>
-      <c r="N63" s="1">
+      <c r="N63" s="2">
         <v>46092</v>
       </c>
       <c r="P63" t="s">
@@ -7181,7 +7207,7 @@
       <c r="E64" t="s">
         <v>888</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="2">
         <v>45799</v>
       </c>
       <c r="G64" t="s">
@@ -7191,7 +7217,7 @@
         <v>1353</v>
       </c>
       <c r="I64">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J64">
         <v>320</v>
@@ -7202,7 +7228,7 @@
       <c r="L64" t="s">
         <v>1382</v>
       </c>
-      <c r="N64" s="1">
+      <c r="N64" s="2">
         <v>46119</v>
       </c>
       <c r="Q64" t="b">
@@ -7225,7 +7251,7 @@
       <c r="E65" t="s">
         <v>889</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="2">
         <v>45799</v>
       </c>
       <c r="G65" t="s">
@@ -7254,7 +7280,7 @@
       <c r="E66" t="s">
         <v>890</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="2">
         <v>45799</v>
       </c>
       <c r="G66" t="s">
@@ -7283,7 +7309,7 @@
       <c r="E67" t="s">
         <v>891</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="2">
         <v>45799</v>
       </c>
       <c r="G67" t="s">
@@ -7312,7 +7338,7 @@
       <c r="E68" t="s">
         <v>892</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="2">
         <v>45799</v>
       </c>
       <c r="G68" t="s">
@@ -7341,7 +7367,7 @@
       <c r="E69" t="s">
         <v>893</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="2">
         <v>45803</v>
       </c>
       <c r="G69" t="s">
@@ -7370,7 +7396,7 @@
       <c r="E70" t="s">
         <v>894</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="2">
         <v>45803</v>
       </c>
       <c r="G70" t="s">
@@ -7380,7 +7406,7 @@
         <v>1353</v>
       </c>
       <c r="I70">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J70">
         <v>429</v>
@@ -7391,7 +7417,7 @@
       <c r="L70" t="s">
         <v>1383</v>
       </c>
-      <c r="N70" s="1">
+      <c r="N70" s="2">
         <v>46232</v>
       </c>
       <c r="Q70" t="b">
@@ -7414,7 +7440,7 @@
       <c r="E71" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="2">
         <v>45803</v>
       </c>
       <c r="G71" t="s">
@@ -7424,7 +7450,7 @@
         <v>1353</v>
       </c>
       <c r="I71">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J71">
         <v>429</v>
@@ -7435,7 +7461,7 @@
       <c r="L71" t="s">
         <v>1383</v>
       </c>
-      <c r="N71" s="1">
+      <c r="N71" s="2">
         <v>46232</v>
       </c>
       <c r="Q71" t="b">
@@ -7458,7 +7484,7 @@
       <c r="E72" t="s">
         <v>896</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="2">
         <v>45803</v>
       </c>
       <c r="G72" t="s">
@@ -7487,7 +7513,7 @@
       <c r="E73" t="s">
         <v>897</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="2">
         <v>45803</v>
       </c>
       <c r="G73" t="s">
@@ -7497,7 +7523,7 @@
         <v>1353</v>
       </c>
       <c r="I73">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K73" t="s">
         <v>1356</v>
@@ -7525,7 +7551,7 @@
       <c r="E74" t="s">
         <v>896</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="2">
         <v>45803</v>
       </c>
       <c r="G74" t="s">
@@ -7554,7 +7580,7 @@
       <c r="E75" t="s">
         <v>898</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="2">
         <v>45803</v>
       </c>
       <c r="G75" t="s">
@@ -7564,7 +7590,7 @@
         <v>1353</v>
       </c>
       <c r="I75">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J75">
         <v>429</v>
@@ -7575,7 +7601,7 @@
       <c r="L75" t="s">
         <v>1383</v>
       </c>
-      <c r="N75" s="1">
+      <c r="N75" s="2">
         <v>46232</v>
       </c>
       <c r="Q75" t="b">
@@ -7598,7 +7624,7 @@
       <c r="E76" t="s">
         <v>899</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="2">
         <v>45803</v>
       </c>
       <c r="G76" t="s">
@@ -7608,7 +7634,7 @@
         <v>1353</v>
       </c>
       <c r="I76">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K76" t="s">
         <v>1363</v>
@@ -7633,7 +7659,7 @@
       <c r="E77" t="s">
         <v>900</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="2">
         <v>45803</v>
       </c>
       <c r="G77" t="s">
@@ -7662,7 +7688,7 @@
       <c r="E78" t="s">
         <v>901</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78" s="2">
         <v>45803</v>
       </c>
       <c r="G78" t="s">
@@ -7691,7 +7717,7 @@
       <c r="E79" t="s">
         <v>902</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="2">
         <v>45803</v>
       </c>
       <c r="G79" t="s">
@@ -7701,7 +7727,7 @@
         <v>1353</v>
       </c>
       <c r="I79">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K79" t="s">
         <v>1363</v>
@@ -7726,7 +7752,7 @@
       <c r="E80" t="s">
         <v>903</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="2">
         <v>45803</v>
       </c>
       <c r="G80" t="s">
@@ -7736,7 +7762,7 @@
         <v>1353</v>
       </c>
       <c r="I80">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J80">
         <v>429</v>
@@ -7747,7 +7773,7 @@
       <c r="L80" t="s">
         <v>1383</v>
       </c>
-      <c r="N80" s="1">
+      <c r="N80" s="2">
         <v>46232</v>
       </c>
       <c r="Q80" t="b">
@@ -7770,7 +7796,7 @@
       <c r="E81" t="s">
         <v>904</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="2">
         <v>45813</v>
       </c>
       <c r="G81" t="s">
@@ -7799,7 +7825,7 @@
       <c r="E82" t="s">
         <v>905</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="2">
         <v>45813</v>
       </c>
       <c r="G82" t="s">
@@ -7809,7 +7835,7 @@
         <v>1353</v>
       </c>
       <c r="I82">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K82" t="s">
         <v>1360</v>
@@ -7837,7 +7863,7 @@
       <c r="E83" t="s">
         <v>906</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="2">
         <v>45813</v>
       </c>
       <c r="G83" t="s">
@@ -7866,7 +7892,7 @@
       <c r="E84" t="s">
         <v>907</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="2">
         <v>45813</v>
       </c>
       <c r="G84" t="s">
@@ -7876,7 +7902,7 @@
         <v>1353</v>
       </c>
       <c r="I84">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J84">
         <v>40</v>
@@ -7887,7 +7913,7 @@
       <c r="L84" t="s">
         <v>1384</v>
       </c>
-      <c r="N84" s="1">
+      <c r="N84" s="2">
         <v>45853</v>
       </c>
       <c r="O84">
@@ -7913,7 +7939,7 @@
       <c r="E85" t="s">
         <v>908</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85" s="2">
         <v>45813</v>
       </c>
       <c r="G85" t="s">
@@ -7923,7 +7949,7 @@
         <v>1353</v>
       </c>
       <c r="I85">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K85" t="s">
         <v>1357</v>
@@ -7951,7 +7977,7 @@
       <c r="E86" t="s">
         <v>909</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="2">
         <v>45813</v>
       </c>
       <c r="G86" t="s">
@@ -7961,7 +7987,7 @@
         <v>1353</v>
       </c>
       <c r="I86">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K86" t="s">
         <v>1357</v>
@@ -7989,7 +8015,7 @@
       <c r="E87" t="s">
         <v>910</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="2">
         <v>45813</v>
       </c>
       <c r="G87" t="s">
@@ -7999,7 +8025,7 @@
         <v>1353</v>
       </c>
       <c r="I87">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J87">
         <v>-16</v>
@@ -8010,7 +8036,7 @@
       <c r="L87" t="s">
         <v>1385</v>
       </c>
-      <c r="N87" s="1">
+      <c r="N87" s="2">
         <v>45797</v>
       </c>
       <c r="O87" t="s">
@@ -8036,7 +8062,7 @@
       <c r="E88" t="s">
         <v>911</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="2">
         <v>45813</v>
       </c>
       <c r="G88" t="s">
@@ -8051,7 +8077,7 @@
       <c r="L88" t="s">
         <v>1386</v>
       </c>
-      <c r="N88" s="1">
+      <c r="N88" s="2">
         <v>46195</v>
       </c>
       <c r="Q88" t="b">
@@ -8074,7 +8100,7 @@
       <c r="E89" t="s">
         <v>912</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89" s="2">
         <v>45813</v>
       </c>
       <c r="G89" t="s">
@@ -8089,7 +8115,7 @@
       <c r="L89" t="s">
         <v>1386</v>
       </c>
-      <c r="N89" s="1">
+      <c r="N89" s="2">
         <v>46195</v>
       </c>
       <c r="Q89" t="b">
@@ -8112,7 +8138,7 @@
       <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90" s="2">
         <v>45831</v>
       </c>
       <c r="G90" t="s">
@@ -8122,7 +8148,7 @@
         <v>1353</v>
       </c>
       <c r="I90">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K90" t="s">
         <v>1330</v>
@@ -8153,7 +8179,7 @@
       <c r="E91" t="s">
         <v>914</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="2">
         <v>45831</v>
       </c>
       <c r="G91" t="s">
@@ -8163,7 +8189,7 @@
         <v>1353</v>
       </c>
       <c r="I91">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J91">
         <v>308</v>
@@ -8174,7 +8200,7 @@
       <c r="L91" t="s">
         <v>1388</v>
       </c>
-      <c r="N91" s="1">
+      <c r="N91" s="2">
         <v>46139</v>
       </c>
       <c r="Q91" t="b">
@@ -8194,7 +8220,7 @@
       <c r="D92" t="s">
         <v>748</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92" s="2">
         <v>45831</v>
       </c>
       <c r="G92" t="s">
@@ -8223,7 +8249,7 @@
       <c r="E93" t="s">
         <v>915</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93" s="2">
         <v>45831</v>
       </c>
       <c r="G93" t="s">
@@ -8233,7 +8259,7 @@
         <v>1353</v>
       </c>
       <c r="I93">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J93">
         <v>308</v>
@@ -8244,7 +8270,7 @@
       <c r="L93" t="s">
         <v>1388</v>
       </c>
-      <c r="N93" s="1">
+      <c r="N93" s="2">
         <v>46139</v>
       </c>
       <c r="Q93" t="b">
@@ -8267,7 +8293,7 @@
       <c r="E94" t="s">
         <v>916</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94" s="2">
         <v>45831</v>
       </c>
       <c r="G94" t="s">
@@ -8277,7 +8303,7 @@
         <v>1353</v>
       </c>
       <c r="I94">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K94" t="s">
         <v>1360</v>
@@ -8305,7 +8331,7 @@
       <c r="E95" t="s">
         <v>917</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95" s="2">
         <v>45831</v>
       </c>
       <c r="G95" t="s">
@@ -8315,7 +8341,7 @@
         <v>1353</v>
       </c>
       <c r="I95">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J95">
         <v>308</v>
@@ -8326,7 +8352,7 @@
       <c r="L95" t="s">
         <v>1388</v>
       </c>
-      <c r="N95" s="1">
+      <c r="N95" s="2">
         <v>46139</v>
       </c>
       <c r="Q95" t="b">
@@ -8349,7 +8375,7 @@
       <c r="E96" t="s">
         <v>918</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96" s="2">
         <v>45831</v>
       </c>
       <c r="G96" t="s">
@@ -8359,7 +8385,7 @@
         <v>1353</v>
       </c>
       <c r="I96">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J96">
         <v>17</v>
@@ -8370,7 +8396,7 @@
       <c r="L96" t="s">
         <v>1369</v>
       </c>
-      <c r="N96" s="1">
+      <c r="N96" s="2">
         <v>45848</v>
       </c>
       <c r="O96" t="s">
@@ -8396,7 +8422,7 @@
       <c r="E97" t="s">
         <v>919</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="2">
         <v>45840</v>
       </c>
       <c r="G97" t="s">
@@ -8406,7 +8432,7 @@
         <v>1353</v>
       </c>
       <c r="I97">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J97">
         <v>20</v>
@@ -8417,7 +8443,7 @@
       <c r="L97" t="s">
         <v>1389</v>
       </c>
-      <c r="N97" s="1">
+      <c r="N97" s="2">
         <v>45860</v>
       </c>
       <c r="P97" t="s">
@@ -8443,7 +8469,7 @@
       <c r="E98" t="s">
         <v>920</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="2">
         <v>45840</v>
       </c>
       <c r="G98" t="s">
@@ -8453,7 +8479,7 @@
         <v>1353</v>
       </c>
       <c r="I98">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K98" t="s">
         <v>1360</v>
@@ -8481,7 +8507,7 @@
       <c r="E99" t="s">
         <v>921</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99" s="2">
         <v>45840</v>
       </c>
       <c r="G99" t="s">
@@ -8510,7 +8536,7 @@
       <c r="E100" t="s">
         <v>922</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100" s="2">
         <v>45840</v>
       </c>
       <c r="G100" t="s">
@@ -8520,7 +8546,7 @@
         <v>1353</v>
       </c>
       <c r="I100">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J100">
         <v>348</v>
@@ -8531,7 +8557,7 @@
       <c r="L100" t="s">
         <v>1388</v>
       </c>
-      <c r="N100" s="1">
+      <c r="N100" s="2">
         <v>46188</v>
       </c>
       <c r="Q100" t="b">
@@ -8554,7 +8580,7 @@
       <c r="E101" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101" s="2">
         <v>45840</v>
       </c>
       <c r="G101" t="s">
@@ -8583,7 +8609,7 @@
       <c r="E102" t="s">
         <v>924</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102" s="2">
         <v>45840</v>
       </c>
       <c r="G102" t="s">
@@ -8612,7 +8638,7 @@
       <c r="E103" t="s">
         <v>925</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103" s="2">
         <v>45840</v>
       </c>
       <c r="G103" t="s">
@@ -8641,7 +8667,7 @@
       <c r="E104" t="s">
         <v>926</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104" s="2">
         <v>45840</v>
       </c>
       <c r="G104" t="s">
@@ -8651,7 +8677,7 @@
         <v>1353</v>
       </c>
       <c r="I104">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J104">
         <v>348</v>
@@ -8662,7 +8688,7 @@
       <c r="L104" t="s">
         <v>1388</v>
       </c>
-      <c r="N104" s="1">
+      <c r="N104" s="2">
         <v>46188</v>
       </c>
       <c r="Q104" t="b">
@@ -8685,7 +8711,7 @@
       <c r="E105" t="s">
         <v>927</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105" s="2">
         <v>45840</v>
       </c>
       <c r="G105" t="s">
@@ -8695,7 +8721,7 @@
         <v>1353</v>
       </c>
       <c r="I105">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J105">
         <v>348</v>
@@ -8706,7 +8732,7 @@
       <c r="L105" t="s">
         <v>1388</v>
       </c>
-      <c r="N105" s="1">
+      <c r="N105" s="2">
         <v>46188</v>
       </c>
       <c r="Q105" t="b">
@@ -8729,7 +8755,7 @@
       <c r="E106" t="s">
         <v>928</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106" s="2">
         <v>45840</v>
       </c>
       <c r="G106" t="s">
@@ -8739,7 +8765,7 @@
         <v>1353</v>
       </c>
       <c r="I106">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J106">
         <v>49</v>
@@ -8750,7 +8776,7 @@
       <c r="L106" t="s">
         <v>1390</v>
       </c>
-      <c r="N106" s="1">
+      <c r="N106" s="2">
         <v>45889</v>
       </c>
       <c r="Q106" t="b">
@@ -8773,7 +8799,7 @@
       <c r="E107" t="s">
         <v>929</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="2">
         <v>45840</v>
       </c>
       <c r="G107" t="s">
@@ -8783,7 +8809,7 @@
         <v>1353</v>
       </c>
       <c r="I107">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J107">
         <v>36</v>
@@ -8794,7 +8820,7 @@
       <c r="L107" t="s">
         <v>1391</v>
       </c>
-      <c r="N107" s="1">
+      <c r="N107" s="2">
         <v>45876</v>
       </c>
       <c r="Q107" t="b">
@@ -8817,7 +8843,7 @@
       <c r="E108" t="s">
         <v>930</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108" s="2">
         <v>45840</v>
       </c>
       <c r="G108" t="s">
@@ -8827,7 +8853,7 @@
         <v>1353</v>
       </c>
       <c r="I108">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K108" t="s">
         <v>1357</v>
@@ -8855,7 +8881,7 @@
       <c r="E109" t="s">
         <v>931</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109" s="2">
         <v>45840</v>
       </c>
       <c r="G109" t="s">
@@ -8865,7 +8891,7 @@
         <v>1353</v>
       </c>
       <c r="I109">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K109" t="s">
         <v>1357</v>
@@ -8893,7 +8919,7 @@
       <c r="E110" t="s">
         <v>932</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="2">
         <v>45840</v>
       </c>
       <c r="G110" t="s">
@@ -8922,7 +8948,7 @@
       <c r="E111" t="s">
         <v>933</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="2">
         <v>45840</v>
       </c>
       <c r="G111" t="s">
@@ -8951,7 +8977,7 @@
       <c r="E112" t="s">
         <v>934</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112" s="2">
         <v>45840</v>
       </c>
       <c r="G112" t="s">
@@ -8980,7 +9006,7 @@
       <c r="E113" t="s">
         <v>935</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113" s="2">
         <v>45840</v>
       </c>
       <c r="G113" t="s">
@@ -9009,7 +9035,7 @@
       <c r="E114" t="s">
         <v>936</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114" s="2">
         <v>45840</v>
       </c>
       <c r="G114" t="s">
@@ -9038,7 +9064,7 @@
       <c r="E115" t="s">
         <v>937</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115" s="2">
         <v>45840</v>
       </c>
       <c r="G115" t="s">
@@ -9048,7 +9074,7 @@
         <v>1353</v>
       </c>
       <c r="I115">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K115" t="s">
         <v>1357</v>
@@ -9076,7 +9102,7 @@
       <c r="E116" t="s">
         <v>938</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116" s="2">
         <v>45840</v>
       </c>
       <c r="G116" t="s">
@@ -9086,7 +9112,7 @@
         <v>1353</v>
       </c>
       <c r="I116">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K116" t="s">
         <v>1357</v>
@@ -9114,7 +9140,7 @@
       <c r="E117" t="s">
         <v>939</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117" s="2">
         <v>45840</v>
       </c>
       <c r="G117" t="s">
@@ -9124,7 +9150,7 @@
         <v>1353</v>
       </c>
       <c r="I117">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K117" t="s">
         <v>1357</v>
@@ -9152,7 +9178,7 @@
       <c r="E118" t="s">
         <v>940</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118" s="2">
         <v>45840</v>
       </c>
       <c r="G118" t="s">
@@ -9162,7 +9188,7 @@
         <v>1353</v>
       </c>
       <c r="I118">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K118" t="s">
         <v>1357</v>
@@ -9190,7 +9216,7 @@
       <c r="E119" t="s">
         <v>941</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119" s="2">
         <v>45840</v>
       </c>
       <c r="G119" t="s">
@@ -9200,7 +9226,7 @@
         <v>1353</v>
       </c>
       <c r="I119">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K119" t="s">
         <v>1357</v>
@@ -9228,7 +9254,7 @@
       <c r="E120" t="s">
         <v>942</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120" s="2">
         <v>45840</v>
       </c>
       <c r="G120" t="s">
@@ -9238,7 +9264,7 @@
         <v>1353</v>
       </c>
       <c r="I120">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K120" t="s">
         <v>1357</v>
@@ -9266,7 +9292,7 @@
       <c r="E121" t="s">
         <v>943</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="2">
         <v>45849</v>
       </c>
       <c r="G121" t="s">
@@ -9276,7 +9302,7 @@
         <v>1353</v>
       </c>
       <c r="I121">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J121">
         <v>251</v>
@@ -9287,7 +9313,7 @@
       <c r="L121" t="s">
         <v>1379</v>
       </c>
-      <c r="N121" s="1">
+      <c r="N121" s="2">
         <v>46100</v>
       </c>
       <c r="O121">
@@ -9313,7 +9339,7 @@
       <c r="E122" t="s">
         <v>944</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F122" s="2">
         <v>45849</v>
       </c>
       <c r="G122" t="s">
@@ -9323,7 +9349,7 @@
         <v>1353</v>
       </c>
       <c r="I122">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K122" t="s">
         <v>1357</v>
@@ -9351,7 +9377,7 @@
       <c r="E123" t="s">
         <v>945</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F123" s="2">
         <v>45849</v>
       </c>
       <c r="G123" t="s">
@@ -9380,7 +9406,7 @@
       <c r="E124" t="s">
         <v>946</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124" s="2">
         <v>45853</v>
       </c>
       <c r="G124" t="s">
@@ -9390,7 +9416,7 @@
         <v>1353</v>
       </c>
       <c r="I124">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K124" t="s">
         <v>1357</v>
@@ -9418,7 +9444,7 @@
       <c r="E125" t="s">
         <v>947</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125" s="2">
         <v>45855</v>
       </c>
       <c r="G125" t="s">
@@ -9428,7 +9454,7 @@
         <v>1353</v>
       </c>
       <c r="I125">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K125" t="s">
         <v>1363</v>
@@ -9456,7 +9482,7 @@
       <c r="E126" t="s">
         <v>948</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126" s="2">
         <v>45855</v>
       </c>
       <c r="G126" t="s">
@@ -9485,7 +9511,7 @@
       <c r="E127" t="s">
         <v>949</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127" s="2">
         <v>45856</v>
       </c>
       <c r="G127" t="s">
@@ -9514,7 +9540,7 @@
       <c r="E128" t="s">
         <v>950</v>
       </c>
-      <c r="F128" s="1">
+      <c r="F128" s="2">
         <v>45869</v>
       </c>
       <c r="G128" t="s">
@@ -9524,7 +9550,7 @@
         <v>1353</v>
       </c>
       <c r="I128">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K128" t="s">
         <v>1357</v>
@@ -9552,7 +9578,7 @@
       <c r="E129" t="s">
         <v>951</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F129" s="2">
         <v>45869</v>
       </c>
       <c r="G129" t="s">
@@ -9562,7 +9588,7 @@
         <v>1353</v>
       </c>
       <c r="I129">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K129" t="s">
         <v>1356</v>
@@ -9590,7 +9616,7 @@
       <c r="E130" t="s">
         <v>952</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F130" s="2">
         <v>45869</v>
       </c>
       <c r="G130" t="s">
@@ -9600,7 +9626,7 @@
         <v>1353</v>
       </c>
       <c r="I130">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J130">
         <v>47</v>
@@ -9611,7 +9637,7 @@
       <c r="L130" t="s">
         <v>1392</v>
       </c>
-      <c r="N130" s="1">
+      <c r="N130" s="2">
         <v>45916</v>
       </c>
       <c r="O130">
@@ -9637,7 +9663,7 @@
       <c r="E131" t="s">
         <v>953</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F131" s="2">
         <v>45869</v>
       </c>
       <c r="G131" t="s">
@@ -9666,7 +9692,7 @@
       <c r="E132" t="s">
         <v>954</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F132" s="2">
         <v>45869</v>
       </c>
       <c r="G132" t="s">
@@ -9676,7 +9702,7 @@
         <v>1353</v>
       </c>
       <c r="I132">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J132">
         <v>145</v>
@@ -9687,7 +9713,7 @@
       <c r="L132" t="s">
         <v>1393</v>
       </c>
-      <c r="N132" s="1">
+      <c r="N132" s="2">
         <v>46014</v>
       </c>
       <c r="O132">
@@ -9713,7 +9739,7 @@
       <c r="E133" t="s">
         <v>955</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F133" s="2">
         <v>45869</v>
       </c>
       <c r="G133" t="s">
@@ -9742,7 +9768,7 @@
       <c r="E134" t="s">
         <v>956</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F134" s="2">
         <v>45882</v>
       </c>
       <c r="G134" t="s">
@@ -9752,7 +9778,7 @@
         <v>1353</v>
       </c>
       <c r="I134">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K134" t="s">
         <v>1356</v>
@@ -9780,7 +9806,7 @@
       <c r="E135" t="s">
         <v>957</v>
       </c>
-      <c r="F135" s="1">
+      <c r="F135" s="2">
         <v>45882</v>
       </c>
       <c r="G135" t="s">
@@ -9809,7 +9835,7 @@
       <c r="E136" t="s">
         <v>958</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F136" s="2">
         <v>45891</v>
       </c>
       <c r="G136" t="s">
@@ -9838,7 +9864,7 @@
       <c r="E137" t="s">
         <v>959</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F137" s="2">
         <v>45891</v>
       </c>
       <c r="G137" t="s">
@@ -9867,7 +9893,7 @@
       <c r="E138" t="s">
         <v>960</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F138" s="2">
         <v>45891</v>
       </c>
       <c r="G138" t="s">
@@ -9877,7 +9903,7 @@
         <v>1353</v>
       </c>
       <c r="I138">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K138" t="s">
         <v>1357</v>
@@ -9905,7 +9931,7 @@
       <c r="E139" t="s">
         <v>961</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F139" s="2">
         <v>45891</v>
       </c>
       <c r="G139" t="s">
@@ -9934,7 +9960,7 @@
       <c r="E140" t="s">
         <v>962</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F140" s="2">
         <v>45891</v>
       </c>
       <c r="G140" t="s">
@@ -9963,7 +9989,7 @@
       <c r="E141" t="s">
         <v>963</v>
       </c>
-      <c r="F141" s="1">
+      <c r="F141" s="2">
         <v>45891</v>
       </c>
       <c r="G141" t="s">
@@ -9992,7 +10018,7 @@
       <c r="E142" t="s">
         <v>964</v>
       </c>
-      <c r="F142" s="1">
+      <c r="F142" s="2">
         <v>45891</v>
       </c>
       <c r="G142" t="s">
@@ -10021,7 +10047,7 @@
       <c r="E143" t="s">
         <v>965</v>
       </c>
-      <c r="F143" s="1">
+      <c r="F143" s="2">
         <v>45891</v>
       </c>
       <c r="G143" t="s">
@@ -10050,7 +10076,7 @@
       <c r="E144" t="s">
         <v>966</v>
       </c>
-      <c r="F144" s="1">
+      <c r="F144" s="2">
         <v>45891</v>
       </c>
       <c r="G144" t="s">
@@ -10079,7 +10105,7 @@
       <c r="E145" t="s">
         <v>967</v>
       </c>
-      <c r="F145" s="1">
+      <c r="F145" s="2">
         <v>45891</v>
       </c>
       <c r="G145" t="s">
@@ -10108,7 +10134,7 @@
       <c r="E146" t="s">
         <v>968</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F146" s="2">
         <v>45891</v>
       </c>
       <c r="G146" t="s">
@@ -10137,7 +10163,7 @@
       <c r="E147" t="s">
         <v>969</v>
       </c>
-      <c r="F147" s="1">
+      <c r="F147" s="2">
         <v>45891</v>
       </c>
       <c r="G147" t="s">
@@ -10166,7 +10192,7 @@
       <c r="E148" t="s">
         <v>970</v>
       </c>
-      <c r="F148" s="1">
+      <c r="F148" s="2">
         <v>45891</v>
       </c>
       <c r="G148" t="s">
@@ -10176,7 +10202,7 @@
         <v>1353</v>
       </c>
       <c r="I148">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J148">
         <v>341</v>
@@ -10187,7 +10213,7 @@
       <c r="L148" t="s">
         <v>1383</v>
       </c>
-      <c r="N148" s="1">
+      <c r="N148" s="2">
         <v>46232</v>
       </c>
       <c r="Q148" t="b">
@@ -10210,7 +10236,7 @@
       <c r="E149" t="s">
         <v>971</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F149" s="2">
         <v>45891</v>
       </c>
       <c r="G149" t="s">
@@ -10220,7 +10246,7 @@
         <v>1353</v>
       </c>
       <c r="I149">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J149">
         <v>374</v>
@@ -10231,7 +10257,7 @@
       <c r="L149" t="s">
         <v>1394</v>
       </c>
-      <c r="N149" s="1">
+      <c r="N149" s="2">
         <v>46265</v>
       </c>
       <c r="P149" t="s">
@@ -10257,7 +10283,7 @@
       <c r="E150" t="s">
         <v>972</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F150" s="2">
         <v>45891</v>
       </c>
       <c r="G150" t="s">
@@ -10267,7 +10293,7 @@
         <v>1353</v>
       </c>
       <c r="I150">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J150">
         <v>201</v>
@@ -10278,7 +10304,7 @@
       <c r="L150" t="s">
         <v>1381</v>
       </c>
-      <c r="N150" s="1">
+      <c r="N150" s="2">
         <v>46092</v>
       </c>
       <c r="P150" t="s">
@@ -10304,7 +10330,7 @@
       <c r="E151" t="s">
         <v>973</v>
       </c>
-      <c r="F151" s="1">
+      <c r="F151" s="2">
         <v>45891</v>
       </c>
       <c r="G151" t="s">
@@ -10333,7 +10359,7 @@
       <c r="E152" t="s">
         <v>963</v>
       </c>
-      <c r="F152" s="1">
+      <c r="F152" s="2">
         <v>45891</v>
       </c>
       <c r="G152" t="s">
@@ -10343,7 +10369,7 @@
         <v>1353</v>
       </c>
       <c r="I152">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J152">
         <v>228</v>
@@ -10354,7 +10380,7 @@
       <c r="L152" t="s">
         <v>1382</v>
       </c>
-      <c r="N152" s="1">
+      <c r="N152" s="2">
         <v>46119</v>
       </c>
       <c r="Q152" t="b">
@@ -10377,7 +10403,7 @@
       <c r="E153" t="s">
         <v>974</v>
       </c>
-      <c r="F153" s="1">
+      <c r="F153" s="2">
         <v>45891</v>
       </c>
       <c r="G153" t="s">
@@ -10395,7 +10421,7 @@
       <c r="L153" t="s">
         <v>1383</v>
       </c>
-      <c r="N153" s="1">
+      <c r="N153" s="2">
         <v>46232</v>
       </c>
       <c r="Q153" t="b">
@@ -10418,7 +10444,7 @@
       <c r="E154" t="s">
         <v>975</v>
       </c>
-      <c r="F154" s="1">
+      <c r="F154" s="2">
         <v>45891</v>
       </c>
       <c r="G154" t="s">
@@ -10447,7 +10473,7 @@
       <c r="E155" t="s">
         <v>976</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F155" s="2">
         <v>45891</v>
       </c>
       <c r="G155" t="s">
@@ -10457,7 +10483,7 @@
         <v>1353</v>
       </c>
       <c r="I155">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K155" t="s">
         <v>1363</v>
@@ -10482,7 +10508,7 @@
       <c r="E156" t="s">
         <v>977</v>
       </c>
-      <c r="F156" s="1">
+      <c r="F156" s="2">
         <v>45891</v>
       </c>
       <c r="G156" t="s">
@@ -10492,7 +10518,7 @@
         <v>1353</v>
       </c>
       <c r="I156">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K156" t="s">
         <v>1357</v>
@@ -10520,7 +10546,7 @@
       <c r="E157" t="s">
         <v>978</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="2">
         <v>45891</v>
       </c>
       <c r="G157" t="s">
@@ -10530,7 +10556,7 @@
         <v>1353</v>
       </c>
       <c r="I157">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J157">
         <v>371</v>
@@ -10541,7 +10567,7 @@
       <c r="L157" t="s">
         <v>1395</v>
       </c>
-      <c r="N157" s="1">
+      <c r="N157" s="2">
         <v>46262</v>
       </c>
       <c r="Q157" t="b">
@@ -10564,7 +10590,7 @@
       <c r="E158" t="s">
         <v>979</v>
       </c>
-      <c r="F158" s="1">
+      <c r="F158" s="2">
         <v>45894</v>
       </c>
       <c r="G158" t="s">
@@ -10574,7 +10600,7 @@
         <v>1353</v>
       </c>
       <c r="I158">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J158">
         <v>52</v>
@@ -10585,7 +10611,7 @@
       <c r="L158" t="s">
         <v>1396</v>
       </c>
-      <c r="N158" s="1">
+      <c r="N158" s="2">
         <v>45946</v>
       </c>
       <c r="Q158" t="b">
@@ -10608,7 +10634,7 @@
       <c r="E159" t="s">
         <v>980</v>
       </c>
-      <c r="F159" s="1">
+      <c r="F159" s="2">
         <v>45894</v>
       </c>
       <c r="G159" t="s">
@@ -10618,7 +10644,7 @@
         <v>1353</v>
       </c>
       <c r="I159">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K159" t="s">
         <v>1357</v>
@@ -10646,7 +10672,7 @@
       <c r="E160" t="s">
         <v>981</v>
       </c>
-      <c r="F160" s="1">
+      <c r="F160" s="2">
         <v>45898</v>
       </c>
       <c r="G160" t="s">
@@ -10656,7 +10682,7 @@
         <v>1353</v>
       </c>
       <c r="I160">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K160" t="s">
         <v>1357</v>
@@ -10684,7 +10710,7 @@
       <c r="E161" t="s">
         <v>982</v>
       </c>
-      <c r="F161" s="1">
+      <c r="F161" s="2">
         <v>45898</v>
       </c>
       <c r="G161" t="s">
@@ -10694,7 +10720,7 @@
         <v>1353</v>
       </c>
       <c r="I161">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J161">
         <v>55</v>
@@ -10705,7 +10731,7 @@
       <c r="L161" t="s">
         <v>1397</v>
       </c>
-      <c r="N161" s="1">
+      <c r="N161" s="2">
         <v>45953</v>
       </c>
       <c r="O161" t="s">
@@ -10731,7 +10757,7 @@
       <c r="E162" t="s">
         <v>983</v>
       </c>
-      <c r="F162" s="1">
+      <c r="F162" s="2">
         <v>45898</v>
       </c>
       <c r="G162" t="s">
@@ -10741,7 +10767,7 @@
         <v>1353</v>
       </c>
       <c r="I162">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J162">
         <v>42</v>
@@ -10752,7 +10778,7 @@
       <c r="L162" t="s">
         <v>1398</v>
       </c>
-      <c r="N162" s="1">
+      <c r="N162" s="2">
         <v>45940</v>
       </c>
       <c r="P162" t="s">
@@ -10778,7 +10804,7 @@
       <c r="E163" t="s">
         <v>984</v>
       </c>
-      <c r="F163" s="1">
+      <c r="F163" s="2">
         <v>45898</v>
       </c>
       <c r="G163" t="s">
@@ -10788,7 +10814,7 @@
         <v>1353</v>
       </c>
       <c r="I163">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J163">
         <v>42</v>
@@ -10799,7 +10825,7 @@
       <c r="L163" t="s">
         <v>1398</v>
       </c>
-      <c r="N163" s="1">
+      <c r="N163" s="2">
         <v>45940</v>
       </c>
       <c r="P163" t="s">
@@ -10825,7 +10851,7 @@
       <c r="E164" t="s">
         <v>985</v>
       </c>
-      <c r="F164" s="1">
+      <c r="F164" s="2">
         <v>45910</v>
       </c>
       <c r="G164" t="s">
@@ -10835,7 +10861,7 @@
         <v>1355</v>
       </c>
       <c r="I164">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O164" t="s">
         <v>1469</v>
@@ -10860,7 +10886,7 @@
       <c r="E165" t="s">
         <v>986</v>
       </c>
-      <c r="F165" s="1">
+      <c r="F165" s="2">
         <v>45917</v>
       </c>
       <c r="G165" t="s">
@@ -10878,7 +10904,7 @@
       <c r="L165" t="s">
         <v>1399</v>
       </c>
-      <c r="N165" s="1">
+      <c r="N165" s="2">
         <v>46204</v>
       </c>
       <c r="P165" t="s">
@@ -10904,7 +10930,7 @@
       <c r="E166" t="s">
         <v>987</v>
       </c>
-      <c r="F166" s="1">
+      <c r="F166" s="2">
         <v>45917</v>
       </c>
       <c r="G166" t="s">
@@ -10933,7 +10959,7 @@
       <c r="E167" t="s">
         <v>988</v>
       </c>
-      <c r="F167" s="1">
+      <c r="F167" s="2">
         <v>45917</v>
       </c>
       <c r="G167" t="s">
@@ -10962,7 +10988,7 @@
       <c r="E168" t="s">
         <v>989</v>
       </c>
-      <c r="F168" s="1">
+      <c r="F168" s="2">
         <v>45917</v>
       </c>
       <c r="G168" t="s">
@@ -10972,7 +10998,7 @@
         <v>1353</v>
       </c>
       <c r="I168">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K168" t="s">
         <v>1360</v>
@@ -11003,7 +11029,7 @@
       <c r="E169" t="s">
         <v>990</v>
       </c>
-      <c r="F169" s="1">
+      <c r="F169" s="2">
         <v>45917</v>
       </c>
       <c r="G169" t="s">
@@ -11013,7 +11039,7 @@
         <v>1353</v>
       </c>
       <c r="I169">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K169" t="s">
         <v>1330</v>
@@ -11021,7 +11047,7 @@
       <c r="L169" t="s">
         <v>1401</v>
       </c>
-      <c r="N169" s="1">
+      <c r="N169" s="2">
         <v>45973</v>
       </c>
       <c r="Q169" t="b">
@@ -11044,7 +11070,7 @@
       <c r="E170" t="s">
         <v>991</v>
       </c>
-      <c r="F170" s="1">
+      <c r="F170" s="2">
         <v>45917</v>
       </c>
       <c r="G170" t="s">
@@ -11079,7 +11105,7 @@
       <c r="E171" t="s">
         <v>992</v>
       </c>
-      <c r="F171" s="1">
+      <c r="F171" s="2">
         <v>45917</v>
       </c>
       <c r="G171" t="s">
@@ -11089,7 +11115,7 @@
         <v>1353</v>
       </c>
       <c r="I171">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K171" t="s">
         <v>1357</v>
@@ -11120,7 +11146,7 @@
       <c r="E172" t="s">
         <v>993</v>
       </c>
-      <c r="F172" s="1">
+      <c r="F172" s="2">
         <v>45917</v>
       </c>
       <c r="G172" t="s">
@@ -11149,7 +11175,7 @@
       <c r="E173" t="s">
         <v>994</v>
       </c>
-      <c r="F173" s="1">
+      <c r="F173" s="2">
         <v>45917</v>
       </c>
       <c r="G173" t="s">
@@ -11178,7 +11204,7 @@
       <c r="E174" t="s">
         <v>995</v>
       </c>
-      <c r="F174" s="1">
+      <c r="F174" s="2">
         <v>45917</v>
       </c>
       <c r="G174" t="s">
@@ -11193,7 +11219,7 @@
       <c r="L174" t="s">
         <v>1386</v>
       </c>
-      <c r="N174" s="1">
+      <c r="N174" s="2">
         <v>46195</v>
       </c>
       <c r="Q174" t="b">
@@ -11216,7 +11242,7 @@
       <c r="E175" t="s">
         <v>996</v>
       </c>
-      <c r="F175" s="1">
+      <c r="F175" s="2">
         <v>45917</v>
       </c>
       <c r="G175" t="s">
@@ -11226,7 +11252,7 @@
         <v>1353</v>
       </c>
       <c r="I175">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J175">
         <v>205</v>
@@ -11237,7 +11263,7 @@
       <c r="L175" t="s">
         <v>1402</v>
       </c>
-      <c r="N175" s="1">
+      <c r="N175" s="2">
         <v>46122</v>
       </c>
       <c r="P175" t="s">
@@ -11263,7 +11289,7 @@
       <c r="E176" t="s">
         <v>900</v>
       </c>
-      <c r="F176" s="1">
+      <c r="F176" s="2">
         <v>45917</v>
       </c>
       <c r="G176" t="s">
@@ -11273,7 +11299,7 @@
         <v>1353</v>
       </c>
       <c r="I176">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K176" t="s">
         <v>1357</v>
@@ -11301,7 +11327,7 @@
       <c r="E177" t="s">
         <v>997</v>
       </c>
-      <c r="F177" s="1">
+      <c r="F177" s="2">
         <v>45917</v>
       </c>
       <c r="G177" t="s">
@@ -11311,7 +11337,7 @@
         <v>1353</v>
       </c>
       <c r="I177">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J177">
         <v>44</v>
@@ -11322,7 +11348,7 @@
       <c r="L177" t="s">
         <v>1403</v>
       </c>
-      <c r="N177" s="1">
+      <c r="N177" s="2">
         <v>45961</v>
       </c>
       <c r="P177" t="s">
@@ -11348,7 +11374,7 @@
       <c r="E178" t="s">
         <v>998</v>
       </c>
-      <c r="F178" s="1">
+      <c r="F178" s="2">
         <v>45937</v>
       </c>
       <c r="G178" t="s">
@@ -11358,7 +11384,7 @@
         <v>1353</v>
       </c>
       <c r="I178">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K178" t="s">
         <v>1356</v>
@@ -11386,7 +11412,7 @@
       <c r="E179" t="s">
         <v>999</v>
       </c>
-      <c r="F179" s="1">
+      <c r="F179" s="2">
         <v>45937</v>
       </c>
       <c r="G179" t="s">
@@ -11415,7 +11441,7 @@
       <c r="E180" t="s">
         <v>1000</v>
       </c>
-      <c r="F180" s="1">
+      <c r="F180" s="2">
         <v>45937</v>
       </c>
       <c r="G180" t="s">
@@ -11425,7 +11451,7 @@
         <v>1353</v>
       </c>
       <c r="I180">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K180" t="s">
         <v>1356</v>
@@ -11453,7 +11479,7 @@
       <c r="E181" t="s">
         <v>1001</v>
       </c>
-      <c r="F181" s="1">
+      <c r="F181" s="2">
         <v>45937</v>
       </c>
       <c r="G181" t="s">
@@ -11482,7 +11508,7 @@
       <c r="E182" t="s">
         <v>1002</v>
       </c>
-      <c r="F182" s="1">
+      <c r="F182" s="2">
         <v>45937</v>
       </c>
       <c r="G182" t="s">
@@ -11511,7 +11537,7 @@
       <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="F183" s="1">
+      <c r="F183" s="2">
         <v>45937</v>
       </c>
       <c r="G183" t="s">
@@ -11521,7 +11547,7 @@
         <v>1353</v>
       </c>
       <c r="I183">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K183" t="s">
         <v>1357</v>
@@ -11549,7 +11575,7 @@
       <c r="D184" t="s">
         <v>774</v>
       </c>
-      <c r="F184" s="1">
+      <c r="F184" s="2">
         <v>45939</v>
       </c>
       <c r="G184" t="s">
@@ -11559,7 +11585,7 @@
         <v>1353</v>
       </c>
       <c r="I184">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K184" t="s">
         <v>1363</v>
@@ -11584,7 +11610,7 @@
       <c r="E185" t="s">
         <v>1004</v>
       </c>
-      <c r="F185" s="1">
+      <c r="F185" s="2">
         <v>45939</v>
       </c>
       <c r="G185" t="s">
@@ -11594,7 +11620,7 @@
         <v>1353</v>
       </c>
       <c r="I185">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K185" t="s">
         <v>1357</v>
@@ -11622,7 +11648,7 @@
       <c r="E186" t="s">
         <v>1005</v>
       </c>
-      <c r="F186" s="1">
+      <c r="F186" s="2">
         <v>45939</v>
       </c>
       <c r="G186" t="s">
@@ -11632,7 +11658,7 @@
         <v>1353</v>
       </c>
       <c r="I186">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K186" t="s">
         <v>1357</v>
@@ -11660,7 +11686,7 @@
       <c r="E187" t="s">
         <v>1006</v>
       </c>
-      <c r="F187" s="1">
+      <c r="F187" s="2">
         <v>45939</v>
       </c>
       <c r="G187" t="s">
@@ -11670,7 +11696,7 @@
         <v>1353</v>
       </c>
       <c r="I187">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J187">
         <v>75</v>
@@ -11681,7 +11707,7 @@
       <c r="L187" t="s">
         <v>1404</v>
       </c>
-      <c r="N187" s="1">
+      <c r="N187" s="2">
         <v>46014</v>
       </c>
       <c r="O187">
@@ -11707,7 +11733,7 @@
       <c r="E188" t="s">
         <v>1007</v>
       </c>
-      <c r="F188" s="1">
+      <c r="F188" s="2">
         <v>45946</v>
       </c>
       <c r="G188" t="s">
@@ -11717,7 +11743,7 @@
         <v>1353</v>
       </c>
       <c r="I188">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J188">
         <v>40</v>
@@ -11728,7 +11754,7 @@
       <c r="L188" t="s">
         <v>1405</v>
       </c>
-      <c r="N188" s="1">
+      <c r="N188" s="2">
         <v>45986</v>
       </c>
       <c r="P188" t="s">
@@ -11754,7 +11780,7 @@
       <c r="E189" t="s">
         <v>1008</v>
       </c>
-      <c r="F189" s="1">
+      <c r="F189" s="2">
         <v>45965</v>
       </c>
       <c r="G189" t="s">
@@ -11764,7 +11790,7 @@
         <v>1353</v>
       </c>
       <c r="I189">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J189">
         <v>155</v>
@@ -11775,7 +11801,7 @@
       <c r="L189" t="s">
         <v>1406</v>
       </c>
-      <c r="N189" s="1">
+      <c r="N189" s="2">
         <v>46120</v>
       </c>
       <c r="Q189" t="b">
@@ -11798,7 +11824,7 @@
       <c r="E190" t="s">
         <v>1009</v>
       </c>
-      <c r="F190" s="1">
+      <c r="F190" s="2">
         <v>45965</v>
       </c>
       <c r="G190" t="s">
@@ -11808,7 +11834,7 @@
         <v>1353</v>
       </c>
       <c r="I190">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J190">
         <v>107</v>
@@ -11819,7 +11845,7 @@
       <c r="L190" t="s">
         <v>1407</v>
       </c>
-      <c r="N190" s="1">
+      <c r="N190" s="2">
         <v>46072</v>
       </c>
       <c r="Q190" t="b">
@@ -11842,7 +11868,7 @@
       <c r="E191" t="s">
         <v>1010</v>
       </c>
-      <c r="F191" s="1">
+      <c r="F191" s="2">
         <v>45967</v>
       </c>
       <c r="G191" t="s">
@@ -11852,7 +11878,7 @@
         <v>1353</v>
       </c>
       <c r="I191">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J191">
         <v>5</v>
@@ -11863,7 +11889,7 @@
       <c r="L191" t="s">
         <v>1408</v>
       </c>
-      <c r="N191" s="1">
+      <c r="N191" s="2">
         <v>45972</v>
       </c>
       <c r="Q191" t="b">
@@ -11886,7 +11912,7 @@
       <c r="E192" t="s">
         <v>1011</v>
       </c>
-      <c r="F192" s="1">
+      <c r="F192" s="2">
         <v>45968</v>
       </c>
       <c r="G192" t="s">
@@ -11896,7 +11922,7 @@
         <v>1353</v>
       </c>
       <c r="I192">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K192" t="s">
         <v>1357</v>
@@ -11924,7 +11950,7 @@
       <c r="E193" t="s">
         <v>1012</v>
       </c>
-      <c r="F193" s="1">
+      <c r="F193" s="2">
         <v>45968</v>
       </c>
       <c r="G193" t="s">
@@ -11934,7 +11960,7 @@
         <v>1353</v>
       </c>
       <c r="I193">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K193" t="s">
         <v>1362</v>
@@ -11962,7 +11988,7 @@
       <c r="E194" t="s">
         <v>1013</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F194" s="2">
         <v>45968</v>
       </c>
       <c r="G194" t="s">
@@ -11991,7 +12017,7 @@
       <c r="E195" t="s">
         <v>1014</v>
       </c>
-      <c r="F195" s="1">
+      <c r="F195" s="2">
         <v>45971</v>
       </c>
       <c r="G195" t="s">
@@ -12001,7 +12027,7 @@
         <v>1353</v>
       </c>
       <c r="I195">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J195">
         <v>186</v>
@@ -12012,7 +12038,7 @@
       <c r="L195" t="s">
         <v>1409</v>
       </c>
-      <c r="N195" s="1">
+      <c r="N195" s="2">
         <v>46157</v>
       </c>
       <c r="Q195" t="b">
@@ -12035,7 +12061,7 @@
       <c r="E196" t="s">
         <v>1015</v>
       </c>
-      <c r="F196" s="1">
+      <c r="F196" s="2">
         <v>45978</v>
       </c>
       <c r="G196" t="s">
@@ -12064,7 +12090,7 @@
       <c r="E197" t="s">
         <v>1016</v>
       </c>
-      <c r="F197" s="1">
+      <c r="F197" s="2">
         <v>45978</v>
       </c>
       <c r="G197" t="s">
@@ -12093,7 +12119,7 @@
       <c r="E198" t="s">
         <v>1017</v>
       </c>
-      <c r="F198" s="1">
+      <c r="F198" s="2">
         <v>45978</v>
       </c>
       <c r="G198" t="s">
@@ -12122,7 +12148,7 @@
       <c r="E199" t="s">
         <v>1018</v>
       </c>
-      <c r="F199" s="1">
+      <c r="F199" s="2">
         <v>45979</v>
       </c>
       <c r="G199" t="s">
@@ -12132,7 +12158,7 @@
         <v>1353</v>
       </c>
       <c r="I199">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J199">
         <v>70</v>
@@ -12143,7 +12169,7 @@
       <c r="L199" t="s">
         <v>1410</v>
       </c>
-      <c r="N199" s="1">
+      <c r="N199" s="2">
         <v>46049</v>
       </c>
       <c r="Q199" t="b">
@@ -12166,7 +12192,7 @@
       <c r="E200" t="s">
         <v>1019</v>
       </c>
-      <c r="F200" s="1">
+      <c r="F200" s="2">
         <v>45986</v>
       </c>
       <c r="G200" t="s">
@@ -12176,7 +12202,7 @@
         <v>1353</v>
       </c>
       <c r="I200">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J200">
         <v>170</v>
@@ -12187,7 +12213,7 @@
       <c r="L200" t="s">
         <v>1409</v>
       </c>
-      <c r="N200" s="1">
+      <c r="N200" s="2">
         <v>46156</v>
       </c>
       <c r="Q200" t="b">
@@ -12210,7 +12236,7 @@
       <c r="E201" t="s">
         <v>1020</v>
       </c>
-      <c r="F201" s="1">
+      <c r="F201" s="2">
         <v>45986</v>
       </c>
       <c r="G201" t="s">
@@ -12220,7 +12246,7 @@
         <v>1353</v>
       </c>
       <c r="I201">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K201" t="s">
         <v>1357</v>
@@ -12248,7 +12274,7 @@
       <c r="E202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" s="1">
+      <c r="F202" s="2">
         <v>45986</v>
       </c>
       <c r="G202" t="s">
@@ -12258,7 +12284,7 @@
         <v>1353</v>
       </c>
       <c r="I202">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K202" t="s">
         <v>1357</v>
@@ -12286,7 +12312,7 @@
       <c r="E203" t="s">
         <v>1022</v>
       </c>
-      <c r="F203" s="1">
+      <c r="F203" s="2">
         <v>45986</v>
       </c>
       <c r="G203" t="s">
@@ -12304,7 +12330,7 @@
       <c r="L203" t="s">
         <v>1411</v>
       </c>
-      <c r="N203" s="1">
+      <c r="N203" s="2">
         <v>46232</v>
       </c>
       <c r="Q203" t="b">
@@ -12327,7 +12353,7 @@
       <c r="E204" t="s">
         <v>1023</v>
       </c>
-      <c r="F204" s="1">
+      <c r="F204" s="2">
         <v>45986</v>
       </c>
       <c r="G204" t="s">
@@ -12337,7 +12363,7 @@
         <v>1353</v>
       </c>
       <c r="I204">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K204" t="s">
         <v>1356</v>
@@ -12365,7 +12391,7 @@
       <c r="E205" t="s">
         <v>1024</v>
       </c>
-      <c r="F205" s="1">
+      <c r="F205" s="2">
         <v>45986</v>
       </c>
       <c r="G205" t="s">
@@ -12375,7 +12401,7 @@
         <v>1353</v>
       </c>
       <c r="I205">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K205" t="s">
         <v>1356</v>
@@ -12403,7 +12429,7 @@
       <c r="E206" t="s">
         <v>1025</v>
       </c>
-      <c r="F206" s="1">
+      <c r="F206" s="2">
         <v>45986</v>
       </c>
       <c r="G206" t="s">
@@ -12432,7 +12458,7 @@
       <c r="E207" t="s">
         <v>1026</v>
       </c>
-      <c r="F207" s="1">
+      <c r="F207" s="2">
         <v>45986</v>
       </c>
       <c r="G207" t="s">
@@ -12442,7 +12468,7 @@
         <v>1353</v>
       </c>
       <c r="I207">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J207">
         <v>167</v>
@@ -12453,7 +12479,7 @@
       <c r="L207" t="s">
         <v>1412</v>
       </c>
-      <c r="N207" s="1">
+      <c r="N207" s="2">
         <v>46153</v>
       </c>
       <c r="Q207" t="b">
@@ -12476,7 +12502,7 @@
       <c r="E208" t="s">
         <v>1027</v>
       </c>
-      <c r="F208" s="1">
+      <c r="F208" s="2">
         <v>45986</v>
       </c>
       <c r="G208" t="s">
@@ -12486,7 +12512,7 @@
         <v>1353</v>
       </c>
       <c r="I208">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J208">
         <v>45</v>
@@ -12497,7 +12523,7 @@
       <c r="L208" t="s">
         <v>1413</v>
       </c>
-      <c r="N208" s="1">
+      <c r="N208" s="2">
         <v>46031</v>
       </c>
       <c r="Q208" t="b">
@@ -12520,7 +12546,7 @@
       <c r="E209" t="s">
         <v>1028</v>
       </c>
-      <c r="F209" s="1">
+      <c r="F209" s="2">
         <v>46000</v>
       </c>
       <c r="G209" t="s">
@@ -12530,7 +12556,7 @@
         <v>1353</v>
       </c>
       <c r="I209">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J209">
         <v>191</v>
@@ -12541,7 +12567,7 @@
       <c r="L209" t="s">
         <v>1414</v>
       </c>
-      <c r="N209" s="1">
+      <c r="N209" s="2">
         <v>46191</v>
       </c>
       <c r="Q209" t="b">
@@ -12564,7 +12590,7 @@
       <c r="E210" t="s">
         <v>1029</v>
       </c>
-      <c r="F210" s="1">
+      <c r="F210" s="2">
         <v>46000</v>
       </c>
       <c r="G210" t="s">
@@ -12574,7 +12600,7 @@
         <v>1353</v>
       </c>
       <c r="I210">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K210" t="s">
         <v>1360</v>
@@ -12602,7 +12628,7 @@
       <c r="E211" t="s">
         <v>1030</v>
       </c>
-      <c r="F211" s="1">
+      <c r="F211" s="2">
         <v>46000</v>
       </c>
       <c r="G211" t="s">
@@ -12631,7 +12657,7 @@
       <c r="E212" t="s">
         <v>1031</v>
       </c>
-      <c r="F212" s="1">
+      <c r="F212" s="2">
         <v>46000</v>
       </c>
       <c r="G212" t="s">
@@ -12660,7 +12686,7 @@
       <c r="E213" t="s">
         <v>1032</v>
       </c>
-      <c r="F213" s="1">
+      <c r="F213" s="2">
         <v>46007</v>
       </c>
       <c r="G213" t="s">
@@ -12670,7 +12696,7 @@
         <v>1353</v>
       </c>
       <c r="I213">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K213" t="s">
         <v>1357</v>
@@ -12698,7 +12724,7 @@
       <c r="E214" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="1">
+      <c r="F214" s="2">
         <v>46007</v>
       </c>
       <c r="G214" t="s">
@@ -12708,7 +12734,7 @@
         <v>1353</v>
       </c>
       <c r="I214">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J214">
         <v>14</v>
@@ -12719,7 +12745,7 @@
       <c r="L214" t="s">
         <v>1415</v>
       </c>
-      <c r="N214" s="1">
+      <c r="N214" s="2">
         <v>46021</v>
       </c>
       <c r="O214">
@@ -12745,7 +12771,7 @@
       <c r="E215" t="s">
         <v>1034</v>
       </c>
-      <c r="F215" s="1">
+      <c r="F215" s="2">
         <v>46007</v>
       </c>
       <c r="G215" t="s">
@@ -12755,7 +12781,7 @@
         <v>1353</v>
       </c>
       <c r="I215">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K215" t="s">
         <v>1357</v>
@@ -12783,7 +12809,7 @@
       <c r="E216" t="s">
         <v>1035</v>
       </c>
-      <c r="F216" s="1">
+      <c r="F216" s="2">
         <v>46010</v>
       </c>
       <c r="G216" t="s">
@@ -12812,7 +12838,7 @@
       <c r="E217" t="s">
         <v>1036</v>
       </c>
-      <c r="F217" s="1">
+      <c r="F217" s="2">
         <v>46010</v>
       </c>
       <c r="G217" t="s">
@@ -12822,7 +12848,7 @@
         <v>1353</v>
       </c>
       <c r="I217">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J217">
         <v>42</v>
@@ -12833,7 +12859,7 @@
       <c r="L217" t="s">
         <v>1416</v>
       </c>
-      <c r="N217" s="1">
+      <c r="N217" s="2">
         <v>46052</v>
       </c>
       <c r="Q217" t="b">
@@ -12856,7 +12882,7 @@
       <c r="E218" t="s">
         <v>1037</v>
       </c>
-      <c r="F218" s="1">
+      <c r="F218" s="2">
         <v>46010</v>
       </c>
       <c r="G218" t="s">
@@ -12866,7 +12892,7 @@
         <v>1353</v>
       </c>
       <c r="I218">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J218">
         <v>166</v>
@@ -12874,7 +12900,7 @@
       <c r="K218" t="s">
         <v>1359</v>
       </c>
-      <c r="N218" s="1">
+      <c r="N218" s="2">
         <v>46176</v>
       </c>
       <c r="P218" t="s">
@@ -12900,7 +12926,7 @@
       <c r="E219" t="s">
         <v>1038</v>
       </c>
-      <c r="F219" s="1">
+      <c r="F219" s="2">
         <v>46010</v>
       </c>
       <c r="G219" t="s">
@@ -12918,7 +12944,7 @@
       <c r="L219" t="s">
         <v>1417</v>
       </c>
-      <c r="N219" s="1">
+      <c r="N219" s="2">
         <v>46176</v>
       </c>
       <c r="P219" t="s">
@@ -12944,7 +12970,7 @@
       <c r="E220" t="s">
         <v>1039</v>
       </c>
-      <c r="F220" s="1">
+      <c r="F220" s="2">
         <v>46010</v>
       </c>
       <c r="G220" t="s">
@@ -12954,7 +12980,7 @@
         <v>1353</v>
       </c>
       <c r="I220">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J220">
         <v>154</v>
@@ -12965,7 +12991,7 @@
       <c r="L220" t="s">
         <v>1418</v>
       </c>
-      <c r="N220" s="1">
+      <c r="N220" s="2">
         <v>46164</v>
       </c>
       <c r="Q220" t="b">
@@ -12988,7 +13014,7 @@
       <c r="E221" t="s">
         <v>1040</v>
       </c>
-      <c r="F221" s="1">
+      <c r="F221" s="2">
         <v>46028</v>
       </c>
       <c r="G221" t="s">
@@ -13003,7 +13029,7 @@
       <c r="L221" t="s">
         <v>1419</v>
       </c>
-      <c r="N221" s="1">
+      <c r="N221" s="2">
         <v>46184</v>
       </c>
       <c r="Q221" t="b">
@@ -13026,7 +13052,7 @@
       <c r="E222" t="s">
         <v>1041</v>
       </c>
-      <c r="F222" s="1">
+      <c r="F222" s="2">
         <v>46028</v>
       </c>
       <c r="G222" t="s">
@@ -13041,7 +13067,7 @@
       <c r="L222" t="s">
         <v>1383</v>
       </c>
-      <c r="N222" s="1">
+      <c r="N222" s="2">
         <v>46232</v>
       </c>
       <c r="Q222" t="b">
@@ -13064,7 +13090,7 @@
       <c r="E223" t="s">
         <v>1042</v>
       </c>
-      <c r="F223" s="1">
+      <c r="F223" s="2">
         <v>46028</v>
       </c>
       <c r="G223" t="s">
@@ -13079,7 +13105,7 @@
       <c r="L223" t="s">
         <v>1383</v>
       </c>
-      <c r="N223" s="1">
+      <c r="N223" s="2">
         <v>46232</v>
       </c>
       <c r="Q223" t="b">
@@ -13102,7 +13128,7 @@
       <c r="E224" t="s">
         <v>1043</v>
       </c>
-      <c r="F224" s="1">
+      <c r="F224" s="2">
         <v>46028</v>
       </c>
       <c r="G224" t="s">
@@ -13112,7 +13138,7 @@
         <v>1353</v>
       </c>
       <c r="I224">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J224">
         <v>204</v>
@@ -13120,7 +13146,7 @@
       <c r="L224" t="s">
         <v>1383</v>
       </c>
-      <c r="N224" s="1">
+      <c r="N224" s="2">
         <v>46232</v>
       </c>
       <c r="Q224" t="b">
@@ -13143,7 +13169,7 @@
       <c r="E225" t="s">
         <v>1044</v>
       </c>
-      <c r="F225" s="1">
+      <c r="F225" s="2">
         <v>46028</v>
       </c>
       <c r="G225" t="s">
@@ -13158,7 +13184,7 @@
       <c r="L225" t="s">
         <v>1383</v>
       </c>
-      <c r="N225" s="1">
+      <c r="N225" s="2">
         <v>46232</v>
       </c>
       <c r="Q225" t="b">
@@ -13181,7 +13207,7 @@
       <c r="E226" t="s">
         <v>1045</v>
       </c>
-      <c r="F226" s="1">
+      <c r="F226" s="2">
         <v>46028</v>
       </c>
       <c r="G226" t="s">
@@ -13196,7 +13222,7 @@
       <c r="L226" t="s">
         <v>1383</v>
       </c>
-      <c r="N226" s="1">
+      <c r="N226" s="2">
         <v>46232</v>
       </c>
       <c r="Q226" t="b">
@@ -13219,7 +13245,7 @@
       <c r="E227" t="s">
         <v>1046</v>
       </c>
-      <c r="F227" s="1">
+      <c r="F227" s="2">
         <v>46028</v>
       </c>
       <c r="G227" t="s">
@@ -13234,7 +13260,7 @@
       <c r="L227" t="s">
         <v>1383</v>
       </c>
-      <c r="N227" s="1">
+      <c r="N227" s="2">
         <v>46232</v>
       </c>
       <c r="Q227" t="b">
@@ -13257,7 +13283,7 @@
       <c r="E228" t="s">
         <v>1047</v>
       </c>
-      <c r="F228" s="1">
+      <c r="F228" s="2">
         <v>46028</v>
       </c>
       <c r="G228" t="s">
@@ -13267,7 +13293,7 @@
         <v>1353</v>
       </c>
       <c r="I228">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J228">
         <v>204</v>
@@ -13275,7 +13301,7 @@
       <c r="L228" t="s">
         <v>1383</v>
       </c>
-      <c r="N228" s="1">
+      <c r="N228" s="2">
         <v>46232</v>
       </c>
       <c r="Q228" t="b">
@@ -13298,7 +13324,7 @@
       <c r="E229" t="s">
         <v>1048</v>
       </c>
-      <c r="F229" s="1">
+      <c r="F229" s="2">
         <v>46028</v>
       </c>
       <c r="G229" t="s">
@@ -13313,7 +13339,7 @@
       <c r="L229" t="s">
         <v>1420</v>
       </c>
-      <c r="N229" s="1">
+      <c r="N229" s="2">
         <v>46191</v>
       </c>
       <c r="Q229" t="b">
@@ -13336,7 +13362,7 @@
       <c r="E230" t="s">
         <v>1049</v>
       </c>
-      <c r="F230" s="1">
+      <c r="F230" s="2">
         <v>46028</v>
       </c>
       <c r="G230" t="s">
@@ -13346,7 +13372,7 @@
         <v>1353</v>
       </c>
       <c r="I230">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J230">
         <v>197</v>
@@ -13357,7 +13383,7 @@
       <c r="L230" t="s">
         <v>1395</v>
       </c>
-      <c r="N230" s="1">
+      <c r="N230" s="2">
         <v>46225</v>
       </c>
       <c r="Q230" t="b">
@@ -13380,7 +13406,7 @@
       <c r="E231" t="s">
         <v>1050</v>
       </c>
-      <c r="F231" s="1">
+      <c r="F231" s="2">
         <v>46028</v>
       </c>
       <c r="G231" t="s">
@@ -13390,7 +13416,7 @@
         <v>1353</v>
       </c>
       <c r="I231">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J231">
         <v>35</v>
@@ -13401,7 +13427,7 @@
       <c r="L231" t="s">
         <v>1421</v>
       </c>
-      <c r="N231" s="1">
+      <c r="N231" s="2">
         <v>46063</v>
       </c>
       <c r="Q231" t="b">
@@ -13424,7 +13450,7 @@
       <c r="E232" t="s">
         <v>1051</v>
       </c>
-      <c r="F232" s="1">
+      <c r="F232" s="2">
         <v>46028</v>
       </c>
       <c r="G232" t="s">
@@ -13453,7 +13479,7 @@
       <c r="E233" t="s">
         <v>1052</v>
       </c>
-      <c r="F233" s="1">
+      <c r="F233" s="2">
         <v>46028</v>
       </c>
       <c r="G233" t="s">
@@ -13482,7 +13508,7 @@
       <c r="E234" t="s">
         <v>1053</v>
       </c>
-      <c r="F234" s="1">
+      <c r="F234" s="2">
         <v>46028</v>
       </c>
       <c r="G234" t="s">
@@ -13492,7 +13518,7 @@
         <v>1353</v>
       </c>
       <c r="I234">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J234">
         <v>35</v>
@@ -13503,7 +13529,7 @@
       <c r="L234" t="s">
         <v>1421</v>
       </c>
-      <c r="N234" s="1">
+      <c r="N234" s="2">
         <v>46063</v>
       </c>
       <c r="P234" t="s">
@@ -13529,7 +13555,7 @@
       <c r="E235" t="s">
         <v>1054</v>
       </c>
-      <c r="F235" s="1">
+      <c r="F235" s="2">
         <v>46028</v>
       </c>
       <c r="G235" t="s">
@@ -13539,7 +13565,7 @@
         <v>1353</v>
       </c>
       <c r="I235">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J235">
         <v>35</v>
@@ -13550,7 +13576,7 @@
       <c r="L235" t="s">
         <v>1421</v>
       </c>
-      <c r="N235" s="1">
+      <c r="N235" s="2">
         <v>46063</v>
       </c>
       <c r="P235" t="s">
@@ -13576,7 +13602,7 @@
       <c r="E236" t="s">
         <v>1055</v>
       </c>
-      <c r="F236" s="1">
+      <c r="F236" s="2">
         <v>46028</v>
       </c>
       <c r="G236" t="s">
@@ -13586,7 +13612,7 @@
         <v>1353</v>
       </c>
       <c r="I236">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J236">
         <v>86</v>
@@ -13597,7 +13623,7 @@
       <c r="L236" t="s">
         <v>1422</v>
       </c>
-      <c r="N236" s="1">
+      <c r="N236" s="2">
         <v>46114</v>
       </c>
       <c r="Q236" t="b">
@@ -13620,7 +13646,7 @@
       <c r="E237" t="s">
         <v>1056</v>
       </c>
-      <c r="F237" s="1">
+      <c r="F237" s="2">
         <v>46028</v>
       </c>
       <c r="G237" t="s">
@@ -13638,7 +13664,7 @@
       <c r="L237" t="s">
         <v>1423</v>
       </c>
-      <c r="N237" s="1">
+      <c r="N237" s="2">
         <v>46210</v>
       </c>
       <c r="P237" t="s">
@@ -13664,7 +13690,7 @@
       <c r="E238" t="s">
         <v>1057</v>
       </c>
-      <c r="F238" s="1">
+      <c r="F238" s="2">
         <v>46028</v>
       </c>
       <c r="G238" t="s">
@@ -13693,7 +13719,7 @@
       <c r="E239" t="s">
         <v>1058</v>
       </c>
-      <c r="F239" s="1">
+      <c r="F239" s="2">
         <v>46036</v>
       </c>
       <c r="G239" t="s">
@@ -13703,7 +13729,7 @@
         <v>1353</v>
       </c>
       <c r="I239">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K239" t="s">
         <v>1330</v>
@@ -13711,7 +13737,7 @@
       <c r="L239" t="s">
         <v>1424</v>
       </c>
-      <c r="N239" s="1">
+      <c r="N239" s="2">
         <v>46052</v>
       </c>
       <c r="Q239" t="b">
@@ -13734,7 +13760,7 @@
       <c r="E240" t="s">
         <v>1059</v>
       </c>
-      <c r="F240" s="1">
+      <c r="F240" s="2">
         <v>46036</v>
       </c>
       <c r="G240" t="s">
@@ -13763,7 +13789,7 @@
       <c r="E241" t="s">
         <v>1060</v>
       </c>
-      <c r="F241" s="1">
+      <c r="F241" s="2">
         <v>46036</v>
       </c>
       <c r="G241" t="s">
@@ -13792,7 +13818,7 @@
       <c r="E242" t="s">
         <v>1061</v>
       </c>
-      <c r="F242" s="1">
+      <c r="F242" s="2">
         <v>46036</v>
       </c>
       <c r="G242" t="s">
@@ -13802,7 +13828,7 @@
         <v>1353</v>
       </c>
       <c r="I242">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K242" t="s">
         <v>1356</v>
@@ -13830,7 +13856,7 @@
       <c r="E243" t="s">
         <v>1062</v>
       </c>
-      <c r="F243" s="1">
+      <c r="F243" s="2">
         <v>46048</v>
       </c>
       <c r="G243" t="s">
@@ -13859,7 +13885,7 @@
       <c r="E244" t="s">
         <v>1063</v>
       </c>
-      <c r="F244" s="1">
+      <c r="F244" s="2">
         <v>46048</v>
       </c>
       <c r="G244" t="s">
@@ -13869,7 +13895,7 @@
         <v>1353</v>
       </c>
       <c r="I244">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J244">
         <v>15</v>
@@ -13877,7 +13903,7 @@
       <c r="K244" t="s">
         <v>1359</v>
       </c>
-      <c r="N244" s="1">
+      <c r="N244" s="2">
         <v>46063</v>
       </c>
       <c r="Q244" t="b">
@@ -13900,7 +13926,7 @@
       <c r="E245" t="s">
         <v>1064</v>
       </c>
-      <c r="F245" s="1">
+      <c r="F245" s="2">
         <v>46048</v>
       </c>
       <c r="G245" t="s">
@@ -13910,7 +13936,7 @@
         <v>1353</v>
       </c>
       <c r="I245">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J245">
         <v>15</v>
@@ -13921,7 +13947,7 @@
       <c r="L245" t="s">
         <v>1425</v>
       </c>
-      <c r="N245" s="1">
+      <c r="N245" s="2">
         <v>46063</v>
       </c>
       <c r="Q245" t="b">
@@ -13944,7 +13970,7 @@
       <c r="E246" t="s">
         <v>1065</v>
       </c>
-      <c r="F246" s="1">
+      <c r="F246" s="2">
         <v>46050</v>
       </c>
       <c r="G246" t="s">
@@ -13962,7 +13988,7 @@
       <c r="L246" t="s">
         <v>1426</v>
       </c>
-      <c r="N246" s="1">
+      <c r="N246" s="2">
         <v>46191</v>
       </c>
       <c r="Q246" t="b">
@@ -13985,7 +14011,7 @@
       <c r="E247" t="s">
         <v>1066</v>
       </c>
-      <c r="F247" s="1">
+      <c r="F247" s="2">
         <v>46050</v>
       </c>
       <c r="G247" t="s">
@@ -14014,7 +14040,7 @@
       <c r="E248" t="s">
         <v>1067</v>
       </c>
-      <c r="F248" s="1">
+      <c r="F248" s="2">
         <v>46050</v>
       </c>
       <c r="G248" t="s">
@@ -14043,7 +14069,7 @@
       <c r="E249" t="s">
         <v>1068</v>
       </c>
-      <c r="F249" s="1">
+      <c r="F249" s="2">
         <v>46050</v>
       </c>
       <c r="G249" t="s">
@@ -14053,7 +14079,7 @@
         <v>1353</v>
       </c>
       <c r="I249">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K249" t="s">
         <v>1357</v>
@@ -14081,7 +14107,7 @@
       <c r="E250" t="s">
         <v>1069</v>
       </c>
-      <c r="F250" s="1">
+      <c r="F250" s="2">
         <v>46063</v>
       </c>
       <c r="G250" t="s">
@@ -14119,7 +14145,7 @@
       <c r="E251" t="s">
         <v>1070</v>
       </c>
-      <c r="F251" s="1">
+      <c r="F251" s="2">
         <v>46063</v>
       </c>
       <c r="G251" t="s">
@@ -14148,7 +14174,7 @@
       <c r="E252" t="s">
         <v>1071</v>
       </c>
-      <c r="F252" s="1">
+      <c r="F252" s="2">
         <v>46063</v>
       </c>
       <c r="G252" t="s">
@@ -14177,7 +14203,7 @@
       <c r="E253" t="s">
         <v>1072</v>
       </c>
-      <c r="F253" s="1">
+      <c r="F253" s="2">
         <v>46063</v>
       </c>
       <c r="G253" t="s">
@@ -14187,7 +14213,7 @@
         <v>1353</v>
       </c>
       <c r="I253">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J253">
         <v>162</v>
@@ -14198,7 +14224,7 @@
       <c r="L253" t="s">
         <v>1395</v>
       </c>
-      <c r="N253" s="1">
+      <c r="N253" s="2">
         <v>46225</v>
       </c>
       <c r="Q253" t="b">
@@ -14221,7 +14247,7 @@
       <c r="E254" t="s">
         <v>1073</v>
       </c>
-      <c r="F254" s="1">
+      <c r="F254" s="2">
         <v>46063</v>
       </c>
       <c r="G254" t="s">
@@ -14231,7 +14257,7 @@
         <v>1353</v>
       </c>
       <c r="I254">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K254" t="s">
         <v>1360</v>
@@ -14259,7 +14285,7 @@
       <c r="E255" t="s">
         <v>1074</v>
       </c>
-      <c r="F255" s="1">
+      <c r="F255" s="2">
         <v>46063</v>
       </c>
       <c r="G255" t="s">
@@ -14269,7 +14295,7 @@
         <v>1353</v>
       </c>
       <c r="I255">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J255">
         <v>72</v>
@@ -14280,7 +14306,7 @@
       <c r="L255" t="s">
         <v>1388</v>
       </c>
-      <c r="N255" s="1">
+      <c r="N255" s="2">
         <v>46135</v>
       </c>
       <c r="Q255" t="b">
@@ -14303,7 +14329,7 @@
       <c r="E256" t="s">
         <v>1075</v>
       </c>
-      <c r="F256" s="1">
+      <c r="F256" s="2">
         <v>46063</v>
       </c>
       <c r="G256" t="s">
@@ -14313,7 +14339,7 @@
         <v>1353</v>
       </c>
       <c r="I256">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J256">
         <v>23</v>
@@ -14321,7 +14347,7 @@
       <c r="K256" t="s">
         <v>1357</v>
       </c>
-      <c r="N256" s="1">
+      <c r="N256" s="2">
         <v>46086</v>
       </c>
       <c r="O256">
@@ -14347,7 +14373,7 @@
       <c r="E257" t="s">
         <v>1076</v>
       </c>
-      <c r="F257" s="1">
+      <c r="F257" s="2">
         <v>46063</v>
       </c>
       <c r="G257" t="s">
@@ -14376,7 +14402,7 @@
       <c r="E258" t="s">
         <v>1077</v>
       </c>
-      <c r="F258" s="1">
+      <c r="F258" s="2">
         <v>46063</v>
       </c>
       <c r="G258" t="s">
@@ -14405,7 +14431,7 @@
       <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="F259" s="1">
+      <c r="F259" s="2">
         <v>46063</v>
       </c>
       <c r="G259" t="s">
@@ -14415,7 +14441,7 @@
         <v>1353</v>
       </c>
       <c r="I259">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J259">
         <v>72</v>
@@ -14426,7 +14452,7 @@
       <c r="L259" t="s">
         <v>1388</v>
       </c>
-      <c r="N259" s="1">
+      <c r="N259" s="2">
         <v>46135</v>
       </c>
       <c r="Q259" t="b">
@@ -14449,7 +14475,7 @@
       <c r="E260" t="s">
         <v>1079</v>
       </c>
-      <c r="F260" s="1">
+      <c r="F260" s="2">
         <v>46063</v>
       </c>
       <c r="G260" t="s">
@@ -14459,7 +14485,7 @@
         <v>1353</v>
       </c>
       <c r="I260">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J260">
         <v>84</v>
@@ -14470,7 +14496,7 @@
       <c r="L260" t="s">
         <v>1388</v>
       </c>
-      <c r="N260" s="1">
+      <c r="N260" s="2">
         <v>46147</v>
       </c>
       <c r="Q260" t="b">
@@ -14493,7 +14519,7 @@
       <c r="E261" t="s">
         <v>1080</v>
       </c>
-      <c r="F261" s="1">
+      <c r="F261" s="2">
         <v>46063</v>
       </c>
       <c r="G261" t="s">
@@ -14503,7 +14529,7 @@
         <v>1353</v>
       </c>
       <c r="I261">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J261">
         <v>162</v>
@@ -14514,7 +14540,7 @@
       <c r="L261" t="s">
         <v>1427</v>
       </c>
-      <c r="N261" s="1">
+      <c r="N261" s="2">
         <v>46225</v>
       </c>
       <c r="Q261" t="b">
@@ -14537,7 +14563,7 @@
       <c r="E262" t="s">
         <v>1081</v>
       </c>
-      <c r="F262" s="1">
+      <c r="F262" s="2">
         <v>46063</v>
       </c>
       <c r="G262" t="s">
@@ -14555,7 +14581,7 @@
       <c r="L262" t="s">
         <v>1428</v>
       </c>
-      <c r="N262" s="1">
+      <c r="N262" s="2">
         <v>46113</v>
       </c>
       <c r="P262" t="s">
@@ -14581,7 +14607,7 @@
       <c r="E263" t="s">
         <v>1082</v>
       </c>
-      <c r="F263" s="1">
+      <c r="F263" s="2">
         <v>46063</v>
       </c>
       <c r="G263" t="s">
@@ -14610,7 +14636,7 @@
       <c r="E264" t="s">
         <v>1083</v>
       </c>
-      <c r="F264" s="1">
+      <c r="F264" s="2">
         <v>46063</v>
       </c>
       <c r="G264" t="s">
@@ -14620,7 +14646,7 @@
         <v>1353</v>
       </c>
       <c r="I264">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J264">
         <v>162</v>
@@ -14631,7 +14657,7 @@
       <c r="L264" t="s">
         <v>1388</v>
       </c>
-      <c r="N264" s="1">
+      <c r="N264" s="2">
         <v>46225</v>
       </c>
       <c r="Q264" t="b">
@@ -14654,7 +14680,7 @@
       <c r="E265" t="s">
         <v>1084</v>
       </c>
-      <c r="F265" s="1">
+      <c r="F265" s="2">
         <v>46063</v>
       </c>
       <c r="G265" t="s">
@@ -14664,7 +14690,7 @@
         <v>1353</v>
       </c>
       <c r="I265">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J265">
         <v>162</v>
@@ -14675,7 +14701,7 @@
       <c r="L265" t="s">
         <v>1395</v>
       </c>
-      <c r="N265" s="1">
+      <c r="N265" s="2">
         <v>46225</v>
       </c>
       <c r="Q265" t="b">
@@ -14698,7 +14724,7 @@
       <c r="E266" t="s">
         <v>1085</v>
       </c>
-      <c r="F266" s="1">
+      <c r="F266" s="2">
         <v>46063</v>
       </c>
       <c r="G266" t="s">
@@ -14708,7 +14734,7 @@
         <v>1353</v>
       </c>
       <c r="I266">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J266">
         <v>84</v>
@@ -14719,7 +14745,7 @@
       <c r="L266" t="s">
         <v>1388</v>
       </c>
-      <c r="N266" s="1">
+      <c r="N266" s="2">
         <v>46147</v>
       </c>
       <c r="Q266" t="b">
@@ -14742,7 +14768,7 @@
       <c r="E267" t="s">
         <v>1086</v>
       </c>
-      <c r="F267" s="1">
+      <c r="F267" s="2">
         <v>46063</v>
       </c>
       <c r="G267" t="s">
@@ -14752,7 +14778,7 @@
         <v>1353</v>
       </c>
       <c r="I267">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K267" t="s">
         <v>1360</v>
@@ -14780,7 +14806,7 @@
       <c r="E268" t="s">
         <v>1087</v>
       </c>
-      <c r="F268" s="1">
+      <c r="F268" s="2">
         <v>46063</v>
       </c>
       <c r="G268" t="s">
@@ -14790,7 +14816,7 @@
         <v>1353</v>
       </c>
       <c r="I268">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K268" t="s">
         <v>1357</v>
@@ -14815,7 +14841,7 @@
       <c r="D269" t="s">
         <v>798</v>
       </c>
-      <c r="F269" s="1">
+      <c r="F269" s="2">
         <v>46063</v>
       </c>
       <c r="G269" t="s">
@@ -14825,7 +14851,7 @@
         <v>1353</v>
       </c>
       <c r="I269">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K269" t="s">
         <v>1357</v>
@@ -14853,7 +14879,7 @@
       <c r="E270" t="s">
         <v>1088</v>
       </c>
-      <c r="F270" s="1">
+      <c r="F270" s="2">
         <v>46063</v>
       </c>
       <c r="G270" t="s">
@@ -14863,7 +14889,7 @@
         <v>1353</v>
       </c>
       <c r="I270">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K270" t="s">
         <v>1360</v>
@@ -14891,7 +14917,7 @@
       <c r="E271" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="1">
+      <c r="F271" s="2">
         <v>46063</v>
       </c>
       <c r="G271" t="s">
@@ -14901,7 +14927,7 @@
         <v>1353</v>
       </c>
       <c r="I271">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K271" t="s">
         <v>1360</v>
@@ -14929,7 +14955,7 @@
       <c r="E272" t="s">
         <v>1090</v>
       </c>
-      <c r="F272" s="1">
+      <c r="F272" s="2">
         <v>46063</v>
       </c>
       <c r="G272" t="s">
@@ -14947,7 +14973,7 @@
       <c r="L272" t="s">
         <v>1429</v>
       </c>
-      <c r="N272" s="1">
+      <c r="N272" s="2">
         <v>46185</v>
       </c>
       <c r="O272" t="s">
@@ -14973,7 +14999,7 @@
       <c r="E273" t="s">
         <v>1091</v>
       </c>
-      <c r="F273" s="1">
+      <c r="F273" s="2">
         <v>46063</v>
       </c>
       <c r="G273" t="s">
@@ -15002,7 +15028,7 @@
       <c r="E274" t="s">
         <v>1092</v>
       </c>
-      <c r="F274" s="1">
+      <c r="F274" s="2">
         <v>46063</v>
       </c>
       <c r="G274" t="s">
@@ -15017,7 +15043,7 @@
       <c r="L274" t="s">
         <v>1383</v>
       </c>
-      <c r="N274" s="1">
+      <c r="N274" s="2">
         <v>46232</v>
       </c>
       <c r="Q274" t="b">
@@ -15040,7 +15066,7 @@
       <c r="E275" t="s">
         <v>1093</v>
       </c>
-      <c r="F275" s="1">
+      <c r="F275" s="2">
         <v>46063</v>
       </c>
       <c r="G275" t="s">
@@ -15069,7 +15095,7 @@
       <c r="E276" t="s">
         <v>1094</v>
       </c>
-      <c r="F276" s="1">
+      <c r="F276" s="2">
         <v>46063</v>
       </c>
       <c r="G276" t="s">
@@ -15079,7 +15105,7 @@
         <v>1353</v>
       </c>
       <c r="I276">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K276" t="s">
         <v>1361</v>
@@ -15107,7 +15133,7 @@
       <c r="E277" t="s">
         <v>1095</v>
       </c>
-      <c r="F277" s="1">
+      <c r="F277" s="2">
         <v>46063</v>
       </c>
       <c r="G277" t="s">
@@ -15117,7 +15143,7 @@
         <v>1353</v>
       </c>
       <c r="I277">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K277" t="s">
         <v>1357</v>
@@ -15145,7 +15171,7 @@
       <c r="E278" t="s">
         <v>1096</v>
       </c>
-      <c r="F278" s="1">
+      <c r="F278" s="2">
         <v>46077</v>
       </c>
       <c r="G278" t="s">
@@ -15155,7 +15181,7 @@
         <v>1353</v>
       </c>
       <c r="I278">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J278">
         <v>148</v>
@@ -15166,7 +15192,7 @@
       <c r="L278" t="s">
         <v>1395</v>
       </c>
-      <c r="N278" s="1">
+      <c r="N278" s="2">
         <v>46225</v>
       </c>
       <c r="Q278" t="b">
@@ -15189,7 +15215,7 @@
       <c r="E279" t="s">
         <v>1097</v>
       </c>
-      <c r="F279" s="1">
+      <c r="F279" s="2">
         <v>46077</v>
       </c>
       <c r="G279" t="s">
@@ -15199,7 +15225,7 @@
         <v>1353</v>
       </c>
       <c r="I279">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K279" t="s">
         <v>1359</v>
@@ -15230,7 +15256,7 @@
       <c r="E280" t="s">
         <v>1098</v>
       </c>
-      <c r="F280" s="1">
+      <c r="F280" s="2">
         <v>46085</v>
       </c>
       <c r="G280" t="s">
@@ -15240,7 +15266,7 @@
         <v>1353</v>
       </c>
       <c r="I280">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K280" t="s">
         <v>1357</v>
@@ -15268,7 +15294,7 @@
       <c r="E281" t="s">
         <v>1099</v>
       </c>
-      <c r="F281" s="1">
+      <c r="F281" s="2">
         <v>46085</v>
       </c>
       <c r="G281" t="s">
@@ -15278,7 +15304,7 @@
         <v>1353</v>
       </c>
       <c r="I281">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K281" t="s">
         <v>1357</v>
@@ -15309,7 +15335,7 @@
       <c r="E282" t="s">
         <v>1100</v>
       </c>
-      <c r="F282" s="1">
+      <c r="F282" s="2">
         <v>46090</v>
       </c>
       <c r="G282" t="s">
@@ -15319,7 +15345,7 @@
         <v>1353</v>
       </c>
       <c r="I282">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K282" t="s">
         <v>1357</v>
@@ -15347,7 +15373,7 @@
       <c r="E283" t="s">
         <v>1101</v>
       </c>
-      <c r="F283" s="1">
+      <c r="F283" s="2">
         <v>46100</v>
       </c>
       <c r="G283" t="s">
@@ -15376,7 +15402,7 @@
       <c r="E284" t="s">
         <v>1102</v>
       </c>
-      <c r="F284" s="1">
+      <c r="F284" s="2">
         <v>46100</v>
       </c>
       <c r="G284" t="s">
@@ -15405,7 +15431,7 @@
       <c r="E285" t="s">
         <v>1103</v>
       </c>
-      <c r="F285" s="1">
+      <c r="F285" s="2">
         <v>46100</v>
       </c>
       <c r="G285" t="s">
@@ -15434,7 +15460,7 @@
       <c r="E286" t="s">
         <v>1104</v>
       </c>
-      <c r="F286" s="1">
+      <c r="F286" s="2">
         <v>46100</v>
       </c>
       <c r="G286" t="s">
@@ -15463,7 +15489,7 @@
       <c r="E287" t="s">
         <v>1105</v>
       </c>
-      <c r="F287" s="1">
+      <c r="F287" s="2">
         <v>46107</v>
       </c>
       <c r="G287" t="s">
@@ -15492,7 +15518,7 @@
       <c r="E288" t="s">
         <v>1106</v>
       </c>
-      <c r="F288" s="1">
+      <c r="F288" s="2">
         <v>46107</v>
       </c>
       <c r="G288" t="s">
@@ -15502,7 +15528,7 @@
         <v>1353</v>
       </c>
       <c r="I288">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J288">
         <v>28</v>
@@ -15513,7 +15539,7 @@
       <c r="L288" t="s">
         <v>1388</v>
       </c>
-      <c r="N288" s="1">
+      <c r="N288" s="2">
         <v>46135</v>
       </c>
       <c r="Q288" t="b">
@@ -15536,7 +15562,7 @@
       <c r="E289" t="s">
         <v>1107</v>
       </c>
-      <c r="F289" s="1">
+      <c r="F289" s="2">
         <v>46107</v>
       </c>
       <c r="G289" t="s">
@@ -15565,7 +15591,7 @@
       <c r="E290" t="s">
         <v>1108</v>
       </c>
-      <c r="F290" s="1">
+      <c r="F290" s="2">
         <v>46107</v>
       </c>
       <c r="G290" t="s">
@@ -15575,7 +15601,7 @@
         <v>1353</v>
       </c>
       <c r="I290">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J290">
         <v>20</v>
@@ -15586,7 +15612,7 @@
       <c r="L290" t="s">
         <v>1388</v>
       </c>
-      <c r="N290" s="1">
+      <c r="N290" s="2">
         <v>46127</v>
       </c>
       <c r="Q290" t="b">
@@ -15609,7 +15635,7 @@
       <c r="E291" t="s">
         <v>1109</v>
       </c>
-      <c r="F291" s="1">
+      <c r="F291" s="2">
         <v>46107</v>
       </c>
       <c r="G291" t="s">
@@ -15619,7 +15645,7 @@
         <v>1353</v>
       </c>
       <c r="I291">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J291">
         <v>20</v>
@@ -15630,7 +15656,7 @@
       <c r="L291" t="s">
         <v>1430</v>
       </c>
-      <c r="N291" s="1">
+      <c r="N291" s="2">
         <v>46127</v>
       </c>
       <c r="Q291" t="b">
@@ -15653,7 +15679,7 @@
       <c r="E292" t="s">
         <v>1110</v>
       </c>
-      <c r="F292" s="1">
+      <c r="F292" s="2">
         <v>46112</v>
       </c>
       <c r="G292" t="s">
@@ -15663,7 +15689,7 @@
         <v>1353</v>
       </c>
       <c r="I292">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K292" t="s">
         <v>1360</v>
@@ -15691,7 +15717,7 @@
       <c r="E293" t="s">
         <v>1111</v>
       </c>
-      <c r="F293" s="1">
+      <c r="F293" s="2">
         <v>46125</v>
       </c>
       <c r="G293" t="s">
@@ -15701,7 +15727,7 @@
         <v>1353</v>
       </c>
       <c r="I293">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K293" t="s">
         <v>1361</v>
@@ -15729,7 +15755,7 @@
       <c r="E294" t="s">
         <v>1112</v>
       </c>
-      <c r="F294" s="1">
+      <c r="F294" s="2">
         <v>46125</v>
       </c>
       <c r="G294" t="s">
@@ -15739,7 +15765,7 @@
         <v>1353</v>
       </c>
       <c r="I294">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K294" t="s">
         <v>1366</v>
@@ -15764,7 +15790,7 @@
       <c r="E295" t="s">
         <v>1113</v>
       </c>
-      <c r="F295" s="1">
+      <c r="F295" s="2">
         <v>46125</v>
       </c>
       <c r="G295" t="s">
@@ -15774,7 +15800,7 @@
         <v>1353</v>
       </c>
       <c r="I295">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K295" t="s">
         <v>1366</v>
@@ -15799,7 +15825,7 @@
       <c r="E296" t="s">
         <v>1114</v>
       </c>
-      <c r="F296" s="1">
+      <c r="F296" s="2">
         <v>46125</v>
       </c>
       <c r="G296" t="s">
@@ -15809,7 +15835,7 @@
         <v>1353</v>
       </c>
       <c r="I296">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K296" t="s">
         <v>1366</v>
@@ -15834,7 +15860,7 @@
       <c r="E297" t="s">
         <v>1115</v>
       </c>
-      <c r="F297" s="1">
+      <c r="F297" s="2">
         <v>46125</v>
       </c>
       <c r="G297" t="s">
@@ -15846,7 +15872,7 @@
       <c r="K297" t="s">
         <v>1359</v>
       </c>
-      <c r="N297" s="1">
+      <c r="N297" s="2">
         <v>46183</v>
       </c>
       <c r="O297">
@@ -15872,7 +15898,7 @@
       <c r="E298" t="s">
         <v>1116</v>
       </c>
-      <c r="F298" s="1">
+      <c r="F298" s="2">
         <v>46125</v>
       </c>
       <c r="G298" t="s">
@@ -15882,7 +15908,7 @@
         <v>1353</v>
       </c>
       <c r="I298">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J298">
         <v>58</v>
@@ -15890,7 +15916,7 @@
       <c r="K298" t="s">
         <v>1359</v>
       </c>
-      <c r="N298" s="1">
+      <c r="N298" s="2">
         <v>46183</v>
       </c>
       <c r="Q298" t="b">
@@ -15913,7 +15939,7 @@
       <c r="E299" t="s">
         <v>1117</v>
       </c>
-      <c r="F299" s="1">
+      <c r="F299" s="2">
         <v>46125</v>
       </c>
       <c r="G299" t="s">
@@ -15923,7 +15949,7 @@
         <v>1353</v>
       </c>
       <c r="I299">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J299">
         <v>100</v>
@@ -15934,7 +15960,7 @@
       <c r="L299" t="s">
         <v>1388</v>
       </c>
-      <c r="N299" s="1">
+      <c r="N299" s="2">
         <v>46225</v>
       </c>
       <c r="Q299" t="b">
@@ -15957,7 +15983,7 @@
       <c r="E300" t="s">
         <v>1118</v>
       </c>
-      <c r="F300" s="1">
+      <c r="F300" s="2">
         <v>46125</v>
       </c>
       <c r="G300" t="s">
@@ -15967,7 +15993,7 @@
         <v>1353</v>
       </c>
       <c r="I300">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J300">
         <v>86</v>
@@ -15978,7 +16004,7 @@
       <c r="L300" t="s">
         <v>1388</v>
       </c>
-      <c r="N300" s="1">
+      <c r="N300" s="2">
         <v>46211</v>
       </c>
       <c r="Q300" t="b">
@@ -16001,7 +16027,7 @@
       <c r="E301" t="s">
         <v>1119</v>
       </c>
-      <c r="F301" s="1">
+      <c r="F301" s="2">
         <v>46125</v>
       </c>
       <c r="G301" t="s">
@@ -16011,7 +16037,7 @@
         <v>1353</v>
       </c>
       <c r="I301">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J301">
         <v>102</v>
@@ -16022,7 +16048,7 @@
       <c r="L301" t="s">
         <v>1388</v>
       </c>
-      <c r="N301" s="1">
+      <c r="N301" s="2">
         <v>46227</v>
       </c>
       <c r="Q301" t="b">
@@ -16045,7 +16071,7 @@
       <c r="E302" t="s">
         <v>1120</v>
       </c>
-      <c r="F302" s="1">
+      <c r="F302" s="2">
         <v>46125</v>
       </c>
       <c r="G302" t="s">
@@ -16055,7 +16081,7 @@
         <v>1353</v>
       </c>
       <c r="I302">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K302" t="s">
         <v>1360</v>
@@ -16083,7 +16109,7 @@
       <c r="E303" t="s">
         <v>1121</v>
       </c>
-      <c r="F303" s="1">
+      <c r="F303" s="2">
         <v>46125</v>
       </c>
       <c r="G303" t="s">
@@ -16093,7 +16119,7 @@
         <v>1353</v>
       </c>
       <c r="I303">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K303" t="s">
         <v>1357</v>
@@ -16121,7 +16147,7 @@
       <c r="E304" t="s">
         <v>1122</v>
       </c>
-      <c r="F304" s="1">
+      <c r="F304" s="2">
         <v>46125</v>
       </c>
       <c r="G304" t="s">
@@ -16131,7 +16157,7 @@
         <v>1353</v>
       </c>
       <c r="I304">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K304" t="s">
         <v>1360</v>
@@ -16159,7 +16185,7 @@
       <c r="E305" t="s">
         <v>1123</v>
       </c>
-      <c r="F305" s="1">
+      <c r="F305" s="2">
         <v>46125</v>
       </c>
       <c r="G305" t="s">
@@ -16169,7 +16195,7 @@
         <v>1353</v>
       </c>
       <c r="I305">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J305">
         <v>35</v>
@@ -16180,7 +16206,7 @@
       <c r="L305" t="s">
         <v>1431</v>
       </c>
-      <c r="N305" s="1">
+      <c r="N305" s="2">
         <v>46160</v>
       </c>
       <c r="Q305" t="b">
@@ -16203,7 +16229,7 @@
       <c r="E306" t="s">
         <v>1124</v>
       </c>
-      <c r="F306" s="1">
+      <c r="F306" s="2">
         <v>46125</v>
       </c>
       <c r="G306" t="s">
@@ -16213,7 +16239,7 @@
         <v>1353</v>
       </c>
       <c r="I306">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J306">
         <v>31</v>
@@ -16224,7 +16250,7 @@
       <c r="L306" t="s">
         <v>1432</v>
       </c>
-      <c r="N306" s="1">
+      <c r="N306" s="2">
         <v>46156</v>
       </c>
       <c r="Q306" t="b">
@@ -16247,7 +16273,7 @@
       <c r="E307" t="s">
         <v>1125</v>
       </c>
-      <c r="F307" s="1">
+      <c r="F307" s="2">
         <v>46125</v>
       </c>
       <c r="G307" t="s">
@@ -16265,7 +16291,7 @@
       <c r="L307" t="s">
         <v>1433</v>
       </c>
-      <c r="N307" s="1">
+      <c r="N307" s="2">
         <v>46209</v>
       </c>
       <c r="P307" t="s">
@@ -16291,7 +16317,7 @@
       <c r="E308" t="s">
         <v>1126</v>
       </c>
-      <c r="F308" s="1">
+      <c r="F308" s="2">
         <v>46125</v>
       </c>
       <c r="G308" t="s">
@@ -16301,7 +16327,7 @@
         <v>1353</v>
       </c>
       <c r="I308">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K308" t="s">
         <v>1356</v>
@@ -16329,7 +16355,7 @@
       <c r="E309" t="s">
         <v>1127</v>
       </c>
-      <c r="F309" s="1">
+      <c r="F309" s="2">
         <v>46125</v>
       </c>
       <c r="G309" t="s">
@@ -16344,7 +16370,7 @@
       <c r="L309" t="s">
         <v>1383</v>
       </c>
-      <c r="N309" s="1">
+      <c r="N309" s="2">
         <v>46232</v>
       </c>
       <c r="Q309" t="b">
@@ -16367,7 +16393,7 @@
       <c r="E310" t="s">
         <v>1128</v>
       </c>
-      <c r="F310" s="1">
+      <c r="F310" s="2">
         <v>46125</v>
       </c>
       <c r="G310" t="s">
@@ -16377,7 +16403,7 @@
         <v>1353</v>
       </c>
       <c r="I310">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J310">
         <v>107</v>
@@ -16388,7 +16414,7 @@
       <c r="L310" t="s">
         <v>1383</v>
       </c>
-      <c r="N310" s="1">
+      <c r="N310" s="2">
         <v>46232</v>
       </c>
       <c r="Q310" t="b">
@@ -16411,7 +16437,7 @@
       <c r="E311" t="s">
         <v>1129</v>
       </c>
-      <c r="F311" s="1">
+      <c r="F311" s="2">
         <v>46125</v>
       </c>
       <c r="G311" t="s">
@@ -16421,7 +16447,7 @@
         <v>1353</v>
       </c>
       <c r="I311">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K311" t="s">
         <v>1356</v>
@@ -16449,7 +16475,7 @@
       <c r="E312" t="s">
         <v>1130</v>
       </c>
-      <c r="F312" s="1">
+      <c r="F312" s="2">
         <v>46125</v>
       </c>
       <c r="G312" t="s">
@@ -16467,7 +16493,7 @@
       <c r="L312" t="s">
         <v>1383</v>
       </c>
-      <c r="N312" s="1">
+      <c r="N312" s="2">
         <v>46232</v>
       </c>
       <c r="Q312" t="b">
@@ -16490,7 +16516,7 @@
       <c r="E313" t="s">
         <v>1131</v>
       </c>
-      <c r="F313" s="1">
+      <c r="F313" s="2">
         <v>46125</v>
       </c>
       <c r="G313" t="s">
@@ -16525,7 +16551,7 @@
       <c r="E314" t="s">
         <v>1132</v>
       </c>
-      <c r="F314" s="1">
+      <c r="F314" s="2">
         <v>46125</v>
       </c>
       <c r="G314" t="s">
@@ -16540,7 +16566,7 @@
       <c r="L314" t="s">
         <v>1383</v>
       </c>
-      <c r="N314" s="1">
+      <c r="N314" s="2">
         <v>46232</v>
       </c>
       <c r="Q314" t="b">
@@ -16563,7 +16589,7 @@
       <c r="E315" t="s">
         <v>1133</v>
       </c>
-      <c r="F315" s="1">
+      <c r="F315" s="2">
         <v>46125</v>
       </c>
       <c r="G315" t="s">
@@ -16578,7 +16604,7 @@
       <c r="L315" t="s">
         <v>1383</v>
       </c>
-      <c r="N315" s="1">
+      <c r="N315" s="2">
         <v>46232</v>
       </c>
       <c r="Q315" t="b">
@@ -16601,7 +16627,7 @@
       <c r="E316" t="s">
         <v>1134</v>
       </c>
-      <c r="F316" s="1">
+      <c r="F316" s="2">
         <v>46125</v>
       </c>
       <c r="G316" t="s">
@@ -16611,7 +16637,7 @@
         <v>1353</v>
       </c>
       <c r="I316">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K316" t="s">
         <v>1357</v>
@@ -16642,7 +16668,7 @@
       <c r="E317" t="s">
         <v>1135</v>
       </c>
-      <c r="F317" s="1">
+      <c r="F317" s="2">
         <v>46125</v>
       </c>
       <c r="G317" t="s">
@@ -16677,7 +16703,7 @@
       <c r="E318" t="s">
         <v>1136</v>
       </c>
-      <c r="F318" s="1">
+      <c r="F318" s="2">
         <v>46125</v>
       </c>
       <c r="G318" t="s">
@@ -16706,7 +16732,7 @@
       <c r="E319" t="s">
         <v>1137</v>
       </c>
-      <c r="F319" s="1">
+      <c r="F319" s="2">
         <v>46125</v>
       </c>
       <c r="G319" t="s">
@@ -16721,7 +16747,7 @@
       <c r="L319" t="s">
         <v>1434</v>
       </c>
-      <c r="N319" s="1">
+      <c r="N319" s="2">
         <v>46175</v>
       </c>
       <c r="Q319" t="b">
@@ -16744,7 +16770,7 @@
       <c r="E320" t="s">
         <v>1138</v>
       </c>
-      <c r="F320" s="1">
+      <c r="F320" s="2">
         <v>46125</v>
       </c>
       <c r="G320" t="s">
@@ -16754,7 +16780,7 @@
         <v>1353</v>
       </c>
       <c r="I320">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K320" t="s">
         <v>1361</v>
@@ -16782,7 +16808,7 @@
       <c r="E321" t="s">
         <v>1139</v>
       </c>
-      <c r="F321" s="1">
+      <c r="F321" s="2">
         <v>46125</v>
       </c>
       <c r="G321" t="s">
@@ -16792,7 +16818,7 @@
         <v>1353</v>
       </c>
       <c r="I321">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K321" t="s">
         <v>1357</v>
@@ -16820,7 +16846,7 @@
       <c r="E322" t="s">
         <v>1140</v>
       </c>
-      <c r="F322" s="1">
+      <c r="F322" s="2">
         <v>46125</v>
       </c>
       <c r="G322" t="s">
@@ -16830,7 +16856,7 @@
         <v>1353</v>
       </c>
       <c r="I322">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J322">
         <v>57</v>
@@ -16841,7 +16867,7 @@
       <c r="L322" t="s">
         <v>1435</v>
       </c>
-      <c r="N322" s="1">
+      <c r="N322" s="2">
         <v>46182</v>
       </c>
       <c r="Q322" t="b">
@@ -16864,7 +16890,7 @@
       <c r="E323" t="s">
         <v>1141</v>
       </c>
-      <c r="F323" s="1">
+      <c r="F323" s="2">
         <v>46125</v>
       </c>
       <c r="G323" t="s">
@@ -16899,7 +16925,7 @@
       <c r="E324" t="s">
         <v>1142</v>
       </c>
-      <c r="F324" s="1">
+      <c r="F324" s="2">
         <v>46125</v>
       </c>
       <c r="G324" t="s">
@@ -16934,7 +16960,7 @@
       <c r="E325" t="s">
         <v>1143</v>
       </c>
-      <c r="F325" s="1">
+      <c r="F325" s="2">
         <v>46125</v>
       </c>
       <c r="G325" t="s">
@@ -16944,7 +16970,7 @@
         <v>1353</v>
       </c>
       <c r="I325">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J325">
         <v>57</v>
@@ -16955,7 +16981,7 @@
       <c r="L325" t="s">
         <v>1435</v>
       </c>
-      <c r="N325" s="1">
+      <c r="N325" s="2">
         <v>46182</v>
       </c>
       <c r="Q325" t="b">
@@ -16978,7 +17004,7 @@
       <c r="E326" t="s">
         <v>1144</v>
       </c>
-      <c r="F326" s="1">
+      <c r="F326" s="2">
         <v>46125</v>
       </c>
       <c r="G326" t="s">
@@ -16993,7 +17019,7 @@
       <c r="L326" t="s">
         <v>1383</v>
       </c>
-      <c r="N326" s="1">
+      <c r="N326" s="2">
         <v>46232</v>
       </c>
       <c r="Q326" t="b">
@@ -17016,7 +17042,7 @@
       <c r="E327" t="s">
         <v>1140</v>
       </c>
-      <c r="F327" s="1">
+      <c r="F327" s="2">
         <v>46125</v>
       </c>
       <c r="G327" t="s">
@@ -17026,7 +17052,7 @@
         <v>1353</v>
       </c>
       <c r="I327">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J327">
         <v>57</v>
@@ -17037,7 +17063,7 @@
       <c r="L327" t="s">
         <v>1435</v>
       </c>
-      <c r="N327" s="1">
+      <c r="N327" s="2">
         <v>46182</v>
       </c>
       <c r="Q327" t="b">
@@ -17060,7 +17086,7 @@
       <c r="E328" t="s">
         <v>1145</v>
       </c>
-      <c r="F328" s="1">
+      <c r="F328" s="2">
         <v>46125</v>
       </c>
       <c r="G328" t="s">
@@ -17070,7 +17096,7 @@
         <v>1353</v>
       </c>
       <c r="I328">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J328">
         <v>57</v>
@@ -17081,7 +17107,7 @@
       <c r="L328" t="s">
         <v>1435</v>
       </c>
-      <c r="N328" s="1">
+      <c r="N328" s="2">
         <v>46182</v>
       </c>
       <c r="Q328" t="b">
@@ -17104,7 +17130,7 @@
       <c r="E329" t="s">
         <v>1146</v>
       </c>
-      <c r="F329" s="1">
+      <c r="F329" s="2">
         <v>46125</v>
       </c>
       <c r="G329" t="s">
@@ -17114,7 +17140,7 @@
         <v>1353</v>
       </c>
       <c r="I329">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J329">
         <v>57</v>
@@ -17125,7 +17151,7 @@
       <c r="L329" t="s">
         <v>1435</v>
       </c>
-      <c r="N329" s="1">
+      <c r="N329" s="2">
         <v>46182</v>
       </c>
       <c r="Q329" t="b">
@@ -17148,7 +17174,7 @@
       <c r="E330" t="s">
         <v>1147</v>
       </c>
-      <c r="F330" s="1">
+      <c r="F330" s="2">
         <v>46125</v>
       </c>
       <c r="G330" t="s">
@@ -17158,7 +17184,7 @@
         <v>1353</v>
       </c>
       <c r="I330">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J330">
         <v>57</v>
@@ -17169,7 +17195,7 @@
       <c r="L330" t="s">
         <v>1435</v>
       </c>
-      <c r="N330" s="1">
+      <c r="N330" s="2">
         <v>46182</v>
       </c>
       <c r="Q330" t="b">
@@ -17192,7 +17218,7 @@
       <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="F331" s="1">
+      <c r="F331" s="2">
         <v>46125</v>
       </c>
       <c r="G331" t="s">
@@ -17202,7 +17228,7 @@
         <v>1353</v>
       </c>
       <c r="I331">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K331" t="s">
         <v>1356</v>
@@ -17230,7 +17256,7 @@
       <c r="E332" t="s">
         <v>1148</v>
       </c>
-      <c r="F332" s="1">
+      <c r="F332" s="2">
         <v>46125</v>
       </c>
       <c r="G332" t="s">
@@ -17240,7 +17266,7 @@
         <v>1353</v>
       </c>
       <c r="I332">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K332" t="s">
         <v>1357</v>
@@ -17268,7 +17294,7 @@
       <c r="E333" t="s">
         <v>910</v>
       </c>
-      <c r="F333" s="1">
+      <c r="F333" s="2">
         <v>46125</v>
       </c>
       <c r="G333" t="s">
@@ -17278,7 +17304,7 @@
         <v>1353</v>
       </c>
       <c r="I333">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J333">
         <v>100</v>
@@ -17289,7 +17315,7 @@
       <c r="L333" t="s">
         <v>1395</v>
       </c>
-      <c r="N333" s="1">
+      <c r="N333" s="2">
         <v>46225</v>
       </c>
       <c r="Q333" t="b">
@@ -17312,7 +17338,7 @@
       <c r="E334" t="s">
         <v>1149</v>
       </c>
-      <c r="F334" s="1">
+      <c r="F334" s="2">
         <v>46125</v>
       </c>
       <c r="G334" t="s">
@@ -17322,7 +17348,7 @@
         <v>1353</v>
       </c>
       <c r="I334">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K334" t="s">
         <v>1357</v>
@@ -17350,7 +17376,7 @@
       <c r="E335" t="s">
         <v>1150</v>
       </c>
-      <c r="F335" s="1">
+      <c r="F335" s="2">
         <v>46127</v>
       </c>
       <c r="G335" t="s">
@@ -17365,7 +17391,7 @@
       <c r="L335" t="s">
         <v>1434</v>
       </c>
-      <c r="N335" s="1">
+      <c r="N335" s="2">
         <v>46175</v>
       </c>
       <c r="Q335" t="b">
@@ -17388,7 +17414,7 @@
       <c r="E336" t="s">
         <v>1151</v>
       </c>
-      <c r="F336" s="1">
+      <c r="F336" s="2">
         <v>46127</v>
       </c>
       <c r="G336" t="s">
@@ -17398,7 +17424,7 @@
         <v>1353</v>
       </c>
       <c r="I336">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J336">
         <v>28</v>
@@ -17409,7 +17435,7 @@
       <c r="L336" t="s">
         <v>1388</v>
       </c>
-      <c r="N336" s="1">
+      <c r="N336" s="2">
         <v>46155</v>
       </c>
       <c r="Q336" t="b">
@@ -17432,7 +17458,7 @@
       <c r="E337" t="s">
         <v>1152</v>
       </c>
-      <c r="F337" s="1">
+      <c r="F337" s="2">
         <v>46127</v>
       </c>
       <c r="G337" t="s">
@@ -17447,7 +17473,7 @@
       <c r="L337" t="s">
         <v>1434</v>
       </c>
-      <c r="N337" s="1">
+      <c r="N337" s="2">
         <v>46175</v>
       </c>
       <c r="Q337" t="b">
@@ -17470,7 +17496,7 @@
       <c r="E338" t="s">
         <v>1153</v>
       </c>
-      <c r="F338" s="1">
+      <c r="F338" s="2">
         <v>46127</v>
       </c>
       <c r="G338" t="s">
@@ -17480,7 +17506,7 @@
         <v>1353</v>
       </c>
       <c r="I338">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J338">
         <v>12</v>
@@ -17491,7 +17517,7 @@
       <c r="L338" t="s">
         <v>1388</v>
       </c>
-      <c r="N338" s="1">
+      <c r="N338" s="2">
         <v>46139</v>
       </c>
       <c r="Q338" t="b">
@@ -17514,7 +17540,7 @@
       <c r="E339" t="s">
         <v>1154</v>
       </c>
-      <c r="F339" s="1">
+      <c r="F339" s="2">
         <v>46129</v>
       </c>
       <c r="G339" t="s">
@@ -17543,7 +17569,7 @@
       <c r="E340" t="s">
         <v>1155</v>
       </c>
-      <c r="F340" s="1">
+      <c r="F340" s="2">
         <v>46142</v>
       </c>
       <c r="G340" t="s">
@@ -17553,7 +17579,7 @@
         <v>1353</v>
       </c>
       <c r="I340">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J340">
         <v>98</v>
@@ -17561,7 +17587,7 @@
       <c r="L340" t="s">
         <v>1383</v>
       </c>
-      <c r="N340" s="1">
+      <c r="N340" s="2">
         <v>46240</v>
       </c>
       <c r="Q340" t="b">
@@ -17584,7 +17610,7 @@
       <c r="E341" t="s">
         <v>1156</v>
       </c>
-      <c r="F341" s="1">
+      <c r="F341" s="2">
         <v>46142</v>
       </c>
       <c r="G341" t="s">
@@ -17594,7 +17620,7 @@
         <v>1353</v>
       </c>
       <c r="I341">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J341">
         <v>90</v>
@@ -17602,7 +17628,7 @@
       <c r="L341" t="s">
         <v>1383</v>
       </c>
-      <c r="N341" s="1">
+      <c r="N341" s="2">
         <v>46232</v>
       </c>
       <c r="Q341" t="b">
@@ -17625,7 +17651,7 @@
       <c r="E342" t="s">
         <v>1157</v>
       </c>
-      <c r="F342" s="1">
+      <c r="F342" s="2">
         <v>46142</v>
       </c>
       <c r="G342" t="s">
@@ -17635,7 +17661,7 @@
         <v>1353</v>
       </c>
       <c r="I342">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K342" t="s">
         <v>1356</v>
@@ -17663,7 +17689,7 @@
       <c r="E343" t="s">
         <v>1158</v>
       </c>
-      <c r="F343" s="1">
+      <c r="F343" s="2">
         <v>46142</v>
       </c>
       <c r="G343" t="s">
@@ -17678,7 +17704,7 @@
       <c r="L343" t="s">
         <v>1383</v>
       </c>
-      <c r="N343" s="1">
+      <c r="N343" s="2">
         <v>46232</v>
       </c>
       <c r="Q343" t="b">
@@ -17701,7 +17727,7 @@
       <c r="E344" t="s">
         <v>1159</v>
       </c>
-      <c r="F344" s="1">
+      <c r="F344" s="2">
         <v>46142</v>
       </c>
       <c r="G344" t="s">
@@ -17716,7 +17742,7 @@
       <c r="L344" t="s">
         <v>1383</v>
       </c>
-      <c r="N344" s="1">
+      <c r="N344" s="2">
         <v>46232</v>
       </c>
       <c r="Q344" t="b">
@@ -17739,7 +17765,7 @@
       <c r="E345" t="s">
         <v>1160</v>
       </c>
-      <c r="F345" s="1">
+      <c r="F345" s="2">
         <v>46142</v>
       </c>
       <c r="G345" t="s">
@@ -17749,7 +17775,7 @@
         <v>1353</v>
       </c>
       <c r="I345">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K345" t="s">
         <v>1356</v>
@@ -17777,7 +17803,7 @@
       <c r="E346" t="s">
         <v>1161</v>
       </c>
-      <c r="F346" s="1">
+      <c r="F346" s="2">
         <v>46142</v>
       </c>
       <c r="G346" t="s">
@@ -17792,7 +17818,7 @@
       <c r="L346" t="s">
         <v>1383</v>
       </c>
-      <c r="N346" s="1">
+      <c r="N346" s="2">
         <v>46232</v>
       </c>
       <c r="Q346" t="b">
@@ -17815,7 +17841,7 @@
       <c r="E347" t="s">
         <v>1162</v>
       </c>
-      <c r="F347" s="1">
+      <c r="F347" s="2">
         <v>46142</v>
       </c>
       <c r="G347" t="s">
@@ -17825,7 +17851,7 @@
         <v>1353</v>
       </c>
       <c r="I347">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J347">
         <v>18</v>
@@ -17836,7 +17862,7 @@
       <c r="L347" t="s">
         <v>1431</v>
       </c>
-      <c r="N347" s="1">
+      <c r="N347" s="2">
         <v>46160</v>
       </c>
       <c r="P347" t="s">
@@ -17862,7 +17888,7 @@
       <c r="E348" t="s">
         <v>1163</v>
       </c>
-      <c r="F348" s="1">
+      <c r="F348" s="2">
         <v>46142</v>
       </c>
       <c r="G348" t="s">
@@ -17872,7 +17898,7 @@
         <v>1353</v>
       </c>
       <c r="I348">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J348">
         <v>14</v>
@@ -17883,7 +17909,7 @@
       <c r="L348" t="s">
         <v>1432</v>
       </c>
-      <c r="N348" s="1">
+      <c r="N348" s="2">
         <v>46156</v>
       </c>
       <c r="Q348" t="b">
@@ -17906,7 +17932,7 @@
       <c r="E349" t="s">
         <v>1164</v>
       </c>
-      <c r="F349" s="1">
+      <c r="F349" s="2">
         <v>46142</v>
       </c>
       <c r="G349" t="s">
@@ -17916,7 +17942,7 @@
         <v>1353</v>
       </c>
       <c r="I349">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K349" t="s">
         <v>1361</v>
@@ -17944,7 +17970,7 @@
       <c r="E350" t="s">
         <v>1165</v>
       </c>
-      <c r="F350" s="1">
+      <c r="F350" s="2">
         <v>46142</v>
       </c>
       <c r="G350" t="s">
@@ -17954,12 +17980,12 @@
         <v>1353</v>
       </c>
       <c r="I350">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J350">
         <v>46</v>
       </c>
-      <c r="N350" s="1">
+      <c r="N350" s="2">
         <v>46188</v>
       </c>
       <c r="Q350" t="b">
@@ -17982,7 +18008,7 @@
       <c r="E351" t="s">
         <v>1166</v>
       </c>
-      <c r="F351" s="1">
+      <c r="F351" s="2">
         <v>46142</v>
       </c>
       <c r="G351" t="s">
@@ -17992,7 +18018,7 @@
         <v>1353</v>
       </c>
       <c r="I351">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J351">
         <v>82</v>
@@ -18003,7 +18029,7 @@
       <c r="L351" t="s">
         <v>1436</v>
       </c>
-      <c r="N351" s="1">
+      <c r="N351" s="2">
         <v>46224</v>
       </c>
       <c r="Q351" t="b">
@@ -18026,7 +18052,7 @@
       <c r="E352" t="s">
         <v>1167</v>
       </c>
-      <c r="F352" s="1">
+      <c r="F352" s="2">
         <v>46142</v>
       </c>
       <c r="G352" t="s">
@@ -18036,7 +18062,7 @@
         <v>1353</v>
       </c>
       <c r="I352">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J352">
         <v>78</v>
@@ -18047,7 +18073,7 @@
       <c r="L352" t="s">
         <v>1437</v>
       </c>
-      <c r="N352" s="1">
+      <c r="N352" s="2">
         <v>46220</v>
       </c>
       <c r="Q352" t="b">
@@ -18070,7 +18096,7 @@
       <c r="E353" t="s">
         <v>1168</v>
       </c>
-      <c r="F353" s="1">
+      <c r="F353" s="2">
         <v>46142</v>
       </c>
       <c r="G353" t="s">
@@ -18080,7 +18106,7 @@
         <v>1353</v>
       </c>
       <c r="I353">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J353">
         <v>83</v>
@@ -18091,7 +18117,7 @@
       <c r="L353" t="s">
         <v>1395</v>
       </c>
-      <c r="N353" s="1">
+      <c r="N353" s="2">
         <v>46225</v>
       </c>
       <c r="Q353" t="b">
@@ -18114,7 +18140,7 @@
       <c r="E354" t="s">
         <v>1169</v>
       </c>
-      <c r="F354" s="1">
+      <c r="F354" s="2">
         <v>46142</v>
       </c>
       <c r="G354" t="s">
@@ -18124,7 +18150,7 @@
         <v>1353</v>
       </c>
       <c r="I354">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K354" t="s">
         <v>1360</v>
@@ -18152,7 +18178,7 @@
       <c r="E355" t="s">
         <v>1170</v>
       </c>
-      <c r="F355" s="1">
+      <c r="F355" s="2">
         <v>46142</v>
       </c>
       <c r="G355" t="s">
@@ -18162,7 +18188,7 @@
         <v>1353</v>
       </c>
       <c r="I355">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J355">
         <v>8</v>
@@ -18173,7 +18199,7 @@
       <c r="L355" t="s">
         <v>1438</v>
       </c>
-      <c r="N355" s="1">
+      <c r="N355" s="2">
         <v>46150</v>
       </c>
       <c r="Q355" t="b">
@@ -18196,7 +18222,7 @@
       <c r="E356" t="s">
         <v>1171</v>
       </c>
-      <c r="F356" s="1">
+      <c r="F356" s="2">
         <v>46142</v>
       </c>
       <c r="G356" t="s">
@@ -18211,7 +18237,7 @@
       <c r="L356" t="s">
         <v>1439</v>
       </c>
-      <c r="N356" s="1">
+      <c r="N356" s="2">
         <v>46176</v>
       </c>
       <c r="Q356" t="b">
@@ -18234,7 +18260,7 @@
       <c r="E357" t="s">
         <v>1172</v>
       </c>
-      <c r="F357" s="1">
+      <c r="F357" s="2">
         <v>46142</v>
       </c>
       <c r="G357" t="s">
@@ -18244,7 +18270,7 @@
         <v>1353</v>
       </c>
       <c r="I357">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J357">
         <v>85</v>
@@ -18252,7 +18278,7 @@
       <c r="K357" t="s">
         <v>1360</v>
       </c>
-      <c r="N357" s="1">
+      <c r="N357" s="2">
         <v>46227</v>
       </c>
       <c r="Q357" t="b">
@@ -18275,7 +18301,7 @@
       <c r="E358" t="s">
         <v>1173</v>
       </c>
-      <c r="F358" s="1">
+      <c r="F358" s="2">
         <v>46142</v>
       </c>
       <c r="G358" t="s">
@@ -18293,7 +18319,7 @@
       <c r="L358" t="s">
         <v>1440</v>
       </c>
-      <c r="N358" s="1">
+      <c r="N358" s="2">
         <v>46227</v>
       </c>
       <c r="P358" t="s">
@@ -18319,7 +18345,7 @@
       <c r="E359" t="s">
         <v>1174</v>
       </c>
-      <c r="F359" s="1">
+      <c r="F359" s="2">
         <v>46142</v>
       </c>
       <c r="G359" t="s">
@@ -18331,7 +18357,7 @@
       <c r="J359">
         <v>63</v>
       </c>
-      <c r="N359" s="1">
+      <c r="N359" s="2">
         <v>46205</v>
       </c>
       <c r="P359" t="s">
@@ -18357,7 +18383,7 @@
       <c r="E360" t="s">
         <v>949</v>
       </c>
-      <c r="F360" s="1">
+      <c r="F360" s="2">
         <v>46142</v>
       </c>
       <c r="G360" t="s">
@@ -18367,7 +18393,7 @@
         <v>1353</v>
       </c>
       <c r="I360">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J360">
         <v>83</v>
@@ -18378,7 +18404,7 @@
       <c r="L360" t="s">
         <v>1395</v>
       </c>
-      <c r="N360" s="1">
+      <c r="N360" s="2">
         <v>46225</v>
       </c>
       <c r="O360" t="s">
@@ -18404,7 +18430,7 @@
       <c r="E361" t="s">
         <v>961</v>
       </c>
-      <c r="F361" s="1">
+      <c r="F361" s="2">
         <v>46142</v>
       </c>
       <c r="G361" t="s">
@@ -18414,7 +18440,7 @@
         <v>1353</v>
       </c>
       <c r="I361">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J361">
         <v>83</v>
@@ -18425,7 +18451,7 @@
       <c r="L361" t="s">
         <v>1395</v>
       </c>
-      <c r="N361" s="1">
+      <c r="N361" s="2">
         <v>46225</v>
       </c>
       <c r="Q361" t="b">
@@ -18448,7 +18474,7 @@
       <c r="E362" t="s">
         <v>1175</v>
       </c>
-      <c r="F362" s="1">
+      <c r="F362" s="2">
         <v>46142</v>
       </c>
       <c r="G362" t="s">
@@ -18458,7 +18484,7 @@
         <v>1353</v>
       </c>
       <c r="I362">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K362" t="s">
         <v>1360</v>
@@ -18486,7 +18512,7 @@
       <c r="E363" t="s">
         <v>1176</v>
       </c>
-      <c r="F363" s="1">
+      <c r="F363" s="2">
         <v>46142</v>
       </c>
       <c r="G363" t="s">
@@ -18496,7 +18522,7 @@
         <v>1353</v>
       </c>
       <c r="I363">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K363" t="s">
         <v>1360</v>
@@ -18524,7 +18550,7 @@
       <c r="E364" t="s">
         <v>958</v>
       </c>
-      <c r="F364" s="1">
+      <c r="F364" s="2">
         <v>46142</v>
       </c>
       <c r="G364" t="s">
@@ -18534,7 +18560,7 @@
         <v>1353</v>
       </c>
       <c r="I364">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J364">
         <v>83</v>
@@ -18545,7 +18571,7 @@
       <c r="L364" t="s">
         <v>1395</v>
       </c>
-      <c r="N364" s="1">
+      <c r="N364" s="2">
         <v>46225</v>
       </c>
       <c r="Q364" t="b">
@@ -18568,7 +18594,7 @@
       <c r="E365" t="s">
         <v>1177</v>
       </c>
-      <c r="F365" s="1">
+      <c r="F365" s="2">
         <v>46142</v>
       </c>
       <c r="G365" t="s">
@@ -18578,7 +18604,7 @@
         <v>1353</v>
       </c>
       <c r="I365">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J365">
         <v>15</v>
@@ -18586,7 +18612,7 @@
       <c r="K365" t="s">
         <v>1359</v>
       </c>
-      <c r="N365" s="1">
+      <c r="N365" s="2">
         <v>46157</v>
       </c>
       <c r="Q365" t="b">
@@ -18609,7 +18635,7 @@
       <c r="E366" t="s">
         <v>1178</v>
       </c>
-      <c r="F366" s="1">
+      <c r="F366" s="2">
         <v>46148</v>
       </c>
       <c r="G366" t="s">
@@ -18619,7 +18645,7 @@
         <v>1353</v>
       </c>
       <c r="I366">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J366">
         <v>77</v>
@@ -18630,7 +18656,7 @@
       <c r="L366" t="s">
         <v>1388</v>
       </c>
-      <c r="N366" s="1">
+      <c r="N366" s="2">
         <v>46225</v>
       </c>
       <c r="Q366" t="b">
@@ -18653,7 +18679,7 @@
       <c r="E367" t="s">
         <v>1179</v>
       </c>
-      <c r="F367" s="1">
+      <c r="F367" s="2">
         <v>46148</v>
       </c>
       <c r="G367" t="s">
@@ -18663,7 +18689,7 @@
         <v>1353</v>
       </c>
       <c r="I367">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J367">
         <v>77</v>
@@ -18674,7 +18700,7 @@
       <c r="L367" t="s">
         <v>1388</v>
       </c>
-      <c r="N367" s="1">
+      <c r="N367" s="2">
         <v>46225</v>
       </c>
       <c r="Q367" t="b">
@@ -18697,7 +18723,7 @@
       <c r="E368" t="s">
         <v>1180</v>
       </c>
-      <c r="F368" s="1">
+      <c r="F368" s="2">
         <v>46148</v>
       </c>
       <c r="G368" t="s">
@@ -18707,7 +18733,7 @@
         <v>1353</v>
       </c>
       <c r="I368">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J368">
         <v>77</v>
@@ -18718,7 +18744,7 @@
       <c r="L368" t="s">
         <v>1395</v>
       </c>
-      <c r="N368" s="1">
+      <c r="N368" s="2">
         <v>46225</v>
       </c>
       <c r="Q368" t="b">
@@ -18741,7 +18767,7 @@
       <c r="E369" t="s">
         <v>1181</v>
       </c>
-      <c r="F369" s="1">
+      <c r="F369" s="2">
         <v>46148</v>
       </c>
       <c r="G369" t="s">
@@ -18751,7 +18777,7 @@
         <v>1353</v>
       </c>
       <c r="I369">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K369" t="s">
         <v>1360</v>
@@ -18779,7 +18805,7 @@
       <c r="E370" t="s">
         <v>1182</v>
       </c>
-      <c r="F370" s="1">
+      <c r="F370" s="2">
         <v>46148</v>
       </c>
       <c r="G370" t="s">
@@ -18789,7 +18815,7 @@
         <v>1353</v>
       </c>
       <c r="I370">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K370" t="s">
         <v>1360</v>
@@ -18817,7 +18843,7 @@
       <c r="E371" t="s">
         <v>1183</v>
       </c>
-      <c r="F371" s="1">
+      <c r="F371" s="2">
         <v>46148</v>
       </c>
       <c r="G371" t="s">
@@ -18827,7 +18853,7 @@
         <v>1353</v>
       </c>
       <c r="I371">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J371">
         <v>16</v>
@@ -18838,7 +18864,7 @@
       <c r="L371" t="s">
         <v>1441</v>
       </c>
-      <c r="N371" s="1">
+      <c r="N371" s="2">
         <v>46164</v>
       </c>
       <c r="Q371" t="b">
@@ -18861,7 +18887,7 @@
       <c r="E372" t="s">
         <v>1184</v>
       </c>
-      <c r="F372" s="1">
+      <c r="F372" s="2">
         <v>46148</v>
       </c>
       <c r="G372" t="s">
@@ -18879,7 +18905,7 @@
       <c r="L372" t="s">
         <v>1428</v>
       </c>
-      <c r="N372" s="1">
+      <c r="N372" s="2">
         <v>46113</v>
       </c>
       <c r="P372" t="s">
@@ -18905,7 +18931,7 @@
       <c r="E373" t="s">
         <v>1185</v>
       </c>
-      <c r="F373" s="1">
+      <c r="F373" s="2">
         <v>46149</v>
       </c>
       <c r="G373" t="s">
@@ -18915,7 +18941,7 @@
         <v>1353</v>
       </c>
       <c r="I373">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K373" t="s">
         <v>1356</v>
@@ -18943,7 +18969,7 @@
       <c r="E374" t="s">
         <v>1186</v>
       </c>
-      <c r="F374" s="1">
+      <c r="F374" s="2">
         <v>46149</v>
       </c>
       <c r="G374" t="s">
@@ -18953,7 +18979,7 @@
         <v>1353</v>
       </c>
       <c r="I374">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K374" t="s">
         <v>1356</v>
@@ -18981,7 +19007,7 @@
       <c r="E375" t="s">
         <v>1187</v>
       </c>
-      <c r="F375" s="1">
+      <c r="F375" s="2">
         <v>46154</v>
       </c>
       <c r="G375" t="s">
@@ -18991,7 +19017,7 @@
         <v>1353</v>
       </c>
       <c r="I375">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J375">
         <v>94</v>
@@ -18999,7 +19025,7 @@
       <c r="K375" t="s">
         <v>1360</v>
       </c>
-      <c r="N375" s="1">
+      <c r="N375" s="2">
         <v>46248</v>
       </c>
       <c r="Q375" t="b">
@@ -19022,7 +19048,7 @@
       <c r="E376" t="s">
         <v>1188</v>
       </c>
-      <c r="F376" s="1">
+      <c r="F376" s="2">
         <v>46154</v>
       </c>
       <c r="G376" t="s">
@@ -19032,7 +19058,7 @@
         <v>1353</v>
       </c>
       <c r="I376">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K376" t="s">
         <v>1360</v>
@@ -19060,7 +19086,7 @@
       <c r="E377" t="s">
         <v>1189</v>
       </c>
-      <c r="F377" s="1">
+      <c r="F377" s="2">
         <v>46154</v>
       </c>
       <c r="G377" t="s">
@@ -19072,7 +19098,7 @@
       <c r="K377" t="s">
         <v>1360</v>
       </c>
-      <c r="N377" s="1">
+      <c r="N377" s="2">
         <v>46176</v>
       </c>
       <c r="O377" t="s">
@@ -19101,7 +19127,7 @@
       <c r="E378" t="s">
         <v>1190</v>
       </c>
-      <c r="F378" s="1">
+      <c r="F378" s="2">
         <v>46154</v>
       </c>
       <c r="G378" t="s">
@@ -19111,7 +19137,7 @@
         <v>1353</v>
       </c>
       <c r="I378">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K378" t="s">
         <v>1360</v>
@@ -19139,7 +19165,7 @@
       <c r="E379" t="s">
         <v>1191</v>
       </c>
-      <c r="F379" s="1">
+      <c r="F379" s="2">
         <v>46154</v>
       </c>
       <c r="G379" t="s">
@@ -19149,7 +19175,7 @@
         <v>1353</v>
       </c>
       <c r="I379">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J379">
         <v>20</v>
@@ -19160,7 +19186,7 @@
       <c r="L379" t="s">
         <v>1442</v>
       </c>
-      <c r="N379" s="1">
+      <c r="N379" s="2">
         <v>46174</v>
       </c>
       <c r="Q379" t="b">
@@ -19183,7 +19209,7 @@
       <c r="E380" t="s">
         <v>1192</v>
       </c>
-      <c r="F380" s="1">
+      <c r="F380" s="2">
         <v>46154</v>
       </c>
       <c r="G380" t="s">
@@ -19193,7 +19219,7 @@
         <v>1353</v>
       </c>
       <c r="I380">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J380">
         <v>94</v>
@@ -19204,7 +19230,7 @@
       <c r="L380" t="s">
         <v>1443</v>
       </c>
-      <c r="N380" s="1">
+      <c r="N380" s="2">
         <v>46248</v>
       </c>
       <c r="Q380" t="b">
@@ -19227,7 +19253,7 @@
       <c r="E381" t="s">
         <v>1193</v>
       </c>
-      <c r="F381" s="1">
+      <c r="F381" s="2">
         <v>46154</v>
       </c>
       <c r="G381" t="s">
@@ -19237,7 +19263,7 @@
         <v>1353</v>
       </c>
       <c r="I381">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K381" t="s">
         <v>1360</v>
@@ -19265,7 +19291,7 @@
       <c r="E382" t="s">
         <v>1194</v>
       </c>
-      <c r="F382" s="1">
+      <c r="F382" s="2">
         <v>46154</v>
       </c>
       <c r="G382" t="s">
@@ -19275,7 +19301,7 @@
         <v>1353</v>
       </c>
       <c r="I382">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K382" t="s">
         <v>1360</v>
@@ -19303,7 +19329,7 @@
       <c r="E383" t="s">
         <v>1195</v>
       </c>
-      <c r="F383" s="1">
+      <c r="F383" s="2">
         <v>46154</v>
       </c>
       <c r="G383" t="s">
@@ -19313,7 +19339,7 @@
         <v>1353</v>
       </c>
       <c r="I383">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J383">
         <v>71</v>
@@ -19324,7 +19350,7 @@
       <c r="L383" t="s">
         <v>1444</v>
       </c>
-      <c r="N383" s="1">
+      <c r="N383" s="2">
         <v>46225</v>
       </c>
       <c r="Q383" t="b">
@@ -19347,7 +19373,7 @@
       <c r="E384" t="s">
         <v>1196</v>
       </c>
-      <c r="F384" s="1">
+      <c r="F384" s="2">
         <v>46164</v>
       </c>
       <c r="G384" t="s">
@@ -19357,7 +19383,7 @@
         <v>1353</v>
       </c>
       <c r="I384">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K384" t="s">
         <v>1357</v>
@@ -19385,7 +19411,7 @@
       <c r="E385" t="s">
         <v>1197</v>
       </c>
-      <c r="F385" s="1">
+      <c r="F385" s="2">
         <v>46164</v>
       </c>
       <c r="G385" t="s">
@@ -19395,7 +19421,7 @@
         <v>1353</v>
       </c>
       <c r="I385">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J385">
         <v>102</v>
@@ -19406,7 +19432,7 @@
       <c r="L385" t="s">
         <v>1445</v>
       </c>
-      <c r="N385" s="1">
+      <c r="N385" s="2">
         <v>46266</v>
       </c>
       <c r="P385" t="s">
@@ -19432,7 +19458,7 @@
       <c r="E386" t="s">
         <v>1198</v>
       </c>
-      <c r="F386" s="1">
+      <c r="F386" s="2">
         <v>46171</v>
       </c>
       <c r="G386" t="s">
@@ -19442,7 +19468,7 @@
         <v>1353</v>
       </c>
       <c r="I386">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K386" t="s">
         <v>1360</v>
@@ -19470,7 +19496,7 @@
       <c r="E387" t="s">
         <v>1199</v>
       </c>
-      <c r="F387" s="1">
+      <c r="F387" s="2">
         <v>46171</v>
       </c>
       <c r="G387" t="s">
@@ -19480,7 +19506,7 @@
         <v>1353</v>
       </c>
       <c r="I387">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K387" t="s">
         <v>1360</v>
@@ -19508,7 +19534,7 @@
       <c r="E388" t="s">
         <v>851</v>
       </c>
-      <c r="F388" s="1">
+      <c r="F388" s="2">
         <v>46171</v>
       </c>
       <c r="G388" t="s">
@@ -19518,7 +19544,7 @@
         <v>1353</v>
       </c>
       <c r="I388">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J388">
         <v>-85</v>
@@ -19529,7 +19555,7 @@
       <c r="L388" t="s">
         <v>1446</v>
       </c>
-      <c r="N388" s="1">
+      <c r="N388" s="2">
         <v>46086</v>
       </c>
       <c r="Q388" t="b">
@@ -19552,7 +19578,7 @@
       <c r="E389" t="s">
         <v>1200</v>
       </c>
-      <c r="F389" s="1">
+      <c r="F389" s="2">
         <v>46171</v>
       </c>
       <c r="G389" t="s">
@@ -19562,7 +19588,7 @@
         <v>1353</v>
       </c>
       <c r="I389">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K389" t="s">
         <v>1361</v>
@@ -19590,7 +19616,7 @@
       <c r="E390" t="s">
         <v>1201</v>
       </c>
-      <c r="F390" s="1">
+      <c r="F390" s="2">
         <v>46171</v>
       </c>
       <c r="G390" t="s">
@@ -19608,7 +19634,7 @@
       <c r="L390" t="s">
         <v>1447</v>
       </c>
-      <c r="N390" s="1">
+      <c r="N390" s="2">
         <v>46191</v>
       </c>
       <c r="P390" t="s">
@@ -19634,7 +19660,7 @@
       <c r="E391" t="s">
         <v>1202</v>
       </c>
-      <c r="F391" s="1">
+      <c r="F391" s="2">
         <v>46171</v>
       </c>
       <c r="G391" t="s">
@@ -19672,7 +19698,7 @@
       <c r="E392" t="s">
         <v>1203</v>
       </c>
-      <c r="F392" s="1">
+      <c r="F392" s="2">
         <v>46171</v>
       </c>
       <c r="G392" t="s">
@@ -19687,7 +19713,7 @@
       <c r="L392" t="s">
         <v>1439</v>
       </c>
-      <c r="N392" s="1">
+      <c r="N392" s="2">
         <v>46176</v>
       </c>
       <c r="Q392" t="b">
@@ -19710,7 +19736,7 @@
       <c r="E393" t="s">
         <v>1204</v>
       </c>
-      <c r="F393" s="1">
+      <c r="F393" s="2">
         <v>46171</v>
       </c>
       <c r="G393" t="s">
@@ -19720,7 +19746,7 @@
         <v>1353</v>
       </c>
       <c r="I393">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J393">
         <v>20</v>
@@ -19731,7 +19757,7 @@
       <c r="L393" t="s">
         <v>1388</v>
       </c>
-      <c r="N393" s="1">
+      <c r="N393" s="2">
         <v>46191</v>
       </c>
       <c r="Q393" t="b">
@@ -19754,7 +19780,7 @@
       <c r="E394" t="s">
         <v>1205</v>
       </c>
-      <c r="F394" s="1">
+      <c r="F394" s="2">
         <v>46171</v>
       </c>
       <c r="G394" t="s">
@@ -19772,7 +19798,7 @@
       <c r="L394" t="s">
         <v>1448</v>
       </c>
-      <c r="N394" s="1">
+      <c r="N394" s="2">
         <v>46241</v>
       </c>
       <c r="P394" t="s">
@@ -19798,7 +19824,7 @@
       <c r="E395" t="s">
         <v>1206</v>
       </c>
-      <c r="F395" s="1">
+      <c r="F395" s="2">
         <v>46171</v>
       </c>
       <c r="G395" t="s">
@@ -19816,7 +19842,7 @@
       <c r="L395" t="s">
         <v>1449</v>
       </c>
-      <c r="N395" s="1">
+      <c r="N395" s="2">
         <v>46191</v>
       </c>
       <c r="P395" t="s">
@@ -19842,7 +19868,7 @@
       <c r="E396" t="s">
         <v>1207</v>
       </c>
-      <c r="F396" s="1">
+      <c r="F396" s="2">
         <v>46171</v>
       </c>
       <c r="G396" t="s">
@@ -19854,7 +19880,7 @@
       <c r="J396">
         <v>20</v>
       </c>
-      <c r="N396" s="1">
+      <c r="N396" s="2">
         <v>46191</v>
       </c>
       <c r="P396" t="s">
@@ -19880,7 +19906,7 @@
       <c r="E397" t="s">
         <v>1208</v>
       </c>
-      <c r="F397" s="1">
+      <c r="F397" s="2">
         <v>46171</v>
       </c>
       <c r="G397" t="s">
@@ -19898,7 +19924,7 @@
       <c r="L397" t="s">
         <v>1448</v>
       </c>
-      <c r="N397" s="1">
+      <c r="N397" s="2">
         <v>46241</v>
       </c>
       <c r="P397" t="s">
@@ -19924,7 +19950,7 @@
       <c r="E398" t="s">
         <v>1209</v>
       </c>
-      <c r="F398" s="1">
+      <c r="F398" s="2">
         <v>46171</v>
       </c>
       <c r="G398" t="s">
@@ -19942,7 +19968,7 @@
       <c r="L398" t="s">
         <v>1449</v>
       </c>
-      <c r="N398" s="1">
+      <c r="N398" s="2">
         <v>46191</v>
       </c>
       <c r="P398" t="s">
@@ -19968,7 +19994,7 @@
       <c r="E399" t="s">
         <v>987</v>
       </c>
-      <c r="F399" s="1">
+      <c r="F399" s="2">
         <v>46163</v>
       </c>
       <c r="G399" t="s">
@@ -19983,7 +20009,7 @@
       <c r="L399" t="s">
         <v>1450</v>
       </c>
-      <c r="N399" s="1">
+      <c r="N399" s="2">
         <v>46171</v>
       </c>
       <c r="Q399" t="b">
@@ -20006,7 +20032,7 @@
       <c r="E400" t="s">
         <v>1210</v>
       </c>
-      <c r="F400" s="1">
+      <c r="F400" s="2">
         <v>46171</v>
       </c>
       <c r="G400" t="s">
@@ -20016,7 +20042,7 @@
         <v>1353</v>
       </c>
       <c r="I400">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K400" t="s">
         <v>1360</v>
@@ -20044,7 +20070,7 @@
       <c r="E401" t="s">
         <v>1211</v>
       </c>
-      <c r="F401" s="1">
+      <c r="F401" s="2">
         <v>46171</v>
       </c>
       <c r="G401" t="s">
@@ -20056,7 +20082,7 @@
       <c r="J401">
         <v>40</v>
       </c>
-      <c r="N401" s="1">
+      <c r="N401" s="2">
         <v>46211</v>
       </c>
       <c r="P401" t="s">
@@ -20082,7 +20108,7 @@
       <c r="E402" t="s">
         <v>1212</v>
       </c>
-      <c r="F402" s="1">
+      <c r="F402" s="2">
         <v>46171</v>
       </c>
       <c r="G402" t="s">
@@ -20092,7 +20118,7 @@
         <v>1353</v>
       </c>
       <c r="I402">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K402" t="s">
         <v>1360</v>
@@ -20120,7 +20146,7 @@
       <c r="E403" t="s">
         <v>1213</v>
       </c>
-      <c r="F403" s="1">
+      <c r="F403" s="2">
         <v>46171</v>
       </c>
       <c r="G403" t="s">
@@ -20130,7 +20156,7 @@
         <v>1353</v>
       </c>
       <c r="I403">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J403">
         <v>83</v>
@@ -20141,7 +20167,7 @@
       <c r="L403" t="s">
         <v>1451</v>
       </c>
-      <c r="N403" s="1">
+      <c r="N403" s="2">
         <v>46254</v>
       </c>
       <c r="Q403" t="b">
@@ -20164,7 +20190,7 @@
       <c r="E404" t="s">
         <v>1214</v>
       </c>
-      <c r="F404" s="1">
+      <c r="F404" s="2">
         <v>46171</v>
       </c>
       <c r="G404" t="s">
@@ -20174,7 +20200,7 @@
         <v>1353</v>
       </c>
       <c r="I404">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K404" t="s">
         <v>1360</v>
@@ -20202,7 +20228,7 @@
       <c r="E405" t="s">
         <v>1215</v>
       </c>
-      <c r="F405" s="1">
+      <c r="F405" s="2">
         <v>46183</v>
       </c>
       <c r="G405" t="s">
@@ -20234,7 +20260,7 @@
       <c r="E406" t="s">
         <v>1216</v>
       </c>
-      <c r="F406" s="1">
+      <c r="F406" s="2">
         <v>46183</v>
       </c>
       <c r="G406" t="s">
@@ -20244,7 +20270,7 @@
         <v>1353</v>
       </c>
       <c r="I406">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q406" t="b">
         <v>1</v>
@@ -20266,7 +20292,7 @@
       <c r="E407" t="s">
         <v>1217</v>
       </c>
-      <c r="F407" s="1">
+      <c r="F407" s="2">
         <v>46183</v>
       </c>
       <c r="G407" t="s">
@@ -20276,7 +20302,7 @@
         <v>1353</v>
       </c>
       <c r="I407">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q407" t="b">
         <v>1</v>
@@ -20298,7 +20324,7 @@
       <c r="E408" t="s">
         <v>1218</v>
       </c>
-      <c r="F408" s="1">
+      <c r="F408" s="2">
         <v>46183</v>
       </c>
       <c r="G408" t="s">
@@ -20308,7 +20334,7 @@
         <v>1353</v>
       </c>
       <c r="I408">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q408" t="b">
         <v>1</v>
@@ -20330,7 +20356,7 @@
       <c r="E409" t="s">
         <v>1219</v>
       </c>
-      <c r="F409" s="1">
+      <c r="F409" s="2">
         <v>46183</v>
       </c>
       <c r="G409" t="s">
@@ -20340,7 +20366,7 @@
         <v>1353</v>
       </c>
       <c r="I409">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q409" t="b">
         <v>1</v>
@@ -20362,7 +20388,7 @@
       <c r="E410" t="s">
         <v>1220</v>
       </c>
-      <c r="F410" s="1">
+      <c r="F410" s="2">
         <v>46183</v>
       </c>
       <c r="G410" t="s">
@@ -20372,7 +20398,7 @@
         <v>1353</v>
       </c>
       <c r="I410">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q410" t="b">
         <v>1</v>
@@ -20394,7 +20420,7 @@
       <c r="E411" t="s">
         <v>1221</v>
       </c>
-      <c r="F411" s="1">
+      <c r="F411" s="2">
         <v>46188</v>
       </c>
       <c r="G411" t="s">
@@ -20404,7 +20430,7 @@
         <v>1353</v>
       </c>
       <c r="I411">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q411" t="b">
         <v>1</v>
@@ -20426,7 +20452,7 @@
       <c r="E412" t="s">
         <v>1222</v>
       </c>
-      <c r="F412" s="1">
+      <c r="F412" s="2">
         <v>46188</v>
       </c>
       <c r="G412" t="s">
@@ -20436,7 +20462,7 @@
         <v>1353</v>
       </c>
       <c r="I412">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q412" t="b">
         <v>1</v>
@@ -20458,7 +20484,7 @@
       <c r="E413" t="s">
         <v>1223</v>
       </c>
-      <c r="F413" s="1">
+      <c r="F413" s="2">
         <v>46188</v>
       </c>
       <c r="G413" t="s">
@@ -20468,7 +20494,7 @@
         <v>1353</v>
       </c>
       <c r="I413">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q413" t="b">
         <v>1</v>
@@ -20490,7 +20516,7 @@
       <c r="E414" t="s">
         <v>1224</v>
       </c>
-      <c r="F414" s="1">
+      <c r="F414" s="2">
         <v>46188</v>
       </c>
       <c r="G414" t="s">
@@ -20519,7 +20545,7 @@
       <c r="E415" t="s">
         <v>1060</v>
       </c>
-      <c r="F415" s="1">
+      <c r="F415" s="2">
         <v>46188</v>
       </c>
       <c r="G415" t="s">
@@ -20548,7 +20574,7 @@
       <c r="E416" t="s">
         <v>1225</v>
       </c>
-      <c r="F416" s="1">
+      <c r="F416" s="2">
         <v>46188</v>
       </c>
       <c r="G416" t="s">
@@ -20558,7 +20584,7 @@
         <v>1353</v>
       </c>
       <c r="I416">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q416" t="b">
         <v>1</v>
@@ -20580,7 +20606,7 @@
       <c r="E417" t="s">
         <v>1226</v>
       </c>
-      <c r="F417" s="1">
+      <c r="F417" s="2">
         <v>46188</v>
       </c>
       <c r="G417" t="s">
@@ -20609,7 +20635,7 @@
       <c r="E418" t="s">
         <v>1227</v>
       </c>
-      <c r="F418" s="1">
+      <c r="F418" s="2">
         <v>46188</v>
       </c>
       <c r="G418" t="s">
@@ -20638,7 +20664,7 @@
       <c r="E419" t="s">
         <v>1228</v>
       </c>
-      <c r="F419" s="1">
+      <c r="F419" s="2">
         <v>46188</v>
       </c>
       <c r="G419" t="s">
@@ -20648,7 +20674,7 @@
         <v>1353</v>
       </c>
       <c r="I419">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q419" t="b">
         <v>1</v>
@@ -20670,7 +20696,7 @@
       <c r="E420" t="s">
         <v>1229</v>
       </c>
-      <c r="F420" s="1">
+      <c r="F420" s="2">
         <v>46188</v>
       </c>
       <c r="G420" t="s">
@@ -20680,7 +20706,7 @@
         <v>1353</v>
       </c>
       <c r="I420">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q420" t="b">
         <v>1</v>
@@ -20702,7 +20728,7 @@
       <c r="E421" t="s">
         <v>1230</v>
       </c>
-      <c r="F421" s="1">
+      <c r="F421" s="2">
         <v>46188</v>
       </c>
       <c r="G421" t="s">
@@ -20712,7 +20738,7 @@
         <v>1353</v>
       </c>
       <c r="I421">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q421" t="b">
         <v>1</v>
@@ -20734,7 +20760,7 @@
       <c r="E422" t="s">
         <v>1231</v>
       </c>
-      <c r="F422" s="1">
+      <c r="F422" s="2">
         <v>46188</v>
       </c>
       <c r="G422" t="s">
@@ -20744,7 +20770,7 @@
         <v>1353</v>
       </c>
       <c r="I422">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q422" t="b">
         <v>1</v>
@@ -20766,7 +20792,7 @@
       <c r="E423" t="s">
         <v>1232</v>
       </c>
-      <c r="F423" s="1">
+      <c r="F423" s="2">
         <v>46188</v>
       </c>
       <c r="G423" t="s">
@@ -20776,7 +20802,7 @@
         <v>1353</v>
       </c>
       <c r="I423">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q423" t="b">
         <v>1</v>
@@ -20798,7 +20824,7 @@
       <c r="E424" t="s">
         <v>1233</v>
       </c>
-      <c r="F424" s="1">
+      <c r="F424" s="2">
         <v>46188</v>
       </c>
       <c r="G424" t="s">
@@ -20808,7 +20834,7 @@
         <v>1353</v>
       </c>
       <c r="I424">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q424" t="b">
         <v>1</v>
@@ -20830,7 +20856,7 @@
       <c r="E425" t="s">
         <v>1234</v>
       </c>
-      <c r="F425" s="1">
+      <c r="F425" s="2">
         <v>46188</v>
       </c>
       <c r="G425" t="s">
@@ -20840,7 +20866,7 @@
         <v>1353</v>
       </c>
       <c r="I425">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q425" t="b">
         <v>1</v>
@@ -20862,7 +20888,7 @@
       <c r="E426" t="s">
         <v>1235</v>
       </c>
-      <c r="F426" s="1">
+      <c r="F426" s="2">
         <v>46188</v>
       </c>
       <c r="G426" t="s">
@@ -20872,7 +20898,7 @@
         <v>1353</v>
       </c>
       <c r="I426">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q426" t="b">
         <v>1</v>
@@ -20894,7 +20920,7 @@
       <c r="E427" t="s">
         <v>1236</v>
       </c>
-      <c r="F427" s="1">
+      <c r="F427" s="2">
         <v>46188</v>
       </c>
       <c r="G427" t="s">
@@ -20904,7 +20930,7 @@
         <v>1353</v>
       </c>
       <c r="I427">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q427" t="b">
         <v>1</v>
@@ -20926,7 +20952,7 @@
       <c r="E428" t="s">
         <v>1237</v>
       </c>
-      <c r="F428" s="1">
+      <c r="F428" s="2">
         <v>46188</v>
       </c>
       <c r="G428" t="s">
@@ -20955,7 +20981,7 @@
       <c r="E429" t="s">
         <v>1238</v>
       </c>
-      <c r="F429" s="1">
+      <c r="F429" s="2">
         <v>46188</v>
       </c>
       <c r="G429" t="s">
@@ -20984,7 +21010,7 @@
       <c r="E430" t="s">
         <v>1239</v>
       </c>
-      <c r="F430" s="1">
+      <c r="F430" s="2">
         <v>46188</v>
       </c>
       <c r="G430" t="s">
@@ -20994,7 +21020,7 @@
         <v>1353</v>
       </c>
       <c r="I430">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q430" t="b">
         <v>1</v>
@@ -21016,7 +21042,7 @@
       <c r="E431" t="s">
         <v>1240</v>
       </c>
-      <c r="F431" s="1">
+      <c r="F431" s="2">
         <v>46188</v>
       </c>
       <c r="G431" t="s">
@@ -21026,7 +21052,7 @@
         <v>1353</v>
       </c>
       <c r="I431">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q431" t="b">
         <v>1</v>
@@ -21048,7 +21074,7 @@
       <c r="E432" t="s">
         <v>1241</v>
       </c>
-      <c r="F432" s="1">
+      <c r="F432" s="2">
         <v>46188</v>
       </c>
       <c r="G432" t="s">
@@ -21058,7 +21084,7 @@
         <v>1353</v>
       </c>
       <c r="I432">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q432" t="b">
         <v>1</v>
@@ -21080,7 +21106,7 @@
       <c r="E433" t="s">
         <v>1242</v>
       </c>
-      <c r="F433" s="1">
+      <c r="F433" s="2">
         <v>46188</v>
       </c>
       <c r="G433" t="s">
@@ -21090,7 +21116,7 @@
         <v>1353</v>
       </c>
       <c r="I433">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q433" t="b">
         <v>1</v>
@@ -21112,7 +21138,7 @@
       <c r="E434" t="s">
         <v>1243</v>
       </c>
-      <c r="F434" s="1">
+      <c r="F434" s="2">
         <v>46188</v>
       </c>
       <c r="G434" t="s">
@@ -21122,7 +21148,7 @@
         <v>1353</v>
       </c>
       <c r="I434">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q434" t="b">
         <v>1</v>
@@ -21144,7 +21170,7 @@
       <c r="E435" t="s">
         <v>856</v>
       </c>
-      <c r="F435" s="1">
+      <c r="F435" s="2">
         <v>46188</v>
       </c>
       <c r="G435" t="s">
@@ -21154,7 +21180,7 @@
         <v>1353</v>
       </c>
       <c r="I435">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q435" t="b">
         <v>1</v>
@@ -21176,7 +21202,7 @@
       <c r="E436" t="s">
         <v>1244</v>
       </c>
-      <c r="F436" s="1">
+      <c r="F436" s="2">
         <v>46188</v>
       </c>
       <c r="G436" t="s">
@@ -21186,7 +21212,7 @@
         <v>1353</v>
       </c>
       <c r="I436">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q436" t="b">
         <v>1</v>
@@ -21208,7 +21234,7 @@
       <c r="E437" t="s">
         <v>1245</v>
       </c>
-      <c r="F437" s="1">
+      <c r="F437" s="2">
         <v>46188</v>
       </c>
       <c r="G437" t="s">
@@ -21218,7 +21244,7 @@
         <v>1355</v>
       </c>
       <c r="I437">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q437" t="b">
         <v>1</v>
@@ -21240,7 +21266,7 @@
       <c r="E438" t="s">
         <v>1246</v>
       </c>
-      <c r="F438" s="1">
+      <c r="F438" s="2">
         <v>46188</v>
       </c>
       <c r="G438" t="s">
@@ -21250,7 +21276,7 @@
         <v>1355</v>
       </c>
       <c r="I438">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q438" t="b">
         <v>1</v>
@@ -21272,7 +21298,7 @@
       <c r="E439" t="s">
         <v>1247</v>
       </c>
-      <c r="F439" s="1">
+      <c r="F439" s="2">
         <v>46196</v>
       </c>
       <c r="G439" t="s">
@@ -21282,7 +21308,7 @@
         <v>1353</v>
       </c>
       <c r="I439">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q439" t="b">
         <v>1</v>
@@ -21304,7 +21330,7 @@
       <c r="E440" t="s">
         <v>1248</v>
       </c>
-      <c r="F440" s="1">
+      <c r="F440" s="2">
         <v>46196</v>
       </c>
       <c r="G440" t="s">
@@ -21314,7 +21340,7 @@
         <v>1353</v>
       </c>
       <c r="I440">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q440" t="b">
         <v>1</v>
@@ -21336,7 +21362,7 @@
       <c r="E441" t="s">
         <v>1249</v>
       </c>
-      <c r="F441" s="1">
+      <c r="F441" s="2">
         <v>46203</v>
       </c>
       <c r="G441" t="s">
@@ -21346,7 +21372,7 @@
         <v>1353</v>
       </c>
       <c r="I441">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q441" t="b">
         <v>1</v>
@@ -21368,7 +21394,7 @@
       <c r="E442" t="s">
         <v>1250</v>
       </c>
-      <c r="F442" s="1">
+      <c r="F442" s="2">
         <v>46203</v>
       </c>
       <c r="G442" t="s">
@@ -21397,7 +21423,7 @@
       <c r="E443" t="s">
         <v>1251</v>
       </c>
-      <c r="F443" s="1">
+      <c r="F443" s="2">
         <v>46205</v>
       </c>
       <c r="G443" t="s">
@@ -21407,7 +21433,7 @@
         <v>1353</v>
       </c>
       <c r="I443">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q443" t="b">
         <v>1</v>
@@ -21429,7 +21455,7 @@
       <c r="E444" t="s">
         <v>1252</v>
       </c>
-      <c r="F444" s="1">
+      <c r="F444" s="2">
         <v>46205</v>
       </c>
       <c r="G444" t="s">
@@ -21458,7 +21484,7 @@
       <c r="E445" t="s">
         <v>1253</v>
       </c>
-      <c r="F445" s="1">
+      <c r="F445" s="2">
         <v>46205</v>
       </c>
       <c r="G445" t="s">
@@ -21487,7 +21513,7 @@
       <c r="E446" t="s">
         <v>1254</v>
       </c>
-      <c r="F446" s="1">
+      <c r="F446" s="2">
         <v>46211</v>
       </c>
       <c r="G446" t="s">
@@ -21497,7 +21523,7 @@
         <v>1353</v>
       </c>
       <c r="I446">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q446" t="b">
         <v>1</v>
@@ -21519,7 +21545,7 @@
       <c r="E447" t="s">
         <v>1255</v>
       </c>
-      <c r="F447" s="1">
+      <c r="F447" s="2">
         <v>46211</v>
       </c>
       <c r="G447" t="s">
@@ -21529,7 +21555,7 @@
         <v>1353</v>
       </c>
       <c r="I447">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q447" t="b">
         <v>1</v>
@@ -21551,7 +21577,7 @@
       <c r="E448" t="s">
         <v>1256</v>
       </c>
-      <c r="F448" s="1">
+      <c r="F448" s="2">
         <v>46226</v>
       </c>
       <c r="G448" t="s">
@@ -21561,7 +21587,7 @@
         <v>1353</v>
       </c>
       <c r="I448">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q448" t="b">
         <v>1</v>
@@ -21583,7 +21609,7 @@
       <c r="E449" t="s">
         <v>1257</v>
       </c>
-      <c r="F449" s="1">
+      <c r="F449" s="2">
         <v>46226</v>
       </c>
       <c r="G449" t="s">
@@ -21593,7 +21619,7 @@
         <v>1353</v>
       </c>
       <c r="I449">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q449" t="b">
         <v>1</v>
@@ -21615,7 +21641,7 @@
       <c r="E450" t="s">
         <v>1258</v>
       </c>
-      <c r="F450" s="1">
+      <c r="F450" s="2">
         <v>46226</v>
       </c>
       <c r="G450" t="s">
@@ -21625,7 +21651,7 @@
         <v>1353</v>
       </c>
       <c r="I450">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q450" t="b">
         <v>1</v>
@@ -21647,7 +21673,7 @@
       <c r="E451" t="s">
         <v>1035</v>
       </c>
-      <c r="F451" s="1">
+      <c r="F451" s="2">
         <v>46230</v>
       </c>
       <c r="G451" t="s">
@@ -21657,7 +21683,7 @@
         <v>1353</v>
       </c>
       <c r="I451">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q451" t="b">
         <v>1</v>
@@ -21679,7 +21705,7 @@
       <c r="E452" t="s">
         <v>1259</v>
       </c>
-      <c r="F452" s="1">
+      <c r="F452" s="2">
         <v>46230</v>
       </c>
       <c r="G452" t="s">
@@ -21689,7 +21715,7 @@
         <v>1353</v>
       </c>
       <c r="I452">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q452" t="b">
         <v>1</v>
@@ -21711,7 +21737,7 @@
       <c r="E453" t="s">
         <v>1260</v>
       </c>
-      <c r="F453" s="1">
+      <c r="F453" s="2">
         <v>46230</v>
       </c>
       <c r="G453" t="s">
@@ -21721,7 +21747,7 @@
         <v>1353</v>
       </c>
       <c r="I453">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q453" t="b">
         <v>1</v>
@@ -21743,7 +21769,7 @@
       <c r="E454" t="s">
         <v>1261</v>
       </c>
-      <c r="F454" s="1">
+      <c r="F454" s="2">
         <v>46230</v>
       </c>
       <c r="G454" t="s">
@@ -21753,7 +21779,7 @@
         <v>1353</v>
       </c>
       <c r="I454">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q454" t="b">
         <v>1</v>
@@ -21775,7 +21801,7 @@
       <c r="E455" t="s">
         <v>1262</v>
       </c>
-      <c r="F455" s="1">
+      <c r="F455" s="2">
         <v>46230</v>
       </c>
       <c r="G455" t="s">
@@ -21785,7 +21811,7 @@
         <v>1353</v>
       </c>
       <c r="I455">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q455" t="b">
         <v>1</v>
@@ -21807,7 +21833,7 @@
       <c r="E456" t="s">
         <v>1263</v>
       </c>
-      <c r="F456" s="1">
+      <c r="F456" s="2">
         <v>46230</v>
       </c>
       <c r="G456" t="s">
@@ -21817,7 +21843,7 @@
         <v>1353</v>
       </c>
       <c r="I456">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q456" t="b">
         <v>1</v>
@@ -21839,7 +21865,7 @@
       <c r="E457" t="s">
         <v>1264</v>
       </c>
-      <c r="F457" s="1">
+      <c r="F457" s="2">
         <v>46230</v>
       </c>
       <c r="G457" t="s">
@@ -21849,7 +21875,7 @@
         <v>1353</v>
       </c>
       <c r="I457">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q457" t="b">
         <v>1</v>
@@ -21871,7 +21897,7 @@
       <c r="E458" t="s">
         <v>1202</v>
       </c>
-      <c r="F458" s="1">
+      <c r="F458" s="2">
         <v>46231</v>
       </c>
       <c r="G458" t="s">
@@ -21881,7 +21907,7 @@
         <v>1353</v>
       </c>
       <c r="I458">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q458" t="b">
         <v>1</v>
@@ -21903,7 +21929,7 @@
       <c r="E459" t="s">
         <v>1265</v>
       </c>
-      <c r="F459" s="1">
+      <c r="F459" s="2">
         <v>46233</v>
       </c>
       <c r="G459" t="s">
@@ -21913,7 +21939,7 @@
         <v>1353</v>
       </c>
       <c r="I459">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q459" t="b">
         <v>1</v>
@@ -21935,7 +21961,7 @@
       <c r="E460" t="s">
         <v>1266</v>
       </c>
-      <c r="F460" s="1">
+      <c r="F460" s